--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1368"/>
+  <dimension ref="A1:F1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44230</v>
       </c>
       <c r="B3" t="n">
-        <v>6.907310962677002</v>
+        <v>6.907310485839844</v>
       </c>
       <c r="C3" t="n">
-        <v>7.020683760016685</v>
+        <v>7.020683275352985</v>
       </c>
       <c r="D3" t="n">
-        <v>6.657472247238046</v>
+        <v>6.657471787648176</v>
       </c>
       <c r="E3" t="n">
-        <v>6.953499639579957</v>
+        <v>6.953499159554224</v>
       </c>
       <c r="F3" t="n">
         <v>3966477</v>
@@ -512,16 +512,16 @@
         <v>44232</v>
       </c>
       <c r="B5" t="n">
-        <v>6.823331356048584</v>
+        <v>6.823330879211426</v>
       </c>
       <c r="C5" t="n">
-        <v>6.909409992235542</v>
+        <v>6.909409509382922</v>
       </c>
       <c r="D5" t="n">
-        <v>6.699461247702325</v>
+        <v>6.699460779521623</v>
       </c>
       <c r="E5" t="n">
-        <v>6.873718632603384</v>
+        <v>6.873718152244995</v>
       </c>
       <c r="F5" t="n">
         <v>4402737</v>
@@ -532,16 +532,16 @@
         <v>44235</v>
       </c>
       <c r="B6" t="n">
-        <v>7.211735725402832</v>
+        <v>7.21173620223999</v>
       </c>
       <c r="C6" t="n">
-        <v>7.619035766065515</v>
+        <v>7.619036269833193</v>
       </c>
       <c r="D6" t="n">
-        <v>6.827529615229921</v>
+        <v>6.82753006666352</v>
       </c>
       <c r="E6" t="n">
-        <v>6.85482295876889</v>
+        <v>6.854823412007115</v>
       </c>
       <c r="F6" t="n">
         <v>3162478</v>
@@ -552,16 +552,16 @@
         <v>44236</v>
       </c>
       <c r="B7" t="n">
-        <v>7.119358539581299</v>
+        <v>7.119358062744141</v>
       </c>
       <c r="C7" t="n">
-        <v>7.367097937617529</v>
+        <v>7.367097444187393</v>
       </c>
       <c r="D7" t="n">
-        <v>6.953499173999</v>
+        <v>6.953498708270694</v>
       </c>
       <c r="E7" t="n">
-        <v>7.266322575504579</v>
+        <v>7.266322088824129</v>
       </c>
       <c r="F7" t="n">
         <v>1374461</v>
@@ -592,16 +592,16 @@
         <v>44238</v>
       </c>
       <c r="B9" t="n">
-        <v>6.963995933532715</v>
+        <v>6.963996887207031</v>
       </c>
       <c r="C9" t="n">
-        <v>7.05847257428985</v>
+        <v>7.058473540902132</v>
       </c>
       <c r="D9" t="n">
-        <v>6.85062315282968</v>
+        <v>6.850624090978325</v>
       </c>
       <c r="E9" t="n">
-        <v>6.928304577736804</v>
+        <v>6.928305526523419</v>
       </c>
       <c r="F9" t="n">
         <v>1655030</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029080390930176</v>
+        <v>7.029079914093018</v>
       </c>
       <c r="C10" t="n">
-        <v>7.194939754112628</v>
+        <v>7.19493926602394</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913608302177867</v>
+        <v>6.913607833174078</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949299660305043</v>
+        <v>6.949299188880033</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -632,16 +632,16 @@
         <v>44244</v>
       </c>
       <c r="B11" t="n">
-        <v>7.274720191955566</v>
+        <v>7.274720668792725</v>
       </c>
       <c r="C11" t="n">
-        <v>7.388092163706458</v>
+        <v>7.388092647974826</v>
       </c>
       <c r="D11" t="n">
-        <v>7.113059436567523</v>
+        <v>7.11305990280828</v>
       </c>
       <c r="E11" t="n">
-        <v>7.117258849481164</v>
+        <v>7.11725931599718</v>
       </c>
       <c r="F11" t="n">
         <v>2613098</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.222233772277832</v>
+        <v>7.222232341766357</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379695135793175</v>
+        <v>7.379693674093248</v>
       </c>
       <c r="D12" t="n">
-        <v>7.138254432522623</v>
+        <v>7.138253018644978</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287317780882985</v>
+        <v>7.287316337480287</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.30621337890625</v>
+        <v>7.306212902069092</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724010745681502</v>
+        <v>7.724010241576962</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050075153474859</v>
+        <v>7.050074693354461</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054274566636445</v>
+        <v>7.054274106241974</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.30621337890625</v>
+        <v>7.306212902069092</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480470759734867</v>
+        <v>7.480470271524869</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243227864044258</v>
+        <v>7.243227391317824</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308311867795231</v>
+        <v>7.308311390821116</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -732,16 +732,16 @@
         <v>44251</v>
       </c>
       <c r="B16" t="n">
-        <v>7.327208518981934</v>
+        <v>7.327207565307617</v>
       </c>
       <c r="C16" t="n">
-        <v>7.556052604266855</v>
+        <v>7.556051620807289</v>
       </c>
       <c r="D16" t="n">
-        <v>7.108861749639317</v>
+        <v>7.108860824383968</v>
       </c>
       <c r="E16" t="n">
-        <v>7.451078633049225</v>
+        <v>7.451077663252569</v>
       </c>
       <c r="F16" t="n">
         <v>1445414</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138254642486572</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400690302893193</v>
+        <v>7.40069079726115</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945101447895325</v>
+        <v>6.945101911829834</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360800341244324</v>
+        <v>7.360800832947622</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -812,16 +812,16 @@
         <v>44257</v>
       </c>
       <c r="B20" t="n">
-        <v>7.178143501281738</v>
+        <v>7.178143978118896</v>
       </c>
       <c r="C20" t="n">
-        <v>7.178143501281738</v>
+        <v>7.178143978118896</v>
       </c>
       <c r="D20" t="n">
-        <v>6.718356084859394</v>
+        <v>6.718356531153318</v>
       </c>
       <c r="E20" t="n">
-        <v>7.003886129168523</v>
+        <v>7.003886594429932</v>
       </c>
       <c r="F20" t="n">
         <v>1173360</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138254642486572</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233502264944</v>
+        <v>7.222233984711942</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966096890895136</v>
+        <v>6.966097356232146</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117259534444174</v>
+        <v>7.117260009878886</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -872,16 +872,16 @@
         <v>44260</v>
       </c>
       <c r="B23" t="n">
-        <v>7.016483783721924</v>
+        <v>7.016482830047607</v>
       </c>
       <c r="C23" t="n">
-        <v>7.176045245164364</v>
+        <v>7.176044269802593</v>
       </c>
       <c r="D23" t="n">
-        <v>7.014383671280806</v>
+        <v>7.014382717891935</v>
       </c>
       <c r="E23" t="n">
-        <v>7.117259144498113</v>
+        <v>7.117258177126498</v>
       </c>
       <c r="F23" t="n">
         <v>1309995</v>
@@ -912,16 +912,16 @@
         <v>44264</v>
       </c>
       <c r="B25" t="n">
-        <v>6.42442798614502</v>
+        <v>6.424428462982178</v>
       </c>
       <c r="C25" t="n">
-        <v>6.819131399595795</v>
+        <v>6.819131905728831</v>
       </c>
       <c r="D25" t="n">
-        <v>6.367742000113356</v>
+        <v>6.36774247274314</v>
       </c>
       <c r="E25" t="n">
-        <v>6.754047399508202</v>
+        <v>6.75404790081054</v>
       </c>
       <c r="F25" t="n">
         <v>2514170</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033279895782471</v>
+        <v>7.033280372619629</v>
       </c>
       <c r="C29" t="n">
-        <v>7.127756543943293</v>
+        <v>7.12775702718571</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1012,16 +1012,16 @@
         <v>44271</v>
       </c>
       <c r="B30" t="n">
-        <v>7.390191555023193</v>
+        <v>7.390192031860352</v>
       </c>
       <c r="C30" t="n">
-        <v>7.425883723946737</v>
+        <v>7.42588420308686</v>
       </c>
       <c r="D30" t="n">
-        <v>6.970294095405131</v>
+        <v>6.970294545149255</v>
       </c>
       <c r="E30" t="n">
-        <v>6.970294095405131</v>
+        <v>6.970294545149255</v>
       </c>
       <c r="F30" t="n">
         <v>4282725</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.516162395477295</v>
+        <v>7.516163349151611</v>
       </c>
       <c r="C33" t="n">
-        <v>7.778597720834538</v>
+        <v>7.778598707807475</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430082134541178</v>
+        <v>7.430083077293361</v>
       </c>
       <c r="E33" t="n">
-        <v>7.600140920268824</v>
+        <v>7.6001418845986</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.516162395477295</v>
+        <v>7.516163349151611</v>
       </c>
       <c r="C35" t="n">
-        <v>7.55815165787306</v>
+        <v>7.558152616875106</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436381660412942</v>
+        <v>7.436382603964429</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511962982160976</v>
+        <v>7.511963935302457</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.705114841461182</v>
+        <v>7.705113887786865</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789094989334038</v>
+        <v>7.789094025265366</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033280152834855</v>
+        <v>7.033279282314587</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159248751055008</v>
+        <v>7.159247864943406</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.518260478973389</v>
+        <v>7.518261432647705</v>
       </c>
       <c r="C38" t="n">
-        <v>7.78909461635681</v>
+        <v>7.789095604385824</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455275776982023</v>
+        <v>7.455276722666873</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721911313070132</v>
+        <v>7.721912292577096</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138254642486572</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379694859893382</v>
+        <v>7.379695352858839</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138254642486572</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257924862390593</v>
+        <v>7.257925347221784</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1272,16 +1272,16 @@
         <v>44291</v>
       </c>
       <c r="B43" t="n">
-        <v>7.327208518981934</v>
+        <v>7.327207565307617</v>
       </c>
       <c r="C43" t="n">
-        <v>7.400690542372653</v>
+        <v>7.400689579134269</v>
       </c>
       <c r="D43" t="n">
-        <v>7.260024398079838</v>
+        <v>7.260023453149884</v>
       </c>
       <c r="E43" t="n">
-        <v>7.400690542372653</v>
+        <v>7.400689579134269</v>
       </c>
       <c r="F43" t="n">
         <v>1080107</v>
@@ -1292,16 +1292,16 @@
         <v>44292</v>
       </c>
       <c r="B44" t="n">
-        <v>7.211735725402832</v>
+        <v>7.21173620223999</v>
       </c>
       <c r="C44" t="n">
-        <v>7.379694387891328</v>
+        <v>7.379694875833847</v>
       </c>
       <c r="D44" t="n">
-        <v>7.190741095540401</v>
+        <v>7.190741570989402</v>
       </c>
       <c r="E44" t="n">
-        <v>7.369197072960112</v>
+        <v>7.369197560208552</v>
       </c>
       <c r="F44" t="n">
         <v>1319726</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652628421783447</v>
+        <v>7.652627468109131</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873074487963351</v>
+        <v>7.873073506816938</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474171618612335</v>
+        <v>7.474170687177393</v>
       </c>
       <c r="E47" t="n">
-        <v>7.595942429644829</v>
+        <v>7.595941483034749</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1372,16 +1372,16 @@
         <v>44298</v>
       </c>
       <c r="B48" t="n">
-        <v>7.789094924926758</v>
+        <v>7.789093971252441</v>
       </c>
       <c r="C48" t="n">
-        <v>8.015839698719409</v>
+        <v>8.015838717283117</v>
       </c>
       <c r="D48" t="n">
-        <v>7.64423018578716</v>
+        <v>7.644229249849665</v>
       </c>
       <c r="E48" t="n">
-        <v>7.688319560107198</v>
+        <v>7.688318618771526</v>
       </c>
       <c r="F48" t="n">
         <v>2187380</v>
@@ -1432,16 +1432,16 @@
         <v>44301</v>
       </c>
       <c r="B51" t="n">
-        <v>8.112414360046387</v>
+        <v>8.112415313720703</v>
       </c>
       <c r="C51" t="n">
-        <v>8.185897180089103</v>
+        <v>8.185898142401868</v>
       </c>
       <c r="D51" t="n">
-        <v>7.891968335301526</v>
+        <v>7.891969263060783</v>
       </c>
       <c r="E51" t="n">
-        <v>7.894067635698465</v>
+        <v>7.894068563704509</v>
       </c>
       <c r="F51" t="n">
         <v>2034122</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208992004394531</v>
+        <v>8.208991050720215</v>
       </c>
       <c r="C53" t="n">
-        <v>8.24468336574694</v>
+        <v>8.244682407926204</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059929468278197</v>
+        <v>8.059928531921125</v>
       </c>
       <c r="E53" t="n">
-        <v>8.187997372467679</v>
+        <v>8.1879964212324</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1552,16 +1552,16 @@
         <v>44312</v>
       </c>
       <c r="B57" t="n">
-        <v>7.978049278259277</v>
+        <v>7.978048324584961</v>
       </c>
       <c r="C57" t="n">
-        <v>8.187997217134104</v>
+        <v>8.187996238363182</v>
       </c>
       <c r="D57" t="n">
-        <v>7.938158504201501</v>
+        <v>7.93815755529562</v>
       </c>
       <c r="E57" t="n">
-        <v>8.185898728134749</v>
+        <v>8.185897749614673</v>
       </c>
       <c r="F57" t="n">
         <v>1270667</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397945404052734</v>
+        <v>8.397946357727051</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469328120611465</v>
+        <v>8.469329082392035</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116615684439186</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116615684439186</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1612,16 +1612,16 @@
         <v>44315</v>
       </c>
       <c r="B60" t="n">
-        <v>8.607892990112305</v>
+        <v>8.607894897460938</v>
       </c>
       <c r="C60" t="n">
-        <v>8.815742398254132</v>
+        <v>8.815744351658321</v>
       </c>
       <c r="D60" t="n">
-        <v>8.167000945770697</v>
+        <v>8.167002755425871</v>
       </c>
       <c r="E60" t="n">
-        <v>8.469326988615892</v>
+        <v>8.469328865260882</v>
       </c>
       <c r="F60" t="n">
         <v>3250459</v>
@@ -1632,16 +1632,16 @@
         <v>44316</v>
       </c>
       <c r="B61" t="n">
-        <v>8.733863830566406</v>
+        <v>8.733864784240723</v>
       </c>
       <c r="C61" t="n">
-        <v>8.733863830566406</v>
+        <v>8.733864784240723</v>
       </c>
       <c r="D61" t="n">
-        <v>8.580601889171566</v>
+        <v>8.580602826110796</v>
       </c>
       <c r="E61" t="n">
-        <v>8.580601889171566</v>
+        <v>8.580602826110796</v>
       </c>
       <c r="F61" t="n">
         <v>3200590</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849333763122559</v>
+        <v>8.849334716796875</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122267169180361</v>
+        <v>9.122268152268145</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641485163873828</v>
+        <v>8.641486095148732</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733862499494249</v>
+        <v>8.733863440724466</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1732,16 +1732,16 @@
         <v>44323</v>
       </c>
       <c r="B66" t="n">
-        <v>9.867585182189941</v>
+        <v>9.867586135864258</v>
       </c>
       <c r="C66" t="n">
-        <v>10.05234067674103</v>
+        <v>10.05234164827144</v>
       </c>
       <c r="D66" t="n">
-        <v>9.554762613617749</v>
+        <v>9.554763537058646</v>
       </c>
       <c r="E66" t="n">
-        <v>9.827695224893009</v>
+        <v>9.827696174712075</v>
       </c>
       <c r="F66" t="n">
         <v>7085572</v>
@@ -1752,16 +1752,16 @@
         <v>44326</v>
       </c>
       <c r="B67" t="n">
-        <v>9.380505561828613</v>
+        <v>9.38050651550293</v>
       </c>
       <c r="C67" t="n">
-        <v>9.886481655948959</v>
+        <v>9.886482661063617</v>
       </c>
       <c r="D67" t="n">
-        <v>9.254536160500752</v>
+        <v>9.254537101368319</v>
       </c>
       <c r="E67" t="n">
-        <v>9.867585515134721</v>
+        <v>9.867586518328292</v>
       </c>
       <c r="F67" t="n">
         <v>3466157</v>
@@ -1772,16 +1772,16 @@
         <v>44327</v>
       </c>
       <c r="B68" t="n">
-        <v>9.617746353149414</v>
+        <v>9.61774730682373</v>
       </c>
       <c r="C68" t="n">
-        <v>9.645040506833098</v>
+        <v>9.645041463213841</v>
       </c>
       <c r="D68" t="n">
-        <v>8.964807071897692</v>
+        <v>8.964807960828002</v>
       </c>
       <c r="E68" t="n">
-        <v>9.294426475068693</v>
+        <v>9.294427396683329</v>
       </c>
       <c r="F68" t="n">
         <v>2188597</v>
@@ -1812,16 +1812,16 @@
         <v>44329</v>
       </c>
       <c r="B70" t="n">
-        <v>9.655537605285645</v>
+        <v>9.655538558959961</v>
       </c>
       <c r="C70" t="n">
-        <v>9.699626973781776</v>
+        <v>9.699627931810785</v>
       </c>
       <c r="D70" t="n">
-        <v>9.489678257157614</v>
+        <v>9.489679194450057</v>
       </c>
       <c r="E70" t="n">
-        <v>9.556861554231343</v>
+        <v>9.556862498159457</v>
       </c>
       <c r="F70" t="n">
         <v>2493897</v>
@@ -1952,16 +1952,16 @@
         <v>44340</v>
       </c>
       <c r="B77" t="n">
-        <v>10.18250942230225</v>
+        <v>10.18250846862793</v>
       </c>
       <c r="C77" t="n">
-        <v>10.39035886155727</v>
+        <v>10.39035788841617</v>
       </c>
       <c r="D77" t="n">
-        <v>9.951566051904743</v>
+        <v>9.951565119860142</v>
       </c>
       <c r="E77" t="n">
-        <v>10.15731537867855</v>
+        <v>10.15731442736386</v>
       </c>
       <c r="F77" t="n">
         <v>3407772</v>
@@ -2052,16 +2052,16 @@
         <v>44347</v>
       </c>
       <c r="B82" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727928161621</v>
       </c>
       <c r="C82" t="n">
-        <v>11.3960123574381</v>
+        <v>11.39601333414453</v>
       </c>
       <c r="D82" t="n">
-        <v>10.70738084874532</v>
+        <v>10.70738176643192</v>
       </c>
       <c r="E82" t="n">
-        <v>10.7493709213828</v>
+        <v>10.74937184266819</v>
       </c>
       <c r="F82" t="n">
         <v>1849644</v>
@@ -2072,16 +2072,16 @@
         <v>44348</v>
       </c>
       <c r="B83" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727928161621</v>
       </c>
       <c r="C83" t="n">
-        <v>11.25324773405977</v>
+        <v>11.25324869853042</v>
       </c>
       <c r="D83" t="n">
-        <v>11.03280086745621</v>
+        <v>11.03280181303325</v>
       </c>
       <c r="E83" t="n">
-        <v>11.23225229184377</v>
+        <v>11.23225325451498</v>
       </c>
       <c r="F83" t="n">
         <v>1761257</v>
@@ -2092,16 +2092,16 @@
         <v>44349</v>
       </c>
       <c r="B84" t="n">
-        <v>10.9152307510376</v>
+        <v>10.91522979736328</v>
       </c>
       <c r="C84" t="n">
-        <v>11.25114809921971</v>
+        <v>11.25114711619596</v>
       </c>
       <c r="D84" t="n">
-        <v>10.79765935445603</v>
+        <v>10.79765841105404</v>
       </c>
       <c r="E84" t="n">
-        <v>11.25114809921971</v>
+        <v>11.25114711619596</v>
       </c>
       <c r="F84" t="n">
         <v>2442811</v>
@@ -2112,16 +2112,16 @@
         <v>44351</v>
       </c>
       <c r="B85" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727928161621</v>
       </c>
       <c r="C85" t="n">
-        <v>11.1419742445191</v>
+        <v>11.14197519945295</v>
       </c>
       <c r="D85" t="n">
-        <v>10.6569935733749</v>
+        <v>10.656994486743</v>
       </c>
       <c r="E85" t="n">
-        <v>10.93832503055962</v>
+        <v>10.93832596803951</v>
       </c>
       <c r="F85" t="n">
         <v>2427404</v>
@@ -2132,16 +2132,16 @@
         <v>44354</v>
       </c>
       <c r="B86" t="n">
-        <v>11.10838222503662</v>
+        <v>11.10838317871094</v>
       </c>
       <c r="C86" t="n">
-        <v>11.6122590026427</v>
+        <v>11.61225999957573</v>
       </c>
       <c r="D86" t="n">
-        <v>10.8984343118457</v>
+        <v>10.89843524749561</v>
       </c>
       <c r="E86" t="n">
-        <v>11.14407358134564</v>
+        <v>11.14407453808413</v>
       </c>
       <c r="F86" t="n">
         <v>2940293</v>
@@ -2172,16 +2172,16 @@
         <v>44356</v>
       </c>
       <c r="B88" t="n">
-        <v>10.90893268585205</v>
+        <v>10.90893173217773</v>
       </c>
       <c r="C88" t="n">
-        <v>11.1251793334517</v>
+        <v>11.1251783608728</v>
       </c>
       <c r="D88" t="n">
-        <v>10.7325751877154</v>
+        <v>10.7325742494585</v>
       </c>
       <c r="E88" t="n">
-        <v>11.00340933714343</v>
+        <v>11.00340837520983</v>
       </c>
       <c r="F88" t="n">
         <v>1361892</v>
@@ -2212,16 +2212,16 @@
         <v>44358</v>
       </c>
       <c r="B90" t="n">
-        <v>10.60240650177002</v>
+        <v>10.60240745544434</v>
       </c>
       <c r="C90" t="n">
-        <v>10.84174787766967</v>
+        <v>10.84174885287247</v>
       </c>
       <c r="D90" t="n">
-        <v>10.51842717132385</v>
+        <v>10.51842811744432</v>
       </c>
       <c r="E90" t="n">
-        <v>10.7598678478309</v>
+        <v>10.75986881566868</v>
       </c>
       <c r="F90" t="n">
         <v>1174982</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462299346924</v>
+        <v>10.94462203979492</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192304724218</v>
+        <v>11.35192205807723</v>
       </c>
       <c r="D92" t="n">
-        <v>10.81445498526105</v>
+        <v>10.8144540429291</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152825044157</v>
+        <v>10.92152729877964</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2272,16 +2272,16 @@
         <v>44363</v>
       </c>
       <c r="B93" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727928161621</v>
       </c>
       <c r="C93" t="n">
-        <v>11.31413313643548</v>
+        <v>11.31413410612437</v>
       </c>
       <c r="D93" t="n">
-        <v>10.89213554476112</v>
+        <v>10.8921364782823</v>
       </c>
       <c r="E93" t="n">
-        <v>10.96141896166432</v>
+        <v>10.9614199011235</v>
       </c>
       <c r="F93" t="n">
         <v>2948808</v>
@@ -2312,16 +2312,16 @@
         <v>44365</v>
       </c>
       <c r="B95" t="n">
-        <v>11.33722591400146</v>
+        <v>11.33722686767578</v>
       </c>
       <c r="C95" t="n">
-        <v>11.33722591400146</v>
+        <v>11.33722686767578</v>
       </c>
       <c r="D95" t="n">
-        <v>10.99290978879124</v>
+        <v>10.99291071350208</v>
       </c>
       <c r="E95" t="n">
-        <v>11.31203187298242</v>
+        <v>11.31203282453744</v>
       </c>
       <c r="F95" t="n">
         <v>1275938</v>
@@ -2332,16 +2332,16 @@
         <v>44368</v>
       </c>
       <c r="B96" t="n">
-        <v>11.24275016784668</v>
+        <v>11.24274921417236</v>
       </c>
       <c r="C96" t="n">
-        <v>11.40441175261605</v>
+        <v>11.40441078522868</v>
       </c>
       <c r="D96" t="n">
-        <v>11.15247211601892</v>
+        <v>11.1524711700025</v>
       </c>
       <c r="E96" t="n">
-        <v>11.34562564799132</v>
+        <v>11.34562468559051</v>
       </c>
       <c r="F96" t="n">
         <v>1065511</v>
@@ -2372,16 +2372,16 @@
         <v>44370</v>
       </c>
       <c r="B98" t="n">
-        <v>11.50308609008789</v>
+        <v>11.50308704376221</v>
       </c>
       <c r="C98" t="n">
-        <v>11.74872535200955</v>
+        <v>11.74872632604882</v>
       </c>
       <c r="D98" t="n">
-        <v>11.30573317441381</v>
+        <v>11.3057341117264</v>
       </c>
       <c r="E98" t="n">
-        <v>11.42120525372139</v>
+        <v>11.4212062006073</v>
       </c>
       <c r="F98" t="n">
         <v>4341920</v>
@@ -2412,16 +2412,16 @@
         <v>44372</v>
       </c>
       <c r="B100" t="n">
-        <v>11.61225986480713</v>
+        <v>11.61226081848145</v>
       </c>
       <c r="C100" t="n">
-        <v>11.71933394168402</v>
+        <v>11.71933490415196</v>
       </c>
       <c r="D100" t="n">
-        <v>11.34142572157541</v>
+        <v>11.34142665300706</v>
       </c>
       <c r="E100" t="n">
-        <v>11.71093592711753</v>
+        <v>11.71093688889577</v>
       </c>
       <c r="F100" t="n">
         <v>3580087</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.01746273040771</v>
+        <v>12.0174617767334</v>
       </c>
       <c r="C102" t="n">
-        <v>12.01746273040771</v>
+        <v>12.0174617767334</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916718832423</v>
+        <v>11.58916626863832</v>
       </c>
       <c r="E102" t="n">
-        <v>11.86000054908383</v>
+        <v>11.8599996079053</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2512,16 +2512,16 @@
         <v>44379</v>
       </c>
       <c r="B105" t="n">
-        <v>12.95803070068359</v>
+        <v>12.95802974700928</v>
       </c>
       <c r="C105" t="n">
-        <v>13.1280894777343</v>
+        <v>13.12808851154414</v>
       </c>
       <c r="D105" t="n">
-        <v>12.5003425684372</v>
+        <v>12.50034164844744</v>
       </c>
       <c r="E105" t="n">
-        <v>12.52133719856387</v>
+        <v>12.52133627702896</v>
       </c>
       <c r="F105" t="n">
         <v>2908669</v>
@@ -2552,16 +2552,16 @@
         <v>44383</v>
       </c>
       <c r="B107" t="n">
-        <v>13.04830932617188</v>
+        <v>13.04830837249756</v>
       </c>
       <c r="C107" t="n">
-        <v>13.36113192669314</v>
+        <v>13.36113095015526</v>
       </c>
       <c r="D107" t="n">
-        <v>13.00002053822385</v>
+        <v>13.00001958807886</v>
       </c>
       <c r="E107" t="n">
-        <v>13.14908469176732</v>
+        <v>13.14908373072754</v>
       </c>
       <c r="F107" t="n">
         <v>1738957</v>
@@ -2612,16 +2612,16 @@
         <v>44389</v>
       </c>
       <c r="B110" t="n">
-        <v>13.33173942565918</v>
+        <v>13.3317403793335</v>
       </c>
       <c r="C110" t="n">
-        <v>13.79572545725768</v>
+        <v>13.79572644412283</v>
       </c>
       <c r="D110" t="n">
-        <v>13.07140260401543</v>
+        <v>13.07140353906678</v>
       </c>
       <c r="E110" t="n">
-        <v>13.19107329393574</v>
+        <v>13.19107423754762</v>
       </c>
       <c r="F110" t="n">
         <v>8663568</v>
@@ -2652,16 +2652,16 @@
         <v>44391</v>
       </c>
       <c r="B112" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196659088135</v>
       </c>
       <c r="C112" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196659088135</v>
       </c>
       <c r="D112" t="n">
-        <v>13.25405823136172</v>
+        <v>13.25405915859814</v>
       </c>
       <c r="E112" t="n">
-        <v>13.27505286174354</v>
+        <v>13.27505379044871</v>
       </c>
       <c r="F112" t="n">
         <v>1800585</v>
@@ -2672,16 +2672,16 @@
         <v>44392</v>
       </c>
       <c r="B113" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196659088135</v>
       </c>
       <c r="C113" t="n">
-        <v>13.72224368436118</v>
+        <v>13.72224464435123</v>
       </c>
       <c r="D113" t="n">
-        <v>13.39682366626494</v>
+        <v>13.39682460348903</v>
       </c>
       <c r="E113" t="n">
-        <v>13.53958828937361</v>
+        <v>13.53958923658533</v>
       </c>
       <c r="F113" t="n">
         <v>1667599</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103643972576</v>
+        <v>14.16103739980534</v>
       </c>
       <c r="D116" t="n">
-        <v>13.77473102080758</v>
+        <v>13.7747319546967</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059038615415</v>
+        <v>13.94059133128809</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2752,16 +2752,16 @@
         <v>44398</v>
       </c>
       <c r="B117" t="n">
-        <v>14.3184986114502</v>
+        <v>14.31849765777588</v>
       </c>
       <c r="C117" t="n">
-        <v>14.34789044445824</v>
+        <v>14.3478894888263</v>
       </c>
       <c r="D117" t="n">
-        <v>14.01617171355511</v>
+        <v>14.01617078001709</v>
       </c>
       <c r="E117" t="n">
-        <v>14.06865910114192</v>
+        <v>14.06865816410801</v>
       </c>
       <c r="F117" t="n">
         <v>2316312</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.99873161315918</v>
+        <v>14.99873065948486</v>
       </c>
       <c r="C118" t="n">
-        <v>15.01132904037419</v>
+        <v>15.01132808589888</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36048740382685</v>
+        <v>14.36048649073444</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36048740382685</v>
+        <v>14.36048649073444</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801509857178</v>
+        <v>15.06801319122314</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127867222671</v>
+        <v>15.22127674547757</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92944987797833</v>
+        <v>14.92944798816965</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127867222671</v>
+        <v>15.22127674547757</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2832,16 +2832,16 @@
         <v>44404</v>
       </c>
       <c r="B121" t="n">
-        <v>14.54944038391113</v>
+        <v>14.54944133758545</v>
       </c>
       <c r="C121" t="n">
-        <v>15.05961588037913</v>
+        <v>15.059616867494</v>
       </c>
       <c r="D121" t="n">
-        <v>14.45076513966624</v>
+        <v>14.45076608687268</v>
       </c>
       <c r="E121" t="n">
-        <v>14.87486119524679</v>
+        <v>14.87486217025152</v>
       </c>
       <c r="F121" t="n">
         <v>2070206</v>
@@ -2892,16 +2892,16 @@
         <v>44407</v>
       </c>
       <c r="B124" t="n">
-        <v>15.45431900024414</v>
+        <v>15.45431709289551</v>
       </c>
       <c r="C124" t="n">
-        <v>15.94140058333477</v>
+        <v>15.94139861587127</v>
       </c>
       <c r="D124" t="n">
-        <v>14.96933834137266</v>
+        <v>14.96933649387961</v>
       </c>
       <c r="E124" t="n">
-        <v>15.28006243564328</v>
+        <v>15.28006054980113</v>
       </c>
       <c r="F124" t="n">
         <v>3070441</v>
@@ -2952,16 +2952,16 @@
         <v>44412</v>
       </c>
       <c r="B127" t="n">
-        <v>14.73839569091797</v>
+        <v>14.73839473724365</v>
       </c>
       <c r="C127" t="n">
-        <v>15.32205328135125</v>
+        <v>15.32205228991032</v>
       </c>
       <c r="D127" t="n">
-        <v>14.73839569091797</v>
+        <v>14.73839473724365</v>
       </c>
       <c r="E127" t="n">
-        <v>15.18768666199287</v>
+        <v>15.18768567924637</v>
       </c>
       <c r="F127" t="n">
         <v>2159810</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.93639183044434</v>
+        <v>13.9363899230957</v>
       </c>
       <c r="C129" t="n">
-        <v>14.41927319977593</v>
+        <v>14.41927122633967</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373643553897</v>
+        <v>13.75373455318874</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153461307515</v>
+        <v>14.17153267354464</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893713905431</v>
+        <v>14.15893809899156</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462098074336</v>
+        <v>13.81462191733692</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351631037553</v>
+        <v>13.83351724825013</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3032,16 +3032,16 @@
         <v>44418</v>
       </c>
       <c r="B131" t="n">
-        <v>13.64666271209717</v>
+        <v>13.64666175842285</v>
       </c>
       <c r="C131" t="n">
-        <v>14.43816890261326</v>
+        <v>14.43816789362585</v>
       </c>
       <c r="D131" t="n">
-        <v>13.56688278990252</v>
+        <v>13.56688184180349</v>
       </c>
       <c r="E131" t="n">
-        <v>14.05396277317898</v>
+        <v>14.05396179104118</v>
       </c>
       <c r="F131" t="n">
         <v>2933806</v>
@@ -3072,16 +3072,16 @@
         <v>44420</v>
       </c>
       <c r="B133" t="n">
-        <v>13.68025302886963</v>
+        <v>13.68025398254395</v>
       </c>
       <c r="C133" t="n">
-        <v>14.21142313065525</v>
+        <v>14.21142412135836</v>
       </c>
       <c r="D133" t="n">
-        <v>13.64666097424787</v>
+        <v>13.64666192558043</v>
       </c>
       <c r="E133" t="n">
-        <v>13.82511774968288</v>
+        <v>13.82511871345597</v>
       </c>
       <c r="F133" t="n">
         <v>1819641</v>
@@ -3112,16 +3112,16 @@
         <v>44424</v>
       </c>
       <c r="B135" t="n">
-        <v>11.84110355377197</v>
+        <v>11.84110450744629</v>
       </c>
       <c r="C135" t="n">
-        <v>12.94963251110049</v>
+        <v>12.94963355405497</v>
       </c>
       <c r="D135" t="n">
-        <v>11.76552223690275</v>
+        <v>11.7655231844898</v>
       </c>
       <c r="E135" t="n">
-        <v>12.94963251110049</v>
+        <v>12.94963355405497</v>
       </c>
       <c r="F135" t="n">
         <v>7844263</v>
@@ -3172,16 +3172,16 @@
         <v>44427</v>
       </c>
       <c r="B138" t="n">
-        <v>13.0840015411377</v>
+        <v>13.08399963378906</v>
       </c>
       <c r="C138" t="n">
-        <v>13.26875625483801</v>
+        <v>13.26875432055636</v>
       </c>
       <c r="D138" t="n">
-        <v>11.91668633982179</v>
+        <v>11.91668460264106</v>
       </c>
       <c r="E138" t="n">
-        <v>12.41216518539795</v>
+        <v>12.41216337598772</v>
       </c>
       <c r="F138" t="n">
         <v>2072031</v>
@@ -3232,16 +3232,16 @@
         <v>44432</v>
       </c>
       <c r="B141" t="n">
-        <v>13.63826465606689</v>
+        <v>13.63826560974121</v>
       </c>
       <c r="C141" t="n">
-        <v>13.92379389167463</v>
+        <v>13.92379486531496</v>
       </c>
       <c r="D141" t="n">
-        <v>13.37792783946889</v>
+        <v>13.3779287749388</v>
       </c>
       <c r="E141" t="n">
-        <v>13.63826465606689</v>
+        <v>13.63826560974121</v>
       </c>
       <c r="F141" t="n">
         <v>2525015</v>
@@ -3252,16 +3252,16 @@
         <v>44433</v>
       </c>
       <c r="B142" t="n">
-        <v>13.47870349884033</v>
+        <v>13.47870445251465</v>
       </c>
       <c r="C142" t="n">
-        <v>13.57947804789503</v>
+        <v>13.57947900869956</v>
       </c>
       <c r="D142" t="n">
-        <v>13.05040801228251</v>
+        <v>13.05040893565314</v>
       </c>
       <c r="E142" t="n">
-        <v>13.44511144129242</v>
+        <v>13.44511239258996</v>
       </c>
       <c r="F142" t="n">
         <v>2709595</v>
@@ -3372,16 +3372,16 @@
         <v>44441</v>
       </c>
       <c r="B148" t="n">
-        <v>12.8068675994873</v>
+        <v>12.80686569213867</v>
       </c>
       <c r="C148" t="n">
-        <v>13.1847750109611</v>
+        <v>13.18477304733007</v>
       </c>
       <c r="D148" t="n">
-        <v>12.69769503279916</v>
+        <v>12.69769314170979</v>
       </c>
       <c r="E148" t="n">
-        <v>13.06720442963625</v>
+        <v>13.0672024835152</v>
       </c>
       <c r="F148" t="n">
         <v>2514879</v>
@@ -3432,16 +3432,16 @@
         <v>44447</v>
       </c>
       <c r="B151" t="n">
-        <v>13.23516368865967</v>
+        <v>13.23516273498535</v>
       </c>
       <c r="C151" t="n">
-        <v>14.67961009363327</v>
+        <v>14.67960903587777</v>
       </c>
       <c r="D151" t="n">
-        <v>13.10079626027822</v>
+        <v>13.10079531628589</v>
       </c>
       <c r="E151" t="n">
-        <v>13.80622302684572</v>
+        <v>13.80622203202309</v>
       </c>
       <c r="F151" t="n">
         <v>4568970</v>
@@ -3472,16 +3472,16 @@
         <v>44449</v>
       </c>
       <c r="B153" t="n">
-        <v>13.0840015411377</v>
+        <v>13.08399963378906</v>
       </c>
       <c r="C153" t="n">
-        <v>13.77263311574551</v>
+        <v>13.77263110801012</v>
       </c>
       <c r="D153" t="n">
-        <v>13.00841940315561</v>
+        <v>13.00841750682512</v>
       </c>
       <c r="E153" t="n">
-        <v>13.77263311574551</v>
+        <v>13.77263110801012</v>
       </c>
       <c r="F153" t="n">
         <v>2018917</v>
@@ -3492,16 +3492,16 @@
         <v>44452</v>
       </c>
       <c r="B154" t="n">
-        <v>13.39472389221191</v>
+        <v>13.3947229385376</v>
       </c>
       <c r="C154" t="n">
-        <v>13.53748933072213</v>
+        <v>13.53748836688323</v>
       </c>
       <c r="D154" t="n">
-        <v>12.9748272149942</v>
+        <v>12.97482629121558</v>
       </c>
       <c r="E154" t="n">
-        <v>13.24356125077245</v>
+        <v>13.24356030786057</v>
       </c>
       <c r="F154" t="n">
         <v>1856739</v>
@@ -3512,16 +3512,16 @@
         <v>44453</v>
       </c>
       <c r="B155" t="n">
-        <v>13.55428504943848</v>
+        <v>13.55428600311279</v>
       </c>
       <c r="C155" t="n">
-        <v>14.04976384781166</v>
+        <v>14.04976483634768</v>
       </c>
       <c r="D155" t="n">
-        <v>13.27715300528965</v>
+        <v>13.27715393946506</v>
       </c>
       <c r="E155" t="n">
-        <v>13.43671365779501</v>
+        <v>13.43671460319705</v>
       </c>
       <c r="F155" t="n">
         <v>1943200</v>
@@ -3532,16 +3532,16 @@
         <v>44454</v>
       </c>
       <c r="B156" t="n">
-        <v>13.44511222839355</v>
+        <v>13.44511032104492</v>
       </c>
       <c r="C156" t="n">
-        <v>14.07495766172759</v>
+        <v>14.07495566502791</v>
       </c>
       <c r="D156" t="n">
-        <v>13.23516348001735</v>
+        <v>13.23516160245244</v>
       </c>
       <c r="E156" t="n">
-        <v>13.47030546123482</v>
+        <v>13.47030355031223</v>
       </c>
       <c r="F156" t="n">
         <v>2602050</v>
@@ -3572,16 +3572,16 @@
         <v>44456</v>
       </c>
       <c r="B158" t="n">
-        <v>13.44511222839355</v>
+        <v>13.44511032104492</v>
       </c>
       <c r="C158" t="n">
-        <v>13.74743914043451</v>
+        <v>13.74743719019722</v>
       </c>
       <c r="D158" t="n">
-        <v>13.29394877237308</v>
+        <v>13.29394688646877</v>
       </c>
       <c r="E158" t="n">
-        <v>13.40312296579506</v>
+        <v>13.4031210644031</v>
       </c>
       <c r="F158" t="n">
         <v>5378949</v>
@@ -3592,16 +3592,16 @@
         <v>44459</v>
       </c>
       <c r="B159" t="n">
-        <v>12.84885692596436</v>
+        <v>12.84885787963867</v>
       </c>
       <c r="C159" t="n">
-        <v>13.10919292918942</v>
+        <v>13.10919390218652</v>
       </c>
       <c r="D159" t="n">
-        <v>12.63051018168811</v>
+        <v>12.63051111915618</v>
       </c>
       <c r="E159" t="n">
-        <v>13.10919292918942</v>
+        <v>13.10919390218652</v>
       </c>
       <c r="F159" t="n">
         <v>1643373</v>
@@ -3632,16 +3632,16 @@
         <v>44461</v>
       </c>
       <c r="B161" t="n">
-        <v>14.10015201568604</v>
+        <v>14.10015106201172</v>
       </c>
       <c r="C161" t="n">
-        <v>14.46126420721415</v>
+        <v>14.46126322911574</v>
       </c>
       <c r="D161" t="n">
-        <v>13.58787718531884</v>
+        <v>13.58787626629261</v>
       </c>
       <c r="E161" t="n">
-        <v>13.71384659221444</v>
+        <v>13.71384566466818</v>
       </c>
       <c r="F161" t="n">
         <v>3751489</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.6124267578125</v>
+        <v>14.61242580413818</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630275876303</v>
+        <v>15.11630177220344</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893722044467</v>
+        <v>14.15893629636717</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19252927855919</v>
+        <v>14.19252835228931</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3712,16 +3712,16 @@
         <v>44467</v>
       </c>
       <c r="B165" t="n">
-        <v>13.1679801940918</v>
+        <v>13.16797828674316</v>
       </c>
       <c r="C165" t="n">
-        <v>13.89020298046473</v>
+        <v>13.89020096850395</v>
       </c>
       <c r="D165" t="n">
-        <v>13.15118335251281</v>
+        <v>13.15118144759716</v>
       </c>
       <c r="E165" t="n">
-        <v>13.64666298397454</v>
+        <v>13.64666100728992</v>
       </c>
       <c r="F165" t="n">
         <v>3700200</v>
@@ -3732,16 +3732,16 @@
         <v>44468</v>
       </c>
       <c r="B166" t="n">
-        <v>12.98322582244873</v>
+        <v>12.98322486877441</v>
       </c>
       <c r="C166" t="n">
-        <v>13.50389788832815</v>
+        <v>13.50389689640821</v>
       </c>
       <c r="D166" t="n">
-        <v>12.80686831699192</v>
+        <v>12.80686737627183</v>
       </c>
       <c r="E166" t="n">
-        <v>13.2939491342371</v>
+        <v>13.29394815773881</v>
       </c>
       <c r="F166" t="n">
         <v>4585796</v>
@@ -3752,16 +3752,16 @@
         <v>44469</v>
       </c>
       <c r="B167" t="n">
-        <v>12.55492973327637</v>
+        <v>12.55492877960205</v>
       </c>
       <c r="C167" t="n">
-        <v>13.05880655802494</v>
+        <v>13.05880556607607</v>
       </c>
       <c r="D167" t="n">
-        <v>12.37017503283432</v>
+        <v>12.370174093194</v>
       </c>
       <c r="E167" t="n">
-        <v>13.05880655802494</v>
+        <v>13.05880556607607</v>
       </c>
       <c r="F167" t="n">
         <v>6213762</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498023986816</v>
+        <v>12.34498119354248</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366299139635</v>
+        <v>12.82366398204986</v>
       </c>
       <c r="D169" t="n">
-        <v>12.1350315079744</v>
+        <v>12.13503244542976</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288763255913</v>
+        <v>12.72288861542754</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14342975616455</v>
+        <v>12.14343070983887</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55492921366123</v>
+        <v>12.55493019965232</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027704898789</v>
+        <v>11.95027798749311</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337849210345</v>
+        <v>12.35337946226592</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3832,16 +3832,16 @@
         <v>44475</v>
       </c>
       <c r="B171" t="n">
-        <v>12.51294136047363</v>
+        <v>12.512939453125</v>
       </c>
       <c r="C171" t="n">
-        <v>12.61371592078883</v>
+        <v>12.61371399807913</v>
       </c>
       <c r="D171" t="n">
-        <v>11.68154352582436</v>
+        <v>11.68154174520576</v>
       </c>
       <c r="E171" t="n">
-        <v>11.94188037732158</v>
+        <v>11.94187855701982</v>
       </c>
       <c r="F171" t="n">
         <v>5058241</v>
@@ -3932,16 +3932,16 @@
         <v>44483</v>
       </c>
       <c r="B176" t="n">
-        <v>13.1679801940918</v>
+        <v>13.16797828674316</v>
       </c>
       <c r="C176" t="n">
-        <v>13.2939487938857</v>
+        <v>13.29394686829084</v>
       </c>
       <c r="D176" t="n">
-        <v>12.85725607846398</v>
+        <v>12.85725421612295</v>
       </c>
       <c r="E176" t="n">
-        <v>13.12599011963078</v>
+        <v>13.1259882183643</v>
       </c>
       <c r="F176" t="n">
         <v>1588233</v>
@@ -3952,16 +3952,16 @@
         <v>44484</v>
       </c>
       <c r="B177" t="n">
-        <v>13.41991806030273</v>
+        <v>13.41991710662842</v>
       </c>
       <c r="C177" t="n">
-        <v>13.48710217871359</v>
+        <v>13.4871012202649</v>
       </c>
       <c r="D177" t="n">
-        <v>13.0840007154267</v>
+        <v>13.08399978562405</v>
       </c>
       <c r="E177" t="n">
-        <v>13.24356137306336</v>
+        <v>13.24356043192167</v>
       </c>
       <c r="F177" t="n">
         <v>1650266</v>
@@ -4012,16 +4012,16 @@
         <v>44489</v>
       </c>
       <c r="B180" t="n">
-        <v>11.9838695526123</v>
+        <v>11.98386859893799</v>
       </c>
       <c r="C180" t="n">
-        <v>12.58852173979385</v>
+        <v>12.58852073800141</v>
       </c>
       <c r="D180" t="n">
-        <v>11.87469617338831</v>
+        <v>11.874695228402</v>
       </c>
       <c r="E180" t="n">
-        <v>12.45415431648865</v>
+        <v>12.45415332538915</v>
       </c>
       <c r="F180" t="n">
         <v>2144403</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.53102397918701</v>
+        <v>10.5310230255127</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174807577158</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624046544360398</v>
+        <v>9.624045672820648</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174807577158</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55621814727783</v>
+        <v>10.55621719360352</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650289901313</v>
+        <v>11.02650190285215</v>
       </c>
       <c r="D183" t="n">
-        <v>10.35466742342063</v>
+        <v>10.35466648795489</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699350920643</v>
+        <v>10.65699254642783</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4092,16 +4092,16 @@
         <v>44495</v>
       </c>
       <c r="B184" t="n">
-        <v>9.98515796661377</v>
+        <v>9.985158920288086</v>
       </c>
       <c r="C184" t="n">
-        <v>10.46384072961404</v>
+        <v>10.46384172900696</v>
       </c>
       <c r="D184" t="n">
-        <v>9.825596504417325</v>
+        <v>9.825597442852056</v>
       </c>
       <c r="E184" t="n">
-        <v>10.46384072961404</v>
+        <v>10.46384172900696</v>
       </c>
       <c r="F184" t="n">
         <v>5760068</v>
@@ -4132,16 +4132,16 @@
         <v>44497</v>
       </c>
       <c r="B186" t="n">
-        <v>9.909575462341309</v>
+        <v>9.909576416015625</v>
       </c>
       <c r="C186" t="n">
-        <v>10.4386454367352</v>
+        <v>10.43864644132597</v>
       </c>
       <c r="D186" t="n">
-        <v>9.82559532818885</v>
+        <v>9.825596273781114</v>
       </c>
       <c r="E186" t="n">
-        <v>10.25389076518866</v>
+        <v>10.25389175199907</v>
       </c>
       <c r="F186" t="n">
         <v>4167680</v>
@@ -4152,16 +4152,16 @@
         <v>44498</v>
       </c>
       <c r="B187" t="n">
-        <v>9.514874458312988</v>
+        <v>9.514873504638672</v>
       </c>
       <c r="C187" t="n">
-        <v>10.06913861155314</v>
+        <v>10.06913760232501</v>
       </c>
       <c r="D187" t="n">
-        <v>9.069782883182105</v>
+        <v>9.069781974119245</v>
       </c>
       <c r="E187" t="n">
-        <v>10.06913861155314</v>
+        <v>10.06913760232501</v>
       </c>
       <c r="F187" t="n">
         <v>8163450</v>
@@ -4192,16 +4192,16 @@
         <v>44503</v>
       </c>
       <c r="B189" t="n">
-        <v>10.14471817016602</v>
+        <v>10.14471912384033</v>
       </c>
       <c r="C189" t="n">
-        <v>10.29588079948901</v>
+        <v>10.29588176737367</v>
       </c>
       <c r="D189" t="n">
-        <v>9.548463231541206</v>
+        <v>9.548464129163397</v>
       </c>
       <c r="E189" t="n">
-        <v>9.657637414199865</v>
+        <v>9.657638322085189</v>
       </c>
       <c r="F189" t="n">
         <v>6020061</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55621814727783</v>
+        <v>10.55621719360352</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771679767463</v>
+        <v>10.96771580682453</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588132208213</v>
+        <v>10.29588039192727</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64019748025258</v>
+        <v>10.64019651899136</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4292,16 +4292,16 @@
         <v>44510</v>
       </c>
       <c r="B194" t="n">
-        <v>10.66539192199707</v>
+        <v>10.66539096832275</v>
       </c>
       <c r="C194" t="n">
-        <v>11.16926875045805</v>
+        <v>11.16926775172825</v>
       </c>
       <c r="D194" t="n">
-        <v>10.44704516103155</v>
+        <v>10.44704422688129</v>
       </c>
       <c r="E194" t="n">
-        <v>10.74937125810814</v>
+        <v>10.74937029692459</v>
       </c>
       <c r="F194" t="n">
         <v>2771222</v>
@@ -4312,16 +4312,16 @@
         <v>44511</v>
       </c>
       <c r="B195" t="n">
-        <v>11.2196569442749</v>
+        <v>11.21965599060059</v>
       </c>
       <c r="C195" t="n">
-        <v>11.53038108153437</v>
+        <v>11.5303801014484</v>
       </c>
       <c r="D195" t="n">
-        <v>10.6905868400013</v>
+        <v>10.69058593129811</v>
       </c>
       <c r="E195" t="n">
-        <v>10.78296338665736</v>
+        <v>10.78296247010213</v>
       </c>
       <c r="F195" t="n">
         <v>2903296</v>
@@ -4352,16 +4352,16 @@
         <v>44516</v>
       </c>
       <c r="B197" t="n">
-        <v>10.16991329193115</v>
+        <v>10.16991233825684</v>
       </c>
       <c r="C197" t="n">
-        <v>10.85854483462774</v>
+        <v>10.85854381637763</v>
       </c>
       <c r="D197" t="n">
-        <v>10.10272917239372</v>
+        <v>10.10272822501953</v>
       </c>
       <c r="E197" t="n">
-        <v>10.85854483462774</v>
+        <v>10.85854381637763</v>
       </c>
       <c r="F197" t="n">
         <v>2296952</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674434661865234</v>
+        <v>9.674432754516602</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34627018804897</v>
+        <v>10.34626814824561</v>
       </c>
       <c r="D202" t="n">
-        <v>9.481281937939977</v>
+        <v>9.481280068672081</v>
       </c>
       <c r="E202" t="n">
-        <v>10.2874840822837</v>
+        <v>10.28748205407023</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4472,16 +4472,16 @@
         <v>44524</v>
       </c>
       <c r="B203" t="n">
-        <v>9.699628829956055</v>
+        <v>9.699627876281738</v>
       </c>
       <c r="C203" t="n">
-        <v>10.11952634355827</v>
+        <v>10.11952534859934</v>
       </c>
       <c r="D203" t="n">
-        <v>9.380506687146584</v>
+        <v>9.38050576484858</v>
       </c>
       <c r="E203" t="n">
-        <v>9.842393465032259</v>
+        <v>9.842392497321224</v>
       </c>
       <c r="F203" t="n">
         <v>3236370</v>
@@ -4492,16 +4492,16 @@
         <v>44525</v>
       </c>
       <c r="B204" t="n">
-        <v>9.825597763061523</v>
+        <v>9.825596809387207</v>
       </c>
       <c r="C204" t="n">
-        <v>10.15311712024066</v>
+        <v>10.15311613477726</v>
       </c>
       <c r="D204" t="n">
-        <v>9.657639076723777</v>
+        <v>9.657638139351562</v>
       </c>
       <c r="E204" t="n">
-        <v>9.901179090734045</v>
+        <v>9.901178129723791</v>
       </c>
       <c r="F204" t="n">
         <v>1557621</v>
@@ -4512,16 +4512,16 @@
         <v>44526</v>
       </c>
       <c r="B205" t="n">
-        <v>9.472883224487305</v>
+        <v>9.472882270812988</v>
       </c>
       <c r="C205" t="n">
-        <v>9.682831981145643</v>
+        <v>9.682831006334919</v>
       </c>
       <c r="D205" t="n">
-        <v>9.178955127524551</v>
+        <v>9.178954203441192</v>
       </c>
       <c r="E205" t="n">
-        <v>9.657638747310545</v>
+        <v>9.657637775036125</v>
       </c>
       <c r="F205" t="n">
         <v>2092506</v>
@@ -4532,16 +4532,16 @@
         <v>44529</v>
       </c>
       <c r="B206" t="n">
-        <v>9.632443428039551</v>
+        <v>9.632444381713867</v>
       </c>
       <c r="C206" t="n">
-        <v>9.909576269733462</v>
+        <v>9.909577250845725</v>
       </c>
       <c r="D206" t="n">
-        <v>9.456086755539426</v>
+        <v>9.456087691753288</v>
       </c>
       <c r="E206" t="n">
-        <v>9.741616799538319</v>
+        <v>9.741617764021505</v>
       </c>
       <c r="F206" t="n">
         <v>2527144</v>
@@ -4592,16 +4592,16 @@
         <v>44532</v>
       </c>
       <c r="B209" t="n">
-        <v>9.220943450927734</v>
+        <v>9.220944404602051</v>
       </c>
       <c r="C209" t="n">
-        <v>9.472881423954535</v>
+        <v>9.472882403685489</v>
       </c>
       <c r="D209" t="n">
-        <v>8.952209450673589</v>
+        <v>8.952210376554143</v>
       </c>
       <c r="E209" t="n">
-        <v>9.10337207213078</v>
+        <v>9.103373013645299</v>
       </c>
       <c r="F209" t="n">
         <v>2421323</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884383201599121</v>
+        <v>9.884382247924805</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709658136135</v>
+        <v>10.23709559365621</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573658272883511</v>
+        <v>9.573657349188849</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867586359950231</v>
+        <v>9.867585407896522</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4652,16 +4652,16 @@
         <v>44537</v>
       </c>
       <c r="B212" t="n">
-        <v>9.98515796661377</v>
+        <v>9.985158920288086</v>
       </c>
       <c r="C212" t="n">
-        <v>10.53102403318413</v>
+        <v>10.53102503899367</v>
       </c>
       <c r="D212" t="n">
-        <v>9.867585764725682</v>
+        <v>9.867586707170773</v>
       </c>
       <c r="E212" t="n">
-        <v>10.00195318366039</v>
+        <v>10.00195413893881</v>
       </c>
       <c r="F212" t="n">
         <v>3095174</v>
@@ -4692,16 +4692,16 @@
         <v>44539</v>
       </c>
       <c r="B214" t="n">
-        <v>10.78222942352295</v>
+        <v>10.78222846984863</v>
       </c>
       <c r="C214" t="n">
-        <v>11.00401677853015</v>
+        <v>11.00401580523902</v>
       </c>
       <c r="D214" t="n">
-        <v>10.23629341206293</v>
+        <v>10.23629250667595</v>
       </c>
       <c r="E214" t="n">
-        <v>10.46661108166976</v>
+        <v>10.46661015591148</v>
       </c>
       <c r="F214" t="n">
         <v>2489235</v>
@@ -4712,16 +4712,16 @@
         <v>44540</v>
       </c>
       <c r="B215" t="n">
-        <v>11.166090965271</v>
+        <v>11.16609001159668</v>
       </c>
       <c r="C215" t="n">
-        <v>11.32816530341248</v>
+        <v>11.32816433589571</v>
       </c>
       <c r="D215" t="n">
-        <v>10.86753323435248</v>
+        <v>10.86753230617741</v>
       </c>
       <c r="E215" t="n">
-        <v>11.012546942251</v>
+        <v>11.01254600169058</v>
       </c>
       <c r="F215" t="n">
         <v>3272354</v>
@@ -4732,16 +4732,16 @@
         <v>44543</v>
       </c>
       <c r="B216" t="n">
-        <v>11.19168186187744</v>
+        <v>11.19168090820312</v>
       </c>
       <c r="C216" t="n">
-        <v>11.55848208514464</v>
+        <v>11.55848110021426</v>
       </c>
       <c r="D216" t="n">
-        <v>11.13196966068666</v>
+        <v>11.13196871210059</v>
       </c>
       <c r="E216" t="n">
-        <v>11.25992355294072</v>
+        <v>11.25992259345134</v>
       </c>
       <c r="F216" t="n">
         <v>3334589</v>
@@ -4932,16 +4932,16 @@
         <v>44558</v>
       </c>
       <c r="B226" t="n">
-        <v>10.08274936676025</v>
+        <v>10.08274841308594</v>
       </c>
       <c r="C226" t="n">
-        <v>10.50073148249594</v>
+        <v>10.50073048928689</v>
       </c>
       <c r="D226" t="n">
-        <v>9.98891755562571</v>
+        <v>9.988916610826452</v>
       </c>
       <c r="E226" t="n">
-        <v>10.15952137333246</v>
+        <v>10.15952041239668</v>
       </c>
       <c r="F226" t="n">
         <v>1405681</v>
@@ -4972,16 +4972,16 @@
         <v>44560</v>
       </c>
       <c r="B228" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="C228" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="D228" t="n">
-        <v>9.647706562908386</v>
+        <v>9.647705662569827</v>
       </c>
       <c r="E228" t="n">
-        <v>9.7927210851769</v>
+        <v>9.792720171305367</v>
       </c>
       <c r="F228" t="n">
         <v>3325771</v>
@@ -5032,16 +5032,16 @@
         <v>44566</v>
       </c>
       <c r="B231" t="n">
-        <v>8.530242919921875</v>
+        <v>8.530243873596191</v>
       </c>
       <c r="C231" t="n">
-        <v>9.255313753646449</v>
+        <v>9.255314788383105</v>
       </c>
       <c r="D231" t="n">
-        <v>8.479061866448102</v>
+        <v>8.479062814400418</v>
       </c>
       <c r="E231" t="n">
-        <v>9.255313753646449</v>
+        <v>9.255314788383105</v>
       </c>
       <c r="F231" t="n">
         <v>5451524</v>
@@ -5052,16 +5052,16 @@
         <v>44567</v>
       </c>
       <c r="B232" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="C232" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="D232" t="n">
-        <v>8.393760513964654</v>
+        <v>8.393761408545751</v>
       </c>
       <c r="E232" t="n">
-        <v>8.547305340985826</v>
+        <v>8.547306251931259</v>
       </c>
       <c r="F232" t="n">
         <v>4969753</v>
@@ -5152,16 +5152,16 @@
         <v>44574</v>
       </c>
       <c r="B237" t="n">
-        <v>8.726439476013184</v>
+        <v>8.7264404296875</v>
       </c>
       <c r="C237" t="n">
-        <v>9.110299446506351</v>
+        <v>9.110300442131042</v>
       </c>
       <c r="D237" t="n">
-        <v>8.555834036858977</v>
+        <v>8.555834971888574</v>
       </c>
       <c r="E237" t="n">
-        <v>9.042057765594588</v>
+        <v>9.042058753761445</v>
       </c>
       <c r="F237" t="n">
         <v>3017328</v>
@@ -5172,16 +5172,16 @@
         <v>44575</v>
       </c>
       <c r="B238" t="n">
-        <v>8.743499755859375</v>
+        <v>8.743500709533691</v>
       </c>
       <c r="C238" t="n">
-        <v>8.769090696819184</v>
+        <v>8.769091653284766</v>
       </c>
       <c r="D238" t="n">
-        <v>8.359639764378452</v>
+        <v>8.359640676184245</v>
       </c>
       <c r="E238" t="n">
-        <v>8.726439953136079</v>
+        <v>8.726440904949643</v>
       </c>
       <c r="F238" t="n">
         <v>2170250</v>
@@ -5272,16 +5272,16 @@
         <v>44582</v>
       </c>
       <c r="B243" t="n">
-        <v>9.536811828613281</v>
+        <v>9.536812782287598</v>
       </c>
       <c r="C243" t="n">
-        <v>9.65623538891044</v>
+        <v>9.656236354527028</v>
       </c>
       <c r="D243" t="n">
-        <v>9.289435219396422</v>
+        <v>9.289436148333257</v>
       </c>
       <c r="E243" t="n">
-        <v>9.332085960841921</v>
+        <v>9.332086894043799</v>
       </c>
       <c r="F243" t="n">
         <v>1959216</v>
@@ -5292,16 +5292,16 @@
         <v>44585</v>
       </c>
       <c r="B244" t="n">
-        <v>9.460041999816895</v>
+        <v>9.460041046142578</v>
       </c>
       <c r="C244" t="n">
-        <v>9.596526217767758</v>
+        <v>9.596525250334361</v>
       </c>
       <c r="D244" t="n">
-        <v>9.144422812706599</v>
+        <v>9.144421890850102</v>
       </c>
       <c r="E244" t="n">
-        <v>9.536814011659024</v>
+        <v>9.536813050245259</v>
       </c>
       <c r="F244" t="n">
         <v>1483323</v>
@@ -5312,16 +5312,16 @@
         <v>44586</v>
       </c>
       <c r="B245" t="n">
-        <v>9.843901634216309</v>
+        <v>9.843902587890625</v>
       </c>
       <c r="C245" t="n">
-        <v>9.929203943244776</v>
+        <v>9.929204905183155</v>
       </c>
       <c r="D245" t="n">
-        <v>9.383268011046082</v>
+        <v>9.383268920094348</v>
       </c>
       <c r="E245" t="n">
-        <v>9.391798324407251</v>
+        <v>9.391799234281931</v>
       </c>
       <c r="F245" t="n">
         <v>2635195</v>
@@ -5352,16 +5352,16 @@
         <v>44588</v>
       </c>
       <c r="B247" t="n">
-        <v>10.15952110290527</v>
+        <v>10.15952014923096</v>
       </c>
       <c r="C247" t="n">
-        <v>10.5007312029864</v>
+        <v>10.50073021728269</v>
       </c>
       <c r="D247" t="n">
-        <v>9.988917289739678</v>
+        <v>9.988916352079942</v>
       </c>
       <c r="E247" t="n">
-        <v>10.28747499350861</v>
+        <v>10.28747402782326</v>
       </c>
       <c r="F247" t="n">
         <v>2570932</v>
@@ -5372,16 +5372,16 @@
         <v>44589</v>
       </c>
       <c r="B248" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="C248" t="n">
-        <v>10.26188426089857</v>
+        <v>10.26188330324402</v>
       </c>
       <c r="D248" t="n">
-        <v>9.681827820991172</v>
+        <v>9.681826917468367</v>
       </c>
       <c r="E248" t="n">
-        <v>10.19364256931633</v>
+        <v>10.1936416180302</v>
       </c>
       <c r="F248" t="n">
         <v>1431224</v>
@@ -5392,16 +5392,16 @@
         <v>44592</v>
       </c>
       <c r="B249" t="n">
-        <v>10.47513961791992</v>
+        <v>10.47514057159424</v>
       </c>
       <c r="C249" t="n">
-        <v>10.56044193156613</v>
+        <v>10.56044289300652</v>
       </c>
       <c r="D249" t="n">
-        <v>10.1851114216895</v>
+        <v>10.18511234895917</v>
       </c>
       <c r="E249" t="n">
-        <v>10.22776299080424</v>
+        <v>10.22776392195697</v>
       </c>
       <c r="F249" t="n">
         <v>3321007</v>
@@ -5492,16 +5492,16 @@
         <v>44599</v>
       </c>
       <c r="B254" t="n">
-        <v>10.13393115997314</v>
+        <v>10.13393020629883</v>
       </c>
       <c r="C254" t="n">
-        <v>10.34718654856125</v>
+        <v>10.3471855748181</v>
       </c>
       <c r="D254" t="n">
-        <v>9.937734751205435</v>
+        <v>9.937733815994584</v>
       </c>
       <c r="E254" t="n">
-        <v>10.04862801503791</v>
+        <v>10.04862706939122</v>
       </c>
       <c r="F254" t="n">
         <v>1517482</v>
@@ -5732,16 +5732,16 @@
         <v>44615</v>
       </c>
       <c r="B266" t="n">
-        <v>9.767128944396973</v>
+        <v>9.767129898071289</v>
       </c>
       <c r="C266" t="n">
-        <v>10.11686932312569</v>
+        <v>10.11687031094908</v>
       </c>
       <c r="D266" t="n">
-        <v>9.68182663422937</v>
+        <v>9.681827579574664</v>
       </c>
       <c r="E266" t="n">
-        <v>9.775660082455282</v>
+        <v>9.775661036962589</v>
       </c>
       <c r="F266" t="n">
         <v>2319860</v>
@@ -5852,16 +5852,16 @@
         <v>44627</v>
       </c>
       <c r="B272" t="n">
-        <v>8.666728019714355</v>
+        <v>8.666728973388672</v>
       </c>
       <c r="C272" t="n">
-        <v>9.417389871825412</v>
+        <v>9.417390908101481</v>
       </c>
       <c r="D272" t="n">
-        <v>8.658197705803062</v>
+        <v>8.658198658538714</v>
       </c>
       <c r="E272" t="n">
-        <v>9.32355641880117</v>
+        <v>9.323557444751941</v>
       </c>
       <c r="F272" t="n">
         <v>2527651</v>
@@ -5932,16 +5932,16 @@
         <v>44631</v>
       </c>
       <c r="B276" t="n">
-        <v>8.615547180175781</v>
+        <v>8.615548133850098</v>
       </c>
       <c r="C276" t="n">
-        <v>9.19560359341205</v>
+        <v>9.195604611294117</v>
       </c>
       <c r="D276" t="n">
-        <v>8.470532664575069</v>
+        <v>8.470533602197403</v>
       </c>
       <c r="E276" t="n">
-        <v>9.19560359341205</v>
+        <v>9.195604611294117</v>
       </c>
       <c r="F276" t="n">
         <v>3220051</v>
@@ -5992,16 +5992,16 @@
         <v>44636</v>
       </c>
       <c r="B279" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="C279" t="n">
-        <v>9.229724687144891</v>
+        <v>9.229725670820471</v>
       </c>
       <c r="D279" t="n">
-        <v>8.589956086292677</v>
+        <v>8.589957001783693</v>
       </c>
       <c r="E279" t="n">
-        <v>8.956756289014645</v>
+        <v>8.956757243598096</v>
       </c>
       <c r="F279" t="n">
         <v>2215964</v>
@@ -6052,16 +6052,16 @@
         <v>44641</v>
       </c>
       <c r="B282" t="n">
-        <v>9.613585472106934</v>
+        <v>9.61358642578125</v>
       </c>
       <c r="C282" t="n">
-        <v>9.741539356585566</v>
+        <v>9.741540322952996</v>
       </c>
       <c r="D282" t="n">
-        <v>9.391798958899509</v>
+        <v>9.39179989057245</v>
       </c>
       <c r="E282" t="n">
-        <v>9.451511156461731</v>
+        <v>9.451512094058163</v>
       </c>
       <c r="F282" t="n">
         <v>1800179</v>
@@ -6192,16 +6192,16 @@
         <v>44650</v>
       </c>
       <c r="B289" t="n">
-        <v>11.166090965271</v>
+        <v>11.16609001159668</v>
       </c>
       <c r="C289" t="n">
-        <v>11.46464952077289</v>
+        <v>11.46464854159927</v>
       </c>
       <c r="D289" t="n">
-        <v>11.02107725737248</v>
+        <v>11.02107631608351</v>
       </c>
       <c r="E289" t="n">
-        <v>11.35375624877694</v>
+        <v>11.3537552790745</v>
       </c>
       <c r="F289" t="n">
         <v>2393651</v>
@@ -6332,16 +6332,16 @@
         <v>44659</v>
       </c>
       <c r="B296" t="n">
-        <v>10.3642463684082</v>
+        <v>10.36424541473389</v>
       </c>
       <c r="C296" t="n">
-        <v>10.53485182037612</v>
+        <v>10.53485085100341</v>
       </c>
       <c r="D296" t="n">
-        <v>10.17658193795169</v>
+        <v>10.17658100154546</v>
       </c>
       <c r="E296" t="n">
-        <v>10.53485182037612</v>
+        <v>10.53485085100341</v>
       </c>
       <c r="F296" t="n">
         <v>1523665</v>
@@ -6372,16 +6372,16 @@
         <v>44663</v>
       </c>
       <c r="B298" t="n">
-        <v>10.55191326141357</v>
+        <v>10.55191230773926</v>
       </c>
       <c r="C298" t="n">
-        <v>10.90165370888366</v>
+        <v>10.90165272360005</v>
       </c>
       <c r="D298" t="n">
-        <v>10.40689955300122</v>
+        <v>10.40689861243314</v>
       </c>
       <c r="E298" t="n">
-        <v>10.4495503041764</v>
+        <v>10.44954935975358</v>
       </c>
       <c r="F298" t="n">
         <v>1608302</v>
@@ -6392,16 +6392,16 @@
         <v>44664</v>
       </c>
       <c r="B299" t="n">
-        <v>10.60309410095215</v>
+        <v>10.60309505462646</v>
       </c>
       <c r="C299" t="n">
-        <v>10.73104799095693</v>
+        <v>10.7310489561398</v>
       </c>
       <c r="D299" t="n">
-        <v>10.38130757816608</v>
+        <v>10.38130851189225</v>
       </c>
       <c r="E299" t="n">
-        <v>10.62015472956389</v>
+        <v>10.62015568477269</v>
       </c>
       <c r="F299" t="n">
         <v>1276242</v>
@@ -6412,16 +6412,16 @@
         <v>44665</v>
       </c>
       <c r="B300" t="n">
-        <v>10.80781841278076</v>
+        <v>10.80781936645508</v>
       </c>
       <c r="C300" t="n">
-        <v>10.85046915348243</v>
+        <v>10.85047011092021</v>
       </c>
       <c r="D300" t="n">
-        <v>10.48366899036544</v>
+        <v>10.48366991543704</v>
       </c>
       <c r="E300" t="n">
-        <v>10.54338118176423</v>
+        <v>10.54338211210479</v>
       </c>
       <c r="F300" t="n">
         <v>1300569</v>
@@ -6452,16 +6452,16 @@
         <v>44670</v>
       </c>
       <c r="B302" t="n">
-        <v>10.94430541992188</v>
+        <v>10.94430446624756</v>
       </c>
       <c r="C302" t="n">
-        <v>11.07225849961239</v>
+        <v>11.07225753478839</v>
       </c>
       <c r="D302" t="n">
-        <v>10.48367169436914</v>
+        <v>10.48367078083392</v>
       </c>
       <c r="E302" t="n">
-        <v>10.68839761137404</v>
+        <v>10.68839667999924</v>
       </c>
       <c r="F302" t="n">
         <v>3002225</v>
@@ -6552,16 +6552,16 @@
         <v>44678</v>
       </c>
       <c r="B307" t="n">
-        <v>10.60309410095215</v>
+        <v>10.60309505462646</v>
       </c>
       <c r="C307" t="n">
-        <v>10.79076019109803</v>
+        <v>10.79076116165161</v>
       </c>
       <c r="D307" t="n">
-        <v>10.4068985210837</v>
+        <v>10.40689945711159</v>
       </c>
       <c r="E307" t="n">
-        <v>10.4068985210837</v>
+        <v>10.40689945711159</v>
       </c>
       <c r="F307" t="n">
         <v>2204206</v>
@@ -6572,16 +6572,16 @@
         <v>44679</v>
       </c>
       <c r="B308" t="n">
-        <v>11.68643569946289</v>
+        <v>11.68643474578857</v>
       </c>
       <c r="C308" t="n">
-        <v>11.8996919216672</v>
+        <v>11.89969095059006</v>
       </c>
       <c r="D308" t="n">
-        <v>10.44102045023973</v>
+        <v>10.44101959819782</v>
       </c>
       <c r="E308" t="n">
-        <v>10.81635100551931</v>
+        <v>10.81635012284846</v>
       </c>
       <c r="F308" t="n">
         <v>5881398</v>
@@ -6592,16 +6592,16 @@
         <v>44680</v>
       </c>
       <c r="B309" t="n">
-        <v>11.65231418609619</v>
+        <v>11.65231323242188</v>
       </c>
       <c r="C309" t="n">
-        <v>11.85704091356727</v>
+        <v>11.85703994313725</v>
       </c>
       <c r="D309" t="n">
-        <v>11.46464891254633</v>
+        <v>11.46464797423132</v>
       </c>
       <c r="E309" t="n">
-        <v>11.68643544477193</v>
+        <v>11.68643448830498</v>
       </c>
       <c r="F309" t="n">
         <v>6890958</v>
@@ -6632,16 +6632,16 @@
         <v>44684</v>
       </c>
       <c r="B311" t="n">
-        <v>11.31963539123535</v>
+        <v>11.31963443756104</v>
       </c>
       <c r="C311" t="n">
-        <v>11.52436129735855</v>
+        <v>11.52436032643616</v>
       </c>
       <c r="D311" t="n">
-        <v>11.25992401219248</v>
+        <v>11.25992306354883</v>
       </c>
       <c r="E311" t="n">
-        <v>11.38787708508197</v>
+        <v>11.38787612565832</v>
       </c>
       <c r="F311" t="n">
         <v>2034324</v>
@@ -6672,16 +6672,16 @@
         <v>44686</v>
       </c>
       <c r="B313" t="n">
-        <v>11.60966205596924</v>
+        <v>11.60966300964355</v>
       </c>
       <c r="C313" t="n">
-        <v>11.76320605257407</v>
+        <v>11.76320701886124</v>
       </c>
       <c r="D313" t="n">
-        <v>11.38787555013271</v>
+        <v>11.3878764855884</v>
       </c>
       <c r="E313" t="n">
-        <v>11.76320605257407</v>
+        <v>11.76320701886124</v>
       </c>
       <c r="F313" t="n">
         <v>3999622</v>
@@ -6712,16 +6712,16 @@
         <v>44690</v>
       </c>
       <c r="B315" t="n">
-        <v>10.99548530578613</v>
+        <v>10.99548625946045</v>
       </c>
       <c r="C315" t="n">
-        <v>11.41346741015497</v>
+        <v>11.41346840008224</v>
       </c>
       <c r="D315" t="n">
-        <v>10.85900192549901</v>
+        <v>10.85900286733568</v>
       </c>
       <c r="E315" t="n">
-        <v>11.40493792039742</v>
+        <v>11.4049389095849</v>
       </c>
       <c r="F315" t="n">
         <v>3635836</v>
@@ -6732,16 +6732,16 @@
         <v>44691</v>
       </c>
       <c r="B316" t="n">
-        <v>11.22580242156982</v>
+        <v>11.22580146789551</v>
       </c>
       <c r="C316" t="n">
-        <v>11.4049382025767</v>
+        <v>11.40493723368412</v>
       </c>
       <c r="D316" t="n">
-        <v>11.02107652149054</v>
+        <v>11.02107558520846</v>
       </c>
       <c r="E316" t="n">
-        <v>11.11490915697827</v>
+        <v>11.11490821272475</v>
       </c>
       <c r="F316" t="n">
         <v>2926103</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381214141846</v>
+        <v>11.93381118774414</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470540028707</v>
+        <v>12.04470443775087</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908542732132</v>
+        <v>11.72908449000746</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81438856843816</v>
+        <v>11.81438762430742</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6932,16 +6932,16 @@
         <v>44705</v>
       </c>
       <c r="B326" t="n">
-        <v>12.26649188995361</v>
+        <v>12.2664909362793</v>
       </c>
       <c r="C326" t="n">
-        <v>12.62476263215845</v>
+        <v>12.62476165062991</v>
       </c>
       <c r="D326" t="n">
-        <v>12.02764555306706</v>
+        <v>12.02764461796216</v>
       </c>
       <c r="E326" t="n">
-        <v>12.53092999542028</v>
+        <v>12.53092902118688</v>
       </c>
       <c r="F326" t="n">
         <v>3539137</v>
@@ -6992,16 +6992,16 @@
         <v>44708</v>
       </c>
       <c r="B329" t="n">
-        <v>13.06833457946777</v>
+        <v>13.06833362579346</v>
       </c>
       <c r="C329" t="n">
-        <v>13.35836279785892</v>
+        <v>13.35836182301952</v>
       </c>
       <c r="D329" t="n">
-        <v>12.76124655671047</v>
+        <v>12.7612456254462</v>
       </c>
       <c r="E329" t="n">
-        <v>12.78683750013469</v>
+        <v>12.78683656700289</v>
       </c>
       <c r="F329" t="n">
         <v>4177410</v>
@@ -7132,16 +7132,16 @@
         <v>44719</v>
       </c>
       <c r="B336" t="n">
-        <v>12.02764415740967</v>
+        <v>12.02764511108398</v>
       </c>
       <c r="C336" t="n">
-        <v>12.37738371978268</v>
+        <v>12.37738470118792</v>
       </c>
       <c r="D336" t="n">
-        <v>11.87410016041255</v>
+        <v>11.87410110191233</v>
       </c>
       <c r="E336" t="n">
-        <v>12.36885340610692</v>
+        <v>12.36885438683579</v>
       </c>
       <c r="F336" t="n">
         <v>3370370</v>
@@ -7152,16 +7152,16 @@
         <v>44720</v>
       </c>
       <c r="B337" t="n">
-        <v>12.02764415740967</v>
+        <v>12.02764511108398</v>
       </c>
       <c r="C337" t="n">
-        <v>12.14706772428701</v>
+        <v>12.14706868743044</v>
       </c>
       <c r="D337" t="n">
-        <v>11.80585847558975</v>
+        <v>11.80585941167863</v>
       </c>
       <c r="E337" t="n">
-        <v>11.96793196167938</v>
+        <v>11.9679329106191</v>
       </c>
       <c r="F337" t="n">
         <v>2224783</v>
@@ -7232,16 +7232,16 @@
         <v>44726</v>
       </c>
       <c r="B341" t="n">
-        <v>10.69692707061768</v>
+        <v>10.69692611694336</v>
       </c>
       <c r="C341" t="n">
-        <v>10.94430454411216</v>
+        <v>10.94430356838314</v>
       </c>
       <c r="D341" t="n">
-        <v>10.57750431574103</v>
+        <v>10.57750337271373</v>
       </c>
       <c r="E341" t="n">
-        <v>10.79076053093742</v>
+        <v>10.79075956889747</v>
       </c>
       <c r="F341" t="n">
         <v>2253062</v>
@@ -7252,16 +7252,16 @@
         <v>44727</v>
       </c>
       <c r="B342" t="n">
-        <v>10.83341121673584</v>
+        <v>10.83341026306152</v>
       </c>
       <c r="C342" t="n">
-        <v>11.07225754969472</v>
+        <v>11.07225657499456</v>
       </c>
       <c r="D342" t="n">
-        <v>10.67133606533815</v>
+        <v>10.67133512593145</v>
       </c>
       <c r="E342" t="n">
-        <v>10.88459227930441</v>
+        <v>10.88459132112458</v>
       </c>
       <c r="F342" t="n">
         <v>3158221</v>
@@ -7272,16 +7272,16 @@
         <v>44729</v>
       </c>
       <c r="B343" t="n">
-        <v>10.66280555725098</v>
+        <v>10.66280460357666</v>
       </c>
       <c r="C343" t="n">
-        <v>10.69692681473284</v>
+        <v>10.69692585800674</v>
       </c>
       <c r="D343" t="n">
-        <v>10.2960053376542</v>
+        <v>10.29600441678626</v>
       </c>
       <c r="E343" t="n">
-        <v>10.69692681473284</v>
+        <v>10.69692585800674</v>
       </c>
       <c r="F343" t="n">
         <v>2862346</v>
@@ -7312,16 +7312,16 @@
         <v>44733</v>
       </c>
       <c r="B345" t="n">
-        <v>10.4666109085083</v>
+        <v>10.46660995483398</v>
       </c>
       <c r="C345" t="n">
-        <v>10.65427617742885</v>
+        <v>10.65427520665525</v>
       </c>
       <c r="D345" t="n">
-        <v>10.33012670175548</v>
+        <v>10.33012576051704</v>
       </c>
       <c r="E345" t="n">
-        <v>10.43248965067427</v>
+        <v>10.43248870010894</v>
       </c>
       <c r="F345" t="n">
         <v>1967020</v>
@@ -7332,16 +7332,16 @@
         <v>44734</v>
       </c>
       <c r="B346" t="n">
-        <v>10.5604419708252</v>
+        <v>10.56044292449951</v>
       </c>
       <c r="C346" t="n">
-        <v>10.77369816802514</v>
+        <v>10.77369914095784</v>
       </c>
       <c r="D346" t="n">
-        <v>10.33012597049919</v>
+        <v>10.33012690337453</v>
       </c>
       <c r="E346" t="n">
-        <v>10.42395859831718</v>
+        <v>10.42395953966619</v>
       </c>
       <c r="F346" t="n">
         <v>1465281</v>
@@ -7352,16 +7352,16 @@
         <v>44735</v>
       </c>
       <c r="B347" t="n">
-        <v>10.80781841278076</v>
+        <v>10.80781936645508</v>
       </c>
       <c r="C347" t="n">
-        <v>10.91018134488122</v>
+        <v>10.91018230758797</v>
       </c>
       <c r="D347" t="n">
-        <v>10.48366899036544</v>
+        <v>10.48366991543704</v>
       </c>
       <c r="E347" t="n">
-        <v>10.49219930342241</v>
+        <v>10.49220022924672</v>
       </c>
       <c r="F347" t="n">
         <v>2364459</v>
@@ -7432,16 +7432,16 @@
         <v>44741</v>
       </c>
       <c r="B351" t="n">
-        <v>10.16805171966553</v>
+        <v>10.16805076599121</v>
       </c>
       <c r="C351" t="n">
-        <v>10.33865636248849</v>
+        <v>10.33865539281295</v>
       </c>
       <c r="D351" t="n">
-        <v>10.03156833524049</v>
+        <v>10.03156739436712</v>
       </c>
       <c r="E351" t="n">
-        <v>10.32159655787287</v>
+        <v>10.32159558979739</v>
       </c>
       <c r="F351" t="n">
         <v>1480384</v>
@@ -7512,16 +7512,16 @@
         <v>44747</v>
       </c>
       <c r="B355" t="n">
-        <v>9.622115135192871</v>
+        <v>9.622114181518555</v>
       </c>
       <c r="C355" t="n">
-        <v>9.681827333833224</v>
+        <v>9.681826374240668</v>
       </c>
       <c r="D355" t="n">
-        <v>9.178542925352392</v>
+        <v>9.178542015641739</v>
       </c>
       <c r="E355" t="n">
-        <v>9.681827333833224</v>
+        <v>9.681826374240668</v>
       </c>
       <c r="F355" t="n">
         <v>3899578</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.110301971435547</v>
+        <v>9.11030101776123</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707419937092304</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076181533814751</v>
+        <v>9.076180583712192</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707419937092304</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7612,16 +7612,16 @@
         <v>44754</v>
       </c>
       <c r="B360" t="n">
-        <v>9.229724884033203</v>
+        <v>9.22972583770752</v>
       </c>
       <c r="C360" t="n">
-        <v>9.289436258569864</v>
+        <v>9.289437218413942</v>
       </c>
       <c r="D360" t="n">
-        <v>8.879984477223353</v>
+        <v>8.879985394760249</v>
       </c>
       <c r="E360" t="n">
-        <v>9.229724884033203</v>
+        <v>9.22972583770752</v>
       </c>
       <c r="F360" t="n">
         <v>1719496</v>
@@ -7712,16 +7712,16 @@
         <v>44761</v>
       </c>
       <c r="B365" t="n">
-        <v>9.767128944396973</v>
+        <v>9.767129898071289</v>
       </c>
       <c r="C365" t="n">
-        <v>9.929204075840321</v>
+        <v>9.929205045339851</v>
       </c>
       <c r="D365" t="n">
-        <v>9.562403894744662</v>
+        <v>9.562404828429376</v>
       </c>
       <c r="E365" t="n">
-        <v>9.562403894744662</v>
+        <v>9.562404828429376</v>
       </c>
       <c r="F365" t="n">
         <v>2310433</v>
@@ -7732,16 +7732,16 @@
         <v>44762</v>
       </c>
       <c r="B366" t="n">
-        <v>10.08274936676025</v>
+        <v>10.08274841308594</v>
       </c>
       <c r="C366" t="n">
-        <v>10.20217294619664</v>
+        <v>10.20217198122667</v>
       </c>
       <c r="D366" t="n">
-        <v>9.724478628451092</v>
+        <v>9.724477708663724</v>
       </c>
       <c r="E366" t="n">
-        <v>9.767130201315277</v>
+        <v>9.767129277493721</v>
       </c>
       <c r="F366" t="n">
         <v>1476532</v>
@@ -7792,16 +7792,16 @@
         <v>44767</v>
       </c>
       <c r="B369" t="n">
-        <v>10.17658233642578</v>
+        <v>10.1765832901001</v>
       </c>
       <c r="C369" t="n">
-        <v>10.41542865919991</v>
+        <v>10.41542963525714</v>
       </c>
       <c r="D369" t="n">
-        <v>10.11687013729478</v>
+        <v>10.11687108537331</v>
       </c>
       <c r="E369" t="n">
-        <v>10.27041414303648</v>
+        <v>10.27041510550403</v>
       </c>
       <c r="F369" t="n">
         <v>1372535</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.50926113128662</v>
+        <v>10.50926208496094</v>
       </c>
       <c r="C371" t="n">
-        <v>10.61162407509244</v>
+        <v>10.6116250380558</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421841396606</v>
+        <v>10.07421932816195</v>
       </c>
       <c r="E371" t="n">
-        <v>10.12539947357733</v>
+        <v>10.1254003924177</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7852,16 +7852,16 @@
         <v>44770</v>
       </c>
       <c r="B372" t="n">
-        <v>10.74810791015625</v>
+        <v>10.74810695648193</v>
       </c>
       <c r="C372" t="n">
-        <v>10.84194136852631</v>
+        <v>10.8419404065262</v>
       </c>
       <c r="D372" t="n">
-        <v>10.21923336502487</v>
+        <v>10.21923245827733</v>
       </c>
       <c r="E372" t="n">
-        <v>10.21923336502487</v>
+        <v>10.21923245827733</v>
       </c>
       <c r="F372" t="n">
         <v>1467207</v>
@@ -7872,16 +7872,16 @@
         <v>44771</v>
       </c>
       <c r="B373" t="n">
-        <v>11.60113334655762</v>
+        <v>11.6011323928833</v>
       </c>
       <c r="C373" t="n">
-        <v>11.60113334655762</v>
+        <v>11.6011323928833</v>
       </c>
       <c r="D373" t="n">
-        <v>10.81635097853681</v>
+        <v>10.81635008937574</v>
       </c>
       <c r="E373" t="n">
-        <v>10.98695562604133</v>
+        <v>10.98695472285566</v>
       </c>
       <c r="F373" t="n">
         <v>3378580</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.1621675491333</v>
+        <v>13.16216659545898</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718124064354</v>
+        <v>13.30718027646215</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271576790837</v>
+        <v>12.75271484390118</v>
       </c>
       <c r="E379" t="n">
-        <v>12.79536651411238</v>
+        <v>12.7953655870149</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248371124268</v>
+        <v>13.39248466491699</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634537898129</v>
+        <v>13.77634635999027</v>
       </c>
       <c r="D381" t="n">
-        <v>13.17922832861007</v>
+        <v>13.17922926709854</v>
       </c>
       <c r="E381" t="n">
-        <v>13.30718139327297</v>
+        <v>13.30718234087294</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8052,16 +8052,16 @@
         <v>44784</v>
       </c>
       <c r="B382" t="n">
-        <v>13.36689376831055</v>
+        <v>13.36689281463623</v>
       </c>
       <c r="C382" t="n">
-        <v>13.63986135430908</v>
+        <v>13.63986038115962</v>
       </c>
       <c r="D382" t="n">
-        <v>13.11951630083012</v>
+        <v>13.1195153648052</v>
       </c>
       <c r="E382" t="n">
-        <v>13.52043777775243</v>
+        <v>13.52043681312337</v>
       </c>
       <c r="F382" t="n">
         <v>2014153</v>
@@ -8072,16 +8072,16 @@
         <v>44785</v>
       </c>
       <c r="B383" t="n">
-        <v>13.75928401947021</v>
+        <v>13.75928497314453</v>
       </c>
       <c r="C383" t="n">
-        <v>13.84458633290799</v>
+        <v>13.84458729249473</v>
       </c>
       <c r="D383" t="n">
-        <v>13.47778613775057</v>
+        <v>13.47778707191389</v>
       </c>
       <c r="E383" t="n">
-        <v>13.47778613775057</v>
+        <v>13.47778707191389</v>
       </c>
       <c r="F383" t="n">
         <v>2291478</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066959381104</v>
+        <v>12.88066864013672</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801884508153</v>
+        <v>12.83801789456504</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8312,16 +8312,16 @@
         <v>44803</v>
       </c>
       <c r="B395" t="n">
-        <v>12.21531105041504</v>
+        <v>12.21531009674072</v>
       </c>
       <c r="C395" t="n">
-        <v>12.47121884590617</v>
+        <v>12.47121787225261</v>
       </c>
       <c r="D395" t="n">
-        <v>12.06176703278704</v>
+        <v>12.06176609110022</v>
       </c>
       <c r="E395" t="n">
-        <v>12.25796262452468</v>
+        <v>12.25796166752047</v>
       </c>
       <c r="F395" t="n">
         <v>2841466</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.33473300933838</v>
+        <v>12.33473491668701</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121720393626</v>
+        <v>12.47121913238976</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646230773766</v>
+        <v>11.97646415968605</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22383975583696</v>
+        <v>12.22384164603791</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8472,16 +8472,16 @@
         <v>44816</v>
       </c>
       <c r="B403" t="n">
-        <v>12.30696201324463</v>
+        <v>12.30696105957031</v>
       </c>
       <c r="C403" t="n">
-        <v>12.58102134762649</v>
+        <v>12.58102037271514</v>
       </c>
       <c r="D403" t="n">
-        <v>12.05859669488552</v>
+        <v>12.05859576045719</v>
       </c>
       <c r="E403" t="n">
-        <v>12.05859669488552</v>
+        <v>12.05859576045719</v>
       </c>
       <c r="F403" t="n">
         <v>4043263</v>
@@ -8612,16 +8612,16 @@
         <v>44825</v>
       </c>
       <c r="B410" t="n">
-        <v>11.65607070922852</v>
+        <v>11.65607166290283</v>
       </c>
       <c r="C410" t="n">
-        <v>12.10998235665763</v>
+        <v>12.10998334747001</v>
       </c>
       <c r="D410" t="n">
-        <v>11.50191321893803</v>
+        <v>11.50191415999951</v>
       </c>
       <c r="E410" t="n">
-        <v>11.9472590954252</v>
+        <v>11.94726007292391</v>
       </c>
       <c r="F410" t="n">
         <v>3396829</v>
@@ -8672,16 +8672,16 @@
         <v>44830</v>
       </c>
       <c r="B413" t="n">
-        <v>11.45909214019775</v>
+        <v>11.45909118652344</v>
       </c>
       <c r="C413" t="n">
-        <v>11.84448752702055</v>
+        <v>11.844486541272</v>
       </c>
       <c r="D413" t="n">
-        <v>11.34775525533786</v>
+        <v>11.34775431092947</v>
       </c>
       <c r="E413" t="n">
-        <v>11.81879433631571</v>
+        <v>11.81879335270545</v>
       </c>
       <c r="F413" t="n">
         <v>3443068</v>
@@ -8692,16 +8692,16 @@
         <v>44831</v>
       </c>
       <c r="B414" t="n">
-        <v>11.30493450164795</v>
+        <v>11.30493354797363</v>
       </c>
       <c r="C414" t="n">
-        <v>11.63894352718433</v>
+        <v>11.6389425453333</v>
       </c>
       <c r="D414" t="n">
-        <v>11.26211306428218</v>
+        <v>11.26211211422024</v>
       </c>
       <c r="E414" t="n">
-        <v>11.53617158275647</v>
+        <v>11.53617060957519</v>
       </c>
       <c r="F414" t="n">
         <v>2656202</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186485290527</v>
+        <v>11.56186389923096</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889411306563</v>
+        <v>11.69889314808853</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072675530685</v>
+        <v>11.21072583059598</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775601546721</v>
+        <v>11.34775507945355</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8732,16 +8732,16 @@
         <v>44833</v>
       </c>
       <c r="B416" t="n">
-        <v>11.61325073242188</v>
+        <v>11.61324977874756</v>
       </c>
       <c r="C416" t="n">
-        <v>11.66463629045436</v>
+        <v>11.66463533256029</v>
       </c>
       <c r="D416" t="n">
-        <v>11.29636913906888</v>
+        <v>11.29636821141672</v>
       </c>
       <c r="E416" t="n">
-        <v>11.45052828691627</v>
+        <v>11.45052734660464</v>
       </c>
       <c r="F416" t="n">
         <v>3327572</v>
@@ -8852,16 +8852,16 @@
         <v>44841</v>
       </c>
       <c r="B422" t="n">
-        <v>12.6238431930542</v>
+        <v>12.62384414672852</v>
       </c>
       <c r="C422" t="n">
-        <v>12.92359488443413</v>
+        <v>12.92359586075333</v>
       </c>
       <c r="D422" t="n">
-        <v>12.54676362127082</v>
+        <v>12.54676456912213</v>
       </c>
       <c r="E422" t="n">
-        <v>12.92359488443413</v>
+        <v>12.92359586075333</v>
       </c>
       <c r="F422" t="n">
         <v>1382517</v>
@@ -8952,16 +8952,16 @@
         <v>44851</v>
       </c>
       <c r="B427" t="n">
-        <v>12.64953517913818</v>
+        <v>12.6495361328125</v>
       </c>
       <c r="C427" t="n">
-        <v>13.19765381341301</v>
+        <v>13.19765480841111</v>
       </c>
       <c r="D427" t="n">
-        <v>12.58102055599965</v>
+        <v>12.5810215045085</v>
       </c>
       <c r="E427" t="n">
-        <v>12.87220811663006</v>
+        <v>12.87220908709215</v>
       </c>
       <c r="F427" t="n">
         <v>1088124</v>
@@ -9012,16 +9012,16 @@
         <v>44854</v>
       </c>
       <c r="B430" t="n">
-        <v>12.78656482696533</v>
+        <v>12.78656578063965</v>
       </c>
       <c r="C430" t="n">
-        <v>13.08631734333896</v>
+        <v>13.08631831937005</v>
       </c>
       <c r="D430" t="n">
-        <v>12.65809969840043</v>
+        <v>12.65810064249329</v>
       </c>
       <c r="E430" t="n">
-        <v>13.08631734333896</v>
+        <v>13.08631831937005</v>
       </c>
       <c r="F430" t="n">
         <v>2107193</v>
@@ -9032,16 +9032,16 @@
         <v>44855</v>
       </c>
       <c r="B431" t="n">
-        <v>13.08631706237793</v>
+        <v>13.08631801605225</v>
       </c>
       <c r="C431" t="n">
-        <v>13.26616856834072</v>
+        <v>13.26616953512184</v>
       </c>
       <c r="D431" t="n">
-        <v>12.58958480281398</v>
+        <v>12.58958572028859</v>
       </c>
       <c r="E431" t="n">
-        <v>12.74374311869877</v>
+        <v>12.74374404740777</v>
       </c>
       <c r="F431" t="n">
         <v>1434409</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805095672607</v>
+        <v>12.71805191040039</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775399772944</v>
+        <v>13.07775497837641</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235858915441</v>
+        <v>12.69235954090216</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87220928507275</v>
+        <v>12.87221025030677</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9092,16 +9092,16 @@
         <v>44860</v>
       </c>
       <c r="B434" t="n">
-        <v>12.2983980178833</v>
+        <v>12.29839897155762</v>
       </c>
       <c r="C434" t="n">
-        <v>13.00923831573856</v>
+        <v>13.0092393245347</v>
       </c>
       <c r="D434" t="n">
-        <v>12.17849783090068</v>
+        <v>12.17849877527738</v>
       </c>
       <c r="E434" t="n">
-        <v>12.61527879154568</v>
+        <v>12.61527976979239</v>
       </c>
       <c r="F434" t="n">
         <v>4556230</v>
@@ -9112,16 +9112,16 @@
         <v>44861</v>
       </c>
       <c r="B435" t="n">
-        <v>13.13770389556885</v>
+        <v>13.13770484924316</v>
       </c>
       <c r="C435" t="n">
-        <v>13.30042633889646</v>
+        <v>13.30042730438291</v>
       </c>
       <c r="D435" t="n">
-        <v>12.22131809049146</v>
+        <v>12.22131897764474</v>
       </c>
       <c r="E435" t="n">
-        <v>12.35834816743837</v>
+        <v>12.35834906453876</v>
       </c>
       <c r="F435" t="n">
         <v>3242667</v>
@@ -9192,16 +9192,16 @@
         <v>44868</v>
       </c>
       <c r="B439" t="n">
-        <v>13.9341869354248</v>
+        <v>13.93418788909912</v>
       </c>
       <c r="C439" t="n">
-        <v>14.04552216479015</v>
+        <v>14.0455231260844</v>
       </c>
       <c r="D439" t="n">
-        <v>13.38606831348592</v>
+        <v>13.38606922964626</v>
       </c>
       <c r="E439" t="n">
-        <v>13.38606831348592</v>
+        <v>13.38606922964626</v>
       </c>
       <c r="F439" t="n">
         <v>2966749</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.40319728851318</v>
+        <v>13.4031982421875</v>
       </c>
       <c r="C441" t="n">
-        <v>14.03695880976449</v>
+        <v>14.03695980853268</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037667840605</v>
+        <v>13.36037762903356</v>
       </c>
       <c r="E441" t="n">
-        <v>13.9341876963408</v>
+        <v>13.93418868779654</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9272,16 +9272,16 @@
         <v>44874</v>
       </c>
       <c r="B443" t="n">
-        <v>13.13770389556885</v>
+        <v>13.13770484924316</v>
       </c>
       <c r="C443" t="n">
-        <v>13.55735659936989</v>
+        <v>13.55735758350707</v>
       </c>
       <c r="D443" t="n">
-        <v>12.98354557436813</v>
+        <v>12.983546516852</v>
       </c>
       <c r="E443" t="n">
-        <v>13.29186139218626</v>
+        <v>13.29186235705097</v>
       </c>
       <c r="F443" t="n">
         <v>3144132</v>
@@ -9292,16 +9292,16 @@
         <v>44875</v>
       </c>
       <c r="B444" t="n">
-        <v>12.2470121383667</v>
+        <v>12.24701118469238</v>
       </c>
       <c r="C444" t="n">
-        <v>12.83795140918214</v>
+        <v>12.83795040949141</v>
       </c>
       <c r="D444" t="n">
-        <v>11.67320111185027</v>
+        <v>11.6732002028586</v>
       </c>
       <c r="E444" t="n">
-        <v>12.83795140918214</v>
+        <v>12.83795040949141</v>
       </c>
       <c r="F444" t="n">
         <v>10581398</v>
@@ -9312,16 +9312,16 @@
         <v>44876</v>
       </c>
       <c r="B445" t="n">
-        <v>11.51904296875</v>
+        <v>11.51904201507568</v>
       </c>
       <c r="C445" t="n">
-        <v>12.25557732774508</v>
+        <v>12.25557631309227</v>
       </c>
       <c r="D445" t="n">
-        <v>11.34775638792752</v>
+        <v>11.34775544843421</v>
       </c>
       <c r="E445" t="n">
-        <v>11.80166644554462</v>
+        <v>11.80166546847159</v>
       </c>
       <c r="F445" t="n">
         <v>9635321</v>
@@ -9352,16 +9352,16 @@
         <v>44881</v>
       </c>
       <c r="B447" t="n">
-        <v>11.26211261749268</v>
+        <v>11.26211166381836</v>
       </c>
       <c r="C447" t="n">
-        <v>12.15280359178205</v>
+        <v>12.15280256268413</v>
       </c>
       <c r="D447" t="n">
-        <v>11.15934067714197</v>
+        <v>11.15933973217037</v>
       </c>
       <c r="E447" t="n">
-        <v>12.06716072044812</v>
+        <v>12.06715969860243</v>
       </c>
       <c r="F447" t="n">
         <v>3929079</v>
@@ -9392,16 +9392,16 @@
         <v>44883</v>
       </c>
       <c r="B449" t="n">
-        <v>10.92810249328613</v>
+        <v>10.92810153961182</v>
       </c>
       <c r="C449" t="n">
-        <v>11.38201332758762</v>
+        <v>11.38201233430139</v>
       </c>
       <c r="D449" t="n">
-        <v>10.91953837129458</v>
+        <v>10.91953741836764</v>
       </c>
       <c r="E449" t="n">
-        <v>11.13364636858307</v>
+        <v>11.13364539697134</v>
       </c>
       <c r="F449" t="n">
         <v>5719164</v>
@@ -9492,16 +9492,16 @@
         <v>44890</v>
       </c>
       <c r="B454" t="n">
-        <v>10.95379638671875</v>
+        <v>10.95379543304443</v>
       </c>
       <c r="C454" t="n">
-        <v>11.54473650913719</v>
+        <v>11.54473550401364</v>
       </c>
       <c r="D454" t="n">
-        <v>10.89384587976446</v>
+        <v>10.89384493130964</v>
       </c>
       <c r="E454" t="n">
-        <v>11.51047836980616</v>
+        <v>11.51047736766524</v>
       </c>
       <c r="F454" t="n">
         <v>2880833</v>
@@ -9512,16 +9512,16 @@
         <v>44893</v>
       </c>
       <c r="B455" t="n">
-        <v>10.96235942840576</v>
+        <v>10.96236038208008</v>
       </c>
       <c r="C455" t="n">
-        <v>11.18503236460255</v>
+        <v>11.18503333764837</v>
       </c>
       <c r="D455" t="n">
-        <v>10.84245842631905</v>
+        <v>10.84245936956254</v>
       </c>
       <c r="E455" t="n">
-        <v>10.95379530670907</v>
+        <v>10.95379625963835</v>
       </c>
       <c r="F455" t="n">
         <v>2642270</v>
@@ -9572,16 +9572,16 @@
         <v>44896</v>
       </c>
       <c r="B458" t="n">
-        <v>11.15077495574951</v>
+        <v>11.15077590942383</v>
       </c>
       <c r="C458" t="n">
-        <v>11.33919057892909</v>
+        <v>11.33919154871773</v>
       </c>
       <c r="D458" t="n">
-        <v>10.97092345419175</v>
+        <v>10.9709243924842</v>
       </c>
       <c r="E458" t="n">
-        <v>11.32206233568545</v>
+        <v>11.32206330400918</v>
       </c>
       <c r="F458" t="n">
         <v>2224001</v>
@@ -9652,16 +9652,16 @@
         <v>44902</v>
       </c>
       <c r="B462" t="n">
-        <v>10.3628568649292</v>
+        <v>10.36285781860352</v>
       </c>
       <c r="C462" t="n">
-        <v>10.91097388904668</v>
+        <v>10.91097489316318</v>
       </c>
       <c r="D462" t="n">
-        <v>10.24295585361184</v>
+        <v>10.24295679625189</v>
       </c>
       <c r="E462" t="n">
-        <v>10.59409394062459</v>
+        <v>10.59409491557922</v>
       </c>
       <c r="F462" t="n">
         <v>7006882</v>
@@ -9712,16 +9712,16 @@
         <v>44907</v>
       </c>
       <c r="B465" t="n">
-        <v>9.50642204284668</v>
+        <v>9.506421089172363</v>
       </c>
       <c r="C465" t="n">
-        <v>10.02884668216042</v>
+        <v>10.02884567607701</v>
       </c>
       <c r="D465" t="n">
-        <v>9.42077834844417</v>
+        <v>9.420777403361539</v>
       </c>
       <c r="E465" t="n">
-        <v>9.57493666853537</v>
+        <v>9.57493570798774</v>
       </c>
       <c r="F465" t="n">
         <v>6343387</v>
@@ -9772,16 +9772,16 @@
         <v>44910</v>
       </c>
       <c r="B468" t="n">
-        <v>9.831867218017578</v>
+        <v>9.831866264343262</v>
       </c>
       <c r="C468" t="n">
-        <v>9.908946799099628</v>
+        <v>9.908945837948723</v>
       </c>
       <c r="D468" t="n">
-        <v>9.352264783785065</v>
+        <v>9.352263876631365</v>
       </c>
       <c r="E468" t="n">
-        <v>9.42934354028373</v>
+        <v>9.429342625653522</v>
       </c>
       <c r="F468" t="n">
         <v>3938569</v>
@@ -9812,16 +9812,16 @@
         <v>44914</v>
       </c>
       <c r="B470" t="n">
-        <v>9.951767921447754</v>
+        <v>9.951766967773438</v>
       </c>
       <c r="C470" t="n">
-        <v>10.03741162283501</v>
+        <v>10.03741066095349</v>
       </c>
       <c r="D470" t="n">
-        <v>9.686273519105638</v>
+        <v>9.686272590873555</v>
       </c>
       <c r="E470" t="n">
-        <v>9.840431027185991</v>
+        <v>9.840430084181047</v>
       </c>
       <c r="F470" t="n">
         <v>3753211</v>
@@ -9852,16 +9852,16 @@
         <v>44916</v>
       </c>
       <c r="B472" t="n">
-        <v>10.42280673980713</v>
+        <v>10.42280578613281</v>
       </c>
       <c r="C472" t="n">
-        <v>10.58553001509685</v>
+        <v>10.58552904653355</v>
       </c>
       <c r="D472" t="n">
-        <v>10.08879771587911</v>
+        <v>10.08879679276622</v>
       </c>
       <c r="E472" t="n">
-        <v>10.36285705761706</v>
+        <v>10.36285610942807</v>
       </c>
       <c r="F472" t="n">
         <v>3195923</v>
@@ -9912,16 +9912,16 @@
         <v>44921</v>
       </c>
       <c r="B475" t="n">
-        <v>10.66260814666748</v>
+        <v>10.6626091003418</v>
       </c>
       <c r="C475" t="n">
-        <v>10.87671696917752</v>
+        <v>10.87671794200195</v>
       </c>
       <c r="D475" t="n">
-        <v>10.57696362816352</v>
+        <v>10.5769645741777</v>
       </c>
       <c r="E475" t="n">
-        <v>10.82533058790846</v>
+        <v>10.82533155613684</v>
       </c>
       <c r="F475" t="n">
         <v>1667319</v>
@@ -9952,16 +9952,16 @@
         <v>44923</v>
       </c>
       <c r="B477" t="n">
-        <v>10.96907043457031</v>
+        <v>10.96907138824463</v>
       </c>
       <c r="C477" t="n">
-        <v>11.03030139033512</v>
+        <v>11.03030234933299</v>
       </c>
       <c r="D477" t="n">
-        <v>10.43548759461291</v>
+        <v>10.4354885018964</v>
       </c>
       <c r="E477" t="n">
-        <v>10.56669570271517</v>
+        <v>10.56669662140617</v>
       </c>
       <c r="F477" t="n">
         <v>2605824</v>
@@ -10052,16 +10052,16 @@
         <v>44931</v>
       </c>
       <c r="B482" t="n">
-        <v>10.05935573577881</v>
+        <v>10.05935478210449</v>
       </c>
       <c r="C482" t="n">
-        <v>10.33926773935673</v>
+        <v>10.33926675914544</v>
       </c>
       <c r="D482" t="n">
-        <v>9.779443732200887</v>
+        <v>9.779442805063548</v>
       </c>
       <c r="E482" t="n">
-        <v>9.796937811326897</v>
+        <v>9.796936882531035</v>
       </c>
       <c r="F482" t="n">
         <v>3524036</v>
@@ -10192,16 +10192,16 @@
         <v>44942</v>
       </c>
       <c r="B489" t="n">
-        <v>10.8028736114502</v>
+        <v>10.80287265777588</v>
       </c>
       <c r="C489" t="n">
-        <v>11.3014683871045</v>
+        <v>11.30146738941439</v>
       </c>
       <c r="D489" t="n">
-        <v>10.69790744273759</v>
+        <v>10.69790649832965</v>
       </c>
       <c r="E489" t="n">
-        <v>11.25773234310836</v>
+        <v>11.25773134927926</v>
       </c>
       <c r="F489" t="n">
         <v>2251058</v>
@@ -10272,16 +10272,16 @@
         <v>44946</v>
       </c>
       <c r="B493" t="n">
-        <v>11.86129379272461</v>
+        <v>11.86129283905029</v>
       </c>
       <c r="C493" t="n">
-        <v>12.0187438835161</v>
+        <v>12.01874291718245</v>
       </c>
       <c r="D493" t="n">
-        <v>11.51140292410906</v>
+        <v>11.51140199856674</v>
       </c>
       <c r="E493" t="n">
-        <v>11.92252475789698</v>
+        <v>11.92252379929955</v>
       </c>
       <c r="F493" t="n">
         <v>2495174</v>
@@ -10372,16 +10372,16 @@
         <v>44953</v>
       </c>
       <c r="B498" t="n">
-        <v>12.43861389160156</v>
+        <v>12.43861293792725</v>
       </c>
       <c r="C498" t="n">
-        <v>12.67478987552819</v>
+        <v>12.67478890374615</v>
       </c>
       <c r="D498" t="n">
-        <v>12.25492099177236</v>
+        <v>12.25492005218186</v>
       </c>
       <c r="E498" t="n">
-        <v>12.41237108625991</v>
+        <v>12.41237013459764</v>
       </c>
       <c r="F498" t="n">
         <v>1981500</v>
@@ -10412,16 +10412,16 @@
         <v>44957</v>
       </c>
       <c r="B500" t="n">
-        <v>12.78850364685059</v>
+        <v>12.78850269317627</v>
       </c>
       <c r="C500" t="n">
-        <v>13.03342750793878</v>
+        <v>13.03342653599981</v>
       </c>
       <c r="D500" t="n">
-        <v>12.48234882049034</v>
+        <v>12.48234788964684</v>
       </c>
       <c r="E500" t="n">
-        <v>12.49109670281154</v>
+        <v>12.49109577131569</v>
       </c>
       <c r="F500" t="n">
         <v>4284855</v>
@@ -10492,16 +10492,16 @@
         <v>44963</v>
       </c>
       <c r="B504" t="n">
-        <v>12.75351428985596</v>
+        <v>12.75351333618164</v>
       </c>
       <c r="C504" t="n">
-        <v>12.83224017538812</v>
+        <v>12.83223921582688</v>
       </c>
       <c r="D504" t="n">
-        <v>12.33364542693687</v>
+        <v>12.33364450465924</v>
       </c>
       <c r="E504" t="n">
-        <v>12.53483239741585</v>
+        <v>12.53483146009399</v>
       </c>
       <c r="F504" t="n">
         <v>1342942</v>
@@ -10512,16 +10512,16 @@
         <v>44964</v>
       </c>
       <c r="B505" t="n">
-        <v>12.76226139068604</v>
+        <v>12.76226043701172</v>
       </c>
       <c r="C505" t="n">
-        <v>12.93720640015643</v>
+        <v>12.93720543340915</v>
       </c>
       <c r="D505" t="n">
-        <v>12.52608541735219</v>
+        <v>12.52608448132639</v>
       </c>
       <c r="E505" t="n">
-        <v>12.85848135644357</v>
+        <v>12.8584803955791</v>
       </c>
       <c r="F505" t="n">
         <v>2203204</v>
@@ -10532,16 +10532,16 @@
         <v>44965</v>
       </c>
       <c r="B506" t="n">
-        <v>12.7710075378418</v>
+        <v>12.77100849151611</v>
       </c>
       <c r="C506" t="n">
-        <v>12.98094237672584</v>
+        <v>12.98094334607703</v>
       </c>
       <c r="D506" t="n">
-        <v>12.56982058046619</v>
+        <v>12.56982151911688</v>
       </c>
       <c r="E506" t="n">
-        <v>12.85848045755975</v>
+        <v>12.8584814177661</v>
       </c>
       <c r="F506" t="n">
         <v>1737889</v>
@@ -10552,16 +10552,16 @@
         <v>44966</v>
       </c>
       <c r="B507" t="n">
-        <v>12.13245677947998</v>
+        <v>12.1324577331543</v>
       </c>
       <c r="C507" t="n">
-        <v>12.7797553723795</v>
+        <v>12.77975637693486</v>
       </c>
       <c r="D507" t="n">
-        <v>12.06247878084089</v>
+        <v>12.06247972901458</v>
       </c>
       <c r="E507" t="n">
-        <v>12.76226045162213</v>
+        <v>12.7622614548023</v>
       </c>
       <c r="F507" t="n">
         <v>2590377</v>
@@ -10632,16 +10632,16 @@
         <v>44972</v>
       </c>
       <c r="B511" t="n">
-        <v>12.75351428985596</v>
+        <v>12.75351333618164</v>
       </c>
       <c r="C511" t="n">
-        <v>12.94595337825676</v>
+        <v>12.94595241019235</v>
       </c>
       <c r="D511" t="n">
-        <v>11.91377656401778</v>
+        <v>11.91377567313685</v>
       </c>
       <c r="E511" t="n">
-        <v>12.24617250152178</v>
+        <v>12.24617158578515</v>
       </c>
       <c r="F511" t="n">
         <v>3838217</v>
@@ -10672,16 +10672,16 @@
         <v>44974</v>
       </c>
       <c r="B513" t="n">
-        <v>12.78850364685059</v>
+        <v>12.78850269317627</v>
       </c>
       <c r="C513" t="n">
-        <v>12.85848165224856</v>
+        <v>12.85848069335579</v>
       </c>
       <c r="D513" t="n">
-        <v>12.6310527136075</v>
+        <v>12.63105177167474</v>
       </c>
       <c r="E513" t="n">
-        <v>12.84098757199671</v>
+        <v>12.84098661440852</v>
       </c>
       <c r="F513" t="n">
         <v>1180399</v>
@@ -10752,16 +10752,16 @@
         <v>44984</v>
       </c>
       <c r="B517" t="n">
-        <v>11.64261150360107</v>
+        <v>11.64261054992676</v>
       </c>
       <c r="C517" t="n">
-        <v>11.87004043423472</v>
+        <v>11.87003946193115</v>
       </c>
       <c r="D517" t="n">
-        <v>11.51140253755071</v>
+        <v>11.51140159462404</v>
       </c>
       <c r="E517" t="n">
-        <v>11.77382046965144</v>
+        <v>11.77381950522948</v>
       </c>
       <c r="F517" t="n">
         <v>3613283</v>
@@ -10852,16 +10852,16 @@
         <v>44991</v>
       </c>
       <c r="B522" t="n">
-        <v>12.13245677947998</v>
+        <v>12.1324577331543</v>
       </c>
       <c r="C522" t="n">
-        <v>12.2374246196338</v>
+        <v>12.23742558155914</v>
       </c>
       <c r="D522" t="n">
-        <v>11.68634682760701</v>
+        <v>11.68634774621477</v>
       </c>
       <c r="E522" t="n">
-        <v>11.68634682760701</v>
+        <v>11.68634774621477</v>
       </c>
       <c r="F522" t="n">
         <v>3047313</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.26366806030273</v>
+        <v>12.26366710662842</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738295346679</v>
+        <v>12.37738199094953</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87004113878769</v>
+        <v>11.87004021572346</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12371120393195</v>
+        <v>12.12371026114126</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10932,16 +10932,16 @@
         <v>44995</v>
       </c>
       <c r="B526" t="n">
-        <v>12.59606266021729</v>
+        <v>12.5960636138916</v>
       </c>
       <c r="C526" t="n">
-        <v>12.78850258010713</v>
+        <v>12.78850354835147</v>
       </c>
       <c r="D526" t="n">
-        <v>12.31615066197402</v>
+        <v>12.31615159445562</v>
       </c>
       <c r="E526" t="n">
-        <v>12.6485457387903</v>
+        <v>12.64854669643821</v>
       </c>
       <c r="F526" t="n">
         <v>1798565</v>
@@ -11012,16 +11012,16 @@
         <v>45001</v>
       </c>
       <c r="B530" t="n">
-        <v>12.44736003875732</v>
+        <v>12.44735908508301</v>
       </c>
       <c r="C530" t="n">
-        <v>12.6310520832104</v>
+        <v>12.63105111546223</v>
       </c>
       <c r="D530" t="n">
-        <v>12.28990911337238</v>
+        <v>12.28990817176142</v>
       </c>
       <c r="E530" t="n">
-        <v>12.35113923339325</v>
+        <v>12.35113828709104</v>
       </c>
       <c r="F530" t="n">
         <v>3275478</v>
@@ -11292,16 +11292,16 @@
         <v>45021</v>
       </c>
       <c r="B544" t="n">
-        <v>10.67166423797607</v>
+        <v>10.67166519165039</v>
       </c>
       <c r="C544" t="n">
-        <v>11.3539509927967</v>
+        <v>11.35395200744364</v>
       </c>
       <c r="D544" t="n">
-        <v>10.58419216015985</v>
+        <v>10.58419310601722</v>
       </c>
       <c r="E544" t="n">
-        <v>11.17900599496905</v>
+        <v>11.17900699398201</v>
       </c>
       <c r="F544" t="n">
         <v>4730079</v>
@@ -11312,16 +11312,16 @@
         <v>45022</v>
       </c>
       <c r="B545" t="n">
-        <v>10.8028736114502</v>
+        <v>10.80287265777588</v>
       </c>
       <c r="C545" t="n">
-        <v>11.10902928820433</v>
+        <v>11.10902830750268</v>
       </c>
       <c r="D545" t="n">
-        <v>10.46173145764599</v>
+        <v>10.4617305340876</v>
       </c>
       <c r="E545" t="n">
-        <v>10.71540152345793</v>
+        <v>10.71540057750562</v>
       </c>
       <c r="F545" t="n">
         <v>8557394</v>
@@ -11332,16 +11332,16 @@
         <v>45026</v>
       </c>
       <c r="B546" t="n">
-        <v>10.89909362792969</v>
+        <v>10.89909267425537</v>
       </c>
       <c r="C546" t="n">
-        <v>11.14401663548793</v>
+        <v>11.14401566038277</v>
       </c>
       <c r="D546" t="n">
-        <v>10.64542273845509</v>
+        <v>10.64542180697705</v>
       </c>
       <c r="E546" t="n">
-        <v>10.71540074061458</v>
+        <v>10.71539980301345</v>
       </c>
       <c r="F546" t="n">
         <v>4871319</v>
@@ -11632,16 +11632,16 @@
         <v>45049</v>
       </c>
       <c r="B561" t="n">
-        <v>10.12933349609375</v>
+        <v>10.12933444976807</v>
       </c>
       <c r="C561" t="n">
-        <v>10.29553229701482</v>
+        <v>10.29553326633671</v>
       </c>
       <c r="D561" t="n">
-        <v>9.875662617229723</v>
+        <v>9.875663547020988</v>
       </c>
       <c r="E561" t="n">
-        <v>10.12058645673849</v>
+        <v>10.12058740958928</v>
       </c>
       <c r="F561" t="n">
         <v>7064832</v>
@@ -27772,19 +27772,39 @@
         <v>46230</v>
       </c>
       <c r="B1368" t="n">
-        <v>3.17</v>
+        <v>3.170000076293945</v>
       </c>
       <c r="C1368" t="n">
-        <v>3.24</v>
+        <v>3.240000009536743</v>
       </c>
       <c r="D1368" t="n">
-        <v>3.12</v>
+        <v>3.119999885559082</v>
       </c>
       <c r="E1368" t="n">
-        <v>3.21</v>
+        <v>3.210000038146973</v>
       </c>
       <c r="F1368" t="n">
         <v>10405600</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1369" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C1369" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>2326600</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -512,16 +512,16 @@
         <v>44232</v>
       </c>
       <c r="B5" t="n">
-        <v>6.823330879211426</v>
+        <v>6.823331356048584</v>
       </c>
       <c r="C5" t="n">
-        <v>6.909409509382922</v>
+        <v>6.909409992235542</v>
       </c>
       <c r="D5" t="n">
-        <v>6.699460779521623</v>
+        <v>6.699461247702325</v>
       </c>
       <c r="E5" t="n">
-        <v>6.873718152244995</v>
+        <v>6.873718632603384</v>
       </c>
       <c r="F5" t="n">
         <v>4402737</v>
@@ -552,16 +552,16 @@
         <v>44236</v>
       </c>
       <c r="B7" t="n">
-        <v>7.119358062744141</v>
+        <v>7.119358539581299</v>
       </c>
       <c r="C7" t="n">
-        <v>7.367097444187393</v>
+        <v>7.367097937617529</v>
       </c>
       <c r="D7" t="n">
-        <v>6.953498708270694</v>
+        <v>6.953499173999</v>
       </c>
       <c r="E7" t="n">
-        <v>7.266322088824129</v>
+        <v>7.266322575504579</v>
       </c>
       <c r="F7" t="n">
         <v>1374461</v>
@@ -572,16 +572,16 @@
         <v>44237</v>
       </c>
       <c r="B8" t="n">
-        <v>6.928305149078369</v>
+        <v>6.928305625915527</v>
       </c>
       <c r="C8" t="n">
-        <v>7.180243149138246</v>
+        <v>7.180243643314912</v>
       </c>
       <c r="D8" t="n">
-        <v>6.74984876127967</v>
+        <v>6.749849225834657</v>
       </c>
       <c r="E8" t="n">
-        <v>7.180243149138246</v>
+        <v>7.180243643314912</v>
       </c>
       <c r="F8" t="n">
         <v>3511567</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029079914093018</v>
+        <v>7.029080390930176</v>
       </c>
       <c r="C10" t="n">
-        <v>7.19493926602394</v>
+        <v>7.194939754112628</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913607833174078</v>
+        <v>6.913608302177867</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949299188880033</v>
+        <v>6.949299660305043</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -632,16 +632,16 @@
         <v>44244</v>
       </c>
       <c r="B11" t="n">
-        <v>7.274720668792725</v>
+        <v>7.274719715118408</v>
       </c>
       <c r="C11" t="n">
-        <v>7.388092647974826</v>
+        <v>7.38809167943809</v>
       </c>
       <c r="D11" t="n">
-        <v>7.11305990280828</v>
+        <v>7.113058970326766</v>
       </c>
       <c r="E11" t="n">
-        <v>7.11725931599718</v>
+        <v>7.117258382965146</v>
       </c>
       <c r="F11" t="n">
         <v>2613098</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.222232341766357</v>
+        <v>7.222233772277832</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379693674093248</v>
+        <v>7.379695135793175</v>
       </c>
       <c r="D12" t="n">
-        <v>7.138253018644978</v>
+        <v>7.138254432522623</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287316337480287</v>
+        <v>7.287317780882985</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.306212902069092</v>
+        <v>7.306213855743408</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724010241576962</v>
+        <v>7.724011249786042</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050074693354461</v>
+        <v>7.050075613595256</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054274106241974</v>
+        <v>7.054275027030914</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.306212902069092</v>
+        <v>7.306213855743408</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480470271524869</v>
+        <v>7.480471247944865</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243227391317824</v>
+        <v>7.243228336770691</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308311390821116</v>
+        <v>7.308312344769346</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -732,16 +732,16 @@
         <v>44251</v>
       </c>
       <c r="B16" t="n">
-        <v>7.327207565307617</v>
+        <v>7.327207088470459</v>
       </c>
       <c r="C16" t="n">
-        <v>7.556051620807289</v>
+        <v>7.556051129077507</v>
       </c>
       <c r="D16" t="n">
-        <v>7.108860824383968</v>
+        <v>7.108860361756294</v>
       </c>
       <c r="E16" t="n">
-        <v>7.451077663252569</v>
+        <v>7.451077178354241</v>
       </c>
       <c r="F16" t="n">
         <v>1445414</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138254642486572</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C17" t="n">
-        <v>7.40069079726115</v>
+        <v>7.400689808525235</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945101911829834</v>
+        <v>6.945100983960817</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360800832947622</v>
+        <v>7.360799849541025</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -792,16 +792,16 @@
         <v>44256</v>
       </c>
       <c r="B19" t="n">
-        <v>7.001786708831787</v>
+        <v>7.001787185668945</v>
       </c>
       <c r="C19" t="n">
-        <v>7.390191404584969</v>
+        <v>7.390191907873347</v>
       </c>
       <c r="D19" t="n">
-        <v>7.001786708831787</v>
+        <v>7.001787185668945</v>
       </c>
       <c r="E19" t="n">
-        <v>7.249526091312114</v>
+        <v>7.249526585020872</v>
       </c>
       <c r="F19" t="n">
         <v>1349729</v>
@@ -812,16 +812,16 @@
         <v>44257</v>
       </c>
       <c r="B20" t="n">
-        <v>7.178143978118896</v>
+        <v>7.17814302444458</v>
       </c>
       <c r="C20" t="n">
-        <v>7.178143978118896</v>
+        <v>7.17814302444458</v>
       </c>
       <c r="D20" t="n">
-        <v>6.718356531153318</v>
+        <v>6.718355638565471</v>
       </c>
       <c r="E20" t="n">
-        <v>7.003886594429932</v>
+        <v>7.003885663907115</v>
       </c>
       <c r="F20" t="n">
         <v>1173360</v>
@@ -832,16 +832,16 @@
         <v>44258</v>
       </c>
       <c r="B21" t="n">
-        <v>7.085767269134521</v>
+        <v>7.085766792297363</v>
       </c>
       <c r="C21" t="n">
-        <v>7.10886120006331</v>
+        <v>7.108860721672044</v>
       </c>
       <c r="D21" t="n">
-        <v>6.896813161397048</v>
+        <v>6.896812697275568</v>
       </c>
       <c r="E21" t="n">
-        <v>7.10886120006331</v>
+        <v>7.108860721672044</v>
       </c>
       <c r="F21" t="n">
         <v>1419466</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138254642486572</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233984711942</v>
+        <v>7.222233019817944</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966097356232146</v>
+        <v>6.966096425558127</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117260009878886</v>
+        <v>7.117259059009463</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -872,16 +872,16 @@
         <v>44260</v>
       </c>
       <c r="B23" t="n">
-        <v>7.016482830047607</v>
+        <v>7.016483783721924</v>
       </c>
       <c r="C23" t="n">
-        <v>7.176044269802593</v>
+        <v>7.176045245164364</v>
       </c>
       <c r="D23" t="n">
-        <v>7.014382717891935</v>
+        <v>7.014383671280806</v>
       </c>
       <c r="E23" t="n">
-        <v>7.117258177126498</v>
+        <v>7.117259144498113</v>
       </c>
       <c r="F23" t="n">
         <v>1309995</v>
@@ -892,16 +892,16 @@
         <v>44263</v>
       </c>
       <c r="B24" t="n">
-        <v>6.65327262878418</v>
+        <v>6.653272151947021</v>
       </c>
       <c r="C24" t="n">
-        <v>7.016484130369983</v>
+        <v>7.016483627501614</v>
       </c>
       <c r="D24" t="n">
-        <v>6.65327262878418</v>
+        <v>6.653272151947021</v>
       </c>
       <c r="E24" t="n">
-        <v>7.016484130369983</v>
+        <v>7.016483627501614</v>
       </c>
       <c r="F24" t="n">
         <v>1015642</v>
@@ -932,16 +932,16 @@
         <v>44265</v>
       </c>
       <c r="B26" t="n">
-        <v>6.252270221710205</v>
+        <v>6.252270698547363</v>
       </c>
       <c r="C26" t="n">
-        <v>6.592386944261464</v>
+        <v>6.592387447038047</v>
       </c>
       <c r="D26" t="n">
-        <v>6.124201524146216</v>
+        <v>6.124201991216056</v>
       </c>
       <c r="E26" t="n">
-        <v>6.586089042665994</v>
+        <v>6.58608954496226</v>
       </c>
       <c r="F26" t="n">
         <v>1291345</v>
@@ -952,16 +952,16 @@
         <v>44266</v>
       </c>
       <c r="B27" t="n">
-        <v>6.67006778717041</v>
+        <v>6.670068740844727</v>
       </c>
       <c r="C27" t="n">
-        <v>6.67006778717041</v>
+        <v>6.670068740844727</v>
       </c>
       <c r="D27" t="n">
-        <v>6.21447937230484</v>
+        <v>6.214480260839943</v>
       </c>
       <c r="E27" t="n">
-        <v>6.287961793693228</v>
+        <v>6.287962692734715</v>
       </c>
       <c r="F27" t="n">
         <v>2230763</v>
@@ -972,16 +972,16 @@
         <v>44267</v>
       </c>
       <c r="B28" t="n">
-        <v>6.69526195526123</v>
+        <v>6.695262432098389</v>
       </c>
       <c r="C28" t="n">
-        <v>6.896813082384956</v>
+        <v>6.896813573576604</v>
       </c>
       <c r="D28" t="n">
-        <v>6.45592016938186</v>
+        <v>6.455920629173074</v>
       </c>
       <c r="E28" t="n">
-        <v>6.646973981495075</v>
+        <v>6.646974454893159</v>
       </c>
       <c r="F28" t="n">
         <v>3263434</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033280372619629</v>
+        <v>7.033279895782471</v>
       </c>
       <c r="C29" t="n">
-        <v>7.12775702718571</v>
+        <v>7.127756543943293</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969559237991</v>
+        <v>6.667969107167907</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969559237991</v>
+        <v>6.667969107167907</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1032,16 +1032,16 @@
         <v>44272</v>
       </c>
       <c r="B31" t="n">
-        <v>7.558151721954346</v>
+        <v>7.558150768280029</v>
       </c>
       <c r="C31" t="n">
-        <v>7.642131059252459</v>
+        <v>7.642130094981778</v>
       </c>
       <c r="D31" t="n">
-        <v>7.285218266889542</v>
+        <v>7.285217347653489</v>
       </c>
       <c r="E31" t="n">
-        <v>7.390192235563539</v>
+        <v>7.390191303082056</v>
       </c>
       <c r="F31" t="n">
         <v>5070506</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.516163349151611</v>
+        <v>7.516162395477295</v>
       </c>
       <c r="C33" t="n">
-        <v>7.778598707807475</v>
+        <v>7.778597720834538</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430083077293361</v>
+        <v>7.430082134541178</v>
       </c>
       <c r="E33" t="n">
-        <v>7.6001418845986</v>
+        <v>7.600140920268824</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1092,16 +1092,16 @@
         <v>44277</v>
       </c>
       <c r="B34" t="n">
-        <v>7.558151721954346</v>
+        <v>7.558150768280029</v>
       </c>
       <c r="C34" t="n">
-        <v>7.807990433070015</v>
+        <v>7.807989447871488</v>
       </c>
       <c r="D34" t="n">
-        <v>7.201238929591428</v>
+        <v>7.201238020951741</v>
       </c>
       <c r="E34" t="n">
-        <v>7.514062346629327</v>
+        <v>7.51406139851813</v>
       </c>
       <c r="F34" t="n">
         <v>5377429</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.516163349151611</v>
+        <v>7.516162395477295</v>
       </c>
       <c r="C35" t="n">
-        <v>7.558152616875106</v>
+        <v>7.55815165787306</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436382603964429</v>
+        <v>7.436381660412942</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511963935302457</v>
+        <v>7.511962982160976</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159248352050781</v>
+        <v>7.159248828887939</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656827250339138</v>
+        <v>7.656827760317221</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159248352050781</v>
+        <v>7.159248828887939</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392291828769327</v>
+        <v>7.392292321128197</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.705113887786865</v>
+        <v>7.70511531829834</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789094025265366</v>
+        <v>7.789095471368375</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033279282314587</v>
+        <v>7.033280588094989</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159247864943406</v>
+        <v>7.159249194110809</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.518261432647705</v>
+        <v>7.51826000213623</v>
       </c>
       <c r="C38" t="n">
-        <v>7.789095604385824</v>
+        <v>7.789094122342303</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455276722666873</v>
+        <v>7.455275304139598</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721912292577096</v>
+        <v>7.721910823316651</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138254642486572</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379695352858839</v>
+        <v>7.379694366927925</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138254642486572</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257925347221784</v>
+        <v>7.257924377559402</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1272,16 +1272,16 @@
         <v>44291</v>
       </c>
       <c r="B43" t="n">
-        <v>7.327207565307617</v>
+        <v>7.327207088470459</v>
       </c>
       <c r="C43" t="n">
-        <v>7.400689579134269</v>
+        <v>7.400689097515077</v>
       </c>
       <c r="D43" t="n">
-        <v>7.260023453149884</v>
+        <v>7.260022980684908</v>
       </c>
       <c r="E43" t="n">
-        <v>7.400689579134269</v>
+        <v>7.400689097515077</v>
       </c>
       <c r="F43" t="n">
         <v>1080107</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652627468109131</v>
+        <v>7.652627944946289</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873073506816938</v>
+        <v>7.873073997390144</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474170687177393</v>
+        <v>7.474171152894864</v>
       </c>
       <c r="E47" t="n">
-        <v>7.595941483034749</v>
+        <v>7.595941956339789</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1372,16 +1372,16 @@
         <v>44298</v>
       </c>
       <c r="B48" t="n">
-        <v>7.789093971252441</v>
+        <v>7.7890944480896</v>
       </c>
       <c r="C48" t="n">
-        <v>8.015838717283117</v>
+        <v>8.015839208001262</v>
       </c>
       <c r="D48" t="n">
-        <v>7.644229249849665</v>
+        <v>7.644229717818412</v>
       </c>
       <c r="E48" t="n">
-        <v>7.688318618771526</v>
+        <v>7.688319089439362</v>
       </c>
       <c r="F48" t="n">
         <v>2187380</v>
@@ -1392,16 +1392,16 @@
         <v>44299</v>
       </c>
       <c r="B49" t="n">
-        <v>7.726109981536865</v>
+        <v>7.726110458374023</v>
       </c>
       <c r="C49" t="n">
-        <v>7.898268060237418</v>
+        <v>7.898268547699764</v>
       </c>
       <c r="D49" t="n">
-        <v>7.642130648749763</v>
+        <v>7.642131120403916</v>
       </c>
       <c r="E49" t="n">
-        <v>7.786995383409918</v>
+        <v>7.786995864004779</v>
       </c>
       <c r="F49" t="n">
         <v>1044023</v>
@@ -1432,16 +1432,16 @@
         <v>44301</v>
       </c>
       <c r="B51" t="n">
-        <v>8.112415313720703</v>
+        <v>8.112414360046387</v>
       </c>
       <c r="C51" t="n">
-        <v>8.185898142401868</v>
+        <v>8.185897180089103</v>
       </c>
       <c r="D51" t="n">
-        <v>7.891969263060783</v>
+        <v>7.891968335301526</v>
       </c>
       <c r="E51" t="n">
-        <v>7.894068563704509</v>
+        <v>7.894067635698465</v>
       </c>
       <c r="F51" t="n">
         <v>2034122</v>
@@ -1552,16 +1552,16 @@
         <v>44312</v>
       </c>
       <c r="B57" t="n">
-        <v>7.978048324584961</v>
+        <v>7.978049278259277</v>
       </c>
       <c r="C57" t="n">
-        <v>8.187996238363182</v>
+        <v>8.187997217134104</v>
       </c>
       <c r="D57" t="n">
-        <v>7.93815755529562</v>
+        <v>7.938158504201501</v>
       </c>
       <c r="E57" t="n">
-        <v>8.185897749614673</v>
+        <v>8.185898728134749</v>
       </c>
       <c r="F57" t="n">
         <v>1270667</v>
@@ -1572,16 +1572,16 @@
         <v>44313</v>
       </c>
       <c r="B58" t="n">
-        <v>8.116615295410156</v>
+        <v>8.116613388061523</v>
       </c>
       <c r="C58" t="n">
-        <v>8.1837986032776</v>
+        <v>8.183796680141354</v>
       </c>
       <c r="D58" t="n">
-        <v>7.9402586048865</v>
+        <v>7.940256738980475</v>
       </c>
       <c r="E58" t="n">
-        <v>7.999043897796192</v>
+        <v>7.999042018076027</v>
       </c>
       <c r="F58" t="n">
         <v>2786224</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397946357727051</v>
+        <v>8.397945404052734</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469329082392035</v>
+        <v>8.469328120611465</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116615684439186</v>
+        <v>8.116614762712898</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116615684439186</v>
+        <v>8.116614762712898</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1612,16 +1612,16 @@
         <v>44315</v>
       </c>
       <c r="B60" t="n">
-        <v>8.607894897460938</v>
+        <v>8.607893943786621</v>
       </c>
       <c r="C60" t="n">
-        <v>8.815744351658321</v>
+        <v>8.815743374956226</v>
       </c>
       <c r="D60" t="n">
-        <v>8.167002755425871</v>
+        <v>8.167001850598284</v>
       </c>
       <c r="E60" t="n">
-        <v>8.469328865260882</v>
+        <v>8.469327926938387</v>
       </c>
       <c r="F60" t="n">
         <v>3250459</v>
@@ -1632,16 +1632,16 @@
         <v>44316</v>
       </c>
       <c r="B61" t="n">
-        <v>8.733864784240723</v>
+        <v>8.733863830566406</v>
       </c>
       <c r="C61" t="n">
-        <v>8.733864784240723</v>
+        <v>8.733863830566406</v>
       </c>
       <c r="D61" t="n">
-        <v>8.580602826110796</v>
+        <v>8.580601889171566</v>
       </c>
       <c r="E61" t="n">
-        <v>8.580602826110796</v>
+        <v>8.580601889171566</v>
       </c>
       <c r="F61" t="n">
         <v>3200590</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849334716796875</v>
+        <v>8.849335670471191</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122268152268145</v>
+        <v>9.122269135355927</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641486095148732</v>
+        <v>8.641487026423638</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733863440724466</v>
+        <v>8.733864381954685</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1712,16 +1712,16 @@
         <v>44322</v>
       </c>
       <c r="B65" t="n">
-        <v>9.764712333679199</v>
+        <v>9.764711380004883</v>
       </c>
       <c r="C65" t="n">
-        <v>9.783606852193223</v>
+        <v>9.783605896673567</v>
       </c>
       <c r="D65" t="n">
-        <v>9.537966746386992</v>
+        <v>9.537965814857868</v>
       </c>
       <c r="E65" t="n">
-        <v>9.783606852193223</v>
+        <v>9.783605896673567</v>
       </c>
       <c r="F65" t="n">
         <v>8042425</v>
@@ -1772,16 +1772,16 @@
         <v>44327</v>
       </c>
       <c r="B68" t="n">
-        <v>9.61774730682373</v>
+        <v>9.617746353149414</v>
       </c>
       <c r="C68" t="n">
-        <v>9.645041463213841</v>
+        <v>9.645040506833098</v>
       </c>
       <c r="D68" t="n">
-        <v>8.964807960828002</v>
+        <v>8.964807071897692</v>
       </c>
       <c r="E68" t="n">
-        <v>9.294427396683329</v>
+        <v>9.294426475068693</v>
       </c>
       <c r="F68" t="n">
         <v>2188597</v>
@@ -1792,16 +1792,16 @@
         <v>44328</v>
       </c>
       <c r="B69" t="n">
-        <v>9.531668663024902</v>
+        <v>9.531667709350586</v>
       </c>
       <c r="C69" t="n">
-        <v>9.743716705677796</v>
+        <v>9.743715730787388</v>
       </c>
       <c r="D69" t="n">
-        <v>9.321719921078722</v>
+        <v>9.321718988410458</v>
       </c>
       <c r="E69" t="n">
-        <v>9.563160609009282</v>
+        <v>9.563159652184094</v>
       </c>
       <c r="F69" t="n">
         <v>1563804</v>
@@ -1852,16 +1852,16 @@
         <v>44333</v>
       </c>
       <c r="B72" t="n">
-        <v>9.657638549804688</v>
+        <v>9.657637596130371</v>
       </c>
       <c r="C72" t="n">
-        <v>9.773109835938806</v>
+        <v>9.773108870861909</v>
       </c>
       <c r="D72" t="n">
-        <v>9.36161115804209</v>
+        <v>9.361610233599944</v>
       </c>
       <c r="E72" t="n">
-        <v>9.613549173803014</v>
+        <v>9.613548224482443</v>
       </c>
       <c r="F72" t="n">
         <v>1884107</v>
@@ -1872,16 +1872,16 @@
         <v>44334</v>
       </c>
       <c r="B73" t="n">
-        <v>9.657638549804688</v>
+        <v>9.657637596130371</v>
       </c>
       <c r="C73" t="n">
-        <v>9.666036564842845</v>
+        <v>9.66603561033924</v>
       </c>
       <c r="D73" t="n">
-        <v>9.458187113289004</v>
+        <v>9.458186179310156</v>
       </c>
       <c r="E73" t="n">
-        <v>9.655539248993795</v>
+        <v>9.655538295526782</v>
       </c>
       <c r="F73" t="n">
         <v>1385003</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.823495864868164</v>
+        <v>9.82349681854248</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272800283195</v>
+        <v>10.10272898361439</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334316624833162</v>
+        <v>9.334317531017494</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678631950423839</v>
+        <v>9.678632890034629</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1912,16 +1912,16 @@
         <v>44336</v>
       </c>
       <c r="B75" t="n">
-        <v>10.13002300262451</v>
+        <v>10.1300220489502</v>
       </c>
       <c r="C75" t="n">
-        <v>10.22869906616216</v>
+        <v>10.22869810319815</v>
       </c>
       <c r="D75" t="n">
-        <v>9.504376186303976</v>
+        <v>9.504375291530147</v>
       </c>
       <c r="E75" t="n">
-        <v>9.873885584647184</v>
+        <v>9.873884655086501</v>
       </c>
       <c r="F75" t="n">
         <v>2816227</v>
@@ -2012,16 +2012,16 @@
         <v>44343</v>
       </c>
       <c r="B80" t="n">
-        <v>10.65489482879639</v>
+        <v>10.65489387512207</v>
       </c>
       <c r="C80" t="n">
-        <v>10.74937148241849</v>
+        <v>10.74937052028797</v>
       </c>
       <c r="D80" t="n">
-        <v>10.44284596565298</v>
+        <v>10.44284503095825</v>
       </c>
       <c r="E80" t="n">
-        <v>10.49743265703344</v>
+        <v>10.49743171745289</v>
       </c>
       <c r="F80" t="n">
         <v>6818384</v>
@@ -2052,16 +2052,16 @@
         <v>44347</v>
       </c>
       <c r="B82" t="n">
-        <v>11.12727928161621</v>
+        <v>11.12727832794189</v>
       </c>
       <c r="C82" t="n">
-        <v>11.39601333414453</v>
+        <v>11.3960123574381</v>
       </c>
       <c r="D82" t="n">
-        <v>10.70738176643192</v>
+        <v>10.70738084874532</v>
       </c>
       <c r="E82" t="n">
-        <v>10.74937184266819</v>
+        <v>10.7493709213828</v>
       </c>
       <c r="F82" t="n">
         <v>1849644</v>
@@ -2072,16 +2072,16 @@
         <v>44348</v>
       </c>
       <c r="B83" t="n">
-        <v>11.12727928161621</v>
+        <v>11.12727832794189</v>
       </c>
       <c r="C83" t="n">
-        <v>11.25324869853042</v>
+        <v>11.25324773405977</v>
       </c>
       <c r="D83" t="n">
-        <v>11.03280181303325</v>
+        <v>11.03280086745621</v>
       </c>
       <c r="E83" t="n">
-        <v>11.23225325451498</v>
+        <v>11.23225229184377</v>
       </c>
       <c r="F83" t="n">
         <v>1761257</v>
@@ -2112,16 +2112,16 @@
         <v>44351</v>
       </c>
       <c r="B85" t="n">
-        <v>11.12727928161621</v>
+        <v>11.12727832794189</v>
       </c>
       <c r="C85" t="n">
-        <v>11.14197519945295</v>
+        <v>11.1419742445191</v>
       </c>
       <c r="D85" t="n">
-        <v>10.656994486743</v>
+        <v>10.6569935733749</v>
       </c>
       <c r="E85" t="n">
-        <v>10.93832596803951</v>
+        <v>10.93832503055962</v>
       </c>
       <c r="F85" t="n">
         <v>2427404</v>
@@ -2212,16 +2212,16 @@
         <v>44358</v>
       </c>
       <c r="B90" t="n">
-        <v>10.60240745544434</v>
+        <v>10.6024055480957</v>
       </c>
       <c r="C90" t="n">
-        <v>10.84174885287247</v>
+        <v>10.84174690246687</v>
       </c>
       <c r="D90" t="n">
-        <v>10.51842811744432</v>
+        <v>10.51842622520338</v>
       </c>
       <c r="E90" t="n">
-        <v>10.75986881566868</v>
+        <v>10.75986687999311</v>
       </c>
       <c r="F90" t="n">
         <v>1174982</v>
@@ -2232,16 +2232,16 @@
         <v>44361</v>
       </c>
       <c r="B91" t="n">
-        <v>10.94252300262451</v>
+        <v>10.94252395629883</v>
       </c>
       <c r="C91" t="n">
-        <v>11.24904848576352</v>
+        <v>11.24904946615247</v>
       </c>
       <c r="D91" t="n">
-        <v>10.64649564588704</v>
+        <v>10.64649657376166</v>
       </c>
       <c r="E91" t="n">
-        <v>10.72837567397531</v>
+        <v>10.72837660898603</v>
       </c>
       <c r="F91" t="n">
         <v>2250630</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462203979492</v>
+        <v>10.94462299346924</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192205807723</v>
+        <v>11.35192304724218</v>
       </c>
       <c r="D92" t="n">
-        <v>10.8144540429291</v>
+        <v>10.81445498526105</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152729877964</v>
+        <v>10.92152825044157</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2272,16 +2272,16 @@
         <v>44363</v>
       </c>
       <c r="B93" t="n">
-        <v>11.12727928161621</v>
+        <v>11.12727832794189</v>
       </c>
       <c r="C93" t="n">
-        <v>11.31413410612437</v>
+        <v>11.31413313643548</v>
       </c>
       <c r="D93" t="n">
-        <v>10.8921364782823</v>
+        <v>10.89213554476112</v>
       </c>
       <c r="E93" t="n">
-        <v>10.9614199011235</v>
+        <v>10.96141896166432</v>
       </c>
       <c r="F93" t="n">
         <v>2948808</v>
@@ -2352,16 +2352,16 @@
         <v>44369</v>
       </c>
       <c r="B97" t="n">
-        <v>11.28474044799805</v>
+        <v>11.28473949432373</v>
       </c>
       <c r="C97" t="n">
-        <v>11.42330729123857</v>
+        <v>11.42330632585396</v>
       </c>
       <c r="D97" t="n">
-        <v>11.16297125854524</v>
+        <v>11.16297031516165</v>
       </c>
       <c r="E97" t="n">
-        <v>11.238552582644</v>
+        <v>11.23855163287302</v>
       </c>
       <c r="F97" t="n">
         <v>1033076</v>
@@ -2392,16 +2392,16 @@
         <v>44371</v>
       </c>
       <c r="B99" t="n">
-        <v>11.71093559265137</v>
+        <v>11.71093654632568</v>
       </c>
       <c r="C99" t="n">
-        <v>12.02165887555918</v>
+        <v>12.02165985453709</v>
       </c>
       <c r="D99" t="n">
-        <v>11.35612212568278</v>
+        <v>11.35612305046303</v>
       </c>
       <c r="E99" t="n">
-        <v>11.54717471917903</v>
+        <v>11.54717565951756</v>
       </c>
       <c r="F99" t="n">
         <v>3545624</v>
@@ -2412,16 +2412,16 @@
         <v>44372</v>
       </c>
       <c r="B100" t="n">
-        <v>11.61226081848145</v>
+        <v>11.61225891113281</v>
       </c>
       <c r="C100" t="n">
-        <v>11.71933490415196</v>
+        <v>11.71933297921609</v>
       </c>
       <c r="D100" t="n">
-        <v>11.34142665300706</v>
+        <v>11.34142479014375</v>
       </c>
       <c r="E100" t="n">
-        <v>11.71093688889577</v>
+        <v>11.71093496533929</v>
       </c>
       <c r="F100" t="n">
         <v>3580087</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.0174617767334</v>
+        <v>12.01746082305908</v>
       </c>
       <c r="C102" t="n">
-        <v>12.0174617767334</v>
+        <v>12.01746082305908</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916626863832</v>
+        <v>11.58916534895242</v>
       </c>
       <c r="E102" t="n">
-        <v>11.8599996079053</v>
+        <v>11.85999866672677</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2492,16 +2492,16 @@
         <v>44378</v>
       </c>
       <c r="B104" t="n">
-        <v>12.47095012664795</v>
+        <v>12.47094821929932</v>
       </c>
       <c r="C104" t="n">
-        <v>12.63471020326512</v>
+        <v>12.63470827087047</v>
       </c>
       <c r="D104" t="n">
-        <v>12.33028479448456</v>
+        <v>12.33028290864975</v>
       </c>
       <c r="E104" t="n">
-        <v>12.38907090013396</v>
+        <v>12.38906900530821</v>
       </c>
       <c r="F104" t="n">
         <v>8890212</v>
@@ -2512,16 +2512,16 @@
         <v>44379</v>
       </c>
       <c r="B105" t="n">
-        <v>12.95802974700928</v>
+        <v>12.95803070068359</v>
       </c>
       <c r="C105" t="n">
-        <v>13.12808851154414</v>
+        <v>13.1280894777343</v>
       </c>
       <c r="D105" t="n">
-        <v>12.50034164844744</v>
+        <v>12.5003425684372</v>
       </c>
       <c r="E105" t="n">
-        <v>12.52133627702896</v>
+        <v>12.52133719856387</v>
       </c>
       <c r="F105" t="n">
         <v>2908669</v>
@@ -2552,16 +2552,16 @@
         <v>44383</v>
       </c>
       <c r="B107" t="n">
-        <v>13.04830837249756</v>
+        <v>13.04830932617188</v>
       </c>
       <c r="C107" t="n">
-        <v>13.36113095015526</v>
+        <v>13.36113192669314</v>
       </c>
       <c r="D107" t="n">
-        <v>13.00001958807886</v>
+        <v>13.00002053822385</v>
       </c>
       <c r="E107" t="n">
-        <v>13.14908373072754</v>
+        <v>13.14908469176732</v>
       </c>
       <c r="F107" t="n">
         <v>1738957</v>
@@ -2572,16 +2572,16 @@
         <v>44384</v>
       </c>
       <c r="B108" t="n">
-        <v>13.22676563262939</v>
+        <v>13.22676658630371</v>
       </c>
       <c r="C108" t="n">
-        <v>13.31074415373561</v>
+        <v>13.31074511346494</v>
       </c>
       <c r="D108" t="n">
-        <v>13.05040814056382</v>
+        <v>13.05040908152244</v>
       </c>
       <c r="E108" t="n">
-        <v>13.05880615503335</v>
+        <v>13.05880709659748</v>
       </c>
       <c r="F108" t="n">
         <v>2057638</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="C114" t="n">
-        <v>13.9384904687512</v>
+        <v>13.93849238737042</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969768169454</v>
+        <v>13.49969953991438</v>
       </c>
       <c r="E114" t="n">
-        <v>13.64246310974914</v>
+        <v>13.6424649876205</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501433064608</v>
+        <v>14.24501629145801</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969768169454</v>
+        <v>13.49969953991438</v>
       </c>
       <c r="E115" t="n">
-        <v>13.7495355572011</v>
+        <v>13.74953744981087</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06656074523926</v>
+        <v>14.06655979156494</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103739980534</v>
+        <v>14.16103643972576</v>
       </c>
       <c r="D116" t="n">
-        <v>13.7747319546967</v>
+        <v>13.77473102080758</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059133128809</v>
+        <v>13.94059038615415</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2752,16 +2752,16 @@
         <v>44398</v>
       </c>
       <c r="B117" t="n">
-        <v>14.31849765777588</v>
+        <v>14.31849956512451</v>
       </c>
       <c r="C117" t="n">
-        <v>14.3478894888263</v>
+        <v>14.34789140009018</v>
       </c>
       <c r="D117" t="n">
-        <v>14.01617078001709</v>
+        <v>14.01617264709314</v>
       </c>
       <c r="E117" t="n">
-        <v>14.06865816410801</v>
+        <v>14.06866003817584</v>
       </c>
       <c r="F117" t="n">
         <v>2316312</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.99873065948486</v>
+        <v>14.99873161315918</v>
       </c>
       <c r="C118" t="n">
-        <v>15.01132808589888</v>
+        <v>15.01132904037419</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36048649073444</v>
+        <v>14.36048740382685</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36048649073444</v>
+        <v>14.36048740382685</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2812,16 +2812,16 @@
         <v>44403</v>
       </c>
       <c r="B120" t="n">
-        <v>14.87486171722412</v>
+        <v>14.8748607635498</v>
       </c>
       <c r="C120" t="n">
-        <v>15.17088908393575</v>
+        <v>15.17088811128218</v>
       </c>
       <c r="D120" t="n">
-        <v>14.64601846513237</v>
+        <v>14.64601752612992</v>
       </c>
       <c r="E120" t="n">
-        <v>15.07431313686146</v>
+        <v>15.07431217039968</v>
       </c>
       <c r="F120" t="n">
         <v>4655330</v>
@@ -2832,16 +2832,16 @@
         <v>44404</v>
       </c>
       <c r="B121" t="n">
-        <v>14.54944133758545</v>
+        <v>14.54943943023682</v>
       </c>
       <c r="C121" t="n">
-        <v>15.059616867494</v>
+        <v>15.05961489326427</v>
       </c>
       <c r="D121" t="n">
-        <v>14.45076608687268</v>
+        <v>14.45076419245981</v>
       </c>
       <c r="E121" t="n">
-        <v>14.87486217025152</v>
+        <v>14.87486022024207</v>
       </c>
       <c r="F121" t="n">
         <v>2070206</v>
@@ -2852,16 +2852,16 @@
         <v>44405</v>
       </c>
       <c r="B122" t="n">
-        <v>15.08691120147705</v>
+        <v>15.08690929412842</v>
       </c>
       <c r="C122" t="n">
-        <v>15.36824185204953</v>
+        <v>15.36823990913394</v>
       </c>
       <c r="D122" t="n">
-        <v>14.03716667235407</v>
+        <v>14.03716489771841</v>
       </c>
       <c r="E122" t="n">
-        <v>15.13519836525918</v>
+        <v>15.13519645180589</v>
       </c>
       <c r="F122" t="n">
         <v>6581198</v>
@@ -2892,16 +2892,16 @@
         <v>44407</v>
       </c>
       <c r="B124" t="n">
-        <v>15.45431709289551</v>
+        <v>15.45431900024414</v>
       </c>
       <c r="C124" t="n">
-        <v>15.94139861587127</v>
+        <v>15.94140058333477</v>
       </c>
       <c r="D124" t="n">
-        <v>14.96933649387961</v>
+        <v>14.96933834137266</v>
       </c>
       <c r="E124" t="n">
-        <v>15.28006054980113</v>
+        <v>15.28006243564328</v>
       </c>
       <c r="F124" t="n">
         <v>3070441</v>
@@ -2912,16 +2912,16 @@
         <v>44410</v>
       </c>
       <c r="B125" t="n">
-        <v>15.31785202026367</v>
+        <v>15.31785297393799</v>
       </c>
       <c r="C125" t="n">
-        <v>15.85742095204634</v>
+        <v>15.85742193931368</v>
       </c>
       <c r="D125" t="n">
-        <v>15.16878869726372</v>
+        <v>15.1687896416575</v>
       </c>
       <c r="E125" t="n">
-        <v>15.64327281971962</v>
+        <v>15.64327379365431</v>
       </c>
       <c r="F125" t="n">
         <v>3314925</v>
@@ -2932,16 +2932,16 @@
         <v>44411</v>
       </c>
       <c r="B126" t="n">
-        <v>15.20448207855225</v>
+        <v>15.20448112487793</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39343538308269</v>
+        <v>15.39343441755661</v>
       </c>
       <c r="D126" t="n">
-        <v>14.76149065149246</v>
+        <v>14.761489725604</v>
       </c>
       <c r="E126" t="n">
-        <v>15.39343538308269</v>
+        <v>15.39343441755661</v>
       </c>
       <c r="F126" t="n">
         <v>3496971</v>
@@ -2972,16 +2972,16 @@
         <v>44413</v>
       </c>
       <c r="B128" t="n">
-        <v>14.17153453826904</v>
+        <v>14.17153358459473</v>
       </c>
       <c r="C128" t="n">
-        <v>14.82237457073309</v>
+        <v>14.82237357326046</v>
       </c>
       <c r="D128" t="n">
-        <v>14.17153453826904</v>
+        <v>14.17153358459473</v>
       </c>
       <c r="E128" t="n">
-        <v>14.61662524586311</v>
+        <v>14.61662426223638</v>
       </c>
       <c r="F128" t="n">
         <v>2928535</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.9363899230957</v>
+        <v>13.93639087677002</v>
       </c>
       <c r="C129" t="n">
-        <v>14.41927122633967</v>
+        <v>14.4192722130578</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373455318874</v>
+        <v>13.75373549436386</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153267354464</v>
+        <v>14.17153364330989</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06656074523926</v>
+        <v>14.06655979156494</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893809899156</v>
+        <v>14.15893713905431</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462191733692</v>
+        <v>13.81462098074336</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351724825013</v>
+        <v>13.83351631037553</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3032,16 +3032,16 @@
         <v>44418</v>
       </c>
       <c r="B131" t="n">
-        <v>13.64666175842285</v>
+        <v>13.64666271209717</v>
       </c>
       <c r="C131" t="n">
-        <v>14.43816789362585</v>
+        <v>14.43816890261326</v>
       </c>
       <c r="D131" t="n">
-        <v>13.56688184180349</v>
+        <v>13.56688278990252</v>
       </c>
       <c r="E131" t="n">
-        <v>14.05396179104118</v>
+        <v>14.05396277317898</v>
       </c>
       <c r="F131" t="n">
         <v>2933806</v>
@@ -3092,16 +3092,16 @@
         <v>44421</v>
       </c>
       <c r="B134" t="n">
-        <v>12.95593070983887</v>
+        <v>12.95593166351318</v>
       </c>
       <c r="C134" t="n">
-        <v>13.76423290704215</v>
+        <v>13.76423392021486</v>
       </c>
       <c r="D134" t="n">
-        <v>12.78797285545454</v>
+        <v>12.78797379676563</v>
       </c>
       <c r="E134" t="n">
-        <v>13.5710801973981</v>
+        <v>13.57108119635301</v>
       </c>
       <c r="F134" t="n">
         <v>3730102</v>
@@ -3252,16 +3252,16 @@
         <v>44433</v>
       </c>
       <c r="B142" t="n">
-        <v>13.47870445251465</v>
+        <v>13.47870349884033</v>
       </c>
       <c r="C142" t="n">
-        <v>13.57947900869956</v>
+        <v>13.57947804789503</v>
       </c>
       <c r="D142" t="n">
-        <v>13.05040893565314</v>
+        <v>13.05040801228251</v>
       </c>
       <c r="E142" t="n">
-        <v>13.44511239258996</v>
+        <v>13.44511144129242</v>
       </c>
       <c r="F142" t="n">
         <v>2709595</v>
@@ -3312,16 +3312,16 @@
         <v>44438</v>
       </c>
       <c r="B145" t="n">
-        <v>13.34433650970459</v>
+        <v>13.34433555603027</v>
       </c>
       <c r="C145" t="n">
-        <v>14.09175331983246</v>
+        <v>14.09175231274281</v>
       </c>
       <c r="D145" t="n">
-        <v>13.24356114561362</v>
+        <v>13.24356019914138</v>
       </c>
       <c r="E145" t="n">
-        <v>13.68865186346858</v>
+        <v>13.68865088518722</v>
       </c>
       <c r="F145" t="n">
         <v>1186841</v>
@@ -3332,16 +3332,16 @@
         <v>44439</v>
       </c>
       <c r="B146" t="n">
-        <v>12.77327728271484</v>
+        <v>12.77327632904053</v>
       </c>
       <c r="C146" t="n">
-        <v>13.40312355555788</v>
+        <v>13.40312255485818</v>
       </c>
       <c r="D146" t="n">
-        <v>12.49614440311536</v>
+        <v>12.49614347013225</v>
       </c>
       <c r="E146" t="n">
-        <v>13.28555134208388</v>
+        <v>13.28555035016233</v>
       </c>
       <c r="F146" t="n">
         <v>2117441</v>
@@ -3372,16 +3372,16 @@
         <v>44441</v>
       </c>
       <c r="B148" t="n">
-        <v>12.80686569213867</v>
+        <v>12.8068675994873</v>
       </c>
       <c r="C148" t="n">
-        <v>13.18477304733007</v>
+        <v>13.1847750109611</v>
       </c>
       <c r="D148" t="n">
-        <v>12.69769314170979</v>
+        <v>12.69769503279916</v>
       </c>
       <c r="E148" t="n">
-        <v>13.0672024835152</v>
+        <v>13.06720442963625</v>
       </c>
       <c r="F148" t="n">
         <v>2514879</v>
@@ -3392,16 +3392,16 @@
         <v>44442</v>
       </c>
       <c r="B149" t="n">
-        <v>13.10079574584961</v>
+        <v>13.10079669952393</v>
       </c>
       <c r="C149" t="n">
-        <v>13.21836713959238</v>
+        <v>13.21836810182533</v>
       </c>
       <c r="D149" t="n">
-        <v>12.74808237641584</v>
+        <v>12.74808330441434</v>
       </c>
       <c r="E149" t="n">
-        <v>12.94963310517644</v>
+        <v>12.94963404784685</v>
       </c>
       <c r="F149" t="n">
         <v>3315331</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00001949529792</v>
+        <v>13.00002128473755</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113085479707</v>
+        <v>13.36113269394332</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3532,16 +3532,16 @@
         <v>44454</v>
       </c>
       <c r="B156" t="n">
-        <v>13.44511032104492</v>
+        <v>13.44511127471924</v>
       </c>
       <c r="C156" t="n">
-        <v>14.07495566502791</v>
+        <v>14.07495666337775</v>
       </c>
       <c r="D156" t="n">
-        <v>13.23516160245244</v>
+        <v>13.2351625412349</v>
       </c>
       <c r="E156" t="n">
-        <v>13.47030355031223</v>
+        <v>13.47030450577353</v>
       </c>
       <c r="F156" t="n">
         <v>2602050</v>
@@ -3552,16 +3552,16 @@
         <v>44455</v>
       </c>
       <c r="B157" t="n">
-        <v>13.56268405914307</v>
+        <v>13.56268310546875</v>
       </c>
       <c r="C157" t="n">
-        <v>13.7894288445363</v>
+        <v>13.78942787491819</v>
       </c>
       <c r="D157" t="n">
-        <v>13.33593927374983</v>
+        <v>13.33593833601931</v>
       </c>
       <c r="E157" t="n">
-        <v>13.47870471946269</v>
+        <v>13.47870377169347</v>
       </c>
       <c r="F157" t="n">
         <v>1227183</v>
@@ -3572,16 +3572,16 @@
         <v>44456</v>
       </c>
       <c r="B158" t="n">
-        <v>13.44511032104492</v>
+        <v>13.44511127471924</v>
       </c>
       <c r="C158" t="n">
-        <v>13.74743719019722</v>
+        <v>13.74743816531587</v>
       </c>
       <c r="D158" t="n">
-        <v>13.29394688646877</v>
+        <v>13.29394782942092</v>
       </c>
       <c r="E158" t="n">
-        <v>13.4031210644031</v>
+        <v>13.40312201509908</v>
       </c>
       <c r="F158" t="n">
         <v>5378949</v>
@@ -3632,16 +3632,16 @@
         <v>44461</v>
       </c>
       <c r="B161" t="n">
-        <v>14.10015106201172</v>
+        <v>14.1001501083374</v>
       </c>
       <c r="C161" t="n">
-        <v>14.46126322911574</v>
+        <v>14.46126225101733</v>
       </c>
       <c r="D161" t="n">
-        <v>13.58787626629261</v>
+        <v>13.58787534726639</v>
       </c>
       <c r="E161" t="n">
-        <v>13.71384566466818</v>
+        <v>13.71384473712192</v>
       </c>
       <c r="F161" t="n">
         <v>3751489</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.61242580413818</v>
+        <v>14.61242771148682</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630177220344</v>
+        <v>15.11630374532261</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893629636717</v>
+        <v>14.15893814452217</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19252835228931</v>
+        <v>14.19253020482906</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26810988418833</v>
+        <v>14.26811184817934</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141639771024</v>
+        <v>13.83141830159083</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733371488308</v>
+        <v>14.16733566500235</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3712,16 +3712,16 @@
         <v>44467</v>
       </c>
       <c r="B165" t="n">
-        <v>13.16797828674316</v>
+        <v>13.16797924041748</v>
       </c>
       <c r="C165" t="n">
-        <v>13.89020096850395</v>
+        <v>13.89020197448434</v>
       </c>
       <c r="D165" t="n">
-        <v>13.15118144759716</v>
+        <v>13.15118240005499</v>
       </c>
       <c r="E165" t="n">
-        <v>13.64666100728992</v>
+        <v>13.64666199563223</v>
       </c>
       <c r="F165" t="n">
         <v>3700200</v>
@@ -3772,16 +3772,16 @@
         <v>44470</v>
       </c>
       <c r="B168" t="n">
-        <v>12.78167247772217</v>
+        <v>12.78167343139648</v>
       </c>
       <c r="C168" t="n">
-        <v>13.11759141127408</v>
+        <v>13.1175923900122</v>
       </c>
       <c r="D168" t="n">
-        <v>12.00066367672549</v>
+        <v>12.00066457212668</v>
       </c>
       <c r="E168" t="n">
-        <v>12.6557038923833</v>
+        <v>12.65570483665877</v>
       </c>
       <c r="F168" t="n">
         <v>6332153</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498119354248</v>
+        <v>12.34498023986816</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366398204986</v>
+        <v>12.82366299139635</v>
       </c>
       <c r="D169" t="n">
-        <v>12.13503244542976</v>
+        <v>12.1350315079744</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288861542754</v>
+        <v>12.72288763255913</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14343070983887</v>
+        <v>12.14342975616455</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55493019965232</v>
+        <v>12.55492921366123</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027798749311</v>
+        <v>11.95027704898789</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337946226592</v>
+        <v>12.35337849210345</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3832,16 +3832,16 @@
         <v>44475</v>
       </c>
       <c r="B171" t="n">
-        <v>12.512939453125</v>
+        <v>12.51294136047363</v>
       </c>
       <c r="C171" t="n">
-        <v>12.61371399807913</v>
+        <v>12.61371592078883</v>
       </c>
       <c r="D171" t="n">
-        <v>11.68154174520576</v>
+        <v>11.68154352582436</v>
       </c>
       <c r="E171" t="n">
-        <v>11.94187855701982</v>
+        <v>11.94188037732158</v>
       </c>
       <c r="F171" t="n">
         <v>5058241</v>
@@ -3852,16 +3852,16 @@
         <v>44476</v>
       </c>
       <c r="B172" t="n">
-        <v>13.00001907348633</v>
+        <v>13.00002098083496</v>
       </c>
       <c r="C172" t="n">
-        <v>13.02521311499517</v>
+        <v>13.02521502604024</v>
       </c>
       <c r="D172" t="n">
-        <v>12.36177489269584</v>
+        <v>12.36177670640198</v>
       </c>
       <c r="E172" t="n">
-        <v>12.5633264129721</v>
+        <v>12.56332825624967</v>
       </c>
       <c r="F172" t="n">
         <v>3555051</v>
@@ -3932,16 +3932,16 @@
         <v>44483</v>
       </c>
       <c r="B176" t="n">
-        <v>13.16797828674316</v>
+        <v>13.16797924041748</v>
       </c>
       <c r="C176" t="n">
-        <v>13.29394686829084</v>
+        <v>13.29394783108827</v>
       </c>
       <c r="D176" t="n">
-        <v>12.85725421612295</v>
+        <v>12.85725514729346</v>
       </c>
       <c r="E176" t="n">
-        <v>13.1259882183643</v>
+        <v>13.12598916899754</v>
       </c>
       <c r="F176" t="n">
         <v>1588233</v>
@@ -3952,16 +3952,16 @@
         <v>44484</v>
       </c>
       <c r="B177" t="n">
-        <v>13.41991710662842</v>
+        <v>13.41991806030273</v>
       </c>
       <c r="C177" t="n">
-        <v>13.4871012202649</v>
+        <v>13.48710217871359</v>
       </c>
       <c r="D177" t="n">
-        <v>13.08399978562405</v>
+        <v>13.0840007154267</v>
       </c>
       <c r="E177" t="n">
-        <v>13.24356043192167</v>
+        <v>13.24356137306336</v>
       </c>
       <c r="F177" t="n">
         <v>1650266</v>
@@ -4032,16 +4032,16 @@
         <v>44490</v>
       </c>
       <c r="B181" t="n">
-        <v>11.24485015869141</v>
+        <v>11.24484920501709</v>
       </c>
       <c r="C181" t="n">
-        <v>11.95867573884459</v>
+        <v>11.95867472463081</v>
       </c>
       <c r="D181" t="n">
-        <v>10.8333514897461</v>
+        <v>10.83335057097093</v>
       </c>
       <c r="E181" t="n">
-        <v>11.84950235751801</v>
+        <v>11.84950135256322</v>
       </c>
       <c r="F181" t="n">
         <v>4870723</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.5310230255127</v>
+        <v>10.53102397918701</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174709395853</v>
+        <v>10.84174807577158</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624045672820648</v>
+        <v>9.624046544360398</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174709395853</v>
+        <v>10.84174807577158</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55621719360352</v>
+        <v>10.55621910095215</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650190285215</v>
+        <v>11.02650389517411</v>
       </c>
       <c r="D183" t="n">
-        <v>10.35466648795489</v>
+        <v>10.35466835888637</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699254642783</v>
+        <v>10.65699447198504</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4092,16 +4092,16 @@
         <v>44495</v>
       </c>
       <c r="B184" t="n">
-        <v>9.985158920288086</v>
+        <v>9.98515796661377</v>
       </c>
       <c r="C184" t="n">
-        <v>10.46384172900696</v>
+        <v>10.46384072961404</v>
       </c>
       <c r="D184" t="n">
-        <v>9.825597442852056</v>
+        <v>9.825596504417325</v>
       </c>
       <c r="E184" t="n">
-        <v>10.46384172900696</v>
+        <v>10.46384072961404</v>
       </c>
       <c r="F184" t="n">
         <v>5760068</v>
@@ -4112,16 +4112,16 @@
         <v>44496</v>
       </c>
       <c r="B185" t="n">
-        <v>10.32947254180908</v>
+        <v>10.3294734954834</v>
       </c>
       <c r="C185" t="n">
-        <v>10.57301250649444</v>
+        <v>10.57301348265372</v>
       </c>
       <c r="D185" t="n">
-        <v>9.976759209577022</v>
+        <v>9.976760130686884</v>
       </c>
       <c r="E185" t="n">
-        <v>10.07753375153378</v>
+        <v>10.07753468194771</v>
       </c>
       <c r="F185" t="n">
         <v>4005501</v>
@@ -4192,16 +4192,16 @@
         <v>44503</v>
       </c>
       <c r="B189" t="n">
-        <v>10.14471912384033</v>
+        <v>10.14471817016602</v>
       </c>
       <c r="C189" t="n">
-        <v>10.29588176737367</v>
+        <v>10.29588079948901</v>
       </c>
       <c r="D189" t="n">
-        <v>9.548464129163397</v>
+        <v>9.548463231541206</v>
       </c>
       <c r="E189" t="n">
-        <v>9.657638322085189</v>
+        <v>9.657637414199865</v>
       </c>
       <c r="F189" t="n">
         <v>6020061</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55621719360352</v>
+        <v>10.55621910095215</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771580682453</v>
+        <v>10.96771778852473</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588039192727</v>
+        <v>10.29588225223699</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64019651899136</v>
+        <v>10.64019844151379</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.74937152862549</v>
+        <v>10.74937057495117</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324836976697</v>
+        <v>11.25324737138916</v>
       </c>
       <c r="D193" t="n">
-        <v>10.40505616072565</v>
+        <v>10.40505523759868</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660608538766</v>
+        <v>10.60660514437936</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4292,16 +4292,16 @@
         <v>44510</v>
       </c>
       <c r="B194" t="n">
-        <v>10.66539096832275</v>
+        <v>10.66539192199707</v>
       </c>
       <c r="C194" t="n">
-        <v>11.16926775172825</v>
+        <v>11.16926875045805</v>
       </c>
       <c r="D194" t="n">
-        <v>10.44704422688129</v>
+        <v>10.44704516103155</v>
       </c>
       <c r="E194" t="n">
-        <v>10.74937029692459</v>
+        <v>10.74937125810814</v>
       </c>
       <c r="F194" t="n">
         <v>2771222</v>
@@ -4312,16 +4312,16 @@
         <v>44511</v>
       </c>
       <c r="B195" t="n">
-        <v>11.21965599060059</v>
+        <v>11.21965503692627</v>
       </c>
       <c r="C195" t="n">
-        <v>11.5303801014484</v>
+        <v>11.53037912136244</v>
       </c>
       <c r="D195" t="n">
-        <v>10.69058593129811</v>
+        <v>10.69058502259491</v>
       </c>
       <c r="E195" t="n">
-        <v>10.78296247010213</v>
+        <v>10.7829615535469</v>
       </c>
       <c r="F195" t="n">
         <v>2903296</v>
@@ -4352,16 +4352,16 @@
         <v>44516</v>
       </c>
       <c r="B197" t="n">
-        <v>10.16991233825684</v>
+        <v>10.16991329193115</v>
       </c>
       <c r="C197" t="n">
-        <v>10.85854381637763</v>
+        <v>10.85854483462774</v>
       </c>
       <c r="D197" t="n">
-        <v>10.10272822501953</v>
+        <v>10.10272917239372</v>
       </c>
       <c r="E197" t="n">
-        <v>10.85854381637763</v>
+        <v>10.85854483462774</v>
       </c>
       <c r="F197" t="n">
         <v>2296952</v>
@@ -4412,16 +4412,16 @@
         <v>44519</v>
       </c>
       <c r="B200" t="n">
-        <v>10.80815601348877</v>
+        <v>10.80815505981445</v>
       </c>
       <c r="C200" t="n">
-        <v>10.950921446049</v>
+        <v>10.95092047977755</v>
       </c>
       <c r="D200" t="n">
-        <v>10.3378712675281</v>
+        <v>10.33787035535008</v>
       </c>
       <c r="E200" t="n">
-        <v>10.3378712675281</v>
+        <v>10.33787035535008</v>
       </c>
       <c r="F200" t="n">
         <v>2187279</v>
@@ -4432,16 +4432,16 @@
         <v>44522</v>
       </c>
       <c r="B201" t="n">
-        <v>10.22029972076416</v>
+        <v>10.22030067443848</v>
       </c>
       <c r="C201" t="n">
-        <v>10.9257272347435</v>
+        <v>10.92572825424251</v>
       </c>
       <c r="D201" t="n">
-        <v>10.19510648982507</v>
+        <v>10.19510744114856</v>
       </c>
       <c r="E201" t="n">
-        <v>10.79135981862546</v>
+        <v>10.7913608255864</v>
       </c>
       <c r="F201" t="n">
         <v>1734497</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674432754516602</v>
+        <v>9.674434661865234</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34626814824561</v>
+        <v>10.34627018804897</v>
       </c>
       <c r="D202" t="n">
-        <v>9.481280068672081</v>
+        <v>9.481281937939977</v>
       </c>
       <c r="E202" t="n">
-        <v>10.28748205407023</v>
+        <v>10.2874840822837</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4472,16 +4472,16 @@
         <v>44524</v>
       </c>
       <c r="B203" t="n">
-        <v>9.699627876281738</v>
+        <v>9.699628829956055</v>
       </c>
       <c r="C203" t="n">
-        <v>10.11952534859934</v>
+        <v>10.11952634355827</v>
       </c>
       <c r="D203" t="n">
-        <v>9.38050576484858</v>
+        <v>9.380506687146584</v>
       </c>
       <c r="E203" t="n">
-        <v>9.842392497321224</v>
+        <v>9.842393465032259</v>
       </c>
       <c r="F203" t="n">
         <v>3236370</v>
@@ -4572,16 +4572,16 @@
         <v>44531</v>
       </c>
       <c r="B208" t="n">
-        <v>9.019394874572754</v>
+        <v>9.01939582824707</v>
       </c>
       <c r="C208" t="n">
-        <v>9.766811700804164</v>
+        <v>9.766812733507312</v>
       </c>
       <c r="D208" t="n">
-        <v>9.019394874572754</v>
+        <v>9.01939582824707</v>
       </c>
       <c r="E208" t="n">
-        <v>9.540066923765492</v>
+        <v>9.540067932493566</v>
       </c>
       <c r="F208" t="n">
         <v>2660840</v>
@@ -4612,16 +4612,16 @@
         <v>44533</v>
       </c>
       <c r="B210" t="n">
-        <v>9.901177406311035</v>
+        <v>9.901178359985352</v>
       </c>
       <c r="C210" t="n">
-        <v>10.08593290400486</v>
+        <v>10.0859338754747</v>
       </c>
       <c r="D210" t="n">
-        <v>9.615647363394388</v>
+        <v>9.615648289566654</v>
       </c>
       <c r="E210" t="n">
-        <v>9.649239419664992</v>
+        <v>9.649240349072821</v>
       </c>
       <c r="F210" t="n">
         <v>1913704</v>
@@ -4652,16 +4652,16 @@
         <v>44537</v>
       </c>
       <c r="B212" t="n">
-        <v>9.985158920288086</v>
+        <v>9.98515796661377</v>
       </c>
       <c r="C212" t="n">
-        <v>10.53102503899367</v>
+        <v>10.53102403318413</v>
       </c>
       <c r="D212" t="n">
-        <v>9.867586707170773</v>
+        <v>9.867585764725682</v>
       </c>
       <c r="E212" t="n">
-        <v>10.00195413893881</v>
+        <v>10.00195318366039</v>
       </c>
       <c r="F212" t="n">
         <v>3095174</v>
@@ -4672,16 +4672,16 @@
         <v>44538</v>
       </c>
       <c r="B213" t="n">
-        <v>10.57301425933838</v>
+        <v>10.57301330566406</v>
       </c>
       <c r="C213" t="n">
-        <v>10.66539242640349</v>
+        <v>10.66539146439676</v>
       </c>
       <c r="D213" t="n">
-        <v>9.792005341235662</v>
+        <v>9.792004458007494</v>
       </c>
       <c r="E213" t="n">
-        <v>9.985158878759011</v>
+        <v>9.985157978108607</v>
       </c>
       <c r="F213" t="n">
         <v>3040540</v>
@@ -4692,16 +4692,16 @@
         <v>44539</v>
       </c>
       <c r="B214" t="n">
-        <v>10.78222846984863</v>
+        <v>10.78222942352295</v>
       </c>
       <c r="C214" t="n">
-        <v>11.00401580523902</v>
+        <v>11.00401677853015</v>
       </c>
       <c r="D214" t="n">
-        <v>10.23629250667595</v>
+        <v>10.23629341206293</v>
       </c>
       <c r="E214" t="n">
-        <v>10.46661015591148</v>
+        <v>10.46661108166976</v>
       </c>
       <c r="F214" t="n">
         <v>2489235</v>
@@ -4732,16 +4732,16 @@
         <v>44543</v>
       </c>
       <c r="B216" t="n">
-        <v>11.19168090820312</v>
+        <v>11.19168186187744</v>
       </c>
       <c r="C216" t="n">
-        <v>11.55848110021426</v>
+        <v>11.55848208514464</v>
       </c>
       <c r="D216" t="n">
-        <v>11.13196871210059</v>
+        <v>11.13196966068666</v>
       </c>
       <c r="E216" t="n">
-        <v>11.25992259345134</v>
+        <v>11.25992355294072</v>
       </c>
       <c r="F216" t="n">
         <v>3334589</v>
@@ -4752,16 +4752,16 @@
         <v>44544</v>
       </c>
       <c r="B217" t="n">
-        <v>11.11490821838379</v>
+        <v>11.11490917205811</v>
       </c>
       <c r="C217" t="n">
-        <v>11.43905767023386</v>
+        <v>11.43905865172065</v>
       </c>
       <c r="D217" t="n">
-        <v>10.91871264942408</v>
+        <v>10.91871358626455</v>
       </c>
       <c r="E217" t="n">
-        <v>11.25992272893731</v>
+        <v>11.25992369505407</v>
       </c>
       <c r="F217" t="n">
         <v>1511299</v>
@@ -4772,16 +4772,16 @@
         <v>44545</v>
       </c>
       <c r="B218" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845455169678</v>
       </c>
       <c r="C218" t="n">
-        <v>11.37934603413065</v>
+        <v>11.37934699719004</v>
       </c>
       <c r="D218" t="n">
-        <v>10.8163502410046</v>
+        <v>10.81635115641641</v>
       </c>
       <c r="E218" t="n">
-        <v>10.90165255894037</v>
+        <v>10.9016534815715</v>
       </c>
       <c r="F218" t="n">
         <v>3122034</v>
@@ -4792,16 +4792,16 @@
         <v>44546</v>
       </c>
       <c r="B219" t="n">
-        <v>11.14049911499023</v>
+        <v>11.14049816131592</v>
       </c>
       <c r="C219" t="n">
-        <v>11.49023953281247</v>
+        <v>11.49023854919888</v>
       </c>
       <c r="D219" t="n">
-        <v>10.85900203718004</v>
+        <v>10.85900110760307</v>
       </c>
       <c r="E219" t="n">
-        <v>11.3964068986813</v>
+        <v>11.39640592310018</v>
       </c>
       <c r="F219" t="n">
         <v>2253468</v>
@@ -4812,16 +4812,16 @@
         <v>44547</v>
       </c>
       <c r="B220" t="n">
-        <v>11.17462062835693</v>
+        <v>11.17461967468262</v>
       </c>
       <c r="C220" t="n">
-        <v>11.21727220147566</v>
+        <v>11.21727124416134</v>
       </c>
       <c r="D220" t="n">
-        <v>10.91871366339456</v>
+        <v>10.91871273156008</v>
       </c>
       <c r="E220" t="n">
-        <v>11.19168208218776</v>
+        <v>11.19168112705737</v>
       </c>
       <c r="F220" t="n">
         <v>2659218</v>
@@ -4832,16 +4832,16 @@
         <v>44550</v>
       </c>
       <c r="B221" t="n">
-        <v>10.92724323272705</v>
+        <v>10.92724227905273</v>
       </c>
       <c r="C221" t="n">
-        <v>11.08931838717097</v>
+        <v>11.08931741935155</v>
       </c>
       <c r="D221" t="n">
-        <v>10.64574614643413</v>
+        <v>10.64574521732745</v>
       </c>
       <c r="E221" t="n">
-        <v>10.83341142035164</v>
+        <v>10.83341047486649</v>
       </c>
       <c r="F221" t="n">
         <v>2144606</v>
@@ -4852,16 +4852,16 @@
         <v>44551</v>
       </c>
       <c r="B222" t="n">
-        <v>10.739577293396</v>
+        <v>10.73957824707031</v>
       </c>
       <c r="C222" t="n">
-        <v>11.05519726804268</v>
+        <v>11.05519824974405</v>
       </c>
       <c r="D222" t="n">
-        <v>10.51779159906087</v>
+        <v>10.51779253304062</v>
       </c>
       <c r="E222" t="n">
-        <v>10.84194106328138</v>
+        <v>10.8419420260456</v>
       </c>
       <c r="F222" t="n">
         <v>1915833</v>
@@ -4872,16 +4872,16 @@
         <v>44552</v>
       </c>
       <c r="B223" t="n">
-        <v>10.5775032043457</v>
+        <v>10.57750415802002</v>
       </c>
       <c r="C223" t="n">
-        <v>10.84194045462105</v>
+        <v>10.84194143213719</v>
       </c>
       <c r="D223" t="n">
-        <v>10.33865524593855</v>
+        <v>10.33865617807819</v>
       </c>
       <c r="E223" t="n">
-        <v>10.83341014094282</v>
+        <v>10.83341111768986</v>
       </c>
       <c r="F223" t="n">
         <v>1137579</v>
@@ -4892,16 +4892,16 @@
         <v>44553</v>
       </c>
       <c r="B224" t="n">
-        <v>10.38983821868896</v>
+        <v>10.38983917236328</v>
       </c>
       <c r="C224" t="n">
-        <v>10.6542754757369</v>
+        <v>10.65427645368369</v>
       </c>
       <c r="D224" t="n">
-        <v>10.1936418236481</v>
+        <v>10.19364275931372</v>
       </c>
       <c r="E224" t="n">
-        <v>10.56897316135316</v>
+        <v>10.56897413147012</v>
       </c>
       <c r="F224" t="n">
         <v>1383482</v>
@@ -4932,16 +4932,16 @@
         <v>44558</v>
       </c>
       <c r="B226" t="n">
-        <v>10.08274841308594</v>
+        <v>10.08274936676025</v>
       </c>
       <c r="C226" t="n">
-        <v>10.50073048928689</v>
+        <v>10.50073148249594</v>
       </c>
       <c r="D226" t="n">
-        <v>9.988916610826452</v>
+        <v>9.98891755562571</v>
       </c>
       <c r="E226" t="n">
-        <v>10.15952041239668</v>
+        <v>10.15952137333246</v>
       </c>
       <c r="F226" t="n">
         <v>1405681</v>
@@ -4952,16 +4952,16 @@
         <v>44559</v>
       </c>
       <c r="B227" t="n">
-        <v>9.715948104858398</v>
+        <v>9.715950012207031</v>
       </c>
       <c r="C227" t="n">
-        <v>10.21923248819867</v>
+        <v>10.21923449434762</v>
       </c>
       <c r="D227" t="n">
-        <v>9.596524538126543</v>
+        <v>9.596526422031003</v>
       </c>
       <c r="E227" t="n">
-        <v>10.21923248819867</v>
+        <v>10.21923449434762</v>
       </c>
       <c r="F227" t="n">
         <v>1535423</v>
@@ -4972,16 +4972,16 @@
         <v>44560</v>
       </c>
       <c r="B228" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="C228" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="D228" t="n">
-        <v>9.647705662569827</v>
+        <v>9.647706562908386</v>
       </c>
       <c r="E228" t="n">
-        <v>9.792720171305367</v>
+        <v>9.7927210851769</v>
       </c>
       <c r="F228" t="n">
         <v>3325771</v>
@@ -4992,16 +4992,16 @@
         <v>44564</v>
       </c>
       <c r="B229" t="n">
-        <v>9.664767265319824</v>
+        <v>9.664769172668457</v>
       </c>
       <c r="C229" t="n">
-        <v>10.21923271856821</v>
+        <v>10.21923473534099</v>
       </c>
       <c r="D229" t="n">
-        <v>9.349147301752897</v>
+        <v>9.349149146813707</v>
       </c>
       <c r="E229" t="n">
-        <v>10.21923271856821</v>
+        <v>10.21923473534099</v>
       </c>
       <c r="F229" t="n">
         <v>4324384</v>
@@ -5032,16 +5032,16 @@
         <v>44566</v>
       </c>
       <c r="B231" t="n">
-        <v>8.530243873596191</v>
+        <v>8.530244827270508</v>
       </c>
       <c r="C231" t="n">
-        <v>9.255314788383105</v>
+        <v>9.255315823119759</v>
       </c>
       <c r="D231" t="n">
-        <v>8.479062814400418</v>
+        <v>8.479063762352734</v>
       </c>
       <c r="E231" t="n">
-        <v>9.255314788383105</v>
+        <v>9.255315823119759</v>
       </c>
       <c r="F231" t="n">
         <v>5451524</v>
@@ -5052,16 +5052,16 @@
         <v>44567</v>
       </c>
       <c r="B232" t="n">
-        <v>8.948226928710938</v>
+        <v>8.948225975036621</v>
       </c>
       <c r="C232" t="n">
-        <v>8.948226928710938</v>
+        <v>8.948225975036621</v>
       </c>
       <c r="D232" t="n">
-        <v>8.393761408545751</v>
+        <v>8.393760513964654</v>
       </c>
       <c r="E232" t="n">
-        <v>8.547306251931259</v>
+        <v>8.547305340985826</v>
       </c>
       <c r="F232" t="n">
         <v>4969753</v>
@@ -5072,16 +5072,16 @@
         <v>44568</v>
       </c>
       <c r="B233" t="n">
-        <v>8.700849533081055</v>
+        <v>8.700850486755371</v>
       </c>
       <c r="C233" t="n">
-        <v>8.94822617008616</v>
+        <v>8.948227150874695</v>
       </c>
       <c r="D233" t="n">
-        <v>8.564365331040909</v>
+        <v>8.564366269755597</v>
       </c>
       <c r="E233" t="n">
-        <v>8.94822617008616</v>
+        <v>8.948227150874695</v>
       </c>
       <c r="F233" t="n">
         <v>1845792</v>
@@ -5092,16 +5092,16 @@
         <v>44571</v>
       </c>
       <c r="B234" t="n">
-        <v>8.581425666809082</v>
+        <v>8.581426620483398</v>
       </c>
       <c r="C234" t="n">
-        <v>8.828803119963837</v>
+        <v>8.8288041011298</v>
       </c>
       <c r="D234" t="n">
-        <v>8.316987585908032</v>
+        <v>8.316988510194713</v>
       </c>
       <c r="E234" t="n">
-        <v>8.828803119963837</v>
+        <v>8.8288041011298</v>
       </c>
       <c r="F234" t="n">
         <v>3048446</v>
@@ -5112,16 +5112,16 @@
         <v>44572</v>
       </c>
       <c r="B235" t="n">
-        <v>8.717909812927246</v>
+        <v>8.71790885925293</v>
       </c>
       <c r="C235" t="n">
-        <v>8.914106224829805</v>
+        <v>8.914105249693064</v>
       </c>
       <c r="D235" t="n">
-        <v>8.530244540237847</v>
+        <v>8.530243607092713</v>
       </c>
       <c r="E235" t="n">
-        <v>8.530244540237847</v>
+        <v>8.530243607092713</v>
       </c>
       <c r="F235" t="n">
         <v>1168089</v>
@@ -5132,16 +5132,16 @@
         <v>44573</v>
       </c>
       <c r="B236" t="n">
-        <v>9.221193313598633</v>
+        <v>9.221194267272949</v>
       </c>
       <c r="C236" t="n">
-        <v>9.408859391749584</v>
+        <v>9.408860364832703</v>
       </c>
       <c r="D236" t="n">
-        <v>8.64113692537425</v>
+        <v>8.64113781905797</v>
       </c>
       <c r="E236" t="n">
-        <v>8.914105316548403</v>
+        <v>8.914106238463063</v>
       </c>
       <c r="F236" t="n">
         <v>2757539</v>
@@ -5192,16 +5192,16 @@
         <v>44578</v>
       </c>
       <c r="B239" t="n">
-        <v>8.700849533081055</v>
+        <v>8.700850486755371</v>
       </c>
       <c r="C239" t="n">
-        <v>8.862923853029804</v>
+        <v>8.862924824468605</v>
       </c>
       <c r="D239" t="n">
-        <v>8.487593328148517</v>
+        <v>8.487594258448453</v>
       </c>
       <c r="E239" t="n">
-        <v>8.862923853029804</v>
+        <v>8.862924824468605</v>
       </c>
       <c r="F239" t="n">
         <v>1156939</v>
@@ -5232,16 +5232,16 @@
         <v>44580</v>
       </c>
       <c r="B241" t="n">
-        <v>8.521713256835938</v>
+        <v>8.521714210510254</v>
       </c>
       <c r="C241" t="n">
-        <v>8.675258078133986</v>
+        <v>8.675259048991672</v>
       </c>
       <c r="D241" t="n">
-        <v>8.291397261763732</v>
+        <v>8.291398189663132</v>
       </c>
       <c r="E241" t="n">
-        <v>8.308457064500631</v>
+        <v>8.308457994309213</v>
       </c>
       <c r="F241" t="n">
         <v>1675201</v>
@@ -5352,16 +5352,16 @@
         <v>44588</v>
       </c>
       <c r="B247" t="n">
-        <v>10.15952014923096</v>
+        <v>10.15952110290527</v>
       </c>
       <c r="C247" t="n">
-        <v>10.50073021728269</v>
+        <v>10.5007312029864</v>
       </c>
       <c r="D247" t="n">
-        <v>9.988916352079942</v>
+        <v>9.988917289739678</v>
       </c>
       <c r="E247" t="n">
-        <v>10.28747402782326</v>
+        <v>10.28747499350861</v>
       </c>
       <c r="F247" t="n">
         <v>2570932</v>
@@ -5372,16 +5372,16 @@
         <v>44589</v>
       </c>
       <c r="B248" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="C248" t="n">
-        <v>10.26188330324402</v>
+        <v>10.26188426089857</v>
       </c>
       <c r="D248" t="n">
-        <v>9.681826917468367</v>
+        <v>9.681827820991172</v>
       </c>
       <c r="E248" t="n">
-        <v>10.1936416180302</v>
+        <v>10.19364256931633</v>
       </c>
       <c r="F248" t="n">
         <v>1431224</v>
@@ -5392,16 +5392,16 @@
         <v>44592</v>
       </c>
       <c r="B249" t="n">
-        <v>10.47514057159424</v>
+        <v>10.47513961791992</v>
       </c>
       <c r="C249" t="n">
-        <v>10.56044289300652</v>
+        <v>10.56044193156613</v>
       </c>
       <c r="D249" t="n">
-        <v>10.18511234895917</v>
+        <v>10.1851114216895</v>
       </c>
       <c r="E249" t="n">
-        <v>10.22776392195697</v>
+        <v>10.22776299080424</v>
       </c>
       <c r="F249" t="n">
         <v>3321007</v>
@@ -5452,16 +5452,16 @@
         <v>44595</v>
       </c>
       <c r="B252" t="n">
-        <v>10.45807933807373</v>
+        <v>10.45808029174805</v>
       </c>
       <c r="C252" t="n">
-        <v>10.84194099912248</v>
+        <v>10.84194198780122</v>
       </c>
       <c r="D252" t="n">
-        <v>10.25335427326433</v>
+        <v>10.25335520826973</v>
       </c>
       <c r="E252" t="n">
-        <v>10.62015448151653</v>
+        <v>10.62015544997051</v>
       </c>
       <c r="F252" t="n">
         <v>1397774</v>
@@ -5472,16 +5472,16 @@
         <v>44596</v>
       </c>
       <c r="B253" t="n">
-        <v>10.25335502624512</v>
+        <v>10.2533540725708</v>
       </c>
       <c r="C253" t="n">
-        <v>10.56044305830264</v>
+        <v>10.56044207606577</v>
       </c>
       <c r="D253" t="n">
-        <v>9.835372078074196</v>
+        <v>9.835371163276871</v>
       </c>
       <c r="E253" t="n">
-        <v>10.56044305830264</v>
+        <v>10.56044207606577</v>
       </c>
       <c r="F253" t="n">
         <v>2130212</v>
@@ -5492,16 +5492,16 @@
         <v>44599</v>
       </c>
       <c r="B254" t="n">
-        <v>10.13393020629883</v>
+        <v>10.13393115997314</v>
       </c>
       <c r="C254" t="n">
-        <v>10.3471855748181</v>
+        <v>10.34718654856125</v>
       </c>
       <c r="D254" t="n">
-        <v>9.937733815994584</v>
+        <v>9.937734751205435</v>
       </c>
       <c r="E254" t="n">
-        <v>10.04862706939122</v>
+        <v>10.04862801503791</v>
       </c>
       <c r="F254" t="n">
         <v>1517482</v>
@@ -5532,16 +5532,16 @@
         <v>44601</v>
       </c>
       <c r="B256" t="n">
-        <v>10.24482345581055</v>
+        <v>10.24482440948486</v>
       </c>
       <c r="C256" t="n">
-        <v>10.33012576810256</v>
+        <v>10.33012672971753</v>
       </c>
       <c r="D256" t="n">
-        <v>9.937733812226112</v>
+        <v>9.937734737313942</v>
       </c>
       <c r="E256" t="n">
-        <v>10.25335376949807</v>
+        <v>10.25335472396646</v>
       </c>
       <c r="F256" t="n">
         <v>1982123</v>
@@ -5592,16 +5592,16 @@
         <v>44606</v>
       </c>
       <c r="B259" t="n">
-        <v>10.5775032043457</v>
+        <v>10.57750415802002</v>
       </c>
       <c r="C259" t="n">
-        <v>10.65427520286651</v>
+        <v>10.65427616346264</v>
       </c>
       <c r="D259" t="n">
-        <v>9.767129176996722</v>
+        <v>9.767130057607208</v>
       </c>
       <c r="E259" t="n">
-        <v>9.775660315258195</v>
+        <v>9.775661196637856</v>
       </c>
       <c r="F259" t="n">
         <v>2873091</v>
@@ -5612,16 +5612,16 @@
         <v>44607</v>
       </c>
       <c r="B260" t="n">
-        <v>10.65427589416504</v>
+        <v>10.65427684783936</v>
       </c>
       <c r="C260" t="n">
-        <v>10.8675321007913</v>
+        <v>10.86753307355439</v>
       </c>
       <c r="D260" t="n">
-        <v>10.42395905907534</v>
+        <v>10.42395999213378</v>
       </c>
       <c r="E260" t="n">
-        <v>10.64574557993332</v>
+        <v>10.64574653284408</v>
       </c>
       <c r="F260" t="n">
         <v>2656887</v>
@@ -5632,16 +5632,16 @@
         <v>44608</v>
       </c>
       <c r="B261" t="n">
-        <v>10.56897258758545</v>
+        <v>10.56897354125977</v>
       </c>
       <c r="C261" t="n">
-        <v>10.69692563992313</v>
+        <v>10.69692660514308</v>
       </c>
       <c r="D261" t="n">
-        <v>10.38983765464612</v>
+        <v>10.38983859215648</v>
       </c>
       <c r="E261" t="n">
-        <v>10.66280438618869</v>
+        <v>10.66280534832977</v>
       </c>
       <c r="F261" t="n">
         <v>4241775</v>
@@ -5712,16 +5712,16 @@
         <v>44614</v>
       </c>
       <c r="B265" t="n">
-        <v>9.733009338378906</v>
+        <v>9.73300838470459</v>
       </c>
       <c r="C265" t="n">
-        <v>9.843903432330309</v>
+        <v>9.843902467790201</v>
       </c>
       <c r="D265" t="n">
-        <v>9.391800039938824</v>
+        <v>9.391799119697389</v>
       </c>
       <c r="E265" t="n">
-        <v>9.545344059320188</v>
+        <v>9.545343124033971</v>
       </c>
       <c r="F265" t="n">
         <v>6936571</v>
@@ -5772,16 +5772,16 @@
         <v>44617</v>
       </c>
       <c r="B268" t="n">
-        <v>9.425920486450195</v>
+        <v>9.425919532775879</v>
       </c>
       <c r="C268" t="n">
-        <v>9.869492701072385</v>
+        <v>9.86949170251933</v>
       </c>
       <c r="D268" t="n">
-        <v>9.383268915533016</v>
+        <v>9.383267966174003</v>
       </c>
       <c r="E268" t="n">
-        <v>9.579464492585451</v>
+        <v>9.579463523376209</v>
       </c>
       <c r="F268" t="n">
         <v>3597927</v>
@@ -5792,16 +5792,16 @@
         <v>44622</v>
       </c>
       <c r="B269" t="n">
-        <v>9.57093334197998</v>
+        <v>9.570934295654297</v>
       </c>
       <c r="C269" t="n">
-        <v>9.656235651776313</v>
+        <v>9.656236613950387</v>
       </c>
       <c r="D269" t="n">
-        <v>9.272374845401204</v>
+        <v>9.272375769326324</v>
       </c>
       <c r="E269" t="n">
-        <v>9.34914684175958</v>
+        <v>9.349147773334476</v>
       </c>
       <c r="F269" t="n">
         <v>1474809</v>
@@ -5812,16 +5812,16 @@
         <v>44623</v>
       </c>
       <c r="B270" t="n">
-        <v>9.639177322387695</v>
+        <v>9.639176368713379</v>
       </c>
       <c r="C270" t="n">
-        <v>10.15952157411429</v>
+        <v>10.15952056895851</v>
       </c>
       <c r="D270" t="n">
-        <v>9.562405314298255</v>
+        <v>9.562404368219553</v>
       </c>
       <c r="E270" t="n">
-        <v>9.860963031914597</v>
+        <v>9.860962056297398</v>
       </c>
       <c r="F270" t="n">
         <v>3265562</v>
@@ -5852,16 +5852,16 @@
         <v>44627</v>
       </c>
       <c r="B272" t="n">
-        <v>8.666728973388672</v>
+        <v>8.666728019714355</v>
       </c>
       <c r="C272" t="n">
-        <v>9.417390908101481</v>
+        <v>9.417389871825412</v>
       </c>
       <c r="D272" t="n">
-        <v>8.658198658538714</v>
+        <v>8.658197705803062</v>
       </c>
       <c r="E272" t="n">
-        <v>9.323557444751941</v>
+        <v>9.32355641880117</v>
       </c>
       <c r="F272" t="n">
         <v>2527651</v>
@@ -5872,16 +5872,16 @@
         <v>44628</v>
       </c>
       <c r="B273" t="n">
-        <v>8.897045135498047</v>
+        <v>8.89704418182373</v>
       </c>
       <c r="C273" t="n">
-        <v>8.92263608043597</v>
+        <v>8.92263512401856</v>
       </c>
       <c r="D273" t="n">
-        <v>8.521714574741987</v>
+        <v>8.521713661299355</v>
       </c>
       <c r="E273" t="n">
-        <v>8.726441309662004</v>
+        <v>8.726440374274713</v>
       </c>
       <c r="F273" t="n">
         <v>2260563</v>
@@ -5892,16 +5892,16 @@
         <v>44629</v>
       </c>
       <c r="B274" t="n">
-        <v>9.255315780639648</v>
+        <v>9.255314826965332</v>
       </c>
       <c r="C274" t="n">
-        <v>9.391799994099552</v>
+        <v>9.391799026361806</v>
       </c>
       <c r="D274" t="n">
-        <v>8.845863964843298</v>
+        <v>8.845863053359189</v>
       </c>
       <c r="E274" t="n">
-        <v>8.939697428498043</v>
+        <v>8.939696507345268</v>
       </c>
       <c r="F274" t="n">
         <v>2821903</v>
@@ -5932,16 +5932,16 @@
         <v>44631</v>
       </c>
       <c r="B276" t="n">
-        <v>8.615548133850098</v>
+        <v>8.615546226501465</v>
       </c>
       <c r="C276" t="n">
-        <v>9.195604611294117</v>
+        <v>9.195602575529984</v>
       </c>
       <c r="D276" t="n">
-        <v>8.470533602197403</v>
+        <v>8.470531726952736</v>
       </c>
       <c r="E276" t="n">
-        <v>9.195604611294117</v>
+        <v>9.195602575529984</v>
       </c>
       <c r="F276" t="n">
         <v>3220051</v>
@@ -5972,16 +5972,16 @@
         <v>44635</v>
       </c>
       <c r="B278" t="n">
-        <v>8.905575752258301</v>
+        <v>8.905576705932617</v>
       </c>
       <c r="C278" t="n">
-        <v>8.948226500067653</v>
+        <v>8.948227458309324</v>
       </c>
       <c r="D278" t="n">
-        <v>8.581426275823933</v>
+        <v>8.581427194785949</v>
       </c>
       <c r="E278" t="n">
-        <v>8.666728596025962</v>
+        <v>8.666729524122774</v>
       </c>
       <c r="F278" t="n">
         <v>2087539</v>
@@ -5992,16 +5992,16 @@
         <v>44636</v>
       </c>
       <c r="B279" t="n">
-        <v>8.948226928710938</v>
+        <v>8.948225975036621</v>
       </c>
       <c r="C279" t="n">
-        <v>9.229725670820471</v>
+        <v>9.229724687144891</v>
       </c>
       <c r="D279" t="n">
-        <v>8.589957001783693</v>
+        <v>8.589956086292677</v>
       </c>
       <c r="E279" t="n">
-        <v>8.956757243598096</v>
+        <v>8.956756289014645</v>
       </c>
       <c r="F279" t="n">
         <v>2215964</v>
@@ -6032,16 +6032,16 @@
         <v>44638</v>
       </c>
       <c r="B281" t="n">
-        <v>9.477102279663086</v>
+        <v>9.47710132598877</v>
       </c>
       <c r="C281" t="n">
-        <v>9.724478936358073</v>
+        <v>9.724477957790413</v>
       </c>
       <c r="D281" t="n">
-        <v>9.10177172490746</v>
+        <v>9.101770809002399</v>
       </c>
       <c r="E281" t="n">
-        <v>9.238255937811031</v>
+        <v>9.238255008171659</v>
       </c>
       <c r="F281" t="n">
         <v>3558801</v>
@@ -6052,16 +6052,16 @@
         <v>44641</v>
       </c>
       <c r="B282" t="n">
-        <v>9.61358642578125</v>
+        <v>9.613585472106934</v>
       </c>
       <c r="C282" t="n">
-        <v>9.741540322952996</v>
+        <v>9.741539356585566</v>
       </c>
       <c r="D282" t="n">
-        <v>9.39179989057245</v>
+        <v>9.391798958899509</v>
       </c>
       <c r="E282" t="n">
-        <v>9.451512094058163</v>
+        <v>9.451511156461731</v>
       </c>
       <c r="F282" t="n">
         <v>1800179</v>
@@ -6072,16 +6072,16 @@
         <v>44642</v>
       </c>
       <c r="B283" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C283" t="n">
-        <v>10.1253999073854</v>
+        <v>10.12539894068065</v>
       </c>
       <c r="D283" t="n">
-        <v>9.57093441902218</v>
+        <v>9.570933505254049</v>
       </c>
       <c r="E283" t="n">
-        <v>9.57093441902218</v>
+        <v>9.570933505254049</v>
       </c>
       <c r="F283" t="n">
         <v>2594043</v>
@@ -6092,16 +6092,16 @@
         <v>44643</v>
       </c>
       <c r="B284" t="n">
-        <v>10.31306457519531</v>
+        <v>10.31306552886963</v>
       </c>
       <c r="C284" t="n">
-        <v>10.31306457519531</v>
+        <v>10.31306552886963</v>
       </c>
       <c r="D284" t="n">
-        <v>9.809781002488929</v>
+        <v>9.809781909623382</v>
       </c>
       <c r="E284" t="n">
-        <v>9.988916769843387</v>
+        <v>9.988917693542961</v>
       </c>
       <c r="F284" t="n">
         <v>2504946</v>
@@ -6112,16 +6112,16 @@
         <v>44644</v>
       </c>
       <c r="B285" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C285" t="n">
-        <v>10.66280508866036</v>
+        <v>10.66280605391772</v>
       </c>
       <c r="D285" t="n">
-        <v>10.11686994044226</v>
+        <v>10.11687085627847</v>
       </c>
       <c r="E285" t="n">
-        <v>10.27894508177519</v>
+        <v>10.27894601228337</v>
       </c>
       <c r="F285" t="n">
         <v>1712400</v>
@@ -6132,16 +6132,16 @@
         <v>44645</v>
       </c>
       <c r="B286" t="n">
-        <v>10.7566385269165</v>
+        <v>10.75663948059082</v>
       </c>
       <c r="C286" t="n">
-        <v>10.83341052818152</v>
+        <v>10.83341148866237</v>
       </c>
       <c r="D286" t="n">
-        <v>10.37277687142488</v>
+        <v>10.37277779106635</v>
       </c>
       <c r="E286" t="n">
-        <v>10.6030936998032</v>
+        <v>10.60309463986436</v>
       </c>
       <c r="F286" t="n">
         <v>2057131</v>
@@ -6172,16 +6172,16 @@
         <v>44649</v>
       </c>
       <c r="B288" t="n">
-        <v>11.3452262878418</v>
+        <v>11.34522533416748</v>
       </c>
       <c r="C288" t="n">
-        <v>11.52436124879894</v>
+        <v>11.52436028006663</v>
       </c>
       <c r="D288" t="n">
-        <v>10.85047132964267</v>
+        <v>10.85047041755722</v>
       </c>
       <c r="E288" t="n">
-        <v>10.97842522657635</v>
+        <v>10.97842430373515</v>
       </c>
       <c r="F288" t="n">
         <v>4333811</v>
@@ -6292,16 +6292,16 @@
         <v>44657</v>
       </c>
       <c r="B294" t="n">
-        <v>10.5775032043457</v>
+        <v>10.57750415802002</v>
       </c>
       <c r="C294" t="n">
-        <v>10.73104720138732</v>
+        <v>10.73104816890526</v>
       </c>
       <c r="D294" t="n">
-        <v>10.21070218993162</v>
+        <v>10.21070311053493</v>
       </c>
       <c r="E294" t="n">
-        <v>10.73104720138732</v>
+        <v>10.73104816890526</v>
       </c>
       <c r="F294" t="n">
         <v>3552010</v>
@@ -6312,16 +6312,16 @@
         <v>44658</v>
       </c>
       <c r="B295" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C295" t="n">
-        <v>10.67133540265596</v>
+        <v>10.67133636868552</v>
       </c>
       <c r="D295" t="n">
-        <v>10.38130720055572</v>
+        <v>10.38130814033029</v>
       </c>
       <c r="E295" t="n">
-        <v>10.50073077191071</v>
+        <v>10.50073172249617</v>
       </c>
       <c r="F295" t="n">
         <v>1517584</v>
@@ -6332,16 +6332,16 @@
         <v>44659</v>
       </c>
       <c r="B296" t="n">
-        <v>10.36424541473389</v>
+        <v>10.3642463684082</v>
       </c>
       <c r="C296" t="n">
-        <v>10.53485085100341</v>
+        <v>10.53485182037612</v>
       </c>
       <c r="D296" t="n">
-        <v>10.17658100154546</v>
+        <v>10.17658193795169</v>
       </c>
       <c r="E296" t="n">
-        <v>10.53485085100341</v>
+        <v>10.53485182037612</v>
       </c>
       <c r="F296" t="n">
         <v>1523665</v>
@@ -6352,16 +6352,16 @@
         <v>44662</v>
       </c>
       <c r="B297" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C297" t="n">
-        <v>10.6116240292701</v>
+        <v>10.61162498989425</v>
       </c>
       <c r="D297" t="n">
-        <v>10.17658213841139</v>
+        <v>10.17658305965309</v>
       </c>
       <c r="E297" t="n">
-        <v>10.28747457118751</v>
+        <v>10.28747550246782</v>
       </c>
       <c r="F297" t="n">
         <v>2558465</v>
@@ -6392,16 +6392,16 @@
         <v>44664</v>
       </c>
       <c r="B299" t="n">
-        <v>10.60309505462646</v>
+        <v>10.60309314727783</v>
       </c>
       <c r="C299" t="n">
-        <v>10.7310489561398</v>
+        <v>10.73104702577405</v>
       </c>
       <c r="D299" t="n">
-        <v>10.38130851189225</v>
+        <v>10.38130664443992</v>
       </c>
       <c r="E299" t="n">
-        <v>10.62015568477269</v>
+        <v>10.62015377435509</v>
       </c>
       <c r="F299" t="n">
         <v>1276242</v>
@@ -6412,16 +6412,16 @@
         <v>44665</v>
       </c>
       <c r="B300" t="n">
-        <v>10.80781936645508</v>
+        <v>10.80782032012939</v>
       </c>
       <c r="C300" t="n">
-        <v>10.85047011092021</v>
+        <v>10.850471068358</v>
       </c>
       <c r="D300" t="n">
-        <v>10.48366991543704</v>
+        <v>10.48367084050864</v>
       </c>
       <c r="E300" t="n">
-        <v>10.54338211210479</v>
+        <v>10.54338304244535</v>
       </c>
       <c r="F300" t="n">
         <v>1300569</v>
@@ -6432,16 +6432,16 @@
         <v>44669</v>
       </c>
       <c r="B301" t="n">
-        <v>10.7566385269165</v>
+        <v>10.75663948059082</v>
       </c>
       <c r="C301" t="n">
-        <v>10.9784242167284</v>
+        <v>10.97842519006605</v>
       </c>
       <c r="D301" t="n">
-        <v>10.66280507310193</v>
+        <v>10.66280601845705</v>
       </c>
       <c r="E301" t="n">
-        <v>10.81634990021523</v>
+        <v>10.81635085918351</v>
       </c>
       <c r="F301" t="n">
         <v>2677159</v>
@@ -6452,16 +6452,16 @@
         <v>44670</v>
       </c>
       <c r="B302" t="n">
-        <v>10.94430446624756</v>
+        <v>10.94430541992188</v>
       </c>
       <c r="C302" t="n">
-        <v>11.07225753478839</v>
+        <v>11.07225849961239</v>
       </c>
       <c r="D302" t="n">
-        <v>10.48367078083392</v>
+        <v>10.48367169436914</v>
       </c>
       <c r="E302" t="n">
-        <v>10.68839667999924</v>
+        <v>10.68839761137404</v>
       </c>
       <c r="F302" t="n">
         <v>3002225</v>
@@ -6472,16 +6472,16 @@
         <v>44671</v>
       </c>
       <c r="B303" t="n">
-        <v>10.90165233612061</v>
+        <v>10.90165328979492</v>
       </c>
       <c r="C303" t="n">
-        <v>11.13196916704802</v>
+        <v>11.13197014087041</v>
       </c>
       <c r="D303" t="n">
-        <v>10.65427570162136</v>
+        <v>10.65427663365522</v>
       </c>
       <c r="E303" t="n">
-        <v>10.92724245376998</v>
+        <v>10.92724340968292</v>
       </c>
       <c r="F303" t="n">
         <v>2911811</v>
@@ -6492,16 +6492,16 @@
         <v>44673</v>
       </c>
       <c r="B304" t="n">
-        <v>10.37277793884277</v>
+        <v>10.37277698516846</v>
       </c>
       <c r="C304" t="n">
-        <v>10.83341164300124</v>
+        <v>10.83341064697621</v>
       </c>
       <c r="D304" t="n">
-        <v>10.30453624453844</v>
+        <v>10.30453529713828</v>
       </c>
       <c r="E304" t="n">
-        <v>10.7225183743921</v>
+        <v>10.72251738856261</v>
       </c>
       <c r="F304" t="n">
         <v>1699122</v>
@@ -6512,16 +6512,16 @@
         <v>44676</v>
       </c>
       <c r="B305" t="n">
-        <v>10.37277793884277</v>
+        <v>10.37277698516846</v>
       </c>
       <c r="C305" t="n">
-        <v>10.4324901428695</v>
+        <v>10.43248918370524</v>
       </c>
       <c r="D305" t="n">
-        <v>10.1509914016245</v>
+        <v>10.15099046834126</v>
       </c>
       <c r="E305" t="n">
-        <v>10.18511266106835</v>
+        <v>10.185111724648</v>
       </c>
       <c r="F305" t="n">
         <v>3255528</v>
@@ -6532,16 +6532,16 @@
         <v>44677</v>
       </c>
       <c r="B306" t="n">
-        <v>10.38983821868896</v>
+        <v>10.38983917236328</v>
       </c>
       <c r="C306" t="n">
-        <v>10.48367002238615</v>
+        <v>10.4836709846732</v>
       </c>
       <c r="D306" t="n">
-        <v>10.168050881958</v>
+        <v>10.16805181527464</v>
       </c>
       <c r="E306" t="n">
-        <v>10.32159570751536</v>
+        <v>10.32159665492575</v>
       </c>
       <c r="F306" t="n">
         <v>4697699</v>
@@ -6552,16 +6552,16 @@
         <v>44678</v>
       </c>
       <c r="B307" t="n">
-        <v>10.60309505462646</v>
+        <v>10.60309314727783</v>
       </c>
       <c r="C307" t="n">
-        <v>10.79076116165161</v>
+        <v>10.79075922054446</v>
       </c>
       <c r="D307" t="n">
-        <v>10.40689945711159</v>
+        <v>10.40689758505581</v>
       </c>
       <c r="E307" t="n">
-        <v>10.40689945711159</v>
+        <v>10.40689758505581</v>
       </c>
       <c r="F307" t="n">
         <v>2204206</v>
@@ -6592,16 +6592,16 @@
         <v>44680</v>
       </c>
       <c r="B309" t="n">
-        <v>11.65231323242188</v>
+        <v>11.65231418609619</v>
       </c>
       <c r="C309" t="n">
-        <v>11.85703994313725</v>
+        <v>11.85704091356727</v>
       </c>
       <c r="D309" t="n">
-        <v>11.46464797423132</v>
+        <v>11.46464891254633</v>
       </c>
       <c r="E309" t="n">
-        <v>11.68643448830498</v>
+        <v>11.68643544477193</v>
       </c>
       <c r="F309" t="n">
         <v>6890958</v>
@@ -6672,16 +6672,16 @@
         <v>44686</v>
       </c>
       <c r="B313" t="n">
-        <v>11.60966300964355</v>
+        <v>11.60966205596924</v>
       </c>
       <c r="C313" t="n">
-        <v>11.76320701886124</v>
+        <v>11.76320605257407</v>
       </c>
       <c r="D313" t="n">
-        <v>11.3878764855884</v>
+        <v>11.38787555013271</v>
       </c>
       <c r="E313" t="n">
-        <v>11.76320701886124</v>
+        <v>11.76320605257407</v>
       </c>
       <c r="F313" t="n">
         <v>3999622</v>
@@ -6712,16 +6712,16 @@
         <v>44690</v>
       </c>
       <c r="B315" t="n">
-        <v>10.99548625946045</v>
+        <v>10.99548530578613</v>
       </c>
       <c r="C315" t="n">
-        <v>11.41346840008224</v>
+        <v>11.41346741015497</v>
       </c>
       <c r="D315" t="n">
-        <v>10.85900286733568</v>
+        <v>10.85900192549901</v>
       </c>
       <c r="E315" t="n">
-        <v>11.4049389095849</v>
+        <v>11.40493792039742</v>
       </c>
       <c r="F315" t="n">
         <v>3635836</v>
@@ -6772,16 +6772,16 @@
         <v>44693</v>
       </c>
       <c r="B318" t="n">
-        <v>11.47317886352539</v>
+        <v>11.47317790985107</v>
       </c>
       <c r="C318" t="n">
-        <v>11.68643507432202</v>
+        <v>11.6864341029214</v>
       </c>
       <c r="D318" t="n">
-        <v>11.06372707072919</v>
+        <v>11.06372615108936</v>
       </c>
       <c r="E318" t="n">
-        <v>11.08078852410957</v>
+        <v>11.08078760305155</v>
       </c>
       <c r="F318" t="n">
         <v>2138727</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381118774414</v>
+        <v>11.93381309509277</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470443775087</v>
+        <v>12.04470636282327</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908449000746</v>
+        <v>11.72908636463518</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81438762430742</v>
+        <v>11.81438951256891</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6852,16 +6852,16 @@
         <v>44699</v>
       </c>
       <c r="B322" t="n">
-        <v>12.08735656738281</v>
+        <v>12.08735752105713</v>
       </c>
       <c r="C322" t="n">
-        <v>12.24943171656819</v>
+        <v>12.24943268302999</v>
       </c>
       <c r="D322" t="n">
-        <v>11.93381255718963</v>
+        <v>11.93381349874956</v>
       </c>
       <c r="E322" t="n">
-        <v>11.99352393346846</v>
+        <v>11.99352487973953</v>
       </c>
       <c r="F322" t="n">
         <v>3728683</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415687561035</v>
+        <v>12.45415782928467</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505013177474</v>
+        <v>12.56505109394068</v>
       </c>
       <c r="D323" t="n">
-        <v>11.9508724782104</v>
+        <v>11.95087339334582</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559753814858</v>
+        <v>12.15559846896078</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6892,16 +6892,16 @@
         <v>44701</v>
       </c>
       <c r="B324" t="n">
-        <v>12.50533771514893</v>
+        <v>12.50533866882324</v>
       </c>
       <c r="C324" t="n">
-        <v>12.658882538139</v>
+        <v>12.65888350352286</v>
       </c>
       <c r="D324" t="n">
-        <v>12.30914297255499</v>
+        <v>12.30914391126722</v>
       </c>
       <c r="E324" t="n">
-        <v>12.4797467738867</v>
+        <v>12.47974772560942</v>
       </c>
       <c r="F324" t="n">
         <v>4482610</v>
@@ -6912,16 +6912,16 @@
         <v>44704</v>
       </c>
       <c r="B325" t="n">
-        <v>12.55652046203613</v>
+        <v>12.55651950836182</v>
       </c>
       <c r="C325" t="n">
-        <v>12.71859562058061</v>
+        <v>12.7185946545966</v>
       </c>
       <c r="D325" t="n">
-        <v>12.45415833238528</v>
+        <v>12.45415738648542</v>
       </c>
       <c r="E325" t="n">
-        <v>12.52240002701364</v>
+        <v>12.52239907593079</v>
       </c>
       <c r="F325" t="n">
         <v>3535792</v>
@@ -6932,16 +6932,16 @@
         <v>44705</v>
       </c>
       <c r="B326" t="n">
-        <v>12.2664909362793</v>
+        <v>12.26649188995361</v>
       </c>
       <c r="C326" t="n">
-        <v>12.62476165062991</v>
+        <v>12.62476263215845</v>
       </c>
       <c r="D326" t="n">
-        <v>12.02764461796216</v>
+        <v>12.02764555306706</v>
       </c>
       <c r="E326" t="n">
-        <v>12.53092902118688</v>
+        <v>12.53092999542028</v>
       </c>
       <c r="F326" t="n">
         <v>3539137</v>
@@ -6972,16 +6972,16 @@
         <v>44707</v>
       </c>
       <c r="B328" t="n">
-        <v>12.70153331756592</v>
+        <v>12.70153427124023</v>
       </c>
       <c r="C328" t="n">
-        <v>12.92331982662067</v>
+        <v>12.92332079694747</v>
       </c>
       <c r="D328" t="n">
-        <v>12.38591500612253</v>
+        <v>12.38591593609915</v>
       </c>
       <c r="E328" t="n">
-        <v>12.42003626123349</v>
+        <v>12.42003719377205</v>
       </c>
       <c r="F328" t="n">
         <v>2007160</v>
@@ -6992,16 +6992,16 @@
         <v>44708</v>
       </c>
       <c r="B329" t="n">
-        <v>13.06833362579346</v>
+        <v>13.06833457946777</v>
       </c>
       <c r="C329" t="n">
-        <v>13.35836182301952</v>
+        <v>13.35836279785892</v>
       </c>
       <c r="D329" t="n">
-        <v>12.7612456254462</v>
+        <v>12.76124655671047</v>
       </c>
       <c r="E329" t="n">
-        <v>12.78683656700289</v>
+        <v>12.78683750013469</v>
       </c>
       <c r="F329" t="n">
         <v>4177410</v>
@@ -7012,16 +7012,16 @@
         <v>44711</v>
       </c>
       <c r="B330" t="n">
-        <v>12.73565578460693</v>
+        <v>12.73565483093262</v>
       </c>
       <c r="C330" t="n">
-        <v>13.33277285837116</v>
+        <v>13.33277185998338</v>
       </c>
       <c r="D330" t="n">
-        <v>12.73565578460693</v>
+        <v>12.73565483093262</v>
       </c>
       <c r="E330" t="n">
-        <v>13.26453116623858</v>
+        <v>13.26453017296089</v>
       </c>
       <c r="F330" t="n">
         <v>1851063</v>
@@ -7132,16 +7132,16 @@
         <v>44719</v>
       </c>
       <c r="B336" t="n">
-        <v>12.02764511108398</v>
+        <v>12.0276460647583</v>
       </c>
       <c r="C336" t="n">
-        <v>12.37738470118792</v>
+        <v>12.37738568259315</v>
       </c>
       <c r="D336" t="n">
-        <v>11.87410110191233</v>
+        <v>11.87410204341212</v>
       </c>
       <c r="E336" t="n">
-        <v>12.36885438683579</v>
+        <v>12.36885536756466</v>
       </c>
       <c r="F336" t="n">
         <v>3370370</v>
@@ -7152,16 +7152,16 @@
         <v>44720</v>
       </c>
       <c r="B337" t="n">
-        <v>12.02764511108398</v>
+        <v>12.0276460647583</v>
       </c>
       <c r="C337" t="n">
-        <v>12.14706868743044</v>
+        <v>12.14706965057388</v>
       </c>
       <c r="D337" t="n">
-        <v>11.80585941167863</v>
+        <v>11.80586034776752</v>
       </c>
       <c r="E337" t="n">
-        <v>11.9679329106191</v>
+        <v>11.96793385955882</v>
       </c>
       <c r="F337" t="n">
         <v>2224783</v>
@@ -7232,16 +7232,16 @@
         <v>44726</v>
       </c>
       <c r="B341" t="n">
-        <v>10.69692611694336</v>
+        <v>10.69692707061768</v>
       </c>
       <c r="C341" t="n">
-        <v>10.94430356838314</v>
+        <v>10.94430454411216</v>
       </c>
       <c r="D341" t="n">
-        <v>10.57750337271373</v>
+        <v>10.57750431574103</v>
       </c>
       <c r="E341" t="n">
-        <v>10.79075956889747</v>
+        <v>10.79076053093742</v>
       </c>
       <c r="F341" t="n">
         <v>2253062</v>
@@ -7252,16 +7252,16 @@
         <v>44727</v>
       </c>
       <c r="B342" t="n">
-        <v>10.83341026306152</v>
+        <v>10.83341121673584</v>
       </c>
       <c r="C342" t="n">
-        <v>11.07225657499456</v>
+        <v>11.07225754969472</v>
       </c>
       <c r="D342" t="n">
-        <v>10.67133512593145</v>
+        <v>10.67133606533815</v>
       </c>
       <c r="E342" t="n">
-        <v>10.88459132112458</v>
+        <v>10.88459227930441</v>
       </c>
       <c r="F342" t="n">
         <v>3158221</v>
@@ -7312,16 +7312,16 @@
         <v>44733</v>
       </c>
       <c r="B345" t="n">
-        <v>10.46660995483398</v>
+        <v>10.4666109085083</v>
       </c>
       <c r="C345" t="n">
-        <v>10.65427520665525</v>
+        <v>10.65427617742885</v>
       </c>
       <c r="D345" t="n">
-        <v>10.33012576051704</v>
+        <v>10.33012670175548</v>
       </c>
       <c r="E345" t="n">
-        <v>10.43248870010894</v>
+        <v>10.43248965067427</v>
       </c>
       <c r="F345" t="n">
         <v>1967020</v>
@@ -7332,16 +7332,16 @@
         <v>44734</v>
       </c>
       <c r="B346" t="n">
-        <v>10.56044292449951</v>
+        <v>10.5604419708252</v>
       </c>
       <c r="C346" t="n">
-        <v>10.77369914095784</v>
+        <v>10.77369816802514</v>
       </c>
       <c r="D346" t="n">
-        <v>10.33012690337453</v>
+        <v>10.33012597049919</v>
       </c>
       <c r="E346" t="n">
-        <v>10.42395953966619</v>
+        <v>10.42395859831718</v>
       </c>
       <c r="F346" t="n">
         <v>1465281</v>
@@ -7352,16 +7352,16 @@
         <v>44735</v>
       </c>
       <c r="B347" t="n">
-        <v>10.80781936645508</v>
+        <v>10.80782032012939</v>
       </c>
       <c r="C347" t="n">
-        <v>10.91018230758797</v>
+        <v>10.91018327029472</v>
       </c>
       <c r="D347" t="n">
-        <v>10.48366991543704</v>
+        <v>10.48367084050864</v>
       </c>
       <c r="E347" t="n">
-        <v>10.49220022924672</v>
+        <v>10.49220115507102</v>
       </c>
       <c r="F347" t="n">
         <v>2364459</v>
@@ -7392,16 +7392,16 @@
         <v>44739</v>
       </c>
       <c r="B349" t="n">
-        <v>10.739577293396</v>
+        <v>10.73957824707031</v>
       </c>
       <c r="C349" t="n">
-        <v>10.8504705528552</v>
+        <v>10.85047151637684</v>
       </c>
       <c r="D349" t="n">
-        <v>10.45807939996106</v>
+        <v>10.45808032863837</v>
       </c>
       <c r="E349" t="n">
-        <v>10.7992894924958</v>
+        <v>10.79929045147256</v>
       </c>
       <c r="F349" t="n">
         <v>1685945</v>
@@ -7452,16 +7452,16 @@
         <v>44742</v>
       </c>
       <c r="B352" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C352" t="n">
-        <v>10.1253999073854</v>
+        <v>10.12539894068065</v>
       </c>
       <c r="D352" t="n">
-        <v>9.724478429017642</v>
+        <v>9.724477500590167</v>
       </c>
       <c r="E352" t="n">
-        <v>9.97185589738994</v>
+        <v>9.971854945344536</v>
       </c>
       <c r="F352" t="n">
         <v>3400779</v>
@@ -7512,16 +7512,16 @@
         <v>44747</v>
       </c>
       <c r="B355" t="n">
-        <v>9.622114181518555</v>
+        <v>9.622116088867188</v>
       </c>
       <c r="C355" t="n">
-        <v>9.681826374240668</v>
+        <v>9.681828293425781</v>
       </c>
       <c r="D355" t="n">
-        <v>9.178542015641739</v>
+        <v>9.178543835063046</v>
       </c>
       <c r="E355" t="n">
-        <v>9.681826374240668</v>
+        <v>9.681828293425781</v>
       </c>
       <c r="F355" t="n">
         <v>3899578</v>
@@ -7552,16 +7552,16 @@
         <v>44749</v>
       </c>
       <c r="B357" t="n">
-        <v>9.912142753601074</v>
+        <v>9.912143707275391</v>
       </c>
       <c r="C357" t="n">
-        <v>10.1168694550903</v>
+        <v>10.11687042846193</v>
       </c>
       <c r="D357" t="n">
-        <v>9.630645703584392</v>
+        <v>9.630646630175109</v>
       </c>
       <c r="E357" t="n">
-        <v>9.647705506173859</v>
+        <v>9.647706434405947</v>
       </c>
       <c r="F357" t="n">
         <v>2588468</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.11030101776123</v>
+        <v>9.110300064086914</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707418920911163</v>
+        <v>9.707417904730018</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076180583712192</v>
+        <v>9.076179633609632</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707418920911163</v>
+        <v>9.707417904730018</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7612,16 +7612,16 @@
         <v>44754</v>
       </c>
       <c r="B360" t="n">
-        <v>9.22972583770752</v>
+        <v>9.229724884033203</v>
       </c>
       <c r="C360" t="n">
-        <v>9.289437218413942</v>
+        <v>9.289436258569864</v>
       </c>
       <c r="D360" t="n">
-        <v>8.879985394760249</v>
+        <v>8.879984477223353</v>
       </c>
       <c r="E360" t="n">
-        <v>9.22972583770752</v>
+        <v>9.229724884033203</v>
       </c>
       <c r="F360" t="n">
         <v>1719496</v>
@@ -7632,16 +7632,16 @@
         <v>44755</v>
       </c>
       <c r="B361" t="n">
-        <v>9.255315780639648</v>
+        <v>9.255314826965332</v>
       </c>
       <c r="C361" t="n">
-        <v>9.383269679221847</v>
+        <v>9.383268712363071</v>
       </c>
       <c r="D361" t="n">
-        <v>9.050590697324836</v>
+        <v>9.050589764745537</v>
       </c>
       <c r="E361" t="n">
-        <v>9.204134715956785</v>
+        <v>9.204133767556202</v>
       </c>
       <c r="F361" t="n">
         <v>1870727</v>
@@ -7732,16 +7732,16 @@
         <v>44762</v>
       </c>
       <c r="B366" t="n">
-        <v>10.08274841308594</v>
+        <v>10.08274936676025</v>
       </c>
       <c r="C366" t="n">
-        <v>10.20217198122667</v>
+        <v>10.20217294619664</v>
       </c>
       <c r="D366" t="n">
-        <v>9.724477708663724</v>
+        <v>9.724478628451092</v>
       </c>
       <c r="E366" t="n">
-        <v>9.767129277493721</v>
+        <v>9.767130201315277</v>
       </c>
       <c r="F366" t="n">
         <v>1476532</v>
@@ -7752,16 +7752,16 @@
         <v>44763</v>
       </c>
       <c r="B367" t="n">
-        <v>9.963324546813965</v>
+        <v>9.963325500488281</v>
       </c>
       <c r="C367" t="n">
-        <v>10.1936413624377</v>
+        <v>10.19364233815759</v>
       </c>
       <c r="D367" t="n">
-        <v>9.94626391979247</v>
+        <v>9.946264871833769</v>
       </c>
       <c r="E367" t="n">
-        <v>10.02303591680597</v>
+        <v>10.02303687619577</v>
       </c>
       <c r="F367" t="n">
         <v>1242590</v>
@@ -7772,16 +7772,16 @@
         <v>44764</v>
       </c>
       <c r="B368" t="n">
-        <v>10.35571765899658</v>
+        <v>10.35571670532227</v>
       </c>
       <c r="C368" t="n">
-        <v>10.3898389168763</v>
+        <v>10.38983796005971</v>
       </c>
       <c r="D368" t="n">
-        <v>9.954796177243145</v>
+        <v>9.954795260490318</v>
       </c>
       <c r="E368" t="n">
-        <v>10.07421893065553</v>
+        <v>10.07421800290487</v>
       </c>
       <c r="F368" t="n">
         <v>1969757</v>
@@ -7792,16 +7792,16 @@
         <v>44767</v>
       </c>
       <c r="B369" t="n">
-        <v>10.1765832901001</v>
+        <v>10.17658138275146</v>
       </c>
       <c r="C369" t="n">
-        <v>10.41542963525714</v>
+        <v>10.41542768314268</v>
       </c>
       <c r="D369" t="n">
-        <v>10.11687108537331</v>
+        <v>10.11686918921625</v>
       </c>
       <c r="E369" t="n">
-        <v>10.27041510550403</v>
+        <v>10.27041318056894</v>
       </c>
       <c r="F369" t="n">
         <v>1372535</v>
@@ -7812,16 +7812,16 @@
         <v>44768</v>
       </c>
       <c r="B370" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C370" t="n">
-        <v>10.40689863334928</v>
+        <v>10.40689763976893</v>
       </c>
       <c r="D370" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="E370" t="n">
-        <v>10.22776368016013</v>
+        <v>10.22776270368238</v>
       </c>
       <c r="F370" t="n">
         <v>1502988</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.50926208496094</v>
+        <v>10.5092601776123</v>
       </c>
       <c r="C371" t="n">
-        <v>10.6116250380558</v>
+        <v>10.61162311212909</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421932816195</v>
+        <v>10.07421749977017</v>
       </c>
       <c r="E371" t="n">
-        <v>10.1254003924177</v>
+        <v>10.12539855473696</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7852,16 +7852,16 @@
         <v>44770</v>
       </c>
       <c r="B372" t="n">
-        <v>10.74810695648193</v>
+        <v>10.74810791015625</v>
       </c>
       <c r="C372" t="n">
-        <v>10.8419404065262</v>
+        <v>10.84194136852631</v>
       </c>
       <c r="D372" t="n">
-        <v>10.21923245827733</v>
+        <v>10.21923336502487</v>
       </c>
       <c r="E372" t="n">
-        <v>10.21923245827733</v>
+        <v>10.21923336502487</v>
       </c>
       <c r="F372" t="n">
         <v>1467207</v>
@@ -7892,16 +7892,16 @@
         <v>44774</v>
       </c>
       <c r="B374" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845455169678</v>
       </c>
       <c r="C374" t="n">
-        <v>11.77173801596846</v>
+        <v>11.77173901223685</v>
       </c>
       <c r="D374" t="n">
-        <v>11.09784813756763</v>
+        <v>11.09784907680322</v>
       </c>
       <c r="E374" t="n">
-        <v>11.64378412677316</v>
+        <v>11.64378511221253</v>
       </c>
       <c r="F374" t="n">
         <v>4838693</v>
@@ -7912,16 +7912,16 @@
         <v>44775</v>
       </c>
       <c r="B375" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845455169678</v>
       </c>
       <c r="C375" t="n">
-        <v>11.49876960907404</v>
+        <v>11.49877058224051</v>
       </c>
       <c r="D375" t="n">
-        <v>11.24286265526674</v>
+        <v>11.24286360677524</v>
       </c>
       <c r="E375" t="n">
-        <v>11.39640666263446</v>
+        <v>11.39640762713773</v>
       </c>
       <c r="F375" t="n">
         <v>2088249</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.16216659545898</v>
+        <v>13.1621675491333</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718027646215</v>
+        <v>13.30718124064354</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271484390118</v>
+        <v>12.75271576790837</v>
       </c>
       <c r="E379" t="n">
-        <v>12.7953655870149</v>
+        <v>12.79536651411238</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248466491699</v>
+        <v>13.39248371124268</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634635999027</v>
+        <v>13.77634537898129</v>
       </c>
       <c r="D381" t="n">
-        <v>13.17922926709854</v>
+        <v>13.17922832861007</v>
       </c>
       <c r="E381" t="n">
-        <v>13.30718234087294</v>
+        <v>13.30718139327297</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8052,16 +8052,16 @@
         <v>44784</v>
       </c>
       <c r="B382" t="n">
-        <v>13.36689281463623</v>
+        <v>13.36689472198486</v>
       </c>
       <c r="C382" t="n">
-        <v>13.63986038115962</v>
+        <v>13.63986232745854</v>
       </c>
       <c r="D382" t="n">
-        <v>13.1195153648052</v>
+        <v>13.11951723685505</v>
       </c>
       <c r="E382" t="n">
-        <v>13.52043681312337</v>
+        <v>13.5204387423815</v>
       </c>
       <c r="F382" t="n">
         <v>2014153</v>
@@ -8132,16 +8132,16 @@
         <v>44790</v>
       </c>
       <c r="B386" t="n">
-        <v>13.56308937072754</v>
+        <v>13.56308841705322</v>
       </c>
       <c r="C386" t="n">
-        <v>13.64839168994857</v>
+        <v>13.64839073027631</v>
       </c>
       <c r="D386" t="n">
-        <v>13.23893989802095</v>
+        <v>13.23893896713886</v>
       </c>
       <c r="E386" t="n">
-        <v>13.64839168994857</v>
+        <v>13.64839073027631</v>
       </c>
       <c r="F386" t="n">
         <v>4054357</v>
@@ -8152,16 +8152,16 @@
         <v>44791</v>
       </c>
       <c r="B387" t="n">
-        <v>13.63986110687256</v>
+        <v>13.63986206054688</v>
       </c>
       <c r="C387" t="n">
-        <v>14.13461438369162</v>
+        <v>14.13461537195818</v>
       </c>
       <c r="D387" t="n">
-        <v>13.23893963722324</v>
+        <v>13.23894056286585</v>
       </c>
       <c r="E387" t="n">
-        <v>13.64839142108495</v>
+        <v>13.64839237535569</v>
       </c>
       <c r="F387" t="n">
         <v>3074090</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066864013672</v>
+        <v>12.88066959381104</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59720924665701</v>
+        <v>13.59721025338341</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801789456504</v>
+        <v>12.83801884508153</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59720924665701</v>
+        <v>13.59721025338341</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8192,16 +8192,16 @@
         <v>44795</v>
       </c>
       <c r="B389" t="n">
-        <v>12.52239894866943</v>
+        <v>12.52239990234375</v>
       </c>
       <c r="C389" t="n">
-        <v>12.81242715659389</v>
+        <v>12.81242813235602</v>
       </c>
       <c r="D389" t="n">
-        <v>12.41150568908313</v>
+        <v>12.41150663431209</v>
       </c>
       <c r="E389" t="n">
-        <v>12.71859452534137</v>
+        <v>12.71859549395744</v>
       </c>
       <c r="F389" t="n">
         <v>3082199</v>
@@ -8212,16 +8212,16 @@
         <v>44796</v>
       </c>
       <c r="B390" t="n">
-        <v>12.29208183288574</v>
+        <v>12.29208278656006</v>
       </c>
       <c r="C390" t="n">
-        <v>12.6418222319422</v>
+        <v>12.64182321275093</v>
       </c>
       <c r="D390" t="n">
-        <v>12.25796140158548</v>
+        <v>12.25796235261258</v>
       </c>
       <c r="E390" t="n">
-        <v>12.6418222319422</v>
+        <v>12.64182321275093</v>
       </c>
       <c r="F390" t="n">
         <v>5845922</v>
@@ -8272,16 +8272,16 @@
         <v>44799</v>
       </c>
       <c r="B393" t="n">
-        <v>12.18118858337402</v>
+        <v>12.18118953704834</v>
       </c>
       <c r="C393" t="n">
-        <v>12.49680855132523</v>
+        <v>12.49680952970967</v>
       </c>
       <c r="D393" t="n">
-        <v>12.03617489494593</v>
+        <v>12.03617583726701</v>
       </c>
       <c r="E393" t="n">
-        <v>12.45415698144445</v>
+        <v>12.45415795648967</v>
       </c>
       <c r="F393" t="n">
         <v>1257591</v>
@@ -8312,16 +8312,16 @@
         <v>44803</v>
       </c>
       <c r="B395" t="n">
-        <v>12.21531009674072</v>
+        <v>12.21530914306641</v>
       </c>
       <c r="C395" t="n">
-        <v>12.47121787225261</v>
+        <v>12.47121689859905</v>
       </c>
       <c r="D395" t="n">
-        <v>12.06176609110022</v>
+        <v>12.0617651494134</v>
       </c>
       <c r="E395" t="n">
-        <v>12.25796166752047</v>
+        <v>12.25796071051626</v>
       </c>
       <c r="F395" t="n">
         <v>2841466</v>
@@ -8332,16 +8332,16 @@
         <v>44804</v>
       </c>
       <c r="B396" t="n">
-        <v>12.03617572784424</v>
+        <v>12.03617477416992</v>
       </c>
       <c r="C396" t="n">
-        <v>12.33473426391999</v>
+        <v>12.33473328658969</v>
       </c>
       <c r="D396" t="n">
-        <v>11.92528246306372</v>
+        <v>11.92528151817592</v>
       </c>
       <c r="E396" t="n">
-        <v>12.1044174197925</v>
+        <v>12.10441646071113</v>
       </c>
       <c r="F396" t="n">
         <v>1958303</v>
@@ -8352,16 +8352,16 @@
         <v>44805</v>
       </c>
       <c r="B397" t="n">
-        <v>12.52239894866943</v>
+        <v>12.52239990234375</v>
       </c>
       <c r="C397" t="n">
-        <v>12.58211032325439</v>
+        <v>12.58211128147617</v>
       </c>
       <c r="D397" t="n">
-        <v>12.12147748115867</v>
+        <v>12.12147840429982</v>
       </c>
       <c r="E397" t="n">
-        <v>12.17265936616002</v>
+        <v>12.17266029319906</v>
       </c>
       <c r="F397" t="n">
         <v>3304080</v>
@@ -8392,16 +8392,16 @@
         <v>44809</v>
       </c>
       <c r="B399" t="n">
-        <v>13.30718231201172</v>
+        <v>13.3071813583374</v>
       </c>
       <c r="C399" t="n">
-        <v>13.40954526555925</v>
+        <v>13.40954430454897</v>
       </c>
       <c r="D399" t="n">
-        <v>12.38591655466734</v>
+        <v>12.38591566701658</v>
       </c>
       <c r="E399" t="n">
-        <v>12.48827868363151</v>
+        <v>12.48827778864485</v>
       </c>
       <c r="F399" t="n">
         <v>2134165</v>
@@ -8412,16 +8412,16 @@
         <v>44810</v>
       </c>
       <c r="B400" t="n">
-        <v>12.19824886322021</v>
+        <v>12.19824981689453</v>
       </c>
       <c r="C400" t="n">
-        <v>13.29012077517622</v>
+        <v>13.29012181421445</v>
       </c>
       <c r="D400" t="n">
-        <v>12.19824886322021</v>
+        <v>12.19824981689453</v>
       </c>
       <c r="E400" t="n">
-        <v>13.29012077517622</v>
+        <v>13.29012181421445</v>
       </c>
       <c r="F400" t="n">
         <v>5053579</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.33473491668701</v>
+        <v>12.3347339630127</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121913238976</v>
+        <v>12.47121816816301</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646415968605</v>
+        <v>11.97646323371185</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22384164603791</v>
+        <v>12.22384070093743</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8472,16 +8472,16 @@
         <v>44816</v>
       </c>
       <c r="B403" t="n">
-        <v>12.30696105957031</v>
+        <v>12.30696201324463</v>
       </c>
       <c r="C403" t="n">
-        <v>12.58102037271514</v>
+        <v>12.58102134762649</v>
       </c>
       <c r="D403" t="n">
-        <v>12.05859576045719</v>
+        <v>12.05859669488552</v>
       </c>
       <c r="E403" t="n">
-        <v>12.05859576045719</v>
+        <v>12.05859669488552</v>
       </c>
       <c r="F403" t="n">
         <v>4043263</v>
@@ -8512,16 +8512,16 @@
         <v>44818</v>
       </c>
       <c r="B405" t="n">
-        <v>12.58102130889893</v>
+        <v>12.58102226257324</v>
       </c>
       <c r="C405" t="n">
-        <v>12.60671367567597</v>
+        <v>12.60671463129783</v>
       </c>
       <c r="D405" t="n">
-        <v>11.73315094150718</v>
+        <v>11.7331518309107</v>
       </c>
       <c r="E405" t="n">
-        <v>11.86161607372562</v>
+        <v>11.86161697286714</v>
       </c>
       <c r="F405" t="n">
         <v>3060135</v>
@@ -8572,16 +8572,16 @@
         <v>44823</v>
       </c>
       <c r="B408" t="n">
-        <v>12.39260578155518</v>
+        <v>12.39260673522949</v>
       </c>
       <c r="C408" t="n">
-        <v>12.6067129485987</v>
+        <v>12.60671391874965</v>
       </c>
       <c r="D408" t="n">
-        <v>12.19562520887531</v>
+        <v>12.19562614739096</v>
       </c>
       <c r="E408" t="n">
-        <v>12.34121940179812</v>
+        <v>12.34122035151799</v>
       </c>
       <c r="F408" t="n">
         <v>1221893</v>
@@ -8612,16 +8612,16 @@
         <v>44825</v>
       </c>
       <c r="B410" t="n">
-        <v>11.65607166290283</v>
+        <v>11.65607070922852</v>
       </c>
       <c r="C410" t="n">
-        <v>12.10998334747001</v>
+        <v>12.10998235665763</v>
       </c>
       <c r="D410" t="n">
-        <v>11.50191415999951</v>
+        <v>11.50191321893803</v>
       </c>
       <c r="E410" t="n">
-        <v>11.94726007292391</v>
+        <v>11.9472590954252</v>
       </c>
       <c r="F410" t="n">
         <v>3396829</v>
@@ -8672,16 +8672,16 @@
         <v>44830</v>
       </c>
       <c r="B413" t="n">
-        <v>11.45909118652344</v>
+        <v>11.45909214019775</v>
       </c>
       <c r="C413" t="n">
-        <v>11.844486541272</v>
+        <v>11.84448752702055</v>
       </c>
       <c r="D413" t="n">
-        <v>11.34775431092947</v>
+        <v>11.34775525533786</v>
       </c>
       <c r="E413" t="n">
-        <v>11.81879335270545</v>
+        <v>11.81879433631571</v>
       </c>
       <c r="F413" t="n">
         <v>3443068</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186389923096</v>
+        <v>11.56186485290527</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889314808853</v>
+        <v>11.69889411306563</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072583059598</v>
+        <v>11.21072675530685</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775507945355</v>
+        <v>11.34775601546721</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8732,16 +8732,16 @@
         <v>44833</v>
       </c>
       <c r="B416" t="n">
-        <v>11.61324977874756</v>
+        <v>11.61325073242188</v>
       </c>
       <c r="C416" t="n">
-        <v>11.66463533256029</v>
+        <v>11.66463629045436</v>
       </c>
       <c r="D416" t="n">
-        <v>11.29636821141672</v>
+        <v>11.29636913906888</v>
       </c>
       <c r="E416" t="n">
-        <v>11.45052734660464</v>
+        <v>11.45052828691627</v>
       </c>
       <c r="F416" t="n">
         <v>3327572</v>
@@ -8852,16 +8852,16 @@
         <v>44841</v>
       </c>
       <c r="B422" t="n">
-        <v>12.62384414672852</v>
+        <v>12.6238431930542</v>
       </c>
       <c r="C422" t="n">
-        <v>12.92359586075333</v>
+        <v>12.92359488443413</v>
       </c>
       <c r="D422" t="n">
-        <v>12.54676456912213</v>
+        <v>12.54676362127082</v>
       </c>
       <c r="E422" t="n">
-        <v>12.92359586075333</v>
+        <v>12.92359488443413</v>
       </c>
       <c r="F422" t="n">
         <v>1382517</v>
@@ -8892,16 +8892,16 @@
         <v>44845</v>
       </c>
       <c r="B424" t="n">
-        <v>12.7523078918457</v>
+        <v>12.75230884552002</v>
       </c>
       <c r="C424" t="n">
-        <v>12.80369427462625</v>
+        <v>12.80369523214346</v>
       </c>
       <c r="D424" t="n">
-        <v>12.53819988762117</v>
+        <v>12.53820082528354</v>
       </c>
       <c r="E424" t="n">
-        <v>12.72661470045543</v>
+        <v>12.7266156522083</v>
       </c>
       <c r="F424" t="n">
         <v>1848640</v>
@@ -8952,16 +8952,16 @@
         <v>44851</v>
       </c>
       <c r="B427" t="n">
-        <v>12.6495361328125</v>
+        <v>12.64953708648682</v>
       </c>
       <c r="C427" t="n">
-        <v>13.19765480841111</v>
+        <v>13.19765580340922</v>
       </c>
       <c r="D427" t="n">
-        <v>12.5810215045085</v>
+        <v>12.58102245301736</v>
       </c>
       <c r="E427" t="n">
-        <v>12.87220908709215</v>
+        <v>12.87221005755423</v>
       </c>
       <c r="F427" t="n">
         <v>1088124</v>
@@ -8992,16 +8992,16 @@
         <v>44853</v>
       </c>
       <c r="B429" t="n">
-        <v>12.95785236358643</v>
+        <v>12.95785140991211</v>
       </c>
       <c r="C429" t="n">
-        <v>13.02636781860678</v>
+        <v>13.02636685988985</v>
       </c>
       <c r="D429" t="n">
-        <v>12.71805115705691</v>
+        <v>12.71805022103153</v>
       </c>
       <c r="E429" t="n">
-        <v>12.80369485739484</v>
+        <v>12.80369391506624</v>
       </c>
       <c r="F429" t="n">
         <v>1282165</v>
@@ -9012,16 +9012,16 @@
         <v>44854</v>
       </c>
       <c r="B430" t="n">
-        <v>12.78656578063965</v>
+        <v>12.78656482696533</v>
       </c>
       <c r="C430" t="n">
-        <v>13.08631831937005</v>
+        <v>13.08631734333896</v>
       </c>
       <c r="D430" t="n">
-        <v>12.65810064249329</v>
+        <v>12.65809969840043</v>
       </c>
       <c r="E430" t="n">
-        <v>13.08631831937005</v>
+        <v>13.08631734333896</v>
       </c>
       <c r="F430" t="n">
         <v>2107193</v>
@@ -9032,16 +9032,16 @@
         <v>44855</v>
       </c>
       <c r="B431" t="n">
-        <v>13.08631801605225</v>
+        <v>13.08631706237793</v>
       </c>
       <c r="C431" t="n">
-        <v>13.26616953512184</v>
+        <v>13.26616856834072</v>
       </c>
       <c r="D431" t="n">
-        <v>12.58958572028859</v>
+        <v>12.58958480281398</v>
       </c>
       <c r="E431" t="n">
-        <v>12.74374404740777</v>
+        <v>12.74374311869877</v>
       </c>
       <c r="F431" t="n">
         <v>1434409</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805191040039</v>
+        <v>12.71805000305176</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775497837641</v>
+        <v>13.07775301708247</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235954090216</v>
+        <v>12.69235763740665</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87221025030677</v>
+        <v>12.87220831983874</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9092,16 +9092,16 @@
         <v>44860</v>
       </c>
       <c r="B434" t="n">
-        <v>12.29839897155762</v>
+        <v>12.2983980178833</v>
       </c>
       <c r="C434" t="n">
-        <v>13.0092393245347</v>
+        <v>13.00923831573856</v>
       </c>
       <c r="D434" t="n">
-        <v>12.17849877527738</v>
+        <v>12.17849783090068</v>
       </c>
       <c r="E434" t="n">
-        <v>12.61527976979239</v>
+        <v>12.61527879154568</v>
       </c>
       <c r="F434" t="n">
         <v>4556230</v>
@@ -9152,16 +9152,16 @@
         <v>44865</v>
       </c>
       <c r="B437" t="n">
-        <v>13.8057222366333</v>
+        <v>13.80572128295898</v>
       </c>
       <c r="C437" t="n">
-        <v>14.0712174500381</v>
+        <v>14.07121647802385</v>
       </c>
       <c r="D437" t="n">
-        <v>12.50394183492532</v>
+        <v>12.50394097117564</v>
       </c>
       <c r="E437" t="n">
-        <v>12.50394183492532</v>
+        <v>12.50394097117564</v>
       </c>
       <c r="F437" t="n">
         <v>7903691</v>
@@ -9172,16 +9172,16 @@
         <v>44866</v>
       </c>
       <c r="B438" t="n">
-        <v>13.61730670928955</v>
+        <v>13.61730575561523</v>
       </c>
       <c r="C438" t="n">
-        <v>14.01126705916312</v>
+        <v>14.01126607789819</v>
       </c>
       <c r="D438" t="n">
-        <v>13.53166383614674</v>
+        <v>13.53166288847033</v>
       </c>
       <c r="E438" t="n">
-        <v>13.70295123159901</v>
+        <v>13.70295027192667</v>
       </c>
       <c r="F438" t="n">
         <v>3366744</v>
@@ -9192,16 +9192,16 @@
         <v>44868</v>
       </c>
       <c r="B439" t="n">
-        <v>13.93418788909912</v>
+        <v>13.9341869354248</v>
       </c>
       <c r="C439" t="n">
-        <v>14.0455231260844</v>
+        <v>14.04552216479015</v>
       </c>
       <c r="D439" t="n">
-        <v>13.38606922964626</v>
+        <v>13.38606831348592</v>
       </c>
       <c r="E439" t="n">
-        <v>13.38606922964626</v>
+        <v>13.38606831348592</v>
       </c>
       <c r="F439" t="n">
         <v>2966749</v>
@@ -9212,16 +9212,16 @@
         <v>44869</v>
       </c>
       <c r="B440" t="n">
-        <v>14.01126575469971</v>
+        <v>14.01126766204834</v>
       </c>
       <c r="C440" t="n">
-        <v>14.29389001334168</v>
+        <v>14.29389195916385</v>
       </c>
       <c r="D440" t="n">
-        <v>13.80572106421007</v>
+        <v>13.80572294357798</v>
       </c>
       <c r="E440" t="n">
-        <v>14.13973087703701</v>
+        <v>14.13973280187356</v>
       </c>
       <c r="F440" t="n">
         <v>3663661</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.4031982421875</v>
+        <v>13.40319919586182</v>
       </c>
       <c r="C441" t="n">
-        <v>14.03695980853268</v>
+        <v>14.03696080730087</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037762903356</v>
+        <v>13.36037857966108</v>
       </c>
       <c r="E441" t="n">
-        <v>13.93418868779654</v>
+        <v>13.93418967925229</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9292,16 +9292,16 @@
         <v>44875</v>
       </c>
       <c r="B444" t="n">
-        <v>12.24701118469238</v>
+        <v>12.2470121383667</v>
       </c>
       <c r="C444" t="n">
-        <v>12.83795040949141</v>
+        <v>12.83795140918214</v>
       </c>
       <c r="D444" t="n">
-        <v>11.6732002028586</v>
+        <v>11.67320111185027</v>
       </c>
       <c r="E444" t="n">
-        <v>12.83795040949141</v>
+        <v>12.83795140918214</v>
       </c>
       <c r="F444" t="n">
         <v>10581398</v>
@@ -9352,16 +9352,16 @@
         <v>44881</v>
       </c>
       <c r="B447" t="n">
-        <v>11.26211166381836</v>
+        <v>11.26211261749268</v>
       </c>
       <c r="C447" t="n">
-        <v>12.15280256268413</v>
+        <v>12.15280359178205</v>
       </c>
       <c r="D447" t="n">
-        <v>11.15933973217037</v>
+        <v>11.15934067714197</v>
       </c>
       <c r="E447" t="n">
-        <v>12.06715969860243</v>
+        <v>12.06716072044812</v>
       </c>
       <c r="F447" t="n">
         <v>3929079</v>
@@ -9392,16 +9392,16 @@
         <v>44883</v>
       </c>
       <c r="B449" t="n">
-        <v>10.92810153961182</v>
+        <v>10.92810344696045</v>
       </c>
       <c r="C449" t="n">
-        <v>11.38201233430139</v>
+        <v>11.38201432087386</v>
       </c>
       <c r="D449" t="n">
-        <v>10.91953741836764</v>
+        <v>10.91953932422152</v>
       </c>
       <c r="E449" t="n">
-        <v>11.13364539697134</v>
+        <v>11.1336473401948</v>
       </c>
       <c r="F449" t="n">
         <v>5719164</v>
@@ -9412,16 +9412,16 @@
         <v>44886</v>
       </c>
       <c r="B450" t="n">
-        <v>11.25354766845703</v>
+        <v>11.25354671478271</v>
       </c>
       <c r="C450" t="n">
-        <v>11.33062724214222</v>
+        <v>11.33062628193585</v>
       </c>
       <c r="D450" t="n">
-        <v>10.80820259369247</v>
+        <v>10.80820167775862</v>
       </c>
       <c r="E450" t="n">
-        <v>10.98805328312464</v>
+        <v>10.98805235194947</v>
       </c>
       <c r="F450" t="n">
         <v>4991964</v>
@@ -9432,16 +9432,16 @@
         <v>44887</v>
       </c>
       <c r="B451" t="n">
-        <v>10.98805332183838</v>
+        <v>10.98805236816406</v>
       </c>
       <c r="C451" t="n">
-        <v>11.33919140430814</v>
+        <v>11.33919042015788</v>
       </c>
       <c r="D451" t="n">
-        <v>10.89384550339121</v>
+        <v>10.89384455789337</v>
       </c>
       <c r="E451" t="n">
-        <v>11.2792408994251</v>
+        <v>11.27923992047805</v>
       </c>
       <c r="F451" t="n">
         <v>2547672</v>
@@ -9512,16 +9512,16 @@
         <v>44893</v>
       </c>
       <c r="B455" t="n">
-        <v>10.96236038208008</v>
+        <v>10.96235942840576</v>
       </c>
       <c r="C455" t="n">
-        <v>11.18503333764837</v>
+        <v>11.18503236460255</v>
       </c>
       <c r="D455" t="n">
-        <v>10.84245936956254</v>
+        <v>10.84245842631905</v>
       </c>
       <c r="E455" t="n">
-        <v>10.95379625963835</v>
+        <v>10.95379530670907</v>
       </c>
       <c r="F455" t="n">
         <v>2642270</v>
@@ -9572,16 +9572,16 @@
         <v>44896</v>
       </c>
       <c r="B458" t="n">
-        <v>11.15077590942383</v>
+        <v>11.15077686309814</v>
       </c>
       <c r="C458" t="n">
-        <v>11.33919154871773</v>
+        <v>11.33919251850636</v>
       </c>
       <c r="D458" t="n">
-        <v>10.9709243924842</v>
+        <v>10.97092533077665</v>
       </c>
       <c r="E458" t="n">
-        <v>11.32206330400918</v>
+        <v>11.32206427233292</v>
       </c>
       <c r="F458" t="n">
         <v>2224001</v>
@@ -9612,16 +9612,16 @@
         <v>44900</v>
       </c>
       <c r="B460" t="n">
-        <v>10.65404415130615</v>
+        <v>10.65404319763184</v>
       </c>
       <c r="C460" t="n">
-        <v>11.26211248883013</v>
+        <v>11.26211148072586</v>
       </c>
       <c r="D460" t="n">
-        <v>10.56839963178404</v>
+        <v>10.56839868577602</v>
       </c>
       <c r="E460" t="n">
-        <v>11.26211248883013</v>
+        <v>11.26211148072586</v>
       </c>
       <c r="F460" t="n">
         <v>2438739</v>
@@ -9652,16 +9652,16 @@
         <v>44902</v>
       </c>
       <c r="B462" t="n">
-        <v>10.36285781860352</v>
+        <v>10.36285591125488</v>
       </c>
       <c r="C462" t="n">
-        <v>10.91097489316318</v>
+        <v>10.91097288493018</v>
       </c>
       <c r="D462" t="n">
-        <v>10.24295679625189</v>
+        <v>10.24295491097179</v>
       </c>
       <c r="E462" t="n">
-        <v>10.59409491557922</v>
+        <v>10.59409296566996</v>
       </c>
       <c r="F462" t="n">
         <v>7006882</v>
@@ -9692,16 +9692,16 @@
         <v>44904</v>
       </c>
       <c r="B464" t="n">
-        <v>9.69483757019043</v>
+        <v>9.694836616516113</v>
       </c>
       <c r="C464" t="n">
-        <v>10.02884742592286</v>
+        <v>10.02884643939223</v>
       </c>
       <c r="D464" t="n">
-        <v>9.463600485196199</v>
+        <v>9.463599554268511</v>
       </c>
       <c r="E464" t="n">
-        <v>9.848995901714368</v>
+        <v>9.848994932875605</v>
       </c>
       <c r="F464" t="n">
         <v>4631040</v>
@@ -9712,16 +9712,16 @@
         <v>44907</v>
       </c>
       <c r="B465" t="n">
-        <v>9.506421089172363</v>
+        <v>9.50642204284668</v>
       </c>
       <c r="C465" t="n">
-        <v>10.02884567607701</v>
+        <v>10.02884668216042</v>
       </c>
       <c r="D465" t="n">
-        <v>9.420777403361539</v>
+        <v>9.42077834844417</v>
       </c>
       <c r="E465" t="n">
-        <v>9.57493570798774</v>
+        <v>9.57493666853537</v>
       </c>
       <c r="F465" t="n">
         <v>6343387</v>
@@ -9832,16 +9832,16 @@
         <v>44915</v>
       </c>
       <c r="B471" t="n">
-        <v>10.33716297149658</v>
+        <v>10.33716106414795</v>
       </c>
       <c r="C471" t="n">
-        <v>10.65404457284976</v>
+        <v>10.65404260703212</v>
       </c>
       <c r="D471" t="n">
-        <v>9.857560569696266</v>
+        <v>9.85755875084087</v>
       </c>
       <c r="E471" t="n">
-        <v>9.926074373941555</v>
+        <v>9.926072542444418</v>
       </c>
       <c r="F471" t="n">
         <v>4483944</v>
@@ -9872,16 +9872,16 @@
         <v>44917</v>
       </c>
       <c r="B473" t="n">
-        <v>10.53414344787598</v>
+        <v>10.53414249420166</v>
       </c>
       <c r="C473" t="n">
-        <v>10.60265807597463</v>
+        <v>10.60265711609756</v>
       </c>
       <c r="D473" t="n">
-        <v>10.29434224953069</v>
+        <v>10.29434131756599</v>
       </c>
       <c r="E473" t="n">
-        <v>10.4399356280945</v>
+        <v>10.43993468294898</v>
       </c>
       <c r="F473" t="n">
         <v>2407341</v>
@@ -9912,16 +9912,16 @@
         <v>44921</v>
       </c>
       <c r="B475" t="n">
-        <v>10.6626091003418</v>
+        <v>10.66260814666748</v>
       </c>
       <c r="C475" t="n">
-        <v>10.87671794200195</v>
+        <v>10.87671696917752</v>
       </c>
       <c r="D475" t="n">
-        <v>10.5769645741777</v>
+        <v>10.57696362816352</v>
       </c>
       <c r="E475" t="n">
-        <v>10.82533155613684</v>
+        <v>10.82533058790846</v>
       </c>
       <c r="F475" t="n">
         <v>1667319</v>
@@ -10052,16 +10052,16 @@
         <v>44931</v>
       </c>
       <c r="B482" t="n">
-        <v>10.05935478210449</v>
+        <v>10.05935668945312</v>
       </c>
       <c r="C482" t="n">
-        <v>10.33926675914544</v>
+        <v>10.33926871956802</v>
       </c>
       <c r="D482" t="n">
-        <v>9.779442805063548</v>
+        <v>9.779444659338226</v>
       </c>
       <c r="E482" t="n">
-        <v>9.796936882531035</v>
+        <v>9.796938740122757</v>
       </c>
       <c r="F482" t="n">
         <v>3524036</v>
@@ -10072,16 +10072,16 @@
         <v>44932</v>
       </c>
       <c r="B483" t="n">
-        <v>10.4354887008667</v>
+        <v>10.43548774719238</v>
       </c>
       <c r="C483" t="n">
-        <v>10.49671882092729</v>
+        <v>10.4967178616573</v>
       </c>
       <c r="D483" t="n">
-        <v>10.03311392635628</v>
+        <v>10.03311300945403</v>
       </c>
       <c r="E483" t="n">
-        <v>10.05935588763667</v>
+        <v>10.05935496833623</v>
       </c>
       <c r="F483" t="n">
         <v>2102448</v>
@@ -10132,16 +10132,16 @@
         <v>44937</v>
       </c>
       <c r="B486" t="n">
-        <v>11.55513858795166</v>
+        <v>11.55513763427734</v>
       </c>
       <c r="C486" t="n">
-        <v>11.63386447296113</v>
+        <v>11.63386351278937</v>
       </c>
       <c r="D486" t="n">
-        <v>11.09153284430542</v>
+        <v>11.09153192889364</v>
       </c>
       <c r="E486" t="n">
-        <v>11.10902860834563</v>
+        <v>11.10902769148988</v>
       </c>
       <c r="F486" t="n">
         <v>4034277</v>
@@ -10192,16 +10192,16 @@
         <v>44942</v>
       </c>
       <c r="B489" t="n">
-        <v>10.80287265777588</v>
+        <v>10.8028736114502</v>
       </c>
       <c r="C489" t="n">
-        <v>11.30146738941439</v>
+        <v>11.3014683871045</v>
       </c>
       <c r="D489" t="n">
-        <v>10.69790649832965</v>
+        <v>10.69790744273759</v>
       </c>
       <c r="E489" t="n">
-        <v>11.25773134927926</v>
+        <v>11.25773234310836</v>
       </c>
       <c r="F489" t="n">
         <v>2251058</v>
@@ -10212,16 +10212,16 @@
         <v>44943</v>
       </c>
       <c r="B490" t="n">
-        <v>11.00406074523926</v>
+        <v>11.00405979156494</v>
       </c>
       <c r="C490" t="n">
-        <v>11.10902859176186</v>
+        <v>11.10902762899043</v>
       </c>
       <c r="D490" t="n">
-        <v>10.7503906953303</v>
+        <v>10.75038976364046</v>
       </c>
       <c r="E490" t="n">
-        <v>10.8466098176506</v>
+        <v>10.84660887762188</v>
       </c>
       <c r="F490" t="n">
         <v>2581089</v>
@@ -10252,16 +10252,16 @@
         <v>44945</v>
       </c>
       <c r="B492" t="n">
-        <v>11.93127059936523</v>
+        <v>11.93127155303955</v>
       </c>
       <c r="C492" t="n">
-        <v>12.30740255052876</v>
+        <v>12.30740353426755</v>
       </c>
       <c r="D492" t="n">
-        <v>11.33645677201188</v>
+        <v>11.33645767814233</v>
       </c>
       <c r="E492" t="n">
-        <v>11.49390684698556</v>
+        <v>11.49390776570111</v>
       </c>
       <c r="F492" t="n">
         <v>5394988</v>
@@ -10272,16 +10272,16 @@
         <v>44946</v>
       </c>
       <c r="B493" t="n">
-        <v>11.86129283905029</v>
+        <v>11.86129379272461</v>
       </c>
       <c r="C493" t="n">
-        <v>12.01874291718245</v>
+        <v>12.0187438835161</v>
       </c>
       <c r="D493" t="n">
-        <v>11.51140199856674</v>
+        <v>11.51140292410906</v>
       </c>
       <c r="E493" t="n">
-        <v>11.92252379929955</v>
+        <v>11.92252475789698</v>
       </c>
       <c r="F493" t="n">
         <v>2495174</v>
@@ -10312,16 +10312,16 @@
         <v>44950</v>
       </c>
       <c r="B495" t="n">
-        <v>12.12371063232422</v>
+        <v>12.1237096786499</v>
       </c>
       <c r="C495" t="n">
-        <v>12.25492044217159</v>
+        <v>12.25491947817606</v>
       </c>
       <c r="D495" t="n">
-        <v>11.5551387198968</v>
+        <v>11.55513781094744</v>
       </c>
       <c r="E495" t="n">
-        <v>11.67760064762417</v>
+        <v>11.67759972904172</v>
       </c>
       <c r="F495" t="n">
         <v>5075153</v>
@@ -10352,16 +10352,16 @@
         <v>44952</v>
       </c>
       <c r="B497" t="n">
-        <v>12.42986488342285</v>
+        <v>12.42986392974854</v>
       </c>
       <c r="C497" t="n">
-        <v>12.56982088460175</v>
+        <v>12.56981992018939</v>
       </c>
       <c r="D497" t="n">
-        <v>12.18494103916456</v>
+        <v>12.18494010428189</v>
       </c>
       <c r="E497" t="n">
-        <v>12.27241396099898</v>
+        <v>12.272413019405</v>
       </c>
       <c r="F497" t="n">
         <v>2815211</v>
@@ -10372,16 +10372,16 @@
         <v>44953</v>
       </c>
       <c r="B498" t="n">
-        <v>12.43861293792725</v>
+        <v>12.43861389160156</v>
       </c>
       <c r="C498" t="n">
-        <v>12.67478890374615</v>
+        <v>12.67478987552819</v>
       </c>
       <c r="D498" t="n">
-        <v>12.25492005218186</v>
+        <v>12.25492099177236</v>
       </c>
       <c r="E498" t="n">
-        <v>12.41237013459764</v>
+        <v>12.41237108625991</v>
       </c>
       <c r="F498" t="n">
         <v>1981500</v>
@@ -10392,16 +10392,16 @@
         <v>44956</v>
       </c>
       <c r="B499" t="n">
-        <v>12.48234844207764</v>
+        <v>12.48234748840332</v>
       </c>
       <c r="C499" t="n">
-        <v>12.81474522093406</v>
+        <v>12.81474424186402</v>
       </c>
       <c r="D499" t="n">
-        <v>12.39487635907959</v>
+        <v>12.3948754120883</v>
       </c>
       <c r="E499" t="n">
-        <v>12.46485436235613</v>
+        <v>12.46485341001839</v>
       </c>
       <c r="F499" t="n">
         <v>2566955</v>
@@ -10412,16 +10412,16 @@
         <v>44957</v>
       </c>
       <c r="B500" t="n">
-        <v>12.78850269317627</v>
+        <v>12.78850364685059</v>
       </c>
       <c r="C500" t="n">
-        <v>13.03342653599981</v>
+        <v>13.03342750793878</v>
       </c>
       <c r="D500" t="n">
-        <v>12.48234788964684</v>
+        <v>12.48234882049034</v>
       </c>
       <c r="E500" t="n">
-        <v>12.49109577131569</v>
+        <v>12.49109670281154</v>
       </c>
       <c r="F500" t="n">
         <v>4284855</v>
@@ -10492,16 +10492,16 @@
         <v>44963</v>
       </c>
       <c r="B504" t="n">
-        <v>12.75351333618164</v>
+        <v>12.75351428985596</v>
       </c>
       <c r="C504" t="n">
-        <v>12.83223921582688</v>
+        <v>12.83224017538812</v>
       </c>
       <c r="D504" t="n">
-        <v>12.33364450465924</v>
+        <v>12.33364542693687</v>
       </c>
       <c r="E504" t="n">
-        <v>12.53483146009399</v>
+        <v>12.53483239741585</v>
       </c>
       <c r="F504" t="n">
         <v>1342942</v>
@@ -10512,16 +10512,16 @@
         <v>44964</v>
       </c>
       <c r="B505" t="n">
-        <v>12.76226043701172</v>
+        <v>12.76226139068604</v>
       </c>
       <c r="C505" t="n">
-        <v>12.93720543340915</v>
+        <v>12.93720640015643</v>
       </c>
       <c r="D505" t="n">
-        <v>12.52608448132639</v>
+        <v>12.52608541735219</v>
       </c>
       <c r="E505" t="n">
-        <v>12.8584803955791</v>
+        <v>12.85848135644357</v>
       </c>
       <c r="F505" t="n">
         <v>2203204</v>
@@ -10532,16 +10532,16 @@
         <v>44965</v>
       </c>
       <c r="B506" t="n">
-        <v>12.77100849151611</v>
+        <v>12.7710075378418</v>
       </c>
       <c r="C506" t="n">
-        <v>12.98094334607703</v>
+        <v>12.98094237672584</v>
       </c>
       <c r="D506" t="n">
-        <v>12.56982151911688</v>
+        <v>12.56982058046619</v>
       </c>
       <c r="E506" t="n">
-        <v>12.8584814177661</v>
+        <v>12.85848045755975</v>
       </c>
       <c r="F506" t="n">
         <v>1737889</v>
@@ -10572,16 +10572,16 @@
         <v>44967</v>
       </c>
       <c r="B508" t="n">
-        <v>12.4036226272583</v>
+        <v>12.40362358093262</v>
       </c>
       <c r="C508" t="n">
-        <v>12.47360062618121</v>
+        <v>12.47360158523591</v>
       </c>
       <c r="D508" t="n">
-        <v>11.97500675220909</v>
+        <v>11.97500767292852</v>
       </c>
       <c r="E508" t="n">
-        <v>12.03623771181543</v>
+        <v>12.03623863724271</v>
       </c>
       <c r="F508" t="n">
         <v>3559170</v>
@@ -10592,16 +10592,16 @@
         <v>44970</v>
       </c>
       <c r="B509" t="n">
-        <v>12.52608489990234</v>
+        <v>12.52608585357666</v>
       </c>
       <c r="C509" t="n">
-        <v>12.77100790304318</v>
+        <v>12.77100887536473</v>
       </c>
       <c r="D509" t="n">
-        <v>12.35113905546367</v>
+        <v>12.35113999581847</v>
       </c>
       <c r="E509" t="n">
-        <v>12.38612889810758</v>
+        <v>12.38612984112634</v>
       </c>
       <c r="F509" t="n">
         <v>2916169</v>
@@ -10632,16 +10632,16 @@
         <v>44972</v>
       </c>
       <c r="B511" t="n">
-        <v>12.75351333618164</v>
+        <v>12.75351428985596</v>
       </c>
       <c r="C511" t="n">
-        <v>12.94595241019235</v>
+        <v>12.94595337825676</v>
       </c>
       <c r="D511" t="n">
-        <v>11.91377567313685</v>
+        <v>11.91377656401778</v>
       </c>
       <c r="E511" t="n">
-        <v>12.24617158578515</v>
+        <v>12.24617250152178</v>
       </c>
       <c r="F511" t="n">
         <v>3838217</v>
@@ -10652,16 +10652,16 @@
         <v>44973</v>
       </c>
       <c r="B512" t="n">
-        <v>12.86722755432129</v>
+        <v>12.86722850799561</v>
       </c>
       <c r="C512" t="n">
-        <v>12.98968947403414</v>
+        <v>12.98969043678491</v>
       </c>
       <c r="D512" t="n">
-        <v>12.6135575177385</v>
+        <v>12.61355845261168</v>
       </c>
       <c r="E512" t="n">
-        <v>12.64854567514766</v>
+        <v>12.64854661261404</v>
       </c>
       <c r="F512" t="n">
         <v>1907195</v>
@@ -10672,16 +10672,16 @@
         <v>44974</v>
       </c>
       <c r="B513" t="n">
-        <v>12.78850269317627</v>
+        <v>12.78850364685059</v>
       </c>
       <c r="C513" t="n">
-        <v>12.85848069335579</v>
+        <v>12.85848165224856</v>
       </c>
       <c r="D513" t="n">
-        <v>12.63105177167474</v>
+        <v>12.6310527136075</v>
       </c>
       <c r="E513" t="n">
-        <v>12.84098661440852</v>
+        <v>12.84098757199671</v>
       </c>
       <c r="F513" t="n">
         <v>1180399</v>
@@ -10692,16 +10692,16 @@
         <v>44979</v>
       </c>
       <c r="B514" t="n">
-        <v>12.63979911804199</v>
+        <v>12.63979816436768</v>
       </c>
       <c r="C514" t="n">
-        <v>12.70977711992058</v>
+        <v>12.70977616096641</v>
       </c>
       <c r="D514" t="n">
-        <v>12.33364514927437</v>
+        <v>12.33364421869941</v>
       </c>
       <c r="E514" t="n">
-        <v>12.70103008023456</v>
+        <v>12.70102912194036</v>
       </c>
       <c r="F514" t="n">
         <v>1228758</v>
@@ -10712,16 +10712,16 @@
         <v>44980</v>
       </c>
       <c r="B515" t="n">
-        <v>12.28990840911865</v>
+        <v>12.28990936279297</v>
       </c>
       <c r="C515" t="n">
-        <v>12.77100735519902</v>
+        <v>12.77100834620573</v>
       </c>
       <c r="D515" t="n">
-        <v>12.24617152878757</v>
+        <v>12.24617247906799</v>
       </c>
       <c r="E515" t="n">
-        <v>12.5785674398888</v>
+        <v>12.57856841596253</v>
       </c>
       <c r="F515" t="n">
         <v>1820271</v>
@@ -10752,16 +10752,16 @@
         <v>44984</v>
       </c>
       <c r="B517" t="n">
-        <v>11.64261054992676</v>
+        <v>11.64261150360107</v>
       </c>
       <c r="C517" t="n">
-        <v>11.87003946193115</v>
+        <v>11.87004043423472</v>
       </c>
       <c r="D517" t="n">
-        <v>11.51140159462404</v>
+        <v>11.51140253755071</v>
       </c>
       <c r="E517" t="n">
-        <v>11.77381950522948</v>
+        <v>11.77382046965144</v>
       </c>
       <c r="F517" t="n">
         <v>3613283</v>
@@ -10792,16 +10792,16 @@
         <v>44986</v>
       </c>
       <c r="B519" t="n">
-        <v>11.74757766723633</v>
+        <v>11.74757862091064</v>
       </c>
       <c r="C519" t="n">
-        <v>11.78256666619927</v>
+        <v>11.78256762271401</v>
       </c>
       <c r="D519" t="n">
-        <v>11.3976876776069</v>
+        <v>11.39768860287697</v>
       </c>
       <c r="E519" t="n">
-        <v>11.6163687105765</v>
+        <v>11.61636965359921</v>
       </c>
       <c r="F519" t="n">
         <v>4662539</v>
@@ -10832,16 +10832,16 @@
         <v>44988</v>
       </c>
       <c r="B521" t="n">
-        <v>11.6776008605957</v>
+        <v>11.67759990692139</v>
       </c>
       <c r="C521" t="n">
-        <v>11.98375484330241</v>
+        <v>11.98375386462542</v>
       </c>
       <c r="D521" t="n">
-        <v>11.60762201333577</v>
+        <v>11.60762106537642</v>
       </c>
       <c r="E521" t="n">
-        <v>11.80006279055649</v>
+        <v>11.80006182688108</v>
       </c>
       <c r="F521" t="n">
         <v>1946973</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.26366710662842</v>
+        <v>12.26366806030273</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738199094953</v>
+        <v>12.37738295346679</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87004021572346</v>
+        <v>11.87004113878769</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12371026114126</v>
+        <v>12.12371120393195</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10892,16 +10892,16 @@
         <v>44993</v>
       </c>
       <c r="B524" t="n">
-        <v>12.6835355758667</v>
+        <v>12.68353652954102</v>
       </c>
       <c r="C524" t="n">
-        <v>12.75351357540048</v>
+        <v>12.75351453433644</v>
       </c>
       <c r="D524" t="n">
-        <v>12.17619381595395</v>
+        <v>12.17619473148127</v>
       </c>
       <c r="E524" t="n">
-        <v>12.28990869684275</v>
+        <v>12.28990962092029</v>
       </c>
       <c r="F524" t="n">
         <v>2396134</v>
@@ -10912,16 +10912,16 @@
         <v>44994</v>
       </c>
       <c r="B525" t="n">
-        <v>12.70977687835693</v>
+        <v>12.70977783203125</v>
       </c>
       <c r="C525" t="n">
-        <v>12.88472272192359</v>
+        <v>12.88472368872491</v>
       </c>
       <c r="D525" t="n">
-        <v>12.55232679822025</v>
+        <v>12.55232774008035</v>
       </c>
       <c r="E525" t="n">
-        <v>12.71852476007192</v>
+        <v>12.71852571440263</v>
       </c>
       <c r="F525" t="n">
         <v>3354932</v>
@@ -10932,16 +10932,16 @@
         <v>44995</v>
       </c>
       <c r="B526" t="n">
-        <v>12.5960636138916</v>
+        <v>12.59606266021729</v>
       </c>
       <c r="C526" t="n">
-        <v>12.78850354835147</v>
+        <v>12.78850258010713</v>
       </c>
       <c r="D526" t="n">
-        <v>12.31615159445562</v>
+        <v>12.31615066197402</v>
       </c>
       <c r="E526" t="n">
-        <v>12.64854669643821</v>
+        <v>12.6485457387903</v>
       </c>
       <c r="F526" t="n">
         <v>1798565</v>
@@ -11012,16 +11012,16 @@
         <v>45001</v>
       </c>
       <c r="B530" t="n">
-        <v>12.44735908508301</v>
+        <v>12.44736099243164</v>
       </c>
       <c r="C530" t="n">
-        <v>12.63105111546223</v>
+        <v>12.63105305095858</v>
       </c>
       <c r="D530" t="n">
-        <v>12.28990817176142</v>
+        <v>12.28991005498334</v>
       </c>
       <c r="E530" t="n">
-        <v>12.35113828709104</v>
+        <v>12.35114017969545</v>
       </c>
       <c r="F530" t="n">
         <v>3275478</v>
@@ -11032,16 +11032,16 @@
         <v>45002</v>
       </c>
       <c r="B531" t="n">
-        <v>11.73008346557617</v>
+        <v>11.73008251190186</v>
       </c>
       <c r="C531" t="n">
-        <v>12.42986517211394</v>
+        <v>12.42986416154627</v>
       </c>
       <c r="D531" t="n">
-        <v>11.52889649866001</v>
+        <v>11.52889556134252</v>
       </c>
       <c r="E531" t="n">
-        <v>12.26366720630515</v>
+        <v>12.26366620924963</v>
       </c>
       <c r="F531" t="n">
         <v>9035530</v>
@@ -11052,16 +11052,16 @@
         <v>45005</v>
       </c>
       <c r="B532" t="n">
-        <v>11.36269855499268</v>
+        <v>11.36269760131836</v>
       </c>
       <c r="C532" t="n">
-        <v>11.90502849431124</v>
+        <v>11.90502749511903</v>
       </c>
       <c r="D532" t="n">
-        <v>11.17025862742956</v>
+        <v>11.17025768990678</v>
       </c>
       <c r="E532" t="n">
-        <v>11.73008348843351</v>
+        <v>11.73008250392448</v>
       </c>
       <c r="F532" t="n">
         <v>5506849</v>
@@ -11092,16 +11092,16 @@
         <v>45007</v>
       </c>
       <c r="B534" t="n">
-        <v>11.49390697479248</v>
+        <v>11.49390602111816</v>
       </c>
       <c r="C534" t="n">
-        <v>11.8437978121478</v>
+        <v>11.84379682944229</v>
       </c>
       <c r="D534" t="n">
-        <v>11.266478899036</v>
+        <v>11.26647796423188</v>
       </c>
       <c r="E534" t="n">
-        <v>11.266478899036</v>
+        <v>11.26647796423188</v>
       </c>
       <c r="F534" t="n">
         <v>2476497</v>
@@ -11132,16 +11132,16 @@
         <v>45009</v>
       </c>
       <c r="B536" t="n">
-        <v>11.12652111053467</v>
+        <v>11.12652206420898</v>
       </c>
       <c r="C536" t="n">
-        <v>11.23148810013704</v>
+        <v>11.23148906280827</v>
       </c>
       <c r="D536" t="n">
-        <v>10.68041035198067</v>
+        <v>10.68041126741802</v>
       </c>
       <c r="E536" t="n">
-        <v>10.68915823276055</v>
+        <v>10.6891591489477</v>
       </c>
       <c r="F536" t="n">
         <v>2554134</v>
@@ -11152,16 +11152,16 @@
         <v>45012</v>
       </c>
       <c r="B537" t="n">
-        <v>11.36269855499268</v>
+        <v>11.36269760131836</v>
       </c>
       <c r="C537" t="n">
-        <v>11.52889652112532</v>
+        <v>11.52889555350197</v>
       </c>
       <c r="D537" t="n">
-        <v>11.12652258650894</v>
+        <v>11.12652165265694</v>
       </c>
       <c r="E537" t="n">
-        <v>11.18775354911495</v>
+        <v>11.18775261012382</v>
       </c>
       <c r="F537" t="n">
         <v>2536971</v>
@@ -11172,16 +11172,16 @@
         <v>45013</v>
       </c>
       <c r="B538" t="n">
-        <v>11.56388664245605</v>
+        <v>11.56388759613037</v>
       </c>
       <c r="C538" t="n">
-        <v>11.77382065455549</v>
+        <v>11.77382162554307</v>
       </c>
       <c r="D538" t="n">
-        <v>11.31021490399421</v>
+        <v>11.3102158367482</v>
       </c>
       <c r="E538" t="n">
-        <v>11.31021490399421</v>
+        <v>11.3102158367482</v>
       </c>
       <c r="F538" t="n">
         <v>2291643</v>
@@ -11192,16 +11192,16 @@
         <v>45014</v>
       </c>
       <c r="B539" t="n">
-        <v>11.72133541107178</v>
+        <v>11.72133636474609</v>
       </c>
       <c r="C539" t="n">
-        <v>11.76507144812072</v>
+        <v>11.7650724053535</v>
       </c>
       <c r="D539" t="n">
-        <v>11.36269754912399</v>
+        <v>11.36269847361872</v>
       </c>
       <c r="E539" t="n">
-        <v>11.6076205356713</v>
+        <v>11.60762148009351</v>
       </c>
       <c r="F539" t="n">
         <v>3319697</v>
@@ -11212,16 +11212,16 @@
         <v>45015</v>
       </c>
       <c r="B540" t="n">
-        <v>12.11496257781982</v>
+        <v>12.11496353149414</v>
       </c>
       <c r="C540" t="n">
-        <v>12.28116053344774</v>
+        <v>12.28116150020495</v>
       </c>
       <c r="D540" t="n">
-        <v>11.71258866863594</v>
+        <v>11.7125895906359</v>
       </c>
       <c r="E540" t="n">
-        <v>11.72133570782815</v>
+        <v>11.72133663051666</v>
       </c>
       <c r="F540" t="n">
         <v>2232381</v>
@@ -11232,16 +11232,16 @@
         <v>45016</v>
       </c>
       <c r="B541" t="n">
-        <v>11.6776008605957</v>
+        <v>11.67759990692139</v>
       </c>
       <c r="C541" t="n">
-        <v>12.14995365807506</v>
+        <v>12.14995266582512</v>
       </c>
       <c r="D541" t="n">
-        <v>11.6601059382319</v>
+        <v>11.66010498598634</v>
       </c>
       <c r="E541" t="n">
-        <v>12.00999680575047</v>
+        <v>12.00999582493039</v>
       </c>
       <c r="F541" t="n">
         <v>2337175</v>
@@ -11292,16 +11292,16 @@
         <v>45021</v>
       </c>
       <c r="B544" t="n">
-        <v>10.67166519165039</v>
+        <v>10.67166423797607</v>
       </c>
       <c r="C544" t="n">
-        <v>11.35395200744364</v>
+        <v>11.3539509927967</v>
       </c>
       <c r="D544" t="n">
-        <v>10.58419310601722</v>
+        <v>10.58419216015985</v>
       </c>
       <c r="E544" t="n">
-        <v>11.17900699398201</v>
+        <v>11.17900599496905</v>
       </c>
       <c r="F544" t="n">
         <v>4730079</v>
@@ -11312,16 +11312,16 @@
         <v>45022</v>
       </c>
       <c r="B545" t="n">
-        <v>10.80287265777588</v>
+        <v>10.8028736114502</v>
       </c>
       <c r="C545" t="n">
-        <v>11.10902830750268</v>
+        <v>11.10902928820433</v>
       </c>
       <c r="D545" t="n">
-        <v>10.4617305340876</v>
+        <v>10.46173145764599</v>
       </c>
       <c r="E545" t="n">
-        <v>10.71540057750562</v>
+        <v>10.71540152345793</v>
       </c>
       <c r="F545" t="n">
         <v>8557394</v>
@@ -11332,16 +11332,16 @@
         <v>45026</v>
       </c>
       <c r="B546" t="n">
-        <v>10.89909267425537</v>
+        <v>10.89909362792969</v>
       </c>
       <c r="C546" t="n">
-        <v>11.14401566038277</v>
+        <v>11.14401663548793</v>
       </c>
       <c r="D546" t="n">
-        <v>10.64542180697705</v>
+        <v>10.64542273845509</v>
       </c>
       <c r="E546" t="n">
-        <v>10.71539980301345</v>
+        <v>10.71540074061458</v>
       </c>
       <c r="F546" t="n">
         <v>4871319</v>
@@ -11372,16 +11372,16 @@
         <v>45028</v>
       </c>
       <c r="B548" t="n">
-        <v>12.11496257781982</v>
+        <v>12.11496353149414</v>
       </c>
       <c r="C548" t="n">
-        <v>12.33364445299137</v>
+        <v>12.33364542388005</v>
       </c>
       <c r="D548" t="n">
-        <v>11.80880862633581</v>
+        <v>11.80880955591008</v>
       </c>
       <c r="E548" t="n">
-        <v>11.96625954277151</v>
+        <v>11.96626048474012</v>
       </c>
       <c r="F548" t="n">
         <v>6602445</v>
@@ -11412,16 +11412,16 @@
         <v>45030</v>
       </c>
       <c r="B550" t="n">
-        <v>12.52608489990234</v>
+        <v>12.52608585357666</v>
       </c>
       <c r="C550" t="n">
-        <v>12.72727186303112</v>
+        <v>12.72727283202282</v>
       </c>
       <c r="D550" t="n">
-        <v>12.22867797499086</v>
+        <v>12.22867890602208</v>
       </c>
       <c r="E550" t="n">
-        <v>12.42111705636105</v>
+        <v>12.42111800204363</v>
       </c>
       <c r="F550" t="n">
         <v>2806225</v>
@@ -11572,16 +11572,16 @@
         <v>45043</v>
       </c>
       <c r="B558" t="n">
-        <v>10.78537750244141</v>
+        <v>10.78537845611572</v>
       </c>
       <c r="C558" t="n">
-        <v>11.5114010862918</v>
+        <v>11.51140210416322</v>
       </c>
       <c r="D558" t="n">
-        <v>10.56669563919525</v>
+        <v>10.56669657353309</v>
       </c>
       <c r="E558" t="n">
-        <v>11.37144425587279</v>
+        <v>11.37144526136882</v>
       </c>
       <c r="F558" t="n">
         <v>8945577</v>
@@ -11592,16 +11592,16 @@
         <v>45044</v>
       </c>
       <c r="B559" t="n">
-        <v>10.68916034698486</v>
+        <v>10.68915939331055</v>
       </c>
       <c r="C559" t="n">
-        <v>10.86410536425811</v>
+        <v>10.86410439497541</v>
       </c>
       <c r="D559" t="n">
-        <v>10.36551143338288</v>
+        <v>10.36551050858414</v>
       </c>
       <c r="E559" t="n">
-        <v>10.8378634011183</v>
+        <v>10.83786243417687</v>
       </c>
       <c r="F559" t="n">
         <v>8236247</v>
@@ -11632,16 +11632,16 @@
         <v>45049</v>
       </c>
       <c r="B561" t="n">
-        <v>10.12933444976807</v>
+        <v>10.12933349609375</v>
       </c>
       <c r="C561" t="n">
-        <v>10.29553326633671</v>
+        <v>10.29553229701482</v>
       </c>
       <c r="D561" t="n">
-        <v>9.875663547020988</v>
+        <v>9.875662617229723</v>
       </c>
       <c r="E561" t="n">
-        <v>10.12058740958928</v>
+        <v>10.12058645673849</v>
       </c>
       <c r="F561" t="n">
         <v>7064832</v>
@@ -11732,16 +11732,16 @@
         <v>45056</v>
       </c>
       <c r="B566" t="n">
-        <v>10.00449466705322</v>
+        <v>10.00449562072754</v>
       </c>
       <c r="C566" t="n">
-        <v>10.33739447891732</v>
+        <v>10.33739546432518</v>
       </c>
       <c r="D566" t="n">
-        <v>9.969453558243071</v>
+        <v>9.969454508577106</v>
       </c>
       <c r="E566" t="n">
-        <v>10.24979001995237</v>
+        <v>10.24979099700936</v>
       </c>
       <c r="F566" t="n">
         <v>5572472</v>
@@ -11812,16 +11812,16 @@
         <v>45062</v>
       </c>
       <c r="B570" t="n">
-        <v>9.951932907104492</v>
+        <v>9.951933860778809</v>
       </c>
       <c r="C570" t="n">
-        <v>10.35491493267188</v>
+        <v>10.35491592496318</v>
       </c>
       <c r="D570" t="n">
-        <v>9.864327605521281</v>
+        <v>9.864328550800552</v>
       </c>
       <c r="E570" t="n">
-        <v>10.17970517297524</v>
+        <v>10.17970614847653</v>
       </c>
       <c r="F570" t="n">
         <v>2372207</v>
@@ -11872,16 +11872,16 @@
         <v>45065</v>
       </c>
       <c r="B573" t="n">
-        <v>11.44121837615967</v>
+        <v>11.44121742248535</v>
       </c>
       <c r="C573" t="n">
-        <v>12.00189047040555</v>
+        <v>12.00188946999683</v>
       </c>
       <c r="D573" t="n">
-        <v>10.51260450838727</v>
+        <v>10.51260363211687</v>
       </c>
       <c r="E573" t="n">
-        <v>10.60897093395166</v>
+        <v>10.60897004964872</v>
       </c>
       <c r="F573" t="n">
         <v>14298668</v>
@@ -11932,16 +11932,16 @@
         <v>45070</v>
       </c>
       <c r="B576" t="n">
-        <v>10.93310832977295</v>
+        <v>10.93310928344727</v>
       </c>
       <c r="C576" t="n">
-        <v>11.28352953369865</v>
+        <v>11.28353051793955</v>
       </c>
       <c r="D576" t="n">
-        <v>10.92434805271574</v>
+        <v>10.92434900562591</v>
       </c>
       <c r="E576" t="n">
-        <v>11.0820372570944</v>
+        <v>11.0820382237595</v>
       </c>
       <c r="F576" t="n">
         <v>2685985</v>
@@ -11972,16 +11972,16 @@
         <v>45072</v>
       </c>
       <c r="B578" t="n">
-        <v>11.6777515411377</v>
+        <v>11.67775058746338</v>
       </c>
       <c r="C578" t="n">
-        <v>11.90552465401795</v>
+        <v>11.90552368174234</v>
       </c>
       <c r="D578" t="n">
-        <v>11.47626010348781</v>
+        <v>11.47625916626848</v>
       </c>
       <c r="E578" t="n">
-        <v>11.54634400845561</v>
+        <v>11.54634306551281</v>
       </c>
       <c r="F578" t="n">
         <v>3617321</v>
@@ -12172,16 +12172,16 @@
         <v>45089</v>
       </c>
       <c r="B588" t="n">
-        <v>12.80785751342773</v>
+        <v>12.80785655975342</v>
       </c>
       <c r="C588" t="n">
-        <v>12.97430785096759</v>
+        <v>12.97430688489936</v>
       </c>
       <c r="D588" t="n">
-        <v>12.72025220579673</v>
+        <v>12.72025125864552</v>
       </c>
       <c r="E588" t="n">
-        <v>12.79909723570558</v>
+        <v>12.79909628268356</v>
       </c>
       <c r="F588" t="n">
         <v>2677201</v>
@@ -12192,16 +12192,16 @@
         <v>45090</v>
       </c>
       <c r="B589" t="n">
-        <v>12.52752113342285</v>
+        <v>12.52752208709717</v>
       </c>
       <c r="C589" t="n">
-        <v>13.04439014033381</v>
+        <v>13.04439113335547</v>
       </c>
       <c r="D589" t="n">
-        <v>12.29974717843629</v>
+        <v>12.29974811477101</v>
       </c>
       <c r="E589" t="n">
-        <v>12.86042010176204</v>
+        <v>12.86042108077874</v>
       </c>
       <c r="F589" t="n">
         <v>6116837</v>
@@ -12212,16 +12212,16 @@
         <v>45091</v>
       </c>
       <c r="B590" t="n">
-        <v>12.8867015838623</v>
+        <v>12.88670063018799</v>
       </c>
       <c r="C590" t="n">
-        <v>12.9392649366617</v>
+        <v>12.93926397909746</v>
       </c>
       <c r="D590" t="n">
-        <v>12.46619813534643</v>
+        <v>12.46619721279127</v>
       </c>
       <c r="E590" t="n">
-        <v>12.58884455276198</v>
+        <v>12.58884362113043</v>
       </c>
       <c r="F590" t="n">
         <v>4237809</v>
@@ -12232,16 +12232,16 @@
         <v>45092</v>
       </c>
       <c r="B591" t="n">
-        <v>12.83413887023926</v>
+        <v>12.83413791656494</v>
       </c>
       <c r="C591" t="n">
-        <v>13.07943254463561</v>
+        <v>13.0794315727341</v>
       </c>
       <c r="D591" t="n">
-        <v>12.77281524077272</v>
+        <v>12.77281429165521</v>
       </c>
       <c r="E591" t="n">
-        <v>12.86918082372445</v>
+        <v>12.86917986744625</v>
       </c>
       <c r="F591" t="n">
         <v>4574806</v>
@@ -12252,16 +12252,16 @@
         <v>45093</v>
       </c>
       <c r="B592" t="n">
-        <v>11.92304515838623</v>
+        <v>11.92304420471191</v>
       </c>
       <c r="C592" t="n">
-        <v>12.76405454487264</v>
+        <v>12.76405352392952</v>
       </c>
       <c r="D592" t="n">
-        <v>11.66023093759705</v>
+        <v>11.66023000494414</v>
       </c>
       <c r="E592" t="n">
-        <v>12.76405454487264</v>
+        <v>12.76405352392952</v>
       </c>
       <c r="F592" t="n">
         <v>19648730</v>
@@ -12312,16 +12312,16 @@
         <v>45098</v>
       </c>
       <c r="B595" t="n">
-        <v>10.9493932723999</v>
+        <v>10.94939422607422</v>
       </c>
       <c r="C595" t="n">
-        <v>10.99361554598554</v>
+        <v>10.99361650351154</v>
       </c>
       <c r="D595" t="n">
-        <v>10.52486062683539</v>
+        <v>10.5248615435336</v>
       </c>
       <c r="E595" t="n">
-        <v>10.93170402557776</v>
+        <v>10.93170497771137</v>
       </c>
       <c r="F595" t="n">
         <v>15399400</v>
@@ -12532,16 +12532,16 @@
         <v>45113</v>
       </c>
       <c r="B606" t="n">
-        <v>10.34797382354736</v>
+        <v>10.34797286987305</v>
       </c>
       <c r="C606" t="n">
-        <v>10.56908437893714</v>
+        <v>10.56908340488516</v>
       </c>
       <c r="D606" t="n">
-        <v>10.19761857840473</v>
+        <v>10.19761763858723</v>
       </c>
       <c r="E606" t="n">
-        <v>10.5160183179867</v>
+        <v>10.51601734882532</v>
       </c>
       <c r="F606" t="n">
         <v>6243800</v>
@@ -12732,16 +12732,16 @@
         <v>45127</v>
       </c>
       <c r="B616" t="n">
-        <v>10.19761848449707</v>
+        <v>10.19761753082275</v>
       </c>
       <c r="C616" t="n">
-        <v>10.22415235819778</v>
+        <v>10.22415140204203</v>
       </c>
       <c r="D616" t="n">
-        <v>9.91459724611479</v>
+        <v>9.914596318908426</v>
       </c>
       <c r="E616" t="n">
-        <v>10.07379711443973</v>
+        <v>10.07379617234511</v>
       </c>
       <c r="F616" t="n">
         <v>5709500</v>
@@ -12792,16 +12792,16 @@
         <v>45132</v>
       </c>
       <c r="B619" t="n">
-        <v>10.53370571136475</v>
+        <v>10.53370666503906</v>
       </c>
       <c r="C619" t="n">
-        <v>10.82557154894893</v>
+        <v>10.82557252904746</v>
       </c>
       <c r="D619" t="n">
-        <v>10.46295040791826</v>
+        <v>10.46295135518671</v>
       </c>
       <c r="E619" t="n">
-        <v>10.61330563860948</v>
+        <v>10.61330659949041</v>
       </c>
       <c r="F619" t="n">
         <v>5058400</v>
@@ -12932,16 +12932,16 @@
         <v>45141</v>
       </c>
       <c r="B626" t="n">
-        <v>10.64868450164795</v>
+        <v>10.64868354797363</v>
       </c>
       <c r="C626" t="n">
-        <v>10.84326202999435</v>
+        <v>10.84326105889407</v>
       </c>
       <c r="D626" t="n">
-        <v>10.50717387865778</v>
+        <v>10.50717293765687</v>
       </c>
       <c r="E626" t="n">
-        <v>10.6309960955091</v>
+        <v>10.63099514341892</v>
       </c>
       <c r="F626" t="n">
         <v>7397700</v>
@@ -12952,16 +12952,16 @@
         <v>45142</v>
       </c>
       <c r="B627" t="n">
-        <v>10.71943950653076</v>
+        <v>10.71943855285645</v>
       </c>
       <c r="C627" t="n">
-        <v>11.21472751629927</v>
+        <v>11.21472651856076</v>
       </c>
       <c r="D627" t="n">
-        <v>10.59561729322118</v>
+        <v>10.59561635056293</v>
       </c>
       <c r="E627" t="n">
-        <v>10.70175110089786</v>
+        <v>10.70175014879723</v>
       </c>
       <c r="F627" t="n">
         <v>16706200</v>
@@ -12992,16 +12992,16 @@
         <v>45146</v>
       </c>
       <c r="B629" t="n">
-        <v>10.53370571136475</v>
+        <v>10.53370666503906</v>
       </c>
       <c r="C629" t="n">
-        <v>10.59561639101298</v>
+        <v>10.59561735029241</v>
       </c>
       <c r="D629" t="n">
-        <v>10.00304093551612</v>
+        <v>10.00304184114644</v>
       </c>
       <c r="E629" t="n">
-        <v>10.24183987378056</v>
+        <v>10.24184080103066</v>
       </c>
       <c r="F629" t="n">
         <v>6465200</v>
@@ -13012,16 +13012,16 @@
         <v>45147</v>
       </c>
       <c r="B630" t="n">
-        <v>10.54255104064941</v>
+        <v>10.5425500869751</v>
       </c>
       <c r="C630" t="n">
-        <v>10.68406165701199</v>
+        <v>10.68406069053669</v>
       </c>
       <c r="D630" t="n">
-        <v>10.3656627701962</v>
+        <v>10.36566183252311</v>
       </c>
       <c r="E630" t="n">
-        <v>10.5337064162593</v>
+        <v>10.53370546338507</v>
       </c>
       <c r="F630" t="n">
         <v>5435200</v>
@@ -13032,16 +13032,16 @@
         <v>45148</v>
       </c>
       <c r="B631" t="n">
-        <v>10.63099575042725</v>
+        <v>10.63099479675293</v>
       </c>
       <c r="C631" t="n">
-        <v>10.86095008358703</v>
+        <v>10.86094910928421</v>
       </c>
       <c r="D631" t="n">
-        <v>10.52486194315988</v>
+        <v>10.5248609990065</v>
       </c>
       <c r="E631" t="n">
-        <v>10.66637340502643</v>
+        <v>10.66637244817849</v>
       </c>
       <c r="F631" t="n">
         <v>4975000</v>
@@ -13112,16 +13112,16 @@
         <v>45154</v>
       </c>
       <c r="B635" t="n">
-        <v>10.38335037231445</v>
+        <v>10.38335132598877</v>
       </c>
       <c r="C635" t="n">
-        <v>10.48063954614038</v>
+        <v>10.48064050875037</v>
       </c>
       <c r="D635" t="n">
-        <v>10.25952901431016</v>
+        <v>10.25952995661192</v>
       </c>
       <c r="E635" t="n">
-        <v>10.46295029872849</v>
+        <v>10.46295125971378</v>
       </c>
       <c r="F635" t="n">
         <v>5623400</v>
@@ -13172,16 +13172,16 @@
         <v>45159</v>
       </c>
       <c r="B638" t="n">
-        <v>10.14455127716064</v>
+        <v>10.14455223083496</v>
       </c>
       <c r="C638" t="n">
-        <v>10.34797255838301</v>
+        <v>10.34797353118066</v>
       </c>
       <c r="D638" t="n">
-        <v>10.09148437922844</v>
+        <v>10.09148532791402</v>
       </c>
       <c r="E638" t="n">
-        <v>10.25952885312231</v>
+        <v>10.2595298176055</v>
       </c>
       <c r="F638" t="n">
         <v>3931700</v>
@@ -13192,16 +13192,16 @@
         <v>45160</v>
       </c>
       <c r="B639" t="n">
-        <v>10.63099575042725</v>
+        <v>10.63099479675293</v>
       </c>
       <c r="C639" t="n">
-        <v>10.70175105962561</v>
+        <v>10.70175009960405</v>
       </c>
       <c r="D639" t="n">
-        <v>10.18877464620255</v>
+        <v>10.18877373219854</v>
       </c>
       <c r="E639" t="n">
-        <v>10.24184070636641</v>
+        <v>10.24183978760201</v>
       </c>
       <c r="F639" t="n">
         <v>5680500</v>
@@ -13232,16 +13232,16 @@
         <v>45162</v>
       </c>
       <c r="B641" t="n">
-        <v>10.73712825775146</v>
+        <v>10.73712730407715</v>
       </c>
       <c r="C641" t="n">
-        <v>10.99361645355878</v>
+        <v>10.99361547710312</v>
       </c>
       <c r="D641" t="n">
-        <v>10.64868370327869</v>
+        <v>10.64868275746004</v>
       </c>
       <c r="E641" t="n">
-        <v>10.85210584117816</v>
+        <v>10.85210487729151</v>
       </c>
       <c r="F641" t="n">
         <v>5730800</v>
@@ -13252,16 +13252,16 @@
         <v>45163</v>
       </c>
       <c r="B642" t="n">
-        <v>10.29490661621094</v>
+        <v>10.29490756988525</v>
       </c>
       <c r="C642" t="n">
-        <v>10.82557138397249</v>
+        <v>10.82557238680523</v>
       </c>
       <c r="D642" t="n">
-        <v>10.25068434136337</v>
+        <v>10.25068529094114</v>
       </c>
       <c r="E642" t="n">
-        <v>10.72828305408364</v>
+        <v>10.72828404790402</v>
       </c>
       <c r="F642" t="n">
         <v>6496000</v>
@@ -13312,16 +13312,16 @@
         <v>45168</v>
       </c>
       <c r="B645" t="n">
-        <v>10.53370571136475</v>
+        <v>10.53370666503906</v>
       </c>
       <c r="C645" t="n">
-        <v>10.59561639101298</v>
+        <v>10.59561735029241</v>
       </c>
       <c r="D645" t="n">
-        <v>10.40103972827003</v>
+        <v>10.40104066993336</v>
       </c>
       <c r="E645" t="n">
-        <v>10.5248610875665</v>
+        <v>10.52486204044006</v>
       </c>
       <c r="F645" t="n">
         <v>3749300</v>
@@ -13352,16 +13352,16 @@
         <v>45170</v>
       </c>
       <c r="B647" t="n">
-        <v>10.5779275894165</v>
+        <v>10.57792854309082</v>
       </c>
       <c r="C647" t="n">
-        <v>10.64868289020433</v>
+        <v>10.64868385025773</v>
       </c>
       <c r="D647" t="n">
-        <v>10.43641698784085</v>
+        <v>10.436417928757</v>
       </c>
       <c r="E647" t="n">
-        <v>10.43641698784085</v>
+        <v>10.436417928757</v>
       </c>
       <c r="F647" t="n">
         <v>11645200</v>
@@ -13372,16 +13372,16 @@
         <v>45173</v>
       </c>
       <c r="B648" t="n">
-        <v>10.78135013580322</v>
+        <v>10.78134918212891</v>
       </c>
       <c r="C648" t="n">
-        <v>10.9051723484737</v>
+        <v>10.90517138384658</v>
       </c>
       <c r="D648" t="n">
-        <v>10.5690842084851</v>
+        <v>10.56908327358697</v>
       </c>
       <c r="E648" t="n">
-        <v>10.57792883299081</v>
+        <v>10.57792789731032</v>
       </c>
       <c r="F648" t="n">
         <v>4629200</v>
@@ -13412,16 +13412,16 @@
         <v>45175</v>
       </c>
       <c r="B650" t="n">
-        <v>9.490063667297363</v>
+        <v>9.49006462097168</v>
       </c>
       <c r="C650" t="n">
-        <v>10.02072928365057</v>
+        <v>10.02073029065247</v>
       </c>
       <c r="D650" t="n">
-        <v>9.419308364246236</v>
+        <v>9.419309310810219</v>
       </c>
       <c r="E650" t="n">
-        <v>10.01188465990174</v>
+        <v>10.01188566601482</v>
       </c>
       <c r="F650" t="n">
         <v>30094100</v>
@@ -13532,16 +13532,16 @@
         <v>45184</v>
       </c>
       <c r="B656" t="n">
-        <v>9.375087738037109</v>
+        <v>9.375086784362793</v>
       </c>
       <c r="C656" t="n">
-        <v>10.00304173917788</v>
+        <v>10.00304072162537</v>
       </c>
       <c r="D656" t="n">
-        <v>9.375087738037109</v>
+        <v>9.375086784362793</v>
       </c>
       <c r="E656" t="n">
-        <v>9.923441805537948</v>
+        <v>9.923440796082692</v>
       </c>
       <c r="F656" t="n">
         <v>14904000</v>
@@ -13672,16 +13672,16 @@
         <v>45195</v>
       </c>
       <c r="B663" t="n">
-        <v>8.49948787689209</v>
+        <v>8.499488830566406</v>
       </c>
       <c r="C663" t="n">
-        <v>8.623310068707225</v>
+        <v>8.623311036274854</v>
       </c>
       <c r="D663" t="n">
-        <v>8.49948787689209</v>
+        <v>8.499488830566406</v>
       </c>
       <c r="E663" t="n">
-        <v>8.561399394534495</v>
+        <v>8.561400355155516</v>
       </c>
       <c r="F663" t="n">
         <v>4158300</v>
@@ -13712,16 +13712,16 @@
         <v>45197</v>
       </c>
       <c r="B665" t="n">
-        <v>8.561400413513184</v>
+        <v>8.561399459838867</v>
       </c>
       <c r="C665" t="n">
-        <v>8.676377995996951</v>
+        <v>8.676377029515013</v>
       </c>
       <c r="D665" t="n">
-        <v>8.33144524854565</v>
+        <v>8.331444320486574</v>
       </c>
       <c r="E665" t="n">
-        <v>8.375667525419372</v>
+        <v>8.375666592434273</v>
       </c>
       <c r="F665" t="n">
         <v>5776700</v>
@@ -13772,16 +13772,16 @@
         <v>45202</v>
       </c>
       <c r="B668" t="n">
-        <v>7.659268856048584</v>
+        <v>7.659268379211426</v>
       </c>
       <c r="C668" t="n">
-        <v>7.933446292673103</v>
+        <v>7.933445798766693</v>
       </c>
       <c r="D668" t="n">
-        <v>7.570825147453722</v>
+        <v>7.570824676122735</v>
       </c>
       <c r="E668" t="n">
-        <v>7.880379392740378</v>
+        <v>7.880378902137712</v>
       </c>
       <c r="F668" t="n">
         <v>18608300</v>
@@ -13792,16 +13792,16 @@
         <v>45203</v>
       </c>
       <c r="B669" t="n">
-        <v>7.738868713378906</v>
+        <v>7.738868236541748</v>
       </c>
       <c r="C669" t="n">
-        <v>7.85384629262262</v>
+        <v>7.853845808701018</v>
       </c>
       <c r="D669" t="n">
-        <v>7.632735757954652</v>
+        <v>7.632735287656968</v>
       </c>
       <c r="E669" t="n">
-        <v>7.756557961017825</v>
+        <v>7.756557483090727</v>
       </c>
       <c r="F669" t="n">
         <v>14186500</v>
@@ -13852,16 +13852,16 @@
         <v>45208</v>
       </c>
       <c r="B672" t="n">
-        <v>7.712335586547852</v>
+        <v>7.71233606338501</v>
       </c>
       <c r="C672" t="n">
-        <v>7.809623916905786</v>
+        <v>7.809624399758072</v>
       </c>
       <c r="D672" t="n">
-        <v>7.385092100649629</v>
+        <v>7.385092557254024</v>
       </c>
       <c r="E672" t="n">
-        <v>7.393935880885993</v>
+        <v>7.393936338037181</v>
       </c>
       <c r="F672" t="n">
         <v>4734000</v>
@@ -13872,16 +13872,16 @@
         <v>45209</v>
       </c>
       <c r="B673" t="n">
-        <v>8.101490020751953</v>
+        <v>8.101489067077637</v>
       </c>
       <c r="C673" t="n">
-        <v>8.18993457381352</v>
+        <v>8.189933609727872</v>
       </c>
       <c r="D673" t="n">
-        <v>7.906912510098369</v>
+        <v>7.906911579328923</v>
       </c>
       <c r="E673" t="n">
-        <v>7.951134786629153</v>
+        <v>7.95113385065404</v>
       </c>
       <c r="F673" t="n">
         <v>9907700</v>
@@ -13892,16 +13892,16 @@
         <v>45210</v>
       </c>
       <c r="B674" t="n">
-        <v>7.933445930480957</v>
+        <v>7.933446407318115</v>
       </c>
       <c r="C674" t="n">
-        <v>8.225311758111753</v>
+        <v>8.22531225249141</v>
       </c>
       <c r="D674" t="n">
-        <v>7.818468355434018</v>
+        <v>7.818468825360488</v>
       </c>
       <c r="E674" t="n">
-        <v>8.207622511118506</v>
+        <v>8.207623004434957</v>
       </c>
       <c r="F674" t="n">
         <v>7415900</v>
@@ -14012,16 +14012,16 @@
         <v>45219</v>
       </c>
       <c r="B680" t="n">
-        <v>7.102070808410645</v>
+        <v>7.102070331573486</v>
       </c>
       <c r="C680" t="n">
-        <v>7.163982337526886</v>
+        <v>7.163981856532952</v>
       </c>
       <c r="D680" t="n">
-        <v>6.916338329736497</v>
+        <v>6.916337865369526</v>
       </c>
       <c r="E680" t="n">
-        <v>7.013626670533689</v>
+        <v>7.013626199634722</v>
       </c>
       <c r="F680" t="n">
         <v>6704900</v>
@@ -14092,16 +14092,16 @@
         <v>45225</v>
       </c>
       <c r="B684" t="n">
-        <v>7.102070808410645</v>
+        <v>7.102070331573486</v>
       </c>
       <c r="C684" t="n">
-        <v>7.137448463561426</v>
+        <v>7.137447984348992</v>
       </c>
       <c r="D684" t="n">
-        <v>6.783671912053608</v>
+        <v>6.783671456593937</v>
       </c>
       <c r="E684" t="n">
-        <v>6.854427222355172</v>
+        <v>6.854426762144948</v>
       </c>
       <c r="F684" t="n">
         <v>6790200</v>
@@ -14172,16 +14172,16 @@
         <v>45231</v>
       </c>
       <c r="B688" t="n">
-        <v>7.013626098632812</v>
+        <v>7.013626575469971</v>
       </c>
       <c r="C688" t="n">
-        <v>7.402780695294118</v>
+        <v>7.402781198588827</v>
       </c>
       <c r="D688" t="n">
-        <v>6.916337765768647</v>
+        <v>6.916338235991438</v>
       </c>
       <c r="E688" t="n">
-        <v>6.969404244167705</v>
+        <v>6.969404717998341</v>
       </c>
       <c r="F688" t="n">
         <v>11133300</v>
@@ -14192,16 +14192,16 @@
         <v>45233</v>
       </c>
       <c r="B689" t="n">
-        <v>8.030735015869141</v>
+        <v>8.030734062194824</v>
       </c>
       <c r="C689" t="n">
-        <v>8.030735015869141</v>
+        <v>8.030734062194824</v>
       </c>
       <c r="D689" t="n">
-        <v>7.234737382440756</v>
+        <v>7.23473652329359</v>
       </c>
       <c r="E689" t="n">
-        <v>7.305492690146844</v>
+        <v>7.305491822597268</v>
       </c>
       <c r="F689" t="n">
         <v>15995000</v>
@@ -14212,16 +14212,16 @@
         <v>45236</v>
       </c>
       <c r="B690" t="n">
-        <v>7.915756702423096</v>
+        <v>7.915757179260254</v>
       </c>
       <c r="C690" t="n">
-        <v>8.119178825983433</v>
+        <v>8.119179315074533</v>
       </c>
       <c r="D690" t="n">
-        <v>7.791935347053061</v>
+        <v>7.791935816431346</v>
       </c>
       <c r="E690" t="n">
-        <v>8.092644955430091</v>
+        <v>8.092645442922818</v>
       </c>
       <c r="F690" t="n">
         <v>6975500</v>
@@ -14252,16 +14252,16 @@
         <v>45238</v>
       </c>
       <c r="B692" t="n">
-        <v>8.101490020751953</v>
+        <v>8.101489067077637</v>
       </c>
       <c r="C692" t="n">
-        <v>8.649844056712263</v>
+        <v>8.649843038487949</v>
       </c>
       <c r="D692" t="n">
-        <v>8.013046311160156</v>
+        <v>8.013045367897073</v>
       </c>
       <c r="E692" t="n">
-        <v>8.357978212466772</v>
+        <v>8.357977228599713</v>
       </c>
       <c r="F692" t="n">
         <v>19964500</v>
@@ -14272,16 +14272,16 @@
         <v>45239</v>
       </c>
       <c r="B693" t="n">
-        <v>7.95997953414917</v>
+        <v>7.959979057312012</v>
       </c>
       <c r="C693" t="n">
-        <v>8.189934700901784</v>
+        <v>8.189934210289316</v>
       </c>
       <c r="D693" t="n">
-        <v>7.774246644613565</v>
+        <v>7.774246178902609</v>
       </c>
       <c r="E693" t="n">
-        <v>8.189934700901784</v>
+        <v>8.189934210289316</v>
       </c>
       <c r="F693" t="n">
         <v>11094800</v>
@@ -14292,16 +14292,16 @@
         <v>45240</v>
       </c>
       <c r="B694" t="n">
-        <v>7.933445930480957</v>
+        <v>7.933446407318115</v>
       </c>
       <c r="C694" t="n">
-        <v>8.136867210084963</v>
+        <v>8.13686769914869</v>
       </c>
       <c r="D694" t="n">
-        <v>7.933445930480956</v>
+        <v>7.933446407318114</v>
       </c>
       <c r="E694" t="n">
-        <v>8.039578882031272</v>
+        <v>8.039579365247516</v>
       </c>
       <c r="F694" t="n">
         <v>6302800</v>
@@ -14372,16 +14372,16 @@
         <v>45247</v>
       </c>
       <c r="B698" t="n">
-        <v>8.641000747680664</v>
+        <v>8.640999794006348</v>
       </c>
       <c r="C698" t="n">
-        <v>8.826732800998892</v>
+        <v>8.826731826826038</v>
       </c>
       <c r="D698" t="n">
-        <v>8.623311498715223</v>
+        <v>8.623310546993203</v>
       </c>
       <c r="E698" t="n">
-        <v>8.747133711063858</v>
+        <v>8.747132745676051</v>
       </c>
       <c r="F698" t="n">
         <v>7834100</v>
@@ -14532,16 +14532,16 @@
         <v>45259</v>
       </c>
       <c r="B706" t="n">
-        <v>8.251845359802246</v>
+        <v>8.25184440612793</v>
       </c>
       <c r="C706" t="n">
-        <v>8.349133694631236</v>
+        <v>8.349132729713206</v>
       </c>
       <c r="D706" t="n">
-        <v>8.128023152635528</v>
+        <v>8.128022213271473</v>
       </c>
       <c r="E706" t="n">
-        <v>8.145712400860679</v>
+        <v>8.14571145945226</v>
       </c>
       <c r="F706" t="n">
         <v>4175000</v>
@@ -14612,16 +14612,16 @@
         <v>45265</v>
       </c>
       <c r="B710" t="n">
-        <v>8.331445693969727</v>
+        <v>8.33144474029541</v>
       </c>
       <c r="C710" t="n">
-        <v>8.472956312755398</v>
+        <v>8.472955342882807</v>
       </c>
       <c r="D710" t="n">
-        <v>8.251845760035332</v>
+        <v>8.251844815472568</v>
       </c>
       <c r="E710" t="n">
-        <v>8.251845760035332</v>
+        <v>8.251844815472568</v>
       </c>
       <c r="F710" t="n">
         <v>4182300</v>
@@ -14652,16 +14652,16 @@
         <v>45267</v>
       </c>
       <c r="B712" t="n">
-        <v>8.340290069580078</v>
+        <v>8.340289115905762</v>
       </c>
       <c r="C712" t="n">
-        <v>8.357978474665433</v>
+        <v>8.357977518968529</v>
       </c>
       <c r="D712" t="n">
-        <v>8.163400957907747</v>
+        <v>8.163400024459897</v>
       </c>
       <c r="E712" t="n">
-        <v>8.243000889466337</v>
+        <v>8.242999946916596</v>
       </c>
       <c r="F712" t="n">
         <v>3161600</v>
@@ -14672,16 +14672,16 @@
         <v>45268</v>
       </c>
       <c r="B713" t="n">
-        <v>8.207622528076172</v>
+        <v>8.207623481750488</v>
       </c>
       <c r="C713" t="n">
-        <v>8.357977753950529</v>
+        <v>8.35797872509518</v>
       </c>
       <c r="D713" t="n">
-        <v>8.048423522156641</v>
+        <v>8.048424457333031</v>
       </c>
       <c r="E713" t="n">
-        <v>8.340289350390458</v>
+        <v>8.340290319479827</v>
       </c>
       <c r="F713" t="n">
         <v>4500000</v>
@@ -14792,16 +14792,16 @@
         <v>45278</v>
       </c>
       <c r="B719" t="n">
-        <v>8.835577011108398</v>
+        <v>8.835576057434082</v>
       </c>
       <c r="C719" t="n">
-        <v>8.977087622316056</v>
+        <v>8.977086653367691</v>
       </c>
       <c r="D719" t="n">
-        <v>8.800199358306484</v>
+        <v>8.800198408450679</v>
       </c>
       <c r="E719" t="n">
-        <v>8.809043982374407</v>
+        <v>8.809043031563952</v>
       </c>
       <c r="F719" t="n">
         <v>3928300</v>
@@ -14832,16 +14832,16 @@
         <v>45280</v>
       </c>
       <c r="B721" t="n">
-        <v>8.676929473876953</v>
+        <v>8.67693042755127</v>
       </c>
       <c r="C721" t="n">
-        <v>9.033140576382147</v>
+        <v>9.033141569207338</v>
       </c>
       <c r="D721" t="n">
-        <v>8.622127430780413</v>
+        <v>8.622128378431482</v>
       </c>
       <c r="E721" t="n">
-        <v>8.950937947261799</v>
+        <v>8.950938931052166</v>
       </c>
       <c r="F721" t="n">
         <v>6032100</v>
@@ -14872,16 +14872,16 @@
         <v>45282</v>
       </c>
       <c r="B723" t="n">
-        <v>8.887002944946289</v>
+        <v>8.887001991271973</v>
       </c>
       <c r="C723" t="n">
-        <v>9.005739990602331</v>
+        <v>9.005739024186209</v>
       </c>
       <c r="D723" t="n">
-        <v>8.731732361756549</v>
+        <v>8.731731424744495</v>
       </c>
       <c r="E723" t="n">
-        <v>8.95093881325278</v>
+        <v>8.950937852717432</v>
       </c>
       <c r="F723" t="n">
         <v>62444400</v>
@@ -14932,16 +14932,16 @@
         <v>45288</v>
       </c>
       <c r="B726" t="n">
-        <v>9.197546005249023</v>
+        <v>9.197545051574707</v>
       </c>
       <c r="C726" t="n">
-        <v>9.33455069298248</v>
+        <v>9.334549725102434</v>
       </c>
       <c r="D726" t="n">
-        <v>8.96920573007562</v>
+        <v>8.969204800077428</v>
       </c>
       <c r="E726" t="n">
-        <v>9.097076597750373</v>
+        <v>9.097075654493521</v>
       </c>
       <c r="F726" t="n">
         <v>16865200</v>
@@ -15092,16 +15092,16 @@
         <v>45302</v>
       </c>
       <c r="B734" t="n">
-        <v>8.676929473876953</v>
+        <v>8.67693042755127</v>
       </c>
       <c r="C734" t="n">
-        <v>8.841334732117646</v>
+        <v>8.841335703861612</v>
       </c>
       <c r="D734" t="n">
-        <v>8.640395068828902</v>
+        <v>8.640396018487751</v>
       </c>
       <c r="E734" t="n">
-        <v>8.640395068828902</v>
+        <v>8.640396018487751</v>
       </c>
       <c r="F734" t="n">
         <v>4234100</v>
@@ -15112,16 +15112,16 @@
         <v>45303</v>
       </c>
       <c r="B735" t="n">
-        <v>8.676929473876953</v>
+        <v>8.67693042755127</v>
       </c>
       <c r="C735" t="n">
-        <v>8.969204714261362</v>
+        <v>8.969205700059415</v>
       </c>
       <c r="D735" t="n">
-        <v>8.640395068828902</v>
+        <v>8.640396018487751</v>
       </c>
       <c r="E735" t="n">
-        <v>8.640395068828902</v>
+        <v>8.640396018487751</v>
       </c>
       <c r="F735" t="n">
         <v>4898500</v>
@@ -15132,16 +15132,16 @@
         <v>45306</v>
       </c>
       <c r="B736" t="n">
-        <v>8.704331398010254</v>
+        <v>8.704330444335938</v>
       </c>
       <c r="C736" t="n">
-        <v>8.759133449531467</v>
+        <v>8.759132489852862</v>
       </c>
       <c r="D736" t="n">
-        <v>8.585594345588509</v>
+        <v>8.585593404923404</v>
       </c>
       <c r="E736" t="n">
-        <v>8.585594345588509</v>
+        <v>8.585593404923404</v>
       </c>
       <c r="F736" t="n">
         <v>2435000</v>
@@ -15212,16 +15212,16 @@
         <v>45310</v>
       </c>
       <c r="B740" t="n">
-        <v>7.763569355010986</v>
+        <v>7.763568878173828</v>
       </c>
       <c r="C740" t="n">
-        <v>7.845771993431888</v>
+        <v>7.845771511545856</v>
       </c>
       <c r="D740" t="n">
-        <v>7.498694670681984</v>
+        <v>7.498694210113386</v>
       </c>
       <c r="E740" t="n">
-        <v>7.690500536647746</v>
+        <v>7.690500064298463</v>
       </c>
       <c r="F740" t="n">
         <v>7953500</v>
@@ -15252,16 +15252,16 @@
         <v>45314</v>
       </c>
       <c r="B742" t="n">
-        <v>7.608297824859619</v>
+        <v>7.608297348022461</v>
       </c>
       <c r="C742" t="n">
-        <v>7.727034871317152</v>
+        <v>7.727034387038351</v>
       </c>
       <c r="D742" t="n">
-        <v>7.443892549603185</v>
+        <v>7.443892083069849</v>
       </c>
       <c r="E742" t="n">
-        <v>7.443892549603185</v>
+        <v>7.443892083069849</v>
       </c>
       <c r="F742" t="n">
         <v>3836100</v>
@@ -15272,16 +15272,16 @@
         <v>45315</v>
       </c>
       <c r="B743" t="n">
-        <v>7.489560127258301</v>
+        <v>7.489560604095459</v>
       </c>
       <c r="C743" t="n">
-        <v>7.727034199527327</v>
+        <v>7.727034691483726</v>
       </c>
       <c r="D743" t="n">
-        <v>7.416491315952283</v>
+        <v>7.416491788137376</v>
       </c>
       <c r="E743" t="n">
-        <v>7.699633613049805</v>
+        <v>7.699634103261693</v>
       </c>
       <c r="F743" t="n">
         <v>5274600</v>
@@ -15312,16 +15312,16 @@
         <v>45317</v>
       </c>
       <c r="B745" t="n">
-        <v>7.471293449401855</v>
+        <v>7.471293926239014</v>
       </c>
       <c r="C745" t="n">
-        <v>7.553496080867482</v>
+        <v>7.553496562951024</v>
       </c>
       <c r="D745" t="n">
-        <v>7.407357585456952</v>
+        <v>7.407358058213559</v>
       </c>
       <c r="E745" t="n">
-        <v>7.489560216922579</v>
+        <v>7.489560694925569</v>
       </c>
       <c r="F745" t="n">
         <v>5075500</v>
@@ -15452,16 +15452,16 @@
         <v>45328</v>
       </c>
       <c r="B752" t="n">
-        <v>7.26121997833252</v>
+        <v>7.261220455169678</v>
       </c>
       <c r="C752" t="n">
-        <v>7.47129346713769</v>
+        <v>7.471293957770166</v>
       </c>
       <c r="D752" t="n">
-        <v>7.087681766753425</v>
+        <v>7.087682232194499</v>
       </c>
       <c r="E752" t="n">
-        <v>7.087681766753425</v>
+        <v>7.087682232194499</v>
       </c>
       <c r="F752" t="n">
         <v>7301900</v>
@@ -15512,16 +15512,16 @@
         <v>45331</v>
       </c>
       <c r="B755" t="n">
-        <v>7.26121997833252</v>
+        <v>7.261220455169678</v>
       </c>
       <c r="C755" t="n">
-        <v>7.47129346713769</v>
+        <v>7.471293957770166</v>
       </c>
       <c r="D755" t="n">
-        <v>7.206418369066836</v>
+        <v>7.206418842305226</v>
       </c>
       <c r="E755" t="n">
-        <v>7.352556429299803</v>
+        <v>7.352556912134935</v>
       </c>
       <c r="F755" t="n">
         <v>5959300</v>
@@ -15552,16 +15552,16 @@
         <v>45337</v>
       </c>
       <c r="B757" t="n">
-        <v>7.26121997833252</v>
+        <v>7.261220455169678</v>
       </c>
       <c r="C757" t="n">
-        <v>7.361690248606321</v>
+        <v>7.361690732041263</v>
       </c>
       <c r="D757" t="n">
-        <v>7.124216172930548</v>
+        <v>7.124216640770801</v>
       </c>
       <c r="E757" t="n">
-        <v>7.270353797639038</v>
+        <v>7.270354275076005</v>
       </c>
       <c r="F757" t="n">
         <v>6551500</v>
@@ -15592,16 +15592,16 @@
         <v>45341</v>
       </c>
       <c r="B759" t="n">
-        <v>7.3982253074646</v>
+        <v>7.398224830627441</v>
       </c>
       <c r="C759" t="n">
-        <v>7.526095304840912</v>
+        <v>7.526094819762161</v>
       </c>
       <c r="D759" t="n">
-        <v>7.261220618926942</v>
+        <v>7.261220150920135</v>
       </c>
       <c r="E759" t="n">
-        <v>7.507828535665309</v>
+        <v>7.507828051763903</v>
       </c>
       <c r="F759" t="n">
         <v>5437200</v>
@@ -15712,16 +15712,16 @@
         <v>45349</v>
       </c>
       <c r="B765" t="n">
-        <v>8.384654998779297</v>
+        <v>8.38465404510498</v>
       </c>
       <c r="C765" t="n">
-        <v>8.457723815544558</v>
+        <v>8.457722853559364</v>
       </c>
       <c r="D765" t="n">
-        <v>8.101512680527156</v>
+        <v>8.101511759057571</v>
       </c>
       <c r="E765" t="n">
-        <v>8.101512680527156</v>
+        <v>8.101511759057571</v>
       </c>
       <c r="F765" t="n">
         <v>7036800</v>
@@ -15772,16 +15772,16 @@
         <v>45352</v>
       </c>
       <c r="B768" t="n">
-        <v>7.991909027099609</v>
+        <v>7.991909503936768</v>
       </c>
       <c r="C768" t="n">
-        <v>8.128912833430306</v>
+        <v>8.128913318441795</v>
       </c>
       <c r="D768" t="n">
-        <v>7.946240801306391</v>
+        <v>7.946241275418755</v>
       </c>
       <c r="E768" t="n">
-        <v>7.973641388362739</v>
+        <v>7.973641864109958</v>
       </c>
       <c r="F768" t="n">
         <v>3021100</v>
@@ -15852,16 +15852,16 @@
         <v>45358</v>
       </c>
       <c r="B772" t="n">
-        <v>7.635698318481445</v>
+        <v>7.635697841644287</v>
       </c>
       <c r="C772" t="n">
-        <v>7.745301543602346</v>
+        <v>7.745301059920641</v>
       </c>
       <c r="D772" t="n">
-        <v>7.535228913216204</v>
+        <v>7.535228442653199</v>
       </c>
       <c r="E772" t="n">
-        <v>7.717900955084372</v>
+        <v>7.71790047311379</v>
       </c>
       <c r="F772" t="n">
         <v>3046600</v>
@@ -15872,16 +15872,16 @@
         <v>45359</v>
       </c>
       <c r="B773" t="n">
-        <v>7.489560127258301</v>
+        <v>7.489560604095459</v>
       </c>
       <c r="C773" t="n">
-        <v>7.745300966829362</v>
+        <v>7.74530145994875</v>
       </c>
       <c r="D773" t="n">
-        <v>7.471293359956266</v>
+        <v>7.471293835630435</v>
       </c>
       <c r="E773" t="n">
-        <v>7.590030396090778</v>
+        <v>7.590030879324569</v>
       </c>
       <c r="F773" t="n">
         <v>5969600</v>
@@ -15892,16 +15892,16 @@
         <v>45362</v>
       </c>
       <c r="B774" t="n">
-        <v>7.681366920471191</v>
+        <v>7.681366443634033</v>
       </c>
       <c r="C774" t="n">
-        <v>7.699634561071378</v>
+        <v>7.699634083100217</v>
       </c>
       <c r="D774" t="n">
-        <v>7.434759869711995</v>
+        <v>7.434759408183492</v>
       </c>
       <c r="E774" t="n">
-        <v>7.462160459563228</v>
+        <v>7.462159996333776</v>
       </c>
       <c r="F774" t="n">
         <v>4043700</v>
@@ -15912,16 +15912,16 @@
         <v>45363</v>
       </c>
       <c r="B775" t="n">
-        <v>7.873172283172607</v>
+        <v>7.873171806335449</v>
       </c>
       <c r="C775" t="n">
-        <v>7.982775506549723</v>
+        <v>7.982775023074468</v>
       </c>
       <c r="D775" t="n">
-        <v>7.717900832292778</v>
+        <v>7.717900364859606</v>
       </c>
       <c r="E775" t="n">
-        <v>7.727034652003119</v>
+        <v>7.727034184016758</v>
       </c>
       <c r="F775" t="n">
         <v>6470300</v>
@@ -15952,16 +15952,16 @@
         <v>45365</v>
       </c>
       <c r="B777" t="n">
-        <v>7.85490608215332</v>
+        <v>7.854905605316162</v>
       </c>
       <c r="C777" t="n">
-        <v>8.101513134801777</v>
+        <v>8.101512642994178</v>
       </c>
       <c r="D777" t="n">
-        <v>7.781837261290884</v>
+        <v>7.781836788889417</v>
       </c>
       <c r="E777" t="n">
-        <v>8.055844904000491</v>
+        <v>8.055844414965213</v>
       </c>
       <c r="F777" t="n">
         <v>5804500</v>
@@ -15992,16 +15992,16 @@
         <v>45369</v>
       </c>
       <c r="B779" t="n">
-        <v>7.653965473175049</v>
+        <v>7.653965950012207</v>
       </c>
       <c r="C779" t="n">
-        <v>7.836637503467626</v>
+        <v>7.836637991685135</v>
       </c>
       <c r="D779" t="n">
-        <v>7.553496074276368</v>
+        <v>7.553496544854347</v>
       </c>
       <c r="E779" t="n">
-        <v>7.6265648863934</v>
+        <v>7.626565361523518</v>
       </c>
       <c r="F779" t="n">
         <v>6064700</v>
@@ -16012,16 +16012,16 @@
         <v>45370</v>
       </c>
       <c r="B780" t="n">
-        <v>7.571763038635254</v>
+        <v>7.571763515472412</v>
       </c>
       <c r="C780" t="n">
-        <v>7.882305933730743</v>
+        <v>7.882306430124562</v>
       </c>
       <c r="D780" t="n">
-        <v>7.297754550548118</v>
+        <v>7.297755010129397</v>
       </c>
       <c r="E780" t="n">
-        <v>7.580896858149585</v>
+        <v>7.580897335561953</v>
       </c>
       <c r="F780" t="n">
         <v>12953700</v>
@@ -16032,16 +16032,16 @@
         <v>45371</v>
       </c>
       <c r="B781" t="n">
-        <v>8.110647201538086</v>
+        <v>8.11064624786377</v>
       </c>
       <c r="C781" t="n">
-        <v>8.183716024620034</v>
+        <v>8.183715062354066</v>
       </c>
       <c r="D781" t="n">
-        <v>7.535229566480925</v>
+        <v>7.535228680465948</v>
       </c>
       <c r="E781" t="n">
-        <v>7.608298389562875</v>
+        <v>7.608297494956244</v>
       </c>
       <c r="F781" t="n">
         <v>10775600</v>
@@ -16052,16 +16052,16 @@
         <v>45372</v>
       </c>
       <c r="B782" t="n">
-        <v>8.147181510925293</v>
+        <v>8.147180557250977</v>
       </c>
       <c r="C782" t="n">
-        <v>8.229384153624055</v>
+        <v>8.229383190327447</v>
       </c>
       <c r="D782" t="n">
-        <v>8.010177687126737</v>
+        <v>8.010176749489503</v>
       </c>
       <c r="E782" t="n">
-        <v>8.083246509292509</v>
+        <v>8.083245563102151</v>
       </c>
       <c r="F782" t="n">
         <v>10797200</v>
@@ -16092,16 +16092,16 @@
         <v>45376</v>
       </c>
       <c r="B784" t="n">
-        <v>7.727035045623779</v>
+        <v>7.727034568786621</v>
       </c>
       <c r="C784" t="n">
-        <v>7.900573273715461</v>
+        <v>7.900572786169216</v>
       </c>
       <c r="D784" t="n">
-        <v>7.663100046492482</v>
+        <v>7.663099573600767</v>
       </c>
       <c r="E784" t="n">
-        <v>7.809237685106326</v>
+        <v>7.809237203196422</v>
       </c>
       <c r="F784" t="n">
         <v>6131300</v>
@@ -16112,16 +16112,16 @@
         <v>45377</v>
       </c>
       <c r="B785" t="n">
-        <v>7.891440391540527</v>
+        <v>7.891439914703369</v>
       </c>
       <c r="C785" t="n">
-        <v>8.019310390887984</v>
+        <v>8.019309906324331</v>
       </c>
       <c r="D785" t="n">
-        <v>7.672233060710954</v>
+        <v>7.672232597119311</v>
       </c>
       <c r="E785" t="n">
-        <v>7.727035111180608</v>
+        <v>7.727034644277572</v>
       </c>
       <c r="F785" t="n">
         <v>16047100</v>
@@ -16232,16 +16232,16 @@
         <v>45386</v>
       </c>
       <c r="B791" t="n">
-        <v>7.389091014862061</v>
+        <v>7.389091491699219</v>
       </c>
       <c r="C791" t="n">
-        <v>7.608297457246477</v>
+        <v>7.608297948229594</v>
       </c>
       <c r="D791" t="n">
-        <v>7.352556607797991</v>
+        <v>7.35255708227749</v>
       </c>
       <c r="E791" t="n">
-        <v>7.3799571953338</v>
+        <v>7.379957671581529</v>
       </c>
       <c r="F791" t="n">
         <v>5937900</v>
@@ -16272,16 +16272,16 @@
         <v>45390</v>
       </c>
       <c r="B793" t="n">
-        <v>7.507827758789062</v>
+        <v>7.507828235626221</v>
       </c>
       <c r="C793" t="n">
-        <v>7.608297156481334</v>
+        <v>7.608297639699505</v>
       </c>
       <c r="D793" t="n">
-        <v>7.316021911522771</v>
+        <v>7.316022376177957</v>
       </c>
       <c r="E793" t="n">
-        <v>7.343422497975402</v>
+        <v>7.343422964370853</v>
       </c>
       <c r="F793" t="n">
         <v>6349600</v>
@@ -16352,16 +16352,16 @@
         <v>45394</v>
       </c>
       <c r="B797" t="n">
-        <v>7.3982253074646</v>
+        <v>7.398224830627441</v>
       </c>
       <c r="C797" t="n">
-        <v>7.608297943753701</v>
+        <v>7.608297453376751</v>
       </c>
       <c r="D797" t="n">
-        <v>7.34342325783973</v>
+        <v>7.343422784534725</v>
       </c>
       <c r="E797" t="n">
-        <v>7.507828535665309</v>
+        <v>7.507828051763903</v>
       </c>
       <c r="F797" t="n">
         <v>9274900</v>
@@ -16372,16 +16372,16 @@
         <v>45397</v>
       </c>
       <c r="B798" t="n">
-        <v>6.923276901245117</v>
+        <v>6.923276424407959</v>
       </c>
       <c r="C798" t="n">
-        <v>7.434759488163705</v>
+        <v>7.434758976098444</v>
       </c>
       <c r="D798" t="n">
-        <v>6.850208084692319</v>
+        <v>6.850207612887738</v>
       </c>
       <c r="E798" t="n">
-        <v>7.416491848501004</v>
+        <v>7.416491337693918</v>
       </c>
       <c r="F798" t="n">
         <v>10745000</v>
@@ -16452,16 +16452,16 @@
         <v>45401</v>
       </c>
       <c r="B802" t="n">
-        <v>6.749737739562988</v>
+        <v>6.749738216400146</v>
       </c>
       <c r="C802" t="n">
-        <v>6.877608594495325</v>
+        <v>6.877609080365956</v>
       </c>
       <c r="D802" t="n">
-        <v>6.704069950393841</v>
+        <v>6.704070424004785</v>
       </c>
       <c r="E802" t="n">
-        <v>6.777138761484052</v>
+        <v>6.777139240256963</v>
       </c>
       <c r="F802" t="n">
         <v>8757100</v>
@@ -16592,16 +16592,16 @@
         <v>45412</v>
       </c>
       <c r="B809" t="n">
-        <v>6.493997097015381</v>
+        <v>6.493997573852539</v>
       </c>
       <c r="C809" t="n">
-        <v>6.786272350209661</v>
+        <v>6.786272848507823</v>
       </c>
       <c r="D809" t="n">
-        <v>6.475729893690739</v>
+        <v>6.475730369186584</v>
       </c>
       <c r="E809" t="n">
-        <v>6.749737943560375</v>
+        <v>6.749738439175912</v>
       </c>
       <c r="F809" t="n">
         <v>8369300</v>
@@ -16712,16 +16712,16 @@
         <v>45421</v>
       </c>
       <c r="B815" t="n">
-        <v>7.3982253074646</v>
+        <v>7.398224830627441</v>
       </c>
       <c r="C815" t="n">
-        <v>7.434759716864836</v>
+        <v>7.434759237672929</v>
       </c>
       <c r="D815" t="n">
-        <v>7.233820029639022</v>
+        <v>7.233819563398263</v>
       </c>
       <c r="E815" t="n">
-        <v>7.316022668551811</v>
+        <v>7.316022197012852</v>
       </c>
       <c r="F815" t="n">
         <v>6908300</v>
@@ -16792,16 +16792,16 @@
         <v>45427</v>
       </c>
       <c r="B819" t="n">
-        <v>7.379957675933838</v>
+        <v>7.37995719909668</v>
       </c>
       <c r="C819" t="n">
-        <v>7.453026494820389</v>
+        <v>7.453026013262074</v>
       </c>
       <c r="D819" t="n">
-        <v>7.22468621803766</v>
+        <v>7.224685751232972</v>
       </c>
       <c r="E819" t="n">
-        <v>7.252087242882374</v>
+        <v>7.252086774307239</v>
       </c>
       <c r="F819" t="n">
         <v>4894000</v>
@@ -16932,16 +16932,16 @@
         <v>45436</v>
       </c>
       <c r="B826" t="n">
-        <v>7.453026294708252</v>
+        <v>7.453025817871094</v>
       </c>
       <c r="C826" t="n">
-        <v>7.644832156897759</v>
+        <v>7.644831667789053</v>
       </c>
       <c r="D826" t="n">
-        <v>7.453026294708252</v>
+        <v>7.453025817871094</v>
       </c>
       <c r="E826" t="n">
-        <v>7.635698337019924</v>
+        <v>7.635697848495591</v>
       </c>
       <c r="F826" t="n">
         <v>5755300</v>
@@ -16952,16 +16952,16 @@
         <v>45439</v>
       </c>
       <c r="B827" t="n">
-        <v>7.453026294708252</v>
+        <v>7.453025817871094</v>
       </c>
       <c r="C827" t="n">
-        <v>7.489560703170587</v>
+        <v>7.489560223995992</v>
       </c>
       <c r="D827" t="n">
-        <v>7.34342306932125</v>
+        <v>7.343422599496395</v>
       </c>
       <c r="E827" t="n">
-        <v>7.489560703170587</v>
+        <v>7.489560223995992</v>
       </c>
       <c r="F827" t="n">
         <v>2664100</v>
@@ -17032,16 +17032,16 @@
         <v>45446</v>
       </c>
       <c r="B831" t="n">
-        <v>7.3982253074646</v>
+        <v>7.398224830627441</v>
       </c>
       <c r="C831" t="n">
-        <v>7.644832353153937</v>
+        <v>7.644831860422237</v>
       </c>
       <c r="D831" t="n">
-        <v>7.370823847127651</v>
+        <v>7.370823372056597</v>
       </c>
       <c r="E831" t="n">
-        <v>7.443892665928123</v>
+        <v>7.443892186147571</v>
       </c>
       <c r="F831" t="n">
         <v>4697400</v>
@@ -17052,16 +17052,16 @@
         <v>45447</v>
       </c>
       <c r="B832" t="n">
-        <v>7.133349895477295</v>
+        <v>7.133349418640137</v>
       </c>
       <c r="C832" t="n">
-        <v>7.389091186386852</v>
+        <v>7.389090692454367</v>
       </c>
       <c r="D832" t="n">
-        <v>7.005479467784764</v>
+        <v>7.005478999495256</v>
       </c>
       <c r="E832" t="n">
-        <v>7.389091186386852</v>
+        <v>7.389090692454367</v>
       </c>
       <c r="F832" t="n">
         <v>9916900</v>
@@ -17072,16 +17072,16 @@
         <v>45448</v>
       </c>
       <c r="B833" t="n">
-        <v>6.950677871704102</v>
+        <v>6.950677394866943</v>
       </c>
       <c r="C833" t="n">
-        <v>7.233819751428645</v>
+        <v>7.233819255167113</v>
       </c>
       <c r="D833" t="n">
-        <v>6.850208031955233</v>
+        <v>6.850207562010604</v>
       </c>
       <c r="E833" t="n">
-        <v>7.096815503684641</v>
+        <v>7.096815016822007</v>
       </c>
       <c r="F833" t="n">
         <v>9111500</v>
@@ -17092,16 +17092,16 @@
         <v>45449</v>
       </c>
       <c r="B834" t="n">
-        <v>7.069414138793945</v>
+        <v>7.069414615631104</v>
       </c>
       <c r="C834" t="n">
-        <v>7.133349567462498</v>
+        <v>7.133350048612147</v>
       </c>
       <c r="D834" t="n">
-        <v>6.932410333185509</v>
+        <v>6.93241080078166</v>
       </c>
       <c r="E834" t="n">
-        <v>6.978078123213496</v>
+        <v>6.978078593889973</v>
       </c>
       <c r="F834" t="n">
         <v>8384200</v>
@@ -17132,16 +17132,16 @@
         <v>45453</v>
       </c>
       <c r="B836" t="n">
-        <v>6.923276901245117</v>
+        <v>6.923276424407959</v>
       </c>
       <c r="C836" t="n">
-        <v>6.987212333491066</v>
+        <v>6.987211852250387</v>
       </c>
       <c r="D836" t="n">
-        <v>6.786272652446371</v>
+        <v>6.78627218504531</v>
       </c>
       <c r="E836" t="n">
-        <v>6.941544105383317</v>
+        <v>6.941543627288014</v>
       </c>
       <c r="F836" t="n">
         <v>7457900</v>
@@ -17232,16 +17232,16 @@
         <v>45460</v>
       </c>
       <c r="B841" t="n">
-        <v>6.448329448699951</v>
+        <v>6.448328971862793</v>
       </c>
       <c r="C841" t="n">
-        <v>6.65840252351774</v>
+        <v>6.658402031146226</v>
       </c>
       <c r="D841" t="n">
-        <v>6.448329448699951</v>
+        <v>6.448328971862793</v>
       </c>
       <c r="E841" t="n">
-        <v>6.64013531855639</v>
+        <v>6.640134827535688</v>
       </c>
       <c r="F841" t="n">
         <v>3992100</v>
@@ -17252,16 +17252,16 @@
         <v>45461</v>
       </c>
       <c r="B842" t="n">
-        <v>6.493997097015381</v>
+        <v>6.493997573852539</v>
       </c>
       <c r="C842" t="n">
-        <v>6.557932090889389</v>
+        <v>6.557932572421126</v>
       </c>
       <c r="D842" t="n">
-        <v>6.402661080392169</v>
+        <v>6.402661550522763</v>
       </c>
       <c r="E842" t="n">
-        <v>6.448328870941534</v>
+        <v>6.448329344425394</v>
       </c>
       <c r="F842" t="n">
         <v>3102800</v>
@@ -17312,16 +17312,16 @@
         <v>45464</v>
       </c>
       <c r="B845" t="n">
-        <v>6.850208282470703</v>
+        <v>6.850207805633545</v>
       </c>
       <c r="C845" t="n">
-        <v>6.932410921228196</v>
+        <v>6.932410438668982</v>
       </c>
       <c r="D845" t="n">
-        <v>6.58533359705713</v>
+        <v>6.585333138657673</v>
       </c>
       <c r="E845" t="n">
-        <v>6.694936825050778</v>
+        <v>6.694936359021934</v>
       </c>
       <c r="F845" t="n">
         <v>6960600</v>
@@ -17372,16 +17372,16 @@
         <v>45469</v>
       </c>
       <c r="B848" t="n">
-        <v>7.042014122009277</v>
+        <v>7.042013645172119</v>
       </c>
       <c r="C848" t="n">
-        <v>7.069414711139547</v>
+        <v>7.069414232447009</v>
       </c>
       <c r="D848" t="n">
-        <v>6.731471208369463</v>
+        <v>6.731470752560154</v>
       </c>
       <c r="E848" t="n">
-        <v>6.804540026749534</v>
+        <v>6.804539565992502</v>
       </c>
       <c r="F848" t="n">
         <v>4179500</v>
@@ -17392,16 +17392,16 @@
         <v>45470</v>
       </c>
       <c r="B849" t="n">
-        <v>7.069414138793945</v>
+        <v>7.069414615631104</v>
       </c>
       <c r="C849" t="n">
-        <v>7.124216183666692</v>
+        <v>7.124216664200287</v>
       </c>
       <c r="D849" t="n">
-        <v>6.850207701400866</v>
+        <v>6.85020816345239</v>
       </c>
       <c r="E849" t="n">
-        <v>7.051146935677855</v>
+        <v>7.051147411282877</v>
       </c>
       <c r="F849" t="n">
         <v>6848800</v>
@@ -17492,16 +17492,16 @@
         <v>45477</v>
       </c>
       <c r="B854" t="n">
-        <v>7.991909027099609</v>
+        <v>7.991909503936768</v>
       </c>
       <c r="C854" t="n">
-        <v>8.110646065742392</v>
+        <v>8.110646549663995</v>
       </c>
       <c r="D854" t="n">
-        <v>7.580896737058564</v>
+        <v>7.580897189372679</v>
       </c>
       <c r="E854" t="n">
-        <v>7.580896737058564</v>
+        <v>7.580897189372679</v>
       </c>
       <c r="F854" t="n">
         <v>16897700</v>
@@ -17512,16 +17512,16 @@
         <v>45478</v>
       </c>
       <c r="B855" t="n">
-        <v>8.220249176025391</v>
+        <v>8.220250129699707</v>
       </c>
       <c r="C855" t="n">
-        <v>8.229382995272722</v>
+        <v>8.229383950006699</v>
       </c>
       <c r="D855" t="n">
-        <v>7.845771297374288</v>
+        <v>7.845772207603456</v>
       </c>
       <c r="E855" t="n">
-        <v>7.991908921135797</v>
+        <v>7.99190984831916</v>
       </c>
       <c r="F855" t="n">
         <v>7882000</v>
@@ -17552,16 +17552,16 @@
         <v>45482</v>
       </c>
       <c r="B857" t="n">
-        <v>8.275052070617676</v>
+        <v>8.275051116943359</v>
       </c>
       <c r="C857" t="n">
-        <v>8.293318839940072</v>
+        <v>8.293317884160565</v>
       </c>
       <c r="D857" t="n">
-        <v>8.01931033171185</v>
+        <v>8.019309407510983</v>
       </c>
       <c r="E857" t="n">
-        <v>8.138047380979048</v>
+        <v>8.138046443094101</v>
       </c>
       <c r="F857" t="n">
         <v>6492100</v>
@@ -17612,16 +17612,16 @@
         <v>45485</v>
       </c>
       <c r="B860" t="n">
-        <v>8.357254028320312</v>
+        <v>8.357253074645996</v>
       </c>
       <c r="C860" t="n">
-        <v>8.57646136249438</v>
+        <v>8.576460383805578</v>
       </c>
       <c r="D860" t="n">
-        <v>8.275052257935224</v>
+        <v>8.275051313641228</v>
       </c>
       <c r="E860" t="n">
-        <v>8.57646136249438</v>
+        <v>8.576460383805578</v>
       </c>
       <c r="F860" t="n">
         <v>9959600</v>
@@ -17812,16 +17812,16 @@
         <v>45499</v>
       </c>
       <c r="B870" t="n">
-        <v>8.165447235107422</v>
+        <v>8.165448188781738</v>
       </c>
       <c r="C870" t="n">
-        <v>8.165447235107422</v>
+        <v>8.165448188781738</v>
       </c>
       <c r="D870" t="n">
-        <v>7.891439622605347</v>
+        <v>7.891440544277249</v>
       </c>
       <c r="E870" t="n">
-        <v>8.03757724821951</v>
+        <v>8.037578186959392</v>
       </c>
       <c r="F870" t="n">
         <v>4118500</v>
@@ -17852,16 +17852,16 @@
         <v>45503</v>
       </c>
       <c r="B872" t="n">
-        <v>7.635698318481445</v>
+        <v>7.635697841644287</v>
       </c>
       <c r="C872" t="n">
-        <v>7.781836823024983</v>
+        <v>7.781836337061709</v>
       </c>
       <c r="D872" t="n">
-        <v>7.544362733071863</v>
+        <v>7.544362261938466</v>
       </c>
       <c r="E872" t="n">
-        <v>7.763569183313664</v>
+        <v>7.763568698491175</v>
       </c>
       <c r="F872" t="n">
         <v>8186100</v>
@@ -17872,16 +17872,16 @@
         <v>45504</v>
       </c>
       <c r="B873" t="n">
-        <v>7.882306098937988</v>
+        <v>7.882306575775146</v>
       </c>
       <c r="C873" t="n">
-        <v>7.918840506712075</v>
+        <v>7.91884098575937</v>
       </c>
       <c r="D873" t="n">
-        <v>7.553496428971203</v>
+        <v>7.553496885917143</v>
       </c>
       <c r="E873" t="n">
-        <v>7.663099652293464</v>
+        <v>7.663100115869812</v>
       </c>
       <c r="F873" t="n">
         <v>7542900</v>
@@ -17972,16 +17972,16 @@
         <v>45511</v>
       </c>
       <c r="B878" t="n">
-        <v>7.59916353225708</v>
+        <v>7.599164009094238</v>
       </c>
       <c r="C878" t="n">
-        <v>7.635697938814125</v>
+        <v>7.635698417943767</v>
       </c>
       <c r="D878" t="n">
-        <v>7.398224731717812</v>
+        <v>7.398225195946334</v>
       </c>
       <c r="E878" t="n">
-        <v>7.498694131987445</v>
+        <v>7.498694602520287</v>
       </c>
       <c r="F878" t="n">
         <v>13715500</v>
@@ -17992,16 +17992,16 @@
         <v>45512</v>
       </c>
       <c r="B879" t="n">
-        <v>7.59916353225708</v>
+        <v>7.599164009094238</v>
       </c>
       <c r="C879" t="n">
-        <v>7.763568797288263</v>
+        <v>7.763569284441628</v>
       </c>
       <c r="D879" t="n">
-        <v>7.480426493184443</v>
+        <v>7.480426962571014</v>
       </c>
       <c r="E879" t="n">
-        <v>7.635697938814125</v>
+        <v>7.635698417943767</v>
       </c>
       <c r="F879" t="n">
         <v>7650900</v>
@@ -18012,16 +18012,16 @@
         <v>45513</v>
       </c>
       <c r="B880" t="n">
-        <v>7.745301246643066</v>
+        <v>7.745301723480225</v>
       </c>
       <c r="C880" t="n">
-        <v>7.873172106572643</v>
+        <v>7.873172591282133</v>
       </c>
       <c r="D880" t="n">
-        <v>7.507828036843809</v>
+        <v>7.507828499061</v>
       </c>
       <c r="E880" t="n">
-        <v>7.653965664735343</v>
+        <v>7.653966135949453</v>
       </c>
       <c r="F880" t="n">
         <v>7501500</v>
@@ -18052,16 +18052,16 @@
         <v>45517</v>
       </c>
       <c r="B882" t="n">
-        <v>7.699633598327637</v>
+        <v>7.699634552001953</v>
       </c>
       <c r="C882" t="n">
-        <v>7.800102995919072</v>
+        <v>7.800103962037498</v>
       </c>
       <c r="D882" t="n">
-        <v>7.635697735270417</v>
+        <v>7.635698681025655</v>
       </c>
       <c r="E882" t="n">
-        <v>7.717900365594744</v>
+        <v>7.717901321531577</v>
       </c>
       <c r="F882" t="n">
         <v>7752600</v>
@@ -18072,16 +18072,16 @@
         <v>45518</v>
       </c>
       <c r="B883" t="n">
-        <v>7.59916353225708</v>
+        <v>7.599164009094238</v>
       </c>
       <c r="C883" t="n">
-        <v>7.818370842648312</v>
+        <v>7.81837133324043</v>
       </c>
       <c r="D883" t="n">
-        <v>7.462159725430401</v>
+        <v>7.462160193670757</v>
       </c>
       <c r="E883" t="n">
-        <v>7.763568797288263</v>
+        <v>7.763569284441628</v>
       </c>
       <c r="F883" t="n">
         <v>7383100</v>
@@ -18152,16 +18152,16 @@
         <v>45524</v>
       </c>
       <c r="B887" t="n">
-        <v>7.745301246643066</v>
+        <v>7.745301723480225</v>
       </c>
       <c r="C887" t="n">
-        <v>8.019309734464178</v>
+        <v>8.019310228170587</v>
       </c>
       <c r="D887" t="n">
-        <v>7.69963389121369</v>
+        <v>7.69963436523935</v>
       </c>
       <c r="E887" t="n">
-        <v>7.937107101012947</v>
+        <v>7.937107589658575</v>
       </c>
       <c r="F887" t="n">
         <v>6543300</v>
@@ -18172,16 +18172,16 @@
         <v>45525</v>
       </c>
       <c r="B888" t="n">
-        <v>7.608297824859619</v>
+        <v>7.608297348022461</v>
       </c>
       <c r="C888" t="n">
-        <v>7.854905737744269</v>
+        <v>7.854905245451379</v>
       </c>
       <c r="D888" t="n">
-        <v>7.489560778402085</v>
+        <v>7.489560309006571</v>
       </c>
       <c r="E888" t="n">
-        <v>7.745301640207304</v>
+        <v>7.745301154783664</v>
       </c>
       <c r="F888" t="n">
         <v>7135600</v>
@@ -18192,16 +18192,16 @@
         <v>45526</v>
       </c>
       <c r="B889" t="n">
-        <v>7.279487133026123</v>
+        <v>7.279487609863281</v>
       </c>
       <c r="C889" t="n">
-        <v>7.663099266384561</v>
+        <v>7.663099768349934</v>
       </c>
       <c r="D889" t="n">
-        <v>7.252086546337681</v>
+        <v>7.252087021379985</v>
       </c>
       <c r="E889" t="n">
-        <v>7.571762816024495</v>
+        <v>7.571763312006945</v>
       </c>
       <c r="F889" t="n">
         <v>6992500</v>
@@ -18332,16 +18332,16 @@
         <v>45537</v>
       </c>
       <c r="B896" t="n">
-        <v>6.868475437164307</v>
+        <v>6.868474960327148</v>
       </c>
       <c r="C896" t="n">
-        <v>6.941544255295122</v>
+        <v>6.941543773385233</v>
       </c>
       <c r="D896" t="n">
-        <v>6.795406619033491</v>
+        <v>6.795406147269064</v>
       </c>
       <c r="E896" t="n">
-        <v>6.895876461725617</v>
+        <v>6.895875982986171</v>
       </c>
       <c r="F896" t="n">
         <v>5645700</v>
@@ -18452,16 +18452,16 @@
         <v>45545</v>
       </c>
       <c r="B902" t="n">
-        <v>6.749737739562988</v>
+        <v>6.749738216400146</v>
       </c>
       <c r="C902" t="n">
-        <v>6.868474775346815</v>
+        <v>6.868475260572184</v>
       </c>
       <c r="D902" t="n">
-        <v>6.722337153166394</v>
+        <v>6.722337628067829</v>
       </c>
       <c r="E902" t="n">
-        <v>6.777138761484052</v>
+        <v>6.777139240256963</v>
       </c>
       <c r="F902" t="n">
         <v>6841000</v>
@@ -18532,16 +18532,16 @@
         <v>45551</v>
       </c>
       <c r="B906" t="n">
-        <v>6.694936752319336</v>
+        <v>6.694936275482178</v>
       </c>
       <c r="C906" t="n">
-        <v>6.777139390183809</v>
+        <v>6.777138907491886</v>
       </c>
       <c r="D906" t="n">
-        <v>6.640135138917858</v>
+        <v>6.640134665983865</v>
       </c>
       <c r="E906" t="n">
-        <v>6.70407057231517</v>
+        <v>6.704070094827469</v>
       </c>
       <c r="F906" t="n">
         <v>4229100</v>
@@ -18572,16 +18572,16 @@
         <v>45553</v>
       </c>
       <c r="B908" t="n">
-        <v>6.539664745330811</v>
+        <v>6.539665222167969</v>
       </c>
       <c r="C908" t="n">
-        <v>6.850207630620085</v>
+        <v>6.850208130100359</v>
       </c>
       <c r="D908" t="n">
-        <v>6.493996955774693</v>
+        <v>6.493997429282001</v>
       </c>
       <c r="E908" t="n">
-        <v>6.676668985048106</v>
+        <v>6.676669471874876</v>
       </c>
       <c r="F908" t="n">
         <v>10313100</v>
@@ -18632,16 +18632,16 @@
         <v>45558</v>
       </c>
       <c r="B911" t="n">
-        <v>6.028182506561279</v>
+        <v>6.028182983398438</v>
       </c>
       <c r="C911" t="n">
-        <v>6.064716911680935</v>
+        <v>6.064717391408013</v>
       </c>
       <c r="D911" t="n">
-        <v>5.863777683522827</v>
+        <v>5.863778147355347</v>
       </c>
       <c r="E911" t="n">
-        <v>5.991648101441623</v>
+        <v>5.991648575388862</v>
       </c>
       <c r="F911" t="n">
         <v>7689600</v>
@@ -18712,16 +18712,16 @@
         <v>45562</v>
       </c>
       <c r="B915" t="n">
-        <v>5.93684720993042</v>
+        <v>5.936846733093262</v>
       </c>
       <c r="C915" t="n">
-        <v>6.137786462328047</v>
+        <v>6.137785969351801</v>
       </c>
       <c r="D915" t="n">
-        <v>5.927713389786452</v>
+        <v>5.927712913682906</v>
       </c>
       <c r="E915" t="n">
-        <v>6.037317053891492</v>
+        <v>6.037316568984771</v>
       </c>
       <c r="F915" t="n">
         <v>5348400</v>
@@ -18792,16 +18792,16 @@
         <v>45568</v>
       </c>
       <c r="B919" t="n">
-        <v>5.270093441009521</v>
+        <v>5.270092964172363</v>
       </c>
       <c r="C919" t="n">
-        <v>5.489300327798264</v>
+        <v>5.489299831127303</v>
       </c>
       <c r="D919" t="n">
-        <v>4.941283328588661</v>
+        <v>4.941282881502185</v>
       </c>
       <c r="E919" t="n">
-        <v>5.480166507900002</v>
+        <v>5.480166012055468</v>
       </c>
       <c r="F919" t="n">
         <v>48426200</v>
@@ -19012,16 +19012,16 @@
         <v>45583</v>
       </c>
       <c r="B930" t="n">
-        <v>5.30662727355957</v>
+        <v>5.306627750396729</v>
       </c>
       <c r="C930" t="n">
-        <v>5.379696082716587</v>
+        <v>5.379696566119483</v>
       </c>
       <c r="D930" t="n">
-        <v>5.169623038627936</v>
+        <v>5.169623503154316</v>
       </c>
       <c r="E930" t="n">
-        <v>5.30662727355957</v>
+        <v>5.306627750396729</v>
       </c>
       <c r="F930" t="n">
         <v>9506300</v>
@@ -19072,16 +19072,16 @@
         <v>45588</v>
       </c>
       <c r="B933" t="n">
-        <v>5.735907554626465</v>
+        <v>5.735908031463623</v>
       </c>
       <c r="C933" t="n">
-        <v>5.927712973407171</v>
+        <v>5.927713466189486</v>
       </c>
       <c r="D933" t="n">
-        <v>5.626303898220296</v>
+        <v>5.626304365945888</v>
       </c>
       <c r="E933" t="n">
-        <v>5.626303898220296</v>
+        <v>5.626304365945888</v>
       </c>
       <c r="F933" t="n">
         <v>15384500</v>
@@ -19092,16 +19092,16 @@
         <v>45589</v>
       </c>
       <c r="B934" t="n">
-        <v>5.836376667022705</v>
+        <v>5.836377143859863</v>
       </c>
       <c r="C934" t="n">
-        <v>5.891178274750094</v>
+        <v>5.891178756064592</v>
       </c>
       <c r="D934" t="n">
-        <v>5.589769214487223</v>
+        <v>5.589769671176334</v>
       </c>
       <c r="E934" t="n">
-        <v>5.717640068042261</v>
+        <v>5.717640535178534</v>
       </c>
       <c r="F934" t="n">
         <v>10139400</v>
@@ -19132,16 +19132,16 @@
         <v>45593</v>
       </c>
       <c r="B936" t="n">
-        <v>5.735907554626465</v>
+        <v>5.735908031463623</v>
       </c>
       <c r="C936" t="n">
-        <v>5.836376956005767</v>
+        <v>5.836377441195141</v>
       </c>
       <c r="D936" t="n">
-        <v>5.717640351146184</v>
+        <v>5.717640826464754</v>
       </c>
       <c r="E936" t="n">
-        <v>5.836376956005767</v>
+        <v>5.836377441195141</v>
       </c>
       <c r="F936" t="n">
         <v>5963100</v>
@@ -19192,16 +19192,16 @@
         <v>45596</v>
       </c>
       <c r="B939" t="n">
-        <v>5.745041370391846</v>
+        <v>5.745040893554688</v>
       </c>
       <c r="C939" t="n">
-        <v>5.973381648819262</v>
+        <v>5.973381153029912</v>
       </c>
       <c r="D939" t="n">
-        <v>5.735907985727498</v>
+        <v>5.735907509648409</v>
       </c>
       <c r="E939" t="n">
-        <v>5.827244009993561</v>
+        <v>5.827243526333603</v>
       </c>
       <c r="F939" t="n">
         <v>7246200</v>
@@ -19212,16 +19212,16 @@
         <v>45597</v>
       </c>
       <c r="B940" t="n">
-        <v>5.270093441009521</v>
+        <v>5.270092964172363</v>
       </c>
       <c r="C940" t="n">
-        <v>5.754175007504804</v>
+        <v>5.754174486868027</v>
       </c>
       <c r="D940" t="n">
-        <v>5.22442521256722</v>
+        <v>5.224424739862115</v>
       </c>
       <c r="E940" t="n">
-        <v>5.745041187606541</v>
+        <v>5.745040667796192</v>
       </c>
       <c r="F940" t="n">
         <v>7357000</v>
@@ -19232,16 +19232,16 @@
         <v>45600</v>
       </c>
       <c r="B941" t="n">
-        <v>5.635437965393066</v>
+        <v>5.635437488555908</v>
       </c>
       <c r="C941" t="n">
-        <v>5.681105758338568</v>
+        <v>5.681105277637273</v>
       </c>
       <c r="D941" t="n">
-        <v>5.352296081242743</v>
+        <v>5.352295628363364</v>
       </c>
       <c r="E941" t="n">
-        <v>5.379696669905143</v>
+        <v>5.379696214707288</v>
       </c>
       <c r="F941" t="n">
         <v>6291500</v>
@@ -19252,16 +19252,16 @@
         <v>45601</v>
       </c>
       <c r="B942" t="n">
-        <v>5.617170810699463</v>
+        <v>5.617170333862305</v>
       </c>
       <c r="C942" t="n">
-        <v>5.726774037365669</v>
+        <v>5.726773551224381</v>
       </c>
       <c r="D942" t="n">
-        <v>5.48016655960445</v>
+        <v>5.480166094397473</v>
       </c>
       <c r="E942" t="n">
-        <v>5.635438015143831</v>
+        <v>5.635437536755984</v>
       </c>
       <c r="F942" t="n">
         <v>5341400</v>
@@ -19272,16 +19272,16 @@
         <v>45602</v>
       </c>
       <c r="B943" t="n">
-        <v>5.580636024475098</v>
+        <v>5.580636501312256</v>
       </c>
       <c r="C943" t="n">
-        <v>5.653704837312009</v>
+        <v>5.653705320392528</v>
       </c>
       <c r="D943" t="n">
-        <v>5.35229576659751</v>
+        <v>5.352296223924147</v>
       </c>
       <c r="E943" t="n">
-        <v>5.461898985852877</v>
+        <v>5.461899452544555</v>
       </c>
       <c r="F943" t="n">
         <v>8155700</v>
@@ -19312,16 +19312,16 @@
         <v>45604</v>
       </c>
       <c r="B945" t="n">
-        <v>5.215291976928711</v>
+        <v>5.215291500091553</v>
       </c>
       <c r="C945" t="n">
-        <v>5.270093591307661</v>
+        <v>5.270093109459959</v>
       </c>
       <c r="D945" t="n">
-        <v>5.10568874817081</v>
+        <v>5.105688281354738</v>
       </c>
       <c r="E945" t="n">
-        <v>5.270093591307661</v>
+        <v>5.270093109459959</v>
       </c>
       <c r="F945" t="n">
         <v>10054800</v>
@@ -19332,16 +19332,16 @@
         <v>45607</v>
       </c>
       <c r="B946" t="n">
-        <v>5.206157684326172</v>
+        <v>5.20615816116333</v>
       </c>
       <c r="C946" t="n">
-        <v>5.224424887461459</v>
+        <v>5.224425365971729</v>
       </c>
       <c r="D946" t="n">
-        <v>5.087421081709041</v>
+        <v>5.087421547670997</v>
       </c>
       <c r="E946" t="n">
-        <v>5.169623278055597</v>
+        <v>5.169623751546532</v>
       </c>
       <c r="F946" t="n">
         <v>6986700</v>
@@ -19412,16 +19412,16 @@
         <v>45614</v>
       </c>
       <c r="B950" t="n">
-        <v>5.096554279327393</v>
+        <v>5.096554756164551</v>
       </c>
       <c r="C950" t="n">
-        <v>5.206157494135098</v>
+        <v>5.206157981226809</v>
       </c>
       <c r="D950" t="n">
-        <v>4.977817245523481</v>
+        <v>4.97781771125152</v>
       </c>
       <c r="E950" t="n">
-        <v>5.06001987439149</v>
+        <v>5.060020347810465</v>
       </c>
       <c r="F950" t="n">
         <v>6191300</v>
@@ -19492,16 +19492,16 @@
         <v>45621</v>
       </c>
       <c r="B954" t="n">
-        <v>5.580636024475098</v>
+        <v>5.580636501312256</v>
       </c>
       <c r="C954" t="n">
-        <v>5.653704837312009</v>
+        <v>5.653705320392528</v>
       </c>
       <c r="D954" t="n">
-        <v>5.324894744021429</v>
+        <v>5.324895199006787</v>
       </c>
       <c r="E954" t="n">
-        <v>5.571502205108245</v>
+        <v>5.571502681164964</v>
       </c>
       <c r="F954" t="n">
         <v>8051200</v>
@@ -19552,16 +19552,16 @@
         <v>45624</v>
       </c>
       <c r="B957" t="n">
-        <v>5.270093441009521</v>
+        <v>5.270092964172363</v>
       </c>
       <c r="C957" t="n">
-        <v>5.589769733532121</v>
+        <v>5.589769227770706</v>
       </c>
       <c r="D957" t="n">
-        <v>5.123955806833363</v>
+        <v>5.123955343218713</v>
       </c>
       <c r="E957" t="n">
-        <v>5.516700916444042</v>
+        <v>5.51670041729388</v>
       </c>
       <c r="F957" t="n">
         <v>16639300</v>
@@ -27792,10 +27792,10 @@
         <v>46231</v>
       </c>
       <c r="B1369" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="C1369" t="n">
-        <v>3.29</v>
+        <v>3.37</v>
       </c>
       <c r="D1369" t="n">
         <v>3.19</v>
@@ -27804,7 +27804,7 @@
         <v>3.25</v>
       </c>
       <c r="F1369" t="n">
-        <v>2326600</v>
+        <v>11432200</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -452,16 +452,16 @@
         <v>44229</v>
       </c>
       <c r="B2" t="n">
-        <v>6.844325542449951</v>
+        <v>6.844326019287109</v>
       </c>
       <c r="C2" t="n">
-        <v>7.276819619617557</v>
+        <v>7.276820126586135</v>
       </c>
       <c r="D2" t="n">
-        <v>6.844325542449951</v>
+        <v>6.844326019287109</v>
       </c>
       <c r="E2" t="n">
-        <v>7.094164231854394</v>
+        <v>7.094164726097559</v>
       </c>
       <c r="F2" t="n">
         <v>4750609</v>
@@ -492,16 +492,16 @@
         <v>44231</v>
       </c>
       <c r="B4" t="n">
-        <v>6.88631534576416</v>
+        <v>6.886315822601318</v>
       </c>
       <c r="C4" t="n">
-        <v>7.012283929972458</v>
+        <v>7.012284415532206</v>
       </c>
       <c r="D4" t="n">
-        <v>6.806534620056473</v>
+        <v>6.806535091369281</v>
       </c>
       <c r="E4" t="n">
-        <v>6.919906589382284</v>
+        <v>6.91990706854544</v>
       </c>
       <c r="F4" t="n">
         <v>3650229</v>
@@ -572,16 +572,16 @@
         <v>44237</v>
       </c>
       <c r="B8" t="n">
-        <v>6.928305625915527</v>
+        <v>6.928304672241211</v>
       </c>
       <c r="C8" t="n">
-        <v>7.180243643314912</v>
+        <v>7.18024265496158</v>
       </c>
       <c r="D8" t="n">
-        <v>6.749849225834657</v>
+        <v>6.749848296724684</v>
       </c>
       <c r="E8" t="n">
-        <v>7.180243643314912</v>
+        <v>7.18024265496158</v>
       </c>
       <c r="F8" t="n">
         <v>3511567</v>
@@ -592,16 +592,16 @@
         <v>44238</v>
       </c>
       <c r="B9" t="n">
-        <v>6.963996887207031</v>
+        <v>6.963996410369873</v>
       </c>
       <c r="C9" t="n">
-        <v>7.058473540902132</v>
+        <v>7.058473057595991</v>
       </c>
       <c r="D9" t="n">
-        <v>6.850624090978325</v>
+        <v>6.850623621904003</v>
       </c>
       <c r="E9" t="n">
-        <v>6.928305526523419</v>
+        <v>6.928305052130111</v>
       </c>
       <c r="F9" t="n">
         <v>1655030</v>
@@ -632,16 +632,16 @@
         <v>44244</v>
       </c>
       <c r="B11" t="n">
-        <v>7.274719715118408</v>
+        <v>7.274720668792725</v>
       </c>
       <c r="C11" t="n">
-        <v>7.38809167943809</v>
+        <v>7.388092647974826</v>
       </c>
       <c r="D11" t="n">
-        <v>7.113058970326766</v>
+        <v>7.11305990280828</v>
       </c>
       <c r="E11" t="n">
-        <v>7.117258382965146</v>
+        <v>7.11725931599718</v>
       </c>
       <c r="F11" t="n">
         <v>2613098</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.222233772277832</v>
+        <v>7.222232818603516</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379695135793175</v>
+        <v>7.379694161326558</v>
       </c>
       <c r="D12" t="n">
-        <v>7.138254432522623</v>
+        <v>7.138253489937527</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287317780882985</v>
+        <v>7.28731681861452</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.306213855743408</v>
+        <v>7.30621337890625</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724011249786042</v>
+        <v>7.724010745681502</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050075613595256</v>
+        <v>7.050075153474859</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054275027030914</v>
+        <v>7.054274566636445</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.306213855743408</v>
+        <v>7.30621337890625</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480471247944865</v>
+        <v>7.480470759734867</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243228336770691</v>
+        <v>7.243227864044258</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308312344769346</v>
+        <v>7.308311867795231</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -732,16 +732,16 @@
         <v>44251</v>
       </c>
       <c r="B16" t="n">
-        <v>7.327207088470459</v>
+        <v>7.327208042144775</v>
       </c>
       <c r="C16" t="n">
-        <v>7.556051129077507</v>
+        <v>7.556052112537071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.108860361756294</v>
+        <v>7.108861287011643</v>
       </c>
       <c r="E16" t="n">
-        <v>7.451077178354241</v>
+        <v>7.451078148150898</v>
       </c>
       <c r="F16" t="n">
         <v>1445414</v>
@@ -772,16 +772,16 @@
         <v>44253</v>
       </c>
       <c r="B18" t="n">
-        <v>7.243227958679199</v>
+        <v>7.243227481842041</v>
       </c>
       <c r="C18" t="n">
-        <v>7.480470857469459</v>
+        <v>7.480470365014094</v>
       </c>
       <c r="D18" t="n">
-        <v>6.833828601083652</v>
+        <v>6.833828151198126</v>
       </c>
       <c r="E18" t="n">
-        <v>7.157149323379279</v>
+        <v>7.157148852208861</v>
       </c>
       <c r="F18" t="n">
         <v>1865862</v>
@@ -792,16 +792,16 @@
         <v>44256</v>
       </c>
       <c r="B19" t="n">
-        <v>7.001787185668945</v>
+        <v>7.001787662506104</v>
       </c>
       <c r="C19" t="n">
-        <v>7.390191907873347</v>
+        <v>7.390192411161723</v>
       </c>
       <c r="D19" t="n">
-        <v>7.001787185668945</v>
+        <v>7.001787662506104</v>
       </c>
       <c r="E19" t="n">
-        <v>7.249526585020872</v>
+        <v>7.24952707872963</v>
       </c>
       <c r="F19" t="n">
         <v>1349729</v>
@@ -812,16 +812,16 @@
         <v>44257</v>
       </c>
       <c r="B20" t="n">
-        <v>7.17814302444458</v>
+        <v>7.178143501281738</v>
       </c>
       <c r="C20" t="n">
-        <v>7.17814302444458</v>
+        <v>7.178143501281738</v>
       </c>
       <c r="D20" t="n">
-        <v>6.718355638565471</v>
+        <v>6.718356084859394</v>
       </c>
       <c r="E20" t="n">
-        <v>7.003885663907115</v>
+        <v>7.003886129168523</v>
       </c>
       <c r="F20" t="n">
         <v>1173360</v>
@@ -832,16 +832,16 @@
         <v>44258</v>
       </c>
       <c r="B21" t="n">
-        <v>7.085766792297363</v>
+        <v>7.085767269134521</v>
       </c>
       <c r="C21" t="n">
-        <v>7.108860721672044</v>
+        <v>7.10886120006331</v>
       </c>
       <c r="D21" t="n">
-        <v>6.896812697275568</v>
+        <v>6.896813161397048</v>
       </c>
       <c r="E21" t="n">
-        <v>7.108860721672044</v>
+        <v>7.10886120006331</v>
       </c>
       <c r="F21" t="n">
         <v>1419466</v>
@@ -872,16 +872,16 @@
         <v>44260</v>
       </c>
       <c r="B23" t="n">
-        <v>7.016483783721924</v>
+        <v>7.016483306884766</v>
       </c>
       <c r="C23" t="n">
-        <v>7.176045245164364</v>
+        <v>7.176044757483478</v>
       </c>
       <c r="D23" t="n">
-        <v>7.014383671280806</v>
+        <v>7.01438319458637</v>
       </c>
       <c r="E23" t="n">
-        <v>7.117259144498113</v>
+        <v>7.117258660812305</v>
       </c>
       <c r="F23" t="n">
         <v>1309995</v>
@@ -892,16 +892,16 @@
         <v>44263</v>
       </c>
       <c r="B24" t="n">
-        <v>6.653272151947021</v>
+        <v>6.65327262878418</v>
       </c>
       <c r="C24" t="n">
-        <v>7.016483627501614</v>
+        <v>7.016484130369983</v>
       </c>
       <c r="D24" t="n">
-        <v>6.653272151947021</v>
+        <v>6.65327262878418</v>
       </c>
       <c r="E24" t="n">
-        <v>7.016483627501614</v>
+        <v>7.016484130369983</v>
       </c>
       <c r="F24" t="n">
         <v>1015642</v>
@@ -952,16 +952,16 @@
         <v>44266</v>
       </c>
       <c r="B27" t="n">
-        <v>6.670068740844727</v>
+        <v>6.67006778717041</v>
       </c>
       <c r="C27" t="n">
-        <v>6.670068740844727</v>
+        <v>6.67006778717041</v>
       </c>
       <c r="D27" t="n">
-        <v>6.214480260839943</v>
+        <v>6.21447937230484</v>
       </c>
       <c r="E27" t="n">
-        <v>6.287962692734715</v>
+        <v>6.287961793693228</v>
       </c>
       <c r="F27" t="n">
         <v>2230763</v>
@@ -972,16 +972,16 @@
         <v>44267</v>
       </c>
       <c r="B28" t="n">
-        <v>6.695262432098389</v>
+        <v>6.695262908935547</v>
       </c>
       <c r="C28" t="n">
-        <v>6.896813573576604</v>
+        <v>6.896814064768251</v>
       </c>
       <c r="D28" t="n">
-        <v>6.455920629173074</v>
+        <v>6.455921088964289</v>
       </c>
       <c r="E28" t="n">
-        <v>6.646974454893159</v>
+        <v>6.646974928291244</v>
       </c>
       <c r="F28" t="n">
         <v>3263434</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033279895782471</v>
+        <v>7.033280372619629</v>
       </c>
       <c r="C29" t="n">
-        <v>7.127756543943293</v>
+        <v>7.12775702718571</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1032,16 +1032,16 @@
         <v>44272</v>
       </c>
       <c r="B31" t="n">
-        <v>7.558150768280029</v>
+        <v>7.558151245117188</v>
       </c>
       <c r="C31" t="n">
-        <v>7.642130094981778</v>
+        <v>7.642130577117119</v>
       </c>
       <c r="D31" t="n">
-        <v>7.285217347653489</v>
+        <v>7.285217807271516</v>
       </c>
       <c r="E31" t="n">
-        <v>7.390191303082056</v>
+        <v>7.390191769322798</v>
       </c>
       <c r="F31" t="n">
         <v>5070506</v>
@@ -1052,16 +1052,16 @@
         <v>44273</v>
       </c>
       <c r="B32" t="n">
-        <v>7.589643955230713</v>
+        <v>7.589643001556396</v>
       </c>
       <c r="C32" t="n">
-        <v>7.898268782349795</v>
+        <v>7.898267789895324</v>
       </c>
       <c r="D32" t="n">
-        <v>7.45947593692015</v>
+        <v>7.459474999602055</v>
       </c>
       <c r="E32" t="n">
-        <v>7.600141271314518</v>
+        <v>7.600140316321165</v>
       </c>
       <c r="F32" t="n">
         <v>3661176</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.516162395477295</v>
+        <v>7.516161441802979</v>
       </c>
       <c r="C33" t="n">
-        <v>7.778597720834538</v>
+        <v>7.778596733861603</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430082134541178</v>
+        <v>7.430081191788996</v>
       </c>
       <c r="E33" t="n">
-        <v>7.600140920268824</v>
+        <v>7.600139955939049</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1092,16 +1092,16 @@
         <v>44277</v>
       </c>
       <c r="B34" t="n">
-        <v>7.558150768280029</v>
+        <v>7.558151245117188</v>
       </c>
       <c r="C34" t="n">
-        <v>7.807989447871488</v>
+        <v>7.807989940470752</v>
       </c>
       <c r="D34" t="n">
-        <v>7.201238020951741</v>
+        <v>7.201238475271585</v>
       </c>
       <c r="E34" t="n">
-        <v>7.51406139851813</v>
+        <v>7.514061872573729</v>
       </c>
       <c r="F34" t="n">
         <v>5377429</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.516162395477295</v>
+        <v>7.516161441802979</v>
       </c>
       <c r="C35" t="n">
-        <v>7.55815165787306</v>
+        <v>7.558150698871014</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436381660412942</v>
+        <v>7.436380716861456</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511962982160976</v>
+        <v>7.511962029019494</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159248828887939</v>
+        <v>7.159248352050781</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656827760317221</v>
+        <v>7.656827250339138</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159248828887939</v>
+        <v>7.159248352050781</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392292321128197</v>
+        <v>7.392291828769327</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.70511531829834</v>
+        <v>7.705114364624023</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789095471368375</v>
+        <v>7.789094507299701</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033280588094989</v>
+        <v>7.033279717574721</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159249194110809</v>
+        <v>7.159248307999206</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1232,16 +1232,16 @@
         <v>44286</v>
       </c>
       <c r="B41" t="n">
-        <v>7.348202228546143</v>
+        <v>7.348202705383301</v>
       </c>
       <c r="C41" t="n">
-        <v>7.379694172420294</v>
+        <v>7.379694651301018</v>
       </c>
       <c r="D41" t="n">
-        <v>6.997588185825906</v>
+        <v>6.997588639911132</v>
       </c>
       <c r="E41" t="n">
-        <v>7.226432242387128</v>
+        <v>7.226432711322428</v>
       </c>
       <c r="F41" t="n">
         <v>2544984</v>
@@ -1252,16 +1252,16 @@
         <v>44287</v>
       </c>
       <c r="B42" t="n">
-        <v>7.348202228546143</v>
+        <v>7.348202705383301</v>
       </c>
       <c r="C42" t="n">
-        <v>7.524558900189283</v>
+        <v>7.524559388470522</v>
       </c>
       <c r="D42" t="n">
-        <v>7.171845556903002</v>
+        <v>7.171846022296081</v>
       </c>
       <c r="E42" t="n">
-        <v>7.35869954317086</v>
+        <v>7.358700020689207</v>
       </c>
       <c r="F42" t="n">
         <v>877384</v>
@@ -1272,16 +1272,16 @@
         <v>44291</v>
       </c>
       <c r="B43" t="n">
-        <v>7.327207088470459</v>
+        <v>7.327208042144775</v>
       </c>
       <c r="C43" t="n">
-        <v>7.400689097515077</v>
+        <v>7.400690060753461</v>
       </c>
       <c r="D43" t="n">
-        <v>7.260022980684908</v>
+        <v>7.260023925614861</v>
       </c>
       <c r="E43" t="n">
-        <v>7.400689097515077</v>
+        <v>7.400690060753461</v>
       </c>
       <c r="F43" t="n">
         <v>1080107</v>
@@ -1312,16 +1312,16 @@
         <v>44293</v>
       </c>
       <c r="B45" t="n">
-        <v>7.243227958679199</v>
+        <v>7.243227481842041</v>
       </c>
       <c r="C45" t="n">
-        <v>7.388092696447584</v>
+        <v>7.388092210073672</v>
       </c>
       <c r="D45" t="n">
-        <v>7.146652008029977</v>
+        <v>7.146651537550619</v>
       </c>
       <c r="E45" t="n">
-        <v>7.213835313342242</v>
+        <v>7.213834838440065</v>
       </c>
       <c r="F45" t="n">
         <v>1401221</v>
@@ -1332,16 +1332,16 @@
         <v>44294</v>
       </c>
       <c r="B46" t="n">
-        <v>7.589643955230713</v>
+        <v>7.589643001556396</v>
       </c>
       <c r="C46" t="n">
-        <v>7.789095396206844</v>
+        <v>7.78909441747052</v>
       </c>
       <c r="D46" t="n">
-        <v>7.215935930750956</v>
+        <v>7.215935024034804</v>
       </c>
       <c r="E46" t="n">
-        <v>7.243228465492086</v>
+        <v>7.2432275553465</v>
       </c>
       <c r="F46" t="n">
         <v>2111967</v>
@@ -1452,16 +1452,16 @@
         <v>44302</v>
       </c>
       <c r="B52" t="n">
-        <v>8.187995910644531</v>
+        <v>8.187996864318848</v>
       </c>
       <c r="C52" t="n">
-        <v>8.25098141876933</v>
+        <v>8.25098237977971</v>
       </c>
       <c r="D52" t="n">
-        <v>8.091419971587269</v>
+        <v>8.09142091401317</v>
       </c>
       <c r="E52" t="n">
-        <v>8.1124145997659</v>
+        <v>8.112415544637091</v>
       </c>
       <c r="F52" t="n">
         <v>1067133</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208991050720215</v>
+        <v>8.208992004394531</v>
       </c>
       <c r="C53" t="n">
-        <v>8.244682407926204</v>
+        <v>8.24468336574694</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059928531921125</v>
+        <v>8.059929468278197</v>
       </c>
       <c r="E53" t="n">
-        <v>8.1879964212324</v>
+        <v>8.187997372467679</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1492,16 +1492,16 @@
         <v>44306</v>
       </c>
       <c r="B54" t="n">
-        <v>8.196395874023438</v>
+        <v>8.196394920349121</v>
       </c>
       <c r="C54" t="n">
-        <v>8.244683038461606</v>
+        <v>8.244682079168939</v>
       </c>
       <c r="D54" t="n">
-        <v>8.078823666875394</v>
+        <v>8.078822726880942</v>
       </c>
       <c r="E54" t="n">
-        <v>8.206893189570158</v>
+        <v>8.206892234674447</v>
       </c>
       <c r="F54" t="n">
         <v>282595</v>
@@ -1512,16 +1512,16 @@
         <v>44308</v>
       </c>
       <c r="B55" t="n">
-        <v>8.183797836303711</v>
+        <v>8.183796882629395</v>
       </c>
       <c r="C55" t="n">
-        <v>8.370652636858729</v>
+        <v>8.37065166140985</v>
       </c>
       <c r="D55" t="n">
-        <v>8.06412714911432</v>
+        <v>8.064126209385469</v>
       </c>
       <c r="E55" t="n">
-        <v>8.259379152045536</v>
+        <v>8.259378189563577</v>
       </c>
       <c r="F55" t="n">
         <v>608979</v>
@@ -1532,16 +1532,16 @@
         <v>44309</v>
       </c>
       <c r="B56" t="n">
-        <v>8.187995910644531</v>
+        <v>8.187996864318848</v>
       </c>
       <c r="C56" t="n">
-        <v>8.21948866470693</v>
+        <v>8.219489622049279</v>
       </c>
       <c r="D56" t="n">
-        <v>7.923460510774868</v>
+        <v>7.923461433638152</v>
       </c>
       <c r="E56" t="n">
-        <v>8.215290063788986</v>
+        <v>8.215291020642315</v>
       </c>
       <c r="F56" t="n">
         <v>1129166</v>
@@ -1552,16 +1552,16 @@
         <v>44312</v>
       </c>
       <c r="B57" t="n">
-        <v>7.978049278259277</v>
+        <v>7.978047370910645</v>
       </c>
       <c r="C57" t="n">
-        <v>8.187997217134104</v>
+        <v>8.18799525959226</v>
       </c>
       <c r="D57" t="n">
-        <v>7.938158504201501</v>
+        <v>7.938156606389738</v>
       </c>
       <c r="E57" t="n">
-        <v>8.185898728134749</v>
+        <v>8.185896771094599</v>
       </c>
       <c r="F57" t="n">
         <v>1270667</v>
@@ -1572,16 +1572,16 @@
         <v>44313</v>
       </c>
       <c r="B58" t="n">
-        <v>8.116613388061523</v>
+        <v>8.116615295410156</v>
       </c>
       <c r="C58" t="n">
-        <v>8.183796680141354</v>
+        <v>8.1837986032776</v>
       </c>
       <c r="D58" t="n">
-        <v>7.940256738980475</v>
+        <v>7.9402586048865</v>
       </c>
       <c r="E58" t="n">
-        <v>7.999042018076027</v>
+        <v>7.999043897796192</v>
       </c>
       <c r="F58" t="n">
         <v>2786224</v>
@@ -1612,16 +1612,16 @@
         <v>44315</v>
       </c>
       <c r="B60" t="n">
-        <v>8.607893943786621</v>
+        <v>8.607894897460938</v>
       </c>
       <c r="C60" t="n">
-        <v>8.815743374956226</v>
+        <v>8.815744351658321</v>
       </c>
       <c r="D60" t="n">
-        <v>8.167001850598284</v>
+        <v>8.167002755425871</v>
       </c>
       <c r="E60" t="n">
-        <v>8.469327926938387</v>
+        <v>8.469328865260882</v>
       </c>
       <c r="F60" t="n">
         <v>3250459</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849335670471191</v>
+        <v>8.849334716796875</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122269135355927</v>
+        <v>9.122268152268145</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641487026423638</v>
+        <v>8.641486095148732</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733864381954685</v>
+        <v>8.733863440724466</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1692,16 +1692,16 @@
         <v>44321</v>
       </c>
       <c r="B64" t="n">
-        <v>9.78360652923584</v>
+        <v>9.783605575561523</v>
       </c>
       <c r="C64" t="n">
-        <v>9.99355526824108</v>
+        <v>9.993554294101639</v>
       </c>
       <c r="D64" t="n">
-        <v>9.273431815950246</v>
+        <v>9.273430912006111</v>
       </c>
       <c r="E64" t="n">
-        <v>9.298625047667027</v>
+        <v>9.298624141267135</v>
       </c>
       <c r="F64" t="n">
         <v>3818084</v>
@@ -1712,16 +1712,16 @@
         <v>44322</v>
       </c>
       <c r="B65" t="n">
-        <v>9.764711380004883</v>
+        <v>9.764712333679199</v>
       </c>
       <c r="C65" t="n">
-        <v>9.783605896673567</v>
+        <v>9.783606852193223</v>
       </c>
       <c r="D65" t="n">
-        <v>9.537965814857868</v>
+        <v>9.537966746386992</v>
       </c>
       <c r="E65" t="n">
-        <v>9.783605896673567</v>
+        <v>9.783606852193223</v>
       </c>
       <c r="F65" t="n">
         <v>8042425</v>
@@ -1732,16 +1732,16 @@
         <v>44323</v>
       </c>
       <c r="B66" t="n">
-        <v>9.867586135864258</v>
+        <v>9.867585182189941</v>
       </c>
       <c r="C66" t="n">
-        <v>10.05234164827144</v>
+        <v>10.05234067674103</v>
       </c>
       <c r="D66" t="n">
-        <v>9.554763537058646</v>
+        <v>9.554762613617749</v>
       </c>
       <c r="E66" t="n">
-        <v>9.827696174712075</v>
+        <v>9.827695224893009</v>
       </c>
       <c r="F66" t="n">
         <v>7085572</v>
@@ -1772,16 +1772,16 @@
         <v>44327</v>
       </c>
       <c r="B68" t="n">
-        <v>9.617746353149414</v>
+        <v>9.61774730682373</v>
       </c>
       <c r="C68" t="n">
-        <v>9.645040506833098</v>
+        <v>9.645041463213841</v>
       </c>
       <c r="D68" t="n">
-        <v>8.964807071897692</v>
+        <v>8.964807960828002</v>
       </c>
       <c r="E68" t="n">
-        <v>9.294426475068693</v>
+        <v>9.294427396683329</v>
       </c>
       <c r="F68" t="n">
         <v>2188597</v>
@@ -1792,16 +1792,16 @@
         <v>44328</v>
       </c>
       <c r="B69" t="n">
-        <v>9.531667709350586</v>
+        <v>9.531668663024902</v>
       </c>
       <c r="C69" t="n">
-        <v>9.743715730787388</v>
+        <v>9.743716705677796</v>
       </c>
       <c r="D69" t="n">
-        <v>9.321718988410458</v>
+        <v>9.321719921078722</v>
       </c>
       <c r="E69" t="n">
-        <v>9.563159652184094</v>
+        <v>9.563160609009282</v>
       </c>
       <c r="F69" t="n">
         <v>1563804</v>
@@ -1812,16 +1812,16 @@
         <v>44329</v>
       </c>
       <c r="B70" t="n">
-        <v>9.655538558959961</v>
+        <v>9.655539512634277</v>
       </c>
       <c r="C70" t="n">
-        <v>9.699627931810785</v>
+        <v>9.699628889839794</v>
       </c>
       <c r="D70" t="n">
-        <v>9.489679194450057</v>
+        <v>9.489680131742498</v>
       </c>
       <c r="E70" t="n">
-        <v>9.556862498159457</v>
+        <v>9.556863442087572</v>
       </c>
       <c r="F70" t="n">
         <v>2493897</v>
@@ -1832,16 +1832,16 @@
         <v>44330</v>
       </c>
       <c r="B71" t="n">
-        <v>9.626145362854004</v>
+        <v>9.626143455505371</v>
       </c>
       <c r="C71" t="n">
-        <v>9.657638120796779</v>
+        <v>9.657636207208093</v>
       </c>
       <c r="D71" t="n">
-        <v>9.273431994097892</v>
+        <v>9.273430156636772</v>
       </c>
       <c r="E71" t="n">
-        <v>9.655538820079142</v>
+        <v>9.655536906906416</v>
       </c>
       <c r="F71" t="n">
         <v>1271072</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.82349681854248</v>
+        <v>9.823495864868164</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272898361439</v>
+        <v>10.10272800283195</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334317531017494</v>
+        <v>9.334316624833162</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678632890034629</v>
+        <v>9.678631950423839</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1952,16 +1952,16 @@
         <v>44340</v>
       </c>
       <c r="B77" t="n">
-        <v>10.18250846862793</v>
+        <v>10.18250942230225</v>
       </c>
       <c r="C77" t="n">
-        <v>10.39035788841617</v>
+        <v>10.39035886155727</v>
       </c>
       <c r="D77" t="n">
-        <v>9.951565119860142</v>
+        <v>9.951566051904743</v>
       </c>
       <c r="E77" t="n">
-        <v>10.15731442736386</v>
+        <v>10.15731537867855</v>
       </c>
       <c r="F77" t="n">
         <v>3407772</v>
@@ -1992,16 +1992,16 @@
         <v>44342</v>
       </c>
       <c r="B79" t="n">
-        <v>10.49743175506592</v>
+        <v>10.49743270874023</v>
       </c>
       <c r="C79" t="n">
-        <v>10.51842719657374</v>
+        <v>10.51842815215546</v>
       </c>
       <c r="D79" t="n">
-        <v>10.31897577891374</v>
+        <v>10.31897671637563</v>
       </c>
       <c r="E79" t="n">
-        <v>10.42395055106932</v>
+        <v>10.423951498068</v>
       </c>
       <c r="F79" t="n">
         <v>2052367</v>
@@ -2032,16 +2032,16 @@
         <v>44344</v>
       </c>
       <c r="B81" t="n">
-        <v>10.7283763885498</v>
+        <v>10.72837543487549</v>
       </c>
       <c r="C81" t="n">
-        <v>10.82915175200188</v>
+        <v>10.82915078936937</v>
       </c>
       <c r="D81" t="n">
-        <v>10.46803955941845</v>
+        <v>10.46803862888618</v>
       </c>
       <c r="E81" t="n">
-        <v>10.65489436961172</v>
+        <v>10.65489342246942</v>
       </c>
       <c r="F81" t="n">
         <v>2512953</v>
@@ -2052,16 +2052,16 @@
         <v>44347</v>
       </c>
       <c r="B82" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727737426758</v>
       </c>
       <c r="C82" t="n">
-        <v>11.3960123574381</v>
+        <v>11.39601138073167</v>
       </c>
       <c r="D82" t="n">
-        <v>10.70738084874532</v>
+        <v>10.70737993105873</v>
       </c>
       <c r="E82" t="n">
-        <v>10.7493709213828</v>
+        <v>10.74937000009741</v>
       </c>
       <c r="F82" t="n">
         <v>1849644</v>
@@ -2072,16 +2072,16 @@
         <v>44348</v>
       </c>
       <c r="B83" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727737426758</v>
       </c>
       <c r="C83" t="n">
-        <v>11.25324773405977</v>
+        <v>11.25324676958913</v>
       </c>
       <c r="D83" t="n">
-        <v>11.03280086745621</v>
+        <v>11.03279992187918</v>
       </c>
       <c r="E83" t="n">
-        <v>11.23225229184377</v>
+        <v>11.23225132917255</v>
       </c>
       <c r="F83" t="n">
         <v>1761257</v>
@@ -2112,16 +2112,16 @@
         <v>44351</v>
       </c>
       <c r="B85" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727737426758</v>
       </c>
       <c r="C85" t="n">
-        <v>11.1419742445191</v>
+        <v>11.14197328958526</v>
       </c>
       <c r="D85" t="n">
-        <v>10.6569935733749</v>
+        <v>10.6569926600068</v>
       </c>
       <c r="E85" t="n">
-        <v>10.93832503055962</v>
+        <v>10.93832409307973</v>
       </c>
       <c r="F85" t="n">
         <v>2427404</v>
@@ -2132,16 +2132,16 @@
         <v>44354</v>
       </c>
       <c r="B86" t="n">
-        <v>11.10838317871094</v>
+        <v>11.10838413238525</v>
       </c>
       <c r="C86" t="n">
-        <v>11.61225999957573</v>
+        <v>11.61226099650877</v>
       </c>
       <c r="D86" t="n">
-        <v>10.89843524749561</v>
+        <v>10.89843618314553</v>
       </c>
       <c r="E86" t="n">
-        <v>11.14407453808413</v>
+        <v>11.14407549482261</v>
       </c>
       <c r="F86" t="n">
         <v>2940293</v>
@@ -2232,16 +2232,16 @@
         <v>44361</v>
       </c>
       <c r="B91" t="n">
-        <v>10.94252395629883</v>
+        <v>10.94252300262451</v>
       </c>
       <c r="C91" t="n">
-        <v>11.24904946615247</v>
+        <v>11.24904848576352</v>
       </c>
       <c r="D91" t="n">
-        <v>10.64649657376166</v>
+        <v>10.64649564588704</v>
       </c>
       <c r="E91" t="n">
-        <v>10.72837660898603</v>
+        <v>10.72837567397531</v>
       </c>
       <c r="F91" t="n">
         <v>2250630</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462299346924</v>
+        <v>10.94462203979492</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192304724218</v>
+        <v>11.35192205807723</v>
       </c>
       <c r="D92" t="n">
-        <v>10.81445498526105</v>
+        <v>10.8144540429291</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152825044157</v>
+        <v>10.92152729877964</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2272,16 +2272,16 @@
         <v>44363</v>
       </c>
       <c r="B93" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727737426758</v>
       </c>
       <c r="C93" t="n">
-        <v>11.31413313643548</v>
+        <v>11.31413216674658</v>
       </c>
       <c r="D93" t="n">
-        <v>10.89213554476112</v>
+        <v>10.89213461123995</v>
       </c>
       <c r="E93" t="n">
-        <v>10.96141896166432</v>
+        <v>10.96141802220514</v>
       </c>
       <c r="F93" t="n">
         <v>2948808</v>
@@ -2312,16 +2312,16 @@
         <v>44365</v>
       </c>
       <c r="B95" t="n">
-        <v>11.33722686767578</v>
+        <v>11.3372278213501</v>
       </c>
       <c r="C95" t="n">
-        <v>11.33722686767578</v>
+        <v>11.3372278213501</v>
       </c>
       <c r="D95" t="n">
-        <v>10.99291071350208</v>
+        <v>10.99291163821293</v>
       </c>
       <c r="E95" t="n">
-        <v>11.31203282453744</v>
+        <v>11.31203377609247</v>
       </c>
       <c r="F95" t="n">
         <v>1275938</v>
@@ -2332,16 +2332,16 @@
         <v>44368</v>
       </c>
       <c r="B96" t="n">
-        <v>11.24274921417236</v>
+        <v>11.24274826049805</v>
       </c>
       <c r="C96" t="n">
-        <v>11.40441078522868</v>
+        <v>11.4044098178413</v>
       </c>
       <c r="D96" t="n">
-        <v>11.1524711700025</v>
+        <v>11.15247022398609</v>
       </c>
       <c r="E96" t="n">
-        <v>11.34562468559051</v>
+        <v>11.34562372318971</v>
       </c>
       <c r="F96" t="n">
         <v>1065511</v>
@@ -2352,16 +2352,16 @@
         <v>44369</v>
       </c>
       <c r="B97" t="n">
-        <v>11.28473949432373</v>
+        <v>11.28474044799805</v>
       </c>
       <c r="C97" t="n">
-        <v>11.42330632585396</v>
+        <v>11.42330729123857</v>
       </c>
       <c r="D97" t="n">
-        <v>11.16297031516165</v>
+        <v>11.16297125854524</v>
       </c>
       <c r="E97" t="n">
-        <v>11.23855163287302</v>
+        <v>11.238552582644</v>
       </c>
       <c r="F97" t="n">
         <v>1033076</v>
@@ -2412,16 +2412,16 @@
         <v>44372</v>
       </c>
       <c r="B100" t="n">
-        <v>11.61225891113281</v>
+        <v>11.61226081848145</v>
       </c>
       <c r="C100" t="n">
-        <v>11.71933297921609</v>
+        <v>11.71933490415196</v>
       </c>
       <c r="D100" t="n">
-        <v>11.34142479014375</v>
+        <v>11.34142665300706</v>
       </c>
       <c r="E100" t="n">
-        <v>11.71093496533929</v>
+        <v>11.71093688889577</v>
       </c>
       <c r="F100" t="n">
         <v>3580087</v>
@@ -2432,16 +2432,16 @@
         <v>44375</v>
       </c>
       <c r="B101" t="n">
-        <v>11.86209869384766</v>
+        <v>11.86209774017334</v>
       </c>
       <c r="C101" t="n">
-        <v>12.00066471799965</v>
+        <v>12.00066375318507</v>
       </c>
       <c r="D101" t="n">
-        <v>11.40441135990023</v>
+        <v>11.40441044302249</v>
       </c>
       <c r="E101" t="n">
-        <v>11.58916605876955</v>
+        <v>11.58916512703814</v>
       </c>
       <c r="F101" t="n">
         <v>1601511</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.01746082305908</v>
+        <v>12.01745986938477</v>
       </c>
       <c r="C102" t="n">
-        <v>12.01746082305908</v>
+        <v>12.01745986938477</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916534895242</v>
+        <v>11.58916442926651</v>
       </c>
       <c r="E102" t="n">
-        <v>11.85999866672677</v>
+        <v>11.85999772554824</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2572,16 +2572,16 @@
         <v>44384</v>
       </c>
       <c r="B108" t="n">
-        <v>13.22676658630371</v>
+        <v>13.22676563262939</v>
       </c>
       <c r="C108" t="n">
-        <v>13.31074511346494</v>
+        <v>13.31074415373561</v>
       </c>
       <c r="D108" t="n">
-        <v>13.05040908152244</v>
+        <v>13.05040814056382</v>
       </c>
       <c r="E108" t="n">
-        <v>13.05880709659748</v>
+        <v>13.05880615503335</v>
       </c>
       <c r="F108" t="n">
         <v>2057638</v>
@@ -2592,16 +2592,16 @@
         <v>44385</v>
       </c>
       <c r="B109" t="n">
-        <v>13.05880546569824</v>
+        <v>13.05880641937256</v>
       </c>
       <c r="C109" t="n">
-        <v>13.61097022010407</v>
+        <v>13.61097121410255</v>
       </c>
       <c r="D109" t="n">
-        <v>13.00631808098297</v>
+        <v>13.00631903082418</v>
       </c>
       <c r="E109" t="n">
-        <v>13.09659531112451</v>
+        <v>13.09659626755859</v>
       </c>
       <c r="F109" t="n">
         <v>8587750</v>
@@ -2612,16 +2612,16 @@
         <v>44389</v>
       </c>
       <c r="B110" t="n">
-        <v>13.3317403793335</v>
+        <v>13.33173942565918</v>
       </c>
       <c r="C110" t="n">
-        <v>13.79572644412283</v>
+        <v>13.79572545725768</v>
       </c>
       <c r="D110" t="n">
-        <v>13.07140353906678</v>
+        <v>13.07140260401543</v>
       </c>
       <c r="E110" t="n">
-        <v>13.19107423754762</v>
+        <v>13.19107329393574</v>
       </c>
       <c r="F110" t="n">
         <v>8663568</v>
@@ -2632,16 +2632,16 @@
         <v>44390</v>
       </c>
       <c r="B111" t="n">
-        <v>13.27295398712158</v>
+        <v>13.27295303344727</v>
       </c>
       <c r="C111" t="n">
-        <v>13.49759946187835</v>
+        <v>13.49759849206305</v>
       </c>
       <c r="D111" t="n">
-        <v>13.13438796092353</v>
+        <v>13.13438701720531</v>
       </c>
       <c r="E111" t="n">
-        <v>13.33174009059002</v>
+        <v>13.33173913269187</v>
       </c>
       <c r="F111" t="n">
         <v>2696620</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C114" t="n">
-        <v>13.93849238737042</v>
+        <v>13.9384904687512</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969953991438</v>
+        <v>13.49969768169454</v>
       </c>
       <c r="E114" t="n">
-        <v>13.6424649876205</v>
+        <v>13.64246310974914</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501629145801</v>
+        <v>14.24501433064608</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969953991438</v>
+        <v>13.49969768169454</v>
       </c>
       <c r="E115" t="n">
-        <v>13.74953744981087</v>
+        <v>13.7495355572011</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103643972576</v>
+        <v>14.16103739980534</v>
       </c>
       <c r="D116" t="n">
-        <v>13.77473102080758</v>
+        <v>13.7747319546967</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059038615415</v>
+        <v>13.94059133128809</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2752,16 +2752,16 @@
         <v>44398</v>
       </c>
       <c r="B117" t="n">
-        <v>14.31849956512451</v>
+        <v>14.3184986114502</v>
       </c>
       <c r="C117" t="n">
-        <v>14.34789140009018</v>
+        <v>14.34789044445824</v>
       </c>
       <c r="D117" t="n">
-        <v>14.01617264709314</v>
+        <v>14.01617171355511</v>
       </c>
       <c r="E117" t="n">
-        <v>14.06866003817584</v>
+        <v>14.06865910114192</v>
       </c>
       <c r="F117" t="n">
         <v>2316312</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.99873161315918</v>
+        <v>14.99873065948486</v>
       </c>
       <c r="C118" t="n">
-        <v>15.01132904037419</v>
+        <v>15.01132808589888</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36048740382685</v>
+        <v>14.36048649073444</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36048740382685</v>
+        <v>14.36048649073444</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801319122314</v>
+        <v>15.06801414489746</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127674547757</v>
+        <v>15.22127770885214</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92944798816965</v>
+        <v>14.92944893307399</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127674547757</v>
+        <v>15.22127770885214</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2832,16 +2832,16 @@
         <v>44404</v>
       </c>
       <c r="B121" t="n">
-        <v>14.54943943023682</v>
+        <v>14.54944133758545</v>
       </c>
       <c r="C121" t="n">
-        <v>15.05961489326427</v>
+        <v>15.059616867494</v>
       </c>
       <c r="D121" t="n">
-        <v>14.45076419245981</v>
+        <v>14.45076608687268</v>
       </c>
       <c r="E121" t="n">
-        <v>14.87486022024207</v>
+        <v>14.87486217025152</v>
       </c>
       <c r="F121" t="n">
         <v>2070206</v>
@@ -2852,16 +2852,16 @@
         <v>44405</v>
       </c>
       <c r="B122" t="n">
-        <v>15.08690929412842</v>
+        <v>15.08691120147705</v>
       </c>
       <c r="C122" t="n">
-        <v>15.36823990913394</v>
+        <v>15.36824185204953</v>
       </c>
       <c r="D122" t="n">
-        <v>14.03716489771841</v>
+        <v>14.03716667235407</v>
       </c>
       <c r="E122" t="n">
-        <v>15.13519645180589</v>
+        <v>15.13519836525918</v>
       </c>
       <c r="F122" t="n">
         <v>6581198</v>
@@ -2872,16 +2872,16 @@
         <v>44406</v>
       </c>
       <c r="B123" t="n">
-        <v>15.28426170349121</v>
+        <v>15.28426265716553</v>
       </c>
       <c r="C123" t="n">
-        <v>15.32415166438117</v>
+        <v>15.32415262054446</v>
       </c>
       <c r="D123" t="n">
-        <v>14.85386771299919</v>
+        <v>14.85386863981871</v>
       </c>
       <c r="E123" t="n">
-        <v>15.09950700409309</v>
+        <v>15.09950794623948</v>
       </c>
       <c r="F123" t="n">
         <v>6067903</v>
@@ -2892,16 +2892,16 @@
         <v>44407</v>
       </c>
       <c r="B124" t="n">
-        <v>15.45431900024414</v>
+        <v>15.45431709289551</v>
       </c>
       <c r="C124" t="n">
-        <v>15.94140058333477</v>
+        <v>15.94139861587127</v>
       </c>
       <c r="D124" t="n">
-        <v>14.96933834137266</v>
+        <v>14.96933649387961</v>
       </c>
       <c r="E124" t="n">
-        <v>15.28006243564328</v>
+        <v>15.28006054980113</v>
       </c>
       <c r="F124" t="n">
         <v>3070441</v>
@@ -2932,16 +2932,16 @@
         <v>44411</v>
       </c>
       <c r="B126" t="n">
-        <v>15.20448112487793</v>
+        <v>15.20448207855225</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39343441755661</v>
+        <v>15.39343538308269</v>
       </c>
       <c r="D126" t="n">
-        <v>14.761489725604</v>
+        <v>14.76149065149246</v>
       </c>
       <c r="E126" t="n">
-        <v>15.39343441755661</v>
+        <v>15.39343538308269</v>
       </c>
       <c r="F126" t="n">
         <v>3496971</v>
@@ -2952,16 +2952,16 @@
         <v>44412</v>
       </c>
       <c r="B127" t="n">
-        <v>14.73839473724365</v>
+        <v>14.73839569091797</v>
       </c>
       <c r="C127" t="n">
-        <v>15.32205228991032</v>
+        <v>15.32205328135125</v>
       </c>
       <c r="D127" t="n">
-        <v>14.73839473724365</v>
+        <v>14.73839569091797</v>
       </c>
       <c r="E127" t="n">
-        <v>15.18768567924637</v>
+        <v>15.18768666199287</v>
       </c>
       <c r="F127" t="n">
         <v>2159810</v>
@@ -2972,16 +2972,16 @@
         <v>44413</v>
       </c>
       <c r="B128" t="n">
-        <v>14.17153358459473</v>
+        <v>14.17153453826904</v>
       </c>
       <c r="C128" t="n">
-        <v>14.82237357326046</v>
+        <v>14.82237457073309</v>
       </c>
       <c r="D128" t="n">
-        <v>14.17153358459473</v>
+        <v>14.17153453826904</v>
       </c>
       <c r="E128" t="n">
-        <v>14.61662426223638</v>
+        <v>14.61662524586311</v>
       </c>
       <c r="F128" t="n">
         <v>2928535</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893713905431</v>
+        <v>14.15893809899156</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462098074336</v>
+        <v>13.81462191733692</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351631037553</v>
+        <v>13.83351724825013</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3072,16 +3072,16 @@
         <v>44420</v>
       </c>
       <c r="B133" t="n">
-        <v>13.68025398254395</v>
+        <v>13.68025588989258</v>
       </c>
       <c r="C133" t="n">
-        <v>14.21142412135836</v>
+        <v>14.21142610276459</v>
       </c>
       <c r="D133" t="n">
-        <v>13.64666192558043</v>
+        <v>13.64666382824554</v>
       </c>
       <c r="E133" t="n">
-        <v>13.82511871345597</v>
+        <v>13.82512064100215</v>
       </c>
       <c r="F133" t="n">
         <v>1819641</v>
@@ -3092,16 +3092,16 @@
         <v>44421</v>
       </c>
       <c r="B134" t="n">
-        <v>12.95593166351318</v>
+        <v>12.95593070983887</v>
       </c>
       <c r="C134" t="n">
-        <v>13.76423392021486</v>
+        <v>13.76423290704215</v>
       </c>
       <c r="D134" t="n">
-        <v>12.78797379676563</v>
+        <v>12.78797285545454</v>
       </c>
       <c r="E134" t="n">
-        <v>13.57108119635301</v>
+        <v>13.5710801973981</v>
       </c>
       <c r="F134" t="n">
         <v>3730102</v>
@@ -3112,16 +3112,16 @@
         <v>44424</v>
       </c>
       <c r="B135" t="n">
-        <v>11.84110450744629</v>
+        <v>11.84110355377197</v>
       </c>
       <c r="C135" t="n">
-        <v>12.94963355405497</v>
+        <v>12.94963251110049</v>
       </c>
       <c r="D135" t="n">
-        <v>11.7655231844898</v>
+        <v>11.76552223690275</v>
       </c>
       <c r="E135" t="n">
-        <v>12.94963355405497</v>
+        <v>12.94963251110049</v>
       </c>
       <c r="F135" t="n">
         <v>7844263</v>
@@ -3132,16 +3132,16 @@
         <v>44425</v>
       </c>
       <c r="B136" t="n">
-        <v>12.27779674530029</v>
+        <v>12.27779769897461</v>
       </c>
       <c r="C136" t="n">
-        <v>12.78167271978735</v>
+        <v>12.78167371260009</v>
       </c>
       <c r="D136" t="n">
-        <v>11.42960381681197</v>
+        <v>11.42960470460314</v>
       </c>
       <c r="E136" t="n">
-        <v>11.66474658767486</v>
+        <v>11.66474749373068</v>
       </c>
       <c r="F136" t="n">
         <v>5635292</v>
@@ -3212,16 +3212,16 @@
         <v>44431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.49549770355225</v>
+        <v>13.49549865722656</v>
       </c>
       <c r="C140" t="n">
-        <v>14.19252797462165</v>
+        <v>14.19252897755238</v>
       </c>
       <c r="D140" t="n">
-        <v>13.26035575373789</v>
+        <v>13.26035669079564</v>
       </c>
       <c r="E140" t="n">
-        <v>13.72224245140401</v>
+        <v>13.72224342110149</v>
       </c>
       <c r="F140" t="n">
         <v>2675233</v>
@@ -3232,16 +3232,16 @@
         <v>44432</v>
       </c>
       <c r="B141" t="n">
-        <v>13.63826560974121</v>
+        <v>13.63826465606689</v>
       </c>
       <c r="C141" t="n">
-        <v>13.92379486531496</v>
+        <v>13.92379389167463</v>
       </c>
       <c r="D141" t="n">
-        <v>13.3779287749388</v>
+        <v>13.37792783946889</v>
       </c>
       <c r="E141" t="n">
-        <v>13.63826560974121</v>
+        <v>13.63826465606689</v>
       </c>
       <c r="F141" t="n">
         <v>2525015</v>
@@ -3292,16 +3292,16 @@
         <v>44435</v>
       </c>
       <c r="B144" t="n">
-        <v>13.6886510848999</v>
+        <v>13.68865203857422</v>
       </c>
       <c r="C144" t="n">
-        <v>13.6886510848999</v>
+        <v>13.68865203857422</v>
       </c>
       <c r="D144" t="n">
-        <v>12.95803034564176</v>
+        <v>12.95803124841448</v>
       </c>
       <c r="E144" t="n">
-        <v>13.32753972236057</v>
+        <v>13.32754065087663</v>
       </c>
       <c r="F144" t="n">
         <v>2006349</v>
@@ -3332,16 +3332,16 @@
         <v>44439</v>
       </c>
       <c r="B146" t="n">
-        <v>12.77327632904053</v>
+        <v>12.77327537536621</v>
       </c>
       <c r="C146" t="n">
-        <v>13.40312255485818</v>
+        <v>13.40312155415849</v>
       </c>
       <c r="D146" t="n">
-        <v>12.49614347013225</v>
+        <v>12.49614253714914</v>
       </c>
       <c r="E146" t="n">
-        <v>13.28555035016233</v>
+        <v>13.28554935824077</v>
       </c>
       <c r="F146" t="n">
         <v>2117441</v>
@@ -3352,16 +3352,16 @@
         <v>44440</v>
       </c>
       <c r="B147" t="n">
-        <v>13.06720352172852</v>
+        <v>13.06720447540283</v>
       </c>
       <c r="C147" t="n">
-        <v>13.2855494517287</v>
+        <v>13.2855504213384</v>
       </c>
       <c r="D147" t="n">
-        <v>12.56332673750791</v>
+        <v>12.56332765440814</v>
       </c>
       <c r="E147" t="n">
-        <v>13.09239756388817</v>
+        <v>13.0923985194012</v>
       </c>
       <c r="F147" t="n">
         <v>3411726</v>
@@ -3372,16 +3372,16 @@
         <v>44441</v>
       </c>
       <c r="B148" t="n">
-        <v>12.8068675994873</v>
+        <v>12.80686664581299</v>
       </c>
       <c r="C148" t="n">
-        <v>13.1847750109611</v>
+        <v>13.18477402914559</v>
       </c>
       <c r="D148" t="n">
-        <v>12.69769503279916</v>
+        <v>12.69769408725448</v>
       </c>
       <c r="E148" t="n">
-        <v>13.06720442963625</v>
+        <v>13.06720345657573</v>
       </c>
       <c r="F148" t="n">
         <v>2514879</v>
@@ -3392,16 +3392,16 @@
         <v>44442</v>
       </c>
       <c r="B149" t="n">
-        <v>13.10079669952393</v>
+        <v>13.10079574584961</v>
       </c>
       <c r="C149" t="n">
-        <v>13.21836810182533</v>
+        <v>13.21836713959238</v>
       </c>
       <c r="D149" t="n">
-        <v>12.74808330441434</v>
+        <v>12.74808237641584</v>
       </c>
       <c r="E149" t="n">
-        <v>12.94963404784685</v>
+        <v>12.94963310517644</v>
       </c>
       <c r="F149" t="n">
         <v>3315331</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00002128473755</v>
+        <v>13.00001949529792</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113269394332</v>
+        <v>13.36113085479707</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3432,16 +3432,16 @@
         <v>44447</v>
       </c>
       <c r="B151" t="n">
-        <v>13.23516273498535</v>
+        <v>13.23516178131104</v>
       </c>
       <c r="C151" t="n">
-        <v>14.67960903587777</v>
+        <v>14.67960797812228</v>
       </c>
       <c r="D151" t="n">
-        <v>13.10079531628589</v>
+        <v>13.10079437229357</v>
       </c>
       <c r="E151" t="n">
-        <v>13.80622203202309</v>
+        <v>13.80622103720047</v>
       </c>
       <c r="F151" t="n">
         <v>4568970</v>
@@ -3512,16 +3512,16 @@
         <v>44453</v>
       </c>
       <c r="B155" t="n">
-        <v>13.55428600311279</v>
+        <v>13.55428504943848</v>
       </c>
       <c r="C155" t="n">
-        <v>14.04976483634768</v>
+        <v>14.04976384781166</v>
       </c>
       <c r="D155" t="n">
-        <v>13.27715393946506</v>
+        <v>13.27715300528965</v>
       </c>
       <c r="E155" t="n">
-        <v>13.43671460319705</v>
+        <v>13.43671365779501</v>
       </c>
       <c r="F155" t="n">
         <v>1943200</v>
@@ -3532,16 +3532,16 @@
         <v>44454</v>
       </c>
       <c r="B156" t="n">
-        <v>13.44511127471924</v>
+        <v>13.44511222839355</v>
       </c>
       <c r="C156" t="n">
-        <v>14.07495666337775</v>
+        <v>14.07495766172759</v>
       </c>
       <c r="D156" t="n">
-        <v>13.2351625412349</v>
+        <v>13.23516348001735</v>
       </c>
       <c r="E156" t="n">
-        <v>13.47030450577353</v>
+        <v>13.47030546123482</v>
       </c>
       <c r="F156" t="n">
         <v>2602050</v>
@@ -3572,16 +3572,16 @@
         <v>44456</v>
       </c>
       <c r="B158" t="n">
-        <v>13.44511127471924</v>
+        <v>13.44511222839355</v>
       </c>
       <c r="C158" t="n">
-        <v>13.74743816531587</v>
+        <v>13.74743914043451</v>
       </c>
       <c r="D158" t="n">
-        <v>13.29394782942092</v>
+        <v>13.29394877237308</v>
       </c>
       <c r="E158" t="n">
-        <v>13.40312201509908</v>
+        <v>13.40312296579506</v>
       </c>
       <c r="F158" t="n">
         <v>5378949</v>
@@ -3632,16 +3632,16 @@
         <v>44461</v>
       </c>
       <c r="B161" t="n">
-        <v>14.1001501083374</v>
+        <v>14.10015106201172</v>
       </c>
       <c r="C161" t="n">
-        <v>14.46126225101733</v>
+        <v>14.46126322911574</v>
       </c>
       <c r="D161" t="n">
-        <v>13.58787534726639</v>
+        <v>13.58787626629261</v>
       </c>
       <c r="E161" t="n">
-        <v>13.71384473712192</v>
+        <v>13.71384566466818</v>
       </c>
       <c r="F161" t="n">
         <v>3751489</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.61242771148682</v>
+        <v>14.6124267578125</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630374532261</v>
+        <v>15.11630275876303</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893814452217</v>
+        <v>14.15893722044467</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19253020482906</v>
+        <v>14.19252927855919</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26811184817934</v>
+        <v>14.26810988418833</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141830159083</v>
+        <v>13.83141639771024</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733566500235</v>
+        <v>14.16733371488308</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3692,16 +3692,16 @@
         <v>44466</v>
       </c>
       <c r="B164" t="n">
-        <v>13.77263069152832</v>
+        <v>13.77263164520264</v>
       </c>
       <c r="C164" t="n">
-        <v>13.99097580453232</v>
+        <v>13.99097677332576</v>
       </c>
       <c r="D164" t="n">
-        <v>13.5122946974641</v>
+        <v>13.51229563311167</v>
       </c>
       <c r="E164" t="n">
-        <v>13.86500803211849</v>
+        <v>13.8650089921894</v>
       </c>
       <c r="F164" t="n">
         <v>2647359</v>
@@ -3752,16 +3752,16 @@
         <v>44469</v>
       </c>
       <c r="B167" t="n">
-        <v>12.55492877960205</v>
+        <v>12.55492973327637</v>
       </c>
       <c r="C167" t="n">
-        <v>13.05880556607607</v>
+        <v>13.05880655802494</v>
       </c>
       <c r="D167" t="n">
-        <v>12.370174093194</v>
+        <v>12.37017503283432</v>
       </c>
       <c r="E167" t="n">
-        <v>13.05880556607607</v>
+        <v>13.05880655802494</v>
       </c>
       <c r="F167" t="n">
         <v>6213762</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498023986816</v>
+        <v>12.34498119354248</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366299139635</v>
+        <v>12.82366398204986</v>
       </c>
       <c r="D169" t="n">
-        <v>12.1350315079744</v>
+        <v>12.13503244542976</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288763255913</v>
+        <v>12.72288861542754</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3832,16 +3832,16 @@
         <v>44475</v>
       </c>
       <c r="B171" t="n">
-        <v>12.51294136047363</v>
+        <v>12.51294040679932</v>
       </c>
       <c r="C171" t="n">
-        <v>12.61371592078883</v>
+        <v>12.61371495943398</v>
       </c>
       <c r="D171" t="n">
-        <v>11.68154352582436</v>
+        <v>11.68154263551506</v>
       </c>
       <c r="E171" t="n">
-        <v>11.94188037732158</v>
+        <v>11.9418794671707</v>
       </c>
       <c r="F171" t="n">
         <v>5058241</v>
@@ -3852,16 +3852,16 @@
         <v>44476</v>
       </c>
       <c r="B172" t="n">
-        <v>13.00002098083496</v>
+        <v>13.00002002716064</v>
       </c>
       <c r="C172" t="n">
-        <v>13.02521502604024</v>
+        <v>13.02521407051771</v>
       </c>
       <c r="D172" t="n">
-        <v>12.36177670640198</v>
+        <v>12.36177579954892</v>
       </c>
       <c r="E172" t="n">
-        <v>12.56332825624967</v>
+        <v>12.56332733461089</v>
       </c>
       <c r="F172" t="n">
         <v>3555051</v>
@@ -3872,16 +3872,16 @@
         <v>44477</v>
       </c>
       <c r="B173" t="n">
-        <v>13.05880546569824</v>
+        <v>13.05880641937256</v>
       </c>
       <c r="C173" t="n">
-        <v>13.38632476554297</v>
+        <v>13.38632574313576</v>
       </c>
       <c r="D173" t="n">
-        <v>12.8992440109945</v>
+        <v>12.89924495301617</v>
       </c>
       <c r="E173" t="n">
-        <v>13.1175915638818</v>
+        <v>13.11759252184922</v>
       </c>
       <c r="F173" t="n">
         <v>3251676</v>
@@ -3892,16 +3892,16 @@
         <v>44480</v>
       </c>
       <c r="B174" t="n">
-        <v>12.97482681274414</v>
+        <v>12.97482585906982</v>
       </c>
       <c r="C174" t="n">
-        <v>13.23516282572755</v>
+        <v>13.23516185291805</v>
       </c>
       <c r="D174" t="n">
-        <v>12.74808204582</v>
+        <v>12.74808110881185</v>
       </c>
       <c r="E174" t="n">
-        <v>13.05880614558413</v>
+        <v>13.05880518573717</v>
       </c>
       <c r="F174" t="n">
         <v>2493289</v>
@@ -3992,16 +3992,16 @@
         <v>44488</v>
       </c>
       <c r="B179" t="n">
-        <v>12.39536762237549</v>
+        <v>12.3953685760498</v>
       </c>
       <c r="C179" t="n">
-        <v>13.10919315473166</v>
+        <v>13.10919416332626</v>
       </c>
       <c r="D179" t="n">
-        <v>12.17702087434261</v>
+        <v>12.17702181121777</v>
       </c>
       <c r="E179" t="n">
-        <v>13.05880588076728</v>
+        <v>13.05880688548518</v>
       </c>
       <c r="F179" t="n">
         <v>2260766</v>
@@ -4032,16 +4032,16 @@
         <v>44490</v>
       </c>
       <c r="B181" t="n">
-        <v>11.24484920501709</v>
+        <v>11.24485015869141</v>
       </c>
       <c r="C181" t="n">
-        <v>11.95867472463081</v>
+        <v>11.95867573884459</v>
       </c>
       <c r="D181" t="n">
-        <v>10.83335057097093</v>
+        <v>10.8333514897461</v>
       </c>
       <c r="E181" t="n">
-        <v>11.84950135256322</v>
+        <v>11.84950235751801</v>
       </c>
       <c r="F181" t="n">
         <v>4870723</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.53102397918701</v>
+        <v>10.5310230255127</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174807577158</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624046544360398</v>
+        <v>9.624045672820648</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174807577158</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55621910095215</v>
+        <v>10.55621814727783</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650389517411</v>
+        <v>11.02650289901313</v>
       </c>
       <c r="D183" t="n">
-        <v>10.35466835888637</v>
+        <v>10.35466742342063</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699447198504</v>
+        <v>10.65699350920643</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4092,16 +4092,16 @@
         <v>44495</v>
       </c>
       <c r="B184" t="n">
-        <v>9.98515796661377</v>
+        <v>9.985157012939453</v>
       </c>
       <c r="C184" t="n">
-        <v>10.46384072961404</v>
+        <v>10.46383973022113</v>
       </c>
       <c r="D184" t="n">
-        <v>9.825596504417325</v>
+        <v>9.825595565982594</v>
       </c>
       <c r="E184" t="n">
-        <v>10.46384072961404</v>
+        <v>10.46383973022113</v>
       </c>
       <c r="F184" t="n">
         <v>5760068</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55621910095215</v>
+        <v>10.55621814727783</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771778852473</v>
+        <v>10.96771679767463</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588225223699</v>
+        <v>10.29588132208213</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64019844151379</v>
+        <v>10.64019748025258</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4252,16 +4252,16 @@
         <v>44508</v>
       </c>
       <c r="B192" t="n">
-        <v>10.58981037139893</v>
+        <v>10.58981132507324</v>
       </c>
       <c r="C192" t="n">
-        <v>10.82495234506</v>
+        <v>10.82495331991022</v>
       </c>
       <c r="D192" t="n">
-        <v>10.11112678587894</v>
+        <v>10.111127696445</v>
       </c>
       <c r="E192" t="n">
-        <v>10.82495234506</v>
+        <v>10.82495331991022</v>
       </c>
       <c r="F192" t="n">
         <v>1684830</v>
@@ -4292,16 +4292,16 @@
         <v>44510</v>
       </c>
       <c r="B194" t="n">
-        <v>10.66539192199707</v>
+        <v>10.66539096832275</v>
       </c>
       <c r="C194" t="n">
-        <v>11.16926875045805</v>
+        <v>11.16926775172825</v>
       </c>
       <c r="D194" t="n">
-        <v>10.44704516103155</v>
+        <v>10.44704422688129</v>
       </c>
       <c r="E194" t="n">
-        <v>10.74937125810814</v>
+        <v>10.74937029692459</v>
       </c>
       <c r="F194" t="n">
         <v>2771222</v>
@@ -4332,16 +4332,16 @@
         <v>44512</v>
       </c>
       <c r="B196" t="n">
-        <v>10.75776863098145</v>
+        <v>10.75776767730713</v>
       </c>
       <c r="C196" t="n">
-        <v>11.5051862765822</v>
+        <v>11.50518525664944</v>
       </c>
       <c r="D196" t="n">
-        <v>10.70738135323696</v>
+        <v>10.70738040402947</v>
       </c>
       <c r="E196" t="n">
-        <v>11.19446297160295</v>
+        <v>11.19446197921575</v>
       </c>
       <c r="F196" t="n">
         <v>1618134</v>
@@ -4372,16 +4372,16 @@
         <v>44517</v>
       </c>
       <c r="B198" t="n">
-        <v>10.10272884368896</v>
+        <v>10.10272789001465</v>
       </c>
       <c r="C198" t="n">
-        <v>10.35466766016802</v>
+        <v>10.35466668271126</v>
       </c>
       <c r="D198" t="n">
-        <v>9.800403562785382</v>
+        <v>9.800402637649874</v>
       </c>
       <c r="E198" t="n">
-        <v>10.29588155748545</v>
+        <v>10.29588058557796</v>
       </c>
       <c r="F198" t="n">
         <v>3557179</v>
@@ -4392,16 +4392,16 @@
         <v>44518</v>
       </c>
       <c r="B199" t="n">
-        <v>10.34626960754395</v>
+        <v>10.34626865386963</v>
       </c>
       <c r="C199" t="n">
-        <v>10.57301356738983</v>
+        <v>10.57301259281523</v>
       </c>
       <c r="D199" t="n">
-        <v>10.01035145740236</v>
+        <v>10.01035053469153</v>
       </c>
       <c r="E199" t="n">
-        <v>10.13632086517977</v>
+        <v>10.13631993085762</v>
       </c>
       <c r="F199" t="n">
         <v>2248603</v>
@@ -4412,16 +4412,16 @@
         <v>44519</v>
       </c>
       <c r="B200" t="n">
-        <v>10.80815505981445</v>
+        <v>10.80815696716309</v>
       </c>
       <c r="C200" t="n">
-        <v>10.95092047977755</v>
+        <v>10.95092241232044</v>
       </c>
       <c r="D200" t="n">
-        <v>10.33787035535008</v>
+        <v>10.33787217970612</v>
       </c>
       <c r="E200" t="n">
-        <v>10.33787035535008</v>
+        <v>10.33787217970612</v>
       </c>
       <c r="F200" t="n">
         <v>2187279</v>
@@ -4472,16 +4472,16 @@
         <v>44524</v>
       </c>
       <c r="B203" t="n">
-        <v>9.699628829956055</v>
+        <v>9.699627876281738</v>
       </c>
       <c r="C203" t="n">
-        <v>10.11952634355827</v>
+        <v>10.11952534859934</v>
       </c>
       <c r="D203" t="n">
-        <v>9.380506687146584</v>
+        <v>9.38050576484858</v>
       </c>
       <c r="E203" t="n">
-        <v>9.842393465032259</v>
+        <v>9.842392497321224</v>
       </c>
       <c r="F203" t="n">
         <v>3236370</v>
@@ -4492,16 +4492,16 @@
         <v>44525</v>
       </c>
       <c r="B204" t="n">
-        <v>9.825596809387207</v>
+        <v>9.825595855712891</v>
       </c>
       <c r="C204" t="n">
-        <v>10.15311613477726</v>
+        <v>10.15311514931385</v>
       </c>
       <c r="D204" t="n">
-        <v>9.657638139351562</v>
+        <v>9.657637201979346</v>
       </c>
       <c r="E204" t="n">
-        <v>9.901178129723791</v>
+        <v>9.901177168713536</v>
       </c>
       <c r="F204" t="n">
         <v>1557621</v>
@@ -4512,16 +4512,16 @@
         <v>44526</v>
       </c>
       <c r="B205" t="n">
-        <v>9.472882270812988</v>
+        <v>9.472881317138672</v>
       </c>
       <c r="C205" t="n">
-        <v>9.682831006334919</v>
+        <v>9.682830031524192</v>
       </c>
       <c r="D205" t="n">
-        <v>9.178954203441192</v>
+        <v>9.178953279357833</v>
       </c>
       <c r="E205" t="n">
-        <v>9.657637775036125</v>
+        <v>9.657636802761706</v>
       </c>
       <c r="F205" t="n">
         <v>2092506</v>
@@ -4572,16 +4572,16 @@
         <v>44531</v>
       </c>
       <c r="B208" t="n">
-        <v>9.01939582824707</v>
+        <v>9.019394874572754</v>
       </c>
       <c r="C208" t="n">
-        <v>9.766812733507312</v>
+        <v>9.766811700804164</v>
       </c>
       <c r="D208" t="n">
-        <v>9.01939582824707</v>
+        <v>9.019394874572754</v>
       </c>
       <c r="E208" t="n">
-        <v>9.540067932493566</v>
+        <v>9.540066923765492</v>
       </c>
       <c r="F208" t="n">
         <v>2660840</v>
@@ -4652,16 +4652,16 @@
         <v>44537</v>
       </c>
       <c r="B212" t="n">
-        <v>9.98515796661377</v>
+        <v>9.985157012939453</v>
       </c>
       <c r="C212" t="n">
-        <v>10.53102403318413</v>
+        <v>10.53102302737459</v>
       </c>
       <c r="D212" t="n">
-        <v>9.867585764725682</v>
+        <v>9.867584822280591</v>
       </c>
       <c r="E212" t="n">
-        <v>10.00195318366039</v>
+        <v>10.00195222838198</v>
       </c>
       <c r="F212" t="n">
         <v>3095174</v>
@@ -4732,16 +4732,16 @@
         <v>44543</v>
       </c>
       <c r="B216" t="n">
-        <v>11.19168186187744</v>
+        <v>11.19168281555176</v>
       </c>
       <c r="C216" t="n">
-        <v>11.55848208514464</v>
+        <v>11.55848307007503</v>
       </c>
       <c r="D216" t="n">
-        <v>11.13196966068666</v>
+        <v>11.13197060927274</v>
       </c>
       <c r="E216" t="n">
-        <v>11.25992355294072</v>
+        <v>11.2599245124301</v>
       </c>
       <c r="F216" t="n">
         <v>3334589</v>
@@ -4752,16 +4752,16 @@
         <v>44544</v>
       </c>
       <c r="B217" t="n">
-        <v>11.11490917205811</v>
+        <v>11.11490726470947</v>
       </c>
       <c r="C217" t="n">
-        <v>11.43905865172065</v>
+        <v>11.43905668874708</v>
       </c>
       <c r="D217" t="n">
-        <v>10.91871358626455</v>
+        <v>10.91871171258361</v>
       </c>
       <c r="E217" t="n">
-        <v>11.25992369505407</v>
+        <v>11.25992176282055</v>
       </c>
       <c r="F217" t="n">
         <v>1511299</v>
@@ -4772,16 +4772,16 @@
         <v>44545</v>
       </c>
       <c r="B218" t="n">
-        <v>11.26845455169678</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C218" t="n">
-        <v>11.37934699719004</v>
+        <v>11.37934603413065</v>
       </c>
       <c r="D218" t="n">
-        <v>10.81635115641641</v>
+        <v>10.8163502410046</v>
       </c>
       <c r="E218" t="n">
-        <v>10.9016534815715</v>
+        <v>10.90165255894037</v>
       </c>
       <c r="F218" t="n">
         <v>3122034</v>
@@ -4812,16 +4812,16 @@
         <v>44547</v>
       </c>
       <c r="B220" t="n">
-        <v>11.17461967468262</v>
+        <v>11.17462062835693</v>
       </c>
       <c r="C220" t="n">
-        <v>11.21727124416134</v>
+        <v>11.21727220147566</v>
       </c>
       <c r="D220" t="n">
-        <v>10.91871273156008</v>
+        <v>10.91871366339456</v>
       </c>
       <c r="E220" t="n">
-        <v>11.19168112705737</v>
+        <v>11.19168208218776</v>
       </c>
       <c r="F220" t="n">
         <v>2659218</v>
@@ -4912,16 +4912,16 @@
         <v>44557</v>
       </c>
       <c r="B225" t="n">
-        <v>10.32159614562988</v>
+        <v>10.32159519195557</v>
       </c>
       <c r="C225" t="n">
-        <v>10.58603341390223</v>
+        <v>10.58603243579497</v>
       </c>
       <c r="D225" t="n">
-        <v>9.971855734769711</v>
+        <v>9.971854813410014</v>
       </c>
       <c r="E225" t="n">
-        <v>10.49220078163893</v>
+        <v>10.49219981220142</v>
       </c>
       <c r="F225" t="n">
         <v>1768251</v>
@@ -4952,16 +4952,16 @@
         <v>44559</v>
       </c>
       <c r="B227" t="n">
-        <v>9.715950012207031</v>
+        <v>9.715949058532715</v>
       </c>
       <c r="C227" t="n">
-        <v>10.21923449434762</v>
+        <v>10.21923349127314</v>
       </c>
       <c r="D227" t="n">
-        <v>9.596526422031003</v>
+        <v>9.596525480078773</v>
       </c>
       <c r="E227" t="n">
-        <v>10.21923449434762</v>
+        <v>10.21923349127314</v>
       </c>
       <c r="F227" t="n">
         <v>1535423</v>
@@ -4992,16 +4992,16 @@
         <v>44564</v>
       </c>
       <c r="B229" t="n">
-        <v>9.664769172668457</v>
+        <v>9.664768218994141</v>
       </c>
       <c r="C229" t="n">
-        <v>10.21923473534099</v>
+        <v>10.2192337269546</v>
       </c>
       <c r="D229" t="n">
-        <v>9.349149146813707</v>
+        <v>9.349148224283301</v>
       </c>
       <c r="E229" t="n">
-        <v>10.21923473534099</v>
+        <v>10.2192337269546</v>
       </c>
       <c r="F229" t="n">
         <v>4324384</v>
@@ -5032,16 +5032,16 @@
         <v>44566</v>
       </c>
       <c r="B231" t="n">
-        <v>8.530244827270508</v>
+        <v>8.530243873596191</v>
       </c>
       <c r="C231" t="n">
-        <v>9.255315823119759</v>
+        <v>9.255314788383105</v>
       </c>
       <c r="D231" t="n">
-        <v>8.479063762352734</v>
+        <v>8.479062814400418</v>
       </c>
       <c r="E231" t="n">
-        <v>9.255315823119759</v>
+        <v>9.255314788383105</v>
       </c>
       <c r="F231" t="n">
         <v>5451524</v>
@@ -5072,16 +5072,16 @@
         <v>44568</v>
       </c>
       <c r="B233" t="n">
-        <v>8.700850486755371</v>
+        <v>8.700849533081055</v>
       </c>
       <c r="C233" t="n">
-        <v>8.948227150874695</v>
+        <v>8.94822617008616</v>
       </c>
       <c r="D233" t="n">
-        <v>8.564366269755597</v>
+        <v>8.564365331040909</v>
       </c>
       <c r="E233" t="n">
-        <v>8.948227150874695</v>
+        <v>8.94822617008616</v>
       </c>
       <c r="F233" t="n">
         <v>1845792</v>
@@ -5092,16 +5092,16 @@
         <v>44571</v>
       </c>
       <c r="B234" t="n">
-        <v>8.581426620483398</v>
+        <v>8.581425666809082</v>
       </c>
       <c r="C234" t="n">
-        <v>8.8288041011298</v>
+        <v>8.828803119963837</v>
       </c>
       <c r="D234" t="n">
-        <v>8.316988510194713</v>
+        <v>8.316987585908032</v>
       </c>
       <c r="E234" t="n">
-        <v>8.8288041011298</v>
+        <v>8.828803119963837</v>
       </c>
       <c r="F234" t="n">
         <v>3048446</v>
@@ -5192,16 +5192,16 @@
         <v>44578</v>
       </c>
       <c r="B239" t="n">
-        <v>8.700850486755371</v>
+        <v>8.700849533081055</v>
       </c>
       <c r="C239" t="n">
-        <v>8.862924824468605</v>
+        <v>8.862923853029804</v>
       </c>
       <c r="D239" t="n">
-        <v>8.487594258448453</v>
+        <v>8.487593328148517</v>
       </c>
       <c r="E239" t="n">
-        <v>8.862924824468605</v>
+        <v>8.862923853029804</v>
       </c>
       <c r="F239" t="n">
         <v>1156939</v>
@@ -5232,16 +5232,16 @@
         <v>44580</v>
       </c>
       <c r="B241" t="n">
-        <v>8.521714210510254</v>
+        <v>8.521713256835938</v>
       </c>
       <c r="C241" t="n">
-        <v>8.675259048991672</v>
+        <v>8.675258078133986</v>
       </c>
       <c r="D241" t="n">
-        <v>8.291398189663132</v>
+        <v>8.291397261763732</v>
       </c>
       <c r="E241" t="n">
-        <v>8.308457994309213</v>
+        <v>8.308457064500631</v>
       </c>
       <c r="F241" t="n">
         <v>1675201</v>
@@ -5392,16 +5392,16 @@
         <v>44592</v>
       </c>
       <c r="B249" t="n">
-        <v>10.47513961791992</v>
+        <v>10.47514057159424</v>
       </c>
       <c r="C249" t="n">
-        <v>10.56044193156613</v>
+        <v>10.56044289300652</v>
       </c>
       <c r="D249" t="n">
-        <v>10.1851114216895</v>
+        <v>10.18511234895917</v>
       </c>
       <c r="E249" t="n">
-        <v>10.22776299080424</v>
+        <v>10.22776392195697</v>
       </c>
       <c r="F249" t="n">
         <v>3321007</v>
@@ -5452,16 +5452,16 @@
         <v>44595</v>
       </c>
       <c r="B252" t="n">
-        <v>10.45808029174805</v>
+        <v>10.45807933807373</v>
       </c>
       <c r="C252" t="n">
-        <v>10.84194198780122</v>
+        <v>10.84194099912248</v>
       </c>
       <c r="D252" t="n">
-        <v>10.25335520826973</v>
+        <v>10.25335427326433</v>
       </c>
       <c r="E252" t="n">
-        <v>10.62015544997051</v>
+        <v>10.62015448151653</v>
       </c>
       <c r="F252" t="n">
         <v>1397774</v>
@@ -5532,16 +5532,16 @@
         <v>44601</v>
       </c>
       <c r="B256" t="n">
-        <v>10.24482440948486</v>
+        <v>10.24482345581055</v>
       </c>
       <c r="C256" t="n">
-        <v>10.33012672971753</v>
+        <v>10.33012576810256</v>
       </c>
       <c r="D256" t="n">
-        <v>9.937734737313942</v>
+        <v>9.937733812226112</v>
       </c>
       <c r="E256" t="n">
-        <v>10.25335472396646</v>
+        <v>10.25335376949807</v>
       </c>
       <c r="F256" t="n">
         <v>1982123</v>
@@ -5572,16 +5572,16 @@
         <v>44603</v>
       </c>
       <c r="B258" t="n">
-        <v>9.929204940795898</v>
+        <v>9.929203987121582</v>
       </c>
       <c r="C258" t="n">
-        <v>10.31306495769742</v>
+        <v>10.31306396715434</v>
       </c>
       <c r="D258" t="n">
-        <v>9.647706220762624</v>
+        <v>9.647705294125526</v>
       </c>
       <c r="E258" t="n">
-        <v>9.997446629958024</v>
+        <v>9.99744566972927</v>
       </c>
       <c r="F258" t="n">
         <v>2967053</v>
@@ -5612,16 +5612,16 @@
         <v>44607</v>
       </c>
       <c r="B260" t="n">
-        <v>10.65427684783936</v>
+        <v>10.65427589416504</v>
       </c>
       <c r="C260" t="n">
-        <v>10.86753307355439</v>
+        <v>10.8675321007913</v>
       </c>
       <c r="D260" t="n">
-        <v>10.42395999213378</v>
+        <v>10.42395905907534</v>
       </c>
       <c r="E260" t="n">
-        <v>10.64574653284408</v>
+        <v>10.64574557993332</v>
       </c>
       <c r="F260" t="n">
         <v>2656887</v>
@@ -5752,16 +5752,16 @@
         <v>44616</v>
       </c>
       <c r="B267" t="n">
-        <v>9.78419017791748</v>
+        <v>9.784191131591797</v>
       </c>
       <c r="C267" t="n">
-        <v>9.886553121381233</v>
+        <v>9.886554085032964</v>
       </c>
       <c r="D267" t="n">
-        <v>9.15295188912712</v>
+        <v>9.15295278127404</v>
       </c>
       <c r="E267" t="n">
-        <v>9.15295188912712</v>
+        <v>9.15295278127404</v>
       </c>
       <c r="F267" t="n">
         <v>2513764</v>
@@ -5812,16 +5812,16 @@
         <v>44623</v>
       </c>
       <c r="B270" t="n">
-        <v>9.639176368713379</v>
+        <v>9.639177322387695</v>
       </c>
       <c r="C270" t="n">
-        <v>10.15952056895851</v>
+        <v>10.15952157411429</v>
       </c>
       <c r="D270" t="n">
-        <v>9.562404368219553</v>
+        <v>9.562405314298255</v>
       </c>
       <c r="E270" t="n">
-        <v>9.860962056297398</v>
+        <v>9.860963031914597</v>
       </c>
       <c r="F270" t="n">
         <v>3265562</v>
@@ -5872,16 +5872,16 @@
         <v>44628</v>
       </c>
       <c r="B273" t="n">
-        <v>8.89704418182373</v>
+        <v>8.897043228149414</v>
       </c>
       <c r="C273" t="n">
-        <v>8.92263512401856</v>
+        <v>8.922634167601151</v>
       </c>
       <c r="D273" t="n">
-        <v>8.521713661299355</v>
+        <v>8.521712747856723</v>
       </c>
       <c r="E273" t="n">
-        <v>8.726440374274713</v>
+        <v>8.726439438887422</v>
       </c>
       <c r="F273" t="n">
         <v>2260563</v>
@@ -5932,16 +5932,16 @@
         <v>44631</v>
       </c>
       <c r="B276" t="n">
-        <v>8.615546226501465</v>
+        <v>8.615548133850098</v>
       </c>
       <c r="C276" t="n">
-        <v>9.195602575529984</v>
+        <v>9.195604611294117</v>
       </c>
       <c r="D276" t="n">
-        <v>8.470531726952736</v>
+        <v>8.470533602197403</v>
       </c>
       <c r="E276" t="n">
-        <v>9.195602575529984</v>
+        <v>9.195604611294117</v>
       </c>
       <c r="F276" t="n">
         <v>3220051</v>
@@ -5972,16 +5972,16 @@
         <v>44635</v>
       </c>
       <c r="B278" t="n">
-        <v>8.905576705932617</v>
+        <v>8.905575752258301</v>
       </c>
       <c r="C278" t="n">
-        <v>8.948227458309324</v>
+        <v>8.948226500067653</v>
       </c>
       <c r="D278" t="n">
-        <v>8.581427194785949</v>
+        <v>8.581426275823933</v>
       </c>
       <c r="E278" t="n">
-        <v>8.666729524122774</v>
+        <v>8.666728596025962</v>
       </c>
       <c r="F278" t="n">
         <v>2087539</v>
@@ -6052,16 +6052,16 @@
         <v>44641</v>
       </c>
       <c r="B282" t="n">
-        <v>9.613585472106934</v>
+        <v>9.61358642578125</v>
       </c>
       <c r="C282" t="n">
-        <v>9.741539356585566</v>
+        <v>9.741540322952996</v>
       </c>
       <c r="D282" t="n">
-        <v>9.391798958899509</v>
+        <v>9.39179989057245</v>
       </c>
       <c r="E282" t="n">
-        <v>9.451511156461731</v>
+        <v>9.451512094058163</v>
       </c>
       <c r="F282" t="n">
         <v>1800179</v>
@@ -6072,16 +6072,16 @@
         <v>44642</v>
       </c>
       <c r="B283" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C283" t="n">
-        <v>10.12539894068065</v>
+        <v>10.1253999073854</v>
       </c>
       <c r="D283" t="n">
-        <v>9.570933505254049</v>
+        <v>9.57093441902218</v>
       </c>
       <c r="E283" t="n">
-        <v>9.570933505254049</v>
+        <v>9.57093441902218</v>
       </c>
       <c r="F283" t="n">
         <v>2594043</v>
@@ -6112,16 +6112,16 @@
         <v>44644</v>
       </c>
       <c r="B285" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485107421875</v>
       </c>
       <c r="C285" t="n">
-        <v>10.66280605391772</v>
+        <v>10.66280412340302</v>
       </c>
       <c r="D285" t="n">
-        <v>10.11687085627847</v>
+        <v>10.11686902460604</v>
       </c>
       <c r="E285" t="n">
-        <v>10.27894601228337</v>
+        <v>10.27894415126702</v>
       </c>
       <c r="F285" t="n">
         <v>1712400</v>
@@ -6212,16 +6212,16 @@
         <v>44651</v>
       </c>
       <c r="B290" t="n">
-        <v>10.91018295288086</v>
+        <v>10.91018199920654</v>
       </c>
       <c r="C290" t="n">
-        <v>11.20021116581417</v>
+        <v>11.20021018678808</v>
       </c>
       <c r="D290" t="n">
-        <v>10.85047075268137</v>
+        <v>10.85046980422658</v>
       </c>
       <c r="E290" t="n">
-        <v>11.20021116581417</v>
+        <v>11.20021018678808</v>
       </c>
       <c r="F290" t="n">
         <v>1571711</v>
@@ -6272,16 +6272,16 @@
         <v>44656</v>
       </c>
       <c r="B293" t="n">
-        <v>10.76516819000244</v>
+        <v>10.76516914367676</v>
       </c>
       <c r="C293" t="n">
-        <v>11.22580185419098</v>
+        <v>11.22580284867232</v>
       </c>
       <c r="D293" t="n">
-        <v>10.66280524513646</v>
+        <v>10.66280618974256</v>
       </c>
       <c r="E293" t="n">
-        <v>11.18315028358712</v>
+        <v>11.18315127429</v>
       </c>
       <c r="F293" t="n">
         <v>1686452</v>
@@ -6312,16 +6312,16 @@
         <v>44658</v>
       </c>
       <c r="B295" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485107421875</v>
       </c>
       <c r="C295" t="n">
-        <v>10.67133636868552</v>
+        <v>10.67133443662639</v>
       </c>
       <c r="D295" t="n">
-        <v>10.38130814033029</v>
+        <v>10.38130626078115</v>
       </c>
       <c r="E295" t="n">
-        <v>10.50073172249617</v>
+        <v>10.50072982132524</v>
       </c>
       <c r="F295" t="n">
         <v>1517584</v>
@@ -6332,16 +6332,16 @@
         <v>44659</v>
       </c>
       <c r="B296" t="n">
-        <v>10.3642463684082</v>
+        <v>10.36424732208252</v>
       </c>
       <c r="C296" t="n">
-        <v>10.53485182037612</v>
+        <v>10.53485278974883</v>
       </c>
       <c r="D296" t="n">
-        <v>10.17658193795169</v>
+        <v>10.17658287435791</v>
       </c>
       <c r="E296" t="n">
-        <v>10.53485182037612</v>
+        <v>10.53485278974883</v>
       </c>
       <c r="F296" t="n">
         <v>1523665</v>
@@ -6352,16 +6352,16 @@
         <v>44662</v>
       </c>
       <c r="B297" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485107421875</v>
       </c>
       <c r="C297" t="n">
-        <v>10.61162498989425</v>
+        <v>10.61162306864595</v>
       </c>
       <c r="D297" t="n">
-        <v>10.17658305965309</v>
+        <v>10.17658121716968</v>
       </c>
       <c r="E297" t="n">
-        <v>10.28747550246782</v>
+        <v>10.28747363990719</v>
       </c>
       <c r="F297" t="n">
         <v>2558465</v>
@@ -6472,16 +6472,16 @@
         <v>44671</v>
       </c>
       <c r="B303" t="n">
-        <v>10.90165328979492</v>
+        <v>10.90165233612061</v>
       </c>
       <c r="C303" t="n">
-        <v>11.13197014087041</v>
+        <v>11.13196916704802</v>
       </c>
       <c r="D303" t="n">
-        <v>10.65427663365522</v>
+        <v>10.65427570162136</v>
       </c>
       <c r="E303" t="n">
-        <v>10.92724340968292</v>
+        <v>10.92724245376998</v>
       </c>
       <c r="F303" t="n">
         <v>2911811</v>
@@ -6592,16 +6592,16 @@
         <v>44680</v>
       </c>
       <c r="B309" t="n">
-        <v>11.65231418609619</v>
+        <v>11.65231323242188</v>
       </c>
       <c r="C309" t="n">
-        <v>11.85704091356727</v>
+        <v>11.85703994313725</v>
       </c>
       <c r="D309" t="n">
-        <v>11.46464891254633</v>
+        <v>11.46464797423132</v>
       </c>
       <c r="E309" t="n">
-        <v>11.68643544477193</v>
+        <v>11.68643448830498</v>
       </c>
       <c r="F309" t="n">
         <v>6890958</v>
@@ -6632,16 +6632,16 @@
         <v>44684</v>
       </c>
       <c r="B311" t="n">
-        <v>11.31963443756104</v>
+        <v>11.31963348388672</v>
       </c>
       <c r="C311" t="n">
-        <v>11.52436032643616</v>
+        <v>11.52435935551378</v>
       </c>
       <c r="D311" t="n">
-        <v>11.25992306354883</v>
+        <v>11.25992211490517</v>
       </c>
       <c r="E311" t="n">
-        <v>11.38787612565832</v>
+        <v>11.38787516623467</v>
       </c>
       <c r="F311" t="n">
         <v>2034324</v>
@@ -6652,16 +6652,16 @@
         <v>44685</v>
       </c>
       <c r="B312" t="n">
-        <v>11.83144950866699</v>
+        <v>11.83144855499268</v>
       </c>
       <c r="C312" t="n">
-        <v>11.95087308479659</v>
+        <v>11.95087212149613</v>
       </c>
       <c r="D312" t="n">
-        <v>10.95283372865995</v>
+        <v>10.95283284580649</v>
       </c>
       <c r="E312" t="n">
-        <v>11.09784824779946</v>
+        <v>11.09784735325709</v>
       </c>
       <c r="F312" t="n">
         <v>3044087</v>
@@ -6672,16 +6672,16 @@
         <v>44686</v>
       </c>
       <c r="B313" t="n">
-        <v>11.60966205596924</v>
+        <v>11.60966300964355</v>
       </c>
       <c r="C313" t="n">
-        <v>11.76320605257407</v>
+        <v>11.76320701886124</v>
       </c>
       <c r="D313" t="n">
-        <v>11.38787555013271</v>
+        <v>11.3878764855884</v>
       </c>
       <c r="E313" t="n">
-        <v>11.76320605257407</v>
+        <v>11.76320701886124</v>
       </c>
       <c r="F313" t="n">
         <v>3999622</v>
@@ -6692,16 +6692,16 @@
         <v>44687</v>
       </c>
       <c r="B314" t="n">
-        <v>11.52436065673828</v>
+        <v>11.52435970306396</v>
       </c>
       <c r="C314" t="n">
-        <v>11.61819328978013</v>
+        <v>11.61819232834089</v>
       </c>
       <c r="D314" t="n">
-        <v>11.20874150029449</v>
+        <v>11.20874057273858</v>
       </c>
       <c r="E314" t="n">
-        <v>11.60966297545057</v>
+        <v>11.60966201471724</v>
       </c>
       <c r="F314" t="n">
         <v>3256744</v>
@@ -6732,16 +6732,16 @@
         <v>44691</v>
       </c>
       <c r="B316" t="n">
-        <v>11.22580146789551</v>
+        <v>11.22580242156982</v>
       </c>
       <c r="C316" t="n">
-        <v>11.40493723368412</v>
+        <v>11.4049382025767</v>
       </c>
       <c r="D316" t="n">
-        <v>11.02107558520846</v>
+        <v>11.02107652149054</v>
       </c>
       <c r="E316" t="n">
-        <v>11.11490821272475</v>
+        <v>11.11490915697827</v>
       </c>
       <c r="F316" t="n">
         <v>2926103</v>
@@ -6772,16 +6772,16 @@
         <v>44693</v>
       </c>
       <c r="B318" t="n">
-        <v>11.47317790985107</v>
+        <v>11.47317886352539</v>
       </c>
       <c r="C318" t="n">
-        <v>11.6864341029214</v>
+        <v>11.68643507432202</v>
       </c>
       <c r="D318" t="n">
-        <v>11.06372615108936</v>
+        <v>11.06372707072919</v>
       </c>
       <c r="E318" t="n">
-        <v>11.08078760305155</v>
+        <v>11.08078852410957</v>
       </c>
       <c r="F318" t="n">
         <v>2138727</v>
@@ -6832,16 +6832,16 @@
         <v>44698</v>
       </c>
       <c r="B321" t="n">
-        <v>12.15559768676758</v>
+        <v>12.15559864044189</v>
       </c>
       <c r="C321" t="n">
-        <v>12.29208188631167</v>
+        <v>12.29208285069394</v>
       </c>
       <c r="D321" t="n">
-        <v>11.95087262432635</v>
+        <v>11.95087356193885</v>
       </c>
       <c r="E321" t="n">
-        <v>12.02764462581472</v>
+        <v>12.02764556945041</v>
       </c>
       <c r="F321" t="n">
         <v>4223023</v>
@@ -6852,16 +6852,16 @@
         <v>44699</v>
       </c>
       <c r="B322" t="n">
-        <v>12.08735752105713</v>
+        <v>12.08735656738281</v>
       </c>
       <c r="C322" t="n">
-        <v>12.24943268302999</v>
+        <v>12.24943171656819</v>
       </c>
       <c r="D322" t="n">
-        <v>11.93381349874956</v>
+        <v>11.93381255718963</v>
       </c>
       <c r="E322" t="n">
-        <v>11.99352487973953</v>
+        <v>11.99352393346846</v>
       </c>
       <c r="F322" t="n">
         <v>3728683</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415782928467</v>
+        <v>12.45415687561035</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505109394068</v>
+        <v>12.56505013177474</v>
       </c>
       <c r="D323" t="n">
-        <v>11.95087339334582</v>
+        <v>11.9508724782104</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559846896078</v>
+        <v>12.15559753814858</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6892,16 +6892,16 @@
         <v>44701</v>
       </c>
       <c r="B324" t="n">
-        <v>12.50533866882324</v>
+        <v>12.50533676147461</v>
       </c>
       <c r="C324" t="n">
-        <v>12.65888350352286</v>
+        <v>12.65888157275515</v>
       </c>
       <c r="D324" t="n">
-        <v>12.30914391126722</v>
+        <v>12.30914203384275</v>
       </c>
       <c r="E324" t="n">
-        <v>12.47974772560942</v>
+        <v>12.47974582216399</v>
       </c>
       <c r="F324" t="n">
         <v>4482610</v>
@@ -6952,16 +6952,16 @@
         <v>44706</v>
       </c>
       <c r="B327" t="n">
-        <v>12.36885356903076</v>
+        <v>12.36885452270508</v>
       </c>
       <c r="C327" t="n">
-        <v>12.51386807884551</v>
+        <v>12.51386904370087</v>
       </c>
       <c r="D327" t="n">
-        <v>12.08735568777263</v>
+        <v>12.08735661974265</v>
       </c>
       <c r="E327" t="n">
-        <v>12.21530957001115</v>
+        <v>12.21531051184678</v>
       </c>
       <c r="F327" t="n">
         <v>1655537</v>
@@ -6992,16 +6992,16 @@
         <v>44708</v>
       </c>
       <c r="B329" t="n">
-        <v>13.06833457946777</v>
+        <v>13.06833362579346</v>
       </c>
       <c r="C329" t="n">
-        <v>13.35836279785892</v>
+        <v>13.35836182301952</v>
       </c>
       <c r="D329" t="n">
-        <v>12.76124655671047</v>
+        <v>12.7612456254462</v>
       </c>
       <c r="E329" t="n">
-        <v>12.78683750013469</v>
+        <v>12.78683656700289</v>
       </c>
       <c r="F329" t="n">
         <v>4177410</v>
@@ -7052,16 +7052,16 @@
         <v>44713</v>
       </c>
       <c r="B332" t="n">
-        <v>12.6930046081543</v>
+        <v>12.69300365447998</v>
       </c>
       <c r="C332" t="n">
-        <v>12.71006606244956</v>
+        <v>12.71006510749335</v>
       </c>
       <c r="D332" t="n">
-        <v>12.23237172884965</v>
+        <v>12.23237080978446</v>
       </c>
       <c r="E332" t="n">
-        <v>12.52239996020196</v>
+        <v>12.52239901934583</v>
       </c>
       <c r="F332" t="n">
         <v>4014218</v>
@@ -7112,16 +7112,16 @@
         <v>44718</v>
       </c>
       <c r="B335" t="n">
-        <v>12.36885356903076</v>
+        <v>12.36885452270508</v>
       </c>
       <c r="C335" t="n">
-        <v>12.65888258866027</v>
+        <v>12.65888356469666</v>
       </c>
       <c r="D335" t="n">
-        <v>12.19824894243491</v>
+        <v>12.19824988295512</v>
       </c>
       <c r="E335" t="n">
-        <v>12.65888258866027</v>
+        <v>12.65888356469666</v>
       </c>
       <c r="F335" t="n">
         <v>1740275</v>
@@ -7132,16 +7132,16 @@
         <v>44719</v>
       </c>
       <c r="B336" t="n">
-        <v>12.0276460647583</v>
+        <v>12.02764511108398</v>
       </c>
       <c r="C336" t="n">
-        <v>12.37738568259315</v>
+        <v>12.37738470118792</v>
       </c>
       <c r="D336" t="n">
-        <v>11.87410204341212</v>
+        <v>11.87410110191233</v>
       </c>
       <c r="E336" t="n">
-        <v>12.36885536756466</v>
+        <v>12.36885438683579</v>
       </c>
       <c r="F336" t="n">
         <v>3370370</v>
@@ -7152,16 +7152,16 @@
         <v>44720</v>
       </c>
       <c r="B337" t="n">
-        <v>12.0276460647583</v>
+        <v>12.02764511108398</v>
       </c>
       <c r="C337" t="n">
-        <v>12.14706965057388</v>
+        <v>12.14706868743044</v>
       </c>
       <c r="D337" t="n">
-        <v>11.80586034776752</v>
+        <v>11.80585941167863</v>
       </c>
       <c r="E337" t="n">
-        <v>11.96793385955882</v>
+        <v>11.9679329106191</v>
       </c>
       <c r="F337" t="n">
         <v>2224783</v>
@@ -7172,16 +7172,16 @@
         <v>44721</v>
       </c>
       <c r="B338" t="n">
-        <v>12.15559768676758</v>
+        <v>12.15559864044189</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20678039539862</v>
+        <v>12.20678135308851</v>
       </c>
       <c r="D338" t="n">
-        <v>11.83997936680614</v>
+        <v>11.83998029571844</v>
       </c>
       <c r="E338" t="n">
-        <v>12.07029619585453</v>
+        <v>12.07029714283646</v>
       </c>
       <c r="F338" t="n">
         <v>1444097</v>
@@ -7192,16 +7192,16 @@
         <v>44722</v>
       </c>
       <c r="B339" t="n">
-        <v>11.64378452301025</v>
+        <v>11.64378356933594</v>
       </c>
       <c r="C339" t="n">
-        <v>12.07882644174544</v>
+        <v>12.07882545243938</v>
       </c>
       <c r="D339" t="n">
-        <v>11.4219979940799</v>
+        <v>11.42199705857082</v>
       </c>
       <c r="E339" t="n">
-        <v>12.06176663724438</v>
+        <v>12.06176564933559</v>
       </c>
       <c r="F339" t="n">
         <v>2898634</v>
@@ -7212,16 +7212,16 @@
         <v>44725</v>
       </c>
       <c r="B340" t="n">
-        <v>10.72251796722412</v>
+        <v>10.7225170135498</v>
       </c>
       <c r="C340" t="n">
-        <v>11.507300307965</v>
+        <v>11.50729928449115</v>
       </c>
       <c r="D340" t="n">
-        <v>10.57750426926113</v>
+        <v>10.57750332848451</v>
       </c>
       <c r="E340" t="n">
-        <v>11.23433271652977</v>
+        <v>11.234331717334</v>
       </c>
       <c r="F340" t="n">
         <v>3958469</v>
@@ -7252,16 +7252,16 @@
         <v>44727</v>
       </c>
       <c r="B342" t="n">
-        <v>10.83341121673584</v>
+        <v>10.83341026306152</v>
       </c>
       <c r="C342" t="n">
-        <v>11.07225754969472</v>
+        <v>11.07225657499456</v>
       </c>
       <c r="D342" t="n">
-        <v>10.67133606533815</v>
+        <v>10.67133512593145</v>
       </c>
       <c r="E342" t="n">
-        <v>10.88459227930441</v>
+        <v>10.88459132112458</v>
       </c>
       <c r="F342" t="n">
         <v>3158221</v>
@@ -7272,16 +7272,16 @@
         <v>44729</v>
       </c>
       <c r="B343" t="n">
-        <v>10.66280460357666</v>
+        <v>10.66280555725098</v>
       </c>
       <c r="C343" t="n">
-        <v>10.69692585800674</v>
+        <v>10.69692681473284</v>
       </c>
       <c r="D343" t="n">
-        <v>10.29600441678626</v>
+        <v>10.2960053376542</v>
       </c>
       <c r="E343" t="n">
-        <v>10.69692585800674</v>
+        <v>10.69692681473284</v>
       </c>
       <c r="F343" t="n">
         <v>2862346</v>
@@ -7292,16 +7292,16 @@
         <v>44732</v>
       </c>
       <c r="B344" t="n">
-        <v>10.38130760192871</v>
+        <v>10.38130855560303</v>
       </c>
       <c r="C344" t="n">
-        <v>10.93577391016304</v>
+        <v>10.93577491477317</v>
       </c>
       <c r="D344" t="n">
-        <v>10.33012654055963</v>
+        <v>10.33012748953222</v>
       </c>
       <c r="E344" t="n">
-        <v>10.93577391016304</v>
+        <v>10.93577491477317</v>
       </c>
       <c r="F344" t="n">
         <v>1404768</v>
@@ -7312,16 +7312,16 @@
         <v>44733</v>
       </c>
       <c r="B345" t="n">
-        <v>10.4666109085083</v>
+        <v>10.46660995483398</v>
       </c>
       <c r="C345" t="n">
-        <v>10.65427617742885</v>
+        <v>10.65427520665525</v>
       </c>
       <c r="D345" t="n">
-        <v>10.33012670175548</v>
+        <v>10.33012576051704</v>
       </c>
       <c r="E345" t="n">
-        <v>10.43248965067427</v>
+        <v>10.43248870010894</v>
       </c>
       <c r="F345" t="n">
         <v>1967020</v>
@@ -7332,16 +7332,16 @@
         <v>44734</v>
       </c>
       <c r="B346" t="n">
-        <v>10.5604419708252</v>
+        <v>10.56044292449951</v>
       </c>
       <c r="C346" t="n">
-        <v>10.77369816802514</v>
+        <v>10.77369914095784</v>
       </c>
       <c r="D346" t="n">
-        <v>10.33012597049919</v>
+        <v>10.33012690337453</v>
       </c>
       <c r="E346" t="n">
-        <v>10.42395859831718</v>
+        <v>10.42395953966619</v>
       </c>
       <c r="F346" t="n">
         <v>1465281</v>
@@ -7432,16 +7432,16 @@
         <v>44741</v>
       </c>
       <c r="B351" t="n">
-        <v>10.16805076599121</v>
+        <v>10.16805171966553</v>
       </c>
       <c r="C351" t="n">
-        <v>10.33865539281295</v>
+        <v>10.33865636248849</v>
       </c>
       <c r="D351" t="n">
-        <v>10.03156739436712</v>
+        <v>10.03156833524049</v>
       </c>
       <c r="E351" t="n">
-        <v>10.32159558979739</v>
+        <v>10.32159655787287</v>
       </c>
       <c r="F351" t="n">
         <v>1480384</v>
@@ -7452,16 +7452,16 @@
         <v>44742</v>
       </c>
       <c r="B352" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C352" t="n">
-        <v>10.12539894068065</v>
+        <v>10.1253999073854</v>
       </c>
       <c r="D352" t="n">
-        <v>9.724477500590167</v>
+        <v>9.724478429017642</v>
       </c>
       <c r="E352" t="n">
-        <v>9.971854945344536</v>
+        <v>9.97185589738994</v>
       </c>
       <c r="F352" t="n">
         <v>3400779</v>
@@ -7552,16 +7552,16 @@
         <v>44749</v>
       </c>
       <c r="B357" t="n">
-        <v>9.912143707275391</v>
+        <v>9.912142753601074</v>
       </c>
       <c r="C357" t="n">
-        <v>10.11687042846193</v>
+        <v>10.1168694550903</v>
       </c>
       <c r="D357" t="n">
-        <v>9.630646630175109</v>
+        <v>9.630645703584392</v>
       </c>
       <c r="E357" t="n">
-        <v>9.647706434405947</v>
+        <v>9.647705506173859</v>
       </c>
       <c r="F357" t="n">
         <v>2588468</v>
@@ -7572,16 +7572,16 @@
         <v>44750</v>
       </c>
       <c r="B358" t="n">
-        <v>9.78419017791748</v>
+        <v>9.784191131591797</v>
       </c>
       <c r="C358" t="n">
-        <v>10.19364195177249</v>
+        <v>10.19364294535647</v>
       </c>
       <c r="D358" t="n">
-        <v>9.724477979890045</v>
+        <v>9.724478927744158</v>
       </c>
       <c r="E358" t="n">
-        <v>9.869492493373395</v>
+        <v>9.86949345536221</v>
       </c>
       <c r="F358" t="n">
         <v>1378414</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.110300064086914</v>
+        <v>9.11030101776123</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707417904730018</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076179633609632</v>
+        <v>9.076180583712192</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707417904730018</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7692,16 +7692,16 @@
         <v>44760</v>
       </c>
       <c r="B364" t="n">
-        <v>9.511222839355469</v>
+        <v>9.511221885681152</v>
       </c>
       <c r="C364" t="n">
-        <v>9.698888119197754</v>
+        <v>9.698887146706557</v>
       </c>
       <c r="D364" t="n">
-        <v>9.212665114265498</v>
+        <v>9.212664190527063</v>
       </c>
       <c r="E364" t="n">
-        <v>9.212665114265498</v>
+        <v>9.212664190527063</v>
       </c>
       <c r="F364" t="n">
         <v>1476836</v>
@@ -7752,16 +7752,16 @@
         <v>44763</v>
       </c>
       <c r="B367" t="n">
-        <v>9.963325500488281</v>
+        <v>9.963326454162598</v>
       </c>
       <c r="C367" t="n">
-        <v>10.19364233815759</v>
+        <v>10.19364331387749</v>
       </c>
       <c r="D367" t="n">
-        <v>9.946264871833769</v>
+        <v>9.946265823875066</v>
       </c>
       <c r="E367" t="n">
-        <v>10.02303687619577</v>
+        <v>10.02303783558557</v>
       </c>
       <c r="F367" t="n">
         <v>1242590</v>
@@ -7772,16 +7772,16 @@
         <v>44764</v>
       </c>
       <c r="B368" t="n">
-        <v>10.35571670532227</v>
+        <v>10.35571765899658</v>
       </c>
       <c r="C368" t="n">
-        <v>10.38983796005971</v>
+        <v>10.3898389168763</v>
       </c>
       <c r="D368" t="n">
-        <v>9.954795260490318</v>
+        <v>9.954796177243145</v>
       </c>
       <c r="E368" t="n">
-        <v>10.07421800290487</v>
+        <v>10.07421893065553</v>
       </c>
       <c r="F368" t="n">
         <v>1969757</v>
@@ -7792,16 +7792,16 @@
         <v>44767</v>
       </c>
       <c r="B369" t="n">
-        <v>10.17658138275146</v>
+        <v>10.17658233642578</v>
       </c>
       <c r="C369" t="n">
-        <v>10.41542768314268</v>
+        <v>10.41542865919991</v>
       </c>
       <c r="D369" t="n">
-        <v>10.11686918921625</v>
+        <v>10.11687013729478</v>
       </c>
       <c r="E369" t="n">
-        <v>10.27041318056894</v>
+        <v>10.27041414303648</v>
       </c>
       <c r="F369" t="n">
         <v>1372535</v>
@@ -7812,16 +7812,16 @@
         <v>44768</v>
       </c>
       <c r="B370" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C370" t="n">
-        <v>10.40689763976893</v>
+        <v>10.40689863334928</v>
       </c>
       <c r="D370" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="E370" t="n">
-        <v>10.22776270368238</v>
+        <v>10.22776368016013</v>
       </c>
       <c r="F370" t="n">
         <v>1502988</v>
@@ -7892,16 +7892,16 @@
         <v>44774</v>
       </c>
       <c r="B374" t="n">
-        <v>11.26845455169678</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C374" t="n">
-        <v>11.77173901223685</v>
+        <v>11.77173801596846</v>
       </c>
       <c r="D374" t="n">
-        <v>11.09784907680322</v>
+        <v>11.09784813756763</v>
       </c>
       <c r="E374" t="n">
-        <v>11.64378511221253</v>
+        <v>11.64378412677316</v>
       </c>
       <c r="F374" t="n">
         <v>4838693</v>
@@ -7912,16 +7912,16 @@
         <v>44775</v>
       </c>
       <c r="B375" t="n">
-        <v>11.26845455169678</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C375" t="n">
-        <v>11.49877058224051</v>
+        <v>11.49876960907404</v>
       </c>
       <c r="D375" t="n">
-        <v>11.24286360677524</v>
+        <v>11.24286265526674</v>
       </c>
       <c r="E375" t="n">
-        <v>11.39640762713773</v>
+        <v>11.39640666263446</v>
       </c>
       <c r="F375" t="n">
         <v>2088249</v>
@@ -7972,16 +7972,16 @@
         <v>44778</v>
       </c>
       <c r="B378" t="n">
-        <v>12.79536628723145</v>
+        <v>12.79536724090576</v>
       </c>
       <c r="C378" t="n">
-        <v>12.93185048674745</v>
+        <v>12.93185145059431</v>
       </c>
       <c r="D378" t="n">
-        <v>12.24090082432778</v>
+        <v>12.24090173667624</v>
       </c>
       <c r="E378" t="n">
-        <v>12.32620313980655</v>
+        <v>12.32620405851283</v>
       </c>
       <c r="F378" t="n">
         <v>4419056</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.1621675491333</v>
+        <v>13.16216850280762</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718124064354</v>
+        <v>13.30718220482493</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271576790837</v>
+        <v>12.75271669191557</v>
       </c>
       <c r="E379" t="n">
-        <v>12.79536651411238</v>
+        <v>12.79536744120987</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8052,16 +8052,16 @@
         <v>44784</v>
       </c>
       <c r="B382" t="n">
-        <v>13.36689472198486</v>
+        <v>13.36689376831055</v>
       </c>
       <c r="C382" t="n">
-        <v>13.63986232745854</v>
+        <v>13.63986135430908</v>
       </c>
       <c r="D382" t="n">
-        <v>13.11951723685505</v>
+        <v>13.11951630083012</v>
       </c>
       <c r="E382" t="n">
-        <v>13.5204387423815</v>
+        <v>13.52043777775243</v>
       </c>
       <c r="F382" t="n">
         <v>2014153</v>
@@ -8152,16 +8152,16 @@
         <v>44791</v>
       </c>
       <c r="B387" t="n">
-        <v>13.63986206054688</v>
+        <v>13.63986110687256</v>
       </c>
       <c r="C387" t="n">
-        <v>14.13461537195818</v>
+        <v>14.13461438369162</v>
       </c>
       <c r="D387" t="n">
-        <v>13.23894056286585</v>
+        <v>13.23893963722324</v>
       </c>
       <c r="E387" t="n">
-        <v>13.64839237535569</v>
+        <v>13.64839142108495</v>
       </c>
       <c r="F387" t="n">
         <v>3074090</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066959381104</v>
+        <v>12.88066864013672</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801884508153</v>
+        <v>12.83801789456504</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8192,16 +8192,16 @@
         <v>44795</v>
       </c>
       <c r="B389" t="n">
-        <v>12.52239990234375</v>
+        <v>12.52239894866943</v>
       </c>
       <c r="C389" t="n">
-        <v>12.81242813235602</v>
+        <v>12.81242715659389</v>
       </c>
       <c r="D389" t="n">
-        <v>12.41150663431209</v>
+        <v>12.41150568908313</v>
       </c>
       <c r="E389" t="n">
-        <v>12.71859549395744</v>
+        <v>12.71859452534137</v>
       </c>
       <c r="F389" t="n">
         <v>3082199</v>
@@ -8212,16 +8212,16 @@
         <v>44796</v>
       </c>
       <c r="B390" t="n">
-        <v>12.29208278656006</v>
+        <v>12.29208183288574</v>
       </c>
       <c r="C390" t="n">
-        <v>12.64182321275093</v>
+        <v>12.6418222319422</v>
       </c>
       <c r="D390" t="n">
-        <v>12.25796235261258</v>
+        <v>12.25796140158548</v>
       </c>
       <c r="E390" t="n">
-        <v>12.64182321275093</v>
+        <v>12.6418222319422</v>
       </c>
       <c r="F390" t="n">
         <v>5845922</v>
@@ -8232,16 +8232,16 @@
         <v>44797</v>
       </c>
       <c r="B391" t="n">
-        <v>12.42856597900391</v>
+        <v>12.42856693267822</v>
       </c>
       <c r="C391" t="n">
-        <v>12.57358049130923</v>
+        <v>12.57358145611087</v>
       </c>
       <c r="D391" t="n">
-        <v>12.1300074650419</v>
+        <v>12.13000839580709</v>
       </c>
       <c r="E391" t="n">
-        <v>12.2920817806332</v>
+        <v>12.29208272383475</v>
       </c>
       <c r="F391" t="n">
         <v>4991546</v>
@@ -8312,16 +8312,16 @@
         <v>44803</v>
       </c>
       <c r="B395" t="n">
-        <v>12.21530914306641</v>
+        <v>12.21531009674072</v>
       </c>
       <c r="C395" t="n">
-        <v>12.47121689859905</v>
+        <v>12.47121787225261</v>
       </c>
       <c r="D395" t="n">
-        <v>12.0617651494134</v>
+        <v>12.06176609110022</v>
       </c>
       <c r="E395" t="n">
-        <v>12.25796071051626</v>
+        <v>12.25796166752047</v>
       </c>
       <c r="F395" t="n">
         <v>2841466</v>
@@ -8352,16 +8352,16 @@
         <v>44805</v>
       </c>
       <c r="B397" t="n">
-        <v>12.52239990234375</v>
+        <v>12.52239894866943</v>
       </c>
       <c r="C397" t="n">
-        <v>12.58211128147617</v>
+        <v>12.58211032325439</v>
       </c>
       <c r="D397" t="n">
-        <v>12.12147840429982</v>
+        <v>12.12147748115867</v>
       </c>
       <c r="E397" t="n">
-        <v>12.17266029319906</v>
+        <v>12.17265936616002</v>
       </c>
       <c r="F397" t="n">
         <v>3304080</v>
@@ -8372,16 +8372,16 @@
         <v>44806</v>
       </c>
       <c r="B398" t="n">
-        <v>12.42003631591797</v>
+        <v>12.42003726959229</v>
       </c>
       <c r="C398" t="n">
-        <v>12.7015333734898</v>
+        <v>12.70153434877891</v>
       </c>
       <c r="D398" t="n">
-        <v>12.36885360844292</v>
+        <v>12.36885455818716</v>
       </c>
       <c r="E398" t="n">
-        <v>12.52239843253504</v>
+        <v>12.52239939406925</v>
       </c>
       <c r="F398" t="n">
         <v>3090207</v>
@@ -8392,16 +8392,16 @@
         <v>44809</v>
       </c>
       <c r="B399" t="n">
-        <v>13.3071813583374</v>
+        <v>13.30718231201172</v>
       </c>
       <c r="C399" t="n">
-        <v>13.40954430454897</v>
+        <v>13.40954526555925</v>
       </c>
       <c r="D399" t="n">
-        <v>12.38591566701658</v>
+        <v>12.38591655466734</v>
       </c>
       <c r="E399" t="n">
-        <v>12.48827778864485</v>
+        <v>12.48827868363151</v>
       </c>
       <c r="F399" t="n">
         <v>2134165</v>
@@ -8432,16 +8432,16 @@
         <v>44812</v>
       </c>
       <c r="B401" t="n">
-        <v>12.15559768676758</v>
+        <v>12.15559864044189</v>
       </c>
       <c r="C401" t="n">
-        <v>12.53945934337598</v>
+        <v>12.53946032716638</v>
       </c>
       <c r="D401" t="n">
-        <v>11.79732779676633</v>
+        <v>11.79732872233238</v>
       </c>
       <c r="E401" t="n">
-        <v>12.53945934337598</v>
+        <v>12.53946032716638</v>
       </c>
       <c r="F401" t="n">
         <v>2311852</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.3347339630127</v>
+        <v>12.33473491668701</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121816816301</v>
+        <v>12.47121913238976</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646323371185</v>
+        <v>11.97646415968605</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22384070093743</v>
+        <v>12.22384164603791</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8492,16 +8492,16 @@
         <v>44817</v>
       </c>
       <c r="B404" t="n">
-        <v>11.82735919952393</v>
+        <v>11.82736015319824</v>
       </c>
       <c r="C404" t="n">
-        <v>12.11854676809748</v>
+        <v>12.11854774525109</v>
       </c>
       <c r="D404" t="n">
-        <v>11.7417155059729</v>
+        <v>11.74171645274152</v>
       </c>
       <c r="E404" t="n">
-        <v>12.11854676809748</v>
+        <v>12.11854774525109</v>
       </c>
       <c r="F404" t="n">
         <v>3904244</v>
@@ -8512,16 +8512,16 @@
         <v>44818</v>
       </c>
       <c r="B405" t="n">
-        <v>12.58102226257324</v>
+        <v>12.58102130889893</v>
       </c>
       <c r="C405" t="n">
-        <v>12.60671463129783</v>
+        <v>12.60671367567597</v>
       </c>
       <c r="D405" t="n">
-        <v>11.7331518309107</v>
+        <v>11.73315094150718</v>
       </c>
       <c r="E405" t="n">
-        <v>11.86161697286714</v>
+        <v>11.86161607372562</v>
       </c>
       <c r="F405" t="n">
         <v>3060135</v>
@@ -8532,16 +8532,16 @@
         <v>44819</v>
       </c>
       <c r="B406" t="n">
-        <v>12.76943683624268</v>
+        <v>12.76943588256836</v>
       </c>
       <c r="C406" t="n">
-        <v>12.9321592806806</v>
+        <v>12.9321583148535</v>
       </c>
       <c r="D406" t="n">
-        <v>12.33265506062422</v>
+        <v>12.33265413957057</v>
       </c>
       <c r="E406" t="n">
-        <v>12.54676388734078</v>
+        <v>12.5467629502966</v>
       </c>
       <c r="F406" t="n">
         <v>3409247</v>
@@ -8612,16 +8612,16 @@
         <v>44825</v>
       </c>
       <c r="B410" t="n">
-        <v>11.65607070922852</v>
+        <v>11.65607166290283</v>
       </c>
       <c r="C410" t="n">
-        <v>12.10998235665763</v>
+        <v>12.10998334747001</v>
       </c>
       <c r="D410" t="n">
-        <v>11.50191321893803</v>
+        <v>11.50191415999951</v>
       </c>
       <c r="E410" t="n">
-        <v>11.9472590954252</v>
+        <v>11.94726007292391</v>
       </c>
       <c r="F410" t="n">
         <v>3396829</v>
@@ -8632,16 +8632,16 @@
         <v>44826</v>
       </c>
       <c r="B411" t="n">
-        <v>12.18706226348877</v>
+        <v>12.18706130981445</v>
       </c>
       <c r="C411" t="n">
-        <v>12.24701277079775</v>
+        <v>12.24701181243212</v>
       </c>
       <c r="D411" t="n">
-        <v>11.07369664156018</v>
+        <v>11.07369577501007</v>
       </c>
       <c r="E411" t="n">
-        <v>11.2621131106622</v>
+        <v>11.26211222936794</v>
       </c>
       <c r="F411" t="n">
         <v>10292961</v>
@@ -8692,16 +8692,16 @@
         <v>44831</v>
       </c>
       <c r="B414" t="n">
-        <v>11.30493354797363</v>
+        <v>11.30493450164795</v>
       </c>
       <c r="C414" t="n">
-        <v>11.6389425453333</v>
+        <v>11.63894352718433</v>
       </c>
       <c r="D414" t="n">
-        <v>11.26211211422024</v>
+        <v>11.26211306428218</v>
       </c>
       <c r="E414" t="n">
-        <v>11.53617060957519</v>
+        <v>11.53617158275647</v>
       </c>
       <c r="F414" t="n">
         <v>2656202</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186485290527</v>
+        <v>11.56186389923096</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889411306563</v>
+        <v>11.69889314808853</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072675530685</v>
+        <v>11.21072583059598</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775601546721</v>
+        <v>11.34775507945355</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8852,16 +8852,16 @@
         <v>44841</v>
       </c>
       <c r="B422" t="n">
-        <v>12.6238431930542</v>
+        <v>12.62384414672852</v>
       </c>
       <c r="C422" t="n">
-        <v>12.92359488443413</v>
+        <v>12.92359586075333</v>
       </c>
       <c r="D422" t="n">
-        <v>12.54676362127082</v>
+        <v>12.54676456912213</v>
       </c>
       <c r="E422" t="n">
-        <v>12.92359488443413</v>
+        <v>12.92359586075333</v>
       </c>
       <c r="F422" t="n">
         <v>1382517</v>
@@ -8892,16 +8892,16 @@
         <v>44845</v>
       </c>
       <c r="B424" t="n">
-        <v>12.75230884552002</v>
+        <v>12.7523078918457</v>
       </c>
       <c r="C424" t="n">
-        <v>12.80369523214346</v>
+        <v>12.80369427462625</v>
       </c>
       <c r="D424" t="n">
-        <v>12.53820082528354</v>
+        <v>12.53819988762117</v>
       </c>
       <c r="E424" t="n">
-        <v>12.7266156522083</v>
+        <v>12.72661470045543</v>
       </c>
       <c r="F424" t="n">
         <v>1848640</v>
@@ -8912,16 +8912,16 @@
         <v>44847</v>
       </c>
       <c r="B425" t="n">
-        <v>13.05206108093262</v>
+        <v>13.0520601272583</v>
       </c>
       <c r="C425" t="n">
-        <v>13.30899135873641</v>
+        <v>13.30899038628898</v>
       </c>
       <c r="D425" t="n">
-        <v>12.57245784072665</v>
+        <v>12.57245692209548</v>
       </c>
       <c r="E425" t="n">
-        <v>12.58958608613578</v>
+        <v>12.58958516625311</v>
       </c>
       <c r="F425" t="n">
         <v>3708082</v>
@@ -8932,16 +8932,16 @@
         <v>44848</v>
       </c>
       <c r="B426" t="n">
-        <v>12.76943683624268</v>
+        <v>12.76943588256836</v>
       </c>
       <c r="C426" t="n">
-        <v>13.12057491625784</v>
+        <v>13.12057393635908</v>
       </c>
       <c r="D426" t="n">
-        <v>12.65809994950008</v>
+        <v>12.65809900414086</v>
       </c>
       <c r="E426" t="n">
-        <v>13.09488172511853</v>
+        <v>13.09488074713864</v>
       </c>
       <c r="F426" t="n">
         <v>2206838</v>
@@ -8952,16 +8952,16 @@
         <v>44851</v>
       </c>
       <c r="B427" t="n">
-        <v>12.64953708648682</v>
+        <v>12.6495361328125</v>
       </c>
       <c r="C427" t="n">
-        <v>13.19765580340922</v>
+        <v>13.19765480841111</v>
       </c>
       <c r="D427" t="n">
-        <v>12.58102245301736</v>
+        <v>12.5810215045085</v>
       </c>
       <c r="E427" t="n">
-        <v>12.87221005755423</v>
+        <v>12.87220908709215</v>
       </c>
       <c r="F427" t="n">
         <v>1088124</v>
@@ -9032,16 +9032,16 @@
         <v>44855</v>
       </c>
       <c r="B431" t="n">
-        <v>13.08631706237793</v>
+        <v>13.08631801605225</v>
       </c>
       <c r="C431" t="n">
-        <v>13.26616856834072</v>
+        <v>13.26616953512184</v>
       </c>
       <c r="D431" t="n">
-        <v>12.58958480281398</v>
+        <v>12.58958572028859</v>
       </c>
       <c r="E431" t="n">
-        <v>12.74374311869877</v>
+        <v>12.74374404740777</v>
       </c>
       <c r="F431" t="n">
         <v>1434409</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805000305176</v>
+        <v>12.71804904937744</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775301708247</v>
+        <v>13.0777520364355</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235763740665</v>
+        <v>12.6923566856589</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87220831983874</v>
+        <v>12.87220735460472</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9092,16 +9092,16 @@
         <v>44860</v>
       </c>
       <c r="B434" t="n">
-        <v>12.2983980178833</v>
+        <v>12.29839706420898</v>
       </c>
       <c r="C434" t="n">
-        <v>13.00923831573856</v>
+        <v>13.00923730694242</v>
       </c>
       <c r="D434" t="n">
-        <v>12.17849783090068</v>
+        <v>12.17849688652397</v>
       </c>
       <c r="E434" t="n">
-        <v>12.61527879154568</v>
+        <v>12.61527781329898</v>
       </c>
       <c r="F434" t="n">
         <v>4556230</v>
@@ -9112,16 +9112,16 @@
         <v>44861</v>
       </c>
       <c r="B435" t="n">
-        <v>13.13770484924316</v>
+        <v>13.13770294189453</v>
       </c>
       <c r="C435" t="n">
-        <v>13.30042730438291</v>
+        <v>13.30042537341002</v>
       </c>
       <c r="D435" t="n">
-        <v>12.22131897764474</v>
+        <v>12.22131720333817</v>
       </c>
       <c r="E435" t="n">
-        <v>12.35834906453876</v>
+        <v>12.35834727033798</v>
       </c>
       <c r="F435" t="n">
         <v>3242667</v>
@@ -9132,16 +9132,16 @@
         <v>44862</v>
       </c>
       <c r="B436" t="n">
-        <v>13.06918907165527</v>
+        <v>13.06918811798096</v>
       </c>
       <c r="C436" t="n">
-        <v>13.48027849763024</v>
+        <v>13.48027751395823</v>
       </c>
       <c r="D436" t="n">
-        <v>12.4525565818595</v>
+        <v>12.45255567318159</v>
       </c>
       <c r="E436" t="n">
-        <v>13.154832770782</v>
+        <v>13.15483181085816</v>
       </c>
       <c r="F436" t="n">
         <v>6048388</v>
@@ -9152,16 +9152,16 @@
         <v>44865</v>
       </c>
       <c r="B437" t="n">
-        <v>13.80572128295898</v>
+        <v>13.8057222366333</v>
       </c>
       <c r="C437" t="n">
-        <v>14.07121647802385</v>
+        <v>14.0712174500381</v>
       </c>
       <c r="D437" t="n">
-        <v>12.50394097117564</v>
+        <v>12.50394183492532</v>
       </c>
       <c r="E437" t="n">
-        <v>12.50394097117564</v>
+        <v>12.50394183492532</v>
       </c>
       <c r="F437" t="n">
         <v>7903691</v>
@@ -9172,16 +9172,16 @@
         <v>44866</v>
       </c>
       <c r="B438" t="n">
-        <v>13.61730575561523</v>
+        <v>13.61730480194092</v>
       </c>
       <c r="C438" t="n">
-        <v>14.01126607789819</v>
+        <v>14.01126509663326</v>
       </c>
       <c r="D438" t="n">
-        <v>13.53166288847033</v>
+        <v>13.53166194079393</v>
       </c>
       <c r="E438" t="n">
-        <v>13.70295027192667</v>
+        <v>13.70294931225432</v>
       </c>
       <c r="F438" t="n">
         <v>3366744</v>
@@ -9192,16 +9192,16 @@
         <v>44868</v>
       </c>
       <c r="B439" t="n">
-        <v>13.9341869354248</v>
+        <v>13.93418788909912</v>
       </c>
       <c r="C439" t="n">
-        <v>14.04552216479015</v>
+        <v>14.0455231260844</v>
       </c>
       <c r="D439" t="n">
-        <v>13.38606831348592</v>
+        <v>13.38606922964626</v>
       </c>
       <c r="E439" t="n">
-        <v>13.38606831348592</v>
+        <v>13.38606922964626</v>
       </c>
       <c r="F439" t="n">
         <v>2966749</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.40319919586182</v>
+        <v>13.40319728851318</v>
       </c>
       <c r="C441" t="n">
-        <v>14.03696080730087</v>
+        <v>14.03695880976449</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037857966108</v>
+        <v>13.36037667840605</v>
       </c>
       <c r="E441" t="n">
-        <v>13.93418967925229</v>
+        <v>13.9341876963408</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9272,16 +9272,16 @@
         <v>44874</v>
       </c>
       <c r="B443" t="n">
-        <v>13.13770484924316</v>
+        <v>13.13770294189453</v>
       </c>
       <c r="C443" t="n">
-        <v>13.55735758350707</v>
+        <v>13.55735561523272</v>
       </c>
       <c r="D443" t="n">
-        <v>12.983546516852</v>
+        <v>12.98354463188427</v>
       </c>
       <c r="E443" t="n">
-        <v>13.29186235705097</v>
+        <v>13.29186042732156</v>
       </c>
       <c r="F443" t="n">
         <v>3144132</v>
@@ -9432,16 +9432,16 @@
         <v>44887</v>
       </c>
       <c r="B451" t="n">
-        <v>10.98805236816406</v>
+        <v>10.98805332183838</v>
       </c>
       <c r="C451" t="n">
-        <v>11.33919042015788</v>
+        <v>11.33919140430814</v>
       </c>
       <c r="D451" t="n">
-        <v>10.89384455789337</v>
+        <v>10.89384550339121</v>
       </c>
       <c r="E451" t="n">
-        <v>11.27923992047805</v>
+        <v>11.2792408994251</v>
       </c>
       <c r="F451" t="n">
         <v>2547672</v>
@@ -9452,16 +9452,16 @@
         <v>44888</v>
       </c>
       <c r="B452" t="n">
-        <v>11.04800415039062</v>
+        <v>11.04800319671631</v>
       </c>
       <c r="C452" t="n">
-        <v>11.09082641203781</v>
+        <v>11.09082545466704</v>
       </c>
       <c r="D452" t="n">
-        <v>10.78250893176141</v>
+        <v>10.78250800100489</v>
       </c>
       <c r="E452" t="n">
-        <v>10.98805364375123</v>
+        <v>10.9880526952519</v>
       </c>
       <c r="F452" t="n">
         <v>2848931</v>
@@ -9472,16 +9472,16 @@
         <v>44889</v>
       </c>
       <c r="B453" t="n">
-        <v>11.53617095947266</v>
+        <v>11.53617000579834</v>
       </c>
       <c r="C453" t="n">
-        <v>11.81879440981701</v>
+        <v>11.81879343277872</v>
       </c>
       <c r="D453" t="n">
-        <v>11.05656775347163</v>
+        <v>11.05656683944524</v>
       </c>
       <c r="E453" t="n">
-        <v>11.11651825729467</v>
+        <v>11.11651733831228</v>
       </c>
       <c r="F453" t="n">
         <v>3457606</v>
@@ -9552,16 +9552,16 @@
         <v>44895</v>
       </c>
       <c r="B457" t="n">
-        <v>11.35631942749023</v>
+        <v>11.35632038116455</v>
       </c>
       <c r="C457" t="n">
-        <v>11.57042825153101</v>
+        <v>11.57042922318563</v>
       </c>
       <c r="D457" t="n">
-        <v>11.04800361142147</v>
+        <v>11.04800453920422</v>
       </c>
       <c r="E457" t="n">
-        <v>11.34775530541193</v>
+        <v>11.34775625836705</v>
       </c>
       <c r="F457" t="n">
         <v>6904107</v>
@@ -9612,16 +9612,16 @@
         <v>44900</v>
       </c>
       <c r="B460" t="n">
-        <v>10.65404319763184</v>
+        <v>10.65404510498047</v>
       </c>
       <c r="C460" t="n">
-        <v>11.26211148072586</v>
+        <v>11.2621134969344</v>
       </c>
       <c r="D460" t="n">
-        <v>10.56839868577602</v>
+        <v>10.56840057779207</v>
       </c>
       <c r="E460" t="n">
-        <v>11.26211148072586</v>
+        <v>11.2621134969344</v>
       </c>
       <c r="F460" t="n">
         <v>2438739</v>
@@ -9632,16 +9632,16 @@
         <v>44901</v>
       </c>
       <c r="B461" t="n">
-        <v>10.64547920227051</v>
+        <v>10.64548015594482</v>
       </c>
       <c r="C461" t="n">
-        <v>10.8852812182133</v>
+        <v>10.88528219337026</v>
       </c>
       <c r="D461" t="n">
-        <v>10.44849944607939</v>
+        <v>10.44850038210729</v>
       </c>
       <c r="E461" t="n">
-        <v>10.62835013345318</v>
+        <v>10.62835108559299</v>
       </c>
       <c r="F461" t="n">
         <v>3634787</v>
@@ -9652,16 +9652,16 @@
         <v>44902</v>
       </c>
       <c r="B462" t="n">
-        <v>10.36285591125488</v>
+        <v>10.36285495758057</v>
       </c>
       <c r="C462" t="n">
-        <v>10.91097288493018</v>
+        <v>10.91097188081368</v>
       </c>
       <c r="D462" t="n">
-        <v>10.24295491097179</v>
+        <v>10.24295396833174</v>
       </c>
       <c r="E462" t="n">
-        <v>10.59409296566996</v>
+        <v>10.59409199071533</v>
       </c>
       <c r="F462" t="n">
         <v>7006882</v>
@@ -9712,16 +9712,16 @@
         <v>44907</v>
       </c>
       <c r="B465" t="n">
-        <v>9.50642204284668</v>
+        <v>9.506422996520996</v>
       </c>
       <c r="C465" t="n">
-        <v>10.02884668216042</v>
+        <v>10.02884768824383</v>
       </c>
       <c r="D465" t="n">
-        <v>9.42077834844417</v>
+        <v>9.420779293526801</v>
       </c>
       <c r="E465" t="n">
-        <v>9.57493666853537</v>
+        <v>9.574937629083003</v>
       </c>
       <c r="F465" t="n">
         <v>6343387</v>
@@ -9732,16 +9732,16 @@
         <v>44908</v>
       </c>
       <c r="B466" t="n">
-        <v>9.377956390380859</v>
+        <v>9.377955436706543</v>
       </c>
       <c r="C466" t="n">
-        <v>9.9517674296964</v>
+        <v>9.951766417669408</v>
       </c>
       <c r="D466" t="n">
-        <v>9.352264023359256</v>
+        <v>9.352263072297678</v>
       </c>
       <c r="E466" t="n">
-        <v>9.532114715427072</v>
+        <v>9.532113746075902</v>
       </c>
       <c r="F466" t="n">
         <v>6881089</v>
@@ -9752,16 +9752,16 @@
         <v>44909</v>
       </c>
       <c r="B467" t="n">
-        <v>9.489292144775391</v>
+        <v>9.489291191101074</v>
       </c>
       <c r="C467" t="n">
-        <v>9.652015411433279</v>
+        <v>9.652014441405267</v>
       </c>
       <c r="D467" t="n">
-        <v>9.138154894443332</v>
+        <v>9.138153976058327</v>
       </c>
       <c r="E467" t="n">
-        <v>9.31800558063984</v>
+        <v>9.318004644179831</v>
       </c>
       <c r="F467" t="n">
         <v>7822016</v>
@@ -9812,16 +9812,16 @@
         <v>44914</v>
       </c>
       <c r="B470" t="n">
-        <v>9.951766967773438</v>
+        <v>9.951766014099121</v>
       </c>
       <c r="C470" t="n">
-        <v>10.03741066095349</v>
+        <v>10.03740969907196</v>
       </c>
       <c r="D470" t="n">
-        <v>9.686272590873555</v>
+        <v>9.68627166264147</v>
       </c>
       <c r="E470" t="n">
-        <v>9.840430084181047</v>
+        <v>9.840429141176106</v>
       </c>
       <c r="F470" t="n">
         <v>3753211</v>
@@ -9832,16 +9832,16 @@
         <v>44915</v>
       </c>
       <c r="B471" t="n">
-        <v>10.33716106414795</v>
+        <v>10.33716297149658</v>
       </c>
       <c r="C471" t="n">
-        <v>10.65404260703212</v>
+        <v>10.65404457284976</v>
       </c>
       <c r="D471" t="n">
-        <v>9.85755875084087</v>
+        <v>9.857560569696266</v>
       </c>
       <c r="E471" t="n">
-        <v>9.926072542444418</v>
+        <v>9.926074373941555</v>
       </c>
       <c r="F471" t="n">
         <v>4483944</v>
@@ -9852,16 +9852,16 @@
         <v>44916</v>
       </c>
       <c r="B472" t="n">
-        <v>10.42280578613281</v>
+        <v>10.42280673980713</v>
       </c>
       <c r="C472" t="n">
-        <v>10.58552904653355</v>
+        <v>10.58553001509685</v>
       </c>
       <c r="D472" t="n">
-        <v>10.08879679276622</v>
+        <v>10.08879771587911</v>
       </c>
       <c r="E472" t="n">
-        <v>10.36285610942807</v>
+        <v>10.36285705761706</v>
       </c>
       <c r="F472" t="n">
         <v>3195923</v>
@@ -9892,16 +9892,16 @@
         <v>44918</v>
       </c>
       <c r="B474" t="n">
-        <v>10.83389472961426</v>
+        <v>10.83389377593994</v>
       </c>
       <c r="C474" t="n">
-        <v>11.26211237541256</v>
+        <v>11.26211138404356</v>
       </c>
       <c r="D474" t="n">
-        <v>10.55983540332002</v>
+        <v>10.55983447377029</v>
       </c>
       <c r="E474" t="n">
-        <v>10.57696364738531</v>
+        <v>10.57696271632784</v>
       </c>
       <c r="F474" t="n">
         <v>4288288</v>
@@ -9912,16 +9912,16 @@
         <v>44921</v>
       </c>
       <c r="B475" t="n">
-        <v>10.66260814666748</v>
+        <v>10.66260719299316</v>
       </c>
       <c r="C475" t="n">
-        <v>10.87671696917752</v>
+        <v>10.8767159963531</v>
       </c>
       <c r="D475" t="n">
-        <v>10.57696362816352</v>
+        <v>10.57696268214933</v>
       </c>
       <c r="E475" t="n">
-        <v>10.82533058790846</v>
+        <v>10.82532961968009</v>
       </c>
       <c r="F475" t="n">
         <v>1667319</v>
@@ -9932,16 +9932,16 @@
         <v>44922</v>
       </c>
       <c r="B476" t="n">
-        <v>10.52296161651611</v>
+        <v>10.5229606628418</v>
       </c>
       <c r="C476" t="n">
-        <v>10.75039054378364</v>
+        <v>10.75038956949791</v>
       </c>
       <c r="D476" t="n">
-        <v>10.37425773083552</v>
+        <v>10.37425679063793</v>
       </c>
       <c r="E476" t="n">
-        <v>10.73289562221141</v>
+        <v>10.73289464951121</v>
       </c>
       <c r="F476" t="n">
         <v>2935250</v>
@@ -9952,16 +9952,16 @@
         <v>44923</v>
       </c>
       <c r="B477" t="n">
-        <v>10.96907138824463</v>
+        <v>10.96907234191895</v>
       </c>
       <c r="C477" t="n">
-        <v>11.03030234933299</v>
+        <v>11.03030330833085</v>
       </c>
       <c r="D477" t="n">
-        <v>10.4354885018964</v>
+        <v>10.43548940917989</v>
       </c>
       <c r="E477" t="n">
-        <v>10.56669662140617</v>
+        <v>10.56669754009717</v>
       </c>
       <c r="F477" t="n">
         <v>2605824</v>
@@ -10052,16 +10052,16 @@
         <v>44931</v>
       </c>
       <c r="B482" t="n">
-        <v>10.05935668945312</v>
+        <v>10.05935573577881</v>
       </c>
       <c r="C482" t="n">
-        <v>10.33926871956802</v>
+        <v>10.33926773935673</v>
       </c>
       <c r="D482" t="n">
-        <v>9.779444659338226</v>
+        <v>9.779443732200887</v>
       </c>
       <c r="E482" t="n">
-        <v>9.796938740122757</v>
+        <v>9.796937811326897</v>
       </c>
       <c r="F482" t="n">
         <v>3524036</v>
@@ -10112,16 +10112,16 @@
         <v>44936</v>
       </c>
       <c r="B485" t="n">
-        <v>11.11777591705322</v>
+        <v>11.11777496337891</v>
       </c>
       <c r="C485" t="n">
-        <v>11.29272092875768</v>
+        <v>11.29271996007671</v>
       </c>
       <c r="D485" t="n">
-        <v>10.48797219052666</v>
+        <v>10.48797129087642</v>
       </c>
       <c r="E485" t="n">
-        <v>10.55795019520844</v>
+        <v>10.55794928955554</v>
       </c>
       <c r="F485" t="n">
         <v>3522522</v>
@@ -10192,16 +10192,16 @@
         <v>44942</v>
       </c>
       <c r="B489" t="n">
-        <v>10.8028736114502</v>
+        <v>10.80287265777588</v>
       </c>
       <c r="C489" t="n">
-        <v>11.3014683871045</v>
+        <v>11.30146738941439</v>
       </c>
       <c r="D489" t="n">
-        <v>10.69790744273759</v>
+        <v>10.69790649832965</v>
       </c>
       <c r="E489" t="n">
-        <v>11.25773234310836</v>
+        <v>11.25773134927926</v>
       </c>
       <c r="F489" t="n">
         <v>2251058</v>
@@ -10212,16 +10212,16 @@
         <v>44943</v>
       </c>
       <c r="B490" t="n">
-        <v>11.00405979156494</v>
+        <v>11.00406074523926</v>
       </c>
       <c r="C490" t="n">
-        <v>11.10902762899043</v>
+        <v>11.10902859176186</v>
       </c>
       <c r="D490" t="n">
-        <v>10.75038976364046</v>
+        <v>10.7503906953303</v>
       </c>
       <c r="E490" t="n">
-        <v>10.84660887762188</v>
+        <v>10.8466098176506</v>
       </c>
       <c r="F490" t="n">
         <v>2581089</v>
@@ -10252,16 +10252,16 @@
         <v>44945</v>
       </c>
       <c r="B492" t="n">
-        <v>11.93127155303955</v>
+        <v>11.93127059936523</v>
       </c>
       <c r="C492" t="n">
-        <v>12.30740353426755</v>
+        <v>12.30740255052876</v>
       </c>
       <c r="D492" t="n">
-        <v>11.33645767814233</v>
+        <v>11.33645677201188</v>
       </c>
       <c r="E492" t="n">
-        <v>11.49390776570111</v>
+        <v>11.49390684698556</v>
       </c>
       <c r="F492" t="n">
         <v>5394988</v>
@@ -10332,16 +10332,16 @@
         <v>44951</v>
       </c>
       <c r="B496" t="n">
-        <v>12.24617099761963</v>
+        <v>12.24617195129395</v>
       </c>
       <c r="C496" t="n">
-        <v>12.44735878558682</v>
+        <v>12.44735975492869</v>
       </c>
       <c r="D496" t="n">
-        <v>11.96625901817858</v>
+        <v>11.96625995005467</v>
       </c>
       <c r="E496" t="n">
-        <v>12.10621500789911</v>
+        <v>12.10621595067431</v>
       </c>
       <c r="F496" t="n">
         <v>2519909</v>
@@ -10372,16 +10372,16 @@
         <v>44953</v>
       </c>
       <c r="B498" t="n">
-        <v>12.43861389160156</v>
+        <v>12.43861293792725</v>
       </c>
       <c r="C498" t="n">
-        <v>12.67478987552819</v>
+        <v>12.67478890374615</v>
       </c>
       <c r="D498" t="n">
-        <v>12.25492099177236</v>
+        <v>12.25492005218186</v>
       </c>
       <c r="E498" t="n">
-        <v>12.41237108625991</v>
+        <v>12.41237013459764</v>
       </c>
       <c r="F498" t="n">
         <v>1981500</v>
@@ -10412,16 +10412,16 @@
         <v>44957</v>
       </c>
       <c r="B500" t="n">
-        <v>12.78850364685059</v>
+        <v>12.78850173950195</v>
       </c>
       <c r="C500" t="n">
-        <v>13.03342750793878</v>
+        <v>13.03342556406084</v>
       </c>
       <c r="D500" t="n">
-        <v>12.48234882049034</v>
+        <v>12.48234695880334</v>
       </c>
       <c r="E500" t="n">
-        <v>12.49109670281154</v>
+        <v>12.49109483981984</v>
       </c>
       <c r="F500" t="n">
         <v>4284855</v>
@@ -10472,16 +10472,16 @@
         <v>44960</v>
       </c>
       <c r="B503" t="n">
-        <v>12.57856845855713</v>
+        <v>12.57856750488281</v>
       </c>
       <c r="C503" t="n">
-        <v>12.90221819887599</v>
+        <v>12.90221722066339</v>
       </c>
       <c r="D503" t="n">
-        <v>12.42986541153535</v>
+        <v>12.42986446913531</v>
       </c>
       <c r="E503" t="n">
-        <v>12.81474527332507</v>
+        <v>12.81474430174445</v>
       </c>
       <c r="F503" t="n">
         <v>2892746</v>
@@ -10492,16 +10492,16 @@
         <v>44963</v>
       </c>
       <c r="B504" t="n">
-        <v>12.75351428985596</v>
+        <v>12.75351333618164</v>
       </c>
       <c r="C504" t="n">
-        <v>12.83224017538812</v>
+        <v>12.83223921582688</v>
       </c>
       <c r="D504" t="n">
-        <v>12.33364542693687</v>
+        <v>12.33364450465924</v>
       </c>
       <c r="E504" t="n">
-        <v>12.53483239741585</v>
+        <v>12.53483146009399</v>
       </c>
       <c r="F504" t="n">
         <v>1342942</v>
@@ -10512,16 +10512,16 @@
         <v>44964</v>
       </c>
       <c r="B505" t="n">
-        <v>12.76226139068604</v>
+        <v>12.76226043701172</v>
       </c>
       <c r="C505" t="n">
-        <v>12.93720640015643</v>
+        <v>12.93720543340915</v>
       </c>
       <c r="D505" t="n">
-        <v>12.52608541735219</v>
+        <v>12.52608448132639</v>
       </c>
       <c r="E505" t="n">
-        <v>12.85848135644357</v>
+        <v>12.8584803955791</v>
       </c>
       <c r="F505" t="n">
         <v>2203204</v>
@@ -10532,16 +10532,16 @@
         <v>44965</v>
       </c>
       <c r="B506" t="n">
-        <v>12.7710075378418</v>
+        <v>12.77100849151611</v>
       </c>
       <c r="C506" t="n">
-        <v>12.98094237672584</v>
+        <v>12.98094334607703</v>
       </c>
       <c r="D506" t="n">
-        <v>12.56982058046619</v>
+        <v>12.56982151911688</v>
       </c>
       <c r="E506" t="n">
-        <v>12.85848045755975</v>
+        <v>12.8584814177661</v>
       </c>
       <c r="F506" t="n">
         <v>1737889</v>
@@ -10592,16 +10592,16 @@
         <v>44970</v>
       </c>
       <c r="B509" t="n">
-        <v>12.52608585357666</v>
+        <v>12.52608489990234</v>
       </c>
       <c r="C509" t="n">
-        <v>12.77100887536473</v>
+        <v>12.77100790304318</v>
       </c>
       <c r="D509" t="n">
-        <v>12.35113999581847</v>
+        <v>12.35113905546367</v>
       </c>
       <c r="E509" t="n">
-        <v>12.38612984112634</v>
+        <v>12.38612889810758</v>
       </c>
       <c r="F509" t="n">
         <v>2916169</v>
@@ -10632,16 +10632,16 @@
         <v>44972</v>
       </c>
       <c r="B511" t="n">
-        <v>12.75351428985596</v>
+        <v>12.75351333618164</v>
       </c>
       <c r="C511" t="n">
-        <v>12.94595337825676</v>
+        <v>12.94595241019235</v>
       </c>
       <c r="D511" t="n">
-        <v>11.91377656401778</v>
+        <v>11.91377567313685</v>
       </c>
       <c r="E511" t="n">
-        <v>12.24617250152178</v>
+        <v>12.24617158578515</v>
       </c>
       <c r="F511" t="n">
         <v>3838217</v>
@@ -10652,16 +10652,16 @@
         <v>44973</v>
       </c>
       <c r="B512" t="n">
-        <v>12.86722850799561</v>
+        <v>12.86722755432129</v>
       </c>
       <c r="C512" t="n">
-        <v>12.98969043678491</v>
+        <v>12.98968947403414</v>
       </c>
       <c r="D512" t="n">
-        <v>12.61355845261168</v>
+        <v>12.6135575177385</v>
       </c>
       <c r="E512" t="n">
-        <v>12.64854661261404</v>
+        <v>12.64854567514766</v>
       </c>
       <c r="F512" t="n">
         <v>1907195</v>
@@ -10672,16 +10672,16 @@
         <v>44974</v>
       </c>
       <c r="B513" t="n">
-        <v>12.78850364685059</v>
+        <v>12.78850173950195</v>
       </c>
       <c r="C513" t="n">
-        <v>12.85848165224856</v>
+        <v>12.85847973446302</v>
       </c>
       <c r="D513" t="n">
-        <v>12.6310527136075</v>
+        <v>12.63105082974197</v>
       </c>
       <c r="E513" t="n">
-        <v>12.84098757199671</v>
+        <v>12.84098565682033</v>
       </c>
       <c r="F513" t="n">
         <v>1180399</v>
@@ -10692,16 +10692,16 @@
         <v>44979</v>
       </c>
       <c r="B514" t="n">
-        <v>12.63979816436768</v>
+        <v>12.63979911804199</v>
       </c>
       <c r="C514" t="n">
-        <v>12.70977616096641</v>
+        <v>12.70977711992058</v>
       </c>
       <c r="D514" t="n">
-        <v>12.33364421869941</v>
+        <v>12.33364514927437</v>
       </c>
       <c r="E514" t="n">
-        <v>12.70102912194036</v>
+        <v>12.70103008023456</v>
       </c>
       <c r="F514" t="n">
         <v>1228758</v>
@@ -10752,16 +10752,16 @@
         <v>44984</v>
       </c>
       <c r="B517" t="n">
-        <v>11.64261150360107</v>
+        <v>11.64261054992676</v>
       </c>
       <c r="C517" t="n">
-        <v>11.87004043423472</v>
+        <v>11.87003946193115</v>
       </c>
       <c r="D517" t="n">
-        <v>11.51140253755071</v>
+        <v>11.51140159462404</v>
       </c>
       <c r="E517" t="n">
-        <v>11.77382046965144</v>
+        <v>11.77381950522948</v>
       </c>
       <c r="F517" t="n">
         <v>3613283</v>
@@ -10792,16 +10792,16 @@
         <v>44986</v>
       </c>
       <c r="B519" t="n">
-        <v>11.74757862091064</v>
+        <v>11.74757766723633</v>
       </c>
       <c r="C519" t="n">
-        <v>11.78256762271401</v>
+        <v>11.78256666619927</v>
       </c>
       <c r="D519" t="n">
-        <v>11.39768860287697</v>
+        <v>11.3976876776069</v>
       </c>
       <c r="E519" t="n">
-        <v>11.61636965359921</v>
+        <v>11.6163687105765</v>
       </c>
       <c r="F519" t="n">
         <v>4662539</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.26366806030273</v>
+        <v>12.26366710662842</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738295346679</v>
+        <v>12.37738199094953</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87004113878769</v>
+        <v>11.87004021572346</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12371120393195</v>
+        <v>12.12371026114126</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10932,16 +10932,16 @@
         <v>44995</v>
       </c>
       <c r="B526" t="n">
-        <v>12.59606266021729</v>
+        <v>12.5960636138916</v>
       </c>
       <c r="C526" t="n">
-        <v>12.78850258010713</v>
+        <v>12.78850354835147</v>
       </c>
       <c r="D526" t="n">
-        <v>12.31615066197402</v>
+        <v>12.31615159445562</v>
       </c>
       <c r="E526" t="n">
-        <v>12.6485457387903</v>
+        <v>12.64854669643821</v>
       </c>
       <c r="F526" t="n">
         <v>1798565</v>
@@ -11012,16 +11012,16 @@
         <v>45001</v>
       </c>
       <c r="B530" t="n">
-        <v>12.44736099243164</v>
+        <v>12.44735908508301</v>
       </c>
       <c r="C530" t="n">
-        <v>12.63105305095858</v>
+        <v>12.63105111546223</v>
       </c>
       <c r="D530" t="n">
-        <v>12.28991005498334</v>
+        <v>12.28990817176142</v>
       </c>
       <c r="E530" t="n">
-        <v>12.35114017969545</v>
+        <v>12.35113828709104</v>
       </c>
       <c r="F530" t="n">
         <v>3275478</v>
@@ -11052,16 +11052,16 @@
         <v>45005</v>
       </c>
       <c r="B532" t="n">
-        <v>11.36269760131836</v>
+        <v>11.36269855499268</v>
       </c>
       <c r="C532" t="n">
-        <v>11.90502749511903</v>
+        <v>11.90502849431124</v>
       </c>
       <c r="D532" t="n">
-        <v>11.17025768990678</v>
+        <v>11.17025862742956</v>
       </c>
       <c r="E532" t="n">
-        <v>11.73008250392448</v>
+        <v>11.73008348843351</v>
       </c>
       <c r="F532" t="n">
         <v>5506849</v>
@@ -11152,16 +11152,16 @@
         <v>45012</v>
       </c>
       <c r="B537" t="n">
-        <v>11.36269760131836</v>
+        <v>11.36269855499268</v>
       </c>
       <c r="C537" t="n">
-        <v>11.52889555350197</v>
+        <v>11.52889652112532</v>
       </c>
       <c r="D537" t="n">
-        <v>11.12652165265694</v>
+        <v>11.12652258650894</v>
       </c>
       <c r="E537" t="n">
-        <v>11.18775261012382</v>
+        <v>11.18775354911495</v>
       </c>
       <c r="F537" t="n">
         <v>2536971</v>
@@ -11312,16 +11312,16 @@
         <v>45022</v>
       </c>
       <c r="B545" t="n">
-        <v>10.8028736114502</v>
+        <v>10.80287265777588</v>
       </c>
       <c r="C545" t="n">
-        <v>11.10902928820433</v>
+        <v>11.10902830750268</v>
       </c>
       <c r="D545" t="n">
-        <v>10.46173145764599</v>
+        <v>10.4617305340876</v>
       </c>
       <c r="E545" t="n">
-        <v>10.71540152345793</v>
+        <v>10.71540057750562</v>
       </c>
       <c r="F545" t="n">
         <v>8557394</v>
@@ -11352,16 +11352,16 @@
         <v>45027</v>
       </c>
       <c r="B547" t="n">
-        <v>11.85254669189453</v>
+        <v>11.85254573822021</v>
       </c>
       <c r="C547" t="n">
-        <v>11.87878781209517</v>
+        <v>11.87878685630945</v>
       </c>
       <c r="D547" t="n">
-        <v>10.9690720636722</v>
+        <v>10.96907118108362</v>
       </c>
       <c r="E547" t="n">
-        <v>10.9690720636722</v>
+        <v>10.96907118108362</v>
       </c>
       <c r="F547" t="n">
         <v>9432295</v>
@@ -11392,16 +11392,16 @@
         <v>45029</v>
       </c>
       <c r="B549" t="n">
-        <v>12.45610618591309</v>
+        <v>12.4561071395874</v>
       </c>
       <c r="C549" t="n">
-        <v>12.64854525626645</v>
+        <v>12.64854622467444</v>
       </c>
       <c r="D549" t="n">
-        <v>11.97500640454174</v>
+        <v>11.97500732138171</v>
       </c>
       <c r="E549" t="n">
-        <v>12.09746832019902</v>
+        <v>12.09746924641502</v>
       </c>
       <c r="F549" t="n">
         <v>4483641</v>
@@ -11412,16 +11412,16 @@
         <v>45030</v>
       </c>
       <c r="B550" t="n">
-        <v>12.52608585357666</v>
+        <v>12.52608489990234</v>
       </c>
       <c r="C550" t="n">
-        <v>12.72727283202282</v>
+        <v>12.72727186303112</v>
       </c>
       <c r="D550" t="n">
-        <v>12.22867890602208</v>
+        <v>12.22867797499086</v>
       </c>
       <c r="E550" t="n">
-        <v>12.42111800204363</v>
+        <v>12.42111705636105</v>
       </c>
       <c r="F550" t="n">
         <v>2806225</v>
@@ -11472,16 +11472,16 @@
         <v>45035</v>
       </c>
       <c r="B553" t="n">
-        <v>11.31021404266357</v>
+        <v>11.31021499633789</v>
       </c>
       <c r="C553" t="n">
-        <v>11.56388576180702</v>
+        <v>11.56388673687087</v>
       </c>
       <c r="D553" t="n">
-        <v>11.11777496732528</v>
+        <v>11.11777590477318</v>
       </c>
       <c r="E553" t="n">
-        <v>11.4326759614931</v>
+        <v>11.43267692549338</v>
       </c>
       <c r="F553" t="n">
         <v>6310878</v>
@@ -11552,16 +11552,16 @@
         <v>45042</v>
       </c>
       <c r="B557" t="n">
-        <v>11.25773143768311</v>
+        <v>11.25773239135742</v>
       </c>
       <c r="C557" t="n">
-        <v>11.49390740377979</v>
+        <v>11.49390837746124</v>
       </c>
       <c r="D557" t="n">
-        <v>11.21399539720453</v>
+        <v>11.21399634717384</v>
       </c>
       <c r="E557" t="n">
-        <v>11.24898355583121</v>
+        <v>11.24898450876447</v>
       </c>
       <c r="F557" t="n">
         <v>2213905</v>
@@ -11652,16 +11652,16 @@
         <v>45050</v>
       </c>
       <c r="B562" t="n">
-        <v>9.429553031921387</v>
+        <v>9.42955207824707</v>
       </c>
       <c r="C562" t="n">
-        <v>10.19056485620714</v>
+        <v>10.19056382556656</v>
       </c>
       <c r="D562" t="n">
-        <v>9.324585186754883</v>
+        <v>9.324584243696673</v>
       </c>
       <c r="E562" t="n">
-        <v>10.14682881551792</v>
+        <v>10.14682778930066</v>
       </c>
       <c r="F562" t="n">
         <v>16781627</v>
@@ -11692,16 +11692,16 @@
         <v>45054</v>
       </c>
       <c r="B564" t="n">
-        <v>9.960693359375</v>
+        <v>9.960692405700684</v>
       </c>
       <c r="C564" t="n">
-        <v>10.13590312215261</v>
+        <v>10.13590215170305</v>
       </c>
       <c r="D564" t="n">
-        <v>9.75920107784351</v>
+        <v>9.759200143460824</v>
       </c>
       <c r="E564" t="n">
-        <v>10.10962144686852</v>
+        <v>10.10962047893527</v>
       </c>
       <c r="F564" t="n">
         <v>5548545</v>
@@ -11732,16 +11732,16 @@
         <v>45056</v>
       </c>
       <c r="B566" t="n">
-        <v>10.00449562072754</v>
+        <v>10.00449466705322</v>
       </c>
       <c r="C566" t="n">
-        <v>10.33739546432518</v>
+        <v>10.33739447891732</v>
       </c>
       <c r="D566" t="n">
-        <v>9.969454508577106</v>
+        <v>9.969453558243071</v>
       </c>
       <c r="E566" t="n">
-        <v>10.24979099700936</v>
+        <v>10.24979001995237</v>
       </c>
       <c r="F566" t="n">
         <v>5572472</v>
@@ -11792,16 +11792,16 @@
         <v>45061</v>
       </c>
       <c r="B569" t="n">
-        <v>10.15342330932617</v>
+        <v>10.15342426300049</v>
       </c>
       <c r="C569" t="n">
-        <v>10.21474693494698</v>
+        <v>10.2147478943812</v>
       </c>
       <c r="D569" t="n">
-        <v>9.986973829842441</v>
+        <v>9.98697476788276</v>
       </c>
       <c r="E569" t="n">
-        <v>10.1621844297504</v>
+        <v>10.16218538424762</v>
       </c>
       <c r="F569" t="n">
         <v>4041445</v>
@@ -11812,16 +11812,16 @@
         <v>45062</v>
       </c>
       <c r="B570" t="n">
-        <v>9.951933860778809</v>
+        <v>9.951932907104492</v>
       </c>
       <c r="C570" t="n">
-        <v>10.35491592496318</v>
+        <v>10.35491493267188</v>
       </c>
       <c r="D570" t="n">
-        <v>9.864328550800552</v>
+        <v>9.864327605521281</v>
       </c>
       <c r="E570" t="n">
-        <v>10.17970614847653</v>
+        <v>10.17970517297524</v>
       </c>
       <c r="F570" t="n">
         <v>2372207</v>
@@ -11832,16 +11832,16 @@
         <v>45063</v>
       </c>
       <c r="B571" t="n">
-        <v>10.0745792388916</v>
+        <v>10.07458019256592</v>
       </c>
       <c r="C571" t="n">
-        <v>10.1446631422258</v>
+        <v>10.14466410253436</v>
       </c>
       <c r="D571" t="n">
-        <v>9.934411432223198</v>
+        <v>9.934412372629026</v>
       </c>
       <c r="E571" t="n">
-        <v>9.986973937988964</v>
+        <v>9.986974883370435</v>
       </c>
       <c r="F571" t="n">
         <v>5003473</v>
@@ -11872,16 +11872,16 @@
         <v>45065</v>
       </c>
       <c r="B573" t="n">
-        <v>11.44121742248535</v>
+        <v>11.44121837615967</v>
       </c>
       <c r="C573" t="n">
-        <v>12.00188946999683</v>
+        <v>12.00189047040555</v>
       </c>
       <c r="D573" t="n">
-        <v>10.51260363211687</v>
+        <v>10.51260450838727</v>
       </c>
       <c r="E573" t="n">
-        <v>10.60897004964872</v>
+        <v>10.60897093395166</v>
       </c>
       <c r="F573" t="n">
         <v>14298668</v>
@@ -11932,16 +11932,16 @@
         <v>45070</v>
       </c>
       <c r="B576" t="n">
-        <v>10.93310928344727</v>
+        <v>10.93310832977295</v>
       </c>
       <c r="C576" t="n">
-        <v>11.28353051793955</v>
+        <v>11.28352953369865</v>
       </c>
       <c r="D576" t="n">
-        <v>10.92434900562591</v>
+        <v>10.92434805271574</v>
       </c>
       <c r="E576" t="n">
-        <v>11.0820382237595</v>
+        <v>11.0820372570944</v>
       </c>
       <c r="F576" t="n">
         <v>2685985</v>
@@ -11972,16 +11972,16 @@
         <v>45072</v>
       </c>
       <c r="B578" t="n">
-        <v>11.67775058746338</v>
+        <v>11.6777515411377</v>
       </c>
       <c r="C578" t="n">
-        <v>11.90552368174234</v>
+        <v>11.90552465401795</v>
       </c>
       <c r="D578" t="n">
-        <v>11.47625916626848</v>
+        <v>11.47626010348781</v>
       </c>
       <c r="E578" t="n">
-        <v>11.54634306551281</v>
+        <v>11.54634400845561</v>
       </c>
       <c r="F578" t="n">
         <v>3617321</v>
@@ -12012,16 +12012,16 @@
         <v>45076</v>
       </c>
       <c r="B580" t="n">
-        <v>11.21344470977783</v>
+        <v>11.21344566345215</v>
       </c>
       <c r="C580" t="n">
-        <v>11.82668012549439</v>
+        <v>11.82668113132278</v>
       </c>
       <c r="D580" t="n">
-        <v>11.12584025286816</v>
+        <v>11.12584119909194</v>
       </c>
       <c r="E580" t="n">
-        <v>11.6689909221993</v>
+        <v>11.66899191461664</v>
       </c>
       <c r="F580" t="n">
         <v>4905847</v>
@@ -12032,16 +12032,16 @@
         <v>45077</v>
       </c>
       <c r="B581" t="n">
-        <v>11.27476787567139</v>
+        <v>11.2747688293457</v>
       </c>
       <c r="C581" t="n">
-        <v>11.46749902256062</v>
+        <v>11.46749999253707</v>
       </c>
       <c r="D581" t="n">
-        <v>11.07327645214257</v>
+        <v>11.07327738877377</v>
       </c>
       <c r="E581" t="n">
-        <v>11.20468397561525</v>
+        <v>11.20468492336154</v>
       </c>
       <c r="F581" t="n">
         <v>3703640</v>
@@ -12112,16 +12112,16 @@
         <v>45083</v>
       </c>
       <c r="B585" t="n">
-        <v>12.53628158569336</v>
+        <v>12.53628063201904</v>
       </c>
       <c r="C585" t="n">
-        <v>12.73777302495092</v>
+        <v>12.73777205594852</v>
       </c>
       <c r="D585" t="n">
-        <v>11.88800419436395</v>
+        <v>11.88800329000613</v>
       </c>
       <c r="E585" t="n">
-        <v>11.91428502633423</v>
+        <v>11.91428411997714</v>
       </c>
       <c r="F585" t="n">
         <v>8194955</v>
@@ -12152,16 +12152,16 @@
         <v>45086</v>
       </c>
       <c r="B587" t="n">
-        <v>12.79033470153809</v>
+        <v>12.7903356552124</v>
       </c>
       <c r="C587" t="n">
-        <v>13.01810780144024</v>
+        <v>13.0181087720978</v>
       </c>
       <c r="D587" t="n">
-        <v>12.60636467234733</v>
+        <v>12.60636561230446</v>
       </c>
       <c r="E587" t="n">
-        <v>12.69396997030039</v>
+        <v>12.69397091678955</v>
       </c>
       <c r="F587" t="n">
         <v>3362705</v>
@@ -12192,16 +12192,16 @@
         <v>45090</v>
       </c>
       <c r="B589" t="n">
-        <v>12.52752208709717</v>
+        <v>12.52752113342285</v>
       </c>
       <c r="C589" t="n">
-        <v>13.04439113335547</v>
+        <v>13.04439014033381</v>
       </c>
       <c r="D589" t="n">
-        <v>12.29974811477101</v>
+        <v>12.29974717843629</v>
       </c>
       <c r="E589" t="n">
-        <v>12.86042108077874</v>
+        <v>12.86042010176204</v>
       </c>
       <c r="F589" t="n">
         <v>6116837</v>
@@ -12252,16 +12252,16 @@
         <v>45093</v>
       </c>
       <c r="B592" t="n">
-        <v>11.92304420471191</v>
+        <v>11.92304515838623</v>
       </c>
       <c r="C592" t="n">
-        <v>12.76405352392952</v>
+        <v>12.76405454487264</v>
       </c>
       <c r="D592" t="n">
-        <v>11.66023000494414</v>
+        <v>11.66023093759705</v>
       </c>
       <c r="E592" t="n">
-        <v>12.76405352392952</v>
+        <v>12.76405454487264</v>
       </c>
       <c r="F592" t="n">
         <v>19648730</v>
@@ -12392,16 +12392,16 @@
         <v>45104</v>
       </c>
       <c r="B599" t="n">
-        <v>10.52486133575439</v>
+        <v>10.52486228942871</v>
       </c>
       <c r="C599" t="n">
-        <v>10.94054938590718</v>
+        <v>10.94055037724765</v>
       </c>
       <c r="D599" t="n">
-        <v>10.41872837808194</v>
+        <v>10.41872932213938</v>
       </c>
       <c r="E599" t="n">
-        <v>10.58677286033232</v>
+        <v>10.58677381961654</v>
       </c>
       <c r="F599" t="n">
         <v>17154900</v>
@@ -12452,16 +12452,16 @@
         <v>45107</v>
       </c>
       <c r="B602" t="n">
-        <v>10.71059417724609</v>
+        <v>10.71059513092041</v>
       </c>
       <c r="C602" t="n">
-        <v>11.12628222564065</v>
+        <v>11.12628321632794</v>
       </c>
       <c r="D602" t="n">
-        <v>10.56023894364529</v>
+        <v>10.56023988393194</v>
       </c>
       <c r="E602" t="n">
-        <v>10.83441638240845</v>
+        <v>10.83441734710793</v>
       </c>
       <c r="F602" t="n">
         <v>11622700</v>
@@ -12472,16 +12472,16 @@
         <v>45110</v>
       </c>
       <c r="B603" t="n">
-        <v>10.79019451141357</v>
+        <v>10.79019355773926</v>
       </c>
       <c r="C603" t="n">
-        <v>11.0024604338354</v>
+        <v>11.00245946140029</v>
       </c>
       <c r="D603" t="n">
-        <v>10.66637314506908</v>
+        <v>10.66637220233851</v>
       </c>
       <c r="E603" t="n">
-        <v>10.83441678945224</v>
+        <v>10.8344158318694</v>
       </c>
       <c r="F603" t="n">
         <v>4753300</v>
@@ -12552,16 +12552,16 @@
         <v>45114</v>
       </c>
       <c r="B607" t="n">
-        <v>10.52486133575439</v>
+        <v>10.52486228942871</v>
       </c>
       <c r="C607" t="n">
-        <v>10.71943884655545</v>
+        <v>10.71943981786074</v>
       </c>
       <c r="D607" t="n">
-        <v>10.40103997353808</v>
+        <v>10.40104091599275</v>
       </c>
       <c r="E607" t="n">
-        <v>10.52486133575439</v>
+        <v>10.52486228942871</v>
       </c>
       <c r="F607" t="n">
         <v>9448200</v>
@@ -12612,16 +12612,16 @@
         <v>45119</v>
       </c>
       <c r="B610" t="n">
-        <v>10.40988445281982</v>
+        <v>10.40988540649414</v>
       </c>
       <c r="C610" t="n">
-        <v>10.7725055973601</v>
+        <v>10.772506584255</v>
       </c>
       <c r="D610" t="n">
-        <v>10.39219520505212</v>
+        <v>10.39219615710589</v>
       </c>
       <c r="E610" t="n">
-        <v>10.61330574132983</v>
+        <v>10.61330671364005</v>
       </c>
       <c r="F610" t="n">
         <v>7787100</v>
@@ -12712,16 +12712,16 @@
         <v>45126</v>
       </c>
       <c r="B615" t="n">
-        <v>9.905752182006836</v>
+        <v>9.905753135681152</v>
       </c>
       <c r="C615" t="n">
-        <v>10.2418403094077</v>
+        <v>10.24184129543884</v>
       </c>
       <c r="D615" t="n">
-        <v>9.720019291692406</v>
+        <v>9.720020227485323</v>
       </c>
       <c r="E615" t="n">
-        <v>10.2418403094077</v>
+        <v>10.24184129543884</v>
       </c>
       <c r="F615" t="n">
         <v>11108100</v>
@@ -12772,16 +12772,16 @@
         <v>45131</v>
       </c>
       <c r="B618" t="n">
-        <v>10.52486133575439</v>
+        <v>10.52486228942871</v>
       </c>
       <c r="C618" t="n">
-        <v>10.64868354144048</v>
+        <v>10.64868450633452</v>
       </c>
       <c r="D618" t="n">
-        <v>10.40988459754489</v>
+        <v>10.40988554080099</v>
       </c>
       <c r="E618" t="n">
-        <v>10.62215051288981</v>
+        <v>10.62215147537965</v>
       </c>
       <c r="F618" t="n">
         <v>4297000</v>
@@ -12852,16 +12852,16 @@
         <v>45135</v>
       </c>
       <c r="B622" t="n">
-        <v>10.3568172454834</v>
+        <v>10.35681819915771</v>
       </c>
       <c r="C622" t="n">
-        <v>10.39219489649865</v>
+        <v>10.3921958534306</v>
       </c>
       <c r="D622" t="n">
-        <v>10.1887736140284</v>
+        <v>10.18877455222896</v>
       </c>
       <c r="E622" t="n">
-        <v>10.34797262186215</v>
+        <v>10.34797357472204</v>
       </c>
       <c r="F622" t="n">
         <v>4029200</v>
@@ -12912,16 +12912,16 @@
         <v>45140</v>
       </c>
       <c r="B625" t="n">
-        <v>10.40988445281982</v>
+        <v>10.40988540649414</v>
       </c>
       <c r="C625" t="n">
-        <v>10.83441627760753</v>
+        <v>10.83441727017422</v>
       </c>
       <c r="D625" t="n">
-        <v>10.25068459678955</v>
+        <v>10.25068553587919</v>
       </c>
       <c r="E625" t="n">
-        <v>10.66637264116317</v>
+        <v>10.66637361833498</v>
       </c>
       <c r="F625" t="n">
         <v>9104400</v>
@@ -12952,16 +12952,16 @@
         <v>45142</v>
       </c>
       <c r="B627" t="n">
-        <v>10.71943855285645</v>
+        <v>10.71943950653076</v>
       </c>
       <c r="C627" t="n">
-        <v>11.21472651856076</v>
+        <v>11.21472751629927</v>
       </c>
       <c r="D627" t="n">
-        <v>10.59561635056293</v>
+        <v>10.59561729322118</v>
       </c>
       <c r="E627" t="n">
-        <v>10.70175014879723</v>
+        <v>10.70175110089786</v>
       </c>
       <c r="F627" t="n">
         <v>16706200</v>
@@ -13032,16 +13032,16 @@
         <v>45148</v>
       </c>
       <c r="B631" t="n">
-        <v>10.63099479675293</v>
+        <v>10.63099575042725</v>
       </c>
       <c r="C631" t="n">
-        <v>10.86094910928421</v>
+        <v>10.86095008358703</v>
       </c>
       <c r="D631" t="n">
-        <v>10.5248609990065</v>
+        <v>10.52486194315988</v>
       </c>
       <c r="E631" t="n">
-        <v>10.66637244817849</v>
+        <v>10.66637340502643</v>
       </c>
       <c r="F631" t="n">
         <v>4975000</v>
@@ -13052,16 +13052,16 @@
         <v>45149</v>
       </c>
       <c r="B632" t="n">
-        <v>10.44526195526123</v>
+        <v>10.44526290893555</v>
       </c>
       <c r="C632" t="n">
-        <v>10.78134922333564</v>
+        <v>10.78135020769543</v>
       </c>
       <c r="D632" t="n">
-        <v>10.39219505618805</v>
+        <v>10.39219600501725</v>
       </c>
       <c r="E632" t="n">
-        <v>10.56908331398241</v>
+        <v>10.56908427896187</v>
       </c>
       <c r="F632" t="n">
         <v>4348800</v>
@@ -13072,16 +13072,16 @@
         <v>45152</v>
       </c>
       <c r="B633" t="n">
-        <v>10.44526195526123</v>
+        <v>10.44526290893555</v>
       </c>
       <c r="C633" t="n">
-        <v>10.60446096554128</v>
+        <v>10.6044619337508</v>
       </c>
       <c r="D633" t="n">
-        <v>10.27721747775428</v>
+        <v>10.27721841608578</v>
       </c>
       <c r="E633" t="n">
-        <v>10.42757270774692</v>
+        <v>10.42757365980617</v>
       </c>
       <c r="F633" t="n">
         <v>3064200</v>
@@ -13132,16 +13132,16 @@
         <v>45155</v>
       </c>
       <c r="B636" t="n">
-        <v>10.13570690155029</v>
+        <v>10.13570785522461</v>
       </c>
       <c r="C636" t="n">
-        <v>10.51601728953731</v>
+        <v>10.51601827899524</v>
       </c>
       <c r="D636" t="n">
-        <v>10.10917387366996</v>
+        <v>10.10917482484777</v>
       </c>
       <c r="E636" t="n">
-        <v>10.43641736242656</v>
+        <v>10.43641834439489</v>
       </c>
       <c r="F636" t="n">
         <v>6587600</v>
@@ -13192,16 +13192,16 @@
         <v>45160</v>
       </c>
       <c r="B639" t="n">
-        <v>10.63099479675293</v>
+        <v>10.63099575042725</v>
       </c>
       <c r="C639" t="n">
-        <v>10.70175009960405</v>
+        <v>10.70175105962561</v>
       </c>
       <c r="D639" t="n">
-        <v>10.18877373219854</v>
+        <v>10.18877464620255</v>
       </c>
       <c r="E639" t="n">
-        <v>10.24183978760201</v>
+        <v>10.24184070636641</v>
       </c>
       <c r="F639" t="n">
         <v>5680500</v>
@@ -13332,16 +13332,16 @@
         <v>45169</v>
       </c>
       <c r="B646" t="n">
-        <v>10.3568172454834</v>
+        <v>10.35681819915771</v>
       </c>
       <c r="C646" t="n">
-        <v>10.71059375563589</v>
+        <v>10.71059474188658</v>
       </c>
       <c r="D646" t="n">
-        <v>10.27721731983166</v>
+        <v>10.27721826617627</v>
       </c>
       <c r="E646" t="n">
-        <v>10.59561617896889</v>
+        <v>10.59561715463224</v>
       </c>
       <c r="F646" t="n">
         <v>8716900</v>
@@ -13392,16 +13392,16 @@
         <v>45174</v>
       </c>
       <c r="B649" t="n">
-        <v>10.21530723571777</v>
+        <v>10.21530818939209</v>
       </c>
       <c r="C649" t="n">
-        <v>10.73712825115294</v>
+        <v>10.7371292535431</v>
       </c>
       <c r="D649" t="n">
-        <v>10.21530723571777</v>
+        <v>10.21530818939209</v>
       </c>
       <c r="E649" t="n">
-        <v>10.73712825115294</v>
+        <v>10.7371292535431</v>
       </c>
       <c r="F649" t="n">
         <v>8659200</v>
@@ -13532,16 +13532,16 @@
         <v>45184</v>
       </c>
       <c r="B656" t="n">
-        <v>9.375086784362793</v>
+        <v>9.375087738037109</v>
       </c>
       <c r="C656" t="n">
-        <v>10.00304072162537</v>
+        <v>10.00304173917788</v>
       </c>
       <c r="D656" t="n">
-        <v>9.375086784362793</v>
+        <v>9.375087738037109</v>
       </c>
       <c r="E656" t="n">
-        <v>9.923440796082692</v>
+        <v>9.923441805537948</v>
       </c>
       <c r="F656" t="n">
         <v>14904000</v>
@@ -13552,16 +13552,16 @@
         <v>45187</v>
       </c>
       <c r="B657" t="n">
-        <v>8.84442138671875</v>
+        <v>8.844422340393066</v>
       </c>
       <c r="C657" t="n">
-        <v>9.322020107862773</v>
+        <v>9.322021113035499</v>
       </c>
       <c r="D657" t="n">
-        <v>8.773666083102581</v>
+        <v>8.773667029147509</v>
       </c>
       <c r="E657" t="n">
-        <v>9.322020107862773</v>
+        <v>9.322021113035499</v>
       </c>
       <c r="F657" t="n">
         <v>19156300</v>
@@ -13572,16 +13572,16 @@
         <v>45188</v>
       </c>
       <c r="B658" t="n">
-        <v>8.800198554992676</v>
+        <v>8.800199508666992</v>
       </c>
       <c r="C658" t="n">
-        <v>8.950553776543289</v>
+        <v>8.950554746511546</v>
       </c>
       <c r="D658" t="n">
-        <v>8.667532579963169</v>
+        <v>8.667533519260521</v>
       </c>
       <c r="E658" t="n">
-        <v>8.844420827825743</v>
+        <v>8.844421786292413</v>
       </c>
       <c r="F658" t="n">
         <v>8872800</v>
@@ -13612,16 +13612,16 @@
         <v>45190</v>
       </c>
       <c r="B660" t="n">
-        <v>8.932866096496582</v>
+        <v>8.932867050170898</v>
       </c>
       <c r="C660" t="n">
-        <v>8.985932153415543</v>
+        <v>8.985933112755202</v>
       </c>
       <c r="D660" t="n">
-        <v>8.738288586364265</v>
+        <v>8.738289519265452</v>
       </c>
       <c r="E660" t="n">
-        <v>8.853266167648371</v>
+        <v>8.853267112824586</v>
       </c>
       <c r="F660" t="n">
         <v>7093000</v>
@@ -13632,16 +13632,16 @@
         <v>45191</v>
       </c>
       <c r="B661" t="n">
-        <v>8.57908821105957</v>
+        <v>8.579089164733887</v>
       </c>
       <c r="C661" t="n">
-        <v>9.003620858146471</v>
+        <v>9.003621859012968</v>
       </c>
       <c r="D661" t="n">
-        <v>8.428732986411056</v>
+        <v>8.428733923371484</v>
       </c>
       <c r="E661" t="n">
-        <v>8.994776234703684</v>
+        <v>8.994777234586989</v>
       </c>
       <c r="F661" t="n">
         <v>16137800</v>
@@ -13732,16 +13732,16 @@
         <v>45198</v>
       </c>
       <c r="B666" t="n">
-        <v>8.623311042785645</v>
+        <v>8.623311996459961</v>
       </c>
       <c r="C666" t="n">
-        <v>8.7559770291329</v>
+        <v>8.755977997479093</v>
       </c>
       <c r="D666" t="n">
-        <v>8.587933390195058</v>
+        <v>8.587934339956869</v>
       </c>
       <c r="E666" t="n">
-        <v>8.702910971981906</v>
+        <v>8.702911934459385</v>
       </c>
       <c r="F666" t="n">
         <v>6662100</v>
@@ -13772,16 +13772,16 @@
         <v>45202</v>
       </c>
       <c r="B668" t="n">
-        <v>7.659268379211426</v>
+        <v>7.659268856048584</v>
       </c>
       <c r="C668" t="n">
-        <v>7.933445798766693</v>
+        <v>7.933446292673103</v>
       </c>
       <c r="D668" t="n">
-        <v>7.570824676122735</v>
+        <v>7.570825147453722</v>
       </c>
       <c r="E668" t="n">
-        <v>7.880378902137712</v>
+        <v>7.880379392740378</v>
       </c>
       <c r="F668" t="n">
         <v>18608300</v>
@@ -13792,16 +13792,16 @@
         <v>45203</v>
       </c>
       <c r="B669" t="n">
-        <v>7.738868236541748</v>
+        <v>7.738869190216064</v>
       </c>
       <c r="C669" t="n">
-        <v>7.853845808701018</v>
+        <v>7.853846776544223</v>
       </c>
       <c r="D669" t="n">
-        <v>7.632735287656968</v>
+        <v>7.632736228252335</v>
       </c>
       <c r="E669" t="n">
-        <v>7.756557483090727</v>
+        <v>7.756558438944921</v>
       </c>
       <c r="F669" t="n">
         <v>14186500</v>
@@ -13812,16 +13812,16 @@
         <v>45204</v>
       </c>
       <c r="B670" t="n">
-        <v>7.68580150604248</v>
+        <v>7.685802459716797</v>
       </c>
       <c r="C670" t="n">
-        <v>7.800779080680249</v>
+        <v>7.800780048621283</v>
       </c>
       <c r="D670" t="n">
-        <v>7.579668554869859</v>
+        <v>7.579669495374922</v>
       </c>
       <c r="E670" t="n">
-        <v>7.73886840336365</v>
+        <v>7.738869363622646</v>
       </c>
       <c r="F670" t="n">
         <v>5277500</v>
@@ -13832,16 +13832,16 @@
         <v>45205</v>
       </c>
       <c r="B671" t="n">
-        <v>7.473536014556885</v>
+        <v>7.473536491394043</v>
       </c>
       <c r="C671" t="n">
-        <v>7.606202843418344</v>
+        <v>7.6062033287201</v>
       </c>
       <c r="D671" t="n">
-        <v>7.385092305452343</v>
+        <v>7.38509277664649</v>
       </c>
       <c r="E671" t="n">
-        <v>7.561980567131191</v>
+        <v>7.561981049611414</v>
       </c>
       <c r="F671" t="n">
         <v>8202400</v>
@@ -13872,16 +13872,16 @@
         <v>45209</v>
       </c>
       <c r="B673" t="n">
-        <v>8.101489067077637</v>
+        <v>8.101490020751953</v>
       </c>
       <c r="C673" t="n">
-        <v>8.189933609727872</v>
+        <v>8.18993457381352</v>
       </c>
       <c r="D673" t="n">
-        <v>7.906911579328923</v>
+        <v>7.906912510098369</v>
       </c>
       <c r="E673" t="n">
-        <v>7.95113385065404</v>
+        <v>7.951134786629153</v>
       </c>
       <c r="F673" t="n">
         <v>9907700</v>
@@ -13912,16 +13912,16 @@
         <v>45212</v>
       </c>
       <c r="B675" t="n">
-        <v>7.561980247497559</v>
+        <v>7.561980724334717</v>
       </c>
       <c r="C675" t="n">
-        <v>7.933446003056718</v>
+        <v>7.933446503317459</v>
       </c>
       <c r="D675" t="n">
-        <v>7.500068725924546</v>
+        <v>7.500069198857738</v>
       </c>
       <c r="E675" t="n">
-        <v>7.898068352216309</v>
+        <v>7.898068850246236</v>
       </c>
       <c r="F675" t="n">
         <v>6681200</v>
@@ -13932,16 +13932,16 @@
         <v>45215</v>
       </c>
       <c r="B676" t="n">
-        <v>7.561980247497559</v>
+        <v>7.561980724334717</v>
       </c>
       <c r="C676" t="n">
-        <v>7.721179254544534</v>
+        <v>7.721179741420333</v>
       </c>
       <c r="D676" t="n">
-        <v>7.473535698661672</v>
+        <v>7.473536169921766</v>
       </c>
       <c r="E676" t="n">
-        <v>7.623890925600842</v>
+        <v>7.623891406341913</v>
       </c>
       <c r="F676" t="n">
         <v>6364500</v>
@@ -13952,16 +13952,16 @@
         <v>45216</v>
       </c>
       <c r="B677" t="n">
-        <v>7.641580104827881</v>
+        <v>7.641581058502197</v>
       </c>
       <c r="C677" t="n">
-        <v>7.668113131854896</v>
+        <v>7.668114088840552</v>
       </c>
       <c r="D677" t="n">
-        <v>7.447002605200417</v>
+        <v>7.447003534591332</v>
       </c>
       <c r="E677" t="n">
-        <v>7.544290933279289</v>
+        <v>7.544291874811851</v>
       </c>
       <c r="F677" t="n">
         <v>6592700</v>
@@ -14232,16 +14232,16 @@
         <v>45237</v>
       </c>
       <c r="B691" t="n">
-        <v>8.357977867126465</v>
+        <v>8.357978820800781</v>
       </c>
       <c r="C691" t="n">
-        <v>8.375667114395791</v>
+        <v>8.37566807008851</v>
       </c>
       <c r="D691" t="n">
-        <v>7.845001504892315</v>
+        <v>7.845002400034246</v>
       </c>
       <c r="E691" t="n">
-        <v>7.871534532326568</v>
+        <v>7.871535430496009</v>
       </c>
       <c r="F691" t="n">
         <v>8029000</v>
@@ -14252,16 +14252,16 @@
         <v>45238</v>
       </c>
       <c r="B692" t="n">
-        <v>8.101489067077637</v>
+        <v>8.101490020751953</v>
       </c>
       <c r="C692" t="n">
-        <v>8.649843038487949</v>
+        <v>8.649844056712263</v>
       </c>
       <c r="D692" t="n">
-        <v>8.013045367897073</v>
+        <v>8.013046311160156</v>
       </c>
       <c r="E692" t="n">
-        <v>8.357977228599713</v>
+        <v>8.357978212466772</v>
       </c>
       <c r="F692" t="n">
         <v>19964500</v>
@@ -14272,16 +14272,16 @@
         <v>45239</v>
       </c>
       <c r="B693" t="n">
-        <v>7.959979057312012</v>
+        <v>7.959980010986328</v>
       </c>
       <c r="C693" t="n">
-        <v>8.189934210289316</v>
+        <v>8.189935191514248</v>
       </c>
       <c r="D693" t="n">
-        <v>7.774246178902609</v>
+        <v>7.77424711032452</v>
       </c>
       <c r="E693" t="n">
-        <v>8.189934210289316</v>
+        <v>8.189935191514248</v>
       </c>
       <c r="F693" t="n">
         <v>11094800</v>
@@ -14392,16 +14392,16 @@
         <v>45250</v>
       </c>
       <c r="B699" t="n">
-        <v>8.932866096496582</v>
+        <v>8.932867050170898</v>
       </c>
       <c r="C699" t="n">
-        <v>8.932866096496582</v>
+        <v>8.932867050170898</v>
       </c>
       <c r="D699" t="n">
-        <v>8.614466381103741</v>
+        <v>8.61446730078565</v>
       </c>
       <c r="E699" t="n">
-        <v>8.676377905468886</v>
+        <v>8.676378831760479</v>
       </c>
       <c r="F699" t="n">
         <v>4921500</v>
@@ -14412,16 +14412,16 @@
         <v>45251</v>
       </c>
       <c r="B700" t="n">
-        <v>8.623311042785645</v>
+        <v>8.623311996459961</v>
       </c>
       <c r="C700" t="n">
-        <v>8.941709916100921</v>
+        <v>8.941710904987794</v>
       </c>
       <c r="D700" t="n">
-        <v>8.614466418770554</v>
+        <v>8.614467371466722</v>
       </c>
       <c r="E700" t="n">
-        <v>8.932866135555601</v>
+        <v>8.932867123464419</v>
       </c>
       <c r="F700" t="n">
         <v>8608600</v>
@@ -14432,16 +14432,16 @@
         <v>45252</v>
       </c>
       <c r="B701" t="n">
-        <v>8.59677791595459</v>
+        <v>8.596778869628906</v>
       </c>
       <c r="C701" t="n">
-        <v>9.030154366103503</v>
+        <v>9.03015536785397</v>
       </c>
       <c r="D701" t="n">
-        <v>8.587933292040589</v>
+        <v>8.587934244733736</v>
       </c>
       <c r="E701" t="n">
-        <v>8.649843972499074</v>
+        <v>8.649844932060216</v>
       </c>
       <c r="F701" t="n">
         <v>12126100</v>
@@ -14492,16 +14492,16 @@
         <v>45257</v>
       </c>
       <c r="B704" t="n">
-        <v>8.092645645141602</v>
+        <v>8.092646598815918</v>
       </c>
       <c r="C704" t="n">
-        <v>8.446423024776681</v>
+        <v>8.446424020141739</v>
       </c>
       <c r="D704" t="n">
-        <v>8.074957240068235</v>
+        <v>8.074958191658068</v>
       </c>
       <c r="E704" t="n">
-        <v>8.411045371160153</v>
+        <v>8.411046362356148</v>
       </c>
       <c r="F704" t="n">
         <v>5901700</v>
@@ -14712,16 +14712,16 @@
         <v>45272</v>
       </c>
       <c r="B715" t="n">
-        <v>8.08380126953125</v>
+        <v>8.083802223205566</v>
       </c>
       <c r="C715" t="n">
-        <v>8.3579778540179</v>
+        <v>8.357978840037788</v>
       </c>
       <c r="D715" t="n">
-        <v>8.066112022289667</v>
+        <v>8.066112973877122</v>
       </c>
       <c r="E715" t="n">
-        <v>8.181089598950749</v>
+        <v>8.18109056410251</v>
       </c>
       <c r="F715" t="n">
         <v>4001400</v>
@@ -14732,16 +14732,16 @@
         <v>45273</v>
       </c>
       <c r="B716" t="n">
-        <v>8.658688545227051</v>
+        <v>8.658689498901367</v>
       </c>
       <c r="C716" t="n">
-        <v>8.71175544492759</v>
+        <v>8.711756404446733</v>
       </c>
       <c r="D716" t="n">
-        <v>8.101489893985299</v>
+        <v>8.101490786289347</v>
       </c>
       <c r="E716" t="n">
-        <v>8.110334517847015</v>
+        <v>8.110335411125217</v>
       </c>
       <c r="F716" t="n">
         <v>4810200</v>
@@ -14752,16 +14752,16 @@
         <v>45274</v>
       </c>
       <c r="B717" t="n">
-        <v>8.623311042785645</v>
+        <v>8.623311996459961</v>
       </c>
       <c r="C717" t="n">
-        <v>8.932866135555601</v>
+        <v>8.932867123464419</v>
       </c>
       <c r="D717" t="n">
-        <v>8.596778014210148</v>
+        <v>8.596778964950108</v>
       </c>
       <c r="E717" t="n">
-        <v>8.685221723951727</v>
+        <v>8.685222684472906</v>
       </c>
       <c r="F717" t="n">
         <v>9075200</v>
@@ -14772,16 +14772,16 @@
         <v>45275</v>
       </c>
       <c r="B718" t="n">
-        <v>8.791355133056641</v>
+        <v>8.791356086730957</v>
       </c>
       <c r="C718" t="n">
-        <v>8.791355133056641</v>
+        <v>8.791356086730957</v>
       </c>
       <c r="D718" t="n">
-        <v>8.534866927739781</v>
+        <v>8.534867853590605</v>
       </c>
       <c r="E718" t="n">
-        <v>8.720599824243012</v>
+        <v>8.720600770241887</v>
       </c>
       <c r="F718" t="n">
         <v>7122400</v>
@@ -14792,16 +14792,16 @@
         <v>45278</v>
       </c>
       <c r="B719" t="n">
-        <v>8.835576057434082</v>
+        <v>8.835577011108398</v>
       </c>
       <c r="C719" t="n">
-        <v>8.977086653367691</v>
+        <v>8.977087622316056</v>
       </c>
       <c r="D719" t="n">
-        <v>8.800198408450679</v>
+        <v>8.800199358306484</v>
       </c>
       <c r="E719" t="n">
-        <v>8.809043031563952</v>
+        <v>8.809043982374407</v>
       </c>
       <c r="F719" t="n">
         <v>3928300</v>
@@ -14812,16 +14812,16 @@
         <v>45279</v>
       </c>
       <c r="B720" t="n">
-        <v>8.879798889160156</v>
+        <v>8.879799842834473</v>
       </c>
       <c r="C720" t="n">
-        <v>8.941709567915471</v>
+        <v>8.941710528238881</v>
       </c>
       <c r="D720" t="n">
-        <v>8.817888210404842</v>
+        <v>8.817889157430063</v>
       </c>
       <c r="E720" t="n">
-        <v>8.932865787714524</v>
+        <v>8.932866747088129</v>
       </c>
       <c r="F720" t="n">
         <v>3267000</v>
@@ -27792,7 +27792,7 @@
         <v>46231</v>
       </c>
       <c r="B1369" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="C1369" t="n">
         <v>3.37</v>
@@ -27804,7 +27804,7 @@
         <v>3.25</v>
       </c>
       <c r="F1369" t="n">
-        <v>11432200</v>
+        <v>14270400</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -512,16 +512,16 @@
         <v>44232</v>
       </c>
       <c r="B5" t="n">
-        <v>6.823331356048584</v>
+        <v>6.823330879211426</v>
       </c>
       <c r="C5" t="n">
-        <v>6.909409992235542</v>
+        <v>6.909409509382922</v>
       </c>
       <c r="D5" t="n">
-        <v>6.699461247702325</v>
+        <v>6.699460779521623</v>
       </c>
       <c r="E5" t="n">
-        <v>6.873718632603384</v>
+        <v>6.873718152244995</v>
       </c>
       <c r="F5" t="n">
         <v>4402737</v>
@@ -532,16 +532,16 @@
         <v>44235</v>
       </c>
       <c r="B6" t="n">
-        <v>7.21173620223999</v>
+        <v>7.211735725402832</v>
       </c>
       <c r="C6" t="n">
-        <v>7.619036269833193</v>
+        <v>7.619035766065515</v>
       </c>
       <c r="D6" t="n">
-        <v>6.82753006666352</v>
+        <v>6.827529615229921</v>
       </c>
       <c r="E6" t="n">
-        <v>6.854823412007115</v>
+        <v>6.85482295876889</v>
       </c>
       <c r="F6" t="n">
         <v>3162478</v>
@@ -552,16 +552,16 @@
         <v>44236</v>
       </c>
       <c r="B7" t="n">
-        <v>7.119358539581299</v>
+        <v>7.119358062744141</v>
       </c>
       <c r="C7" t="n">
-        <v>7.367097937617529</v>
+        <v>7.367097444187393</v>
       </c>
       <c r="D7" t="n">
-        <v>6.953499173999</v>
+        <v>6.953498708270694</v>
       </c>
       <c r="E7" t="n">
-        <v>7.266322575504579</v>
+        <v>7.266322088824129</v>
       </c>
       <c r="F7" t="n">
         <v>1374461</v>
@@ -572,16 +572,16 @@
         <v>44237</v>
       </c>
       <c r="B8" t="n">
-        <v>6.928304672241211</v>
+        <v>6.928305625915527</v>
       </c>
       <c r="C8" t="n">
-        <v>7.18024265496158</v>
+        <v>7.180243643314912</v>
       </c>
       <c r="D8" t="n">
-        <v>6.749848296724684</v>
+        <v>6.749849225834657</v>
       </c>
       <c r="E8" t="n">
-        <v>7.18024265496158</v>
+        <v>7.180243643314912</v>
       </c>
       <c r="F8" t="n">
         <v>3511567</v>
@@ -592,16 +592,16 @@
         <v>44238</v>
       </c>
       <c r="B9" t="n">
-        <v>6.963996410369873</v>
+        <v>6.963996887207031</v>
       </c>
       <c r="C9" t="n">
-        <v>7.058473057595991</v>
+        <v>7.058473540902132</v>
       </c>
       <c r="D9" t="n">
-        <v>6.850623621904003</v>
+        <v>6.850624090978325</v>
       </c>
       <c r="E9" t="n">
-        <v>6.928305052130111</v>
+        <v>6.928305526523419</v>
       </c>
       <c r="F9" t="n">
         <v>1655030</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029080390930176</v>
+        <v>7.029080867767334</v>
       </c>
       <c r="C10" t="n">
-        <v>7.194939754112628</v>
+        <v>7.194940242201317</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913608302177867</v>
+        <v>6.913608771181656</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949299660305043</v>
+        <v>6.949300131730055</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -632,16 +632,16 @@
         <v>44244</v>
       </c>
       <c r="B11" t="n">
-        <v>7.274720668792725</v>
+        <v>7.274720191955566</v>
       </c>
       <c r="C11" t="n">
-        <v>7.388092647974826</v>
+        <v>7.388092163706458</v>
       </c>
       <c r="D11" t="n">
-        <v>7.11305990280828</v>
+        <v>7.113059436567523</v>
       </c>
       <c r="E11" t="n">
-        <v>7.11725931599718</v>
+        <v>7.117258849481164</v>
       </c>
       <c r="F11" t="n">
         <v>2613098</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.30621337890625</v>
+        <v>7.306213855743408</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724010745681502</v>
+        <v>7.724011249786042</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050075153474859</v>
+        <v>7.050075613595256</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054274566636445</v>
+        <v>7.054275027030914</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.30621337890625</v>
+        <v>7.306213855743408</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480470759734867</v>
+        <v>7.480471247944865</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243227864044258</v>
+        <v>7.243228336770691</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308311867795231</v>
+        <v>7.308312344769346</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400689808525235</v>
+        <v>7.400690302893193</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945100983960817</v>
+        <v>6.945101447895325</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360799849541025</v>
+        <v>7.360800341244324</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -772,16 +772,16 @@
         <v>44253</v>
       </c>
       <c r="B18" t="n">
-        <v>7.243227481842041</v>
+        <v>7.243227958679199</v>
       </c>
       <c r="C18" t="n">
-        <v>7.480470365014094</v>
+        <v>7.480470857469459</v>
       </c>
       <c r="D18" t="n">
-        <v>6.833828151198126</v>
+        <v>6.833828601083652</v>
       </c>
       <c r="E18" t="n">
-        <v>7.157148852208861</v>
+        <v>7.157149323379279</v>
       </c>
       <c r="F18" t="n">
         <v>1865862</v>
@@ -812,16 +812,16 @@
         <v>44257</v>
       </c>
       <c r="B20" t="n">
-        <v>7.178143501281738</v>
+        <v>7.178143978118896</v>
       </c>
       <c r="C20" t="n">
-        <v>7.178143501281738</v>
+        <v>7.178143978118896</v>
       </c>
       <c r="D20" t="n">
-        <v>6.718356084859394</v>
+        <v>6.718356531153318</v>
       </c>
       <c r="E20" t="n">
-        <v>7.003886129168523</v>
+        <v>7.003886594429932</v>
       </c>
       <c r="F20" t="n">
         <v>1173360</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233019817944</v>
+        <v>7.222233502264944</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966096425558127</v>
+        <v>6.966096890895136</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117259059009463</v>
+        <v>7.117259534444174</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -932,16 +932,16 @@
         <v>44265</v>
       </c>
       <c r="B26" t="n">
-        <v>6.252270698547363</v>
+        <v>6.252270221710205</v>
       </c>
       <c r="C26" t="n">
-        <v>6.592387447038047</v>
+        <v>6.592386944261464</v>
       </c>
       <c r="D26" t="n">
-        <v>6.124201991216056</v>
+        <v>6.124201524146216</v>
       </c>
       <c r="E26" t="n">
-        <v>6.58608954496226</v>
+        <v>6.586089042665994</v>
       </c>
       <c r="F26" t="n">
         <v>1291345</v>
@@ -972,16 +972,16 @@
         <v>44267</v>
       </c>
       <c r="B28" t="n">
-        <v>6.695262908935547</v>
+        <v>6.69526195526123</v>
       </c>
       <c r="C28" t="n">
-        <v>6.896814064768251</v>
+        <v>6.896813082384956</v>
       </c>
       <c r="D28" t="n">
-        <v>6.455921088964289</v>
+        <v>6.45592016938186</v>
       </c>
       <c r="E28" t="n">
-        <v>6.646974928291244</v>
+        <v>6.646973981495075</v>
       </c>
       <c r="F28" t="n">
         <v>3263434</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033280372619629</v>
+        <v>7.033279895782471</v>
       </c>
       <c r="C29" t="n">
-        <v>7.12775702718571</v>
+        <v>7.127756543943293</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969559237991</v>
+        <v>6.667969107167907</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969559237991</v>
+        <v>6.667969107167907</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1032,16 +1032,16 @@
         <v>44272</v>
       </c>
       <c r="B31" t="n">
-        <v>7.558151245117188</v>
+        <v>7.558150768280029</v>
       </c>
       <c r="C31" t="n">
-        <v>7.642130577117119</v>
+        <v>7.642130094981778</v>
       </c>
       <c r="D31" t="n">
-        <v>7.285217807271516</v>
+        <v>7.285217347653489</v>
       </c>
       <c r="E31" t="n">
-        <v>7.390191769322798</v>
+        <v>7.390191303082056</v>
       </c>
       <c r="F31" t="n">
         <v>5070506</v>
@@ -1052,16 +1052,16 @@
         <v>44273</v>
       </c>
       <c r="B32" t="n">
-        <v>7.589643001556396</v>
+        <v>7.589643955230713</v>
       </c>
       <c r="C32" t="n">
-        <v>7.898267789895324</v>
+        <v>7.898268782349795</v>
       </c>
       <c r="D32" t="n">
-        <v>7.459474999602055</v>
+        <v>7.45947593692015</v>
       </c>
       <c r="E32" t="n">
-        <v>7.600140316321165</v>
+        <v>7.600141271314518</v>
       </c>
       <c r="F32" t="n">
         <v>3661176</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.516161441802979</v>
+        <v>7.516162395477295</v>
       </c>
       <c r="C33" t="n">
-        <v>7.778596733861603</v>
+        <v>7.778597720834538</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430081191788996</v>
+        <v>7.430082134541178</v>
       </c>
       <c r="E33" t="n">
-        <v>7.600139955939049</v>
+        <v>7.600140920268824</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1092,16 +1092,16 @@
         <v>44277</v>
       </c>
       <c r="B34" t="n">
-        <v>7.558151245117188</v>
+        <v>7.558150768280029</v>
       </c>
       <c r="C34" t="n">
-        <v>7.807989940470752</v>
+        <v>7.807989447871488</v>
       </c>
       <c r="D34" t="n">
-        <v>7.201238475271585</v>
+        <v>7.201238020951741</v>
       </c>
       <c r="E34" t="n">
-        <v>7.514061872573729</v>
+        <v>7.51406139851813</v>
       </c>
       <c r="F34" t="n">
         <v>5377429</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.516161441802979</v>
+        <v>7.516162395477295</v>
       </c>
       <c r="C35" t="n">
-        <v>7.558150698871014</v>
+        <v>7.55815165787306</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436380716861456</v>
+        <v>7.436381660412942</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511962029019494</v>
+        <v>7.511962982160976</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159248352050781</v>
+        <v>7.159248828887939</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656827250339138</v>
+        <v>7.656827760317221</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159248352050781</v>
+        <v>7.159248828887939</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392291828769327</v>
+        <v>7.392292321128197</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.705114364624023</v>
+        <v>7.705113410949707</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789094507299701</v>
+        <v>7.789093543231029</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033279717574721</v>
+        <v>7.033278847054452</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159248307999206</v>
+        <v>7.159247421887605</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.51826000213623</v>
+        <v>7.518261432647705</v>
       </c>
       <c r="C38" t="n">
-        <v>7.789094122342303</v>
+        <v>7.789095604385824</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455275304139598</v>
+        <v>7.455276722666873</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721910823316651</v>
+        <v>7.721912292577096</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1192,16 +1192,16 @@
         <v>44284</v>
       </c>
       <c r="B39" t="n">
-        <v>7.232730388641357</v>
+        <v>7.232729911804199</v>
       </c>
       <c r="C39" t="n">
-        <v>7.663125173574427</v>
+        <v>7.663124668362338</v>
       </c>
       <c r="D39" t="n">
-        <v>7.232730388641357</v>
+        <v>7.232729911804199</v>
       </c>
       <c r="E39" t="n">
-        <v>7.568648526962992</v>
+        <v>7.568648027979529</v>
       </c>
       <c r="F39" t="n">
         <v>3953908</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379694366927925</v>
+        <v>7.379694859893382</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257924377559402</v>
+        <v>7.257924862390593</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1232,16 +1232,16 @@
         <v>44286</v>
       </c>
       <c r="B41" t="n">
-        <v>7.348202705383301</v>
+        <v>7.348202228546143</v>
       </c>
       <c r="C41" t="n">
-        <v>7.379694651301018</v>
+        <v>7.379694172420294</v>
       </c>
       <c r="D41" t="n">
-        <v>6.997588639911132</v>
+        <v>6.997588185825906</v>
       </c>
       <c r="E41" t="n">
-        <v>7.226432711322428</v>
+        <v>7.226432242387128</v>
       </c>
       <c r="F41" t="n">
         <v>2544984</v>
@@ -1252,16 +1252,16 @@
         <v>44287</v>
       </c>
       <c r="B42" t="n">
-        <v>7.348202705383301</v>
+        <v>7.348202228546143</v>
       </c>
       <c r="C42" t="n">
-        <v>7.524559388470522</v>
+        <v>7.524558900189283</v>
       </c>
       <c r="D42" t="n">
-        <v>7.171846022296081</v>
+        <v>7.171845556903002</v>
       </c>
       <c r="E42" t="n">
-        <v>7.358700020689207</v>
+        <v>7.35869954317086</v>
       </c>
       <c r="F42" t="n">
         <v>877384</v>
@@ -1292,16 +1292,16 @@
         <v>44292</v>
       </c>
       <c r="B44" t="n">
-        <v>7.21173620223999</v>
+        <v>7.211735725402832</v>
       </c>
       <c r="C44" t="n">
-        <v>7.379694875833847</v>
+        <v>7.379694387891328</v>
       </c>
       <c r="D44" t="n">
-        <v>7.190741570989402</v>
+        <v>7.190741095540401</v>
       </c>
       <c r="E44" t="n">
-        <v>7.369197560208552</v>
+        <v>7.369197072960112</v>
       </c>
       <c r="F44" t="n">
         <v>1319726</v>
@@ -1312,16 +1312,16 @@
         <v>44293</v>
       </c>
       <c r="B45" t="n">
-        <v>7.243227481842041</v>
+        <v>7.243227958679199</v>
       </c>
       <c r="C45" t="n">
-        <v>7.388092210073672</v>
+        <v>7.388092696447584</v>
       </c>
       <c r="D45" t="n">
-        <v>7.146651537550619</v>
+        <v>7.146652008029977</v>
       </c>
       <c r="E45" t="n">
-        <v>7.213834838440065</v>
+        <v>7.213835313342242</v>
       </c>
       <c r="F45" t="n">
         <v>1401221</v>
@@ -1332,16 +1332,16 @@
         <v>44294</v>
       </c>
       <c r="B46" t="n">
-        <v>7.589643001556396</v>
+        <v>7.589643955230713</v>
       </c>
       <c r="C46" t="n">
-        <v>7.78909441747052</v>
+        <v>7.789095396206844</v>
       </c>
       <c r="D46" t="n">
-        <v>7.215935024034804</v>
+        <v>7.215935930750956</v>
       </c>
       <c r="E46" t="n">
-        <v>7.2432275553465</v>
+        <v>7.243228465492086</v>
       </c>
       <c r="F46" t="n">
         <v>2111967</v>
@@ -1392,16 +1392,16 @@
         <v>44299</v>
       </c>
       <c r="B49" t="n">
-        <v>7.726110458374023</v>
+        <v>7.726109504699707</v>
       </c>
       <c r="C49" t="n">
-        <v>7.898268547699764</v>
+        <v>7.898267572775072</v>
       </c>
       <c r="D49" t="n">
-        <v>7.642131120403916</v>
+        <v>7.64213017709561</v>
       </c>
       <c r="E49" t="n">
-        <v>7.786995864004779</v>
+        <v>7.786994902815057</v>
       </c>
       <c r="F49" t="n">
         <v>1044023</v>
@@ -1432,16 +1432,16 @@
         <v>44301</v>
       </c>
       <c r="B51" t="n">
-        <v>8.112414360046387</v>
+        <v>8.112415313720703</v>
       </c>
       <c r="C51" t="n">
-        <v>8.185897180089103</v>
+        <v>8.185898142401868</v>
       </c>
       <c r="D51" t="n">
-        <v>7.891968335301526</v>
+        <v>7.891969263060783</v>
       </c>
       <c r="E51" t="n">
-        <v>7.894067635698465</v>
+        <v>7.894068563704509</v>
       </c>
       <c r="F51" t="n">
         <v>2034122</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208992004394531</v>
+        <v>8.208990097045898</v>
       </c>
       <c r="C53" t="n">
-        <v>8.24468336574694</v>
+        <v>8.244681450105466</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059929468278197</v>
+        <v>8.059927595564051</v>
       </c>
       <c r="E53" t="n">
-        <v>8.187997372467679</v>
+        <v>8.187995469997121</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1492,16 +1492,16 @@
         <v>44306</v>
       </c>
       <c r="B54" t="n">
-        <v>8.196394920349121</v>
+        <v>8.196395874023438</v>
       </c>
       <c r="C54" t="n">
-        <v>8.244682079168939</v>
+        <v>8.244683038461606</v>
       </c>
       <c r="D54" t="n">
-        <v>8.078822726880942</v>
+        <v>8.078823666875394</v>
       </c>
       <c r="E54" t="n">
-        <v>8.206892234674447</v>
+        <v>8.206893189570158</v>
       </c>
       <c r="F54" t="n">
         <v>282595</v>
@@ -1512,16 +1512,16 @@
         <v>44308</v>
       </c>
       <c r="B55" t="n">
-        <v>8.183796882629395</v>
+        <v>8.183797836303711</v>
       </c>
       <c r="C55" t="n">
-        <v>8.37065166140985</v>
+        <v>8.370652636858729</v>
       </c>
       <c r="D55" t="n">
-        <v>8.064126209385469</v>
+        <v>8.06412714911432</v>
       </c>
       <c r="E55" t="n">
-        <v>8.259378189563577</v>
+        <v>8.259379152045536</v>
       </c>
       <c r="F55" t="n">
         <v>608979</v>
@@ -1552,16 +1552,16 @@
         <v>44312</v>
       </c>
       <c r="B57" t="n">
-        <v>7.978047370910645</v>
+        <v>7.978049278259277</v>
       </c>
       <c r="C57" t="n">
-        <v>8.18799525959226</v>
+        <v>8.187997217134104</v>
       </c>
       <c r="D57" t="n">
-        <v>7.938156606389738</v>
+        <v>7.938158504201501</v>
       </c>
       <c r="E57" t="n">
-        <v>8.185896771094599</v>
+        <v>8.185898728134749</v>
       </c>
       <c r="F57" t="n">
         <v>1270667</v>
@@ -1572,16 +1572,16 @@
         <v>44313</v>
       </c>
       <c r="B58" t="n">
-        <v>8.116615295410156</v>
+        <v>8.11661434173584</v>
       </c>
       <c r="C58" t="n">
-        <v>8.1837986032776</v>
+        <v>8.183797641709477</v>
       </c>
       <c r="D58" t="n">
-        <v>7.9402586048865</v>
+        <v>7.940257671933487</v>
       </c>
       <c r="E58" t="n">
-        <v>7.999043897796192</v>
+        <v>7.999042957936108</v>
       </c>
       <c r="F58" t="n">
         <v>2786224</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397945404052734</v>
+        <v>8.397944450378418</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469328120611465</v>
+        <v>8.469327158830897</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116613840986611</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116613840986611</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1632,16 +1632,16 @@
         <v>44316</v>
       </c>
       <c r="B61" t="n">
-        <v>8.733863830566406</v>
+        <v>8.733864784240723</v>
       </c>
       <c r="C61" t="n">
-        <v>8.733863830566406</v>
+        <v>8.733864784240723</v>
       </c>
       <c r="D61" t="n">
-        <v>8.580601889171566</v>
+        <v>8.580602826110796</v>
       </c>
       <c r="E61" t="n">
-        <v>8.580601889171566</v>
+        <v>8.580602826110796</v>
       </c>
       <c r="F61" t="n">
         <v>3200590</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849334716796875</v>
+        <v>8.849335670471191</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122268152268145</v>
+        <v>9.122269135355927</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641486095148732</v>
+        <v>8.641487026423638</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733863440724466</v>
+        <v>8.733864381954685</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1692,16 +1692,16 @@
         <v>44321</v>
       </c>
       <c r="B64" t="n">
-        <v>9.783605575561523</v>
+        <v>9.78360652923584</v>
       </c>
       <c r="C64" t="n">
-        <v>9.993554294101639</v>
+        <v>9.99355526824108</v>
       </c>
       <c r="D64" t="n">
-        <v>9.273430912006111</v>
+        <v>9.273431815950246</v>
       </c>
       <c r="E64" t="n">
-        <v>9.298624141267135</v>
+        <v>9.298625047667027</v>
       </c>
       <c r="F64" t="n">
         <v>3818084</v>
@@ -1712,16 +1712,16 @@
         <v>44322</v>
       </c>
       <c r="B65" t="n">
-        <v>9.764712333679199</v>
+        <v>9.764713287353516</v>
       </c>
       <c r="C65" t="n">
-        <v>9.783606852193223</v>
+        <v>9.78360780771288</v>
       </c>
       <c r="D65" t="n">
-        <v>9.537966746386992</v>
+        <v>9.537967677916114</v>
       </c>
       <c r="E65" t="n">
-        <v>9.783606852193223</v>
+        <v>9.78360780771288</v>
       </c>
       <c r="F65" t="n">
         <v>8042425</v>
@@ -1732,16 +1732,16 @@
         <v>44323</v>
       </c>
       <c r="B66" t="n">
-        <v>9.867585182189941</v>
+        <v>9.867586135864258</v>
       </c>
       <c r="C66" t="n">
-        <v>10.05234067674103</v>
+        <v>10.05234164827144</v>
       </c>
       <c r="D66" t="n">
-        <v>9.554762613617749</v>
+        <v>9.554763537058646</v>
       </c>
       <c r="E66" t="n">
-        <v>9.827695224893009</v>
+        <v>9.827696174712075</v>
       </c>
       <c r="F66" t="n">
         <v>7085572</v>
@@ -1752,16 +1752,16 @@
         <v>44326</v>
       </c>
       <c r="B67" t="n">
-        <v>9.38050651550293</v>
+        <v>9.380505561828613</v>
       </c>
       <c r="C67" t="n">
-        <v>9.886482661063617</v>
+        <v>9.886481655948959</v>
       </c>
       <c r="D67" t="n">
-        <v>9.254537101368319</v>
+        <v>9.254536160500752</v>
       </c>
       <c r="E67" t="n">
-        <v>9.867586518328292</v>
+        <v>9.867585515134721</v>
       </c>
       <c r="F67" t="n">
         <v>3466157</v>
@@ -1792,16 +1792,16 @@
         <v>44328</v>
       </c>
       <c r="B69" t="n">
-        <v>9.531668663024902</v>
+        <v>9.531667709350586</v>
       </c>
       <c r="C69" t="n">
-        <v>9.743716705677796</v>
+        <v>9.743715730787388</v>
       </c>
       <c r="D69" t="n">
-        <v>9.321719921078722</v>
+        <v>9.321718988410458</v>
       </c>
       <c r="E69" t="n">
-        <v>9.563160609009282</v>
+        <v>9.563159652184094</v>
       </c>
       <c r="F69" t="n">
         <v>1563804</v>
@@ -1832,16 +1832,16 @@
         <v>44330</v>
       </c>
       <c r="B71" t="n">
-        <v>9.626143455505371</v>
+        <v>9.626144409179688</v>
       </c>
       <c r="C71" t="n">
-        <v>9.657636207208093</v>
+        <v>9.657637164002436</v>
       </c>
       <c r="D71" t="n">
-        <v>9.273430156636772</v>
+        <v>9.273431075367332</v>
       </c>
       <c r="E71" t="n">
-        <v>9.655536906906416</v>
+        <v>9.655537863492778</v>
       </c>
       <c r="F71" t="n">
         <v>1271072</v>
@@ -1852,16 +1852,16 @@
         <v>44333</v>
       </c>
       <c r="B72" t="n">
-        <v>9.657637596130371</v>
+        <v>9.657638549804688</v>
       </c>
       <c r="C72" t="n">
-        <v>9.773108870861909</v>
+        <v>9.773109835938806</v>
       </c>
       <c r="D72" t="n">
-        <v>9.361610233599944</v>
+        <v>9.36161115804209</v>
       </c>
       <c r="E72" t="n">
-        <v>9.613548224482443</v>
+        <v>9.613549173803014</v>
       </c>
       <c r="F72" t="n">
         <v>1884107</v>
@@ -1872,16 +1872,16 @@
         <v>44334</v>
       </c>
       <c r="B73" t="n">
-        <v>9.657637596130371</v>
+        <v>9.657638549804688</v>
       </c>
       <c r="C73" t="n">
-        <v>9.66603561033924</v>
+        <v>9.666036564842845</v>
       </c>
       <c r="D73" t="n">
-        <v>9.458186179310156</v>
+        <v>9.458187113289004</v>
       </c>
       <c r="E73" t="n">
-        <v>9.655538295526782</v>
+        <v>9.655539248993795</v>
       </c>
       <c r="F73" t="n">
         <v>1385003</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.823495864868164</v>
+        <v>9.823494911193848</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272800283195</v>
+        <v>10.10272702204951</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334316624833162</v>
+        <v>9.334315718648831</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678631950423839</v>
+        <v>9.678631010813049</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1932,16 +1932,16 @@
         <v>44337</v>
       </c>
       <c r="B76" t="n">
-        <v>10.1069278717041</v>
+        <v>10.10692882537842</v>
       </c>
       <c r="C76" t="n">
-        <v>10.19090720339814</v>
+        <v>10.19090816499662</v>
       </c>
       <c r="D76" t="n">
-        <v>9.873885205958286</v>
+        <v>9.873886137643053</v>
       </c>
       <c r="E76" t="n">
-        <v>10.12792250167898</v>
+        <v>10.12792345733432</v>
       </c>
       <c r="F76" t="n">
         <v>1597862</v>
@@ -1992,16 +1992,16 @@
         <v>44342</v>
       </c>
       <c r="B79" t="n">
-        <v>10.49743270874023</v>
+        <v>10.4974308013916</v>
       </c>
       <c r="C79" t="n">
-        <v>10.51842815215546</v>
+        <v>10.51842624099203</v>
       </c>
       <c r="D79" t="n">
-        <v>10.31897671637563</v>
+        <v>10.31897484145185</v>
       </c>
       <c r="E79" t="n">
-        <v>10.423951498068</v>
+        <v>10.42394960407066</v>
       </c>
       <c r="F79" t="n">
         <v>2052367</v>
@@ -2052,16 +2052,16 @@
         <v>44347</v>
       </c>
       <c r="B82" t="n">
-        <v>11.12727737426758</v>
+        <v>11.12727832794189</v>
       </c>
       <c r="C82" t="n">
-        <v>11.39601138073167</v>
+        <v>11.3960123574381</v>
       </c>
       <c r="D82" t="n">
-        <v>10.70737993105873</v>
+        <v>10.70738084874532</v>
       </c>
       <c r="E82" t="n">
-        <v>10.74937000009741</v>
+        <v>10.7493709213828</v>
       </c>
       <c r="F82" t="n">
         <v>1849644</v>
@@ -2072,16 +2072,16 @@
         <v>44348</v>
       </c>
       <c r="B83" t="n">
-        <v>11.12727737426758</v>
+        <v>11.12727832794189</v>
       </c>
       <c r="C83" t="n">
-        <v>11.25324676958913</v>
+        <v>11.25324773405977</v>
       </c>
       <c r="D83" t="n">
-        <v>11.03279992187918</v>
+        <v>11.03280086745621</v>
       </c>
       <c r="E83" t="n">
-        <v>11.23225132917255</v>
+        <v>11.23225229184377</v>
       </c>
       <c r="F83" t="n">
         <v>1761257</v>
@@ -2092,16 +2092,16 @@
         <v>44349</v>
       </c>
       <c r="B84" t="n">
-        <v>10.91522979736328</v>
+        <v>10.9152307510376</v>
       </c>
       <c r="C84" t="n">
-        <v>11.25114711619596</v>
+        <v>11.25114809921971</v>
       </c>
       <c r="D84" t="n">
-        <v>10.79765841105404</v>
+        <v>10.79765935445603</v>
       </c>
       <c r="E84" t="n">
-        <v>11.25114711619596</v>
+        <v>11.25114809921971</v>
       </c>
       <c r="F84" t="n">
         <v>2442811</v>
@@ -2112,16 +2112,16 @@
         <v>44351</v>
       </c>
       <c r="B85" t="n">
-        <v>11.12727737426758</v>
+        <v>11.12727832794189</v>
       </c>
       <c r="C85" t="n">
-        <v>11.14197328958526</v>
+        <v>11.1419742445191</v>
       </c>
       <c r="D85" t="n">
-        <v>10.6569926600068</v>
+        <v>10.6569935733749</v>
       </c>
       <c r="E85" t="n">
-        <v>10.93832409307973</v>
+        <v>10.93832503055962</v>
       </c>
       <c r="F85" t="n">
         <v>2427404</v>
@@ -2132,16 +2132,16 @@
         <v>44354</v>
       </c>
       <c r="B86" t="n">
-        <v>11.10838413238525</v>
+        <v>11.10838317871094</v>
       </c>
       <c r="C86" t="n">
-        <v>11.61226099650877</v>
+        <v>11.61225999957573</v>
       </c>
       <c r="D86" t="n">
-        <v>10.89843618314553</v>
+        <v>10.89843524749561</v>
       </c>
       <c r="E86" t="n">
-        <v>11.14407549482261</v>
+        <v>11.14407453808413</v>
       </c>
       <c r="F86" t="n">
         <v>2940293</v>
@@ -2152,16 +2152,16 @@
         <v>44355</v>
       </c>
       <c r="B87" t="n">
-        <v>11.0202054977417</v>
+        <v>11.02020454406738</v>
       </c>
       <c r="C87" t="n">
-        <v>11.16926884083993</v>
+        <v>11.16926787426587</v>
       </c>
       <c r="D87" t="n">
-        <v>10.93412604839051</v>
+        <v>10.9341251021654</v>
       </c>
       <c r="E87" t="n">
-        <v>11.1209800524548</v>
+        <v>11.12097909005958</v>
       </c>
       <c r="F87" t="n">
         <v>1135248</v>
@@ -2192,16 +2192,16 @@
         <v>44357</v>
       </c>
       <c r="B89" t="n">
-        <v>10.79136085510254</v>
+        <v>10.79135990142822</v>
       </c>
       <c r="C89" t="n">
-        <v>10.99081229192654</v>
+        <v>10.99081132062593</v>
       </c>
       <c r="D89" t="n">
-        <v>10.70108361394333</v>
+        <v>10.70108266824717</v>
       </c>
       <c r="E89" t="n">
-        <v>10.9404250134143</v>
+        <v>10.94042404656661</v>
       </c>
       <c r="F89" t="n">
         <v>1040779</v>
@@ -2212,16 +2212,16 @@
         <v>44358</v>
       </c>
       <c r="B90" t="n">
-        <v>10.6024055480957</v>
+        <v>10.60240745544434</v>
       </c>
       <c r="C90" t="n">
-        <v>10.84174690246687</v>
+        <v>10.84174885287247</v>
       </c>
       <c r="D90" t="n">
-        <v>10.51842622520338</v>
+        <v>10.51842811744432</v>
       </c>
       <c r="E90" t="n">
-        <v>10.75986687999311</v>
+        <v>10.75986881566868</v>
       </c>
       <c r="F90" t="n">
         <v>1174982</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462203979492</v>
+        <v>10.94462394714355</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192205807723</v>
+        <v>11.35192403640713</v>
       </c>
       <c r="D92" t="n">
-        <v>10.8144540429291</v>
+        <v>10.81445592759301</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152729877964</v>
+        <v>10.92152920210349</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2272,16 +2272,16 @@
         <v>44363</v>
       </c>
       <c r="B93" t="n">
-        <v>11.12727737426758</v>
+        <v>11.12727832794189</v>
       </c>
       <c r="C93" t="n">
-        <v>11.31413216674658</v>
+        <v>11.31413313643548</v>
       </c>
       <c r="D93" t="n">
-        <v>10.89213461123995</v>
+        <v>10.89213554476112</v>
       </c>
       <c r="E93" t="n">
-        <v>10.96141802220514</v>
+        <v>10.96141896166432</v>
       </c>
       <c r="F93" t="n">
         <v>2948808</v>
@@ -2312,16 +2312,16 @@
         <v>44365</v>
       </c>
       <c r="B95" t="n">
-        <v>11.3372278213501</v>
+        <v>11.33722686767578</v>
       </c>
       <c r="C95" t="n">
-        <v>11.3372278213501</v>
+        <v>11.33722686767578</v>
       </c>
       <c r="D95" t="n">
-        <v>10.99291163821293</v>
+        <v>10.99291071350208</v>
       </c>
       <c r="E95" t="n">
-        <v>11.31203377609247</v>
+        <v>11.31203282453744</v>
       </c>
       <c r="F95" t="n">
         <v>1275938</v>
@@ -2332,16 +2332,16 @@
         <v>44368</v>
       </c>
       <c r="B96" t="n">
-        <v>11.24274826049805</v>
+        <v>11.24274921417236</v>
       </c>
       <c r="C96" t="n">
-        <v>11.4044098178413</v>
+        <v>11.40441078522868</v>
       </c>
       <c r="D96" t="n">
-        <v>11.15247022398609</v>
+        <v>11.1524711700025</v>
       </c>
       <c r="E96" t="n">
-        <v>11.34562372318971</v>
+        <v>11.34562468559051</v>
       </c>
       <c r="F96" t="n">
         <v>1065511</v>
@@ -2352,16 +2352,16 @@
         <v>44369</v>
       </c>
       <c r="B97" t="n">
-        <v>11.28474044799805</v>
+        <v>11.28474140167236</v>
       </c>
       <c r="C97" t="n">
-        <v>11.42330729123857</v>
+        <v>11.42330825662318</v>
       </c>
       <c r="D97" t="n">
-        <v>11.16297125854524</v>
+        <v>11.16297220192883</v>
       </c>
       <c r="E97" t="n">
-        <v>11.238552582644</v>
+        <v>11.23855353241498</v>
       </c>
       <c r="F97" t="n">
         <v>1033076</v>
@@ -2372,16 +2372,16 @@
         <v>44370</v>
       </c>
       <c r="B98" t="n">
-        <v>11.50308704376221</v>
+        <v>11.50308799743652</v>
       </c>
       <c r="C98" t="n">
-        <v>11.74872632604882</v>
+        <v>11.7487273000881</v>
       </c>
       <c r="D98" t="n">
-        <v>11.3057341117264</v>
+        <v>11.30573504903898</v>
       </c>
       <c r="E98" t="n">
-        <v>11.4212062006073</v>
+        <v>11.42120714749321</v>
       </c>
       <c r="F98" t="n">
         <v>4341920</v>
@@ -2432,16 +2432,16 @@
         <v>44375</v>
       </c>
       <c r="B101" t="n">
-        <v>11.86209774017334</v>
+        <v>11.86209869384766</v>
       </c>
       <c r="C101" t="n">
-        <v>12.00066375318507</v>
+        <v>12.00066471799965</v>
       </c>
       <c r="D101" t="n">
-        <v>11.40441044302249</v>
+        <v>11.40441135990023</v>
       </c>
       <c r="E101" t="n">
-        <v>11.58916512703814</v>
+        <v>11.58916605876955</v>
       </c>
       <c r="F101" t="n">
         <v>1601511</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.01745986938477</v>
+        <v>12.0174617767334</v>
       </c>
       <c r="C102" t="n">
-        <v>12.01745986938477</v>
+        <v>12.0174617767334</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916442926651</v>
+        <v>11.58916626863832</v>
       </c>
       <c r="E102" t="n">
-        <v>11.85999772554824</v>
+        <v>11.8599996079053</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2492,16 +2492,16 @@
         <v>44378</v>
       </c>
       <c r="B104" t="n">
-        <v>12.47094821929932</v>
+        <v>12.47094917297363</v>
       </c>
       <c r="C104" t="n">
-        <v>12.63470827087047</v>
+        <v>12.6347092370678</v>
       </c>
       <c r="D104" t="n">
-        <v>12.33028290864975</v>
+        <v>12.33028385156715</v>
       </c>
       <c r="E104" t="n">
-        <v>12.38906900530821</v>
+        <v>12.38906995272109</v>
       </c>
       <c r="F104" t="n">
         <v>8890212</v>
@@ -2592,16 +2592,16 @@
         <v>44385</v>
       </c>
       <c r="B109" t="n">
-        <v>13.05880641937256</v>
+        <v>13.05880451202393</v>
       </c>
       <c r="C109" t="n">
-        <v>13.61097121410255</v>
+        <v>13.6109692261056</v>
       </c>
       <c r="D109" t="n">
-        <v>13.00631903082418</v>
+        <v>13.00631713114177</v>
       </c>
       <c r="E109" t="n">
-        <v>13.09659626755859</v>
+        <v>13.09659435469043</v>
       </c>
       <c r="F109" t="n">
         <v>8587750</v>
@@ -2612,16 +2612,16 @@
         <v>44389</v>
       </c>
       <c r="B110" t="n">
-        <v>13.33173942565918</v>
+        <v>13.3317403793335</v>
       </c>
       <c r="C110" t="n">
-        <v>13.79572545725768</v>
+        <v>13.79572644412283</v>
       </c>
       <c r="D110" t="n">
-        <v>13.07140260401543</v>
+        <v>13.07140353906678</v>
       </c>
       <c r="E110" t="n">
-        <v>13.19107329393574</v>
+        <v>13.19107423754762</v>
       </c>
       <c r="F110" t="n">
         <v>8663568</v>
@@ -2632,16 +2632,16 @@
         <v>44390</v>
       </c>
       <c r="B111" t="n">
-        <v>13.27295303344727</v>
+        <v>13.27295398712158</v>
       </c>
       <c r="C111" t="n">
-        <v>13.49759849206305</v>
+        <v>13.49759946187835</v>
       </c>
       <c r="D111" t="n">
-        <v>13.13438701720531</v>
+        <v>13.13438796092353</v>
       </c>
       <c r="E111" t="n">
-        <v>13.33173913269187</v>
+        <v>13.33174009059002</v>
       </c>
       <c r="F111" t="n">
         <v>2696620</v>
@@ -2652,16 +2652,16 @@
         <v>44391</v>
       </c>
       <c r="B112" t="n">
-        <v>13.63196659088135</v>
+        <v>13.63196563720703</v>
       </c>
       <c r="C112" t="n">
-        <v>13.63196659088135</v>
+        <v>13.63196563720703</v>
       </c>
       <c r="D112" t="n">
-        <v>13.25405915859814</v>
+        <v>13.25405823136172</v>
       </c>
       <c r="E112" t="n">
-        <v>13.27505379044871</v>
+        <v>13.27505286174354</v>
       </c>
       <c r="F112" t="n">
         <v>1800585</v>
@@ -2672,16 +2672,16 @@
         <v>44392</v>
       </c>
       <c r="B113" t="n">
-        <v>13.63196659088135</v>
+        <v>13.63196563720703</v>
       </c>
       <c r="C113" t="n">
-        <v>13.72224464435123</v>
+        <v>13.72224368436118</v>
       </c>
       <c r="D113" t="n">
-        <v>13.39682460348903</v>
+        <v>13.39682366626494</v>
       </c>
       <c r="E113" t="n">
-        <v>13.53958923658533</v>
+        <v>13.53958828937361</v>
       </c>
       <c r="F113" t="n">
         <v>1667599</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="C114" t="n">
-        <v>13.9384904687512</v>
+        <v>13.93849238737042</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969768169454</v>
+        <v>13.49969953991438</v>
       </c>
       <c r="E114" t="n">
-        <v>13.64246310974914</v>
+        <v>13.6424649876205</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501433064608</v>
+        <v>14.24501629145801</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969768169454</v>
+        <v>13.49969953991438</v>
       </c>
       <c r="E115" t="n">
-        <v>13.7495355572011</v>
+        <v>13.74953744981087</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06656074523926</v>
+        <v>14.06655979156494</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103739980534</v>
+        <v>14.16103643972576</v>
       </c>
       <c r="D116" t="n">
-        <v>13.7747319546967</v>
+        <v>13.77473102080758</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059133128809</v>
+        <v>13.94059038615415</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2752,16 +2752,16 @@
         <v>44398</v>
       </c>
       <c r="B117" t="n">
-        <v>14.3184986114502</v>
+        <v>14.31849956512451</v>
       </c>
       <c r="C117" t="n">
-        <v>14.34789044445824</v>
+        <v>14.34789140009018</v>
       </c>
       <c r="D117" t="n">
-        <v>14.01617171355511</v>
+        <v>14.01617264709314</v>
       </c>
       <c r="E117" t="n">
-        <v>14.06865910114192</v>
+        <v>14.06866003817584</v>
       </c>
       <c r="F117" t="n">
         <v>2316312</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.99873065948486</v>
+        <v>14.99872970581055</v>
       </c>
       <c r="C118" t="n">
-        <v>15.01132808589888</v>
+        <v>15.01132713142357</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36048649073444</v>
+        <v>14.36048557764203</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36048649073444</v>
+        <v>14.36048557764203</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801414489746</v>
+        <v>15.06801319122314</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127770885214</v>
+        <v>15.22127674547757</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92944893307399</v>
+        <v>14.92944798816965</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127770885214</v>
+        <v>15.22127674547757</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2812,16 +2812,16 @@
         <v>44403</v>
       </c>
       <c r="B120" t="n">
-        <v>14.8748607635498</v>
+        <v>14.87486171722412</v>
       </c>
       <c r="C120" t="n">
-        <v>15.17088811128218</v>
+        <v>15.17088908393575</v>
       </c>
       <c r="D120" t="n">
-        <v>14.64601752612992</v>
+        <v>14.64601846513237</v>
       </c>
       <c r="E120" t="n">
-        <v>15.07431217039968</v>
+        <v>15.07431313686146</v>
       </c>
       <c r="F120" t="n">
         <v>4655330</v>
@@ -2832,16 +2832,16 @@
         <v>44404</v>
       </c>
       <c r="B121" t="n">
-        <v>14.54944133758545</v>
+        <v>14.54944038391113</v>
       </c>
       <c r="C121" t="n">
-        <v>15.059616867494</v>
+        <v>15.05961588037913</v>
       </c>
       <c r="D121" t="n">
-        <v>14.45076608687268</v>
+        <v>14.45076513966624</v>
       </c>
       <c r="E121" t="n">
-        <v>14.87486217025152</v>
+        <v>14.87486119524679</v>
       </c>
       <c r="F121" t="n">
         <v>2070206</v>
@@ -2872,16 +2872,16 @@
         <v>44406</v>
       </c>
       <c r="B123" t="n">
-        <v>15.28426265716553</v>
+        <v>15.28426170349121</v>
       </c>
       <c r="C123" t="n">
-        <v>15.32415262054446</v>
+        <v>15.32415166438117</v>
       </c>
       <c r="D123" t="n">
-        <v>14.85386863981871</v>
+        <v>14.85386771299919</v>
       </c>
       <c r="E123" t="n">
-        <v>15.09950794623948</v>
+        <v>15.09950700409309</v>
       </c>
       <c r="F123" t="n">
         <v>6067903</v>
@@ -2892,16 +2892,16 @@
         <v>44407</v>
       </c>
       <c r="B124" t="n">
-        <v>15.45431709289551</v>
+        <v>15.45431900024414</v>
       </c>
       <c r="C124" t="n">
-        <v>15.94139861587127</v>
+        <v>15.94140058333477</v>
       </c>
       <c r="D124" t="n">
-        <v>14.96933649387961</v>
+        <v>14.96933834137266</v>
       </c>
       <c r="E124" t="n">
-        <v>15.28006054980113</v>
+        <v>15.28006243564328</v>
       </c>
       <c r="F124" t="n">
         <v>3070441</v>
@@ -2932,16 +2932,16 @@
         <v>44411</v>
       </c>
       <c r="B126" t="n">
-        <v>15.20448207855225</v>
+        <v>15.20448303222656</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39343538308269</v>
+        <v>15.39343634860877</v>
       </c>
       <c r="D126" t="n">
-        <v>14.76149065149246</v>
+        <v>14.76149157738092</v>
       </c>
       <c r="E126" t="n">
-        <v>15.39343538308269</v>
+        <v>15.39343634860877</v>
       </c>
       <c r="F126" t="n">
         <v>3496971</v>
@@ -2952,16 +2952,16 @@
         <v>44412</v>
       </c>
       <c r="B127" t="n">
-        <v>14.73839569091797</v>
+        <v>14.73839664459229</v>
       </c>
       <c r="C127" t="n">
-        <v>15.32205328135125</v>
+        <v>15.32205427279218</v>
       </c>
       <c r="D127" t="n">
-        <v>14.73839569091797</v>
+        <v>14.73839664459229</v>
       </c>
       <c r="E127" t="n">
-        <v>15.18768666199287</v>
+        <v>15.18768764473936</v>
       </c>
       <c r="F127" t="n">
         <v>2159810</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.93639087677002</v>
+        <v>13.93639183044434</v>
       </c>
       <c r="C129" t="n">
-        <v>14.4192722130578</v>
+        <v>14.41927319977593</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373549436386</v>
+        <v>13.75373643553897</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153364330989</v>
+        <v>14.17153461307515</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06656074523926</v>
+        <v>14.06655979156494</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893809899156</v>
+        <v>14.15893713905431</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462191733692</v>
+        <v>13.81462098074336</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351724825013</v>
+        <v>13.83351631037553</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3032,16 +3032,16 @@
         <v>44418</v>
       </c>
       <c r="B131" t="n">
-        <v>13.64666271209717</v>
+        <v>13.64666175842285</v>
       </c>
       <c r="C131" t="n">
-        <v>14.43816890261326</v>
+        <v>14.43816789362585</v>
       </c>
       <c r="D131" t="n">
-        <v>13.56688278990252</v>
+        <v>13.56688184180349</v>
       </c>
       <c r="E131" t="n">
-        <v>14.05396277317898</v>
+        <v>14.05396179104118</v>
       </c>
       <c r="F131" t="n">
         <v>2933806</v>
@@ -3072,16 +3072,16 @@
         <v>44420</v>
       </c>
       <c r="B133" t="n">
-        <v>13.68025588989258</v>
+        <v>13.68025493621826</v>
       </c>
       <c r="C133" t="n">
-        <v>14.21142610276459</v>
+        <v>14.21142511206147</v>
       </c>
       <c r="D133" t="n">
-        <v>13.64666382824554</v>
+        <v>13.64666287691298</v>
       </c>
       <c r="E133" t="n">
-        <v>13.82512064100215</v>
+        <v>13.82511967722906</v>
       </c>
       <c r="F133" t="n">
         <v>1819641</v>
@@ -3092,16 +3092,16 @@
         <v>44421</v>
       </c>
       <c r="B134" t="n">
-        <v>12.95593070983887</v>
+        <v>12.95593166351318</v>
       </c>
       <c r="C134" t="n">
-        <v>13.76423290704215</v>
+        <v>13.76423392021486</v>
       </c>
       <c r="D134" t="n">
-        <v>12.78797285545454</v>
+        <v>12.78797379676563</v>
       </c>
       <c r="E134" t="n">
-        <v>13.5710801973981</v>
+        <v>13.57108119635301</v>
       </c>
       <c r="F134" t="n">
         <v>3730102</v>
@@ -3112,16 +3112,16 @@
         <v>44424</v>
       </c>
       <c r="B135" t="n">
-        <v>11.84110355377197</v>
+        <v>11.84110450744629</v>
       </c>
       <c r="C135" t="n">
-        <v>12.94963251110049</v>
+        <v>12.94963355405497</v>
       </c>
       <c r="D135" t="n">
-        <v>11.76552223690275</v>
+        <v>11.7655231844898</v>
       </c>
       <c r="E135" t="n">
-        <v>12.94963251110049</v>
+        <v>12.94963355405497</v>
       </c>
       <c r="F135" t="n">
         <v>7844263</v>
@@ -3132,16 +3132,16 @@
         <v>44425</v>
       </c>
       <c r="B136" t="n">
-        <v>12.27779769897461</v>
+        <v>12.27779674530029</v>
       </c>
       <c r="C136" t="n">
-        <v>12.78167371260009</v>
+        <v>12.78167271978735</v>
       </c>
       <c r="D136" t="n">
-        <v>11.42960470460314</v>
+        <v>11.42960381681197</v>
       </c>
       <c r="E136" t="n">
-        <v>11.66474749373068</v>
+        <v>11.66474658767486</v>
       </c>
       <c r="F136" t="n">
         <v>5635292</v>
@@ -3152,16 +3152,16 @@
         <v>44426</v>
       </c>
       <c r="B137" t="n">
-        <v>12.5969181060791</v>
+        <v>12.59691905975342</v>
       </c>
       <c r="C137" t="n">
-        <v>13.13438695180978</v>
+        <v>13.13438794617422</v>
       </c>
       <c r="D137" t="n">
-        <v>12.21901071713769</v>
+        <v>12.21901164220178</v>
       </c>
       <c r="E137" t="n">
-        <v>12.38696937626842</v>
+        <v>12.38697031404816</v>
       </c>
       <c r="F137" t="n">
         <v>3796291</v>
@@ -3232,16 +3232,16 @@
         <v>44432</v>
       </c>
       <c r="B141" t="n">
-        <v>13.63826465606689</v>
+        <v>13.63826656341553</v>
       </c>
       <c r="C141" t="n">
-        <v>13.92379389167463</v>
+        <v>13.9237958389553</v>
       </c>
       <c r="D141" t="n">
-        <v>13.37792783946889</v>
+        <v>13.37792971040871</v>
       </c>
       <c r="E141" t="n">
-        <v>13.63826465606689</v>
+        <v>13.63826656341553</v>
       </c>
       <c r="F141" t="n">
         <v>2525015</v>
@@ -3252,16 +3252,16 @@
         <v>44433</v>
       </c>
       <c r="B142" t="n">
-        <v>13.47870349884033</v>
+        <v>13.47870445251465</v>
       </c>
       <c r="C142" t="n">
-        <v>13.57947804789503</v>
+        <v>13.57947900869956</v>
       </c>
       <c r="D142" t="n">
-        <v>13.05040801228251</v>
+        <v>13.05040893565314</v>
       </c>
       <c r="E142" t="n">
-        <v>13.44511144129242</v>
+        <v>13.44511239258996</v>
       </c>
       <c r="F142" t="n">
         <v>2709595</v>
@@ -3272,16 +3272,16 @@
         <v>44434</v>
       </c>
       <c r="B143" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12599086761475</v>
       </c>
       <c r="C143" t="n">
-        <v>13.76423335318433</v>
+        <v>13.76423435323049</v>
       </c>
       <c r="D143" t="n">
-        <v>12.82366381794241</v>
+        <v>12.82366474965109</v>
       </c>
       <c r="E143" t="n">
-        <v>13.47870409850207</v>
+        <v>13.47870507780299</v>
       </c>
       <c r="F143" t="n">
         <v>2624147</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00001949529792</v>
+        <v>13.00002128473755</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113085479707</v>
+        <v>13.36113269394332</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3452,16 +3452,16 @@
         <v>44448</v>
       </c>
       <c r="B152" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12599086761475</v>
       </c>
       <c r="C152" t="n">
-        <v>13.3779287331694</v>
+        <v>13.37792970514844</v>
       </c>
       <c r="D152" t="n">
-        <v>12.52973573670498</v>
+        <v>12.5297366470582</v>
       </c>
       <c r="E152" t="n">
-        <v>13.2183672645125</v>
+        <v>13.21836822489853</v>
       </c>
       <c r="F152" t="n">
         <v>3739731</v>
@@ -3492,16 +3492,16 @@
         <v>44452</v>
       </c>
       <c r="B154" t="n">
-        <v>13.3947229385376</v>
+        <v>13.39472389221191</v>
       </c>
       <c r="C154" t="n">
-        <v>13.53748836688323</v>
+        <v>13.53748933072213</v>
       </c>
       <c r="D154" t="n">
-        <v>12.97482629121558</v>
+        <v>12.9748272149942</v>
       </c>
       <c r="E154" t="n">
-        <v>13.24356030786057</v>
+        <v>13.24356125077245</v>
       </c>
       <c r="F154" t="n">
         <v>1856739</v>
@@ -3512,16 +3512,16 @@
         <v>44453</v>
       </c>
       <c r="B155" t="n">
-        <v>13.55428504943848</v>
+        <v>13.55428600311279</v>
       </c>
       <c r="C155" t="n">
-        <v>14.04976384781166</v>
+        <v>14.04976483634768</v>
       </c>
       <c r="D155" t="n">
-        <v>13.27715300528965</v>
+        <v>13.27715393946506</v>
       </c>
       <c r="E155" t="n">
-        <v>13.43671365779501</v>
+        <v>13.43671460319705</v>
       </c>
       <c r="F155" t="n">
         <v>1943200</v>
@@ -3532,16 +3532,16 @@
         <v>44454</v>
       </c>
       <c r="B156" t="n">
-        <v>13.44511222839355</v>
+        <v>13.44511127471924</v>
       </c>
       <c r="C156" t="n">
-        <v>14.07495766172759</v>
+        <v>14.07495666337775</v>
       </c>
       <c r="D156" t="n">
-        <v>13.23516348001735</v>
+        <v>13.2351625412349</v>
       </c>
       <c r="E156" t="n">
-        <v>13.47030546123482</v>
+        <v>13.47030450577353</v>
       </c>
       <c r="F156" t="n">
         <v>2602050</v>
@@ -3552,16 +3552,16 @@
         <v>44455</v>
       </c>
       <c r="B157" t="n">
-        <v>13.56268310546875</v>
+        <v>13.56268405914307</v>
       </c>
       <c r="C157" t="n">
-        <v>13.78942787491819</v>
+        <v>13.7894288445363</v>
       </c>
       <c r="D157" t="n">
-        <v>13.33593833601931</v>
+        <v>13.33593927374983</v>
       </c>
       <c r="E157" t="n">
-        <v>13.47870377169347</v>
+        <v>13.47870471946269</v>
       </c>
       <c r="F157" t="n">
         <v>1227183</v>
@@ -3572,16 +3572,16 @@
         <v>44456</v>
       </c>
       <c r="B158" t="n">
-        <v>13.44511222839355</v>
+        <v>13.44511127471924</v>
       </c>
       <c r="C158" t="n">
-        <v>13.74743914043451</v>
+        <v>13.74743816531587</v>
       </c>
       <c r="D158" t="n">
-        <v>13.29394877237308</v>
+        <v>13.29394782942092</v>
       </c>
       <c r="E158" t="n">
-        <v>13.40312296579506</v>
+        <v>13.40312201509908</v>
       </c>
       <c r="F158" t="n">
         <v>5378949</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.6124267578125</v>
+        <v>14.61242771148682</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630275876303</v>
+        <v>15.11630374532261</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893722044467</v>
+        <v>14.15893814452217</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19252927855919</v>
+        <v>14.19253020482906</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661315917969</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26810988418833</v>
+        <v>14.26811184817934</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141639771024</v>
+        <v>13.83141830159083</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733371488308</v>
+        <v>14.16733566500235</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3752,16 +3752,16 @@
         <v>44469</v>
       </c>
       <c r="B167" t="n">
-        <v>12.55492973327637</v>
+        <v>12.55492877960205</v>
       </c>
       <c r="C167" t="n">
-        <v>13.05880655802494</v>
+        <v>13.05880556607607</v>
       </c>
       <c r="D167" t="n">
-        <v>12.37017503283432</v>
+        <v>12.370174093194</v>
       </c>
       <c r="E167" t="n">
-        <v>13.05880655802494</v>
+        <v>13.05880556607607</v>
       </c>
       <c r="F167" t="n">
         <v>6213762</v>
@@ -3772,16 +3772,16 @@
         <v>44470</v>
       </c>
       <c r="B168" t="n">
-        <v>12.78167343139648</v>
+        <v>12.78167247772217</v>
       </c>
       <c r="C168" t="n">
-        <v>13.1175923900122</v>
+        <v>13.11759141127408</v>
       </c>
       <c r="D168" t="n">
-        <v>12.00066457212668</v>
+        <v>12.00066367672549</v>
       </c>
       <c r="E168" t="n">
-        <v>12.65570483665877</v>
+        <v>12.6557038923833</v>
       </c>
       <c r="F168" t="n">
         <v>6332153</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14342975616455</v>
+        <v>12.14343070983887</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55492921366123</v>
+        <v>12.55493019965232</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027704898789</v>
+        <v>11.95027798749311</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337849210345</v>
+        <v>12.35337946226592</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3872,16 +3872,16 @@
         <v>44477</v>
       </c>
       <c r="B173" t="n">
-        <v>13.05880641937256</v>
+        <v>13.05880451202393</v>
       </c>
       <c r="C173" t="n">
-        <v>13.38632574313576</v>
+        <v>13.38632378795018</v>
       </c>
       <c r="D173" t="n">
-        <v>12.89924495301617</v>
+        <v>12.89924306897283</v>
       </c>
       <c r="E173" t="n">
-        <v>13.11759252184922</v>
+        <v>13.11759060591438</v>
       </c>
       <c r="F173" t="n">
         <v>3251676</v>
@@ -3892,16 +3892,16 @@
         <v>44480</v>
       </c>
       <c r="B174" t="n">
-        <v>12.97482585906982</v>
+        <v>12.97482681274414</v>
       </c>
       <c r="C174" t="n">
-        <v>13.23516185291805</v>
+        <v>13.23516282572755</v>
       </c>
       <c r="D174" t="n">
-        <v>12.74808110881185</v>
+        <v>12.74808204582</v>
       </c>
       <c r="E174" t="n">
-        <v>13.05880518573717</v>
+        <v>13.05880614558413</v>
       </c>
       <c r="F174" t="n">
         <v>2493289</v>
@@ -3912,16 +3912,16 @@
         <v>44482</v>
       </c>
       <c r="B175" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12599086761475</v>
       </c>
       <c r="C175" t="n">
-        <v>13.34433667412699</v>
+        <v>13.34433764366538</v>
       </c>
       <c r="D175" t="n">
-        <v>12.83206264449757</v>
+        <v>12.83206357681648</v>
       </c>
       <c r="E175" t="n">
-        <v>12.83206264449757</v>
+        <v>12.83206357681648</v>
       </c>
       <c r="F175" t="n">
         <v>2244954</v>
@@ -3992,16 +3992,16 @@
         <v>44488</v>
       </c>
       <c r="B179" t="n">
-        <v>12.3953685760498</v>
+        <v>12.39536762237549</v>
       </c>
       <c r="C179" t="n">
-        <v>13.10919416332626</v>
+        <v>13.10919315473166</v>
       </c>
       <c r="D179" t="n">
-        <v>12.17702181121777</v>
+        <v>12.17702087434261</v>
       </c>
       <c r="E179" t="n">
-        <v>13.05880688548518</v>
+        <v>13.05880588076728</v>
       </c>
       <c r="F179" t="n">
         <v>2260766</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.5310230255127</v>
+        <v>10.53102397918701</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174709395853</v>
+        <v>10.84174807577158</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624045672820648</v>
+        <v>9.624046544360398</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174709395853</v>
+        <v>10.84174807577158</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55621814727783</v>
+        <v>10.55621719360352</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650289901313</v>
+        <v>11.02650190285215</v>
       </c>
       <c r="D183" t="n">
-        <v>10.35466742342063</v>
+        <v>10.35466648795489</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699350920643</v>
+        <v>10.65699254642783</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4092,16 +4092,16 @@
         <v>44495</v>
       </c>
       <c r="B184" t="n">
-        <v>9.985157012939453</v>
+        <v>9.985158920288086</v>
       </c>
       <c r="C184" t="n">
-        <v>10.46383973022113</v>
+        <v>10.46384172900696</v>
       </c>
       <c r="D184" t="n">
-        <v>9.825595565982594</v>
+        <v>9.825597442852056</v>
       </c>
       <c r="E184" t="n">
-        <v>10.46383973022113</v>
+        <v>10.46384172900696</v>
       </c>
       <c r="F184" t="n">
         <v>5760068</v>
@@ -4212,16 +4212,16 @@
         <v>44504</v>
       </c>
       <c r="B190" t="n">
-        <v>10.35466766357422</v>
+        <v>10.3546667098999</v>
       </c>
       <c r="C190" t="n">
-        <v>11.22805469507473</v>
+        <v>11.22805366096068</v>
       </c>
       <c r="D190" t="n">
-        <v>10.02714752676152</v>
+        <v>10.02714660325211</v>
       </c>
       <c r="E190" t="n">
-        <v>10.08593362946343</v>
+        <v>10.08593270053977</v>
       </c>
       <c r="F190" t="n">
         <v>7850142</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55621814727783</v>
+        <v>10.55621719360352</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771679767463</v>
+        <v>10.96771580682453</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588132208213</v>
+        <v>10.29588039192727</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64019748025258</v>
+        <v>10.64019651899136</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4252,16 +4252,16 @@
         <v>44508</v>
       </c>
       <c r="B192" t="n">
-        <v>10.58981132507324</v>
+        <v>10.58981037139893</v>
       </c>
       <c r="C192" t="n">
-        <v>10.82495331991022</v>
+        <v>10.82495234506</v>
       </c>
       <c r="D192" t="n">
-        <v>10.111127696445</v>
+        <v>10.11112678587894</v>
       </c>
       <c r="E192" t="n">
-        <v>10.82495331991022</v>
+        <v>10.82495234506</v>
       </c>
       <c r="F192" t="n">
         <v>1684830</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.74937057495117</v>
+        <v>10.74937152862549</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324737138916</v>
+        <v>11.25324836976697</v>
       </c>
       <c r="D193" t="n">
-        <v>10.40505523759868</v>
+        <v>10.40505616072565</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660514437936</v>
+        <v>10.60660608538766</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4292,16 +4292,16 @@
         <v>44510</v>
       </c>
       <c r="B194" t="n">
-        <v>10.66539096832275</v>
+        <v>10.66539192199707</v>
       </c>
       <c r="C194" t="n">
-        <v>11.16926775172825</v>
+        <v>11.16926875045805</v>
       </c>
       <c r="D194" t="n">
-        <v>10.44704422688129</v>
+        <v>10.44704516103155</v>
       </c>
       <c r="E194" t="n">
-        <v>10.74937029692459</v>
+        <v>10.74937125810814</v>
       </c>
       <c r="F194" t="n">
         <v>2771222</v>
@@ -4332,16 +4332,16 @@
         <v>44512</v>
       </c>
       <c r="B196" t="n">
-        <v>10.75776767730713</v>
+        <v>10.75776863098145</v>
       </c>
       <c r="C196" t="n">
-        <v>11.50518525664944</v>
+        <v>11.5051862765822</v>
       </c>
       <c r="D196" t="n">
-        <v>10.70738040402947</v>
+        <v>10.70738135323696</v>
       </c>
       <c r="E196" t="n">
-        <v>11.19446197921575</v>
+        <v>11.19446297160295</v>
       </c>
       <c r="F196" t="n">
         <v>1618134</v>
@@ -4392,16 +4392,16 @@
         <v>44518</v>
       </c>
       <c r="B199" t="n">
-        <v>10.34626865386963</v>
+        <v>10.34626960754395</v>
       </c>
       <c r="C199" t="n">
-        <v>10.57301259281523</v>
+        <v>10.57301356738983</v>
       </c>
       <c r="D199" t="n">
-        <v>10.01035053469153</v>
+        <v>10.01035145740236</v>
       </c>
       <c r="E199" t="n">
-        <v>10.13631993085762</v>
+        <v>10.13632086517977</v>
       </c>
       <c r="F199" t="n">
         <v>2248603</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674434661865234</v>
+        <v>9.674432754516602</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34627018804897</v>
+        <v>10.34626814824561</v>
       </c>
       <c r="D202" t="n">
-        <v>9.481281937939977</v>
+        <v>9.481280068672081</v>
       </c>
       <c r="E202" t="n">
-        <v>10.2874840822837</v>
+        <v>10.28748205407023</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4492,16 +4492,16 @@
         <v>44525</v>
       </c>
       <c r="B204" t="n">
-        <v>9.825595855712891</v>
+        <v>9.825596809387207</v>
       </c>
       <c r="C204" t="n">
-        <v>10.15311514931385</v>
+        <v>10.15311613477726</v>
       </c>
       <c r="D204" t="n">
-        <v>9.657637201979346</v>
+        <v>9.657638139351562</v>
       </c>
       <c r="E204" t="n">
-        <v>9.901177168713536</v>
+        <v>9.901178129723791</v>
       </c>
       <c r="F204" t="n">
         <v>1557621</v>
@@ -4512,16 +4512,16 @@
         <v>44526</v>
       </c>
       <c r="B205" t="n">
-        <v>9.472881317138672</v>
+        <v>9.472882270812988</v>
       </c>
       <c r="C205" t="n">
-        <v>9.682830031524192</v>
+        <v>9.682831006334919</v>
       </c>
       <c r="D205" t="n">
-        <v>9.178953279357833</v>
+        <v>9.178954203441192</v>
       </c>
       <c r="E205" t="n">
-        <v>9.657636802761706</v>
+        <v>9.657637775036125</v>
       </c>
       <c r="F205" t="n">
         <v>2092506</v>
@@ -4572,16 +4572,16 @@
         <v>44531</v>
       </c>
       <c r="B208" t="n">
-        <v>9.019394874572754</v>
+        <v>9.019393920898438</v>
       </c>
       <c r="C208" t="n">
-        <v>9.766811700804164</v>
+        <v>9.766810668101018</v>
       </c>
       <c r="D208" t="n">
-        <v>9.019394874572754</v>
+        <v>9.019393920898438</v>
       </c>
       <c r="E208" t="n">
-        <v>9.540066923765492</v>
+        <v>9.54006591503742</v>
       </c>
       <c r="F208" t="n">
         <v>2660840</v>
@@ -4612,16 +4612,16 @@
         <v>44533</v>
       </c>
       <c r="B210" t="n">
-        <v>9.901178359985352</v>
+        <v>9.901177406311035</v>
       </c>
       <c r="C210" t="n">
-        <v>10.0859338754747</v>
+        <v>10.08593290400486</v>
       </c>
       <c r="D210" t="n">
-        <v>9.615648289566654</v>
+        <v>9.615647363394388</v>
       </c>
       <c r="E210" t="n">
-        <v>9.649240349072821</v>
+        <v>9.649239419664992</v>
       </c>
       <c r="F210" t="n">
         <v>1913704</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884382247924805</v>
+        <v>9.884383201599121</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709559365621</v>
+        <v>10.23709658136135</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573657349188849</v>
+        <v>9.573658272883511</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867585407896522</v>
+        <v>9.867586359950231</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4652,16 +4652,16 @@
         <v>44537</v>
       </c>
       <c r="B212" t="n">
-        <v>9.985157012939453</v>
+        <v>9.985158920288086</v>
       </c>
       <c r="C212" t="n">
-        <v>10.53102302737459</v>
+        <v>10.53102503899367</v>
       </c>
       <c r="D212" t="n">
-        <v>9.867584822280591</v>
+        <v>9.867586707170773</v>
       </c>
       <c r="E212" t="n">
-        <v>10.00195222838198</v>
+        <v>10.00195413893881</v>
       </c>
       <c r="F212" t="n">
         <v>3095174</v>
@@ -4732,16 +4732,16 @@
         <v>44543</v>
       </c>
       <c r="B216" t="n">
-        <v>11.19168281555176</v>
+        <v>11.19168090820312</v>
       </c>
       <c r="C216" t="n">
-        <v>11.55848307007503</v>
+        <v>11.55848110021426</v>
       </c>
       <c r="D216" t="n">
-        <v>11.13197060927274</v>
+        <v>11.13196871210059</v>
       </c>
       <c r="E216" t="n">
-        <v>11.2599245124301</v>
+        <v>11.25992259345134</v>
       </c>
       <c r="F216" t="n">
         <v>3334589</v>
@@ -4752,16 +4752,16 @@
         <v>44544</v>
       </c>
       <c r="B217" t="n">
-        <v>11.11490726470947</v>
+        <v>11.11490917205811</v>
       </c>
       <c r="C217" t="n">
-        <v>11.43905668874708</v>
+        <v>11.43905865172065</v>
       </c>
       <c r="D217" t="n">
-        <v>10.91871171258361</v>
+        <v>10.91871358626455</v>
       </c>
       <c r="E217" t="n">
-        <v>11.25992176282055</v>
+        <v>11.25992369505407</v>
       </c>
       <c r="F217" t="n">
         <v>1511299</v>
@@ -4832,16 +4832,16 @@
         <v>44550</v>
       </c>
       <c r="B221" t="n">
-        <v>10.92724227905273</v>
+        <v>10.92724323272705</v>
       </c>
       <c r="C221" t="n">
-        <v>11.08931741935155</v>
+        <v>11.08931838717097</v>
       </c>
       <c r="D221" t="n">
-        <v>10.64574521732745</v>
+        <v>10.64574614643413</v>
       </c>
       <c r="E221" t="n">
-        <v>10.83341047486649</v>
+        <v>10.83341142035164</v>
       </c>
       <c r="F221" t="n">
         <v>2144606</v>
@@ -4872,16 +4872,16 @@
         <v>44552</v>
       </c>
       <c r="B223" t="n">
-        <v>10.57750415802002</v>
+        <v>10.5775032043457</v>
       </c>
       <c r="C223" t="n">
-        <v>10.84194143213719</v>
+        <v>10.84194045462105</v>
       </c>
       <c r="D223" t="n">
-        <v>10.33865617807819</v>
+        <v>10.33865524593855</v>
       </c>
       <c r="E223" t="n">
-        <v>10.83341111768986</v>
+        <v>10.83341014094282</v>
       </c>
       <c r="F223" t="n">
         <v>1137579</v>
@@ -4892,16 +4892,16 @@
         <v>44553</v>
       </c>
       <c r="B224" t="n">
-        <v>10.38983917236328</v>
+        <v>10.38983821868896</v>
       </c>
       <c r="C224" t="n">
-        <v>10.65427645368369</v>
+        <v>10.6542754757369</v>
       </c>
       <c r="D224" t="n">
-        <v>10.19364275931372</v>
+        <v>10.1936418236481</v>
       </c>
       <c r="E224" t="n">
-        <v>10.56897413147012</v>
+        <v>10.56897316135316</v>
       </c>
       <c r="F224" t="n">
         <v>1383482</v>
@@ -4912,16 +4912,16 @@
         <v>44557</v>
       </c>
       <c r="B225" t="n">
-        <v>10.32159519195557</v>
+        <v>10.32159614562988</v>
       </c>
       <c r="C225" t="n">
-        <v>10.58603243579497</v>
+        <v>10.58603341390223</v>
       </c>
       <c r="D225" t="n">
-        <v>9.971854813410014</v>
+        <v>9.971855734769711</v>
       </c>
       <c r="E225" t="n">
-        <v>10.49219981220142</v>
+        <v>10.49220078163893</v>
       </c>
       <c r="F225" t="n">
         <v>1768251</v>
@@ -4932,16 +4932,16 @@
         <v>44558</v>
       </c>
       <c r="B226" t="n">
-        <v>10.08274936676025</v>
+        <v>10.08274841308594</v>
       </c>
       <c r="C226" t="n">
-        <v>10.50073148249594</v>
+        <v>10.50073048928689</v>
       </c>
       <c r="D226" t="n">
-        <v>9.98891755562571</v>
+        <v>9.988916610826452</v>
       </c>
       <c r="E226" t="n">
-        <v>10.15952137333246</v>
+        <v>10.15952041239668</v>
       </c>
       <c r="F226" t="n">
         <v>1405681</v>
@@ -4972,16 +4972,16 @@
         <v>44560</v>
       </c>
       <c r="B228" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="C228" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="D228" t="n">
-        <v>9.647706562908386</v>
+        <v>9.647705662569827</v>
       </c>
       <c r="E228" t="n">
-        <v>9.7927210851769</v>
+        <v>9.792720171305367</v>
       </c>
       <c r="F228" t="n">
         <v>3325771</v>
@@ -5152,16 +5152,16 @@
         <v>44574</v>
       </c>
       <c r="B237" t="n">
-        <v>8.7264404296875</v>
+        <v>8.726439476013184</v>
       </c>
       <c r="C237" t="n">
-        <v>9.110300442131042</v>
+        <v>9.110299446506351</v>
       </c>
       <c r="D237" t="n">
-        <v>8.555834971888574</v>
+        <v>8.555834036858977</v>
       </c>
       <c r="E237" t="n">
-        <v>9.042058753761445</v>
+        <v>9.042057765594588</v>
       </c>
       <c r="F237" t="n">
         <v>3017328</v>
@@ -5172,16 +5172,16 @@
         <v>44575</v>
       </c>
       <c r="B238" t="n">
-        <v>8.743500709533691</v>
+        <v>8.743501663208008</v>
       </c>
       <c r="C238" t="n">
-        <v>8.769091653284766</v>
+        <v>8.769092609750347</v>
       </c>
       <c r="D238" t="n">
-        <v>8.359640676184245</v>
+        <v>8.359641587990039</v>
       </c>
       <c r="E238" t="n">
-        <v>8.726440904949643</v>
+        <v>8.726441856763206</v>
       </c>
       <c r="F238" t="n">
         <v>2170250</v>
@@ -5232,16 +5232,16 @@
         <v>44580</v>
       </c>
       <c r="B241" t="n">
-        <v>8.521713256835938</v>
+        <v>8.521714210510254</v>
       </c>
       <c r="C241" t="n">
-        <v>8.675258078133986</v>
+        <v>8.675259048991672</v>
       </c>
       <c r="D241" t="n">
-        <v>8.291397261763732</v>
+        <v>8.291398189663132</v>
       </c>
       <c r="E241" t="n">
-        <v>8.308457064500631</v>
+        <v>8.308457994309213</v>
       </c>
       <c r="F241" t="n">
         <v>1675201</v>
@@ -5312,16 +5312,16 @@
         <v>44586</v>
       </c>
       <c r="B245" t="n">
-        <v>9.843902587890625</v>
+        <v>9.843903541564941</v>
       </c>
       <c r="C245" t="n">
-        <v>9.929204905183155</v>
+        <v>9.929205867121535</v>
       </c>
       <c r="D245" t="n">
-        <v>9.383268920094348</v>
+        <v>9.383269829142614</v>
       </c>
       <c r="E245" t="n">
-        <v>9.391799234281931</v>
+        <v>9.391800144156612</v>
       </c>
       <c r="F245" t="n">
         <v>2635195</v>
@@ -5372,16 +5372,16 @@
         <v>44589</v>
       </c>
       <c r="B248" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="C248" t="n">
-        <v>10.26188426089857</v>
+        <v>10.26188330324402</v>
       </c>
       <c r="D248" t="n">
-        <v>9.681827820991172</v>
+        <v>9.681826917468367</v>
       </c>
       <c r="E248" t="n">
-        <v>10.19364256931633</v>
+        <v>10.1936416180302</v>
       </c>
       <c r="F248" t="n">
         <v>1431224</v>
@@ -5452,16 +5452,16 @@
         <v>44595</v>
       </c>
       <c r="B252" t="n">
-        <v>10.45807933807373</v>
+        <v>10.45808029174805</v>
       </c>
       <c r="C252" t="n">
-        <v>10.84194099912248</v>
+        <v>10.84194198780122</v>
       </c>
       <c r="D252" t="n">
-        <v>10.25335427326433</v>
+        <v>10.25335520826973</v>
       </c>
       <c r="E252" t="n">
-        <v>10.62015448151653</v>
+        <v>10.62015544997051</v>
       </c>
       <c r="F252" t="n">
         <v>1397774</v>
@@ -5472,16 +5472,16 @@
         <v>44596</v>
       </c>
       <c r="B253" t="n">
-        <v>10.2533540725708</v>
+        <v>10.25335597991943</v>
       </c>
       <c r="C253" t="n">
-        <v>10.56044207606577</v>
+        <v>10.56044404053951</v>
       </c>
       <c r="D253" t="n">
-        <v>9.835371163276871</v>
+        <v>9.835372992871521</v>
       </c>
       <c r="E253" t="n">
-        <v>10.56044207606577</v>
+        <v>10.56044404053951</v>
       </c>
       <c r="F253" t="n">
         <v>2130212</v>
@@ -5492,16 +5492,16 @@
         <v>44599</v>
       </c>
       <c r="B254" t="n">
-        <v>10.13393115997314</v>
+        <v>10.13393020629883</v>
       </c>
       <c r="C254" t="n">
-        <v>10.34718654856125</v>
+        <v>10.3471855748181</v>
       </c>
       <c r="D254" t="n">
-        <v>9.937734751205435</v>
+        <v>9.937733815994584</v>
       </c>
       <c r="E254" t="n">
-        <v>10.04862801503791</v>
+        <v>10.04862706939122</v>
       </c>
       <c r="F254" t="n">
         <v>1517482</v>
@@ -5572,16 +5572,16 @@
         <v>44603</v>
       </c>
       <c r="B258" t="n">
-        <v>9.929203987121582</v>
+        <v>9.929204940795898</v>
       </c>
       <c r="C258" t="n">
-        <v>10.31306396715434</v>
+        <v>10.31306495769742</v>
       </c>
       <c r="D258" t="n">
-        <v>9.647705294125526</v>
+        <v>9.647706220762624</v>
       </c>
       <c r="E258" t="n">
-        <v>9.99744566972927</v>
+        <v>9.997446629958024</v>
       </c>
       <c r="F258" t="n">
         <v>2967053</v>
@@ -5592,16 +5592,16 @@
         <v>44606</v>
       </c>
       <c r="B259" t="n">
-        <v>10.57750415802002</v>
+        <v>10.5775032043457</v>
       </c>
       <c r="C259" t="n">
-        <v>10.65427616346264</v>
+        <v>10.65427520286651</v>
       </c>
       <c r="D259" t="n">
-        <v>9.767130057607208</v>
+        <v>9.767129176996722</v>
       </c>
       <c r="E259" t="n">
-        <v>9.775661196637856</v>
+        <v>9.775660315258195</v>
       </c>
       <c r="F259" t="n">
         <v>2873091</v>
@@ -5712,16 +5712,16 @@
         <v>44614</v>
       </c>
       <c r="B265" t="n">
-        <v>9.73300838470459</v>
+        <v>9.733009338378906</v>
       </c>
       <c r="C265" t="n">
-        <v>9.843902467790201</v>
+        <v>9.843903432330309</v>
       </c>
       <c r="D265" t="n">
-        <v>9.391799119697389</v>
+        <v>9.391800039938824</v>
       </c>
       <c r="E265" t="n">
-        <v>9.545343124033971</v>
+        <v>9.545344059320188</v>
       </c>
       <c r="F265" t="n">
         <v>6936571</v>
@@ -5772,16 +5772,16 @@
         <v>44617</v>
       </c>
       <c r="B268" t="n">
-        <v>9.425919532775879</v>
+        <v>9.425920486450195</v>
       </c>
       <c r="C268" t="n">
-        <v>9.86949170251933</v>
+        <v>9.869492701072385</v>
       </c>
       <c r="D268" t="n">
-        <v>9.383267966174003</v>
+        <v>9.383268915533016</v>
       </c>
       <c r="E268" t="n">
-        <v>9.579463523376209</v>
+        <v>9.579464492585451</v>
       </c>
       <c r="F268" t="n">
         <v>3597927</v>
@@ -5792,16 +5792,16 @@
         <v>44622</v>
       </c>
       <c r="B269" t="n">
-        <v>9.570934295654297</v>
+        <v>9.57093334197998</v>
       </c>
       <c r="C269" t="n">
-        <v>9.656236613950387</v>
+        <v>9.656235651776313</v>
       </c>
       <c r="D269" t="n">
-        <v>9.272375769326324</v>
+        <v>9.272374845401204</v>
       </c>
       <c r="E269" t="n">
-        <v>9.349147773334476</v>
+        <v>9.34914684175958</v>
       </c>
       <c r="F269" t="n">
         <v>1474809</v>
@@ -5812,16 +5812,16 @@
         <v>44623</v>
       </c>
       <c r="B270" t="n">
-        <v>9.639177322387695</v>
+        <v>9.639176368713379</v>
       </c>
       <c r="C270" t="n">
-        <v>10.15952157411429</v>
+        <v>10.15952056895851</v>
       </c>
       <c r="D270" t="n">
-        <v>9.562405314298255</v>
+        <v>9.562404368219553</v>
       </c>
       <c r="E270" t="n">
-        <v>9.860963031914597</v>
+        <v>9.860962056297398</v>
       </c>
       <c r="F270" t="n">
         <v>3265562</v>
@@ -5872,16 +5872,16 @@
         <v>44628</v>
       </c>
       <c r="B273" t="n">
-        <v>8.897043228149414</v>
+        <v>8.89704418182373</v>
       </c>
       <c r="C273" t="n">
-        <v>8.922634167601151</v>
+        <v>8.92263512401856</v>
       </c>
       <c r="D273" t="n">
-        <v>8.521712747856723</v>
+        <v>8.521713661299355</v>
       </c>
       <c r="E273" t="n">
-        <v>8.726439438887422</v>
+        <v>8.726440374274713</v>
       </c>
       <c r="F273" t="n">
         <v>2260563</v>
@@ -5892,16 +5892,16 @@
         <v>44629</v>
       </c>
       <c r="B274" t="n">
-        <v>9.255314826965332</v>
+        <v>9.255315780639648</v>
       </c>
       <c r="C274" t="n">
-        <v>9.391799026361806</v>
+        <v>9.391799994099552</v>
       </c>
       <c r="D274" t="n">
-        <v>8.845863053359189</v>
+        <v>8.845863964843298</v>
       </c>
       <c r="E274" t="n">
-        <v>8.939696507345268</v>
+        <v>8.939697428498043</v>
       </c>
       <c r="F274" t="n">
         <v>2821903</v>
@@ -5912,16 +5912,16 @@
         <v>44630</v>
       </c>
       <c r="B275" t="n">
-        <v>9.19560432434082</v>
+        <v>9.195603370666504</v>
       </c>
       <c r="C275" t="n">
-        <v>9.280906647822642</v>
+        <v>9.28090568530164</v>
       </c>
       <c r="D275" t="n">
-        <v>8.922635899698962</v>
+        <v>8.922634974334148</v>
       </c>
       <c r="E275" t="n">
-        <v>9.144422435501713</v>
+        <v>9.144421487135462</v>
       </c>
       <c r="F275" t="n">
         <v>2148356</v>
@@ -5932,16 +5932,16 @@
         <v>44631</v>
       </c>
       <c r="B276" t="n">
-        <v>8.615548133850098</v>
+        <v>8.615547180175781</v>
       </c>
       <c r="C276" t="n">
-        <v>9.195604611294117</v>
+        <v>9.19560359341205</v>
       </c>
       <c r="D276" t="n">
-        <v>8.470533602197403</v>
+        <v>8.470532664575069</v>
       </c>
       <c r="E276" t="n">
-        <v>9.195604611294117</v>
+        <v>9.19560359341205</v>
       </c>
       <c r="F276" t="n">
         <v>3220051</v>
@@ -6052,16 +6052,16 @@
         <v>44641</v>
       </c>
       <c r="B282" t="n">
-        <v>9.61358642578125</v>
+        <v>9.613585472106934</v>
       </c>
       <c r="C282" t="n">
-        <v>9.741540322952996</v>
+        <v>9.741539356585566</v>
       </c>
       <c r="D282" t="n">
-        <v>9.39179989057245</v>
+        <v>9.391798958899509</v>
       </c>
       <c r="E282" t="n">
-        <v>9.451512094058163</v>
+        <v>9.451511156461731</v>
       </c>
       <c r="F282" t="n">
         <v>1800179</v>
@@ -6112,16 +6112,16 @@
         <v>44644</v>
       </c>
       <c r="B285" t="n">
-        <v>10.53485107421875</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C285" t="n">
-        <v>10.66280412340302</v>
+        <v>10.66280508866036</v>
       </c>
       <c r="D285" t="n">
-        <v>10.11686902460604</v>
+        <v>10.11686994044226</v>
       </c>
       <c r="E285" t="n">
-        <v>10.27894415126702</v>
+        <v>10.27894508177519</v>
       </c>
       <c r="F285" t="n">
         <v>1712400</v>
@@ -6132,16 +6132,16 @@
         <v>44645</v>
       </c>
       <c r="B286" t="n">
-        <v>10.75663948059082</v>
+        <v>10.7566385269165</v>
       </c>
       <c r="C286" t="n">
-        <v>10.83341148866237</v>
+        <v>10.83341052818152</v>
       </c>
       <c r="D286" t="n">
-        <v>10.37277779106635</v>
+        <v>10.37277687142488</v>
       </c>
       <c r="E286" t="n">
-        <v>10.60309463986436</v>
+        <v>10.6030936998032</v>
       </c>
       <c r="F286" t="n">
         <v>2057131</v>
@@ -6232,16 +6232,16 @@
         <v>44652</v>
       </c>
       <c r="B291" t="n">
-        <v>11.24286270141602</v>
+        <v>11.2428617477417</v>
       </c>
       <c r="C291" t="n">
-        <v>11.25139219111963</v>
+        <v>11.2513912367218</v>
       </c>
       <c r="D291" t="n">
-        <v>10.77369871396854</v>
+        <v>10.77369780009099</v>
       </c>
       <c r="E291" t="n">
-        <v>10.96136397911421</v>
+        <v>10.96136304931798</v>
       </c>
       <c r="F291" t="n">
         <v>2500385</v>
@@ -6252,16 +6252,16 @@
         <v>44655</v>
       </c>
       <c r="B292" t="n">
-        <v>11.24286270141602</v>
+        <v>11.2428617477417</v>
       </c>
       <c r="C292" t="n">
-        <v>11.32816419511862</v>
+        <v>11.32816323420862</v>
       </c>
       <c r="D292" t="n">
-        <v>10.84194122826391</v>
+        <v>10.84194030859771</v>
       </c>
       <c r="E292" t="n">
-        <v>11.14903006884318</v>
+        <v>11.14902912312821</v>
       </c>
       <c r="F292" t="n">
         <v>2094330</v>
@@ -6272,16 +6272,16 @@
         <v>44656</v>
       </c>
       <c r="B293" t="n">
-        <v>10.76516914367676</v>
+        <v>10.76516819000244</v>
       </c>
       <c r="C293" t="n">
-        <v>11.22580284867232</v>
+        <v>11.22580185419098</v>
       </c>
       <c r="D293" t="n">
-        <v>10.66280618974256</v>
+        <v>10.66280524513646</v>
       </c>
       <c r="E293" t="n">
-        <v>11.18315127429</v>
+        <v>11.18315028358712</v>
       </c>
       <c r="F293" t="n">
         <v>1686452</v>
@@ -6292,16 +6292,16 @@
         <v>44657</v>
       </c>
       <c r="B294" t="n">
-        <v>10.57750415802002</v>
+        <v>10.5775032043457</v>
       </c>
       <c r="C294" t="n">
-        <v>10.73104816890526</v>
+        <v>10.73104720138732</v>
       </c>
       <c r="D294" t="n">
-        <v>10.21070311053493</v>
+        <v>10.21070218993162</v>
       </c>
       <c r="E294" t="n">
-        <v>10.73104816890526</v>
+        <v>10.73104720138732</v>
       </c>
       <c r="F294" t="n">
         <v>3552010</v>
@@ -6312,16 +6312,16 @@
         <v>44658</v>
       </c>
       <c r="B295" t="n">
-        <v>10.53485107421875</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C295" t="n">
-        <v>10.67133443662639</v>
+        <v>10.67133540265596</v>
       </c>
       <c r="D295" t="n">
-        <v>10.38130626078115</v>
+        <v>10.38130720055572</v>
       </c>
       <c r="E295" t="n">
-        <v>10.50072982132524</v>
+        <v>10.50073077191071</v>
       </c>
       <c r="F295" t="n">
         <v>1517584</v>
@@ -6352,16 +6352,16 @@
         <v>44662</v>
       </c>
       <c r="B297" t="n">
-        <v>10.53485107421875</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C297" t="n">
-        <v>10.61162306864595</v>
+        <v>10.6116240292701</v>
       </c>
       <c r="D297" t="n">
-        <v>10.17658121716968</v>
+        <v>10.17658213841139</v>
       </c>
       <c r="E297" t="n">
-        <v>10.28747363990719</v>
+        <v>10.28747457118751</v>
       </c>
       <c r="F297" t="n">
         <v>2558465</v>
@@ -6372,16 +6372,16 @@
         <v>44663</v>
       </c>
       <c r="B298" t="n">
-        <v>10.55191230773926</v>
+        <v>10.55191135406494</v>
       </c>
       <c r="C298" t="n">
-        <v>10.90165272360005</v>
+        <v>10.90165173831644</v>
       </c>
       <c r="D298" t="n">
-        <v>10.40689861243314</v>
+        <v>10.40689767186506</v>
       </c>
       <c r="E298" t="n">
-        <v>10.44954935975358</v>
+        <v>10.44954841533075</v>
       </c>
       <c r="F298" t="n">
         <v>1608302</v>
@@ -6432,16 +6432,16 @@
         <v>44669</v>
       </c>
       <c r="B301" t="n">
-        <v>10.75663948059082</v>
+        <v>10.7566385269165</v>
       </c>
       <c r="C301" t="n">
-        <v>10.97842519006605</v>
+        <v>10.9784242167284</v>
       </c>
       <c r="D301" t="n">
-        <v>10.66280601845705</v>
+        <v>10.66280507310193</v>
       </c>
       <c r="E301" t="n">
-        <v>10.81635085918351</v>
+        <v>10.81634990021523</v>
       </c>
       <c r="F301" t="n">
         <v>2677159</v>
@@ -6532,16 +6532,16 @@
         <v>44677</v>
       </c>
       <c r="B306" t="n">
-        <v>10.38983917236328</v>
+        <v>10.38983821868896</v>
       </c>
       <c r="C306" t="n">
-        <v>10.4836709846732</v>
+        <v>10.48367002238615</v>
       </c>
       <c r="D306" t="n">
-        <v>10.16805181527464</v>
+        <v>10.168050881958</v>
       </c>
       <c r="E306" t="n">
-        <v>10.32159665492575</v>
+        <v>10.32159570751536</v>
       </c>
       <c r="F306" t="n">
         <v>4697699</v>
@@ -6632,16 +6632,16 @@
         <v>44684</v>
       </c>
       <c r="B311" t="n">
-        <v>11.31963348388672</v>
+        <v>11.31963443756104</v>
       </c>
       <c r="C311" t="n">
-        <v>11.52435935551378</v>
+        <v>11.52436032643616</v>
       </c>
       <c r="D311" t="n">
-        <v>11.25992211490517</v>
+        <v>11.25992306354883</v>
       </c>
       <c r="E311" t="n">
-        <v>11.38787516623467</v>
+        <v>11.38787612565832</v>
       </c>
       <c r="F311" t="n">
         <v>2034324</v>
@@ -6652,16 +6652,16 @@
         <v>44685</v>
       </c>
       <c r="B312" t="n">
-        <v>11.83144855499268</v>
+        <v>11.83144950866699</v>
       </c>
       <c r="C312" t="n">
-        <v>11.95087212149613</v>
+        <v>11.95087308479659</v>
       </c>
       <c r="D312" t="n">
-        <v>10.95283284580649</v>
+        <v>10.95283372865995</v>
       </c>
       <c r="E312" t="n">
-        <v>11.09784735325709</v>
+        <v>11.09784824779946</v>
       </c>
       <c r="F312" t="n">
         <v>3044087</v>
@@ -6772,16 +6772,16 @@
         <v>44693</v>
       </c>
       <c r="B318" t="n">
-        <v>11.47317886352539</v>
+        <v>11.47317790985107</v>
       </c>
       <c r="C318" t="n">
-        <v>11.68643507432202</v>
+        <v>11.6864341029214</v>
       </c>
       <c r="D318" t="n">
-        <v>11.06372707072919</v>
+        <v>11.06372615108936</v>
       </c>
       <c r="E318" t="n">
-        <v>11.08078852410957</v>
+        <v>11.08078760305155</v>
       </c>
       <c r="F318" t="n">
         <v>2138727</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381309509277</v>
+        <v>11.93381214141846</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470636282327</v>
+        <v>12.04470540028707</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908636463518</v>
+        <v>11.72908542732132</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81438951256891</v>
+        <v>11.81438856843816</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415687561035</v>
+        <v>12.45415782928467</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505013177474</v>
+        <v>12.56505109394068</v>
       </c>
       <c r="D323" t="n">
-        <v>11.9508724782104</v>
+        <v>11.95087339334582</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559753814858</v>
+        <v>12.15559846896078</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6892,16 +6892,16 @@
         <v>44701</v>
       </c>
       <c r="B324" t="n">
-        <v>12.50533676147461</v>
+        <v>12.50533866882324</v>
       </c>
       <c r="C324" t="n">
-        <v>12.65888157275515</v>
+        <v>12.65888350352286</v>
       </c>
       <c r="D324" t="n">
-        <v>12.30914203384275</v>
+        <v>12.30914391126722</v>
       </c>
       <c r="E324" t="n">
-        <v>12.47974582216399</v>
+        <v>12.47974772560942</v>
       </c>
       <c r="F324" t="n">
         <v>4482610</v>
@@ -6932,16 +6932,16 @@
         <v>44705</v>
       </c>
       <c r="B326" t="n">
-        <v>12.26649188995361</v>
+        <v>12.2664909362793</v>
       </c>
       <c r="C326" t="n">
-        <v>12.62476263215845</v>
+        <v>12.62476165062991</v>
       </c>
       <c r="D326" t="n">
-        <v>12.02764555306706</v>
+        <v>12.02764461796216</v>
       </c>
       <c r="E326" t="n">
-        <v>12.53092999542028</v>
+        <v>12.53092902118688</v>
       </c>
       <c r="F326" t="n">
         <v>3539137</v>
@@ -6952,16 +6952,16 @@
         <v>44706</v>
       </c>
       <c r="B327" t="n">
-        <v>12.36885452270508</v>
+        <v>12.36885356903076</v>
       </c>
       <c r="C327" t="n">
-        <v>12.51386904370087</v>
+        <v>12.51386807884551</v>
       </c>
       <c r="D327" t="n">
-        <v>12.08735661974265</v>
+        <v>12.08735568777263</v>
       </c>
       <c r="E327" t="n">
-        <v>12.21531051184678</v>
+        <v>12.21530957001115</v>
       </c>
       <c r="F327" t="n">
         <v>1655537</v>
@@ -6972,16 +6972,16 @@
         <v>44707</v>
       </c>
       <c r="B328" t="n">
-        <v>12.70153427124023</v>
+        <v>12.70153331756592</v>
       </c>
       <c r="C328" t="n">
-        <v>12.92332079694747</v>
+        <v>12.92331982662067</v>
       </c>
       <c r="D328" t="n">
-        <v>12.38591593609915</v>
+        <v>12.38591500612253</v>
       </c>
       <c r="E328" t="n">
-        <v>12.42003719377205</v>
+        <v>12.42003626123349</v>
       </c>
       <c r="F328" t="n">
         <v>2007160</v>
@@ -7052,16 +7052,16 @@
         <v>44713</v>
       </c>
       <c r="B332" t="n">
-        <v>12.69300365447998</v>
+        <v>12.6930046081543</v>
       </c>
       <c r="C332" t="n">
-        <v>12.71006510749335</v>
+        <v>12.71006606244956</v>
       </c>
       <c r="D332" t="n">
-        <v>12.23237080978446</v>
+        <v>12.23237172884965</v>
       </c>
       <c r="E332" t="n">
-        <v>12.52239901934583</v>
+        <v>12.52239996020196</v>
       </c>
       <c r="F332" t="n">
         <v>4014218</v>
@@ -7072,16 +7072,16 @@
         <v>44714</v>
       </c>
       <c r="B333" t="n">
-        <v>12.57358074188232</v>
+        <v>12.57357978820801</v>
       </c>
       <c r="C333" t="n">
-        <v>13.05980452292923</v>
+        <v>13.05980353237607</v>
       </c>
       <c r="D333" t="n">
-        <v>12.43709654079169</v>
+        <v>12.43709559746936</v>
       </c>
       <c r="E333" t="n">
-        <v>12.69300349018043</v>
+        <v>12.6930025274482</v>
       </c>
       <c r="F333" t="n">
         <v>2071017</v>
@@ -7112,16 +7112,16 @@
         <v>44718</v>
       </c>
       <c r="B335" t="n">
-        <v>12.36885452270508</v>
+        <v>12.36885356903076</v>
       </c>
       <c r="C335" t="n">
-        <v>12.65888356469666</v>
+        <v>12.65888258866027</v>
       </c>
       <c r="D335" t="n">
-        <v>12.19824988295512</v>
+        <v>12.19824894243491</v>
       </c>
       <c r="E335" t="n">
-        <v>12.65888356469666</v>
+        <v>12.65888258866027</v>
       </c>
       <c r="F335" t="n">
         <v>1740275</v>
@@ -7132,16 +7132,16 @@
         <v>44719</v>
       </c>
       <c r="B336" t="n">
-        <v>12.02764511108398</v>
+        <v>12.0276460647583</v>
       </c>
       <c r="C336" t="n">
-        <v>12.37738470118792</v>
+        <v>12.37738568259315</v>
       </c>
       <c r="D336" t="n">
-        <v>11.87410110191233</v>
+        <v>11.87410204341212</v>
       </c>
       <c r="E336" t="n">
-        <v>12.36885438683579</v>
+        <v>12.36885536756466</v>
       </c>
       <c r="F336" t="n">
         <v>3370370</v>
@@ -7152,16 +7152,16 @@
         <v>44720</v>
       </c>
       <c r="B337" t="n">
-        <v>12.02764511108398</v>
+        <v>12.0276460647583</v>
       </c>
       <c r="C337" t="n">
-        <v>12.14706868743044</v>
+        <v>12.14706965057388</v>
       </c>
       <c r="D337" t="n">
-        <v>11.80585941167863</v>
+        <v>11.80586034776752</v>
       </c>
       <c r="E337" t="n">
-        <v>11.9679329106191</v>
+        <v>11.96793385955882</v>
       </c>
       <c r="F337" t="n">
         <v>2224783</v>
@@ -7192,16 +7192,16 @@
         <v>44722</v>
       </c>
       <c r="B339" t="n">
-        <v>11.64378356933594</v>
+        <v>11.64378547668457</v>
       </c>
       <c r="C339" t="n">
-        <v>12.07882545243938</v>
+        <v>12.0788274310515</v>
       </c>
       <c r="D339" t="n">
-        <v>11.42199705857082</v>
+        <v>11.42199892958898</v>
       </c>
       <c r="E339" t="n">
-        <v>12.06176564933559</v>
+        <v>12.06176762515317</v>
       </c>
       <c r="F339" t="n">
         <v>2898634</v>
@@ -7252,16 +7252,16 @@
         <v>44727</v>
       </c>
       <c r="B342" t="n">
-        <v>10.83341026306152</v>
+        <v>10.83341121673584</v>
       </c>
       <c r="C342" t="n">
-        <v>11.07225657499456</v>
+        <v>11.07225754969472</v>
       </c>
       <c r="D342" t="n">
-        <v>10.67133512593145</v>
+        <v>10.67133606533815</v>
       </c>
       <c r="E342" t="n">
-        <v>10.88459132112458</v>
+        <v>10.88459227930441</v>
       </c>
       <c r="F342" t="n">
         <v>3158221</v>
@@ -7272,16 +7272,16 @@
         <v>44729</v>
       </c>
       <c r="B343" t="n">
-        <v>10.66280555725098</v>
+        <v>10.66280460357666</v>
       </c>
       <c r="C343" t="n">
-        <v>10.69692681473284</v>
+        <v>10.69692585800674</v>
       </c>
       <c r="D343" t="n">
-        <v>10.2960053376542</v>
+        <v>10.29600441678626</v>
       </c>
       <c r="E343" t="n">
-        <v>10.69692681473284</v>
+        <v>10.69692585800674</v>
       </c>
       <c r="F343" t="n">
         <v>2862346</v>
@@ -7292,16 +7292,16 @@
         <v>44732</v>
       </c>
       <c r="B344" t="n">
-        <v>10.38130855560303</v>
+        <v>10.38130760192871</v>
       </c>
       <c r="C344" t="n">
-        <v>10.93577491477317</v>
+        <v>10.93577391016304</v>
       </c>
       <c r="D344" t="n">
-        <v>10.33012748953222</v>
+        <v>10.33012654055963</v>
       </c>
       <c r="E344" t="n">
-        <v>10.93577491477317</v>
+        <v>10.93577391016304</v>
       </c>
       <c r="F344" t="n">
         <v>1404768</v>
@@ -7412,16 +7412,16 @@
         <v>44740</v>
       </c>
       <c r="B350" t="n">
-        <v>10.23629283905029</v>
+        <v>10.23629188537598</v>
       </c>
       <c r="C350" t="n">
-        <v>10.81635007643811</v>
+        <v>10.81634906872219</v>
       </c>
       <c r="D350" t="n">
-        <v>10.18511177890085</v>
+        <v>10.18511082999487</v>
       </c>
       <c r="E350" t="n">
-        <v>10.70545681743382</v>
+        <v>10.70545582004938</v>
       </c>
       <c r="F350" t="n">
         <v>2763519</v>
@@ -7512,16 +7512,16 @@
         <v>44747</v>
       </c>
       <c r="B355" t="n">
-        <v>9.622116088867188</v>
+        <v>9.622115135192871</v>
       </c>
       <c r="C355" t="n">
-        <v>9.681828293425781</v>
+        <v>9.681827333833224</v>
       </c>
       <c r="D355" t="n">
-        <v>9.178543835063046</v>
+        <v>9.178542925352392</v>
       </c>
       <c r="E355" t="n">
-        <v>9.681828293425781</v>
+        <v>9.681827333833224</v>
       </c>
       <c r="F355" t="n">
         <v>3899578</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.11030101776123</v>
+        <v>9.110300064086914</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707418920911163</v>
+        <v>9.707417904730018</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076180583712192</v>
+        <v>9.076179633609632</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707418920911163</v>
+        <v>9.707417904730018</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7612,16 +7612,16 @@
         <v>44754</v>
       </c>
       <c r="B360" t="n">
-        <v>9.229724884033203</v>
+        <v>9.22972583770752</v>
       </c>
       <c r="C360" t="n">
-        <v>9.289436258569864</v>
+        <v>9.289437218413942</v>
       </c>
       <c r="D360" t="n">
-        <v>8.879984477223353</v>
+        <v>8.879985394760249</v>
       </c>
       <c r="E360" t="n">
-        <v>9.229724884033203</v>
+        <v>9.22972583770752</v>
       </c>
       <c r="F360" t="n">
         <v>1719496</v>
@@ -7632,16 +7632,16 @@
         <v>44755</v>
       </c>
       <c r="B361" t="n">
-        <v>9.255314826965332</v>
+        <v>9.255315780639648</v>
       </c>
       <c r="C361" t="n">
-        <v>9.383268712363071</v>
+        <v>9.383269679221847</v>
       </c>
       <c r="D361" t="n">
-        <v>9.050589764745537</v>
+        <v>9.050590697324836</v>
       </c>
       <c r="E361" t="n">
-        <v>9.204133767556202</v>
+        <v>9.204134715956785</v>
       </c>
       <c r="F361" t="n">
         <v>1870727</v>
@@ -7692,16 +7692,16 @@
         <v>44760</v>
       </c>
       <c r="B364" t="n">
-        <v>9.511221885681152</v>
+        <v>9.511222839355469</v>
       </c>
       <c r="C364" t="n">
-        <v>9.698887146706557</v>
+        <v>9.698888119197754</v>
       </c>
       <c r="D364" t="n">
-        <v>9.212664190527063</v>
+        <v>9.212665114265498</v>
       </c>
       <c r="E364" t="n">
-        <v>9.212664190527063</v>
+        <v>9.212665114265498</v>
       </c>
       <c r="F364" t="n">
         <v>1476836</v>
@@ -7732,16 +7732,16 @@
         <v>44762</v>
       </c>
       <c r="B366" t="n">
-        <v>10.08274936676025</v>
+        <v>10.08274841308594</v>
       </c>
       <c r="C366" t="n">
-        <v>10.20217294619664</v>
+        <v>10.20217198122667</v>
       </c>
       <c r="D366" t="n">
-        <v>9.724478628451092</v>
+        <v>9.724477708663724</v>
       </c>
       <c r="E366" t="n">
-        <v>9.767130201315277</v>
+        <v>9.767129277493721</v>
       </c>
       <c r="F366" t="n">
         <v>1476532</v>
@@ -7752,16 +7752,16 @@
         <v>44763</v>
       </c>
       <c r="B367" t="n">
-        <v>9.963326454162598</v>
+        <v>9.963324546813965</v>
       </c>
       <c r="C367" t="n">
-        <v>10.19364331387749</v>
+        <v>10.1936413624377</v>
       </c>
       <c r="D367" t="n">
-        <v>9.946265823875066</v>
+        <v>9.94626391979247</v>
       </c>
       <c r="E367" t="n">
-        <v>10.02303783558557</v>
+        <v>10.02303591680597</v>
       </c>
       <c r="F367" t="n">
         <v>1242590</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.5092601776123</v>
+        <v>10.50926113128662</v>
       </c>
       <c r="C371" t="n">
-        <v>10.61162311212909</v>
+        <v>10.61162407509244</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421749977017</v>
+        <v>10.07421841396606</v>
       </c>
       <c r="E371" t="n">
-        <v>10.12539855473696</v>
+        <v>10.12539947357733</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7972,16 +7972,16 @@
         <v>44778</v>
       </c>
       <c r="B378" t="n">
-        <v>12.79536724090576</v>
+        <v>12.79536628723145</v>
       </c>
       <c r="C378" t="n">
-        <v>12.93185145059431</v>
+        <v>12.93185048674745</v>
       </c>
       <c r="D378" t="n">
-        <v>12.24090173667624</v>
+        <v>12.24090082432778</v>
       </c>
       <c r="E378" t="n">
-        <v>12.32620405851283</v>
+        <v>12.32620313980655</v>
       </c>
       <c r="F378" t="n">
         <v>4419056</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.16216850280762</v>
+        <v>13.1621675491333</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718220482493</v>
+        <v>13.30718124064354</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271669191557</v>
+        <v>12.75271576790837</v>
       </c>
       <c r="E379" t="n">
-        <v>12.79536744120987</v>
+        <v>12.79536651411238</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248371124268</v>
+        <v>13.39248466491699</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634537898129</v>
+        <v>13.77634635999027</v>
       </c>
       <c r="D381" t="n">
-        <v>13.17922832861007</v>
+        <v>13.17922926709854</v>
       </c>
       <c r="E381" t="n">
-        <v>13.30718139327297</v>
+        <v>13.30718234087294</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8072,16 +8072,16 @@
         <v>44785</v>
       </c>
       <c r="B383" t="n">
-        <v>13.75928497314453</v>
+        <v>13.75928401947021</v>
       </c>
       <c r="C383" t="n">
-        <v>13.84458729249473</v>
+        <v>13.84458633290799</v>
       </c>
       <c r="D383" t="n">
-        <v>13.47778707191389</v>
+        <v>13.47778613775057</v>
       </c>
       <c r="E383" t="n">
-        <v>13.47778707191389</v>
+        <v>13.47778613775057</v>
       </c>
       <c r="F383" t="n">
         <v>2291478</v>
@@ -8152,16 +8152,16 @@
         <v>44791</v>
       </c>
       <c r="B387" t="n">
-        <v>13.63986110687256</v>
+        <v>13.63986206054688</v>
       </c>
       <c r="C387" t="n">
-        <v>14.13461438369162</v>
+        <v>14.13461537195818</v>
       </c>
       <c r="D387" t="n">
-        <v>13.23893963722324</v>
+        <v>13.23894056286585</v>
       </c>
       <c r="E387" t="n">
-        <v>13.64839142108495</v>
+        <v>13.64839237535569</v>
       </c>
       <c r="F387" t="n">
         <v>3074090</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066864013672</v>
+        <v>12.88066959381104</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59720924665701</v>
+        <v>13.59721025338341</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801789456504</v>
+        <v>12.83801884508153</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59720924665701</v>
+        <v>13.59721025338341</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8232,16 +8232,16 @@
         <v>44797</v>
       </c>
       <c r="B391" t="n">
-        <v>12.42856693267822</v>
+        <v>12.42856597900391</v>
       </c>
       <c r="C391" t="n">
-        <v>12.57358145611087</v>
+        <v>12.57358049130923</v>
       </c>
       <c r="D391" t="n">
-        <v>12.13000839580709</v>
+        <v>12.1300074650419</v>
       </c>
       <c r="E391" t="n">
-        <v>12.29208272383475</v>
+        <v>12.2920817806332</v>
       </c>
       <c r="F391" t="n">
         <v>4991546</v>
@@ -8292,16 +8292,16 @@
         <v>44802</v>
       </c>
       <c r="B394" t="n">
-        <v>12.25796127319336</v>
+        <v>12.25796222686768</v>
       </c>
       <c r="C394" t="n">
-        <v>12.40297496001295</v>
+        <v>12.40297592496939</v>
       </c>
       <c r="D394" t="n">
-        <v>12.04470507532147</v>
+        <v>12.04470601240437</v>
       </c>
       <c r="E394" t="n">
-        <v>12.18118844825953</v>
+        <v>12.18118939596089</v>
       </c>
       <c r="F394" t="n">
         <v>4196061</v>
@@ -8372,16 +8372,16 @@
         <v>44806</v>
       </c>
       <c r="B398" t="n">
-        <v>12.42003726959229</v>
+        <v>12.42003631591797</v>
       </c>
       <c r="C398" t="n">
-        <v>12.70153434877891</v>
+        <v>12.7015333734898</v>
       </c>
       <c r="D398" t="n">
-        <v>12.36885455818716</v>
+        <v>12.36885360844292</v>
       </c>
       <c r="E398" t="n">
-        <v>12.52239939406925</v>
+        <v>12.52239843253504</v>
       </c>
       <c r="F398" t="n">
         <v>3090207</v>
@@ -8392,16 +8392,16 @@
         <v>44809</v>
       </c>
       <c r="B399" t="n">
-        <v>13.30718231201172</v>
+        <v>13.3071813583374</v>
       </c>
       <c r="C399" t="n">
-        <v>13.40954526555925</v>
+        <v>13.40954430454897</v>
       </c>
       <c r="D399" t="n">
-        <v>12.38591655466734</v>
+        <v>12.38591566701658</v>
       </c>
       <c r="E399" t="n">
-        <v>12.48827868363151</v>
+        <v>12.48827778864485</v>
       </c>
       <c r="F399" t="n">
         <v>2134165</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.33473491668701</v>
+        <v>12.3347339630127</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121913238976</v>
+        <v>12.47121816816301</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646415968605</v>
+        <v>11.97646323371185</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22384164603791</v>
+        <v>12.22384070093743</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8492,16 +8492,16 @@
         <v>44817</v>
       </c>
       <c r="B404" t="n">
-        <v>11.82736015319824</v>
+        <v>11.82735919952393</v>
       </c>
       <c r="C404" t="n">
-        <v>12.11854774525109</v>
+        <v>12.11854676809748</v>
       </c>
       <c r="D404" t="n">
-        <v>11.74171645274152</v>
+        <v>11.7417155059729</v>
       </c>
       <c r="E404" t="n">
-        <v>12.11854774525109</v>
+        <v>12.11854676809748</v>
       </c>
       <c r="F404" t="n">
         <v>3904244</v>
@@ -8532,16 +8532,16 @@
         <v>44819</v>
       </c>
       <c r="B406" t="n">
-        <v>12.76943588256836</v>
+        <v>12.76943683624268</v>
       </c>
       <c r="C406" t="n">
-        <v>12.9321583148535</v>
+        <v>12.9321592806806</v>
       </c>
       <c r="D406" t="n">
-        <v>12.33265413957057</v>
+        <v>12.33265506062422</v>
       </c>
       <c r="E406" t="n">
-        <v>12.5467629502966</v>
+        <v>12.54676388734078</v>
       </c>
       <c r="F406" t="n">
         <v>3409247</v>
@@ -8592,16 +8592,16 @@
         <v>44824</v>
       </c>
       <c r="B409" t="n">
-        <v>11.88731002807617</v>
+        <v>11.88731098175049</v>
       </c>
       <c r="C409" t="n">
-        <v>12.52107073904231</v>
+        <v>12.52107174356088</v>
       </c>
       <c r="D409" t="n">
-        <v>11.87018013448028</v>
+        <v>11.87018108678033</v>
       </c>
       <c r="E409" t="n">
-        <v>12.44399116536064</v>
+        <v>12.4439921636954</v>
       </c>
       <c r="F409" t="n">
         <v>1700434</v>
@@ -8612,16 +8612,16 @@
         <v>44825</v>
       </c>
       <c r="B410" t="n">
-        <v>11.65607166290283</v>
+        <v>11.65607070922852</v>
       </c>
       <c r="C410" t="n">
-        <v>12.10998334747001</v>
+        <v>12.10998235665763</v>
       </c>
       <c r="D410" t="n">
-        <v>11.50191415999951</v>
+        <v>11.50191321893803</v>
       </c>
       <c r="E410" t="n">
-        <v>11.94726007292391</v>
+        <v>11.9472590954252</v>
       </c>
       <c r="F410" t="n">
         <v>3396829</v>
@@ -8632,16 +8632,16 @@
         <v>44826</v>
       </c>
       <c r="B411" t="n">
-        <v>12.18706130981445</v>
+        <v>12.18706226348877</v>
       </c>
       <c r="C411" t="n">
-        <v>12.24701181243212</v>
+        <v>12.24701277079775</v>
       </c>
       <c r="D411" t="n">
-        <v>11.07369577501007</v>
+        <v>11.07369664156018</v>
       </c>
       <c r="E411" t="n">
-        <v>11.26211222936794</v>
+        <v>11.2621131106622</v>
       </c>
       <c r="F411" t="n">
         <v>10292961</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186389923096</v>
+        <v>11.56186485290527</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889314808853</v>
+        <v>11.69889411306563</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072583059598</v>
+        <v>11.21072675530685</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775507945355</v>
+        <v>11.34775601546721</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8772,16 +8772,16 @@
         <v>44837</v>
       </c>
       <c r="B418" t="n">
-        <v>12.41829872131348</v>
+        <v>12.41829776763916</v>
       </c>
       <c r="C418" t="n">
-        <v>12.62384342526681</v>
+        <v>12.6238424558075</v>
       </c>
       <c r="D418" t="n">
-        <v>12.01577426015137</v>
+        <v>12.01577333738928</v>
       </c>
       <c r="E418" t="n">
-        <v>12.06716064228553</v>
+        <v>12.06715971557718</v>
       </c>
       <c r="F418" t="n">
         <v>3117277</v>
@@ -8792,16 +8792,16 @@
         <v>44838</v>
       </c>
       <c r="B419" t="n">
-        <v>12.84651660919189</v>
+        <v>12.84651756286621</v>
       </c>
       <c r="C419" t="n">
-        <v>12.94072360386043</v>
+        <v>12.9407245645283</v>
       </c>
       <c r="D419" t="n">
-        <v>12.55532820453467</v>
+        <v>12.55532913659232</v>
       </c>
       <c r="E419" t="n">
-        <v>12.59814964070976</v>
+        <v>12.5981505759463</v>
       </c>
       <c r="F419" t="n">
         <v>4425287</v>
@@ -8812,16 +8812,16 @@
         <v>44839</v>
       </c>
       <c r="B420" t="n">
-        <v>12.84651660919189</v>
+        <v>12.84651756286621</v>
       </c>
       <c r="C420" t="n">
-        <v>13.1377041892658</v>
+        <v>13.13770516455673</v>
       </c>
       <c r="D420" t="n">
-        <v>12.56389315143634</v>
+        <v>12.56389408412982</v>
       </c>
       <c r="E420" t="n">
-        <v>12.84651660919189</v>
+        <v>12.84651756286621</v>
       </c>
       <c r="F420" t="n">
         <v>2792192</v>
@@ -8852,16 +8852,16 @@
         <v>44841</v>
       </c>
       <c r="B422" t="n">
-        <v>12.62384414672852</v>
+        <v>12.6238431930542</v>
       </c>
       <c r="C422" t="n">
-        <v>12.92359586075333</v>
+        <v>12.92359488443413</v>
       </c>
       <c r="D422" t="n">
-        <v>12.54676456912213</v>
+        <v>12.54676362127082</v>
       </c>
       <c r="E422" t="n">
-        <v>12.92359586075333</v>
+        <v>12.92359488443413</v>
       </c>
       <c r="F422" t="n">
         <v>1382517</v>
@@ -8932,16 +8932,16 @@
         <v>44848</v>
       </c>
       <c r="B426" t="n">
-        <v>12.76943588256836</v>
+        <v>12.76943683624268</v>
       </c>
       <c r="C426" t="n">
-        <v>13.12057393635908</v>
+        <v>13.12057491625784</v>
       </c>
       <c r="D426" t="n">
-        <v>12.65809900414086</v>
+        <v>12.65809994950008</v>
       </c>
       <c r="E426" t="n">
-        <v>13.09488074713864</v>
+        <v>13.09488172511853</v>
       </c>
       <c r="F426" t="n">
         <v>2206838</v>
@@ -8972,16 +8972,16 @@
         <v>44852</v>
       </c>
       <c r="B428" t="n">
-        <v>12.84651660919189</v>
+        <v>12.84651756286621</v>
       </c>
       <c r="C428" t="n">
-        <v>13.16339655622087</v>
+        <v>13.16339753341909</v>
       </c>
       <c r="D428" t="n">
-        <v>12.65810014610488</v>
+        <v>12.6581010857919</v>
       </c>
       <c r="E428" t="n">
-        <v>12.80369434843349</v>
+        <v>12.80369529892885</v>
       </c>
       <c r="F428" t="n">
         <v>2211886</v>
@@ -9012,16 +9012,16 @@
         <v>44854</v>
       </c>
       <c r="B430" t="n">
-        <v>12.78656482696533</v>
+        <v>12.78656387329102</v>
       </c>
       <c r="C430" t="n">
-        <v>13.08631734333896</v>
+        <v>13.08631636730787</v>
       </c>
       <c r="D430" t="n">
-        <v>12.65809969840043</v>
+        <v>12.65809875430757</v>
       </c>
       <c r="E430" t="n">
-        <v>13.08631734333896</v>
+        <v>13.08631636730787</v>
       </c>
       <c r="F430" t="n">
         <v>2107193</v>
@@ -9032,16 +9032,16 @@
         <v>44855</v>
       </c>
       <c r="B431" t="n">
-        <v>13.08631801605225</v>
+        <v>13.08631706237793</v>
       </c>
       <c r="C431" t="n">
-        <v>13.26616953512184</v>
+        <v>13.26616856834072</v>
       </c>
       <c r="D431" t="n">
-        <v>12.58958572028859</v>
+        <v>12.58958480281398</v>
       </c>
       <c r="E431" t="n">
-        <v>12.74374404740777</v>
+        <v>12.74374311869877</v>
       </c>
       <c r="F431" t="n">
         <v>1434409</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71804904937744</v>
+        <v>12.71805000305176</v>
       </c>
       <c r="C433" t="n">
-        <v>13.0777520364355</v>
+        <v>13.07775301708247</v>
       </c>
       <c r="D433" t="n">
-        <v>12.6923566856589</v>
+        <v>12.69235763740665</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87220735460472</v>
+        <v>12.87220831983874</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9112,16 +9112,16 @@
         <v>44861</v>
       </c>
       <c r="B435" t="n">
-        <v>13.13770294189453</v>
+        <v>13.13770389556885</v>
       </c>
       <c r="C435" t="n">
-        <v>13.30042537341002</v>
+        <v>13.30042633889646</v>
       </c>
       <c r="D435" t="n">
-        <v>12.22131720333817</v>
+        <v>12.22131809049146</v>
       </c>
       <c r="E435" t="n">
-        <v>12.35834727033798</v>
+        <v>12.35834816743837</v>
       </c>
       <c r="F435" t="n">
         <v>3242667</v>
@@ -9152,16 +9152,16 @@
         <v>44865</v>
       </c>
       <c r="B437" t="n">
-        <v>13.8057222366333</v>
+        <v>13.80572319030762</v>
       </c>
       <c r="C437" t="n">
-        <v>14.0712174500381</v>
+        <v>14.07121842205234</v>
       </c>
       <c r="D437" t="n">
-        <v>12.50394183492532</v>
+        <v>12.50394269867501</v>
       </c>
       <c r="E437" t="n">
-        <v>12.50394183492532</v>
+        <v>12.50394269867501</v>
       </c>
       <c r="F437" t="n">
         <v>7903691</v>
@@ -9172,16 +9172,16 @@
         <v>44866</v>
       </c>
       <c r="B438" t="n">
-        <v>13.61730480194092</v>
+        <v>13.61730575561523</v>
       </c>
       <c r="C438" t="n">
-        <v>14.01126509663326</v>
+        <v>14.01126607789819</v>
       </c>
       <c r="D438" t="n">
-        <v>13.53166194079393</v>
+        <v>13.53166288847033</v>
       </c>
       <c r="E438" t="n">
-        <v>13.70294931225432</v>
+        <v>13.70295027192667</v>
       </c>
       <c r="F438" t="n">
         <v>3366744</v>
@@ -9212,16 +9212,16 @@
         <v>44869</v>
       </c>
       <c r="B440" t="n">
-        <v>14.01126766204834</v>
+        <v>14.01126670837402</v>
       </c>
       <c r="C440" t="n">
-        <v>14.29389195916385</v>
+        <v>14.29389098625276</v>
       </c>
       <c r="D440" t="n">
-        <v>13.80572294357798</v>
+        <v>13.80572200389402</v>
       </c>
       <c r="E440" t="n">
-        <v>14.13973280187356</v>
+        <v>14.13973183945529</v>
       </c>
       <c r="F440" t="n">
         <v>3663661</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.40319728851318</v>
+        <v>13.4031982421875</v>
       </c>
       <c r="C441" t="n">
-        <v>14.03695880976449</v>
+        <v>14.03695980853268</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037667840605</v>
+        <v>13.36037762903356</v>
       </c>
       <c r="E441" t="n">
-        <v>13.9341876963408</v>
+        <v>13.93418868779654</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9272,16 +9272,16 @@
         <v>44874</v>
       </c>
       <c r="B443" t="n">
-        <v>13.13770294189453</v>
+        <v>13.13770389556885</v>
       </c>
       <c r="C443" t="n">
-        <v>13.55735561523272</v>
+        <v>13.55735659936989</v>
       </c>
       <c r="D443" t="n">
-        <v>12.98354463188427</v>
+        <v>12.98354557436813</v>
       </c>
       <c r="E443" t="n">
-        <v>13.29186042732156</v>
+        <v>13.29186139218626</v>
       </c>
       <c r="F443" t="n">
         <v>3144132</v>
@@ -9412,16 +9412,16 @@
         <v>44886</v>
       </c>
       <c r="B450" t="n">
-        <v>11.25354671478271</v>
+        <v>11.25354766845703</v>
       </c>
       <c r="C450" t="n">
-        <v>11.33062628193585</v>
+        <v>11.33062724214222</v>
       </c>
       <c r="D450" t="n">
-        <v>10.80820167775862</v>
+        <v>10.80820259369247</v>
       </c>
       <c r="E450" t="n">
-        <v>10.98805235194947</v>
+        <v>10.98805328312464</v>
       </c>
       <c r="F450" t="n">
         <v>4991964</v>
@@ -9432,16 +9432,16 @@
         <v>44887</v>
       </c>
       <c r="B451" t="n">
-        <v>10.98805332183838</v>
+        <v>10.98805236816406</v>
       </c>
       <c r="C451" t="n">
-        <v>11.33919140430814</v>
+        <v>11.33919042015788</v>
       </c>
       <c r="D451" t="n">
-        <v>10.89384550339121</v>
+        <v>10.89384455789337</v>
       </c>
       <c r="E451" t="n">
-        <v>11.2792408994251</v>
+        <v>11.27923992047805</v>
       </c>
       <c r="F451" t="n">
         <v>2547672</v>
@@ -9452,16 +9452,16 @@
         <v>44888</v>
       </c>
       <c r="B452" t="n">
-        <v>11.04800319671631</v>
+        <v>11.04800415039062</v>
       </c>
       <c r="C452" t="n">
-        <v>11.09082545466704</v>
+        <v>11.09082641203781</v>
       </c>
       <c r="D452" t="n">
-        <v>10.78250800100489</v>
+        <v>10.78250893176141</v>
       </c>
       <c r="E452" t="n">
-        <v>10.9880526952519</v>
+        <v>10.98805364375123</v>
       </c>
       <c r="F452" t="n">
         <v>2848931</v>
@@ -9472,16 +9472,16 @@
         <v>44889</v>
       </c>
       <c r="B453" t="n">
-        <v>11.53617000579834</v>
+        <v>11.53617191314697</v>
       </c>
       <c r="C453" t="n">
-        <v>11.81879343277872</v>
+        <v>11.81879538685529</v>
       </c>
       <c r="D453" t="n">
-        <v>11.05656683944524</v>
+        <v>11.05656866749802</v>
       </c>
       <c r="E453" t="n">
-        <v>11.11651733831228</v>
+        <v>11.11651917627706</v>
       </c>
       <c r="F453" t="n">
         <v>3457606</v>
@@ -9492,16 +9492,16 @@
         <v>44890</v>
       </c>
       <c r="B454" t="n">
-        <v>10.95379543304443</v>
+        <v>10.95379638671875</v>
       </c>
       <c r="C454" t="n">
-        <v>11.54473550401364</v>
+        <v>11.54473650913719</v>
       </c>
       <c r="D454" t="n">
-        <v>10.89384493130964</v>
+        <v>10.89384587976446</v>
       </c>
       <c r="E454" t="n">
-        <v>11.51047736766524</v>
+        <v>11.51047836980616</v>
       </c>
       <c r="F454" t="n">
         <v>2880833</v>
@@ -9512,16 +9512,16 @@
         <v>44893</v>
       </c>
       <c r="B455" t="n">
-        <v>10.96235942840576</v>
+        <v>10.96236038208008</v>
       </c>
       <c r="C455" t="n">
-        <v>11.18503236460255</v>
+        <v>11.18503333764837</v>
       </c>
       <c r="D455" t="n">
-        <v>10.84245842631905</v>
+        <v>10.84245936956254</v>
       </c>
       <c r="E455" t="n">
-        <v>10.95379530670907</v>
+        <v>10.95379625963835</v>
       </c>
       <c r="F455" t="n">
         <v>2642270</v>
@@ -9552,16 +9552,16 @@
         <v>44895</v>
       </c>
       <c r="B457" t="n">
-        <v>11.35632038116455</v>
+        <v>11.35631942749023</v>
       </c>
       <c r="C457" t="n">
-        <v>11.57042922318563</v>
+        <v>11.57042825153101</v>
       </c>
       <c r="D457" t="n">
-        <v>11.04800453920422</v>
+        <v>11.04800361142147</v>
       </c>
       <c r="E457" t="n">
-        <v>11.34775625836705</v>
+        <v>11.34775530541193</v>
       </c>
       <c r="F457" t="n">
         <v>6904107</v>
@@ -9572,16 +9572,16 @@
         <v>44896</v>
       </c>
       <c r="B458" t="n">
-        <v>11.15077686309814</v>
+        <v>11.15077590942383</v>
       </c>
       <c r="C458" t="n">
-        <v>11.33919251850636</v>
+        <v>11.33919154871773</v>
       </c>
       <c r="D458" t="n">
-        <v>10.97092533077665</v>
+        <v>10.9709243924842</v>
       </c>
       <c r="E458" t="n">
-        <v>11.32206427233292</v>
+        <v>11.32206330400918</v>
       </c>
       <c r="F458" t="n">
         <v>2224001</v>
@@ -9612,16 +9612,16 @@
         <v>44900</v>
       </c>
       <c r="B460" t="n">
-        <v>10.65404510498047</v>
+        <v>10.65404319763184</v>
       </c>
       <c r="C460" t="n">
-        <v>11.2621134969344</v>
+        <v>11.26211148072586</v>
       </c>
       <c r="D460" t="n">
-        <v>10.56840057779207</v>
+        <v>10.56839868577602</v>
       </c>
       <c r="E460" t="n">
-        <v>11.2621134969344</v>
+        <v>11.26211148072586</v>
       </c>
       <c r="F460" t="n">
         <v>2438739</v>
@@ -9632,16 +9632,16 @@
         <v>44901</v>
       </c>
       <c r="B461" t="n">
-        <v>10.64548015594482</v>
+        <v>10.64547920227051</v>
       </c>
       <c r="C461" t="n">
-        <v>10.88528219337026</v>
+        <v>10.8852812182133</v>
       </c>
       <c r="D461" t="n">
-        <v>10.44850038210729</v>
+        <v>10.44849944607939</v>
       </c>
       <c r="E461" t="n">
-        <v>10.62835108559299</v>
+        <v>10.62835013345318</v>
       </c>
       <c r="F461" t="n">
         <v>3634787</v>
@@ -9652,16 +9652,16 @@
         <v>44902</v>
       </c>
       <c r="B462" t="n">
-        <v>10.36285495758057</v>
+        <v>10.36285591125488</v>
       </c>
       <c r="C462" t="n">
-        <v>10.91097188081368</v>
+        <v>10.91097288493018</v>
       </c>
       <c r="D462" t="n">
-        <v>10.24295396833174</v>
+        <v>10.24295491097179</v>
       </c>
       <c r="E462" t="n">
-        <v>10.59409199071533</v>
+        <v>10.59409296566996</v>
       </c>
       <c r="F462" t="n">
         <v>7006882</v>
@@ -9712,16 +9712,16 @@
         <v>44907</v>
       </c>
       <c r="B465" t="n">
-        <v>9.506422996520996</v>
+        <v>9.506421089172363</v>
       </c>
       <c r="C465" t="n">
-        <v>10.02884768824383</v>
+        <v>10.02884567607701</v>
       </c>
       <c r="D465" t="n">
-        <v>9.420779293526801</v>
+        <v>9.420777403361539</v>
       </c>
       <c r="E465" t="n">
-        <v>9.574937629083003</v>
+        <v>9.57493570798774</v>
       </c>
       <c r="F465" t="n">
         <v>6343387</v>
@@ -9752,16 +9752,16 @@
         <v>44909</v>
       </c>
       <c r="B467" t="n">
-        <v>9.489291191101074</v>
+        <v>9.489292144775391</v>
       </c>
       <c r="C467" t="n">
-        <v>9.652014441405267</v>
+        <v>9.652015411433279</v>
       </c>
       <c r="D467" t="n">
-        <v>9.138153976058327</v>
+        <v>9.138154894443332</v>
       </c>
       <c r="E467" t="n">
-        <v>9.318004644179831</v>
+        <v>9.31800558063984</v>
       </c>
       <c r="F467" t="n">
         <v>7822016</v>
@@ -9812,16 +9812,16 @@
         <v>44914</v>
       </c>
       <c r="B470" t="n">
-        <v>9.951766014099121</v>
+        <v>9.951767921447754</v>
       </c>
       <c r="C470" t="n">
-        <v>10.03740969907196</v>
+        <v>10.03741162283501</v>
       </c>
       <c r="D470" t="n">
-        <v>9.68627166264147</v>
+        <v>9.686273519105638</v>
       </c>
       <c r="E470" t="n">
-        <v>9.840429141176106</v>
+        <v>9.840431027185991</v>
       </c>
       <c r="F470" t="n">
         <v>3753211</v>
@@ -9832,16 +9832,16 @@
         <v>44915</v>
       </c>
       <c r="B471" t="n">
-        <v>10.33716297149658</v>
+        <v>10.33716201782227</v>
       </c>
       <c r="C471" t="n">
-        <v>10.65404457284976</v>
+        <v>10.65404358994094</v>
       </c>
       <c r="D471" t="n">
-        <v>9.857560569696266</v>
+        <v>9.857559660268567</v>
       </c>
       <c r="E471" t="n">
-        <v>9.926074373941555</v>
+        <v>9.926073458192986</v>
       </c>
       <c r="F471" t="n">
         <v>4483944</v>
@@ -9852,16 +9852,16 @@
         <v>44916</v>
       </c>
       <c r="B472" t="n">
-        <v>10.42280673980713</v>
+        <v>10.42280578613281</v>
       </c>
       <c r="C472" t="n">
-        <v>10.58553001509685</v>
+        <v>10.58552904653355</v>
       </c>
       <c r="D472" t="n">
-        <v>10.08879771587911</v>
+        <v>10.08879679276622</v>
       </c>
       <c r="E472" t="n">
-        <v>10.36285705761706</v>
+        <v>10.36285610942807</v>
       </c>
       <c r="F472" t="n">
         <v>3195923</v>
@@ -9892,16 +9892,16 @@
         <v>44918</v>
       </c>
       <c r="B474" t="n">
-        <v>10.83389377593994</v>
+        <v>10.83389472961426</v>
       </c>
       <c r="C474" t="n">
-        <v>11.26211138404356</v>
+        <v>11.26211237541256</v>
       </c>
       <c r="D474" t="n">
-        <v>10.55983447377029</v>
+        <v>10.55983540332002</v>
       </c>
       <c r="E474" t="n">
-        <v>10.57696271632784</v>
+        <v>10.57696364738531</v>
       </c>
       <c r="F474" t="n">
         <v>4288288</v>
@@ -9912,16 +9912,16 @@
         <v>44921</v>
       </c>
       <c r="B475" t="n">
-        <v>10.66260719299316</v>
+        <v>10.66260814666748</v>
       </c>
       <c r="C475" t="n">
-        <v>10.8767159963531</v>
+        <v>10.87671696917752</v>
       </c>
       <c r="D475" t="n">
-        <v>10.57696268214933</v>
+        <v>10.57696362816352</v>
       </c>
       <c r="E475" t="n">
-        <v>10.82532961968009</v>
+        <v>10.82533058790846</v>
       </c>
       <c r="F475" t="n">
         <v>1667319</v>
@@ -9932,16 +9932,16 @@
         <v>44922</v>
       </c>
       <c r="B476" t="n">
-        <v>10.5229606628418</v>
+        <v>10.52296161651611</v>
       </c>
       <c r="C476" t="n">
-        <v>10.75038956949791</v>
+        <v>10.75039054378364</v>
       </c>
       <c r="D476" t="n">
-        <v>10.37425679063793</v>
+        <v>10.37425773083552</v>
       </c>
       <c r="E476" t="n">
-        <v>10.73289464951121</v>
+        <v>10.73289562221141</v>
       </c>
       <c r="F476" t="n">
         <v>2935250</v>
@@ -9952,16 +9952,16 @@
         <v>44923</v>
       </c>
       <c r="B477" t="n">
-        <v>10.96907234191895</v>
+        <v>10.96907138824463</v>
       </c>
       <c r="C477" t="n">
-        <v>11.03030330833085</v>
+        <v>11.03030234933299</v>
       </c>
       <c r="D477" t="n">
-        <v>10.43548940917989</v>
+        <v>10.4354885018964</v>
       </c>
       <c r="E477" t="n">
-        <v>10.56669754009717</v>
+        <v>10.56669662140617</v>
       </c>
       <c r="F477" t="n">
         <v>2605824</v>
@@ -10052,16 +10052,16 @@
         <v>44931</v>
       </c>
       <c r="B482" t="n">
-        <v>10.05935573577881</v>
+        <v>10.05935668945312</v>
       </c>
       <c r="C482" t="n">
-        <v>10.33926773935673</v>
+        <v>10.33926871956802</v>
       </c>
       <c r="D482" t="n">
-        <v>9.779443732200887</v>
+        <v>9.779444659338226</v>
       </c>
       <c r="E482" t="n">
-        <v>9.796937811326897</v>
+        <v>9.796938740122757</v>
       </c>
       <c r="F482" t="n">
         <v>3524036</v>
@@ -10112,16 +10112,16 @@
         <v>44936</v>
       </c>
       <c r="B485" t="n">
-        <v>11.11777496337891</v>
+        <v>11.11777591705322</v>
       </c>
       <c r="C485" t="n">
-        <v>11.29271996007671</v>
+        <v>11.29272092875768</v>
       </c>
       <c r="D485" t="n">
-        <v>10.48797129087642</v>
+        <v>10.48797219052666</v>
       </c>
       <c r="E485" t="n">
-        <v>10.55794928955554</v>
+        <v>10.55795019520844</v>
       </c>
       <c r="F485" t="n">
         <v>3522522</v>
@@ -10192,16 +10192,16 @@
         <v>44942</v>
       </c>
       <c r="B489" t="n">
-        <v>10.80287265777588</v>
+        <v>10.8028736114502</v>
       </c>
       <c r="C489" t="n">
-        <v>11.30146738941439</v>
+        <v>11.3014683871045</v>
       </c>
       <c r="D489" t="n">
-        <v>10.69790649832965</v>
+        <v>10.69790744273759</v>
       </c>
       <c r="E489" t="n">
-        <v>11.25773134927926</v>
+        <v>11.25773234310836</v>
       </c>
       <c r="F489" t="n">
         <v>2251058</v>
@@ -10212,16 +10212,16 @@
         <v>44943</v>
       </c>
       <c r="B490" t="n">
-        <v>11.00406074523926</v>
+        <v>11.00405979156494</v>
       </c>
       <c r="C490" t="n">
-        <v>11.10902859176186</v>
+        <v>11.10902762899043</v>
       </c>
       <c r="D490" t="n">
-        <v>10.7503906953303</v>
+        <v>10.75038976364046</v>
       </c>
       <c r="E490" t="n">
-        <v>10.8466098176506</v>
+        <v>10.84660887762188</v>
       </c>
       <c r="F490" t="n">
         <v>2581089</v>
@@ -10252,16 +10252,16 @@
         <v>44945</v>
       </c>
       <c r="B492" t="n">
-        <v>11.93127059936523</v>
+        <v>11.93127155303955</v>
       </c>
       <c r="C492" t="n">
-        <v>12.30740255052876</v>
+        <v>12.30740353426755</v>
       </c>
       <c r="D492" t="n">
-        <v>11.33645677201188</v>
+        <v>11.33645767814233</v>
       </c>
       <c r="E492" t="n">
-        <v>11.49390684698556</v>
+        <v>11.49390776570111</v>
       </c>
       <c r="F492" t="n">
         <v>5394988</v>
@@ -10332,16 +10332,16 @@
         <v>44951</v>
       </c>
       <c r="B496" t="n">
-        <v>12.24617195129395</v>
+        <v>12.24617099761963</v>
       </c>
       <c r="C496" t="n">
-        <v>12.44735975492869</v>
+        <v>12.44735878558682</v>
       </c>
       <c r="D496" t="n">
-        <v>11.96625995005467</v>
+        <v>11.96625901817858</v>
       </c>
       <c r="E496" t="n">
-        <v>12.10621595067431</v>
+        <v>12.10621500789911</v>
       </c>
       <c r="F496" t="n">
         <v>2519909</v>
@@ -10372,16 +10372,16 @@
         <v>44953</v>
       </c>
       <c r="B498" t="n">
-        <v>12.43861293792725</v>
+        <v>12.43861389160156</v>
       </c>
       <c r="C498" t="n">
-        <v>12.67478890374615</v>
+        <v>12.67478987552819</v>
       </c>
       <c r="D498" t="n">
-        <v>12.25492005218186</v>
+        <v>12.25492099177236</v>
       </c>
       <c r="E498" t="n">
-        <v>12.41237013459764</v>
+        <v>12.41237108625991</v>
       </c>
       <c r="F498" t="n">
         <v>1981500</v>
@@ -10412,16 +10412,16 @@
         <v>44957</v>
       </c>
       <c r="B500" t="n">
-        <v>12.78850173950195</v>
+        <v>12.78850364685059</v>
       </c>
       <c r="C500" t="n">
-        <v>13.03342556406084</v>
+        <v>13.03342750793878</v>
       </c>
       <c r="D500" t="n">
-        <v>12.48234695880334</v>
+        <v>12.48234882049034</v>
       </c>
       <c r="E500" t="n">
-        <v>12.49109483981984</v>
+        <v>12.49109670281154</v>
       </c>
       <c r="F500" t="n">
         <v>4284855</v>
@@ -10472,16 +10472,16 @@
         <v>44960</v>
       </c>
       <c r="B503" t="n">
-        <v>12.57856750488281</v>
+        <v>12.57856845855713</v>
       </c>
       <c r="C503" t="n">
-        <v>12.90221722066339</v>
+        <v>12.90221819887599</v>
       </c>
       <c r="D503" t="n">
-        <v>12.42986446913531</v>
+        <v>12.42986541153535</v>
       </c>
       <c r="E503" t="n">
-        <v>12.81474430174445</v>
+        <v>12.81474527332507</v>
       </c>
       <c r="F503" t="n">
         <v>2892746</v>
@@ -10492,16 +10492,16 @@
         <v>44963</v>
       </c>
       <c r="B504" t="n">
-        <v>12.75351333618164</v>
+        <v>12.75351428985596</v>
       </c>
       <c r="C504" t="n">
-        <v>12.83223921582688</v>
+        <v>12.83224017538812</v>
       </c>
       <c r="D504" t="n">
-        <v>12.33364450465924</v>
+        <v>12.33364542693687</v>
       </c>
       <c r="E504" t="n">
-        <v>12.53483146009399</v>
+        <v>12.53483239741585</v>
       </c>
       <c r="F504" t="n">
         <v>1342942</v>
@@ -10512,16 +10512,16 @@
         <v>44964</v>
       </c>
       <c r="B505" t="n">
-        <v>12.76226043701172</v>
+        <v>12.76226139068604</v>
       </c>
       <c r="C505" t="n">
-        <v>12.93720543340915</v>
+        <v>12.93720640015643</v>
       </c>
       <c r="D505" t="n">
-        <v>12.52608448132639</v>
+        <v>12.52608541735219</v>
       </c>
       <c r="E505" t="n">
-        <v>12.8584803955791</v>
+        <v>12.85848135644357</v>
       </c>
       <c r="F505" t="n">
         <v>2203204</v>
@@ -10532,16 +10532,16 @@
         <v>44965</v>
       </c>
       <c r="B506" t="n">
-        <v>12.77100849151611</v>
+        <v>12.7710075378418</v>
       </c>
       <c r="C506" t="n">
-        <v>12.98094334607703</v>
+        <v>12.98094237672584</v>
       </c>
       <c r="D506" t="n">
-        <v>12.56982151911688</v>
+        <v>12.56982058046619</v>
       </c>
       <c r="E506" t="n">
-        <v>12.8584814177661</v>
+        <v>12.85848045755975</v>
       </c>
       <c r="F506" t="n">
         <v>1737889</v>
@@ -10592,16 +10592,16 @@
         <v>44970</v>
       </c>
       <c r="B509" t="n">
-        <v>12.52608489990234</v>
+        <v>12.52608585357666</v>
       </c>
       <c r="C509" t="n">
-        <v>12.77100790304318</v>
+        <v>12.77100887536473</v>
       </c>
       <c r="D509" t="n">
-        <v>12.35113905546367</v>
+        <v>12.35113999581847</v>
       </c>
       <c r="E509" t="n">
-        <v>12.38612889810758</v>
+        <v>12.38612984112634</v>
       </c>
       <c r="F509" t="n">
         <v>2916169</v>
@@ -10632,16 +10632,16 @@
         <v>44972</v>
       </c>
       <c r="B511" t="n">
-        <v>12.75351333618164</v>
+        <v>12.75351428985596</v>
       </c>
       <c r="C511" t="n">
-        <v>12.94595241019235</v>
+        <v>12.94595337825676</v>
       </c>
       <c r="D511" t="n">
-        <v>11.91377567313685</v>
+        <v>11.91377656401778</v>
       </c>
       <c r="E511" t="n">
-        <v>12.24617158578515</v>
+        <v>12.24617250152178</v>
       </c>
       <c r="F511" t="n">
         <v>3838217</v>
@@ -10652,16 +10652,16 @@
         <v>44973</v>
       </c>
       <c r="B512" t="n">
-        <v>12.86722755432129</v>
+        <v>12.86722850799561</v>
       </c>
       <c r="C512" t="n">
-        <v>12.98968947403414</v>
+        <v>12.98969043678491</v>
       </c>
       <c r="D512" t="n">
-        <v>12.6135575177385</v>
+        <v>12.61355845261168</v>
       </c>
       <c r="E512" t="n">
-        <v>12.64854567514766</v>
+        <v>12.64854661261404</v>
       </c>
       <c r="F512" t="n">
         <v>1907195</v>
@@ -10672,16 +10672,16 @@
         <v>44974</v>
       </c>
       <c r="B513" t="n">
-        <v>12.78850173950195</v>
+        <v>12.78850364685059</v>
       </c>
       <c r="C513" t="n">
-        <v>12.85847973446302</v>
+        <v>12.85848165224856</v>
       </c>
       <c r="D513" t="n">
-        <v>12.63105082974197</v>
+        <v>12.6310527136075</v>
       </c>
       <c r="E513" t="n">
-        <v>12.84098565682033</v>
+        <v>12.84098757199671</v>
       </c>
       <c r="F513" t="n">
         <v>1180399</v>
@@ -10692,16 +10692,16 @@
         <v>44979</v>
       </c>
       <c r="B514" t="n">
-        <v>12.63979911804199</v>
+        <v>12.63979816436768</v>
       </c>
       <c r="C514" t="n">
-        <v>12.70977711992058</v>
+        <v>12.70977616096641</v>
       </c>
       <c r="D514" t="n">
-        <v>12.33364514927437</v>
+        <v>12.33364421869941</v>
       </c>
       <c r="E514" t="n">
-        <v>12.70103008023456</v>
+        <v>12.70102912194036</v>
       </c>
       <c r="F514" t="n">
         <v>1228758</v>
@@ -10752,16 +10752,16 @@
         <v>44984</v>
       </c>
       <c r="B517" t="n">
-        <v>11.64261054992676</v>
+        <v>11.64261150360107</v>
       </c>
       <c r="C517" t="n">
-        <v>11.87003946193115</v>
+        <v>11.87004043423472</v>
       </c>
       <c r="D517" t="n">
-        <v>11.51140159462404</v>
+        <v>11.51140253755071</v>
       </c>
       <c r="E517" t="n">
-        <v>11.77381950522948</v>
+        <v>11.77382046965144</v>
       </c>
       <c r="F517" t="n">
         <v>3613283</v>
@@ -10792,16 +10792,16 @@
         <v>44986</v>
       </c>
       <c r="B519" t="n">
-        <v>11.74757766723633</v>
+        <v>11.74757862091064</v>
       </c>
       <c r="C519" t="n">
-        <v>11.78256666619927</v>
+        <v>11.78256762271401</v>
       </c>
       <c r="D519" t="n">
-        <v>11.3976876776069</v>
+        <v>11.39768860287697</v>
       </c>
       <c r="E519" t="n">
-        <v>11.6163687105765</v>
+        <v>11.61636965359921</v>
       </c>
       <c r="F519" t="n">
         <v>4662539</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.26366710662842</v>
+        <v>12.26366806030273</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738199094953</v>
+        <v>12.37738295346679</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87004021572346</v>
+        <v>11.87004113878769</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12371026114126</v>
+        <v>12.12371120393195</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10932,16 +10932,16 @@
         <v>44995</v>
       </c>
       <c r="B526" t="n">
-        <v>12.5960636138916</v>
+        <v>12.59606266021729</v>
       </c>
       <c r="C526" t="n">
-        <v>12.78850354835147</v>
+        <v>12.78850258010713</v>
       </c>
       <c r="D526" t="n">
-        <v>12.31615159445562</v>
+        <v>12.31615066197402</v>
       </c>
       <c r="E526" t="n">
-        <v>12.64854669643821</v>
+        <v>12.6485457387903</v>
       </c>
       <c r="F526" t="n">
         <v>1798565</v>
@@ -11012,16 +11012,16 @@
         <v>45001</v>
       </c>
       <c r="B530" t="n">
-        <v>12.44735908508301</v>
+        <v>12.44736099243164</v>
       </c>
       <c r="C530" t="n">
-        <v>12.63105111546223</v>
+        <v>12.63105305095858</v>
       </c>
       <c r="D530" t="n">
-        <v>12.28990817176142</v>
+        <v>12.28991005498334</v>
       </c>
       <c r="E530" t="n">
-        <v>12.35113828709104</v>
+        <v>12.35114017969545</v>
       </c>
       <c r="F530" t="n">
         <v>3275478</v>
@@ -11052,16 +11052,16 @@
         <v>45005</v>
       </c>
       <c r="B532" t="n">
-        <v>11.36269855499268</v>
+        <v>11.36269760131836</v>
       </c>
       <c r="C532" t="n">
-        <v>11.90502849431124</v>
+        <v>11.90502749511903</v>
       </c>
       <c r="D532" t="n">
-        <v>11.17025862742956</v>
+        <v>11.17025768990678</v>
       </c>
       <c r="E532" t="n">
-        <v>11.73008348843351</v>
+        <v>11.73008250392448</v>
       </c>
       <c r="F532" t="n">
         <v>5506849</v>
@@ -11152,16 +11152,16 @@
         <v>45012</v>
       </c>
       <c r="B537" t="n">
-        <v>11.36269855499268</v>
+        <v>11.36269760131836</v>
       </c>
       <c r="C537" t="n">
-        <v>11.52889652112532</v>
+        <v>11.52889555350197</v>
       </c>
       <c r="D537" t="n">
-        <v>11.12652258650894</v>
+        <v>11.12652165265694</v>
       </c>
       <c r="E537" t="n">
-        <v>11.18775354911495</v>
+        <v>11.18775261012382</v>
       </c>
       <c r="F537" t="n">
         <v>2536971</v>
@@ -11312,16 +11312,16 @@
         <v>45022</v>
       </c>
       <c r="B545" t="n">
-        <v>10.80287265777588</v>
+        <v>10.8028736114502</v>
       </c>
       <c r="C545" t="n">
-        <v>11.10902830750268</v>
+        <v>11.10902928820433</v>
       </c>
       <c r="D545" t="n">
-        <v>10.4617305340876</v>
+        <v>10.46173145764599</v>
       </c>
       <c r="E545" t="n">
-        <v>10.71540057750562</v>
+        <v>10.71540152345793</v>
       </c>
       <c r="F545" t="n">
         <v>8557394</v>
@@ -11352,16 +11352,16 @@
         <v>45027</v>
       </c>
       <c r="B547" t="n">
-        <v>11.85254573822021</v>
+        <v>11.85254669189453</v>
       </c>
       <c r="C547" t="n">
-        <v>11.87878685630945</v>
+        <v>11.87878781209517</v>
       </c>
       <c r="D547" t="n">
-        <v>10.96907118108362</v>
+        <v>10.9690720636722</v>
       </c>
       <c r="E547" t="n">
-        <v>10.96907118108362</v>
+        <v>10.9690720636722</v>
       </c>
       <c r="F547" t="n">
         <v>9432295</v>
@@ -11392,16 +11392,16 @@
         <v>45029</v>
       </c>
       <c r="B549" t="n">
-        <v>12.4561071395874</v>
+        <v>12.45610618591309</v>
       </c>
       <c r="C549" t="n">
-        <v>12.64854622467444</v>
+        <v>12.64854525626645</v>
       </c>
       <c r="D549" t="n">
-        <v>11.97500732138171</v>
+        <v>11.97500640454174</v>
       </c>
       <c r="E549" t="n">
-        <v>12.09746924641502</v>
+        <v>12.09746832019902</v>
       </c>
       <c r="F549" t="n">
         <v>4483641</v>
@@ -11412,16 +11412,16 @@
         <v>45030</v>
       </c>
       <c r="B550" t="n">
-        <v>12.52608489990234</v>
+        <v>12.52608585357666</v>
       </c>
       <c r="C550" t="n">
-        <v>12.72727186303112</v>
+        <v>12.72727283202282</v>
       </c>
       <c r="D550" t="n">
-        <v>12.22867797499086</v>
+        <v>12.22867890602208</v>
       </c>
       <c r="E550" t="n">
-        <v>12.42111705636105</v>
+        <v>12.42111800204363</v>
       </c>
       <c r="F550" t="n">
         <v>2806225</v>
@@ -11472,16 +11472,16 @@
         <v>45035</v>
       </c>
       <c r="B553" t="n">
-        <v>11.31021499633789</v>
+        <v>11.31021404266357</v>
       </c>
       <c r="C553" t="n">
-        <v>11.56388673687087</v>
+        <v>11.56388576180702</v>
       </c>
       <c r="D553" t="n">
-        <v>11.11777590477318</v>
+        <v>11.11777496732528</v>
       </c>
       <c r="E553" t="n">
-        <v>11.43267692549338</v>
+        <v>11.4326759614931</v>
       </c>
       <c r="F553" t="n">
         <v>6310878</v>
@@ -11552,16 +11552,16 @@
         <v>45042</v>
       </c>
       <c r="B557" t="n">
-        <v>11.25773239135742</v>
+        <v>11.25773143768311</v>
       </c>
       <c r="C557" t="n">
-        <v>11.49390837746124</v>
+        <v>11.49390740377979</v>
       </c>
       <c r="D557" t="n">
-        <v>11.21399634717384</v>
+        <v>11.21399539720453</v>
       </c>
       <c r="E557" t="n">
-        <v>11.24898450876447</v>
+        <v>11.24898355583121</v>
       </c>
       <c r="F557" t="n">
         <v>2213905</v>
@@ -11652,16 +11652,16 @@
         <v>45050</v>
       </c>
       <c r="B562" t="n">
-        <v>9.42955207824707</v>
+        <v>9.429553031921387</v>
       </c>
       <c r="C562" t="n">
-        <v>10.19056382556656</v>
+        <v>10.19056485620714</v>
       </c>
       <c r="D562" t="n">
-        <v>9.324584243696673</v>
+        <v>9.324585186754883</v>
       </c>
       <c r="E562" t="n">
-        <v>10.14682778930066</v>
+        <v>10.14682881551792</v>
       </c>
       <c r="F562" t="n">
         <v>16781627</v>
@@ -11692,16 +11692,16 @@
         <v>45054</v>
       </c>
       <c r="B564" t="n">
-        <v>9.960692405700684</v>
+        <v>9.960693359375</v>
       </c>
       <c r="C564" t="n">
-        <v>10.13590215170305</v>
+        <v>10.13590312215261</v>
       </c>
       <c r="D564" t="n">
-        <v>9.759200143460824</v>
+        <v>9.75920107784351</v>
       </c>
       <c r="E564" t="n">
-        <v>10.10962047893527</v>
+        <v>10.10962144686852</v>
       </c>
       <c r="F564" t="n">
         <v>5548545</v>
@@ -11732,16 +11732,16 @@
         <v>45056</v>
       </c>
       <c r="B566" t="n">
-        <v>10.00449466705322</v>
+        <v>10.00449562072754</v>
       </c>
       <c r="C566" t="n">
-        <v>10.33739447891732</v>
+        <v>10.33739546432518</v>
       </c>
       <c r="D566" t="n">
-        <v>9.969453558243071</v>
+        <v>9.969454508577106</v>
       </c>
       <c r="E566" t="n">
-        <v>10.24979001995237</v>
+        <v>10.24979099700936</v>
       </c>
       <c r="F566" t="n">
         <v>5572472</v>
@@ -11792,16 +11792,16 @@
         <v>45061</v>
       </c>
       <c r="B569" t="n">
-        <v>10.15342426300049</v>
+        <v>10.15342330932617</v>
       </c>
       <c r="C569" t="n">
-        <v>10.2147478943812</v>
+        <v>10.21474693494698</v>
       </c>
       <c r="D569" t="n">
-        <v>9.98697476788276</v>
+        <v>9.986973829842441</v>
       </c>
       <c r="E569" t="n">
-        <v>10.16218538424762</v>
+        <v>10.1621844297504</v>
       </c>
       <c r="F569" t="n">
         <v>4041445</v>
@@ -11812,16 +11812,16 @@
         <v>45062</v>
       </c>
       <c r="B570" t="n">
-        <v>9.951932907104492</v>
+        <v>9.951933860778809</v>
       </c>
       <c r="C570" t="n">
-        <v>10.35491493267188</v>
+        <v>10.35491592496318</v>
       </c>
       <c r="D570" t="n">
-        <v>9.864327605521281</v>
+        <v>9.864328550800552</v>
       </c>
       <c r="E570" t="n">
-        <v>10.17970517297524</v>
+        <v>10.17970614847653</v>
       </c>
       <c r="F570" t="n">
         <v>2372207</v>
@@ -11832,16 +11832,16 @@
         <v>45063</v>
       </c>
       <c r="B571" t="n">
-        <v>10.07458019256592</v>
+        <v>10.0745792388916</v>
       </c>
       <c r="C571" t="n">
-        <v>10.14466410253436</v>
+        <v>10.1446631422258</v>
       </c>
       <c r="D571" t="n">
-        <v>9.934412372629026</v>
+        <v>9.934411432223198</v>
       </c>
       <c r="E571" t="n">
-        <v>9.986974883370435</v>
+        <v>9.986973937988964</v>
       </c>
       <c r="F571" t="n">
         <v>5003473</v>
@@ -11872,16 +11872,16 @@
         <v>45065</v>
       </c>
       <c r="B573" t="n">
-        <v>11.44121837615967</v>
+        <v>11.44121742248535</v>
       </c>
       <c r="C573" t="n">
-        <v>12.00189047040555</v>
+        <v>12.00188946999683</v>
       </c>
       <c r="D573" t="n">
-        <v>10.51260450838727</v>
+        <v>10.51260363211687</v>
       </c>
       <c r="E573" t="n">
-        <v>10.60897093395166</v>
+        <v>10.60897004964872</v>
       </c>
       <c r="F573" t="n">
         <v>14298668</v>
@@ -11932,16 +11932,16 @@
         <v>45070</v>
       </c>
       <c r="B576" t="n">
-        <v>10.93310832977295</v>
+        <v>10.93310928344727</v>
       </c>
       <c r="C576" t="n">
-        <v>11.28352953369865</v>
+        <v>11.28353051793955</v>
       </c>
       <c r="D576" t="n">
-        <v>10.92434805271574</v>
+        <v>10.92434900562591</v>
       </c>
       <c r="E576" t="n">
-        <v>11.0820372570944</v>
+        <v>11.0820382237595</v>
       </c>
       <c r="F576" t="n">
         <v>2685985</v>
@@ -11972,16 +11972,16 @@
         <v>45072</v>
       </c>
       <c r="B578" t="n">
-        <v>11.6777515411377</v>
+        <v>11.67775058746338</v>
       </c>
       <c r="C578" t="n">
-        <v>11.90552465401795</v>
+        <v>11.90552368174234</v>
       </c>
       <c r="D578" t="n">
-        <v>11.47626010348781</v>
+        <v>11.47625916626848</v>
       </c>
       <c r="E578" t="n">
-        <v>11.54634400845561</v>
+        <v>11.54634306551281</v>
       </c>
       <c r="F578" t="n">
         <v>3617321</v>
@@ -12012,16 +12012,16 @@
         <v>45076</v>
       </c>
       <c r="B580" t="n">
-        <v>11.21344566345215</v>
+        <v>11.21344470977783</v>
       </c>
       <c r="C580" t="n">
-        <v>11.82668113132278</v>
+        <v>11.82668012549439</v>
       </c>
       <c r="D580" t="n">
-        <v>11.12584119909194</v>
+        <v>11.12584025286816</v>
       </c>
       <c r="E580" t="n">
-        <v>11.66899191461664</v>
+        <v>11.6689909221993</v>
       </c>
       <c r="F580" t="n">
         <v>4905847</v>
@@ -12032,16 +12032,16 @@
         <v>45077</v>
       </c>
       <c r="B581" t="n">
-        <v>11.2747688293457</v>
+        <v>11.27476787567139</v>
       </c>
       <c r="C581" t="n">
-        <v>11.46749999253707</v>
+        <v>11.46749902256062</v>
       </c>
       <c r="D581" t="n">
-        <v>11.07327738877377</v>
+        <v>11.07327645214257</v>
       </c>
       <c r="E581" t="n">
-        <v>11.20468492336154</v>
+        <v>11.20468397561525</v>
       </c>
       <c r="F581" t="n">
         <v>3703640</v>
@@ -12112,16 +12112,16 @@
         <v>45083</v>
       </c>
       <c r="B585" t="n">
-        <v>12.53628063201904</v>
+        <v>12.53628158569336</v>
       </c>
       <c r="C585" t="n">
-        <v>12.73777205594852</v>
+        <v>12.73777302495092</v>
       </c>
       <c r="D585" t="n">
-        <v>11.88800329000613</v>
+        <v>11.88800419436395</v>
       </c>
       <c r="E585" t="n">
-        <v>11.91428411997714</v>
+        <v>11.91428502633423</v>
       </c>
       <c r="F585" t="n">
         <v>8194955</v>
@@ -12152,16 +12152,16 @@
         <v>45086</v>
       </c>
       <c r="B587" t="n">
-        <v>12.7903356552124</v>
+        <v>12.79033470153809</v>
       </c>
       <c r="C587" t="n">
-        <v>13.0181087720978</v>
+        <v>13.01810780144024</v>
       </c>
       <c r="D587" t="n">
-        <v>12.60636561230446</v>
+        <v>12.60636467234733</v>
       </c>
       <c r="E587" t="n">
-        <v>12.69397091678955</v>
+        <v>12.69396997030039</v>
       </c>
       <c r="F587" t="n">
         <v>3362705</v>
@@ -12192,16 +12192,16 @@
         <v>45090</v>
       </c>
       <c r="B589" t="n">
-        <v>12.52752113342285</v>
+        <v>12.52752208709717</v>
       </c>
       <c r="C589" t="n">
-        <v>13.04439014033381</v>
+        <v>13.04439113335547</v>
       </c>
       <c r="D589" t="n">
-        <v>12.29974717843629</v>
+        <v>12.29974811477101</v>
       </c>
       <c r="E589" t="n">
-        <v>12.86042010176204</v>
+        <v>12.86042108077874</v>
       </c>
       <c r="F589" t="n">
         <v>6116837</v>
@@ -12252,16 +12252,16 @@
         <v>45093</v>
       </c>
       <c r="B592" t="n">
-        <v>11.92304515838623</v>
+        <v>11.92304420471191</v>
       </c>
       <c r="C592" t="n">
-        <v>12.76405454487264</v>
+        <v>12.76405352392952</v>
       </c>
       <c r="D592" t="n">
-        <v>11.66023093759705</v>
+        <v>11.66023000494414</v>
       </c>
       <c r="E592" t="n">
-        <v>12.76405454487264</v>
+        <v>12.76405352392952</v>
       </c>
       <c r="F592" t="n">
         <v>19648730</v>
@@ -12392,16 +12392,16 @@
         <v>45104</v>
       </c>
       <c r="B599" t="n">
-        <v>10.52486228942871</v>
+        <v>10.52486133575439</v>
       </c>
       <c r="C599" t="n">
-        <v>10.94055037724765</v>
+        <v>10.94054938590718</v>
       </c>
       <c r="D599" t="n">
-        <v>10.41872932213938</v>
+        <v>10.41872837808194</v>
       </c>
       <c r="E599" t="n">
-        <v>10.58677381961654</v>
+        <v>10.58677286033232</v>
       </c>
       <c r="F599" t="n">
         <v>17154900</v>
@@ -12452,16 +12452,16 @@
         <v>45107</v>
       </c>
       <c r="B602" t="n">
-        <v>10.71059513092041</v>
+        <v>10.71059417724609</v>
       </c>
       <c r="C602" t="n">
-        <v>11.12628321632794</v>
+        <v>11.12628222564065</v>
       </c>
       <c r="D602" t="n">
-        <v>10.56023988393194</v>
+        <v>10.56023894364529</v>
       </c>
       <c r="E602" t="n">
-        <v>10.83441734710793</v>
+        <v>10.83441638240845</v>
       </c>
       <c r="F602" t="n">
         <v>11622700</v>
@@ -12472,16 +12472,16 @@
         <v>45110</v>
       </c>
       <c r="B603" t="n">
-        <v>10.79019355773926</v>
+        <v>10.79019451141357</v>
       </c>
       <c r="C603" t="n">
-        <v>11.00245946140029</v>
+        <v>11.0024604338354</v>
       </c>
       <c r="D603" t="n">
-        <v>10.66637220233851</v>
+        <v>10.66637314506908</v>
       </c>
       <c r="E603" t="n">
-        <v>10.8344158318694</v>
+        <v>10.83441678945224</v>
       </c>
       <c r="F603" t="n">
         <v>4753300</v>
@@ -12552,16 +12552,16 @@
         <v>45114</v>
       </c>
       <c r="B607" t="n">
-        <v>10.52486228942871</v>
+        <v>10.52486133575439</v>
       </c>
       <c r="C607" t="n">
-        <v>10.71943981786074</v>
+        <v>10.71943884655545</v>
       </c>
       <c r="D607" t="n">
-        <v>10.40104091599275</v>
+        <v>10.40103997353808</v>
       </c>
       <c r="E607" t="n">
-        <v>10.52486228942871</v>
+        <v>10.52486133575439</v>
       </c>
       <c r="F607" t="n">
         <v>9448200</v>
@@ -12612,16 +12612,16 @@
         <v>45119</v>
       </c>
       <c r="B610" t="n">
-        <v>10.40988540649414</v>
+        <v>10.40988445281982</v>
       </c>
       <c r="C610" t="n">
-        <v>10.772506584255</v>
+        <v>10.7725055973601</v>
       </c>
       <c r="D610" t="n">
-        <v>10.39219615710589</v>
+        <v>10.39219520505212</v>
       </c>
       <c r="E610" t="n">
-        <v>10.61330671364005</v>
+        <v>10.61330574132983</v>
       </c>
       <c r="F610" t="n">
         <v>7787100</v>
@@ -12712,16 +12712,16 @@
         <v>45126</v>
       </c>
       <c r="B615" t="n">
-        <v>9.905753135681152</v>
+        <v>9.905752182006836</v>
       </c>
       <c r="C615" t="n">
-        <v>10.24184129543884</v>
+        <v>10.2418403094077</v>
       </c>
       <c r="D615" t="n">
-        <v>9.720020227485323</v>
+        <v>9.720019291692406</v>
       </c>
       <c r="E615" t="n">
-        <v>10.24184129543884</v>
+        <v>10.2418403094077</v>
       </c>
       <c r="F615" t="n">
         <v>11108100</v>
@@ -12772,16 +12772,16 @@
         <v>45131</v>
       </c>
       <c r="B618" t="n">
-        <v>10.52486228942871</v>
+        <v>10.52486133575439</v>
       </c>
       <c r="C618" t="n">
-        <v>10.64868450633452</v>
+        <v>10.64868354144048</v>
       </c>
       <c r="D618" t="n">
-        <v>10.40988554080099</v>
+        <v>10.40988459754489</v>
       </c>
       <c r="E618" t="n">
-        <v>10.62215147537965</v>
+        <v>10.62215051288981</v>
       </c>
       <c r="F618" t="n">
         <v>4297000</v>
@@ -12852,16 +12852,16 @@
         <v>45135</v>
       </c>
       <c r="B622" t="n">
-        <v>10.35681819915771</v>
+        <v>10.3568172454834</v>
       </c>
       <c r="C622" t="n">
-        <v>10.3921958534306</v>
+        <v>10.39219489649865</v>
       </c>
       <c r="D622" t="n">
-        <v>10.18877455222896</v>
+        <v>10.1887736140284</v>
       </c>
       <c r="E622" t="n">
-        <v>10.34797357472204</v>
+        <v>10.34797262186215</v>
       </c>
       <c r="F622" t="n">
         <v>4029200</v>
@@ -12912,16 +12912,16 @@
         <v>45140</v>
       </c>
       <c r="B625" t="n">
-        <v>10.40988540649414</v>
+        <v>10.40988445281982</v>
       </c>
       <c r="C625" t="n">
-        <v>10.83441727017422</v>
+        <v>10.83441627760753</v>
       </c>
       <c r="D625" t="n">
-        <v>10.25068553587919</v>
+        <v>10.25068459678955</v>
       </c>
       <c r="E625" t="n">
-        <v>10.66637361833498</v>
+        <v>10.66637264116317</v>
       </c>
       <c r="F625" t="n">
         <v>9104400</v>
@@ -12952,16 +12952,16 @@
         <v>45142</v>
       </c>
       <c r="B627" t="n">
-        <v>10.71943950653076</v>
+        <v>10.71943855285645</v>
       </c>
       <c r="C627" t="n">
-        <v>11.21472751629927</v>
+        <v>11.21472651856076</v>
       </c>
       <c r="D627" t="n">
-        <v>10.59561729322118</v>
+        <v>10.59561635056293</v>
       </c>
       <c r="E627" t="n">
-        <v>10.70175110089786</v>
+        <v>10.70175014879723</v>
       </c>
       <c r="F627" t="n">
         <v>16706200</v>
@@ -13032,16 +13032,16 @@
         <v>45148</v>
       </c>
       <c r="B631" t="n">
-        <v>10.63099575042725</v>
+        <v>10.63099479675293</v>
       </c>
       <c r="C631" t="n">
-        <v>10.86095008358703</v>
+        <v>10.86094910928421</v>
       </c>
       <c r="D631" t="n">
-        <v>10.52486194315988</v>
+        <v>10.5248609990065</v>
       </c>
       <c r="E631" t="n">
-        <v>10.66637340502643</v>
+        <v>10.66637244817849</v>
       </c>
       <c r="F631" t="n">
         <v>4975000</v>
@@ -13052,16 +13052,16 @@
         <v>45149</v>
       </c>
       <c r="B632" t="n">
-        <v>10.44526290893555</v>
+        <v>10.44526195526123</v>
       </c>
       <c r="C632" t="n">
-        <v>10.78135020769543</v>
+        <v>10.78134922333564</v>
       </c>
       <c r="D632" t="n">
-        <v>10.39219600501725</v>
+        <v>10.39219505618805</v>
       </c>
       <c r="E632" t="n">
-        <v>10.56908427896187</v>
+        <v>10.56908331398241</v>
       </c>
       <c r="F632" t="n">
         <v>4348800</v>
@@ -13072,16 +13072,16 @@
         <v>45152</v>
       </c>
       <c r="B633" t="n">
-        <v>10.44526290893555</v>
+        <v>10.44526195526123</v>
       </c>
       <c r="C633" t="n">
-        <v>10.6044619337508</v>
+        <v>10.60446096554128</v>
       </c>
       <c r="D633" t="n">
-        <v>10.27721841608578</v>
+        <v>10.27721747775428</v>
       </c>
       <c r="E633" t="n">
-        <v>10.42757365980617</v>
+        <v>10.42757270774692</v>
       </c>
       <c r="F633" t="n">
         <v>3064200</v>
@@ -13132,16 +13132,16 @@
         <v>45155</v>
       </c>
       <c r="B636" t="n">
-        <v>10.13570785522461</v>
+        <v>10.13570690155029</v>
       </c>
       <c r="C636" t="n">
-        <v>10.51601827899524</v>
+        <v>10.51601728953731</v>
       </c>
       <c r="D636" t="n">
-        <v>10.10917482484777</v>
+        <v>10.10917387366996</v>
       </c>
       <c r="E636" t="n">
-        <v>10.43641834439489</v>
+        <v>10.43641736242656</v>
       </c>
       <c r="F636" t="n">
         <v>6587600</v>
@@ -13192,16 +13192,16 @@
         <v>45160</v>
       </c>
       <c r="B639" t="n">
-        <v>10.63099575042725</v>
+        <v>10.63099479675293</v>
       </c>
       <c r="C639" t="n">
-        <v>10.70175105962561</v>
+        <v>10.70175009960405</v>
       </c>
       <c r="D639" t="n">
-        <v>10.18877464620255</v>
+        <v>10.18877373219854</v>
       </c>
       <c r="E639" t="n">
-        <v>10.24184070636641</v>
+        <v>10.24183978760201</v>
       </c>
       <c r="F639" t="n">
         <v>5680500</v>
@@ -13332,16 +13332,16 @@
         <v>45169</v>
       </c>
       <c r="B646" t="n">
-        <v>10.35681819915771</v>
+        <v>10.3568172454834</v>
       </c>
       <c r="C646" t="n">
-        <v>10.71059474188658</v>
+        <v>10.71059375563589</v>
       </c>
       <c r="D646" t="n">
-        <v>10.27721826617627</v>
+        <v>10.27721731983166</v>
       </c>
       <c r="E646" t="n">
-        <v>10.59561715463224</v>
+        <v>10.59561617896889</v>
       </c>
       <c r="F646" t="n">
         <v>8716900</v>
@@ -13392,16 +13392,16 @@
         <v>45174</v>
       </c>
       <c r="B649" t="n">
-        <v>10.21530818939209</v>
+        <v>10.21530723571777</v>
       </c>
       <c r="C649" t="n">
-        <v>10.7371292535431</v>
+        <v>10.73712825115294</v>
       </c>
       <c r="D649" t="n">
-        <v>10.21530818939209</v>
+        <v>10.21530723571777</v>
       </c>
       <c r="E649" t="n">
-        <v>10.7371292535431</v>
+        <v>10.73712825115294</v>
       </c>
       <c r="F649" t="n">
         <v>8659200</v>
@@ -13532,16 +13532,16 @@
         <v>45184</v>
       </c>
       <c r="B656" t="n">
-        <v>9.375087738037109</v>
+        <v>9.375086784362793</v>
       </c>
       <c r="C656" t="n">
-        <v>10.00304173917788</v>
+        <v>10.00304072162537</v>
       </c>
       <c r="D656" t="n">
-        <v>9.375087738037109</v>
+        <v>9.375086784362793</v>
       </c>
       <c r="E656" t="n">
-        <v>9.923441805537948</v>
+        <v>9.923440796082692</v>
       </c>
       <c r="F656" t="n">
         <v>14904000</v>
@@ -13552,16 +13552,16 @@
         <v>45187</v>
       </c>
       <c r="B657" t="n">
-        <v>8.844422340393066</v>
+        <v>8.84442138671875</v>
       </c>
       <c r="C657" t="n">
-        <v>9.322021113035499</v>
+        <v>9.322020107862773</v>
       </c>
       <c r="D657" t="n">
-        <v>8.773667029147509</v>
+        <v>8.773666083102581</v>
       </c>
       <c r="E657" t="n">
-        <v>9.322021113035499</v>
+        <v>9.322020107862773</v>
       </c>
       <c r="F657" t="n">
         <v>19156300</v>
@@ -13572,16 +13572,16 @@
         <v>45188</v>
       </c>
       <c r="B658" t="n">
-        <v>8.800199508666992</v>
+        <v>8.800198554992676</v>
       </c>
       <c r="C658" t="n">
-        <v>8.950554746511546</v>
+        <v>8.950553776543289</v>
       </c>
       <c r="D658" t="n">
-        <v>8.667533519260521</v>
+        <v>8.667532579963169</v>
       </c>
       <c r="E658" t="n">
-        <v>8.844421786292413</v>
+        <v>8.844420827825743</v>
       </c>
       <c r="F658" t="n">
         <v>8872800</v>
@@ -13612,16 +13612,16 @@
         <v>45190</v>
       </c>
       <c r="B660" t="n">
-        <v>8.932867050170898</v>
+        <v>8.932866096496582</v>
       </c>
       <c r="C660" t="n">
-        <v>8.985933112755202</v>
+        <v>8.985932153415543</v>
       </c>
       <c r="D660" t="n">
-        <v>8.738289519265452</v>
+        <v>8.738288586364265</v>
       </c>
       <c r="E660" t="n">
-        <v>8.853267112824586</v>
+        <v>8.853266167648371</v>
       </c>
       <c r="F660" t="n">
         <v>7093000</v>
@@ -13632,16 +13632,16 @@
         <v>45191</v>
       </c>
       <c r="B661" t="n">
-        <v>8.579089164733887</v>
+        <v>8.57908821105957</v>
       </c>
       <c r="C661" t="n">
-        <v>9.003621859012968</v>
+        <v>9.003620858146471</v>
       </c>
       <c r="D661" t="n">
-        <v>8.428733923371484</v>
+        <v>8.428732986411056</v>
       </c>
       <c r="E661" t="n">
-        <v>8.994777234586989</v>
+        <v>8.994776234703684</v>
       </c>
       <c r="F661" t="n">
         <v>16137800</v>
@@ -13732,16 +13732,16 @@
         <v>45198</v>
       </c>
       <c r="B666" t="n">
-        <v>8.623311996459961</v>
+        <v>8.623311042785645</v>
       </c>
       <c r="C666" t="n">
-        <v>8.755977997479093</v>
+        <v>8.7559770291329</v>
       </c>
       <c r="D666" t="n">
-        <v>8.587934339956869</v>
+        <v>8.587933390195058</v>
       </c>
       <c r="E666" t="n">
-        <v>8.702911934459385</v>
+        <v>8.702910971981906</v>
       </c>
       <c r="F666" t="n">
         <v>6662100</v>
@@ -13772,16 +13772,16 @@
         <v>45202</v>
       </c>
       <c r="B668" t="n">
-        <v>7.659268856048584</v>
+        <v>7.659268379211426</v>
       </c>
       <c r="C668" t="n">
-        <v>7.933446292673103</v>
+        <v>7.933445798766693</v>
       </c>
       <c r="D668" t="n">
-        <v>7.570825147453722</v>
+        <v>7.570824676122735</v>
       </c>
       <c r="E668" t="n">
-        <v>7.880379392740378</v>
+        <v>7.880378902137712</v>
       </c>
       <c r="F668" t="n">
         <v>18608300</v>
@@ -13792,16 +13792,16 @@
         <v>45203</v>
       </c>
       <c r="B669" t="n">
-        <v>7.738869190216064</v>
+        <v>7.738868236541748</v>
       </c>
       <c r="C669" t="n">
-        <v>7.853846776544223</v>
+        <v>7.853845808701018</v>
       </c>
       <c r="D669" t="n">
-        <v>7.632736228252335</v>
+        <v>7.632735287656968</v>
       </c>
       <c r="E669" t="n">
-        <v>7.756558438944921</v>
+        <v>7.756557483090727</v>
       </c>
       <c r="F669" t="n">
         <v>14186500</v>
@@ -13812,16 +13812,16 @@
         <v>45204</v>
       </c>
       <c r="B670" t="n">
-        <v>7.685802459716797</v>
+        <v>7.68580150604248</v>
       </c>
       <c r="C670" t="n">
-        <v>7.800780048621283</v>
+        <v>7.800779080680249</v>
       </c>
       <c r="D670" t="n">
-        <v>7.579669495374922</v>
+        <v>7.579668554869859</v>
       </c>
       <c r="E670" t="n">
-        <v>7.738869363622646</v>
+        <v>7.73886840336365</v>
       </c>
       <c r="F670" t="n">
         <v>5277500</v>
@@ -13832,16 +13832,16 @@
         <v>45205</v>
       </c>
       <c r="B671" t="n">
-        <v>7.473536491394043</v>
+        <v>7.473536014556885</v>
       </c>
       <c r="C671" t="n">
-        <v>7.6062033287201</v>
+        <v>7.606202843418344</v>
       </c>
       <c r="D671" t="n">
-        <v>7.38509277664649</v>
+        <v>7.385092305452343</v>
       </c>
       <c r="E671" t="n">
-        <v>7.561981049611414</v>
+        <v>7.561980567131191</v>
       </c>
       <c r="F671" t="n">
         <v>8202400</v>
@@ -13872,16 +13872,16 @@
         <v>45209</v>
       </c>
       <c r="B673" t="n">
-        <v>8.101490020751953</v>
+        <v>8.101489067077637</v>
       </c>
       <c r="C673" t="n">
-        <v>8.18993457381352</v>
+        <v>8.189933609727872</v>
       </c>
       <c r="D673" t="n">
-        <v>7.906912510098369</v>
+        <v>7.906911579328923</v>
       </c>
       <c r="E673" t="n">
-        <v>7.951134786629153</v>
+        <v>7.95113385065404</v>
       </c>
       <c r="F673" t="n">
         <v>9907700</v>
@@ -13912,16 +13912,16 @@
         <v>45212</v>
       </c>
       <c r="B675" t="n">
-        <v>7.561980724334717</v>
+        <v>7.561980247497559</v>
       </c>
       <c r="C675" t="n">
-        <v>7.933446503317459</v>
+        <v>7.933446003056718</v>
       </c>
       <c r="D675" t="n">
-        <v>7.500069198857738</v>
+        <v>7.500068725924546</v>
       </c>
       <c r="E675" t="n">
-        <v>7.898068850246236</v>
+        <v>7.898068352216309</v>
       </c>
       <c r="F675" t="n">
         <v>6681200</v>
@@ -13932,16 +13932,16 @@
         <v>45215</v>
       </c>
       <c r="B676" t="n">
-        <v>7.561980724334717</v>
+        <v>7.561980247497559</v>
       </c>
       <c r="C676" t="n">
-        <v>7.721179741420333</v>
+        <v>7.721179254544534</v>
       </c>
       <c r="D676" t="n">
-        <v>7.473536169921766</v>
+        <v>7.473535698661672</v>
       </c>
       <c r="E676" t="n">
-        <v>7.623891406341913</v>
+        <v>7.623890925600842</v>
       </c>
       <c r="F676" t="n">
         <v>6364500</v>
@@ -13952,16 +13952,16 @@
         <v>45216</v>
       </c>
       <c r="B677" t="n">
-        <v>7.641581058502197</v>
+        <v>7.641580104827881</v>
       </c>
       <c r="C677" t="n">
-        <v>7.668114088840552</v>
+        <v>7.668113131854896</v>
       </c>
       <c r="D677" t="n">
-        <v>7.447003534591332</v>
+        <v>7.447002605200417</v>
       </c>
       <c r="E677" t="n">
-        <v>7.544291874811851</v>
+        <v>7.544290933279289</v>
       </c>
       <c r="F677" t="n">
         <v>6592700</v>
@@ -14232,16 +14232,16 @@
         <v>45237</v>
       </c>
       <c r="B691" t="n">
-        <v>8.357978820800781</v>
+        <v>8.357977867126465</v>
       </c>
       <c r="C691" t="n">
-        <v>8.37566807008851</v>
+        <v>8.375667114395791</v>
       </c>
       <c r="D691" t="n">
-        <v>7.845002400034246</v>
+        <v>7.845001504892315</v>
       </c>
       <c r="E691" t="n">
-        <v>7.871535430496009</v>
+        <v>7.871534532326568</v>
       </c>
       <c r="F691" t="n">
         <v>8029000</v>
@@ -14252,16 +14252,16 @@
         <v>45238</v>
       </c>
       <c r="B692" t="n">
-        <v>8.101490020751953</v>
+        <v>8.101489067077637</v>
       </c>
       <c r="C692" t="n">
-        <v>8.649844056712263</v>
+        <v>8.649843038487949</v>
       </c>
       <c r="D692" t="n">
-        <v>8.013046311160156</v>
+        <v>8.013045367897073</v>
       </c>
       <c r="E692" t="n">
-        <v>8.357978212466772</v>
+        <v>8.357977228599713</v>
       </c>
       <c r="F692" t="n">
         <v>19964500</v>
@@ -14272,16 +14272,16 @@
         <v>45239</v>
       </c>
       <c r="B693" t="n">
-        <v>7.959980010986328</v>
+        <v>7.959979057312012</v>
       </c>
       <c r="C693" t="n">
-        <v>8.189935191514248</v>
+        <v>8.189934210289316</v>
       </c>
       <c r="D693" t="n">
-        <v>7.77424711032452</v>
+        <v>7.774246178902609</v>
       </c>
       <c r="E693" t="n">
-        <v>8.189935191514248</v>
+        <v>8.189934210289316</v>
       </c>
       <c r="F693" t="n">
         <v>11094800</v>
@@ -14392,16 +14392,16 @@
         <v>45250</v>
       </c>
       <c r="B699" t="n">
-        <v>8.932867050170898</v>
+        <v>8.932866096496582</v>
       </c>
       <c r="C699" t="n">
-        <v>8.932867050170898</v>
+        <v>8.932866096496582</v>
       </c>
       <c r="D699" t="n">
-        <v>8.61446730078565</v>
+        <v>8.614466381103741</v>
       </c>
       <c r="E699" t="n">
-        <v>8.676378831760479</v>
+        <v>8.676377905468886</v>
       </c>
       <c r="F699" t="n">
         <v>4921500</v>
@@ -14412,16 +14412,16 @@
         <v>45251</v>
       </c>
       <c r="B700" t="n">
-        <v>8.623311996459961</v>
+        <v>8.623311042785645</v>
       </c>
       <c r="C700" t="n">
-        <v>8.941710904987794</v>
+        <v>8.941709916100921</v>
       </c>
       <c r="D700" t="n">
-        <v>8.614467371466722</v>
+        <v>8.614466418770554</v>
       </c>
       <c r="E700" t="n">
-        <v>8.932867123464419</v>
+        <v>8.932866135555601</v>
       </c>
       <c r="F700" t="n">
         <v>8608600</v>
@@ -14432,16 +14432,16 @@
         <v>45252</v>
       </c>
       <c r="B701" t="n">
-        <v>8.596778869628906</v>
+        <v>8.59677791595459</v>
       </c>
       <c r="C701" t="n">
-        <v>9.03015536785397</v>
+        <v>9.030154366103503</v>
       </c>
       <c r="D701" t="n">
-        <v>8.587934244733736</v>
+        <v>8.587933292040589</v>
       </c>
       <c r="E701" t="n">
-        <v>8.649844932060216</v>
+        <v>8.649843972499074</v>
       </c>
       <c r="F701" t="n">
         <v>12126100</v>
@@ -14492,16 +14492,16 @@
         <v>45257</v>
       </c>
       <c r="B704" t="n">
-        <v>8.092646598815918</v>
+        <v>8.092645645141602</v>
       </c>
       <c r="C704" t="n">
-        <v>8.446424020141739</v>
+        <v>8.446423024776681</v>
       </c>
       <c r="D704" t="n">
-        <v>8.074958191658068</v>
+        <v>8.074957240068235</v>
       </c>
       <c r="E704" t="n">
-        <v>8.411046362356148</v>
+        <v>8.411045371160153</v>
       </c>
       <c r="F704" t="n">
         <v>5901700</v>
@@ -14712,16 +14712,16 @@
         <v>45272</v>
       </c>
       <c r="B715" t="n">
-        <v>8.083802223205566</v>
+        <v>8.08380126953125</v>
       </c>
       <c r="C715" t="n">
-        <v>8.357978840037788</v>
+        <v>8.3579778540179</v>
       </c>
       <c r="D715" t="n">
-        <v>8.066112973877122</v>
+        <v>8.066112022289667</v>
       </c>
       <c r="E715" t="n">
-        <v>8.18109056410251</v>
+        <v>8.181089598950749</v>
       </c>
       <c r="F715" t="n">
         <v>4001400</v>
@@ -14732,16 +14732,16 @@
         <v>45273</v>
       </c>
       <c r="B716" t="n">
-        <v>8.658689498901367</v>
+        <v>8.658688545227051</v>
       </c>
       <c r="C716" t="n">
-        <v>8.711756404446733</v>
+        <v>8.71175544492759</v>
       </c>
       <c r="D716" t="n">
-        <v>8.101490786289347</v>
+        <v>8.101489893985299</v>
       </c>
       <c r="E716" t="n">
-        <v>8.110335411125217</v>
+        <v>8.110334517847015</v>
       </c>
       <c r="F716" t="n">
         <v>4810200</v>
@@ -14752,16 +14752,16 @@
         <v>45274</v>
       </c>
       <c r="B717" t="n">
-        <v>8.623311996459961</v>
+        <v>8.623311042785645</v>
       </c>
       <c r="C717" t="n">
-        <v>8.932867123464419</v>
+        <v>8.932866135555601</v>
       </c>
       <c r="D717" t="n">
-        <v>8.596778964950108</v>
+        <v>8.596778014210148</v>
       </c>
       <c r="E717" t="n">
-        <v>8.685222684472906</v>
+        <v>8.685221723951727</v>
       </c>
       <c r="F717" t="n">
         <v>9075200</v>
@@ -14772,16 +14772,16 @@
         <v>45275</v>
       </c>
       <c r="B718" t="n">
-        <v>8.791356086730957</v>
+        <v>8.791355133056641</v>
       </c>
       <c r="C718" t="n">
-        <v>8.791356086730957</v>
+        <v>8.791355133056641</v>
       </c>
       <c r="D718" t="n">
-        <v>8.534867853590605</v>
+        <v>8.534866927739781</v>
       </c>
       <c r="E718" t="n">
-        <v>8.720600770241887</v>
+        <v>8.720599824243012</v>
       </c>
       <c r="F718" t="n">
         <v>7122400</v>
@@ -14792,16 +14792,16 @@
         <v>45278</v>
       </c>
       <c r="B719" t="n">
-        <v>8.835577011108398</v>
+        <v>8.835576057434082</v>
       </c>
       <c r="C719" t="n">
-        <v>8.977087622316056</v>
+        <v>8.977086653367691</v>
       </c>
       <c r="D719" t="n">
-        <v>8.800199358306484</v>
+        <v>8.800198408450679</v>
       </c>
       <c r="E719" t="n">
-        <v>8.809043982374407</v>
+        <v>8.809043031563952</v>
       </c>
       <c r="F719" t="n">
         <v>3928300</v>
@@ -14812,16 +14812,16 @@
         <v>45279</v>
       </c>
       <c r="B720" t="n">
-        <v>8.879799842834473</v>
+        <v>8.879798889160156</v>
       </c>
       <c r="C720" t="n">
-        <v>8.941710528238881</v>
+        <v>8.941709567915471</v>
       </c>
       <c r="D720" t="n">
-        <v>8.817889157430063</v>
+        <v>8.817888210404842</v>
       </c>
       <c r="E720" t="n">
-        <v>8.932866747088129</v>
+        <v>8.932865787714524</v>
       </c>
       <c r="F720" t="n">
         <v>3267000</v>
@@ -27792,13 +27792,13 @@
         <v>46231</v>
       </c>
       <c r="B1369" t="n">
-        <v>3.33</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="C1369" t="n">
-        <v>3.37</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="D1369" t="n">
-        <v>3.19</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="E1369" t="n">
         <v>3.25</v>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1369"/>
+  <dimension ref="A1:F1370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44232</v>
       </c>
       <c r="B5" t="n">
-        <v>6.823330879211426</v>
+        <v>6.823331356048584</v>
       </c>
       <c r="C5" t="n">
-        <v>6.909409509382922</v>
+        <v>6.909409992235542</v>
       </c>
       <c r="D5" t="n">
-        <v>6.699460779521623</v>
+        <v>6.699461247702325</v>
       </c>
       <c r="E5" t="n">
-        <v>6.873718152244995</v>
+        <v>6.873718632603384</v>
       </c>
       <c r="F5" t="n">
         <v>4402737</v>
@@ -532,16 +532,16 @@
         <v>44235</v>
       </c>
       <c r="B6" t="n">
-        <v>7.211735725402832</v>
+        <v>7.21173620223999</v>
       </c>
       <c r="C6" t="n">
-        <v>7.619035766065515</v>
+        <v>7.619036269833193</v>
       </c>
       <c r="D6" t="n">
-        <v>6.827529615229921</v>
+        <v>6.82753006666352</v>
       </c>
       <c r="E6" t="n">
-        <v>6.85482295876889</v>
+        <v>6.854823412007115</v>
       </c>
       <c r="F6" t="n">
         <v>3162478</v>
@@ -552,16 +552,16 @@
         <v>44236</v>
       </c>
       <c r="B7" t="n">
-        <v>7.119358062744141</v>
+        <v>7.119358539581299</v>
       </c>
       <c r="C7" t="n">
-        <v>7.367097444187393</v>
+        <v>7.367097937617529</v>
       </c>
       <c r="D7" t="n">
-        <v>6.953498708270694</v>
+        <v>6.953499173999</v>
       </c>
       <c r="E7" t="n">
-        <v>7.266322088824129</v>
+        <v>7.266322575504579</v>
       </c>
       <c r="F7" t="n">
         <v>1374461</v>
@@ -572,16 +572,16 @@
         <v>44237</v>
       </c>
       <c r="B8" t="n">
-        <v>6.928305625915527</v>
+        <v>6.928305149078369</v>
       </c>
       <c r="C8" t="n">
-        <v>7.180243643314912</v>
+        <v>7.180243149138246</v>
       </c>
       <c r="D8" t="n">
-        <v>6.749849225834657</v>
+        <v>6.74984876127967</v>
       </c>
       <c r="E8" t="n">
-        <v>7.180243643314912</v>
+        <v>7.180243149138246</v>
       </c>
       <c r="F8" t="n">
         <v>3511567</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.222232818603516</v>
+        <v>7.222233295440674</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379694161326558</v>
+        <v>7.379694648559866</v>
       </c>
       <c r="D12" t="n">
-        <v>7.138253489937527</v>
+        <v>7.138253961230074</v>
       </c>
       <c r="E12" t="n">
-        <v>7.28731681861452</v>
+        <v>7.287317299748752</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -672,16 +672,16 @@
         <v>44246</v>
       </c>
       <c r="B13" t="n">
-        <v>7.453176498413086</v>
+        <v>7.453176021575928</v>
       </c>
       <c r="C13" t="n">
-        <v>7.595941931589037</v>
+        <v>7.595941445618074</v>
       </c>
       <c r="D13" t="n">
-        <v>7.142453212420159</v>
+        <v>7.142452755462365</v>
       </c>
       <c r="E13" t="n">
-        <v>7.159248429445686</v>
+        <v>7.159247971413373</v>
       </c>
       <c r="F13" t="n">
         <v>1995604</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.306213855743408</v>
+        <v>7.30621337890625</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724011249786042</v>
+        <v>7.724010745681502</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050075613595256</v>
+        <v>7.050075153474859</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054275027030914</v>
+        <v>7.054274566636445</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.306213855743408</v>
+        <v>7.30621337890625</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480471247944865</v>
+        <v>7.480470759734867</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243228336770691</v>
+        <v>7.243227864044258</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308312344769346</v>
+        <v>7.308311867795231</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400690302893193</v>
+        <v>7.400689808525235</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945101447895325</v>
+        <v>6.945100983960817</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360800341244324</v>
+        <v>7.360799849541025</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -792,16 +792,16 @@
         <v>44256</v>
       </c>
       <c r="B19" t="n">
-        <v>7.001787662506104</v>
+        <v>7.001787185668945</v>
       </c>
       <c r="C19" t="n">
-        <v>7.390192411161723</v>
+        <v>7.390191907873347</v>
       </c>
       <c r="D19" t="n">
-        <v>7.001787662506104</v>
+        <v>7.001787185668945</v>
       </c>
       <c r="E19" t="n">
-        <v>7.24952707872963</v>
+        <v>7.249526585020872</v>
       </c>
       <c r="F19" t="n">
         <v>1349729</v>
@@ -812,16 +812,16 @@
         <v>44257</v>
       </c>
       <c r="B20" t="n">
-        <v>7.178143978118896</v>
+        <v>7.178143501281738</v>
       </c>
       <c r="C20" t="n">
-        <v>7.178143978118896</v>
+        <v>7.178143501281738</v>
       </c>
       <c r="D20" t="n">
-        <v>6.718356531153318</v>
+        <v>6.718356084859394</v>
       </c>
       <c r="E20" t="n">
-        <v>7.003886594429932</v>
+        <v>7.003886129168523</v>
       </c>
       <c r="F20" t="n">
         <v>1173360</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233502264944</v>
+        <v>7.222233019817944</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966096890895136</v>
+        <v>6.966096425558127</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117259534444174</v>
+        <v>7.117259059009463</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -872,16 +872,16 @@
         <v>44260</v>
       </c>
       <c r="B23" t="n">
-        <v>7.016483306884766</v>
+        <v>7.016484260559082</v>
       </c>
       <c r="C23" t="n">
-        <v>7.176044757483478</v>
+        <v>7.176045732845249</v>
       </c>
       <c r="D23" t="n">
-        <v>7.01438319458637</v>
+        <v>7.014384147975241</v>
       </c>
       <c r="E23" t="n">
-        <v>7.117258660812305</v>
+        <v>7.11725962818392</v>
       </c>
       <c r="F23" t="n">
         <v>1309995</v>
@@ -912,16 +912,16 @@
         <v>44264</v>
       </c>
       <c r="B25" t="n">
-        <v>6.424428462982178</v>
+        <v>6.42442798614502</v>
       </c>
       <c r="C25" t="n">
-        <v>6.819131905728831</v>
+        <v>6.819131399595795</v>
       </c>
       <c r="D25" t="n">
-        <v>6.36774247274314</v>
+        <v>6.367742000113356</v>
       </c>
       <c r="E25" t="n">
-        <v>6.75404790081054</v>
+        <v>6.754047399508202</v>
       </c>
       <c r="F25" t="n">
         <v>2514170</v>
@@ -952,16 +952,16 @@
         <v>44266</v>
       </c>
       <c r="B27" t="n">
-        <v>6.67006778717041</v>
+        <v>6.670068264007568</v>
       </c>
       <c r="C27" t="n">
-        <v>6.67006778717041</v>
+        <v>6.670068264007568</v>
       </c>
       <c r="D27" t="n">
-        <v>6.21447937230484</v>
+        <v>6.214479816572392</v>
       </c>
       <c r="E27" t="n">
-        <v>6.287961793693228</v>
+        <v>6.287962243213972</v>
       </c>
       <c r="F27" t="n">
         <v>2230763</v>
@@ -1012,16 +1012,16 @@
         <v>44271</v>
       </c>
       <c r="B30" t="n">
-        <v>7.390192031860352</v>
+        <v>7.390191078186035</v>
       </c>
       <c r="C30" t="n">
-        <v>7.42588420308686</v>
+        <v>7.425883244806614</v>
       </c>
       <c r="D30" t="n">
-        <v>6.970294545149255</v>
+        <v>6.970293645661006</v>
       </c>
       <c r="E30" t="n">
-        <v>6.970294545149255</v>
+        <v>6.970293645661006</v>
       </c>
       <c r="F30" t="n">
         <v>4282725</v>
@@ -1032,16 +1032,16 @@
         <v>44272</v>
       </c>
       <c r="B31" t="n">
-        <v>7.558150768280029</v>
+        <v>7.558151245117188</v>
       </c>
       <c r="C31" t="n">
-        <v>7.642130094981778</v>
+        <v>7.642130577117119</v>
       </c>
       <c r="D31" t="n">
-        <v>7.285217347653489</v>
+        <v>7.285217807271516</v>
       </c>
       <c r="E31" t="n">
-        <v>7.390191303082056</v>
+        <v>7.390191769322798</v>
       </c>
       <c r="F31" t="n">
         <v>5070506</v>
@@ -1052,16 +1052,16 @@
         <v>44273</v>
       </c>
       <c r="B32" t="n">
-        <v>7.589643955230713</v>
+        <v>7.589643001556396</v>
       </c>
       <c r="C32" t="n">
-        <v>7.898268782349795</v>
+        <v>7.898267789895324</v>
       </c>
       <c r="D32" t="n">
-        <v>7.45947593692015</v>
+        <v>7.459474999602055</v>
       </c>
       <c r="E32" t="n">
-        <v>7.600141271314518</v>
+        <v>7.600140316321165</v>
       </c>
       <c r="F32" t="n">
         <v>3661176</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.516162395477295</v>
+        <v>7.516161441802979</v>
       </c>
       <c r="C33" t="n">
-        <v>7.778597720834538</v>
+        <v>7.778596733861603</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430082134541178</v>
+        <v>7.430081191788996</v>
       </c>
       <c r="E33" t="n">
-        <v>7.600140920268824</v>
+        <v>7.600139955939049</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1092,16 +1092,16 @@
         <v>44277</v>
       </c>
       <c r="B34" t="n">
-        <v>7.558150768280029</v>
+        <v>7.558151245117188</v>
       </c>
       <c r="C34" t="n">
-        <v>7.807989447871488</v>
+        <v>7.807989940470752</v>
       </c>
       <c r="D34" t="n">
-        <v>7.201238020951741</v>
+        <v>7.201238475271585</v>
       </c>
       <c r="E34" t="n">
-        <v>7.51406139851813</v>
+        <v>7.514061872573729</v>
       </c>
       <c r="F34" t="n">
         <v>5377429</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.516162395477295</v>
+        <v>7.516161441802979</v>
       </c>
       <c r="C35" t="n">
-        <v>7.55815165787306</v>
+        <v>7.558150698871014</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436381660412942</v>
+        <v>7.436380716861456</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511962982160976</v>
+        <v>7.511962029019494</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159248828887939</v>
+        <v>7.159247875213623</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656827760317221</v>
+        <v>7.656826740361056</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159248828887939</v>
+        <v>7.159247875213623</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392292321128197</v>
+        <v>7.392291336410457</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.705113410949707</v>
+        <v>7.70511531829834</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789093543231029</v>
+        <v>7.789095471368375</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033278847054452</v>
+        <v>7.033280588094989</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159247421887605</v>
+        <v>7.159249194110809</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.518261432647705</v>
+        <v>7.518260955810547</v>
       </c>
       <c r="C38" t="n">
-        <v>7.789095604385824</v>
+        <v>7.789095110371317</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455276722666873</v>
+        <v>7.455276249824448</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721912292577096</v>
+        <v>7.721911802823614</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1192,16 +1192,16 @@
         <v>44284</v>
       </c>
       <c r="B39" t="n">
-        <v>7.232729911804199</v>
+        <v>7.232730388641357</v>
       </c>
       <c r="C39" t="n">
-        <v>7.663124668362338</v>
+        <v>7.663125173574427</v>
       </c>
       <c r="D39" t="n">
-        <v>7.232729911804199</v>
+        <v>7.232730388641357</v>
       </c>
       <c r="E39" t="n">
-        <v>7.568648027979529</v>
+        <v>7.568648526962992</v>
       </c>
       <c r="F39" t="n">
         <v>3953908</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379694859893382</v>
+        <v>7.379694366927925</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257924862390593</v>
+        <v>7.257924377559402</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1292,16 +1292,16 @@
         <v>44292</v>
       </c>
       <c r="B44" t="n">
-        <v>7.211735725402832</v>
+        <v>7.21173620223999</v>
       </c>
       <c r="C44" t="n">
-        <v>7.379694387891328</v>
+        <v>7.379694875833847</v>
       </c>
       <c r="D44" t="n">
-        <v>7.190741095540401</v>
+        <v>7.190741570989402</v>
       </c>
       <c r="E44" t="n">
-        <v>7.369197072960112</v>
+        <v>7.369197560208552</v>
       </c>
       <c r="F44" t="n">
         <v>1319726</v>
@@ -1332,16 +1332,16 @@
         <v>44294</v>
       </c>
       <c r="B46" t="n">
-        <v>7.589643955230713</v>
+        <v>7.589643001556396</v>
       </c>
       <c r="C46" t="n">
-        <v>7.789095396206844</v>
+        <v>7.78909441747052</v>
       </c>
       <c r="D46" t="n">
-        <v>7.215935930750956</v>
+        <v>7.215935024034804</v>
       </c>
       <c r="E46" t="n">
-        <v>7.243228465492086</v>
+        <v>7.2432275553465</v>
       </c>
       <c r="F46" t="n">
         <v>2111967</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652627944946289</v>
+        <v>7.652626991271973</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873073997390144</v>
+        <v>7.873073016243731</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474171152894864</v>
+        <v>7.474170221459922</v>
       </c>
       <c r="E47" t="n">
-        <v>7.595941956339789</v>
+        <v>7.595941009729709</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1392,16 +1392,16 @@
         <v>44299</v>
       </c>
       <c r="B49" t="n">
-        <v>7.726109504699707</v>
+        <v>7.726110458374023</v>
       </c>
       <c r="C49" t="n">
-        <v>7.898267572775072</v>
+        <v>7.898268547699764</v>
       </c>
       <c r="D49" t="n">
-        <v>7.64213017709561</v>
+        <v>7.642131120403916</v>
       </c>
       <c r="E49" t="n">
-        <v>7.786994902815057</v>
+        <v>7.786995864004779</v>
       </c>
       <c r="F49" t="n">
         <v>1044023</v>
@@ -1412,16 +1412,16 @@
         <v>44300</v>
       </c>
       <c r="B50" t="n">
-        <v>7.877273082733154</v>
+        <v>7.877272129058838</v>
       </c>
       <c r="C50" t="n">
-        <v>7.877273082733154</v>
+        <v>7.877272129058838</v>
       </c>
       <c r="D50" t="n">
-        <v>7.518260212908098</v>
+        <v>7.518259302698232</v>
       </c>
       <c r="E50" t="n">
-        <v>7.78699504013355</v>
+        <v>7.786994097388884</v>
       </c>
       <c r="F50" t="n">
         <v>2026013</v>
@@ -1432,16 +1432,16 @@
         <v>44301</v>
       </c>
       <c r="B51" t="n">
-        <v>8.112415313720703</v>
+        <v>8.112414360046387</v>
       </c>
       <c r="C51" t="n">
-        <v>8.185898142401868</v>
+        <v>8.185897180089103</v>
       </c>
       <c r="D51" t="n">
-        <v>7.891969263060783</v>
+        <v>7.891968335301526</v>
       </c>
       <c r="E51" t="n">
-        <v>7.894068563704509</v>
+        <v>7.894067635698465</v>
       </c>
       <c r="F51" t="n">
         <v>2034122</v>
@@ -1452,16 +1452,16 @@
         <v>44302</v>
       </c>
       <c r="B52" t="n">
-        <v>8.187996864318848</v>
+        <v>8.187995910644531</v>
       </c>
       <c r="C52" t="n">
-        <v>8.25098237977971</v>
+        <v>8.25098141876933</v>
       </c>
       <c r="D52" t="n">
-        <v>8.09142091401317</v>
+        <v>8.091419971587269</v>
       </c>
       <c r="E52" t="n">
-        <v>8.112415544637091</v>
+        <v>8.1124145997659</v>
       </c>
       <c r="F52" t="n">
         <v>1067133</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208990097045898</v>
+        <v>8.208992958068848</v>
       </c>
       <c r="C53" t="n">
-        <v>8.244681450105466</v>
+        <v>8.244684323567677</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059927595564051</v>
+        <v>8.059930404635271</v>
       </c>
       <c r="E53" t="n">
-        <v>8.187995469997121</v>
+        <v>8.187998323702958</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1492,16 +1492,16 @@
         <v>44306</v>
       </c>
       <c r="B54" t="n">
-        <v>8.196395874023438</v>
+        <v>8.196394920349121</v>
       </c>
       <c r="C54" t="n">
-        <v>8.244683038461606</v>
+        <v>8.244682079168939</v>
       </c>
       <c r="D54" t="n">
-        <v>8.078823666875394</v>
+        <v>8.078822726880942</v>
       </c>
       <c r="E54" t="n">
-        <v>8.206893189570158</v>
+        <v>8.206892234674447</v>
       </c>
       <c r="F54" t="n">
         <v>282595</v>
@@ -1512,16 +1512,16 @@
         <v>44308</v>
       </c>
       <c r="B55" t="n">
-        <v>8.183797836303711</v>
+        <v>8.183796882629395</v>
       </c>
       <c r="C55" t="n">
-        <v>8.370652636858729</v>
+        <v>8.37065166140985</v>
       </c>
       <c r="D55" t="n">
-        <v>8.06412714911432</v>
+        <v>8.064126209385469</v>
       </c>
       <c r="E55" t="n">
-        <v>8.259379152045536</v>
+        <v>8.259378189563577</v>
       </c>
       <c r="F55" t="n">
         <v>608979</v>
@@ -1532,16 +1532,16 @@
         <v>44309</v>
       </c>
       <c r="B56" t="n">
-        <v>8.187996864318848</v>
+        <v>8.187995910644531</v>
       </c>
       <c r="C56" t="n">
-        <v>8.219489622049279</v>
+        <v>8.21948866470693</v>
       </c>
       <c r="D56" t="n">
-        <v>7.923461433638152</v>
+        <v>7.923460510774868</v>
       </c>
       <c r="E56" t="n">
-        <v>8.215291020642315</v>
+        <v>8.215290063788986</v>
       </c>
       <c r="F56" t="n">
         <v>1129166</v>
@@ -1572,16 +1572,16 @@
         <v>44313</v>
       </c>
       <c r="B58" t="n">
-        <v>8.11661434173584</v>
+        <v>8.116615295410156</v>
       </c>
       <c r="C58" t="n">
-        <v>8.183797641709477</v>
+        <v>8.1837986032776</v>
       </c>
       <c r="D58" t="n">
-        <v>7.940257671933487</v>
+        <v>7.9402586048865</v>
       </c>
       <c r="E58" t="n">
-        <v>7.999042957936108</v>
+        <v>7.999043897796192</v>
       </c>
       <c r="F58" t="n">
         <v>2786224</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397944450378418</v>
+        <v>8.397945404052734</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469327158830897</v>
+        <v>8.469328120611465</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116613840986611</v>
+        <v>8.116614762712898</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116613840986611</v>
+        <v>8.116614762712898</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1612,16 +1612,16 @@
         <v>44315</v>
       </c>
       <c r="B60" t="n">
-        <v>8.607894897460938</v>
+        <v>8.607893943786621</v>
       </c>
       <c r="C60" t="n">
-        <v>8.815744351658321</v>
+        <v>8.815743374956226</v>
       </c>
       <c r="D60" t="n">
-        <v>8.167002755425871</v>
+        <v>8.167001850598284</v>
       </c>
       <c r="E60" t="n">
-        <v>8.469328865260882</v>
+        <v>8.469327926938387</v>
       </c>
       <c r="F60" t="n">
         <v>3250459</v>
@@ -1632,16 +1632,16 @@
         <v>44316</v>
       </c>
       <c r="B61" t="n">
-        <v>8.733864784240723</v>
+        <v>8.733863830566406</v>
       </c>
       <c r="C61" t="n">
-        <v>8.733864784240723</v>
+        <v>8.733863830566406</v>
       </c>
       <c r="D61" t="n">
-        <v>8.580602826110796</v>
+        <v>8.580601889171566</v>
       </c>
       <c r="E61" t="n">
-        <v>8.580602826110796</v>
+        <v>8.580601889171566</v>
       </c>
       <c r="F61" t="n">
         <v>3200590</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849335670471191</v>
+        <v>8.849333763122559</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122269135355927</v>
+        <v>9.122267169180361</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641487026423638</v>
+        <v>8.641485163873828</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733864381954685</v>
+        <v>8.733862499494249</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1672,16 +1672,16 @@
         <v>44320</v>
       </c>
       <c r="B63" t="n">
-        <v>9.298624992370605</v>
+        <v>9.298625946044922</v>
       </c>
       <c r="C63" t="n">
-        <v>9.544265900402022</v>
+        <v>9.544266879269465</v>
       </c>
       <c r="D63" t="n">
-        <v>8.719166865823404</v>
+        <v>8.719167760068038</v>
       </c>
       <c r="E63" t="n">
-        <v>8.849334872165999</v>
+        <v>8.849335779760766</v>
       </c>
       <c r="F63" t="n">
         <v>2875017</v>
@@ -1712,16 +1712,16 @@
         <v>44322</v>
       </c>
       <c r="B65" t="n">
-        <v>9.764713287353516</v>
+        <v>9.764711380004883</v>
       </c>
       <c r="C65" t="n">
-        <v>9.78360780771288</v>
+        <v>9.783605896673567</v>
       </c>
       <c r="D65" t="n">
-        <v>9.537967677916114</v>
+        <v>9.537965814857868</v>
       </c>
       <c r="E65" t="n">
-        <v>9.78360780771288</v>
+        <v>9.783605896673567</v>
       </c>
       <c r="F65" t="n">
         <v>8042425</v>
@@ -1732,16 +1732,16 @@
         <v>44323</v>
       </c>
       <c r="B66" t="n">
-        <v>9.867586135864258</v>
+        <v>9.867585182189941</v>
       </c>
       <c r="C66" t="n">
-        <v>10.05234164827144</v>
+        <v>10.05234067674103</v>
       </c>
       <c r="D66" t="n">
-        <v>9.554763537058646</v>
+        <v>9.554762613617749</v>
       </c>
       <c r="E66" t="n">
-        <v>9.827696174712075</v>
+        <v>9.827695224893009</v>
       </c>
       <c r="F66" t="n">
         <v>7085572</v>
@@ -1772,16 +1772,16 @@
         <v>44327</v>
       </c>
       <c r="B68" t="n">
-        <v>9.61774730682373</v>
+        <v>9.617746353149414</v>
       </c>
       <c r="C68" t="n">
-        <v>9.645041463213841</v>
+        <v>9.645040506833098</v>
       </c>
       <c r="D68" t="n">
-        <v>8.964807960828002</v>
+        <v>8.964807071897692</v>
       </c>
       <c r="E68" t="n">
-        <v>9.294427396683329</v>
+        <v>9.294426475068693</v>
       </c>
       <c r="F68" t="n">
         <v>2188597</v>
@@ -1792,16 +1792,16 @@
         <v>44328</v>
       </c>
       <c r="B69" t="n">
-        <v>9.531667709350586</v>
+        <v>9.531668663024902</v>
       </c>
       <c r="C69" t="n">
-        <v>9.743715730787388</v>
+        <v>9.743716705677796</v>
       </c>
       <c r="D69" t="n">
-        <v>9.321718988410458</v>
+        <v>9.321719921078722</v>
       </c>
       <c r="E69" t="n">
-        <v>9.563159652184094</v>
+        <v>9.563160609009282</v>
       </c>
       <c r="F69" t="n">
         <v>1563804</v>
@@ -1812,16 +1812,16 @@
         <v>44329</v>
       </c>
       <c r="B70" t="n">
-        <v>9.655539512634277</v>
+        <v>9.655538558959961</v>
       </c>
       <c r="C70" t="n">
-        <v>9.699628889839794</v>
+        <v>9.699627931810785</v>
       </c>
       <c r="D70" t="n">
-        <v>9.489680131742498</v>
+        <v>9.489679194450057</v>
       </c>
       <c r="E70" t="n">
-        <v>9.556863442087572</v>
+        <v>9.556862498159457</v>
       </c>
       <c r="F70" t="n">
         <v>2493897</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.823494911193848</v>
+        <v>9.82349681854248</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272702204951</v>
+        <v>10.10272898361439</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334315718648831</v>
+        <v>9.334317531017494</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678631010813049</v>
+        <v>9.678632890034629</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1932,16 +1932,16 @@
         <v>44337</v>
       </c>
       <c r="B76" t="n">
-        <v>10.10692882537842</v>
+        <v>10.1069278717041</v>
       </c>
       <c r="C76" t="n">
-        <v>10.19090816499662</v>
+        <v>10.19090720339814</v>
       </c>
       <c r="D76" t="n">
-        <v>9.873886137643053</v>
+        <v>9.873885205958286</v>
       </c>
       <c r="E76" t="n">
-        <v>10.12792345733432</v>
+        <v>10.12792250167898</v>
       </c>
       <c r="F76" t="n">
         <v>1597862</v>
@@ -1952,16 +1952,16 @@
         <v>44340</v>
       </c>
       <c r="B77" t="n">
-        <v>10.18250942230225</v>
+        <v>10.18250846862793</v>
       </c>
       <c r="C77" t="n">
-        <v>10.39035886155727</v>
+        <v>10.39035788841617</v>
       </c>
       <c r="D77" t="n">
-        <v>9.951566051904743</v>
+        <v>9.951565119860142</v>
       </c>
       <c r="E77" t="n">
-        <v>10.15731537867855</v>
+        <v>10.15731442736386</v>
       </c>
       <c r="F77" t="n">
         <v>3407772</v>
@@ -1972,16 +1972,16 @@
         <v>44341</v>
       </c>
       <c r="B78" t="n">
-        <v>10.4344482421875</v>
+        <v>10.43444728851318</v>
       </c>
       <c r="C78" t="n">
-        <v>10.49323272042781</v>
+        <v>10.49323176138078</v>
       </c>
       <c r="D78" t="n">
-        <v>10.18880814322383</v>
+        <v>10.18880721200021</v>
       </c>
       <c r="E78" t="n">
-        <v>10.23499681733537</v>
+        <v>10.23499588189026</v>
       </c>
       <c r="F78" t="n">
         <v>2528360</v>
@@ -1992,16 +1992,16 @@
         <v>44342</v>
       </c>
       <c r="B79" t="n">
-        <v>10.4974308013916</v>
+        <v>10.49743175506592</v>
       </c>
       <c r="C79" t="n">
-        <v>10.51842624099203</v>
+        <v>10.51842719657374</v>
       </c>
       <c r="D79" t="n">
-        <v>10.31897484145185</v>
+        <v>10.31897577891374</v>
       </c>
       <c r="E79" t="n">
-        <v>10.42394960407066</v>
+        <v>10.42395055106932</v>
       </c>
       <c r="F79" t="n">
         <v>2052367</v>
@@ -2012,16 +2012,16 @@
         <v>44343</v>
       </c>
       <c r="B80" t="n">
-        <v>10.65489387512207</v>
+        <v>10.65489482879639</v>
       </c>
       <c r="C80" t="n">
-        <v>10.74937052028797</v>
+        <v>10.74937148241849</v>
       </c>
       <c r="D80" t="n">
-        <v>10.44284503095825</v>
+        <v>10.44284596565298</v>
       </c>
       <c r="E80" t="n">
-        <v>10.49743171745289</v>
+        <v>10.49743265703344</v>
       </c>
       <c r="F80" t="n">
         <v>6818384</v>
@@ -2092,16 +2092,16 @@
         <v>44349</v>
       </c>
       <c r="B84" t="n">
-        <v>10.9152307510376</v>
+        <v>10.91522979736328</v>
       </c>
       <c r="C84" t="n">
-        <v>11.25114809921971</v>
+        <v>11.25114711619596</v>
       </c>
       <c r="D84" t="n">
-        <v>10.79765935445603</v>
+        <v>10.79765841105404</v>
       </c>
       <c r="E84" t="n">
-        <v>11.25114809921971</v>
+        <v>11.25114711619596</v>
       </c>
       <c r="F84" t="n">
         <v>2442811</v>
@@ -2152,16 +2152,16 @@
         <v>44355</v>
       </c>
       <c r="B87" t="n">
-        <v>11.02020454406738</v>
+        <v>11.02020645141602</v>
       </c>
       <c r="C87" t="n">
-        <v>11.16926787426587</v>
+        <v>11.169269807414</v>
       </c>
       <c r="D87" t="n">
-        <v>10.9341251021654</v>
+        <v>10.93412699461562</v>
       </c>
       <c r="E87" t="n">
-        <v>11.12097909005958</v>
+        <v>11.12098101485001</v>
       </c>
       <c r="F87" t="n">
         <v>1135248</v>
@@ -2172,16 +2172,16 @@
         <v>44356</v>
       </c>
       <c r="B88" t="n">
-        <v>10.90893173217773</v>
+        <v>10.90893268585205</v>
       </c>
       <c r="C88" t="n">
-        <v>11.1251783608728</v>
+        <v>11.1251793334517</v>
       </c>
       <c r="D88" t="n">
-        <v>10.7325742494585</v>
+        <v>10.7325751877154</v>
       </c>
       <c r="E88" t="n">
-        <v>11.00340837520983</v>
+        <v>11.00340933714343</v>
       </c>
       <c r="F88" t="n">
         <v>1361892</v>
@@ -2192,16 +2192,16 @@
         <v>44357</v>
       </c>
       <c r="B89" t="n">
-        <v>10.79135990142822</v>
+        <v>10.79136085510254</v>
       </c>
       <c r="C89" t="n">
-        <v>10.99081132062593</v>
+        <v>10.99081229192654</v>
       </c>
       <c r="D89" t="n">
-        <v>10.70108266824717</v>
+        <v>10.70108361394333</v>
       </c>
       <c r="E89" t="n">
-        <v>10.94042404656661</v>
+        <v>10.9404250134143</v>
       </c>
       <c r="F89" t="n">
         <v>1040779</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462394714355</v>
+        <v>10.94462299346924</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192403640713</v>
+        <v>11.35192304724218</v>
       </c>
       <c r="D92" t="n">
-        <v>10.81445592759301</v>
+        <v>10.81445498526105</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152920210349</v>
+        <v>10.92152825044157</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2332,16 +2332,16 @@
         <v>44368</v>
       </c>
       <c r="B96" t="n">
-        <v>11.24274921417236</v>
+        <v>11.24275016784668</v>
       </c>
       <c r="C96" t="n">
-        <v>11.40441078522868</v>
+        <v>11.40441175261605</v>
       </c>
       <c r="D96" t="n">
-        <v>11.1524711700025</v>
+        <v>11.15247211601892</v>
       </c>
       <c r="E96" t="n">
-        <v>11.34562468559051</v>
+        <v>11.34562564799132</v>
       </c>
       <c r="F96" t="n">
         <v>1065511</v>
@@ -2352,16 +2352,16 @@
         <v>44369</v>
       </c>
       <c r="B97" t="n">
-        <v>11.28474140167236</v>
+        <v>11.28473949432373</v>
       </c>
       <c r="C97" t="n">
-        <v>11.42330825662318</v>
+        <v>11.42330632585396</v>
       </c>
       <c r="D97" t="n">
-        <v>11.16297220192883</v>
+        <v>11.16297031516165</v>
       </c>
       <c r="E97" t="n">
-        <v>11.23855353241498</v>
+        <v>11.23855163287302</v>
       </c>
       <c r="F97" t="n">
         <v>1033076</v>
@@ -2372,16 +2372,16 @@
         <v>44370</v>
       </c>
       <c r="B98" t="n">
-        <v>11.50308799743652</v>
+        <v>11.50308704376221</v>
       </c>
       <c r="C98" t="n">
-        <v>11.7487273000881</v>
+        <v>11.74872632604882</v>
       </c>
       <c r="D98" t="n">
-        <v>11.30573504903898</v>
+        <v>11.3057341117264</v>
       </c>
       <c r="E98" t="n">
-        <v>11.42120714749321</v>
+        <v>11.4212062006073</v>
       </c>
       <c r="F98" t="n">
         <v>4341920</v>
@@ -2412,16 +2412,16 @@
         <v>44372</v>
       </c>
       <c r="B100" t="n">
-        <v>11.61226081848145</v>
+        <v>11.61225986480713</v>
       </c>
       <c r="C100" t="n">
-        <v>11.71933490415196</v>
+        <v>11.71933394168402</v>
       </c>
       <c r="D100" t="n">
-        <v>11.34142665300706</v>
+        <v>11.34142572157541</v>
       </c>
       <c r="E100" t="n">
-        <v>11.71093688889577</v>
+        <v>11.71093592711753</v>
       </c>
       <c r="F100" t="n">
         <v>3580087</v>
@@ -2432,16 +2432,16 @@
         <v>44375</v>
       </c>
       <c r="B101" t="n">
-        <v>11.86209869384766</v>
+        <v>11.86209774017334</v>
       </c>
       <c r="C101" t="n">
-        <v>12.00066471799965</v>
+        <v>12.00066375318507</v>
       </c>
       <c r="D101" t="n">
-        <v>11.40441135990023</v>
+        <v>11.40441044302249</v>
       </c>
       <c r="E101" t="n">
-        <v>11.58916605876955</v>
+        <v>11.58916512703814</v>
       </c>
       <c r="F101" t="n">
         <v>1601511</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.0174617767334</v>
+        <v>12.01746082305908</v>
       </c>
       <c r="C102" t="n">
-        <v>12.0174617767334</v>
+        <v>12.01746082305908</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916626863832</v>
+        <v>11.58916534895242</v>
       </c>
       <c r="E102" t="n">
-        <v>11.8599996079053</v>
+        <v>11.85999866672677</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2472,16 +2472,16 @@
         <v>44377</v>
       </c>
       <c r="B103" t="n">
-        <v>11.88939189910889</v>
+        <v>11.8893928527832</v>
       </c>
       <c r="C103" t="n">
-        <v>12.16862405664855</v>
+        <v>12.16862503272069</v>
       </c>
       <c r="D103" t="n">
-        <v>11.85160123949193</v>
+        <v>11.85160219013497</v>
       </c>
       <c r="E103" t="n">
-        <v>12.02375932025384</v>
+        <v>12.02376028470606</v>
       </c>
       <c r="F103" t="n">
         <v>3669691</v>
@@ -2492,16 +2492,16 @@
         <v>44378</v>
       </c>
       <c r="B104" t="n">
-        <v>12.47094917297363</v>
+        <v>12.47094821929932</v>
       </c>
       <c r="C104" t="n">
-        <v>12.6347092370678</v>
+        <v>12.63470827087047</v>
       </c>
       <c r="D104" t="n">
-        <v>12.33028385156715</v>
+        <v>12.33028290864975</v>
       </c>
       <c r="E104" t="n">
-        <v>12.38906995272109</v>
+        <v>12.38906900530821</v>
       </c>
       <c r="F104" t="n">
         <v>8890212</v>
@@ -2572,16 +2572,16 @@
         <v>44384</v>
       </c>
       <c r="B108" t="n">
-        <v>13.22676563262939</v>
+        <v>13.22676658630371</v>
       </c>
       <c r="C108" t="n">
-        <v>13.31074415373561</v>
+        <v>13.31074511346494</v>
       </c>
       <c r="D108" t="n">
-        <v>13.05040814056382</v>
+        <v>13.05040908152244</v>
       </c>
       <c r="E108" t="n">
-        <v>13.05880615503335</v>
+        <v>13.05880709659748</v>
       </c>
       <c r="F108" t="n">
         <v>2057638</v>
@@ -2592,16 +2592,16 @@
         <v>44385</v>
       </c>
       <c r="B109" t="n">
-        <v>13.05880451202393</v>
+        <v>13.05880546569824</v>
       </c>
       <c r="C109" t="n">
-        <v>13.6109692261056</v>
+        <v>13.61097022010407</v>
       </c>
       <c r="D109" t="n">
-        <v>13.00631713114177</v>
+        <v>13.00631808098297</v>
       </c>
       <c r="E109" t="n">
-        <v>13.09659435469043</v>
+        <v>13.09659531112451</v>
       </c>
       <c r="F109" t="n">
         <v>8587750</v>
@@ -2612,16 +2612,16 @@
         <v>44389</v>
       </c>
       <c r="B110" t="n">
-        <v>13.3317403793335</v>
+        <v>13.33173942565918</v>
       </c>
       <c r="C110" t="n">
-        <v>13.79572644412283</v>
+        <v>13.79572545725768</v>
       </c>
       <c r="D110" t="n">
-        <v>13.07140353906678</v>
+        <v>13.07140260401543</v>
       </c>
       <c r="E110" t="n">
-        <v>13.19107423754762</v>
+        <v>13.19107329393574</v>
       </c>
       <c r="F110" t="n">
         <v>8663568</v>
@@ -2632,16 +2632,16 @@
         <v>44390</v>
       </c>
       <c r="B111" t="n">
-        <v>13.27295398712158</v>
+        <v>13.27295303344727</v>
       </c>
       <c r="C111" t="n">
-        <v>13.49759946187835</v>
+        <v>13.49759849206305</v>
       </c>
       <c r="D111" t="n">
-        <v>13.13438796092353</v>
+        <v>13.13438701720531</v>
       </c>
       <c r="E111" t="n">
-        <v>13.33174009059002</v>
+        <v>13.33173913269187</v>
       </c>
       <c r="F111" t="n">
         <v>2696620</v>
@@ -2652,16 +2652,16 @@
         <v>44391</v>
       </c>
       <c r="B112" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196468353271</v>
       </c>
       <c r="C112" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196468353271</v>
       </c>
       <c r="D112" t="n">
-        <v>13.25405823136172</v>
+        <v>13.25405730412531</v>
       </c>
       <c r="E112" t="n">
-        <v>13.27505286174354</v>
+        <v>13.27505193303836</v>
       </c>
       <c r="F112" t="n">
         <v>1800585</v>
@@ -2672,16 +2672,16 @@
         <v>44392</v>
       </c>
       <c r="B113" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196468353271</v>
       </c>
       <c r="C113" t="n">
-        <v>13.72224368436118</v>
+        <v>13.72224272437113</v>
       </c>
       <c r="D113" t="n">
-        <v>13.39682366626494</v>
+        <v>13.39682272904084</v>
       </c>
       <c r="E113" t="n">
-        <v>13.53958828937361</v>
+        <v>13.53958734216189</v>
       </c>
       <c r="F113" t="n">
         <v>1667599</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C114" t="n">
-        <v>13.93849238737042</v>
+        <v>13.93849142806081</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969953991438</v>
+        <v>13.49969861080446</v>
       </c>
       <c r="E114" t="n">
-        <v>13.6424649876205</v>
+        <v>13.64246404868482</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501629145801</v>
+        <v>14.24501531105205</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969953991438</v>
+        <v>13.49969861080446</v>
       </c>
       <c r="E115" t="n">
-        <v>13.74953744981087</v>
+        <v>13.74953650350598</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2752,16 +2752,16 @@
         <v>44398</v>
       </c>
       <c r="B117" t="n">
-        <v>14.31849956512451</v>
+        <v>14.31849765777588</v>
       </c>
       <c r="C117" t="n">
-        <v>14.34789140009018</v>
+        <v>14.3478894888263</v>
       </c>
       <c r="D117" t="n">
-        <v>14.01617264709314</v>
+        <v>14.01617078001709</v>
       </c>
       <c r="E117" t="n">
-        <v>14.06866003817584</v>
+        <v>14.06865816410801</v>
       </c>
       <c r="F117" t="n">
         <v>2316312</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.99872970581055</v>
+        <v>14.9987325668335</v>
       </c>
       <c r="C118" t="n">
-        <v>15.01132713142357</v>
+        <v>15.01132999484949</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36048557764203</v>
+        <v>14.36048831691926</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36048557764203</v>
+        <v>14.36048831691926</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801319122314</v>
+        <v>15.06801414489746</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127674547757</v>
+        <v>15.22127770885214</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92944798816965</v>
+        <v>14.92944893307399</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127674547757</v>
+        <v>15.22127770885214</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2812,16 +2812,16 @@
         <v>44403</v>
       </c>
       <c r="B120" t="n">
-        <v>14.87486171722412</v>
+        <v>14.8748607635498</v>
       </c>
       <c r="C120" t="n">
-        <v>15.17088908393575</v>
+        <v>15.17088811128218</v>
       </c>
       <c r="D120" t="n">
-        <v>14.64601846513237</v>
+        <v>14.64601752612992</v>
       </c>
       <c r="E120" t="n">
-        <v>15.07431313686146</v>
+        <v>15.07431217039968</v>
       </c>
       <c r="F120" t="n">
         <v>4655330</v>
@@ -2852,16 +2852,16 @@
         <v>44405</v>
       </c>
       <c r="B122" t="n">
-        <v>15.08691120147705</v>
+        <v>15.08690929412842</v>
       </c>
       <c r="C122" t="n">
-        <v>15.36824185204953</v>
+        <v>15.36823990913394</v>
       </c>
       <c r="D122" t="n">
-        <v>14.03716667235407</v>
+        <v>14.03716489771841</v>
       </c>
       <c r="E122" t="n">
-        <v>15.13519836525918</v>
+        <v>15.13519645180589</v>
       </c>
       <c r="F122" t="n">
         <v>6581198</v>
@@ -2872,16 +2872,16 @@
         <v>44406</v>
       </c>
       <c r="B123" t="n">
-        <v>15.28426170349121</v>
+        <v>15.28426265716553</v>
       </c>
       <c r="C123" t="n">
-        <v>15.32415166438117</v>
+        <v>15.32415262054446</v>
       </c>
       <c r="D123" t="n">
-        <v>14.85386771299919</v>
+        <v>14.85386863981871</v>
       </c>
       <c r="E123" t="n">
-        <v>15.09950700409309</v>
+        <v>15.09950794623948</v>
       </c>
       <c r="F123" t="n">
         <v>6067903</v>
@@ -2932,16 +2932,16 @@
         <v>44411</v>
       </c>
       <c r="B126" t="n">
-        <v>15.20448303222656</v>
+        <v>15.20448017120361</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39343634860877</v>
+        <v>15.39343345203053</v>
       </c>
       <c r="D126" t="n">
-        <v>14.76149157738092</v>
+        <v>14.76148879971554</v>
       </c>
       <c r="E126" t="n">
-        <v>15.39343634860877</v>
+        <v>15.39343345203053</v>
       </c>
       <c r="F126" t="n">
         <v>3496971</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.93639183044434</v>
+        <v>13.93639087677002</v>
       </c>
       <c r="C129" t="n">
-        <v>14.41927319977593</v>
+        <v>14.4192722130578</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373643553897</v>
+        <v>13.75373549436386</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153461307515</v>
+        <v>14.17153364330989</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3032,16 +3032,16 @@
         <v>44418</v>
       </c>
       <c r="B131" t="n">
-        <v>13.64666175842285</v>
+        <v>13.64666271209717</v>
       </c>
       <c r="C131" t="n">
-        <v>14.43816789362585</v>
+        <v>14.43816890261326</v>
       </c>
       <c r="D131" t="n">
-        <v>13.56688184180349</v>
+        <v>13.56688278990252</v>
       </c>
       <c r="E131" t="n">
-        <v>14.05396179104118</v>
+        <v>14.05396277317898</v>
       </c>
       <c r="F131" t="n">
         <v>2933806</v>
@@ -3112,16 +3112,16 @@
         <v>44424</v>
       </c>
       <c r="B135" t="n">
-        <v>11.84110450744629</v>
+        <v>11.84110355377197</v>
       </c>
       <c r="C135" t="n">
-        <v>12.94963355405497</v>
+        <v>12.94963251110049</v>
       </c>
       <c r="D135" t="n">
-        <v>11.7655231844898</v>
+        <v>11.76552223690275</v>
       </c>
       <c r="E135" t="n">
-        <v>12.94963355405497</v>
+        <v>12.94963251110049</v>
       </c>
       <c r="F135" t="n">
         <v>7844263</v>
@@ -3132,16 +3132,16 @@
         <v>44425</v>
       </c>
       <c r="B136" t="n">
-        <v>12.27779674530029</v>
+        <v>12.27779769897461</v>
       </c>
       <c r="C136" t="n">
-        <v>12.78167271978735</v>
+        <v>12.78167371260009</v>
       </c>
       <c r="D136" t="n">
-        <v>11.42960381681197</v>
+        <v>11.42960470460314</v>
       </c>
       <c r="E136" t="n">
-        <v>11.66474658767486</v>
+        <v>11.66474749373068</v>
       </c>
       <c r="F136" t="n">
         <v>5635292</v>
@@ -3152,16 +3152,16 @@
         <v>44426</v>
       </c>
       <c r="B137" t="n">
-        <v>12.59691905975342</v>
+        <v>12.5969181060791</v>
       </c>
       <c r="C137" t="n">
-        <v>13.13438794617422</v>
+        <v>13.13438695180978</v>
       </c>
       <c r="D137" t="n">
-        <v>12.21901164220178</v>
+        <v>12.21901071713769</v>
       </c>
       <c r="E137" t="n">
-        <v>12.38697031404816</v>
+        <v>12.38696937626842</v>
       </c>
       <c r="F137" t="n">
         <v>3796291</v>
@@ -3172,16 +3172,16 @@
         <v>44427</v>
       </c>
       <c r="B138" t="n">
-        <v>13.08399963378906</v>
+        <v>13.08400058746338</v>
       </c>
       <c r="C138" t="n">
-        <v>13.26875432055636</v>
+        <v>13.26875528769718</v>
       </c>
       <c r="D138" t="n">
-        <v>11.91668460264106</v>
+        <v>11.91668547123142</v>
       </c>
       <c r="E138" t="n">
-        <v>12.41216337598772</v>
+        <v>12.41216428069283</v>
       </c>
       <c r="F138" t="n">
         <v>2072031</v>
@@ -3192,16 +3192,16 @@
         <v>44428</v>
       </c>
       <c r="B139" t="n">
-        <v>13.52069282531738</v>
+        <v>13.5206937789917</v>
       </c>
       <c r="C139" t="n">
-        <v>13.70544751914833</v>
+        <v>13.70544848585422</v>
       </c>
       <c r="D139" t="n">
-        <v>12.6473066309372</v>
+        <v>12.64730752300772</v>
       </c>
       <c r="E139" t="n">
-        <v>12.8068672814836</v>
+        <v>12.80686818480864</v>
       </c>
       <c r="F139" t="n">
         <v>3576438</v>
@@ -3232,16 +3232,16 @@
         <v>44432</v>
       </c>
       <c r="B141" t="n">
-        <v>13.63826656341553</v>
+        <v>13.63826560974121</v>
       </c>
       <c r="C141" t="n">
-        <v>13.9237958389553</v>
+        <v>13.92379486531496</v>
       </c>
       <c r="D141" t="n">
-        <v>13.37792971040871</v>
+        <v>13.3779287749388</v>
       </c>
       <c r="E141" t="n">
-        <v>13.63826656341553</v>
+        <v>13.63826560974121</v>
       </c>
       <c r="F141" t="n">
         <v>2525015</v>
@@ -3252,16 +3252,16 @@
         <v>44433</v>
       </c>
       <c r="B142" t="n">
-        <v>13.47870445251465</v>
+        <v>13.47870254516602</v>
       </c>
       <c r="C142" t="n">
-        <v>13.57947900869956</v>
+        <v>13.57947708709049</v>
       </c>
       <c r="D142" t="n">
-        <v>13.05040893565314</v>
+        <v>13.05040708891188</v>
       </c>
       <c r="E142" t="n">
-        <v>13.44511239258996</v>
+        <v>13.44511048999488</v>
       </c>
       <c r="F142" t="n">
         <v>2709595</v>
@@ -3272,16 +3272,16 @@
         <v>44434</v>
       </c>
       <c r="B143" t="n">
-        <v>13.12599086761475</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C143" t="n">
-        <v>13.76423435323049</v>
+        <v>13.76423235313817</v>
       </c>
       <c r="D143" t="n">
-        <v>12.82366474965109</v>
+        <v>12.82366288623372</v>
       </c>
       <c r="E143" t="n">
-        <v>13.47870507780299</v>
+        <v>13.47870311920116</v>
       </c>
       <c r="F143" t="n">
         <v>2624147</v>
@@ -3372,16 +3372,16 @@
         <v>44441</v>
       </c>
       <c r="B148" t="n">
-        <v>12.80686664581299</v>
+        <v>12.80686855316162</v>
       </c>
       <c r="C148" t="n">
-        <v>13.18477402914559</v>
+        <v>13.18477599277661</v>
       </c>
       <c r="D148" t="n">
-        <v>12.69769408725448</v>
+        <v>12.69769597834385</v>
       </c>
       <c r="E148" t="n">
-        <v>13.06720345657573</v>
+        <v>13.06720540269677</v>
       </c>
       <c r="F148" t="n">
         <v>2514879</v>
@@ -3392,16 +3392,16 @@
         <v>44442</v>
       </c>
       <c r="B149" t="n">
-        <v>13.10079574584961</v>
+        <v>13.10079669952393</v>
       </c>
       <c r="C149" t="n">
-        <v>13.21836713959238</v>
+        <v>13.21836810182533</v>
       </c>
       <c r="D149" t="n">
-        <v>12.74808237641584</v>
+        <v>12.74808330441434</v>
       </c>
       <c r="E149" t="n">
-        <v>12.94963310517644</v>
+        <v>12.94963404784685</v>
       </c>
       <c r="F149" t="n">
         <v>3315331</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00002128473755</v>
+        <v>13.00002039001773</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113269394332</v>
+        <v>13.36113177437019</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3432,16 +3432,16 @@
         <v>44447</v>
       </c>
       <c r="B151" t="n">
-        <v>13.23516178131104</v>
+        <v>13.23516273498535</v>
       </c>
       <c r="C151" t="n">
-        <v>14.67960797812228</v>
+        <v>14.67960903587777</v>
       </c>
       <c r="D151" t="n">
-        <v>13.10079437229357</v>
+        <v>13.10079531628589</v>
       </c>
       <c r="E151" t="n">
-        <v>13.80622103720047</v>
+        <v>13.80622203202309</v>
       </c>
       <c r="F151" t="n">
         <v>4568970</v>
@@ -3452,16 +3452,16 @@
         <v>44448</v>
       </c>
       <c r="B152" t="n">
-        <v>13.12599086761475</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C152" t="n">
-        <v>13.37792970514844</v>
+        <v>13.37792776119036</v>
       </c>
       <c r="D152" t="n">
-        <v>12.5297366470582</v>
+        <v>12.52973482635177</v>
       </c>
       <c r="E152" t="n">
-        <v>13.21836822489853</v>
+        <v>13.21836630412647</v>
       </c>
       <c r="F152" t="n">
         <v>3739731</v>
@@ -3472,16 +3472,16 @@
         <v>44449</v>
       </c>
       <c r="B153" t="n">
-        <v>13.08399963378906</v>
+        <v>13.08400058746338</v>
       </c>
       <c r="C153" t="n">
-        <v>13.77263110801012</v>
+        <v>13.77263211187781</v>
       </c>
       <c r="D153" t="n">
-        <v>13.00841750682512</v>
+        <v>13.00841845499036</v>
       </c>
       <c r="E153" t="n">
-        <v>13.77263110801012</v>
+        <v>13.77263211187781</v>
       </c>
       <c r="F153" t="n">
         <v>2018917</v>
@@ -3492,16 +3492,16 @@
         <v>44452</v>
       </c>
       <c r="B154" t="n">
-        <v>13.39472389221191</v>
+        <v>13.3947229385376</v>
       </c>
       <c r="C154" t="n">
-        <v>13.53748933072213</v>
+        <v>13.53748836688323</v>
       </c>
       <c r="D154" t="n">
-        <v>12.9748272149942</v>
+        <v>12.97482629121558</v>
       </c>
       <c r="E154" t="n">
-        <v>13.24356125077245</v>
+        <v>13.24356030786057</v>
       </c>
       <c r="F154" t="n">
         <v>1856739</v>
@@ -3512,16 +3512,16 @@
         <v>44453</v>
       </c>
       <c r="B155" t="n">
-        <v>13.55428600311279</v>
+        <v>13.55428504943848</v>
       </c>
       <c r="C155" t="n">
-        <v>14.04976483634768</v>
+        <v>14.04976384781166</v>
       </c>
       <c r="D155" t="n">
-        <v>13.27715393946506</v>
+        <v>13.27715300528965</v>
       </c>
       <c r="E155" t="n">
-        <v>13.43671460319705</v>
+        <v>13.43671365779501</v>
       </c>
       <c r="F155" t="n">
         <v>1943200</v>
@@ -3532,16 +3532,16 @@
         <v>44454</v>
       </c>
       <c r="B156" t="n">
-        <v>13.44511127471924</v>
+        <v>13.44511222839355</v>
       </c>
       <c r="C156" t="n">
-        <v>14.07495666337775</v>
+        <v>14.07495766172759</v>
       </c>
       <c r="D156" t="n">
-        <v>13.2351625412349</v>
+        <v>13.23516348001735</v>
       </c>
       <c r="E156" t="n">
-        <v>13.47030450577353</v>
+        <v>13.47030546123482</v>
       </c>
       <c r="F156" t="n">
         <v>2602050</v>
@@ -3552,16 +3552,16 @@
         <v>44455</v>
       </c>
       <c r="B157" t="n">
-        <v>13.56268405914307</v>
+        <v>13.56268215179443</v>
       </c>
       <c r="C157" t="n">
-        <v>13.7894288445363</v>
+        <v>13.78942690530008</v>
       </c>
       <c r="D157" t="n">
-        <v>13.33593927374983</v>
+        <v>13.33593739828879</v>
       </c>
       <c r="E157" t="n">
-        <v>13.47870471946269</v>
+        <v>13.47870282392425</v>
       </c>
       <c r="F157" t="n">
         <v>1227183</v>
@@ -3572,16 +3572,16 @@
         <v>44456</v>
       </c>
       <c r="B158" t="n">
-        <v>13.44511127471924</v>
+        <v>13.44511222839355</v>
       </c>
       <c r="C158" t="n">
-        <v>13.74743816531587</v>
+        <v>13.74743914043451</v>
       </c>
       <c r="D158" t="n">
-        <v>13.29394782942092</v>
+        <v>13.29394877237308</v>
       </c>
       <c r="E158" t="n">
-        <v>13.40312201509908</v>
+        <v>13.40312296579506</v>
       </c>
       <c r="F158" t="n">
         <v>5378949</v>
@@ -3592,16 +3592,16 @@
         <v>44459</v>
       </c>
       <c r="B159" t="n">
-        <v>12.84885787963867</v>
+        <v>12.84885692596436</v>
       </c>
       <c r="C159" t="n">
-        <v>13.10919390218652</v>
+        <v>13.10919292918942</v>
       </c>
       <c r="D159" t="n">
-        <v>12.63051111915618</v>
+        <v>12.63051018168811</v>
       </c>
       <c r="E159" t="n">
-        <v>13.10919390218652</v>
+        <v>13.10919292918942</v>
       </c>
       <c r="F159" t="n">
         <v>1643373</v>
@@ -3612,16 +3612,16 @@
         <v>44460</v>
       </c>
       <c r="B160" t="n">
-        <v>13.52069282531738</v>
+        <v>13.5206937789917</v>
       </c>
       <c r="C160" t="n">
-        <v>13.64666222994559</v>
+        <v>13.64666319250508</v>
       </c>
       <c r="D160" t="n">
-        <v>12.8068672814836</v>
+        <v>12.80686818480864</v>
       </c>
       <c r="E160" t="n">
-        <v>12.9832247726809</v>
+        <v>12.98322568844521</v>
       </c>
       <c r="F160" t="n">
         <v>1911981</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.61242771148682</v>
+        <v>14.6124267578125</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630374532261</v>
+        <v>15.11630275876303</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893814452217</v>
+        <v>14.15893722044467</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19253020482906</v>
+        <v>14.19252927855919</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661315917969</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26811184817934</v>
+        <v>14.26811086618383</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141830159083</v>
+        <v>13.83141734965053</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733566500235</v>
+        <v>14.16733468994271</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3712,16 +3712,16 @@
         <v>44467</v>
       </c>
       <c r="B165" t="n">
-        <v>13.16797924041748</v>
+        <v>13.16797828674316</v>
       </c>
       <c r="C165" t="n">
-        <v>13.89020197448434</v>
+        <v>13.89020096850395</v>
       </c>
       <c r="D165" t="n">
-        <v>13.15118240005499</v>
+        <v>13.15118144759716</v>
       </c>
       <c r="E165" t="n">
-        <v>13.64666199563223</v>
+        <v>13.64666100728992</v>
       </c>
       <c r="F165" t="n">
         <v>3700200</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498119354248</v>
+        <v>12.34497928619385</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366398204986</v>
+        <v>12.82366200074284</v>
       </c>
       <c r="D169" t="n">
-        <v>12.13503244542976</v>
+        <v>12.13503057051905</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288861542754</v>
+        <v>12.72288664969071</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14343070983887</v>
+        <v>12.14342880249023</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55493019965232</v>
+        <v>12.55492822767014</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027798749311</v>
+        <v>11.95027611048266</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337946226592</v>
+        <v>12.35337752194098</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3852,16 +3852,16 @@
         <v>44476</v>
       </c>
       <c r="B172" t="n">
-        <v>13.00002002716064</v>
+        <v>13.00002098083496</v>
       </c>
       <c r="C172" t="n">
-        <v>13.02521407051771</v>
+        <v>13.02521502604024</v>
       </c>
       <c r="D172" t="n">
-        <v>12.36177579954892</v>
+        <v>12.36177670640198</v>
       </c>
       <c r="E172" t="n">
-        <v>12.56332733461089</v>
+        <v>12.56332825624967</v>
       </c>
       <c r="F172" t="n">
         <v>3555051</v>
@@ -3872,16 +3872,16 @@
         <v>44477</v>
       </c>
       <c r="B173" t="n">
-        <v>13.05880451202393</v>
+        <v>13.05880546569824</v>
       </c>
       <c r="C173" t="n">
-        <v>13.38632378795018</v>
+        <v>13.38632476554297</v>
       </c>
       <c r="D173" t="n">
-        <v>12.89924306897283</v>
+        <v>12.8992440109945</v>
       </c>
       <c r="E173" t="n">
-        <v>13.11759060591438</v>
+        <v>13.1175915638818</v>
       </c>
       <c r="F173" t="n">
         <v>3251676</v>
@@ -3912,16 +3912,16 @@
         <v>44482</v>
       </c>
       <c r="B175" t="n">
-        <v>13.12599086761475</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C175" t="n">
-        <v>13.34433764366538</v>
+        <v>13.34433570458859</v>
       </c>
       <c r="D175" t="n">
-        <v>12.83206357681648</v>
+        <v>12.83206171217867</v>
       </c>
       <c r="E175" t="n">
-        <v>12.83206357681648</v>
+        <v>12.83206171217867</v>
       </c>
       <c r="F175" t="n">
         <v>2244954</v>
@@ -3932,16 +3932,16 @@
         <v>44483</v>
       </c>
       <c r="B176" t="n">
-        <v>13.16797924041748</v>
+        <v>13.16797828674316</v>
       </c>
       <c r="C176" t="n">
-        <v>13.29394783108827</v>
+        <v>13.29394686829084</v>
       </c>
       <c r="D176" t="n">
-        <v>12.85725514729346</v>
+        <v>12.85725421612295</v>
       </c>
       <c r="E176" t="n">
-        <v>13.12598916899754</v>
+        <v>13.1259882183643</v>
       </c>
       <c r="F176" t="n">
         <v>1588233</v>
@@ -3992,16 +3992,16 @@
         <v>44488</v>
       </c>
       <c r="B179" t="n">
-        <v>12.39536762237549</v>
+        <v>12.3953685760498</v>
       </c>
       <c r="C179" t="n">
-        <v>13.10919315473166</v>
+        <v>13.10919416332626</v>
       </c>
       <c r="D179" t="n">
-        <v>12.17702087434261</v>
+        <v>12.17702181121777</v>
       </c>
       <c r="E179" t="n">
-        <v>13.05880588076728</v>
+        <v>13.05880688548518</v>
       </c>
       <c r="F179" t="n">
         <v>2260766</v>
@@ -4012,16 +4012,16 @@
         <v>44489</v>
       </c>
       <c r="B180" t="n">
-        <v>11.98386859893799</v>
+        <v>11.9838695526123</v>
       </c>
       <c r="C180" t="n">
-        <v>12.58852073800141</v>
+        <v>12.58852173979385</v>
       </c>
       <c r="D180" t="n">
-        <v>11.874695228402</v>
+        <v>11.87469617338831</v>
       </c>
       <c r="E180" t="n">
-        <v>12.45415332538915</v>
+        <v>12.45415431648865</v>
       </c>
       <c r="F180" t="n">
         <v>2144403</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.53102397918701</v>
+        <v>10.5310230255127</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174807577158</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624046544360398</v>
+        <v>9.624045672820648</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174807577158</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55621719360352</v>
+        <v>10.55622005462646</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650190285215</v>
+        <v>11.02650489133509</v>
       </c>
       <c r="D183" t="n">
-        <v>10.35466648795489</v>
+        <v>10.3546692943521</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699254642783</v>
+        <v>10.65699543476365</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4092,16 +4092,16 @@
         <v>44495</v>
       </c>
       <c r="B184" t="n">
-        <v>9.985158920288086</v>
+        <v>9.98515796661377</v>
       </c>
       <c r="C184" t="n">
-        <v>10.46384172900696</v>
+        <v>10.46384072961404</v>
       </c>
       <c r="D184" t="n">
-        <v>9.825597442852056</v>
+        <v>9.825596504417325</v>
       </c>
       <c r="E184" t="n">
-        <v>10.46384172900696</v>
+        <v>10.46384072961404</v>
       </c>
       <c r="F184" t="n">
         <v>5760068</v>
@@ -4152,16 +4152,16 @@
         <v>44498</v>
       </c>
       <c r="B187" t="n">
-        <v>9.514873504638672</v>
+        <v>9.514872550964355</v>
       </c>
       <c r="C187" t="n">
-        <v>10.06913760232501</v>
+        <v>10.06913659309689</v>
       </c>
       <c r="D187" t="n">
-        <v>9.069781974119245</v>
+        <v>9.069781065056384</v>
       </c>
       <c r="E187" t="n">
-        <v>10.06913760232501</v>
+        <v>10.06913659309689</v>
       </c>
       <c r="F187" t="n">
         <v>8163450</v>
@@ -4192,16 +4192,16 @@
         <v>44503</v>
       </c>
       <c r="B189" t="n">
-        <v>10.14471817016602</v>
+        <v>10.14471912384033</v>
       </c>
       <c r="C189" t="n">
-        <v>10.29588079948901</v>
+        <v>10.29588176737367</v>
       </c>
       <c r="D189" t="n">
-        <v>9.548463231541206</v>
+        <v>9.548464129163397</v>
       </c>
       <c r="E189" t="n">
-        <v>9.657637414199865</v>
+        <v>9.657638322085189</v>
       </c>
       <c r="F189" t="n">
         <v>6020061</v>
@@ -4212,16 +4212,16 @@
         <v>44504</v>
       </c>
       <c r="B190" t="n">
-        <v>10.3546667098999</v>
+        <v>10.35466766357422</v>
       </c>
       <c r="C190" t="n">
-        <v>11.22805366096068</v>
+        <v>11.22805469507473</v>
       </c>
       <c r="D190" t="n">
-        <v>10.02714660325211</v>
+        <v>10.02714752676152</v>
       </c>
       <c r="E190" t="n">
-        <v>10.08593270053977</v>
+        <v>10.08593362946343</v>
       </c>
       <c r="F190" t="n">
         <v>7850142</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55621719360352</v>
+        <v>10.55622005462646</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771580682453</v>
+        <v>10.96771877937483</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588039192727</v>
+        <v>10.29588318239185</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64019651899136</v>
+        <v>10.640199402775</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.74937152862549</v>
+        <v>10.74936962127686</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324836976697</v>
+        <v>11.25324637301136</v>
       </c>
       <c r="D193" t="n">
-        <v>10.40505616072565</v>
+        <v>10.4050543144717</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660608538766</v>
+        <v>10.60660420337106</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4312,16 +4312,16 @@
         <v>44511</v>
       </c>
       <c r="B195" t="n">
-        <v>11.21965503692627</v>
+        <v>11.21965599060059</v>
       </c>
       <c r="C195" t="n">
-        <v>11.53037912136244</v>
+        <v>11.5303801014484</v>
       </c>
       <c r="D195" t="n">
-        <v>10.69058502259491</v>
+        <v>10.69058593129811</v>
       </c>
       <c r="E195" t="n">
-        <v>10.7829615535469</v>
+        <v>10.78296247010213</v>
       </c>
       <c r="F195" t="n">
         <v>2903296</v>
@@ -4372,16 +4372,16 @@
         <v>44517</v>
       </c>
       <c r="B198" t="n">
-        <v>10.10272789001465</v>
+        <v>10.10272884368896</v>
       </c>
       <c r="C198" t="n">
-        <v>10.35466668271126</v>
+        <v>10.35466766016802</v>
       </c>
       <c r="D198" t="n">
-        <v>9.800402637649874</v>
+        <v>9.800403562785382</v>
       </c>
       <c r="E198" t="n">
-        <v>10.29588058557796</v>
+        <v>10.29588155748545</v>
       </c>
       <c r="F198" t="n">
         <v>3557179</v>
@@ -4412,16 +4412,16 @@
         <v>44519</v>
       </c>
       <c r="B200" t="n">
-        <v>10.80815696716309</v>
+        <v>10.80815601348877</v>
       </c>
       <c r="C200" t="n">
-        <v>10.95092241232044</v>
+        <v>10.950921446049</v>
       </c>
       <c r="D200" t="n">
-        <v>10.33787217970612</v>
+        <v>10.3378712675281</v>
       </c>
       <c r="E200" t="n">
-        <v>10.33787217970612</v>
+        <v>10.3378712675281</v>
       </c>
       <c r="F200" t="n">
         <v>2187279</v>
@@ -4432,16 +4432,16 @@
         <v>44522</v>
       </c>
       <c r="B201" t="n">
-        <v>10.22030067443848</v>
+        <v>10.22029876708984</v>
       </c>
       <c r="C201" t="n">
-        <v>10.92572825424251</v>
+        <v>10.92572621524449</v>
       </c>
       <c r="D201" t="n">
-        <v>10.19510744114856</v>
+        <v>10.19510553850158</v>
       </c>
       <c r="E201" t="n">
-        <v>10.7913608255864</v>
+        <v>10.79135881166451</v>
       </c>
       <c r="F201" t="n">
         <v>1734497</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674432754516602</v>
+        <v>9.674434661865234</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34626814824561</v>
+        <v>10.34627018804897</v>
       </c>
       <c r="D202" t="n">
-        <v>9.481280068672081</v>
+        <v>9.481281937939977</v>
       </c>
       <c r="E202" t="n">
-        <v>10.28748205407023</v>
+        <v>10.2874840822837</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4532,16 +4532,16 @@
         <v>44529</v>
       </c>
       <c r="B206" t="n">
-        <v>9.632444381713867</v>
+        <v>9.632443428039551</v>
       </c>
       <c r="C206" t="n">
-        <v>9.909577250845725</v>
+        <v>9.909576269733462</v>
       </c>
       <c r="D206" t="n">
-        <v>9.456087691753288</v>
+        <v>9.456086755539426</v>
       </c>
       <c r="E206" t="n">
-        <v>9.741617764021505</v>
+        <v>9.741616799538319</v>
       </c>
       <c r="F206" t="n">
         <v>2527144</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884383201599121</v>
+        <v>9.884382247924805</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709658136135</v>
+        <v>10.23709559365621</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573658272883511</v>
+        <v>9.573657349188849</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867586359950231</v>
+        <v>9.867585407896522</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4652,16 +4652,16 @@
         <v>44537</v>
       </c>
       <c r="B212" t="n">
-        <v>9.985158920288086</v>
+        <v>9.98515796661377</v>
       </c>
       <c r="C212" t="n">
-        <v>10.53102503899367</v>
+        <v>10.53102403318413</v>
       </c>
       <c r="D212" t="n">
-        <v>9.867586707170773</v>
+        <v>9.867585764725682</v>
       </c>
       <c r="E212" t="n">
-        <v>10.00195413893881</v>
+        <v>10.00195318366039</v>
       </c>
       <c r="F212" t="n">
         <v>3095174</v>
@@ -4692,16 +4692,16 @@
         <v>44539</v>
       </c>
       <c r="B214" t="n">
-        <v>10.78222942352295</v>
+        <v>10.78222846984863</v>
       </c>
       <c r="C214" t="n">
-        <v>11.00401677853015</v>
+        <v>11.00401580523902</v>
       </c>
       <c r="D214" t="n">
-        <v>10.23629341206293</v>
+        <v>10.23629250667595</v>
       </c>
       <c r="E214" t="n">
-        <v>10.46661108166976</v>
+        <v>10.46661015591148</v>
       </c>
       <c r="F214" t="n">
         <v>2489235</v>
@@ -4732,16 +4732,16 @@
         <v>44543</v>
       </c>
       <c r="B216" t="n">
-        <v>11.19168090820312</v>
+        <v>11.19168186187744</v>
       </c>
       <c r="C216" t="n">
-        <v>11.55848110021426</v>
+        <v>11.55848208514464</v>
       </c>
       <c r="D216" t="n">
-        <v>11.13196871210059</v>
+        <v>11.13196966068666</v>
       </c>
       <c r="E216" t="n">
-        <v>11.25992259345134</v>
+        <v>11.25992355294072</v>
       </c>
       <c r="F216" t="n">
         <v>3334589</v>
@@ -4772,16 +4772,16 @@
         <v>44545</v>
       </c>
       <c r="B218" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845264434814</v>
       </c>
       <c r="C218" t="n">
-        <v>11.37934603413065</v>
+        <v>11.37934507107126</v>
       </c>
       <c r="D218" t="n">
-        <v>10.8163502410046</v>
+        <v>10.8163493255928</v>
       </c>
       <c r="E218" t="n">
-        <v>10.90165255894037</v>
+        <v>10.90165163630924</v>
       </c>
       <c r="F218" t="n">
         <v>3122034</v>
@@ -4972,16 +4972,16 @@
         <v>44560</v>
       </c>
       <c r="B228" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="C228" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="D228" t="n">
-        <v>9.647705662569827</v>
+        <v>9.647706562908386</v>
       </c>
       <c r="E228" t="n">
-        <v>9.792720171305367</v>
+        <v>9.7927210851769</v>
       </c>
       <c r="F228" t="n">
         <v>3325771</v>
@@ -5012,16 +5012,16 @@
         <v>44565</v>
       </c>
       <c r="B230" t="n">
-        <v>9.238255500793457</v>
+        <v>9.238256454467773</v>
       </c>
       <c r="C230" t="n">
-        <v>9.826842249612479</v>
+        <v>9.826843264047191</v>
       </c>
       <c r="D230" t="n">
-        <v>9.170012985278218</v>
+        <v>9.170013931907791</v>
       </c>
       <c r="E230" t="n">
-        <v>9.75859973409724</v>
+        <v>9.758600741487211</v>
       </c>
       <c r="F230" t="n">
         <v>4143150</v>
@@ -5032,16 +5032,16 @@
         <v>44566</v>
       </c>
       <c r="B231" t="n">
-        <v>8.530243873596191</v>
+        <v>8.530244827270508</v>
       </c>
       <c r="C231" t="n">
-        <v>9.255314788383105</v>
+        <v>9.255315823119759</v>
       </c>
       <c r="D231" t="n">
-        <v>8.479062814400418</v>
+        <v>8.479063762352734</v>
       </c>
       <c r="E231" t="n">
-        <v>9.255314788383105</v>
+        <v>9.255315823119759</v>
       </c>
       <c r="F231" t="n">
         <v>5451524</v>
@@ -5132,16 +5132,16 @@
         <v>44573</v>
       </c>
       <c r="B236" t="n">
-        <v>9.221194267272949</v>
+        <v>9.221193313598633</v>
       </c>
       <c r="C236" t="n">
-        <v>9.408860364832703</v>
+        <v>9.408859391749584</v>
       </c>
       <c r="D236" t="n">
-        <v>8.64113781905797</v>
+        <v>8.64113692537425</v>
       </c>
       <c r="E236" t="n">
-        <v>8.914106238463063</v>
+        <v>8.914105316548403</v>
       </c>
       <c r="F236" t="n">
         <v>2757539</v>
@@ -5152,16 +5152,16 @@
         <v>44574</v>
       </c>
       <c r="B237" t="n">
-        <v>8.726439476013184</v>
+        <v>8.7264404296875</v>
       </c>
       <c r="C237" t="n">
-        <v>9.110299446506351</v>
+        <v>9.110300442131042</v>
       </c>
       <c r="D237" t="n">
-        <v>8.555834036858977</v>
+        <v>8.555834971888574</v>
       </c>
       <c r="E237" t="n">
-        <v>9.042057765594588</v>
+        <v>9.042058753761445</v>
       </c>
       <c r="F237" t="n">
         <v>3017328</v>
@@ -5172,16 +5172,16 @@
         <v>44575</v>
       </c>
       <c r="B238" t="n">
-        <v>8.743501663208008</v>
+        <v>8.743500709533691</v>
       </c>
       <c r="C238" t="n">
-        <v>8.769092609750347</v>
+        <v>8.769091653284766</v>
       </c>
       <c r="D238" t="n">
-        <v>8.359641587990039</v>
+        <v>8.359640676184245</v>
       </c>
       <c r="E238" t="n">
-        <v>8.726441856763206</v>
+        <v>8.726440904949643</v>
       </c>
       <c r="F238" t="n">
         <v>2170250</v>
@@ -5212,16 +5212,16 @@
         <v>44579</v>
       </c>
       <c r="B240" t="n">
-        <v>8.308457374572754</v>
+        <v>8.30845832824707</v>
       </c>
       <c r="C240" t="n">
-        <v>8.76056154167938</v>
+        <v>8.760562547247821</v>
       </c>
       <c r="D240" t="n">
-        <v>8.206094431414945</v>
+        <v>8.206095373339679</v>
       </c>
       <c r="E240" t="n">
-        <v>8.530243888845217</v>
+        <v>8.530244867976979</v>
       </c>
       <c r="F240" t="n">
         <v>2291580</v>
@@ -5232,16 +5232,16 @@
         <v>44580</v>
       </c>
       <c r="B241" t="n">
-        <v>8.521714210510254</v>
+        <v>8.521713256835938</v>
       </c>
       <c r="C241" t="n">
-        <v>8.675259048991672</v>
+        <v>8.675258078133986</v>
       </c>
       <c r="D241" t="n">
-        <v>8.291398189663132</v>
+        <v>8.291397261763732</v>
       </c>
       <c r="E241" t="n">
-        <v>8.308457994309213</v>
+        <v>8.308457064500631</v>
       </c>
       <c r="F241" t="n">
         <v>1675201</v>
@@ -5252,16 +5252,16 @@
         <v>44581</v>
       </c>
       <c r="B242" t="n">
-        <v>9.383269309997559</v>
+        <v>9.383268356323242</v>
       </c>
       <c r="C242" t="n">
-        <v>9.656236901592942</v>
+        <v>9.6562359201754</v>
       </c>
       <c r="D242" t="n">
-        <v>8.530244452459904</v>
+        <v>8.530243585483291</v>
       </c>
       <c r="E242" t="n">
-        <v>8.581426339712161</v>
+        <v>8.581425467533645</v>
       </c>
       <c r="F242" t="n">
         <v>5361414</v>
@@ -5312,16 +5312,16 @@
         <v>44586</v>
       </c>
       <c r="B245" t="n">
-        <v>9.843903541564941</v>
+        <v>9.843902587890625</v>
       </c>
       <c r="C245" t="n">
-        <v>9.929205867121535</v>
+        <v>9.929204905183155</v>
       </c>
       <c r="D245" t="n">
-        <v>9.383269829142614</v>
+        <v>9.383268920094348</v>
       </c>
       <c r="E245" t="n">
-        <v>9.391800144156612</v>
+        <v>9.391799234281931</v>
       </c>
       <c r="F245" t="n">
         <v>2635195</v>
@@ -5372,16 +5372,16 @@
         <v>44589</v>
       </c>
       <c r="B248" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="C248" t="n">
-        <v>10.26188330324402</v>
+        <v>10.26188426089857</v>
       </c>
       <c r="D248" t="n">
-        <v>9.681826917468367</v>
+        <v>9.681827820991172</v>
       </c>
       <c r="E248" t="n">
-        <v>10.1936416180302</v>
+        <v>10.19364256931633</v>
       </c>
       <c r="F248" t="n">
         <v>1431224</v>
@@ -5392,16 +5392,16 @@
         <v>44592</v>
       </c>
       <c r="B249" t="n">
-        <v>10.47514057159424</v>
+        <v>10.47513961791992</v>
       </c>
       <c r="C249" t="n">
-        <v>10.56044289300652</v>
+        <v>10.56044193156613</v>
       </c>
       <c r="D249" t="n">
-        <v>10.18511234895917</v>
+        <v>10.1851114216895</v>
       </c>
       <c r="E249" t="n">
-        <v>10.22776392195697</v>
+        <v>10.22776299080424</v>
       </c>
       <c r="F249" t="n">
         <v>3321007</v>
@@ -5452,16 +5452,16 @@
         <v>44595</v>
       </c>
       <c r="B252" t="n">
-        <v>10.45808029174805</v>
+        <v>10.45807933807373</v>
       </c>
       <c r="C252" t="n">
-        <v>10.84194198780122</v>
+        <v>10.84194099912248</v>
       </c>
       <c r="D252" t="n">
-        <v>10.25335520826973</v>
+        <v>10.25335427326433</v>
       </c>
       <c r="E252" t="n">
-        <v>10.62015544997051</v>
+        <v>10.62015448151653</v>
       </c>
       <c r="F252" t="n">
         <v>1397774</v>
@@ -5472,16 +5472,16 @@
         <v>44596</v>
       </c>
       <c r="B253" t="n">
-        <v>10.25335597991943</v>
+        <v>10.2533540725708</v>
       </c>
       <c r="C253" t="n">
-        <v>10.56044404053951</v>
+        <v>10.56044207606577</v>
       </c>
       <c r="D253" t="n">
-        <v>9.835372992871521</v>
+        <v>9.835371163276871</v>
       </c>
       <c r="E253" t="n">
-        <v>10.56044404053951</v>
+        <v>10.56044207606577</v>
       </c>
       <c r="F253" t="n">
         <v>2130212</v>
@@ -5492,16 +5492,16 @@
         <v>44599</v>
       </c>
       <c r="B254" t="n">
-        <v>10.13393020629883</v>
+        <v>10.13393115997314</v>
       </c>
       <c r="C254" t="n">
-        <v>10.3471855748181</v>
+        <v>10.34718654856125</v>
       </c>
       <c r="D254" t="n">
-        <v>9.937733815994584</v>
+        <v>9.937734751205435</v>
       </c>
       <c r="E254" t="n">
-        <v>10.04862706939122</v>
+        <v>10.04862801503791</v>
       </c>
       <c r="F254" t="n">
         <v>1517482</v>
@@ -5552,16 +5552,16 @@
         <v>44602</v>
       </c>
       <c r="B257" t="n">
-        <v>9.997446060180664</v>
+        <v>9.99744701385498</v>
       </c>
       <c r="C257" t="n">
-        <v>10.38130687978837</v>
+        <v>10.38130787007986</v>
       </c>
       <c r="D257" t="n">
-        <v>9.920674061175772</v>
+        <v>9.92067500752667</v>
       </c>
       <c r="E257" t="n">
-        <v>10.36424625232434</v>
+        <v>10.36424724098838</v>
       </c>
       <c r="F257" t="n">
         <v>2000064</v>
@@ -5632,16 +5632,16 @@
         <v>44608</v>
       </c>
       <c r="B261" t="n">
-        <v>10.56897354125977</v>
+        <v>10.56897258758545</v>
       </c>
       <c r="C261" t="n">
-        <v>10.69692660514308</v>
+        <v>10.69692563992313</v>
       </c>
       <c r="D261" t="n">
-        <v>10.38983859215648</v>
+        <v>10.38983765464612</v>
       </c>
       <c r="E261" t="n">
-        <v>10.66280534832977</v>
+        <v>10.66280438618869</v>
       </c>
       <c r="F261" t="n">
         <v>4241775</v>
@@ -5692,16 +5692,16 @@
         <v>44613</v>
       </c>
       <c r="B264" t="n">
-        <v>9.383269309997559</v>
+        <v>9.383268356323242</v>
       </c>
       <c r="C264" t="n">
-        <v>10.193642594825</v>
+        <v>10.1936415587879</v>
       </c>
       <c r="D264" t="n">
-        <v>9.263846555575617</v>
+        <v>9.263845614038905</v>
       </c>
       <c r="E264" t="n">
-        <v>10.06568952586101</v>
+        <v>10.0656885028285</v>
       </c>
       <c r="F264" t="n">
         <v>2949517</v>
@@ -5732,16 +5732,16 @@
         <v>44615</v>
       </c>
       <c r="B266" t="n">
-        <v>9.767129898071289</v>
+        <v>9.767128944396973</v>
       </c>
       <c r="C266" t="n">
-        <v>10.11687031094908</v>
+        <v>10.11686932312569</v>
       </c>
       <c r="D266" t="n">
-        <v>9.681827579574664</v>
+        <v>9.68182663422937</v>
       </c>
       <c r="E266" t="n">
-        <v>9.775661036962589</v>
+        <v>9.775660082455282</v>
       </c>
       <c r="F266" t="n">
         <v>2319860</v>
@@ -5752,16 +5752,16 @@
         <v>44616</v>
       </c>
       <c r="B267" t="n">
-        <v>9.784191131591797</v>
+        <v>9.78419017791748</v>
       </c>
       <c r="C267" t="n">
-        <v>9.886554085032964</v>
+        <v>9.886553121381233</v>
       </c>
       <c r="D267" t="n">
-        <v>9.15295278127404</v>
+        <v>9.15295188912712</v>
       </c>
       <c r="E267" t="n">
-        <v>9.15295278127404</v>
+        <v>9.15295188912712</v>
       </c>
       <c r="F267" t="n">
         <v>2513764</v>
@@ -5772,16 +5772,16 @@
         <v>44617</v>
       </c>
       <c r="B268" t="n">
-        <v>9.425920486450195</v>
+        <v>9.425921440124512</v>
       </c>
       <c r="C268" t="n">
-        <v>9.869492701072385</v>
+        <v>9.869493699625441</v>
       </c>
       <c r="D268" t="n">
-        <v>9.383268915533016</v>
+        <v>9.383269864892029</v>
       </c>
       <c r="E268" t="n">
-        <v>9.579464492585451</v>
+        <v>9.579465461794694</v>
       </c>
       <c r="F268" t="n">
         <v>3597927</v>
@@ -5852,16 +5852,16 @@
         <v>44627</v>
       </c>
       <c r="B272" t="n">
-        <v>8.666728019714355</v>
+        <v>8.666728973388672</v>
       </c>
       <c r="C272" t="n">
-        <v>9.417389871825412</v>
+        <v>9.417390908101481</v>
       </c>
       <c r="D272" t="n">
-        <v>8.658197705803062</v>
+        <v>8.658198658538714</v>
       </c>
       <c r="E272" t="n">
-        <v>9.32355641880117</v>
+        <v>9.323557444751941</v>
       </c>
       <c r="F272" t="n">
         <v>2527651</v>
@@ -5892,16 +5892,16 @@
         <v>44629</v>
       </c>
       <c r="B274" t="n">
-        <v>9.255315780639648</v>
+        <v>9.255314826965332</v>
       </c>
       <c r="C274" t="n">
-        <v>9.391799994099552</v>
+        <v>9.391799026361806</v>
       </c>
       <c r="D274" t="n">
-        <v>8.845863964843298</v>
+        <v>8.845863053359189</v>
       </c>
       <c r="E274" t="n">
-        <v>8.939697428498043</v>
+        <v>8.939696507345268</v>
       </c>
       <c r="F274" t="n">
         <v>2821903</v>
@@ -5912,16 +5912,16 @@
         <v>44630</v>
       </c>
       <c r="B275" t="n">
-        <v>9.195603370666504</v>
+        <v>9.19560432434082</v>
       </c>
       <c r="C275" t="n">
-        <v>9.28090568530164</v>
+        <v>9.280906647822642</v>
       </c>
       <c r="D275" t="n">
-        <v>8.922634974334148</v>
+        <v>8.922635899698962</v>
       </c>
       <c r="E275" t="n">
-        <v>9.144421487135462</v>
+        <v>9.144422435501713</v>
       </c>
       <c r="F275" t="n">
         <v>2148356</v>
@@ -6012,16 +6012,16 @@
         <v>44637</v>
       </c>
       <c r="B280" t="n">
-        <v>9.238255500793457</v>
+        <v>9.238256454467773</v>
       </c>
       <c r="C280" t="n">
-        <v>9.297966052702654</v>
+        <v>9.297967012540948</v>
       </c>
       <c r="D280" t="n">
-        <v>8.632607298512305</v>
+        <v>8.632608189664953</v>
       </c>
       <c r="E280" t="n">
-        <v>8.999408345656759</v>
+        <v>8.999409274674644</v>
       </c>
       <c r="F280" t="n">
         <v>2645230</v>
@@ -6112,16 +6112,16 @@
         <v>44644</v>
       </c>
       <c r="B285" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C285" t="n">
-        <v>10.66280508866036</v>
+        <v>10.66280605391772</v>
       </c>
       <c r="D285" t="n">
-        <v>10.11686994044226</v>
+        <v>10.11687085627847</v>
       </c>
       <c r="E285" t="n">
-        <v>10.27894508177519</v>
+        <v>10.27894601228337</v>
       </c>
       <c r="F285" t="n">
         <v>1712400</v>
@@ -6212,16 +6212,16 @@
         <v>44651</v>
       </c>
       <c r="B290" t="n">
-        <v>10.91018199920654</v>
+        <v>10.91018295288086</v>
       </c>
       <c r="C290" t="n">
-        <v>11.20021018678808</v>
+        <v>11.20021116581417</v>
       </c>
       <c r="D290" t="n">
-        <v>10.85046980422658</v>
+        <v>10.85047075268137</v>
       </c>
       <c r="E290" t="n">
-        <v>11.20021018678808</v>
+        <v>11.20021116581417</v>
       </c>
       <c r="F290" t="n">
         <v>1571711</v>
@@ -6232,16 +6232,16 @@
         <v>44652</v>
       </c>
       <c r="B291" t="n">
-        <v>11.2428617477417</v>
+        <v>11.24286365509033</v>
       </c>
       <c r="C291" t="n">
-        <v>11.2513912367218</v>
+        <v>11.25139314551746</v>
       </c>
       <c r="D291" t="n">
-        <v>10.77369780009099</v>
+        <v>10.77369962784609</v>
       </c>
       <c r="E291" t="n">
-        <v>10.96136304931798</v>
+        <v>10.96136490891043</v>
       </c>
       <c r="F291" t="n">
         <v>2500385</v>
@@ -6252,16 +6252,16 @@
         <v>44655</v>
       </c>
       <c r="B292" t="n">
-        <v>11.2428617477417</v>
+        <v>11.24286365509033</v>
       </c>
       <c r="C292" t="n">
-        <v>11.32816323420862</v>
+        <v>11.32816515602863</v>
       </c>
       <c r="D292" t="n">
-        <v>10.84194030859771</v>
+        <v>10.84194214793012</v>
       </c>
       <c r="E292" t="n">
-        <v>11.14902912312821</v>
+        <v>11.14903101455816</v>
       </c>
       <c r="F292" t="n">
         <v>2094330</v>
@@ -6312,16 +6312,16 @@
         <v>44658</v>
       </c>
       <c r="B295" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C295" t="n">
-        <v>10.67133540265596</v>
+        <v>10.67133636868552</v>
       </c>
       <c r="D295" t="n">
-        <v>10.38130720055572</v>
+        <v>10.38130814033029</v>
       </c>
       <c r="E295" t="n">
-        <v>10.50073077191071</v>
+        <v>10.50073172249617</v>
       </c>
       <c r="F295" t="n">
         <v>1517584</v>
@@ -6352,16 +6352,16 @@
         <v>44662</v>
       </c>
       <c r="B297" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C297" t="n">
-        <v>10.6116240292701</v>
+        <v>10.61162498989425</v>
       </c>
       <c r="D297" t="n">
-        <v>10.17658213841139</v>
+        <v>10.17658305965309</v>
       </c>
       <c r="E297" t="n">
-        <v>10.28747457118751</v>
+        <v>10.28747550246782</v>
       </c>
       <c r="F297" t="n">
         <v>2558465</v>
@@ -6372,16 +6372,16 @@
         <v>44663</v>
       </c>
       <c r="B298" t="n">
-        <v>10.55191135406494</v>
+        <v>10.55191230773926</v>
       </c>
       <c r="C298" t="n">
-        <v>10.90165173831644</v>
+        <v>10.90165272360005</v>
       </c>
       <c r="D298" t="n">
-        <v>10.40689767186506</v>
+        <v>10.40689861243314</v>
       </c>
       <c r="E298" t="n">
-        <v>10.44954841533075</v>
+        <v>10.44954935975358</v>
       </c>
       <c r="F298" t="n">
         <v>1608302</v>
@@ -6452,16 +6452,16 @@
         <v>44670</v>
       </c>
       <c r="B302" t="n">
-        <v>10.94430541992188</v>
+        <v>10.94430446624756</v>
       </c>
       <c r="C302" t="n">
-        <v>11.07225849961239</v>
+        <v>11.07225753478839</v>
       </c>
       <c r="D302" t="n">
-        <v>10.48367169436914</v>
+        <v>10.48367078083392</v>
       </c>
       <c r="E302" t="n">
-        <v>10.68839761137404</v>
+        <v>10.68839667999924</v>
       </c>
       <c r="F302" t="n">
         <v>3002225</v>
@@ -6632,16 +6632,16 @@
         <v>44684</v>
       </c>
       <c r="B311" t="n">
-        <v>11.31963443756104</v>
+        <v>11.31963348388672</v>
       </c>
       <c r="C311" t="n">
-        <v>11.52436032643616</v>
+        <v>11.52435935551378</v>
       </c>
       <c r="D311" t="n">
-        <v>11.25992306354883</v>
+        <v>11.25992211490517</v>
       </c>
       <c r="E311" t="n">
-        <v>11.38787612565832</v>
+        <v>11.38787516623467</v>
       </c>
       <c r="F311" t="n">
         <v>2034324</v>
@@ -6652,16 +6652,16 @@
         <v>44685</v>
       </c>
       <c r="B312" t="n">
-        <v>11.83144950866699</v>
+        <v>11.83144855499268</v>
       </c>
       <c r="C312" t="n">
-        <v>11.95087308479659</v>
+        <v>11.95087212149613</v>
       </c>
       <c r="D312" t="n">
-        <v>10.95283372865995</v>
+        <v>10.95283284580649</v>
       </c>
       <c r="E312" t="n">
-        <v>11.09784824779946</v>
+        <v>11.09784735325709</v>
       </c>
       <c r="F312" t="n">
         <v>3044087</v>
@@ -6692,16 +6692,16 @@
         <v>44687</v>
       </c>
       <c r="B314" t="n">
-        <v>11.52435970306396</v>
+        <v>11.52436065673828</v>
       </c>
       <c r="C314" t="n">
-        <v>11.61819232834089</v>
+        <v>11.61819328978013</v>
       </c>
       <c r="D314" t="n">
-        <v>11.20874057273858</v>
+        <v>11.20874150029449</v>
       </c>
       <c r="E314" t="n">
-        <v>11.60966201471724</v>
+        <v>11.60966297545057</v>
       </c>
       <c r="F314" t="n">
         <v>3256744</v>
@@ -6732,16 +6732,16 @@
         <v>44691</v>
       </c>
       <c r="B316" t="n">
-        <v>11.22580242156982</v>
+        <v>11.22580146789551</v>
       </c>
       <c r="C316" t="n">
-        <v>11.4049382025767</v>
+        <v>11.40493723368412</v>
       </c>
       <c r="D316" t="n">
-        <v>11.02107652149054</v>
+        <v>11.02107558520846</v>
       </c>
       <c r="E316" t="n">
-        <v>11.11490915697827</v>
+        <v>11.11490821272475</v>
       </c>
       <c r="F316" t="n">
         <v>2926103</v>
@@ -6772,16 +6772,16 @@
         <v>44693</v>
       </c>
       <c r="B318" t="n">
-        <v>11.47317790985107</v>
+        <v>11.47317886352539</v>
       </c>
       <c r="C318" t="n">
-        <v>11.6864341029214</v>
+        <v>11.68643507432202</v>
       </c>
       <c r="D318" t="n">
-        <v>11.06372615108936</v>
+        <v>11.06372707072919</v>
       </c>
       <c r="E318" t="n">
-        <v>11.08078760305155</v>
+        <v>11.08078852410957</v>
       </c>
       <c r="F318" t="n">
         <v>2138727</v>
@@ -6792,16 +6792,16 @@
         <v>44694</v>
       </c>
       <c r="B319" t="n">
-        <v>11.82291984558105</v>
+        <v>11.82291889190674</v>
       </c>
       <c r="C319" t="n">
-        <v>12.07882681602652</v>
+        <v>12.07882584170994</v>
       </c>
       <c r="D319" t="n">
-        <v>11.45611960723421</v>
+        <v>11.45611868314717</v>
       </c>
       <c r="E319" t="n">
-        <v>11.53289161590952</v>
+        <v>11.5328906856298</v>
       </c>
       <c r="F319" t="n">
         <v>2912723</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381214141846</v>
+        <v>11.93381404876709</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470540028707</v>
+        <v>12.04470732535947</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908542732132</v>
+        <v>11.72908730194904</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81438856843816</v>
+        <v>11.81439045669965</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6932,16 +6932,16 @@
         <v>44705</v>
       </c>
       <c r="B326" t="n">
-        <v>12.2664909362793</v>
+        <v>12.26649188995361</v>
       </c>
       <c r="C326" t="n">
-        <v>12.62476165062991</v>
+        <v>12.62476263215845</v>
       </c>
       <c r="D326" t="n">
-        <v>12.02764461796216</v>
+        <v>12.02764555306706</v>
       </c>
       <c r="E326" t="n">
-        <v>12.53092902118688</v>
+        <v>12.53092999542028</v>
       </c>
       <c r="F326" t="n">
         <v>3539137</v>
@@ -6952,16 +6952,16 @@
         <v>44706</v>
       </c>
       <c r="B327" t="n">
-        <v>12.36885356903076</v>
+        <v>12.36885452270508</v>
       </c>
       <c r="C327" t="n">
-        <v>12.51386807884551</v>
+        <v>12.51386904370087</v>
       </c>
       <c r="D327" t="n">
-        <v>12.08735568777263</v>
+        <v>12.08735661974265</v>
       </c>
       <c r="E327" t="n">
-        <v>12.21530957001115</v>
+        <v>12.21531051184678</v>
       </c>
       <c r="F327" t="n">
         <v>1655537</v>
@@ -7012,16 +7012,16 @@
         <v>44711</v>
       </c>
       <c r="B330" t="n">
-        <v>12.73565483093262</v>
+        <v>12.73565578460693</v>
       </c>
       <c r="C330" t="n">
-        <v>13.33277185998338</v>
+        <v>13.33277285837116</v>
       </c>
       <c r="D330" t="n">
-        <v>12.73565483093262</v>
+        <v>12.73565578460693</v>
       </c>
       <c r="E330" t="n">
-        <v>13.26453017296089</v>
+        <v>13.26453116623858</v>
       </c>
       <c r="F330" t="n">
         <v>1851063</v>
@@ -7092,16 +7092,16 @@
         <v>44715</v>
       </c>
       <c r="B334" t="n">
-        <v>12.44562721252441</v>
+        <v>12.4456262588501</v>
       </c>
       <c r="C334" t="n">
-        <v>12.51386890273903</v>
+        <v>12.51386794383554</v>
       </c>
       <c r="D334" t="n">
-        <v>12.34326344032753</v>
+        <v>12.34326249449706</v>
       </c>
       <c r="E334" t="n">
-        <v>12.44562721252441</v>
+        <v>12.4456262588501</v>
       </c>
       <c r="F334" t="n">
         <v>1748789</v>
@@ -7112,16 +7112,16 @@
         <v>44718</v>
       </c>
       <c r="B335" t="n">
-        <v>12.36885356903076</v>
+        <v>12.36885452270508</v>
       </c>
       <c r="C335" t="n">
-        <v>12.65888258866027</v>
+        <v>12.65888356469666</v>
       </c>
       <c r="D335" t="n">
-        <v>12.19824894243491</v>
+        <v>12.19824988295512</v>
       </c>
       <c r="E335" t="n">
-        <v>12.65888258866027</v>
+        <v>12.65888356469666</v>
       </c>
       <c r="F335" t="n">
         <v>1740275</v>
@@ -7132,16 +7132,16 @@
         <v>44719</v>
       </c>
       <c r="B336" t="n">
-        <v>12.0276460647583</v>
+        <v>12.02764511108398</v>
       </c>
       <c r="C336" t="n">
-        <v>12.37738568259315</v>
+        <v>12.37738470118792</v>
       </c>
       <c r="D336" t="n">
-        <v>11.87410204341212</v>
+        <v>11.87410110191233</v>
       </c>
       <c r="E336" t="n">
-        <v>12.36885536756466</v>
+        <v>12.36885438683579</v>
       </c>
       <c r="F336" t="n">
         <v>3370370</v>
@@ -7152,16 +7152,16 @@
         <v>44720</v>
       </c>
       <c r="B337" t="n">
-        <v>12.0276460647583</v>
+        <v>12.02764511108398</v>
       </c>
       <c r="C337" t="n">
-        <v>12.14706965057388</v>
+        <v>12.14706868743044</v>
       </c>
       <c r="D337" t="n">
-        <v>11.80586034776752</v>
+        <v>11.80585941167863</v>
       </c>
       <c r="E337" t="n">
-        <v>11.96793385955882</v>
+        <v>11.9679329106191</v>
       </c>
       <c r="F337" t="n">
         <v>2224783</v>
@@ -7192,16 +7192,16 @@
         <v>44722</v>
       </c>
       <c r="B339" t="n">
-        <v>11.64378547668457</v>
+        <v>11.64378356933594</v>
       </c>
       <c r="C339" t="n">
-        <v>12.0788274310515</v>
+        <v>12.07882545243938</v>
       </c>
       <c r="D339" t="n">
-        <v>11.42199892958898</v>
+        <v>11.42199705857082</v>
       </c>
       <c r="E339" t="n">
-        <v>12.06176762515317</v>
+        <v>12.06176564933559</v>
       </c>
       <c r="F339" t="n">
         <v>2898634</v>
@@ -7212,16 +7212,16 @@
         <v>44725</v>
       </c>
       <c r="B340" t="n">
-        <v>10.7225170135498</v>
+        <v>10.72251892089844</v>
       </c>
       <c r="C340" t="n">
-        <v>11.50729928449115</v>
+        <v>11.50730133143885</v>
       </c>
       <c r="D340" t="n">
-        <v>10.57750332848451</v>
+        <v>10.57750521003774</v>
       </c>
       <c r="E340" t="n">
-        <v>11.234331717334</v>
+        <v>11.23433371572554</v>
       </c>
       <c r="F340" t="n">
         <v>3958469</v>
@@ -7232,16 +7232,16 @@
         <v>44726</v>
       </c>
       <c r="B341" t="n">
-        <v>10.69692707061768</v>
+        <v>10.69692611694336</v>
       </c>
       <c r="C341" t="n">
-        <v>10.94430454411216</v>
+        <v>10.94430356838314</v>
       </c>
       <c r="D341" t="n">
-        <v>10.57750431574103</v>
+        <v>10.57750337271373</v>
       </c>
       <c r="E341" t="n">
-        <v>10.79076053093742</v>
+        <v>10.79075956889747</v>
       </c>
       <c r="F341" t="n">
         <v>2253062</v>
@@ -7272,16 +7272,16 @@
         <v>44729</v>
       </c>
       <c r="B343" t="n">
-        <v>10.66280460357666</v>
+        <v>10.66280555725098</v>
       </c>
       <c r="C343" t="n">
-        <v>10.69692585800674</v>
+        <v>10.69692681473284</v>
       </c>
       <c r="D343" t="n">
-        <v>10.29600441678626</v>
+        <v>10.2960053376542</v>
       </c>
       <c r="E343" t="n">
-        <v>10.69692585800674</v>
+        <v>10.69692681473284</v>
       </c>
       <c r="F343" t="n">
         <v>2862346</v>
@@ -7292,16 +7292,16 @@
         <v>44732</v>
       </c>
       <c r="B344" t="n">
-        <v>10.38130760192871</v>
+        <v>10.38130664825439</v>
       </c>
       <c r="C344" t="n">
-        <v>10.93577391016304</v>
+        <v>10.93577290555292</v>
       </c>
       <c r="D344" t="n">
-        <v>10.33012654055963</v>
+        <v>10.33012559158704</v>
       </c>
       <c r="E344" t="n">
-        <v>10.93577391016304</v>
+        <v>10.93577290555292</v>
       </c>
       <c r="F344" t="n">
         <v>1404768</v>
@@ -7412,16 +7412,16 @@
         <v>44740</v>
       </c>
       <c r="B350" t="n">
-        <v>10.23629188537598</v>
+        <v>10.23629283905029</v>
       </c>
       <c r="C350" t="n">
-        <v>10.81634906872219</v>
+        <v>10.81635007643811</v>
       </c>
       <c r="D350" t="n">
-        <v>10.18511082999487</v>
+        <v>10.18511177890085</v>
       </c>
       <c r="E350" t="n">
-        <v>10.70545582004938</v>
+        <v>10.70545681743382</v>
       </c>
       <c r="F350" t="n">
         <v>2763519</v>
@@ -7492,16 +7492,16 @@
         <v>44746</v>
       </c>
       <c r="B354" t="n">
-        <v>9.65623664855957</v>
+        <v>9.656235694885254</v>
       </c>
       <c r="C354" t="n">
-        <v>10.02303686592241</v>
+        <v>10.02303587602198</v>
       </c>
       <c r="D354" t="n">
-        <v>9.65623664855957</v>
+        <v>9.656235694885254</v>
       </c>
       <c r="E354" t="n">
-        <v>9.920674743266868</v>
+        <v>9.920673763475978</v>
       </c>
       <c r="F354" t="n">
         <v>1779400</v>
@@ -7512,16 +7512,16 @@
         <v>44747</v>
       </c>
       <c r="B355" t="n">
-        <v>9.622115135192871</v>
+        <v>9.622116088867188</v>
       </c>
       <c r="C355" t="n">
-        <v>9.681827333833224</v>
+        <v>9.681828293425781</v>
       </c>
       <c r="D355" t="n">
-        <v>9.178542925352392</v>
+        <v>9.178543835063046</v>
       </c>
       <c r="E355" t="n">
-        <v>9.681827333833224</v>
+        <v>9.681828293425781</v>
       </c>
       <c r="F355" t="n">
         <v>3899578</v>
@@ -7532,16 +7532,16 @@
         <v>44748</v>
       </c>
       <c r="B356" t="n">
-        <v>9.647706031799316</v>
+        <v>9.647706985473633</v>
       </c>
       <c r="C356" t="n">
-        <v>9.869492547961359</v>
+        <v>9.869493523559241</v>
       </c>
       <c r="D356" t="n">
-        <v>9.400329398067255</v>
+        <v>9.400330327288428</v>
       </c>
       <c r="E356" t="n">
-        <v>9.681827288003719</v>
+        <v>9.681828245050916</v>
       </c>
       <c r="F356" t="n">
         <v>2475348</v>
@@ -7552,16 +7552,16 @@
         <v>44749</v>
       </c>
       <c r="B357" t="n">
-        <v>9.912142753601074</v>
+        <v>9.912143707275391</v>
       </c>
       <c r="C357" t="n">
-        <v>10.1168694550903</v>
+        <v>10.11687042846193</v>
       </c>
       <c r="D357" t="n">
-        <v>9.630645703584392</v>
+        <v>9.630646630175109</v>
       </c>
       <c r="E357" t="n">
-        <v>9.647705506173859</v>
+        <v>9.647706434405947</v>
       </c>
       <c r="F357" t="n">
         <v>2588468</v>
@@ -7572,16 +7572,16 @@
         <v>44750</v>
       </c>
       <c r="B358" t="n">
-        <v>9.784191131591797</v>
+        <v>9.78419017791748</v>
       </c>
       <c r="C358" t="n">
-        <v>10.19364294535647</v>
+        <v>10.19364195177249</v>
       </c>
       <c r="D358" t="n">
-        <v>9.724478927744158</v>
+        <v>9.724477979890045</v>
       </c>
       <c r="E358" t="n">
-        <v>9.86949345536221</v>
+        <v>9.869492493373395</v>
       </c>
       <c r="F358" t="n">
         <v>1378414</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.110300064086914</v>
+        <v>9.11030101776123</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707417904730018</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076179633609632</v>
+        <v>9.076180583712192</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707417904730018</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7612,16 +7612,16 @@
         <v>44754</v>
       </c>
       <c r="B360" t="n">
-        <v>9.22972583770752</v>
+        <v>9.229724884033203</v>
       </c>
       <c r="C360" t="n">
-        <v>9.289437218413942</v>
+        <v>9.289436258569864</v>
       </c>
       <c r="D360" t="n">
-        <v>8.879985394760249</v>
+        <v>8.879984477223353</v>
       </c>
       <c r="E360" t="n">
-        <v>9.22972583770752</v>
+        <v>9.229724884033203</v>
       </c>
       <c r="F360" t="n">
         <v>1719496</v>
@@ -7632,16 +7632,16 @@
         <v>44755</v>
       </c>
       <c r="B361" t="n">
-        <v>9.255315780639648</v>
+        <v>9.255314826965332</v>
       </c>
       <c r="C361" t="n">
-        <v>9.383269679221847</v>
+        <v>9.383268712363071</v>
       </c>
       <c r="D361" t="n">
-        <v>9.050590697324836</v>
+        <v>9.050589764745537</v>
       </c>
       <c r="E361" t="n">
-        <v>9.204134715956785</v>
+        <v>9.204133767556202</v>
       </c>
       <c r="F361" t="n">
         <v>1870727</v>
@@ -7652,16 +7652,16 @@
         <v>44756</v>
       </c>
       <c r="B362" t="n">
-        <v>9.383269309997559</v>
+        <v>9.383268356323242</v>
       </c>
       <c r="C362" t="n">
-        <v>9.485632259918743</v>
+        <v>9.485631295840706</v>
       </c>
       <c r="D362" t="n">
-        <v>9.067650145691958</v>
+        <v>9.06764922409579</v>
       </c>
       <c r="E362" t="n">
-        <v>9.204134353781315</v>
+        <v>9.204133418313491</v>
       </c>
       <c r="F362" t="n">
         <v>823562</v>
@@ -7712,16 +7712,16 @@
         <v>44761</v>
       </c>
       <c r="B365" t="n">
-        <v>9.767129898071289</v>
+        <v>9.767128944396973</v>
       </c>
       <c r="C365" t="n">
-        <v>9.929205045339851</v>
+        <v>9.929204075840321</v>
       </c>
       <c r="D365" t="n">
-        <v>9.562404828429376</v>
+        <v>9.562403894744662</v>
       </c>
       <c r="E365" t="n">
-        <v>9.562404828429376</v>
+        <v>9.562403894744662</v>
       </c>
       <c r="F365" t="n">
         <v>2310433</v>
@@ -7752,16 +7752,16 @@
         <v>44763</v>
       </c>
       <c r="B367" t="n">
-        <v>9.963324546813965</v>
+        <v>9.963325500488281</v>
       </c>
       <c r="C367" t="n">
-        <v>10.1936413624377</v>
+        <v>10.19364233815759</v>
       </c>
       <c r="D367" t="n">
-        <v>9.94626391979247</v>
+        <v>9.946264871833769</v>
       </c>
       <c r="E367" t="n">
-        <v>10.02303591680597</v>
+        <v>10.02303687619577</v>
       </c>
       <c r="F367" t="n">
         <v>1242590</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.50926113128662</v>
+        <v>10.5092601776123</v>
       </c>
       <c r="C371" t="n">
-        <v>10.61162407509244</v>
+        <v>10.61162311212909</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421841396606</v>
+        <v>10.07421749977017</v>
       </c>
       <c r="E371" t="n">
-        <v>10.12539947357733</v>
+        <v>10.12539855473696</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7892,16 +7892,16 @@
         <v>44774</v>
       </c>
       <c r="B374" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845264434814</v>
       </c>
       <c r="C374" t="n">
-        <v>11.77173801596846</v>
+        <v>11.77173701970006</v>
       </c>
       <c r="D374" t="n">
-        <v>11.09784813756763</v>
+        <v>11.09784719833203</v>
       </c>
       <c r="E374" t="n">
-        <v>11.64378412677316</v>
+        <v>11.64378314133378</v>
       </c>
       <c r="F374" t="n">
         <v>4838693</v>
@@ -7912,16 +7912,16 @@
         <v>44775</v>
       </c>
       <c r="B375" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845264434814</v>
       </c>
       <c r="C375" t="n">
-        <v>11.49876960907404</v>
+        <v>11.49876863590757</v>
       </c>
       <c r="D375" t="n">
-        <v>11.24286265526674</v>
+        <v>11.24286170375824</v>
       </c>
       <c r="E375" t="n">
-        <v>11.39640666263446</v>
+        <v>11.39640569813119</v>
       </c>
       <c r="F375" t="n">
         <v>2088249</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248466491699</v>
+        <v>13.39248371124268</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634635999027</v>
+        <v>13.77634537898129</v>
       </c>
       <c r="D381" t="n">
-        <v>13.17922926709854</v>
+        <v>13.17922832861007</v>
       </c>
       <c r="E381" t="n">
-        <v>13.30718234087294</v>
+        <v>13.30718139327297</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8052,16 +8052,16 @@
         <v>44784</v>
       </c>
       <c r="B382" t="n">
-        <v>13.36689376831055</v>
+        <v>13.36689472198486</v>
       </c>
       <c r="C382" t="n">
-        <v>13.63986135430908</v>
+        <v>13.63986232745854</v>
       </c>
       <c r="D382" t="n">
-        <v>13.11951630083012</v>
+        <v>13.11951723685505</v>
       </c>
       <c r="E382" t="n">
-        <v>13.52043777775243</v>
+        <v>13.5204387423815</v>
       </c>
       <c r="F382" t="n">
         <v>2014153</v>
@@ -8072,16 +8072,16 @@
         <v>44785</v>
       </c>
       <c r="B383" t="n">
-        <v>13.75928401947021</v>
+        <v>13.75928497314453</v>
       </c>
       <c r="C383" t="n">
-        <v>13.84458633290799</v>
+        <v>13.84458729249473</v>
       </c>
       <c r="D383" t="n">
-        <v>13.47778613775057</v>
+        <v>13.47778707191389</v>
       </c>
       <c r="E383" t="n">
-        <v>13.47778613775057</v>
+        <v>13.47778707191389</v>
       </c>
       <c r="F383" t="n">
         <v>2291478</v>
@@ -8132,16 +8132,16 @@
         <v>44790</v>
       </c>
       <c r="B386" t="n">
-        <v>13.56308841705322</v>
+        <v>13.56308746337891</v>
       </c>
       <c r="C386" t="n">
-        <v>13.64839073027631</v>
+        <v>13.64838977060406</v>
       </c>
       <c r="D386" t="n">
-        <v>13.23893896713886</v>
+        <v>13.23893803625678</v>
       </c>
       <c r="E386" t="n">
-        <v>13.64839073027631</v>
+        <v>13.64838977060406</v>
       </c>
       <c r="F386" t="n">
         <v>4054357</v>
@@ -8152,16 +8152,16 @@
         <v>44791</v>
       </c>
       <c r="B387" t="n">
-        <v>13.63986206054688</v>
+        <v>13.63986110687256</v>
       </c>
       <c r="C387" t="n">
-        <v>14.13461537195818</v>
+        <v>14.13461438369162</v>
       </c>
       <c r="D387" t="n">
-        <v>13.23894056286585</v>
+        <v>13.23893963722324</v>
       </c>
       <c r="E387" t="n">
-        <v>13.64839237535569</v>
+        <v>13.64839142108495</v>
       </c>
       <c r="F387" t="n">
         <v>3074090</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066959381104</v>
+        <v>12.88066864013672</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801884508153</v>
+        <v>12.83801789456504</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8212,16 +8212,16 @@
         <v>44796</v>
       </c>
       <c r="B390" t="n">
-        <v>12.29208183288574</v>
+        <v>12.29208278656006</v>
       </c>
       <c r="C390" t="n">
-        <v>12.6418222319422</v>
+        <v>12.64182321275093</v>
       </c>
       <c r="D390" t="n">
-        <v>12.25796140158548</v>
+        <v>12.25796235261258</v>
       </c>
       <c r="E390" t="n">
-        <v>12.6418222319422</v>
+        <v>12.64182321275093</v>
       </c>
       <c r="F390" t="n">
         <v>5845922</v>
@@ -8232,16 +8232,16 @@
         <v>44797</v>
       </c>
       <c r="B391" t="n">
-        <v>12.42856597900391</v>
+        <v>12.42856693267822</v>
       </c>
       <c r="C391" t="n">
-        <v>12.57358049130923</v>
+        <v>12.57358145611087</v>
       </c>
       <c r="D391" t="n">
-        <v>12.1300074650419</v>
+        <v>12.13000839580709</v>
       </c>
       <c r="E391" t="n">
-        <v>12.2920817806332</v>
+        <v>12.29208272383475</v>
       </c>
       <c r="F391" t="n">
         <v>4991546</v>
@@ -8292,16 +8292,16 @@
         <v>44802</v>
       </c>
       <c r="B394" t="n">
-        <v>12.25796222686768</v>
+        <v>12.25796031951904</v>
       </c>
       <c r="C394" t="n">
-        <v>12.40297592496939</v>
+        <v>12.40297399505652</v>
       </c>
       <c r="D394" t="n">
-        <v>12.04470601240437</v>
+        <v>12.04470413823857</v>
       </c>
       <c r="E394" t="n">
-        <v>12.18118939596089</v>
+        <v>12.18118750055817</v>
       </c>
       <c r="F394" t="n">
         <v>4196061</v>
@@ -8372,16 +8372,16 @@
         <v>44806</v>
       </c>
       <c r="B398" t="n">
-        <v>12.42003631591797</v>
+        <v>12.42003726959229</v>
       </c>
       <c r="C398" t="n">
-        <v>12.7015333734898</v>
+        <v>12.70153434877891</v>
       </c>
       <c r="D398" t="n">
-        <v>12.36885360844292</v>
+        <v>12.36885455818716</v>
       </c>
       <c r="E398" t="n">
-        <v>12.52239843253504</v>
+        <v>12.52239939406925</v>
       </c>
       <c r="F398" t="n">
         <v>3090207</v>
@@ -8492,16 +8492,16 @@
         <v>44817</v>
       </c>
       <c r="B404" t="n">
-        <v>11.82735919952393</v>
+        <v>11.82735824584961</v>
       </c>
       <c r="C404" t="n">
-        <v>12.11854676809748</v>
+        <v>12.11854579094386</v>
       </c>
       <c r="D404" t="n">
-        <v>11.7417155059729</v>
+        <v>11.74171455920428</v>
       </c>
       <c r="E404" t="n">
-        <v>12.11854676809748</v>
+        <v>12.11854579094386</v>
       </c>
       <c r="F404" t="n">
         <v>3904244</v>
@@ -8572,16 +8572,16 @@
         <v>44823</v>
       </c>
       <c r="B408" t="n">
-        <v>12.39260673522949</v>
+        <v>12.39260578155518</v>
       </c>
       <c r="C408" t="n">
-        <v>12.60671391874965</v>
+        <v>12.6067129485987</v>
       </c>
       <c r="D408" t="n">
-        <v>12.19562614739096</v>
+        <v>12.19562520887531</v>
       </c>
       <c r="E408" t="n">
-        <v>12.34122035151799</v>
+        <v>12.34121940179812</v>
       </c>
       <c r="F408" t="n">
         <v>1221893</v>
@@ -8592,16 +8592,16 @@
         <v>44824</v>
       </c>
       <c r="B409" t="n">
-        <v>11.88731098175049</v>
+        <v>11.88731002807617</v>
       </c>
       <c r="C409" t="n">
-        <v>12.52107174356088</v>
+        <v>12.52107073904231</v>
       </c>
       <c r="D409" t="n">
-        <v>11.87018108678033</v>
+        <v>11.87018013448028</v>
       </c>
       <c r="E409" t="n">
-        <v>12.4439921636954</v>
+        <v>12.44399116536064</v>
       </c>
       <c r="F409" t="n">
         <v>1700434</v>
@@ -8772,16 +8772,16 @@
         <v>44837</v>
       </c>
       <c r="B418" t="n">
-        <v>12.41829776763916</v>
+        <v>12.41829967498779</v>
       </c>
       <c r="C418" t="n">
-        <v>12.6238424558075</v>
+        <v>12.62384439472611</v>
       </c>
       <c r="D418" t="n">
-        <v>12.01577333738928</v>
+        <v>12.01577518291347</v>
       </c>
       <c r="E418" t="n">
-        <v>12.06715971557718</v>
+        <v>12.06716156899389</v>
       </c>
       <c r="F418" t="n">
         <v>3117277</v>
@@ -8792,16 +8792,16 @@
         <v>44838</v>
       </c>
       <c r="B419" t="n">
-        <v>12.84651756286621</v>
+        <v>12.84651660919189</v>
       </c>
       <c r="C419" t="n">
-        <v>12.9407245645283</v>
+        <v>12.94072360386043</v>
       </c>
       <c r="D419" t="n">
-        <v>12.55532913659232</v>
+        <v>12.55532820453467</v>
       </c>
       <c r="E419" t="n">
-        <v>12.5981505759463</v>
+        <v>12.59814964070976</v>
       </c>
       <c r="F419" t="n">
         <v>4425287</v>
@@ -8812,16 +8812,16 @@
         <v>44839</v>
       </c>
       <c r="B420" t="n">
-        <v>12.84651756286621</v>
+        <v>12.84651660919189</v>
       </c>
       <c r="C420" t="n">
-        <v>13.13770516455673</v>
+        <v>13.1377041892658</v>
       </c>
       <c r="D420" t="n">
-        <v>12.56389408412982</v>
+        <v>12.56389315143634</v>
       </c>
       <c r="E420" t="n">
-        <v>12.84651756286621</v>
+        <v>12.84651660919189</v>
       </c>
       <c r="F420" t="n">
         <v>2792192</v>
@@ -8972,16 +8972,16 @@
         <v>44852</v>
       </c>
       <c r="B428" t="n">
-        <v>12.84651756286621</v>
+        <v>12.84651660919189</v>
       </c>
       <c r="C428" t="n">
-        <v>13.16339753341909</v>
+        <v>13.16339655622087</v>
       </c>
       <c r="D428" t="n">
-        <v>12.6581010857919</v>
+        <v>12.65810014610488</v>
       </c>
       <c r="E428" t="n">
-        <v>12.80369529892885</v>
+        <v>12.80369434843349</v>
       </c>
       <c r="F428" t="n">
         <v>2211886</v>
@@ -8992,16 +8992,16 @@
         <v>44853</v>
       </c>
       <c r="B429" t="n">
-        <v>12.95785140991211</v>
+        <v>12.95785045623779</v>
       </c>
       <c r="C429" t="n">
-        <v>13.02636685988985</v>
+        <v>13.02636590117292</v>
       </c>
       <c r="D429" t="n">
-        <v>12.71805022103153</v>
+        <v>12.71804928500614</v>
       </c>
       <c r="E429" t="n">
-        <v>12.80369391506624</v>
+        <v>12.80369297273763</v>
       </c>
       <c r="F429" t="n">
         <v>1282165</v>
@@ -9032,16 +9032,16 @@
         <v>44855</v>
       </c>
       <c r="B431" t="n">
-        <v>13.08631706237793</v>
+        <v>13.08631801605225</v>
       </c>
       <c r="C431" t="n">
-        <v>13.26616856834072</v>
+        <v>13.26616953512184</v>
       </c>
       <c r="D431" t="n">
-        <v>12.58958480281398</v>
+        <v>12.58958572028859</v>
       </c>
       <c r="E431" t="n">
-        <v>12.74374311869877</v>
+        <v>12.74374404740777</v>
       </c>
       <c r="F431" t="n">
         <v>1434409</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805000305176</v>
+        <v>12.71805095672607</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775301708247</v>
+        <v>13.07775399772944</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235763740665</v>
+        <v>12.69235858915441</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87220831983874</v>
+        <v>12.87220928507275</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9132,16 +9132,16 @@
         <v>44862</v>
       </c>
       <c r="B436" t="n">
-        <v>13.06918811798096</v>
+        <v>13.06918907165527</v>
       </c>
       <c r="C436" t="n">
-        <v>13.48027751395823</v>
+        <v>13.48027849763024</v>
       </c>
       <c r="D436" t="n">
-        <v>12.45255567318159</v>
+        <v>12.4525565818595</v>
       </c>
       <c r="E436" t="n">
-        <v>13.15483181085816</v>
+        <v>13.154832770782</v>
       </c>
       <c r="F436" t="n">
         <v>6048388</v>
@@ -9152,16 +9152,16 @@
         <v>44865</v>
       </c>
       <c r="B437" t="n">
-        <v>13.80572319030762</v>
+        <v>13.8057222366333</v>
       </c>
       <c r="C437" t="n">
-        <v>14.07121842205234</v>
+        <v>14.0712174500381</v>
       </c>
       <c r="D437" t="n">
-        <v>12.50394269867501</v>
+        <v>12.50394183492532</v>
       </c>
       <c r="E437" t="n">
-        <v>12.50394269867501</v>
+        <v>12.50394183492532</v>
       </c>
       <c r="F437" t="n">
         <v>7903691</v>
@@ -9172,16 +9172,16 @@
         <v>44866</v>
       </c>
       <c r="B438" t="n">
-        <v>13.61730575561523</v>
+        <v>13.61730670928955</v>
       </c>
       <c r="C438" t="n">
-        <v>14.01126607789819</v>
+        <v>14.01126705916312</v>
       </c>
       <c r="D438" t="n">
-        <v>13.53166288847033</v>
+        <v>13.53166383614674</v>
       </c>
       <c r="E438" t="n">
-        <v>13.70295027192667</v>
+        <v>13.70295123159901</v>
       </c>
       <c r="F438" t="n">
         <v>3366744</v>
@@ -9212,16 +9212,16 @@
         <v>44869</v>
       </c>
       <c r="B440" t="n">
-        <v>14.01126670837402</v>
+        <v>14.01126766204834</v>
       </c>
       <c r="C440" t="n">
-        <v>14.29389098625276</v>
+        <v>14.29389195916385</v>
       </c>
       <c r="D440" t="n">
-        <v>13.80572200389402</v>
+        <v>13.80572294357798</v>
       </c>
       <c r="E440" t="n">
-        <v>14.13973183945529</v>
+        <v>14.13973280187356</v>
       </c>
       <c r="F440" t="n">
         <v>3663661</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.4031982421875</v>
+        <v>13.40319728851318</v>
       </c>
       <c r="C441" t="n">
-        <v>14.03695980853268</v>
+        <v>14.03695880976449</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037762903356</v>
+        <v>13.36037667840605</v>
       </c>
       <c r="E441" t="n">
-        <v>13.93418868779654</v>
+        <v>13.9341876963408</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9352,16 +9352,16 @@
         <v>44881</v>
       </c>
       <c r="B447" t="n">
-        <v>11.26211261749268</v>
+        <v>11.26211357116699</v>
       </c>
       <c r="C447" t="n">
-        <v>12.15280359178205</v>
+        <v>12.15280462087997</v>
       </c>
       <c r="D447" t="n">
-        <v>11.15934067714197</v>
+        <v>11.15934162211358</v>
       </c>
       <c r="E447" t="n">
-        <v>12.06716072044812</v>
+        <v>12.06716174229381</v>
       </c>
       <c r="F447" t="n">
         <v>3929079</v>
@@ -9392,16 +9392,16 @@
         <v>44883</v>
       </c>
       <c r="B449" t="n">
-        <v>10.92810344696045</v>
+        <v>10.92810249328613</v>
       </c>
       <c r="C449" t="n">
-        <v>11.38201432087386</v>
+        <v>11.38201332758762</v>
       </c>
       <c r="D449" t="n">
-        <v>10.91953932422152</v>
+        <v>10.91953837129458</v>
       </c>
       <c r="E449" t="n">
-        <v>11.1336473401948</v>
+        <v>11.13364636858307</v>
       </c>
       <c r="F449" t="n">
         <v>5719164</v>
@@ -9412,16 +9412,16 @@
         <v>44886</v>
       </c>
       <c r="B450" t="n">
-        <v>11.25354766845703</v>
+        <v>11.25354671478271</v>
       </c>
       <c r="C450" t="n">
-        <v>11.33062724214222</v>
+        <v>11.33062628193585</v>
       </c>
       <c r="D450" t="n">
-        <v>10.80820259369247</v>
+        <v>10.80820167775862</v>
       </c>
       <c r="E450" t="n">
-        <v>10.98805328312464</v>
+        <v>10.98805235194947</v>
       </c>
       <c r="F450" t="n">
         <v>4991964</v>
@@ -9432,16 +9432,16 @@
         <v>44887</v>
       </c>
       <c r="B451" t="n">
-        <v>10.98805236816406</v>
+        <v>10.98805332183838</v>
       </c>
       <c r="C451" t="n">
-        <v>11.33919042015788</v>
+        <v>11.33919140430814</v>
       </c>
       <c r="D451" t="n">
-        <v>10.89384455789337</v>
+        <v>10.89384550339121</v>
       </c>
       <c r="E451" t="n">
-        <v>11.27923992047805</v>
+        <v>11.2792408994251</v>
       </c>
       <c r="F451" t="n">
         <v>2547672</v>
@@ -9472,16 +9472,16 @@
         <v>44889</v>
       </c>
       <c r="B453" t="n">
-        <v>11.53617191314697</v>
+        <v>11.53617095947266</v>
       </c>
       <c r="C453" t="n">
-        <v>11.81879538685529</v>
+        <v>11.81879440981701</v>
       </c>
       <c r="D453" t="n">
-        <v>11.05656866749802</v>
+        <v>11.05656775347163</v>
       </c>
       <c r="E453" t="n">
-        <v>11.11651917627706</v>
+        <v>11.11651825729467</v>
       </c>
       <c r="F453" t="n">
         <v>3457606</v>
@@ -9492,16 +9492,16 @@
         <v>44890</v>
       </c>
       <c r="B454" t="n">
-        <v>10.95379638671875</v>
+        <v>10.95379543304443</v>
       </c>
       <c r="C454" t="n">
-        <v>11.54473650913719</v>
+        <v>11.54473550401364</v>
       </c>
       <c r="D454" t="n">
-        <v>10.89384587976446</v>
+        <v>10.89384493130964</v>
       </c>
       <c r="E454" t="n">
-        <v>11.51047836980616</v>
+        <v>11.51047736766524</v>
       </c>
       <c r="F454" t="n">
         <v>2880833</v>
@@ -9512,16 +9512,16 @@
         <v>44893</v>
       </c>
       <c r="B455" t="n">
-        <v>10.96236038208008</v>
+        <v>10.96235847473145</v>
       </c>
       <c r="C455" t="n">
-        <v>11.18503333764837</v>
+        <v>11.18503139155672</v>
       </c>
       <c r="D455" t="n">
-        <v>10.84245936956254</v>
+        <v>10.84245748307556</v>
       </c>
       <c r="E455" t="n">
-        <v>10.95379625963835</v>
+        <v>10.95379435377979</v>
       </c>
       <c r="F455" t="n">
         <v>2642270</v>
@@ -9552,16 +9552,16 @@
         <v>44895</v>
       </c>
       <c r="B457" t="n">
-        <v>11.35631942749023</v>
+        <v>11.35632038116455</v>
       </c>
       <c r="C457" t="n">
-        <v>11.57042825153101</v>
+        <v>11.57042922318563</v>
       </c>
       <c r="D457" t="n">
-        <v>11.04800361142147</v>
+        <v>11.04800453920422</v>
       </c>
       <c r="E457" t="n">
-        <v>11.34775530541193</v>
+        <v>11.34775625836705</v>
       </c>
       <c r="F457" t="n">
         <v>6904107</v>
@@ -9592,16 +9592,16 @@
         <v>44897</v>
       </c>
       <c r="B459" t="n">
-        <v>11.32206344604492</v>
+        <v>11.32206249237061</v>
       </c>
       <c r="C459" t="n">
-        <v>11.47622094868901</v>
+        <v>11.47621998202977</v>
       </c>
       <c r="D459" t="n">
-        <v>11.07369647340539</v>
+        <v>11.07369554065139</v>
       </c>
       <c r="E459" t="n">
-        <v>11.19359748620264</v>
+        <v>11.1935965433492</v>
       </c>
       <c r="F459" t="n">
         <v>2110020</v>
@@ -9612,16 +9612,16 @@
         <v>44900</v>
       </c>
       <c r="B460" t="n">
-        <v>10.65404319763184</v>
+        <v>10.65404415130615</v>
       </c>
       <c r="C460" t="n">
-        <v>11.26211148072586</v>
+        <v>11.26211248883013</v>
       </c>
       <c r="D460" t="n">
-        <v>10.56839868577602</v>
+        <v>10.56839963178404</v>
       </c>
       <c r="E460" t="n">
-        <v>11.26211148072586</v>
+        <v>11.26211248883013</v>
       </c>
       <c r="F460" t="n">
         <v>2438739</v>
@@ -9632,16 +9632,16 @@
         <v>44901</v>
       </c>
       <c r="B461" t="n">
-        <v>10.64547920227051</v>
+        <v>10.64548015594482</v>
       </c>
       <c r="C461" t="n">
-        <v>10.8852812182133</v>
+        <v>10.88528219337026</v>
       </c>
       <c r="D461" t="n">
-        <v>10.44849944607939</v>
+        <v>10.44850038210729</v>
       </c>
       <c r="E461" t="n">
-        <v>10.62835013345318</v>
+        <v>10.62835108559299</v>
       </c>
       <c r="F461" t="n">
         <v>3634787</v>
@@ -9672,16 +9672,16 @@
         <v>44903</v>
       </c>
       <c r="B463" t="n">
-        <v>9.763351440429688</v>
+        <v>9.763352394104004</v>
       </c>
       <c r="C463" t="n">
-        <v>10.37998471849188</v>
+        <v>10.37998573239832</v>
       </c>
       <c r="D463" t="n">
-        <v>9.686272692963557</v>
+        <v>9.686273639108899</v>
       </c>
       <c r="E463" t="n">
-        <v>10.27721195575933</v>
+        <v>10.27721295962702</v>
       </c>
       <c r="F463" t="n">
         <v>6542779</v>
@@ -9712,16 +9712,16 @@
         <v>44907</v>
       </c>
       <c r="B465" t="n">
-        <v>9.506421089172363</v>
+        <v>9.50642204284668</v>
       </c>
       <c r="C465" t="n">
-        <v>10.02884567607701</v>
+        <v>10.02884668216042</v>
       </c>
       <c r="D465" t="n">
-        <v>9.420777403361539</v>
+        <v>9.42077834844417</v>
       </c>
       <c r="E465" t="n">
-        <v>9.57493570798774</v>
+        <v>9.57493666853537</v>
       </c>
       <c r="F465" t="n">
         <v>6343387</v>
@@ -9812,16 +9812,16 @@
         <v>44914</v>
       </c>
       <c r="B470" t="n">
-        <v>9.951767921447754</v>
+        <v>9.951766967773438</v>
       </c>
       <c r="C470" t="n">
-        <v>10.03741162283501</v>
+        <v>10.03741066095349</v>
       </c>
       <c r="D470" t="n">
-        <v>9.686273519105638</v>
+        <v>9.686272590873555</v>
       </c>
       <c r="E470" t="n">
-        <v>9.840431027185991</v>
+        <v>9.840430084181047</v>
       </c>
       <c r="F470" t="n">
         <v>3753211</v>
@@ -9852,16 +9852,16 @@
         <v>44916</v>
       </c>
       <c r="B472" t="n">
-        <v>10.42280578613281</v>
+        <v>10.42280673980713</v>
       </c>
       <c r="C472" t="n">
-        <v>10.58552904653355</v>
+        <v>10.58553001509685</v>
       </c>
       <c r="D472" t="n">
-        <v>10.08879679276622</v>
+        <v>10.08879771587911</v>
       </c>
       <c r="E472" t="n">
-        <v>10.36285610942807</v>
+        <v>10.36285705761706</v>
       </c>
       <c r="F472" t="n">
         <v>3195923</v>
@@ -9952,16 +9952,16 @@
         <v>44923</v>
       </c>
       <c r="B477" t="n">
-        <v>10.96907138824463</v>
+        <v>10.96907043457031</v>
       </c>
       <c r="C477" t="n">
-        <v>11.03030234933299</v>
+        <v>11.03030139033512</v>
       </c>
       <c r="D477" t="n">
-        <v>10.4354885018964</v>
+        <v>10.43548759461291</v>
       </c>
       <c r="E477" t="n">
-        <v>10.56669662140617</v>
+        <v>10.56669570271517</v>
       </c>
       <c r="F477" t="n">
         <v>2605824</v>
@@ -9992,16 +9992,16 @@
         <v>44928</v>
       </c>
       <c r="B479" t="n">
-        <v>10.1555757522583</v>
+        <v>10.15557670593262</v>
       </c>
       <c r="C479" t="n">
-        <v>10.91658756882882</v>
+        <v>10.91658859396708</v>
       </c>
       <c r="D479" t="n">
-        <v>9.963135827664333</v>
+        <v>9.963136763267295</v>
       </c>
       <c r="E479" t="n">
-        <v>10.91658756882882</v>
+        <v>10.91658859396708</v>
       </c>
       <c r="F479" t="n">
         <v>2948980</v>
@@ -10052,16 +10052,16 @@
         <v>44931</v>
       </c>
       <c r="B482" t="n">
-        <v>10.05935668945312</v>
+        <v>10.05935573577881</v>
       </c>
       <c r="C482" t="n">
-        <v>10.33926871956802</v>
+        <v>10.33926773935673</v>
       </c>
       <c r="D482" t="n">
-        <v>9.779444659338226</v>
+        <v>9.779443732200887</v>
       </c>
       <c r="E482" t="n">
-        <v>9.796938740122757</v>
+        <v>9.796937811326897</v>
       </c>
       <c r="F482" t="n">
         <v>3524036</v>
@@ -10072,16 +10072,16 @@
         <v>44932</v>
       </c>
       <c r="B483" t="n">
-        <v>10.43548774719238</v>
+        <v>10.4354887008667</v>
       </c>
       <c r="C483" t="n">
-        <v>10.4967178616573</v>
+        <v>10.49671882092729</v>
       </c>
       <c r="D483" t="n">
-        <v>10.03311300945403</v>
+        <v>10.03311392635628</v>
       </c>
       <c r="E483" t="n">
-        <v>10.05935496833623</v>
+        <v>10.05935588763667</v>
       </c>
       <c r="F483" t="n">
         <v>2102448</v>
@@ -10172,16 +10172,16 @@
         <v>44939</v>
       </c>
       <c r="B488" t="n">
-        <v>11.24898338317871</v>
+        <v>11.24898242950439</v>
       </c>
       <c r="C488" t="n">
-        <v>11.33645714718375</v>
+        <v>11.33645618609352</v>
       </c>
       <c r="D488" t="n">
-        <v>10.94282942013715</v>
+        <v>10.94282849241817</v>
       </c>
       <c r="E488" t="n">
-        <v>11.12652230327921</v>
+        <v>11.12652135998699</v>
       </c>
       <c r="F488" t="n">
         <v>2088011</v>
@@ -10232,16 +10232,16 @@
         <v>44944</v>
       </c>
       <c r="B491" t="n">
-        <v>11.61636829376221</v>
+        <v>11.61636924743652</v>
       </c>
       <c r="C491" t="n">
-        <v>11.81755524112901</v>
+        <v>11.81755621132026</v>
       </c>
       <c r="D491" t="n">
-        <v>11.08278460488162</v>
+        <v>11.08278551475007</v>
       </c>
       <c r="E491" t="n">
-        <v>11.12652148366233</v>
+        <v>11.12652239712147</v>
       </c>
       <c r="F491" t="n">
         <v>4176830</v>
@@ -10332,16 +10332,16 @@
         <v>44951</v>
       </c>
       <c r="B496" t="n">
-        <v>12.24617099761963</v>
+        <v>12.24617195129395</v>
       </c>
       <c r="C496" t="n">
-        <v>12.44735878558682</v>
+        <v>12.44735975492869</v>
       </c>
       <c r="D496" t="n">
-        <v>11.96625901817858</v>
+        <v>11.96625995005467</v>
       </c>
       <c r="E496" t="n">
-        <v>12.10621500789911</v>
+        <v>12.10621595067431</v>
       </c>
       <c r="F496" t="n">
         <v>2519909</v>
@@ -10412,16 +10412,16 @@
         <v>44957</v>
       </c>
       <c r="B500" t="n">
-        <v>12.78850364685059</v>
+        <v>12.78850269317627</v>
       </c>
       <c r="C500" t="n">
-        <v>13.03342750793878</v>
+        <v>13.03342653599981</v>
       </c>
       <c r="D500" t="n">
-        <v>12.48234882049034</v>
+        <v>12.48234788964684</v>
       </c>
       <c r="E500" t="n">
-        <v>12.49109670281154</v>
+        <v>12.49109577131569</v>
       </c>
       <c r="F500" t="n">
         <v>4284855</v>
@@ -10472,16 +10472,16 @@
         <v>44960</v>
       </c>
       <c r="B503" t="n">
-        <v>12.57856845855713</v>
+        <v>12.57856750488281</v>
       </c>
       <c r="C503" t="n">
-        <v>12.90221819887599</v>
+        <v>12.90221722066339</v>
       </c>
       <c r="D503" t="n">
-        <v>12.42986541153535</v>
+        <v>12.42986446913531</v>
       </c>
       <c r="E503" t="n">
-        <v>12.81474527332507</v>
+        <v>12.81474430174445</v>
       </c>
       <c r="F503" t="n">
         <v>2892746</v>
@@ -10552,16 +10552,16 @@
         <v>44966</v>
       </c>
       <c r="B507" t="n">
-        <v>12.1324577331543</v>
+        <v>12.13245677947998</v>
       </c>
       <c r="C507" t="n">
-        <v>12.77975637693486</v>
+        <v>12.7797553723795</v>
       </c>
       <c r="D507" t="n">
-        <v>12.06247972901458</v>
+        <v>12.06247878084089</v>
       </c>
       <c r="E507" t="n">
-        <v>12.7622614548023</v>
+        <v>12.76226045162213</v>
       </c>
       <c r="F507" t="n">
         <v>2590377</v>
@@ -10672,16 +10672,16 @@
         <v>44974</v>
       </c>
       <c r="B513" t="n">
-        <v>12.78850364685059</v>
+        <v>12.78850269317627</v>
       </c>
       <c r="C513" t="n">
-        <v>12.85848165224856</v>
+        <v>12.85848069335579</v>
       </c>
       <c r="D513" t="n">
-        <v>12.6310527136075</v>
+        <v>12.63105177167474</v>
       </c>
       <c r="E513" t="n">
-        <v>12.84098757199671</v>
+        <v>12.84098661440852</v>
       </c>
       <c r="F513" t="n">
         <v>1180399</v>
@@ -10692,16 +10692,16 @@
         <v>44979</v>
       </c>
       <c r="B514" t="n">
-        <v>12.63979816436768</v>
+        <v>12.63979911804199</v>
       </c>
       <c r="C514" t="n">
-        <v>12.70977616096641</v>
+        <v>12.70977711992058</v>
       </c>
       <c r="D514" t="n">
-        <v>12.33364421869941</v>
+        <v>12.33364514927437</v>
       </c>
       <c r="E514" t="n">
-        <v>12.70102912194036</v>
+        <v>12.70103008023456</v>
       </c>
       <c r="F514" t="n">
         <v>1228758</v>
@@ -10732,16 +10732,16 @@
         <v>44981</v>
       </c>
       <c r="B516" t="n">
-        <v>11.80880928039551</v>
+        <v>11.80881023406982</v>
       </c>
       <c r="C516" t="n">
-        <v>12.48234817940498</v>
+        <v>12.48234918747401</v>
       </c>
       <c r="D516" t="n">
-        <v>11.69509523801289</v>
+        <v>11.69509618250371</v>
       </c>
       <c r="E516" t="n">
-        <v>12.33364513612039</v>
+        <v>12.33364613218022</v>
       </c>
       <c r="F516" t="n">
         <v>3419242</v>
@@ -10752,16 +10752,16 @@
         <v>44984</v>
       </c>
       <c r="B517" t="n">
-        <v>11.64261150360107</v>
+        <v>11.64261054992676</v>
       </c>
       <c r="C517" t="n">
-        <v>11.87004043423472</v>
+        <v>11.87003946193115</v>
       </c>
       <c r="D517" t="n">
-        <v>11.51140253755071</v>
+        <v>11.51140159462404</v>
       </c>
       <c r="E517" t="n">
-        <v>11.77382046965144</v>
+        <v>11.77381950522948</v>
       </c>
       <c r="F517" t="n">
         <v>3613283</v>
@@ -10772,16 +10772,16 @@
         <v>44985</v>
       </c>
       <c r="B518" t="n">
-        <v>11.61636829376221</v>
+        <v>11.61636924743652</v>
       </c>
       <c r="C518" t="n">
-        <v>11.86129211990972</v>
+        <v>11.86129309369166</v>
       </c>
       <c r="D518" t="n">
-        <v>11.40643430751733</v>
+        <v>11.4064352439566</v>
       </c>
       <c r="E518" t="n">
-        <v>11.71258824800656</v>
+        <v>11.7125892095803</v>
       </c>
       <c r="F518" t="n">
         <v>5639205</v>
@@ -10812,16 +10812,16 @@
         <v>44987</v>
       </c>
       <c r="B520" t="n">
-        <v>11.80880928039551</v>
+        <v>11.80881023406982</v>
       </c>
       <c r="C520" t="n">
-        <v>11.9750072452287</v>
+        <v>11.9750082123251</v>
       </c>
       <c r="D520" t="n">
-        <v>11.67760031646429</v>
+        <v>11.67760125954223</v>
       </c>
       <c r="E520" t="n">
-        <v>11.76507239762161</v>
+        <v>11.76507334776376</v>
       </c>
       <c r="F520" t="n">
         <v>2331118</v>
@@ -10852,16 +10852,16 @@
         <v>44991</v>
       </c>
       <c r="B522" t="n">
-        <v>12.1324577331543</v>
+        <v>12.13245677947998</v>
       </c>
       <c r="C522" t="n">
-        <v>12.23742558155914</v>
+        <v>12.2374246196338</v>
       </c>
       <c r="D522" t="n">
-        <v>11.68634774621477</v>
+        <v>11.68634682760701</v>
       </c>
       <c r="E522" t="n">
-        <v>11.68634774621477</v>
+        <v>11.68634682760701</v>
       </c>
       <c r="F522" t="n">
         <v>3047313</v>
@@ -11012,16 +11012,16 @@
         <v>45001</v>
       </c>
       <c r="B530" t="n">
-        <v>12.44736099243164</v>
+        <v>12.44736003875732</v>
       </c>
       <c r="C530" t="n">
-        <v>12.63105305095858</v>
+        <v>12.6310520832104</v>
       </c>
       <c r="D530" t="n">
-        <v>12.28991005498334</v>
+        <v>12.28990911337238</v>
       </c>
       <c r="E530" t="n">
-        <v>12.35114017969545</v>
+        <v>12.35113923339325</v>
       </c>
       <c r="F530" t="n">
         <v>3275478</v>
@@ -11052,16 +11052,16 @@
         <v>45005</v>
       </c>
       <c r="B532" t="n">
-        <v>11.36269760131836</v>
+        <v>11.36269855499268</v>
       </c>
       <c r="C532" t="n">
-        <v>11.90502749511903</v>
+        <v>11.90502849431124</v>
       </c>
       <c r="D532" t="n">
-        <v>11.17025768990678</v>
+        <v>11.17025862742956</v>
       </c>
       <c r="E532" t="n">
-        <v>11.73008250392448</v>
+        <v>11.73008348843351</v>
       </c>
       <c r="F532" t="n">
         <v>5506849</v>
@@ -11092,16 +11092,16 @@
         <v>45007</v>
       </c>
       <c r="B534" t="n">
-        <v>11.49390602111816</v>
+        <v>11.49390697479248</v>
       </c>
       <c r="C534" t="n">
-        <v>11.84379682944229</v>
+        <v>11.8437978121478</v>
       </c>
       <c r="D534" t="n">
-        <v>11.26647796423188</v>
+        <v>11.266478899036</v>
       </c>
       <c r="E534" t="n">
-        <v>11.26647796423188</v>
+        <v>11.266478899036</v>
       </c>
       <c r="F534" t="n">
         <v>2476497</v>
@@ -11152,16 +11152,16 @@
         <v>45012</v>
       </c>
       <c r="B537" t="n">
-        <v>11.36269760131836</v>
+        <v>11.36269855499268</v>
       </c>
       <c r="C537" t="n">
-        <v>11.52889555350197</v>
+        <v>11.52889652112532</v>
       </c>
       <c r="D537" t="n">
-        <v>11.12652165265694</v>
+        <v>11.12652258650894</v>
       </c>
       <c r="E537" t="n">
-        <v>11.18775261012382</v>
+        <v>11.18775354911495</v>
       </c>
       <c r="F537" t="n">
         <v>2536971</v>
@@ -11212,16 +11212,16 @@
         <v>45015</v>
       </c>
       <c r="B540" t="n">
-        <v>12.11496353149414</v>
+        <v>12.11496257781982</v>
       </c>
       <c r="C540" t="n">
-        <v>12.28116150020495</v>
+        <v>12.28116053344774</v>
       </c>
       <c r="D540" t="n">
-        <v>11.7125895906359</v>
+        <v>11.71258866863594</v>
       </c>
       <c r="E540" t="n">
-        <v>11.72133663051666</v>
+        <v>11.72133570782815</v>
       </c>
       <c r="F540" t="n">
         <v>2232381</v>
@@ -11352,16 +11352,16 @@
         <v>45027</v>
       </c>
       <c r="B547" t="n">
-        <v>11.85254669189453</v>
+        <v>11.85254573822021</v>
       </c>
       <c r="C547" t="n">
-        <v>11.87878781209517</v>
+        <v>11.87878685630945</v>
       </c>
       <c r="D547" t="n">
-        <v>10.9690720636722</v>
+        <v>10.96907118108362</v>
       </c>
       <c r="E547" t="n">
-        <v>10.9690720636722</v>
+        <v>10.96907118108362</v>
       </c>
       <c r="F547" t="n">
         <v>9432295</v>
@@ -11372,16 +11372,16 @@
         <v>45028</v>
       </c>
       <c r="B548" t="n">
-        <v>12.11496353149414</v>
+        <v>12.11496257781982</v>
       </c>
       <c r="C548" t="n">
-        <v>12.33364542388005</v>
+        <v>12.33364445299137</v>
       </c>
       <c r="D548" t="n">
-        <v>11.80880955591008</v>
+        <v>11.80880862633581</v>
       </c>
       <c r="E548" t="n">
-        <v>11.96626048474012</v>
+        <v>11.96625954277151</v>
       </c>
       <c r="F548" t="n">
         <v>6602445</v>
@@ -11392,16 +11392,16 @@
         <v>45029</v>
       </c>
       <c r="B549" t="n">
-        <v>12.45610618591309</v>
+        <v>12.4561071395874</v>
       </c>
       <c r="C549" t="n">
-        <v>12.64854525626645</v>
+        <v>12.64854622467444</v>
       </c>
       <c r="D549" t="n">
-        <v>11.97500640454174</v>
+        <v>11.97500732138171</v>
       </c>
       <c r="E549" t="n">
-        <v>12.09746832019902</v>
+        <v>12.09746924641502</v>
       </c>
       <c r="F549" t="n">
         <v>4483641</v>
@@ -11512,16 +11512,16 @@
         <v>45040</v>
       </c>
       <c r="B555" t="n">
-        <v>11.52889633178711</v>
+        <v>11.52889728546143</v>
       </c>
       <c r="C555" t="n">
-        <v>11.6688523341908</v>
+        <v>11.66885329944233</v>
       </c>
       <c r="D555" t="n">
-        <v>11.41518229038292</v>
+        <v>11.41518323465077</v>
       </c>
       <c r="E555" t="n">
-        <v>11.53764337138853</v>
+        <v>11.53764432578641</v>
       </c>
       <c r="F555" t="n">
         <v>1779282</v>
@@ -11612,16 +11612,16 @@
         <v>45048</v>
       </c>
       <c r="B560" t="n">
-        <v>10.1555757522583</v>
+        <v>10.15557670593262</v>
       </c>
       <c r="C560" t="n">
-        <v>10.65416964296346</v>
+        <v>10.65417064345897</v>
       </c>
       <c r="D560" t="n">
-        <v>10.02436678932562</v>
+        <v>10.02436773067856</v>
       </c>
       <c r="E560" t="n">
-        <v>10.5929395234974</v>
+        <v>10.592940518243</v>
       </c>
       <c r="F560" t="n">
         <v>7078259</v>
@@ -27805,6 +27805,26 @@
       </c>
       <c r="F1369" t="n">
         <v>14270400</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1370" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="C1370" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>5118100</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -452,16 +452,16 @@
         <v>44229</v>
       </c>
       <c r="B2" t="n">
-        <v>6.844326019287109</v>
+        <v>6.844325542449951</v>
       </c>
       <c r="C2" t="n">
-        <v>7.276820126586135</v>
+        <v>7.276819619617557</v>
       </c>
       <c r="D2" t="n">
-        <v>6.844326019287109</v>
+        <v>6.844325542449951</v>
       </c>
       <c r="E2" t="n">
-        <v>7.094164726097559</v>
+        <v>7.094164231854394</v>
       </c>
       <c r="F2" t="n">
         <v>4750609</v>
@@ -492,16 +492,16 @@
         <v>44231</v>
       </c>
       <c r="B4" t="n">
-        <v>6.886315822601318</v>
+        <v>6.88631534576416</v>
       </c>
       <c r="C4" t="n">
-        <v>7.012284415532206</v>
+        <v>7.012283929972458</v>
       </c>
       <c r="D4" t="n">
-        <v>6.806535091369281</v>
+        <v>6.806534620056473</v>
       </c>
       <c r="E4" t="n">
-        <v>6.91990706854544</v>
+        <v>6.919906589382284</v>
       </c>
       <c r="F4" t="n">
         <v>3650229</v>
@@ -592,16 +592,16 @@
         <v>44238</v>
       </c>
       <c r="B9" t="n">
-        <v>6.963996887207031</v>
+        <v>6.963996410369873</v>
       </c>
       <c r="C9" t="n">
-        <v>7.058473540902132</v>
+        <v>7.058473057595991</v>
       </c>
       <c r="D9" t="n">
-        <v>6.850624090978325</v>
+        <v>6.850623621904003</v>
       </c>
       <c r="E9" t="n">
-        <v>6.928305526523419</v>
+        <v>6.928305052130111</v>
       </c>
       <c r="F9" t="n">
         <v>1655030</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029080867767334</v>
+        <v>7.029080390930176</v>
       </c>
       <c r="C10" t="n">
-        <v>7.194940242201317</v>
+        <v>7.194939754112628</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913608771181656</v>
+        <v>6.913608302177867</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949300131730055</v>
+        <v>6.949299660305043</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.222233295440674</v>
+        <v>7.222232341766357</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379694648559866</v>
+        <v>7.379693674093248</v>
       </c>
       <c r="D12" t="n">
-        <v>7.138253961230074</v>
+        <v>7.138253018644978</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287317299748752</v>
+        <v>7.287316337480287</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -672,16 +672,16 @@
         <v>44246</v>
       </c>
       <c r="B13" t="n">
-        <v>7.453176021575928</v>
+        <v>7.453177452087402</v>
       </c>
       <c r="C13" t="n">
-        <v>7.595941445618074</v>
+        <v>7.595942903530964</v>
       </c>
       <c r="D13" t="n">
-        <v>7.142452755462365</v>
+        <v>7.142454126335747</v>
       </c>
       <c r="E13" t="n">
-        <v>7.159247971413373</v>
+        <v>7.159249345510314</v>
       </c>
       <c r="F13" t="n">
         <v>1995604</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.30621337890625</v>
+        <v>7.306212902069092</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724010745681502</v>
+        <v>7.724010241576962</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050075153474859</v>
+        <v>7.050074693354461</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054274566636445</v>
+        <v>7.054274106241974</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.30621337890625</v>
+        <v>7.306212902069092</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480470759734867</v>
+        <v>7.480470271524869</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243227864044258</v>
+        <v>7.243227391317824</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308311867795231</v>
+        <v>7.308311390821116</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400689808525235</v>
+        <v>7.400690302893193</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945100983960817</v>
+        <v>6.945101447895325</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360799849541025</v>
+        <v>7.360800341244324</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -772,16 +772,16 @@
         <v>44253</v>
       </c>
       <c r="B18" t="n">
-        <v>7.243227958679199</v>
+        <v>7.243227481842041</v>
       </c>
       <c r="C18" t="n">
-        <v>7.480470857469459</v>
+        <v>7.480470365014094</v>
       </c>
       <c r="D18" t="n">
-        <v>6.833828601083652</v>
+        <v>6.833828151198126</v>
       </c>
       <c r="E18" t="n">
-        <v>7.157149323379279</v>
+        <v>7.157148852208861</v>
       </c>
       <c r="F18" t="n">
         <v>1865862</v>
@@ -832,16 +832,16 @@
         <v>44258</v>
       </c>
       <c r="B21" t="n">
-        <v>7.085767269134521</v>
+        <v>7.085766792297363</v>
       </c>
       <c r="C21" t="n">
-        <v>7.10886120006331</v>
+        <v>7.108860721672044</v>
       </c>
       <c r="D21" t="n">
-        <v>6.896813161397048</v>
+        <v>6.896812697275568</v>
       </c>
       <c r="E21" t="n">
-        <v>7.10886120006331</v>
+        <v>7.108860721672044</v>
       </c>
       <c r="F21" t="n">
         <v>1419466</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233019817944</v>
+        <v>7.222233502264944</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966096425558127</v>
+        <v>6.966096890895136</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117259059009463</v>
+        <v>7.117259534444174</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -892,16 +892,16 @@
         <v>44263</v>
       </c>
       <c r="B24" t="n">
-        <v>6.65327262878418</v>
+        <v>6.653271675109863</v>
       </c>
       <c r="C24" t="n">
-        <v>7.016484130369983</v>
+        <v>7.016483124633246</v>
       </c>
       <c r="D24" t="n">
-        <v>6.65327262878418</v>
+        <v>6.653271675109863</v>
       </c>
       <c r="E24" t="n">
-        <v>7.016484130369983</v>
+        <v>7.016483124633246</v>
       </c>
       <c r="F24" t="n">
         <v>1015642</v>
@@ -912,16 +912,16 @@
         <v>44264</v>
       </c>
       <c r="B25" t="n">
-        <v>6.42442798614502</v>
+        <v>6.424428462982178</v>
       </c>
       <c r="C25" t="n">
-        <v>6.819131399595795</v>
+        <v>6.819131905728831</v>
       </c>
       <c r="D25" t="n">
-        <v>6.367742000113356</v>
+        <v>6.36774247274314</v>
       </c>
       <c r="E25" t="n">
-        <v>6.754047399508202</v>
+        <v>6.75404790081054</v>
       </c>
       <c r="F25" t="n">
         <v>2514170</v>
@@ -932,16 +932,16 @@
         <v>44265</v>
       </c>
       <c r="B26" t="n">
-        <v>6.252270221710205</v>
+        <v>6.252270698547363</v>
       </c>
       <c r="C26" t="n">
-        <v>6.592386944261464</v>
+        <v>6.592387447038047</v>
       </c>
       <c r="D26" t="n">
-        <v>6.124201524146216</v>
+        <v>6.124201991216056</v>
       </c>
       <c r="E26" t="n">
-        <v>6.586089042665994</v>
+        <v>6.58608954496226</v>
       </c>
       <c r="F26" t="n">
         <v>1291345</v>
@@ -952,16 +952,16 @@
         <v>44266</v>
       </c>
       <c r="B27" t="n">
-        <v>6.670068264007568</v>
+        <v>6.670067310333252</v>
       </c>
       <c r="C27" t="n">
-        <v>6.670068264007568</v>
+        <v>6.670067310333252</v>
       </c>
       <c r="D27" t="n">
-        <v>6.214479816572392</v>
+        <v>6.214478928037289</v>
       </c>
       <c r="E27" t="n">
-        <v>6.287962243213972</v>
+        <v>6.287961344172484</v>
       </c>
       <c r="F27" t="n">
         <v>2230763</v>
@@ -972,16 +972,16 @@
         <v>44267</v>
       </c>
       <c r="B28" t="n">
-        <v>6.69526195526123</v>
+        <v>6.695262432098389</v>
       </c>
       <c r="C28" t="n">
-        <v>6.896813082384956</v>
+        <v>6.896813573576604</v>
       </c>
       <c r="D28" t="n">
-        <v>6.45592016938186</v>
+        <v>6.455920629173074</v>
       </c>
       <c r="E28" t="n">
-        <v>6.646973981495075</v>
+        <v>6.646974454893159</v>
       </c>
       <c r="F28" t="n">
         <v>3263434</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033279895782471</v>
+        <v>7.033280372619629</v>
       </c>
       <c r="C29" t="n">
-        <v>7.127756543943293</v>
+        <v>7.12775702718571</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1012,16 +1012,16 @@
         <v>44271</v>
       </c>
       <c r="B30" t="n">
-        <v>7.390191078186035</v>
+        <v>7.390192031860352</v>
       </c>
       <c r="C30" t="n">
-        <v>7.425883244806614</v>
+        <v>7.42588420308686</v>
       </c>
       <c r="D30" t="n">
-        <v>6.970293645661006</v>
+        <v>6.970294545149255</v>
       </c>
       <c r="E30" t="n">
-        <v>6.970293645661006</v>
+        <v>6.970294545149255</v>
       </c>
       <c r="F30" t="n">
         <v>4282725</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159247875213623</v>
+        <v>7.159248352050781</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656826740361056</v>
+        <v>7.656827250339138</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159247875213623</v>
+        <v>7.159248352050781</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392291336410457</v>
+        <v>7.392291828769327</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.70511531829834</v>
+        <v>7.705114841461182</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789095471368375</v>
+        <v>7.789094989334038</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033280588094989</v>
+        <v>7.033280152834855</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159249194110809</v>
+        <v>7.159248751055008</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.518260955810547</v>
+        <v>7.51826000213623</v>
       </c>
       <c r="C38" t="n">
-        <v>7.789095110371317</v>
+        <v>7.789094122342303</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455276249824448</v>
+        <v>7.455275304139598</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721911802823614</v>
+        <v>7.721910823316651</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1192,16 +1192,16 @@
         <v>44284</v>
       </c>
       <c r="B39" t="n">
-        <v>7.232730388641357</v>
+        <v>7.232729911804199</v>
       </c>
       <c r="C39" t="n">
-        <v>7.663125173574427</v>
+        <v>7.663124668362338</v>
       </c>
       <c r="D39" t="n">
-        <v>7.232730388641357</v>
+        <v>7.232729911804199</v>
       </c>
       <c r="E39" t="n">
-        <v>7.568648526962992</v>
+        <v>7.568648027979529</v>
       </c>
       <c r="F39" t="n">
         <v>3953908</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379694366927925</v>
+        <v>7.379694859893382</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257924377559402</v>
+        <v>7.257924862390593</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1232,16 +1232,16 @@
         <v>44286</v>
       </c>
       <c r="B41" t="n">
-        <v>7.348202228546143</v>
+        <v>7.348202705383301</v>
       </c>
       <c r="C41" t="n">
-        <v>7.379694172420294</v>
+        <v>7.379694651301018</v>
       </c>
       <c r="D41" t="n">
-        <v>6.997588185825906</v>
+        <v>6.997588639911132</v>
       </c>
       <c r="E41" t="n">
-        <v>7.226432242387128</v>
+        <v>7.226432711322428</v>
       </c>
       <c r="F41" t="n">
         <v>2544984</v>
@@ -1252,16 +1252,16 @@
         <v>44287</v>
       </c>
       <c r="B42" t="n">
-        <v>7.348202228546143</v>
+        <v>7.348202705383301</v>
       </c>
       <c r="C42" t="n">
-        <v>7.524558900189283</v>
+        <v>7.524559388470522</v>
       </c>
       <c r="D42" t="n">
-        <v>7.171845556903002</v>
+        <v>7.171846022296081</v>
       </c>
       <c r="E42" t="n">
-        <v>7.35869954317086</v>
+        <v>7.358700020689207</v>
       </c>
       <c r="F42" t="n">
         <v>877384</v>
@@ -1312,16 +1312,16 @@
         <v>44293</v>
       </c>
       <c r="B45" t="n">
-        <v>7.243227958679199</v>
+        <v>7.243227481842041</v>
       </c>
       <c r="C45" t="n">
-        <v>7.388092696447584</v>
+        <v>7.388092210073672</v>
       </c>
       <c r="D45" t="n">
-        <v>7.146652008029977</v>
+        <v>7.146651537550619</v>
       </c>
       <c r="E45" t="n">
-        <v>7.213835313342242</v>
+        <v>7.213834838440065</v>
       </c>
       <c r="F45" t="n">
         <v>1401221</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652626991271973</v>
+        <v>7.652628421783447</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873073016243731</v>
+        <v>7.873074487963351</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474170221459922</v>
+        <v>7.474171618612335</v>
       </c>
       <c r="E47" t="n">
-        <v>7.595941009729709</v>
+        <v>7.595942429644829</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1372,16 +1372,16 @@
         <v>44298</v>
       </c>
       <c r="B48" t="n">
-        <v>7.7890944480896</v>
+        <v>7.789094924926758</v>
       </c>
       <c r="C48" t="n">
-        <v>8.015839208001262</v>
+        <v>8.015839698719409</v>
       </c>
       <c r="D48" t="n">
-        <v>7.644229717818412</v>
+        <v>7.64423018578716</v>
       </c>
       <c r="E48" t="n">
-        <v>7.688319089439362</v>
+        <v>7.688319560107198</v>
       </c>
       <c r="F48" t="n">
         <v>2187380</v>
@@ -1392,16 +1392,16 @@
         <v>44299</v>
       </c>
       <c r="B49" t="n">
-        <v>7.726110458374023</v>
+        <v>7.726109981536865</v>
       </c>
       <c r="C49" t="n">
-        <v>7.898268547699764</v>
+        <v>7.898268060237418</v>
       </c>
       <c r="D49" t="n">
-        <v>7.642131120403916</v>
+        <v>7.642130648749763</v>
       </c>
       <c r="E49" t="n">
-        <v>7.786995864004779</v>
+        <v>7.786995383409918</v>
       </c>
       <c r="F49" t="n">
         <v>1044023</v>
@@ -1412,16 +1412,16 @@
         <v>44300</v>
       </c>
       <c r="B50" t="n">
-        <v>7.877272129058838</v>
+        <v>7.877273082733154</v>
       </c>
       <c r="C50" t="n">
-        <v>7.877272129058838</v>
+        <v>7.877273082733154</v>
       </c>
       <c r="D50" t="n">
-        <v>7.518259302698232</v>
+        <v>7.518260212908098</v>
       </c>
       <c r="E50" t="n">
-        <v>7.786994097388884</v>
+        <v>7.78699504013355</v>
       </c>
       <c r="F50" t="n">
         <v>2026013</v>
@@ -1432,16 +1432,16 @@
         <v>44301</v>
       </c>
       <c r="B51" t="n">
-        <v>8.112414360046387</v>
+        <v>8.11241626739502</v>
       </c>
       <c r="C51" t="n">
-        <v>8.185897180089103</v>
+        <v>8.185899104714634</v>
       </c>
       <c r="D51" t="n">
-        <v>7.891968335301526</v>
+        <v>7.891970190820038</v>
       </c>
       <c r="E51" t="n">
-        <v>7.894067635698465</v>
+        <v>7.894069491710552</v>
       </c>
       <c r="F51" t="n">
         <v>2034122</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208992958068848</v>
+        <v>8.208991050720215</v>
       </c>
       <c r="C53" t="n">
-        <v>8.244684323567677</v>
+        <v>8.244682407926204</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059930404635271</v>
+        <v>8.059928531921125</v>
       </c>
       <c r="E53" t="n">
-        <v>8.187998323702958</v>
+        <v>8.1879964212324</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1512,16 +1512,16 @@
         <v>44308</v>
       </c>
       <c r="B55" t="n">
-        <v>8.183796882629395</v>
+        <v>8.183797836303711</v>
       </c>
       <c r="C55" t="n">
-        <v>8.37065166140985</v>
+        <v>8.370652636858729</v>
       </c>
       <c r="D55" t="n">
-        <v>8.064126209385469</v>
+        <v>8.06412714911432</v>
       </c>
       <c r="E55" t="n">
-        <v>8.259378189563577</v>
+        <v>8.259379152045536</v>
       </c>
       <c r="F55" t="n">
         <v>608979</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397945404052734</v>
+        <v>8.397946357727051</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469328120611465</v>
+        <v>8.469329082392035</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116615684439186</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116615684439186</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849333763122559</v>
+        <v>8.849335670471191</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122267169180361</v>
+        <v>9.122269135355927</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641485163873828</v>
+        <v>8.641487026423638</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733862499494249</v>
+        <v>8.733864381954685</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1672,16 +1672,16 @@
         <v>44320</v>
       </c>
       <c r="B63" t="n">
-        <v>9.298625946044922</v>
+        <v>9.298624992370605</v>
       </c>
       <c r="C63" t="n">
-        <v>9.544266879269465</v>
+        <v>9.544265900402022</v>
       </c>
       <c r="D63" t="n">
-        <v>8.719167760068038</v>
+        <v>8.719166865823404</v>
       </c>
       <c r="E63" t="n">
-        <v>8.849335779760766</v>
+        <v>8.849334872165999</v>
       </c>
       <c r="F63" t="n">
         <v>2875017</v>
@@ -1712,16 +1712,16 @@
         <v>44322</v>
       </c>
       <c r="B65" t="n">
-        <v>9.764711380004883</v>
+        <v>9.764712333679199</v>
       </c>
       <c r="C65" t="n">
-        <v>9.783605896673567</v>
+        <v>9.783606852193223</v>
       </c>
       <c r="D65" t="n">
-        <v>9.537965814857868</v>
+        <v>9.537966746386992</v>
       </c>
       <c r="E65" t="n">
-        <v>9.783605896673567</v>
+        <v>9.783606852193223</v>
       </c>
       <c r="F65" t="n">
         <v>8042425</v>
@@ -1832,16 +1832,16 @@
         <v>44330</v>
       </c>
       <c r="B71" t="n">
-        <v>9.626144409179688</v>
+        <v>9.626145362854004</v>
       </c>
       <c r="C71" t="n">
-        <v>9.657637164002436</v>
+        <v>9.657638120796779</v>
       </c>
       <c r="D71" t="n">
-        <v>9.273431075367332</v>
+        <v>9.273431994097892</v>
       </c>
       <c r="E71" t="n">
-        <v>9.655537863492778</v>
+        <v>9.655538820079142</v>
       </c>
       <c r="F71" t="n">
         <v>1271072</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.82349681854248</v>
+        <v>9.823495864868164</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272898361439</v>
+        <v>10.10272800283195</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334317531017494</v>
+        <v>9.334316624833162</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678632890034629</v>
+        <v>9.678631950423839</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1932,16 +1932,16 @@
         <v>44337</v>
       </c>
       <c r="B76" t="n">
-        <v>10.1069278717041</v>
+        <v>10.10692882537842</v>
       </c>
       <c r="C76" t="n">
-        <v>10.19090720339814</v>
+        <v>10.19090816499662</v>
       </c>
       <c r="D76" t="n">
-        <v>9.873885205958286</v>
+        <v>9.873886137643053</v>
       </c>
       <c r="E76" t="n">
-        <v>10.12792250167898</v>
+        <v>10.12792345733432</v>
       </c>
       <c r="F76" t="n">
         <v>1597862</v>
@@ -1952,16 +1952,16 @@
         <v>44340</v>
       </c>
       <c r="B77" t="n">
-        <v>10.18250846862793</v>
+        <v>10.18251037597656</v>
       </c>
       <c r="C77" t="n">
-        <v>10.39035788841617</v>
+        <v>10.39035983469837</v>
       </c>
       <c r="D77" t="n">
-        <v>9.951565119860142</v>
+        <v>9.951566983949347</v>
       </c>
       <c r="E77" t="n">
-        <v>10.15731442736386</v>
+        <v>10.15731632999324</v>
       </c>
       <c r="F77" t="n">
         <v>3407772</v>
@@ -1972,16 +1972,16 @@
         <v>44341</v>
       </c>
       <c r="B78" t="n">
-        <v>10.43444728851318</v>
+        <v>10.43444919586182</v>
       </c>
       <c r="C78" t="n">
-        <v>10.49323176138078</v>
+        <v>10.49323367947483</v>
       </c>
       <c r="D78" t="n">
-        <v>10.18880721200021</v>
+        <v>10.18880907444745</v>
       </c>
       <c r="E78" t="n">
-        <v>10.23499588189026</v>
+        <v>10.23499775278048</v>
       </c>
       <c r="F78" t="n">
         <v>2528360</v>
@@ -2032,16 +2032,16 @@
         <v>44344</v>
       </c>
       <c r="B81" t="n">
-        <v>10.72837543487549</v>
+        <v>10.7283763885498</v>
       </c>
       <c r="C81" t="n">
-        <v>10.82915078936937</v>
+        <v>10.82915175200188</v>
       </c>
       <c r="D81" t="n">
-        <v>10.46803862888618</v>
+        <v>10.46803955941845</v>
       </c>
       <c r="E81" t="n">
-        <v>10.65489342246942</v>
+        <v>10.65489436961172</v>
       </c>
       <c r="F81" t="n">
         <v>2512953</v>
@@ -2132,16 +2132,16 @@
         <v>44354</v>
       </c>
       <c r="B86" t="n">
-        <v>11.10838317871094</v>
+        <v>11.10838222503662</v>
       </c>
       <c r="C86" t="n">
-        <v>11.61225999957573</v>
+        <v>11.6122590026427</v>
       </c>
       <c r="D86" t="n">
-        <v>10.89843524749561</v>
+        <v>10.8984343118457</v>
       </c>
       <c r="E86" t="n">
-        <v>11.14407453808413</v>
+        <v>11.14407358134564</v>
       </c>
       <c r="F86" t="n">
         <v>2940293</v>
@@ -2152,16 +2152,16 @@
         <v>44355</v>
       </c>
       <c r="B87" t="n">
-        <v>11.02020645141602</v>
+        <v>11.0202054977417</v>
       </c>
       <c r="C87" t="n">
-        <v>11.169269807414</v>
+        <v>11.16926884083993</v>
       </c>
       <c r="D87" t="n">
-        <v>10.93412699461562</v>
+        <v>10.93412604839051</v>
       </c>
       <c r="E87" t="n">
-        <v>11.12098101485001</v>
+        <v>11.1209800524548</v>
       </c>
       <c r="F87" t="n">
         <v>1135248</v>
@@ -2192,16 +2192,16 @@
         <v>44357</v>
       </c>
       <c r="B89" t="n">
-        <v>10.79136085510254</v>
+        <v>10.79135990142822</v>
       </c>
       <c r="C89" t="n">
-        <v>10.99081229192654</v>
+        <v>10.99081132062593</v>
       </c>
       <c r="D89" t="n">
-        <v>10.70108361394333</v>
+        <v>10.70108266824717</v>
       </c>
       <c r="E89" t="n">
-        <v>10.9404250134143</v>
+        <v>10.94042404656661</v>
       </c>
       <c r="F89" t="n">
         <v>1040779</v>
@@ -2212,16 +2212,16 @@
         <v>44358</v>
       </c>
       <c r="B90" t="n">
-        <v>10.60240745544434</v>
+        <v>10.60240650177002</v>
       </c>
       <c r="C90" t="n">
-        <v>10.84174885287247</v>
+        <v>10.84174787766967</v>
       </c>
       <c r="D90" t="n">
-        <v>10.51842811744432</v>
+        <v>10.51842717132385</v>
       </c>
       <c r="E90" t="n">
-        <v>10.75986881566868</v>
+        <v>10.7598678478309</v>
       </c>
       <c r="F90" t="n">
         <v>1174982</v>
@@ -2332,16 +2332,16 @@
         <v>44368</v>
       </c>
       <c r="B96" t="n">
-        <v>11.24275016784668</v>
+        <v>11.24274921417236</v>
       </c>
       <c r="C96" t="n">
-        <v>11.40441175261605</v>
+        <v>11.40441078522868</v>
       </c>
       <c r="D96" t="n">
-        <v>11.15247211601892</v>
+        <v>11.1524711700025</v>
       </c>
       <c r="E96" t="n">
-        <v>11.34562564799132</v>
+        <v>11.34562468559051</v>
       </c>
       <c r="F96" t="n">
         <v>1065511</v>
@@ -2352,16 +2352,16 @@
         <v>44369</v>
       </c>
       <c r="B97" t="n">
-        <v>11.28473949432373</v>
+        <v>11.28474044799805</v>
       </c>
       <c r="C97" t="n">
-        <v>11.42330632585396</v>
+        <v>11.42330729123857</v>
       </c>
       <c r="D97" t="n">
-        <v>11.16297031516165</v>
+        <v>11.16297125854524</v>
       </c>
       <c r="E97" t="n">
-        <v>11.23855163287302</v>
+        <v>11.238552582644</v>
       </c>
       <c r="F97" t="n">
         <v>1033076</v>
@@ -2392,16 +2392,16 @@
         <v>44371</v>
       </c>
       <c r="B99" t="n">
-        <v>11.71093654632568</v>
+        <v>11.71093559265137</v>
       </c>
       <c r="C99" t="n">
-        <v>12.02165985453709</v>
+        <v>12.02165887555918</v>
       </c>
       <c r="D99" t="n">
-        <v>11.35612305046303</v>
+        <v>11.35612212568278</v>
       </c>
       <c r="E99" t="n">
-        <v>11.54717565951756</v>
+        <v>11.54717471917903</v>
       </c>
       <c r="F99" t="n">
         <v>3545624</v>
@@ -2432,16 +2432,16 @@
         <v>44375</v>
       </c>
       <c r="B101" t="n">
-        <v>11.86209774017334</v>
+        <v>11.86209869384766</v>
       </c>
       <c r="C101" t="n">
-        <v>12.00066375318507</v>
+        <v>12.00066471799965</v>
       </c>
       <c r="D101" t="n">
-        <v>11.40441044302249</v>
+        <v>11.40441135990023</v>
       </c>
       <c r="E101" t="n">
-        <v>11.58916512703814</v>
+        <v>11.58916605876955</v>
       </c>
       <c r="F101" t="n">
         <v>1601511</v>
@@ -2472,16 +2472,16 @@
         <v>44377</v>
       </c>
       <c r="B103" t="n">
-        <v>11.8893928527832</v>
+        <v>11.88939094543457</v>
       </c>
       <c r="C103" t="n">
-        <v>12.16862503272069</v>
+        <v>12.16862308057641</v>
       </c>
       <c r="D103" t="n">
-        <v>11.85160219013497</v>
+        <v>11.85160028884888</v>
       </c>
       <c r="E103" t="n">
-        <v>12.02376028470606</v>
+        <v>12.02375835580161</v>
       </c>
       <c r="F103" t="n">
         <v>3669691</v>
@@ -2492,16 +2492,16 @@
         <v>44378</v>
       </c>
       <c r="B104" t="n">
-        <v>12.47094821929932</v>
+        <v>12.47094917297363</v>
       </c>
       <c r="C104" t="n">
-        <v>12.63470827087047</v>
+        <v>12.6347092370678</v>
       </c>
       <c r="D104" t="n">
-        <v>12.33028290864975</v>
+        <v>12.33028385156715</v>
       </c>
       <c r="E104" t="n">
-        <v>12.38906900530821</v>
+        <v>12.38906995272109</v>
       </c>
       <c r="F104" t="n">
         <v>8890212</v>
@@ -2512,16 +2512,16 @@
         <v>44379</v>
       </c>
       <c r="B105" t="n">
-        <v>12.95803070068359</v>
+        <v>12.95803165435791</v>
       </c>
       <c r="C105" t="n">
-        <v>13.1280894777343</v>
+        <v>13.12809044392446</v>
       </c>
       <c r="D105" t="n">
-        <v>12.5003425684372</v>
+        <v>12.50034348842697</v>
       </c>
       <c r="E105" t="n">
-        <v>12.52133719856387</v>
+        <v>12.52133812009879</v>
       </c>
       <c r="F105" t="n">
         <v>2908669</v>
@@ -2532,16 +2532,16 @@
         <v>44382</v>
       </c>
       <c r="B106" t="n">
-        <v>13.12179088592529</v>
+        <v>13.12179183959961</v>
       </c>
       <c r="C106" t="n">
-        <v>13.50179840315787</v>
+        <v>13.50179938445063</v>
       </c>
       <c r="D106" t="n">
-        <v>12.96432872312831</v>
+        <v>12.96432966535849</v>
       </c>
       <c r="E106" t="n">
-        <v>12.96432872312831</v>
+        <v>12.96432966535849</v>
       </c>
       <c r="F106" t="n">
         <v>1748688</v>
@@ -2572,16 +2572,16 @@
         <v>44384</v>
       </c>
       <c r="B108" t="n">
-        <v>13.22676658630371</v>
+        <v>13.22676467895508</v>
       </c>
       <c r="C108" t="n">
-        <v>13.31074511346494</v>
+        <v>13.31074319400629</v>
       </c>
       <c r="D108" t="n">
-        <v>13.05040908152244</v>
+        <v>13.05040719960521</v>
       </c>
       <c r="E108" t="n">
-        <v>13.05880709659748</v>
+        <v>13.05880521346923</v>
       </c>
       <c r="F108" t="n">
         <v>2057638</v>
@@ -2592,16 +2592,16 @@
         <v>44385</v>
       </c>
       <c r="B109" t="n">
-        <v>13.05880546569824</v>
+        <v>13.05880641937256</v>
       </c>
       <c r="C109" t="n">
-        <v>13.61097022010407</v>
+        <v>13.61097121410255</v>
       </c>
       <c r="D109" t="n">
-        <v>13.00631808098297</v>
+        <v>13.00631903082418</v>
       </c>
       <c r="E109" t="n">
-        <v>13.09659531112451</v>
+        <v>13.09659626755859</v>
       </c>
       <c r="F109" t="n">
         <v>8587750</v>
@@ -2612,16 +2612,16 @@
         <v>44389</v>
       </c>
       <c r="B110" t="n">
-        <v>13.33173942565918</v>
+        <v>13.3317403793335</v>
       </c>
       <c r="C110" t="n">
-        <v>13.79572545725768</v>
+        <v>13.79572644412283</v>
       </c>
       <c r="D110" t="n">
-        <v>13.07140260401543</v>
+        <v>13.07140353906678</v>
       </c>
       <c r="E110" t="n">
-        <v>13.19107329393574</v>
+        <v>13.19107423754762</v>
       </c>
       <c r="F110" t="n">
         <v>8663568</v>
@@ -2632,16 +2632,16 @@
         <v>44390</v>
       </c>
       <c r="B111" t="n">
-        <v>13.27295303344727</v>
+        <v>13.27295207977295</v>
       </c>
       <c r="C111" t="n">
-        <v>13.49759849206305</v>
+        <v>13.49759752224774</v>
       </c>
       <c r="D111" t="n">
-        <v>13.13438701720531</v>
+        <v>13.1343860734871</v>
       </c>
       <c r="E111" t="n">
-        <v>13.33173913269187</v>
+        <v>13.33173817479372</v>
       </c>
       <c r="F111" t="n">
         <v>2696620</v>
@@ -2652,16 +2652,16 @@
         <v>44391</v>
       </c>
       <c r="B112" t="n">
-        <v>13.63196468353271</v>
+        <v>13.63196563720703</v>
       </c>
       <c r="C112" t="n">
-        <v>13.63196468353271</v>
+        <v>13.63196563720703</v>
       </c>
       <c r="D112" t="n">
-        <v>13.25405730412531</v>
+        <v>13.25405823136172</v>
       </c>
       <c r="E112" t="n">
-        <v>13.27505193303836</v>
+        <v>13.27505286174354</v>
       </c>
       <c r="F112" t="n">
         <v>1800585</v>
@@ -2672,16 +2672,16 @@
         <v>44392</v>
       </c>
       <c r="B113" t="n">
-        <v>13.63196468353271</v>
+        <v>13.63196563720703</v>
       </c>
       <c r="C113" t="n">
-        <v>13.72224272437113</v>
+        <v>13.72224368436118</v>
       </c>
       <c r="D113" t="n">
-        <v>13.39682272904084</v>
+        <v>13.39682366626494</v>
       </c>
       <c r="E113" t="n">
-        <v>13.53958734216189</v>
+        <v>13.53958828937361</v>
       </c>
       <c r="F113" t="n">
         <v>1667599</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C114" t="n">
-        <v>13.93849142806081</v>
+        <v>13.9384904687512</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969861080446</v>
+        <v>13.49969768169454</v>
       </c>
       <c r="E114" t="n">
-        <v>13.64246404868482</v>
+        <v>13.64246310974914</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501531105205</v>
+        <v>14.24501433064608</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969861080446</v>
+        <v>13.49969768169454</v>
       </c>
       <c r="E115" t="n">
-        <v>13.74953650350598</v>
+        <v>13.7495355572011</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103643972576</v>
+        <v>14.16103739980534</v>
       </c>
       <c r="D116" t="n">
-        <v>13.77473102080758</v>
+        <v>13.7747319546967</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059038615415</v>
+        <v>13.94059133128809</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801414489746</v>
+        <v>15.06801509857178</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127770885214</v>
+        <v>15.22127867222671</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92944893307399</v>
+        <v>14.92944987797833</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127770885214</v>
+        <v>15.22127867222671</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2812,16 +2812,16 @@
         <v>44403</v>
       </c>
       <c r="B120" t="n">
-        <v>14.8748607635498</v>
+        <v>14.87486171722412</v>
       </c>
       <c r="C120" t="n">
-        <v>15.17088811128218</v>
+        <v>15.17088908393575</v>
       </c>
       <c r="D120" t="n">
-        <v>14.64601752612992</v>
+        <v>14.64601846513237</v>
       </c>
       <c r="E120" t="n">
-        <v>15.07431217039968</v>
+        <v>15.07431313686146</v>
       </c>
       <c r="F120" t="n">
         <v>4655330</v>
@@ -2852,16 +2852,16 @@
         <v>44405</v>
       </c>
       <c r="B122" t="n">
-        <v>15.08690929412842</v>
+        <v>15.08691024780273</v>
       </c>
       <c r="C122" t="n">
-        <v>15.36823990913394</v>
+        <v>15.36824088059173</v>
       </c>
       <c r="D122" t="n">
-        <v>14.03716489771841</v>
+        <v>14.03716578503624</v>
       </c>
       <c r="E122" t="n">
-        <v>15.13519645180589</v>
+        <v>15.13519740853254</v>
       </c>
       <c r="F122" t="n">
         <v>6581198</v>
@@ -2872,16 +2872,16 @@
         <v>44406</v>
       </c>
       <c r="B123" t="n">
-        <v>15.28426265716553</v>
+        <v>15.28426170349121</v>
       </c>
       <c r="C123" t="n">
-        <v>15.32415262054446</v>
+        <v>15.32415166438117</v>
       </c>
       <c r="D123" t="n">
-        <v>14.85386863981871</v>
+        <v>14.85386771299919</v>
       </c>
       <c r="E123" t="n">
-        <v>15.09950794623948</v>
+        <v>15.09950700409309</v>
       </c>
       <c r="F123" t="n">
         <v>6067903</v>
@@ -2892,16 +2892,16 @@
         <v>44407</v>
       </c>
       <c r="B124" t="n">
-        <v>15.45431900024414</v>
+        <v>15.45431709289551</v>
       </c>
       <c r="C124" t="n">
-        <v>15.94140058333477</v>
+        <v>15.94139861587127</v>
       </c>
       <c r="D124" t="n">
-        <v>14.96933834137266</v>
+        <v>14.96933649387961</v>
       </c>
       <c r="E124" t="n">
-        <v>15.28006243564328</v>
+        <v>15.28006054980113</v>
       </c>
       <c r="F124" t="n">
         <v>3070441</v>
@@ -2912,16 +2912,16 @@
         <v>44410</v>
       </c>
       <c r="B125" t="n">
-        <v>15.31785297393799</v>
+        <v>15.3178539276123</v>
       </c>
       <c r="C125" t="n">
-        <v>15.85742193931368</v>
+        <v>15.85742292658102</v>
       </c>
       <c r="D125" t="n">
-        <v>15.1687896416575</v>
+        <v>15.16879058605128</v>
       </c>
       <c r="E125" t="n">
-        <v>15.64327379365431</v>
+        <v>15.64327476758901</v>
       </c>
       <c r="F125" t="n">
         <v>3314925</v>
@@ -2932,16 +2932,16 @@
         <v>44411</v>
       </c>
       <c r="B126" t="n">
-        <v>15.20448017120361</v>
+        <v>15.20448112487793</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39343345203053</v>
+        <v>15.39343441755661</v>
       </c>
       <c r="D126" t="n">
-        <v>14.76148879971554</v>
+        <v>14.761489725604</v>
       </c>
       <c r="E126" t="n">
-        <v>15.39343345203053</v>
+        <v>15.39343441755661</v>
       </c>
       <c r="F126" t="n">
         <v>3496971</v>
@@ -2952,16 +2952,16 @@
         <v>44412</v>
       </c>
       <c r="B127" t="n">
-        <v>14.73839664459229</v>
+        <v>14.73839378356934</v>
       </c>
       <c r="C127" t="n">
-        <v>15.32205427279218</v>
+        <v>15.3220512984694</v>
       </c>
       <c r="D127" t="n">
-        <v>14.73839664459229</v>
+        <v>14.73839378356934</v>
       </c>
       <c r="E127" t="n">
-        <v>15.18768764473936</v>
+        <v>15.18768469649988</v>
       </c>
       <c r="F127" t="n">
         <v>2159810</v>
@@ -2972,16 +2972,16 @@
         <v>44413</v>
       </c>
       <c r="B128" t="n">
-        <v>14.17153453826904</v>
+        <v>14.17153358459473</v>
       </c>
       <c r="C128" t="n">
-        <v>14.82237457073309</v>
+        <v>14.82237357326046</v>
       </c>
       <c r="D128" t="n">
-        <v>14.17153453826904</v>
+        <v>14.17153358459473</v>
       </c>
       <c r="E128" t="n">
-        <v>14.61662524586311</v>
+        <v>14.61662426223638</v>
       </c>
       <c r="F128" t="n">
         <v>2928535</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.93639087677002</v>
+        <v>13.93639278411865</v>
       </c>
       <c r="C129" t="n">
-        <v>14.4192722130578</v>
+        <v>14.41927418649407</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373549436386</v>
+        <v>13.75373737671409</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153364330989</v>
+        <v>14.17153558284041</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893713905431</v>
+        <v>14.15893809899156</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462098074336</v>
+        <v>13.81462191733692</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351631037553</v>
+        <v>13.83351724825013</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3052,16 +3052,16 @@
         <v>44419</v>
       </c>
       <c r="B132" t="n">
-        <v>13.82511901855469</v>
+        <v>13.825119972229</v>
       </c>
       <c r="C132" t="n">
-        <v>13.86710827889121</v>
+        <v>13.867109235462</v>
       </c>
       <c r="D132" t="n">
-        <v>13.6340647992043</v>
+        <v>13.63406573969946</v>
       </c>
       <c r="E132" t="n">
-        <v>13.64666222674088</v>
+        <v>13.64666316810502</v>
       </c>
       <c r="F132" t="n">
         <v>1882485</v>
@@ -3072,16 +3072,16 @@
         <v>44420</v>
       </c>
       <c r="B133" t="n">
-        <v>13.68025493621826</v>
+        <v>13.68025398254395</v>
       </c>
       <c r="C133" t="n">
-        <v>14.21142511206147</v>
+        <v>14.21142412135836</v>
       </c>
       <c r="D133" t="n">
-        <v>13.64666287691298</v>
+        <v>13.64666192558043</v>
       </c>
       <c r="E133" t="n">
-        <v>13.82511967722906</v>
+        <v>13.82511871345597</v>
       </c>
       <c r="F133" t="n">
         <v>1819641</v>
@@ -3092,16 +3092,16 @@
         <v>44421</v>
       </c>
       <c r="B134" t="n">
-        <v>12.95593166351318</v>
+        <v>12.95592975616455</v>
       </c>
       <c r="C134" t="n">
-        <v>13.76423392021486</v>
+        <v>13.76423189386945</v>
       </c>
       <c r="D134" t="n">
-        <v>12.78797379676563</v>
+        <v>12.78797191414345</v>
       </c>
       <c r="E134" t="n">
-        <v>13.57108119635301</v>
+        <v>13.57107919844318</v>
       </c>
       <c r="F134" t="n">
         <v>3730102</v>
@@ -3112,16 +3112,16 @@
         <v>44424</v>
       </c>
       <c r="B135" t="n">
-        <v>11.84110355377197</v>
+        <v>11.84110450744629</v>
       </c>
       <c r="C135" t="n">
-        <v>12.94963251110049</v>
+        <v>12.94963355405497</v>
       </c>
       <c r="D135" t="n">
-        <v>11.76552223690275</v>
+        <v>11.7655231844898</v>
       </c>
       <c r="E135" t="n">
-        <v>12.94963251110049</v>
+        <v>12.94963355405497</v>
       </c>
       <c r="F135" t="n">
         <v>7844263</v>
@@ -3132,16 +3132,16 @@
         <v>44425</v>
       </c>
       <c r="B136" t="n">
-        <v>12.27779769897461</v>
+        <v>12.27779674530029</v>
       </c>
       <c r="C136" t="n">
-        <v>12.78167371260009</v>
+        <v>12.78167271978735</v>
       </c>
       <c r="D136" t="n">
-        <v>11.42960470460314</v>
+        <v>11.42960381681197</v>
       </c>
       <c r="E136" t="n">
-        <v>11.66474749373068</v>
+        <v>11.66474658767486</v>
       </c>
       <c r="F136" t="n">
         <v>5635292</v>
@@ -3192,16 +3192,16 @@
         <v>44428</v>
       </c>
       <c r="B139" t="n">
-        <v>13.5206937789917</v>
+        <v>13.52069282531738</v>
       </c>
       <c r="C139" t="n">
-        <v>13.70544848585422</v>
+        <v>13.70544751914833</v>
       </c>
       <c r="D139" t="n">
-        <v>12.64730752300772</v>
+        <v>12.6473066309372</v>
       </c>
       <c r="E139" t="n">
-        <v>12.80686818480864</v>
+        <v>12.8068672814836</v>
       </c>
       <c r="F139" t="n">
         <v>3576438</v>
@@ -3252,16 +3252,16 @@
         <v>44433</v>
       </c>
       <c r="B142" t="n">
-        <v>13.47870254516602</v>
+        <v>13.47870349884033</v>
       </c>
       <c r="C142" t="n">
-        <v>13.57947708709049</v>
+        <v>13.57947804789503</v>
       </c>
       <c r="D142" t="n">
-        <v>13.05040708891188</v>
+        <v>13.05040801228251</v>
       </c>
       <c r="E142" t="n">
-        <v>13.44511048999488</v>
+        <v>13.44511144129242</v>
       </c>
       <c r="F142" t="n">
         <v>2709595</v>
@@ -3272,16 +3272,16 @@
         <v>44434</v>
       </c>
       <c r="B143" t="n">
-        <v>13.12598896026611</v>
+        <v>13.12598991394043</v>
       </c>
       <c r="C143" t="n">
-        <v>13.76423235313817</v>
+        <v>13.76423335318433</v>
       </c>
       <c r="D143" t="n">
-        <v>12.82366288623372</v>
+        <v>12.82366381794241</v>
       </c>
       <c r="E143" t="n">
-        <v>13.47870311920116</v>
+        <v>13.47870409850207</v>
       </c>
       <c r="F143" t="n">
         <v>2624147</v>
@@ -3292,16 +3292,16 @@
         <v>44435</v>
       </c>
       <c r="B144" t="n">
-        <v>13.68865203857422</v>
+        <v>13.6886510848999</v>
       </c>
       <c r="C144" t="n">
-        <v>13.68865203857422</v>
+        <v>13.6886510848999</v>
       </c>
       <c r="D144" t="n">
-        <v>12.95803124841448</v>
+        <v>12.95803034564176</v>
       </c>
       <c r="E144" t="n">
-        <v>13.32754065087663</v>
+        <v>13.32753972236057</v>
       </c>
       <c r="F144" t="n">
         <v>2006349</v>
@@ -3312,16 +3312,16 @@
         <v>44438</v>
       </c>
       <c r="B145" t="n">
-        <v>13.34433555603027</v>
+        <v>13.34433746337891</v>
       </c>
       <c r="C145" t="n">
-        <v>14.09175231274281</v>
+        <v>14.09175432692212</v>
       </c>
       <c r="D145" t="n">
-        <v>13.24356019914138</v>
+        <v>13.24356209208586</v>
       </c>
       <c r="E145" t="n">
-        <v>13.68865088518722</v>
+        <v>13.68865284174995</v>
       </c>
       <c r="F145" t="n">
         <v>1186841</v>
@@ -3332,16 +3332,16 @@
         <v>44439</v>
       </c>
       <c r="B146" t="n">
-        <v>12.77327537536621</v>
+        <v>12.77327728271484</v>
       </c>
       <c r="C146" t="n">
-        <v>13.40312155415849</v>
+        <v>13.40312355555788</v>
       </c>
       <c r="D146" t="n">
-        <v>12.49614253714914</v>
+        <v>12.49614440311536</v>
       </c>
       <c r="E146" t="n">
-        <v>13.28554935824077</v>
+        <v>13.28555134208388</v>
       </c>
       <c r="F146" t="n">
         <v>2117441</v>
@@ -3352,16 +3352,16 @@
         <v>44440</v>
       </c>
       <c r="B147" t="n">
-        <v>13.06720447540283</v>
+        <v>13.06720352172852</v>
       </c>
       <c r="C147" t="n">
-        <v>13.2855504213384</v>
+        <v>13.2855494517287</v>
       </c>
       <c r="D147" t="n">
-        <v>12.56332765440814</v>
+        <v>12.56332673750791</v>
       </c>
       <c r="E147" t="n">
-        <v>13.0923985194012</v>
+        <v>13.09239756388817</v>
       </c>
       <c r="F147" t="n">
         <v>3411726</v>
@@ -3372,16 +3372,16 @@
         <v>44441</v>
       </c>
       <c r="B148" t="n">
-        <v>12.80686855316162</v>
+        <v>12.8068675994873</v>
       </c>
       <c r="C148" t="n">
-        <v>13.18477599277661</v>
+        <v>13.1847750109611</v>
       </c>
       <c r="D148" t="n">
-        <v>12.69769597834385</v>
+        <v>12.69769503279916</v>
       </c>
       <c r="E148" t="n">
-        <v>13.06720540269677</v>
+        <v>13.06720442963625</v>
       </c>
       <c r="F148" t="n">
         <v>2514879</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00002039001773</v>
+        <v>13.00001949529792</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113177437019</v>
+        <v>13.36113085479707</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3432,16 +3432,16 @@
         <v>44447</v>
       </c>
       <c r="B151" t="n">
-        <v>13.23516273498535</v>
+        <v>13.23516368865967</v>
       </c>
       <c r="C151" t="n">
-        <v>14.67960903587777</v>
+        <v>14.67961009363327</v>
       </c>
       <c r="D151" t="n">
-        <v>13.10079531628589</v>
+        <v>13.10079626027822</v>
       </c>
       <c r="E151" t="n">
-        <v>13.80622203202309</v>
+        <v>13.80622302684572</v>
       </c>
       <c r="F151" t="n">
         <v>4568970</v>
@@ -3452,16 +3452,16 @@
         <v>44448</v>
       </c>
       <c r="B152" t="n">
-        <v>13.12598896026611</v>
+        <v>13.12598991394043</v>
       </c>
       <c r="C152" t="n">
-        <v>13.37792776119036</v>
+        <v>13.3779287331694</v>
       </c>
       <c r="D152" t="n">
-        <v>12.52973482635177</v>
+        <v>12.52973573670498</v>
       </c>
       <c r="E152" t="n">
-        <v>13.21836630412647</v>
+        <v>13.2183672645125</v>
       </c>
       <c r="F152" t="n">
         <v>3739731</v>
@@ -3492,16 +3492,16 @@
         <v>44452</v>
       </c>
       <c r="B154" t="n">
-        <v>13.3947229385376</v>
+        <v>13.39472389221191</v>
       </c>
       <c r="C154" t="n">
-        <v>13.53748836688323</v>
+        <v>13.53748933072213</v>
       </c>
       <c r="D154" t="n">
-        <v>12.97482629121558</v>
+        <v>12.9748272149942</v>
       </c>
       <c r="E154" t="n">
-        <v>13.24356030786057</v>
+        <v>13.24356125077245</v>
       </c>
       <c r="F154" t="n">
         <v>1856739</v>
@@ -3532,16 +3532,16 @@
         <v>44454</v>
       </c>
       <c r="B156" t="n">
-        <v>13.44511222839355</v>
+        <v>13.44511127471924</v>
       </c>
       <c r="C156" t="n">
-        <v>14.07495766172759</v>
+        <v>14.07495666337775</v>
       </c>
       <c r="D156" t="n">
-        <v>13.23516348001735</v>
+        <v>13.2351625412349</v>
       </c>
       <c r="E156" t="n">
-        <v>13.47030546123482</v>
+        <v>13.47030450577353</v>
       </c>
       <c r="F156" t="n">
         <v>2602050</v>
@@ -3552,16 +3552,16 @@
         <v>44455</v>
       </c>
       <c r="B157" t="n">
-        <v>13.56268215179443</v>
+        <v>13.56268310546875</v>
       </c>
       <c r="C157" t="n">
-        <v>13.78942690530008</v>
+        <v>13.78942787491819</v>
       </c>
       <c r="D157" t="n">
-        <v>13.33593739828879</v>
+        <v>13.33593833601931</v>
       </c>
       <c r="E157" t="n">
-        <v>13.47870282392425</v>
+        <v>13.47870377169347</v>
       </c>
       <c r="F157" t="n">
         <v>1227183</v>
@@ -3572,16 +3572,16 @@
         <v>44456</v>
       </c>
       <c r="B158" t="n">
-        <v>13.44511222839355</v>
+        <v>13.44511127471924</v>
       </c>
       <c r="C158" t="n">
-        <v>13.74743914043451</v>
+        <v>13.74743816531587</v>
       </c>
       <c r="D158" t="n">
-        <v>13.29394877237308</v>
+        <v>13.29394782942092</v>
       </c>
       <c r="E158" t="n">
-        <v>13.40312296579506</v>
+        <v>13.40312201509908</v>
       </c>
       <c r="F158" t="n">
         <v>5378949</v>
@@ -3592,16 +3592,16 @@
         <v>44459</v>
       </c>
       <c r="B159" t="n">
-        <v>12.84885692596436</v>
+        <v>12.84885787963867</v>
       </c>
       <c r="C159" t="n">
-        <v>13.10919292918942</v>
+        <v>13.10919390218652</v>
       </c>
       <c r="D159" t="n">
-        <v>12.63051018168811</v>
+        <v>12.63051111915618</v>
       </c>
       <c r="E159" t="n">
-        <v>13.10919292918942</v>
+        <v>13.10919390218652</v>
       </c>
       <c r="F159" t="n">
         <v>1643373</v>
@@ -3612,16 +3612,16 @@
         <v>44460</v>
       </c>
       <c r="B160" t="n">
-        <v>13.5206937789917</v>
+        <v>13.52069282531738</v>
       </c>
       <c r="C160" t="n">
-        <v>13.64666319250508</v>
+        <v>13.64666222994559</v>
       </c>
       <c r="D160" t="n">
-        <v>12.80686818480864</v>
+        <v>12.8068672814836</v>
       </c>
       <c r="E160" t="n">
-        <v>12.98322568844521</v>
+        <v>12.9832247726809</v>
       </c>
       <c r="F160" t="n">
         <v>1911981</v>
@@ -3632,16 +3632,16 @@
         <v>44461</v>
       </c>
       <c r="B161" t="n">
-        <v>14.10015106201172</v>
+        <v>14.10015201568604</v>
       </c>
       <c r="C161" t="n">
-        <v>14.46126322911574</v>
+        <v>14.46126420721415</v>
       </c>
       <c r="D161" t="n">
-        <v>13.58787626629261</v>
+        <v>13.58787718531884</v>
       </c>
       <c r="E161" t="n">
-        <v>13.71384566466818</v>
+        <v>13.71384659221444</v>
       </c>
       <c r="F161" t="n">
         <v>3751489</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.6124267578125</v>
+        <v>14.61242580413818</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630275876303</v>
+        <v>15.11630177220344</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893722044467</v>
+        <v>14.15893629636717</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19252927855919</v>
+        <v>14.19252835228931</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26811086618383</v>
+        <v>14.26810988418833</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141734965053</v>
+        <v>13.83141639771024</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733468994271</v>
+        <v>14.16733371488308</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3692,16 +3692,16 @@
         <v>44466</v>
       </c>
       <c r="B164" t="n">
-        <v>13.77263164520264</v>
+        <v>13.77263069152832</v>
       </c>
       <c r="C164" t="n">
-        <v>13.99097677332576</v>
+        <v>13.99097580453232</v>
       </c>
       <c r="D164" t="n">
-        <v>13.51229563311167</v>
+        <v>13.5122946974641</v>
       </c>
       <c r="E164" t="n">
-        <v>13.8650089921894</v>
+        <v>13.86500803211849</v>
       </c>
       <c r="F164" t="n">
         <v>2647359</v>
@@ -3712,16 +3712,16 @@
         <v>44467</v>
       </c>
       <c r="B165" t="n">
-        <v>13.16797828674316</v>
+        <v>13.1679801940918</v>
       </c>
       <c r="C165" t="n">
-        <v>13.89020096850395</v>
+        <v>13.89020298046473</v>
       </c>
       <c r="D165" t="n">
-        <v>13.15118144759716</v>
+        <v>13.15118335251281</v>
       </c>
       <c r="E165" t="n">
-        <v>13.64666100728992</v>
+        <v>13.64666298397454</v>
       </c>
       <c r="F165" t="n">
         <v>3700200</v>
@@ -3752,16 +3752,16 @@
         <v>44469</v>
       </c>
       <c r="B167" t="n">
-        <v>12.55492877960205</v>
+        <v>12.55492973327637</v>
       </c>
       <c r="C167" t="n">
-        <v>13.05880556607607</v>
+        <v>13.05880655802494</v>
       </c>
       <c r="D167" t="n">
-        <v>12.370174093194</v>
+        <v>12.37017503283432</v>
       </c>
       <c r="E167" t="n">
-        <v>13.05880556607607</v>
+        <v>13.05880655802494</v>
       </c>
       <c r="F167" t="n">
         <v>6213762</v>
@@ -3772,16 +3772,16 @@
         <v>44470</v>
       </c>
       <c r="B168" t="n">
-        <v>12.78167247772217</v>
+        <v>12.7816743850708</v>
       </c>
       <c r="C168" t="n">
-        <v>13.11759141127408</v>
+        <v>13.11759336875031</v>
       </c>
       <c r="D168" t="n">
-        <v>12.00066367672549</v>
+        <v>12.00066546752786</v>
       </c>
       <c r="E168" t="n">
-        <v>12.6557038923833</v>
+        <v>12.65570578093424</v>
       </c>
       <c r="F168" t="n">
         <v>6332153</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34497928619385</v>
+        <v>12.34498023986816</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366200074284</v>
+        <v>12.82366299139635</v>
       </c>
       <c r="D169" t="n">
-        <v>12.13503057051905</v>
+        <v>12.1350315079744</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288664969071</v>
+        <v>12.72288763255913</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14342880249023</v>
+        <v>12.14342975616455</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55492822767014</v>
+        <v>12.55492921366123</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027611048266</v>
+        <v>11.95027704898789</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337752194098</v>
+        <v>12.35337849210345</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3852,16 +3852,16 @@
         <v>44476</v>
       </c>
       <c r="B172" t="n">
-        <v>13.00002098083496</v>
+        <v>13.00001811981201</v>
       </c>
       <c r="C172" t="n">
-        <v>13.02521502604024</v>
+        <v>13.02521215947263</v>
       </c>
       <c r="D172" t="n">
-        <v>12.36177670640198</v>
+        <v>12.36177398584277</v>
       </c>
       <c r="E172" t="n">
-        <v>12.56332825624967</v>
+        <v>12.56332549133332</v>
       </c>
       <c r="F172" t="n">
         <v>3555051</v>
@@ -3872,16 +3872,16 @@
         <v>44477</v>
       </c>
       <c r="B173" t="n">
-        <v>13.05880546569824</v>
+        <v>13.05880641937256</v>
       </c>
       <c r="C173" t="n">
-        <v>13.38632476554297</v>
+        <v>13.38632574313576</v>
       </c>
       <c r="D173" t="n">
-        <v>12.8992440109945</v>
+        <v>12.89924495301617</v>
       </c>
       <c r="E173" t="n">
-        <v>13.1175915638818</v>
+        <v>13.11759252184922</v>
       </c>
       <c r="F173" t="n">
         <v>3251676</v>
@@ -3912,16 +3912,16 @@
         <v>44482</v>
       </c>
       <c r="B175" t="n">
-        <v>13.12598896026611</v>
+        <v>13.12598991394043</v>
       </c>
       <c r="C175" t="n">
-        <v>13.34433570458859</v>
+        <v>13.34433667412699</v>
       </c>
       <c r="D175" t="n">
-        <v>12.83206171217867</v>
+        <v>12.83206264449757</v>
       </c>
       <c r="E175" t="n">
-        <v>12.83206171217867</v>
+        <v>12.83206264449757</v>
       </c>
       <c r="F175" t="n">
         <v>2244954</v>
@@ -3932,16 +3932,16 @@
         <v>44483</v>
       </c>
       <c r="B176" t="n">
-        <v>13.16797828674316</v>
+        <v>13.1679801940918</v>
       </c>
       <c r="C176" t="n">
-        <v>13.29394686829084</v>
+        <v>13.2939487938857</v>
       </c>
       <c r="D176" t="n">
-        <v>12.85725421612295</v>
+        <v>12.85725607846398</v>
       </c>
       <c r="E176" t="n">
-        <v>13.1259882183643</v>
+        <v>13.12599011963078</v>
       </c>
       <c r="F176" t="n">
         <v>1588233</v>
@@ -3992,16 +3992,16 @@
         <v>44488</v>
       </c>
       <c r="B179" t="n">
-        <v>12.3953685760498</v>
+        <v>12.39536762237549</v>
       </c>
       <c r="C179" t="n">
-        <v>13.10919416332626</v>
+        <v>13.10919315473166</v>
       </c>
       <c r="D179" t="n">
-        <v>12.17702181121777</v>
+        <v>12.17702087434261</v>
       </c>
       <c r="E179" t="n">
-        <v>13.05880688548518</v>
+        <v>13.05880588076728</v>
       </c>
       <c r="F179" t="n">
         <v>2260766</v>
@@ -4032,16 +4032,16 @@
         <v>44490</v>
       </c>
       <c r="B181" t="n">
-        <v>11.24485015869141</v>
+        <v>11.24484920501709</v>
       </c>
       <c r="C181" t="n">
-        <v>11.95867573884459</v>
+        <v>11.95867472463081</v>
       </c>
       <c r="D181" t="n">
-        <v>10.8333514897461</v>
+        <v>10.83335057097093</v>
       </c>
       <c r="E181" t="n">
-        <v>11.84950235751801</v>
+        <v>11.84950135256322</v>
       </c>
       <c r="F181" t="n">
         <v>4870723</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.5310230255127</v>
+        <v>10.53102493286133</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174709395853</v>
+        <v>10.84174905758462</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624045672820648</v>
+        <v>9.624047415900147</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174709395853</v>
+        <v>10.84174905758462</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55622005462646</v>
+        <v>10.55621719360352</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650489133509</v>
+        <v>11.02650190285215</v>
       </c>
       <c r="D183" t="n">
-        <v>10.3546692943521</v>
+        <v>10.35466648795489</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699543476365</v>
+        <v>10.65699254642783</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4092,16 +4092,16 @@
         <v>44495</v>
       </c>
       <c r="B184" t="n">
-        <v>9.98515796661377</v>
+        <v>9.985158920288086</v>
       </c>
       <c r="C184" t="n">
-        <v>10.46384072961404</v>
+        <v>10.46384172900696</v>
       </c>
       <c r="D184" t="n">
-        <v>9.825596504417325</v>
+        <v>9.825597442852056</v>
       </c>
       <c r="E184" t="n">
-        <v>10.46384072961404</v>
+        <v>10.46384172900696</v>
       </c>
       <c r="F184" t="n">
         <v>5760068</v>
@@ -4112,16 +4112,16 @@
         <v>44496</v>
       </c>
       <c r="B185" t="n">
-        <v>10.3294734954834</v>
+        <v>10.32947254180908</v>
       </c>
       <c r="C185" t="n">
-        <v>10.57301348265372</v>
+        <v>10.57301250649444</v>
       </c>
       <c r="D185" t="n">
-        <v>9.976760130686884</v>
+        <v>9.976759209577022</v>
       </c>
       <c r="E185" t="n">
-        <v>10.07753468194771</v>
+        <v>10.07753375153378</v>
       </c>
       <c r="F185" t="n">
         <v>4005501</v>
@@ -4132,16 +4132,16 @@
         <v>44497</v>
       </c>
       <c r="B186" t="n">
-        <v>9.909576416015625</v>
+        <v>9.909577369689941</v>
       </c>
       <c r="C186" t="n">
-        <v>10.43864644132597</v>
+        <v>10.43864744591674</v>
       </c>
       <c r="D186" t="n">
-        <v>9.825596273781114</v>
+        <v>9.825597219373378</v>
       </c>
       <c r="E186" t="n">
-        <v>10.25389175199907</v>
+        <v>10.25389273880949</v>
       </c>
       <c r="F186" t="n">
         <v>4167680</v>
@@ -4152,16 +4152,16 @@
         <v>44498</v>
       </c>
       <c r="B187" t="n">
-        <v>9.514872550964355</v>
+        <v>9.514873504638672</v>
       </c>
       <c r="C187" t="n">
-        <v>10.06913659309689</v>
+        <v>10.06913760232501</v>
       </c>
       <c r="D187" t="n">
-        <v>9.069781065056384</v>
+        <v>9.069781974119245</v>
       </c>
       <c r="E187" t="n">
-        <v>10.06913659309689</v>
+        <v>10.06913760232501</v>
       </c>
       <c r="F187" t="n">
         <v>8163450</v>
@@ -4172,16 +4172,16 @@
         <v>44501</v>
       </c>
       <c r="B188" t="n">
-        <v>9.464485168457031</v>
+        <v>9.464484214782715</v>
       </c>
       <c r="C188" t="n">
-        <v>9.817198528320054</v>
+        <v>9.817197539105118</v>
       </c>
       <c r="D188" t="n">
-        <v>9.002597620700316</v>
+        <v>9.002596713567389</v>
       </c>
       <c r="E188" t="n">
-        <v>9.220944372898632</v>
+        <v>9.22094344376433</v>
       </c>
       <c r="F188" t="n">
         <v>8542036</v>
@@ -4192,16 +4192,16 @@
         <v>44503</v>
       </c>
       <c r="B189" t="n">
-        <v>10.14471912384033</v>
+        <v>10.14472007751465</v>
       </c>
       <c r="C189" t="n">
-        <v>10.29588176737367</v>
+        <v>10.29588273525833</v>
       </c>
       <c r="D189" t="n">
-        <v>9.548464129163397</v>
+        <v>9.548465026785587</v>
       </c>
       <c r="E189" t="n">
-        <v>9.657638322085189</v>
+        <v>9.657639229970515</v>
       </c>
       <c r="F189" t="n">
         <v>6020061</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55622005462646</v>
+        <v>10.55621719360352</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771877937483</v>
+        <v>10.96771580682453</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588318239185</v>
+        <v>10.29588039192727</v>
       </c>
       <c r="E191" t="n">
-        <v>10.640199402775</v>
+        <v>10.64019651899136</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.74936962127686</v>
+        <v>10.7493724822998</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324637301136</v>
+        <v>11.25324936814477</v>
       </c>
       <c r="D193" t="n">
-        <v>10.4050543144717</v>
+        <v>10.40505708385263</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660420337106</v>
+        <v>10.60660702639595</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4292,16 +4292,16 @@
         <v>44510</v>
       </c>
       <c r="B194" t="n">
-        <v>10.66539192199707</v>
+        <v>10.66539096832275</v>
       </c>
       <c r="C194" t="n">
-        <v>11.16926875045805</v>
+        <v>11.16926775172825</v>
       </c>
       <c r="D194" t="n">
-        <v>10.44704516103155</v>
+        <v>10.44704422688129</v>
       </c>
       <c r="E194" t="n">
-        <v>10.74937125810814</v>
+        <v>10.74937029692459</v>
       </c>
       <c r="F194" t="n">
         <v>2771222</v>
@@ -4312,16 +4312,16 @@
         <v>44511</v>
       </c>
       <c r="B195" t="n">
-        <v>11.21965599060059</v>
+        <v>11.21965503692627</v>
       </c>
       <c r="C195" t="n">
-        <v>11.5303801014484</v>
+        <v>11.53037912136244</v>
       </c>
       <c r="D195" t="n">
-        <v>10.69058593129811</v>
+        <v>10.69058502259491</v>
       </c>
       <c r="E195" t="n">
-        <v>10.78296247010213</v>
+        <v>10.7829615535469</v>
       </c>
       <c r="F195" t="n">
         <v>2903296</v>
@@ -4372,16 +4372,16 @@
         <v>44517</v>
       </c>
       <c r="B198" t="n">
-        <v>10.10272884368896</v>
+        <v>10.10272979736328</v>
       </c>
       <c r="C198" t="n">
-        <v>10.35466766016802</v>
+        <v>10.35466863762478</v>
       </c>
       <c r="D198" t="n">
-        <v>9.800403562785382</v>
+        <v>9.800404487920888</v>
       </c>
       <c r="E198" t="n">
-        <v>10.29588155748545</v>
+        <v>10.29588252939294</v>
       </c>
       <c r="F198" t="n">
         <v>3557179</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674434661865234</v>
+        <v>9.674433708190918</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34627018804897</v>
+        <v>10.34626916814729</v>
       </c>
       <c r="D202" t="n">
-        <v>9.481281937939977</v>
+        <v>9.48128100330603</v>
       </c>
       <c r="E202" t="n">
-        <v>10.2874840822837</v>
+        <v>10.28748306817697</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4532,16 +4532,16 @@
         <v>44529</v>
       </c>
       <c r="B206" t="n">
-        <v>9.632443428039551</v>
+        <v>9.632444381713867</v>
       </c>
       <c r="C206" t="n">
-        <v>9.909576269733462</v>
+        <v>9.909577250845725</v>
       </c>
       <c r="D206" t="n">
-        <v>9.456086755539426</v>
+        <v>9.456087691753288</v>
       </c>
       <c r="E206" t="n">
-        <v>9.741616799538319</v>
+        <v>9.741617764021505</v>
       </c>
       <c r="F206" t="n">
         <v>2527144</v>
@@ -4612,16 +4612,16 @@
         <v>44533</v>
       </c>
       <c r="B210" t="n">
-        <v>9.901177406311035</v>
+        <v>9.901176452636719</v>
       </c>
       <c r="C210" t="n">
-        <v>10.08593290400486</v>
+        <v>10.08593193253503</v>
       </c>
       <c r="D210" t="n">
-        <v>9.615647363394388</v>
+        <v>9.615646437222118</v>
       </c>
       <c r="E210" t="n">
-        <v>9.649239419664992</v>
+        <v>9.64923849025716</v>
       </c>
       <c r="F210" t="n">
         <v>1913704</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884382247924805</v>
+        <v>9.884383201599121</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709559365621</v>
+        <v>10.23709658136135</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573657349188849</v>
+        <v>9.573658272883511</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867585407896522</v>
+        <v>9.867586359950231</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4652,16 +4652,16 @@
         <v>44537</v>
       </c>
       <c r="B212" t="n">
-        <v>9.98515796661377</v>
+        <v>9.985158920288086</v>
       </c>
       <c r="C212" t="n">
-        <v>10.53102403318413</v>
+        <v>10.53102503899367</v>
       </c>
       <c r="D212" t="n">
-        <v>9.867585764725682</v>
+        <v>9.867586707170773</v>
       </c>
       <c r="E212" t="n">
-        <v>10.00195318366039</v>
+        <v>10.00195413893881</v>
       </c>
       <c r="F212" t="n">
         <v>3095174</v>
@@ -4672,16 +4672,16 @@
         <v>44538</v>
       </c>
       <c r="B213" t="n">
-        <v>10.57301330566406</v>
+        <v>10.57301425933838</v>
       </c>
       <c r="C213" t="n">
-        <v>10.66539146439676</v>
+        <v>10.66539242640349</v>
       </c>
       <c r="D213" t="n">
-        <v>9.792004458007494</v>
+        <v>9.792005341235662</v>
       </c>
       <c r="E213" t="n">
-        <v>9.985157978108607</v>
+        <v>9.985158878759011</v>
       </c>
       <c r="F213" t="n">
         <v>3040540</v>
@@ -4692,16 +4692,16 @@
         <v>44539</v>
       </c>
       <c r="B214" t="n">
-        <v>10.78222846984863</v>
+        <v>10.78222942352295</v>
       </c>
       <c r="C214" t="n">
-        <v>11.00401580523902</v>
+        <v>11.00401677853015</v>
       </c>
       <c r="D214" t="n">
-        <v>10.23629250667595</v>
+        <v>10.23629341206293</v>
       </c>
       <c r="E214" t="n">
-        <v>10.46661015591148</v>
+        <v>10.46661108166976</v>
       </c>
       <c r="F214" t="n">
         <v>2489235</v>
@@ -4772,16 +4772,16 @@
         <v>44545</v>
       </c>
       <c r="B218" t="n">
-        <v>11.26845264434814</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C218" t="n">
-        <v>11.37934507107126</v>
+        <v>11.37934603413065</v>
       </c>
       <c r="D218" t="n">
-        <v>10.8163493255928</v>
+        <v>10.8163502410046</v>
       </c>
       <c r="E218" t="n">
-        <v>10.90165163630924</v>
+        <v>10.90165255894037</v>
       </c>
       <c r="F218" t="n">
         <v>3122034</v>
@@ -4792,16 +4792,16 @@
         <v>44546</v>
       </c>
       <c r="B219" t="n">
-        <v>11.14049816131592</v>
+        <v>11.14049911499023</v>
       </c>
       <c r="C219" t="n">
-        <v>11.49023854919888</v>
+        <v>11.49023953281247</v>
       </c>
       <c r="D219" t="n">
-        <v>10.85900110760307</v>
+        <v>10.85900203718004</v>
       </c>
       <c r="E219" t="n">
-        <v>11.39640592310018</v>
+        <v>11.3964068986813</v>
       </c>
       <c r="F219" t="n">
         <v>2253468</v>
@@ -4812,16 +4812,16 @@
         <v>44547</v>
       </c>
       <c r="B220" t="n">
-        <v>11.17462062835693</v>
+        <v>11.17461967468262</v>
       </c>
       <c r="C220" t="n">
-        <v>11.21727220147566</v>
+        <v>11.21727124416134</v>
       </c>
       <c r="D220" t="n">
-        <v>10.91871366339456</v>
+        <v>10.91871273156008</v>
       </c>
       <c r="E220" t="n">
-        <v>11.19168208218776</v>
+        <v>11.19168112705737</v>
       </c>
       <c r="F220" t="n">
         <v>2659218</v>
@@ -4852,16 +4852,16 @@
         <v>44551</v>
       </c>
       <c r="B222" t="n">
-        <v>10.73957824707031</v>
+        <v>10.739577293396</v>
       </c>
       <c r="C222" t="n">
-        <v>11.05519824974405</v>
+        <v>11.05519726804268</v>
       </c>
       <c r="D222" t="n">
-        <v>10.51779253304062</v>
+        <v>10.51779159906087</v>
       </c>
       <c r="E222" t="n">
-        <v>10.8419420260456</v>
+        <v>10.84194106328138</v>
       </c>
       <c r="F222" t="n">
         <v>1915833</v>
@@ -4872,16 +4872,16 @@
         <v>44552</v>
       </c>
       <c r="B223" t="n">
-        <v>10.5775032043457</v>
+        <v>10.57750511169434</v>
       </c>
       <c r="C223" t="n">
-        <v>10.84194045462105</v>
+        <v>10.84194240965334</v>
       </c>
       <c r="D223" t="n">
-        <v>10.33865524593855</v>
+        <v>10.33865711021782</v>
       </c>
       <c r="E223" t="n">
-        <v>10.83341014094282</v>
+        <v>10.83341209443691</v>
       </c>
       <c r="F223" t="n">
         <v>1137579</v>
@@ -4892,16 +4892,16 @@
         <v>44553</v>
       </c>
       <c r="B224" t="n">
-        <v>10.38983821868896</v>
+        <v>10.38983917236328</v>
       </c>
       <c r="C224" t="n">
-        <v>10.6542754757369</v>
+        <v>10.65427645368369</v>
       </c>
       <c r="D224" t="n">
-        <v>10.1936418236481</v>
+        <v>10.19364275931372</v>
       </c>
       <c r="E224" t="n">
-        <v>10.56897316135316</v>
+        <v>10.56897413147012</v>
       </c>
       <c r="F224" t="n">
         <v>1383482</v>
@@ -4932,16 +4932,16 @@
         <v>44558</v>
       </c>
       <c r="B226" t="n">
-        <v>10.08274841308594</v>
+        <v>10.08274936676025</v>
       </c>
       <c r="C226" t="n">
-        <v>10.50073048928689</v>
+        <v>10.50073148249594</v>
       </c>
       <c r="D226" t="n">
-        <v>9.988916610826452</v>
+        <v>9.98891755562571</v>
       </c>
       <c r="E226" t="n">
-        <v>10.15952041239668</v>
+        <v>10.15952137333246</v>
       </c>
       <c r="F226" t="n">
         <v>1405681</v>
@@ -4972,16 +4972,16 @@
         <v>44560</v>
       </c>
       <c r="B228" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="C228" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="D228" t="n">
-        <v>9.647706562908386</v>
+        <v>9.647705662569827</v>
       </c>
       <c r="E228" t="n">
-        <v>9.7927210851769</v>
+        <v>9.792720171305367</v>
       </c>
       <c r="F228" t="n">
         <v>3325771</v>
@@ -5012,16 +5012,16 @@
         <v>44565</v>
       </c>
       <c r="B230" t="n">
-        <v>9.238256454467773</v>
+        <v>9.238255500793457</v>
       </c>
       <c r="C230" t="n">
-        <v>9.826843264047191</v>
+        <v>9.826842249612479</v>
       </c>
       <c r="D230" t="n">
-        <v>9.170013931907791</v>
+        <v>9.170012985278218</v>
       </c>
       <c r="E230" t="n">
-        <v>9.758600741487211</v>
+        <v>9.75859973409724</v>
       </c>
       <c r="F230" t="n">
         <v>4143150</v>
@@ -5152,16 +5152,16 @@
         <v>44574</v>
       </c>
       <c r="B237" t="n">
-        <v>8.7264404296875</v>
+        <v>8.726439476013184</v>
       </c>
       <c r="C237" t="n">
-        <v>9.110300442131042</v>
+        <v>9.110299446506351</v>
       </c>
       <c r="D237" t="n">
-        <v>8.555834971888574</v>
+        <v>8.555834036858977</v>
       </c>
       <c r="E237" t="n">
-        <v>9.042058753761445</v>
+        <v>9.042057765594588</v>
       </c>
       <c r="F237" t="n">
         <v>3017328</v>
@@ -5212,16 +5212,16 @@
         <v>44579</v>
       </c>
       <c r="B240" t="n">
-        <v>8.30845832824707</v>
+        <v>8.308457374572754</v>
       </c>
       <c r="C240" t="n">
-        <v>8.760562547247821</v>
+        <v>8.76056154167938</v>
       </c>
       <c r="D240" t="n">
-        <v>8.206095373339679</v>
+        <v>8.206094431414945</v>
       </c>
       <c r="E240" t="n">
-        <v>8.530244867976979</v>
+        <v>8.530243888845217</v>
       </c>
       <c r="F240" t="n">
         <v>2291580</v>
@@ -5232,16 +5232,16 @@
         <v>44580</v>
       </c>
       <c r="B241" t="n">
-        <v>8.521713256835938</v>
+        <v>8.521714210510254</v>
       </c>
       <c r="C241" t="n">
-        <v>8.675258078133986</v>
+        <v>8.675259048991672</v>
       </c>
       <c r="D241" t="n">
-        <v>8.291397261763732</v>
+        <v>8.291398189663132</v>
       </c>
       <c r="E241" t="n">
-        <v>8.308457064500631</v>
+        <v>8.308457994309213</v>
       </c>
       <c r="F241" t="n">
         <v>1675201</v>
@@ -5292,16 +5292,16 @@
         <v>44585</v>
       </c>
       <c r="B244" t="n">
-        <v>9.460041046142578</v>
+        <v>9.460041999816895</v>
       </c>
       <c r="C244" t="n">
-        <v>9.596525250334361</v>
+        <v>9.596526217767758</v>
       </c>
       <c r="D244" t="n">
-        <v>9.144421890850102</v>
+        <v>9.144422812706599</v>
       </c>
       <c r="E244" t="n">
-        <v>9.536813050245259</v>
+        <v>9.536814011659024</v>
       </c>
       <c r="F244" t="n">
         <v>1483323</v>
@@ -5312,16 +5312,16 @@
         <v>44586</v>
       </c>
       <c r="B245" t="n">
-        <v>9.843902587890625</v>
+        <v>9.843901634216309</v>
       </c>
       <c r="C245" t="n">
-        <v>9.929204905183155</v>
+        <v>9.929203943244776</v>
       </c>
       <c r="D245" t="n">
-        <v>9.383268920094348</v>
+        <v>9.383268011046082</v>
       </c>
       <c r="E245" t="n">
-        <v>9.391799234281931</v>
+        <v>9.391798324407251</v>
       </c>
       <c r="F245" t="n">
         <v>2635195</v>
@@ -5372,16 +5372,16 @@
         <v>44589</v>
       </c>
       <c r="B248" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="C248" t="n">
-        <v>10.26188426089857</v>
+        <v>10.26188330324402</v>
       </c>
       <c r="D248" t="n">
-        <v>9.681827820991172</v>
+        <v>9.681826917468367</v>
       </c>
       <c r="E248" t="n">
-        <v>10.19364256931633</v>
+        <v>10.1936416180302</v>
       </c>
       <c r="F248" t="n">
         <v>1431224</v>
@@ -5392,16 +5392,16 @@
         <v>44592</v>
       </c>
       <c r="B249" t="n">
-        <v>10.47513961791992</v>
+        <v>10.47514057159424</v>
       </c>
       <c r="C249" t="n">
-        <v>10.56044193156613</v>
+        <v>10.56044289300652</v>
       </c>
       <c r="D249" t="n">
-        <v>10.1851114216895</v>
+        <v>10.18511234895917</v>
       </c>
       <c r="E249" t="n">
-        <v>10.22776299080424</v>
+        <v>10.22776392195697</v>
       </c>
       <c r="F249" t="n">
         <v>3321007</v>
@@ -5412,16 +5412,16 @@
         <v>44593</v>
       </c>
       <c r="B250" t="n">
-        <v>10.62015438079834</v>
+        <v>10.62015533447266</v>
       </c>
       <c r="C250" t="n">
-        <v>10.68839606842096</v>
+        <v>10.68839702822328</v>
       </c>
       <c r="D250" t="n">
-        <v>10.33012617767312</v>
+        <v>10.33012710530333</v>
       </c>
       <c r="E250" t="n">
-        <v>10.65427563690129</v>
+        <v>10.65427659363964</v>
       </c>
       <c r="F250" t="n">
         <v>1255057</v>
@@ -5432,16 +5432,16 @@
         <v>44594</v>
       </c>
       <c r="B251" t="n">
-        <v>10.62015438079834</v>
+        <v>10.62015533447266</v>
       </c>
       <c r="C251" t="n">
-        <v>10.92724238739176</v>
+        <v>10.92724336864213</v>
       </c>
       <c r="D251" t="n">
-        <v>10.40689817932147</v>
+        <v>10.40689911384569</v>
       </c>
       <c r="E251" t="n">
-        <v>10.62015438079834</v>
+        <v>10.62015533447266</v>
       </c>
       <c r="F251" t="n">
         <v>1616614</v>
@@ -5472,16 +5472,16 @@
         <v>44596</v>
       </c>
       <c r="B253" t="n">
-        <v>10.2533540725708</v>
+        <v>10.25335502624512</v>
       </c>
       <c r="C253" t="n">
-        <v>10.56044207606577</v>
+        <v>10.56044305830264</v>
       </c>
       <c r="D253" t="n">
-        <v>9.835371163276871</v>
+        <v>9.835372078074196</v>
       </c>
       <c r="E253" t="n">
-        <v>10.56044207606577</v>
+        <v>10.56044305830264</v>
       </c>
       <c r="F253" t="n">
         <v>2130212</v>
@@ -5592,16 +5592,16 @@
         <v>44606</v>
       </c>
       <c r="B259" t="n">
-        <v>10.5775032043457</v>
+        <v>10.57750511169434</v>
       </c>
       <c r="C259" t="n">
-        <v>10.65427520286651</v>
+        <v>10.65427712405877</v>
       </c>
       <c r="D259" t="n">
-        <v>9.767129176996722</v>
+        <v>9.767130938217694</v>
       </c>
       <c r="E259" t="n">
-        <v>9.775660315258195</v>
+        <v>9.775662078017515</v>
       </c>
       <c r="F259" t="n">
         <v>2873091</v>
@@ -5672,16 +5672,16 @@
         <v>44610</v>
       </c>
       <c r="B263" t="n">
-        <v>9.954795837402344</v>
+        <v>9.95479679107666</v>
       </c>
       <c r="C263" t="n">
-        <v>10.38983856218384</v>
+        <v>10.38983955753546</v>
       </c>
       <c r="D263" t="n">
-        <v>9.519753112620847</v>
+        <v>9.519754024617859</v>
       </c>
       <c r="E263" t="n">
-        <v>10.38983856218384</v>
+        <v>10.38983955753546</v>
       </c>
       <c r="F263" t="n">
         <v>12813814</v>
@@ -5732,16 +5732,16 @@
         <v>44615</v>
       </c>
       <c r="B266" t="n">
-        <v>9.767128944396973</v>
+        <v>9.767129898071289</v>
       </c>
       <c r="C266" t="n">
-        <v>10.11686932312569</v>
+        <v>10.11687031094908</v>
       </c>
       <c r="D266" t="n">
-        <v>9.68182663422937</v>
+        <v>9.681827579574664</v>
       </c>
       <c r="E266" t="n">
-        <v>9.775660082455282</v>
+        <v>9.775661036962589</v>
       </c>
       <c r="F266" t="n">
         <v>2319860</v>
@@ -5772,16 +5772,16 @@
         <v>44617</v>
       </c>
       <c r="B268" t="n">
-        <v>9.425921440124512</v>
+        <v>9.425919532775879</v>
       </c>
       <c r="C268" t="n">
-        <v>9.869493699625441</v>
+        <v>9.86949170251933</v>
       </c>
       <c r="D268" t="n">
-        <v>9.383269864892029</v>
+        <v>9.383267966174003</v>
       </c>
       <c r="E268" t="n">
-        <v>9.579465461794694</v>
+        <v>9.579463523376209</v>
       </c>
       <c r="F268" t="n">
         <v>3597927</v>
@@ -5792,16 +5792,16 @@
         <v>44622</v>
       </c>
       <c r="B269" t="n">
-        <v>9.57093334197998</v>
+        <v>9.570934295654297</v>
       </c>
       <c r="C269" t="n">
-        <v>9.656235651776313</v>
+        <v>9.656236613950387</v>
       </c>
       <c r="D269" t="n">
-        <v>9.272374845401204</v>
+        <v>9.272375769326324</v>
       </c>
       <c r="E269" t="n">
-        <v>9.34914684175958</v>
+        <v>9.349147773334476</v>
       </c>
       <c r="F269" t="n">
         <v>1474809</v>
@@ -5832,16 +5832,16 @@
         <v>44624</v>
       </c>
       <c r="B271" t="n">
-        <v>9.323555946350098</v>
+        <v>9.323556900024414</v>
       </c>
       <c r="C271" t="n">
-        <v>9.613584955470987</v>
+        <v>9.613585938811369</v>
       </c>
       <c r="D271" t="n">
-        <v>8.931164824647187</v>
+        <v>8.931165738185172</v>
       </c>
       <c r="E271" t="n">
-        <v>9.511221193722513</v>
+        <v>9.511222166592459</v>
       </c>
       <c r="F271" t="n">
         <v>3245493</v>
@@ -5912,16 +5912,16 @@
         <v>44630</v>
       </c>
       <c r="B275" t="n">
-        <v>9.19560432434082</v>
+        <v>9.195603370666504</v>
       </c>
       <c r="C275" t="n">
-        <v>9.280906647822642</v>
+        <v>9.28090568530164</v>
       </c>
       <c r="D275" t="n">
-        <v>8.922635899698962</v>
+        <v>8.922634974334148</v>
       </c>
       <c r="E275" t="n">
-        <v>9.144422435501713</v>
+        <v>9.144421487135462</v>
       </c>
       <c r="F275" t="n">
         <v>2148356</v>
@@ -5932,16 +5932,16 @@
         <v>44631</v>
       </c>
       <c r="B276" t="n">
-        <v>8.615547180175781</v>
+        <v>8.615548133850098</v>
       </c>
       <c r="C276" t="n">
-        <v>9.19560359341205</v>
+        <v>9.195604611294117</v>
       </c>
       <c r="D276" t="n">
-        <v>8.470532664575069</v>
+        <v>8.470533602197403</v>
       </c>
       <c r="E276" t="n">
-        <v>9.19560359341205</v>
+        <v>9.195604611294117</v>
       </c>
       <c r="F276" t="n">
         <v>3220051</v>
@@ -5952,16 +5952,16 @@
         <v>44634</v>
       </c>
       <c r="B277" t="n">
-        <v>8.769091606140137</v>
+        <v>8.76909065246582</v>
       </c>
       <c r="C277" t="n">
-        <v>8.879984870548604</v>
+        <v>8.879983904814196</v>
       </c>
       <c r="D277" t="n">
-        <v>8.572896020936692</v>
+        <v>8.572895088599443</v>
       </c>
       <c r="E277" t="n">
-        <v>8.624077908163676</v>
+        <v>8.624076970260189</v>
       </c>
       <c r="F277" t="n">
         <v>3142307</v>
@@ -6012,16 +6012,16 @@
         <v>44637</v>
       </c>
       <c r="B280" t="n">
-        <v>9.238256454467773</v>
+        <v>9.238255500793457</v>
       </c>
       <c r="C280" t="n">
-        <v>9.297967012540948</v>
+        <v>9.297966052702654</v>
       </c>
       <c r="D280" t="n">
-        <v>8.632608189664953</v>
+        <v>8.632607298512305</v>
       </c>
       <c r="E280" t="n">
-        <v>8.999409274674644</v>
+        <v>8.999408345656759</v>
       </c>
       <c r="F280" t="n">
         <v>2645230</v>
@@ -6072,16 +6072,16 @@
         <v>44642</v>
       </c>
       <c r="B283" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C283" t="n">
-        <v>10.1253999073854</v>
+        <v>10.12539894068065</v>
       </c>
       <c r="D283" t="n">
-        <v>9.57093441902218</v>
+        <v>9.570933505254049</v>
       </c>
       <c r="E283" t="n">
-        <v>9.57093441902218</v>
+        <v>9.570933505254049</v>
       </c>
       <c r="F283" t="n">
         <v>2594043</v>
@@ -6092,16 +6092,16 @@
         <v>44643</v>
       </c>
       <c r="B284" t="n">
-        <v>10.31306552886963</v>
+        <v>10.31306457519531</v>
       </c>
       <c r="C284" t="n">
-        <v>10.31306552886963</v>
+        <v>10.31306457519531</v>
       </c>
       <c r="D284" t="n">
-        <v>9.809781909623382</v>
+        <v>9.809781002488929</v>
       </c>
       <c r="E284" t="n">
-        <v>9.988917693542961</v>
+        <v>9.988916769843387</v>
       </c>
       <c r="F284" t="n">
         <v>2504946</v>
@@ -6152,16 +6152,16 @@
         <v>44648</v>
       </c>
       <c r="B287" t="n">
-        <v>10.8845911026001</v>
+        <v>10.88459205627441</v>
       </c>
       <c r="C287" t="n">
-        <v>11.12343823432117</v>
+        <v>11.12343920892254</v>
       </c>
       <c r="D287" t="n">
-        <v>10.7139856551208</v>
+        <v>10.71398659384719</v>
       </c>
       <c r="E287" t="n">
-        <v>10.73957659593018</v>
+        <v>10.73957753689877</v>
       </c>
       <c r="F287" t="n">
         <v>1829574</v>
@@ -6172,16 +6172,16 @@
         <v>44649</v>
       </c>
       <c r="B288" t="n">
-        <v>11.34522533416748</v>
+        <v>11.3452262878418</v>
       </c>
       <c r="C288" t="n">
-        <v>11.52436028006663</v>
+        <v>11.52436124879894</v>
       </c>
       <c r="D288" t="n">
-        <v>10.85047041755722</v>
+        <v>10.85047132964267</v>
       </c>
       <c r="E288" t="n">
-        <v>10.97842430373515</v>
+        <v>10.97842522657635</v>
       </c>
       <c r="F288" t="n">
         <v>4333811</v>
@@ -6292,16 +6292,16 @@
         <v>44657</v>
       </c>
       <c r="B294" t="n">
-        <v>10.5775032043457</v>
+        <v>10.57750511169434</v>
       </c>
       <c r="C294" t="n">
-        <v>10.73104720138732</v>
+        <v>10.7310491364232</v>
       </c>
       <c r="D294" t="n">
-        <v>10.21070218993162</v>
+        <v>10.21070403113823</v>
       </c>
       <c r="E294" t="n">
-        <v>10.73104720138732</v>
+        <v>10.7310491364232</v>
       </c>
       <c r="F294" t="n">
         <v>3552010</v>
@@ -6332,16 +6332,16 @@
         <v>44659</v>
       </c>
       <c r="B296" t="n">
-        <v>10.36424732208252</v>
+        <v>10.3642463684082</v>
       </c>
       <c r="C296" t="n">
-        <v>10.53485278974883</v>
+        <v>10.53485182037612</v>
       </c>
       <c r="D296" t="n">
-        <v>10.17658287435791</v>
+        <v>10.17658193795169</v>
       </c>
       <c r="E296" t="n">
-        <v>10.53485278974883</v>
+        <v>10.53485182037612</v>
       </c>
       <c r="F296" t="n">
         <v>1523665</v>
@@ -6392,16 +6392,16 @@
         <v>44664</v>
       </c>
       <c r="B299" t="n">
-        <v>10.60309314727783</v>
+        <v>10.60309410095215</v>
       </c>
       <c r="C299" t="n">
-        <v>10.73104702577405</v>
+        <v>10.73104799095693</v>
       </c>
       <c r="D299" t="n">
-        <v>10.38130664443992</v>
+        <v>10.38130757816608</v>
       </c>
       <c r="E299" t="n">
-        <v>10.62015377435509</v>
+        <v>10.62015472956389</v>
       </c>
       <c r="F299" t="n">
         <v>1276242</v>
@@ -6452,16 +6452,16 @@
         <v>44670</v>
       </c>
       <c r="B302" t="n">
-        <v>10.94430446624756</v>
+        <v>10.94430351257324</v>
       </c>
       <c r="C302" t="n">
-        <v>11.07225753478839</v>
+        <v>11.07225656996439</v>
       </c>
       <c r="D302" t="n">
-        <v>10.48367078083392</v>
+        <v>10.4836698672987</v>
       </c>
       <c r="E302" t="n">
-        <v>10.68839667999924</v>
+        <v>10.68839574862444</v>
       </c>
       <c r="F302" t="n">
         <v>3002225</v>
@@ -6492,16 +6492,16 @@
         <v>44673</v>
       </c>
       <c r="B304" t="n">
-        <v>10.37277698516846</v>
+        <v>10.37277793884277</v>
       </c>
       <c r="C304" t="n">
-        <v>10.83341064697621</v>
+        <v>10.83341164300124</v>
       </c>
       <c r="D304" t="n">
-        <v>10.30453529713828</v>
+        <v>10.30453624453844</v>
       </c>
       <c r="E304" t="n">
-        <v>10.72251738856261</v>
+        <v>10.7225183743921</v>
       </c>
       <c r="F304" t="n">
         <v>1699122</v>
@@ -6512,16 +6512,16 @@
         <v>44676</v>
       </c>
       <c r="B305" t="n">
-        <v>10.37277698516846</v>
+        <v>10.37277793884277</v>
       </c>
       <c r="C305" t="n">
-        <v>10.43248918370524</v>
+        <v>10.4324901428695</v>
       </c>
       <c r="D305" t="n">
-        <v>10.15099046834126</v>
+        <v>10.1509914016245</v>
       </c>
       <c r="E305" t="n">
-        <v>10.185111724648</v>
+        <v>10.18511266106835</v>
       </c>
       <c r="F305" t="n">
         <v>3255528</v>
@@ -6532,16 +6532,16 @@
         <v>44677</v>
       </c>
       <c r="B306" t="n">
-        <v>10.38983821868896</v>
+        <v>10.38983917236328</v>
       </c>
       <c r="C306" t="n">
-        <v>10.48367002238615</v>
+        <v>10.4836709846732</v>
       </c>
       <c r="D306" t="n">
-        <v>10.168050881958</v>
+        <v>10.16805181527464</v>
       </c>
       <c r="E306" t="n">
-        <v>10.32159570751536</v>
+        <v>10.32159665492575</v>
       </c>
       <c r="F306" t="n">
         <v>4697699</v>
@@ -6552,16 +6552,16 @@
         <v>44678</v>
       </c>
       <c r="B307" t="n">
-        <v>10.60309314727783</v>
+        <v>10.60309410095215</v>
       </c>
       <c r="C307" t="n">
-        <v>10.79075922054446</v>
+        <v>10.79076019109803</v>
       </c>
       <c r="D307" t="n">
-        <v>10.40689758505581</v>
+        <v>10.4068985210837</v>
       </c>
       <c r="E307" t="n">
-        <v>10.40689758505581</v>
+        <v>10.4068985210837</v>
       </c>
       <c r="F307" t="n">
         <v>2204206</v>
@@ -6592,16 +6592,16 @@
         <v>44680</v>
       </c>
       <c r="B309" t="n">
-        <v>11.65231323242188</v>
+        <v>11.65231418609619</v>
       </c>
       <c r="C309" t="n">
-        <v>11.85703994313725</v>
+        <v>11.85704091356727</v>
       </c>
       <c r="D309" t="n">
-        <v>11.46464797423132</v>
+        <v>11.46464891254633</v>
       </c>
       <c r="E309" t="n">
-        <v>11.68643448830498</v>
+        <v>11.68643544477193</v>
       </c>
       <c r="F309" t="n">
         <v>6890958</v>
@@ -6632,16 +6632,16 @@
         <v>44684</v>
       </c>
       <c r="B311" t="n">
-        <v>11.31963348388672</v>
+        <v>11.31963443756104</v>
       </c>
       <c r="C311" t="n">
-        <v>11.52435935551378</v>
+        <v>11.52436032643616</v>
       </c>
       <c r="D311" t="n">
-        <v>11.25992211490517</v>
+        <v>11.25992306354883</v>
       </c>
       <c r="E311" t="n">
-        <v>11.38787516623467</v>
+        <v>11.38787612565832</v>
       </c>
       <c r="F311" t="n">
         <v>2034324</v>
@@ -6652,16 +6652,16 @@
         <v>44685</v>
       </c>
       <c r="B312" t="n">
-        <v>11.83144855499268</v>
+        <v>11.83144950866699</v>
       </c>
       <c r="C312" t="n">
-        <v>11.95087212149613</v>
+        <v>11.95087308479659</v>
       </c>
       <c r="D312" t="n">
-        <v>10.95283284580649</v>
+        <v>10.95283372865995</v>
       </c>
       <c r="E312" t="n">
-        <v>11.09784735325709</v>
+        <v>11.09784824779946</v>
       </c>
       <c r="F312" t="n">
         <v>3044087</v>
@@ -6672,16 +6672,16 @@
         <v>44686</v>
       </c>
       <c r="B313" t="n">
-        <v>11.60966300964355</v>
+        <v>11.60966205596924</v>
       </c>
       <c r="C313" t="n">
-        <v>11.76320701886124</v>
+        <v>11.76320605257407</v>
       </c>
       <c r="D313" t="n">
-        <v>11.3878764855884</v>
+        <v>11.38787555013271</v>
       </c>
       <c r="E313" t="n">
-        <v>11.76320701886124</v>
+        <v>11.76320605257407</v>
       </c>
       <c r="F313" t="n">
         <v>3999622</v>
@@ -6692,16 +6692,16 @@
         <v>44687</v>
       </c>
       <c r="B314" t="n">
-        <v>11.52436065673828</v>
+        <v>11.52435970306396</v>
       </c>
       <c r="C314" t="n">
-        <v>11.61819328978013</v>
+        <v>11.61819232834089</v>
       </c>
       <c r="D314" t="n">
-        <v>11.20874150029449</v>
+        <v>11.20874057273858</v>
       </c>
       <c r="E314" t="n">
-        <v>11.60966297545057</v>
+        <v>11.60966201471724</v>
       </c>
       <c r="F314" t="n">
         <v>3256744</v>
@@ -6732,16 +6732,16 @@
         <v>44691</v>
       </c>
       <c r="B316" t="n">
-        <v>11.22580146789551</v>
+        <v>11.22580242156982</v>
       </c>
       <c r="C316" t="n">
-        <v>11.40493723368412</v>
+        <v>11.4049382025767</v>
       </c>
       <c r="D316" t="n">
-        <v>11.02107558520846</v>
+        <v>11.02107652149054</v>
       </c>
       <c r="E316" t="n">
-        <v>11.11490821272475</v>
+        <v>11.11490915697827</v>
       </c>
       <c r="F316" t="n">
         <v>2926103</v>
@@ -6752,16 +6752,16 @@
         <v>44692</v>
       </c>
       <c r="B317" t="n">
-        <v>11.25992393493652</v>
+        <v>11.25992298126221</v>
       </c>
       <c r="C317" t="n">
-        <v>11.45611952490985</v>
+        <v>11.45611855461848</v>
       </c>
       <c r="D317" t="n">
-        <v>11.00401696633002</v>
+        <v>11.00401603433009</v>
       </c>
       <c r="E317" t="n">
-        <v>11.22580267595565</v>
+        <v>11.22580172517128</v>
       </c>
       <c r="F317" t="n">
         <v>2884545</v>
@@ -6792,16 +6792,16 @@
         <v>44694</v>
       </c>
       <c r="B319" t="n">
-        <v>11.82291889190674</v>
+        <v>11.82291984558105</v>
       </c>
       <c r="C319" t="n">
-        <v>12.07882584170994</v>
+        <v>12.07882681602652</v>
       </c>
       <c r="D319" t="n">
-        <v>11.45611868314717</v>
+        <v>11.45611960723421</v>
       </c>
       <c r="E319" t="n">
-        <v>11.5328906856298</v>
+        <v>11.53289161590952</v>
       </c>
       <c r="F319" t="n">
         <v>2912723</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381404876709</v>
+        <v>11.93381214141846</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470732535947</v>
+        <v>12.04470540028707</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908730194904</v>
+        <v>11.72908542732132</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81439045669965</v>
+        <v>11.81438856843816</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6832,16 +6832,16 @@
         <v>44698</v>
       </c>
       <c r="B321" t="n">
-        <v>12.15559864044189</v>
+        <v>12.15559673309326</v>
       </c>
       <c r="C321" t="n">
-        <v>12.29208285069394</v>
+        <v>12.29208092192941</v>
       </c>
       <c r="D321" t="n">
-        <v>11.95087356193885</v>
+        <v>11.95087168671386</v>
       </c>
       <c r="E321" t="n">
-        <v>12.02764556945041</v>
+        <v>12.02764368217903</v>
       </c>
       <c r="F321" t="n">
         <v>4223023</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415782928467</v>
+        <v>12.45415687561035</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505109394068</v>
+        <v>12.56505013177474</v>
       </c>
       <c r="D323" t="n">
-        <v>11.95087339334582</v>
+        <v>11.9508724782104</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559846896078</v>
+        <v>12.15559753814858</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6892,16 +6892,16 @@
         <v>44701</v>
       </c>
       <c r="B324" t="n">
-        <v>12.50533866882324</v>
+        <v>12.50533771514893</v>
       </c>
       <c r="C324" t="n">
-        <v>12.65888350352286</v>
+        <v>12.658882538139</v>
       </c>
       <c r="D324" t="n">
-        <v>12.30914391126722</v>
+        <v>12.30914297255499</v>
       </c>
       <c r="E324" t="n">
-        <v>12.47974772560942</v>
+        <v>12.4797467738867</v>
       </c>
       <c r="F324" t="n">
         <v>4482610</v>
@@ -6932,16 +6932,16 @@
         <v>44705</v>
       </c>
       <c r="B326" t="n">
-        <v>12.26649188995361</v>
+        <v>12.2664909362793</v>
       </c>
       <c r="C326" t="n">
-        <v>12.62476263215845</v>
+        <v>12.62476165062991</v>
       </c>
       <c r="D326" t="n">
-        <v>12.02764555306706</v>
+        <v>12.02764461796216</v>
       </c>
       <c r="E326" t="n">
-        <v>12.53092999542028</v>
+        <v>12.53092902118688</v>
       </c>
       <c r="F326" t="n">
         <v>3539137</v>
@@ -6992,16 +6992,16 @@
         <v>44708</v>
       </c>
       <c r="B329" t="n">
-        <v>13.06833362579346</v>
+        <v>13.06833457946777</v>
       </c>
       <c r="C329" t="n">
-        <v>13.35836182301952</v>
+        <v>13.35836279785892</v>
       </c>
       <c r="D329" t="n">
-        <v>12.7612456254462</v>
+        <v>12.76124655671047</v>
       </c>
       <c r="E329" t="n">
-        <v>12.78683656700289</v>
+        <v>12.78683750013469</v>
       </c>
       <c r="F329" t="n">
         <v>4177410</v>
@@ -7012,16 +7012,16 @@
         <v>44711</v>
       </c>
       <c r="B330" t="n">
-        <v>12.73565578460693</v>
+        <v>12.73565483093262</v>
       </c>
       <c r="C330" t="n">
-        <v>13.33277285837116</v>
+        <v>13.33277185998338</v>
       </c>
       <c r="D330" t="n">
-        <v>12.73565578460693</v>
+        <v>12.73565483093262</v>
       </c>
       <c r="E330" t="n">
-        <v>13.26453116623858</v>
+        <v>13.26453017296089</v>
       </c>
       <c r="F330" t="n">
         <v>1851063</v>
@@ -7052,16 +7052,16 @@
         <v>44713</v>
       </c>
       <c r="B332" t="n">
-        <v>12.6930046081543</v>
+        <v>12.69300365447998</v>
       </c>
       <c r="C332" t="n">
-        <v>12.71006606244956</v>
+        <v>12.71006510749335</v>
       </c>
       <c r="D332" t="n">
-        <v>12.23237172884965</v>
+        <v>12.23237080978446</v>
       </c>
       <c r="E332" t="n">
-        <v>12.52239996020196</v>
+        <v>12.52239901934583</v>
       </c>
       <c r="F332" t="n">
         <v>4014218</v>
@@ -7072,16 +7072,16 @@
         <v>44714</v>
       </c>
       <c r="B333" t="n">
-        <v>12.57357978820801</v>
+        <v>12.57358074188232</v>
       </c>
       <c r="C333" t="n">
-        <v>13.05980353237607</v>
+        <v>13.05980452292923</v>
       </c>
       <c r="D333" t="n">
-        <v>12.43709559746936</v>
+        <v>12.43709654079169</v>
       </c>
       <c r="E333" t="n">
-        <v>12.6930025274482</v>
+        <v>12.69300349018043</v>
       </c>
       <c r="F333" t="n">
         <v>2071017</v>
@@ -7092,16 +7092,16 @@
         <v>44715</v>
       </c>
       <c r="B334" t="n">
-        <v>12.4456262588501</v>
+        <v>12.44562721252441</v>
       </c>
       <c r="C334" t="n">
-        <v>12.51386794383554</v>
+        <v>12.51386890273903</v>
       </c>
       <c r="D334" t="n">
-        <v>12.34326249449706</v>
+        <v>12.34326344032753</v>
       </c>
       <c r="E334" t="n">
-        <v>12.4456262588501</v>
+        <v>12.44562721252441</v>
       </c>
       <c r="F334" t="n">
         <v>1748789</v>
@@ -7172,16 +7172,16 @@
         <v>44721</v>
       </c>
       <c r="B338" t="n">
-        <v>12.15559864044189</v>
+        <v>12.15559673309326</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20678135308851</v>
+        <v>12.20677943770874</v>
       </c>
       <c r="D338" t="n">
-        <v>11.83998029571844</v>
+        <v>11.83997843789384</v>
       </c>
       <c r="E338" t="n">
-        <v>12.07029714283646</v>
+        <v>12.07029524887259</v>
       </c>
       <c r="F338" t="n">
         <v>1444097</v>
@@ -7192,16 +7192,16 @@
         <v>44722</v>
       </c>
       <c r="B339" t="n">
-        <v>11.64378356933594</v>
+        <v>11.64378452301025</v>
       </c>
       <c r="C339" t="n">
-        <v>12.07882545243938</v>
+        <v>12.07882644174544</v>
       </c>
       <c r="D339" t="n">
-        <v>11.42199705857082</v>
+        <v>11.4219979940799</v>
       </c>
       <c r="E339" t="n">
-        <v>12.06176564933559</v>
+        <v>12.06176663724438</v>
       </c>
       <c r="F339" t="n">
         <v>2898634</v>
@@ -7212,16 +7212,16 @@
         <v>44725</v>
       </c>
       <c r="B340" t="n">
-        <v>10.72251892089844</v>
+        <v>10.72251796722412</v>
       </c>
       <c r="C340" t="n">
-        <v>11.50730133143885</v>
+        <v>11.507300307965</v>
       </c>
       <c r="D340" t="n">
-        <v>10.57750521003774</v>
+        <v>10.57750426926113</v>
       </c>
       <c r="E340" t="n">
-        <v>11.23433371572554</v>
+        <v>11.23433271652977</v>
       </c>
       <c r="F340" t="n">
         <v>3958469</v>
@@ -7232,16 +7232,16 @@
         <v>44726</v>
       </c>
       <c r="B341" t="n">
-        <v>10.69692611694336</v>
+        <v>10.69692707061768</v>
       </c>
       <c r="C341" t="n">
-        <v>10.94430356838314</v>
+        <v>10.94430454411216</v>
       </c>
       <c r="D341" t="n">
-        <v>10.57750337271373</v>
+        <v>10.57750431574103</v>
       </c>
       <c r="E341" t="n">
-        <v>10.79075956889747</v>
+        <v>10.79076053093742</v>
       </c>
       <c r="F341" t="n">
         <v>2253062</v>
@@ -7332,16 +7332,16 @@
         <v>44734</v>
       </c>
       <c r="B346" t="n">
-        <v>10.56044292449951</v>
+        <v>10.5604419708252</v>
       </c>
       <c r="C346" t="n">
-        <v>10.77369914095784</v>
+        <v>10.77369816802514</v>
       </c>
       <c r="D346" t="n">
-        <v>10.33012690337453</v>
+        <v>10.33012597049919</v>
       </c>
       <c r="E346" t="n">
-        <v>10.42395953966619</v>
+        <v>10.42395859831718</v>
       </c>
       <c r="F346" t="n">
         <v>1465281</v>
@@ -7372,16 +7372,16 @@
         <v>44736</v>
       </c>
       <c r="B348" t="n">
-        <v>10.62015438079834</v>
+        <v>10.62015533447266</v>
       </c>
       <c r="C348" t="n">
-        <v>10.9187128979493</v>
+        <v>10.91871387843373</v>
       </c>
       <c r="D348" t="n">
-        <v>10.48367018096983</v>
+        <v>10.48367112238806</v>
       </c>
       <c r="E348" t="n">
-        <v>10.9187128979493</v>
+        <v>10.91871387843373</v>
       </c>
       <c r="F348" t="n">
         <v>1300163</v>
@@ -7392,16 +7392,16 @@
         <v>44739</v>
       </c>
       <c r="B349" t="n">
-        <v>10.73957824707031</v>
+        <v>10.739577293396</v>
       </c>
       <c r="C349" t="n">
-        <v>10.85047151637684</v>
+        <v>10.8504705528552</v>
       </c>
       <c r="D349" t="n">
-        <v>10.45808032863837</v>
+        <v>10.45807939996106</v>
       </c>
       <c r="E349" t="n">
-        <v>10.79929045147256</v>
+        <v>10.7992894924958</v>
       </c>
       <c r="F349" t="n">
         <v>1685945</v>
@@ -7412,16 +7412,16 @@
         <v>44740</v>
       </c>
       <c r="B350" t="n">
-        <v>10.23629283905029</v>
+        <v>10.23629188537598</v>
       </c>
       <c r="C350" t="n">
-        <v>10.81635007643811</v>
+        <v>10.81634906872219</v>
       </c>
       <c r="D350" t="n">
-        <v>10.18511177890085</v>
+        <v>10.18511082999487</v>
       </c>
       <c r="E350" t="n">
-        <v>10.70545681743382</v>
+        <v>10.70545582004938</v>
       </c>
       <c r="F350" t="n">
         <v>2763519</v>
@@ -7432,16 +7432,16 @@
         <v>44741</v>
       </c>
       <c r="B351" t="n">
-        <v>10.16805171966553</v>
+        <v>10.16805076599121</v>
       </c>
       <c r="C351" t="n">
-        <v>10.33865636248849</v>
+        <v>10.33865539281295</v>
       </c>
       <c r="D351" t="n">
-        <v>10.03156833524049</v>
+        <v>10.03156739436712</v>
       </c>
       <c r="E351" t="n">
-        <v>10.32159655787287</v>
+        <v>10.32159558979739</v>
       </c>
       <c r="F351" t="n">
         <v>1480384</v>
@@ -7452,16 +7452,16 @@
         <v>44742</v>
       </c>
       <c r="B352" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C352" t="n">
-        <v>10.1253999073854</v>
+        <v>10.12539894068065</v>
       </c>
       <c r="D352" t="n">
-        <v>9.724478429017642</v>
+        <v>9.724477500590167</v>
       </c>
       <c r="E352" t="n">
-        <v>9.97185589738994</v>
+        <v>9.971854945344536</v>
       </c>
       <c r="F352" t="n">
         <v>3400779</v>
@@ -7472,16 +7472,16 @@
         <v>44743</v>
       </c>
       <c r="B353" t="n">
-        <v>9.954795837402344</v>
+        <v>9.95479679107666</v>
       </c>
       <c r="C353" t="n">
-        <v>10.01450721207008</v>
+        <v>10.01450817146478</v>
       </c>
       <c r="D353" t="n">
-        <v>9.698887236624065</v>
+        <v>9.698888165782213</v>
       </c>
       <c r="E353" t="n">
-        <v>9.801251006768695</v>
+        <v>9.801251945733341</v>
       </c>
       <c r="F353" t="n">
         <v>1955465</v>
@@ -7512,16 +7512,16 @@
         <v>44747</v>
       </c>
       <c r="B355" t="n">
-        <v>9.622116088867188</v>
+        <v>9.622115135192871</v>
       </c>
       <c r="C355" t="n">
-        <v>9.681828293425781</v>
+        <v>9.681827333833224</v>
       </c>
       <c r="D355" t="n">
-        <v>9.178543835063046</v>
+        <v>9.178542925352392</v>
       </c>
       <c r="E355" t="n">
-        <v>9.681828293425781</v>
+        <v>9.681827333833224</v>
       </c>
       <c r="F355" t="n">
         <v>3899578</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.11030101776123</v>
+        <v>9.110301971435547</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707418920911163</v>
+        <v>9.707419937092304</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076180583712192</v>
+        <v>9.076181533814751</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707418920911163</v>
+        <v>9.707419937092304</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7612,16 +7612,16 @@
         <v>44754</v>
       </c>
       <c r="B360" t="n">
-        <v>9.229724884033203</v>
+        <v>9.22972583770752</v>
       </c>
       <c r="C360" t="n">
-        <v>9.289436258569864</v>
+        <v>9.289437218413942</v>
       </c>
       <c r="D360" t="n">
-        <v>8.879984477223353</v>
+        <v>8.879985394760249</v>
       </c>
       <c r="E360" t="n">
-        <v>9.229724884033203</v>
+        <v>9.22972583770752</v>
       </c>
       <c r="F360" t="n">
         <v>1719496</v>
@@ -7692,16 +7692,16 @@
         <v>44760</v>
       </c>
       <c r="B364" t="n">
-        <v>9.511222839355469</v>
+        <v>9.511221885681152</v>
       </c>
       <c r="C364" t="n">
-        <v>9.698888119197754</v>
+        <v>9.698887146706557</v>
       </c>
       <c r="D364" t="n">
-        <v>9.212665114265498</v>
+        <v>9.212664190527063</v>
       </c>
       <c r="E364" t="n">
-        <v>9.212665114265498</v>
+        <v>9.212664190527063</v>
       </c>
       <c r="F364" t="n">
         <v>1476836</v>
@@ -7712,16 +7712,16 @@
         <v>44761</v>
       </c>
       <c r="B365" t="n">
-        <v>9.767128944396973</v>
+        <v>9.767129898071289</v>
       </c>
       <c r="C365" t="n">
-        <v>9.929204075840321</v>
+        <v>9.929205045339851</v>
       </c>
       <c r="D365" t="n">
-        <v>9.562403894744662</v>
+        <v>9.562404828429376</v>
       </c>
       <c r="E365" t="n">
-        <v>9.562403894744662</v>
+        <v>9.562404828429376</v>
       </c>
       <c r="F365" t="n">
         <v>2310433</v>
@@ -7732,16 +7732,16 @@
         <v>44762</v>
       </c>
       <c r="B366" t="n">
-        <v>10.08274841308594</v>
+        <v>10.08274936676025</v>
       </c>
       <c r="C366" t="n">
-        <v>10.20217198122667</v>
+        <v>10.20217294619664</v>
       </c>
       <c r="D366" t="n">
-        <v>9.724477708663724</v>
+        <v>9.724478628451092</v>
       </c>
       <c r="E366" t="n">
-        <v>9.767129277493721</v>
+        <v>9.767130201315277</v>
       </c>
       <c r="F366" t="n">
         <v>1476532</v>
@@ -7752,16 +7752,16 @@
         <v>44763</v>
       </c>
       <c r="B367" t="n">
-        <v>9.963325500488281</v>
+        <v>9.963324546813965</v>
       </c>
       <c r="C367" t="n">
-        <v>10.19364233815759</v>
+        <v>10.1936413624377</v>
       </c>
       <c r="D367" t="n">
-        <v>9.946264871833769</v>
+        <v>9.94626391979247</v>
       </c>
       <c r="E367" t="n">
-        <v>10.02303687619577</v>
+        <v>10.02303591680597</v>
       </c>
       <c r="F367" t="n">
         <v>1242590</v>
@@ -7812,16 +7812,16 @@
         <v>44768</v>
       </c>
       <c r="B370" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C370" t="n">
-        <v>10.40689863334928</v>
+        <v>10.40689763976893</v>
       </c>
       <c r="D370" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="E370" t="n">
-        <v>10.22776368016013</v>
+        <v>10.22776270368238</v>
       </c>
       <c r="F370" t="n">
         <v>1502988</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.5092601776123</v>
+        <v>10.50926113128662</v>
       </c>
       <c r="C371" t="n">
-        <v>10.61162311212909</v>
+        <v>10.61162407509244</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421749977017</v>
+        <v>10.07421841396606</v>
       </c>
       <c r="E371" t="n">
-        <v>10.12539855473696</v>
+        <v>10.12539947357733</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7872,16 +7872,16 @@
         <v>44771</v>
       </c>
       <c r="B373" t="n">
-        <v>11.6011323928833</v>
+        <v>11.60113334655762</v>
       </c>
       <c r="C373" t="n">
-        <v>11.6011323928833</v>
+        <v>11.60113334655762</v>
       </c>
       <c r="D373" t="n">
-        <v>10.81635008937574</v>
+        <v>10.81635097853681</v>
       </c>
       <c r="E373" t="n">
-        <v>10.98695472285566</v>
+        <v>10.98695562604133</v>
       </c>
       <c r="F373" t="n">
         <v>3378580</v>
@@ -7892,16 +7892,16 @@
         <v>44774</v>
       </c>
       <c r="B374" t="n">
-        <v>11.26845264434814</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C374" t="n">
-        <v>11.77173701970006</v>
+        <v>11.77173801596846</v>
       </c>
       <c r="D374" t="n">
-        <v>11.09784719833203</v>
+        <v>11.09784813756763</v>
       </c>
       <c r="E374" t="n">
-        <v>11.64378314133378</v>
+        <v>11.64378412677316</v>
       </c>
       <c r="F374" t="n">
         <v>4838693</v>
@@ -7912,16 +7912,16 @@
         <v>44775</v>
       </c>
       <c r="B375" t="n">
-        <v>11.26845264434814</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C375" t="n">
-        <v>11.49876863590757</v>
+        <v>11.49876960907404</v>
       </c>
       <c r="D375" t="n">
-        <v>11.24286170375824</v>
+        <v>11.24286265526674</v>
       </c>
       <c r="E375" t="n">
-        <v>11.39640569813119</v>
+        <v>11.39640666263446</v>
       </c>
       <c r="F375" t="n">
         <v>2088249</v>
@@ -7972,16 +7972,16 @@
         <v>44778</v>
       </c>
       <c r="B378" t="n">
-        <v>12.79536628723145</v>
+        <v>12.79536724090576</v>
       </c>
       <c r="C378" t="n">
-        <v>12.93185048674745</v>
+        <v>12.93185145059431</v>
       </c>
       <c r="D378" t="n">
-        <v>12.24090082432778</v>
+        <v>12.24090173667624</v>
       </c>
       <c r="E378" t="n">
-        <v>12.32620313980655</v>
+        <v>12.32620405851283</v>
       </c>
       <c r="F378" t="n">
         <v>4419056</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.1621675491333</v>
+        <v>13.16216850280762</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718124064354</v>
+        <v>13.30718220482493</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271576790837</v>
+        <v>12.75271669191557</v>
       </c>
       <c r="E379" t="n">
-        <v>12.79536651411238</v>
+        <v>12.79536744120987</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8012,16 +8012,16 @@
         <v>44782</v>
       </c>
       <c r="B380" t="n">
-        <v>13.0939245223999</v>
+        <v>13.09392547607422</v>
       </c>
       <c r="C380" t="n">
-        <v>13.34983228792179</v>
+        <v>13.34983326023473</v>
       </c>
       <c r="D380" t="n">
-        <v>12.92331989510748</v>
+        <v>12.92332083635609</v>
       </c>
       <c r="E380" t="n">
-        <v>13.34130197409885</v>
+        <v>13.34130294579049</v>
       </c>
       <c r="F380" t="n">
         <v>4116999</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248371124268</v>
+        <v>13.39248275756836</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634537898129</v>
+        <v>13.77634439797231</v>
       </c>
       <c r="D381" t="n">
-        <v>13.17922832861007</v>
+        <v>13.1792273901216</v>
       </c>
       <c r="E381" t="n">
-        <v>13.30718139327297</v>
+        <v>13.307180445673</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8052,16 +8052,16 @@
         <v>44784</v>
       </c>
       <c r="B382" t="n">
-        <v>13.36689472198486</v>
+        <v>13.36689281463623</v>
       </c>
       <c r="C382" t="n">
-        <v>13.63986232745854</v>
+        <v>13.63986038115962</v>
       </c>
       <c r="D382" t="n">
-        <v>13.11951723685505</v>
+        <v>13.1195153648052</v>
       </c>
       <c r="E382" t="n">
-        <v>13.5204387423815</v>
+        <v>13.52043681312337</v>
       </c>
       <c r="F382" t="n">
         <v>2014153</v>
@@ -8072,16 +8072,16 @@
         <v>44785</v>
       </c>
       <c r="B383" t="n">
-        <v>13.75928497314453</v>
+        <v>13.75928401947021</v>
       </c>
       <c r="C383" t="n">
-        <v>13.84458729249473</v>
+        <v>13.84458633290799</v>
       </c>
       <c r="D383" t="n">
-        <v>13.47778707191389</v>
+        <v>13.47778613775057</v>
       </c>
       <c r="E383" t="n">
-        <v>13.47778707191389</v>
+        <v>13.47778613775057</v>
       </c>
       <c r="F383" t="n">
         <v>2291478</v>
@@ -8132,16 +8132,16 @@
         <v>44790</v>
       </c>
       <c r="B386" t="n">
-        <v>13.56308746337891</v>
+        <v>13.56309032440186</v>
       </c>
       <c r="C386" t="n">
-        <v>13.64838977060406</v>
+        <v>13.64839264962083</v>
       </c>
       <c r="D386" t="n">
-        <v>13.23893803625678</v>
+        <v>13.23894082890304</v>
       </c>
       <c r="E386" t="n">
-        <v>13.64838977060406</v>
+        <v>13.64839264962083</v>
       </c>
       <c r="F386" t="n">
         <v>4054357</v>
@@ -8152,16 +8152,16 @@
         <v>44791</v>
       </c>
       <c r="B387" t="n">
-        <v>13.63986110687256</v>
+        <v>13.63986015319824</v>
       </c>
       <c r="C387" t="n">
-        <v>14.13461438369162</v>
+        <v>14.13461339542505</v>
       </c>
       <c r="D387" t="n">
-        <v>13.23893963722324</v>
+        <v>13.23893871158062</v>
       </c>
       <c r="E387" t="n">
-        <v>13.64839142108495</v>
+        <v>13.64839046681421</v>
       </c>
       <c r="F387" t="n">
         <v>3074090</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066864013672</v>
+        <v>12.88066959381104</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59720924665701</v>
+        <v>13.59721025338341</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801789456504</v>
+        <v>12.83801884508153</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59720924665701</v>
+        <v>13.59721025338341</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8212,16 +8212,16 @@
         <v>44796</v>
       </c>
       <c r="B390" t="n">
-        <v>12.29208278656006</v>
+        <v>12.29208183288574</v>
       </c>
       <c r="C390" t="n">
-        <v>12.64182321275093</v>
+        <v>12.6418222319422</v>
       </c>
       <c r="D390" t="n">
-        <v>12.25796235261258</v>
+        <v>12.25796140158548</v>
       </c>
       <c r="E390" t="n">
-        <v>12.64182321275093</v>
+        <v>12.6418222319422</v>
       </c>
       <c r="F390" t="n">
         <v>5845922</v>
@@ -8232,16 +8232,16 @@
         <v>44797</v>
       </c>
       <c r="B391" t="n">
-        <v>12.42856693267822</v>
+        <v>12.42856597900391</v>
       </c>
       <c r="C391" t="n">
-        <v>12.57358145611087</v>
+        <v>12.57358049130923</v>
       </c>
       <c r="D391" t="n">
-        <v>12.13000839580709</v>
+        <v>12.1300074650419</v>
       </c>
       <c r="E391" t="n">
-        <v>12.29208272383475</v>
+        <v>12.2920817806332</v>
       </c>
       <c r="F391" t="n">
         <v>4991546</v>
@@ -8272,16 +8272,16 @@
         <v>44799</v>
       </c>
       <c r="B393" t="n">
-        <v>12.18118953704834</v>
+        <v>12.18118858337402</v>
       </c>
       <c r="C393" t="n">
-        <v>12.49680952970967</v>
+        <v>12.49680855132523</v>
       </c>
       <c r="D393" t="n">
-        <v>12.03617583726701</v>
+        <v>12.03617489494593</v>
       </c>
       <c r="E393" t="n">
-        <v>12.45415795648967</v>
+        <v>12.45415698144445</v>
       </c>
       <c r="F393" t="n">
         <v>1257591</v>
@@ -8292,16 +8292,16 @@
         <v>44802</v>
       </c>
       <c r="B394" t="n">
-        <v>12.25796031951904</v>
+        <v>12.25796222686768</v>
       </c>
       <c r="C394" t="n">
-        <v>12.40297399505652</v>
+        <v>12.40297592496939</v>
       </c>
       <c r="D394" t="n">
-        <v>12.04470413823857</v>
+        <v>12.04470601240437</v>
       </c>
       <c r="E394" t="n">
-        <v>12.18118750055817</v>
+        <v>12.18118939596089</v>
       </c>
       <c r="F394" t="n">
         <v>4196061</v>
@@ -8312,16 +8312,16 @@
         <v>44803</v>
       </c>
       <c r="B395" t="n">
-        <v>12.21531009674072</v>
+        <v>12.21531105041504</v>
       </c>
       <c r="C395" t="n">
-        <v>12.47121787225261</v>
+        <v>12.47121884590617</v>
       </c>
       <c r="D395" t="n">
-        <v>12.06176609110022</v>
+        <v>12.06176703278704</v>
       </c>
       <c r="E395" t="n">
-        <v>12.25796166752047</v>
+        <v>12.25796262452468</v>
       </c>
       <c r="F395" t="n">
         <v>2841466</v>
@@ -8332,16 +8332,16 @@
         <v>44804</v>
       </c>
       <c r="B396" t="n">
-        <v>12.03617477416992</v>
+        <v>12.03617572784424</v>
       </c>
       <c r="C396" t="n">
-        <v>12.33473328658969</v>
+        <v>12.33473426391999</v>
       </c>
       <c r="D396" t="n">
-        <v>11.92528151817592</v>
+        <v>11.92528246306372</v>
       </c>
       <c r="E396" t="n">
-        <v>12.10441646071113</v>
+        <v>12.1044174197925</v>
       </c>
       <c r="F396" t="n">
         <v>1958303</v>
@@ -8412,16 +8412,16 @@
         <v>44810</v>
       </c>
       <c r="B400" t="n">
-        <v>12.19824981689453</v>
+        <v>12.19824886322021</v>
       </c>
       <c r="C400" t="n">
-        <v>13.29012181421445</v>
+        <v>13.29012077517622</v>
       </c>
       <c r="D400" t="n">
-        <v>12.19824981689453</v>
+        <v>12.19824886322021</v>
       </c>
       <c r="E400" t="n">
-        <v>13.29012181421445</v>
+        <v>13.29012077517622</v>
       </c>
       <c r="F400" t="n">
         <v>5053579</v>
@@ -8432,16 +8432,16 @@
         <v>44812</v>
       </c>
       <c r="B401" t="n">
-        <v>12.15559864044189</v>
+        <v>12.15559673309326</v>
       </c>
       <c r="C401" t="n">
-        <v>12.53946032716638</v>
+        <v>12.53945835958558</v>
       </c>
       <c r="D401" t="n">
-        <v>11.79732872233238</v>
+        <v>11.79732687120029</v>
       </c>
       <c r="E401" t="n">
-        <v>12.53946032716638</v>
+        <v>12.53945835958558</v>
       </c>
       <c r="F401" t="n">
         <v>2311852</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.3347339630127</v>
+        <v>12.33473300933838</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121816816301</v>
+        <v>12.47121720393626</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646323371185</v>
+        <v>11.97646230773766</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22384070093743</v>
+        <v>12.22383975583696</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8472,16 +8472,16 @@
         <v>44816</v>
       </c>
       <c r="B403" t="n">
-        <v>12.30696201324463</v>
+        <v>12.30696105957031</v>
       </c>
       <c r="C403" t="n">
-        <v>12.58102134762649</v>
+        <v>12.58102037271514</v>
       </c>
       <c r="D403" t="n">
-        <v>12.05859669488552</v>
+        <v>12.05859576045719</v>
       </c>
       <c r="E403" t="n">
-        <v>12.05859669488552</v>
+        <v>12.05859576045719</v>
       </c>
       <c r="F403" t="n">
         <v>4043263</v>
@@ -8492,16 +8492,16 @@
         <v>44817</v>
       </c>
       <c r="B404" t="n">
-        <v>11.82735824584961</v>
+        <v>11.82735919952393</v>
       </c>
       <c r="C404" t="n">
-        <v>12.11854579094386</v>
+        <v>12.11854676809748</v>
       </c>
       <c r="D404" t="n">
-        <v>11.74171455920428</v>
+        <v>11.7417155059729</v>
       </c>
       <c r="E404" t="n">
-        <v>12.11854579094386</v>
+        <v>12.11854676809748</v>
       </c>
       <c r="F404" t="n">
         <v>3904244</v>
@@ -8532,16 +8532,16 @@
         <v>44819</v>
       </c>
       <c r="B406" t="n">
-        <v>12.76943683624268</v>
+        <v>12.76943588256836</v>
       </c>
       <c r="C406" t="n">
-        <v>12.9321592806806</v>
+        <v>12.9321583148535</v>
       </c>
       <c r="D406" t="n">
-        <v>12.33265506062422</v>
+        <v>12.33265413957057</v>
       </c>
       <c r="E406" t="n">
-        <v>12.54676388734078</v>
+        <v>12.5467629502966</v>
       </c>
       <c r="F406" t="n">
         <v>3409247</v>
@@ -8572,16 +8572,16 @@
         <v>44823</v>
       </c>
       <c r="B408" t="n">
-        <v>12.39260578155518</v>
+        <v>12.39260673522949</v>
       </c>
       <c r="C408" t="n">
-        <v>12.6067129485987</v>
+        <v>12.60671391874965</v>
       </c>
       <c r="D408" t="n">
-        <v>12.19562520887531</v>
+        <v>12.19562614739096</v>
       </c>
       <c r="E408" t="n">
-        <v>12.34121940179812</v>
+        <v>12.34122035151799</v>
       </c>
       <c r="F408" t="n">
         <v>1221893</v>
@@ -8592,16 +8592,16 @@
         <v>44824</v>
       </c>
       <c r="B409" t="n">
-        <v>11.88731002807617</v>
+        <v>11.88731098175049</v>
       </c>
       <c r="C409" t="n">
-        <v>12.52107073904231</v>
+        <v>12.52107174356088</v>
       </c>
       <c r="D409" t="n">
-        <v>11.87018013448028</v>
+        <v>11.87018108678033</v>
       </c>
       <c r="E409" t="n">
-        <v>12.44399116536064</v>
+        <v>12.4439921636954</v>
       </c>
       <c r="F409" t="n">
         <v>1700434</v>
@@ -8612,16 +8612,16 @@
         <v>44825</v>
       </c>
       <c r="B410" t="n">
-        <v>11.65607070922852</v>
+        <v>11.65607166290283</v>
       </c>
       <c r="C410" t="n">
-        <v>12.10998235665763</v>
+        <v>12.10998334747001</v>
       </c>
       <c r="D410" t="n">
-        <v>11.50191321893803</v>
+        <v>11.50191415999951</v>
       </c>
       <c r="E410" t="n">
-        <v>11.9472590954252</v>
+        <v>11.94726007292391</v>
       </c>
       <c r="F410" t="n">
         <v>3396829</v>
@@ -8692,16 +8692,16 @@
         <v>44831</v>
       </c>
       <c r="B414" t="n">
-        <v>11.30493450164795</v>
+        <v>11.30493259429932</v>
       </c>
       <c r="C414" t="n">
-        <v>11.63894352718433</v>
+        <v>11.63894156348228</v>
       </c>
       <c r="D414" t="n">
-        <v>11.26211306428218</v>
+        <v>11.2621111641583</v>
       </c>
       <c r="E414" t="n">
-        <v>11.53617158275647</v>
+        <v>11.53616963639392</v>
       </c>
       <c r="F414" t="n">
         <v>2656202</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186485290527</v>
+        <v>11.56186389923096</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889411306563</v>
+        <v>11.69889314808853</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072675530685</v>
+        <v>11.21072583059598</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775601546721</v>
+        <v>11.34775507945355</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8772,16 +8772,16 @@
         <v>44837</v>
       </c>
       <c r="B418" t="n">
-        <v>12.41829967498779</v>
+        <v>12.41829872131348</v>
       </c>
       <c r="C418" t="n">
-        <v>12.62384439472611</v>
+        <v>12.62384342526681</v>
       </c>
       <c r="D418" t="n">
-        <v>12.01577518291347</v>
+        <v>12.01577426015137</v>
       </c>
       <c r="E418" t="n">
-        <v>12.06716156899389</v>
+        <v>12.06716064228553</v>
       </c>
       <c r="F418" t="n">
         <v>3117277</v>
@@ -8832,16 +8832,16 @@
         <v>44840</v>
       </c>
       <c r="B421" t="n">
-        <v>13.0263671875</v>
+        <v>13.02636814117432</v>
       </c>
       <c r="C421" t="n">
-        <v>13.26616920699484</v>
+        <v>13.26617017822532</v>
       </c>
       <c r="D421" t="n">
-        <v>12.92359524682363</v>
+        <v>12.9235961929739</v>
       </c>
       <c r="E421" t="n">
-        <v>12.98354575169734</v>
+        <v>12.98354670223665</v>
       </c>
       <c r="F421" t="n">
         <v>6127236</v>
@@ -8912,16 +8912,16 @@
         <v>44847</v>
       </c>
       <c r="B425" t="n">
-        <v>13.0520601272583</v>
+        <v>13.05206108093262</v>
       </c>
       <c r="C425" t="n">
-        <v>13.30899038628898</v>
+        <v>13.30899135873641</v>
       </c>
       <c r="D425" t="n">
-        <v>12.57245692209548</v>
+        <v>12.57245784072665</v>
       </c>
       <c r="E425" t="n">
-        <v>12.58958516625311</v>
+        <v>12.58958608613578</v>
       </c>
       <c r="F425" t="n">
         <v>3708082</v>
@@ -8932,16 +8932,16 @@
         <v>44848</v>
       </c>
       <c r="B426" t="n">
-        <v>12.76943683624268</v>
+        <v>12.76943588256836</v>
       </c>
       <c r="C426" t="n">
-        <v>13.12057491625784</v>
+        <v>13.12057393635908</v>
       </c>
       <c r="D426" t="n">
-        <v>12.65809994950008</v>
+        <v>12.65809900414086</v>
       </c>
       <c r="E426" t="n">
-        <v>13.09488172511853</v>
+        <v>13.09488074713864</v>
       </c>
       <c r="F426" t="n">
         <v>2206838</v>
@@ -8952,16 +8952,16 @@
         <v>44851</v>
       </c>
       <c r="B427" t="n">
-        <v>12.6495361328125</v>
+        <v>12.64953708648682</v>
       </c>
       <c r="C427" t="n">
-        <v>13.19765480841111</v>
+        <v>13.19765580340922</v>
       </c>
       <c r="D427" t="n">
-        <v>12.5810215045085</v>
+        <v>12.58102245301736</v>
       </c>
       <c r="E427" t="n">
-        <v>12.87220908709215</v>
+        <v>12.87221005755423</v>
       </c>
       <c r="F427" t="n">
         <v>1088124</v>
@@ -8992,16 +8992,16 @@
         <v>44853</v>
       </c>
       <c r="B429" t="n">
-        <v>12.95785045623779</v>
+        <v>12.95785236358643</v>
       </c>
       <c r="C429" t="n">
-        <v>13.02636590117292</v>
+        <v>13.02636781860678</v>
       </c>
       <c r="D429" t="n">
-        <v>12.71804928500614</v>
+        <v>12.71805115705691</v>
       </c>
       <c r="E429" t="n">
-        <v>12.80369297273763</v>
+        <v>12.80369485739484</v>
       </c>
       <c r="F429" t="n">
         <v>1282165</v>
@@ -9012,16 +9012,16 @@
         <v>44854</v>
       </c>
       <c r="B430" t="n">
-        <v>12.78656387329102</v>
+        <v>12.78656578063965</v>
       </c>
       <c r="C430" t="n">
-        <v>13.08631636730787</v>
+        <v>13.08631831937005</v>
       </c>
       <c r="D430" t="n">
-        <v>12.65809875430757</v>
+        <v>12.65810064249329</v>
       </c>
       <c r="E430" t="n">
-        <v>13.08631636730787</v>
+        <v>13.08631831937005</v>
       </c>
       <c r="F430" t="n">
         <v>2107193</v>
@@ -9032,16 +9032,16 @@
         <v>44855</v>
       </c>
       <c r="B431" t="n">
-        <v>13.08631801605225</v>
+        <v>13.08631706237793</v>
       </c>
       <c r="C431" t="n">
-        <v>13.26616953512184</v>
+        <v>13.26616856834072</v>
       </c>
       <c r="D431" t="n">
-        <v>12.58958572028859</v>
+        <v>12.58958480281398</v>
       </c>
       <c r="E431" t="n">
-        <v>12.74374404740777</v>
+        <v>12.74374311869877</v>
       </c>
       <c r="F431" t="n">
         <v>1434409</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805095672607</v>
+        <v>12.71805191040039</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775399772944</v>
+        <v>13.07775497837641</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235858915441</v>
+        <v>12.69235954090216</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87220928507275</v>
+        <v>12.87221025030677</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9092,16 +9092,16 @@
         <v>44860</v>
       </c>
       <c r="B434" t="n">
-        <v>12.29839706420898</v>
+        <v>12.2983980178833</v>
       </c>
       <c r="C434" t="n">
-        <v>13.00923730694242</v>
+        <v>13.00923831573856</v>
       </c>
       <c r="D434" t="n">
-        <v>12.17849688652397</v>
+        <v>12.17849783090068</v>
       </c>
       <c r="E434" t="n">
-        <v>12.61527781329898</v>
+        <v>12.61527879154568</v>
       </c>
       <c r="F434" t="n">
         <v>4556230</v>
@@ -9132,16 +9132,16 @@
         <v>44862</v>
       </c>
       <c r="B436" t="n">
-        <v>13.06918907165527</v>
+        <v>13.06918811798096</v>
       </c>
       <c r="C436" t="n">
-        <v>13.48027849763024</v>
+        <v>13.48027751395823</v>
       </c>
       <c r="D436" t="n">
-        <v>12.4525565818595</v>
+        <v>12.45255567318159</v>
       </c>
       <c r="E436" t="n">
-        <v>13.154832770782</v>
+        <v>13.15483181085816</v>
       </c>
       <c r="F436" t="n">
         <v>6048388</v>
@@ -9172,16 +9172,16 @@
         <v>44866</v>
       </c>
       <c r="B438" t="n">
-        <v>13.61730670928955</v>
+        <v>13.61730575561523</v>
       </c>
       <c r="C438" t="n">
-        <v>14.01126705916312</v>
+        <v>14.01126607789819</v>
       </c>
       <c r="D438" t="n">
-        <v>13.53166383614674</v>
+        <v>13.53166288847033</v>
       </c>
       <c r="E438" t="n">
-        <v>13.70295123159901</v>
+        <v>13.70295027192667</v>
       </c>
       <c r="F438" t="n">
         <v>3366744</v>
@@ -9192,16 +9192,16 @@
         <v>44868</v>
       </c>
       <c r="B439" t="n">
-        <v>13.93418788909912</v>
+        <v>13.9341869354248</v>
       </c>
       <c r="C439" t="n">
-        <v>14.0455231260844</v>
+        <v>14.04552216479015</v>
       </c>
       <c r="D439" t="n">
-        <v>13.38606922964626</v>
+        <v>13.38606831348592</v>
       </c>
       <c r="E439" t="n">
-        <v>13.38606922964626</v>
+        <v>13.38606831348592</v>
       </c>
       <c r="F439" t="n">
         <v>2966749</v>
@@ -9212,16 +9212,16 @@
         <v>44869</v>
       </c>
       <c r="B440" t="n">
-        <v>14.01126766204834</v>
+        <v>14.01126575469971</v>
       </c>
       <c r="C440" t="n">
-        <v>14.29389195916385</v>
+        <v>14.29389001334168</v>
       </c>
       <c r="D440" t="n">
-        <v>13.80572294357798</v>
+        <v>13.80572106421007</v>
       </c>
       <c r="E440" t="n">
-        <v>14.13973280187356</v>
+        <v>14.13973087703701</v>
       </c>
       <c r="F440" t="n">
         <v>3663661</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.40319728851318</v>
+        <v>13.40319919586182</v>
       </c>
       <c r="C441" t="n">
-        <v>14.03695880976449</v>
+        <v>14.03696080730087</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037667840605</v>
+        <v>13.36037857966108</v>
       </c>
       <c r="E441" t="n">
-        <v>13.9341876963408</v>
+        <v>13.93418967925229</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9292,16 +9292,16 @@
         <v>44875</v>
       </c>
       <c r="B444" t="n">
-        <v>12.2470121383667</v>
+        <v>12.24701118469238</v>
       </c>
       <c r="C444" t="n">
-        <v>12.83795140918214</v>
+        <v>12.83795040949141</v>
       </c>
       <c r="D444" t="n">
-        <v>11.67320111185027</v>
+        <v>11.6732002028586</v>
       </c>
       <c r="E444" t="n">
-        <v>12.83795140918214</v>
+        <v>12.83795040949141</v>
       </c>
       <c r="F444" t="n">
         <v>10581398</v>
@@ -9352,16 +9352,16 @@
         <v>44881</v>
       </c>
       <c r="B447" t="n">
-        <v>11.26211357116699</v>
+        <v>11.26211166381836</v>
       </c>
       <c r="C447" t="n">
-        <v>12.15280462087997</v>
+        <v>12.15280256268413</v>
       </c>
       <c r="D447" t="n">
-        <v>11.15934162211358</v>
+        <v>11.15933973217037</v>
       </c>
       <c r="E447" t="n">
-        <v>12.06716174229381</v>
+        <v>12.06715969860243</v>
       </c>
       <c r="F447" t="n">
         <v>3929079</v>
@@ -9372,16 +9372,16 @@
         <v>44882</v>
       </c>
       <c r="B448" t="n">
-        <v>10.94523143768311</v>
+        <v>10.94523239135742</v>
       </c>
       <c r="C448" t="n">
-        <v>10.94523143768311</v>
+        <v>10.94523239135742</v>
       </c>
       <c r="D448" t="n">
-        <v>9.900381355318869</v>
+        <v>9.900382217953842</v>
       </c>
       <c r="E448" t="n">
-        <v>10.79963724256202</v>
+        <v>10.7996381835505</v>
       </c>
       <c r="F448" t="n">
         <v>12061945</v>
@@ -9392,16 +9392,16 @@
         <v>44883</v>
       </c>
       <c r="B449" t="n">
-        <v>10.92810249328613</v>
+        <v>10.92810153961182</v>
       </c>
       <c r="C449" t="n">
-        <v>11.38201332758762</v>
+        <v>11.38201233430139</v>
       </c>
       <c r="D449" t="n">
-        <v>10.91953837129458</v>
+        <v>10.91953741836764</v>
       </c>
       <c r="E449" t="n">
-        <v>11.13364636858307</v>
+        <v>11.13364539697134</v>
       </c>
       <c r="F449" t="n">
         <v>5719164</v>
@@ -9432,16 +9432,16 @@
         <v>44887</v>
       </c>
       <c r="B451" t="n">
-        <v>10.98805332183838</v>
+        <v>10.9880542755127</v>
       </c>
       <c r="C451" t="n">
-        <v>11.33919140430814</v>
+        <v>11.33919238845841</v>
       </c>
       <c r="D451" t="n">
-        <v>10.89384550339121</v>
+        <v>10.89384644888905</v>
       </c>
       <c r="E451" t="n">
-        <v>11.2792408994251</v>
+        <v>11.27924187837214</v>
       </c>
       <c r="F451" t="n">
         <v>2547672</v>
@@ -9472,16 +9472,16 @@
         <v>44889</v>
       </c>
       <c r="B453" t="n">
-        <v>11.53617095947266</v>
+        <v>11.53617191314697</v>
       </c>
       <c r="C453" t="n">
-        <v>11.81879440981701</v>
+        <v>11.81879538685529</v>
       </c>
       <c r="D453" t="n">
-        <v>11.05656775347163</v>
+        <v>11.05656866749802</v>
       </c>
       <c r="E453" t="n">
-        <v>11.11651825729467</v>
+        <v>11.11651917627706</v>
       </c>
       <c r="F453" t="n">
         <v>3457606</v>
@@ -9512,16 +9512,16 @@
         <v>44893</v>
       </c>
       <c r="B455" t="n">
-        <v>10.96235847473145</v>
+        <v>10.96236038208008</v>
       </c>
       <c r="C455" t="n">
-        <v>11.18503139155672</v>
+        <v>11.18503333764837</v>
       </c>
       <c r="D455" t="n">
-        <v>10.84245748307556</v>
+        <v>10.84245936956254</v>
       </c>
       <c r="E455" t="n">
-        <v>10.95379435377979</v>
+        <v>10.95379625963835</v>
       </c>
       <c r="F455" t="n">
         <v>2642270</v>
@@ -9572,16 +9572,16 @@
         <v>44896</v>
       </c>
       <c r="B458" t="n">
-        <v>11.15077590942383</v>
+        <v>11.15077495574951</v>
       </c>
       <c r="C458" t="n">
-        <v>11.33919154871773</v>
+        <v>11.33919057892909</v>
       </c>
       <c r="D458" t="n">
-        <v>10.9709243924842</v>
+        <v>10.97092345419175</v>
       </c>
       <c r="E458" t="n">
-        <v>11.32206330400918</v>
+        <v>11.32206233568545</v>
       </c>
       <c r="F458" t="n">
         <v>2224001</v>
@@ -9632,16 +9632,16 @@
         <v>44901</v>
       </c>
       <c r="B461" t="n">
-        <v>10.64548015594482</v>
+        <v>10.64547920227051</v>
       </c>
       <c r="C461" t="n">
-        <v>10.88528219337026</v>
+        <v>10.8852812182133</v>
       </c>
       <c r="D461" t="n">
-        <v>10.44850038210729</v>
+        <v>10.44849944607939</v>
       </c>
       <c r="E461" t="n">
-        <v>10.62835108559299</v>
+        <v>10.62835013345318</v>
       </c>
       <c r="F461" t="n">
         <v>3634787</v>
@@ -9652,16 +9652,16 @@
         <v>44902</v>
       </c>
       <c r="B462" t="n">
-        <v>10.36285591125488</v>
+        <v>10.3628568649292</v>
       </c>
       <c r="C462" t="n">
-        <v>10.91097288493018</v>
+        <v>10.91097388904668</v>
       </c>
       <c r="D462" t="n">
-        <v>10.24295491097179</v>
+        <v>10.24295585361184</v>
       </c>
       <c r="E462" t="n">
-        <v>10.59409296566996</v>
+        <v>10.59409394062459</v>
       </c>
       <c r="F462" t="n">
         <v>7006882</v>
@@ -9672,16 +9672,16 @@
         <v>44903</v>
       </c>
       <c r="B463" t="n">
-        <v>9.763352394104004</v>
+        <v>9.763351440429688</v>
       </c>
       <c r="C463" t="n">
-        <v>10.37998573239832</v>
+        <v>10.37998471849188</v>
       </c>
       <c r="D463" t="n">
-        <v>9.686273639108899</v>
+        <v>9.686272692963557</v>
       </c>
       <c r="E463" t="n">
-        <v>10.27721295962702</v>
+        <v>10.27721195575933</v>
       </c>
       <c r="F463" t="n">
         <v>6542779</v>
@@ -9732,16 +9732,16 @@
         <v>44908</v>
       </c>
       <c r="B466" t="n">
-        <v>9.377955436706543</v>
+        <v>9.377956390380859</v>
       </c>
       <c r="C466" t="n">
-        <v>9.951766417669408</v>
+        <v>9.9517674296964</v>
       </c>
       <c r="D466" t="n">
-        <v>9.352263072297678</v>
+        <v>9.352264023359256</v>
       </c>
       <c r="E466" t="n">
-        <v>9.532113746075902</v>
+        <v>9.532114715427072</v>
       </c>
       <c r="F466" t="n">
         <v>6881089</v>
@@ -9852,16 +9852,16 @@
         <v>44916</v>
       </c>
       <c r="B472" t="n">
-        <v>10.42280673980713</v>
+        <v>10.42280578613281</v>
       </c>
       <c r="C472" t="n">
-        <v>10.58553001509685</v>
+        <v>10.58552904653355</v>
       </c>
       <c r="D472" t="n">
-        <v>10.08879771587911</v>
+        <v>10.08879679276622</v>
       </c>
       <c r="E472" t="n">
-        <v>10.36285705761706</v>
+        <v>10.36285610942807</v>
       </c>
       <c r="F472" t="n">
         <v>3195923</v>
@@ -9872,16 +9872,16 @@
         <v>44917</v>
       </c>
       <c r="B473" t="n">
-        <v>10.53414249420166</v>
+        <v>10.53414344787598</v>
       </c>
       <c r="C473" t="n">
-        <v>10.60265711609756</v>
+        <v>10.60265807597463</v>
       </c>
       <c r="D473" t="n">
-        <v>10.29434131756599</v>
+        <v>10.29434224953069</v>
       </c>
       <c r="E473" t="n">
-        <v>10.43993468294898</v>
+        <v>10.4399356280945</v>
       </c>
       <c r="F473" t="n">
         <v>2407341</v>
@@ -9892,16 +9892,16 @@
         <v>44918</v>
       </c>
       <c r="B474" t="n">
-        <v>10.83389472961426</v>
+        <v>10.83389568328857</v>
       </c>
       <c r="C474" t="n">
-        <v>11.26211237541256</v>
+        <v>11.26211336678155</v>
       </c>
       <c r="D474" t="n">
-        <v>10.55983540332002</v>
+        <v>10.55983633286973</v>
       </c>
       <c r="E474" t="n">
-        <v>10.57696364738531</v>
+        <v>10.57696457844277</v>
       </c>
       <c r="F474" t="n">
         <v>4288288</v>
@@ -9932,16 +9932,16 @@
         <v>44922</v>
       </c>
       <c r="B476" t="n">
-        <v>10.52296161651611</v>
+        <v>10.5229606628418</v>
       </c>
       <c r="C476" t="n">
-        <v>10.75039054378364</v>
+        <v>10.75038956949791</v>
       </c>
       <c r="D476" t="n">
-        <v>10.37425773083552</v>
+        <v>10.37425679063793</v>
       </c>
       <c r="E476" t="n">
-        <v>10.73289562221141</v>
+        <v>10.73289464951121</v>
       </c>
       <c r="F476" t="n">
         <v>2935250</v>
@@ -9952,16 +9952,16 @@
         <v>44923</v>
       </c>
       <c r="B477" t="n">
-        <v>10.96907043457031</v>
+        <v>10.96907138824463</v>
       </c>
       <c r="C477" t="n">
-        <v>11.03030139033512</v>
+        <v>11.03030234933299</v>
       </c>
       <c r="D477" t="n">
-        <v>10.43548759461291</v>
+        <v>10.4354885018964</v>
       </c>
       <c r="E477" t="n">
-        <v>10.56669570271517</v>
+        <v>10.56669662140617</v>
       </c>
       <c r="F477" t="n">
         <v>2605824</v>
@@ -9972,16 +9972,16 @@
         <v>44924</v>
       </c>
       <c r="B478" t="n">
-        <v>11.05654430389404</v>
+        <v>11.05654525756836</v>
       </c>
       <c r="C478" t="n">
-        <v>11.29272026639114</v>
+        <v>11.29272124043664</v>
       </c>
       <c r="D478" t="n">
-        <v>10.75039034081968</v>
+        <v>10.7503912680869</v>
       </c>
       <c r="E478" t="n">
-        <v>11.00406038236348</v>
+        <v>11.00406133151083</v>
       </c>
       <c r="F478" t="n">
         <v>3691424</v>
@@ -9992,16 +9992,16 @@
         <v>44928</v>
       </c>
       <c r="B479" t="n">
-        <v>10.15557670593262</v>
+        <v>10.1555757522583</v>
       </c>
       <c r="C479" t="n">
-        <v>10.91658859396708</v>
+        <v>10.91658756882882</v>
       </c>
       <c r="D479" t="n">
-        <v>9.963136763267295</v>
+        <v>9.963135827664333</v>
       </c>
       <c r="E479" t="n">
-        <v>10.91658859396708</v>
+        <v>10.91658756882882</v>
       </c>
       <c r="F479" t="n">
         <v>2948980</v>
@@ -10012,16 +10012,16 @@
         <v>44929</v>
       </c>
       <c r="B480" t="n">
-        <v>9.578255653381348</v>
+        <v>9.578256607055664</v>
       </c>
       <c r="C480" t="n">
-        <v>10.18181736770337</v>
+        <v>10.18181838147228</v>
       </c>
       <c r="D480" t="n">
-        <v>9.53451961461997</v>
+        <v>9.534520563939639</v>
       </c>
       <c r="E480" t="n">
-        <v>10.15557540756847</v>
+        <v>10.15557641872455</v>
       </c>
       <c r="F480" t="n">
         <v>3313438</v>
@@ -10092,16 +10092,16 @@
         <v>44935</v>
       </c>
       <c r="B484" t="n">
-        <v>10.59294033050537</v>
+        <v>10.59293937683105</v>
       </c>
       <c r="C484" t="n">
-        <v>10.64542341435966</v>
+        <v>10.64542245596033</v>
       </c>
       <c r="D484" t="n">
-        <v>10.09434555962026</v>
+        <v>10.09434465083405</v>
       </c>
       <c r="E484" t="n">
-        <v>10.2517964955737</v>
+        <v>10.2517955726123</v>
       </c>
       <c r="F484" t="n">
         <v>3368460</v>
@@ -10172,16 +10172,16 @@
         <v>44939</v>
       </c>
       <c r="B488" t="n">
-        <v>11.24898242950439</v>
+        <v>11.24898338317871</v>
       </c>
       <c r="C488" t="n">
-        <v>11.33645618609352</v>
+        <v>11.33645714718375</v>
       </c>
       <c r="D488" t="n">
-        <v>10.94282849241817</v>
+        <v>10.94282942013715</v>
       </c>
       <c r="E488" t="n">
-        <v>11.12652135998699</v>
+        <v>11.12652230327921</v>
       </c>
       <c r="F488" t="n">
         <v>2088011</v>
@@ -10212,16 +10212,16 @@
         <v>44943</v>
       </c>
       <c r="B490" t="n">
-        <v>11.00405979156494</v>
+        <v>11.00406074523926</v>
       </c>
       <c r="C490" t="n">
-        <v>11.10902762899043</v>
+        <v>11.10902859176186</v>
       </c>
       <c r="D490" t="n">
-        <v>10.75038976364046</v>
+        <v>10.7503906953303</v>
       </c>
       <c r="E490" t="n">
-        <v>10.84660887762188</v>
+        <v>10.8466098176506</v>
       </c>
       <c r="F490" t="n">
         <v>2581089</v>
@@ -10252,16 +10252,16 @@
         <v>44945</v>
       </c>
       <c r="B492" t="n">
-        <v>11.93127155303955</v>
+        <v>11.93127059936523</v>
       </c>
       <c r="C492" t="n">
-        <v>12.30740353426755</v>
+        <v>12.30740255052876</v>
       </c>
       <c r="D492" t="n">
-        <v>11.33645767814233</v>
+        <v>11.33645677201188</v>
       </c>
       <c r="E492" t="n">
-        <v>11.49390776570111</v>
+        <v>11.49390684698556</v>
       </c>
       <c r="F492" t="n">
         <v>5394988</v>
@@ -10292,16 +10292,16 @@
         <v>44949</v>
       </c>
       <c r="B494" t="n">
-        <v>11.66885185241699</v>
+        <v>11.66885280609131</v>
       </c>
       <c r="C494" t="n">
-        <v>12.07122660600753</v>
+        <v>12.07122759256721</v>
       </c>
       <c r="D494" t="n">
-        <v>11.65135777393643</v>
+        <v>11.65135872618098</v>
       </c>
       <c r="E494" t="n">
-        <v>11.86129261106957</v>
+        <v>11.86129358047173</v>
       </c>
       <c r="F494" t="n">
         <v>1283174</v>
@@ -10352,16 +10352,16 @@
         <v>44952</v>
       </c>
       <c r="B497" t="n">
-        <v>12.42986392974854</v>
+        <v>12.42986488342285</v>
       </c>
       <c r="C497" t="n">
-        <v>12.56981992018939</v>
+        <v>12.56982088460175</v>
       </c>
       <c r="D497" t="n">
-        <v>12.18494010428189</v>
+        <v>12.18494103916456</v>
       </c>
       <c r="E497" t="n">
-        <v>12.272413019405</v>
+        <v>12.27241396099898</v>
       </c>
       <c r="F497" t="n">
         <v>2815211</v>
@@ -10372,16 +10372,16 @@
         <v>44953</v>
       </c>
       <c r="B498" t="n">
-        <v>12.43861389160156</v>
+        <v>12.43861198425293</v>
       </c>
       <c r="C498" t="n">
-        <v>12.67478987552819</v>
+        <v>12.67478793196411</v>
       </c>
       <c r="D498" t="n">
-        <v>12.25492099177236</v>
+        <v>12.25491911259136</v>
       </c>
       <c r="E498" t="n">
-        <v>12.41237108625991</v>
+        <v>12.41236918293538</v>
       </c>
       <c r="F498" t="n">
         <v>1981500</v>
@@ -10392,16 +10392,16 @@
         <v>44956</v>
       </c>
       <c r="B499" t="n">
-        <v>12.48234748840332</v>
+        <v>12.48234844207764</v>
       </c>
       <c r="C499" t="n">
-        <v>12.81474424186402</v>
+        <v>12.81474522093406</v>
       </c>
       <c r="D499" t="n">
-        <v>12.3948754120883</v>
+        <v>12.39487635907959</v>
       </c>
       <c r="E499" t="n">
-        <v>12.46485341001839</v>
+        <v>12.46485436235613</v>
       </c>
       <c r="F499" t="n">
         <v>2566955</v>
@@ -10452,16 +10452,16 @@
         <v>44959</v>
       </c>
       <c r="B502" t="n">
-        <v>12.91096496582031</v>
+        <v>12.91096591949463</v>
       </c>
       <c r="C502" t="n">
-        <v>13.36582282155647</v>
+        <v>13.36582380882906</v>
       </c>
       <c r="D502" t="n">
-        <v>12.77100811945864</v>
+        <v>12.77100906279498</v>
       </c>
       <c r="E502" t="n">
-        <v>12.77100811945864</v>
+        <v>12.77100906279498</v>
       </c>
       <c r="F502" t="n">
         <v>4085160</v>
@@ -10472,16 +10472,16 @@
         <v>44960</v>
       </c>
       <c r="B503" t="n">
-        <v>12.57856750488281</v>
+        <v>12.57856845855713</v>
       </c>
       <c r="C503" t="n">
-        <v>12.90221722066339</v>
+        <v>12.90221819887599</v>
       </c>
       <c r="D503" t="n">
-        <v>12.42986446913531</v>
+        <v>12.42986541153535</v>
       </c>
       <c r="E503" t="n">
-        <v>12.81474430174445</v>
+        <v>12.81474527332507</v>
       </c>
       <c r="F503" t="n">
         <v>2892746</v>
@@ -10492,16 +10492,16 @@
         <v>44963</v>
       </c>
       <c r="B504" t="n">
-        <v>12.75351428985596</v>
+        <v>12.75351524353027</v>
       </c>
       <c r="C504" t="n">
-        <v>12.83224017538812</v>
+        <v>12.83224113494935</v>
       </c>
       <c r="D504" t="n">
-        <v>12.33364542693687</v>
+        <v>12.33364634921449</v>
       </c>
       <c r="E504" t="n">
-        <v>12.53483239741585</v>
+        <v>12.53483333473771</v>
       </c>
       <c r="F504" t="n">
         <v>1342942</v>
@@ -10532,16 +10532,16 @@
         <v>44965</v>
       </c>
       <c r="B506" t="n">
-        <v>12.7710075378418</v>
+        <v>12.77100849151611</v>
       </c>
       <c r="C506" t="n">
-        <v>12.98094237672584</v>
+        <v>12.98094334607703</v>
       </c>
       <c r="D506" t="n">
-        <v>12.56982058046619</v>
+        <v>12.56982151911688</v>
       </c>
       <c r="E506" t="n">
-        <v>12.85848045755975</v>
+        <v>12.8584814177661</v>
       </c>
       <c r="F506" t="n">
         <v>1737889</v>
@@ -10552,16 +10552,16 @@
         <v>44966</v>
       </c>
       <c r="B507" t="n">
-        <v>12.13245677947998</v>
+        <v>12.1324577331543</v>
       </c>
       <c r="C507" t="n">
-        <v>12.7797553723795</v>
+        <v>12.77975637693486</v>
       </c>
       <c r="D507" t="n">
-        <v>12.06247878084089</v>
+        <v>12.06247972901458</v>
       </c>
       <c r="E507" t="n">
-        <v>12.76226045162213</v>
+        <v>12.7622614548023</v>
       </c>
       <c r="F507" t="n">
         <v>2590377</v>
@@ -10572,16 +10572,16 @@
         <v>44967</v>
       </c>
       <c r="B508" t="n">
-        <v>12.40362358093262</v>
+        <v>12.4036226272583</v>
       </c>
       <c r="C508" t="n">
-        <v>12.47360158523591</v>
+        <v>12.47360062618121</v>
       </c>
       <c r="D508" t="n">
-        <v>11.97500767292852</v>
+        <v>11.97500675220909</v>
       </c>
       <c r="E508" t="n">
-        <v>12.03623863724271</v>
+        <v>12.03623771181543</v>
       </c>
       <c r="F508" t="n">
         <v>3559170</v>
@@ -10592,16 +10592,16 @@
         <v>44970</v>
       </c>
       <c r="B509" t="n">
-        <v>12.52608585357666</v>
+        <v>12.52608489990234</v>
       </c>
       <c r="C509" t="n">
-        <v>12.77100887536473</v>
+        <v>12.77100790304318</v>
       </c>
       <c r="D509" t="n">
-        <v>12.35113999581847</v>
+        <v>12.35113905546367</v>
       </c>
       <c r="E509" t="n">
-        <v>12.38612984112634</v>
+        <v>12.38612889810758</v>
       </c>
       <c r="F509" t="n">
         <v>2916169</v>
@@ -10632,16 +10632,16 @@
         <v>44972</v>
       </c>
       <c r="B511" t="n">
-        <v>12.75351428985596</v>
+        <v>12.75351524353027</v>
       </c>
       <c r="C511" t="n">
-        <v>12.94595337825676</v>
+        <v>12.94595434632116</v>
       </c>
       <c r="D511" t="n">
-        <v>11.91377656401778</v>
+        <v>11.91377745489871</v>
       </c>
       <c r="E511" t="n">
-        <v>12.24617250152178</v>
+        <v>12.24617341725841</v>
       </c>
       <c r="F511" t="n">
         <v>3838217</v>
@@ -10652,16 +10652,16 @@
         <v>44973</v>
       </c>
       <c r="B512" t="n">
-        <v>12.86722850799561</v>
+        <v>12.86722755432129</v>
       </c>
       <c r="C512" t="n">
-        <v>12.98969043678491</v>
+        <v>12.98968947403414</v>
       </c>
       <c r="D512" t="n">
-        <v>12.61355845261168</v>
+        <v>12.6135575177385</v>
       </c>
       <c r="E512" t="n">
-        <v>12.64854661261404</v>
+        <v>12.64854567514766</v>
       </c>
       <c r="F512" t="n">
         <v>1907195</v>
@@ -10692,16 +10692,16 @@
         <v>44979</v>
       </c>
       <c r="B514" t="n">
-        <v>12.63979911804199</v>
+        <v>12.63980007171631</v>
       </c>
       <c r="C514" t="n">
-        <v>12.70977711992058</v>
+        <v>12.70977807887474</v>
       </c>
       <c r="D514" t="n">
-        <v>12.33364514927437</v>
+        <v>12.33364607984934</v>
       </c>
       <c r="E514" t="n">
-        <v>12.70103008023456</v>
+        <v>12.70103103852876</v>
       </c>
       <c r="F514" t="n">
         <v>1228758</v>
@@ -10732,16 +10732,16 @@
         <v>44981</v>
       </c>
       <c r="B516" t="n">
-        <v>11.80881023406982</v>
+        <v>11.80880928039551</v>
       </c>
       <c r="C516" t="n">
-        <v>12.48234918747401</v>
+        <v>12.48234817940498</v>
       </c>
       <c r="D516" t="n">
-        <v>11.69509618250371</v>
+        <v>11.69509523801289</v>
       </c>
       <c r="E516" t="n">
-        <v>12.33364613218022</v>
+        <v>12.33364513612039</v>
       </c>
       <c r="F516" t="n">
         <v>3419242</v>
@@ -10752,16 +10752,16 @@
         <v>44984</v>
       </c>
       <c r="B517" t="n">
-        <v>11.64261054992676</v>
+        <v>11.64261150360107</v>
       </c>
       <c r="C517" t="n">
-        <v>11.87003946193115</v>
+        <v>11.87004043423472</v>
       </c>
       <c r="D517" t="n">
-        <v>11.51140159462404</v>
+        <v>11.51140253755071</v>
       </c>
       <c r="E517" t="n">
-        <v>11.77381950522948</v>
+        <v>11.77382046965144</v>
       </c>
       <c r="F517" t="n">
         <v>3613283</v>
@@ -10812,16 +10812,16 @@
         <v>44987</v>
       </c>
       <c r="B520" t="n">
-        <v>11.80881023406982</v>
+        <v>11.80880928039551</v>
       </c>
       <c r="C520" t="n">
-        <v>11.9750082123251</v>
+        <v>11.9750072452287</v>
       </c>
       <c r="D520" t="n">
-        <v>11.67760125954223</v>
+        <v>11.67760031646429</v>
       </c>
       <c r="E520" t="n">
-        <v>11.76507334776376</v>
+        <v>11.76507239762161</v>
       </c>
       <c r="F520" t="n">
         <v>2331118</v>
@@ -10832,16 +10832,16 @@
         <v>44988</v>
       </c>
       <c r="B521" t="n">
-        <v>11.67759990692139</v>
+        <v>11.6776008605957</v>
       </c>
       <c r="C521" t="n">
-        <v>11.98375386462542</v>
+        <v>11.98375484330241</v>
       </c>
       <c r="D521" t="n">
-        <v>11.60762106537642</v>
+        <v>11.60762201333577</v>
       </c>
       <c r="E521" t="n">
-        <v>11.80006182688108</v>
+        <v>11.80006279055649</v>
       </c>
       <c r="F521" t="n">
         <v>1946973</v>
@@ -10852,16 +10852,16 @@
         <v>44991</v>
       </c>
       <c r="B522" t="n">
-        <v>12.13245677947998</v>
+        <v>12.1324577331543</v>
       </c>
       <c r="C522" t="n">
-        <v>12.2374246196338</v>
+        <v>12.23742558155914</v>
       </c>
       <c r="D522" t="n">
-        <v>11.68634682760701</v>
+        <v>11.68634774621477</v>
       </c>
       <c r="E522" t="n">
-        <v>11.68634682760701</v>
+        <v>11.68634774621477</v>
       </c>
       <c r="F522" t="n">
         <v>3047313</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.26366806030273</v>
+        <v>12.2636661529541</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738295346679</v>
+        <v>12.37738102843226</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87004113878769</v>
+        <v>11.87003929265923</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12371120393195</v>
+        <v>12.12370931835058</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10912,16 +10912,16 @@
         <v>44994</v>
       </c>
       <c r="B525" t="n">
-        <v>12.70977783203125</v>
+        <v>12.70977687835693</v>
       </c>
       <c r="C525" t="n">
-        <v>12.88472368872491</v>
+        <v>12.88472272192359</v>
       </c>
       <c r="D525" t="n">
-        <v>12.55232774008035</v>
+        <v>12.55232679822025</v>
       </c>
       <c r="E525" t="n">
-        <v>12.71852571440263</v>
+        <v>12.71852476007192</v>
       </c>
       <c r="F525" t="n">
         <v>3354932</v>
@@ -10992,16 +10992,16 @@
         <v>45000</v>
       </c>
       <c r="B529" t="n">
-        <v>12.34239196777344</v>
+        <v>12.34239101409912</v>
       </c>
       <c r="C529" t="n">
-        <v>12.44735981090543</v>
+        <v>12.44735884912044</v>
       </c>
       <c r="D529" t="n">
-        <v>11.6338640798038</v>
+        <v>11.63386318087615</v>
       </c>
       <c r="E529" t="n">
-        <v>11.94001804308486</v>
+        <v>11.94001712050125</v>
       </c>
       <c r="F529" t="n">
         <v>3332216</v>
@@ -11032,16 +11032,16 @@
         <v>45002</v>
       </c>
       <c r="B531" t="n">
-        <v>11.73008251190186</v>
+        <v>11.73008346557617</v>
       </c>
       <c r="C531" t="n">
-        <v>12.42986416154627</v>
+        <v>12.42986517211394</v>
       </c>
       <c r="D531" t="n">
-        <v>11.52889556134252</v>
+        <v>11.52889649866001</v>
       </c>
       <c r="E531" t="n">
-        <v>12.26366620924963</v>
+        <v>12.26366720630515</v>
       </c>
       <c r="F531" t="n">
         <v>9035530</v>
@@ -11072,16 +11072,16 @@
         <v>45006</v>
       </c>
       <c r="B533" t="n">
-        <v>11.33645725250244</v>
+        <v>11.33645629882812</v>
       </c>
       <c r="C533" t="n">
-        <v>11.60762137558309</v>
+        <v>11.60762039909721</v>
       </c>
       <c r="D533" t="n">
-        <v>11.24023644808107</v>
+        <v>11.24023550250128</v>
       </c>
       <c r="E533" t="n">
-        <v>11.33645725250244</v>
+        <v>11.33645629882812</v>
       </c>
       <c r="F533" t="n">
         <v>1775142</v>
@@ -11112,16 +11112,16 @@
         <v>45008</v>
       </c>
       <c r="B535" t="n">
-        <v>10.74164295196533</v>
+        <v>10.74164390563965</v>
       </c>
       <c r="C535" t="n">
-        <v>11.58138068181313</v>
+        <v>11.5813817100418</v>
       </c>
       <c r="D535" t="n">
-        <v>10.5054661364364</v>
+        <v>10.50546706914225</v>
       </c>
       <c r="E535" t="n">
-        <v>11.49390775598037</v>
+        <v>11.49390877644294</v>
       </c>
       <c r="F535" t="n">
         <v>4691110</v>
@@ -11172,16 +11172,16 @@
         <v>45013</v>
       </c>
       <c r="B538" t="n">
-        <v>11.56388759613037</v>
+        <v>11.56388568878174</v>
       </c>
       <c r="C538" t="n">
-        <v>11.77382162554307</v>
+        <v>11.7738196835679</v>
       </c>
       <c r="D538" t="n">
-        <v>11.3102158367482</v>
+        <v>11.31021397124021</v>
       </c>
       <c r="E538" t="n">
-        <v>11.3102158367482</v>
+        <v>11.31021397124021</v>
       </c>
       <c r="F538" t="n">
         <v>2291643</v>
@@ -11232,16 +11232,16 @@
         <v>45016</v>
       </c>
       <c r="B541" t="n">
-        <v>11.67759990692139</v>
+        <v>11.6776008605957</v>
       </c>
       <c r="C541" t="n">
-        <v>12.14995266582512</v>
+        <v>12.14995365807506</v>
       </c>
       <c r="D541" t="n">
-        <v>11.66010498598634</v>
+        <v>11.6601059382319</v>
       </c>
       <c r="E541" t="n">
-        <v>12.00999582493039</v>
+        <v>12.00999680575047</v>
       </c>
       <c r="F541" t="n">
         <v>2337175</v>
@@ -11292,16 +11292,16 @@
         <v>45021</v>
       </c>
       <c r="B544" t="n">
-        <v>10.67166423797607</v>
+        <v>10.67166519165039</v>
       </c>
       <c r="C544" t="n">
-        <v>11.3539509927967</v>
+        <v>11.35395200744364</v>
       </c>
       <c r="D544" t="n">
-        <v>10.58419216015985</v>
+        <v>10.58419310601722</v>
       </c>
       <c r="E544" t="n">
-        <v>11.17900599496905</v>
+        <v>11.17900699398201</v>
       </c>
       <c r="F544" t="n">
         <v>4730079</v>
@@ -11332,16 +11332,16 @@
         <v>45026</v>
       </c>
       <c r="B546" t="n">
-        <v>10.89909362792969</v>
+        <v>10.899094581604</v>
       </c>
       <c r="C546" t="n">
-        <v>11.14401663548793</v>
+        <v>11.14401761059309</v>
       </c>
       <c r="D546" t="n">
-        <v>10.64542273845509</v>
+        <v>10.64542366993311</v>
       </c>
       <c r="E546" t="n">
-        <v>10.71540074061458</v>
+        <v>10.71540167821571</v>
       </c>
       <c r="F546" t="n">
         <v>4871319</v>
@@ -11392,16 +11392,16 @@
         <v>45029</v>
       </c>
       <c r="B549" t="n">
-        <v>12.4561071395874</v>
+        <v>12.45610618591309</v>
       </c>
       <c r="C549" t="n">
-        <v>12.64854622467444</v>
+        <v>12.64854525626645</v>
       </c>
       <c r="D549" t="n">
-        <v>11.97500732138171</v>
+        <v>11.97500640454174</v>
       </c>
       <c r="E549" t="n">
-        <v>12.09746924641502</v>
+        <v>12.09746832019902</v>
       </c>
       <c r="F549" t="n">
         <v>4483641</v>
@@ -11412,16 +11412,16 @@
         <v>45030</v>
       </c>
       <c r="B550" t="n">
-        <v>12.52608585357666</v>
+        <v>12.52608489990234</v>
       </c>
       <c r="C550" t="n">
-        <v>12.72727283202282</v>
+        <v>12.72727186303112</v>
       </c>
       <c r="D550" t="n">
-        <v>12.22867890602208</v>
+        <v>12.22867797499086</v>
       </c>
       <c r="E550" t="n">
-        <v>12.42111800204363</v>
+        <v>12.42111705636105</v>
       </c>
       <c r="F550" t="n">
         <v>2806225</v>
@@ -11432,16 +11432,16 @@
         <v>45033</v>
       </c>
       <c r="B551" t="n">
-        <v>12.34239196777344</v>
+        <v>12.34239101409912</v>
       </c>
       <c r="C551" t="n">
-        <v>12.56982089090072</v>
+        <v>12.56981991965339</v>
       </c>
       <c r="D551" t="n">
-        <v>12.2286779273074</v>
+        <v>12.22867698241957</v>
       </c>
       <c r="E551" t="n">
-        <v>12.50859077200068</v>
+        <v>12.50858980548449</v>
       </c>
       <c r="F551" t="n">
         <v>3419242</v>
@@ -11452,16 +11452,16 @@
         <v>45034</v>
       </c>
       <c r="B552" t="n">
-        <v>11.62511730194092</v>
+        <v>11.62511825561523</v>
       </c>
       <c r="C552" t="n">
-        <v>12.42111728751052</v>
+        <v>12.42111830648523</v>
       </c>
       <c r="D552" t="n">
-        <v>11.55513845754605</v>
+        <v>11.55513940547961</v>
       </c>
       <c r="E552" t="n">
-        <v>12.3336452058586</v>
+        <v>12.33364621765748</v>
       </c>
       <c r="F552" t="n">
         <v>3919084</v>
@@ -11492,16 +11492,16 @@
         <v>45036</v>
       </c>
       <c r="B554" t="n">
-        <v>11.47641372680664</v>
+        <v>11.47641277313232</v>
       </c>
       <c r="C554" t="n">
-        <v>11.60762185284227</v>
+        <v>11.60762088826473</v>
       </c>
       <c r="D554" t="n">
-        <v>11.24023691023484</v>
+        <v>11.24023597618649</v>
       </c>
       <c r="E554" t="n">
-        <v>11.34520475857576</v>
+        <v>11.34520381580472</v>
       </c>
       <c r="F554" t="n">
         <v>2067718</v>
@@ -11512,16 +11512,16 @@
         <v>45040</v>
       </c>
       <c r="B555" t="n">
-        <v>11.52889728546143</v>
+        <v>11.52889633178711</v>
       </c>
       <c r="C555" t="n">
-        <v>11.66885329944233</v>
+        <v>11.6688523341908</v>
       </c>
       <c r="D555" t="n">
-        <v>11.41518323465077</v>
+        <v>11.41518229038292</v>
       </c>
       <c r="E555" t="n">
-        <v>11.53764432578641</v>
+        <v>11.53764337138853</v>
       </c>
       <c r="F555" t="n">
         <v>1779282</v>
@@ -11552,16 +11552,16 @@
         <v>45042</v>
       </c>
       <c r="B557" t="n">
-        <v>11.25773143768311</v>
+        <v>11.25773048400879</v>
       </c>
       <c r="C557" t="n">
-        <v>11.49390740377979</v>
+        <v>11.49390643009834</v>
       </c>
       <c r="D557" t="n">
-        <v>11.21399539720453</v>
+        <v>11.21399444723522</v>
       </c>
       <c r="E557" t="n">
-        <v>11.24898355583121</v>
+        <v>11.24898260289795</v>
       </c>
       <c r="F557" t="n">
         <v>2213905</v>
@@ -11592,16 +11592,16 @@
         <v>45044</v>
       </c>
       <c r="B559" t="n">
-        <v>10.68915939331055</v>
+        <v>10.68916034698486</v>
       </c>
       <c r="C559" t="n">
-        <v>10.86410439497541</v>
+        <v>10.86410536425811</v>
       </c>
       <c r="D559" t="n">
-        <v>10.36551050858414</v>
+        <v>10.36551143338288</v>
       </c>
       <c r="E559" t="n">
-        <v>10.83786243417687</v>
+        <v>10.8378634011183</v>
       </c>
       <c r="F559" t="n">
         <v>8236247</v>
@@ -11612,16 +11612,16 @@
         <v>45048</v>
       </c>
       <c r="B560" t="n">
-        <v>10.15557670593262</v>
+        <v>10.1555757522583</v>
       </c>
       <c r="C560" t="n">
-        <v>10.65417064345897</v>
+        <v>10.65416964296346</v>
       </c>
       <c r="D560" t="n">
-        <v>10.02436773067856</v>
+        <v>10.02436678932562</v>
       </c>
       <c r="E560" t="n">
-        <v>10.592940518243</v>
+        <v>10.5929395234974</v>
       </c>
       <c r="F560" t="n">
         <v>7078259</v>
@@ -11652,16 +11652,16 @@
         <v>45050</v>
       </c>
       <c r="B562" t="n">
-        <v>9.429553031921387</v>
+        <v>9.42955207824707</v>
       </c>
       <c r="C562" t="n">
-        <v>10.19056485620714</v>
+        <v>10.19056382556656</v>
       </c>
       <c r="D562" t="n">
-        <v>9.324585186754883</v>
+        <v>9.324584243696673</v>
       </c>
       <c r="E562" t="n">
-        <v>10.14682881551792</v>
+        <v>10.14682778930066</v>
       </c>
       <c r="F562" t="n">
         <v>16781627</v>
@@ -11692,16 +11692,16 @@
         <v>45054</v>
       </c>
       <c r="B564" t="n">
-        <v>9.960693359375</v>
+        <v>9.960694313049316</v>
       </c>
       <c r="C564" t="n">
-        <v>10.13590312215261</v>
+        <v>10.13590409260217</v>
       </c>
       <c r="D564" t="n">
-        <v>9.75920107784351</v>
+        <v>9.759202012226195</v>
       </c>
       <c r="E564" t="n">
-        <v>10.10962144686852</v>
+        <v>10.10962241480177</v>
       </c>
       <c r="F564" t="n">
         <v>5548545</v>
@@ -11712,16 +11712,16 @@
         <v>45055</v>
       </c>
       <c r="B565" t="n">
-        <v>10.18846702575684</v>
+        <v>10.18846607208252</v>
       </c>
       <c r="C565" t="n">
-        <v>10.2322692579614</v>
+        <v>10.23226830018705</v>
       </c>
       <c r="D565" t="n">
-        <v>9.732920774337941</v>
+        <v>9.732919863304266</v>
       </c>
       <c r="E565" t="n">
-        <v>9.943172501083659</v>
+        <v>9.943171570369724</v>
       </c>
       <c r="F565" t="n">
         <v>5766311</v>
@@ -11732,16 +11732,16 @@
         <v>45056</v>
       </c>
       <c r="B566" t="n">
-        <v>10.00449562072754</v>
+        <v>10.00449466705322</v>
       </c>
       <c r="C566" t="n">
-        <v>10.33739546432518</v>
+        <v>10.33739447891732</v>
       </c>
       <c r="D566" t="n">
-        <v>9.969454508577106</v>
+        <v>9.969453558243071</v>
       </c>
       <c r="E566" t="n">
-        <v>10.24979099700936</v>
+        <v>10.24979001995237</v>
       </c>
       <c r="F566" t="n">
         <v>5572472</v>
@@ -11812,16 +11812,16 @@
         <v>45062</v>
       </c>
       <c r="B570" t="n">
-        <v>9.951933860778809</v>
+        <v>9.951932907104492</v>
       </c>
       <c r="C570" t="n">
-        <v>10.35491592496318</v>
+        <v>10.35491493267188</v>
       </c>
       <c r="D570" t="n">
-        <v>9.864328550800552</v>
+        <v>9.864327605521281</v>
       </c>
       <c r="E570" t="n">
-        <v>10.17970614847653</v>
+        <v>10.17970517297524</v>
       </c>
       <c r="F570" t="n">
         <v>2372207</v>
@@ -11932,16 +11932,16 @@
         <v>45070</v>
       </c>
       <c r="B576" t="n">
-        <v>10.93310928344727</v>
+        <v>10.93310832977295</v>
       </c>
       <c r="C576" t="n">
-        <v>11.28353051793955</v>
+        <v>11.28352953369865</v>
       </c>
       <c r="D576" t="n">
-        <v>10.92434900562591</v>
+        <v>10.92434805271574</v>
       </c>
       <c r="E576" t="n">
-        <v>11.0820382237595</v>
+        <v>11.0820372570944</v>
       </c>
       <c r="F576" t="n">
         <v>2685985</v>
@@ -11972,16 +11972,16 @@
         <v>45072</v>
       </c>
       <c r="B578" t="n">
-        <v>11.67775058746338</v>
+        <v>11.67775249481201</v>
       </c>
       <c r="C578" t="n">
-        <v>11.90552368174234</v>
+        <v>11.90552562629357</v>
       </c>
       <c r="D578" t="n">
-        <v>11.47625916626848</v>
+        <v>11.47626104070714</v>
       </c>
       <c r="E578" t="n">
-        <v>11.54634306551281</v>
+        <v>11.54634495139841</v>
       </c>
       <c r="F578" t="n">
         <v>3617321</v>
@@ -11992,16 +11992,16 @@
         <v>45075</v>
       </c>
       <c r="B579" t="n">
-        <v>11.62518787384033</v>
+        <v>11.62518882751465</v>
       </c>
       <c r="C579" t="n">
-        <v>11.76535652342553</v>
+        <v>11.76535748859861</v>
       </c>
       <c r="D579" t="n">
-        <v>11.45873923668059</v>
+        <v>11.45874017670026</v>
       </c>
       <c r="E579" t="n">
-        <v>11.73031457189667</v>
+        <v>11.73031553419508</v>
       </c>
       <c r="F579" t="n">
         <v>1756970</v>
@@ -12012,16 +12012,16 @@
         <v>45076</v>
       </c>
       <c r="B580" t="n">
-        <v>11.21344470977783</v>
+        <v>11.21344566345215</v>
       </c>
       <c r="C580" t="n">
-        <v>11.82668012549439</v>
+        <v>11.82668113132278</v>
       </c>
       <c r="D580" t="n">
-        <v>11.12584025286816</v>
+        <v>11.12584119909194</v>
       </c>
       <c r="E580" t="n">
-        <v>11.6689909221993</v>
+        <v>11.66899191461664</v>
       </c>
       <c r="F580" t="n">
         <v>4905847</v>
@@ -12052,16 +12052,16 @@
         <v>45078</v>
       </c>
       <c r="B582" t="n">
-        <v>11.79163837432861</v>
+        <v>11.79163932800293</v>
       </c>
       <c r="C582" t="n">
-        <v>11.8704833990503</v>
+        <v>11.87048435910138</v>
       </c>
       <c r="D582" t="n">
-        <v>11.23096629801013</v>
+        <v>11.23096720633888</v>
       </c>
       <c r="E582" t="n">
-        <v>11.34485327478486</v>
+        <v>11.34485419232446</v>
       </c>
       <c r="F582" t="n">
         <v>6914909</v>
@@ -12152,16 +12152,16 @@
         <v>45086</v>
       </c>
       <c r="B587" t="n">
-        <v>12.79033470153809</v>
+        <v>12.7903356552124</v>
       </c>
       <c r="C587" t="n">
-        <v>13.01810780144024</v>
+        <v>13.0181087720978</v>
       </c>
       <c r="D587" t="n">
-        <v>12.60636467234733</v>
+        <v>12.60636561230446</v>
       </c>
       <c r="E587" t="n">
-        <v>12.69396997030039</v>
+        <v>12.69397091678955</v>
       </c>
       <c r="F587" t="n">
         <v>3362705</v>
@@ -12172,16 +12172,16 @@
         <v>45089</v>
       </c>
       <c r="B588" t="n">
-        <v>12.80785655975342</v>
+        <v>12.80785751342773</v>
       </c>
       <c r="C588" t="n">
-        <v>12.97430688489936</v>
+        <v>12.97430785096759</v>
       </c>
       <c r="D588" t="n">
-        <v>12.72025125864552</v>
+        <v>12.72025220579673</v>
       </c>
       <c r="E588" t="n">
-        <v>12.79909628268356</v>
+        <v>12.79909723570558</v>
       </c>
       <c r="F588" t="n">
         <v>2677201</v>
@@ -12192,16 +12192,16 @@
         <v>45090</v>
       </c>
       <c r="B589" t="n">
-        <v>12.52752208709717</v>
+        <v>12.52752017974854</v>
       </c>
       <c r="C589" t="n">
-        <v>13.04439113335547</v>
+        <v>13.04438914731215</v>
       </c>
       <c r="D589" t="n">
-        <v>12.29974811477101</v>
+        <v>12.29974624210157</v>
       </c>
       <c r="E589" t="n">
-        <v>12.86042108077874</v>
+        <v>12.86041912274534</v>
       </c>
       <c r="F589" t="n">
         <v>6116837</v>
@@ -12212,16 +12212,16 @@
         <v>45091</v>
       </c>
       <c r="B590" t="n">
-        <v>12.88670063018799</v>
+        <v>12.8867015838623</v>
       </c>
       <c r="C590" t="n">
-        <v>12.93926397909746</v>
+        <v>12.9392649366617</v>
       </c>
       <c r="D590" t="n">
-        <v>12.46619721279127</v>
+        <v>12.46619813534643</v>
       </c>
       <c r="E590" t="n">
-        <v>12.58884362113043</v>
+        <v>12.58884455276198</v>
       </c>
       <c r="F590" t="n">
         <v>4237809</v>
@@ -12232,16 +12232,16 @@
         <v>45092</v>
       </c>
       <c r="B591" t="n">
-        <v>12.83413791656494</v>
+        <v>12.83413887023926</v>
       </c>
       <c r="C591" t="n">
-        <v>13.0794315727341</v>
+        <v>13.07943254463561</v>
       </c>
       <c r="D591" t="n">
-        <v>12.77281429165521</v>
+        <v>12.77281524077272</v>
       </c>
       <c r="E591" t="n">
-        <v>12.86917986744625</v>
+        <v>12.86918082372445</v>
       </c>
       <c r="F591" t="n">
         <v>4574806</v>
@@ -12252,16 +12252,16 @@
         <v>45093</v>
       </c>
       <c r="B592" t="n">
-        <v>11.92304420471191</v>
+        <v>11.92304611206055</v>
       </c>
       <c r="C592" t="n">
-        <v>12.76405352392952</v>
+        <v>12.76405556581577</v>
       </c>
       <c r="D592" t="n">
-        <v>11.66023000494414</v>
+        <v>11.66023187024996</v>
       </c>
       <c r="E592" t="n">
-        <v>12.76405352392952</v>
+        <v>12.76405556581577</v>
       </c>
       <c r="F592" t="n">
         <v>19648730</v>
@@ -12532,16 +12532,16 @@
         <v>45113</v>
       </c>
       <c r="B606" t="n">
-        <v>10.34797286987305</v>
+        <v>10.34797382354736</v>
       </c>
       <c r="C606" t="n">
-        <v>10.56908340488516</v>
+        <v>10.56908437893714</v>
       </c>
       <c r="D606" t="n">
-        <v>10.19761763858723</v>
+        <v>10.19761857840473</v>
       </c>
       <c r="E606" t="n">
-        <v>10.51601734882532</v>
+        <v>10.5160183179867</v>
       </c>
       <c r="F606" t="n">
         <v>6243800</v>
@@ -12572,16 +12572,16 @@
         <v>45117</v>
       </c>
       <c r="B608" t="n">
-        <v>10.58677291870117</v>
+        <v>10.58677387237549</v>
       </c>
       <c r="C608" t="n">
-        <v>10.6840612529032</v>
+        <v>10.68406221534142</v>
       </c>
       <c r="D608" t="n">
-        <v>10.41872843552429</v>
+        <v>10.41872937406088</v>
       </c>
       <c r="E608" t="n">
-        <v>10.54255064189306</v>
+        <v>10.54255159158376</v>
       </c>
       <c r="F608" t="n">
         <v>4418500</v>
@@ -12792,16 +12792,16 @@
         <v>45132</v>
       </c>
       <c r="B619" t="n">
-        <v>10.53370666503906</v>
+        <v>10.53370571136475</v>
       </c>
       <c r="C619" t="n">
-        <v>10.82557252904746</v>
+        <v>10.82557154894893</v>
       </c>
       <c r="D619" t="n">
-        <v>10.46295135518671</v>
+        <v>10.46295040791826</v>
       </c>
       <c r="E619" t="n">
-        <v>10.61330659949041</v>
+        <v>10.61330563860948</v>
       </c>
       <c r="F619" t="n">
         <v>5058400</v>
@@ -12852,16 +12852,16 @@
         <v>45135</v>
       </c>
       <c r="B622" t="n">
-        <v>10.3568172454834</v>
+        <v>10.35681819915771</v>
       </c>
       <c r="C622" t="n">
-        <v>10.39219489649865</v>
+        <v>10.3921958534306</v>
       </c>
       <c r="D622" t="n">
-        <v>10.1887736140284</v>
+        <v>10.18877455222896</v>
       </c>
       <c r="E622" t="n">
-        <v>10.34797262186215</v>
+        <v>10.34797357472204</v>
       </c>
       <c r="F622" t="n">
         <v>4029200</v>
@@ -12952,16 +12952,16 @@
         <v>45142</v>
       </c>
       <c r="B627" t="n">
-        <v>10.71943855285645</v>
+        <v>10.71943950653076</v>
       </c>
       <c r="C627" t="n">
-        <v>11.21472651856076</v>
+        <v>11.21472751629927</v>
       </c>
       <c r="D627" t="n">
-        <v>10.59561635056293</v>
+        <v>10.59561729322118</v>
       </c>
       <c r="E627" t="n">
-        <v>10.70175014879723</v>
+        <v>10.70175110089786</v>
       </c>
       <c r="F627" t="n">
         <v>16706200</v>
@@ -12972,16 +12972,16 @@
         <v>45145</v>
       </c>
       <c r="B628" t="n">
-        <v>10.31259536743164</v>
+        <v>10.31259632110596</v>
       </c>
       <c r="C628" t="n">
-        <v>10.80788334416182</v>
+        <v>10.80788434363871</v>
       </c>
       <c r="D628" t="n">
-        <v>10.25952931060291</v>
+        <v>10.25953025936985</v>
       </c>
       <c r="E628" t="n">
-        <v>10.79019409623906</v>
+        <v>10.79019509408012</v>
       </c>
       <c r="F628" t="n">
         <v>9603900</v>
@@ -12992,16 +12992,16 @@
         <v>45146</v>
       </c>
       <c r="B629" t="n">
-        <v>10.53370666503906</v>
+        <v>10.53370571136475</v>
       </c>
       <c r="C629" t="n">
-        <v>10.59561735029241</v>
+        <v>10.59561639101298</v>
       </c>
       <c r="D629" t="n">
-        <v>10.00304184114644</v>
+        <v>10.00304093551612</v>
       </c>
       <c r="E629" t="n">
-        <v>10.24184080103066</v>
+        <v>10.24183987378056</v>
       </c>
       <c r="F629" t="n">
         <v>6465200</v>
@@ -13012,16 +13012,16 @@
         <v>45147</v>
       </c>
       <c r="B630" t="n">
-        <v>10.5425500869751</v>
+        <v>10.54255104064941</v>
       </c>
       <c r="C630" t="n">
-        <v>10.68406069053669</v>
+        <v>10.68406165701199</v>
       </c>
       <c r="D630" t="n">
-        <v>10.36566183252311</v>
+        <v>10.3656627701962</v>
       </c>
       <c r="E630" t="n">
-        <v>10.53370546338507</v>
+        <v>10.5337064162593</v>
       </c>
       <c r="F630" t="n">
         <v>5435200</v>
@@ -13032,16 +13032,16 @@
         <v>45148</v>
       </c>
       <c r="B631" t="n">
-        <v>10.63099479675293</v>
+        <v>10.63099575042725</v>
       </c>
       <c r="C631" t="n">
-        <v>10.86094910928421</v>
+        <v>10.86095008358703</v>
       </c>
       <c r="D631" t="n">
-        <v>10.5248609990065</v>
+        <v>10.52486194315988</v>
       </c>
       <c r="E631" t="n">
-        <v>10.66637244817849</v>
+        <v>10.66637340502643</v>
       </c>
       <c r="F631" t="n">
         <v>4975000</v>
@@ -13112,16 +13112,16 @@
         <v>45154</v>
       </c>
       <c r="B635" t="n">
-        <v>10.38335132598877</v>
+        <v>10.38335037231445</v>
       </c>
       <c r="C635" t="n">
-        <v>10.48064050875037</v>
+        <v>10.48063954614038</v>
       </c>
       <c r="D635" t="n">
-        <v>10.25952995661192</v>
+        <v>10.25952901431016</v>
       </c>
       <c r="E635" t="n">
-        <v>10.46295125971378</v>
+        <v>10.46295029872849</v>
       </c>
       <c r="F635" t="n">
         <v>5623400</v>
@@ -13132,16 +13132,16 @@
         <v>45155</v>
       </c>
       <c r="B636" t="n">
-        <v>10.13570690155029</v>
+        <v>10.13570785522461</v>
       </c>
       <c r="C636" t="n">
-        <v>10.51601728953731</v>
+        <v>10.51601827899524</v>
       </c>
       <c r="D636" t="n">
-        <v>10.10917387366996</v>
+        <v>10.10917482484777</v>
       </c>
       <c r="E636" t="n">
-        <v>10.43641736242656</v>
+        <v>10.43641834439489</v>
       </c>
       <c r="F636" t="n">
         <v>6587600</v>
@@ -13192,16 +13192,16 @@
         <v>45160</v>
       </c>
       <c r="B639" t="n">
-        <v>10.63099479675293</v>
+        <v>10.63099575042725</v>
       </c>
       <c r="C639" t="n">
-        <v>10.70175009960405</v>
+        <v>10.70175105962561</v>
       </c>
       <c r="D639" t="n">
-        <v>10.18877373219854</v>
+        <v>10.18877464620255</v>
       </c>
       <c r="E639" t="n">
-        <v>10.24183978760201</v>
+        <v>10.24184070636641</v>
       </c>
       <c r="F639" t="n">
         <v>5680500</v>
@@ -13232,16 +13232,16 @@
         <v>45162</v>
       </c>
       <c r="B641" t="n">
-        <v>10.73712730407715</v>
+        <v>10.73712825775146</v>
       </c>
       <c r="C641" t="n">
-        <v>10.99361547710312</v>
+        <v>10.99361645355878</v>
       </c>
       <c r="D641" t="n">
-        <v>10.64868275746004</v>
+        <v>10.64868370327869</v>
       </c>
       <c r="E641" t="n">
-        <v>10.85210487729151</v>
+        <v>10.85210584117816</v>
       </c>
       <c r="F641" t="n">
         <v>5730800</v>
@@ -13312,16 +13312,16 @@
         <v>45168</v>
       </c>
       <c r="B645" t="n">
-        <v>10.53370666503906</v>
+        <v>10.53370571136475</v>
       </c>
       <c r="C645" t="n">
-        <v>10.59561735029241</v>
+        <v>10.59561639101298</v>
       </c>
       <c r="D645" t="n">
-        <v>10.40104066993336</v>
+        <v>10.40103972827003</v>
       </c>
       <c r="E645" t="n">
-        <v>10.52486204044006</v>
+        <v>10.5248610875665</v>
       </c>
       <c r="F645" t="n">
         <v>3749300</v>
@@ -13332,16 +13332,16 @@
         <v>45169</v>
       </c>
       <c r="B646" t="n">
-        <v>10.3568172454834</v>
+        <v>10.35681819915771</v>
       </c>
       <c r="C646" t="n">
-        <v>10.71059375563589</v>
+        <v>10.71059474188658</v>
       </c>
       <c r="D646" t="n">
-        <v>10.27721731983166</v>
+        <v>10.27721826617627</v>
       </c>
       <c r="E646" t="n">
-        <v>10.59561617896889</v>
+        <v>10.59561715463224</v>
       </c>
       <c r="F646" t="n">
         <v>8716900</v>
@@ -13372,16 +13372,16 @@
         <v>45173</v>
       </c>
       <c r="B648" t="n">
-        <v>10.78134918212891</v>
+        <v>10.78135013580322</v>
       </c>
       <c r="C648" t="n">
-        <v>10.90517138384658</v>
+        <v>10.9051723484737</v>
       </c>
       <c r="D648" t="n">
-        <v>10.56908327358697</v>
+        <v>10.5690842084851</v>
       </c>
       <c r="E648" t="n">
-        <v>10.57792789731032</v>
+        <v>10.57792883299081</v>
       </c>
       <c r="F648" t="n">
         <v>4629200</v>
@@ -13472,16 +13472,16 @@
         <v>45181</v>
       </c>
       <c r="B653" t="n">
-        <v>9.843840599060059</v>
+        <v>9.843841552734375</v>
       </c>
       <c r="C653" t="n">
-        <v>9.879218249051167</v>
+        <v>9.879219206152881</v>
       </c>
       <c r="D653" t="n">
-        <v>9.454685605688161</v>
+        <v>9.454686521661021</v>
       </c>
       <c r="E653" t="n">
-        <v>9.560819399131194</v>
+        <v>9.560820325386327</v>
       </c>
       <c r="F653" t="n">
         <v>7074900</v>
@@ -13532,16 +13532,16 @@
         <v>45184</v>
       </c>
       <c r="B656" t="n">
-        <v>9.375086784362793</v>
+        <v>9.375087738037109</v>
       </c>
       <c r="C656" t="n">
-        <v>10.00304072162537</v>
+        <v>10.00304173917788</v>
       </c>
       <c r="D656" t="n">
-        <v>9.375086784362793</v>
+        <v>9.375087738037109</v>
       </c>
       <c r="E656" t="n">
-        <v>9.923440796082692</v>
+        <v>9.923441805537948</v>
       </c>
       <c r="F656" t="n">
         <v>14904000</v>
@@ -13632,16 +13632,16 @@
         <v>45191</v>
       </c>
       <c r="B661" t="n">
-        <v>8.57908821105957</v>
+        <v>8.579089164733887</v>
       </c>
       <c r="C661" t="n">
-        <v>9.003620858146471</v>
+        <v>9.003621859012968</v>
       </c>
       <c r="D661" t="n">
-        <v>8.428732986411056</v>
+        <v>8.428733923371484</v>
       </c>
       <c r="E661" t="n">
-        <v>8.994776234703684</v>
+        <v>8.994777234586989</v>
       </c>
       <c r="F661" t="n">
         <v>16137800</v>
@@ -13692,16 +13692,16 @@
         <v>45196</v>
       </c>
       <c r="B664" t="n">
-        <v>8.38451099395752</v>
+        <v>8.384511947631836</v>
       </c>
       <c r="C664" t="n">
-        <v>8.738288352310379</v>
+        <v>8.738289346224178</v>
       </c>
       <c r="D664" t="n">
-        <v>8.181089708767164</v>
+        <v>8.181090639303859</v>
       </c>
       <c r="E664" t="n">
-        <v>8.579088498878106</v>
+        <v>8.579089474684132</v>
       </c>
       <c r="F664" t="n">
         <v>7653500</v>
@@ -13712,16 +13712,16 @@
         <v>45197</v>
       </c>
       <c r="B665" t="n">
-        <v>8.561399459838867</v>
+        <v>8.561400413513184</v>
       </c>
       <c r="C665" t="n">
-        <v>8.676377029515013</v>
+        <v>8.676377995996951</v>
       </c>
       <c r="D665" t="n">
-        <v>8.331444320486574</v>
+        <v>8.33144524854565</v>
       </c>
       <c r="E665" t="n">
-        <v>8.375666592434273</v>
+        <v>8.375667525419372</v>
       </c>
       <c r="F665" t="n">
         <v>5776700</v>
@@ -13772,16 +13772,16 @@
         <v>45202</v>
       </c>
       <c r="B668" t="n">
-        <v>7.659268379211426</v>
+        <v>7.659268856048584</v>
       </c>
       <c r="C668" t="n">
-        <v>7.933445798766693</v>
+        <v>7.933446292673103</v>
       </c>
       <c r="D668" t="n">
-        <v>7.570824676122735</v>
+        <v>7.570825147453722</v>
       </c>
       <c r="E668" t="n">
-        <v>7.880378902137712</v>
+        <v>7.880379392740378</v>
       </c>
       <c r="F668" t="n">
         <v>18608300</v>
@@ -13792,16 +13792,16 @@
         <v>45203</v>
       </c>
       <c r="B669" t="n">
-        <v>7.738868236541748</v>
+        <v>7.738868713378906</v>
       </c>
       <c r="C669" t="n">
-        <v>7.853845808701018</v>
+        <v>7.85384629262262</v>
       </c>
       <c r="D669" t="n">
-        <v>7.632735287656968</v>
+        <v>7.632735757954652</v>
       </c>
       <c r="E669" t="n">
-        <v>7.756557483090727</v>
+        <v>7.756557961017825</v>
       </c>
       <c r="F669" t="n">
         <v>14186500</v>
@@ -13812,16 +13812,16 @@
         <v>45204</v>
       </c>
       <c r="B670" t="n">
-        <v>7.68580150604248</v>
+        <v>7.685802459716797</v>
       </c>
       <c r="C670" t="n">
-        <v>7.800779080680249</v>
+        <v>7.800780048621283</v>
       </c>
       <c r="D670" t="n">
-        <v>7.579668554869859</v>
+        <v>7.579669495374922</v>
       </c>
       <c r="E670" t="n">
-        <v>7.73886840336365</v>
+        <v>7.738869363622646</v>
       </c>
       <c r="F670" t="n">
         <v>5277500</v>
@@ -13832,16 +13832,16 @@
         <v>45205</v>
       </c>
       <c r="B671" t="n">
-        <v>7.473536014556885</v>
+        <v>7.473536491394043</v>
       </c>
       <c r="C671" t="n">
-        <v>7.606202843418344</v>
+        <v>7.6062033287201</v>
       </c>
       <c r="D671" t="n">
-        <v>7.385092305452343</v>
+        <v>7.38509277664649</v>
       </c>
       <c r="E671" t="n">
-        <v>7.561980567131191</v>
+        <v>7.561981049611414</v>
       </c>
       <c r="F671" t="n">
         <v>8202400</v>
@@ -13852,16 +13852,16 @@
         <v>45208</v>
       </c>
       <c r="B672" t="n">
-        <v>7.71233606338501</v>
+        <v>7.712336540222168</v>
       </c>
       <c r="C672" t="n">
-        <v>7.809624399758072</v>
+        <v>7.809624882610359</v>
       </c>
       <c r="D672" t="n">
-        <v>7.385092557254024</v>
+        <v>7.385093013858421</v>
       </c>
       <c r="E672" t="n">
-        <v>7.393936338037181</v>
+        <v>7.393936795188369</v>
       </c>
       <c r="F672" t="n">
         <v>4734000</v>
@@ -13872,16 +13872,16 @@
         <v>45209</v>
       </c>
       <c r="B673" t="n">
-        <v>8.101489067077637</v>
+        <v>8.101490020751953</v>
       </c>
       <c r="C673" t="n">
-        <v>8.189933609727872</v>
+        <v>8.18993457381352</v>
       </c>
       <c r="D673" t="n">
-        <v>7.906911579328923</v>
+        <v>7.906912510098369</v>
       </c>
       <c r="E673" t="n">
-        <v>7.95113385065404</v>
+        <v>7.951134786629153</v>
       </c>
       <c r="F673" t="n">
         <v>9907700</v>
@@ -13892,16 +13892,16 @@
         <v>45210</v>
       </c>
       <c r="B674" t="n">
-        <v>7.933446407318115</v>
+        <v>7.933446884155273</v>
       </c>
       <c r="C674" t="n">
-        <v>8.22531225249141</v>
+        <v>8.225312746871069</v>
       </c>
       <c r="D674" t="n">
-        <v>7.818468825360488</v>
+        <v>7.818469295286956</v>
       </c>
       <c r="E674" t="n">
-        <v>8.207623004434957</v>
+        <v>8.20762349775141</v>
       </c>
       <c r="F674" t="n">
         <v>7415900</v>
@@ -13912,16 +13912,16 @@
         <v>45212</v>
       </c>
       <c r="B675" t="n">
-        <v>7.561980247497559</v>
+        <v>7.561981201171875</v>
       </c>
       <c r="C675" t="n">
-        <v>7.933446003056718</v>
+        <v>7.933447003578201</v>
       </c>
       <c r="D675" t="n">
-        <v>7.500068725924546</v>
+        <v>7.50006967179093</v>
       </c>
       <c r="E675" t="n">
-        <v>7.898068352216309</v>
+        <v>7.898069348276162</v>
       </c>
       <c r="F675" t="n">
         <v>6681200</v>
@@ -13932,16 +13932,16 @@
         <v>45215</v>
       </c>
       <c r="B676" t="n">
-        <v>7.561980247497559</v>
+        <v>7.561981201171875</v>
       </c>
       <c r="C676" t="n">
-        <v>7.721179254544534</v>
+        <v>7.721180228296132</v>
       </c>
       <c r="D676" t="n">
-        <v>7.473535698661672</v>
+        <v>7.47353664118186</v>
       </c>
       <c r="E676" t="n">
-        <v>7.623890925600842</v>
+        <v>7.623891887082984</v>
       </c>
       <c r="F676" t="n">
         <v>6364500</v>
@@ -13952,16 +13952,16 @@
         <v>45216</v>
       </c>
       <c r="B677" t="n">
-        <v>7.641580104827881</v>
+        <v>7.641581058502197</v>
       </c>
       <c r="C677" t="n">
-        <v>7.668113131854896</v>
+        <v>7.668114088840552</v>
       </c>
       <c r="D677" t="n">
-        <v>7.447002605200417</v>
+        <v>7.447003534591332</v>
       </c>
       <c r="E677" t="n">
-        <v>7.544290933279289</v>
+        <v>7.544291874811851</v>
       </c>
       <c r="F677" t="n">
         <v>6592700</v>
@@ -13992,16 +13992,16 @@
         <v>45218</v>
       </c>
       <c r="B679" t="n">
-        <v>7.06669282913208</v>
+        <v>7.066692352294922</v>
       </c>
       <c r="C679" t="n">
-        <v>7.287803374550253</v>
+        <v>7.287802882793285</v>
       </c>
       <c r="D679" t="n">
-        <v>7.06669282913208</v>
+        <v>7.066692352294922</v>
       </c>
       <c r="E679" t="n">
-        <v>7.199359662464859</v>
+        <v>7.199359176675781</v>
       </c>
       <c r="F679" t="n">
         <v>6424400</v>
@@ -14012,16 +14012,16 @@
         <v>45219</v>
       </c>
       <c r="B680" t="n">
-        <v>7.102070331573486</v>
+        <v>7.102070808410645</v>
       </c>
       <c r="C680" t="n">
-        <v>7.163981856532952</v>
+        <v>7.163982337526886</v>
       </c>
       <c r="D680" t="n">
-        <v>6.916337865369526</v>
+        <v>6.916338329736497</v>
       </c>
       <c r="E680" t="n">
-        <v>7.013626199634722</v>
+        <v>7.013626670533689</v>
       </c>
       <c r="F680" t="n">
         <v>6704900</v>
@@ -14092,16 +14092,16 @@
         <v>45225</v>
       </c>
       <c r="B684" t="n">
-        <v>7.102070331573486</v>
+        <v>7.102070808410645</v>
       </c>
       <c r="C684" t="n">
-        <v>7.137447984348992</v>
+        <v>7.137448463561426</v>
       </c>
       <c r="D684" t="n">
-        <v>6.783671456593937</v>
+        <v>6.783671912053608</v>
       </c>
       <c r="E684" t="n">
-        <v>6.854426762144948</v>
+        <v>6.854427222355172</v>
       </c>
       <c r="F684" t="n">
         <v>6790200</v>
@@ -14172,16 +14172,16 @@
         <v>45231</v>
       </c>
       <c r="B688" t="n">
-        <v>7.013626575469971</v>
+        <v>7.013626098632812</v>
       </c>
       <c r="C688" t="n">
-        <v>7.402781198588827</v>
+        <v>7.402780695294118</v>
       </c>
       <c r="D688" t="n">
-        <v>6.916338235991438</v>
+        <v>6.916337765768647</v>
       </c>
       <c r="E688" t="n">
-        <v>6.969404717998341</v>
+        <v>6.969404244167705</v>
       </c>
       <c r="F688" t="n">
         <v>11133300</v>
@@ -14192,16 +14192,16 @@
         <v>45233</v>
       </c>
       <c r="B689" t="n">
-        <v>8.030734062194824</v>
+        <v>8.030735015869141</v>
       </c>
       <c r="C689" t="n">
-        <v>8.030734062194824</v>
+        <v>8.030735015869141</v>
       </c>
       <c r="D689" t="n">
-        <v>7.23473652329359</v>
+        <v>7.234737382440756</v>
       </c>
       <c r="E689" t="n">
-        <v>7.305491822597268</v>
+        <v>7.305492690146844</v>
       </c>
       <c r="F689" t="n">
         <v>15995000</v>
@@ -14212,16 +14212,16 @@
         <v>45236</v>
       </c>
       <c r="B690" t="n">
-        <v>7.915757179260254</v>
+        <v>7.915757656097412</v>
       </c>
       <c r="C690" t="n">
-        <v>8.119179315074533</v>
+        <v>8.119179804165633</v>
       </c>
       <c r="D690" t="n">
-        <v>7.791935816431346</v>
+        <v>7.791936285809632</v>
       </c>
       <c r="E690" t="n">
-        <v>8.092645442922818</v>
+        <v>8.092645930415545</v>
       </c>
       <c r="F690" t="n">
         <v>6975500</v>
@@ -14232,16 +14232,16 @@
         <v>45237</v>
       </c>
       <c r="B691" t="n">
-        <v>8.357977867126465</v>
+        <v>8.357978820800781</v>
       </c>
       <c r="C691" t="n">
-        <v>8.375667114395791</v>
+        <v>8.37566807008851</v>
       </c>
       <c r="D691" t="n">
-        <v>7.845001504892315</v>
+        <v>7.845002400034246</v>
       </c>
       <c r="E691" t="n">
-        <v>7.871534532326568</v>
+        <v>7.871535430496009</v>
       </c>
       <c r="F691" t="n">
         <v>8029000</v>
@@ -14252,16 +14252,16 @@
         <v>45238</v>
       </c>
       <c r="B692" t="n">
-        <v>8.101489067077637</v>
+        <v>8.101490020751953</v>
       </c>
       <c r="C692" t="n">
-        <v>8.649843038487949</v>
+        <v>8.649844056712263</v>
       </c>
       <c r="D692" t="n">
-        <v>8.013045367897073</v>
+        <v>8.013046311160156</v>
       </c>
       <c r="E692" t="n">
-        <v>8.357977228599713</v>
+        <v>8.357978212466772</v>
       </c>
       <c r="F692" t="n">
         <v>19964500</v>
@@ -14272,16 +14272,16 @@
         <v>45239</v>
       </c>
       <c r="B693" t="n">
-        <v>7.959979057312012</v>
+        <v>7.95997953414917</v>
       </c>
       <c r="C693" t="n">
-        <v>8.189934210289316</v>
+        <v>8.189934700901784</v>
       </c>
       <c r="D693" t="n">
-        <v>7.774246178902609</v>
+        <v>7.774246644613565</v>
       </c>
       <c r="E693" t="n">
-        <v>8.189934210289316</v>
+        <v>8.189934700901784</v>
       </c>
       <c r="F693" t="n">
         <v>11094800</v>
@@ -14292,16 +14292,16 @@
         <v>45240</v>
       </c>
       <c r="B694" t="n">
-        <v>7.933446407318115</v>
+        <v>7.933446884155273</v>
       </c>
       <c r="C694" t="n">
-        <v>8.13686769914869</v>
+        <v>8.136868188212418</v>
       </c>
       <c r="D694" t="n">
-        <v>7.933446407318114</v>
+        <v>7.933446884155273</v>
       </c>
       <c r="E694" t="n">
-        <v>8.039579365247516</v>
+        <v>8.03957984846376</v>
       </c>
       <c r="F694" t="n">
         <v>6302800</v>
@@ -14312,16 +14312,16 @@
         <v>45243</v>
       </c>
       <c r="B695" t="n">
-        <v>7.853846073150635</v>
+        <v>7.853847026824951</v>
       </c>
       <c r="C695" t="n">
-        <v>7.933445998361882</v>
+        <v>7.933446961701833</v>
       </c>
       <c r="D695" t="n">
-        <v>7.721179249975314</v>
+        <v>7.721180187540206</v>
       </c>
       <c r="E695" t="n">
-        <v>7.915756751217281</v>
+        <v>7.915757712409268</v>
       </c>
       <c r="F695" t="n">
         <v>4933800</v>
@@ -14332,16 +14332,16 @@
         <v>45244</v>
       </c>
       <c r="B696" t="n">
-        <v>8.508333206176758</v>
+        <v>8.508334159851074</v>
       </c>
       <c r="C696" t="n">
-        <v>8.587933132989026</v>
+        <v>8.587934095585465</v>
       </c>
       <c r="D696" t="n">
-        <v>7.898068506398949</v>
+        <v>7.898069391670471</v>
       </c>
       <c r="E696" t="n">
-        <v>7.915756910429595</v>
+        <v>7.915757797683757</v>
       </c>
       <c r="F696" t="n">
         <v>17983500</v>
@@ -14352,16 +14352,16 @@
         <v>45246</v>
       </c>
       <c r="B697" t="n">
-        <v>8.729443550109863</v>
+        <v>8.72944450378418</v>
       </c>
       <c r="C697" t="n">
-        <v>8.835576502405061</v>
+        <v>8.835577467674192</v>
       </c>
       <c r="D697" t="n">
-        <v>8.517177645519467</v>
+        <v>8.517178576004156</v>
       </c>
       <c r="E697" t="n">
-        <v>8.517177645519467</v>
+        <v>8.517178576004156</v>
       </c>
       <c r="F697" t="n">
         <v>10830700</v>
@@ -14372,16 +14372,16 @@
         <v>45247</v>
       </c>
       <c r="B698" t="n">
-        <v>8.640999794006348</v>
+        <v>8.641000747680664</v>
       </c>
       <c r="C698" t="n">
-        <v>8.826731826826038</v>
+        <v>8.826732800998892</v>
       </c>
       <c r="D698" t="n">
-        <v>8.623310546993203</v>
+        <v>8.623311498715223</v>
       </c>
       <c r="E698" t="n">
-        <v>8.747132745676051</v>
+        <v>8.747133711063858</v>
       </c>
       <c r="F698" t="n">
         <v>7834100</v>
@@ -14472,16 +14472,16 @@
         <v>45254</v>
       </c>
       <c r="B703" t="n">
-        <v>8.366822242736816</v>
+        <v>8.366823196411133</v>
       </c>
       <c r="C703" t="n">
-        <v>8.526022089562519</v>
+        <v>8.526023061382888</v>
       </c>
       <c r="D703" t="n">
-        <v>8.29606694269644</v>
+        <v>8.296067888305865</v>
       </c>
       <c r="E703" t="n">
-        <v>8.517177466190045</v>
+        <v>8.517178437002279</v>
       </c>
       <c r="F703" t="n">
         <v>8295700</v>
@@ -14492,16 +14492,16 @@
         <v>45257</v>
       </c>
       <c r="B704" t="n">
-        <v>8.092645645141602</v>
+        <v>8.092646598815918</v>
       </c>
       <c r="C704" t="n">
-        <v>8.446423024776681</v>
+        <v>8.446424020141739</v>
       </c>
       <c r="D704" t="n">
-        <v>8.074957240068235</v>
+        <v>8.074958191658068</v>
       </c>
       <c r="E704" t="n">
-        <v>8.411045371160153</v>
+        <v>8.411046362356148</v>
       </c>
       <c r="F704" t="n">
         <v>5901700</v>
@@ -14512,16 +14512,16 @@
         <v>45258</v>
       </c>
       <c r="B705" t="n">
-        <v>8.057267189025879</v>
+        <v>8.057268142700195</v>
       </c>
       <c r="C705" t="n">
-        <v>8.313755363067084</v>
+        <v>8.313756347099856</v>
       </c>
       <c r="D705" t="n">
-        <v>8.021889538932944</v>
+        <v>8.02189048841989</v>
       </c>
       <c r="E705" t="n">
-        <v>8.092644839118813</v>
+        <v>8.0926457969805</v>
       </c>
       <c r="F705" t="n">
         <v>5106400</v>
@@ -14532,16 +14532,16 @@
         <v>45259</v>
       </c>
       <c r="B706" t="n">
-        <v>8.25184440612793</v>
+        <v>8.251845359802246</v>
       </c>
       <c r="C706" t="n">
-        <v>8.349132729713206</v>
+        <v>8.349133694631236</v>
       </c>
       <c r="D706" t="n">
-        <v>8.128022213271473</v>
+        <v>8.128023152635528</v>
       </c>
       <c r="E706" t="n">
-        <v>8.14571145945226</v>
+        <v>8.145712400860679</v>
       </c>
       <c r="F706" t="n">
         <v>4175000</v>
@@ -14612,16 +14612,16 @@
         <v>45265</v>
       </c>
       <c r="B710" t="n">
-        <v>8.33144474029541</v>
+        <v>8.331445693969727</v>
       </c>
       <c r="C710" t="n">
-        <v>8.472955342882807</v>
+        <v>8.472956312755398</v>
       </c>
       <c r="D710" t="n">
-        <v>8.251844815472568</v>
+        <v>8.251845760035332</v>
       </c>
       <c r="E710" t="n">
-        <v>8.251844815472568</v>
+        <v>8.251845760035332</v>
       </c>
       <c r="F710" t="n">
         <v>4182300</v>
@@ -14652,16 +14652,16 @@
         <v>45267</v>
       </c>
       <c r="B712" t="n">
-        <v>8.340289115905762</v>
+        <v>8.340290069580078</v>
       </c>
       <c r="C712" t="n">
-        <v>8.357977518968529</v>
+        <v>8.357978474665433</v>
       </c>
       <c r="D712" t="n">
-        <v>8.163400024459897</v>
+        <v>8.163400957907747</v>
       </c>
       <c r="E712" t="n">
-        <v>8.242999946916596</v>
+        <v>8.243000889466337</v>
       </c>
       <c r="F712" t="n">
         <v>3161600</v>
@@ -14712,16 +14712,16 @@
         <v>45272</v>
       </c>
       <c r="B715" t="n">
-        <v>8.08380126953125</v>
+        <v>8.083802223205566</v>
       </c>
       <c r="C715" t="n">
-        <v>8.3579778540179</v>
+        <v>8.357978840037788</v>
       </c>
       <c r="D715" t="n">
-        <v>8.066112022289667</v>
+        <v>8.066112973877122</v>
       </c>
       <c r="E715" t="n">
-        <v>8.181089598950749</v>
+        <v>8.18109056410251</v>
       </c>
       <c r="F715" t="n">
         <v>4001400</v>
@@ -14732,16 +14732,16 @@
         <v>45273</v>
       </c>
       <c r="B716" t="n">
-        <v>8.658688545227051</v>
+        <v>8.658689498901367</v>
       </c>
       <c r="C716" t="n">
-        <v>8.71175544492759</v>
+        <v>8.711756404446733</v>
       </c>
       <c r="D716" t="n">
-        <v>8.101489893985299</v>
+        <v>8.101490786289347</v>
       </c>
       <c r="E716" t="n">
-        <v>8.110334517847015</v>
+        <v>8.110335411125217</v>
       </c>
       <c r="F716" t="n">
         <v>4810200</v>
@@ -14792,16 +14792,16 @@
         <v>45278</v>
       </c>
       <c r="B719" t="n">
-        <v>8.835576057434082</v>
+        <v>8.835577964782715</v>
       </c>
       <c r="C719" t="n">
-        <v>8.977086653367691</v>
+        <v>8.977088591264421</v>
       </c>
       <c r="D719" t="n">
-        <v>8.800198408450679</v>
+        <v>8.800200308162289</v>
       </c>
       <c r="E719" t="n">
-        <v>8.809043031563952</v>
+        <v>8.809044933184863</v>
       </c>
       <c r="F719" t="n">
         <v>3928300</v>
@@ -14812,16 +14812,16 @@
         <v>45279</v>
       </c>
       <c r="B720" t="n">
-        <v>8.879798889160156</v>
+        <v>8.879799842834473</v>
       </c>
       <c r="C720" t="n">
-        <v>8.941709567915471</v>
+        <v>8.941710528238881</v>
       </c>
       <c r="D720" t="n">
-        <v>8.817888210404842</v>
+        <v>8.817889157430063</v>
       </c>
       <c r="E720" t="n">
-        <v>8.932865787714524</v>
+        <v>8.932866747088129</v>
       </c>
       <c r="F720" t="n">
         <v>3267000</v>
@@ -14832,16 +14832,16 @@
         <v>45280</v>
       </c>
       <c r="B721" t="n">
-        <v>8.67693042755127</v>
+        <v>8.676929473876953</v>
       </c>
       <c r="C721" t="n">
-        <v>9.033141569207338</v>
+        <v>9.033140576382147</v>
       </c>
       <c r="D721" t="n">
-        <v>8.622128378431482</v>
+        <v>8.622127430780413</v>
       </c>
       <c r="E721" t="n">
-        <v>8.950938931052166</v>
+        <v>8.950937947261799</v>
       </c>
       <c r="F721" t="n">
         <v>6032100</v>
@@ -14872,16 +14872,16 @@
         <v>45282</v>
       </c>
       <c r="B723" t="n">
-        <v>8.887001991271973</v>
+        <v>8.887002944946289</v>
       </c>
       <c r="C723" t="n">
-        <v>9.005739024186209</v>
+        <v>9.005739990602331</v>
       </c>
       <c r="D723" t="n">
-        <v>8.731731424744495</v>
+        <v>8.731732361756549</v>
       </c>
       <c r="E723" t="n">
-        <v>8.950937852717432</v>
+        <v>8.95093881325278</v>
       </c>
       <c r="F723" t="n">
         <v>62444400</v>
@@ -14932,16 +14932,16 @@
         <v>45288</v>
       </c>
       <c r="B726" t="n">
-        <v>9.197545051574707</v>
+        <v>9.197546005249023</v>
       </c>
       <c r="C726" t="n">
-        <v>9.334549725102434</v>
+        <v>9.33455069298248</v>
       </c>
       <c r="D726" t="n">
-        <v>8.969204800077428</v>
+        <v>8.96920573007562</v>
       </c>
       <c r="E726" t="n">
-        <v>9.097075654493521</v>
+        <v>9.097076597750373</v>
       </c>
       <c r="F726" t="n">
         <v>16865200</v>
@@ -15092,16 +15092,16 @@
         <v>45302</v>
       </c>
       <c r="B734" t="n">
-        <v>8.67693042755127</v>
+        <v>8.676929473876953</v>
       </c>
       <c r="C734" t="n">
-        <v>8.841335703861612</v>
+        <v>8.841334732117646</v>
       </c>
       <c r="D734" t="n">
-        <v>8.640396018487751</v>
+        <v>8.640395068828902</v>
       </c>
       <c r="E734" t="n">
-        <v>8.640396018487751</v>
+        <v>8.640395068828902</v>
       </c>
       <c r="F734" t="n">
         <v>4234100</v>
@@ -15112,16 +15112,16 @@
         <v>45303</v>
       </c>
       <c r="B735" t="n">
-        <v>8.67693042755127</v>
+        <v>8.676929473876953</v>
       </c>
       <c r="C735" t="n">
-        <v>8.969205700059415</v>
+        <v>8.969204714261362</v>
       </c>
       <c r="D735" t="n">
-        <v>8.640396018487751</v>
+        <v>8.640395068828902</v>
       </c>
       <c r="E735" t="n">
-        <v>8.640396018487751</v>
+        <v>8.640395068828902</v>
       </c>
       <c r="F735" t="n">
         <v>4898500</v>
@@ -15132,16 +15132,16 @@
         <v>45306</v>
       </c>
       <c r="B736" t="n">
-        <v>8.704330444335938</v>
+        <v>8.704331398010254</v>
       </c>
       <c r="C736" t="n">
-        <v>8.759132489852862</v>
+        <v>8.759133449531467</v>
       </c>
       <c r="D736" t="n">
-        <v>8.585593404923404</v>
+        <v>8.585594345588509</v>
       </c>
       <c r="E736" t="n">
-        <v>8.585593404923404</v>
+        <v>8.585594345588509</v>
       </c>
       <c r="F736" t="n">
         <v>2435000</v>
@@ -15212,16 +15212,16 @@
         <v>45310</v>
       </c>
       <c r="B740" t="n">
-        <v>7.763568878173828</v>
+        <v>7.763569355010986</v>
       </c>
       <c r="C740" t="n">
-        <v>7.845771511545856</v>
+        <v>7.845771993431888</v>
       </c>
       <c r="D740" t="n">
-        <v>7.498694210113386</v>
+        <v>7.498694670681984</v>
       </c>
       <c r="E740" t="n">
-        <v>7.690500064298463</v>
+        <v>7.690500536647746</v>
       </c>
       <c r="F740" t="n">
         <v>7953500</v>
@@ -15252,16 +15252,16 @@
         <v>45314</v>
       </c>
       <c r="B742" t="n">
-        <v>7.608297348022461</v>
+        <v>7.608297824859619</v>
       </c>
       <c r="C742" t="n">
-        <v>7.727034387038351</v>
+        <v>7.727034871317152</v>
       </c>
       <c r="D742" t="n">
-        <v>7.443892083069849</v>
+        <v>7.443892549603185</v>
       </c>
       <c r="E742" t="n">
-        <v>7.443892083069849</v>
+        <v>7.443892549603185</v>
       </c>
       <c r="F742" t="n">
         <v>3836100</v>
@@ -15272,16 +15272,16 @@
         <v>45315</v>
       </c>
       <c r="B743" t="n">
-        <v>7.489560604095459</v>
+        <v>7.489560127258301</v>
       </c>
       <c r="C743" t="n">
-        <v>7.727034691483726</v>
+        <v>7.727034199527327</v>
       </c>
       <c r="D743" t="n">
-        <v>7.416491788137376</v>
+        <v>7.416491315952283</v>
       </c>
       <c r="E743" t="n">
-        <v>7.699634103261693</v>
+        <v>7.699633613049805</v>
       </c>
       <c r="F743" t="n">
         <v>5274600</v>
@@ -15312,16 +15312,16 @@
         <v>45317</v>
       </c>
       <c r="B745" t="n">
-        <v>7.471293926239014</v>
+        <v>7.471293449401855</v>
       </c>
       <c r="C745" t="n">
-        <v>7.553496562951024</v>
+        <v>7.553496080867482</v>
       </c>
       <c r="D745" t="n">
-        <v>7.407358058213559</v>
+        <v>7.407357585456952</v>
       </c>
       <c r="E745" t="n">
-        <v>7.489560694925569</v>
+        <v>7.489560216922579</v>
       </c>
       <c r="F745" t="n">
         <v>5075500</v>
@@ -15452,16 +15452,16 @@
         <v>45328</v>
       </c>
       <c r="B752" t="n">
-        <v>7.261220455169678</v>
+        <v>7.26121997833252</v>
       </c>
       <c r="C752" t="n">
-        <v>7.471293957770166</v>
+        <v>7.47129346713769</v>
       </c>
       <c r="D752" t="n">
-        <v>7.087682232194499</v>
+        <v>7.087681766753425</v>
       </c>
       <c r="E752" t="n">
-        <v>7.087682232194499</v>
+        <v>7.087681766753425</v>
       </c>
       <c r="F752" t="n">
         <v>7301900</v>
@@ -15512,16 +15512,16 @@
         <v>45331</v>
       </c>
       <c r="B755" t="n">
-        <v>7.261220455169678</v>
+        <v>7.26121997833252</v>
       </c>
       <c r="C755" t="n">
-        <v>7.471293957770166</v>
+        <v>7.47129346713769</v>
       </c>
       <c r="D755" t="n">
-        <v>7.206418842305226</v>
+        <v>7.206418369066836</v>
       </c>
       <c r="E755" t="n">
-        <v>7.352556912134935</v>
+        <v>7.352556429299803</v>
       </c>
       <c r="F755" t="n">
         <v>5959300</v>
@@ -15552,16 +15552,16 @@
         <v>45337</v>
       </c>
       <c r="B757" t="n">
-        <v>7.261220455169678</v>
+        <v>7.26121997833252</v>
       </c>
       <c r="C757" t="n">
-        <v>7.361690732041263</v>
+        <v>7.361690248606321</v>
       </c>
       <c r="D757" t="n">
-        <v>7.124216640770801</v>
+        <v>7.124216172930548</v>
       </c>
       <c r="E757" t="n">
-        <v>7.270354275076005</v>
+        <v>7.270353797639038</v>
       </c>
       <c r="F757" t="n">
         <v>6551500</v>
@@ -15592,16 +15592,16 @@
         <v>45341</v>
       </c>
       <c r="B759" t="n">
-        <v>7.398224830627441</v>
+        <v>7.3982253074646</v>
       </c>
       <c r="C759" t="n">
-        <v>7.526094819762161</v>
+        <v>7.526095304840912</v>
       </c>
       <c r="D759" t="n">
-        <v>7.261220150920135</v>
+        <v>7.261220618926942</v>
       </c>
       <c r="E759" t="n">
-        <v>7.507828051763903</v>
+        <v>7.507828535665309</v>
       </c>
       <c r="F759" t="n">
         <v>5437200</v>
@@ -15712,16 +15712,16 @@
         <v>45349</v>
       </c>
       <c r="B765" t="n">
-        <v>8.38465404510498</v>
+        <v>8.384654998779297</v>
       </c>
       <c r="C765" t="n">
-        <v>8.457722853559364</v>
+        <v>8.457723815544558</v>
       </c>
       <c r="D765" t="n">
-        <v>8.101511759057571</v>
+        <v>8.101512680527156</v>
       </c>
       <c r="E765" t="n">
-        <v>8.101511759057571</v>
+        <v>8.101512680527156</v>
       </c>
       <c r="F765" t="n">
         <v>7036800</v>
@@ -15772,16 +15772,16 @@
         <v>45352</v>
       </c>
       <c r="B768" t="n">
-        <v>7.991909503936768</v>
+        <v>7.991909027099609</v>
       </c>
       <c r="C768" t="n">
-        <v>8.128913318441795</v>
+        <v>8.128912833430306</v>
       </c>
       <c r="D768" t="n">
-        <v>7.946241275418755</v>
+        <v>7.946240801306391</v>
       </c>
       <c r="E768" t="n">
-        <v>7.973641864109958</v>
+        <v>7.973641388362739</v>
       </c>
       <c r="F768" t="n">
         <v>3021100</v>
@@ -15852,16 +15852,16 @@
         <v>45358</v>
       </c>
       <c r="B772" t="n">
-        <v>7.635697841644287</v>
+        <v>7.635698318481445</v>
       </c>
       <c r="C772" t="n">
-        <v>7.745301059920641</v>
+        <v>7.745301543602346</v>
       </c>
       <c r="D772" t="n">
-        <v>7.535228442653199</v>
+        <v>7.535228913216204</v>
       </c>
       <c r="E772" t="n">
-        <v>7.71790047311379</v>
+        <v>7.717900955084372</v>
       </c>
       <c r="F772" t="n">
         <v>3046600</v>
@@ -15872,16 +15872,16 @@
         <v>45359</v>
       </c>
       <c r="B773" t="n">
-        <v>7.489560604095459</v>
+        <v>7.489560127258301</v>
       </c>
       <c r="C773" t="n">
-        <v>7.74530145994875</v>
+        <v>7.745300966829362</v>
       </c>
       <c r="D773" t="n">
-        <v>7.471293835630435</v>
+        <v>7.471293359956266</v>
       </c>
       <c r="E773" t="n">
-        <v>7.590030879324569</v>
+        <v>7.590030396090778</v>
       </c>
       <c r="F773" t="n">
         <v>5969600</v>
@@ -15892,16 +15892,16 @@
         <v>45362</v>
       </c>
       <c r="B774" t="n">
-        <v>7.681366443634033</v>
+        <v>7.681366920471191</v>
       </c>
       <c r="C774" t="n">
-        <v>7.699634083100217</v>
+        <v>7.699634561071378</v>
       </c>
       <c r="D774" t="n">
-        <v>7.434759408183492</v>
+        <v>7.434759869711995</v>
       </c>
       <c r="E774" t="n">
-        <v>7.462159996333776</v>
+        <v>7.462160459563228</v>
       </c>
       <c r="F774" t="n">
         <v>4043700</v>
@@ -15912,16 +15912,16 @@
         <v>45363</v>
       </c>
       <c r="B775" t="n">
-        <v>7.873171806335449</v>
+        <v>7.873172283172607</v>
       </c>
       <c r="C775" t="n">
-        <v>7.982775023074468</v>
+        <v>7.982775506549723</v>
       </c>
       <c r="D775" t="n">
-        <v>7.717900364859606</v>
+        <v>7.717900832292778</v>
       </c>
       <c r="E775" t="n">
-        <v>7.727034184016758</v>
+        <v>7.727034652003119</v>
       </c>
       <c r="F775" t="n">
         <v>6470300</v>
@@ -15952,16 +15952,16 @@
         <v>45365</v>
       </c>
       <c r="B777" t="n">
-        <v>7.854905605316162</v>
+        <v>7.85490608215332</v>
       </c>
       <c r="C777" t="n">
-        <v>8.101512642994178</v>
+        <v>8.101513134801777</v>
       </c>
       <c r="D777" t="n">
-        <v>7.781836788889417</v>
+        <v>7.781837261290884</v>
       </c>
       <c r="E777" t="n">
-        <v>8.055844414965213</v>
+        <v>8.055844904000491</v>
       </c>
       <c r="F777" t="n">
         <v>5804500</v>
@@ -15992,16 +15992,16 @@
         <v>45369</v>
       </c>
       <c r="B779" t="n">
-        <v>7.653965950012207</v>
+        <v>7.653965473175049</v>
       </c>
       <c r="C779" t="n">
-        <v>7.836637991685135</v>
+        <v>7.836637503467626</v>
       </c>
       <c r="D779" t="n">
-        <v>7.553496544854347</v>
+        <v>7.553496074276368</v>
       </c>
       <c r="E779" t="n">
-        <v>7.626565361523518</v>
+        <v>7.6265648863934</v>
       </c>
       <c r="F779" t="n">
         <v>6064700</v>
@@ -16012,16 +16012,16 @@
         <v>45370</v>
       </c>
       <c r="B780" t="n">
-        <v>7.571763515472412</v>
+        <v>7.571763038635254</v>
       </c>
       <c r="C780" t="n">
-        <v>7.882306430124562</v>
+        <v>7.882305933730743</v>
       </c>
       <c r="D780" t="n">
-        <v>7.297755010129397</v>
+        <v>7.297754550548118</v>
       </c>
       <c r="E780" t="n">
-        <v>7.580897335561953</v>
+        <v>7.580896858149585</v>
       </c>
       <c r="F780" t="n">
         <v>12953700</v>
@@ -16032,16 +16032,16 @@
         <v>45371</v>
       </c>
       <c r="B781" t="n">
-        <v>8.11064624786377</v>
+        <v>8.110647201538086</v>
       </c>
       <c r="C781" t="n">
-        <v>8.183715062354066</v>
+        <v>8.183716024620034</v>
       </c>
       <c r="D781" t="n">
-        <v>7.535228680465948</v>
+        <v>7.535229566480925</v>
       </c>
       <c r="E781" t="n">
-        <v>7.608297494956244</v>
+        <v>7.608298389562875</v>
       </c>
       <c r="F781" t="n">
         <v>10775600</v>
@@ -16052,16 +16052,16 @@
         <v>45372</v>
       </c>
       <c r="B782" t="n">
-        <v>8.147180557250977</v>
+        <v>8.147181510925293</v>
       </c>
       <c r="C782" t="n">
-        <v>8.229383190327447</v>
+        <v>8.229384153624055</v>
       </c>
       <c r="D782" t="n">
-        <v>8.010176749489503</v>
+        <v>8.010177687126737</v>
       </c>
       <c r="E782" t="n">
-        <v>8.083245563102151</v>
+        <v>8.083246509292509</v>
       </c>
       <c r="F782" t="n">
         <v>10797200</v>
@@ -16092,16 +16092,16 @@
         <v>45376</v>
       </c>
       <c r="B784" t="n">
-        <v>7.727034568786621</v>
+        <v>7.727035045623779</v>
       </c>
       <c r="C784" t="n">
-        <v>7.900572786169216</v>
+        <v>7.900573273715461</v>
       </c>
       <c r="D784" t="n">
-        <v>7.663099573600767</v>
+        <v>7.663100046492482</v>
       </c>
       <c r="E784" t="n">
-        <v>7.809237203196422</v>
+        <v>7.809237685106326</v>
       </c>
       <c r="F784" t="n">
         <v>6131300</v>
@@ -16112,16 +16112,16 @@
         <v>45377</v>
       </c>
       <c r="B785" t="n">
-        <v>7.891439914703369</v>
+        <v>7.891440391540527</v>
       </c>
       <c r="C785" t="n">
-        <v>8.019309906324331</v>
+        <v>8.019310390887984</v>
       </c>
       <c r="D785" t="n">
-        <v>7.672232597119311</v>
+        <v>7.672233060710954</v>
       </c>
       <c r="E785" t="n">
-        <v>7.727034644277572</v>
+        <v>7.727035111180608</v>
       </c>
       <c r="F785" t="n">
         <v>16047100</v>
@@ -16232,16 +16232,16 @@
         <v>45386</v>
       </c>
       <c r="B791" t="n">
-        <v>7.389091491699219</v>
+        <v>7.389091014862061</v>
       </c>
       <c r="C791" t="n">
-        <v>7.608297948229594</v>
+        <v>7.608297457246477</v>
       </c>
       <c r="D791" t="n">
-        <v>7.35255708227749</v>
+        <v>7.352556607797991</v>
       </c>
       <c r="E791" t="n">
-        <v>7.379957671581529</v>
+        <v>7.3799571953338</v>
       </c>
       <c r="F791" t="n">
         <v>5937900</v>
@@ -16272,16 +16272,16 @@
         <v>45390</v>
       </c>
       <c r="B793" t="n">
-        <v>7.507828235626221</v>
+        <v>7.507827758789062</v>
       </c>
       <c r="C793" t="n">
-        <v>7.608297639699505</v>
+        <v>7.608297156481334</v>
       </c>
       <c r="D793" t="n">
-        <v>7.316022376177957</v>
+        <v>7.316021911522771</v>
       </c>
       <c r="E793" t="n">
-        <v>7.343422964370853</v>
+        <v>7.343422497975402</v>
       </c>
       <c r="F793" t="n">
         <v>6349600</v>
@@ -16352,16 +16352,16 @@
         <v>45394</v>
       </c>
       <c r="B797" t="n">
-        <v>7.398224830627441</v>
+        <v>7.3982253074646</v>
       </c>
       <c r="C797" t="n">
-        <v>7.608297453376751</v>
+        <v>7.608297943753701</v>
       </c>
       <c r="D797" t="n">
-        <v>7.343422784534725</v>
+        <v>7.34342325783973</v>
       </c>
       <c r="E797" t="n">
-        <v>7.507828051763903</v>
+        <v>7.507828535665309</v>
       </c>
       <c r="F797" t="n">
         <v>9274900</v>
@@ -16372,16 +16372,16 @@
         <v>45397</v>
       </c>
       <c r="B798" t="n">
-        <v>6.923276424407959</v>
+        <v>6.923276901245117</v>
       </c>
       <c r="C798" t="n">
-        <v>7.434758976098444</v>
+        <v>7.434759488163705</v>
       </c>
       <c r="D798" t="n">
-        <v>6.850207612887738</v>
+        <v>6.850208084692319</v>
       </c>
       <c r="E798" t="n">
-        <v>7.416491337693918</v>
+        <v>7.416491848501004</v>
       </c>
       <c r="F798" t="n">
         <v>10745000</v>
@@ -16452,16 +16452,16 @@
         <v>45401</v>
       </c>
       <c r="B802" t="n">
-        <v>6.749738216400146</v>
+        <v>6.749737739562988</v>
       </c>
       <c r="C802" t="n">
-        <v>6.877609080365956</v>
+        <v>6.877608594495325</v>
       </c>
       <c r="D802" t="n">
-        <v>6.704070424004785</v>
+        <v>6.704069950393841</v>
       </c>
       <c r="E802" t="n">
-        <v>6.777139240256963</v>
+        <v>6.777138761484052</v>
       </c>
       <c r="F802" t="n">
         <v>8757100</v>
@@ -16592,16 +16592,16 @@
         <v>45412</v>
       </c>
       <c r="B809" t="n">
-        <v>6.493997573852539</v>
+        <v>6.493997097015381</v>
       </c>
       <c r="C809" t="n">
-        <v>6.786272848507823</v>
+        <v>6.786272350209661</v>
       </c>
       <c r="D809" t="n">
-        <v>6.475730369186584</v>
+        <v>6.475729893690739</v>
       </c>
       <c r="E809" t="n">
-        <v>6.749738439175912</v>
+        <v>6.749737943560375</v>
       </c>
       <c r="F809" t="n">
         <v>8369300</v>
@@ -16712,16 +16712,16 @@
         <v>45421</v>
       </c>
       <c r="B815" t="n">
-        <v>7.398224830627441</v>
+        <v>7.3982253074646</v>
       </c>
       <c r="C815" t="n">
-        <v>7.434759237672929</v>
+        <v>7.434759716864836</v>
       </c>
       <c r="D815" t="n">
-        <v>7.233819563398263</v>
+        <v>7.233820029639022</v>
       </c>
       <c r="E815" t="n">
-        <v>7.316022197012852</v>
+        <v>7.316022668551811</v>
       </c>
       <c r="F815" t="n">
         <v>6908300</v>
@@ -16792,16 +16792,16 @@
         <v>45427</v>
       </c>
       <c r="B819" t="n">
-        <v>7.37995719909668</v>
+        <v>7.379957675933838</v>
       </c>
       <c r="C819" t="n">
-        <v>7.453026013262074</v>
+        <v>7.453026494820389</v>
       </c>
       <c r="D819" t="n">
-        <v>7.224685751232972</v>
+        <v>7.22468621803766</v>
       </c>
       <c r="E819" t="n">
-        <v>7.252086774307239</v>
+        <v>7.252087242882374</v>
       </c>
       <c r="F819" t="n">
         <v>4894000</v>
@@ -16932,16 +16932,16 @@
         <v>45436</v>
       </c>
       <c r="B826" t="n">
-        <v>7.453025817871094</v>
+        <v>7.453026294708252</v>
       </c>
       <c r="C826" t="n">
-        <v>7.644831667789053</v>
+        <v>7.644832156897759</v>
       </c>
       <c r="D826" t="n">
-        <v>7.453025817871094</v>
+        <v>7.453026294708252</v>
       </c>
       <c r="E826" t="n">
-        <v>7.635697848495591</v>
+        <v>7.635698337019924</v>
       </c>
       <c r="F826" t="n">
         <v>5755300</v>
@@ -16952,16 +16952,16 @@
         <v>45439</v>
       </c>
       <c r="B827" t="n">
-        <v>7.453025817871094</v>
+        <v>7.453026294708252</v>
       </c>
       <c r="C827" t="n">
-        <v>7.489560223995992</v>
+        <v>7.489560703170587</v>
       </c>
       <c r="D827" t="n">
-        <v>7.343422599496395</v>
+        <v>7.34342306932125</v>
       </c>
       <c r="E827" t="n">
-        <v>7.489560223995992</v>
+        <v>7.489560703170587</v>
       </c>
       <c r="F827" t="n">
         <v>2664100</v>
@@ -17032,16 +17032,16 @@
         <v>45446</v>
       </c>
       <c r="B831" t="n">
-        <v>7.398224830627441</v>
+        <v>7.3982253074646</v>
       </c>
       <c r="C831" t="n">
-        <v>7.644831860422237</v>
+        <v>7.644832353153937</v>
       </c>
       <c r="D831" t="n">
-        <v>7.370823372056597</v>
+        <v>7.370823847127651</v>
       </c>
       <c r="E831" t="n">
-        <v>7.443892186147571</v>
+        <v>7.443892665928123</v>
       </c>
       <c r="F831" t="n">
         <v>4697400</v>
@@ -17052,16 +17052,16 @@
         <v>45447</v>
       </c>
       <c r="B832" t="n">
-        <v>7.133349418640137</v>
+        <v>7.133349895477295</v>
       </c>
       <c r="C832" t="n">
-        <v>7.389090692454367</v>
+        <v>7.389091186386852</v>
       </c>
       <c r="D832" t="n">
-        <v>7.005478999495256</v>
+        <v>7.005479467784764</v>
       </c>
       <c r="E832" t="n">
-        <v>7.389090692454367</v>
+        <v>7.389091186386852</v>
       </c>
       <c r="F832" t="n">
         <v>9916900</v>
@@ -17072,16 +17072,16 @@
         <v>45448</v>
       </c>
       <c r="B833" t="n">
-        <v>6.950677394866943</v>
+        <v>6.950677871704102</v>
       </c>
       <c r="C833" t="n">
-        <v>7.233819255167113</v>
+        <v>7.233819751428645</v>
       </c>
       <c r="D833" t="n">
-        <v>6.850207562010604</v>
+        <v>6.850208031955233</v>
       </c>
       <c r="E833" t="n">
-        <v>7.096815016822007</v>
+        <v>7.096815503684641</v>
       </c>
       <c r="F833" t="n">
         <v>9111500</v>
@@ -17092,16 +17092,16 @@
         <v>45449</v>
       </c>
       <c r="B834" t="n">
-        <v>7.069414615631104</v>
+        <v>7.069414138793945</v>
       </c>
       <c r="C834" t="n">
-        <v>7.133350048612147</v>
+        <v>7.133349567462498</v>
       </c>
       <c r="D834" t="n">
-        <v>6.93241080078166</v>
+        <v>6.932410333185509</v>
       </c>
       <c r="E834" t="n">
-        <v>6.978078593889973</v>
+        <v>6.978078123213496</v>
       </c>
       <c r="F834" t="n">
         <v>8384200</v>
@@ -17132,16 +17132,16 @@
         <v>45453</v>
       </c>
       <c r="B836" t="n">
-        <v>6.923276424407959</v>
+        <v>6.923276901245117</v>
       </c>
       <c r="C836" t="n">
-        <v>6.987211852250387</v>
+        <v>6.987212333491066</v>
       </c>
       <c r="D836" t="n">
-        <v>6.78627218504531</v>
+        <v>6.786272652446371</v>
       </c>
       <c r="E836" t="n">
-        <v>6.941543627288014</v>
+        <v>6.941544105383317</v>
       </c>
       <c r="F836" t="n">
         <v>7457900</v>
@@ -17232,16 +17232,16 @@
         <v>45460</v>
       </c>
       <c r="B841" t="n">
-        <v>6.448328971862793</v>
+        <v>6.448329448699951</v>
       </c>
       <c r="C841" t="n">
-        <v>6.658402031146226</v>
+        <v>6.65840252351774</v>
       </c>
       <c r="D841" t="n">
-        <v>6.448328971862793</v>
+        <v>6.448329448699951</v>
       </c>
       <c r="E841" t="n">
-        <v>6.640134827535688</v>
+        <v>6.64013531855639</v>
       </c>
       <c r="F841" t="n">
         <v>3992100</v>
@@ -17252,16 +17252,16 @@
         <v>45461</v>
       </c>
       <c r="B842" t="n">
-        <v>6.493997573852539</v>
+        <v>6.493997097015381</v>
       </c>
       <c r="C842" t="n">
-        <v>6.557932572421126</v>
+        <v>6.557932090889389</v>
       </c>
       <c r="D842" t="n">
-        <v>6.402661550522763</v>
+        <v>6.402661080392169</v>
       </c>
       <c r="E842" t="n">
-        <v>6.448329344425394</v>
+        <v>6.448328870941534</v>
       </c>
       <c r="F842" t="n">
         <v>3102800</v>
@@ -17312,16 +17312,16 @@
         <v>45464</v>
       </c>
       <c r="B845" t="n">
-        <v>6.850207805633545</v>
+        <v>6.850208282470703</v>
       </c>
       <c r="C845" t="n">
-        <v>6.932410438668982</v>
+        <v>6.932410921228196</v>
       </c>
       <c r="D845" t="n">
-        <v>6.585333138657673</v>
+        <v>6.58533359705713</v>
       </c>
       <c r="E845" t="n">
-        <v>6.694936359021934</v>
+        <v>6.694936825050778</v>
       </c>
       <c r="F845" t="n">
         <v>6960600</v>
@@ -17372,16 +17372,16 @@
         <v>45469</v>
       </c>
       <c r="B848" t="n">
-        <v>7.042013645172119</v>
+        <v>7.042014122009277</v>
       </c>
       <c r="C848" t="n">
-        <v>7.069414232447009</v>
+        <v>7.069414711139547</v>
       </c>
       <c r="D848" t="n">
-        <v>6.731470752560154</v>
+        <v>6.731471208369463</v>
       </c>
       <c r="E848" t="n">
-        <v>6.804539565992502</v>
+        <v>6.804540026749534</v>
       </c>
       <c r="F848" t="n">
         <v>4179500</v>
@@ -17392,16 +17392,16 @@
         <v>45470</v>
       </c>
       <c r="B849" t="n">
-        <v>7.069414615631104</v>
+        <v>7.069414138793945</v>
       </c>
       <c r="C849" t="n">
-        <v>7.124216664200287</v>
+        <v>7.124216183666692</v>
       </c>
       <c r="D849" t="n">
-        <v>6.85020816345239</v>
+        <v>6.850207701400866</v>
       </c>
       <c r="E849" t="n">
-        <v>7.051147411282877</v>
+        <v>7.051146935677855</v>
       </c>
       <c r="F849" t="n">
         <v>6848800</v>
@@ -17492,16 +17492,16 @@
         <v>45477</v>
       </c>
       <c r="B854" t="n">
-        <v>7.991909503936768</v>
+        <v>7.991909027099609</v>
       </c>
       <c r="C854" t="n">
-        <v>8.110646549663995</v>
+        <v>8.110646065742392</v>
       </c>
       <c r="D854" t="n">
-        <v>7.580897189372679</v>
+        <v>7.580896737058564</v>
       </c>
       <c r="E854" t="n">
-        <v>7.580897189372679</v>
+        <v>7.580896737058564</v>
       </c>
       <c r="F854" t="n">
         <v>16897700</v>
@@ -17512,16 +17512,16 @@
         <v>45478</v>
       </c>
       <c r="B855" t="n">
-        <v>8.220250129699707</v>
+        <v>8.220249176025391</v>
       </c>
       <c r="C855" t="n">
-        <v>8.229383950006699</v>
+        <v>8.229382995272722</v>
       </c>
       <c r="D855" t="n">
-        <v>7.845772207603456</v>
+        <v>7.845771297374288</v>
       </c>
       <c r="E855" t="n">
-        <v>7.99190984831916</v>
+        <v>7.991908921135797</v>
       </c>
       <c r="F855" t="n">
         <v>7882000</v>
@@ -17552,16 +17552,16 @@
         <v>45482</v>
       </c>
       <c r="B857" t="n">
-        <v>8.275051116943359</v>
+        <v>8.275052070617676</v>
       </c>
       <c r="C857" t="n">
-        <v>8.293317884160565</v>
+        <v>8.293318839940072</v>
       </c>
       <c r="D857" t="n">
-        <v>8.019309407510983</v>
+        <v>8.01931033171185</v>
       </c>
       <c r="E857" t="n">
-        <v>8.138046443094101</v>
+        <v>8.138047380979048</v>
       </c>
       <c r="F857" t="n">
         <v>6492100</v>
@@ -17612,16 +17612,16 @@
         <v>45485</v>
       </c>
       <c r="B860" t="n">
-        <v>8.357253074645996</v>
+        <v>8.357254028320312</v>
       </c>
       <c r="C860" t="n">
-        <v>8.576460383805578</v>
+        <v>8.57646136249438</v>
       </c>
       <c r="D860" t="n">
-        <v>8.275051313641228</v>
+        <v>8.275052257935224</v>
       </c>
       <c r="E860" t="n">
-        <v>8.576460383805578</v>
+        <v>8.57646136249438</v>
       </c>
       <c r="F860" t="n">
         <v>9959600</v>
@@ -17812,16 +17812,16 @@
         <v>45499</v>
       </c>
       <c r="B870" t="n">
-        <v>8.165448188781738</v>
+        <v>8.165447235107422</v>
       </c>
       <c r="C870" t="n">
-        <v>8.165448188781738</v>
+        <v>8.165447235107422</v>
       </c>
       <c r="D870" t="n">
-        <v>7.891440544277249</v>
+        <v>7.891439622605347</v>
       </c>
       <c r="E870" t="n">
-        <v>8.037578186959392</v>
+        <v>8.03757724821951</v>
       </c>
       <c r="F870" t="n">
         <v>4118500</v>
@@ -17852,16 +17852,16 @@
         <v>45503</v>
       </c>
       <c r="B872" t="n">
-        <v>7.635697841644287</v>
+        <v>7.635698318481445</v>
       </c>
       <c r="C872" t="n">
-        <v>7.781836337061709</v>
+        <v>7.781836823024983</v>
       </c>
       <c r="D872" t="n">
-        <v>7.544362261938466</v>
+        <v>7.544362733071863</v>
       </c>
       <c r="E872" t="n">
-        <v>7.763568698491175</v>
+        <v>7.763569183313664</v>
       </c>
       <c r="F872" t="n">
         <v>8186100</v>
@@ -17872,16 +17872,16 @@
         <v>45504</v>
       </c>
       <c r="B873" t="n">
-        <v>7.882306575775146</v>
+        <v>7.882306098937988</v>
       </c>
       <c r="C873" t="n">
-        <v>7.91884098575937</v>
+        <v>7.918840506712075</v>
       </c>
       <c r="D873" t="n">
-        <v>7.553496885917143</v>
+        <v>7.553496428971203</v>
       </c>
       <c r="E873" t="n">
-        <v>7.663100115869812</v>
+        <v>7.663099652293464</v>
       </c>
       <c r="F873" t="n">
         <v>7542900</v>
@@ -17972,16 +17972,16 @@
         <v>45511</v>
       </c>
       <c r="B878" t="n">
-        <v>7.599164009094238</v>
+        <v>7.59916353225708</v>
       </c>
       <c r="C878" t="n">
-        <v>7.635698417943767</v>
+        <v>7.635697938814125</v>
       </c>
       <c r="D878" t="n">
-        <v>7.398225195946334</v>
+        <v>7.398224731717812</v>
       </c>
       <c r="E878" t="n">
-        <v>7.498694602520287</v>
+        <v>7.498694131987445</v>
       </c>
       <c r="F878" t="n">
         <v>13715500</v>
@@ -17992,16 +17992,16 @@
         <v>45512</v>
       </c>
       <c r="B879" t="n">
-        <v>7.599164009094238</v>
+        <v>7.59916353225708</v>
       </c>
       <c r="C879" t="n">
-        <v>7.763569284441628</v>
+        <v>7.763568797288263</v>
       </c>
       <c r="D879" t="n">
-        <v>7.480426962571014</v>
+        <v>7.480426493184443</v>
       </c>
       <c r="E879" t="n">
-        <v>7.635698417943767</v>
+        <v>7.635697938814125</v>
       </c>
       <c r="F879" t="n">
         <v>7650900</v>
@@ -18012,16 +18012,16 @@
         <v>45513</v>
       </c>
       <c r="B880" t="n">
-        <v>7.745301723480225</v>
+        <v>7.745301246643066</v>
       </c>
       <c r="C880" t="n">
-        <v>7.873172591282133</v>
+        <v>7.873172106572643</v>
       </c>
       <c r="D880" t="n">
-        <v>7.507828499061</v>
+        <v>7.507828036843809</v>
       </c>
       <c r="E880" t="n">
-        <v>7.653966135949453</v>
+        <v>7.653965664735343</v>
       </c>
       <c r="F880" t="n">
         <v>7501500</v>
@@ -18052,16 +18052,16 @@
         <v>45517</v>
       </c>
       <c r="B882" t="n">
-        <v>7.699634552001953</v>
+        <v>7.699633598327637</v>
       </c>
       <c r="C882" t="n">
-        <v>7.800103962037498</v>
+        <v>7.800102995919072</v>
       </c>
       <c r="D882" t="n">
-        <v>7.635698681025655</v>
+        <v>7.635697735270417</v>
       </c>
       <c r="E882" t="n">
-        <v>7.717901321531577</v>
+        <v>7.717900365594744</v>
       </c>
       <c r="F882" t="n">
         <v>7752600</v>
@@ -18072,16 +18072,16 @@
         <v>45518</v>
       </c>
       <c r="B883" t="n">
-        <v>7.599164009094238</v>
+        <v>7.59916353225708</v>
       </c>
       <c r="C883" t="n">
-        <v>7.81837133324043</v>
+        <v>7.818370842648312</v>
       </c>
       <c r="D883" t="n">
-        <v>7.462160193670757</v>
+        <v>7.462159725430401</v>
       </c>
       <c r="E883" t="n">
-        <v>7.763569284441628</v>
+        <v>7.763568797288263</v>
       </c>
       <c r="F883" t="n">
         <v>7383100</v>
@@ -18152,16 +18152,16 @@
         <v>45524</v>
       </c>
       <c r="B887" t="n">
-        <v>7.745301723480225</v>
+        <v>7.745301246643066</v>
       </c>
       <c r="C887" t="n">
-        <v>8.019310228170587</v>
+        <v>8.019309734464178</v>
       </c>
       <c r="D887" t="n">
-        <v>7.69963436523935</v>
+        <v>7.69963389121369</v>
       </c>
       <c r="E887" t="n">
-        <v>7.937107589658575</v>
+        <v>7.937107101012947</v>
       </c>
       <c r="F887" t="n">
         <v>6543300</v>
@@ -18172,16 +18172,16 @@
         <v>45525</v>
       </c>
       <c r="B888" t="n">
-        <v>7.608297348022461</v>
+        <v>7.608297824859619</v>
       </c>
       <c r="C888" t="n">
-        <v>7.854905245451379</v>
+        <v>7.854905737744269</v>
       </c>
       <c r="D888" t="n">
-        <v>7.489560309006571</v>
+        <v>7.489560778402085</v>
       </c>
       <c r="E888" t="n">
-        <v>7.745301154783664</v>
+        <v>7.745301640207304</v>
       </c>
       <c r="F888" t="n">
         <v>7135600</v>
@@ -18192,16 +18192,16 @@
         <v>45526</v>
       </c>
       <c r="B889" t="n">
-        <v>7.279487609863281</v>
+        <v>7.279487133026123</v>
       </c>
       <c r="C889" t="n">
-        <v>7.663099768349934</v>
+        <v>7.663099266384561</v>
       </c>
       <c r="D889" t="n">
-        <v>7.252087021379985</v>
+        <v>7.252086546337681</v>
       </c>
       <c r="E889" t="n">
-        <v>7.571763312006945</v>
+        <v>7.571762816024495</v>
       </c>
       <c r="F889" t="n">
         <v>6992500</v>
@@ -18332,16 +18332,16 @@
         <v>45537</v>
       </c>
       <c r="B896" t="n">
-        <v>6.868474960327148</v>
+        <v>6.868475437164307</v>
       </c>
       <c r="C896" t="n">
-        <v>6.941543773385233</v>
+        <v>6.941544255295122</v>
       </c>
       <c r="D896" t="n">
-        <v>6.795406147269064</v>
+        <v>6.795406619033491</v>
       </c>
       <c r="E896" t="n">
-        <v>6.895875982986171</v>
+        <v>6.895876461725617</v>
       </c>
       <c r="F896" t="n">
         <v>5645700</v>
@@ -18452,16 +18452,16 @@
         <v>45545</v>
       </c>
       <c r="B902" t="n">
-        <v>6.749738216400146</v>
+        <v>6.749737739562988</v>
       </c>
       <c r="C902" t="n">
-        <v>6.868475260572184</v>
+        <v>6.868474775346815</v>
       </c>
       <c r="D902" t="n">
-        <v>6.722337628067829</v>
+        <v>6.722337153166394</v>
       </c>
       <c r="E902" t="n">
-        <v>6.777139240256963</v>
+        <v>6.777138761484052</v>
       </c>
       <c r="F902" t="n">
         <v>6841000</v>
@@ -18532,16 +18532,16 @@
         <v>45551</v>
       </c>
       <c r="B906" t="n">
-        <v>6.694936275482178</v>
+        <v>6.694936752319336</v>
       </c>
       <c r="C906" t="n">
-        <v>6.777138907491886</v>
+        <v>6.777139390183809</v>
       </c>
       <c r="D906" t="n">
-        <v>6.640134665983865</v>
+        <v>6.640135138917858</v>
       </c>
       <c r="E906" t="n">
-        <v>6.704070094827469</v>
+        <v>6.70407057231517</v>
       </c>
       <c r="F906" t="n">
         <v>4229100</v>
@@ -18572,16 +18572,16 @@
         <v>45553</v>
       </c>
       <c r="B908" t="n">
-        <v>6.539665222167969</v>
+        <v>6.539664745330811</v>
       </c>
       <c r="C908" t="n">
-        <v>6.850208130100359</v>
+        <v>6.850207630620085</v>
       </c>
       <c r="D908" t="n">
-        <v>6.493997429282001</v>
+        <v>6.493996955774693</v>
       </c>
       <c r="E908" t="n">
-        <v>6.676669471874876</v>
+        <v>6.676668985048106</v>
       </c>
       <c r="F908" t="n">
         <v>10313100</v>
@@ -18632,16 +18632,16 @@
         <v>45558</v>
       </c>
       <c r="B911" t="n">
-        <v>6.028182983398438</v>
+        <v>6.028182506561279</v>
       </c>
       <c r="C911" t="n">
-        <v>6.064717391408013</v>
+        <v>6.064716911680935</v>
       </c>
       <c r="D911" t="n">
-        <v>5.863778147355347</v>
+        <v>5.863777683522827</v>
       </c>
       <c r="E911" t="n">
-        <v>5.991648575388862</v>
+        <v>5.991648101441623</v>
       </c>
       <c r="F911" t="n">
         <v>7689600</v>
@@ -18712,16 +18712,16 @@
         <v>45562</v>
       </c>
       <c r="B915" t="n">
-        <v>5.936846733093262</v>
+        <v>5.93684720993042</v>
       </c>
       <c r="C915" t="n">
-        <v>6.137785969351801</v>
+        <v>6.137786462328047</v>
       </c>
       <c r="D915" t="n">
-        <v>5.927712913682906</v>
+        <v>5.927713389786452</v>
       </c>
       <c r="E915" t="n">
-        <v>6.037316568984771</v>
+        <v>6.037317053891492</v>
       </c>
       <c r="F915" t="n">
         <v>5348400</v>
@@ -18792,16 +18792,16 @@
         <v>45568</v>
       </c>
       <c r="B919" t="n">
-        <v>5.270092964172363</v>
+        <v>5.270093441009521</v>
       </c>
       <c r="C919" t="n">
-        <v>5.489299831127303</v>
+        <v>5.489300327798264</v>
       </c>
       <c r="D919" t="n">
-        <v>4.941282881502185</v>
+        <v>4.941283328588661</v>
       </c>
       <c r="E919" t="n">
-        <v>5.480166012055468</v>
+        <v>5.480166507900002</v>
       </c>
       <c r="F919" t="n">
         <v>48426200</v>
@@ -19012,16 +19012,16 @@
         <v>45583</v>
       </c>
       <c r="B930" t="n">
-        <v>5.306627750396729</v>
+        <v>5.30662727355957</v>
       </c>
       <c r="C930" t="n">
-        <v>5.379696566119483</v>
+        <v>5.379696082716587</v>
       </c>
       <c r="D930" t="n">
-        <v>5.169623503154316</v>
+        <v>5.169623038627936</v>
       </c>
       <c r="E930" t="n">
-        <v>5.306627750396729</v>
+        <v>5.30662727355957</v>
       </c>
       <c r="F930" t="n">
         <v>9506300</v>
@@ -19072,16 +19072,16 @@
         <v>45588</v>
       </c>
       <c r="B933" t="n">
-        <v>5.735908031463623</v>
+        <v>5.735907554626465</v>
       </c>
       <c r="C933" t="n">
-        <v>5.927713466189486</v>
+        <v>5.927712973407171</v>
       </c>
       <c r="D933" t="n">
-        <v>5.626304365945888</v>
+        <v>5.626303898220296</v>
       </c>
       <c r="E933" t="n">
-        <v>5.626304365945888</v>
+        <v>5.626303898220296</v>
       </c>
       <c r="F933" t="n">
         <v>15384500</v>
@@ -19092,16 +19092,16 @@
         <v>45589</v>
       </c>
       <c r="B934" t="n">
-        <v>5.836377143859863</v>
+        <v>5.836376667022705</v>
       </c>
       <c r="C934" t="n">
-        <v>5.891178756064592</v>
+        <v>5.891178274750094</v>
       </c>
       <c r="D934" t="n">
-        <v>5.589769671176334</v>
+        <v>5.589769214487223</v>
       </c>
       <c r="E934" t="n">
-        <v>5.717640535178534</v>
+        <v>5.717640068042261</v>
       </c>
       <c r="F934" t="n">
         <v>10139400</v>
@@ -19132,16 +19132,16 @@
         <v>45593</v>
       </c>
       <c r="B936" t="n">
-        <v>5.735908031463623</v>
+        <v>5.735907554626465</v>
       </c>
       <c r="C936" t="n">
-        <v>5.836377441195141</v>
+        <v>5.836376956005767</v>
       </c>
       <c r="D936" t="n">
-        <v>5.717640826464754</v>
+        <v>5.717640351146184</v>
       </c>
       <c r="E936" t="n">
-        <v>5.836377441195141</v>
+        <v>5.836376956005767</v>
       </c>
       <c r="F936" t="n">
         <v>5963100</v>
@@ -19192,16 +19192,16 @@
         <v>45596</v>
       </c>
       <c r="B939" t="n">
-        <v>5.745040893554688</v>
+        <v>5.745041370391846</v>
       </c>
       <c r="C939" t="n">
-        <v>5.973381153029912</v>
+        <v>5.973381648819262</v>
       </c>
       <c r="D939" t="n">
-        <v>5.735907509648409</v>
+        <v>5.735907985727498</v>
       </c>
       <c r="E939" t="n">
-        <v>5.827243526333603</v>
+        <v>5.827244009993561</v>
       </c>
       <c r="F939" t="n">
         <v>7246200</v>
@@ -19212,16 +19212,16 @@
         <v>45597</v>
       </c>
       <c r="B940" t="n">
-        <v>5.270092964172363</v>
+        <v>5.270093441009521</v>
       </c>
       <c r="C940" t="n">
-        <v>5.754174486868027</v>
+        <v>5.754175007504804</v>
       </c>
       <c r="D940" t="n">
-        <v>5.224424739862115</v>
+        <v>5.22442521256722</v>
       </c>
       <c r="E940" t="n">
-        <v>5.745040667796192</v>
+        <v>5.745041187606541</v>
       </c>
       <c r="F940" t="n">
         <v>7357000</v>
@@ -19232,16 +19232,16 @@
         <v>45600</v>
       </c>
       <c r="B941" t="n">
-        <v>5.635437488555908</v>
+        <v>5.635437965393066</v>
       </c>
       <c r="C941" t="n">
-        <v>5.681105277637273</v>
+        <v>5.681105758338568</v>
       </c>
       <c r="D941" t="n">
-        <v>5.352295628363364</v>
+        <v>5.352296081242743</v>
       </c>
       <c r="E941" t="n">
-        <v>5.379696214707288</v>
+        <v>5.379696669905143</v>
       </c>
       <c r="F941" t="n">
         <v>6291500</v>
@@ -19252,16 +19252,16 @@
         <v>45601</v>
       </c>
       <c r="B942" t="n">
-        <v>5.617170333862305</v>
+        <v>5.617170810699463</v>
       </c>
       <c r="C942" t="n">
-        <v>5.726773551224381</v>
+        <v>5.726774037365669</v>
       </c>
       <c r="D942" t="n">
-        <v>5.480166094397473</v>
+        <v>5.48016655960445</v>
       </c>
       <c r="E942" t="n">
-        <v>5.635437536755984</v>
+        <v>5.635438015143831</v>
       </c>
       <c r="F942" t="n">
         <v>5341400</v>
@@ -19272,16 +19272,16 @@
         <v>45602</v>
       </c>
       <c r="B943" t="n">
-        <v>5.580636501312256</v>
+        <v>5.580636024475098</v>
       </c>
       <c r="C943" t="n">
-        <v>5.653705320392528</v>
+        <v>5.653704837312009</v>
       </c>
       <c r="D943" t="n">
-        <v>5.352296223924147</v>
+        <v>5.35229576659751</v>
       </c>
       <c r="E943" t="n">
-        <v>5.461899452544555</v>
+        <v>5.461898985852877</v>
       </c>
       <c r="F943" t="n">
         <v>8155700</v>
@@ -19312,16 +19312,16 @@
         <v>45604</v>
       </c>
       <c r="B945" t="n">
-        <v>5.215291500091553</v>
+        <v>5.215291976928711</v>
       </c>
       <c r="C945" t="n">
-        <v>5.270093109459959</v>
+        <v>5.270093591307661</v>
       </c>
       <c r="D945" t="n">
-        <v>5.105688281354738</v>
+        <v>5.10568874817081</v>
       </c>
       <c r="E945" t="n">
-        <v>5.270093109459959</v>
+        <v>5.270093591307661</v>
       </c>
       <c r="F945" t="n">
         <v>10054800</v>
@@ -19332,16 +19332,16 @@
         <v>45607</v>
       </c>
       <c r="B946" t="n">
-        <v>5.20615816116333</v>
+        <v>5.206157684326172</v>
       </c>
       <c r="C946" t="n">
-        <v>5.224425365971729</v>
+        <v>5.224424887461459</v>
       </c>
       <c r="D946" t="n">
-        <v>5.087421547670997</v>
+        <v>5.087421081709041</v>
       </c>
       <c r="E946" t="n">
-        <v>5.169623751546532</v>
+        <v>5.169623278055597</v>
       </c>
       <c r="F946" t="n">
         <v>6986700</v>
@@ -19412,16 +19412,16 @@
         <v>45614</v>
       </c>
       <c r="B950" t="n">
-        <v>5.096554756164551</v>
+        <v>5.096554279327393</v>
       </c>
       <c r="C950" t="n">
-        <v>5.206157981226809</v>
+        <v>5.206157494135098</v>
       </c>
       <c r="D950" t="n">
-        <v>4.97781771125152</v>
+        <v>4.977817245523481</v>
       </c>
       <c r="E950" t="n">
-        <v>5.060020347810465</v>
+        <v>5.06001987439149</v>
       </c>
       <c r="F950" t="n">
         <v>6191300</v>
@@ -19492,16 +19492,16 @@
         <v>45621</v>
       </c>
       <c r="B954" t="n">
-        <v>5.580636501312256</v>
+        <v>5.580636024475098</v>
       </c>
       <c r="C954" t="n">
-        <v>5.653705320392528</v>
+        <v>5.653704837312009</v>
       </c>
       <c r="D954" t="n">
-        <v>5.324895199006787</v>
+        <v>5.324894744021429</v>
       </c>
       <c r="E954" t="n">
-        <v>5.571502681164964</v>
+        <v>5.571502205108245</v>
       </c>
       <c r="F954" t="n">
         <v>8051200</v>
@@ -19552,16 +19552,16 @@
         <v>45624</v>
       </c>
       <c r="B957" t="n">
-        <v>5.270092964172363</v>
+        <v>5.270093441009521</v>
       </c>
       <c r="C957" t="n">
-        <v>5.589769227770706</v>
+        <v>5.589769733532121</v>
       </c>
       <c r="D957" t="n">
-        <v>5.123955343218713</v>
+        <v>5.123955806833363</v>
       </c>
       <c r="E957" t="n">
-        <v>5.51670041729388</v>
+        <v>5.516700916444042</v>
       </c>
       <c r="F957" t="n">
         <v>16639300</v>
@@ -27812,7 +27812,7 @@
         <v>46232</v>
       </c>
       <c r="B1370" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="C1370" t="n">
         <v>3.35</v>
@@ -27824,7 +27824,7 @@
         <v>3.34</v>
       </c>
       <c r="F1370" t="n">
-        <v>5118100</v>
+        <v>6988600</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1370"/>
+  <dimension ref="A1:F1371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44229</v>
       </c>
       <c r="B2" t="n">
-        <v>6.844325542449951</v>
+        <v>6.844326496124268</v>
       </c>
       <c r="C2" t="n">
-        <v>7.276819619617557</v>
+        <v>7.276820633554713</v>
       </c>
       <c r="D2" t="n">
-        <v>6.844325542449951</v>
+        <v>6.844326496124268</v>
       </c>
       <c r="E2" t="n">
-        <v>7.094164231854394</v>
+        <v>7.094165220340723</v>
       </c>
       <c r="F2" t="n">
         <v>4750609</v>
@@ -472,16 +472,16 @@
         <v>44230</v>
       </c>
       <c r="B3" t="n">
-        <v>6.907310485839844</v>
+        <v>6.907310009002686</v>
       </c>
       <c r="C3" t="n">
-        <v>7.020683275352985</v>
+        <v>7.020682790689285</v>
       </c>
       <c r="D3" t="n">
-        <v>6.657471787648176</v>
+        <v>6.657471328058306</v>
       </c>
       <c r="E3" t="n">
-        <v>6.953499159554224</v>
+        <v>6.953498679528491</v>
       </c>
       <c r="F3" t="n">
         <v>3966477</v>
@@ -512,16 +512,16 @@
         <v>44232</v>
       </c>
       <c r="B5" t="n">
-        <v>6.823331356048584</v>
+        <v>6.823330879211426</v>
       </c>
       <c r="C5" t="n">
-        <v>6.909409992235542</v>
+        <v>6.909409509382922</v>
       </c>
       <c r="D5" t="n">
-        <v>6.699461247702325</v>
+        <v>6.699460779521623</v>
       </c>
       <c r="E5" t="n">
-        <v>6.873718632603384</v>
+        <v>6.873718152244995</v>
       </c>
       <c r="F5" t="n">
         <v>4402737</v>
@@ -532,16 +532,16 @@
         <v>44235</v>
       </c>
       <c r="B6" t="n">
-        <v>7.21173620223999</v>
+        <v>7.211735248565674</v>
       </c>
       <c r="C6" t="n">
-        <v>7.619036269833193</v>
+        <v>7.619035262297836</v>
       </c>
       <c r="D6" t="n">
-        <v>6.82753006666352</v>
+        <v>6.827529163796321</v>
       </c>
       <c r="E6" t="n">
-        <v>6.854823412007115</v>
+        <v>6.854822505530665</v>
       </c>
       <c r="F6" t="n">
         <v>3162478</v>
@@ -552,16 +552,16 @@
         <v>44236</v>
       </c>
       <c r="B7" t="n">
-        <v>7.119358539581299</v>
+        <v>7.119358062744141</v>
       </c>
       <c r="C7" t="n">
-        <v>7.367097937617529</v>
+        <v>7.367097444187393</v>
       </c>
       <c r="D7" t="n">
-        <v>6.953499173999</v>
+        <v>6.953498708270694</v>
       </c>
       <c r="E7" t="n">
-        <v>7.266322575504579</v>
+        <v>7.266322088824129</v>
       </c>
       <c r="F7" t="n">
         <v>1374461</v>
@@ -592,16 +592,16 @@
         <v>44238</v>
       </c>
       <c r="B9" t="n">
-        <v>6.963996410369873</v>
+        <v>6.963997364044189</v>
       </c>
       <c r="C9" t="n">
-        <v>7.058473057595991</v>
+        <v>7.058474024208274</v>
       </c>
       <c r="D9" t="n">
-        <v>6.850623621904003</v>
+        <v>6.850624560052649</v>
       </c>
       <c r="E9" t="n">
-        <v>6.928305052130111</v>
+        <v>6.928306000916726</v>
       </c>
       <c r="F9" t="n">
         <v>1655030</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029080390930176</v>
+        <v>7.029079914093018</v>
       </c>
       <c r="C10" t="n">
-        <v>7.194939754112628</v>
+        <v>7.19493926602394</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913608302177867</v>
+        <v>6.913607833174078</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949299660305043</v>
+        <v>6.949299188880033</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -632,16 +632,16 @@
         <v>44244</v>
       </c>
       <c r="B11" t="n">
-        <v>7.274720191955566</v>
+        <v>7.274720668792725</v>
       </c>
       <c r="C11" t="n">
-        <v>7.388092163706458</v>
+        <v>7.388092647974826</v>
       </c>
       <c r="D11" t="n">
-        <v>7.113059436567523</v>
+        <v>7.11305990280828</v>
       </c>
       <c r="E11" t="n">
-        <v>7.117258849481164</v>
+        <v>7.11725931599718</v>
       </c>
       <c r="F11" t="n">
         <v>2613098</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.222232341766357</v>
+        <v>7.222233295440674</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379693674093248</v>
+        <v>7.379694648559866</v>
       </c>
       <c r="D12" t="n">
-        <v>7.138253018644978</v>
+        <v>7.138253961230074</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287316337480287</v>
+        <v>7.287317299748752</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -672,16 +672,16 @@
         <v>44246</v>
       </c>
       <c r="B13" t="n">
-        <v>7.453177452087402</v>
+        <v>7.453176975250244</v>
       </c>
       <c r="C13" t="n">
-        <v>7.595942903530964</v>
+        <v>7.595942417560001</v>
       </c>
       <c r="D13" t="n">
-        <v>7.142454126335747</v>
+        <v>7.142453669377954</v>
       </c>
       <c r="E13" t="n">
-        <v>7.159249345510314</v>
+        <v>7.159248887478</v>
       </c>
       <c r="F13" t="n">
         <v>1995604</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.306212902069092</v>
+        <v>7.306213855743408</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724010241576962</v>
+        <v>7.724011249786042</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050074693354461</v>
+        <v>7.050075613595256</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054274106241974</v>
+        <v>7.054275027030914</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.306212902069092</v>
+        <v>7.306213855743408</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480470271524869</v>
+        <v>7.480471247944865</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243227391317824</v>
+        <v>7.243228336770691</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308311390821116</v>
+        <v>7.308312344769346</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -732,16 +732,16 @@
         <v>44251</v>
       </c>
       <c r="B16" t="n">
-        <v>7.327208042144775</v>
+        <v>7.327207088470459</v>
       </c>
       <c r="C16" t="n">
-        <v>7.556052112537071</v>
+        <v>7.556051129077507</v>
       </c>
       <c r="D16" t="n">
-        <v>7.108861287011643</v>
+        <v>7.108860361756294</v>
       </c>
       <c r="E16" t="n">
-        <v>7.451078148150898</v>
+        <v>7.451077178354241</v>
       </c>
       <c r="F16" t="n">
         <v>1445414</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400690302893193</v>
+        <v>7.400689808525235</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945101447895325</v>
+        <v>6.945100983960817</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360800341244324</v>
+        <v>7.360799849541025</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -772,16 +772,16 @@
         <v>44253</v>
       </c>
       <c r="B18" t="n">
-        <v>7.243227481842041</v>
+        <v>7.243227005004883</v>
       </c>
       <c r="C18" t="n">
-        <v>7.480470365014094</v>
+        <v>7.48046987255873</v>
       </c>
       <c r="D18" t="n">
-        <v>6.833828151198126</v>
+        <v>6.833827701312602</v>
       </c>
       <c r="E18" t="n">
-        <v>7.157148852208861</v>
+        <v>7.157148381038444</v>
       </c>
       <c r="F18" t="n">
         <v>1865862</v>
@@ -792,16 +792,16 @@
         <v>44256</v>
       </c>
       <c r="B19" t="n">
-        <v>7.001787185668945</v>
+        <v>7.001787662506104</v>
       </c>
       <c r="C19" t="n">
-        <v>7.390191907873347</v>
+        <v>7.390192411161723</v>
       </c>
       <c r="D19" t="n">
-        <v>7.001787185668945</v>
+        <v>7.001787662506104</v>
       </c>
       <c r="E19" t="n">
-        <v>7.249526585020872</v>
+        <v>7.24952707872963</v>
       </c>
       <c r="F19" t="n">
         <v>1349729</v>
@@ -832,16 +832,16 @@
         <v>44258</v>
       </c>
       <c r="B21" t="n">
-        <v>7.085766792297363</v>
+        <v>7.085767269134521</v>
       </c>
       <c r="C21" t="n">
-        <v>7.108860721672044</v>
+        <v>7.10886120006331</v>
       </c>
       <c r="D21" t="n">
-        <v>6.896812697275568</v>
+        <v>6.896813161397048</v>
       </c>
       <c r="E21" t="n">
-        <v>7.108860721672044</v>
+        <v>7.10886120006331</v>
       </c>
       <c r="F21" t="n">
         <v>1419466</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233502264944</v>
+        <v>7.222233019817944</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966096890895136</v>
+        <v>6.966096425558127</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117259534444174</v>
+        <v>7.117259059009463</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -892,16 +892,16 @@
         <v>44263</v>
       </c>
       <c r="B24" t="n">
-        <v>6.653271675109863</v>
+        <v>6.653272151947021</v>
       </c>
       <c r="C24" t="n">
-        <v>7.016483124633246</v>
+        <v>7.016483627501614</v>
       </c>
       <c r="D24" t="n">
-        <v>6.653271675109863</v>
+        <v>6.653272151947021</v>
       </c>
       <c r="E24" t="n">
-        <v>7.016483124633246</v>
+        <v>7.016483627501614</v>
       </c>
       <c r="F24" t="n">
         <v>1015642</v>
@@ -952,16 +952,16 @@
         <v>44266</v>
       </c>
       <c r="B27" t="n">
-        <v>6.670067310333252</v>
+        <v>6.670068264007568</v>
       </c>
       <c r="C27" t="n">
-        <v>6.670067310333252</v>
+        <v>6.670068264007568</v>
       </c>
       <c r="D27" t="n">
-        <v>6.214478928037289</v>
+        <v>6.214479816572392</v>
       </c>
       <c r="E27" t="n">
-        <v>6.287961344172484</v>
+        <v>6.287962243213972</v>
       </c>
       <c r="F27" t="n">
         <v>2230763</v>
@@ -972,16 +972,16 @@
         <v>44267</v>
       </c>
       <c r="B28" t="n">
-        <v>6.695262432098389</v>
+        <v>6.695262908935547</v>
       </c>
       <c r="C28" t="n">
-        <v>6.896813573576604</v>
+        <v>6.896814064768251</v>
       </c>
       <c r="D28" t="n">
-        <v>6.455920629173074</v>
+        <v>6.455921088964289</v>
       </c>
       <c r="E28" t="n">
-        <v>6.646974454893159</v>
+        <v>6.646974928291244</v>
       </c>
       <c r="F28" t="n">
         <v>3263434</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033280372619629</v>
+        <v>7.033279895782471</v>
       </c>
       <c r="C29" t="n">
-        <v>7.12775702718571</v>
+        <v>7.127756543943293</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969559237991</v>
+        <v>6.667969107167907</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969559237991</v>
+        <v>6.667969107167907</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1012,16 +1012,16 @@
         <v>44271</v>
       </c>
       <c r="B30" t="n">
-        <v>7.390192031860352</v>
+        <v>7.390191555023193</v>
       </c>
       <c r="C30" t="n">
-        <v>7.42588420308686</v>
+        <v>7.425883723946737</v>
       </c>
       <c r="D30" t="n">
-        <v>6.970294545149255</v>
+        <v>6.970294095405131</v>
       </c>
       <c r="E30" t="n">
-        <v>6.970294545149255</v>
+        <v>6.970294095405131</v>
       </c>
       <c r="F30" t="n">
         <v>4282725</v>
@@ -1032,16 +1032,16 @@
         <v>44272</v>
       </c>
       <c r="B31" t="n">
-        <v>7.558151245117188</v>
+        <v>7.558151721954346</v>
       </c>
       <c r="C31" t="n">
-        <v>7.642130577117119</v>
+        <v>7.642131059252459</v>
       </c>
       <c r="D31" t="n">
-        <v>7.285217807271516</v>
+        <v>7.285218266889542</v>
       </c>
       <c r="E31" t="n">
-        <v>7.390191769322798</v>
+        <v>7.390192235563539</v>
       </c>
       <c r="F31" t="n">
         <v>5070506</v>
@@ -1052,16 +1052,16 @@
         <v>44273</v>
       </c>
       <c r="B32" t="n">
-        <v>7.589643001556396</v>
+        <v>7.589643955230713</v>
       </c>
       <c r="C32" t="n">
-        <v>7.898267789895324</v>
+        <v>7.898268782349795</v>
       </c>
       <c r="D32" t="n">
-        <v>7.459474999602055</v>
+        <v>7.45947593692015</v>
       </c>
       <c r="E32" t="n">
-        <v>7.600140316321165</v>
+        <v>7.600141271314518</v>
       </c>
       <c r="F32" t="n">
         <v>3661176</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.516161441802979</v>
+        <v>7.51616096496582</v>
       </c>
       <c r="C33" t="n">
-        <v>7.778596733861603</v>
+        <v>7.778596240375135</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430081191788996</v>
+        <v>7.430080720412905</v>
       </c>
       <c r="E33" t="n">
-        <v>7.600139955939049</v>
+        <v>7.600139473774162</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1092,16 +1092,16 @@
         <v>44277</v>
       </c>
       <c r="B34" t="n">
-        <v>7.558151245117188</v>
+        <v>7.558151721954346</v>
       </c>
       <c r="C34" t="n">
-        <v>7.807989940470752</v>
+        <v>7.807990433070015</v>
       </c>
       <c r="D34" t="n">
-        <v>7.201238475271585</v>
+        <v>7.201238929591428</v>
       </c>
       <c r="E34" t="n">
-        <v>7.514061872573729</v>
+        <v>7.514062346629327</v>
       </c>
       <c r="F34" t="n">
         <v>5377429</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.516161441802979</v>
+        <v>7.51616096496582</v>
       </c>
       <c r="C35" t="n">
-        <v>7.558150698871014</v>
+        <v>7.558150219369991</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436380716861456</v>
+        <v>7.436380245085714</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511962029019494</v>
+        <v>7.511961552448754</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159248352050781</v>
+        <v>7.159247875213623</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656827250339138</v>
+        <v>7.656826740361056</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159248352050781</v>
+        <v>7.159247875213623</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392291828769327</v>
+        <v>7.392291336410457</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.705114841461182</v>
+        <v>7.705114364624023</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789094989334038</v>
+        <v>7.789094507299701</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033280152834855</v>
+        <v>7.033279717574721</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159248751055008</v>
+        <v>7.159248307999206</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.51826000213623</v>
+        <v>7.518260955810547</v>
       </c>
       <c r="C38" t="n">
-        <v>7.789094122342303</v>
+        <v>7.789095110371317</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455275304139598</v>
+        <v>7.455276249824448</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721910823316651</v>
+        <v>7.721911802823614</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379694859893382</v>
+        <v>7.379694366927925</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257924862390593</v>
+        <v>7.257924377559402</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1232,16 +1232,16 @@
         <v>44286</v>
       </c>
       <c r="B41" t="n">
-        <v>7.348202705383301</v>
+        <v>7.348202228546143</v>
       </c>
       <c r="C41" t="n">
-        <v>7.379694651301018</v>
+        <v>7.379694172420294</v>
       </c>
       <c r="D41" t="n">
-        <v>6.997588639911132</v>
+        <v>6.997588185825906</v>
       </c>
       <c r="E41" t="n">
-        <v>7.226432711322428</v>
+        <v>7.226432242387128</v>
       </c>
       <c r="F41" t="n">
         <v>2544984</v>
@@ -1252,16 +1252,16 @@
         <v>44287</v>
       </c>
       <c r="B42" t="n">
-        <v>7.348202705383301</v>
+        <v>7.348202228546143</v>
       </c>
       <c r="C42" t="n">
-        <v>7.524559388470522</v>
+        <v>7.524558900189283</v>
       </c>
       <c r="D42" t="n">
-        <v>7.171846022296081</v>
+        <v>7.171845556903002</v>
       </c>
       <c r="E42" t="n">
-        <v>7.358700020689207</v>
+        <v>7.35869954317086</v>
       </c>
       <c r="F42" t="n">
         <v>877384</v>
@@ -1272,16 +1272,16 @@
         <v>44291</v>
       </c>
       <c r="B43" t="n">
-        <v>7.327208042144775</v>
+        <v>7.327207088470459</v>
       </c>
       <c r="C43" t="n">
-        <v>7.400690060753461</v>
+        <v>7.400689097515077</v>
       </c>
       <c r="D43" t="n">
-        <v>7.260023925614861</v>
+        <v>7.260022980684908</v>
       </c>
       <c r="E43" t="n">
-        <v>7.400690060753461</v>
+        <v>7.400689097515077</v>
       </c>
       <c r="F43" t="n">
         <v>1080107</v>
@@ -1292,16 +1292,16 @@
         <v>44292</v>
       </c>
       <c r="B44" t="n">
-        <v>7.21173620223999</v>
+        <v>7.211735248565674</v>
       </c>
       <c r="C44" t="n">
-        <v>7.379694875833847</v>
+        <v>7.379693899948808</v>
       </c>
       <c r="D44" t="n">
-        <v>7.190741570989402</v>
+        <v>7.190740620091399</v>
       </c>
       <c r="E44" t="n">
-        <v>7.369197560208552</v>
+        <v>7.36919658571167</v>
       </c>
       <c r="F44" t="n">
         <v>1319726</v>
@@ -1312,16 +1312,16 @@
         <v>44293</v>
       </c>
       <c r="B45" t="n">
-        <v>7.243227481842041</v>
+        <v>7.243227005004883</v>
       </c>
       <c r="C45" t="n">
-        <v>7.388092210073672</v>
+        <v>7.388091723699758</v>
       </c>
       <c r="D45" t="n">
-        <v>7.146651537550619</v>
+        <v>7.146651067071263</v>
       </c>
       <c r="E45" t="n">
-        <v>7.213834838440065</v>
+        <v>7.213834363537887</v>
       </c>
       <c r="F45" t="n">
         <v>1401221</v>
@@ -1332,16 +1332,16 @@
         <v>44294</v>
       </c>
       <c r="B46" t="n">
-        <v>7.589643001556396</v>
+        <v>7.589643955230713</v>
       </c>
       <c r="C46" t="n">
-        <v>7.78909441747052</v>
+        <v>7.789095396206844</v>
       </c>
       <c r="D46" t="n">
-        <v>7.215935024034804</v>
+        <v>7.215935930750956</v>
       </c>
       <c r="E46" t="n">
-        <v>7.2432275553465</v>
+        <v>7.243228465492086</v>
       </c>
       <c r="F46" t="n">
         <v>2111967</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652628421783447</v>
+        <v>7.652626991271973</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873074487963351</v>
+        <v>7.873073016243731</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474171618612335</v>
+        <v>7.474170221459922</v>
       </c>
       <c r="E47" t="n">
-        <v>7.595942429644829</v>
+        <v>7.595941009729709</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1432,16 +1432,16 @@
         <v>44301</v>
       </c>
       <c r="B51" t="n">
-        <v>8.11241626739502</v>
+        <v>8.112415313720703</v>
       </c>
       <c r="C51" t="n">
-        <v>8.185899104714634</v>
+        <v>8.185898142401868</v>
       </c>
       <c r="D51" t="n">
-        <v>7.891970190820038</v>
+        <v>7.891969263060783</v>
       </c>
       <c r="E51" t="n">
-        <v>7.894069491710552</v>
+        <v>7.894068563704509</v>
       </c>
       <c r="F51" t="n">
         <v>2034122</v>
@@ -1492,16 +1492,16 @@
         <v>44306</v>
       </c>
       <c r="B54" t="n">
-        <v>8.196394920349121</v>
+        <v>8.196395874023438</v>
       </c>
       <c r="C54" t="n">
-        <v>8.244682079168939</v>
+        <v>8.244683038461606</v>
       </c>
       <c r="D54" t="n">
-        <v>8.078822726880942</v>
+        <v>8.078823666875394</v>
       </c>
       <c r="E54" t="n">
-        <v>8.206892234674447</v>
+        <v>8.206893189570158</v>
       </c>
       <c r="F54" t="n">
         <v>282595</v>
@@ -1552,16 +1552,16 @@
         <v>44312</v>
       </c>
       <c r="B57" t="n">
-        <v>7.978049278259277</v>
+        <v>7.978048324584961</v>
       </c>
       <c r="C57" t="n">
-        <v>8.187997217134104</v>
+        <v>8.187996238363182</v>
       </c>
       <c r="D57" t="n">
-        <v>7.938158504201501</v>
+        <v>7.93815755529562</v>
       </c>
       <c r="E57" t="n">
-        <v>8.185898728134749</v>
+        <v>8.185897749614673</v>
       </c>
       <c r="F57" t="n">
         <v>1270667</v>
@@ -1572,16 +1572,16 @@
         <v>44313</v>
       </c>
       <c r="B58" t="n">
-        <v>8.116615295410156</v>
+        <v>8.11661434173584</v>
       </c>
       <c r="C58" t="n">
-        <v>8.1837986032776</v>
+        <v>8.183797641709477</v>
       </c>
       <c r="D58" t="n">
-        <v>7.9402586048865</v>
+        <v>7.940257671933487</v>
       </c>
       <c r="E58" t="n">
-        <v>7.999043897796192</v>
+        <v>7.999042957936108</v>
       </c>
       <c r="F58" t="n">
         <v>2786224</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397946357727051</v>
+        <v>8.397945404052734</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469329082392035</v>
+        <v>8.469328120611465</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116615684439186</v>
+        <v>8.116614762712898</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116615684439186</v>
+        <v>8.116614762712898</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849335670471191</v>
+        <v>8.849334716796875</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122269135355927</v>
+        <v>9.122268152268145</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641487026423638</v>
+        <v>8.641486095148732</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733864381954685</v>
+        <v>8.733863440724466</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1672,16 +1672,16 @@
         <v>44320</v>
       </c>
       <c r="B63" t="n">
-        <v>9.298624992370605</v>
+        <v>9.298624038696289</v>
       </c>
       <c r="C63" t="n">
-        <v>9.544265900402022</v>
+        <v>9.54426492153458</v>
       </c>
       <c r="D63" t="n">
-        <v>8.719166865823404</v>
+        <v>8.71916597157877</v>
       </c>
       <c r="E63" t="n">
-        <v>8.849334872165999</v>
+        <v>8.849333964571231</v>
       </c>
       <c r="F63" t="n">
         <v>2875017</v>
@@ -1772,16 +1772,16 @@
         <v>44327</v>
       </c>
       <c r="B68" t="n">
-        <v>9.617746353149414</v>
+        <v>9.617748260498047</v>
       </c>
       <c r="C68" t="n">
-        <v>9.645040506833098</v>
+        <v>9.645042419594585</v>
       </c>
       <c r="D68" t="n">
-        <v>8.964807071897692</v>
+        <v>8.964808849758313</v>
       </c>
       <c r="E68" t="n">
-        <v>9.294426475068693</v>
+        <v>9.294428318297966</v>
       </c>
       <c r="F68" t="n">
         <v>2188597</v>
@@ -1792,16 +1792,16 @@
         <v>44328</v>
       </c>
       <c r="B69" t="n">
-        <v>9.531668663024902</v>
+        <v>9.531667709350586</v>
       </c>
       <c r="C69" t="n">
-        <v>9.743716705677796</v>
+        <v>9.743715730787388</v>
       </c>
       <c r="D69" t="n">
-        <v>9.321719921078722</v>
+        <v>9.321718988410458</v>
       </c>
       <c r="E69" t="n">
-        <v>9.563160609009282</v>
+        <v>9.563159652184094</v>
       </c>
       <c r="F69" t="n">
         <v>1563804</v>
@@ -1812,16 +1812,16 @@
         <v>44329</v>
       </c>
       <c r="B70" t="n">
-        <v>9.655538558959961</v>
+        <v>9.655539512634277</v>
       </c>
       <c r="C70" t="n">
-        <v>9.699627931810785</v>
+        <v>9.699628889839794</v>
       </c>
       <c r="D70" t="n">
-        <v>9.489679194450057</v>
+        <v>9.489680131742498</v>
       </c>
       <c r="E70" t="n">
-        <v>9.556862498159457</v>
+        <v>9.556863442087572</v>
       </c>
       <c r="F70" t="n">
         <v>2493897</v>
@@ -1852,16 +1852,16 @@
         <v>44333</v>
       </c>
       <c r="B72" t="n">
-        <v>9.657638549804688</v>
+        <v>9.657637596130371</v>
       </c>
       <c r="C72" t="n">
-        <v>9.773109835938806</v>
+        <v>9.773108870861909</v>
       </c>
       <c r="D72" t="n">
-        <v>9.36161115804209</v>
+        <v>9.361610233599944</v>
       </c>
       <c r="E72" t="n">
-        <v>9.613549173803014</v>
+        <v>9.613548224482443</v>
       </c>
       <c r="F72" t="n">
         <v>1884107</v>
@@ -1872,16 +1872,16 @@
         <v>44334</v>
       </c>
       <c r="B73" t="n">
-        <v>9.657638549804688</v>
+        <v>9.657637596130371</v>
       </c>
       <c r="C73" t="n">
-        <v>9.666036564842845</v>
+        <v>9.66603561033924</v>
       </c>
       <c r="D73" t="n">
-        <v>9.458187113289004</v>
+        <v>9.458186179310156</v>
       </c>
       <c r="E73" t="n">
-        <v>9.655539248993795</v>
+        <v>9.655538295526782</v>
       </c>
       <c r="F73" t="n">
         <v>1385003</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.823495864868164</v>
+        <v>9.82349681854248</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272800283195</v>
+        <v>10.10272898361439</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334316624833162</v>
+        <v>9.334317531017494</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678631950423839</v>
+        <v>9.678632890034629</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1912,16 +1912,16 @@
         <v>44336</v>
       </c>
       <c r="B75" t="n">
-        <v>10.1300220489502</v>
+        <v>10.13002300262451</v>
       </c>
       <c r="C75" t="n">
-        <v>10.22869810319815</v>
+        <v>10.22869906616216</v>
       </c>
       <c r="D75" t="n">
-        <v>9.504375291530147</v>
+        <v>9.504376186303976</v>
       </c>
       <c r="E75" t="n">
-        <v>9.873884655086501</v>
+        <v>9.873885584647184</v>
       </c>
       <c r="F75" t="n">
         <v>2816227</v>
@@ -1932,16 +1932,16 @@
         <v>44337</v>
       </c>
       <c r="B76" t="n">
-        <v>10.10692882537842</v>
+        <v>10.1069278717041</v>
       </c>
       <c r="C76" t="n">
-        <v>10.19090816499662</v>
+        <v>10.19090720339814</v>
       </c>
       <c r="D76" t="n">
-        <v>9.873886137643053</v>
+        <v>9.873885205958286</v>
       </c>
       <c r="E76" t="n">
-        <v>10.12792345733432</v>
+        <v>10.12792250167898</v>
       </c>
       <c r="F76" t="n">
         <v>1597862</v>
@@ -1952,16 +1952,16 @@
         <v>44340</v>
       </c>
       <c r="B77" t="n">
-        <v>10.18251037597656</v>
+        <v>10.18250846862793</v>
       </c>
       <c r="C77" t="n">
-        <v>10.39035983469837</v>
+        <v>10.39035788841617</v>
       </c>
       <c r="D77" t="n">
-        <v>9.951566983949347</v>
+        <v>9.951565119860142</v>
       </c>
       <c r="E77" t="n">
-        <v>10.15731632999324</v>
+        <v>10.15731442736386</v>
       </c>
       <c r="F77" t="n">
         <v>3407772</v>
@@ -1992,16 +1992,16 @@
         <v>44342</v>
       </c>
       <c r="B79" t="n">
-        <v>10.49743175506592</v>
+        <v>10.49743270874023</v>
       </c>
       <c r="C79" t="n">
-        <v>10.51842719657374</v>
+        <v>10.51842815215546</v>
       </c>
       <c r="D79" t="n">
-        <v>10.31897577891374</v>
+        <v>10.31897671637563</v>
       </c>
       <c r="E79" t="n">
-        <v>10.42395055106932</v>
+        <v>10.423951498068</v>
       </c>
       <c r="F79" t="n">
         <v>2052367</v>
@@ -2032,16 +2032,16 @@
         <v>44344</v>
       </c>
       <c r="B81" t="n">
-        <v>10.7283763885498</v>
+        <v>10.72837543487549</v>
       </c>
       <c r="C81" t="n">
-        <v>10.82915175200188</v>
+        <v>10.82915078936937</v>
       </c>
       <c r="D81" t="n">
-        <v>10.46803955941845</v>
+        <v>10.46803862888618</v>
       </c>
       <c r="E81" t="n">
-        <v>10.65489436961172</v>
+        <v>10.65489342246942</v>
       </c>
       <c r="F81" t="n">
         <v>2512953</v>
@@ -2132,16 +2132,16 @@
         <v>44354</v>
       </c>
       <c r="B86" t="n">
-        <v>11.10838222503662</v>
+        <v>11.10838317871094</v>
       </c>
       <c r="C86" t="n">
-        <v>11.6122590026427</v>
+        <v>11.61225999957573</v>
       </c>
       <c r="D86" t="n">
-        <v>10.8984343118457</v>
+        <v>10.89843524749561</v>
       </c>
       <c r="E86" t="n">
-        <v>11.14407358134564</v>
+        <v>11.14407453808413</v>
       </c>
       <c r="F86" t="n">
         <v>2940293</v>
@@ -2152,16 +2152,16 @@
         <v>44355</v>
       </c>
       <c r="B87" t="n">
-        <v>11.0202054977417</v>
+        <v>11.02020454406738</v>
       </c>
       <c r="C87" t="n">
-        <v>11.16926884083993</v>
+        <v>11.16926787426587</v>
       </c>
       <c r="D87" t="n">
-        <v>10.93412604839051</v>
+        <v>10.9341251021654</v>
       </c>
       <c r="E87" t="n">
-        <v>11.1209800524548</v>
+        <v>11.12097909005958</v>
       </c>
       <c r="F87" t="n">
         <v>1135248</v>
@@ -2172,16 +2172,16 @@
         <v>44356</v>
       </c>
       <c r="B88" t="n">
-        <v>10.90893268585205</v>
+        <v>10.90893363952637</v>
       </c>
       <c r="C88" t="n">
-        <v>11.1251793334517</v>
+        <v>11.12518030603061</v>
       </c>
       <c r="D88" t="n">
-        <v>10.7325751877154</v>
+        <v>10.73257612597229</v>
       </c>
       <c r="E88" t="n">
-        <v>11.00340933714343</v>
+        <v>11.00341029907703</v>
       </c>
       <c r="F88" t="n">
         <v>1361892</v>
@@ -2212,16 +2212,16 @@
         <v>44358</v>
       </c>
       <c r="B90" t="n">
-        <v>10.60240650177002</v>
+        <v>10.60240745544434</v>
       </c>
       <c r="C90" t="n">
-        <v>10.84174787766967</v>
+        <v>10.84174885287247</v>
       </c>
       <c r="D90" t="n">
-        <v>10.51842717132385</v>
+        <v>10.51842811744432</v>
       </c>
       <c r="E90" t="n">
-        <v>10.7598678478309</v>
+        <v>10.75986881566868</v>
       </c>
       <c r="F90" t="n">
         <v>1174982</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462299346924</v>
+        <v>10.94462394714355</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192304724218</v>
+        <v>11.35192403640713</v>
       </c>
       <c r="D92" t="n">
-        <v>10.81445498526105</v>
+        <v>10.81445592759301</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152825044157</v>
+        <v>10.92152920210349</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2292,16 +2292,16 @@
         <v>44364</v>
       </c>
       <c r="B94" t="n">
-        <v>11.30573463439941</v>
+        <v>11.3057336807251</v>
       </c>
       <c r="C94" t="n">
-        <v>11.52408220658267</v>
+        <v>11.52408123449005</v>
       </c>
       <c r="D94" t="n">
-        <v>11.07689055849889</v>
+        <v>11.0768896241283</v>
       </c>
       <c r="E94" t="n">
-        <v>11.21125798299837</v>
+        <v>11.21125703729346</v>
       </c>
       <c r="F94" t="n">
         <v>2709189</v>
@@ -2312,16 +2312,16 @@
         <v>44365</v>
       </c>
       <c r="B95" t="n">
-        <v>11.33722686767578</v>
+        <v>11.3372278213501</v>
       </c>
       <c r="C95" t="n">
-        <v>11.33722686767578</v>
+        <v>11.3372278213501</v>
       </c>
       <c r="D95" t="n">
-        <v>10.99291071350208</v>
+        <v>10.99291163821293</v>
       </c>
       <c r="E95" t="n">
-        <v>11.31203282453744</v>
+        <v>11.31203377609247</v>
       </c>
       <c r="F95" t="n">
         <v>1275938</v>
@@ -2432,16 +2432,16 @@
         <v>44375</v>
       </c>
       <c r="B101" t="n">
-        <v>11.86209869384766</v>
+        <v>11.86209774017334</v>
       </c>
       <c r="C101" t="n">
-        <v>12.00066471799965</v>
+        <v>12.00066375318507</v>
       </c>
       <c r="D101" t="n">
-        <v>11.40441135990023</v>
+        <v>11.40441044302249</v>
       </c>
       <c r="E101" t="n">
-        <v>11.58916605876955</v>
+        <v>11.58916512703814</v>
       </c>
       <c r="F101" t="n">
         <v>1601511</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.01746082305908</v>
+        <v>12.01746273040771</v>
       </c>
       <c r="C102" t="n">
-        <v>12.01746082305908</v>
+        <v>12.01746273040771</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916534895242</v>
+        <v>11.58916718832423</v>
       </c>
       <c r="E102" t="n">
-        <v>11.85999866672677</v>
+        <v>11.86000054908383</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2472,16 +2472,16 @@
         <v>44377</v>
       </c>
       <c r="B103" t="n">
-        <v>11.88939094543457</v>
+        <v>11.88939189910889</v>
       </c>
       <c r="C103" t="n">
-        <v>12.16862308057641</v>
+        <v>12.16862405664855</v>
       </c>
       <c r="D103" t="n">
-        <v>11.85160028884888</v>
+        <v>11.85160123949193</v>
       </c>
       <c r="E103" t="n">
-        <v>12.02375835580161</v>
+        <v>12.02375932025384</v>
       </c>
       <c r="F103" t="n">
         <v>3669691</v>
@@ -2492,16 +2492,16 @@
         <v>44378</v>
       </c>
       <c r="B104" t="n">
-        <v>12.47094917297363</v>
+        <v>12.47095012664795</v>
       </c>
       <c r="C104" t="n">
-        <v>12.6347092370678</v>
+        <v>12.63471020326512</v>
       </c>
       <c r="D104" t="n">
-        <v>12.33028385156715</v>
+        <v>12.33028479448456</v>
       </c>
       <c r="E104" t="n">
-        <v>12.38906995272109</v>
+        <v>12.38907090013396</v>
       </c>
       <c r="F104" t="n">
         <v>8890212</v>
@@ -2512,16 +2512,16 @@
         <v>44379</v>
       </c>
       <c r="B105" t="n">
-        <v>12.95803165435791</v>
+        <v>12.95803070068359</v>
       </c>
       <c r="C105" t="n">
-        <v>13.12809044392446</v>
+        <v>13.1280894777343</v>
       </c>
       <c r="D105" t="n">
-        <v>12.50034348842697</v>
+        <v>12.5003425684372</v>
       </c>
       <c r="E105" t="n">
-        <v>12.52133812009879</v>
+        <v>12.52133719856387</v>
       </c>
       <c r="F105" t="n">
         <v>2908669</v>
@@ -2532,16 +2532,16 @@
         <v>44382</v>
       </c>
       <c r="B106" t="n">
-        <v>13.12179183959961</v>
+        <v>13.12178993225098</v>
       </c>
       <c r="C106" t="n">
-        <v>13.50179938445063</v>
+        <v>13.50179742186512</v>
       </c>
       <c r="D106" t="n">
-        <v>12.96432966535849</v>
+        <v>12.96432778089814</v>
       </c>
       <c r="E106" t="n">
-        <v>12.96432966535849</v>
+        <v>12.96432778089814</v>
       </c>
       <c r="F106" t="n">
         <v>1748688</v>
@@ -2592,16 +2592,16 @@
         <v>44385</v>
       </c>
       <c r="B109" t="n">
-        <v>13.05880641937256</v>
+        <v>13.05880546569824</v>
       </c>
       <c r="C109" t="n">
-        <v>13.61097121410255</v>
+        <v>13.61097022010407</v>
       </c>
       <c r="D109" t="n">
-        <v>13.00631903082418</v>
+        <v>13.00631808098297</v>
       </c>
       <c r="E109" t="n">
-        <v>13.09659626755859</v>
+        <v>13.09659531112451</v>
       </c>
       <c r="F109" t="n">
         <v>8587750</v>
@@ -2632,16 +2632,16 @@
         <v>44390</v>
       </c>
       <c r="B111" t="n">
-        <v>13.27295207977295</v>
+        <v>13.27295398712158</v>
       </c>
       <c r="C111" t="n">
-        <v>13.49759752224774</v>
+        <v>13.49759946187835</v>
       </c>
       <c r="D111" t="n">
-        <v>13.1343860734871</v>
+        <v>13.13438796092353</v>
       </c>
       <c r="E111" t="n">
-        <v>13.33173817479372</v>
+        <v>13.33174009059002</v>
       </c>
       <c r="F111" t="n">
         <v>2696620</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C114" t="n">
-        <v>13.9384904687512</v>
+        <v>13.93849142806081</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969768169454</v>
+        <v>13.49969861080446</v>
       </c>
       <c r="E114" t="n">
-        <v>13.64246310974914</v>
+        <v>13.64246404868482</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501433064608</v>
+        <v>14.24501531105205</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969768169454</v>
+        <v>13.49969861080446</v>
       </c>
       <c r="E115" t="n">
-        <v>13.7495355572011</v>
+        <v>13.74953650350598</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06656074523926</v>
+        <v>14.06655979156494</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103739980534</v>
+        <v>14.16103643972576</v>
       </c>
       <c r="D116" t="n">
-        <v>13.7747319546967</v>
+        <v>13.77473102080758</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059133128809</v>
+        <v>13.94059038615415</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801509857178</v>
+        <v>15.06801414489746</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127867222671</v>
+        <v>15.22127770885214</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92944987797833</v>
+        <v>14.92944893307399</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127867222671</v>
+        <v>15.22127770885214</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2812,16 +2812,16 @@
         <v>44403</v>
       </c>
       <c r="B120" t="n">
-        <v>14.87486171722412</v>
+        <v>14.87486362457275</v>
       </c>
       <c r="C120" t="n">
-        <v>15.17088908393575</v>
+        <v>15.17089102924288</v>
       </c>
       <c r="D120" t="n">
-        <v>14.64601846513237</v>
+        <v>14.64602034313728</v>
       </c>
       <c r="E120" t="n">
-        <v>15.07431313686146</v>
+        <v>15.07431506978501</v>
       </c>
       <c r="F120" t="n">
         <v>4655330</v>
@@ -2832,16 +2832,16 @@
         <v>44404</v>
       </c>
       <c r="B121" t="n">
-        <v>14.54944038391113</v>
+        <v>14.54944133758545</v>
       </c>
       <c r="C121" t="n">
-        <v>15.05961588037913</v>
+        <v>15.059616867494</v>
       </c>
       <c r="D121" t="n">
-        <v>14.45076513966624</v>
+        <v>14.45076608687268</v>
       </c>
       <c r="E121" t="n">
-        <v>14.87486119524679</v>
+        <v>14.87486217025152</v>
       </c>
       <c r="F121" t="n">
         <v>2070206</v>
@@ -2852,16 +2852,16 @@
         <v>44405</v>
       </c>
       <c r="B122" t="n">
-        <v>15.08691024780273</v>
+        <v>15.08691120147705</v>
       </c>
       <c r="C122" t="n">
-        <v>15.36824088059173</v>
+        <v>15.36824185204953</v>
       </c>
       <c r="D122" t="n">
-        <v>14.03716578503624</v>
+        <v>14.03716667235407</v>
       </c>
       <c r="E122" t="n">
-        <v>15.13519740853254</v>
+        <v>15.13519836525918</v>
       </c>
       <c r="F122" t="n">
         <v>6581198</v>
@@ -2892,16 +2892,16 @@
         <v>44407</v>
       </c>
       <c r="B124" t="n">
-        <v>15.45431709289551</v>
+        <v>15.45431804656982</v>
       </c>
       <c r="C124" t="n">
-        <v>15.94139861587127</v>
+        <v>15.94139959960302</v>
       </c>
       <c r="D124" t="n">
-        <v>14.96933649387961</v>
+        <v>14.96933741762614</v>
       </c>
       <c r="E124" t="n">
-        <v>15.28006054980113</v>
+        <v>15.28006149272221</v>
       </c>
       <c r="F124" t="n">
         <v>3070441</v>
@@ -2912,16 +2912,16 @@
         <v>44410</v>
       </c>
       <c r="B125" t="n">
-        <v>15.3178539276123</v>
+        <v>15.31785297393799</v>
       </c>
       <c r="C125" t="n">
-        <v>15.85742292658102</v>
+        <v>15.85742193931368</v>
       </c>
       <c r="D125" t="n">
-        <v>15.16879058605128</v>
+        <v>15.1687896416575</v>
       </c>
       <c r="E125" t="n">
-        <v>15.64327476758901</v>
+        <v>15.64327379365431</v>
       </c>
       <c r="F125" t="n">
         <v>3314925</v>
@@ -2932,16 +2932,16 @@
         <v>44411</v>
       </c>
       <c r="B126" t="n">
-        <v>15.20448112487793</v>
+        <v>15.20448207855225</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39343441755661</v>
+        <v>15.39343538308269</v>
       </c>
       <c r="D126" t="n">
-        <v>14.761489725604</v>
+        <v>14.76149065149246</v>
       </c>
       <c r="E126" t="n">
-        <v>15.39343441755661</v>
+        <v>15.39343538308269</v>
       </c>
       <c r="F126" t="n">
         <v>3496971</v>
@@ -2952,16 +2952,16 @@
         <v>44412</v>
       </c>
       <c r="B127" t="n">
-        <v>14.73839378356934</v>
+        <v>14.73839569091797</v>
       </c>
       <c r="C127" t="n">
-        <v>15.3220512984694</v>
+        <v>15.32205328135125</v>
       </c>
       <c r="D127" t="n">
-        <v>14.73839378356934</v>
+        <v>14.73839569091797</v>
       </c>
       <c r="E127" t="n">
-        <v>15.18768469649988</v>
+        <v>15.18768666199287</v>
       </c>
       <c r="F127" t="n">
         <v>2159810</v>
@@ -2972,16 +2972,16 @@
         <v>44413</v>
       </c>
       <c r="B128" t="n">
-        <v>14.17153358459473</v>
+        <v>14.17153453826904</v>
       </c>
       <c r="C128" t="n">
-        <v>14.82237357326046</v>
+        <v>14.82237457073309</v>
       </c>
       <c r="D128" t="n">
-        <v>14.17153358459473</v>
+        <v>14.17153453826904</v>
       </c>
       <c r="E128" t="n">
-        <v>14.61662426223638</v>
+        <v>14.61662524586311</v>
       </c>
       <c r="F128" t="n">
         <v>2928535</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.93639278411865</v>
+        <v>13.93639183044434</v>
       </c>
       <c r="C129" t="n">
-        <v>14.41927418649407</v>
+        <v>14.41927319977593</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373737671409</v>
+        <v>13.75373643553897</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153558284041</v>
+        <v>14.17153461307515</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06656074523926</v>
+        <v>14.06655979156494</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893809899156</v>
+        <v>14.15893713905431</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462191733692</v>
+        <v>13.81462098074336</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351724825013</v>
+        <v>13.83351631037553</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3032,16 +3032,16 @@
         <v>44418</v>
       </c>
       <c r="B131" t="n">
-        <v>13.64666271209717</v>
+        <v>13.64666175842285</v>
       </c>
       <c r="C131" t="n">
-        <v>14.43816890261326</v>
+        <v>14.43816789362585</v>
       </c>
       <c r="D131" t="n">
-        <v>13.56688278990252</v>
+        <v>13.56688184180349</v>
       </c>
       <c r="E131" t="n">
-        <v>14.05396277317898</v>
+        <v>14.05396179104118</v>
       </c>
       <c r="F131" t="n">
         <v>2933806</v>
@@ -3072,16 +3072,16 @@
         <v>44420</v>
       </c>
       <c r="B133" t="n">
-        <v>13.68025398254395</v>
+        <v>13.68025493621826</v>
       </c>
       <c r="C133" t="n">
-        <v>14.21142412135836</v>
+        <v>14.21142511206147</v>
       </c>
       <c r="D133" t="n">
-        <v>13.64666192558043</v>
+        <v>13.64666287691298</v>
       </c>
       <c r="E133" t="n">
-        <v>13.82511871345597</v>
+        <v>13.82511967722906</v>
       </c>
       <c r="F133" t="n">
         <v>1819641</v>
@@ -3092,16 +3092,16 @@
         <v>44421</v>
       </c>
       <c r="B134" t="n">
-        <v>12.95592975616455</v>
+        <v>12.95593070983887</v>
       </c>
       <c r="C134" t="n">
-        <v>13.76423189386945</v>
+        <v>13.76423290704215</v>
       </c>
       <c r="D134" t="n">
-        <v>12.78797191414345</v>
+        <v>12.78797285545454</v>
       </c>
       <c r="E134" t="n">
-        <v>13.57107919844318</v>
+        <v>13.5710801973981</v>
       </c>
       <c r="F134" t="n">
         <v>3730102</v>
@@ -3112,16 +3112,16 @@
         <v>44424</v>
       </c>
       <c r="B135" t="n">
-        <v>11.84110450744629</v>
+        <v>11.84110355377197</v>
       </c>
       <c r="C135" t="n">
-        <v>12.94963355405497</v>
+        <v>12.94963251110049</v>
       </c>
       <c r="D135" t="n">
-        <v>11.7655231844898</v>
+        <v>11.76552223690275</v>
       </c>
       <c r="E135" t="n">
-        <v>12.94963355405497</v>
+        <v>12.94963251110049</v>
       </c>
       <c r="F135" t="n">
         <v>7844263</v>
@@ -3192,16 +3192,16 @@
         <v>44428</v>
       </c>
       <c r="B139" t="n">
-        <v>13.52069282531738</v>
+        <v>13.5206937789917</v>
       </c>
       <c r="C139" t="n">
-        <v>13.70544751914833</v>
+        <v>13.70544848585422</v>
       </c>
       <c r="D139" t="n">
-        <v>12.6473066309372</v>
+        <v>12.64730752300772</v>
       </c>
       <c r="E139" t="n">
-        <v>12.8068672814836</v>
+        <v>12.80686818480864</v>
       </c>
       <c r="F139" t="n">
         <v>3576438</v>
@@ -3212,16 +3212,16 @@
         <v>44431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.49549865722656</v>
+        <v>13.49549770355225</v>
       </c>
       <c r="C140" t="n">
-        <v>14.19252897755238</v>
+        <v>14.19252797462165</v>
       </c>
       <c r="D140" t="n">
-        <v>13.26035669079564</v>
+        <v>13.26035575373789</v>
       </c>
       <c r="E140" t="n">
-        <v>13.72224342110149</v>
+        <v>13.72224245140401</v>
       </c>
       <c r="F140" t="n">
         <v>2675233</v>
@@ -3232,16 +3232,16 @@
         <v>44432</v>
       </c>
       <c r="B141" t="n">
-        <v>13.63826560974121</v>
+        <v>13.63826465606689</v>
       </c>
       <c r="C141" t="n">
-        <v>13.92379486531496</v>
+        <v>13.92379389167463</v>
       </c>
       <c r="D141" t="n">
-        <v>13.3779287749388</v>
+        <v>13.37792783946889</v>
       </c>
       <c r="E141" t="n">
-        <v>13.63826560974121</v>
+        <v>13.63826465606689</v>
       </c>
       <c r="F141" t="n">
         <v>2525015</v>
@@ -3272,16 +3272,16 @@
         <v>44434</v>
       </c>
       <c r="B143" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C143" t="n">
-        <v>13.76423335318433</v>
+        <v>13.76423235313817</v>
       </c>
       <c r="D143" t="n">
-        <v>12.82366381794241</v>
+        <v>12.82366288623372</v>
       </c>
       <c r="E143" t="n">
-        <v>13.47870409850207</v>
+        <v>13.47870311920116</v>
       </c>
       <c r="F143" t="n">
         <v>2624147</v>
@@ -3292,16 +3292,16 @@
         <v>44435</v>
       </c>
       <c r="B144" t="n">
-        <v>13.6886510848999</v>
+        <v>13.68865299224854</v>
       </c>
       <c r="C144" t="n">
-        <v>13.6886510848999</v>
+        <v>13.68865299224854</v>
       </c>
       <c r="D144" t="n">
-        <v>12.95803034564176</v>
+        <v>12.9580321511872</v>
       </c>
       <c r="E144" t="n">
-        <v>13.32753972236057</v>
+        <v>13.32754157939268</v>
       </c>
       <c r="F144" t="n">
         <v>2006349</v>
@@ -3312,16 +3312,16 @@
         <v>44438</v>
       </c>
       <c r="B145" t="n">
-        <v>13.34433746337891</v>
+        <v>13.34433650970459</v>
       </c>
       <c r="C145" t="n">
-        <v>14.09175432692212</v>
+        <v>14.09175331983246</v>
       </c>
       <c r="D145" t="n">
-        <v>13.24356209208586</v>
+        <v>13.24356114561362</v>
       </c>
       <c r="E145" t="n">
-        <v>13.68865284174995</v>
+        <v>13.68865186346858</v>
       </c>
       <c r="F145" t="n">
         <v>1186841</v>
@@ -3332,16 +3332,16 @@
         <v>44439</v>
       </c>
       <c r="B146" t="n">
-        <v>12.77327728271484</v>
+        <v>12.77327537536621</v>
       </c>
       <c r="C146" t="n">
-        <v>13.40312355555788</v>
+        <v>13.40312155415849</v>
       </c>
       <c r="D146" t="n">
-        <v>12.49614440311536</v>
+        <v>12.49614253714914</v>
       </c>
       <c r="E146" t="n">
-        <v>13.28555134208388</v>
+        <v>13.28554935824077</v>
       </c>
       <c r="F146" t="n">
         <v>2117441</v>
@@ -3352,16 +3352,16 @@
         <v>44440</v>
       </c>
       <c r="B147" t="n">
-        <v>13.06720352172852</v>
+        <v>13.06720447540283</v>
       </c>
       <c r="C147" t="n">
-        <v>13.2855494517287</v>
+        <v>13.2855504213384</v>
       </c>
       <c r="D147" t="n">
-        <v>12.56332673750791</v>
+        <v>12.56332765440814</v>
       </c>
       <c r="E147" t="n">
-        <v>13.09239756388817</v>
+        <v>13.0923985194012</v>
       </c>
       <c r="F147" t="n">
         <v>3411726</v>
@@ -3392,16 +3392,16 @@
         <v>44442</v>
       </c>
       <c r="B149" t="n">
-        <v>13.10079669952393</v>
+        <v>13.10079479217529</v>
       </c>
       <c r="C149" t="n">
-        <v>13.21836810182533</v>
+        <v>13.21836617735944</v>
       </c>
       <c r="D149" t="n">
-        <v>12.74808330441434</v>
+        <v>12.74808144841735</v>
       </c>
       <c r="E149" t="n">
-        <v>12.94963404784685</v>
+        <v>12.94963216250603</v>
       </c>
       <c r="F149" t="n">
         <v>3315331</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00001949529792</v>
+        <v>13.00002039001773</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113085479707</v>
+        <v>13.36113177437019</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3432,16 +3432,16 @@
         <v>44447</v>
       </c>
       <c r="B151" t="n">
-        <v>13.23516368865967</v>
+        <v>13.23516273498535</v>
       </c>
       <c r="C151" t="n">
-        <v>14.67961009363327</v>
+        <v>14.67960903587777</v>
       </c>
       <c r="D151" t="n">
-        <v>13.10079626027822</v>
+        <v>13.10079531628589</v>
       </c>
       <c r="E151" t="n">
-        <v>13.80622302684572</v>
+        <v>13.80622203202309</v>
       </c>
       <c r="F151" t="n">
         <v>4568970</v>
@@ -3452,16 +3452,16 @@
         <v>44448</v>
       </c>
       <c r="B152" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C152" t="n">
-        <v>13.3779287331694</v>
+        <v>13.37792776119036</v>
       </c>
       <c r="D152" t="n">
-        <v>12.52973573670498</v>
+        <v>12.52973482635177</v>
       </c>
       <c r="E152" t="n">
-        <v>13.2183672645125</v>
+        <v>13.21836630412647</v>
       </c>
       <c r="F152" t="n">
         <v>3739731</v>
@@ -3492,16 +3492,16 @@
         <v>44452</v>
       </c>
       <c r="B154" t="n">
-        <v>13.39472389221191</v>
+        <v>13.3947229385376</v>
       </c>
       <c r="C154" t="n">
-        <v>13.53748933072213</v>
+        <v>13.53748836688323</v>
       </c>
       <c r="D154" t="n">
-        <v>12.9748272149942</v>
+        <v>12.97482629121558</v>
       </c>
       <c r="E154" t="n">
-        <v>13.24356125077245</v>
+        <v>13.24356030786057</v>
       </c>
       <c r="F154" t="n">
         <v>1856739</v>
@@ -3532,16 +3532,16 @@
         <v>44454</v>
       </c>
       <c r="B156" t="n">
-        <v>13.44511127471924</v>
+        <v>13.44511222839355</v>
       </c>
       <c r="C156" t="n">
-        <v>14.07495666337775</v>
+        <v>14.07495766172759</v>
       </c>
       <c r="D156" t="n">
-        <v>13.2351625412349</v>
+        <v>13.23516348001735</v>
       </c>
       <c r="E156" t="n">
-        <v>13.47030450577353</v>
+        <v>13.47030546123482</v>
       </c>
       <c r="F156" t="n">
         <v>2602050</v>
@@ -3552,16 +3552,16 @@
         <v>44455</v>
       </c>
       <c r="B157" t="n">
-        <v>13.56268310546875</v>
+        <v>13.56268215179443</v>
       </c>
       <c r="C157" t="n">
-        <v>13.78942787491819</v>
+        <v>13.78942690530008</v>
       </c>
       <c r="D157" t="n">
-        <v>13.33593833601931</v>
+        <v>13.33593739828879</v>
       </c>
       <c r="E157" t="n">
-        <v>13.47870377169347</v>
+        <v>13.47870282392425</v>
       </c>
       <c r="F157" t="n">
         <v>1227183</v>
@@ -3572,16 +3572,16 @@
         <v>44456</v>
       </c>
       <c r="B158" t="n">
-        <v>13.44511127471924</v>
+        <v>13.44511222839355</v>
       </c>
       <c r="C158" t="n">
-        <v>13.74743816531587</v>
+        <v>13.74743914043451</v>
       </c>
       <c r="D158" t="n">
-        <v>13.29394782942092</v>
+        <v>13.29394877237308</v>
       </c>
       <c r="E158" t="n">
-        <v>13.40312201509908</v>
+        <v>13.40312296579506</v>
       </c>
       <c r="F158" t="n">
         <v>5378949</v>
@@ -3612,16 +3612,16 @@
         <v>44460</v>
       </c>
       <c r="B160" t="n">
-        <v>13.52069282531738</v>
+        <v>13.5206937789917</v>
       </c>
       <c r="C160" t="n">
-        <v>13.64666222994559</v>
+        <v>13.64666319250508</v>
       </c>
       <c r="D160" t="n">
-        <v>12.8068672814836</v>
+        <v>12.80686818480864</v>
       </c>
       <c r="E160" t="n">
-        <v>12.9832247726809</v>
+        <v>12.98322568844521</v>
       </c>
       <c r="F160" t="n">
         <v>1911981</v>
@@ -3632,16 +3632,16 @@
         <v>44461</v>
       </c>
       <c r="B161" t="n">
-        <v>14.10015201568604</v>
+        <v>14.10015106201172</v>
       </c>
       <c r="C161" t="n">
-        <v>14.46126420721415</v>
+        <v>14.46126322911574</v>
       </c>
       <c r="D161" t="n">
-        <v>13.58787718531884</v>
+        <v>13.58787626629261</v>
       </c>
       <c r="E161" t="n">
-        <v>13.71384659221444</v>
+        <v>13.71384566466818</v>
       </c>
       <c r="F161" t="n">
         <v>3751489</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.61242580413818</v>
+        <v>14.61242771148682</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630177220344</v>
+        <v>15.11630374532261</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893629636717</v>
+        <v>14.15893814452217</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19252835228931</v>
+        <v>14.19253020482906</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26810988418833</v>
+        <v>14.26811086618383</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141639771024</v>
+        <v>13.83141734965053</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733371488308</v>
+        <v>14.16733468994271</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3732,16 +3732,16 @@
         <v>44468</v>
       </c>
       <c r="B166" t="n">
-        <v>12.98322486877441</v>
+        <v>12.9832239151001</v>
       </c>
       <c r="C166" t="n">
-        <v>13.50389689640821</v>
+        <v>13.50389590448827</v>
       </c>
       <c r="D166" t="n">
-        <v>12.80686737627183</v>
+        <v>12.80686643555174</v>
       </c>
       <c r="E166" t="n">
-        <v>13.29394815773881</v>
+        <v>13.29394718124052</v>
       </c>
       <c r="F166" t="n">
         <v>4585796</v>
@@ -3772,16 +3772,16 @@
         <v>44470</v>
       </c>
       <c r="B168" t="n">
-        <v>12.7816743850708</v>
+        <v>12.78167343139648</v>
       </c>
       <c r="C168" t="n">
-        <v>13.11759336875031</v>
+        <v>13.1175923900122</v>
       </c>
       <c r="D168" t="n">
-        <v>12.00066546752786</v>
+        <v>12.00066457212668</v>
       </c>
       <c r="E168" t="n">
-        <v>12.65570578093424</v>
+        <v>12.65570483665877</v>
       </c>
       <c r="F168" t="n">
         <v>6332153</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498023986816</v>
+        <v>12.34498119354248</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366299139635</v>
+        <v>12.82366398204986</v>
       </c>
       <c r="D169" t="n">
-        <v>12.1350315079744</v>
+        <v>12.13503244542976</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288763255913</v>
+        <v>12.72288861542754</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3852,16 +3852,16 @@
         <v>44476</v>
       </c>
       <c r="B172" t="n">
-        <v>13.00001811981201</v>
+        <v>13.00002002716064</v>
       </c>
       <c r="C172" t="n">
-        <v>13.02521215947263</v>
+        <v>13.02521407051771</v>
       </c>
       <c r="D172" t="n">
-        <v>12.36177398584277</v>
+        <v>12.36177579954892</v>
       </c>
       <c r="E172" t="n">
-        <v>12.56332549133332</v>
+        <v>12.56332733461089</v>
       </c>
       <c r="F172" t="n">
         <v>3555051</v>
@@ -3872,16 +3872,16 @@
         <v>44477</v>
       </c>
       <c r="B173" t="n">
-        <v>13.05880641937256</v>
+        <v>13.05880546569824</v>
       </c>
       <c r="C173" t="n">
-        <v>13.38632574313576</v>
+        <v>13.38632476554297</v>
       </c>
       <c r="D173" t="n">
-        <v>12.89924495301617</v>
+        <v>12.8992440109945</v>
       </c>
       <c r="E173" t="n">
-        <v>13.11759252184922</v>
+        <v>13.1175915638818</v>
       </c>
       <c r="F173" t="n">
         <v>3251676</v>
@@ -3912,16 +3912,16 @@
         <v>44482</v>
       </c>
       <c r="B175" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C175" t="n">
-        <v>13.34433667412699</v>
+        <v>13.34433570458859</v>
       </c>
       <c r="D175" t="n">
-        <v>12.83206264449757</v>
+        <v>12.83206171217867</v>
       </c>
       <c r="E175" t="n">
-        <v>12.83206264449757</v>
+        <v>12.83206171217867</v>
       </c>
       <c r="F175" t="n">
         <v>2244954</v>
@@ -3952,16 +3952,16 @@
         <v>44484</v>
       </c>
       <c r="B177" t="n">
-        <v>13.41991806030273</v>
+        <v>13.41991901397705</v>
       </c>
       <c r="C177" t="n">
-        <v>13.48710217871359</v>
+        <v>13.48710313716229</v>
       </c>
       <c r="D177" t="n">
-        <v>13.0840007154267</v>
+        <v>13.08400164522936</v>
       </c>
       <c r="E177" t="n">
-        <v>13.24356137306336</v>
+        <v>13.24356231420505</v>
       </c>
       <c r="F177" t="n">
         <v>1650266</v>
@@ -3972,16 +3972,16 @@
         <v>44487</v>
       </c>
       <c r="B178" t="n">
-        <v>13.20157051086426</v>
+        <v>13.20156955718994</v>
       </c>
       <c r="C178" t="n">
-        <v>13.36952998506892</v>
+        <v>13.3695290192613</v>
       </c>
       <c r="D178" t="n">
-        <v>13.04200986275408</v>
+        <v>13.04200892060634</v>
       </c>
       <c r="E178" t="n">
-        <v>13.30234668246376</v>
+        <v>13.30234572150943</v>
       </c>
       <c r="F178" t="n">
         <v>1423013</v>
@@ -4012,16 +4012,16 @@
         <v>44489</v>
       </c>
       <c r="B180" t="n">
-        <v>11.9838695526123</v>
+        <v>11.98386859893799</v>
       </c>
       <c r="C180" t="n">
-        <v>12.58852173979385</v>
+        <v>12.58852073800141</v>
       </c>
       <c r="D180" t="n">
-        <v>11.87469617338831</v>
+        <v>11.874695228402</v>
       </c>
       <c r="E180" t="n">
-        <v>12.45415431648865</v>
+        <v>12.45415332538915</v>
       </c>
       <c r="F180" t="n">
         <v>2144403</v>
@@ -4032,16 +4032,16 @@
         <v>44490</v>
       </c>
       <c r="B181" t="n">
-        <v>11.24484920501709</v>
+        <v>11.24485015869141</v>
       </c>
       <c r="C181" t="n">
-        <v>11.95867472463081</v>
+        <v>11.95867573884459</v>
       </c>
       <c r="D181" t="n">
-        <v>10.83335057097093</v>
+        <v>10.8333514897461</v>
       </c>
       <c r="E181" t="n">
-        <v>11.84950135256322</v>
+        <v>11.84950235751801</v>
       </c>
       <c r="F181" t="n">
         <v>4870723</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.53102493286133</v>
+        <v>10.5310230255127</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174905758462</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624047415900147</v>
+        <v>9.624045672820648</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174905758462</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4092,16 +4092,16 @@
         <v>44495</v>
       </c>
       <c r="B184" t="n">
-        <v>9.985158920288086</v>
+        <v>9.98515796661377</v>
       </c>
       <c r="C184" t="n">
-        <v>10.46384172900696</v>
+        <v>10.46384072961404</v>
       </c>
       <c r="D184" t="n">
-        <v>9.825597442852056</v>
+        <v>9.825596504417325</v>
       </c>
       <c r="E184" t="n">
-        <v>10.46384172900696</v>
+        <v>10.46384072961404</v>
       </c>
       <c r="F184" t="n">
         <v>5760068</v>
@@ -4112,16 +4112,16 @@
         <v>44496</v>
       </c>
       <c r="B185" t="n">
-        <v>10.32947254180908</v>
+        <v>10.3294734954834</v>
       </c>
       <c r="C185" t="n">
-        <v>10.57301250649444</v>
+        <v>10.57301348265372</v>
       </c>
       <c r="D185" t="n">
-        <v>9.976759209577022</v>
+        <v>9.976760130686884</v>
       </c>
       <c r="E185" t="n">
-        <v>10.07753375153378</v>
+        <v>10.07753468194771</v>
       </c>
       <c r="F185" t="n">
         <v>4005501</v>
@@ -4172,16 +4172,16 @@
         <v>44501</v>
       </c>
       <c r="B188" t="n">
-        <v>9.464484214782715</v>
+        <v>9.464485168457031</v>
       </c>
       <c r="C188" t="n">
-        <v>9.817197539105118</v>
+        <v>9.817198528320054</v>
       </c>
       <c r="D188" t="n">
-        <v>9.002596713567389</v>
+        <v>9.002597620700316</v>
       </c>
       <c r="E188" t="n">
-        <v>9.22094344376433</v>
+        <v>9.220944372898632</v>
       </c>
       <c r="F188" t="n">
         <v>8542036</v>
@@ -4192,16 +4192,16 @@
         <v>44503</v>
       </c>
       <c r="B189" t="n">
-        <v>10.14472007751465</v>
+        <v>10.14471817016602</v>
       </c>
       <c r="C189" t="n">
-        <v>10.29588273525833</v>
+        <v>10.29588079948901</v>
       </c>
       <c r="D189" t="n">
-        <v>9.548465026785587</v>
+        <v>9.548463231541206</v>
       </c>
       <c r="E189" t="n">
-        <v>9.657639229970515</v>
+        <v>9.657637414199865</v>
       </c>
       <c r="F189" t="n">
         <v>6020061</v>
@@ -4252,16 +4252,16 @@
         <v>44508</v>
       </c>
       <c r="B192" t="n">
-        <v>10.58981037139893</v>
+        <v>10.58980941772461</v>
       </c>
       <c r="C192" t="n">
-        <v>10.82495234506</v>
+        <v>10.82495137020977</v>
       </c>
       <c r="D192" t="n">
-        <v>10.11112678587894</v>
+        <v>10.11112587531288</v>
       </c>
       <c r="E192" t="n">
-        <v>10.82495234506</v>
+        <v>10.82495137020977</v>
       </c>
       <c r="F192" t="n">
         <v>1684830</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.7493724822998</v>
+        <v>10.74937152862549</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324936814477</v>
+        <v>11.25324836976697</v>
       </c>
       <c r="D193" t="n">
-        <v>10.40505708385263</v>
+        <v>10.40505616072565</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660702639595</v>
+        <v>10.60660608538766</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4352,16 +4352,16 @@
         <v>44516</v>
       </c>
       <c r="B197" t="n">
-        <v>10.16991329193115</v>
+        <v>10.16991233825684</v>
       </c>
       <c r="C197" t="n">
-        <v>10.85854483462774</v>
+        <v>10.85854381637763</v>
       </c>
       <c r="D197" t="n">
-        <v>10.10272917239372</v>
+        <v>10.10272822501953</v>
       </c>
       <c r="E197" t="n">
-        <v>10.85854483462774</v>
+        <v>10.85854381637763</v>
       </c>
       <c r="F197" t="n">
         <v>2296952</v>
@@ -4372,16 +4372,16 @@
         <v>44517</v>
       </c>
       <c r="B198" t="n">
-        <v>10.10272979736328</v>
+        <v>10.10272789001465</v>
       </c>
       <c r="C198" t="n">
-        <v>10.35466863762478</v>
+        <v>10.35466668271126</v>
       </c>
       <c r="D198" t="n">
-        <v>9.800404487920888</v>
+        <v>9.800402637649874</v>
       </c>
       <c r="E198" t="n">
-        <v>10.29588252939294</v>
+        <v>10.29588058557796</v>
       </c>
       <c r="F198" t="n">
         <v>3557179</v>
@@ -4392,16 +4392,16 @@
         <v>44518</v>
       </c>
       <c r="B199" t="n">
-        <v>10.34626960754395</v>
+        <v>10.34627056121826</v>
       </c>
       <c r="C199" t="n">
-        <v>10.57301356738983</v>
+        <v>10.57301454196442</v>
       </c>
       <c r="D199" t="n">
-        <v>10.01035145740236</v>
+        <v>10.0103523801132</v>
       </c>
       <c r="E199" t="n">
-        <v>10.13632086517977</v>
+        <v>10.13632179950193</v>
       </c>
       <c r="F199" t="n">
         <v>2248603</v>
@@ -4432,16 +4432,16 @@
         <v>44522</v>
       </c>
       <c r="B201" t="n">
-        <v>10.22029876708984</v>
+        <v>10.22029972076416</v>
       </c>
       <c r="C201" t="n">
-        <v>10.92572621524449</v>
+        <v>10.9257272347435</v>
       </c>
       <c r="D201" t="n">
-        <v>10.19510553850158</v>
+        <v>10.19510648982507</v>
       </c>
       <c r="E201" t="n">
-        <v>10.79135881166451</v>
+        <v>10.79135981862546</v>
       </c>
       <c r="F201" t="n">
         <v>1734497</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674433708190918</v>
+        <v>9.674434661865234</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34626916814729</v>
+        <v>10.34627018804897</v>
       </c>
       <c r="D202" t="n">
-        <v>9.48128100330603</v>
+        <v>9.481281937939977</v>
       </c>
       <c r="E202" t="n">
-        <v>10.28748306817697</v>
+        <v>10.2874840822837</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4512,16 +4512,16 @@
         <v>44526</v>
       </c>
       <c r="B205" t="n">
-        <v>9.472882270812988</v>
+        <v>9.472883224487305</v>
       </c>
       <c r="C205" t="n">
-        <v>9.682831006334919</v>
+        <v>9.682831981145643</v>
       </c>
       <c r="D205" t="n">
-        <v>9.178954203441192</v>
+        <v>9.178955127524551</v>
       </c>
       <c r="E205" t="n">
-        <v>9.657637775036125</v>
+        <v>9.657638747310545</v>
       </c>
       <c r="F205" t="n">
         <v>2092506</v>
@@ -4532,16 +4532,16 @@
         <v>44529</v>
       </c>
       <c r="B206" t="n">
-        <v>9.632444381713867</v>
+        <v>9.632443428039551</v>
       </c>
       <c r="C206" t="n">
-        <v>9.909577250845725</v>
+        <v>9.909576269733462</v>
       </c>
       <c r="D206" t="n">
-        <v>9.456087691753288</v>
+        <v>9.456086755539426</v>
       </c>
       <c r="E206" t="n">
-        <v>9.741617764021505</v>
+        <v>9.741616799538319</v>
       </c>
       <c r="F206" t="n">
         <v>2527144</v>
@@ -4552,16 +4552,16 @@
         <v>44530</v>
       </c>
       <c r="B207" t="n">
-        <v>9.38890266418457</v>
+        <v>9.388903617858887</v>
       </c>
       <c r="C207" t="n">
-        <v>9.624046247712556</v>
+        <v>9.624047225271497</v>
       </c>
       <c r="D207" t="n">
-        <v>8.952209988986741</v>
+        <v>8.952210898304161</v>
       </c>
       <c r="E207" t="n">
-        <v>9.498076035932652</v>
+        <v>9.498077000696213</v>
       </c>
       <c r="F207" t="n">
         <v>4785579</v>
@@ -4612,16 +4612,16 @@
         <v>44533</v>
       </c>
       <c r="B210" t="n">
-        <v>9.901176452636719</v>
+        <v>9.901179313659668</v>
       </c>
       <c r="C210" t="n">
-        <v>10.08593193253503</v>
+        <v>10.08593484694453</v>
       </c>
       <c r="D210" t="n">
-        <v>9.615646437222118</v>
+        <v>9.61564921573892</v>
       </c>
       <c r="E210" t="n">
-        <v>9.64923849025716</v>
+        <v>9.64924127848065</v>
       </c>
       <c r="F210" t="n">
         <v>1913704</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884383201599121</v>
+        <v>9.884381294250488</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709658136135</v>
+        <v>10.23709460595107</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573658272883511</v>
+        <v>9.573656425494187</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867586359950231</v>
+        <v>9.867584455842815</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4652,16 +4652,16 @@
         <v>44537</v>
       </c>
       <c r="B212" t="n">
-        <v>9.985158920288086</v>
+        <v>9.98515796661377</v>
       </c>
       <c r="C212" t="n">
-        <v>10.53102503899367</v>
+        <v>10.53102403318413</v>
       </c>
       <c r="D212" t="n">
-        <v>9.867586707170773</v>
+        <v>9.867585764725682</v>
       </c>
       <c r="E212" t="n">
-        <v>10.00195413893881</v>
+        <v>10.00195318366039</v>
       </c>
       <c r="F212" t="n">
         <v>3095174</v>
@@ -4712,16 +4712,16 @@
         <v>44540</v>
       </c>
       <c r="B215" t="n">
-        <v>11.16609001159668</v>
+        <v>11.166090965271</v>
       </c>
       <c r="C215" t="n">
-        <v>11.32816433589571</v>
+        <v>11.32816530341248</v>
       </c>
       <c r="D215" t="n">
-        <v>10.86753230617741</v>
+        <v>10.86753323435248</v>
       </c>
       <c r="E215" t="n">
-        <v>11.01254600169058</v>
+        <v>11.012546942251</v>
       </c>
       <c r="F215" t="n">
         <v>3272354</v>
@@ -4752,16 +4752,16 @@
         <v>44544</v>
       </c>
       <c r="B217" t="n">
-        <v>11.11490917205811</v>
+        <v>11.11490821838379</v>
       </c>
       <c r="C217" t="n">
-        <v>11.43905865172065</v>
+        <v>11.43905767023386</v>
       </c>
       <c r="D217" t="n">
-        <v>10.91871358626455</v>
+        <v>10.91871264942408</v>
       </c>
       <c r="E217" t="n">
-        <v>11.25992369505407</v>
+        <v>11.25992272893731</v>
       </c>
       <c r="F217" t="n">
         <v>1511299</v>
@@ -4872,16 +4872,16 @@
         <v>44552</v>
       </c>
       <c r="B223" t="n">
-        <v>10.57750511169434</v>
+        <v>10.57750415802002</v>
       </c>
       <c r="C223" t="n">
-        <v>10.84194240965334</v>
+        <v>10.84194143213719</v>
       </c>
       <c r="D223" t="n">
-        <v>10.33865711021782</v>
+        <v>10.33865617807819</v>
       </c>
       <c r="E223" t="n">
-        <v>10.83341209443691</v>
+        <v>10.83341111768986</v>
       </c>
       <c r="F223" t="n">
         <v>1137579</v>
@@ -4892,16 +4892,16 @@
         <v>44553</v>
       </c>
       <c r="B224" t="n">
-        <v>10.38983917236328</v>
+        <v>10.38983821868896</v>
       </c>
       <c r="C224" t="n">
-        <v>10.65427645368369</v>
+        <v>10.6542754757369</v>
       </c>
       <c r="D224" t="n">
-        <v>10.19364275931372</v>
+        <v>10.1936418236481</v>
       </c>
       <c r="E224" t="n">
-        <v>10.56897413147012</v>
+        <v>10.56897316135316</v>
       </c>
       <c r="F224" t="n">
         <v>1383482</v>
@@ -4912,16 +4912,16 @@
         <v>44557</v>
       </c>
       <c r="B225" t="n">
-        <v>10.32159614562988</v>
+        <v>10.3215970993042</v>
       </c>
       <c r="C225" t="n">
-        <v>10.58603341390223</v>
+        <v>10.58603439200949</v>
       </c>
       <c r="D225" t="n">
-        <v>9.971855734769711</v>
+        <v>9.971856656129408</v>
       </c>
       <c r="E225" t="n">
-        <v>10.49220078163893</v>
+        <v>10.49220175107643</v>
       </c>
       <c r="F225" t="n">
         <v>1768251</v>
@@ -4952,16 +4952,16 @@
         <v>44559</v>
       </c>
       <c r="B227" t="n">
-        <v>9.715949058532715</v>
+        <v>9.715948104858398</v>
       </c>
       <c r="C227" t="n">
-        <v>10.21923349127314</v>
+        <v>10.21923248819867</v>
       </c>
       <c r="D227" t="n">
-        <v>9.596525480078773</v>
+        <v>9.596524538126543</v>
       </c>
       <c r="E227" t="n">
-        <v>10.21923349127314</v>
+        <v>10.21923248819867</v>
       </c>
       <c r="F227" t="n">
         <v>1535423</v>
@@ -5032,16 +5032,16 @@
         <v>44566</v>
       </c>
       <c r="B231" t="n">
-        <v>8.530244827270508</v>
+        <v>8.530243873596191</v>
       </c>
       <c r="C231" t="n">
-        <v>9.255315823119759</v>
+        <v>9.255314788383105</v>
       </c>
       <c r="D231" t="n">
-        <v>8.479063762352734</v>
+        <v>8.479062814400418</v>
       </c>
       <c r="E231" t="n">
-        <v>9.255315823119759</v>
+        <v>9.255314788383105</v>
       </c>
       <c r="F231" t="n">
         <v>5451524</v>
@@ -5112,16 +5112,16 @@
         <v>44572</v>
       </c>
       <c r="B235" t="n">
-        <v>8.71790885925293</v>
+        <v>8.717909812927246</v>
       </c>
       <c r="C235" t="n">
-        <v>8.914105249693064</v>
+        <v>8.914106224829805</v>
       </c>
       <c r="D235" t="n">
-        <v>8.530243607092713</v>
+        <v>8.530244540237847</v>
       </c>
       <c r="E235" t="n">
-        <v>8.530243607092713</v>
+        <v>8.530244540237847</v>
       </c>
       <c r="F235" t="n">
         <v>1168089</v>
@@ -5132,16 +5132,16 @@
         <v>44573</v>
       </c>
       <c r="B236" t="n">
-        <v>9.221193313598633</v>
+        <v>9.221194267272949</v>
       </c>
       <c r="C236" t="n">
-        <v>9.408859391749584</v>
+        <v>9.408860364832703</v>
       </c>
       <c r="D236" t="n">
-        <v>8.64113692537425</v>
+        <v>8.64113781905797</v>
       </c>
       <c r="E236" t="n">
-        <v>8.914105316548403</v>
+        <v>8.914106238463063</v>
       </c>
       <c r="F236" t="n">
         <v>2757539</v>
@@ -5152,16 +5152,16 @@
         <v>44574</v>
       </c>
       <c r="B237" t="n">
-        <v>8.726439476013184</v>
+        <v>8.7264404296875</v>
       </c>
       <c r="C237" t="n">
-        <v>9.110299446506351</v>
+        <v>9.110300442131042</v>
       </c>
       <c r="D237" t="n">
-        <v>8.555834036858977</v>
+        <v>8.555834971888574</v>
       </c>
       <c r="E237" t="n">
-        <v>9.042057765594588</v>
+        <v>9.042058753761445</v>
       </c>
       <c r="F237" t="n">
         <v>3017328</v>
@@ -5172,16 +5172,16 @@
         <v>44575</v>
       </c>
       <c r="B238" t="n">
-        <v>8.743500709533691</v>
+        <v>8.743499755859375</v>
       </c>
       <c r="C238" t="n">
-        <v>8.769091653284766</v>
+        <v>8.769090696819184</v>
       </c>
       <c r="D238" t="n">
-        <v>8.359640676184245</v>
+        <v>8.359639764378452</v>
       </c>
       <c r="E238" t="n">
-        <v>8.726440904949643</v>
+        <v>8.726439953136079</v>
       </c>
       <c r="F238" t="n">
         <v>2170250</v>
@@ -5252,16 +5252,16 @@
         <v>44581</v>
       </c>
       <c r="B242" t="n">
-        <v>9.383268356323242</v>
+        <v>9.383269309997559</v>
       </c>
       <c r="C242" t="n">
-        <v>9.6562359201754</v>
+        <v>9.656236901592942</v>
       </c>
       <c r="D242" t="n">
-        <v>8.530243585483291</v>
+        <v>8.530244452459904</v>
       </c>
       <c r="E242" t="n">
-        <v>8.581425467533645</v>
+        <v>8.581426339712161</v>
       </c>
       <c r="F242" t="n">
         <v>5361414</v>
@@ -5292,16 +5292,16 @@
         <v>44585</v>
       </c>
       <c r="B244" t="n">
-        <v>9.460041999816895</v>
+        <v>9.460041046142578</v>
       </c>
       <c r="C244" t="n">
-        <v>9.596526217767758</v>
+        <v>9.596525250334361</v>
       </c>
       <c r="D244" t="n">
-        <v>9.144422812706599</v>
+        <v>9.144421890850102</v>
       </c>
       <c r="E244" t="n">
-        <v>9.536814011659024</v>
+        <v>9.536813050245259</v>
       </c>
       <c r="F244" t="n">
         <v>1483323</v>
@@ -5312,16 +5312,16 @@
         <v>44586</v>
       </c>
       <c r="B245" t="n">
-        <v>9.843901634216309</v>
+        <v>9.843902587890625</v>
       </c>
       <c r="C245" t="n">
-        <v>9.929203943244776</v>
+        <v>9.929204905183155</v>
       </c>
       <c r="D245" t="n">
-        <v>9.383268011046082</v>
+        <v>9.383268920094348</v>
       </c>
       <c r="E245" t="n">
-        <v>9.391798324407251</v>
+        <v>9.391799234281931</v>
       </c>
       <c r="F245" t="n">
         <v>2635195</v>
@@ -5332,16 +5332,16 @@
         <v>44587</v>
       </c>
       <c r="B246" t="n">
-        <v>10.21070289611816</v>
+        <v>10.21070194244385</v>
       </c>
       <c r="C246" t="n">
-        <v>10.50073110748695</v>
+        <v>10.50073012672415</v>
       </c>
       <c r="D246" t="n">
-        <v>9.767129852505134</v>
+        <v>9.767128940260308</v>
       </c>
       <c r="E246" t="n">
-        <v>9.80978142384612</v>
+        <v>9.809780507617658</v>
       </c>
       <c r="F246" t="n">
         <v>3425105</v>
@@ -5412,16 +5412,16 @@
         <v>44593</v>
       </c>
       <c r="B250" t="n">
-        <v>10.62015533447266</v>
+        <v>10.62015438079834</v>
       </c>
       <c r="C250" t="n">
-        <v>10.68839702822328</v>
+        <v>10.68839606842096</v>
       </c>
       <c r="D250" t="n">
-        <v>10.33012710530333</v>
+        <v>10.33012617767312</v>
       </c>
       <c r="E250" t="n">
-        <v>10.65427659363964</v>
+        <v>10.65427563690129</v>
       </c>
       <c r="F250" t="n">
         <v>1255057</v>
@@ -5432,16 +5432,16 @@
         <v>44594</v>
       </c>
       <c r="B251" t="n">
-        <v>10.62015533447266</v>
+        <v>10.62015438079834</v>
       </c>
       <c r="C251" t="n">
-        <v>10.92724336864213</v>
+        <v>10.92724238739176</v>
       </c>
       <c r="D251" t="n">
-        <v>10.40689911384569</v>
+        <v>10.40689817932147</v>
       </c>
       <c r="E251" t="n">
-        <v>10.62015533447266</v>
+        <v>10.62015438079834</v>
       </c>
       <c r="F251" t="n">
         <v>1616614</v>
@@ -5472,16 +5472,16 @@
         <v>44596</v>
       </c>
       <c r="B253" t="n">
-        <v>10.25335502624512</v>
+        <v>10.2533540725708</v>
       </c>
       <c r="C253" t="n">
-        <v>10.56044305830264</v>
+        <v>10.56044207606577</v>
       </c>
       <c r="D253" t="n">
-        <v>9.835372078074196</v>
+        <v>9.835371163276871</v>
       </c>
       <c r="E253" t="n">
-        <v>10.56044305830264</v>
+        <v>10.56044207606577</v>
       </c>
       <c r="F253" t="n">
         <v>2130212</v>
@@ -5492,16 +5492,16 @@
         <v>44599</v>
       </c>
       <c r="B254" t="n">
-        <v>10.13393115997314</v>
+        <v>10.13392925262451</v>
       </c>
       <c r="C254" t="n">
-        <v>10.34718654856125</v>
+        <v>10.34718460107495</v>
       </c>
       <c r="D254" t="n">
-        <v>9.937734751205435</v>
+        <v>9.937732880783731</v>
       </c>
       <c r="E254" t="n">
-        <v>10.04862801503791</v>
+        <v>10.04862612374453</v>
       </c>
       <c r="F254" t="n">
         <v>1517482</v>
@@ -5512,16 +5512,16 @@
         <v>44600</v>
       </c>
       <c r="B255" t="n">
-        <v>10.05715751647949</v>
+        <v>10.05715656280518</v>
       </c>
       <c r="C255" t="n">
-        <v>10.27894485079779</v>
+        <v>10.2789438760924</v>
       </c>
       <c r="D255" t="n">
-        <v>9.912143006396347</v>
+        <v>9.912142066473093</v>
       </c>
       <c r="E255" t="n">
-        <v>10.21070234036655</v>
+        <v>10.21070137213227</v>
       </c>
       <c r="F255" t="n">
         <v>1782745</v>
@@ -5532,16 +5532,16 @@
         <v>44601</v>
       </c>
       <c r="B256" t="n">
-        <v>10.24482345581055</v>
+        <v>10.24482536315918</v>
       </c>
       <c r="C256" t="n">
-        <v>10.33012576810256</v>
+        <v>10.3301276913325</v>
       </c>
       <c r="D256" t="n">
-        <v>9.937733812226112</v>
+        <v>9.937735662401773</v>
       </c>
       <c r="E256" t="n">
-        <v>10.25335376949807</v>
+        <v>10.25335567843485</v>
       </c>
       <c r="F256" t="n">
         <v>1982123</v>
@@ -5592,16 +5592,16 @@
         <v>44606</v>
       </c>
       <c r="B259" t="n">
-        <v>10.57750511169434</v>
+        <v>10.57750415802002</v>
       </c>
       <c r="C259" t="n">
-        <v>10.65427712405877</v>
+        <v>10.65427616346264</v>
       </c>
       <c r="D259" t="n">
-        <v>9.767130938217694</v>
+        <v>9.767130057607208</v>
       </c>
       <c r="E259" t="n">
-        <v>9.775662078017515</v>
+        <v>9.775661196637856</v>
       </c>
       <c r="F259" t="n">
         <v>2873091</v>
@@ -5612,16 +5612,16 @@
         <v>44607</v>
       </c>
       <c r="B260" t="n">
-        <v>10.65427589416504</v>
+        <v>10.65427684783936</v>
       </c>
       <c r="C260" t="n">
-        <v>10.8675321007913</v>
+        <v>10.86753307355439</v>
       </c>
       <c r="D260" t="n">
-        <v>10.42395905907534</v>
+        <v>10.42395999213378</v>
       </c>
       <c r="E260" t="n">
-        <v>10.64574557993332</v>
+        <v>10.64574653284408</v>
       </c>
       <c r="F260" t="n">
         <v>2656887</v>
@@ -5632,16 +5632,16 @@
         <v>44608</v>
       </c>
       <c r="B261" t="n">
-        <v>10.56897258758545</v>
+        <v>10.56897354125977</v>
       </c>
       <c r="C261" t="n">
-        <v>10.69692563992313</v>
+        <v>10.69692660514308</v>
       </c>
       <c r="D261" t="n">
-        <v>10.38983765464612</v>
+        <v>10.38983859215648</v>
       </c>
       <c r="E261" t="n">
-        <v>10.66280438618869</v>
+        <v>10.66280534832977</v>
       </c>
       <c r="F261" t="n">
         <v>4241775</v>
@@ -5652,16 +5652,16 @@
         <v>44609</v>
       </c>
       <c r="B262" t="n">
-        <v>10.29600524902344</v>
+        <v>10.29600429534912</v>
       </c>
       <c r="C262" t="n">
-        <v>10.64574566145193</v>
+        <v>10.64574467538268</v>
       </c>
       <c r="D262" t="n">
-        <v>10.22776355923047</v>
+        <v>10.22776261187708</v>
       </c>
       <c r="E262" t="n">
-        <v>10.54338271447082</v>
+        <v>10.54338173788301</v>
       </c>
       <c r="F262" t="n">
         <v>3533562</v>
@@ -5692,16 +5692,16 @@
         <v>44613</v>
       </c>
       <c r="B264" t="n">
-        <v>9.383268356323242</v>
+        <v>9.383269309997559</v>
       </c>
       <c r="C264" t="n">
-        <v>10.1936415587879</v>
+        <v>10.193642594825</v>
       </c>
       <c r="D264" t="n">
-        <v>9.263845614038905</v>
+        <v>9.263846555575617</v>
       </c>
       <c r="E264" t="n">
-        <v>10.0656885028285</v>
+        <v>10.06568952586101</v>
       </c>
       <c r="F264" t="n">
         <v>2949517</v>
@@ -5712,16 +5712,16 @@
         <v>44614</v>
       </c>
       <c r="B265" t="n">
-        <v>9.733009338378906</v>
+        <v>9.73300838470459</v>
       </c>
       <c r="C265" t="n">
-        <v>9.843903432330309</v>
+        <v>9.843902467790201</v>
       </c>
       <c r="D265" t="n">
-        <v>9.391800039938824</v>
+        <v>9.391799119697389</v>
       </c>
       <c r="E265" t="n">
-        <v>9.545344059320188</v>
+        <v>9.545343124033971</v>
       </c>
       <c r="F265" t="n">
         <v>6936571</v>
@@ -5772,16 +5772,16 @@
         <v>44617</v>
       </c>
       <c r="B268" t="n">
-        <v>9.425919532775879</v>
+        <v>9.425920486450195</v>
       </c>
       <c r="C268" t="n">
-        <v>9.86949170251933</v>
+        <v>9.869492701072385</v>
       </c>
       <c r="D268" t="n">
-        <v>9.383267966174003</v>
+        <v>9.383268915533016</v>
       </c>
       <c r="E268" t="n">
-        <v>9.579463523376209</v>
+        <v>9.579464492585451</v>
       </c>
       <c r="F268" t="n">
         <v>3597927</v>
@@ -5792,16 +5792,16 @@
         <v>44622</v>
       </c>
       <c r="B269" t="n">
-        <v>9.570934295654297</v>
+        <v>9.57093334197998</v>
       </c>
       <c r="C269" t="n">
-        <v>9.656236613950387</v>
+        <v>9.656235651776313</v>
       </c>
       <c r="D269" t="n">
-        <v>9.272375769326324</v>
+        <v>9.272374845401204</v>
       </c>
       <c r="E269" t="n">
-        <v>9.349147773334476</v>
+        <v>9.34914684175958</v>
       </c>
       <c r="F269" t="n">
         <v>1474809</v>
@@ -5812,16 +5812,16 @@
         <v>44623</v>
       </c>
       <c r="B270" t="n">
-        <v>9.639176368713379</v>
+        <v>9.639177322387695</v>
       </c>
       <c r="C270" t="n">
-        <v>10.15952056895851</v>
+        <v>10.15952157411429</v>
       </c>
       <c r="D270" t="n">
-        <v>9.562404368219553</v>
+        <v>9.562405314298255</v>
       </c>
       <c r="E270" t="n">
-        <v>9.860962056297398</v>
+        <v>9.860963031914597</v>
       </c>
       <c r="F270" t="n">
         <v>3265562</v>
@@ -5832,16 +5832,16 @@
         <v>44624</v>
       </c>
       <c r="B271" t="n">
-        <v>9.323556900024414</v>
+        <v>9.323555946350098</v>
       </c>
       <c r="C271" t="n">
-        <v>9.613585938811369</v>
+        <v>9.613584955470987</v>
       </c>
       <c r="D271" t="n">
-        <v>8.931165738185172</v>
+        <v>8.931164824647187</v>
       </c>
       <c r="E271" t="n">
-        <v>9.511222166592459</v>
+        <v>9.511221193722513</v>
       </c>
       <c r="F271" t="n">
         <v>3245493</v>
@@ -5852,16 +5852,16 @@
         <v>44627</v>
       </c>
       <c r="B272" t="n">
-        <v>8.666728973388672</v>
+        <v>8.666728019714355</v>
       </c>
       <c r="C272" t="n">
-        <v>9.417390908101481</v>
+        <v>9.417389871825412</v>
       </c>
       <c r="D272" t="n">
-        <v>8.658198658538714</v>
+        <v>8.658197705803062</v>
       </c>
       <c r="E272" t="n">
-        <v>9.323557444751941</v>
+        <v>9.32355641880117</v>
       </c>
       <c r="F272" t="n">
         <v>2527651</v>
@@ -5872,16 +5872,16 @@
         <v>44628</v>
       </c>
       <c r="B273" t="n">
-        <v>8.89704418182373</v>
+        <v>8.897043228149414</v>
       </c>
       <c r="C273" t="n">
-        <v>8.92263512401856</v>
+        <v>8.922634167601151</v>
       </c>
       <c r="D273" t="n">
-        <v>8.521713661299355</v>
+        <v>8.521712747856723</v>
       </c>
       <c r="E273" t="n">
-        <v>8.726440374274713</v>
+        <v>8.726439438887422</v>
       </c>
       <c r="F273" t="n">
         <v>2260563</v>
@@ -5912,16 +5912,16 @@
         <v>44630</v>
       </c>
       <c r="B275" t="n">
-        <v>9.195603370666504</v>
+        <v>9.195605278015137</v>
       </c>
       <c r="C275" t="n">
-        <v>9.28090568530164</v>
+        <v>9.280907610343647</v>
       </c>
       <c r="D275" t="n">
-        <v>8.922634974334148</v>
+        <v>8.922636825063778</v>
       </c>
       <c r="E275" t="n">
-        <v>9.144421487135462</v>
+        <v>9.144423383867966</v>
       </c>
       <c r="F275" t="n">
         <v>2148356</v>
@@ -5952,16 +5952,16 @@
         <v>44634</v>
       </c>
       <c r="B277" t="n">
-        <v>8.76909065246582</v>
+        <v>8.769091606140137</v>
       </c>
       <c r="C277" t="n">
-        <v>8.879983904814196</v>
+        <v>8.879984870548604</v>
       </c>
       <c r="D277" t="n">
-        <v>8.572895088599443</v>
+        <v>8.572896020936692</v>
       </c>
       <c r="E277" t="n">
-        <v>8.624076970260189</v>
+        <v>8.624077908163676</v>
       </c>
       <c r="F277" t="n">
         <v>3142307</v>
@@ -6052,16 +6052,16 @@
         <v>44641</v>
       </c>
       <c r="B282" t="n">
-        <v>9.613585472106934</v>
+        <v>9.61358642578125</v>
       </c>
       <c r="C282" t="n">
-        <v>9.741539356585566</v>
+        <v>9.741540322952996</v>
       </c>
       <c r="D282" t="n">
-        <v>9.391798958899509</v>
+        <v>9.39179989057245</v>
       </c>
       <c r="E282" t="n">
-        <v>9.451511156461731</v>
+        <v>9.451512094058163</v>
       </c>
       <c r="F282" t="n">
         <v>1800179</v>
@@ -6072,16 +6072,16 @@
         <v>44642</v>
       </c>
       <c r="B283" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C283" t="n">
-        <v>10.12539894068065</v>
+        <v>10.1253999073854</v>
       </c>
       <c r="D283" t="n">
-        <v>9.570933505254049</v>
+        <v>9.57093441902218</v>
       </c>
       <c r="E283" t="n">
-        <v>9.570933505254049</v>
+        <v>9.57093441902218</v>
       </c>
       <c r="F283" t="n">
         <v>2594043</v>
@@ -6092,16 +6092,16 @@
         <v>44643</v>
       </c>
       <c r="B284" t="n">
-        <v>10.31306457519531</v>
+        <v>10.31306552886963</v>
       </c>
       <c r="C284" t="n">
-        <v>10.31306457519531</v>
+        <v>10.31306552886963</v>
       </c>
       <c r="D284" t="n">
-        <v>9.809781002488929</v>
+        <v>9.809781909623382</v>
       </c>
       <c r="E284" t="n">
-        <v>9.988916769843387</v>
+        <v>9.988917693542961</v>
       </c>
       <c r="F284" t="n">
         <v>2504946</v>
@@ -6112,16 +6112,16 @@
         <v>44644</v>
       </c>
       <c r="B285" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C285" t="n">
-        <v>10.66280605391772</v>
+        <v>10.66280508866036</v>
       </c>
       <c r="D285" t="n">
-        <v>10.11687085627847</v>
+        <v>10.11686994044226</v>
       </c>
       <c r="E285" t="n">
-        <v>10.27894601228337</v>
+        <v>10.27894508177519</v>
       </c>
       <c r="F285" t="n">
         <v>1712400</v>
@@ -6172,16 +6172,16 @@
         <v>44649</v>
       </c>
       <c r="B288" t="n">
-        <v>11.3452262878418</v>
+        <v>11.34522438049316</v>
       </c>
       <c r="C288" t="n">
-        <v>11.52436124879894</v>
+        <v>11.52435931133431</v>
       </c>
       <c r="D288" t="n">
-        <v>10.85047132964267</v>
+        <v>10.85046950547176</v>
       </c>
       <c r="E288" t="n">
-        <v>10.97842522657635</v>
+        <v>10.97842338089396</v>
       </c>
       <c r="F288" t="n">
         <v>4333811</v>
@@ -6192,16 +6192,16 @@
         <v>44650</v>
       </c>
       <c r="B289" t="n">
-        <v>11.16609001159668</v>
+        <v>11.166090965271</v>
       </c>
       <c r="C289" t="n">
-        <v>11.46464854159927</v>
+        <v>11.46464952077289</v>
       </c>
       <c r="D289" t="n">
-        <v>11.02107631608351</v>
+        <v>11.02107725737248</v>
       </c>
       <c r="E289" t="n">
-        <v>11.3537552790745</v>
+        <v>11.35375624877694</v>
       </c>
       <c r="F289" t="n">
         <v>2393651</v>
@@ -6292,16 +6292,16 @@
         <v>44657</v>
       </c>
       <c r="B294" t="n">
-        <v>10.57750511169434</v>
+        <v>10.57750415802002</v>
       </c>
       <c r="C294" t="n">
-        <v>10.7310491364232</v>
+        <v>10.73104816890526</v>
       </c>
       <c r="D294" t="n">
-        <v>10.21070403113823</v>
+        <v>10.21070311053493</v>
       </c>
       <c r="E294" t="n">
-        <v>10.7310491364232</v>
+        <v>10.73104816890526</v>
       </c>
       <c r="F294" t="n">
         <v>3552010</v>
@@ -6312,16 +6312,16 @@
         <v>44658</v>
       </c>
       <c r="B295" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C295" t="n">
-        <v>10.67133636868552</v>
+        <v>10.67133540265596</v>
       </c>
       <c r="D295" t="n">
-        <v>10.38130814033029</v>
+        <v>10.38130720055572</v>
       </c>
       <c r="E295" t="n">
-        <v>10.50073172249617</v>
+        <v>10.50073077191071</v>
       </c>
       <c r="F295" t="n">
         <v>1517584</v>
@@ -6332,16 +6332,16 @@
         <v>44659</v>
       </c>
       <c r="B296" t="n">
-        <v>10.3642463684082</v>
+        <v>10.36424732208252</v>
       </c>
       <c r="C296" t="n">
-        <v>10.53485182037612</v>
+        <v>10.53485278974883</v>
       </c>
       <c r="D296" t="n">
-        <v>10.17658193795169</v>
+        <v>10.17658287435791</v>
       </c>
       <c r="E296" t="n">
-        <v>10.53485182037612</v>
+        <v>10.53485278974883</v>
       </c>
       <c r="F296" t="n">
         <v>1523665</v>
@@ -6352,16 +6352,16 @@
         <v>44662</v>
       </c>
       <c r="B297" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C297" t="n">
-        <v>10.61162498989425</v>
+        <v>10.6116240292701</v>
       </c>
       <c r="D297" t="n">
-        <v>10.17658305965309</v>
+        <v>10.17658213841139</v>
       </c>
       <c r="E297" t="n">
-        <v>10.28747550246782</v>
+        <v>10.28747457118751</v>
       </c>
       <c r="F297" t="n">
         <v>2558465</v>
@@ -6412,16 +6412,16 @@
         <v>44665</v>
       </c>
       <c r="B300" t="n">
-        <v>10.80782032012939</v>
+        <v>10.80781936645508</v>
       </c>
       <c r="C300" t="n">
-        <v>10.850471068358</v>
+        <v>10.85047011092021</v>
       </c>
       <c r="D300" t="n">
-        <v>10.48367084050864</v>
+        <v>10.48366991543704</v>
       </c>
       <c r="E300" t="n">
-        <v>10.54338304244535</v>
+        <v>10.54338211210479</v>
       </c>
       <c r="F300" t="n">
         <v>1300569</v>
@@ -6452,16 +6452,16 @@
         <v>44670</v>
       </c>
       <c r="B302" t="n">
-        <v>10.94430351257324</v>
+        <v>10.94430446624756</v>
       </c>
       <c r="C302" t="n">
-        <v>11.07225656996439</v>
+        <v>11.07225753478839</v>
       </c>
       <c r="D302" t="n">
-        <v>10.4836698672987</v>
+        <v>10.48367078083392</v>
       </c>
       <c r="E302" t="n">
-        <v>10.68839574862444</v>
+        <v>10.68839667999924</v>
       </c>
       <c r="F302" t="n">
         <v>3002225</v>
@@ -6472,16 +6472,16 @@
         <v>44671</v>
       </c>
       <c r="B303" t="n">
-        <v>10.90165233612061</v>
+        <v>10.90165328979492</v>
       </c>
       <c r="C303" t="n">
-        <v>11.13196916704802</v>
+        <v>11.13197014087041</v>
       </c>
       <c r="D303" t="n">
-        <v>10.65427570162136</v>
+        <v>10.65427663365522</v>
       </c>
       <c r="E303" t="n">
-        <v>10.92724245376998</v>
+        <v>10.92724340968292</v>
       </c>
       <c r="F303" t="n">
         <v>2911811</v>
@@ -6492,16 +6492,16 @@
         <v>44673</v>
       </c>
       <c r="B304" t="n">
-        <v>10.37277793884277</v>
+        <v>10.37277603149414</v>
       </c>
       <c r="C304" t="n">
-        <v>10.83341164300124</v>
+        <v>10.83340965095118</v>
       </c>
       <c r="D304" t="n">
-        <v>10.30453624453844</v>
+        <v>10.30453434973811</v>
       </c>
       <c r="E304" t="n">
-        <v>10.7225183743921</v>
+        <v>10.72251640273312</v>
       </c>
       <c r="F304" t="n">
         <v>1699122</v>
@@ -6512,16 +6512,16 @@
         <v>44676</v>
       </c>
       <c r="B305" t="n">
-        <v>10.37277793884277</v>
+        <v>10.37277603149414</v>
       </c>
       <c r="C305" t="n">
-        <v>10.4324901428695</v>
+        <v>10.43248822454098</v>
       </c>
       <c r="D305" t="n">
-        <v>10.1509914016245</v>
+        <v>10.15098953505802</v>
       </c>
       <c r="E305" t="n">
-        <v>10.18511266106835</v>
+        <v>10.18511078822764</v>
       </c>
       <c r="F305" t="n">
         <v>3255528</v>
@@ -6532,16 +6532,16 @@
         <v>44677</v>
       </c>
       <c r="B306" t="n">
-        <v>10.38983917236328</v>
+        <v>10.38983821868896</v>
       </c>
       <c r="C306" t="n">
-        <v>10.4836709846732</v>
+        <v>10.48367002238615</v>
       </c>
       <c r="D306" t="n">
-        <v>10.16805181527464</v>
+        <v>10.168050881958</v>
       </c>
       <c r="E306" t="n">
-        <v>10.32159665492575</v>
+        <v>10.32159570751536</v>
       </c>
       <c r="F306" t="n">
         <v>4697699</v>
@@ -6572,16 +6572,16 @@
         <v>44679</v>
       </c>
       <c r="B308" t="n">
-        <v>11.68643474578857</v>
+        <v>11.68643379211426</v>
       </c>
       <c r="C308" t="n">
-        <v>11.89969095059006</v>
+        <v>11.89968997951292</v>
       </c>
       <c r="D308" t="n">
-        <v>10.44101959819782</v>
+        <v>10.4410187461559</v>
       </c>
       <c r="E308" t="n">
-        <v>10.81635012284846</v>
+        <v>10.81634924017761</v>
       </c>
       <c r="F308" t="n">
         <v>5881398</v>
@@ -6592,16 +6592,16 @@
         <v>44680</v>
       </c>
       <c r="B309" t="n">
-        <v>11.65231418609619</v>
+        <v>11.65231323242188</v>
       </c>
       <c r="C309" t="n">
-        <v>11.85704091356727</v>
+        <v>11.85703994313725</v>
       </c>
       <c r="D309" t="n">
-        <v>11.46464891254633</v>
+        <v>11.46464797423132</v>
       </c>
       <c r="E309" t="n">
-        <v>11.68643544477193</v>
+        <v>11.68643448830498</v>
       </c>
       <c r="F309" t="n">
         <v>6890958</v>
@@ -6692,16 +6692,16 @@
         <v>44687</v>
       </c>
       <c r="B314" t="n">
-        <v>11.52435970306396</v>
+        <v>11.52436065673828</v>
       </c>
       <c r="C314" t="n">
-        <v>11.61819232834089</v>
+        <v>11.61819328978013</v>
       </c>
       <c r="D314" t="n">
-        <v>11.20874057273858</v>
+        <v>11.20874150029449</v>
       </c>
       <c r="E314" t="n">
-        <v>11.60966201471724</v>
+        <v>11.60966297545057</v>
       </c>
       <c r="F314" t="n">
         <v>3256744</v>
@@ -6732,16 +6732,16 @@
         <v>44691</v>
       </c>
       <c r="B316" t="n">
-        <v>11.22580242156982</v>
+        <v>11.22580146789551</v>
       </c>
       <c r="C316" t="n">
-        <v>11.4049382025767</v>
+        <v>11.40493723368412</v>
       </c>
       <c r="D316" t="n">
-        <v>11.02107652149054</v>
+        <v>11.02107558520846</v>
       </c>
       <c r="E316" t="n">
-        <v>11.11490915697827</v>
+        <v>11.11490821272475</v>
       </c>
       <c r="F316" t="n">
         <v>2926103</v>
@@ -6792,16 +6792,16 @@
         <v>44694</v>
       </c>
       <c r="B319" t="n">
-        <v>11.82291984558105</v>
+        <v>11.82291889190674</v>
       </c>
       <c r="C319" t="n">
-        <v>12.07882681602652</v>
+        <v>12.07882584170994</v>
       </c>
       <c r="D319" t="n">
-        <v>11.45611960723421</v>
+        <v>11.45611868314717</v>
       </c>
       <c r="E319" t="n">
-        <v>11.53289161590952</v>
+        <v>11.5328906856298</v>
       </c>
       <c r="F319" t="n">
         <v>2912723</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381214141846</v>
+        <v>11.93381118774414</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470540028707</v>
+        <v>12.04470443775087</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908542732132</v>
+        <v>11.72908449000746</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81438856843816</v>
+        <v>11.81438762430742</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415687561035</v>
+        <v>12.45415878295898</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505013177474</v>
+        <v>12.56505205610663</v>
       </c>
       <c r="D323" t="n">
-        <v>11.9508724782104</v>
+        <v>11.95087430848125</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559753814858</v>
+        <v>12.15559939977298</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6972,16 +6972,16 @@
         <v>44707</v>
       </c>
       <c r="B328" t="n">
-        <v>12.70153331756592</v>
+        <v>12.70153427124023</v>
       </c>
       <c r="C328" t="n">
-        <v>12.92331982662067</v>
+        <v>12.92332079694747</v>
       </c>
       <c r="D328" t="n">
-        <v>12.38591500612253</v>
+        <v>12.38591593609915</v>
       </c>
       <c r="E328" t="n">
-        <v>12.42003626123349</v>
+        <v>12.42003719377205</v>
       </c>
       <c r="F328" t="n">
         <v>2007160</v>
@@ -7052,16 +7052,16 @@
         <v>44713</v>
       </c>
       <c r="B332" t="n">
-        <v>12.69300365447998</v>
+        <v>12.69300270080566</v>
       </c>
       <c r="C332" t="n">
-        <v>12.71006510749335</v>
+        <v>12.71006415253714</v>
       </c>
       <c r="D332" t="n">
-        <v>12.23237080978446</v>
+        <v>12.23236989071926</v>
       </c>
       <c r="E332" t="n">
-        <v>12.52239901934583</v>
+        <v>12.5223980784897</v>
       </c>
       <c r="F332" t="n">
         <v>4014218</v>
@@ -7212,16 +7212,16 @@
         <v>44725</v>
       </c>
       <c r="B340" t="n">
-        <v>10.72251796722412</v>
+        <v>10.7225170135498</v>
       </c>
       <c r="C340" t="n">
-        <v>11.507300307965</v>
+        <v>11.50729928449115</v>
       </c>
       <c r="D340" t="n">
-        <v>10.57750426926113</v>
+        <v>10.57750332848451</v>
       </c>
       <c r="E340" t="n">
-        <v>11.23433271652977</v>
+        <v>11.234331717334</v>
       </c>
       <c r="F340" t="n">
         <v>3958469</v>
@@ -7232,16 +7232,16 @@
         <v>44726</v>
       </c>
       <c r="B341" t="n">
-        <v>10.69692707061768</v>
+        <v>10.69692611694336</v>
       </c>
       <c r="C341" t="n">
-        <v>10.94430454411216</v>
+        <v>10.94430356838314</v>
       </c>
       <c r="D341" t="n">
-        <v>10.57750431574103</v>
+        <v>10.57750337271373</v>
       </c>
       <c r="E341" t="n">
-        <v>10.79076053093742</v>
+        <v>10.79075956889747</v>
       </c>
       <c r="F341" t="n">
         <v>2253062</v>
@@ -7252,16 +7252,16 @@
         <v>44727</v>
       </c>
       <c r="B342" t="n">
-        <v>10.83341121673584</v>
+        <v>10.83340930938721</v>
       </c>
       <c r="C342" t="n">
-        <v>11.07225754969472</v>
+        <v>11.0722556002944</v>
       </c>
       <c r="D342" t="n">
-        <v>10.67133606533815</v>
+        <v>10.67133418652475</v>
       </c>
       <c r="E342" t="n">
-        <v>10.88459227930441</v>
+        <v>10.88459036294475</v>
       </c>
       <c r="F342" t="n">
         <v>3158221</v>
@@ -7272,16 +7272,16 @@
         <v>44729</v>
       </c>
       <c r="B343" t="n">
-        <v>10.66280555725098</v>
+        <v>10.66280460357666</v>
       </c>
       <c r="C343" t="n">
-        <v>10.69692681473284</v>
+        <v>10.69692585800674</v>
       </c>
       <c r="D343" t="n">
-        <v>10.2960053376542</v>
+        <v>10.29600441678626</v>
       </c>
       <c r="E343" t="n">
-        <v>10.69692681473284</v>
+        <v>10.69692585800674</v>
       </c>
       <c r="F343" t="n">
         <v>2862346</v>
@@ -7312,16 +7312,16 @@
         <v>44733</v>
       </c>
       <c r="B345" t="n">
-        <v>10.46660995483398</v>
+        <v>10.4666109085083</v>
       </c>
       <c r="C345" t="n">
-        <v>10.65427520665525</v>
+        <v>10.65427617742885</v>
       </c>
       <c r="D345" t="n">
-        <v>10.33012576051704</v>
+        <v>10.33012670175548</v>
       </c>
       <c r="E345" t="n">
-        <v>10.43248870010894</v>
+        <v>10.43248965067427</v>
       </c>
       <c r="F345" t="n">
         <v>1967020</v>
@@ -7332,16 +7332,16 @@
         <v>44734</v>
       </c>
       <c r="B346" t="n">
-        <v>10.5604419708252</v>
+        <v>10.56044292449951</v>
       </c>
       <c r="C346" t="n">
-        <v>10.77369816802514</v>
+        <v>10.77369914095784</v>
       </c>
       <c r="D346" t="n">
-        <v>10.33012597049919</v>
+        <v>10.33012690337453</v>
       </c>
       <c r="E346" t="n">
-        <v>10.42395859831718</v>
+        <v>10.42395953966619</v>
       </c>
       <c r="F346" t="n">
         <v>1465281</v>
@@ -7352,16 +7352,16 @@
         <v>44735</v>
       </c>
       <c r="B347" t="n">
-        <v>10.80782032012939</v>
+        <v>10.80781936645508</v>
       </c>
       <c r="C347" t="n">
-        <v>10.91018327029472</v>
+        <v>10.91018230758797</v>
       </c>
       <c r="D347" t="n">
-        <v>10.48367084050864</v>
+        <v>10.48366991543704</v>
       </c>
       <c r="E347" t="n">
-        <v>10.49220115507102</v>
+        <v>10.49220022924672</v>
       </c>
       <c r="F347" t="n">
         <v>2364459</v>
@@ -7372,16 +7372,16 @@
         <v>44736</v>
       </c>
       <c r="B348" t="n">
-        <v>10.62015533447266</v>
+        <v>10.62015438079834</v>
       </c>
       <c r="C348" t="n">
-        <v>10.91871387843373</v>
+        <v>10.9187128979493</v>
       </c>
       <c r="D348" t="n">
-        <v>10.48367112238806</v>
+        <v>10.48367018096983</v>
       </c>
       <c r="E348" t="n">
-        <v>10.91871387843373</v>
+        <v>10.9187128979493</v>
       </c>
       <c r="F348" t="n">
         <v>1300163</v>
@@ -7412,16 +7412,16 @@
         <v>44740</v>
       </c>
       <c r="B350" t="n">
-        <v>10.23629188537598</v>
+        <v>10.23629379272461</v>
       </c>
       <c r="C350" t="n">
-        <v>10.81634906872219</v>
+        <v>10.81635108415403</v>
       </c>
       <c r="D350" t="n">
-        <v>10.18511082999487</v>
+        <v>10.18511272780684</v>
       </c>
       <c r="E350" t="n">
-        <v>10.70545582004938</v>
+        <v>10.70545781481826</v>
       </c>
       <c r="F350" t="n">
         <v>2763519</v>
@@ -7432,16 +7432,16 @@
         <v>44741</v>
       </c>
       <c r="B351" t="n">
-        <v>10.16805076599121</v>
+        <v>10.16805171966553</v>
       </c>
       <c r="C351" t="n">
-        <v>10.33865539281295</v>
+        <v>10.33865636248849</v>
       </c>
       <c r="D351" t="n">
-        <v>10.03156739436712</v>
+        <v>10.03156833524049</v>
       </c>
       <c r="E351" t="n">
-        <v>10.32159558979739</v>
+        <v>10.32159655787287</v>
       </c>
       <c r="F351" t="n">
         <v>1480384</v>
@@ -7452,16 +7452,16 @@
         <v>44742</v>
       </c>
       <c r="B352" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C352" t="n">
-        <v>10.12539894068065</v>
+        <v>10.1253999073854</v>
       </c>
       <c r="D352" t="n">
-        <v>9.724477500590167</v>
+        <v>9.724478429017642</v>
       </c>
       <c r="E352" t="n">
-        <v>9.971854945344536</v>
+        <v>9.97185589738994</v>
       </c>
       <c r="F352" t="n">
         <v>3400779</v>
@@ -7492,16 +7492,16 @@
         <v>44746</v>
       </c>
       <c r="B354" t="n">
-        <v>9.656235694885254</v>
+        <v>9.656237602233887</v>
       </c>
       <c r="C354" t="n">
-        <v>10.02303587602198</v>
+        <v>10.02303785582285</v>
       </c>
       <c r="D354" t="n">
-        <v>9.656235694885254</v>
+        <v>9.656237602233887</v>
       </c>
       <c r="E354" t="n">
-        <v>9.920673763475978</v>
+        <v>9.920675723057759</v>
       </c>
       <c r="F354" t="n">
         <v>1779400</v>
@@ -7532,16 +7532,16 @@
         <v>44748</v>
       </c>
       <c r="B356" t="n">
-        <v>9.647706985473633</v>
+        <v>9.647706031799316</v>
       </c>
       <c r="C356" t="n">
-        <v>9.869493523559241</v>
+        <v>9.869492547961359</v>
       </c>
       <c r="D356" t="n">
-        <v>9.400330327288428</v>
+        <v>9.400329398067255</v>
       </c>
       <c r="E356" t="n">
-        <v>9.681828245050916</v>
+        <v>9.681827288003719</v>
       </c>
       <c r="F356" t="n">
         <v>2475348</v>
@@ -7552,16 +7552,16 @@
         <v>44749</v>
       </c>
       <c r="B357" t="n">
-        <v>9.912143707275391</v>
+        <v>9.912142753601074</v>
       </c>
       <c r="C357" t="n">
-        <v>10.11687042846193</v>
+        <v>10.1168694550903</v>
       </c>
       <c r="D357" t="n">
-        <v>9.630646630175109</v>
+        <v>9.630645703584392</v>
       </c>
       <c r="E357" t="n">
-        <v>9.647706434405947</v>
+        <v>9.647705506173859</v>
       </c>
       <c r="F357" t="n">
         <v>2588468</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.110301971435547</v>
+        <v>9.11030101776123</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707419937092304</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076181533814751</v>
+        <v>9.076180583712192</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707419937092304</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7612,16 +7612,16 @@
         <v>44754</v>
       </c>
       <c r="B360" t="n">
-        <v>9.22972583770752</v>
+        <v>9.229723930358887</v>
       </c>
       <c r="C360" t="n">
-        <v>9.289437218413942</v>
+        <v>9.289435298725786</v>
       </c>
       <c r="D360" t="n">
-        <v>8.879985394760249</v>
+        <v>8.879983559686456</v>
       </c>
       <c r="E360" t="n">
-        <v>9.22972583770752</v>
+        <v>9.229723930358887</v>
       </c>
       <c r="F360" t="n">
         <v>1719496</v>
@@ -7652,16 +7652,16 @@
         <v>44756</v>
       </c>
       <c r="B362" t="n">
-        <v>9.383268356323242</v>
+        <v>9.383269309997559</v>
       </c>
       <c r="C362" t="n">
-        <v>9.485631295840706</v>
+        <v>9.485632259918743</v>
       </c>
       <c r="D362" t="n">
-        <v>9.06764922409579</v>
+        <v>9.067650145691958</v>
       </c>
       <c r="E362" t="n">
-        <v>9.204133418313491</v>
+        <v>9.204134353781315</v>
       </c>
       <c r="F362" t="n">
         <v>823562</v>
@@ -7672,16 +7672,16 @@
         <v>44757</v>
       </c>
       <c r="B363" t="n">
-        <v>9.297965049743652</v>
+        <v>9.297966003417969</v>
       </c>
       <c r="C363" t="n">
-        <v>9.451510693090178</v>
+        <v>9.451511662513374</v>
       </c>
       <c r="D363" t="n">
-        <v>9.263845444833107</v>
+        <v>9.263846395007841</v>
       </c>
       <c r="E363" t="n">
-        <v>9.374738696000145</v>
+        <v>9.374739657548986</v>
       </c>
       <c r="F363" t="n">
         <v>1899514</v>
@@ -7692,16 +7692,16 @@
         <v>44760</v>
       </c>
       <c r="B364" t="n">
-        <v>9.511221885681152</v>
+        <v>9.511222839355469</v>
       </c>
       <c r="C364" t="n">
-        <v>9.698887146706557</v>
+        <v>9.698888119197754</v>
       </c>
       <c r="D364" t="n">
-        <v>9.212664190527063</v>
+        <v>9.212665114265498</v>
       </c>
       <c r="E364" t="n">
-        <v>9.212664190527063</v>
+        <v>9.212665114265498</v>
       </c>
       <c r="F364" t="n">
         <v>1476836</v>
@@ -7812,16 +7812,16 @@
         <v>44768</v>
       </c>
       <c r="B370" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C370" t="n">
-        <v>10.40689763976893</v>
+        <v>10.40689863334928</v>
       </c>
       <c r="D370" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="E370" t="n">
-        <v>10.22776270368238</v>
+        <v>10.22776368016013</v>
       </c>
       <c r="F370" t="n">
         <v>1502988</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.50926113128662</v>
+        <v>10.50926208496094</v>
       </c>
       <c r="C371" t="n">
-        <v>10.61162407509244</v>
+        <v>10.6116250380558</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421841396606</v>
+        <v>10.07421932816195</v>
       </c>
       <c r="E371" t="n">
-        <v>10.12539947357733</v>
+        <v>10.1254003924177</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7872,16 +7872,16 @@
         <v>44771</v>
       </c>
       <c r="B373" t="n">
-        <v>11.60113334655762</v>
+        <v>11.6011323928833</v>
       </c>
       <c r="C373" t="n">
-        <v>11.60113334655762</v>
+        <v>11.6011323928833</v>
       </c>
       <c r="D373" t="n">
-        <v>10.81635097853681</v>
+        <v>10.81635008937574</v>
       </c>
       <c r="E373" t="n">
-        <v>10.98695562604133</v>
+        <v>10.98695472285566</v>
       </c>
       <c r="F373" t="n">
         <v>3378580</v>
@@ -7932,16 +7932,16 @@
         <v>44776</v>
       </c>
       <c r="B376" t="n">
-        <v>11.59260272979736</v>
+        <v>11.59260177612305</v>
       </c>
       <c r="C376" t="n">
-        <v>11.59260272979736</v>
+        <v>11.59260177612305</v>
       </c>
       <c r="D376" t="n">
-        <v>11.16609029756113</v>
+        <v>11.16608937897419</v>
       </c>
       <c r="E376" t="n">
-        <v>11.37934651367925</v>
+        <v>11.37934557754862</v>
       </c>
       <c r="F376" t="n">
         <v>1856232</v>
@@ -7952,16 +7952,16 @@
         <v>44777</v>
       </c>
       <c r="B377" t="n">
-        <v>12.6247615814209</v>
+        <v>12.62476253509521</v>
       </c>
       <c r="C377" t="n">
-        <v>12.6844737791103</v>
+        <v>12.68447473729527</v>
       </c>
       <c r="D377" t="n">
-        <v>11.54141995488882</v>
+        <v>11.54142082672753</v>
       </c>
       <c r="E377" t="n">
-        <v>11.55848140738335</v>
+        <v>11.55848228051088</v>
       </c>
       <c r="F377" t="n">
         <v>5052363</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.16216850280762</v>
+        <v>13.1621675491333</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718220482493</v>
+        <v>13.30718124064354</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271669191557</v>
+        <v>12.75271576790837</v>
       </c>
       <c r="E379" t="n">
-        <v>12.79536744120987</v>
+        <v>12.79536651411238</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8012,16 +8012,16 @@
         <v>44782</v>
       </c>
       <c r="B380" t="n">
-        <v>13.09392547607422</v>
+        <v>13.0939245223999</v>
       </c>
       <c r="C380" t="n">
-        <v>13.34983326023473</v>
+        <v>13.34983228792179</v>
       </c>
       <c r="D380" t="n">
-        <v>12.92332083635609</v>
+        <v>12.92331989510748</v>
       </c>
       <c r="E380" t="n">
-        <v>13.34130294579049</v>
+        <v>13.34130197409885</v>
       </c>
       <c r="F380" t="n">
         <v>4116999</v>
@@ -8072,16 +8072,16 @@
         <v>44785</v>
       </c>
       <c r="B383" t="n">
-        <v>13.75928401947021</v>
+        <v>13.75928497314453</v>
       </c>
       <c r="C383" t="n">
-        <v>13.84458633290799</v>
+        <v>13.84458729249473</v>
       </c>
       <c r="D383" t="n">
-        <v>13.47778613775057</v>
+        <v>13.47778707191389</v>
       </c>
       <c r="E383" t="n">
-        <v>13.47778613775057</v>
+        <v>13.47778707191389</v>
       </c>
       <c r="F383" t="n">
         <v>2291478</v>
@@ -8092,16 +8092,16 @@
         <v>44788</v>
       </c>
       <c r="B384" t="n">
-        <v>13.55455875396729</v>
+        <v>13.55455780029297</v>
       </c>
       <c r="C384" t="n">
-        <v>13.70810276022317</v>
+        <v>13.70810179574578</v>
       </c>
       <c r="D384" t="n">
-        <v>13.44366549407879</v>
+        <v>13.44366454820672</v>
       </c>
       <c r="E384" t="n">
-        <v>13.6483913854755</v>
+        <v>13.64839042519929</v>
       </c>
       <c r="F384" t="n">
         <v>3349490</v>
@@ -8132,16 +8132,16 @@
         <v>44790</v>
       </c>
       <c r="B386" t="n">
-        <v>13.56309032440186</v>
+        <v>13.56308841705322</v>
       </c>
       <c r="C386" t="n">
-        <v>13.64839264962083</v>
+        <v>13.64839073027631</v>
       </c>
       <c r="D386" t="n">
-        <v>13.23894082890304</v>
+        <v>13.23893896713886</v>
       </c>
       <c r="E386" t="n">
-        <v>13.64839264962083</v>
+        <v>13.64839073027631</v>
       </c>
       <c r="F386" t="n">
         <v>4054357</v>
@@ -8152,16 +8152,16 @@
         <v>44791</v>
       </c>
       <c r="B387" t="n">
-        <v>13.63986015319824</v>
+        <v>13.63986110687256</v>
       </c>
       <c r="C387" t="n">
-        <v>14.13461339542505</v>
+        <v>14.13461438369162</v>
       </c>
       <c r="D387" t="n">
-        <v>13.23893871158062</v>
+        <v>13.23893963722324</v>
       </c>
       <c r="E387" t="n">
-        <v>13.64839046681421</v>
+        <v>13.64839142108495</v>
       </c>
       <c r="F387" t="n">
         <v>3074090</v>
@@ -8212,16 +8212,16 @@
         <v>44796</v>
       </c>
       <c r="B390" t="n">
-        <v>12.29208183288574</v>
+        <v>12.29208278656006</v>
       </c>
       <c r="C390" t="n">
-        <v>12.6418222319422</v>
+        <v>12.64182321275093</v>
       </c>
       <c r="D390" t="n">
-        <v>12.25796140158548</v>
+        <v>12.25796235261258</v>
       </c>
       <c r="E390" t="n">
-        <v>12.6418222319422</v>
+        <v>12.64182321275093</v>
       </c>
       <c r="F390" t="n">
         <v>5845922</v>
@@ -8252,16 +8252,16 @@
         <v>44798</v>
       </c>
       <c r="B392" t="n">
-        <v>12.37738418579102</v>
+        <v>12.37738513946533</v>
       </c>
       <c r="C392" t="n">
-        <v>12.61623132853828</v>
+        <v>12.61623230061571</v>
       </c>
       <c r="D392" t="n">
-        <v>12.25796143900066</v>
+        <v>12.25796238347348</v>
       </c>
       <c r="E392" t="n">
-        <v>12.47974712917081</v>
+        <v>12.47974809073216</v>
       </c>
       <c r="F392" t="n">
         <v>1475823</v>
@@ -8272,16 +8272,16 @@
         <v>44799</v>
       </c>
       <c r="B393" t="n">
-        <v>12.18118858337402</v>
+        <v>12.18118953704834</v>
       </c>
       <c r="C393" t="n">
-        <v>12.49680855132523</v>
+        <v>12.49680952970967</v>
       </c>
       <c r="D393" t="n">
-        <v>12.03617489494593</v>
+        <v>12.03617583726701</v>
       </c>
       <c r="E393" t="n">
-        <v>12.45415698144445</v>
+        <v>12.45415795648967</v>
       </c>
       <c r="F393" t="n">
         <v>1257591</v>
@@ -8372,16 +8372,16 @@
         <v>44806</v>
       </c>
       <c r="B398" t="n">
-        <v>12.42003726959229</v>
+        <v>12.42003631591797</v>
       </c>
       <c r="C398" t="n">
-        <v>12.70153434877891</v>
+        <v>12.7015333734898</v>
       </c>
       <c r="D398" t="n">
-        <v>12.36885455818716</v>
+        <v>12.36885360844292</v>
       </c>
       <c r="E398" t="n">
-        <v>12.52239939406925</v>
+        <v>12.52239843253504</v>
       </c>
       <c r="F398" t="n">
         <v>3090207</v>
@@ -8392,16 +8392,16 @@
         <v>44809</v>
       </c>
       <c r="B399" t="n">
-        <v>13.3071813583374</v>
+        <v>13.30718231201172</v>
       </c>
       <c r="C399" t="n">
-        <v>13.40954430454897</v>
+        <v>13.40954526555925</v>
       </c>
       <c r="D399" t="n">
-        <v>12.38591566701658</v>
+        <v>12.38591655466734</v>
       </c>
       <c r="E399" t="n">
-        <v>12.48827778864485</v>
+        <v>12.48827868363151</v>
       </c>
       <c r="F399" t="n">
         <v>2134165</v>
@@ -8412,16 +8412,16 @@
         <v>44810</v>
       </c>
       <c r="B400" t="n">
-        <v>12.19824886322021</v>
+        <v>12.19824981689453</v>
       </c>
       <c r="C400" t="n">
-        <v>13.29012077517622</v>
+        <v>13.29012181421445</v>
       </c>
       <c r="D400" t="n">
-        <v>12.19824886322021</v>
+        <v>12.19824981689453</v>
       </c>
       <c r="E400" t="n">
-        <v>13.29012077517622</v>
+        <v>13.29012181421445</v>
       </c>
       <c r="F400" t="n">
         <v>5053579</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.33473300933838</v>
+        <v>12.3347339630127</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121720393626</v>
+        <v>12.47121816816301</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646230773766</v>
+        <v>11.97646323371185</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22383975583696</v>
+        <v>12.22384070093743</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8512,16 +8512,16 @@
         <v>44818</v>
       </c>
       <c r="B405" t="n">
-        <v>12.58102130889893</v>
+        <v>12.58102035522461</v>
       </c>
       <c r="C405" t="n">
-        <v>12.60671367567597</v>
+        <v>12.6067127200541</v>
       </c>
       <c r="D405" t="n">
-        <v>11.73315094150718</v>
+        <v>11.73315005210365</v>
       </c>
       <c r="E405" t="n">
-        <v>11.86161607372562</v>
+        <v>11.86161517458411</v>
       </c>
       <c r="F405" t="n">
         <v>3060135</v>
@@ -8532,16 +8532,16 @@
         <v>44819</v>
       </c>
       <c r="B406" t="n">
-        <v>12.76943588256836</v>
+        <v>12.76943683624268</v>
       </c>
       <c r="C406" t="n">
-        <v>12.9321583148535</v>
+        <v>12.9321592806806</v>
       </c>
       <c r="D406" t="n">
-        <v>12.33265413957057</v>
+        <v>12.33265506062422</v>
       </c>
       <c r="E406" t="n">
-        <v>12.5467629502966</v>
+        <v>12.54676388734078</v>
       </c>
       <c r="F406" t="n">
         <v>3409247</v>
@@ -8552,16 +8552,16 @@
         <v>44820</v>
       </c>
       <c r="B407" t="n">
-        <v>12.40117073059082</v>
+        <v>12.40117168426514</v>
       </c>
       <c r="C407" t="n">
-        <v>12.57245730023527</v>
+        <v>12.57245826708186</v>
       </c>
       <c r="D407" t="n">
-        <v>12.09285325606418</v>
+        <v>12.09285418602828</v>
       </c>
       <c r="E407" t="n">
-        <v>12.57245730023527</v>
+        <v>12.57245826708186</v>
       </c>
       <c r="F407" t="n">
         <v>2796130</v>
@@ -8592,16 +8592,16 @@
         <v>44824</v>
       </c>
       <c r="B409" t="n">
-        <v>11.88731098175049</v>
+        <v>11.88730907440186</v>
       </c>
       <c r="C409" t="n">
-        <v>12.52107174356088</v>
+        <v>12.52106973452375</v>
       </c>
       <c r="D409" t="n">
-        <v>11.87018108678033</v>
+        <v>11.87017918218023</v>
       </c>
       <c r="E409" t="n">
-        <v>12.4439921636954</v>
+        <v>12.44399016702588</v>
       </c>
       <c r="F409" t="n">
         <v>1700434</v>
@@ -8612,16 +8612,16 @@
         <v>44825</v>
       </c>
       <c r="B410" t="n">
-        <v>11.65607166290283</v>
+        <v>11.65607070922852</v>
       </c>
       <c r="C410" t="n">
-        <v>12.10998334747001</v>
+        <v>12.10998235665763</v>
       </c>
       <c r="D410" t="n">
-        <v>11.50191415999951</v>
+        <v>11.50191321893803</v>
       </c>
       <c r="E410" t="n">
-        <v>11.94726007292391</v>
+        <v>11.9472590954252</v>
       </c>
       <c r="F410" t="n">
         <v>3396829</v>
@@ -8632,16 +8632,16 @@
         <v>44826</v>
       </c>
       <c r="B411" t="n">
-        <v>12.18706226348877</v>
+        <v>12.18706130981445</v>
       </c>
       <c r="C411" t="n">
-        <v>12.24701277079775</v>
+        <v>12.24701181243212</v>
       </c>
       <c r="D411" t="n">
-        <v>11.07369664156018</v>
+        <v>11.07369577501007</v>
       </c>
       <c r="E411" t="n">
-        <v>11.2621131106622</v>
+        <v>11.26211222936794</v>
       </c>
       <c r="F411" t="n">
         <v>10292961</v>
@@ -8652,16 +8652,16 @@
         <v>44827</v>
       </c>
       <c r="B412" t="n">
-        <v>11.90443801879883</v>
+        <v>11.90443897247314</v>
       </c>
       <c r="C412" t="n">
-        <v>12.15280332981337</v>
+        <v>12.15280430338444</v>
       </c>
       <c r="D412" t="n">
-        <v>11.80166525608022</v>
+        <v>11.80166620152132</v>
       </c>
       <c r="E412" t="n">
-        <v>11.93869450692731</v>
+        <v>11.93869546334595</v>
       </c>
       <c r="F412" t="n">
         <v>2822076</v>
@@ -8672,16 +8672,16 @@
         <v>44830</v>
       </c>
       <c r="B413" t="n">
-        <v>11.45909214019775</v>
+        <v>11.45909309387207</v>
       </c>
       <c r="C413" t="n">
-        <v>11.84448752702055</v>
+        <v>11.84448851276911</v>
       </c>
       <c r="D413" t="n">
-        <v>11.34775525533786</v>
+        <v>11.34775619974625</v>
       </c>
       <c r="E413" t="n">
-        <v>11.81879433631571</v>
+        <v>11.81879531992597</v>
       </c>
       <c r="F413" t="n">
         <v>3443068</v>
@@ -8692,16 +8692,16 @@
         <v>44831</v>
       </c>
       <c r="B414" t="n">
-        <v>11.30493259429932</v>
+        <v>11.30493354797363</v>
       </c>
       <c r="C414" t="n">
-        <v>11.63894156348228</v>
+        <v>11.6389425453333</v>
       </c>
       <c r="D414" t="n">
-        <v>11.2621111641583</v>
+        <v>11.26211211422024</v>
       </c>
       <c r="E414" t="n">
-        <v>11.53616963639392</v>
+        <v>11.53617060957519</v>
       </c>
       <c r="F414" t="n">
         <v>2656202</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186389923096</v>
+        <v>11.56186485290527</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889314808853</v>
+        <v>11.69889411306563</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072583059598</v>
+        <v>11.21072675530685</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775507945355</v>
+        <v>11.34775601546721</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8772,16 +8772,16 @@
         <v>44837</v>
       </c>
       <c r="B418" t="n">
-        <v>12.41829872131348</v>
+        <v>12.41829776763916</v>
       </c>
       <c r="C418" t="n">
-        <v>12.62384342526681</v>
+        <v>12.6238424558075</v>
       </c>
       <c r="D418" t="n">
-        <v>12.01577426015137</v>
+        <v>12.01577333738928</v>
       </c>
       <c r="E418" t="n">
-        <v>12.06716064228553</v>
+        <v>12.06715971557718</v>
       </c>
       <c r="F418" t="n">
         <v>3117277</v>
@@ -8832,16 +8832,16 @@
         <v>44840</v>
       </c>
       <c r="B421" t="n">
-        <v>13.02636814117432</v>
+        <v>13.02636623382568</v>
       </c>
       <c r="C421" t="n">
-        <v>13.26617017822532</v>
+        <v>13.26616823576436</v>
       </c>
       <c r="D421" t="n">
-        <v>12.9235961929739</v>
+        <v>12.92359430067336</v>
       </c>
       <c r="E421" t="n">
-        <v>12.98354670223665</v>
+        <v>12.98354480115803</v>
       </c>
       <c r="F421" t="n">
         <v>6127236</v>
@@ -8892,16 +8892,16 @@
         <v>44845</v>
       </c>
       <c r="B424" t="n">
-        <v>12.7523078918457</v>
+        <v>12.75230693817139</v>
       </c>
       <c r="C424" t="n">
-        <v>12.80369427462625</v>
+        <v>12.80369331710903</v>
       </c>
       <c r="D424" t="n">
-        <v>12.53819988762117</v>
+        <v>12.5381989499588</v>
       </c>
       <c r="E424" t="n">
-        <v>12.72661470045543</v>
+        <v>12.72661374870257</v>
       </c>
       <c r="F424" t="n">
         <v>1848640</v>
@@ -8932,16 +8932,16 @@
         <v>44848</v>
       </c>
       <c r="B426" t="n">
-        <v>12.76943588256836</v>
+        <v>12.76943683624268</v>
       </c>
       <c r="C426" t="n">
-        <v>13.12057393635908</v>
+        <v>13.12057491625784</v>
       </c>
       <c r="D426" t="n">
-        <v>12.65809900414086</v>
+        <v>12.65809994950008</v>
       </c>
       <c r="E426" t="n">
-        <v>13.09488074713864</v>
+        <v>13.09488172511853</v>
       </c>
       <c r="F426" t="n">
         <v>2206838</v>
@@ -8952,16 +8952,16 @@
         <v>44851</v>
       </c>
       <c r="B427" t="n">
-        <v>12.64953708648682</v>
+        <v>12.6495361328125</v>
       </c>
       <c r="C427" t="n">
-        <v>13.19765580340922</v>
+        <v>13.19765480841111</v>
       </c>
       <c r="D427" t="n">
-        <v>12.58102245301736</v>
+        <v>12.5810215045085</v>
       </c>
       <c r="E427" t="n">
-        <v>12.87221005755423</v>
+        <v>12.87220908709215</v>
       </c>
       <c r="F427" t="n">
         <v>1088124</v>
@@ -8992,16 +8992,16 @@
         <v>44853</v>
       </c>
       <c r="B429" t="n">
-        <v>12.95785236358643</v>
+        <v>12.95785045623779</v>
       </c>
       <c r="C429" t="n">
-        <v>13.02636781860678</v>
+        <v>13.02636590117292</v>
       </c>
       <c r="D429" t="n">
-        <v>12.71805115705691</v>
+        <v>12.71804928500614</v>
       </c>
       <c r="E429" t="n">
-        <v>12.80369485739484</v>
+        <v>12.80369297273763</v>
       </c>
       <c r="F429" t="n">
         <v>1282165</v>
@@ -9052,16 +9052,16 @@
         <v>44858</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94928741455078</v>
+        <v>12.94928646087646</v>
       </c>
       <c r="C432" t="n">
-        <v>13.31755456037738</v>
+        <v>13.31755357958135</v>
       </c>
       <c r="D432" t="n">
-        <v>12.82082228453374</v>
+        <v>12.82082134032048</v>
       </c>
       <c r="E432" t="n">
-        <v>13.00923791850317</v>
+        <v>13.00923696041369</v>
       </c>
       <c r="F432" t="n">
         <v>2377861</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805191040039</v>
+        <v>12.71805095672607</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775497837641</v>
+        <v>13.07775399772944</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235954090216</v>
+        <v>12.69235858915441</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87221025030677</v>
+        <v>12.87220928507275</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9132,16 +9132,16 @@
         <v>44862</v>
       </c>
       <c r="B436" t="n">
-        <v>13.06918811798096</v>
+        <v>13.06918907165527</v>
       </c>
       <c r="C436" t="n">
-        <v>13.48027751395823</v>
+        <v>13.48027849763024</v>
       </c>
       <c r="D436" t="n">
-        <v>12.45255567318159</v>
+        <v>12.4525565818595</v>
       </c>
       <c r="E436" t="n">
-        <v>13.15483181085816</v>
+        <v>13.154832770782</v>
       </c>
       <c r="F436" t="n">
         <v>6048388</v>
@@ -9172,16 +9172,16 @@
         <v>44866</v>
       </c>
       <c r="B438" t="n">
-        <v>13.61730575561523</v>
+        <v>13.61730670928955</v>
       </c>
       <c r="C438" t="n">
-        <v>14.01126607789819</v>
+        <v>14.01126705916312</v>
       </c>
       <c r="D438" t="n">
-        <v>13.53166288847033</v>
+        <v>13.53166383614674</v>
       </c>
       <c r="E438" t="n">
-        <v>13.70295027192667</v>
+        <v>13.70295123159901</v>
       </c>
       <c r="F438" t="n">
         <v>3366744</v>
@@ -9192,16 +9192,16 @@
         <v>44868</v>
       </c>
       <c r="B439" t="n">
-        <v>13.9341869354248</v>
+        <v>13.93418788909912</v>
       </c>
       <c r="C439" t="n">
-        <v>14.04552216479015</v>
+        <v>14.0455231260844</v>
       </c>
       <c r="D439" t="n">
-        <v>13.38606831348592</v>
+        <v>13.38606922964626</v>
       </c>
       <c r="E439" t="n">
-        <v>13.38606831348592</v>
+        <v>13.38606922964626</v>
       </c>
       <c r="F439" t="n">
         <v>2966749</v>
@@ -9212,16 +9212,16 @@
         <v>44869</v>
       </c>
       <c r="B440" t="n">
-        <v>14.01126575469971</v>
+        <v>14.01126766204834</v>
       </c>
       <c r="C440" t="n">
-        <v>14.29389001334168</v>
+        <v>14.29389195916385</v>
       </c>
       <c r="D440" t="n">
-        <v>13.80572106421007</v>
+        <v>13.80572294357798</v>
       </c>
       <c r="E440" t="n">
-        <v>14.13973087703701</v>
+        <v>14.13973280187356</v>
       </c>
       <c r="F440" t="n">
         <v>3663661</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.40319919586182</v>
+        <v>13.40319633483887</v>
       </c>
       <c r="C441" t="n">
-        <v>14.03696080730087</v>
+        <v>14.0369578109963</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037857966108</v>
+        <v>13.36037572777854</v>
       </c>
       <c r="E441" t="n">
-        <v>13.93418967925229</v>
+        <v>13.93418670488506</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9252,16 +9252,16 @@
         <v>44873</v>
       </c>
       <c r="B442" t="n">
-        <v>13.36037731170654</v>
+        <v>13.36037635803223</v>
       </c>
       <c r="C442" t="n">
-        <v>13.54879212802549</v>
+        <v>13.54879116090197</v>
       </c>
       <c r="D442" t="n">
-        <v>12.91503140131632</v>
+        <v>12.91503047943115</v>
       </c>
       <c r="E442" t="n">
-        <v>13.33468411984108</v>
+        <v>13.33468316800077</v>
       </c>
       <c r="F442" t="n">
         <v>6245357</v>
@@ -9312,16 +9312,16 @@
         <v>44876</v>
       </c>
       <c r="B445" t="n">
-        <v>11.51904201507568</v>
+        <v>11.51904106140137</v>
       </c>
       <c r="C445" t="n">
-        <v>12.25557631309227</v>
+        <v>12.25557529843945</v>
       </c>
       <c r="D445" t="n">
-        <v>11.34775544843421</v>
+        <v>11.3477545089409</v>
       </c>
       <c r="E445" t="n">
-        <v>11.80166546847159</v>
+        <v>11.80166449139856</v>
       </c>
       <c r="F445" t="n">
         <v>9635321</v>
@@ -9332,16 +9332,16 @@
         <v>44879</v>
       </c>
       <c r="B446" t="n">
-        <v>11.90443801879883</v>
+        <v>11.90443897247314</v>
       </c>
       <c r="C446" t="n">
-        <v>12.05859633829346</v>
+        <v>12.05859730431752</v>
       </c>
       <c r="D446" t="n">
-        <v>11.51904180777061</v>
+        <v>11.51904273057052</v>
       </c>
       <c r="E446" t="n">
-        <v>11.69889331794489</v>
+        <v>11.69889425515285</v>
       </c>
       <c r="F446" t="n">
         <v>2658625</v>
@@ -9352,16 +9352,16 @@
         <v>44881</v>
       </c>
       <c r="B447" t="n">
-        <v>11.26211166381836</v>
+        <v>11.26211261749268</v>
       </c>
       <c r="C447" t="n">
-        <v>12.15280256268413</v>
+        <v>12.15280359178205</v>
       </c>
       <c r="D447" t="n">
-        <v>11.15933973217037</v>
+        <v>11.15934067714197</v>
       </c>
       <c r="E447" t="n">
-        <v>12.06715969860243</v>
+        <v>12.06716072044812</v>
       </c>
       <c r="F447" t="n">
         <v>3929079</v>
@@ -9372,16 +9372,16 @@
         <v>44882</v>
       </c>
       <c r="B448" t="n">
-        <v>10.94523239135742</v>
+        <v>10.94523143768311</v>
       </c>
       <c r="C448" t="n">
-        <v>10.94523239135742</v>
+        <v>10.94523143768311</v>
       </c>
       <c r="D448" t="n">
-        <v>9.900382217953842</v>
+        <v>9.900381355318869</v>
       </c>
       <c r="E448" t="n">
-        <v>10.7996381835505</v>
+        <v>10.79963724256202</v>
       </c>
       <c r="F448" t="n">
         <v>12061945</v>
@@ -9392,16 +9392,16 @@
         <v>44883</v>
       </c>
       <c r="B449" t="n">
-        <v>10.92810153961182</v>
+        <v>10.92810249328613</v>
       </c>
       <c r="C449" t="n">
-        <v>11.38201233430139</v>
+        <v>11.38201332758762</v>
       </c>
       <c r="D449" t="n">
-        <v>10.91953741836764</v>
+        <v>10.91953837129458</v>
       </c>
       <c r="E449" t="n">
-        <v>11.13364539697134</v>
+        <v>11.13364636858307</v>
       </c>
       <c r="F449" t="n">
         <v>5719164</v>
@@ -9412,16 +9412,16 @@
         <v>44886</v>
       </c>
       <c r="B450" t="n">
-        <v>11.25354671478271</v>
+        <v>11.25354766845703</v>
       </c>
       <c r="C450" t="n">
-        <v>11.33062628193585</v>
+        <v>11.33062724214222</v>
       </c>
       <c r="D450" t="n">
-        <v>10.80820167775862</v>
+        <v>10.80820259369247</v>
       </c>
       <c r="E450" t="n">
-        <v>10.98805235194947</v>
+        <v>10.98805328312464</v>
       </c>
       <c r="F450" t="n">
         <v>4991964</v>
@@ -9432,16 +9432,16 @@
         <v>44887</v>
       </c>
       <c r="B451" t="n">
-        <v>10.9880542755127</v>
+        <v>10.98805236816406</v>
       </c>
       <c r="C451" t="n">
-        <v>11.33919238845841</v>
+        <v>11.33919042015788</v>
       </c>
       <c r="D451" t="n">
-        <v>10.89384644888905</v>
+        <v>10.89384455789337</v>
       </c>
       <c r="E451" t="n">
-        <v>11.27924187837214</v>
+        <v>11.27923992047805</v>
       </c>
       <c r="F451" t="n">
         <v>2547672</v>
@@ -9472,16 +9472,16 @@
         <v>44889</v>
       </c>
       <c r="B453" t="n">
-        <v>11.53617191314697</v>
+        <v>11.53617095947266</v>
       </c>
       <c r="C453" t="n">
-        <v>11.81879538685529</v>
+        <v>11.81879440981701</v>
       </c>
       <c r="D453" t="n">
-        <v>11.05656866749802</v>
+        <v>11.05656775347163</v>
       </c>
       <c r="E453" t="n">
-        <v>11.11651917627706</v>
+        <v>11.11651825729467</v>
       </c>
       <c r="F453" t="n">
         <v>3457606</v>
@@ -9552,16 +9552,16 @@
         <v>44895</v>
       </c>
       <c r="B457" t="n">
-        <v>11.35632038116455</v>
+        <v>11.35631942749023</v>
       </c>
       <c r="C457" t="n">
-        <v>11.57042922318563</v>
+        <v>11.57042825153101</v>
       </c>
       <c r="D457" t="n">
-        <v>11.04800453920422</v>
+        <v>11.04800361142147</v>
       </c>
       <c r="E457" t="n">
-        <v>11.34775625836705</v>
+        <v>11.34775530541193</v>
       </c>
       <c r="F457" t="n">
         <v>6904107</v>
@@ -9592,16 +9592,16 @@
         <v>44897</v>
       </c>
       <c r="B459" t="n">
-        <v>11.32206249237061</v>
+        <v>11.32206344604492</v>
       </c>
       <c r="C459" t="n">
-        <v>11.47621998202977</v>
+        <v>11.47622094868901</v>
       </c>
       <c r="D459" t="n">
-        <v>11.07369554065139</v>
+        <v>11.07369647340539</v>
       </c>
       <c r="E459" t="n">
-        <v>11.1935965433492</v>
+        <v>11.19359748620264</v>
       </c>
       <c r="F459" t="n">
         <v>2110020</v>
@@ -9632,16 +9632,16 @@
         <v>44901</v>
       </c>
       <c r="B461" t="n">
-        <v>10.64547920227051</v>
+        <v>10.64548015594482</v>
       </c>
       <c r="C461" t="n">
-        <v>10.8852812182133</v>
+        <v>10.88528219337026</v>
       </c>
       <c r="D461" t="n">
-        <v>10.44849944607939</v>
+        <v>10.44850038210729</v>
       </c>
       <c r="E461" t="n">
-        <v>10.62835013345318</v>
+        <v>10.62835108559299</v>
       </c>
       <c r="F461" t="n">
         <v>3634787</v>
@@ -9652,16 +9652,16 @@
         <v>44902</v>
       </c>
       <c r="B462" t="n">
-        <v>10.3628568649292</v>
+        <v>10.36285591125488</v>
       </c>
       <c r="C462" t="n">
-        <v>10.91097388904668</v>
+        <v>10.91097288493018</v>
       </c>
       <c r="D462" t="n">
-        <v>10.24295585361184</v>
+        <v>10.24295491097179</v>
       </c>
       <c r="E462" t="n">
-        <v>10.59409394062459</v>
+        <v>10.59409296566996</v>
       </c>
       <c r="F462" t="n">
         <v>7006882</v>
@@ -9672,16 +9672,16 @@
         <v>44903</v>
       </c>
       <c r="B463" t="n">
-        <v>9.763351440429688</v>
+        <v>9.763352394104004</v>
       </c>
       <c r="C463" t="n">
-        <v>10.37998471849188</v>
+        <v>10.37998573239832</v>
       </c>
       <c r="D463" t="n">
-        <v>9.686272692963557</v>
+        <v>9.686273639108899</v>
       </c>
       <c r="E463" t="n">
-        <v>10.27721195575933</v>
+        <v>10.27721295962702</v>
       </c>
       <c r="F463" t="n">
         <v>6542779</v>
@@ -9692,16 +9692,16 @@
         <v>44904</v>
       </c>
       <c r="B464" t="n">
-        <v>9.694836616516113</v>
+        <v>9.694835662841797</v>
       </c>
       <c r="C464" t="n">
-        <v>10.02884643939223</v>
+        <v>10.02884545286159</v>
       </c>
       <c r="D464" t="n">
-        <v>9.463599554268511</v>
+        <v>9.463598623340824</v>
       </c>
       <c r="E464" t="n">
-        <v>9.848994932875605</v>
+        <v>9.848993964036843</v>
       </c>
       <c r="F464" t="n">
         <v>4631040</v>
@@ -9752,16 +9752,16 @@
         <v>44909</v>
       </c>
       <c r="B467" t="n">
-        <v>9.489292144775391</v>
+        <v>9.489291191101074</v>
       </c>
       <c r="C467" t="n">
-        <v>9.652015411433279</v>
+        <v>9.652014441405267</v>
       </c>
       <c r="D467" t="n">
-        <v>9.138154894443332</v>
+        <v>9.138153976058327</v>
       </c>
       <c r="E467" t="n">
-        <v>9.31800558063984</v>
+        <v>9.318004644179831</v>
       </c>
       <c r="F467" t="n">
         <v>7822016</v>
@@ -9772,16 +9772,16 @@
         <v>44910</v>
       </c>
       <c r="B468" t="n">
-        <v>9.831866264343262</v>
+        <v>9.831865310668945</v>
       </c>
       <c r="C468" t="n">
-        <v>9.908945837948723</v>
+        <v>9.90894487679782</v>
       </c>
       <c r="D468" t="n">
-        <v>9.352263876631365</v>
+        <v>9.352262969477668</v>
       </c>
       <c r="E468" t="n">
-        <v>9.429342625653522</v>
+        <v>9.429341711023316</v>
       </c>
       <c r="F468" t="n">
         <v>3938569</v>
@@ -9812,16 +9812,16 @@
         <v>44914</v>
       </c>
       <c r="B470" t="n">
-        <v>9.951766967773438</v>
+        <v>9.951767921447754</v>
       </c>
       <c r="C470" t="n">
-        <v>10.03741066095349</v>
+        <v>10.03741162283501</v>
       </c>
       <c r="D470" t="n">
-        <v>9.686272590873555</v>
+        <v>9.686273519105638</v>
       </c>
       <c r="E470" t="n">
-        <v>9.840430084181047</v>
+        <v>9.840431027185991</v>
       </c>
       <c r="F470" t="n">
         <v>3753211</v>
@@ -9832,16 +9832,16 @@
         <v>44915</v>
       </c>
       <c r="B471" t="n">
-        <v>10.33716201782227</v>
+        <v>10.33716297149658</v>
       </c>
       <c r="C471" t="n">
-        <v>10.65404358994094</v>
+        <v>10.65404457284976</v>
       </c>
       <c r="D471" t="n">
-        <v>9.857559660268567</v>
+        <v>9.857560569696266</v>
       </c>
       <c r="E471" t="n">
-        <v>9.926073458192986</v>
+        <v>9.926074373941555</v>
       </c>
       <c r="F471" t="n">
         <v>4483944</v>
@@ -9932,16 +9932,16 @@
         <v>44922</v>
       </c>
       <c r="B476" t="n">
-        <v>10.5229606628418</v>
+        <v>10.52296161651611</v>
       </c>
       <c r="C476" t="n">
-        <v>10.75038956949791</v>
+        <v>10.75039054378364</v>
       </c>
       <c r="D476" t="n">
-        <v>10.37425679063793</v>
+        <v>10.37425773083552</v>
       </c>
       <c r="E476" t="n">
-        <v>10.73289464951121</v>
+        <v>10.73289562221141</v>
       </c>
       <c r="F476" t="n">
         <v>2935250</v>
@@ -9972,16 +9972,16 @@
         <v>44924</v>
       </c>
       <c r="B478" t="n">
-        <v>11.05654525756836</v>
+        <v>11.05654335021973</v>
       </c>
       <c r="C478" t="n">
-        <v>11.29272124043664</v>
+        <v>11.29271929234563</v>
       </c>
       <c r="D478" t="n">
-        <v>10.7503912680869</v>
+        <v>10.75038941355245</v>
       </c>
       <c r="E478" t="n">
-        <v>11.00406133151083</v>
+        <v>11.00405943321613</v>
       </c>
       <c r="F478" t="n">
         <v>3691424</v>
@@ -10012,16 +10012,16 @@
         <v>44929</v>
       </c>
       <c r="B480" t="n">
-        <v>9.578256607055664</v>
+        <v>9.578255653381348</v>
       </c>
       <c r="C480" t="n">
-        <v>10.18181838147228</v>
+        <v>10.18181736770337</v>
       </c>
       <c r="D480" t="n">
-        <v>9.534520563939639</v>
+        <v>9.53451961461997</v>
       </c>
       <c r="E480" t="n">
-        <v>10.15557641872455</v>
+        <v>10.15557540756847</v>
       </c>
       <c r="F480" t="n">
         <v>3313438</v>
@@ -10032,16 +10032,16 @@
         <v>44930</v>
       </c>
       <c r="B481" t="n">
-        <v>9.814432144165039</v>
+        <v>9.814431190490723</v>
       </c>
       <c r="C481" t="n">
-        <v>9.83192706593853</v>
+        <v>9.83192611056422</v>
       </c>
       <c r="D481" t="n">
-        <v>9.482037052421148</v>
+        <v>9.482036131045863</v>
       </c>
       <c r="E481" t="n">
-        <v>9.648235019390714</v>
+        <v>9.648234081865873</v>
       </c>
       <c r="F481" t="n">
         <v>3712928</v>
@@ -10052,16 +10052,16 @@
         <v>44931</v>
       </c>
       <c r="B482" t="n">
-        <v>10.05935573577881</v>
+        <v>10.05935668945312</v>
       </c>
       <c r="C482" t="n">
-        <v>10.33926773935673</v>
+        <v>10.33926871956802</v>
       </c>
       <c r="D482" t="n">
-        <v>9.779443732200887</v>
+        <v>9.779444659338226</v>
       </c>
       <c r="E482" t="n">
-        <v>9.796937811326897</v>
+        <v>9.796938740122757</v>
       </c>
       <c r="F482" t="n">
         <v>3524036</v>
@@ -10072,16 +10072,16 @@
         <v>44932</v>
       </c>
       <c r="B483" t="n">
-        <v>10.4354887008667</v>
+        <v>10.43548774719238</v>
       </c>
       <c r="C483" t="n">
-        <v>10.49671882092729</v>
+        <v>10.4967178616573</v>
       </c>
       <c r="D483" t="n">
-        <v>10.03311392635628</v>
+        <v>10.03311300945403</v>
       </c>
       <c r="E483" t="n">
-        <v>10.05935588763667</v>
+        <v>10.05935496833623</v>
       </c>
       <c r="F483" t="n">
         <v>2102448</v>
@@ -10192,16 +10192,16 @@
         <v>44942</v>
       </c>
       <c r="B489" t="n">
-        <v>10.8028736114502</v>
+        <v>10.80287265777588</v>
       </c>
       <c r="C489" t="n">
-        <v>11.3014683871045</v>
+        <v>11.30146738941439</v>
       </c>
       <c r="D489" t="n">
-        <v>10.69790744273759</v>
+        <v>10.69790649832965</v>
       </c>
       <c r="E489" t="n">
-        <v>11.25773234310836</v>
+        <v>11.25773134927926</v>
       </c>
       <c r="F489" t="n">
         <v>2251058</v>
@@ -10272,16 +10272,16 @@
         <v>44946</v>
       </c>
       <c r="B493" t="n">
-        <v>11.86129379272461</v>
+        <v>11.86129283905029</v>
       </c>
       <c r="C493" t="n">
-        <v>12.0187438835161</v>
+        <v>12.01874291718245</v>
       </c>
       <c r="D493" t="n">
-        <v>11.51140292410906</v>
+        <v>11.51140199856674</v>
       </c>
       <c r="E493" t="n">
-        <v>11.92252475789698</v>
+        <v>11.92252379929955</v>
       </c>
       <c r="F493" t="n">
         <v>2495174</v>
@@ -10312,16 +10312,16 @@
         <v>44950</v>
       </c>
       <c r="B495" t="n">
-        <v>12.1237096786499</v>
+        <v>12.12371063232422</v>
       </c>
       <c r="C495" t="n">
-        <v>12.25491947817606</v>
+        <v>12.25492044217159</v>
       </c>
       <c r="D495" t="n">
-        <v>11.55513781094744</v>
+        <v>11.5551387198968</v>
       </c>
       <c r="E495" t="n">
-        <v>11.67759972904172</v>
+        <v>11.67760064762417</v>
       </c>
       <c r="F495" t="n">
         <v>5075153</v>
@@ -10332,16 +10332,16 @@
         <v>44951</v>
       </c>
       <c r="B496" t="n">
-        <v>12.24617195129395</v>
+        <v>12.24617290496826</v>
       </c>
       <c r="C496" t="n">
-        <v>12.44735975492869</v>
+        <v>12.44736072427057</v>
       </c>
       <c r="D496" t="n">
-        <v>11.96625995005467</v>
+        <v>11.96626088193075</v>
       </c>
       <c r="E496" t="n">
-        <v>12.10621595067431</v>
+        <v>12.10621689344951</v>
       </c>
       <c r="F496" t="n">
         <v>2519909</v>
@@ -10472,16 +10472,16 @@
         <v>44960</v>
       </c>
       <c r="B503" t="n">
-        <v>12.57856845855713</v>
+        <v>12.57856750488281</v>
       </c>
       <c r="C503" t="n">
-        <v>12.90221819887599</v>
+        <v>12.90221722066339</v>
       </c>
       <c r="D503" t="n">
-        <v>12.42986541153535</v>
+        <v>12.42986446913531</v>
       </c>
       <c r="E503" t="n">
-        <v>12.81474527332507</v>
+        <v>12.81474430174445</v>
       </c>
       <c r="F503" t="n">
         <v>2892746</v>
@@ -10492,16 +10492,16 @@
         <v>44963</v>
       </c>
       <c r="B504" t="n">
-        <v>12.75351524353027</v>
+        <v>12.75351428985596</v>
       </c>
       <c r="C504" t="n">
-        <v>12.83224113494935</v>
+        <v>12.83224017538812</v>
       </c>
       <c r="D504" t="n">
-        <v>12.33364634921449</v>
+        <v>12.33364542693687</v>
       </c>
       <c r="E504" t="n">
-        <v>12.53483333473771</v>
+        <v>12.53483239741585</v>
       </c>
       <c r="F504" t="n">
         <v>1342942</v>
@@ -10512,16 +10512,16 @@
         <v>44964</v>
       </c>
       <c r="B505" t="n">
-        <v>12.76226139068604</v>
+        <v>12.76226043701172</v>
       </c>
       <c r="C505" t="n">
-        <v>12.93720640015643</v>
+        <v>12.93720543340915</v>
       </c>
       <c r="D505" t="n">
-        <v>12.52608541735219</v>
+        <v>12.52608448132639</v>
       </c>
       <c r="E505" t="n">
-        <v>12.85848135644357</v>
+        <v>12.8584803955791</v>
       </c>
       <c r="F505" t="n">
         <v>2203204</v>
@@ -10572,16 +10572,16 @@
         <v>44967</v>
       </c>
       <c r="B508" t="n">
-        <v>12.4036226272583</v>
+        <v>12.40362358093262</v>
       </c>
       <c r="C508" t="n">
-        <v>12.47360062618121</v>
+        <v>12.47360158523591</v>
       </c>
       <c r="D508" t="n">
-        <v>11.97500675220909</v>
+        <v>11.97500767292852</v>
       </c>
       <c r="E508" t="n">
-        <v>12.03623771181543</v>
+        <v>12.03623863724271</v>
       </c>
       <c r="F508" t="n">
         <v>3559170</v>
@@ -10592,16 +10592,16 @@
         <v>44970</v>
       </c>
       <c r="B509" t="n">
-        <v>12.52608489990234</v>
+        <v>12.52608394622803</v>
       </c>
       <c r="C509" t="n">
-        <v>12.77100790304318</v>
+        <v>12.77100693072163</v>
       </c>
       <c r="D509" t="n">
-        <v>12.35113905546367</v>
+        <v>12.35113811510887</v>
       </c>
       <c r="E509" t="n">
-        <v>12.38612889810758</v>
+        <v>12.38612795508882</v>
       </c>
       <c r="F509" t="n">
         <v>2916169</v>
@@ -10632,16 +10632,16 @@
         <v>44972</v>
       </c>
       <c r="B511" t="n">
-        <v>12.75351524353027</v>
+        <v>12.75351428985596</v>
       </c>
       <c r="C511" t="n">
-        <v>12.94595434632116</v>
+        <v>12.94595337825676</v>
       </c>
       <c r="D511" t="n">
-        <v>11.91377745489871</v>
+        <v>11.91377656401778</v>
       </c>
       <c r="E511" t="n">
-        <v>12.24617341725841</v>
+        <v>12.24617250152178</v>
       </c>
       <c r="F511" t="n">
         <v>3838217</v>
@@ -10692,16 +10692,16 @@
         <v>44979</v>
       </c>
       <c r="B514" t="n">
-        <v>12.63980007171631</v>
+        <v>12.63979911804199</v>
       </c>
       <c r="C514" t="n">
-        <v>12.70977807887474</v>
+        <v>12.70977711992058</v>
       </c>
       <c r="D514" t="n">
-        <v>12.33364607984934</v>
+        <v>12.33364514927437</v>
       </c>
       <c r="E514" t="n">
-        <v>12.70103103852876</v>
+        <v>12.70103008023456</v>
       </c>
       <c r="F514" t="n">
         <v>1228758</v>
@@ -10752,16 +10752,16 @@
         <v>44984</v>
       </c>
       <c r="B517" t="n">
-        <v>11.64261150360107</v>
+        <v>11.64261054992676</v>
       </c>
       <c r="C517" t="n">
-        <v>11.87004043423472</v>
+        <v>11.87003946193115</v>
       </c>
       <c r="D517" t="n">
-        <v>11.51140253755071</v>
+        <v>11.51140159462404</v>
       </c>
       <c r="E517" t="n">
-        <v>11.77382046965144</v>
+        <v>11.77381950522948</v>
       </c>
       <c r="F517" t="n">
         <v>3613283</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.2636661529541</v>
+        <v>12.26366710662842</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738102843226</v>
+        <v>12.37738199094953</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87003929265923</v>
+        <v>11.87004021572346</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12370931835058</v>
+        <v>12.12371026114126</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10892,16 +10892,16 @@
         <v>44993</v>
       </c>
       <c r="B524" t="n">
-        <v>12.68353652954102</v>
+        <v>12.6835355758667</v>
       </c>
       <c r="C524" t="n">
-        <v>12.75351453433644</v>
+        <v>12.75351357540048</v>
       </c>
       <c r="D524" t="n">
-        <v>12.17619473148127</v>
+        <v>12.17619381595395</v>
       </c>
       <c r="E524" t="n">
-        <v>12.28990962092029</v>
+        <v>12.28990869684275</v>
       </c>
       <c r="F524" t="n">
         <v>2396134</v>
@@ -10972,16 +10972,16 @@
         <v>44999</v>
       </c>
       <c r="B528" t="n">
-        <v>12.176194190979</v>
+        <v>12.17619514465332</v>
       </c>
       <c r="C528" t="n">
-        <v>12.80599789057135</v>
+        <v>12.80599889357369</v>
       </c>
       <c r="D528" t="n">
-        <v>12.10621618928991</v>
+        <v>12.10621713748334</v>
       </c>
       <c r="E528" t="n">
-        <v>12.58731600364649</v>
+        <v>12.58731698952104</v>
       </c>
       <c r="F528" t="n">
         <v>1444505</v>
@@ -10992,16 +10992,16 @@
         <v>45000</v>
       </c>
       <c r="B529" t="n">
-        <v>12.34239101409912</v>
+        <v>12.34239292144775</v>
       </c>
       <c r="C529" t="n">
-        <v>12.44735884912044</v>
+        <v>12.44736077269042</v>
       </c>
       <c r="D529" t="n">
-        <v>11.63386318087615</v>
+        <v>11.63386497873145</v>
       </c>
       <c r="E529" t="n">
-        <v>11.94001712050125</v>
+        <v>11.94001896566847</v>
       </c>
       <c r="F529" t="n">
         <v>3332216</v>
@@ -11052,16 +11052,16 @@
         <v>45005</v>
       </c>
       <c r="B532" t="n">
-        <v>11.36269855499268</v>
+        <v>11.36269950866699</v>
       </c>
       <c r="C532" t="n">
-        <v>11.90502849431124</v>
+        <v>11.90502949350345</v>
       </c>
       <c r="D532" t="n">
-        <v>11.17025862742956</v>
+        <v>11.17025956495234</v>
       </c>
       <c r="E532" t="n">
-        <v>11.73008348843351</v>
+        <v>11.73008447294255</v>
       </c>
       <c r="F532" t="n">
         <v>5506849</v>
@@ -11072,16 +11072,16 @@
         <v>45006</v>
       </c>
       <c r="B533" t="n">
-        <v>11.33645629882812</v>
+        <v>11.33645725250244</v>
       </c>
       <c r="C533" t="n">
-        <v>11.60762039909721</v>
+        <v>11.60762137558309</v>
       </c>
       <c r="D533" t="n">
-        <v>11.24023550250128</v>
+        <v>11.24023644808107</v>
       </c>
       <c r="E533" t="n">
-        <v>11.33645629882812</v>
+        <v>11.33645725250244</v>
       </c>
       <c r="F533" t="n">
         <v>1775142</v>
@@ -11112,16 +11112,16 @@
         <v>45008</v>
       </c>
       <c r="B535" t="n">
-        <v>10.74164390563965</v>
+        <v>10.74164295196533</v>
       </c>
       <c r="C535" t="n">
-        <v>11.5813817100418</v>
+        <v>11.58138068181313</v>
       </c>
       <c r="D535" t="n">
-        <v>10.50546706914225</v>
+        <v>10.5054661364364</v>
       </c>
       <c r="E535" t="n">
-        <v>11.49390877644294</v>
+        <v>11.49390775598037</v>
       </c>
       <c r="F535" t="n">
         <v>4691110</v>
@@ -11152,16 +11152,16 @@
         <v>45012</v>
       </c>
       <c r="B537" t="n">
-        <v>11.36269855499268</v>
+        <v>11.36269950866699</v>
       </c>
       <c r="C537" t="n">
-        <v>11.52889652112532</v>
+        <v>11.52889748874868</v>
       </c>
       <c r="D537" t="n">
-        <v>11.12652258650894</v>
+        <v>11.12652352036094</v>
       </c>
       <c r="E537" t="n">
-        <v>11.18775354911495</v>
+        <v>11.18775448810609</v>
       </c>
       <c r="F537" t="n">
         <v>2536971</v>
@@ -11192,16 +11192,16 @@
         <v>45014</v>
       </c>
       <c r="B539" t="n">
-        <v>11.72133636474609</v>
+        <v>11.72133541107178</v>
       </c>
       <c r="C539" t="n">
-        <v>11.7650724053535</v>
+        <v>11.76507144812072</v>
       </c>
       <c r="D539" t="n">
-        <v>11.36269847361872</v>
+        <v>11.36269754912399</v>
       </c>
       <c r="E539" t="n">
-        <v>11.60762148009351</v>
+        <v>11.6076205356713</v>
       </c>
       <c r="F539" t="n">
         <v>3319697</v>
@@ -11212,16 +11212,16 @@
         <v>45015</v>
       </c>
       <c r="B540" t="n">
-        <v>12.11496257781982</v>
+        <v>12.11496353149414</v>
       </c>
       <c r="C540" t="n">
-        <v>12.28116053344774</v>
+        <v>12.28116150020495</v>
       </c>
       <c r="D540" t="n">
-        <v>11.71258866863594</v>
+        <v>11.7125895906359</v>
       </c>
       <c r="E540" t="n">
-        <v>11.72133570782815</v>
+        <v>11.72133663051666</v>
       </c>
       <c r="F540" t="n">
         <v>2232381</v>
@@ -11272,16 +11272,16 @@
         <v>45020</v>
       </c>
       <c r="B543" t="n">
-        <v>11.27522659301758</v>
+        <v>11.27522563934326</v>
       </c>
       <c r="C543" t="n">
-        <v>11.66010561004019</v>
+        <v>11.66010462381228</v>
       </c>
       <c r="D543" t="n">
-        <v>11.2577316711462</v>
+        <v>11.25773071895163</v>
       </c>
       <c r="E543" t="n">
-        <v>11.29272067269371</v>
+        <v>11.29271971753972</v>
       </c>
       <c r="F543" t="n">
         <v>2416225</v>
@@ -11292,16 +11292,16 @@
         <v>45021</v>
       </c>
       <c r="B544" t="n">
-        <v>10.67166519165039</v>
+        <v>10.67166423797607</v>
       </c>
       <c r="C544" t="n">
-        <v>11.35395200744364</v>
+        <v>11.3539509927967</v>
       </c>
       <c r="D544" t="n">
-        <v>10.58419310601722</v>
+        <v>10.58419216015985</v>
       </c>
       <c r="E544" t="n">
-        <v>11.17900699398201</v>
+        <v>11.17900599496905</v>
       </c>
       <c r="F544" t="n">
         <v>4730079</v>
@@ -11312,16 +11312,16 @@
         <v>45022</v>
       </c>
       <c r="B545" t="n">
-        <v>10.8028736114502</v>
+        <v>10.80287265777588</v>
       </c>
       <c r="C545" t="n">
-        <v>11.10902928820433</v>
+        <v>11.10902830750268</v>
       </c>
       <c r="D545" t="n">
-        <v>10.46173145764599</v>
+        <v>10.4617305340876</v>
       </c>
       <c r="E545" t="n">
-        <v>10.71540152345793</v>
+        <v>10.71540057750562</v>
       </c>
       <c r="F545" t="n">
         <v>8557394</v>
@@ -11332,16 +11332,16 @@
         <v>45026</v>
       </c>
       <c r="B546" t="n">
-        <v>10.899094581604</v>
+        <v>10.89909362792969</v>
       </c>
       <c r="C546" t="n">
-        <v>11.14401761059309</v>
+        <v>11.14401663548793</v>
       </c>
       <c r="D546" t="n">
-        <v>10.64542366993311</v>
+        <v>10.64542273845509</v>
       </c>
       <c r="E546" t="n">
-        <v>10.71540167821571</v>
+        <v>10.71540074061458</v>
       </c>
       <c r="F546" t="n">
         <v>4871319</v>
@@ -11372,16 +11372,16 @@
         <v>45028</v>
       </c>
       <c r="B548" t="n">
-        <v>12.11496257781982</v>
+        <v>12.11496353149414</v>
       </c>
       <c r="C548" t="n">
-        <v>12.33364445299137</v>
+        <v>12.33364542388005</v>
       </c>
       <c r="D548" t="n">
-        <v>11.80880862633581</v>
+        <v>11.80880955591008</v>
       </c>
       <c r="E548" t="n">
-        <v>11.96625954277151</v>
+        <v>11.96626048474012</v>
       </c>
       <c r="F548" t="n">
         <v>6602445</v>
@@ -11392,16 +11392,16 @@
         <v>45029</v>
       </c>
       <c r="B549" t="n">
-        <v>12.45610618591309</v>
+        <v>12.4561071395874</v>
       </c>
       <c r="C549" t="n">
-        <v>12.64854525626645</v>
+        <v>12.64854622467444</v>
       </c>
       <c r="D549" t="n">
-        <v>11.97500640454174</v>
+        <v>11.97500732138171</v>
       </c>
       <c r="E549" t="n">
-        <v>12.09746832019902</v>
+        <v>12.09746924641502</v>
       </c>
       <c r="F549" t="n">
         <v>4483641</v>
@@ -11412,16 +11412,16 @@
         <v>45030</v>
       </c>
       <c r="B550" t="n">
-        <v>12.52608489990234</v>
+        <v>12.52608394622803</v>
       </c>
       <c r="C550" t="n">
-        <v>12.72727186303112</v>
+        <v>12.72727089403942</v>
       </c>
       <c r="D550" t="n">
-        <v>12.22867797499086</v>
+        <v>12.22867704395964</v>
       </c>
       <c r="E550" t="n">
-        <v>12.42111705636105</v>
+        <v>12.42111611067847</v>
       </c>
       <c r="F550" t="n">
         <v>2806225</v>
@@ -11432,16 +11432,16 @@
         <v>45033</v>
       </c>
       <c r="B551" t="n">
-        <v>12.34239101409912</v>
+        <v>12.34239292144775</v>
       </c>
       <c r="C551" t="n">
-        <v>12.56981991965339</v>
+        <v>12.56982186214806</v>
       </c>
       <c r="D551" t="n">
-        <v>12.22867698241957</v>
+        <v>12.22867887219524</v>
       </c>
       <c r="E551" t="n">
-        <v>12.50858980548449</v>
+        <v>12.50859173851688</v>
       </c>
       <c r="F551" t="n">
         <v>3419242</v>
@@ -11452,16 +11452,16 @@
         <v>45034</v>
       </c>
       <c r="B552" t="n">
-        <v>11.62511825561523</v>
+        <v>11.62511730194092</v>
       </c>
       <c r="C552" t="n">
-        <v>12.42111830648523</v>
+        <v>12.42111728751052</v>
       </c>
       <c r="D552" t="n">
-        <v>11.55513940547961</v>
+        <v>11.55513845754605</v>
       </c>
       <c r="E552" t="n">
-        <v>12.33364621765748</v>
+        <v>12.3336452058586</v>
       </c>
       <c r="F552" t="n">
         <v>3919084</v>
@@ -11552,16 +11552,16 @@
         <v>45042</v>
       </c>
       <c r="B557" t="n">
-        <v>11.25773048400879</v>
+        <v>11.25773143768311</v>
       </c>
       <c r="C557" t="n">
-        <v>11.49390643009834</v>
+        <v>11.49390740377979</v>
       </c>
       <c r="D557" t="n">
-        <v>11.21399444723522</v>
+        <v>11.21399539720453</v>
       </c>
       <c r="E557" t="n">
-        <v>11.24898260289795</v>
+        <v>11.24898355583121</v>
       </c>
       <c r="F557" t="n">
         <v>2213905</v>
@@ -11592,16 +11592,16 @@
         <v>45044</v>
       </c>
       <c r="B559" t="n">
-        <v>10.68916034698486</v>
+        <v>10.68915939331055</v>
       </c>
       <c r="C559" t="n">
-        <v>10.86410536425811</v>
+        <v>10.86410439497541</v>
       </c>
       <c r="D559" t="n">
-        <v>10.36551143338288</v>
+        <v>10.36551050858414</v>
       </c>
       <c r="E559" t="n">
-        <v>10.8378634011183</v>
+        <v>10.83786243417687</v>
       </c>
       <c r="F559" t="n">
         <v>8236247</v>
@@ -11652,16 +11652,16 @@
         <v>45050</v>
       </c>
       <c r="B562" t="n">
-        <v>9.42955207824707</v>
+        <v>9.429553031921387</v>
       </c>
       <c r="C562" t="n">
-        <v>10.19056382556656</v>
+        <v>10.19056485620714</v>
       </c>
       <c r="D562" t="n">
-        <v>9.324584243696673</v>
+        <v>9.324585186754883</v>
       </c>
       <c r="E562" t="n">
-        <v>10.14682778930066</v>
+        <v>10.14682881551792</v>
       </c>
       <c r="F562" t="n">
         <v>16781627</v>
@@ -11692,16 +11692,16 @@
         <v>45054</v>
       </c>
       <c r="B564" t="n">
-        <v>9.960694313049316</v>
+        <v>9.960692405700684</v>
       </c>
       <c r="C564" t="n">
-        <v>10.13590409260217</v>
+        <v>10.13590215170305</v>
       </c>
       <c r="D564" t="n">
-        <v>9.759202012226195</v>
+        <v>9.759200143460824</v>
       </c>
       <c r="E564" t="n">
-        <v>10.10962241480177</v>
+        <v>10.10962047893527</v>
       </c>
       <c r="F564" t="n">
         <v>5548545</v>
@@ -11712,16 +11712,16 @@
         <v>45055</v>
       </c>
       <c r="B565" t="n">
-        <v>10.18846607208252</v>
+        <v>10.18846702575684</v>
       </c>
       <c r="C565" t="n">
-        <v>10.23226830018705</v>
+        <v>10.2322692579614</v>
       </c>
       <c r="D565" t="n">
-        <v>9.732919863304266</v>
+        <v>9.732920774337941</v>
       </c>
       <c r="E565" t="n">
-        <v>9.943171570369724</v>
+        <v>9.943172501083659</v>
       </c>
       <c r="F565" t="n">
         <v>5766311</v>
@@ -11792,16 +11792,16 @@
         <v>45061</v>
       </c>
       <c r="B569" t="n">
-        <v>10.15342330932617</v>
+        <v>10.15342426300049</v>
       </c>
       <c r="C569" t="n">
-        <v>10.21474693494698</v>
+        <v>10.2147478943812</v>
       </c>
       <c r="D569" t="n">
-        <v>9.986973829842441</v>
+        <v>9.98697476788276</v>
       </c>
       <c r="E569" t="n">
-        <v>10.1621844297504</v>
+        <v>10.16218538424762</v>
       </c>
       <c r="F569" t="n">
         <v>4041445</v>
@@ -11832,16 +11832,16 @@
         <v>45063</v>
       </c>
       <c r="B571" t="n">
-        <v>10.0745792388916</v>
+        <v>10.07458019256592</v>
       </c>
       <c r="C571" t="n">
-        <v>10.1446631422258</v>
+        <v>10.14466410253436</v>
       </c>
       <c r="D571" t="n">
-        <v>9.934411432223198</v>
+        <v>9.934412372629026</v>
       </c>
       <c r="E571" t="n">
-        <v>9.986973937988964</v>
+        <v>9.986974883370435</v>
       </c>
       <c r="F571" t="n">
         <v>5003473</v>
@@ -11872,16 +11872,16 @@
         <v>45065</v>
       </c>
       <c r="B573" t="n">
-        <v>11.44121742248535</v>
+        <v>11.44121837615967</v>
       </c>
       <c r="C573" t="n">
-        <v>12.00188946999683</v>
+        <v>12.00189047040555</v>
       </c>
       <c r="D573" t="n">
-        <v>10.51260363211687</v>
+        <v>10.51260450838727</v>
       </c>
       <c r="E573" t="n">
-        <v>10.60897004964872</v>
+        <v>10.60897093395166</v>
       </c>
       <c r="F573" t="n">
         <v>14298668</v>
@@ -11972,16 +11972,16 @@
         <v>45072</v>
       </c>
       <c r="B578" t="n">
-        <v>11.67775249481201</v>
+        <v>11.6777515411377</v>
       </c>
       <c r="C578" t="n">
-        <v>11.90552562629357</v>
+        <v>11.90552465401795</v>
       </c>
       <c r="D578" t="n">
-        <v>11.47626104070714</v>
+        <v>11.47626010348781</v>
       </c>
       <c r="E578" t="n">
-        <v>11.54634495139841</v>
+        <v>11.54634400845561</v>
       </c>
       <c r="F578" t="n">
         <v>3617321</v>
@@ -11992,16 +11992,16 @@
         <v>45075</v>
       </c>
       <c r="B579" t="n">
-        <v>11.62518882751465</v>
+        <v>11.62518787384033</v>
       </c>
       <c r="C579" t="n">
-        <v>11.76535748859861</v>
+        <v>11.76535652342553</v>
       </c>
       <c r="D579" t="n">
-        <v>11.45874017670026</v>
+        <v>11.45873923668059</v>
       </c>
       <c r="E579" t="n">
-        <v>11.73031553419508</v>
+        <v>11.73031457189667</v>
       </c>
       <c r="F579" t="n">
         <v>1756970</v>
@@ -12032,16 +12032,16 @@
         <v>45077</v>
       </c>
       <c r="B581" t="n">
-        <v>11.27476787567139</v>
+        <v>11.2747688293457</v>
       </c>
       <c r="C581" t="n">
-        <v>11.46749902256062</v>
+        <v>11.46749999253707</v>
       </c>
       <c r="D581" t="n">
-        <v>11.07327645214257</v>
+        <v>11.07327738877377</v>
       </c>
       <c r="E581" t="n">
-        <v>11.20468397561525</v>
+        <v>11.20468492336154</v>
       </c>
       <c r="F581" t="n">
         <v>3703640</v>
@@ -12052,16 +12052,16 @@
         <v>45078</v>
       </c>
       <c r="B582" t="n">
-        <v>11.79163932800293</v>
+        <v>11.79163837432861</v>
       </c>
       <c r="C582" t="n">
-        <v>11.87048435910138</v>
+        <v>11.8704833990503</v>
       </c>
       <c r="D582" t="n">
-        <v>11.23096720633888</v>
+        <v>11.23096629801013</v>
       </c>
       <c r="E582" t="n">
-        <v>11.34485419232446</v>
+        <v>11.34485327478486</v>
       </c>
       <c r="F582" t="n">
         <v>6914909</v>
@@ -12112,16 +12112,16 @@
         <v>45083</v>
       </c>
       <c r="B585" t="n">
-        <v>12.53628158569336</v>
+        <v>12.53628063201904</v>
       </c>
       <c r="C585" t="n">
-        <v>12.73777302495092</v>
+        <v>12.73777205594852</v>
       </c>
       <c r="D585" t="n">
-        <v>11.88800419436395</v>
+        <v>11.88800329000613</v>
       </c>
       <c r="E585" t="n">
-        <v>11.91428502633423</v>
+        <v>11.91428411997714</v>
       </c>
       <c r="F585" t="n">
         <v>8194955</v>
@@ -12172,16 +12172,16 @@
         <v>45089</v>
       </c>
       <c r="B588" t="n">
-        <v>12.80785751342773</v>
+        <v>12.80785655975342</v>
       </c>
       <c r="C588" t="n">
-        <v>12.97430785096759</v>
+        <v>12.97430688489936</v>
       </c>
       <c r="D588" t="n">
-        <v>12.72025220579673</v>
+        <v>12.72025125864552</v>
       </c>
       <c r="E588" t="n">
-        <v>12.79909723570558</v>
+        <v>12.79909628268356</v>
       </c>
       <c r="F588" t="n">
         <v>2677201</v>
@@ -12192,16 +12192,16 @@
         <v>45090</v>
       </c>
       <c r="B589" t="n">
-        <v>12.52752017974854</v>
+        <v>12.52752113342285</v>
       </c>
       <c r="C589" t="n">
-        <v>13.04438914731215</v>
+        <v>13.04439014033381</v>
       </c>
       <c r="D589" t="n">
-        <v>12.29974624210157</v>
+        <v>12.29974717843629</v>
       </c>
       <c r="E589" t="n">
-        <v>12.86041912274534</v>
+        <v>12.86042010176204</v>
       </c>
       <c r="F589" t="n">
         <v>6116837</v>
@@ -12212,16 +12212,16 @@
         <v>45091</v>
       </c>
       <c r="B590" t="n">
-        <v>12.8867015838623</v>
+        <v>12.88670063018799</v>
       </c>
       <c r="C590" t="n">
-        <v>12.9392649366617</v>
+        <v>12.93926397909746</v>
       </c>
       <c r="D590" t="n">
-        <v>12.46619813534643</v>
+        <v>12.46619721279127</v>
       </c>
       <c r="E590" t="n">
-        <v>12.58884455276198</v>
+        <v>12.58884362113043</v>
       </c>
       <c r="F590" t="n">
         <v>4237809</v>
@@ -12232,16 +12232,16 @@
         <v>45092</v>
       </c>
       <c r="B591" t="n">
-        <v>12.83413887023926</v>
+        <v>12.83413791656494</v>
       </c>
       <c r="C591" t="n">
-        <v>13.07943254463561</v>
+        <v>13.0794315727341</v>
       </c>
       <c r="D591" t="n">
-        <v>12.77281524077272</v>
+        <v>12.77281429165521</v>
       </c>
       <c r="E591" t="n">
-        <v>12.86918082372445</v>
+        <v>12.86917986744625</v>
       </c>
       <c r="F591" t="n">
         <v>4574806</v>
@@ -12252,16 +12252,16 @@
         <v>45093</v>
       </c>
       <c r="B592" t="n">
-        <v>11.92304611206055</v>
+        <v>11.92304515838623</v>
       </c>
       <c r="C592" t="n">
-        <v>12.76405556581577</v>
+        <v>12.76405454487264</v>
       </c>
       <c r="D592" t="n">
-        <v>11.66023187024996</v>
+        <v>11.66023093759705</v>
       </c>
       <c r="E592" t="n">
-        <v>12.76405556581577</v>
+        <v>12.76405454487264</v>
       </c>
       <c r="F592" t="n">
         <v>19648730</v>
@@ -12392,16 +12392,16 @@
         <v>45104</v>
       </c>
       <c r="B599" t="n">
-        <v>10.52486133575439</v>
+        <v>10.52486228942871</v>
       </c>
       <c r="C599" t="n">
-        <v>10.94054938590718</v>
+        <v>10.94055037724765</v>
       </c>
       <c r="D599" t="n">
-        <v>10.41872837808194</v>
+        <v>10.41872932213938</v>
       </c>
       <c r="E599" t="n">
-        <v>10.58677286033232</v>
+        <v>10.58677381961654</v>
       </c>
       <c r="F599" t="n">
         <v>17154900</v>
@@ -12452,16 +12452,16 @@
         <v>45107</v>
       </c>
       <c r="B602" t="n">
-        <v>10.71059417724609</v>
+        <v>10.71059513092041</v>
       </c>
       <c r="C602" t="n">
-        <v>11.12628222564065</v>
+        <v>11.12628321632794</v>
       </c>
       <c r="D602" t="n">
-        <v>10.56023894364529</v>
+        <v>10.56023988393194</v>
       </c>
       <c r="E602" t="n">
-        <v>10.83441638240845</v>
+        <v>10.83441734710793</v>
       </c>
       <c r="F602" t="n">
         <v>11622700</v>
@@ -12472,16 +12472,16 @@
         <v>45110</v>
       </c>
       <c r="B603" t="n">
-        <v>10.79019451141357</v>
+        <v>10.79019355773926</v>
       </c>
       <c r="C603" t="n">
-        <v>11.0024604338354</v>
+        <v>11.00245946140029</v>
       </c>
       <c r="D603" t="n">
-        <v>10.66637314506908</v>
+        <v>10.66637220233851</v>
       </c>
       <c r="E603" t="n">
-        <v>10.83441678945224</v>
+        <v>10.8344158318694</v>
       </c>
       <c r="F603" t="n">
         <v>4753300</v>
@@ -12532,16 +12532,16 @@
         <v>45113</v>
       </c>
       <c r="B606" t="n">
-        <v>10.34797382354736</v>
+        <v>10.34797286987305</v>
       </c>
       <c r="C606" t="n">
-        <v>10.56908437893714</v>
+        <v>10.56908340488516</v>
       </c>
       <c r="D606" t="n">
-        <v>10.19761857840473</v>
+        <v>10.19761763858723</v>
       </c>
       <c r="E606" t="n">
-        <v>10.5160183179867</v>
+        <v>10.51601734882532</v>
       </c>
       <c r="F606" t="n">
         <v>6243800</v>
@@ -12552,16 +12552,16 @@
         <v>45114</v>
       </c>
       <c r="B607" t="n">
-        <v>10.52486133575439</v>
+        <v>10.52486228942871</v>
       </c>
       <c r="C607" t="n">
-        <v>10.71943884655545</v>
+        <v>10.71943981786074</v>
       </c>
       <c r="D607" t="n">
-        <v>10.40103997353808</v>
+        <v>10.40104091599275</v>
       </c>
       <c r="E607" t="n">
-        <v>10.52486133575439</v>
+        <v>10.52486228942871</v>
       </c>
       <c r="F607" t="n">
         <v>9448200</v>
@@ -12572,16 +12572,16 @@
         <v>45117</v>
       </c>
       <c r="B608" t="n">
-        <v>10.58677387237549</v>
+        <v>10.58677291870117</v>
       </c>
       <c r="C608" t="n">
-        <v>10.68406221534142</v>
+        <v>10.6840612529032</v>
       </c>
       <c r="D608" t="n">
-        <v>10.41872937406088</v>
+        <v>10.41872843552429</v>
       </c>
       <c r="E608" t="n">
-        <v>10.54255159158376</v>
+        <v>10.54255064189306</v>
       </c>
       <c r="F608" t="n">
         <v>4418500</v>
@@ -12612,16 +12612,16 @@
         <v>45119</v>
       </c>
       <c r="B610" t="n">
-        <v>10.40988445281982</v>
+        <v>10.40988540649414</v>
       </c>
       <c r="C610" t="n">
-        <v>10.7725055973601</v>
+        <v>10.772506584255</v>
       </c>
       <c r="D610" t="n">
-        <v>10.39219520505212</v>
+        <v>10.39219615710589</v>
       </c>
       <c r="E610" t="n">
-        <v>10.61330574132983</v>
+        <v>10.61330671364005</v>
       </c>
       <c r="F610" t="n">
         <v>7787100</v>
@@ -12712,16 +12712,16 @@
         <v>45126</v>
       </c>
       <c r="B615" t="n">
-        <v>9.905752182006836</v>
+        <v>9.905753135681152</v>
       </c>
       <c r="C615" t="n">
-        <v>10.2418403094077</v>
+        <v>10.24184129543884</v>
       </c>
       <c r="D615" t="n">
-        <v>9.720019291692406</v>
+        <v>9.720020227485323</v>
       </c>
       <c r="E615" t="n">
-        <v>10.2418403094077</v>
+        <v>10.24184129543884</v>
       </c>
       <c r="F615" t="n">
         <v>11108100</v>
@@ -12772,16 +12772,16 @@
         <v>45131</v>
       </c>
       <c r="B618" t="n">
-        <v>10.52486133575439</v>
+        <v>10.52486228942871</v>
       </c>
       <c r="C618" t="n">
-        <v>10.64868354144048</v>
+        <v>10.64868450633452</v>
       </c>
       <c r="D618" t="n">
-        <v>10.40988459754489</v>
+        <v>10.40988554080099</v>
       </c>
       <c r="E618" t="n">
-        <v>10.62215051288981</v>
+        <v>10.62215147537965</v>
       </c>
       <c r="F618" t="n">
         <v>4297000</v>
@@ -12792,16 +12792,16 @@
         <v>45132</v>
       </c>
       <c r="B619" t="n">
-        <v>10.53370571136475</v>
+        <v>10.53370666503906</v>
       </c>
       <c r="C619" t="n">
-        <v>10.82557154894893</v>
+        <v>10.82557252904746</v>
       </c>
       <c r="D619" t="n">
-        <v>10.46295040791826</v>
+        <v>10.46295135518671</v>
       </c>
       <c r="E619" t="n">
-        <v>10.61330563860948</v>
+        <v>10.61330659949041</v>
       </c>
       <c r="F619" t="n">
         <v>5058400</v>
@@ -12912,16 +12912,16 @@
         <v>45140</v>
       </c>
       <c r="B625" t="n">
-        <v>10.40988445281982</v>
+        <v>10.40988540649414</v>
       </c>
       <c r="C625" t="n">
-        <v>10.83441627760753</v>
+        <v>10.83441727017422</v>
       </c>
       <c r="D625" t="n">
-        <v>10.25068459678955</v>
+        <v>10.25068553587919</v>
       </c>
       <c r="E625" t="n">
-        <v>10.66637264116317</v>
+        <v>10.66637361833498</v>
       </c>
       <c r="F625" t="n">
         <v>9104400</v>
@@ -12972,16 +12972,16 @@
         <v>45145</v>
       </c>
       <c r="B628" t="n">
-        <v>10.31259632110596</v>
+        <v>10.31259536743164</v>
       </c>
       <c r="C628" t="n">
-        <v>10.80788434363871</v>
+        <v>10.80788334416182</v>
       </c>
       <c r="D628" t="n">
-        <v>10.25953025936985</v>
+        <v>10.25952931060291</v>
       </c>
       <c r="E628" t="n">
-        <v>10.79019509408012</v>
+        <v>10.79019409623906</v>
       </c>
       <c r="F628" t="n">
         <v>9603900</v>
@@ -12992,16 +12992,16 @@
         <v>45146</v>
       </c>
       <c r="B629" t="n">
-        <v>10.53370571136475</v>
+        <v>10.53370666503906</v>
       </c>
       <c r="C629" t="n">
-        <v>10.59561639101298</v>
+        <v>10.59561735029241</v>
       </c>
       <c r="D629" t="n">
-        <v>10.00304093551612</v>
+        <v>10.00304184114644</v>
       </c>
       <c r="E629" t="n">
-        <v>10.24183987378056</v>
+        <v>10.24184080103066</v>
       </c>
       <c r="F629" t="n">
         <v>6465200</v>
@@ -13012,16 +13012,16 @@
         <v>45147</v>
       </c>
       <c r="B630" t="n">
-        <v>10.54255104064941</v>
+        <v>10.5425500869751</v>
       </c>
       <c r="C630" t="n">
-        <v>10.68406165701199</v>
+        <v>10.68406069053669</v>
       </c>
       <c r="D630" t="n">
-        <v>10.3656627701962</v>
+        <v>10.36566183252311</v>
       </c>
       <c r="E630" t="n">
-        <v>10.5337064162593</v>
+        <v>10.53370546338507</v>
       </c>
       <c r="F630" t="n">
         <v>5435200</v>
@@ -13052,16 +13052,16 @@
         <v>45149</v>
       </c>
       <c r="B632" t="n">
-        <v>10.44526195526123</v>
+        <v>10.44526290893555</v>
       </c>
       <c r="C632" t="n">
-        <v>10.78134922333564</v>
+        <v>10.78135020769543</v>
       </c>
       <c r="D632" t="n">
-        <v>10.39219505618805</v>
+        <v>10.39219600501725</v>
       </c>
       <c r="E632" t="n">
-        <v>10.56908331398241</v>
+        <v>10.56908427896187</v>
       </c>
       <c r="F632" t="n">
         <v>4348800</v>
@@ -13072,16 +13072,16 @@
         <v>45152</v>
       </c>
       <c r="B633" t="n">
-        <v>10.44526195526123</v>
+        <v>10.44526290893555</v>
       </c>
       <c r="C633" t="n">
-        <v>10.60446096554128</v>
+        <v>10.6044619337508</v>
       </c>
       <c r="D633" t="n">
-        <v>10.27721747775428</v>
+        <v>10.27721841608578</v>
       </c>
       <c r="E633" t="n">
-        <v>10.42757270774692</v>
+        <v>10.42757365980617</v>
       </c>
       <c r="F633" t="n">
         <v>3064200</v>
@@ -13112,16 +13112,16 @@
         <v>45154</v>
       </c>
       <c r="B635" t="n">
-        <v>10.38335037231445</v>
+        <v>10.38335132598877</v>
       </c>
       <c r="C635" t="n">
-        <v>10.48063954614038</v>
+        <v>10.48064050875037</v>
       </c>
       <c r="D635" t="n">
-        <v>10.25952901431016</v>
+        <v>10.25952995661192</v>
       </c>
       <c r="E635" t="n">
-        <v>10.46295029872849</v>
+        <v>10.46295125971378</v>
       </c>
       <c r="F635" t="n">
         <v>5623400</v>
@@ -13232,16 +13232,16 @@
         <v>45162</v>
       </c>
       <c r="B641" t="n">
-        <v>10.73712825775146</v>
+        <v>10.73712730407715</v>
       </c>
       <c r="C641" t="n">
-        <v>10.99361645355878</v>
+        <v>10.99361547710312</v>
       </c>
       <c r="D641" t="n">
-        <v>10.64868370327869</v>
+        <v>10.64868275746004</v>
       </c>
       <c r="E641" t="n">
-        <v>10.85210584117816</v>
+        <v>10.85210487729151</v>
       </c>
       <c r="F641" t="n">
         <v>5730800</v>
@@ -13312,16 +13312,16 @@
         <v>45168</v>
       </c>
       <c r="B645" t="n">
-        <v>10.53370571136475</v>
+        <v>10.53370666503906</v>
       </c>
       <c r="C645" t="n">
-        <v>10.59561639101298</v>
+        <v>10.59561735029241</v>
       </c>
       <c r="D645" t="n">
-        <v>10.40103972827003</v>
+        <v>10.40104066993336</v>
       </c>
       <c r="E645" t="n">
-        <v>10.5248610875665</v>
+        <v>10.52486204044006</v>
       </c>
       <c r="F645" t="n">
         <v>3749300</v>
@@ -13372,16 +13372,16 @@
         <v>45173</v>
       </c>
       <c r="B648" t="n">
-        <v>10.78135013580322</v>
+        <v>10.78134918212891</v>
       </c>
       <c r="C648" t="n">
-        <v>10.9051723484737</v>
+        <v>10.90517138384658</v>
       </c>
       <c r="D648" t="n">
-        <v>10.5690842084851</v>
+        <v>10.56908327358697</v>
       </c>
       <c r="E648" t="n">
-        <v>10.57792883299081</v>
+        <v>10.57792789731032</v>
       </c>
       <c r="F648" t="n">
         <v>4629200</v>
@@ -13392,16 +13392,16 @@
         <v>45174</v>
       </c>
       <c r="B649" t="n">
-        <v>10.21530723571777</v>
+        <v>10.21530818939209</v>
       </c>
       <c r="C649" t="n">
-        <v>10.73712825115294</v>
+        <v>10.7371292535431</v>
       </c>
       <c r="D649" t="n">
-        <v>10.21530723571777</v>
+        <v>10.21530818939209</v>
       </c>
       <c r="E649" t="n">
-        <v>10.73712825115294</v>
+        <v>10.7371292535431</v>
       </c>
       <c r="F649" t="n">
         <v>8659200</v>
@@ -13472,16 +13472,16 @@
         <v>45181</v>
       </c>
       <c r="B653" t="n">
-        <v>9.843841552734375</v>
+        <v>9.843840599060059</v>
       </c>
       <c r="C653" t="n">
-        <v>9.879219206152881</v>
+        <v>9.879218249051167</v>
       </c>
       <c r="D653" t="n">
-        <v>9.454686521661021</v>
+        <v>9.454685605688161</v>
       </c>
       <c r="E653" t="n">
-        <v>9.560820325386327</v>
+        <v>9.560819399131194</v>
       </c>
       <c r="F653" t="n">
         <v>7074900</v>
@@ -13552,16 +13552,16 @@
         <v>45187</v>
       </c>
       <c r="B657" t="n">
-        <v>8.84442138671875</v>
+        <v>8.844422340393066</v>
       </c>
       <c r="C657" t="n">
-        <v>9.322020107862773</v>
+        <v>9.322021113035499</v>
       </c>
       <c r="D657" t="n">
-        <v>8.773666083102581</v>
+        <v>8.773667029147509</v>
       </c>
       <c r="E657" t="n">
-        <v>9.322020107862773</v>
+        <v>9.322021113035499</v>
       </c>
       <c r="F657" t="n">
         <v>19156300</v>
@@ -13572,16 +13572,16 @@
         <v>45188</v>
       </c>
       <c r="B658" t="n">
-        <v>8.800198554992676</v>
+        <v>8.800199508666992</v>
       </c>
       <c r="C658" t="n">
-        <v>8.950553776543289</v>
+        <v>8.950554746511546</v>
       </c>
       <c r="D658" t="n">
-        <v>8.667532579963169</v>
+        <v>8.667533519260521</v>
       </c>
       <c r="E658" t="n">
-        <v>8.844420827825743</v>
+        <v>8.844421786292413</v>
       </c>
       <c r="F658" t="n">
         <v>8872800</v>
@@ -13612,16 +13612,16 @@
         <v>45190</v>
       </c>
       <c r="B660" t="n">
-        <v>8.932866096496582</v>
+        <v>8.932867050170898</v>
       </c>
       <c r="C660" t="n">
-        <v>8.985932153415543</v>
+        <v>8.985933112755202</v>
       </c>
       <c r="D660" t="n">
-        <v>8.738288586364265</v>
+        <v>8.738289519265452</v>
       </c>
       <c r="E660" t="n">
-        <v>8.853266167648371</v>
+        <v>8.853267112824586</v>
       </c>
       <c r="F660" t="n">
         <v>7093000</v>
@@ -13692,16 +13692,16 @@
         <v>45196</v>
       </c>
       <c r="B664" t="n">
-        <v>8.384511947631836</v>
+        <v>8.38451099395752</v>
       </c>
       <c r="C664" t="n">
-        <v>8.738289346224178</v>
+        <v>8.738288352310379</v>
       </c>
       <c r="D664" t="n">
-        <v>8.181090639303859</v>
+        <v>8.181089708767164</v>
       </c>
       <c r="E664" t="n">
-        <v>8.579089474684132</v>
+        <v>8.579088498878106</v>
       </c>
       <c r="F664" t="n">
         <v>7653500</v>
@@ -13712,16 +13712,16 @@
         <v>45197</v>
       </c>
       <c r="B665" t="n">
-        <v>8.561400413513184</v>
+        <v>8.561399459838867</v>
       </c>
       <c r="C665" t="n">
-        <v>8.676377995996951</v>
+        <v>8.676377029515013</v>
       </c>
       <c r="D665" t="n">
-        <v>8.33144524854565</v>
+        <v>8.331444320486574</v>
       </c>
       <c r="E665" t="n">
-        <v>8.375667525419372</v>
+        <v>8.375666592434273</v>
       </c>
       <c r="F665" t="n">
         <v>5776700</v>
@@ -13732,16 +13732,16 @@
         <v>45198</v>
       </c>
       <c r="B666" t="n">
-        <v>8.623311042785645</v>
+        <v>8.623311996459961</v>
       </c>
       <c r="C666" t="n">
-        <v>8.7559770291329</v>
+        <v>8.755977997479093</v>
       </c>
       <c r="D666" t="n">
-        <v>8.587933390195058</v>
+        <v>8.587934339956869</v>
       </c>
       <c r="E666" t="n">
-        <v>8.702910971981906</v>
+        <v>8.702911934459385</v>
       </c>
       <c r="F666" t="n">
         <v>6662100</v>
@@ -13792,16 +13792,16 @@
         <v>45203</v>
       </c>
       <c r="B669" t="n">
-        <v>7.738868713378906</v>
+        <v>7.738869190216064</v>
       </c>
       <c r="C669" t="n">
-        <v>7.85384629262262</v>
+        <v>7.853846776544223</v>
       </c>
       <c r="D669" t="n">
-        <v>7.632735757954652</v>
+        <v>7.632736228252335</v>
       </c>
       <c r="E669" t="n">
-        <v>7.756557961017825</v>
+        <v>7.756558438944921</v>
       </c>
       <c r="F669" t="n">
         <v>14186500</v>
@@ -13852,16 +13852,16 @@
         <v>45208</v>
       </c>
       <c r="B672" t="n">
-        <v>7.712336540222168</v>
+        <v>7.71233606338501</v>
       </c>
       <c r="C672" t="n">
-        <v>7.809624882610359</v>
+        <v>7.809624399758072</v>
       </c>
       <c r="D672" t="n">
-        <v>7.385093013858421</v>
+        <v>7.385092557254024</v>
       </c>
       <c r="E672" t="n">
-        <v>7.393936795188369</v>
+        <v>7.393936338037181</v>
       </c>
       <c r="F672" t="n">
         <v>4734000</v>
@@ -13892,16 +13892,16 @@
         <v>45210</v>
       </c>
       <c r="B674" t="n">
-        <v>7.933446884155273</v>
+        <v>7.933446407318115</v>
       </c>
       <c r="C674" t="n">
-        <v>8.225312746871069</v>
+        <v>8.22531225249141</v>
       </c>
       <c r="D674" t="n">
-        <v>7.818469295286956</v>
+        <v>7.818468825360488</v>
       </c>
       <c r="E674" t="n">
-        <v>8.20762349775141</v>
+        <v>8.207623004434957</v>
       </c>
       <c r="F674" t="n">
         <v>7415900</v>
@@ -13912,16 +13912,16 @@
         <v>45212</v>
       </c>
       <c r="B675" t="n">
-        <v>7.561981201171875</v>
+        <v>7.561980724334717</v>
       </c>
       <c r="C675" t="n">
-        <v>7.933447003578201</v>
+        <v>7.933446503317459</v>
       </c>
       <c r="D675" t="n">
-        <v>7.50006967179093</v>
+        <v>7.500069198857738</v>
       </c>
       <c r="E675" t="n">
-        <v>7.898069348276162</v>
+        <v>7.898068850246236</v>
       </c>
       <c r="F675" t="n">
         <v>6681200</v>
@@ -13932,16 +13932,16 @@
         <v>45215</v>
       </c>
       <c r="B676" t="n">
-        <v>7.561981201171875</v>
+        <v>7.561980724334717</v>
       </c>
       <c r="C676" t="n">
-        <v>7.721180228296132</v>
+        <v>7.721179741420333</v>
       </c>
       <c r="D676" t="n">
-        <v>7.47353664118186</v>
+        <v>7.473536169921766</v>
       </c>
       <c r="E676" t="n">
-        <v>7.623891887082984</v>
+        <v>7.623891406341913</v>
       </c>
       <c r="F676" t="n">
         <v>6364500</v>
@@ -13992,16 +13992,16 @@
         <v>45218</v>
       </c>
       <c r="B679" t="n">
-        <v>7.066692352294922</v>
+        <v>7.06669282913208</v>
       </c>
       <c r="C679" t="n">
-        <v>7.287802882793285</v>
+        <v>7.287803374550253</v>
       </c>
       <c r="D679" t="n">
-        <v>7.066692352294922</v>
+        <v>7.06669282913208</v>
       </c>
       <c r="E679" t="n">
-        <v>7.199359176675781</v>
+        <v>7.199359662464859</v>
       </c>
       <c r="F679" t="n">
         <v>6424400</v>
@@ -14012,16 +14012,16 @@
         <v>45219</v>
       </c>
       <c r="B680" t="n">
-        <v>7.102070808410645</v>
+        <v>7.102070331573486</v>
       </c>
       <c r="C680" t="n">
-        <v>7.163982337526886</v>
+        <v>7.163981856532952</v>
       </c>
       <c r="D680" t="n">
-        <v>6.916338329736497</v>
+        <v>6.916337865369526</v>
       </c>
       <c r="E680" t="n">
-        <v>7.013626670533689</v>
+        <v>7.013626199634722</v>
       </c>
       <c r="F680" t="n">
         <v>6704900</v>
@@ -14092,16 +14092,16 @@
         <v>45225</v>
       </c>
       <c r="B684" t="n">
-        <v>7.102070808410645</v>
+        <v>7.102070331573486</v>
       </c>
       <c r="C684" t="n">
-        <v>7.137448463561426</v>
+        <v>7.137447984348992</v>
       </c>
       <c r="D684" t="n">
-        <v>6.783671912053608</v>
+        <v>6.783671456593937</v>
       </c>
       <c r="E684" t="n">
-        <v>6.854427222355172</v>
+        <v>6.854426762144948</v>
       </c>
       <c r="F684" t="n">
         <v>6790200</v>
@@ -14172,16 +14172,16 @@
         <v>45231</v>
       </c>
       <c r="B688" t="n">
-        <v>7.013626098632812</v>
+        <v>7.013626575469971</v>
       </c>
       <c r="C688" t="n">
-        <v>7.402780695294118</v>
+        <v>7.402781198588827</v>
       </c>
       <c r="D688" t="n">
-        <v>6.916337765768647</v>
+        <v>6.916338235991438</v>
       </c>
       <c r="E688" t="n">
-        <v>6.969404244167705</v>
+        <v>6.969404717998341</v>
       </c>
       <c r="F688" t="n">
         <v>11133300</v>
@@ -14192,16 +14192,16 @@
         <v>45233</v>
       </c>
       <c r="B689" t="n">
-        <v>8.030735015869141</v>
+        <v>8.030734062194824</v>
       </c>
       <c r="C689" t="n">
-        <v>8.030735015869141</v>
+        <v>8.030734062194824</v>
       </c>
       <c r="D689" t="n">
-        <v>7.234737382440756</v>
+        <v>7.23473652329359</v>
       </c>
       <c r="E689" t="n">
-        <v>7.305492690146844</v>
+        <v>7.305491822597268</v>
       </c>
       <c r="F689" t="n">
         <v>15995000</v>
@@ -14212,16 +14212,16 @@
         <v>45236</v>
       </c>
       <c r="B690" t="n">
-        <v>7.915757656097412</v>
+        <v>7.915757179260254</v>
       </c>
       <c r="C690" t="n">
-        <v>8.119179804165633</v>
+        <v>8.119179315074533</v>
       </c>
       <c r="D690" t="n">
-        <v>7.791936285809632</v>
+        <v>7.791935816431346</v>
       </c>
       <c r="E690" t="n">
-        <v>8.092645930415545</v>
+        <v>8.092645442922818</v>
       </c>
       <c r="F690" t="n">
         <v>6975500</v>
@@ -14272,16 +14272,16 @@
         <v>45239</v>
       </c>
       <c r="B693" t="n">
-        <v>7.95997953414917</v>
+        <v>7.959980010986328</v>
       </c>
       <c r="C693" t="n">
-        <v>8.189934700901784</v>
+        <v>8.189935191514248</v>
       </c>
       <c r="D693" t="n">
-        <v>7.774246644613565</v>
+        <v>7.77424711032452</v>
       </c>
       <c r="E693" t="n">
-        <v>8.189934700901784</v>
+        <v>8.189935191514248</v>
       </c>
       <c r="F693" t="n">
         <v>11094800</v>
@@ -14292,16 +14292,16 @@
         <v>45240</v>
       </c>
       <c r="B694" t="n">
-        <v>7.933446884155273</v>
+        <v>7.933446407318115</v>
       </c>
       <c r="C694" t="n">
-        <v>8.136868188212418</v>
+        <v>8.13686769914869</v>
       </c>
       <c r="D694" t="n">
-        <v>7.933446884155273</v>
+        <v>7.933446407318114</v>
       </c>
       <c r="E694" t="n">
-        <v>8.03957984846376</v>
+        <v>8.039579365247516</v>
       </c>
       <c r="F694" t="n">
         <v>6302800</v>
@@ -14312,16 +14312,16 @@
         <v>45243</v>
       </c>
       <c r="B695" t="n">
-        <v>7.853847026824951</v>
+        <v>7.853846073150635</v>
       </c>
       <c r="C695" t="n">
-        <v>7.933446961701833</v>
+        <v>7.933445998361882</v>
       </c>
       <c r="D695" t="n">
-        <v>7.721180187540206</v>
+        <v>7.721179249975314</v>
       </c>
       <c r="E695" t="n">
-        <v>7.915757712409268</v>
+        <v>7.915756751217281</v>
       </c>
       <c r="F695" t="n">
         <v>4933800</v>
@@ -14332,16 +14332,16 @@
         <v>45244</v>
       </c>
       <c r="B696" t="n">
-        <v>8.508334159851074</v>
+        <v>8.508333206176758</v>
       </c>
       <c r="C696" t="n">
-        <v>8.587934095585465</v>
+        <v>8.587933132989026</v>
       </c>
       <c r="D696" t="n">
-        <v>7.898069391670471</v>
+        <v>7.898068506398949</v>
       </c>
       <c r="E696" t="n">
-        <v>7.915757797683757</v>
+        <v>7.915756910429595</v>
       </c>
       <c r="F696" t="n">
         <v>17983500</v>
@@ -14352,16 +14352,16 @@
         <v>45246</v>
       </c>
       <c r="B697" t="n">
-        <v>8.72944450378418</v>
+        <v>8.729443550109863</v>
       </c>
       <c r="C697" t="n">
-        <v>8.835577467674192</v>
+        <v>8.835576502405061</v>
       </c>
       <c r="D697" t="n">
-        <v>8.517178576004156</v>
+        <v>8.517177645519467</v>
       </c>
       <c r="E697" t="n">
-        <v>8.517178576004156</v>
+        <v>8.517177645519467</v>
       </c>
       <c r="F697" t="n">
         <v>10830700</v>
@@ -14372,16 +14372,16 @@
         <v>45247</v>
       </c>
       <c r="B698" t="n">
-        <v>8.641000747680664</v>
+        <v>8.640999794006348</v>
       </c>
       <c r="C698" t="n">
-        <v>8.826732800998892</v>
+        <v>8.826731826826038</v>
       </c>
       <c r="D698" t="n">
-        <v>8.623311498715223</v>
+        <v>8.623310546993203</v>
       </c>
       <c r="E698" t="n">
-        <v>8.747133711063858</v>
+        <v>8.747132745676051</v>
       </c>
       <c r="F698" t="n">
         <v>7834100</v>
@@ -14392,16 +14392,16 @@
         <v>45250</v>
       </c>
       <c r="B699" t="n">
-        <v>8.932866096496582</v>
+        <v>8.932867050170898</v>
       </c>
       <c r="C699" t="n">
-        <v>8.932866096496582</v>
+        <v>8.932867050170898</v>
       </c>
       <c r="D699" t="n">
-        <v>8.614466381103741</v>
+        <v>8.61446730078565</v>
       </c>
       <c r="E699" t="n">
-        <v>8.676377905468886</v>
+        <v>8.676378831760479</v>
       </c>
       <c r="F699" t="n">
         <v>4921500</v>
@@ -14412,16 +14412,16 @@
         <v>45251</v>
       </c>
       <c r="B700" t="n">
-        <v>8.623311042785645</v>
+        <v>8.623311996459961</v>
       </c>
       <c r="C700" t="n">
-        <v>8.941709916100921</v>
+        <v>8.941710904987794</v>
       </c>
       <c r="D700" t="n">
-        <v>8.614466418770554</v>
+        <v>8.614467371466722</v>
       </c>
       <c r="E700" t="n">
-        <v>8.932866135555601</v>
+        <v>8.932867123464419</v>
       </c>
       <c r="F700" t="n">
         <v>8608600</v>
@@ -14432,16 +14432,16 @@
         <v>45252</v>
       </c>
       <c r="B701" t="n">
-        <v>8.59677791595459</v>
+        <v>8.596778869628906</v>
       </c>
       <c r="C701" t="n">
-        <v>9.030154366103503</v>
+        <v>9.03015536785397</v>
       </c>
       <c r="D701" t="n">
-        <v>8.587933292040589</v>
+        <v>8.587934244733736</v>
       </c>
       <c r="E701" t="n">
-        <v>8.649843972499074</v>
+        <v>8.649844932060216</v>
       </c>
       <c r="F701" t="n">
         <v>12126100</v>
@@ -14472,16 +14472,16 @@
         <v>45254</v>
       </c>
       <c r="B703" t="n">
-        <v>8.366823196411133</v>
+        <v>8.366822242736816</v>
       </c>
       <c r="C703" t="n">
-        <v>8.526023061382888</v>
+        <v>8.526022089562519</v>
       </c>
       <c r="D703" t="n">
-        <v>8.296067888305865</v>
+        <v>8.29606694269644</v>
       </c>
       <c r="E703" t="n">
-        <v>8.517178437002279</v>
+        <v>8.517177466190045</v>
       </c>
       <c r="F703" t="n">
         <v>8295700</v>
@@ -14512,16 +14512,16 @@
         <v>45258</v>
       </c>
       <c r="B705" t="n">
-        <v>8.057268142700195</v>
+        <v>8.057267189025879</v>
       </c>
       <c r="C705" t="n">
-        <v>8.313756347099856</v>
+        <v>8.313755363067084</v>
       </c>
       <c r="D705" t="n">
-        <v>8.02189048841989</v>
+        <v>8.021889538932944</v>
       </c>
       <c r="E705" t="n">
-        <v>8.0926457969805</v>
+        <v>8.092644839118813</v>
       </c>
       <c r="F705" t="n">
         <v>5106400</v>
@@ -14532,16 +14532,16 @@
         <v>45259</v>
       </c>
       <c r="B706" t="n">
-        <v>8.251845359802246</v>
+        <v>8.25184440612793</v>
       </c>
       <c r="C706" t="n">
-        <v>8.349133694631236</v>
+        <v>8.349132729713206</v>
       </c>
       <c r="D706" t="n">
-        <v>8.128023152635528</v>
+        <v>8.128022213271473</v>
       </c>
       <c r="E706" t="n">
-        <v>8.145712400860679</v>
+        <v>8.14571145945226</v>
       </c>
       <c r="F706" t="n">
         <v>4175000</v>
@@ -14612,16 +14612,16 @@
         <v>45265</v>
       </c>
       <c r="B710" t="n">
-        <v>8.331445693969727</v>
+        <v>8.33144474029541</v>
       </c>
       <c r="C710" t="n">
-        <v>8.472956312755398</v>
+        <v>8.472955342882807</v>
       </c>
       <c r="D710" t="n">
-        <v>8.251845760035332</v>
+        <v>8.251844815472568</v>
       </c>
       <c r="E710" t="n">
-        <v>8.251845760035332</v>
+        <v>8.251844815472568</v>
       </c>
       <c r="F710" t="n">
         <v>4182300</v>
@@ -14652,16 +14652,16 @@
         <v>45267</v>
       </c>
       <c r="B712" t="n">
-        <v>8.340290069580078</v>
+        <v>8.340289115905762</v>
       </c>
       <c r="C712" t="n">
-        <v>8.357978474665433</v>
+        <v>8.357977518968529</v>
       </c>
       <c r="D712" t="n">
-        <v>8.163400957907747</v>
+        <v>8.163400024459897</v>
       </c>
       <c r="E712" t="n">
-        <v>8.243000889466337</v>
+        <v>8.242999946916596</v>
       </c>
       <c r="F712" t="n">
         <v>3161600</v>
@@ -14752,16 +14752,16 @@
         <v>45274</v>
       </c>
       <c r="B717" t="n">
-        <v>8.623311042785645</v>
+        <v>8.623311996459961</v>
       </c>
       <c r="C717" t="n">
-        <v>8.932866135555601</v>
+        <v>8.932867123464419</v>
       </c>
       <c r="D717" t="n">
-        <v>8.596778014210148</v>
+        <v>8.596778964950108</v>
       </c>
       <c r="E717" t="n">
-        <v>8.685221723951727</v>
+        <v>8.685222684472906</v>
       </c>
       <c r="F717" t="n">
         <v>9075200</v>
@@ -14772,16 +14772,16 @@
         <v>45275</v>
       </c>
       <c r="B718" t="n">
-        <v>8.791355133056641</v>
+        <v>8.791356086730957</v>
       </c>
       <c r="C718" t="n">
-        <v>8.791355133056641</v>
+        <v>8.791356086730957</v>
       </c>
       <c r="D718" t="n">
-        <v>8.534866927739781</v>
+        <v>8.534867853590605</v>
       </c>
       <c r="E718" t="n">
-        <v>8.720599824243012</v>
+        <v>8.720600770241887</v>
       </c>
       <c r="F718" t="n">
         <v>7122400</v>
@@ -14792,16 +14792,16 @@
         <v>45278</v>
       </c>
       <c r="B719" t="n">
-        <v>8.835577964782715</v>
+        <v>8.835577011108398</v>
       </c>
       <c r="C719" t="n">
-        <v>8.977088591264421</v>
+        <v>8.977087622316056</v>
       </c>
       <c r="D719" t="n">
-        <v>8.800200308162289</v>
+        <v>8.800199358306484</v>
       </c>
       <c r="E719" t="n">
-        <v>8.809044933184863</v>
+        <v>8.809043982374407</v>
       </c>
       <c r="F719" t="n">
         <v>3928300</v>
@@ -14832,16 +14832,16 @@
         <v>45280</v>
       </c>
       <c r="B721" t="n">
-        <v>8.676929473876953</v>
+        <v>8.67693042755127</v>
       </c>
       <c r="C721" t="n">
-        <v>9.033140576382147</v>
+        <v>9.033141569207338</v>
       </c>
       <c r="D721" t="n">
-        <v>8.622127430780413</v>
+        <v>8.622128378431482</v>
       </c>
       <c r="E721" t="n">
-        <v>8.950937947261799</v>
+        <v>8.950938931052166</v>
       </c>
       <c r="F721" t="n">
         <v>6032100</v>
@@ -14872,16 +14872,16 @@
         <v>45282</v>
       </c>
       <c r="B723" t="n">
-        <v>8.887002944946289</v>
+        <v>8.887001991271973</v>
       </c>
       <c r="C723" t="n">
-        <v>9.005739990602331</v>
+        <v>9.005739024186209</v>
       </c>
       <c r="D723" t="n">
-        <v>8.731732361756549</v>
+        <v>8.731731424744495</v>
       </c>
       <c r="E723" t="n">
-        <v>8.95093881325278</v>
+        <v>8.950937852717432</v>
       </c>
       <c r="F723" t="n">
         <v>62444400</v>
@@ -14932,16 +14932,16 @@
         <v>45288</v>
       </c>
       <c r="B726" t="n">
-        <v>9.197546005249023</v>
+        <v>9.197545051574707</v>
       </c>
       <c r="C726" t="n">
-        <v>9.33455069298248</v>
+        <v>9.334549725102434</v>
       </c>
       <c r="D726" t="n">
-        <v>8.96920573007562</v>
+        <v>8.969204800077428</v>
       </c>
       <c r="E726" t="n">
-        <v>9.097076597750373</v>
+        <v>9.097075654493521</v>
       </c>
       <c r="F726" t="n">
         <v>16865200</v>
@@ -15092,16 +15092,16 @@
         <v>45302</v>
       </c>
       <c r="B734" t="n">
-        <v>8.676929473876953</v>
+        <v>8.67693042755127</v>
       </c>
       <c r="C734" t="n">
-        <v>8.841334732117646</v>
+        <v>8.841335703861612</v>
       </c>
       <c r="D734" t="n">
-        <v>8.640395068828902</v>
+        <v>8.640396018487751</v>
       </c>
       <c r="E734" t="n">
-        <v>8.640395068828902</v>
+        <v>8.640396018487751</v>
       </c>
       <c r="F734" t="n">
         <v>4234100</v>
@@ -15112,16 +15112,16 @@
         <v>45303</v>
       </c>
       <c r="B735" t="n">
-        <v>8.676929473876953</v>
+        <v>8.67693042755127</v>
       </c>
       <c r="C735" t="n">
-        <v>8.969204714261362</v>
+        <v>8.969205700059415</v>
       </c>
       <c r="D735" t="n">
-        <v>8.640395068828902</v>
+        <v>8.640396018487751</v>
       </c>
       <c r="E735" t="n">
-        <v>8.640395068828902</v>
+        <v>8.640396018487751</v>
       </c>
       <c r="F735" t="n">
         <v>4898500</v>
@@ -15132,16 +15132,16 @@
         <v>45306</v>
       </c>
       <c r="B736" t="n">
-        <v>8.704331398010254</v>
+        <v>8.704330444335938</v>
       </c>
       <c r="C736" t="n">
-        <v>8.759133449531467</v>
+        <v>8.759132489852862</v>
       </c>
       <c r="D736" t="n">
-        <v>8.585594345588509</v>
+        <v>8.585593404923404</v>
       </c>
       <c r="E736" t="n">
-        <v>8.585594345588509</v>
+        <v>8.585593404923404</v>
       </c>
       <c r="F736" t="n">
         <v>2435000</v>
@@ -15212,16 +15212,16 @@
         <v>45310</v>
       </c>
       <c r="B740" t="n">
-        <v>7.763569355010986</v>
+        <v>7.763568878173828</v>
       </c>
       <c r="C740" t="n">
-        <v>7.845771993431888</v>
+        <v>7.845771511545856</v>
       </c>
       <c r="D740" t="n">
-        <v>7.498694670681984</v>
+        <v>7.498694210113386</v>
       </c>
       <c r="E740" t="n">
-        <v>7.690500536647746</v>
+        <v>7.690500064298463</v>
       </c>
       <c r="F740" t="n">
         <v>7953500</v>
@@ -15252,16 +15252,16 @@
         <v>45314</v>
       </c>
       <c r="B742" t="n">
-        <v>7.608297824859619</v>
+        <v>7.608297348022461</v>
       </c>
       <c r="C742" t="n">
-        <v>7.727034871317152</v>
+        <v>7.727034387038351</v>
       </c>
       <c r="D742" t="n">
-        <v>7.443892549603185</v>
+        <v>7.443892083069849</v>
       </c>
       <c r="E742" t="n">
-        <v>7.443892549603185</v>
+        <v>7.443892083069849</v>
       </c>
       <c r="F742" t="n">
         <v>3836100</v>
@@ -15272,16 +15272,16 @@
         <v>45315</v>
       </c>
       <c r="B743" t="n">
-        <v>7.489560127258301</v>
+        <v>7.489560604095459</v>
       </c>
       <c r="C743" t="n">
-        <v>7.727034199527327</v>
+        <v>7.727034691483726</v>
       </c>
       <c r="D743" t="n">
-        <v>7.416491315952283</v>
+        <v>7.416491788137376</v>
       </c>
       <c r="E743" t="n">
-        <v>7.699633613049805</v>
+        <v>7.699634103261693</v>
       </c>
       <c r="F743" t="n">
         <v>5274600</v>
@@ -15312,16 +15312,16 @@
         <v>45317</v>
       </c>
       <c r="B745" t="n">
-        <v>7.471293449401855</v>
+        <v>7.471293926239014</v>
       </c>
       <c r="C745" t="n">
-        <v>7.553496080867482</v>
+        <v>7.553496562951024</v>
       </c>
       <c r="D745" t="n">
-        <v>7.407357585456952</v>
+        <v>7.407358058213559</v>
       </c>
       <c r="E745" t="n">
-        <v>7.489560216922579</v>
+        <v>7.489560694925569</v>
       </c>
       <c r="F745" t="n">
         <v>5075500</v>
@@ -15452,16 +15452,16 @@
         <v>45328</v>
       </c>
       <c r="B752" t="n">
-        <v>7.26121997833252</v>
+        <v>7.261220455169678</v>
       </c>
       <c r="C752" t="n">
-        <v>7.47129346713769</v>
+        <v>7.471293957770166</v>
       </c>
       <c r="D752" t="n">
-        <v>7.087681766753425</v>
+        <v>7.087682232194499</v>
       </c>
       <c r="E752" t="n">
-        <v>7.087681766753425</v>
+        <v>7.087682232194499</v>
       </c>
       <c r="F752" t="n">
         <v>7301900</v>
@@ -15512,16 +15512,16 @@
         <v>45331</v>
       </c>
       <c r="B755" t="n">
-        <v>7.26121997833252</v>
+        <v>7.261220455169678</v>
       </c>
       <c r="C755" t="n">
-        <v>7.47129346713769</v>
+        <v>7.471293957770166</v>
       </c>
       <c r="D755" t="n">
-        <v>7.206418369066836</v>
+        <v>7.206418842305226</v>
       </c>
       <c r="E755" t="n">
-        <v>7.352556429299803</v>
+        <v>7.352556912134935</v>
       </c>
       <c r="F755" t="n">
         <v>5959300</v>
@@ -15552,16 +15552,16 @@
         <v>45337</v>
       </c>
       <c r="B757" t="n">
-        <v>7.26121997833252</v>
+        <v>7.261220455169678</v>
       </c>
       <c r="C757" t="n">
-        <v>7.361690248606321</v>
+        <v>7.361690732041263</v>
       </c>
       <c r="D757" t="n">
-        <v>7.124216172930548</v>
+        <v>7.124216640770801</v>
       </c>
       <c r="E757" t="n">
-        <v>7.270353797639038</v>
+        <v>7.270354275076005</v>
       </c>
       <c r="F757" t="n">
         <v>6551500</v>
@@ -15592,16 +15592,16 @@
         <v>45341</v>
       </c>
       <c r="B759" t="n">
-        <v>7.3982253074646</v>
+        <v>7.398224830627441</v>
       </c>
       <c r="C759" t="n">
-        <v>7.526095304840912</v>
+        <v>7.526094819762161</v>
       </c>
       <c r="D759" t="n">
-        <v>7.261220618926942</v>
+        <v>7.261220150920135</v>
       </c>
       <c r="E759" t="n">
-        <v>7.507828535665309</v>
+        <v>7.507828051763903</v>
       </c>
       <c r="F759" t="n">
         <v>5437200</v>
@@ -15712,16 +15712,16 @@
         <v>45349</v>
       </c>
       <c r="B765" t="n">
-        <v>8.384654998779297</v>
+        <v>8.38465404510498</v>
       </c>
       <c r="C765" t="n">
-        <v>8.457723815544558</v>
+        <v>8.457722853559364</v>
       </c>
       <c r="D765" t="n">
-        <v>8.101512680527156</v>
+        <v>8.101511759057571</v>
       </c>
       <c r="E765" t="n">
-        <v>8.101512680527156</v>
+        <v>8.101511759057571</v>
       </c>
       <c r="F765" t="n">
         <v>7036800</v>
@@ -15772,16 +15772,16 @@
         <v>45352</v>
       </c>
       <c r="B768" t="n">
-        <v>7.991909027099609</v>
+        <v>7.991909503936768</v>
       </c>
       <c r="C768" t="n">
-        <v>8.128912833430306</v>
+        <v>8.128913318441795</v>
       </c>
       <c r="D768" t="n">
-        <v>7.946240801306391</v>
+        <v>7.946241275418755</v>
       </c>
       <c r="E768" t="n">
-        <v>7.973641388362739</v>
+        <v>7.973641864109958</v>
       </c>
       <c r="F768" t="n">
         <v>3021100</v>
@@ -15852,16 +15852,16 @@
         <v>45358</v>
       </c>
       <c r="B772" t="n">
-        <v>7.635698318481445</v>
+        <v>7.635697841644287</v>
       </c>
       <c r="C772" t="n">
-        <v>7.745301543602346</v>
+        <v>7.745301059920641</v>
       </c>
       <c r="D772" t="n">
-        <v>7.535228913216204</v>
+        <v>7.535228442653199</v>
       </c>
       <c r="E772" t="n">
-        <v>7.717900955084372</v>
+        <v>7.71790047311379</v>
       </c>
       <c r="F772" t="n">
         <v>3046600</v>
@@ -15872,16 +15872,16 @@
         <v>45359</v>
       </c>
       <c r="B773" t="n">
-        <v>7.489560127258301</v>
+        <v>7.489560604095459</v>
       </c>
       <c r="C773" t="n">
-        <v>7.745300966829362</v>
+        <v>7.74530145994875</v>
       </c>
       <c r="D773" t="n">
-        <v>7.471293359956266</v>
+        <v>7.471293835630435</v>
       </c>
       <c r="E773" t="n">
-        <v>7.590030396090778</v>
+        <v>7.590030879324569</v>
       </c>
       <c r="F773" t="n">
         <v>5969600</v>
@@ -15892,16 +15892,16 @@
         <v>45362</v>
       </c>
       <c r="B774" t="n">
-        <v>7.681366920471191</v>
+        <v>7.681366443634033</v>
       </c>
       <c r="C774" t="n">
-        <v>7.699634561071378</v>
+        <v>7.699634083100217</v>
       </c>
       <c r="D774" t="n">
-        <v>7.434759869711995</v>
+        <v>7.434759408183492</v>
       </c>
       <c r="E774" t="n">
-        <v>7.462160459563228</v>
+        <v>7.462159996333776</v>
       </c>
       <c r="F774" t="n">
         <v>4043700</v>
@@ -15912,16 +15912,16 @@
         <v>45363</v>
       </c>
       <c r="B775" t="n">
-        <v>7.873172283172607</v>
+        <v>7.873171806335449</v>
       </c>
       <c r="C775" t="n">
-        <v>7.982775506549723</v>
+        <v>7.982775023074468</v>
       </c>
       <c r="D775" t="n">
-        <v>7.717900832292778</v>
+        <v>7.717900364859606</v>
       </c>
       <c r="E775" t="n">
-        <v>7.727034652003119</v>
+        <v>7.727034184016758</v>
       </c>
       <c r="F775" t="n">
         <v>6470300</v>
@@ -15952,16 +15952,16 @@
         <v>45365</v>
       </c>
       <c r="B777" t="n">
-        <v>7.85490608215332</v>
+        <v>7.854905605316162</v>
       </c>
       <c r="C777" t="n">
-        <v>8.101513134801777</v>
+        <v>8.101512642994178</v>
       </c>
       <c r="D777" t="n">
-        <v>7.781837261290884</v>
+        <v>7.781836788889417</v>
       </c>
       <c r="E777" t="n">
-        <v>8.055844904000491</v>
+        <v>8.055844414965213</v>
       </c>
       <c r="F777" t="n">
         <v>5804500</v>
@@ -15992,16 +15992,16 @@
         <v>45369</v>
       </c>
       <c r="B779" t="n">
-        <v>7.653965473175049</v>
+        <v>7.653965950012207</v>
       </c>
       <c r="C779" t="n">
-        <v>7.836637503467626</v>
+        <v>7.836637991685135</v>
       </c>
       <c r="D779" t="n">
-        <v>7.553496074276368</v>
+        <v>7.553496544854347</v>
       </c>
       <c r="E779" t="n">
-        <v>7.6265648863934</v>
+        <v>7.626565361523518</v>
       </c>
       <c r="F779" t="n">
         <v>6064700</v>
@@ -16012,16 +16012,16 @@
         <v>45370</v>
       </c>
       <c r="B780" t="n">
-        <v>7.571763038635254</v>
+        <v>7.571763515472412</v>
       </c>
       <c r="C780" t="n">
-        <v>7.882305933730743</v>
+        <v>7.882306430124562</v>
       </c>
       <c r="D780" t="n">
-        <v>7.297754550548118</v>
+        <v>7.297755010129397</v>
       </c>
       <c r="E780" t="n">
-        <v>7.580896858149585</v>
+        <v>7.580897335561953</v>
       </c>
       <c r="F780" t="n">
         <v>12953700</v>
@@ -16032,16 +16032,16 @@
         <v>45371</v>
       </c>
       <c r="B781" t="n">
-        <v>8.110647201538086</v>
+        <v>8.11064624786377</v>
       </c>
       <c r="C781" t="n">
-        <v>8.183716024620034</v>
+        <v>8.183715062354066</v>
       </c>
       <c r="D781" t="n">
-        <v>7.535229566480925</v>
+        <v>7.535228680465948</v>
       </c>
       <c r="E781" t="n">
-        <v>7.608298389562875</v>
+        <v>7.608297494956244</v>
       </c>
       <c r="F781" t="n">
         <v>10775600</v>
@@ -16052,16 +16052,16 @@
         <v>45372</v>
       </c>
       <c r="B782" t="n">
-        <v>8.147181510925293</v>
+        <v>8.147180557250977</v>
       </c>
       <c r="C782" t="n">
-        <v>8.229384153624055</v>
+        <v>8.229383190327447</v>
       </c>
       <c r="D782" t="n">
-        <v>8.010177687126737</v>
+        <v>8.010176749489503</v>
       </c>
       <c r="E782" t="n">
-        <v>8.083246509292509</v>
+        <v>8.083245563102151</v>
       </c>
       <c r="F782" t="n">
         <v>10797200</v>
@@ -16092,16 +16092,16 @@
         <v>45376</v>
       </c>
       <c r="B784" t="n">
-        <v>7.727035045623779</v>
+        <v>7.727034568786621</v>
       </c>
       <c r="C784" t="n">
-        <v>7.900573273715461</v>
+        <v>7.900572786169216</v>
       </c>
       <c r="D784" t="n">
-        <v>7.663100046492482</v>
+        <v>7.663099573600767</v>
       </c>
       <c r="E784" t="n">
-        <v>7.809237685106326</v>
+        <v>7.809237203196422</v>
       </c>
       <c r="F784" t="n">
         <v>6131300</v>
@@ -16112,16 +16112,16 @@
         <v>45377</v>
       </c>
       <c r="B785" t="n">
-        <v>7.891440391540527</v>
+        <v>7.891439914703369</v>
       </c>
       <c r="C785" t="n">
-        <v>8.019310390887984</v>
+        <v>8.019309906324331</v>
       </c>
       <c r="D785" t="n">
-        <v>7.672233060710954</v>
+        <v>7.672232597119311</v>
       </c>
       <c r="E785" t="n">
-        <v>7.727035111180608</v>
+        <v>7.727034644277572</v>
       </c>
       <c r="F785" t="n">
         <v>16047100</v>
@@ -16232,16 +16232,16 @@
         <v>45386</v>
       </c>
       <c r="B791" t="n">
-        <v>7.389091014862061</v>
+        <v>7.389091491699219</v>
       </c>
       <c r="C791" t="n">
-        <v>7.608297457246477</v>
+        <v>7.608297948229594</v>
       </c>
       <c r="D791" t="n">
-        <v>7.352556607797991</v>
+        <v>7.35255708227749</v>
       </c>
       <c r="E791" t="n">
-        <v>7.3799571953338</v>
+        <v>7.379957671581529</v>
       </c>
       <c r="F791" t="n">
         <v>5937900</v>
@@ -16272,16 +16272,16 @@
         <v>45390</v>
       </c>
       <c r="B793" t="n">
-        <v>7.507827758789062</v>
+        <v>7.507828235626221</v>
       </c>
       <c r="C793" t="n">
-        <v>7.608297156481334</v>
+        <v>7.608297639699505</v>
       </c>
       <c r="D793" t="n">
-        <v>7.316021911522771</v>
+        <v>7.316022376177957</v>
       </c>
       <c r="E793" t="n">
-        <v>7.343422497975402</v>
+        <v>7.343422964370853</v>
       </c>
       <c r="F793" t="n">
         <v>6349600</v>
@@ -16352,16 +16352,16 @@
         <v>45394</v>
       </c>
       <c r="B797" t="n">
-        <v>7.3982253074646</v>
+        <v>7.398224830627441</v>
       </c>
       <c r="C797" t="n">
-        <v>7.608297943753701</v>
+        <v>7.608297453376751</v>
       </c>
       <c r="D797" t="n">
-        <v>7.34342325783973</v>
+        <v>7.343422784534725</v>
       </c>
       <c r="E797" t="n">
-        <v>7.507828535665309</v>
+        <v>7.507828051763903</v>
       </c>
       <c r="F797" t="n">
         <v>9274900</v>
@@ -16372,16 +16372,16 @@
         <v>45397</v>
       </c>
       <c r="B798" t="n">
-        <v>6.923276901245117</v>
+        <v>6.923276424407959</v>
       </c>
       <c r="C798" t="n">
-        <v>7.434759488163705</v>
+        <v>7.434758976098444</v>
       </c>
       <c r="D798" t="n">
-        <v>6.850208084692319</v>
+        <v>6.850207612887738</v>
       </c>
       <c r="E798" t="n">
-        <v>7.416491848501004</v>
+        <v>7.416491337693918</v>
       </c>
       <c r="F798" t="n">
         <v>10745000</v>
@@ -16452,16 +16452,16 @@
         <v>45401</v>
       </c>
       <c r="B802" t="n">
-        <v>6.749737739562988</v>
+        <v>6.749738216400146</v>
       </c>
       <c r="C802" t="n">
-        <v>6.877608594495325</v>
+        <v>6.877609080365956</v>
       </c>
       <c r="D802" t="n">
-        <v>6.704069950393841</v>
+        <v>6.704070424004785</v>
       </c>
       <c r="E802" t="n">
-        <v>6.777138761484052</v>
+        <v>6.777139240256963</v>
       </c>
       <c r="F802" t="n">
         <v>8757100</v>
@@ -16592,16 +16592,16 @@
         <v>45412</v>
       </c>
       <c r="B809" t="n">
-        <v>6.493997097015381</v>
+        <v>6.493997573852539</v>
       </c>
       <c r="C809" t="n">
-        <v>6.786272350209661</v>
+        <v>6.786272848507823</v>
       </c>
       <c r="D809" t="n">
-        <v>6.475729893690739</v>
+        <v>6.475730369186584</v>
       </c>
       <c r="E809" t="n">
-        <v>6.749737943560375</v>
+        <v>6.749738439175912</v>
       </c>
       <c r="F809" t="n">
         <v>8369300</v>
@@ -16712,16 +16712,16 @@
         <v>45421</v>
       </c>
       <c r="B815" t="n">
-        <v>7.3982253074646</v>
+        <v>7.398224830627441</v>
       </c>
       <c r="C815" t="n">
-        <v>7.434759716864836</v>
+        <v>7.434759237672929</v>
       </c>
       <c r="D815" t="n">
-        <v>7.233820029639022</v>
+        <v>7.233819563398263</v>
       </c>
       <c r="E815" t="n">
-        <v>7.316022668551811</v>
+        <v>7.316022197012852</v>
       </c>
       <c r="F815" t="n">
         <v>6908300</v>
@@ -16792,16 +16792,16 @@
         <v>45427</v>
       </c>
       <c r="B819" t="n">
-        <v>7.379957675933838</v>
+        <v>7.37995719909668</v>
       </c>
       <c r="C819" t="n">
-        <v>7.453026494820389</v>
+        <v>7.453026013262074</v>
       </c>
       <c r="D819" t="n">
-        <v>7.22468621803766</v>
+        <v>7.224685751232972</v>
       </c>
       <c r="E819" t="n">
-        <v>7.252087242882374</v>
+        <v>7.252086774307239</v>
       </c>
       <c r="F819" t="n">
         <v>4894000</v>
@@ -16932,16 +16932,16 @@
         <v>45436</v>
       </c>
       <c r="B826" t="n">
-        <v>7.453026294708252</v>
+        <v>7.453025817871094</v>
       </c>
       <c r="C826" t="n">
-        <v>7.644832156897759</v>
+        <v>7.644831667789053</v>
       </c>
       <c r="D826" t="n">
-        <v>7.453026294708252</v>
+        <v>7.453025817871094</v>
       </c>
       <c r="E826" t="n">
-        <v>7.635698337019924</v>
+        <v>7.635697848495591</v>
       </c>
       <c r="F826" t="n">
         <v>5755300</v>
@@ -16952,16 +16952,16 @@
         <v>45439</v>
       </c>
       <c r="B827" t="n">
-        <v>7.453026294708252</v>
+        <v>7.453025817871094</v>
       </c>
       <c r="C827" t="n">
-        <v>7.489560703170587</v>
+        <v>7.489560223995992</v>
       </c>
       <c r="D827" t="n">
-        <v>7.34342306932125</v>
+        <v>7.343422599496395</v>
       </c>
       <c r="E827" t="n">
-        <v>7.489560703170587</v>
+        <v>7.489560223995992</v>
       </c>
       <c r="F827" t="n">
         <v>2664100</v>
@@ -17032,16 +17032,16 @@
         <v>45446</v>
       </c>
       <c r="B831" t="n">
-        <v>7.3982253074646</v>
+        <v>7.398224830627441</v>
       </c>
       <c r="C831" t="n">
-        <v>7.644832353153937</v>
+        <v>7.644831860422237</v>
       </c>
       <c r="D831" t="n">
-        <v>7.370823847127651</v>
+        <v>7.370823372056597</v>
       </c>
       <c r="E831" t="n">
-        <v>7.443892665928123</v>
+        <v>7.443892186147571</v>
       </c>
       <c r="F831" t="n">
         <v>4697400</v>
@@ -17052,16 +17052,16 @@
         <v>45447</v>
       </c>
       <c r="B832" t="n">
-        <v>7.133349895477295</v>
+        <v>7.133349418640137</v>
       </c>
       <c r="C832" t="n">
-        <v>7.389091186386852</v>
+        <v>7.389090692454367</v>
       </c>
       <c r="D832" t="n">
-        <v>7.005479467784764</v>
+        <v>7.005478999495256</v>
       </c>
       <c r="E832" t="n">
-        <v>7.389091186386852</v>
+        <v>7.389090692454367</v>
       </c>
       <c r="F832" t="n">
         <v>9916900</v>
@@ -17072,16 +17072,16 @@
         <v>45448</v>
       </c>
       <c r="B833" t="n">
-        <v>6.950677871704102</v>
+        <v>6.950677394866943</v>
       </c>
       <c r="C833" t="n">
-        <v>7.233819751428645</v>
+        <v>7.233819255167113</v>
       </c>
       <c r="D833" t="n">
-        <v>6.850208031955233</v>
+        <v>6.850207562010604</v>
       </c>
       <c r="E833" t="n">
-        <v>7.096815503684641</v>
+        <v>7.096815016822007</v>
       </c>
       <c r="F833" t="n">
         <v>9111500</v>
@@ -17092,16 +17092,16 @@
         <v>45449</v>
       </c>
       <c r="B834" t="n">
-        <v>7.069414138793945</v>
+        <v>7.069414615631104</v>
       </c>
       <c r="C834" t="n">
-        <v>7.133349567462498</v>
+        <v>7.133350048612147</v>
       </c>
       <c r="D834" t="n">
-        <v>6.932410333185509</v>
+        <v>6.93241080078166</v>
       </c>
       <c r="E834" t="n">
-        <v>6.978078123213496</v>
+        <v>6.978078593889973</v>
       </c>
       <c r="F834" t="n">
         <v>8384200</v>
@@ -17132,16 +17132,16 @@
         <v>45453</v>
       </c>
       <c r="B836" t="n">
-        <v>6.923276901245117</v>
+        <v>6.923276424407959</v>
       </c>
       <c r="C836" t="n">
-        <v>6.987212333491066</v>
+        <v>6.987211852250387</v>
       </c>
       <c r="D836" t="n">
-        <v>6.786272652446371</v>
+        <v>6.78627218504531</v>
       </c>
       <c r="E836" t="n">
-        <v>6.941544105383317</v>
+        <v>6.941543627288014</v>
       </c>
       <c r="F836" t="n">
         <v>7457900</v>
@@ -17232,16 +17232,16 @@
         <v>45460</v>
       </c>
       <c r="B841" t="n">
-        <v>6.448329448699951</v>
+        <v>6.448328971862793</v>
       </c>
       <c r="C841" t="n">
-        <v>6.65840252351774</v>
+        <v>6.658402031146226</v>
       </c>
       <c r="D841" t="n">
-        <v>6.448329448699951</v>
+        <v>6.448328971862793</v>
       </c>
       <c r="E841" t="n">
-        <v>6.64013531855639</v>
+        <v>6.640134827535688</v>
       </c>
       <c r="F841" t="n">
         <v>3992100</v>
@@ -17252,16 +17252,16 @@
         <v>45461</v>
       </c>
       <c r="B842" t="n">
-        <v>6.493997097015381</v>
+        <v>6.493997573852539</v>
       </c>
       <c r="C842" t="n">
-        <v>6.557932090889389</v>
+        <v>6.557932572421126</v>
       </c>
       <c r="D842" t="n">
-        <v>6.402661080392169</v>
+        <v>6.402661550522763</v>
       </c>
       <c r="E842" t="n">
-        <v>6.448328870941534</v>
+        <v>6.448329344425394</v>
       </c>
       <c r="F842" t="n">
         <v>3102800</v>
@@ -17312,16 +17312,16 @@
         <v>45464</v>
       </c>
       <c r="B845" t="n">
-        <v>6.850208282470703</v>
+        <v>6.850207805633545</v>
       </c>
       <c r="C845" t="n">
-        <v>6.932410921228196</v>
+        <v>6.932410438668982</v>
       </c>
       <c r="D845" t="n">
-        <v>6.58533359705713</v>
+        <v>6.585333138657673</v>
       </c>
       <c r="E845" t="n">
-        <v>6.694936825050778</v>
+        <v>6.694936359021934</v>
       </c>
       <c r="F845" t="n">
         <v>6960600</v>
@@ -17372,16 +17372,16 @@
         <v>45469</v>
       </c>
       <c r="B848" t="n">
-        <v>7.042014122009277</v>
+        <v>7.042013645172119</v>
       </c>
       <c r="C848" t="n">
-        <v>7.069414711139547</v>
+        <v>7.069414232447009</v>
       </c>
       <c r="D848" t="n">
-        <v>6.731471208369463</v>
+        <v>6.731470752560154</v>
       </c>
       <c r="E848" t="n">
-        <v>6.804540026749534</v>
+        <v>6.804539565992502</v>
       </c>
       <c r="F848" t="n">
         <v>4179500</v>
@@ -17392,16 +17392,16 @@
         <v>45470</v>
       </c>
       <c r="B849" t="n">
-        <v>7.069414138793945</v>
+        <v>7.069414615631104</v>
       </c>
       <c r="C849" t="n">
-        <v>7.124216183666692</v>
+        <v>7.124216664200287</v>
       </c>
       <c r="D849" t="n">
-        <v>6.850207701400866</v>
+        <v>6.85020816345239</v>
       </c>
       <c r="E849" t="n">
-        <v>7.051146935677855</v>
+        <v>7.051147411282877</v>
       </c>
       <c r="F849" t="n">
         <v>6848800</v>
@@ -17492,16 +17492,16 @@
         <v>45477</v>
       </c>
       <c r="B854" t="n">
-        <v>7.991909027099609</v>
+        <v>7.991909503936768</v>
       </c>
       <c r="C854" t="n">
-        <v>8.110646065742392</v>
+        <v>8.110646549663995</v>
       </c>
       <c r="D854" t="n">
-        <v>7.580896737058564</v>
+        <v>7.580897189372679</v>
       </c>
       <c r="E854" t="n">
-        <v>7.580896737058564</v>
+        <v>7.580897189372679</v>
       </c>
       <c r="F854" t="n">
         <v>16897700</v>
@@ -17512,16 +17512,16 @@
         <v>45478</v>
       </c>
       <c r="B855" t="n">
-        <v>8.220249176025391</v>
+        <v>8.220250129699707</v>
       </c>
       <c r="C855" t="n">
-        <v>8.229382995272722</v>
+        <v>8.229383950006699</v>
       </c>
       <c r="D855" t="n">
-        <v>7.845771297374288</v>
+        <v>7.845772207603456</v>
       </c>
       <c r="E855" t="n">
-        <v>7.991908921135797</v>
+        <v>7.99190984831916</v>
       </c>
       <c r="F855" t="n">
         <v>7882000</v>
@@ -17552,16 +17552,16 @@
         <v>45482</v>
       </c>
       <c r="B857" t="n">
-        <v>8.275052070617676</v>
+        <v>8.275051116943359</v>
       </c>
       <c r="C857" t="n">
-        <v>8.293318839940072</v>
+        <v>8.293317884160565</v>
       </c>
       <c r="D857" t="n">
-        <v>8.01931033171185</v>
+        <v>8.019309407510983</v>
       </c>
       <c r="E857" t="n">
-        <v>8.138047380979048</v>
+        <v>8.138046443094101</v>
       </c>
       <c r="F857" t="n">
         <v>6492100</v>
@@ -17612,16 +17612,16 @@
         <v>45485</v>
       </c>
       <c r="B860" t="n">
-        <v>8.357254028320312</v>
+        <v>8.357253074645996</v>
       </c>
       <c r="C860" t="n">
-        <v>8.57646136249438</v>
+        <v>8.576460383805578</v>
       </c>
       <c r="D860" t="n">
-        <v>8.275052257935224</v>
+        <v>8.275051313641228</v>
       </c>
       <c r="E860" t="n">
-        <v>8.57646136249438</v>
+        <v>8.576460383805578</v>
       </c>
       <c r="F860" t="n">
         <v>9959600</v>
@@ -17812,16 +17812,16 @@
         <v>45499</v>
       </c>
       <c r="B870" t="n">
-        <v>8.165447235107422</v>
+        <v>8.165448188781738</v>
       </c>
       <c r="C870" t="n">
-        <v>8.165447235107422</v>
+        <v>8.165448188781738</v>
       </c>
       <c r="D870" t="n">
-        <v>7.891439622605347</v>
+        <v>7.891440544277249</v>
       </c>
       <c r="E870" t="n">
-        <v>8.03757724821951</v>
+        <v>8.037578186959392</v>
       </c>
       <c r="F870" t="n">
         <v>4118500</v>
@@ -17852,16 +17852,16 @@
         <v>45503</v>
       </c>
       <c r="B872" t="n">
-        <v>7.635698318481445</v>
+        <v>7.635697841644287</v>
       </c>
       <c r="C872" t="n">
-        <v>7.781836823024983</v>
+        <v>7.781836337061709</v>
       </c>
       <c r="D872" t="n">
-        <v>7.544362733071863</v>
+        <v>7.544362261938466</v>
       </c>
       <c r="E872" t="n">
-        <v>7.763569183313664</v>
+        <v>7.763568698491175</v>
       </c>
       <c r="F872" t="n">
         <v>8186100</v>
@@ -17872,16 +17872,16 @@
         <v>45504</v>
       </c>
       <c r="B873" t="n">
-        <v>7.882306098937988</v>
+        <v>7.882306575775146</v>
       </c>
       <c r="C873" t="n">
-        <v>7.918840506712075</v>
+        <v>7.91884098575937</v>
       </c>
       <c r="D873" t="n">
-        <v>7.553496428971203</v>
+        <v>7.553496885917143</v>
       </c>
       <c r="E873" t="n">
-        <v>7.663099652293464</v>
+        <v>7.663100115869812</v>
       </c>
       <c r="F873" t="n">
         <v>7542900</v>
@@ -17972,16 +17972,16 @@
         <v>45511</v>
       </c>
       <c r="B878" t="n">
-        <v>7.59916353225708</v>
+        <v>7.599164009094238</v>
       </c>
       <c r="C878" t="n">
-        <v>7.635697938814125</v>
+        <v>7.635698417943767</v>
       </c>
       <c r="D878" t="n">
-        <v>7.398224731717812</v>
+        <v>7.398225195946334</v>
       </c>
       <c r="E878" t="n">
-        <v>7.498694131987445</v>
+        <v>7.498694602520287</v>
       </c>
       <c r="F878" t="n">
         <v>13715500</v>
@@ -17992,16 +17992,16 @@
         <v>45512</v>
       </c>
       <c r="B879" t="n">
-        <v>7.59916353225708</v>
+        <v>7.599164009094238</v>
       </c>
       <c r="C879" t="n">
-        <v>7.763568797288263</v>
+        <v>7.763569284441628</v>
       </c>
       <c r="D879" t="n">
-        <v>7.480426493184443</v>
+        <v>7.480426962571014</v>
       </c>
       <c r="E879" t="n">
-        <v>7.635697938814125</v>
+        <v>7.635698417943767</v>
       </c>
       <c r="F879" t="n">
         <v>7650900</v>
@@ -18012,16 +18012,16 @@
         <v>45513</v>
       </c>
       <c r="B880" t="n">
-        <v>7.745301246643066</v>
+        <v>7.745301723480225</v>
       </c>
       <c r="C880" t="n">
-        <v>7.873172106572643</v>
+        <v>7.873172591282133</v>
       </c>
       <c r="D880" t="n">
-        <v>7.507828036843809</v>
+        <v>7.507828499061</v>
       </c>
       <c r="E880" t="n">
-        <v>7.653965664735343</v>
+        <v>7.653966135949453</v>
       </c>
       <c r="F880" t="n">
         <v>7501500</v>
@@ -18052,16 +18052,16 @@
         <v>45517</v>
       </c>
       <c r="B882" t="n">
-        <v>7.699633598327637</v>
+        <v>7.699634552001953</v>
       </c>
       <c r="C882" t="n">
-        <v>7.800102995919072</v>
+        <v>7.800103962037498</v>
       </c>
       <c r="D882" t="n">
-        <v>7.635697735270417</v>
+        <v>7.635698681025655</v>
       </c>
       <c r="E882" t="n">
-        <v>7.717900365594744</v>
+        <v>7.717901321531577</v>
       </c>
       <c r="F882" t="n">
         <v>7752600</v>
@@ -18072,16 +18072,16 @@
         <v>45518</v>
       </c>
       <c r="B883" t="n">
-        <v>7.59916353225708</v>
+        <v>7.599164009094238</v>
       </c>
       <c r="C883" t="n">
-        <v>7.818370842648312</v>
+        <v>7.81837133324043</v>
       </c>
       <c r="D883" t="n">
-        <v>7.462159725430401</v>
+        <v>7.462160193670757</v>
       </c>
       <c r="E883" t="n">
-        <v>7.763568797288263</v>
+        <v>7.763569284441628</v>
       </c>
       <c r="F883" t="n">
         <v>7383100</v>
@@ -18152,16 +18152,16 @@
         <v>45524</v>
       </c>
       <c r="B887" t="n">
-        <v>7.745301246643066</v>
+        <v>7.745301723480225</v>
       </c>
       <c r="C887" t="n">
-        <v>8.019309734464178</v>
+        <v>8.019310228170587</v>
       </c>
       <c r="D887" t="n">
-        <v>7.69963389121369</v>
+        <v>7.69963436523935</v>
       </c>
       <c r="E887" t="n">
-        <v>7.937107101012947</v>
+        <v>7.937107589658575</v>
       </c>
       <c r="F887" t="n">
         <v>6543300</v>
@@ -18172,16 +18172,16 @@
         <v>45525</v>
       </c>
       <c r="B888" t="n">
-        <v>7.608297824859619</v>
+        <v>7.608297348022461</v>
       </c>
       <c r="C888" t="n">
-        <v>7.854905737744269</v>
+        <v>7.854905245451379</v>
       </c>
       <c r="D888" t="n">
-        <v>7.489560778402085</v>
+        <v>7.489560309006571</v>
       </c>
       <c r="E888" t="n">
-        <v>7.745301640207304</v>
+        <v>7.745301154783664</v>
       </c>
       <c r="F888" t="n">
         <v>7135600</v>
@@ -18192,16 +18192,16 @@
         <v>45526</v>
       </c>
       <c r="B889" t="n">
-        <v>7.279487133026123</v>
+        <v>7.279487609863281</v>
       </c>
       <c r="C889" t="n">
-        <v>7.663099266384561</v>
+        <v>7.663099768349934</v>
       </c>
       <c r="D889" t="n">
-        <v>7.252086546337681</v>
+        <v>7.252087021379985</v>
       </c>
       <c r="E889" t="n">
-        <v>7.571762816024495</v>
+        <v>7.571763312006945</v>
       </c>
       <c r="F889" t="n">
         <v>6992500</v>
@@ -18332,16 +18332,16 @@
         <v>45537</v>
       </c>
       <c r="B896" t="n">
-        <v>6.868475437164307</v>
+        <v>6.868474960327148</v>
       </c>
       <c r="C896" t="n">
-        <v>6.941544255295122</v>
+        <v>6.941543773385233</v>
       </c>
       <c r="D896" t="n">
-        <v>6.795406619033491</v>
+        <v>6.795406147269064</v>
       </c>
       <c r="E896" t="n">
-        <v>6.895876461725617</v>
+        <v>6.895875982986171</v>
       </c>
       <c r="F896" t="n">
         <v>5645700</v>
@@ -18452,16 +18452,16 @@
         <v>45545</v>
       </c>
       <c r="B902" t="n">
-        <v>6.749737739562988</v>
+        <v>6.749738216400146</v>
       </c>
       <c r="C902" t="n">
-        <v>6.868474775346815</v>
+        <v>6.868475260572184</v>
       </c>
       <c r="D902" t="n">
-        <v>6.722337153166394</v>
+        <v>6.722337628067829</v>
       </c>
       <c r="E902" t="n">
-        <v>6.777138761484052</v>
+        <v>6.777139240256963</v>
       </c>
       <c r="F902" t="n">
         <v>6841000</v>
@@ -18532,16 +18532,16 @@
         <v>45551</v>
       </c>
       <c r="B906" t="n">
-        <v>6.694936752319336</v>
+        <v>6.694936275482178</v>
       </c>
       <c r="C906" t="n">
-        <v>6.777139390183809</v>
+        <v>6.777138907491886</v>
       </c>
       <c r="D906" t="n">
-        <v>6.640135138917858</v>
+        <v>6.640134665983865</v>
       </c>
       <c r="E906" t="n">
-        <v>6.70407057231517</v>
+        <v>6.704070094827469</v>
       </c>
       <c r="F906" t="n">
         <v>4229100</v>
@@ -18572,16 +18572,16 @@
         <v>45553</v>
       </c>
       <c r="B908" t="n">
-        <v>6.539664745330811</v>
+        <v>6.539665222167969</v>
       </c>
       <c r="C908" t="n">
-        <v>6.850207630620085</v>
+        <v>6.850208130100359</v>
       </c>
       <c r="D908" t="n">
-        <v>6.493996955774693</v>
+        <v>6.493997429282001</v>
       </c>
       <c r="E908" t="n">
-        <v>6.676668985048106</v>
+        <v>6.676669471874876</v>
       </c>
       <c r="F908" t="n">
         <v>10313100</v>
@@ -18632,16 +18632,16 @@
         <v>45558</v>
       </c>
       <c r="B911" t="n">
-        <v>6.028182506561279</v>
+        <v>6.028182983398438</v>
       </c>
       <c r="C911" t="n">
-        <v>6.064716911680935</v>
+        <v>6.064717391408013</v>
       </c>
       <c r="D911" t="n">
-        <v>5.863777683522827</v>
+        <v>5.863778147355347</v>
       </c>
       <c r="E911" t="n">
-        <v>5.991648101441623</v>
+        <v>5.991648575388862</v>
       </c>
       <c r="F911" t="n">
         <v>7689600</v>
@@ -18712,16 +18712,16 @@
         <v>45562</v>
       </c>
       <c r="B915" t="n">
-        <v>5.93684720993042</v>
+        <v>5.936846733093262</v>
       </c>
       <c r="C915" t="n">
-        <v>6.137786462328047</v>
+        <v>6.137785969351801</v>
       </c>
       <c r="D915" t="n">
-        <v>5.927713389786452</v>
+        <v>5.927712913682906</v>
       </c>
       <c r="E915" t="n">
-        <v>6.037317053891492</v>
+        <v>6.037316568984771</v>
       </c>
       <c r="F915" t="n">
         <v>5348400</v>
@@ -18792,16 +18792,16 @@
         <v>45568</v>
       </c>
       <c r="B919" t="n">
-        <v>5.270093441009521</v>
+        <v>5.270092964172363</v>
       </c>
       <c r="C919" t="n">
-        <v>5.489300327798264</v>
+        <v>5.489299831127303</v>
       </c>
       <c r="D919" t="n">
-        <v>4.941283328588661</v>
+        <v>4.941282881502185</v>
       </c>
       <c r="E919" t="n">
-        <v>5.480166507900002</v>
+        <v>5.480166012055468</v>
       </c>
       <c r="F919" t="n">
         <v>48426200</v>
@@ -19012,16 +19012,16 @@
         <v>45583</v>
       </c>
       <c r="B930" t="n">
-        <v>5.30662727355957</v>
+        <v>5.306627750396729</v>
       </c>
       <c r="C930" t="n">
-        <v>5.379696082716587</v>
+        <v>5.379696566119483</v>
       </c>
       <c r="D930" t="n">
-        <v>5.169623038627936</v>
+        <v>5.169623503154316</v>
       </c>
       <c r="E930" t="n">
-        <v>5.30662727355957</v>
+        <v>5.306627750396729</v>
       </c>
       <c r="F930" t="n">
         <v>9506300</v>
@@ -19072,16 +19072,16 @@
         <v>45588</v>
       </c>
       <c r="B933" t="n">
-        <v>5.735907554626465</v>
+        <v>5.735908031463623</v>
       </c>
       <c r="C933" t="n">
-        <v>5.927712973407171</v>
+        <v>5.927713466189486</v>
       </c>
       <c r="D933" t="n">
-        <v>5.626303898220296</v>
+        <v>5.626304365945888</v>
       </c>
       <c r="E933" t="n">
-        <v>5.626303898220296</v>
+        <v>5.626304365945888</v>
       </c>
       <c r="F933" t="n">
         <v>15384500</v>
@@ -19092,16 +19092,16 @@
         <v>45589</v>
       </c>
       <c r="B934" t="n">
-        <v>5.836376667022705</v>
+        <v>5.836377143859863</v>
       </c>
       <c r="C934" t="n">
-        <v>5.891178274750094</v>
+        <v>5.891178756064592</v>
       </c>
       <c r="D934" t="n">
-        <v>5.589769214487223</v>
+        <v>5.589769671176334</v>
       </c>
       <c r="E934" t="n">
-        <v>5.717640068042261</v>
+        <v>5.717640535178534</v>
       </c>
       <c r="F934" t="n">
         <v>10139400</v>
@@ -19132,16 +19132,16 @@
         <v>45593</v>
       </c>
       <c r="B936" t="n">
-        <v>5.735907554626465</v>
+        <v>5.735908031463623</v>
       </c>
       <c r="C936" t="n">
-        <v>5.836376956005767</v>
+        <v>5.836377441195141</v>
       </c>
       <c r="D936" t="n">
-        <v>5.717640351146184</v>
+        <v>5.717640826464754</v>
       </c>
       <c r="E936" t="n">
-        <v>5.836376956005767</v>
+        <v>5.836377441195141</v>
       </c>
       <c r="F936" t="n">
         <v>5963100</v>
@@ -19192,16 +19192,16 @@
         <v>45596</v>
       </c>
       <c r="B939" t="n">
-        <v>5.745041370391846</v>
+        <v>5.745040893554688</v>
       </c>
       <c r="C939" t="n">
-        <v>5.973381648819262</v>
+        <v>5.973381153029912</v>
       </c>
       <c r="D939" t="n">
-        <v>5.735907985727498</v>
+        <v>5.735907509648409</v>
       </c>
       <c r="E939" t="n">
-        <v>5.827244009993561</v>
+        <v>5.827243526333603</v>
       </c>
       <c r="F939" t="n">
         <v>7246200</v>
@@ -19212,16 +19212,16 @@
         <v>45597</v>
       </c>
       <c r="B940" t="n">
-        <v>5.270093441009521</v>
+        <v>5.270092964172363</v>
       </c>
       <c r="C940" t="n">
-        <v>5.754175007504804</v>
+        <v>5.754174486868027</v>
       </c>
       <c r="D940" t="n">
-        <v>5.22442521256722</v>
+        <v>5.224424739862115</v>
       </c>
       <c r="E940" t="n">
-        <v>5.745041187606541</v>
+        <v>5.745040667796192</v>
       </c>
       <c r="F940" t="n">
         <v>7357000</v>
@@ -19232,16 +19232,16 @@
         <v>45600</v>
       </c>
       <c r="B941" t="n">
-        <v>5.635437965393066</v>
+        <v>5.635437488555908</v>
       </c>
       <c r="C941" t="n">
-        <v>5.681105758338568</v>
+        <v>5.681105277637273</v>
       </c>
       <c r="D941" t="n">
-        <v>5.352296081242743</v>
+        <v>5.352295628363364</v>
       </c>
       <c r="E941" t="n">
-        <v>5.379696669905143</v>
+        <v>5.379696214707288</v>
       </c>
       <c r="F941" t="n">
         <v>6291500</v>
@@ -19252,16 +19252,16 @@
         <v>45601</v>
       </c>
       <c r="B942" t="n">
-        <v>5.617170810699463</v>
+        <v>5.617170333862305</v>
       </c>
       <c r="C942" t="n">
-        <v>5.726774037365669</v>
+        <v>5.726773551224381</v>
       </c>
       <c r="D942" t="n">
-        <v>5.48016655960445</v>
+        <v>5.480166094397473</v>
       </c>
       <c r="E942" t="n">
-        <v>5.635438015143831</v>
+        <v>5.635437536755984</v>
       </c>
       <c r="F942" t="n">
         <v>5341400</v>
@@ -19272,16 +19272,16 @@
         <v>45602</v>
       </c>
       <c r="B943" t="n">
-        <v>5.580636024475098</v>
+        <v>5.580636501312256</v>
       </c>
       <c r="C943" t="n">
-        <v>5.653704837312009</v>
+        <v>5.653705320392528</v>
       </c>
       <c r="D943" t="n">
-        <v>5.35229576659751</v>
+        <v>5.352296223924147</v>
       </c>
       <c r="E943" t="n">
-        <v>5.461898985852877</v>
+        <v>5.461899452544555</v>
       </c>
       <c r="F943" t="n">
         <v>8155700</v>
@@ -19312,16 +19312,16 @@
         <v>45604</v>
       </c>
       <c r="B945" t="n">
-        <v>5.215291976928711</v>
+        <v>5.215291500091553</v>
       </c>
       <c r="C945" t="n">
-        <v>5.270093591307661</v>
+        <v>5.270093109459959</v>
       </c>
       <c r="D945" t="n">
-        <v>5.10568874817081</v>
+        <v>5.105688281354738</v>
       </c>
       <c r="E945" t="n">
-        <v>5.270093591307661</v>
+        <v>5.270093109459959</v>
       </c>
       <c r="F945" t="n">
         <v>10054800</v>
@@ -19332,16 +19332,16 @@
         <v>45607</v>
       </c>
       <c r="B946" t="n">
-        <v>5.206157684326172</v>
+        <v>5.20615816116333</v>
       </c>
       <c r="C946" t="n">
-        <v>5.224424887461459</v>
+        <v>5.224425365971729</v>
       </c>
       <c r="D946" t="n">
-        <v>5.087421081709041</v>
+        <v>5.087421547670997</v>
       </c>
       <c r="E946" t="n">
-        <v>5.169623278055597</v>
+        <v>5.169623751546532</v>
       </c>
       <c r="F946" t="n">
         <v>6986700</v>
@@ -19412,16 +19412,16 @@
         <v>45614</v>
       </c>
       <c r="B950" t="n">
-        <v>5.096554279327393</v>
+        <v>5.096554756164551</v>
       </c>
       <c r="C950" t="n">
-        <v>5.206157494135098</v>
+        <v>5.206157981226809</v>
       </c>
       <c r="D950" t="n">
-        <v>4.977817245523481</v>
+        <v>4.97781771125152</v>
       </c>
       <c r="E950" t="n">
-        <v>5.06001987439149</v>
+        <v>5.060020347810465</v>
       </c>
       <c r="F950" t="n">
         <v>6191300</v>
@@ -19492,16 +19492,16 @@
         <v>45621</v>
       </c>
       <c r="B954" t="n">
-        <v>5.580636024475098</v>
+        <v>5.580636501312256</v>
       </c>
       <c r="C954" t="n">
-        <v>5.653704837312009</v>
+        <v>5.653705320392528</v>
       </c>
       <c r="D954" t="n">
-        <v>5.324894744021429</v>
+        <v>5.324895199006787</v>
       </c>
       <c r="E954" t="n">
-        <v>5.571502205108245</v>
+        <v>5.571502681164964</v>
       </c>
       <c r="F954" t="n">
         <v>8051200</v>
@@ -19552,16 +19552,16 @@
         <v>45624</v>
       </c>
       <c r="B957" t="n">
-        <v>5.270093441009521</v>
+        <v>5.270092964172363</v>
       </c>
       <c r="C957" t="n">
-        <v>5.589769733532121</v>
+        <v>5.589769227770706</v>
       </c>
       <c r="D957" t="n">
-        <v>5.123955806833363</v>
+        <v>5.123955343218713</v>
       </c>
       <c r="E957" t="n">
-        <v>5.516700916444042</v>
+        <v>5.51670041729388</v>
       </c>
       <c r="F957" t="n">
         <v>16639300</v>
@@ -27812,19 +27812,39 @@
         <v>46232</v>
       </c>
       <c r="B1370" t="n">
-        <v>3.31</v>
+        <v>3.309999942779541</v>
       </c>
       <c r="C1370" t="n">
-        <v>3.35</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="D1370" t="n">
-        <v>3.24</v>
+        <v>3.240000009536743</v>
       </c>
       <c r="E1370" t="n">
-        <v>3.34</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="F1370" t="n">
         <v>6988600</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1371" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="C1371" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>6351000</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1371"/>
+  <dimension ref="A1:F1372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44229</v>
       </c>
       <c r="B2" t="n">
-        <v>6.844326496124268</v>
+        <v>6.844325542449951</v>
       </c>
       <c r="C2" t="n">
-        <v>7.276820633554713</v>
+        <v>7.276819619617557</v>
       </c>
       <c r="D2" t="n">
-        <v>6.844326496124268</v>
+        <v>6.844325542449951</v>
       </c>
       <c r="E2" t="n">
-        <v>7.094165220340723</v>
+        <v>7.094164231854394</v>
       </c>
       <c r="F2" t="n">
         <v>4750609</v>
@@ -472,16 +472,16 @@
         <v>44230</v>
       </c>
       <c r="B3" t="n">
-        <v>6.907310009002686</v>
+        <v>6.907310485839844</v>
       </c>
       <c r="C3" t="n">
-        <v>7.020682790689285</v>
+        <v>7.020683275352985</v>
       </c>
       <c r="D3" t="n">
-        <v>6.657471328058306</v>
+        <v>6.657471787648176</v>
       </c>
       <c r="E3" t="n">
-        <v>6.953498679528491</v>
+        <v>6.953499159554224</v>
       </c>
       <c r="F3" t="n">
         <v>3966477</v>
@@ -492,16 +492,16 @@
         <v>44231</v>
       </c>
       <c r="B4" t="n">
-        <v>6.88631534576416</v>
+        <v>6.886315822601318</v>
       </c>
       <c r="C4" t="n">
-        <v>7.012283929972458</v>
+        <v>7.012284415532206</v>
       </c>
       <c r="D4" t="n">
-        <v>6.806534620056473</v>
+        <v>6.806535091369281</v>
       </c>
       <c r="E4" t="n">
-        <v>6.919906589382284</v>
+        <v>6.91990706854544</v>
       </c>
       <c r="F4" t="n">
         <v>3650229</v>
@@ -512,16 +512,16 @@
         <v>44232</v>
       </c>
       <c r="B5" t="n">
-        <v>6.823330879211426</v>
+        <v>6.823331356048584</v>
       </c>
       <c r="C5" t="n">
-        <v>6.909409509382922</v>
+        <v>6.909409992235542</v>
       </c>
       <c r="D5" t="n">
-        <v>6.699460779521623</v>
+        <v>6.699461247702325</v>
       </c>
       <c r="E5" t="n">
-        <v>6.873718152244995</v>
+        <v>6.873718632603384</v>
       </c>
       <c r="F5" t="n">
         <v>4402737</v>
@@ -532,16 +532,16 @@
         <v>44235</v>
       </c>
       <c r="B6" t="n">
-        <v>7.211735248565674</v>
+        <v>7.211735725402832</v>
       </c>
       <c r="C6" t="n">
-        <v>7.619035262297836</v>
+        <v>7.619035766065515</v>
       </c>
       <c r="D6" t="n">
-        <v>6.827529163796321</v>
+        <v>6.827529615229921</v>
       </c>
       <c r="E6" t="n">
-        <v>6.854822505530665</v>
+        <v>6.85482295876889</v>
       </c>
       <c r="F6" t="n">
         <v>3162478</v>
@@ -552,16 +552,16 @@
         <v>44236</v>
       </c>
       <c r="B7" t="n">
-        <v>7.119358062744141</v>
+        <v>7.119358539581299</v>
       </c>
       <c r="C7" t="n">
-        <v>7.367097444187393</v>
+        <v>7.367097937617529</v>
       </c>
       <c r="D7" t="n">
-        <v>6.953498708270694</v>
+        <v>6.953499173999</v>
       </c>
       <c r="E7" t="n">
-        <v>7.266322088824129</v>
+        <v>7.266322575504579</v>
       </c>
       <c r="F7" t="n">
         <v>1374461</v>
@@ -592,16 +592,16 @@
         <v>44238</v>
       </c>
       <c r="B9" t="n">
-        <v>6.963997364044189</v>
+        <v>6.963996410369873</v>
       </c>
       <c r="C9" t="n">
-        <v>7.058474024208274</v>
+        <v>7.058473057595991</v>
       </c>
       <c r="D9" t="n">
-        <v>6.850624560052649</v>
+        <v>6.850623621904003</v>
       </c>
       <c r="E9" t="n">
-        <v>6.928306000916726</v>
+        <v>6.928305052130111</v>
       </c>
       <c r="F9" t="n">
         <v>1655030</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029079914093018</v>
+        <v>7.029080867767334</v>
       </c>
       <c r="C10" t="n">
-        <v>7.19493926602394</v>
+        <v>7.194940242201317</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913607833174078</v>
+        <v>6.913608771181656</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949299188880033</v>
+        <v>6.949300131730055</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -632,16 +632,16 @@
         <v>44244</v>
       </c>
       <c r="B11" t="n">
-        <v>7.274720668792725</v>
+        <v>7.274719715118408</v>
       </c>
       <c r="C11" t="n">
-        <v>7.388092647974826</v>
+        <v>7.38809167943809</v>
       </c>
       <c r="D11" t="n">
-        <v>7.11305990280828</v>
+        <v>7.113058970326766</v>
       </c>
       <c r="E11" t="n">
-        <v>7.11725931599718</v>
+        <v>7.117258382965146</v>
       </c>
       <c r="F11" t="n">
         <v>2613098</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.222233295440674</v>
+        <v>7.22223424911499</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379694648559866</v>
+        <v>7.379695623026483</v>
       </c>
       <c r="D12" t="n">
-        <v>7.138253961230074</v>
+        <v>7.13825490381517</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287317299748752</v>
+        <v>7.287318262017216</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.306213855743408</v>
+        <v>7.306214332580566</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724011249786042</v>
+        <v>7.724011753890583</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050075613595256</v>
+        <v>7.050076073715654</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054275027030914</v>
+        <v>7.054275487425385</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.306213855743408</v>
+        <v>7.306214332580566</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480471247944865</v>
+        <v>7.480471736154864</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243228336770691</v>
+        <v>7.243228809497124</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308312344769346</v>
+        <v>7.308312821743462</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400689808525235</v>
+        <v>7.400690302893193</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945100983960817</v>
+        <v>6.945101447895325</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360799849541025</v>
+        <v>7.360800341244324</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -772,16 +772,16 @@
         <v>44253</v>
       </c>
       <c r="B18" t="n">
-        <v>7.243227005004883</v>
+        <v>7.243227958679199</v>
       </c>
       <c r="C18" t="n">
-        <v>7.48046987255873</v>
+        <v>7.480470857469459</v>
       </c>
       <c r="D18" t="n">
-        <v>6.833827701312602</v>
+        <v>6.833828601083652</v>
       </c>
       <c r="E18" t="n">
-        <v>7.157148381038444</v>
+        <v>7.157149323379279</v>
       </c>
       <c r="F18" t="n">
         <v>1865862</v>
@@ -792,16 +792,16 @@
         <v>44256</v>
       </c>
       <c r="B19" t="n">
-        <v>7.001787662506104</v>
+        <v>7.001787185668945</v>
       </c>
       <c r="C19" t="n">
-        <v>7.390192411161723</v>
+        <v>7.390191907873347</v>
       </c>
       <c r="D19" t="n">
-        <v>7.001787662506104</v>
+        <v>7.001787185668945</v>
       </c>
       <c r="E19" t="n">
-        <v>7.24952707872963</v>
+        <v>7.249526585020872</v>
       </c>
       <c r="F19" t="n">
         <v>1349729</v>
@@ -832,16 +832,16 @@
         <v>44258</v>
       </c>
       <c r="B21" t="n">
-        <v>7.085767269134521</v>
+        <v>7.085766792297363</v>
       </c>
       <c r="C21" t="n">
-        <v>7.10886120006331</v>
+        <v>7.108860721672044</v>
       </c>
       <c r="D21" t="n">
-        <v>6.896813161397048</v>
+        <v>6.896812697275568</v>
       </c>
       <c r="E21" t="n">
-        <v>7.10886120006331</v>
+        <v>7.108860721672044</v>
       </c>
       <c r="F21" t="n">
         <v>1419466</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233019817944</v>
+        <v>7.222233502264944</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966096425558127</v>
+        <v>6.966096890895136</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117259059009463</v>
+        <v>7.117259534444174</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -892,16 +892,16 @@
         <v>44263</v>
       </c>
       <c r="B24" t="n">
-        <v>6.653272151947021</v>
+        <v>6.65327262878418</v>
       </c>
       <c r="C24" t="n">
-        <v>7.016483627501614</v>
+        <v>7.016484130369983</v>
       </c>
       <c r="D24" t="n">
-        <v>6.653272151947021</v>
+        <v>6.65327262878418</v>
       </c>
       <c r="E24" t="n">
-        <v>7.016483627501614</v>
+        <v>7.016484130369983</v>
       </c>
       <c r="F24" t="n">
         <v>1015642</v>
@@ -912,16 +912,16 @@
         <v>44264</v>
       </c>
       <c r="B25" t="n">
-        <v>6.424428462982178</v>
+        <v>6.42442798614502</v>
       </c>
       <c r="C25" t="n">
-        <v>6.819131905728831</v>
+        <v>6.819131399595795</v>
       </c>
       <c r="D25" t="n">
-        <v>6.36774247274314</v>
+        <v>6.367742000113356</v>
       </c>
       <c r="E25" t="n">
-        <v>6.75404790081054</v>
+        <v>6.754047399508202</v>
       </c>
       <c r="F25" t="n">
         <v>2514170</v>
@@ -952,16 +952,16 @@
         <v>44266</v>
       </c>
       <c r="B27" t="n">
-        <v>6.670068264007568</v>
+        <v>6.67006778717041</v>
       </c>
       <c r="C27" t="n">
-        <v>6.670068264007568</v>
+        <v>6.67006778717041</v>
       </c>
       <c r="D27" t="n">
-        <v>6.214479816572392</v>
+        <v>6.21447937230484</v>
       </c>
       <c r="E27" t="n">
-        <v>6.287962243213972</v>
+        <v>6.287961793693228</v>
       </c>
       <c r="F27" t="n">
         <v>2230763</v>
@@ -972,16 +972,16 @@
         <v>44267</v>
       </c>
       <c r="B28" t="n">
-        <v>6.695262908935547</v>
+        <v>6.695262432098389</v>
       </c>
       <c r="C28" t="n">
-        <v>6.896814064768251</v>
+        <v>6.896813573576604</v>
       </c>
       <c r="D28" t="n">
-        <v>6.455921088964289</v>
+        <v>6.455920629173074</v>
       </c>
       <c r="E28" t="n">
-        <v>6.646974928291244</v>
+        <v>6.646974454893159</v>
       </c>
       <c r="F28" t="n">
         <v>3263434</v>
@@ -1012,16 +1012,16 @@
         <v>44271</v>
       </c>
       <c r="B30" t="n">
-        <v>7.390191555023193</v>
+        <v>7.390192031860352</v>
       </c>
       <c r="C30" t="n">
-        <v>7.425883723946737</v>
+        <v>7.42588420308686</v>
       </c>
       <c r="D30" t="n">
-        <v>6.970294095405131</v>
+        <v>6.970294545149255</v>
       </c>
       <c r="E30" t="n">
-        <v>6.970294095405131</v>
+        <v>6.970294545149255</v>
       </c>
       <c r="F30" t="n">
         <v>4282725</v>
@@ -1032,16 +1032,16 @@
         <v>44272</v>
       </c>
       <c r="B31" t="n">
-        <v>7.558151721954346</v>
+        <v>7.558151245117188</v>
       </c>
       <c r="C31" t="n">
-        <v>7.642131059252459</v>
+        <v>7.642130577117119</v>
       </c>
       <c r="D31" t="n">
-        <v>7.285218266889542</v>
+        <v>7.285217807271516</v>
       </c>
       <c r="E31" t="n">
-        <v>7.390192235563539</v>
+        <v>7.390191769322798</v>
       </c>
       <c r="F31" t="n">
         <v>5070506</v>
@@ -1052,16 +1052,16 @@
         <v>44273</v>
       </c>
       <c r="B32" t="n">
-        <v>7.589643955230713</v>
+        <v>7.589643478393555</v>
       </c>
       <c r="C32" t="n">
-        <v>7.898268782349795</v>
+        <v>7.89826828612256</v>
       </c>
       <c r="D32" t="n">
-        <v>7.45947593692015</v>
+        <v>7.459475468261102</v>
       </c>
       <c r="E32" t="n">
-        <v>7.600141271314518</v>
+        <v>7.600140793817841</v>
       </c>
       <c r="F32" t="n">
         <v>3661176</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.51616096496582</v>
+        <v>7.516162395477295</v>
       </c>
       <c r="C33" t="n">
-        <v>7.778596240375135</v>
+        <v>7.778597720834538</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430080720412905</v>
+        <v>7.430082134541178</v>
       </c>
       <c r="E33" t="n">
-        <v>7.600139473774162</v>
+        <v>7.600140920268824</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1092,16 +1092,16 @@
         <v>44277</v>
       </c>
       <c r="B34" t="n">
-        <v>7.558151721954346</v>
+        <v>7.558151245117188</v>
       </c>
       <c r="C34" t="n">
-        <v>7.807990433070015</v>
+        <v>7.807989940470752</v>
       </c>
       <c r="D34" t="n">
-        <v>7.201238929591428</v>
+        <v>7.201238475271585</v>
       </c>
       <c r="E34" t="n">
-        <v>7.514062346629327</v>
+        <v>7.514061872573729</v>
       </c>
       <c r="F34" t="n">
         <v>5377429</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.51616096496582</v>
+        <v>7.516162395477295</v>
       </c>
       <c r="C35" t="n">
-        <v>7.558150219369991</v>
+        <v>7.55815165787306</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436380245085714</v>
+        <v>7.436381660412942</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511961552448754</v>
+        <v>7.511962982160976</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159247875213623</v>
+        <v>7.159248352050781</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656826740361056</v>
+        <v>7.656827250339138</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159247875213623</v>
+        <v>7.159248352050781</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392291336410457</v>
+        <v>7.392291828769327</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.518260955810547</v>
+        <v>7.51826000213623</v>
       </c>
       <c r="C38" t="n">
-        <v>7.789095110371317</v>
+        <v>7.789094122342303</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455276249824448</v>
+        <v>7.455275304139598</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721911802823614</v>
+        <v>7.721910823316651</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1192,16 +1192,16 @@
         <v>44284</v>
       </c>
       <c r="B39" t="n">
-        <v>7.232729911804199</v>
+        <v>7.232730865478516</v>
       </c>
       <c r="C39" t="n">
-        <v>7.663124668362338</v>
+        <v>7.663125678786516</v>
       </c>
       <c r="D39" t="n">
-        <v>7.232729911804199</v>
+        <v>7.232730865478516</v>
       </c>
       <c r="E39" t="n">
-        <v>7.568648027979529</v>
+        <v>7.568649025946455</v>
       </c>
       <c r="F39" t="n">
         <v>3953908</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379694366927925</v>
+        <v>7.379694859893382</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254165649414</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257924377559402</v>
+        <v>7.257924862390593</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1232,16 +1232,16 @@
         <v>44286</v>
       </c>
       <c r="B41" t="n">
-        <v>7.348202228546143</v>
+        <v>7.348202705383301</v>
       </c>
       <c r="C41" t="n">
-        <v>7.379694172420294</v>
+        <v>7.379694651301018</v>
       </c>
       <c r="D41" t="n">
-        <v>6.997588185825906</v>
+        <v>6.997588639911132</v>
       </c>
       <c r="E41" t="n">
-        <v>7.226432242387128</v>
+        <v>7.226432711322428</v>
       </c>
       <c r="F41" t="n">
         <v>2544984</v>
@@ -1252,16 +1252,16 @@
         <v>44287</v>
       </c>
       <c r="B42" t="n">
-        <v>7.348202228546143</v>
+        <v>7.348202705383301</v>
       </c>
       <c r="C42" t="n">
-        <v>7.524558900189283</v>
+        <v>7.524559388470522</v>
       </c>
       <c r="D42" t="n">
-        <v>7.171845556903002</v>
+        <v>7.171846022296081</v>
       </c>
       <c r="E42" t="n">
-        <v>7.35869954317086</v>
+        <v>7.358700020689207</v>
       </c>
       <c r="F42" t="n">
         <v>877384</v>
@@ -1292,16 +1292,16 @@
         <v>44292</v>
       </c>
       <c r="B44" t="n">
-        <v>7.211735248565674</v>
+        <v>7.211735725402832</v>
       </c>
       <c r="C44" t="n">
-        <v>7.379693899948808</v>
+        <v>7.379694387891328</v>
       </c>
       <c r="D44" t="n">
-        <v>7.190740620091399</v>
+        <v>7.190741095540401</v>
       </c>
       <c r="E44" t="n">
-        <v>7.36919658571167</v>
+        <v>7.369197072960112</v>
       </c>
       <c r="F44" t="n">
         <v>1319726</v>
@@ -1312,16 +1312,16 @@
         <v>44293</v>
       </c>
       <c r="B45" t="n">
-        <v>7.243227005004883</v>
+        <v>7.243227958679199</v>
       </c>
       <c r="C45" t="n">
-        <v>7.388091723699758</v>
+        <v>7.388092696447584</v>
       </c>
       <c r="D45" t="n">
-        <v>7.146651067071263</v>
+        <v>7.146652008029977</v>
       </c>
       <c r="E45" t="n">
-        <v>7.213834363537887</v>
+        <v>7.213835313342242</v>
       </c>
       <c r="F45" t="n">
         <v>1401221</v>
@@ -1332,16 +1332,16 @@
         <v>44294</v>
       </c>
       <c r="B46" t="n">
-        <v>7.589643955230713</v>
+        <v>7.589643478393555</v>
       </c>
       <c r="C46" t="n">
-        <v>7.789095396206844</v>
+        <v>7.789094906838682</v>
       </c>
       <c r="D46" t="n">
-        <v>7.215935930750956</v>
+        <v>7.215935477392881</v>
       </c>
       <c r="E46" t="n">
-        <v>7.243228465492086</v>
+        <v>7.243228010419292</v>
       </c>
       <c r="F46" t="n">
         <v>2111967</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652626991271973</v>
+        <v>7.652628898620605</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873073016243731</v>
+        <v>7.873074978536558</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474170221459922</v>
+        <v>7.474172084329807</v>
       </c>
       <c r="E47" t="n">
-        <v>7.595941009729709</v>
+        <v>7.59594290294987</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1372,16 +1372,16 @@
         <v>44298</v>
       </c>
       <c r="B48" t="n">
-        <v>7.789094924926758</v>
+        <v>7.7890944480896</v>
       </c>
       <c r="C48" t="n">
-        <v>8.015839698719409</v>
+        <v>8.015839208001262</v>
       </c>
       <c r="D48" t="n">
-        <v>7.64423018578716</v>
+        <v>7.644229717818412</v>
       </c>
       <c r="E48" t="n">
-        <v>7.688319560107198</v>
+        <v>7.688319089439362</v>
       </c>
       <c r="F48" t="n">
         <v>2187380</v>
@@ -1392,16 +1392,16 @@
         <v>44299</v>
       </c>
       <c r="B49" t="n">
-        <v>7.726109981536865</v>
+        <v>7.726109504699707</v>
       </c>
       <c r="C49" t="n">
-        <v>7.898268060237418</v>
+        <v>7.898267572775072</v>
       </c>
       <c r="D49" t="n">
-        <v>7.642130648749763</v>
+        <v>7.64213017709561</v>
       </c>
       <c r="E49" t="n">
-        <v>7.786995383409918</v>
+        <v>7.786994902815057</v>
       </c>
       <c r="F49" t="n">
         <v>1044023</v>
@@ -1432,16 +1432,16 @@
         <v>44301</v>
       </c>
       <c r="B51" t="n">
-        <v>8.112415313720703</v>
+        <v>8.112414360046387</v>
       </c>
       <c r="C51" t="n">
-        <v>8.185898142401868</v>
+        <v>8.185897180089103</v>
       </c>
       <c r="D51" t="n">
-        <v>7.891969263060783</v>
+        <v>7.891968335301526</v>
       </c>
       <c r="E51" t="n">
-        <v>7.894068563704509</v>
+        <v>7.894067635698465</v>
       </c>
       <c r="F51" t="n">
         <v>2034122</v>
@@ -1452,16 +1452,16 @@
         <v>44302</v>
       </c>
       <c r="B52" t="n">
-        <v>8.187995910644531</v>
+        <v>8.187996864318848</v>
       </c>
       <c r="C52" t="n">
-        <v>8.25098141876933</v>
+        <v>8.25098237977971</v>
       </c>
       <c r="D52" t="n">
-        <v>8.091419971587269</v>
+        <v>8.09142091401317</v>
       </c>
       <c r="E52" t="n">
-        <v>8.1124145997659</v>
+        <v>8.112415544637091</v>
       </c>
       <c r="F52" t="n">
         <v>1067133</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208991050720215</v>
+        <v>8.208992004394531</v>
       </c>
       <c r="C53" t="n">
-        <v>8.244682407926204</v>
+        <v>8.24468336574694</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059928531921125</v>
+        <v>8.059929468278197</v>
       </c>
       <c r="E53" t="n">
-        <v>8.1879964212324</v>
+        <v>8.187997372467679</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1532,16 +1532,16 @@
         <v>44309</v>
       </c>
       <c r="B56" t="n">
-        <v>8.187995910644531</v>
+        <v>8.187996864318848</v>
       </c>
       <c r="C56" t="n">
-        <v>8.21948866470693</v>
+        <v>8.219489622049279</v>
       </c>
       <c r="D56" t="n">
-        <v>7.923460510774868</v>
+        <v>7.923461433638152</v>
       </c>
       <c r="E56" t="n">
-        <v>8.215290063788986</v>
+        <v>8.215291020642315</v>
       </c>
       <c r="F56" t="n">
         <v>1129166</v>
@@ -1552,16 +1552,16 @@
         <v>44312</v>
       </c>
       <c r="B57" t="n">
-        <v>7.978048324584961</v>
+        <v>7.978049278259277</v>
       </c>
       <c r="C57" t="n">
-        <v>8.187996238363182</v>
+        <v>8.187997217134104</v>
       </c>
       <c r="D57" t="n">
-        <v>7.93815755529562</v>
+        <v>7.938158504201501</v>
       </c>
       <c r="E57" t="n">
-        <v>8.185897749614673</v>
+        <v>8.185898728134749</v>
       </c>
       <c r="F57" t="n">
         <v>1270667</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397945404052734</v>
+        <v>8.397944450378418</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469328120611465</v>
+        <v>8.469327158830897</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116613840986611</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116613840986611</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1612,16 +1612,16 @@
         <v>44315</v>
       </c>
       <c r="B60" t="n">
-        <v>8.607893943786621</v>
+        <v>8.607894897460938</v>
       </c>
       <c r="C60" t="n">
-        <v>8.815743374956226</v>
+        <v>8.815744351658321</v>
       </c>
       <c r="D60" t="n">
-        <v>8.167001850598284</v>
+        <v>8.167002755425871</v>
       </c>
       <c r="E60" t="n">
-        <v>8.469327926938387</v>
+        <v>8.469328865260882</v>
       </c>
       <c r="F60" t="n">
         <v>3250459</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849334716796875</v>
+        <v>8.849335670471191</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122268152268145</v>
+        <v>9.122269135355927</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641486095148732</v>
+        <v>8.641487026423638</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733863440724466</v>
+        <v>8.733864381954685</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1692,16 +1692,16 @@
         <v>44321</v>
       </c>
       <c r="B64" t="n">
-        <v>9.78360652923584</v>
+        <v>9.783605575561523</v>
       </c>
       <c r="C64" t="n">
-        <v>9.99355526824108</v>
+        <v>9.993554294101639</v>
       </c>
       <c r="D64" t="n">
-        <v>9.273431815950246</v>
+        <v>9.273430912006111</v>
       </c>
       <c r="E64" t="n">
-        <v>9.298625047667027</v>
+        <v>9.298624141267135</v>
       </c>
       <c r="F64" t="n">
         <v>3818084</v>
@@ -1712,16 +1712,16 @@
         <v>44322</v>
       </c>
       <c r="B65" t="n">
-        <v>9.764712333679199</v>
+        <v>9.764713287353516</v>
       </c>
       <c r="C65" t="n">
-        <v>9.783606852193223</v>
+        <v>9.78360780771288</v>
       </c>
       <c r="D65" t="n">
-        <v>9.537966746386992</v>
+        <v>9.537967677916114</v>
       </c>
       <c r="E65" t="n">
-        <v>9.783606852193223</v>
+        <v>9.78360780771288</v>
       </c>
       <c r="F65" t="n">
         <v>8042425</v>
@@ -1752,16 +1752,16 @@
         <v>44326</v>
       </c>
       <c r="B67" t="n">
-        <v>9.380505561828613</v>
+        <v>9.38050651550293</v>
       </c>
       <c r="C67" t="n">
-        <v>9.886481655948959</v>
+        <v>9.886482661063617</v>
       </c>
       <c r="D67" t="n">
-        <v>9.254536160500752</v>
+        <v>9.254537101368319</v>
       </c>
       <c r="E67" t="n">
-        <v>9.867585515134721</v>
+        <v>9.867586518328292</v>
       </c>
       <c r="F67" t="n">
         <v>3466157</v>
@@ -1772,16 +1772,16 @@
         <v>44327</v>
       </c>
       <c r="B68" t="n">
-        <v>9.617748260498047</v>
+        <v>9.61774730682373</v>
       </c>
       <c r="C68" t="n">
-        <v>9.645042419594585</v>
+        <v>9.645041463213841</v>
       </c>
       <c r="D68" t="n">
-        <v>8.964808849758313</v>
+        <v>8.964807960828002</v>
       </c>
       <c r="E68" t="n">
-        <v>9.294428318297966</v>
+        <v>9.294427396683329</v>
       </c>
       <c r="F68" t="n">
         <v>2188597</v>
@@ -1792,16 +1792,16 @@
         <v>44328</v>
       </c>
       <c r="B69" t="n">
-        <v>9.531667709350586</v>
+        <v>9.531668663024902</v>
       </c>
       <c r="C69" t="n">
-        <v>9.743715730787388</v>
+        <v>9.743716705677796</v>
       </c>
       <c r="D69" t="n">
-        <v>9.321718988410458</v>
+        <v>9.321719921078722</v>
       </c>
       <c r="E69" t="n">
-        <v>9.563159652184094</v>
+        <v>9.563160609009282</v>
       </c>
       <c r="F69" t="n">
         <v>1563804</v>
@@ -1832,16 +1832,16 @@
         <v>44330</v>
       </c>
       <c r="B71" t="n">
-        <v>9.626145362854004</v>
+        <v>9.626144409179688</v>
       </c>
       <c r="C71" t="n">
-        <v>9.657638120796779</v>
+        <v>9.657637164002436</v>
       </c>
       <c r="D71" t="n">
-        <v>9.273431994097892</v>
+        <v>9.273431075367332</v>
       </c>
       <c r="E71" t="n">
-        <v>9.655538820079142</v>
+        <v>9.655537863492778</v>
       </c>
       <c r="F71" t="n">
         <v>1271072</v>
@@ -1852,16 +1852,16 @@
         <v>44333</v>
       </c>
       <c r="B72" t="n">
-        <v>9.657637596130371</v>
+        <v>9.657638549804688</v>
       </c>
       <c r="C72" t="n">
-        <v>9.773108870861909</v>
+        <v>9.773109835938806</v>
       </c>
       <c r="D72" t="n">
-        <v>9.361610233599944</v>
+        <v>9.36161115804209</v>
       </c>
       <c r="E72" t="n">
-        <v>9.613548224482443</v>
+        <v>9.613549173803014</v>
       </c>
       <c r="F72" t="n">
         <v>1884107</v>
@@ -1872,16 +1872,16 @@
         <v>44334</v>
       </c>
       <c r="B73" t="n">
-        <v>9.657637596130371</v>
+        <v>9.657638549804688</v>
       </c>
       <c r="C73" t="n">
-        <v>9.66603561033924</v>
+        <v>9.666036564842845</v>
       </c>
       <c r="D73" t="n">
-        <v>9.458186179310156</v>
+        <v>9.458187113289004</v>
       </c>
       <c r="E73" t="n">
-        <v>9.655538295526782</v>
+        <v>9.655539248993795</v>
       </c>
       <c r="F73" t="n">
         <v>1385003</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.82349681854248</v>
+        <v>9.823495864868164</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272898361439</v>
+        <v>10.10272800283195</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334317531017494</v>
+        <v>9.334316624833162</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678632890034629</v>
+        <v>9.678631950423839</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1912,16 +1912,16 @@
         <v>44336</v>
       </c>
       <c r="B75" t="n">
-        <v>10.13002300262451</v>
+        <v>10.1300220489502</v>
       </c>
       <c r="C75" t="n">
-        <v>10.22869906616216</v>
+        <v>10.22869810319815</v>
       </c>
       <c r="D75" t="n">
-        <v>9.504376186303976</v>
+        <v>9.504375291530147</v>
       </c>
       <c r="E75" t="n">
-        <v>9.873885584647184</v>
+        <v>9.873884655086501</v>
       </c>
       <c r="F75" t="n">
         <v>2816227</v>
@@ -1952,16 +1952,16 @@
         <v>44340</v>
       </c>
       <c r="B77" t="n">
-        <v>10.18250846862793</v>
+        <v>10.18250942230225</v>
       </c>
       <c r="C77" t="n">
-        <v>10.39035788841617</v>
+        <v>10.39035886155727</v>
       </c>
       <c r="D77" t="n">
-        <v>9.951565119860142</v>
+        <v>9.951566051904743</v>
       </c>
       <c r="E77" t="n">
-        <v>10.15731442736386</v>
+        <v>10.15731537867855</v>
       </c>
       <c r="F77" t="n">
         <v>3407772</v>
@@ -1972,16 +1972,16 @@
         <v>44341</v>
       </c>
       <c r="B78" t="n">
-        <v>10.43444919586182</v>
+        <v>10.4344482421875</v>
       </c>
       <c r="C78" t="n">
-        <v>10.49323367947483</v>
+        <v>10.49323272042781</v>
       </c>
       <c r="D78" t="n">
-        <v>10.18880907444745</v>
+        <v>10.18880814322383</v>
       </c>
       <c r="E78" t="n">
-        <v>10.23499775278048</v>
+        <v>10.23499681733537</v>
       </c>
       <c r="F78" t="n">
         <v>2528360</v>
@@ -1992,16 +1992,16 @@
         <v>44342</v>
       </c>
       <c r="B79" t="n">
-        <v>10.49743270874023</v>
+        <v>10.4974308013916</v>
       </c>
       <c r="C79" t="n">
-        <v>10.51842815215546</v>
+        <v>10.51842624099203</v>
       </c>
       <c r="D79" t="n">
-        <v>10.31897671637563</v>
+        <v>10.31897484145185</v>
       </c>
       <c r="E79" t="n">
-        <v>10.423951498068</v>
+        <v>10.42394960407066</v>
       </c>
       <c r="F79" t="n">
         <v>2052367</v>
@@ -2012,16 +2012,16 @@
         <v>44343</v>
       </c>
       <c r="B80" t="n">
-        <v>10.65489482879639</v>
+        <v>10.65489387512207</v>
       </c>
       <c r="C80" t="n">
-        <v>10.74937148241849</v>
+        <v>10.74937052028797</v>
       </c>
       <c r="D80" t="n">
-        <v>10.44284596565298</v>
+        <v>10.44284503095825</v>
       </c>
       <c r="E80" t="n">
-        <v>10.49743265703344</v>
+        <v>10.49743171745289</v>
       </c>
       <c r="F80" t="n">
         <v>6818384</v>
@@ -2032,16 +2032,16 @@
         <v>44344</v>
       </c>
       <c r="B81" t="n">
-        <v>10.72837543487549</v>
+        <v>10.72837734222412</v>
       </c>
       <c r="C81" t="n">
-        <v>10.82915078936937</v>
+        <v>10.82915271463439</v>
       </c>
       <c r="D81" t="n">
-        <v>10.46803862888618</v>
+        <v>10.46804048995072</v>
       </c>
       <c r="E81" t="n">
-        <v>10.65489342246942</v>
+        <v>10.65489531675402</v>
       </c>
       <c r="F81" t="n">
         <v>2512953</v>
@@ -2152,16 +2152,16 @@
         <v>44355</v>
       </c>
       <c r="B87" t="n">
-        <v>11.02020454406738</v>
+        <v>11.0202054977417</v>
       </c>
       <c r="C87" t="n">
-        <v>11.16926787426587</v>
+        <v>11.16926884083993</v>
       </c>
       <c r="D87" t="n">
-        <v>10.9341251021654</v>
+        <v>10.93412604839051</v>
       </c>
       <c r="E87" t="n">
-        <v>11.12097909005958</v>
+        <v>11.1209800524548</v>
       </c>
       <c r="F87" t="n">
         <v>1135248</v>
@@ -2172,16 +2172,16 @@
         <v>44356</v>
       </c>
       <c r="B88" t="n">
-        <v>10.90893363952637</v>
+        <v>10.90893268585205</v>
       </c>
       <c r="C88" t="n">
-        <v>11.12518030603061</v>
+        <v>11.1251793334517</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73257612597229</v>
+        <v>10.7325751877154</v>
       </c>
       <c r="E88" t="n">
-        <v>11.00341029907703</v>
+        <v>11.00340933714343</v>
       </c>
       <c r="F88" t="n">
         <v>1361892</v>
@@ -2212,16 +2212,16 @@
         <v>44358</v>
       </c>
       <c r="B90" t="n">
-        <v>10.60240745544434</v>
+        <v>10.60240650177002</v>
       </c>
       <c r="C90" t="n">
-        <v>10.84174885287247</v>
+        <v>10.84174787766967</v>
       </c>
       <c r="D90" t="n">
-        <v>10.51842811744432</v>
+        <v>10.51842717132385</v>
       </c>
       <c r="E90" t="n">
-        <v>10.75986881566868</v>
+        <v>10.7598678478309</v>
       </c>
       <c r="F90" t="n">
         <v>1174982</v>
@@ -2232,16 +2232,16 @@
         <v>44361</v>
       </c>
       <c r="B91" t="n">
-        <v>10.94252300262451</v>
+        <v>10.9425220489502</v>
       </c>
       <c r="C91" t="n">
-        <v>11.24904848576352</v>
+        <v>11.24904750537457</v>
       </c>
       <c r="D91" t="n">
-        <v>10.64649564588704</v>
+        <v>10.64649471801241</v>
       </c>
       <c r="E91" t="n">
-        <v>10.72837567397531</v>
+        <v>10.72837473896458</v>
       </c>
       <c r="F91" t="n">
         <v>2250630</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462394714355</v>
+        <v>10.94462299346924</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192403640713</v>
+        <v>11.35192304724218</v>
       </c>
       <c r="D92" t="n">
-        <v>10.81445592759301</v>
+        <v>10.81445498526105</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152920210349</v>
+        <v>10.92152825044157</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2292,16 +2292,16 @@
         <v>44364</v>
       </c>
       <c r="B94" t="n">
-        <v>11.3057336807251</v>
+        <v>11.30573463439941</v>
       </c>
       <c r="C94" t="n">
-        <v>11.52408123449005</v>
+        <v>11.52408220658267</v>
       </c>
       <c r="D94" t="n">
-        <v>11.0768896241283</v>
+        <v>11.07689055849889</v>
       </c>
       <c r="E94" t="n">
-        <v>11.21125703729346</v>
+        <v>11.21125798299837</v>
       </c>
       <c r="F94" t="n">
         <v>2709189</v>
@@ -2312,16 +2312,16 @@
         <v>44365</v>
       </c>
       <c r="B95" t="n">
-        <v>11.3372278213501</v>
+        <v>11.33722591400146</v>
       </c>
       <c r="C95" t="n">
-        <v>11.3372278213501</v>
+        <v>11.33722591400146</v>
       </c>
       <c r="D95" t="n">
-        <v>10.99291163821293</v>
+        <v>10.99290978879124</v>
       </c>
       <c r="E95" t="n">
-        <v>11.31203377609247</v>
+        <v>11.31203187298242</v>
       </c>
       <c r="F95" t="n">
         <v>1275938</v>
@@ -2352,16 +2352,16 @@
         <v>44369</v>
       </c>
       <c r="B97" t="n">
-        <v>11.28474044799805</v>
+        <v>11.28473949432373</v>
       </c>
       <c r="C97" t="n">
-        <v>11.42330729123857</v>
+        <v>11.42330632585396</v>
       </c>
       <c r="D97" t="n">
-        <v>11.16297125854524</v>
+        <v>11.16297031516165</v>
       </c>
       <c r="E97" t="n">
-        <v>11.238552582644</v>
+        <v>11.23855163287302</v>
       </c>
       <c r="F97" t="n">
         <v>1033076</v>
@@ -2372,16 +2372,16 @@
         <v>44370</v>
       </c>
       <c r="B98" t="n">
-        <v>11.50308704376221</v>
+        <v>11.50308799743652</v>
       </c>
       <c r="C98" t="n">
-        <v>11.74872632604882</v>
+        <v>11.7487273000881</v>
       </c>
       <c r="D98" t="n">
-        <v>11.3057341117264</v>
+        <v>11.30573504903898</v>
       </c>
       <c r="E98" t="n">
-        <v>11.4212062006073</v>
+        <v>11.42120714749321</v>
       </c>
       <c r="F98" t="n">
         <v>4341920</v>
@@ -2392,16 +2392,16 @@
         <v>44371</v>
       </c>
       <c r="B99" t="n">
-        <v>11.71093559265137</v>
+        <v>11.71093654632568</v>
       </c>
       <c r="C99" t="n">
-        <v>12.02165887555918</v>
+        <v>12.02165985453709</v>
       </c>
       <c r="D99" t="n">
-        <v>11.35612212568278</v>
+        <v>11.35612305046303</v>
       </c>
       <c r="E99" t="n">
-        <v>11.54717471917903</v>
+        <v>11.54717565951756</v>
       </c>
       <c r="F99" t="n">
         <v>3545624</v>
@@ -2432,16 +2432,16 @@
         <v>44375</v>
       </c>
       <c r="B101" t="n">
-        <v>11.86209774017334</v>
+        <v>11.86209869384766</v>
       </c>
       <c r="C101" t="n">
-        <v>12.00066375318507</v>
+        <v>12.00066471799965</v>
       </c>
       <c r="D101" t="n">
-        <v>11.40441044302249</v>
+        <v>11.40441135990023</v>
       </c>
       <c r="E101" t="n">
-        <v>11.58916512703814</v>
+        <v>11.58916605876955</v>
       </c>
       <c r="F101" t="n">
         <v>1601511</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.01746273040771</v>
+        <v>12.0174617767334</v>
       </c>
       <c r="C102" t="n">
-        <v>12.01746273040771</v>
+        <v>12.0174617767334</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916718832423</v>
+        <v>11.58916626863832</v>
       </c>
       <c r="E102" t="n">
-        <v>11.86000054908383</v>
+        <v>11.8599996079053</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2492,16 +2492,16 @@
         <v>44378</v>
       </c>
       <c r="B104" t="n">
-        <v>12.47095012664795</v>
+        <v>12.47094821929932</v>
       </c>
       <c r="C104" t="n">
-        <v>12.63471020326512</v>
+        <v>12.63470827087047</v>
       </c>
       <c r="D104" t="n">
-        <v>12.33028479448456</v>
+        <v>12.33028290864975</v>
       </c>
       <c r="E104" t="n">
-        <v>12.38907090013396</v>
+        <v>12.38906900530821</v>
       </c>
       <c r="F104" t="n">
         <v>8890212</v>
@@ -2512,16 +2512,16 @@
         <v>44379</v>
       </c>
       <c r="B105" t="n">
-        <v>12.95803070068359</v>
+        <v>12.95803165435791</v>
       </c>
       <c r="C105" t="n">
-        <v>13.1280894777343</v>
+        <v>13.12809044392446</v>
       </c>
       <c r="D105" t="n">
-        <v>12.5003425684372</v>
+        <v>12.50034348842697</v>
       </c>
       <c r="E105" t="n">
-        <v>12.52133719856387</v>
+        <v>12.52133812009879</v>
       </c>
       <c r="F105" t="n">
         <v>2908669</v>
@@ -2532,16 +2532,16 @@
         <v>44382</v>
       </c>
       <c r="B106" t="n">
-        <v>13.12178993225098</v>
+        <v>13.12179088592529</v>
       </c>
       <c r="C106" t="n">
-        <v>13.50179742186512</v>
+        <v>13.50179840315787</v>
       </c>
       <c r="D106" t="n">
-        <v>12.96432778089814</v>
+        <v>12.96432872312831</v>
       </c>
       <c r="E106" t="n">
-        <v>12.96432778089814</v>
+        <v>12.96432872312831</v>
       </c>
       <c r="F106" t="n">
         <v>1748688</v>
@@ -2572,16 +2572,16 @@
         <v>44384</v>
       </c>
       <c r="B108" t="n">
-        <v>13.22676467895508</v>
+        <v>13.22676563262939</v>
       </c>
       <c r="C108" t="n">
-        <v>13.31074319400629</v>
+        <v>13.31074415373561</v>
       </c>
       <c r="D108" t="n">
-        <v>13.05040719960521</v>
+        <v>13.05040814056382</v>
       </c>
       <c r="E108" t="n">
-        <v>13.05880521346923</v>
+        <v>13.05880615503335</v>
       </c>
       <c r="F108" t="n">
         <v>2057638</v>
@@ -2612,16 +2612,16 @@
         <v>44389</v>
       </c>
       <c r="B110" t="n">
-        <v>13.3317403793335</v>
+        <v>13.33173942565918</v>
       </c>
       <c r="C110" t="n">
-        <v>13.79572644412283</v>
+        <v>13.79572545725768</v>
       </c>
       <c r="D110" t="n">
-        <v>13.07140353906678</v>
+        <v>13.07140260401543</v>
       </c>
       <c r="E110" t="n">
-        <v>13.19107423754762</v>
+        <v>13.19107329393574</v>
       </c>
       <c r="F110" t="n">
         <v>8663568</v>
@@ -2632,16 +2632,16 @@
         <v>44390</v>
       </c>
       <c r="B111" t="n">
-        <v>13.27295398712158</v>
+        <v>13.27295303344727</v>
       </c>
       <c r="C111" t="n">
-        <v>13.49759946187835</v>
+        <v>13.49759849206305</v>
       </c>
       <c r="D111" t="n">
-        <v>13.13438796092353</v>
+        <v>13.13438701720531</v>
       </c>
       <c r="E111" t="n">
-        <v>13.33174009059002</v>
+        <v>13.33173913269187</v>
       </c>
       <c r="F111" t="n">
         <v>2696620</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C114" t="n">
-        <v>13.93849142806081</v>
+        <v>13.9384904687512</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969861080446</v>
+        <v>13.49969768169454</v>
       </c>
       <c r="E114" t="n">
-        <v>13.64246404868482</v>
+        <v>13.64246310974914</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501531105205</v>
+        <v>14.24501433064608</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969861080446</v>
+        <v>13.49969768169454</v>
       </c>
       <c r="E115" t="n">
-        <v>13.74953650350598</v>
+        <v>13.7495355572011</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2752,16 +2752,16 @@
         <v>44398</v>
       </c>
       <c r="B117" t="n">
-        <v>14.31849765777588</v>
+        <v>14.3184986114502</v>
       </c>
       <c r="C117" t="n">
-        <v>14.3478894888263</v>
+        <v>14.34789044445824</v>
       </c>
       <c r="D117" t="n">
-        <v>14.01617078001709</v>
+        <v>14.01617171355511</v>
       </c>
       <c r="E117" t="n">
-        <v>14.06865816410801</v>
+        <v>14.06865910114192</v>
       </c>
       <c r="F117" t="n">
         <v>2316312</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.9987325668335</v>
+        <v>14.99873352050781</v>
       </c>
       <c r="C118" t="n">
-        <v>15.01132999484949</v>
+        <v>15.0113309493248</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36048831691926</v>
+        <v>14.36048923001167</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36048831691926</v>
+        <v>14.36048923001167</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2812,16 +2812,16 @@
         <v>44403</v>
       </c>
       <c r="B120" t="n">
-        <v>14.87486362457275</v>
+        <v>14.87486267089844</v>
       </c>
       <c r="C120" t="n">
-        <v>15.17089102924288</v>
+        <v>15.17089005658931</v>
       </c>
       <c r="D120" t="n">
-        <v>14.64602034313728</v>
+        <v>14.64601940413482</v>
       </c>
       <c r="E120" t="n">
-        <v>15.07431506978501</v>
+        <v>15.07431410332324</v>
       </c>
       <c r="F120" t="n">
         <v>4655330</v>
@@ -2832,16 +2832,16 @@
         <v>44404</v>
       </c>
       <c r="B121" t="n">
-        <v>14.54944133758545</v>
+        <v>14.54943943023682</v>
       </c>
       <c r="C121" t="n">
-        <v>15.059616867494</v>
+        <v>15.05961489326427</v>
       </c>
       <c r="D121" t="n">
-        <v>14.45076608687268</v>
+        <v>14.45076419245981</v>
       </c>
       <c r="E121" t="n">
-        <v>14.87486217025152</v>
+        <v>14.87486022024207</v>
       </c>
       <c r="F121" t="n">
         <v>2070206</v>
@@ -2892,16 +2892,16 @@
         <v>44407</v>
       </c>
       <c r="B124" t="n">
-        <v>15.45431804656982</v>
+        <v>15.45431900024414</v>
       </c>
       <c r="C124" t="n">
-        <v>15.94139959960302</v>
+        <v>15.94140058333477</v>
       </c>
       <c r="D124" t="n">
-        <v>14.96933741762614</v>
+        <v>14.96933834137266</v>
       </c>
       <c r="E124" t="n">
-        <v>15.28006149272221</v>
+        <v>15.28006243564328</v>
       </c>
       <c r="F124" t="n">
         <v>3070441</v>
@@ -2952,16 +2952,16 @@
         <v>44412</v>
       </c>
       <c r="B127" t="n">
-        <v>14.73839569091797</v>
+        <v>14.73839473724365</v>
       </c>
       <c r="C127" t="n">
-        <v>15.32205328135125</v>
+        <v>15.32205228991032</v>
       </c>
       <c r="D127" t="n">
-        <v>14.73839569091797</v>
+        <v>14.73839473724365</v>
       </c>
       <c r="E127" t="n">
-        <v>15.18768666199287</v>
+        <v>15.18768567924637</v>
       </c>
       <c r="F127" t="n">
         <v>2159810</v>
@@ -2972,16 +2972,16 @@
         <v>44413</v>
       </c>
       <c r="B128" t="n">
-        <v>14.17153453826904</v>
+        <v>14.17153358459473</v>
       </c>
       <c r="C128" t="n">
-        <v>14.82237457073309</v>
+        <v>14.82237357326046</v>
       </c>
       <c r="D128" t="n">
-        <v>14.17153453826904</v>
+        <v>14.17153358459473</v>
       </c>
       <c r="E128" t="n">
-        <v>14.61662524586311</v>
+        <v>14.61662426223638</v>
       </c>
       <c r="F128" t="n">
         <v>2928535</v>
@@ -3032,16 +3032,16 @@
         <v>44418</v>
       </c>
       <c r="B131" t="n">
-        <v>13.64666175842285</v>
+        <v>13.64666271209717</v>
       </c>
       <c r="C131" t="n">
-        <v>14.43816789362585</v>
+        <v>14.43816890261326</v>
       </c>
       <c r="D131" t="n">
-        <v>13.56688184180349</v>
+        <v>13.56688278990252</v>
       </c>
       <c r="E131" t="n">
-        <v>14.05396179104118</v>
+        <v>14.05396277317898</v>
       </c>
       <c r="F131" t="n">
         <v>2933806</v>
@@ -3052,16 +3052,16 @@
         <v>44419</v>
       </c>
       <c r="B132" t="n">
-        <v>13.825119972229</v>
+        <v>13.82511901855469</v>
       </c>
       <c r="C132" t="n">
-        <v>13.867109235462</v>
+        <v>13.86710827889121</v>
       </c>
       <c r="D132" t="n">
-        <v>13.63406573969946</v>
+        <v>13.6340647992043</v>
       </c>
       <c r="E132" t="n">
-        <v>13.64666316810502</v>
+        <v>13.64666222674088</v>
       </c>
       <c r="F132" t="n">
         <v>1882485</v>
@@ -3072,16 +3072,16 @@
         <v>44420</v>
       </c>
       <c r="B133" t="n">
-        <v>13.68025493621826</v>
+        <v>13.68025398254395</v>
       </c>
       <c r="C133" t="n">
-        <v>14.21142511206147</v>
+        <v>14.21142412135836</v>
       </c>
       <c r="D133" t="n">
-        <v>13.64666287691298</v>
+        <v>13.64666192558043</v>
       </c>
       <c r="E133" t="n">
-        <v>13.82511967722906</v>
+        <v>13.82511871345597</v>
       </c>
       <c r="F133" t="n">
         <v>1819641</v>
@@ -3152,16 +3152,16 @@
         <v>44426</v>
       </c>
       <c r="B137" t="n">
-        <v>12.5969181060791</v>
+        <v>12.59691905975342</v>
       </c>
       <c r="C137" t="n">
-        <v>13.13438695180978</v>
+        <v>13.13438794617422</v>
       </c>
       <c r="D137" t="n">
-        <v>12.21901071713769</v>
+        <v>12.21901164220178</v>
       </c>
       <c r="E137" t="n">
-        <v>12.38696937626842</v>
+        <v>12.38697031404816</v>
       </c>
       <c r="F137" t="n">
         <v>3796291</v>
@@ -3192,16 +3192,16 @@
         <v>44428</v>
       </c>
       <c r="B139" t="n">
-        <v>13.5206937789917</v>
+        <v>13.52069187164307</v>
       </c>
       <c r="C139" t="n">
-        <v>13.70544848585422</v>
+        <v>13.70544655244245</v>
       </c>
       <c r="D139" t="n">
-        <v>12.64730752300772</v>
+        <v>12.64730573886667</v>
       </c>
       <c r="E139" t="n">
-        <v>12.80686818480864</v>
+        <v>12.80686637815856</v>
       </c>
       <c r="F139" t="n">
         <v>3576438</v>
@@ -3212,16 +3212,16 @@
         <v>44431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.49549770355225</v>
+        <v>13.49549865722656</v>
       </c>
       <c r="C140" t="n">
-        <v>14.19252797462165</v>
+        <v>14.19252897755238</v>
       </c>
       <c r="D140" t="n">
-        <v>13.26035575373789</v>
+        <v>13.26035669079564</v>
       </c>
       <c r="E140" t="n">
-        <v>13.72224245140401</v>
+        <v>13.72224342110149</v>
       </c>
       <c r="F140" t="n">
         <v>2675233</v>
@@ -3272,16 +3272,16 @@
         <v>44434</v>
       </c>
       <c r="B143" t="n">
-        <v>13.12598896026611</v>
+        <v>13.12599086761475</v>
       </c>
       <c r="C143" t="n">
-        <v>13.76423235313817</v>
+        <v>13.76423435323049</v>
       </c>
       <c r="D143" t="n">
-        <v>12.82366288623372</v>
+        <v>12.82366474965109</v>
       </c>
       <c r="E143" t="n">
-        <v>13.47870311920116</v>
+        <v>13.47870507780299</v>
       </c>
       <c r="F143" t="n">
         <v>2624147</v>
@@ -3292,16 +3292,16 @@
         <v>44435</v>
       </c>
       <c r="B144" t="n">
-        <v>13.68865299224854</v>
+        <v>13.6886510848999</v>
       </c>
       <c r="C144" t="n">
-        <v>13.68865299224854</v>
+        <v>13.6886510848999</v>
       </c>
       <c r="D144" t="n">
-        <v>12.9580321511872</v>
+        <v>12.95803034564176</v>
       </c>
       <c r="E144" t="n">
-        <v>13.32754157939268</v>
+        <v>13.32753972236057</v>
       </c>
       <c r="F144" t="n">
         <v>2006349</v>
@@ -3312,16 +3312,16 @@
         <v>44438</v>
       </c>
       <c r="B145" t="n">
-        <v>13.34433650970459</v>
+        <v>13.34433555603027</v>
       </c>
       <c r="C145" t="n">
-        <v>14.09175331983246</v>
+        <v>14.09175231274281</v>
       </c>
       <c r="D145" t="n">
-        <v>13.24356114561362</v>
+        <v>13.24356019914138</v>
       </c>
       <c r="E145" t="n">
-        <v>13.68865186346858</v>
+        <v>13.68865088518722</v>
       </c>
       <c r="F145" t="n">
         <v>1186841</v>
@@ -3372,16 +3372,16 @@
         <v>44441</v>
       </c>
       <c r="B148" t="n">
-        <v>12.8068675994873</v>
+        <v>12.80686664581299</v>
       </c>
       <c r="C148" t="n">
-        <v>13.1847750109611</v>
+        <v>13.18477402914559</v>
       </c>
       <c r="D148" t="n">
-        <v>12.69769503279916</v>
+        <v>12.69769408725448</v>
       </c>
       <c r="E148" t="n">
-        <v>13.06720442963625</v>
+        <v>13.06720345657573</v>
       </c>
       <c r="F148" t="n">
         <v>2514879</v>
@@ -3392,16 +3392,16 @@
         <v>44442</v>
       </c>
       <c r="B149" t="n">
-        <v>13.10079479217529</v>
+        <v>13.10079574584961</v>
       </c>
       <c r="C149" t="n">
-        <v>13.21836617735944</v>
+        <v>13.21836713959238</v>
       </c>
       <c r="D149" t="n">
-        <v>12.74808144841735</v>
+        <v>12.74808237641584</v>
       </c>
       <c r="E149" t="n">
-        <v>12.94963216250603</v>
+        <v>12.94963310517644</v>
       </c>
       <c r="F149" t="n">
         <v>3315331</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00002039001773</v>
+        <v>13.00001949529792</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113177437019</v>
+        <v>13.36113085479707</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3452,16 +3452,16 @@
         <v>44448</v>
       </c>
       <c r="B152" t="n">
-        <v>13.12598896026611</v>
+        <v>13.12599086761475</v>
       </c>
       <c r="C152" t="n">
-        <v>13.37792776119036</v>
+        <v>13.37792970514844</v>
       </c>
       <c r="D152" t="n">
-        <v>12.52973482635177</v>
+        <v>12.5297366470582</v>
       </c>
       <c r="E152" t="n">
-        <v>13.21836630412647</v>
+        <v>13.21836822489853</v>
       </c>
       <c r="F152" t="n">
         <v>3739731</v>
@@ -3512,16 +3512,16 @@
         <v>44453</v>
       </c>
       <c r="B155" t="n">
-        <v>13.55428504943848</v>
+        <v>13.55428600311279</v>
       </c>
       <c r="C155" t="n">
-        <v>14.04976384781166</v>
+        <v>14.04976483634768</v>
       </c>
       <c r="D155" t="n">
-        <v>13.27715300528965</v>
+        <v>13.27715393946506</v>
       </c>
       <c r="E155" t="n">
-        <v>13.43671365779501</v>
+        <v>13.43671460319705</v>
       </c>
       <c r="F155" t="n">
         <v>1943200</v>
@@ -3592,16 +3592,16 @@
         <v>44459</v>
       </c>
       <c r="B159" t="n">
-        <v>12.84885787963867</v>
+        <v>12.84885692596436</v>
       </c>
       <c r="C159" t="n">
-        <v>13.10919390218652</v>
+        <v>13.10919292918942</v>
       </c>
       <c r="D159" t="n">
-        <v>12.63051111915618</v>
+        <v>12.63051018168811</v>
       </c>
       <c r="E159" t="n">
-        <v>13.10919390218652</v>
+        <v>13.10919292918942</v>
       </c>
       <c r="F159" t="n">
         <v>1643373</v>
@@ -3612,16 +3612,16 @@
         <v>44460</v>
       </c>
       <c r="B160" t="n">
-        <v>13.5206937789917</v>
+        <v>13.52069187164307</v>
       </c>
       <c r="C160" t="n">
-        <v>13.64666319250508</v>
+        <v>13.64666126738609</v>
       </c>
       <c r="D160" t="n">
-        <v>12.80686818480864</v>
+        <v>12.80686637815856</v>
       </c>
       <c r="E160" t="n">
-        <v>12.98322568844521</v>
+        <v>12.98322385691658</v>
       </c>
       <c r="F160" t="n">
         <v>1911981</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.61242771148682</v>
+        <v>14.61242866516113</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630374532261</v>
+        <v>15.1163047318822</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893814452217</v>
+        <v>14.15893906859966</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19253020482906</v>
+        <v>14.19253113109893</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26811086618383</v>
+        <v>14.26810988418833</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141734965053</v>
+        <v>13.83141639771024</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733468994271</v>
+        <v>14.16733371488308</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3692,16 +3692,16 @@
         <v>44466</v>
       </c>
       <c r="B164" t="n">
-        <v>13.77263069152832</v>
+        <v>13.77263164520264</v>
       </c>
       <c r="C164" t="n">
-        <v>13.99097580453232</v>
+        <v>13.99097677332576</v>
       </c>
       <c r="D164" t="n">
-        <v>13.5122946974641</v>
+        <v>13.51229563311167</v>
       </c>
       <c r="E164" t="n">
-        <v>13.86500803211849</v>
+        <v>13.8650089921894</v>
       </c>
       <c r="F164" t="n">
         <v>2647359</v>
@@ -3732,16 +3732,16 @@
         <v>44468</v>
       </c>
       <c r="B166" t="n">
-        <v>12.9832239151001</v>
+        <v>12.98322486877441</v>
       </c>
       <c r="C166" t="n">
-        <v>13.50389590448827</v>
+        <v>13.50389689640821</v>
       </c>
       <c r="D166" t="n">
-        <v>12.80686643555174</v>
+        <v>12.80686737627183</v>
       </c>
       <c r="E166" t="n">
-        <v>13.29394718124052</v>
+        <v>13.29394815773881</v>
       </c>
       <c r="F166" t="n">
         <v>4585796</v>
@@ -3752,16 +3752,16 @@
         <v>44469</v>
       </c>
       <c r="B167" t="n">
-        <v>12.55492973327637</v>
+        <v>12.55492782592773</v>
       </c>
       <c r="C167" t="n">
-        <v>13.05880655802494</v>
+        <v>13.05880457412719</v>
       </c>
       <c r="D167" t="n">
-        <v>12.37017503283432</v>
+        <v>12.37017315355367</v>
       </c>
       <c r="E167" t="n">
-        <v>13.05880655802494</v>
+        <v>13.05880457412719</v>
       </c>
       <c r="F167" t="n">
         <v>6213762</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498119354248</v>
+        <v>12.34498023986816</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366398204986</v>
+        <v>12.82366299139635</v>
       </c>
       <c r="D169" t="n">
-        <v>12.13503244542976</v>
+        <v>12.1350315079744</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288861542754</v>
+        <v>12.72288763255913</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14342975616455</v>
+        <v>12.14343070983887</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55492921366123</v>
+        <v>12.55493019965232</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027704898789</v>
+        <v>11.95027798749311</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337849210345</v>
+        <v>12.35337946226592</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3852,16 +3852,16 @@
         <v>44476</v>
       </c>
       <c r="B172" t="n">
-        <v>13.00002002716064</v>
+        <v>13.00002098083496</v>
       </c>
       <c r="C172" t="n">
-        <v>13.02521407051771</v>
+        <v>13.02521502604024</v>
       </c>
       <c r="D172" t="n">
-        <v>12.36177579954892</v>
+        <v>12.36177670640198</v>
       </c>
       <c r="E172" t="n">
-        <v>12.56332733461089</v>
+        <v>12.56332825624967</v>
       </c>
       <c r="F172" t="n">
         <v>3555051</v>
@@ -3912,16 +3912,16 @@
         <v>44482</v>
       </c>
       <c r="B175" t="n">
-        <v>13.12598896026611</v>
+        <v>13.12599086761475</v>
       </c>
       <c r="C175" t="n">
-        <v>13.34433570458859</v>
+        <v>13.34433764366538</v>
       </c>
       <c r="D175" t="n">
-        <v>12.83206171217867</v>
+        <v>12.83206357681648</v>
       </c>
       <c r="E175" t="n">
-        <v>12.83206171217867</v>
+        <v>12.83206357681648</v>
       </c>
       <c r="F175" t="n">
         <v>2244954</v>
@@ -3952,16 +3952,16 @@
         <v>44484</v>
       </c>
       <c r="B177" t="n">
-        <v>13.41991901397705</v>
+        <v>13.41991710662842</v>
       </c>
       <c r="C177" t="n">
-        <v>13.48710313716229</v>
+        <v>13.4871012202649</v>
       </c>
       <c r="D177" t="n">
-        <v>13.08400164522936</v>
+        <v>13.08399978562405</v>
       </c>
       <c r="E177" t="n">
-        <v>13.24356231420505</v>
+        <v>13.24356043192167</v>
       </c>
       <c r="F177" t="n">
         <v>1650266</v>
@@ -4032,16 +4032,16 @@
         <v>44490</v>
       </c>
       <c r="B181" t="n">
-        <v>11.24485015869141</v>
+        <v>11.24484920501709</v>
       </c>
       <c r="C181" t="n">
-        <v>11.95867573884459</v>
+        <v>11.95867472463081</v>
       </c>
       <c r="D181" t="n">
-        <v>10.8333514897461</v>
+        <v>10.83335057097093</v>
       </c>
       <c r="E181" t="n">
-        <v>11.84950235751801</v>
+        <v>11.84950135256322</v>
       </c>
       <c r="F181" t="n">
         <v>4870723</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.5310230255127</v>
+        <v>10.53102397918701</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174709395853</v>
+        <v>10.84174807577158</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624045672820648</v>
+        <v>9.624046544360398</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174709395853</v>
+        <v>10.84174807577158</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55621719360352</v>
+        <v>10.55621814727783</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650190285215</v>
+        <v>11.02650289901313</v>
       </c>
       <c r="D183" t="n">
-        <v>10.35466648795489</v>
+        <v>10.35466742342063</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699254642783</v>
+        <v>10.65699350920643</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4152,16 +4152,16 @@
         <v>44498</v>
       </c>
       <c r="B187" t="n">
-        <v>9.514873504638672</v>
+        <v>9.514872550964355</v>
       </c>
       <c r="C187" t="n">
-        <v>10.06913760232501</v>
+        <v>10.06913659309689</v>
       </c>
       <c r="D187" t="n">
-        <v>9.069781974119245</v>
+        <v>9.069781065056384</v>
       </c>
       <c r="E187" t="n">
-        <v>10.06913760232501</v>
+        <v>10.06913659309689</v>
       </c>
       <c r="F187" t="n">
         <v>8163450</v>
@@ -4172,16 +4172,16 @@
         <v>44501</v>
       </c>
       <c r="B188" t="n">
-        <v>9.464485168457031</v>
+        <v>9.464486122131348</v>
       </c>
       <c r="C188" t="n">
-        <v>9.817198528320054</v>
+        <v>9.817199517534991</v>
       </c>
       <c r="D188" t="n">
-        <v>9.002597620700316</v>
+        <v>9.002598527833245</v>
       </c>
       <c r="E188" t="n">
-        <v>9.220944372898632</v>
+        <v>9.220945302032934</v>
       </c>
       <c r="F188" t="n">
         <v>8542036</v>
@@ -4212,16 +4212,16 @@
         <v>44504</v>
       </c>
       <c r="B190" t="n">
-        <v>10.35466766357422</v>
+        <v>10.3546667098999</v>
       </c>
       <c r="C190" t="n">
-        <v>11.22805469507473</v>
+        <v>11.22805366096068</v>
       </c>
       <c r="D190" t="n">
-        <v>10.02714752676152</v>
+        <v>10.02714660325211</v>
       </c>
       <c r="E190" t="n">
-        <v>10.08593362946343</v>
+        <v>10.08593270053977</v>
       </c>
       <c r="F190" t="n">
         <v>7850142</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55621719360352</v>
+        <v>10.55621814727783</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771580682453</v>
+        <v>10.96771679767463</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588039192727</v>
+        <v>10.29588132208213</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64019651899136</v>
+        <v>10.64019748025258</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4252,16 +4252,16 @@
         <v>44508</v>
       </c>
       <c r="B192" t="n">
-        <v>10.58980941772461</v>
+        <v>10.58981037139893</v>
       </c>
       <c r="C192" t="n">
-        <v>10.82495137020977</v>
+        <v>10.82495234506</v>
       </c>
       <c r="D192" t="n">
-        <v>10.11112587531288</v>
+        <v>10.11112678587894</v>
       </c>
       <c r="E192" t="n">
-        <v>10.82495137020977</v>
+        <v>10.82495234506</v>
       </c>
       <c r="F192" t="n">
         <v>1684830</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.74937152862549</v>
+        <v>10.74937057495117</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324836976697</v>
+        <v>11.25324737138916</v>
       </c>
       <c r="D193" t="n">
-        <v>10.40505616072565</v>
+        <v>10.40505523759868</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660608538766</v>
+        <v>10.60660514437936</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4372,16 +4372,16 @@
         <v>44517</v>
       </c>
       <c r="B198" t="n">
-        <v>10.10272789001465</v>
+        <v>10.10272884368896</v>
       </c>
       <c r="C198" t="n">
-        <v>10.35466668271126</v>
+        <v>10.35466766016802</v>
       </c>
       <c r="D198" t="n">
-        <v>9.800402637649874</v>
+        <v>9.800403562785382</v>
       </c>
       <c r="E198" t="n">
-        <v>10.29588058557796</v>
+        <v>10.29588155748545</v>
       </c>
       <c r="F198" t="n">
         <v>3557179</v>
@@ -4392,16 +4392,16 @@
         <v>44518</v>
       </c>
       <c r="B199" t="n">
-        <v>10.34627056121826</v>
+        <v>10.34626960754395</v>
       </c>
       <c r="C199" t="n">
-        <v>10.57301454196442</v>
+        <v>10.57301356738983</v>
       </c>
       <c r="D199" t="n">
-        <v>10.0103523801132</v>
+        <v>10.01035145740236</v>
       </c>
       <c r="E199" t="n">
-        <v>10.13632179950193</v>
+        <v>10.13632086517977</v>
       </c>
       <c r="F199" t="n">
         <v>2248603</v>
@@ -4412,16 +4412,16 @@
         <v>44519</v>
       </c>
       <c r="B200" t="n">
-        <v>10.80815601348877</v>
+        <v>10.80815505981445</v>
       </c>
       <c r="C200" t="n">
-        <v>10.950921446049</v>
+        <v>10.95092047977755</v>
       </c>
       <c r="D200" t="n">
-        <v>10.3378712675281</v>
+        <v>10.33787035535008</v>
       </c>
       <c r="E200" t="n">
-        <v>10.3378712675281</v>
+        <v>10.33787035535008</v>
       </c>
       <c r="F200" t="n">
         <v>2187279</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674434661865234</v>
+        <v>9.674433708190918</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34627018804897</v>
+        <v>10.34626916814729</v>
       </c>
       <c r="D202" t="n">
-        <v>9.481281937939977</v>
+        <v>9.48128100330603</v>
       </c>
       <c r="E202" t="n">
-        <v>10.2874840822837</v>
+        <v>10.28748306817697</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4492,16 +4492,16 @@
         <v>44525</v>
       </c>
       <c r="B204" t="n">
-        <v>9.825596809387207</v>
+        <v>9.825597763061523</v>
       </c>
       <c r="C204" t="n">
-        <v>10.15311613477726</v>
+        <v>10.15311712024066</v>
       </c>
       <c r="D204" t="n">
-        <v>9.657638139351562</v>
+        <v>9.657639076723777</v>
       </c>
       <c r="E204" t="n">
-        <v>9.901178129723791</v>
+        <v>9.901179090734045</v>
       </c>
       <c r="F204" t="n">
         <v>1557621</v>
@@ -4512,16 +4512,16 @@
         <v>44526</v>
       </c>
       <c r="B205" t="n">
-        <v>9.472883224487305</v>
+        <v>9.472881317138672</v>
       </c>
       <c r="C205" t="n">
-        <v>9.682831981145643</v>
+        <v>9.682830031524192</v>
       </c>
       <c r="D205" t="n">
-        <v>9.178955127524551</v>
+        <v>9.178953279357833</v>
       </c>
       <c r="E205" t="n">
-        <v>9.657638747310545</v>
+        <v>9.657636802761706</v>
       </c>
       <c r="F205" t="n">
         <v>2092506</v>
@@ -4532,16 +4532,16 @@
         <v>44529</v>
       </c>
       <c r="B206" t="n">
-        <v>9.632443428039551</v>
+        <v>9.632444381713867</v>
       </c>
       <c r="C206" t="n">
-        <v>9.909576269733462</v>
+        <v>9.909577250845725</v>
       </c>
       <c r="D206" t="n">
-        <v>9.456086755539426</v>
+        <v>9.456087691753288</v>
       </c>
       <c r="E206" t="n">
-        <v>9.741616799538319</v>
+        <v>9.741617764021505</v>
       </c>
       <c r="F206" t="n">
         <v>2527144</v>
@@ -4552,16 +4552,16 @@
         <v>44530</v>
       </c>
       <c r="B207" t="n">
-        <v>9.388903617858887</v>
+        <v>9.38890266418457</v>
       </c>
       <c r="C207" t="n">
-        <v>9.624047225271497</v>
+        <v>9.624046247712556</v>
       </c>
       <c r="D207" t="n">
-        <v>8.952210898304161</v>
+        <v>8.952209988986741</v>
       </c>
       <c r="E207" t="n">
-        <v>9.498077000696213</v>
+        <v>9.498076035932652</v>
       </c>
       <c r="F207" t="n">
         <v>4785579</v>
@@ -4572,16 +4572,16 @@
         <v>44531</v>
       </c>
       <c r="B208" t="n">
-        <v>9.019393920898438</v>
+        <v>9.019394874572754</v>
       </c>
       <c r="C208" t="n">
-        <v>9.766810668101018</v>
+        <v>9.766811700804164</v>
       </c>
       <c r="D208" t="n">
-        <v>9.019393920898438</v>
+        <v>9.019394874572754</v>
       </c>
       <c r="E208" t="n">
-        <v>9.54006591503742</v>
+        <v>9.540066923765492</v>
       </c>
       <c r="F208" t="n">
         <v>2660840</v>
@@ -4612,16 +4612,16 @@
         <v>44533</v>
       </c>
       <c r="B210" t="n">
-        <v>9.901179313659668</v>
+        <v>9.901178359985352</v>
       </c>
       <c r="C210" t="n">
-        <v>10.08593484694453</v>
+        <v>10.0859338754747</v>
       </c>
       <c r="D210" t="n">
-        <v>9.61564921573892</v>
+        <v>9.615648289566654</v>
       </c>
       <c r="E210" t="n">
-        <v>9.64924127848065</v>
+        <v>9.649240349072821</v>
       </c>
       <c r="F210" t="n">
         <v>1913704</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884381294250488</v>
+        <v>9.884383201599121</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709460595107</v>
+        <v>10.23709658136135</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573656425494187</v>
+        <v>9.573658272883511</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867584455842815</v>
+        <v>9.867586359950231</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4672,16 +4672,16 @@
         <v>44538</v>
       </c>
       <c r="B213" t="n">
-        <v>10.57301425933838</v>
+        <v>10.57301330566406</v>
       </c>
       <c r="C213" t="n">
-        <v>10.66539242640349</v>
+        <v>10.66539146439676</v>
       </c>
       <c r="D213" t="n">
-        <v>9.792005341235662</v>
+        <v>9.792004458007494</v>
       </c>
       <c r="E213" t="n">
-        <v>9.985158878759011</v>
+        <v>9.985157978108607</v>
       </c>
       <c r="F213" t="n">
         <v>3040540</v>
@@ -4712,16 +4712,16 @@
         <v>44540</v>
       </c>
       <c r="B215" t="n">
-        <v>11.166090965271</v>
+        <v>11.16609001159668</v>
       </c>
       <c r="C215" t="n">
-        <v>11.32816530341248</v>
+        <v>11.32816433589571</v>
       </c>
       <c r="D215" t="n">
-        <v>10.86753323435248</v>
+        <v>10.86753230617741</v>
       </c>
       <c r="E215" t="n">
-        <v>11.012546942251</v>
+        <v>11.01254600169058</v>
       </c>
       <c r="F215" t="n">
         <v>3272354</v>
@@ -4732,16 +4732,16 @@
         <v>44543</v>
       </c>
       <c r="B216" t="n">
-        <v>11.19168186187744</v>
+        <v>11.19168281555176</v>
       </c>
       <c r="C216" t="n">
-        <v>11.55848208514464</v>
+        <v>11.55848307007503</v>
       </c>
       <c r="D216" t="n">
-        <v>11.13196966068666</v>
+        <v>11.13197060927274</v>
       </c>
       <c r="E216" t="n">
-        <v>11.25992355294072</v>
+        <v>11.2599245124301</v>
       </c>
       <c r="F216" t="n">
         <v>3334589</v>
@@ -4772,16 +4772,16 @@
         <v>44545</v>
       </c>
       <c r="B218" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845455169678</v>
       </c>
       <c r="C218" t="n">
-        <v>11.37934603413065</v>
+        <v>11.37934699719004</v>
       </c>
       <c r="D218" t="n">
-        <v>10.8163502410046</v>
+        <v>10.81635115641641</v>
       </c>
       <c r="E218" t="n">
-        <v>10.90165255894037</v>
+        <v>10.9016534815715</v>
       </c>
       <c r="F218" t="n">
         <v>3122034</v>
@@ -4852,16 +4852,16 @@
         <v>44551</v>
       </c>
       <c r="B222" t="n">
-        <v>10.739577293396</v>
+        <v>10.73957824707031</v>
       </c>
       <c r="C222" t="n">
-        <v>11.05519726804268</v>
+        <v>11.05519824974405</v>
       </c>
       <c r="D222" t="n">
-        <v>10.51779159906087</v>
+        <v>10.51779253304062</v>
       </c>
       <c r="E222" t="n">
-        <v>10.84194106328138</v>
+        <v>10.8419420260456</v>
       </c>
       <c r="F222" t="n">
         <v>1915833</v>
@@ -4872,16 +4872,16 @@
         <v>44552</v>
       </c>
       <c r="B223" t="n">
-        <v>10.57750415802002</v>
+        <v>10.5775032043457</v>
       </c>
       <c r="C223" t="n">
-        <v>10.84194143213719</v>
+        <v>10.84194045462105</v>
       </c>
       <c r="D223" t="n">
-        <v>10.33865617807819</v>
+        <v>10.33865524593855</v>
       </c>
       <c r="E223" t="n">
-        <v>10.83341111768986</v>
+        <v>10.83341014094282</v>
       </c>
       <c r="F223" t="n">
         <v>1137579</v>
@@ -4912,16 +4912,16 @@
         <v>44557</v>
       </c>
       <c r="B225" t="n">
-        <v>10.3215970993042</v>
+        <v>10.32159614562988</v>
       </c>
       <c r="C225" t="n">
-        <v>10.58603439200949</v>
+        <v>10.58603341390223</v>
       </c>
       <c r="D225" t="n">
-        <v>9.971856656129408</v>
+        <v>9.971855734769711</v>
       </c>
       <c r="E225" t="n">
-        <v>10.49220175107643</v>
+        <v>10.49220078163893</v>
       </c>
       <c r="F225" t="n">
         <v>1768251</v>
@@ -4932,16 +4932,16 @@
         <v>44558</v>
       </c>
       <c r="B226" t="n">
-        <v>10.08274936676025</v>
+        <v>10.08274841308594</v>
       </c>
       <c r="C226" t="n">
-        <v>10.50073148249594</v>
+        <v>10.50073048928689</v>
       </c>
       <c r="D226" t="n">
-        <v>9.98891755562571</v>
+        <v>9.988916610826452</v>
       </c>
       <c r="E226" t="n">
-        <v>10.15952137333246</v>
+        <v>10.15952041239668</v>
       </c>
       <c r="F226" t="n">
         <v>1405681</v>
@@ -4952,16 +4952,16 @@
         <v>44559</v>
       </c>
       <c r="B227" t="n">
-        <v>9.715948104858398</v>
+        <v>9.715949058532715</v>
       </c>
       <c r="C227" t="n">
-        <v>10.21923248819867</v>
+        <v>10.21923349127314</v>
       </c>
       <c r="D227" t="n">
-        <v>9.596524538126543</v>
+        <v>9.596525480078773</v>
       </c>
       <c r="E227" t="n">
-        <v>10.21923248819867</v>
+        <v>10.21923349127314</v>
       </c>
       <c r="F227" t="n">
         <v>1535423</v>
@@ -4992,16 +4992,16 @@
         <v>44564</v>
       </c>
       <c r="B229" t="n">
-        <v>9.664768218994141</v>
+        <v>9.664767265319824</v>
       </c>
       <c r="C229" t="n">
-        <v>10.2192337269546</v>
+        <v>10.21923271856821</v>
       </c>
       <c r="D229" t="n">
-        <v>9.349148224283301</v>
+        <v>9.349147301752897</v>
       </c>
       <c r="E229" t="n">
-        <v>10.2192337269546</v>
+        <v>10.21923271856821</v>
       </c>
       <c r="F229" t="n">
         <v>4324384</v>
@@ -5052,16 +5052,16 @@
         <v>44567</v>
       </c>
       <c r="B232" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="C232" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="D232" t="n">
-        <v>8.393760513964654</v>
+        <v>8.393761408545751</v>
       </c>
       <c r="E232" t="n">
-        <v>8.547305340985826</v>
+        <v>8.547306251931259</v>
       </c>
       <c r="F232" t="n">
         <v>4969753</v>
@@ -5092,16 +5092,16 @@
         <v>44571</v>
       </c>
       <c r="B234" t="n">
-        <v>8.581425666809082</v>
+        <v>8.581424713134766</v>
       </c>
       <c r="C234" t="n">
-        <v>8.828803119963837</v>
+        <v>8.828802138797872</v>
       </c>
       <c r="D234" t="n">
-        <v>8.316987585908032</v>
+        <v>8.316986661621351</v>
       </c>
       <c r="E234" t="n">
-        <v>8.828803119963837</v>
+        <v>8.828802138797872</v>
       </c>
       <c r="F234" t="n">
         <v>3048446</v>
@@ -5112,16 +5112,16 @@
         <v>44572</v>
       </c>
       <c r="B235" t="n">
-        <v>8.717909812927246</v>
+        <v>8.71790885925293</v>
       </c>
       <c r="C235" t="n">
-        <v>8.914106224829805</v>
+        <v>8.914105249693064</v>
       </c>
       <c r="D235" t="n">
-        <v>8.530244540237847</v>
+        <v>8.530243607092713</v>
       </c>
       <c r="E235" t="n">
-        <v>8.530244540237847</v>
+        <v>8.530243607092713</v>
       </c>
       <c r="F235" t="n">
         <v>1168089</v>
@@ -5172,16 +5172,16 @@
         <v>44575</v>
       </c>
       <c r="B238" t="n">
-        <v>8.743499755859375</v>
+        <v>8.743500709533691</v>
       </c>
       <c r="C238" t="n">
-        <v>8.769090696819184</v>
+        <v>8.769091653284766</v>
       </c>
       <c r="D238" t="n">
-        <v>8.359639764378452</v>
+        <v>8.359640676184245</v>
       </c>
       <c r="E238" t="n">
-        <v>8.726439953136079</v>
+        <v>8.726440904949643</v>
       </c>
       <c r="F238" t="n">
         <v>2170250</v>
@@ -5212,16 +5212,16 @@
         <v>44579</v>
       </c>
       <c r="B240" t="n">
-        <v>8.308457374572754</v>
+        <v>8.308456420898438</v>
       </c>
       <c r="C240" t="n">
-        <v>8.76056154167938</v>
+        <v>8.760560536110937</v>
       </c>
       <c r="D240" t="n">
-        <v>8.206094431414945</v>
+        <v>8.206093489490213</v>
       </c>
       <c r="E240" t="n">
-        <v>8.530243888845217</v>
+        <v>8.530242909713456</v>
       </c>
       <c r="F240" t="n">
         <v>2291580</v>
@@ -5232,16 +5232,16 @@
         <v>44580</v>
       </c>
       <c r="B241" t="n">
-        <v>8.521714210510254</v>
+        <v>8.521713256835938</v>
       </c>
       <c r="C241" t="n">
-        <v>8.675259048991672</v>
+        <v>8.675258078133986</v>
       </c>
       <c r="D241" t="n">
-        <v>8.291398189663132</v>
+        <v>8.291397261763732</v>
       </c>
       <c r="E241" t="n">
-        <v>8.308457994309213</v>
+        <v>8.308457064500631</v>
       </c>
       <c r="F241" t="n">
         <v>1675201</v>
@@ -5332,16 +5332,16 @@
         <v>44587</v>
       </c>
       <c r="B246" t="n">
-        <v>10.21070194244385</v>
+        <v>10.21070289611816</v>
       </c>
       <c r="C246" t="n">
-        <v>10.50073012672415</v>
+        <v>10.50073110748695</v>
       </c>
       <c r="D246" t="n">
-        <v>9.767128940260308</v>
+        <v>9.767129852505134</v>
       </c>
       <c r="E246" t="n">
-        <v>9.809780507617658</v>
+        <v>9.80978142384612</v>
       </c>
       <c r="F246" t="n">
         <v>3425105</v>
@@ -5352,16 +5352,16 @@
         <v>44588</v>
       </c>
       <c r="B247" t="n">
-        <v>10.15952110290527</v>
+        <v>10.15952014923096</v>
       </c>
       <c r="C247" t="n">
-        <v>10.5007312029864</v>
+        <v>10.50073021728269</v>
       </c>
       <c r="D247" t="n">
-        <v>9.988917289739678</v>
+        <v>9.988916352079942</v>
       </c>
       <c r="E247" t="n">
-        <v>10.28747499350861</v>
+        <v>10.28747402782326</v>
       </c>
       <c r="F247" t="n">
         <v>2570932</v>
@@ -5392,16 +5392,16 @@
         <v>44592</v>
       </c>
       <c r="B249" t="n">
-        <v>10.47514057159424</v>
+        <v>10.47513961791992</v>
       </c>
       <c r="C249" t="n">
-        <v>10.56044289300652</v>
+        <v>10.56044193156613</v>
       </c>
       <c r="D249" t="n">
-        <v>10.18511234895917</v>
+        <v>10.1851114216895</v>
       </c>
       <c r="E249" t="n">
-        <v>10.22776392195697</v>
+        <v>10.22776299080424</v>
       </c>
       <c r="F249" t="n">
         <v>3321007</v>
@@ -5492,16 +5492,16 @@
         <v>44599</v>
       </c>
       <c r="B254" t="n">
-        <v>10.13392925262451</v>
+        <v>10.13393115997314</v>
       </c>
       <c r="C254" t="n">
-        <v>10.34718460107495</v>
+        <v>10.34718654856125</v>
       </c>
       <c r="D254" t="n">
-        <v>9.937732880783731</v>
+        <v>9.937734751205435</v>
       </c>
       <c r="E254" t="n">
-        <v>10.04862612374453</v>
+        <v>10.04862801503791</v>
       </c>
       <c r="F254" t="n">
         <v>1517482</v>
@@ -5512,16 +5512,16 @@
         <v>44600</v>
       </c>
       <c r="B255" t="n">
-        <v>10.05715656280518</v>
+        <v>10.05715751647949</v>
       </c>
       <c r="C255" t="n">
-        <v>10.2789438760924</v>
+        <v>10.27894485079779</v>
       </c>
       <c r="D255" t="n">
-        <v>9.912142066473093</v>
+        <v>9.912143006396347</v>
       </c>
       <c r="E255" t="n">
-        <v>10.21070137213227</v>
+        <v>10.21070234036655</v>
       </c>
       <c r="F255" t="n">
         <v>1782745</v>
@@ -5532,16 +5532,16 @@
         <v>44601</v>
       </c>
       <c r="B256" t="n">
-        <v>10.24482536315918</v>
+        <v>10.24482345581055</v>
       </c>
       <c r="C256" t="n">
-        <v>10.3301276913325</v>
+        <v>10.33012576810256</v>
       </c>
       <c r="D256" t="n">
-        <v>9.937735662401773</v>
+        <v>9.937733812226112</v>
       </c>
       <c r="E256" t="n">
-        <v>10.25335567843485</v>
+        <v>10.25335376949807</v>
       </c>
       <c r="F256" t="n">
         <v>1982123</v>
@@ -5552,16 +5552,16 @@
         <v>44602</v>
       </c>
       <c r="B257" t="n">
-        <v>9.99744701385498</v>
+        <v>9.997446060180664</v>
       </c>
       <c r="C257" t="n">
-        <v>10.38130787007986</v>
+        <v>10.38130687978837</v>
       </c>
       <c r="D257" t="n">
-        <v>9.92067500752667</v>
+        <v>9.920674061175772</v>
       </c>
       <c r="E257" t="n">
-        <v>10.36424724098838</v>
+        <v>10.36424625232434</v>
       </c>
       <c r="F257" t="n">
         <v>2000064</v>
@@ -5592,16 +5592,16 @@
         <v>44606</v>
       </c>
       <c r="B259" t="n">
-        <v>10.57750415802002</v>
+        <v>10.5775032043457</v>
       </c>
       <c r="C259" t="n">
-        <v>10.65427616346264</v>
+        <v>10.65427520286651</v>
       </c>
       <c r="D259" t="n">
-        <v>9.767130057607208</v>
+        <v>9.767129176996722</v>
       </c>
       <c r="E259" t="n">
-        <v>9.775661196637856</v>
+        <v>9.775660315258195</v>
       </c>
       <c r="F259" t="n">
         <v>2873091</v>
@@ -5652,16 +5652,16 @@
         <v>44609</v>
       </c>
       <c r="B262" t="n">
-        <v>10.29600429534912</v>
+        <v>10.29600524902344</v>
       </c>
       <c r="C262" t="n">
-        <v>10.64574467538268</v>
+        <v>10.64574566145193</v>
       </c>
       <c r="D262" t="n">
-        <v>10.22776261187708</v>
+        <v>10.22776355923047</v>
       </c>
       <c r="E262" t="n">
-        <v>10.54338173788301</v>
+        <v>10.54338271447082</v>
       </c>
       <c r="F262" t="n">
         <v>3533562</v>
@@ -5732,16 +5732,16 @@
         <v>44615</v>
       </c>
       <c r="B266" t="n">
-        <v>9.767129898071289</v>
+        <v>9.767128944396973</v>
       </c>
       <c r="C266" t="n">
-        <v>10.11687031094908</v>
+        <v>10.11686932312569</v>
       </c>
       <c r="D266" t="n">
-        <v>9.681827579574664</v>
+        <v>9.68182663422937</v>
       </c>
       <c r="E266" t="n">
-        <v>9.775661036962589</v>
+        <v>9.775660082455282</v>
       </c>
       <c r="F266" t="n">
         <v>2319860</v>
@@ -5752,16 +5752,16 @@
         <v>44616</v>
       </c>
       <c r="B267" t="n">
-        <v>9.78419017791748</v>
+        <v>9.784191131591797</v>
       </c>
       <c r="C267" t="n">
-        <v>9.886553121381233</v>
+        <v>9.886554085032964</v>
       </c>
       <c r="D267" t="n">
-        <v>9.15295188912712</v>
+        <v>9.15295278127404</v>
       </c>
       <c r="E267" t="n">
-        <v>9.15295188912712</v>
+        <v>9.15295278127404</v>
       </c>
       <c r="F267" t="n">
         <v>2513764</v>
@@ -5772,16 +5772,16 @@
         <v>44617</v>
       </c>
       <c r="B268" t="n">
-        <v>9.425920486450195</v>
+        <v>9.425919532775879</v>
       </c>
       <c r="C268" t="n">
-        <v>9.869492701072385</v>
+        <v>9.86949170251933</v>
       </c>
       <c r="D268" t="n">
-        <v>9.383268915533016</v>
+        <v>9.383267966174003</v>
       </c>
       <c r="E268" t="n">
-        <v>9.579464492585451</v>
+        <v>9.579463523376209</v>
       </c>
       <c r="F268" t="n">
         <v>3597927</v>
@@ -5832,16 +5832,16 @@
         <v>44624</v>
       </c>
       <c r="B271" t="n">
-        <v>9.323555946350098</v>
+        <v>9.323556900024414</v>
       </c>
       <c r="C271" t="n">
-        <v>9.613584955470987</v>
+        <v>9.613585938811369</v>
       </c>
       <c r="D271" t="n">
-        <v>8.931164824647187</v>
+        <v>8.931165738185172</v>
       </c>
       <c r="E271" t="n">
-        <v>9.511221193722513</v>
+        <v>9.511222166592459</v>
       </c>
       <c r="F271" t="n">
         <v>3245493</v>
@@ -5892,16 +5892,16 @@
         <v>44629</v>
       </c>
       <c r="B274" t="n">
-        <v>9.255314826965332</v>
+        <v>9.255313873291016</v>
       </c>
       <c r="C274" t="n">
-        <v>9.391799026361806</v>
+        <v>9.391798058624058</v>
       </c>
       <c r="D274" t="n">
-        <v>8.845863053359189</v>
+        <v>8.845862141875079</v>
       </c>
       <c r="E274" t="n">
-        <v>8.939696507345268</v>
+        <v>8.93969558619249</v>
       </c>
       <c r="F274" t="n">
         <v>2821903</v>
@@ -5912,16 +5912,16 @@
         <v>44630</v>
       </c>
       <c r="B275" t="n">
-        <v>9.195605278015137</v>
+        <v>9.19560432434082</v>
       </c>
       <c r="C275" t="n">
-        <v>9.280907610343647</v>
+        <v>9.280906647822642</v>
       </c>
       <c r="D275" t="n">
-        <v>8.922636825063778</v>
+        <v>8.922635899698962</v>
       </c>
       <c r="E275" t="n">
-        <v>9.144423383867966</v>
+        <v>9.144422435501713</v>
       </c>
       <c r="F275" t="n">
         <v>2148356</v>
@@ -5972,16 +5972,16 @@
         <v>44635</v>
       </c>
       <c r="B278" t="n">
-        <v>8.905575752258301</v>
+        <v>8.905576705932617</v>
       </c>
       <c r="C278" t="n">
-        <v>8.948226500067653</v>
+        <v>8.948227458309324</v>
       </c>
       <c r="D278" t="n">
-        <v>8.581426275823933</v>
+        <v>8.581427194785949</v>
       </c>
       <c r="E278" t="n">
-        <v>8.666728596025962</v>
+        <v>8.666729524122774</v>
       </c>
       <c r="F278" t="n">
         <v>2087539</v>
@@ -5992,16 +5992,16 @@
         <v>44636</v>
       </c>
       <c r="B279" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="C279" t="n">
-        <v>9.229724687144891</v>
+        <v>9.229725670820471</v>
       </c>
       <c r="D279" t="n">
-        <v>8.589956086292677</v>
+        <v>8.589957001783693</v>
       </c>
       <c r="E279" t="n">
-        <v>8.956756289014645</v>
+        <v>8.956757243598096</v>
       </c>
       <c r="F279" t="n">
         <v>2215964</v>
@@ -6072,16 +6072,16 @@
         <v>44642</v>
       </c>
       <c r="B283" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C283" t="n">
-        <v>10.1253999073854</v>
+        <v>10.12539894068065</v>
       </c>
       <c r="D283" t="n">
-        <v>9.57093441902218</v>
+        <v>9.570933505254049</v>
       </c>
       <c r="E283" t="n">
-        <v>9.57093441902218</v>
+        <v>9.570933505254049</v>
       </c>
       <c r="F283" t="n">
         <v>2594043</v>
@@ -6132,16 +6132,16 @@
         <v>44645</v>
       </c>
       <c r="B286" t="n">
-        <v>10.7566385269165</v>
+        <v>10.75663948059082</v>
       </c>
       <c r="C286" t="n">
-        <v>10.83341052818152</v>
+        <v>10.83341148866237</v>
       </c>
       <c r="D286" t="n">
-        <v>10.37277687142488</v>
+        <v>10.37277779106635</v>
       </c>
       <c r="E286" t="n">
-        <v>10.6030936998032</v>
+        <v>10.60309463986436</v>
       </c>
       <c r="F286" t="n">
         <v>2057131</v>
@@ -6172,16 +6172,16 @@
         <v>44649</v>
       </c>
       <c r="B288" t="n">
-        <v>11.34522438049316</v>
+        <v>11.34522533416748</v>
       </c>
       <c r="C288" t="n">
-        <v>11.52435931133431</v>
+        <v>11.52436028006663</v>
       </c>
       <c r="D288" t="n">
-        <v>10.85046950547176</v>
+        <v>10.85047041755722</v>
       </c>
       <c r="E288" t="n">
-        <v>10.97842338089396</v>
+        <v>10.97842430373515</v>
       </c>
       <c r="F288" t="n">
         <v>4333811</v>
@@ -6192,16 +6192,16 @@
         <v>44650</v>
       </c>
       <c r="B289" t="n">
-        <v>11.166090965271</v>
+        <v>11.16609001159668</v>
       </c>
       <c r="C289" t="n">
-        <v>11.46464952077289</v>
+        <v>11.46464854159927</v>
       </c>
       <c r="D289" t="n">
-        <v>11.02107725737248</v>
+        <v>11.02107631608351</v>
       </c>
       <c r="E289" t="n">
-        <v>11.35375624877694</v>
+        <v>11.3537552790745</v>
       </c>
       <c r="F289" t="n">
         <v>2393651</v>
@@ -6232,16 +6232,16 @@
         <v>44652</v>
       </c>
       <c r="B291" t="n">
-        <v>11.24286365509033</v>
+        <v>11.24286270141602</v>
       </c>
       <c r="C291" t="n">
-        <v>11.25139314551746</v>
+        <v>11.25139219111963</v>
       </c>
       <c r="D291" t="n">
-        <v>10.77369962784609</v>
+        <v>10.77369871396854</v>
       </c>
       <c r="E291" t="n">
-        <v>10.96136490891043</v>
+        <v>10.96136397911421</v>
       </c>
       <c r="F291" t="n">
         <v>2500385</v>
@@ -6252,16 +6252,16 @@
         <v>44655</v>
       </c>
       <c r="B292" t="n">
-        <v>11.24286365509033</v>
+        <v>11.24286270141602</v>
       </c>
       <c r="C292" t="n">
-        <v>11.32816515602863</v>
+        <v>11.32816419511862</v>
       </c>
       <c r="D292" t="n">
-        <v>10.84194214793012</v>
+        <v>10.84194122826391</v>
       </c>
       <c r="E292" t="n">
-        <v>11.14903101455816</v>
+        <v>11.14903006884318</v>
       </c>
       <c r="F292" t="n">
         <v>2094330</v>
@@ -6292,16 +6292,16 @@
         <v>44657</v>
       </c>
       <c r="B294" t="n">
-        <v>10.57750415802002</v>
+        <v>10.5775032043457</v>
       </c>
       <c r="C294" t="n">
-        <v>10.73104816890526</v>
+        <v>10.73104720138732</v>
       </c>
       <c r="D294" t="n">
-        <v>10.21070311053493</v>
+        <v>10.21070218993162</v>
       </c>
       <c r="E294" t="n">
-        <v>10.73104816890526</v>
+        <v>10.73104720138732</v>
       </c>
       <c r="F294" t="n">
         <v>3552010</v>
@@ -6372,16 +6372,16 @@
         <v>44663</v>
       </c>
       <c r="B298" t="n">
-        <v>10.55191230773926</v>
+        <v>10.55191135406494</v>
       </c>
       <c r="C298" t="n">
-        <v>10.90165272360005</v>
+        <v>10.90165173831644</v>
       </c>
       <c r="D298" t="n">
-        <v>10.40689861243314</v>
+        <v>10.40689767186506</v>
       </c>
       <c r="E298" t="n">
-        <v>10.44954935975358</v>
+        <v>10.44954841533075</v>
       </c>
       <c r="F298" t="n">
         <v>1608302</v>
@@ -6432,16 +6432,16 @@
         <v>44669</v>
       </c>
       <c r="B301" t="n">
-        <v>10.7566385269165</v>
+        <v>10.75663948059082</v>
       </c>
       <c r="C301" t="n">
-        <v>10.9784242167284</v>
+        <v>10.97842519006605</v>
       </c>
       <c r="D301" t="n">
-        <v>10.66280507310193</v>
+        <v>10.66280601845705</v>
       </c>
       <c r="E301" t="n">
-        <v>10.81634990021523</v>
+        <v>10.81635085918351</v>
       </c>
       <c r="F301" t="n">
         <v>2677159</v>
@@ -6452,16 +6452,16 @@
         <v>44670</v>
       </c>
       <c r="B302" t="n">
-        <v>10.94430446624756</v>
+        <v>10.94430351257324</v>
       </c>
       <c r="C302" t="n">
-        <v>11.07225753478839</v>
+        <v>11.07225656996439</v>
       </c>
       <c r="D302" t="n">
-        <v>10.48367078083392</v>
+        <v>10.4836698672987</v>
       </c>
       <c r="E302" t="n">
-        <v>10.68839667999924</v>
+        <v>10.68839574862444</v>
       </c>
       <c r="F302" t="n">
         <v>3002225</v>
@@ -6572,16 +6572,16 @@
         <v>44679</v>
       </c>
       <c r="B308" t="n">
-        <v>11.68643379211426</v>
+        <v>11.68643474578857</v>
       </c>
       <c r="C308" t="n">
-        <v>11.89968997951292</v>
+        <v>11.89969095059006</v>
       </c>
       <c r="D308" t="n">
-        <v>10.4410187461559</v>
+        <v>10.44101959819782</v>
       </c>
       <c r="E308" t="n">
-        <v>10.81634924017761</v>
+        <v>10.81635012284846</v>
       </c>
       <c r="F308" t="n">
         <v>5881398</v>
@@ -6612,16 +6612,16 @@
         <v>44683</v>
       </c>
       <c r="B310" t="n">
-        <v>11.43905830383301</v>
+        <v>11.43905925750732</v>
       </c>
       <c r="C310" t="n">
-        <v>11.75467663475006</v>
+        <v>11.75467761473748</v>
       </c>
       <c r="D310" t="n">
-        <v>11.32816421788021</v>
+        <v>11.32816516230928</v>
       </c>
       <c r="E310" t="n">
-        <v>11.47317873646595</v>
+        <v>11.47317969298488</v>
       </c>
       <c r="F310" t="n">
         <v>3385270</v>
@@ -6632,16 +6632,16 @@
         <v>44684</v>
       </c>
       <c r="B311" t="n">
-        <v>11.31963443756104</v>
+        <v>11.31963348388672</v>
       </c>
       <c r="C311" t="n">
-        <v>11.52436032643616</v>
+        <v>11.52435935551378</v>
       </c>
       <c r="D311" t="n">
-        <v>11.25992306354883</v>
+        <v>11.25992211490517</v>
       </c>
       <c r="E311" t="n">
-        <v>11.38787612565832</v>
+        <v>11.38787516623467</v>
       </c>
       <c r="F311" t="n">
         <v>2034324</v>
@@ -6652,16 +6652,16 @@
         <v>44685</v>
       </c>
       <c r="B312" t="n">
-        <v>11.83144950866699</v>
+        <v>11.83144855499268</v>
       </c>
       <c r="C312" t="n">
-        <v>11.95087308479659</v>
+        <v>11.95087212149613</v>
       </c>
       <c r="D312" t="n">
-        <v>10.95283372865995</v>
+        <v>10.95283284580649</v>
       </c>
       <c r="E312" t="n">
-        <v>11.09784824779946</v>
+        <v>11.09784735325709</v>
       </c>
       <c r="F312" t="n">
         <v>3044087</v>
@@ -6672,16 +6672,16 @@
         <v>44686</v>
       </c>
       <c r="B313" t="n">
-        <v>11.60966205596924</v>
+        <v>11.60966300964355</v>
       </c>
       <c r="C313" t="n">
-        <v>11.76320605257407</v>
+        <v>11.76320701886124</v>
       </c>
       <c r="D313" t="n">
-        <v>11.38787555013271</v>
+        <v>11.3878764855884</v>
       </c>
       <c r="E313" t="n">
-        <v>11.76320605257407</v>
+        <v>11.76320701886124</v>
       </c>
       <c r="F313" t="n">
         <v>3999622</v>
@@ -6712,16 +6712,16 @@
         <v>44690</v>
       </c>
       <c r="B315" t="n">
-        <v>10.99548530578613</v>
+        <v>10.99548625946045</v>
       </c>
       <c r="C315" t="n">
-        <v>11.41346741015497</v>
+        <v>11.41346840008224</v>
       </c>
       <c r="D315" t="n">
-        <v>10.85900192549901</v>
+        <v>10.85900286733568</v>
       </c>
       <c r="E315" t="n">
-        <v>11.40493792039742</v>
+        <v>11.4049389095849</v>
       </c>
       <c r="F315" t="n">
         <v>3635836</v>
@@ -6792,16 +6792,16 @@
         <v>44694</v>
       </c>
       <c r="B319" t="n">
-        <v>11.82291889190674</v>
+        <v>11.82291984558105</v>
       </c>
       <c r="C319" t="n">
-        <v>12.07882584170994</v>
+        <v>12.07882681602652</v>
       </c>
       <c r="D319" t="n">
-        <v>11.45611868314717</v>
+        <v>11.45611960723421</v>
       </c>
       <c r="E319" t="n">
-        <v>11.5328906856298</v>
+        <v>11.53289161590952</v>
       </c>
       <c r="F319" t="n">
         <v>2912723</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381118774414</v>
+        <v>11.93381214141846</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470443775087</v>
+        <v>12.04470540028707</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908449000746</v>
+        <v>11.72908542732132</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81438762430742</v>
+        <v>11.81438856843816</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6832,16 +6832,16 @@
         <v>44698</v>
       </c>
       <c r="B321" t="n">
-        <v>12.15559673309326</v>
+        <v>12.15559768676758</v>
       </c>
       <c r="C321" t="n">
-        <v>12.29208092192941</v>
+        <v>12.29208188631167</v>
       </c>
       <c r="D321" t="n">
-        <v>11.95087168671386</v>
+        <v>11.95087262432635</v>
       </c>
       <c r="E321" t="n">
-        <v>12.02764368217903</v>
+        <v>12.02764462581472</v>
       </c>
       <c r="F321" t="n">
         <v>4223023</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415878295898</v>
+        <v>12.45415782928467</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505205610663</v>
+        <v>12.56505109394068</v>
       </c>
       <c r="D323" t="n">
-        <v>11.95087430848125</v>
+        <v>11.95087339334582</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559939977298</v>
+        <v>12.15559846896078</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6892,16 +6892,16 @@
         <v>44701</v>
       </c>
       <c r="B324" t="n">
-        <v>12.50533771514893</v>
+        <v>12.50533866882324</v>
       </c>
       <c r="C324" t="n">
-        <v>12.658882538139</v>
+        <v>12.65888350352286</v>
       </c>
       <c r="D324" t="n">
-        <v>12.30914297255499</v>
+        <v>12.30914391126722</v>
       </c>
       <c r="E324" t="n">
-        <v>12.4797467738867</v>
+        <v>12.47974772560942</v>
       </c>
       <c r="F324" t="n">
         <v>4482610</v>
@@ -6952,16 +6952,16 @@
         <v>44706</v>
       </c>
       <c r="B327" t="n">
-        <v>12.36885452270508</v>
+        <v>12.36885356903076</v>
       </c>
       <c r="C327" t="n">
-        <v>12.51386904370087</v>
+        <v>12.51386807884551</v>
       </c>
       <c r="D327" t="n">
-        <v>12.08735661974265</v>
+        <v>12.08735568777263</v>
       </c>
       <c r="E327" t="n">
-        <v>12.21531051184678</v>
+        <v>12.21530957001115</v>
       </c>
       <c r="F327" t="n">
         <v>1655537</v>
@@ -7052,16 +7052,16 @@
         <v>44713</v>
       </c>
       <c r="B332" t="n">
-        <v>12.69300270080566</v>
+        <v>12.6930046081543</v>
       </c>
       <c r="C332" t="n">
-        <v>12.71006415253714</v>
+        <v>12.71006606244956</v>
       </c>
       <c r="D332" t="n">
-        <v>12.23236989071926</v>
+        <v>12.23237172884965</v>
       </c>
       <c r="E332" t="n">
-        <v>12.5223980784897</v>
+        <v>12.52239996020196</v>
       </c>
       <c r="F332" t="n">
         <v>4014218</v>
@@ -7072,16 +7072,16 @@
         <v>44714</v>
       </c>
       <c r="B333" t="n">
-        <v>12.57358074188232</v>
+        <v>12.57358169555664</v>
       </c>
       <c r="C333" t="n">
-        <v>13.05980452292923</v>
+        <v>13.05980551348239</v>
       </c>
       <c r="D333" t="n">
-        <v>12.43709654079169</v>
+        <v>12.43709748411402</v>
       </c>
       <c r="E333" t="n">
-        <v>12.69300349018043</v>
+        <v>12.69300445291266</v>
       </c>
       <c r="F333" t="n">
         <v>2071017</v>
@@ -7112,16 +7112,16 @@
         <v>44718</v>
       </c>
       <c r="B335" t="n">
-        <v>12.36885452270508</v>
+        <v>12.36885356903076</v>
       </c>
       <c r="C335" t="n">
-        <v>12.65888356469666</v>
+        <v>12.65888258866027</v>
       </c>
       <c r="D335" t="n">
-        <v>12.19824988295512</v>
+        <v>12.19824894243491</v>
       </c>
       <c r="E335" t="n">
-        <v>12.65888356469666</v>
+        <v>12.65888258866027</v>
       </c>
       <c r="F335" t="n">
         <v>1740275</v>
@@ -7132,16 +7132,16 @@
         <v>44719</v>
       </c>
       <c r="B336" t="n">
-        <v>12.02764511108398</v>
+        <v>12.02764415740967</v>
       </c>
       <c r="C336" t="n">
-        <v>12.37738470118792</v>
+        <v>12.37738371978268</v>
       </c>
       <c r="D336" t="n">
-        <v>11.87410110191233</v>
+        <v>11.87410016041255</v>
       </c>
       <c r="E336" t="n">
-        <v>12.36885438683579</v>
+        <v>12.36885340610692</v>
       </c>
       <c r="F336" t="n">
         <v>3370370</v>
@@ -7152,16 +7152,16 @@
         <v>44720</v>
       </c>
       <c r="B337" t="n">
-        <v>12.02764511108398</v>
+        <v>12.02764415740967</v>
       </c>
       <c r="C337" t="n">
-        <v>12.14706868743044</v>
+        <v>12.14706772428701</v>
       </c>
       <c r="D337" t="n">
-        <v>11.80585941167863</v>
+        <v>11.80585847558975</v>
       </c>
       <c r="E337" t="n">
-        <v>11.9679329106191</v>
+        <v>11.96793196167938</v>
       </c>
       <c r="F337" t="n">
         <v>2224783</v>
@@ -7172,16 +7172,16 @@
         <v>44721</v>
       </c>
       <c r="B338" t="n">
-        <v>12.15559673309326</v>
+        <v>12.15559768676758</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20677943770874</v>
+        <v>12.20678039539862</v>
       </c>
       <c r="D338" t="n">
-        <v>11.83997843789384</v>
+        <v>11.83997936680614</v>
       </c>
       <c r="E338" t="n">
-        <v>12.07029524887259</v>
+        <v>12.07029619585453</v>
       </c>
       <c r="F338" t="n">
         <v>1444097</v>
@@ -7212,16 +7212,16 @@
         <v>44725</v>
       </c>
       <c r="B340" t="n">
-        <v>10.7225170135498</v>
+        <v>10.72251796722412</v>
       </c>
       <c r="C340" t="n">
-        <v>11.50729928449115</v>
+        <v>11.507300307965</v>
       </c>
       <c r="D340" t="n">
-        <v>10.57750332848451</v>
+        <v>10.57750426926113</v>
       </c>
       <c r="E340" t="n">
-        <v>11.234331717334</v>
+        <v>11.23433271652977</v>
       </c>
       <c r="F340" t="n">
         <v>3958469</v>
@@ -7232,16 +7232,16 @@
         <v>44726</v>
       </c>
       <c r="B341" t="n">
-        <v>10.69692611694336</v>
+        <v>10.69692707061768</v>
       </c>
       <c r="C341" t="n">
-        <v>10.94430356838314</v>
+        <v>10.94430454411216</v>
       </c>
       <c r="D341" t="n">
-        <v>10.57750337271373</v>
+        <v>10.57750431574103</v>
       </c>
       <c r="E341" t="n">
-        <v>10.79075956889747</v>
+        <v>10.79076053093742</v>
       </c>
       <c r="F341" t="n">
         <v>2253062</v>
@@ -7252,16 +7252,16 @@
         <v>44727</v>
       </c>
       <c r="B342" t="n">
-        <v>10.83340930938721</v>
+        <v>10.83341026306152</v>
       </c>
       <c r="C342" t="n">
-        <v>11.0722556002944</v>
+        <v>11.07225657499456</v>
       </c>
       <c r="D342" t="n">
-        <v>10.67133418652475</v>
+        <v>10.67133512593145</v>
       </c>
       <c r="E342" t="n">
-        <v>10.88459036294475</v>
+        <v>10.88459132112458</v>
       </c>
       <c r="F342" t="n">
         <v>3158221</v>
@@ -7292,16 +7292,16 @@
         <v>44732</v>
       </c>
       <c r="B344" t="n">
-        <v>10.38130664825439</v>
+        <v>10.38130760192871</v>
       </c>
       <c r="C344" t="n">
-        <v>10.93577290555292</v>
+        <v>10.93577391016304</v>
       </c>
       <c r="D344" t="n">
-        <v>10.33012559158704</v>
+        <v>10.33012654055963</v>
       </c>
       <c r="E344" t="n">
-        <v>10.93577290555292</v>
+        <v>10.93577391016304</v>
       </c>
       <c r="F344" t="n">
         <v>1404768</v>
@@ -7392,16 +7392,16 @@
         <v>44739</v>
       </c>
       <c r="B349" t="n">
-        <v>10.739577293396</v>
+        <v>10.73957824707031</v>
       </c>
       <c r="C349" t="n">
-        <v>10.8504705528552</v>
+        <v>10.85047151637684</v>
       </c>
       <c r="D349" t="n">
-        <v>10.45807939996106</v>
+        <v>10.45808032863837</v>
       </c>
       <c r="E349" t="n">
-        <v>10.7992894924958</v>
+        <v>10.79929045147256</v>
       </c>
       <c r="F349" t="n">
         <v>1685945</v>
@@ -7412,16 +7412,16 @@
         <v>44740</v>
       </c>
       <c r="B350" t="n">
-        <v>10.23629379272461</v>
+        <v>10.23629283905029</v>
       </c>
       <c r="C350" t="n">
-        <v>10.81635108415403</v>
+        <v>10.81635007643811</v>
       </c>
       <c r="D350" t="n">
-        <v>10.18511272780684</v>
+        <v>10.18511177890085</v>
       </c>
       <c r="E350" t="n">
-        <v>10.70545781481826</v>
+        <v>10.70545681743382</v>
       </c>
       <c r="F350" t="n">
         <v>2763519</v>
@@ -7452,16 +7452,16 @@
         <v>44742</v>
       </c>
       <c r="B352" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C352" t="n">
-        <v>10.1253999073854</v>
+        <v>10.12539894068065</v>
       </c>
       <c r="D352" t="n">
-        <v>9.724478429017642</v>
+        <v>9.724477500590167</v>
       </c>
       <c r="E352" t="n">
-        <v>9.97185589738994</v>
+        <v>9.971854945344536</v>
       </c>
       <c r="F352" t="n">
         <v>3400779</v>
@@ -7492,16 +7492,16 @@
         <v>44746</v>
       </c>
       <c r="B354" t="n">
-        <v>9.656237602233887</v>
+        <v>9.65623664855957</v>
       </c>
       <c r="C354" t="n">
-        <v>10.02303785582285</v>
+        <v>10.02303686592241</v>
       </c>
       <c r="D354" t="n">
-        <v>9.656237602233887</v>
+        <v>9.65623664855957</v>
       </c>
       <c r="E354" t="n">
-        <v>9.920675723057759</v>
+        <v>9.920674743266868</v>
       </c>
       <c r="F354" t="n">
         <v>1779400</v>
@@ -7552,16 +7552,16 @@
         <v>44749</v>
       </c>
       <c r="B357" t="n">
-        <v>9.912142753601074</v>
+        <v>9.912143707275391</v>
       </c>
       <c r="C357" t="n">
-        <v>10.1168694550903</v>
+        <v>10.11687042846193</v>
       </c>
       <c r="D357" t="n">
-        <v>9.630645703584392</v>
+        <v>9.630646630175109</v>
       </c>
       <c r="E357" t="n">
-        <v>9.647705506173859</v>
+        <v>9.647706434405947</v>
       </c>
       <c r="F357" t="n">
         <v>2588468</v>
@@ -7572,16 +7572,16 @@
         <v>44750</v>
       </c>
       <c r="B358" t="n">
-        <v>9.78419017791748</v>
+        <v>9.784191131591797</v>
       </c>
       <c r="C358" t="n">
-        <v>10.19364195177249</v>
+        <v>10.19364294535647</v>
       </c>
       <c r="D358" t="n">
-        <v>9.724477979890045</v>
+        <v>9.724478927744158</v>
       </c>
       <c r="E358" t="n">
-        <v>9.869492493373395</v>
+        <v>9.86949345536221</v>
       </c>
       <c r="F358" t="n">
         <v>1378414</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.11030101776123</v>
+        <v>9.110300064086914</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707418920911163</v>
+        <v>9.707417904730018</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076180583712192</v>
+        <v>9.076179633609632</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707418920911163</v>
+        <v>9.707417904730018</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7632,16 +7632,16 @@
         <v>44755</v>
       </c>
       <c r="B361" t="n">
-        <v>9.255314826965332</v>
+        <v>9.255313873291016</v>
       </c>
       <c r="C361" t="n">
-        <v>9.383268712363071</v>
+        <v>9.383267745504293</v>
       </c>
       <c r="D361" t="n">
-        <v>9.050589764745537</v>
+        <v>9.050588832166239</v>
       </c>
       <c r="E361" t="n">
-        <v>9.204133767556202</v>
+        <v>9.204132819155619</v>
       </c>
       <c r="F361" t="n">
         <v>1870727</v>
@@ -7692,16 +7692,16 @@
         <v>44760</v>
       </c>
       <c r="B364" t="n">
-        <v>9.511222839355469</v>
+        <v>9.511221885681152</v>
       </c>
       <c r="C364" t="n">
-        <v>9.698888119197754</v>
+        <v>9.698887146706557</v>
       </c>
       <c r="D364" t="n">
-        <v>9.212665114265498</v>
+        <v>9.212664190527063</v>
       </c>
       <c r="E364" t="n">
-        <v>9.212665114265498</v>
+        <v>9.212664190527063</v>
       </c>
       <c r="F364" t="n">
         <v>1476836</v>
@@ -7712,16 +7712,16 @@
         <v>44761</v>
       </c>
       <c r="B365" t="n">
-        <v>9.767129898071289</v>
+        <v>9.767128944396973</v>
       </c>
       <c r="C365" t="n">
-        <v>9.929205045339851</v>
+        <v>9.929204075840321</v>
       </c>
       <c r="D365" t="n">
-        <v>9.562404828429376</v>
+        <v>9.562403894744662</v>
       </c>
       <c r="E365" t="n">
-        <v>9.562404828429376</v>
+        <v>9.562403894744662</v>
       </c>
       <c r="F365" t="n">
         <v>2310433</v>
@@ -7732,16 +7732,16 @@
         <v>44762</v>
       </c>
       <c r="B366" t="n">
-        <v>10.08274936676025</v>
+        <v>10.08274841308594</v>
       </c>
       <c r="C366" t="n">
-        <v>10.20217294619664</v>
+        <v>10.20217198122667</v>
       </c>
       <c r="D366" t="n">
-        <v>9.724478628451092</v>
+        <v>9.724477708663724</v>
       </c>
       <c r="E366" t="n">
-        <v>9.767130201315277</v>
+        <v>9.767129277493721</v>
       </c>
       <c r="F366" t="n">
         <v>1476532</v>
@@ -7772,16 +7772,16 @@
         <v>44764</v>
       </c>
       <c r="B368" t="n">
-        <v>10.35571765899658</v>
+        <v>10.35571670532227</v>
       </c>
       <c r="C368" t="n">
-        <v>10.3898389168763</v>
+        <v>10.38983796005971</v>
       </c>
       <c r="D368" t="n">
-        <v>9.954796177243145</v>
+        <v>9.954795260490318</v>
       </c>
       <c r="E368" t="n">
-        <v>10.07421893065553</v>
+        <v>10.07421800290487</v>
       </c>
       <c r="F368" t="n">
         <v>1969757</v>
@@ -7792,16 +7792,16 @@
         <v>44767</v>
       </c>
       <c r="B369" t="n">
-        <v>10.17658233642578</v>
+        <v>10.17658138275146</v>
       </c>
       <c r="C369" t="n">
-        <v>10.41542865919991</v>
+        <v>10.41542768314268</v>
       </c>
       <c r="D369" t="n">
-        <v>10.11687013729478</v>
+        <v>10.11686918921625</v>
       </c>
       <c r="E369" t="n">
-        <v>10.27041414303648</v>
+        <v>10.27041318056894</v>
       </c>
       <c r="F369" t="n">
         <v>1372535</v>
@@ -7812,16 +7812,16 @@
         <v>44768</v>
       </c>
       <c r="B370" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="C370" t="n">
-        <v>10.40689863334928</v>
+        <v>10.40689763976893</v>
       </c>
       <c r="D370" t="n">
-        <v>9.988917350769043</v>
+        <v>9.988916397094727</v>
       </c>
       <c r="E370" t="n">
-        <v>10.22776368016013</v>
+        <v>10.22776270368238</v>
       </c>
       <c r="F370" t="n">
         <v>1502988</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.50926208496094</v>
+        <v>10.50926113128662</v>
       </c>
       <c r="C371" t="n">
-        <v>10.6116250380558</v>
+        <v>10.61162407509244</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421932816195</v>
+        <v>10.07421841396606</v>
       </c>
       <c r="E371" t="n">
-        <v>10.1254003924177</v>
+        <v>10.12539947357733</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7852,16 +7852,16 @@
         <v>44770</v>
       </c>
       <c r="B372" t="n">
-        <v>10.74810791015625</v>
+        <v>10.74810695648193</v>
       </c>
       <c r="C372" t="n">
-        <v>10.84194136852631</v>
+        <v>10.8419404065262</v>
       </c>
       <c r="D372" t="n">
-        <v>10.21923336502487</v>
+        <v>10.21923245827733</v>
       </c>
       <c r="E372" t="n">
-        <v>10.21923336502487</v>
+        <v>10.21923245827733</v>
       </c>
       <c r="F372" t="n">
         <v>1467207</v>
@@ -7892,16 +7892,16 @@
         <v>44774</v>
       </c>
       <c r="B374" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845455169678</v>
       </c>
       <c r="C374" t="n">
-        <v>11.77173801596846</v>
+        <v>11.77173901223685</v>
       </c>
       <c r="D374" t="n">
-        <v>11.09784813756763</v>
+        <v>11.09784907680322</v>
       </c>
       <c r="E374" t="n">
-        <v>11.64378412677316</v>
+        <v>11.64378511221253</v>
       </c>
       <c r="F374" t="n">
         <v>4838693</v>
@@ -7912,16 +7912,16 @@
         <v>44775</v>
       </c>
       <c r="B375" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845455169678</v>
       </c>
       <c r="C375" t="n">
-        <v>11.49876960907404</v>
+        <v>11.49877058224051</v>
       </c>
       <c r="D375" t="n">
-        <v>11.24286265526674</v>
+        <v>11.24286360677524</v>
       </c>
       <c r="E375" t="n">
-        <v>11.39640666263446</v>
+        <v>11.39640762713773</v>
       </c>
       <c r="F375" t="n">
         <v>2088249</v>
@@ -7952,16 +7952,16 @@
         <v>44777</v>
       </c>
       <c r="B377" t="n">
-        <v>12.62476253509521</v>
+        <v>12.6247615814209</v>
       </c>
       <c r="C377" t="n">
-        <v>12.68447473729527</v>
+        <v>12.6844737791103</v>
       </c>
       <c r="D377" t="n">
-        <v>11.54142082672753</v>
+        <v>11.54141995488882</v>
       </c>
       <c r="E377" t="n">
-        <v>11.55848228051088</v>
+        <v>11.55848140738335</v>
       </c>
       <c r="F377" t="n">
         <v>5052363</v>
@@ -7972,16 +7972,16 @@
         <v>44778</v>
       </c>
       <c r="B378" t="n">
-        <v>12.79536724090576</v>
+        <v>12.79536628723145</v>
       </c>
       <c r="C378" t="n">
-        <v>12.93185145059431</v>
+        <v>12.93185048674745</v>
       </c>
       <c r="D378" t="n">
-        <v>12.24090173667624</v>
+        <v>12.24090082432778</v>
       </c>
       <c r="E378" t="n">
-        <v>12.32620405851283</v>
+        <v>12.32620313980655</v>
       </c>
       <c r="F378" t="n">
         <v>4419056</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.1621675491333</v>
+        <v>13.16216850280762</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718124064354</v>
+        <v>13.30718220482493</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271576790837</v>
+        <v>12.75271669191557</v>
       </c>
       <c r="E379" t="n">
-        <v>12.79536651411238</v>
+        <v>12.79536744120987</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8012,16 +8012,16 @@
         <v>44782</v>
       </c>
       <c r="B380" t="n">
-        <v>13.0939245223999</v>
+        <v>13.09392356872559</v>
       </c>
       <c r="C380" t="n">
-        <v>13.34983228792179</v>
+        <v>13.34983131560886</v>
       </c>
       <c r="D380" t="n">
-        <v>12.92331989510748</v>
+        <v>12.92331895385887</v>
       </c>
       <c r="E380" t="n">
-        <v>13.34130197409885</v>
+        <v>13.3413010024072</v>
       </c>
       <c r="F380" t="n">
         <v>4116999</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248275756836</v>
+        <v>13.39248371124268</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634439797231</v>
+        <v>13.77634537898129</v>
       </c>
       <c r="D381" t="n">
-        <v>13.1792273901216</v>
+        <v>13.17922832861007</v>
       </c>
       <c r="E381" t="n">
-        <v>13.307180445673</v>
+        <v>13.30718139327297</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8092,16 +8092,16 @@
         <v>44788</v>
       </c>
       <c r="B384" t="n">
-        <v>13.55455780029297</v>
+        <v>13.55455875396729</v>
       </c>
       <c r="C384" t="n">
-        <v>13.70810179574578</v>
+        <v>13.70810276022317</v>
       </c>
       <c r="D384" t="n">
-        <v>13.44366454820672</v>
+        <v>13.44366549407879</v>
       </c>
       <c r="E384" t="n">
-        <v>13.64839042519929</v>
+        <v>13.6483913854755</v>
       </c>
       <c r="F384" t="n">
         <v>3349490</v>
@@ -8132,16 +8132,16 @@
         <v>44790</v>
       </c>
       <c r="B386" t="n">
-        <v>13.56308841705322</v>
+        <v>13.56308746337891</v>
       </c>
       <c r="C386" t="n">
-        <v>13.64839073027631</v>
+        <v>13.64838977060406</v>
       </c>
       <c r="D386" t="n">
-        <v>13.23893896713886</v>
+        <v>13.23893803625678</v>
       </c>
       <c r="E386" t="n">
-        <v>13.64839073027631</v>
+        <v>13.64838977060406</v>
       </c>
       <c r="F386" t="n">
         <v>4054357</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066959381104</v>
+        <v>12.88066864013672</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801884508153</v>
+        <v>12.83801789456504</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8232,16 +8232,16 @@
         <v>44797</v>
       </c>
       <c r="B391" t="n">
-        <v>12.42856597900391</v>
+        <v>12.42856693267822</v>
       </c>
       <c r="C391" t="n">
-        <v>12.57358049130923</v>
+        <v>12.57358145611087</v>
       </c>
       <c r="D391" t="n">
-        <v>12.1300074650419</v>
+        <v>12.13000839580709</v>
       </c>
       <c r="E391" t="n">
-        <v>12.2920817806332</v>
+        <v>12.29208272383475</v>
       </c>
       <c r="F391" t="n">
         <v>4991546</v>
@@ -8312,16 +8312,16 @@
         <v>44803</v>
       </c>
       <c r="B395" t="n">
-        <v>12.21531105041504</v>
+        <v>12.21531009674072</v>
       </c>
       <c r="C395" t="n">
-        <v>12.47121884590617</v>
+        <v>12.47121787225261</v>
       </c>
       <c r="D395" t="n">
-        <v>12.06176703278704</v>
+        <v>12.06176609110022</v>
       </c>
       <c r="E395" t="n">
-        <v>12.25796262452468</v>
+        <v>12.25796166752047</v>
       </c>
       <c r="F395" t="n">
         <v>2841466</v>
@@ -8392,16 +8392,16 @@
         <v>44809</v>
       </c>
       <c r="B399" t="n">
-        <v>13.30718231201172</v>
+        <v>13.3071813583374</v>
       </c>
       <c r="C399" t="n">
-        <v>13.40954526555925</v>
+        <v>13.40954430454897</v>
       </c>
       <c r="D399" t="n">
-        <v>12.38591655466734</v>
+        <v>12.38591566701658</v>
       </c>
       <c r="E399" t="n">
-        <v>12.48827868363151</v>
+        <v>12.48827778864485</v>
       </c>
       <c r="F399" t="n">
         <v>2134165</v>
@@ -8432,16 +8432,16 @@
         <v>44812</v>
       </c>
       <c r="B401" t="n">
-        <v>12.15559673309326</v>
+        <v>12.15559768676758</v>
       </c>
       <c r="C401" t="n">
-        <v>12.53945835958558</v>
+        <v>12.53945934337598</v>
       </c>
       <c r="D401" t="n">
-        <v>11.79732687120029</v>
+        <v>11.79732779676633</v>
       </c>
       <c r="E401" t="n">
-        <v>12.53945835958558</v>
+        <v>12.53945934337598</v>
       </c>
       <c r="F401" t="n">
         <v>2311852</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.3347339630127</v>
+        <v>12.33473491668701</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121816816301</v>
+        <v>12.47121913238976</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646323371185</v>
+        <v>11.97646415968605</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22384070093743</v>
+        <v>12.22384164603791</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8532,16 +8532,16 @@
         <v>44819</v>
       </c>
       <c r="B406" t="n">
-        <v>12.76943683624268</v>
+        <v>12.76943778991699</v>
       </c>
       <c r="C406" t="n">
-        <v>12.9321592806806</v>
+        <v>12.9321602465077</v>
       </c>
       <c r="D406" t="n">
-        <v>12.33265506062422</v>
+        <v>12.33265598167787</v>
       </c>
       <c r="E406" t="n">
-        <v>12.54676388734078</v>
+        <v>12.54676482438496</v>
       </c>
       <c r="F406" t="n">
         <v>3409247</v>
@@ -8572,16 +8572,16 @@
         <v>44823</v>
       </c>
       <c r="B408" t="n">
-        <v>12.39260673522949</v>
+        <v>12.39260768890381</v>
       </c>
       <c r="C408" t="n">
-        <v>12.60671391874965</v>
+        <v>12.60671488890061</v>
       </c>
       <c r="D408" t="n">
-        <v>12.19562614739096</v>
+        <v>12.19562708590662</v>
       </c>
       <c r="E408" t="n">
-        <v>12.34122035151799</v>
+        <v>12.34122130123787</v>
       </c>
       <c r="F408" t="n">
         <v>1221893</v>
@@ -8652,16 +8652,16 @@
         <v>44827</v>
       </c>
       <c r="B412" t="n">
-        <v>11.90443897247314</v>
+        <v>11.90443801879883</v>
       </c>
       <c r="C412" t="n">
-        <v>12.15280430338444</v>
+        <v>12.15280332981337</v>
       </c>
       <c r="D412" t="n">
-        <v>11.80166620152132</v>
+        <v>11.80166525608022</v>
       </c>
       <c r="E412" t="n">
-        <v>11.93869546334595</v>
+        <v>11.93869450692731</v>
       </c>
       <c r="F412" t="n">
         <v>2822076</v>
@@ -8672,16 +8672,16 @@
         <v>44830</v>
       </c>
       <c r="B413" t="n">
-        <v>11.45909309387207</v>
+        <v>11.45909214019775</v>
       </c>
       <c r="C413" t="n">
-        <v>11.84448851276911</v>
+        <v>11.84448752702055</v>
       </c>
       <c r="D413" t="n">
-        <v>11.34775619974625</v>
+        <v>11.34775525533786</v>
       </c>
       <c r="E413" t="n">
-        <v>11.81879531992597</v>
+        <v>11.81879433631571</v>
       </c>
       <c r="F413" t="n">
         <v>3443068</v>
@@ -8692,16 +8692,16 @@
         <v>44831</v>
       </c>
       <c r="B414" t="n">
-        <v>11.30493354797363</v>
+        <v>11.30493450164795</v>
       </c>
       <c r="C414" t="n">
-        <v>11.6389425453333</v>
+        <v>11.63894352718433</v>
       </c>
       <c r="D414" t="n">
-        <v>11.26211211422024</v>
+        <v>11.26211306428218</v>
       </c>
       <c r="E414" t="n">
-        <v>11.53617060957519</v>
+        <v>11.53617158275647</v>
       </c>
       <c r="F414" t="n">
         <v>2656202</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186485290527</v>
+        <v>11.56186389923096</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889411306563</v>
+        <v>11.69889314808853</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072675530685</v>
+        <v>11.21072583059598</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775601546721</v>
+        <v>11.34775507945355</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8732,16 +8732,16 @@
         <v>44833</v>
       </c>
       <c r="B416" t="n">
-        <v>11.61325073242188</v>
+        <v>11.61324977874756</v>
       </c>
       <c r="C416" t="n">
-        <v>11.66463629045436</v>
+        <v>11.66463533256029</v>
       </c>
       <c r="D416" t="n">
-        <v>11.29636913906888</v>
+        <v>11.29636821141672</v>
       </c>
       <c r="E416" t="n">
-        <v>11.45052828691627</v>
+        <v>11.45052734660464</v>
       </c>
       <c r="F416" t="n">
         <v>3327572</v>
@@ -8772,16 +8772,16 @@
         <v>44837</v>
       </c>
       <c r="B418" t="n">
-        <v>12.41829776763916</v>
+        <v>12.41829872131348</v>
       </c>
       <c r="C418" t="n">
-        <v>12.6238424558075</v>
+        <v>12.62384342526681</v>
       </c>
       <c r="D418" t="n">
-        <v>12.01577333738928</v>
+        <v>12.01577426015137</v>
       </c>
       <c r="E418" t="n">
-        <v>12.06715971557718</v>
+        <v>12.06716064228553</v>
       </c>
       <c r="F418" t="n">
         <v>3117277</v>
@@ -8832,16 +8832,16 @@
         <v>44840</v>
       </c>
       <c r="B421" t="n">
-        <v>13.02636623382568</v>
+        <v>13.0263671875</v>
       </c>
       <c r="C421" t="n">
-        <v>13.26616823576436</v>
+        <v>13.26616920699484</v>
       </c>
       <c r="D421" t="n">
-        <v>12.92359430067336</v>
+        <v>12.92359524682363</v>
       </c>
       <c r="E421" t="n">
-        <v>12.98354480115803</v>
+        <v>12.98354575169734</v>
       </c>
       <c r="F421" t="n">
         <v>6127236</v>
@@ -8872,16 +8872,16 @@
         <v>44844</v>
       </c>
       <c r="B423" t="n">
-        <v>12.76087284088135</v>
+        <v>12.76087188720703</v>
       </c>
       <c r="C423" t="n">
-        <v>12.8465165373358</v>
+        <v>12.84651557726097</v>
       </c>
       <c r="D423" t="n">
-        <v>12.49537762924753</v>
+        <v>12.4953766954148</v>
       </c>
       <c r="E423" t="n">
-        <v>12.66666419757313</v>
+        <v>12.66666325093943</v>
       </c>
       <c r="F423" t="n">
         <v>2045508</v>
@@ -8912,16 +8912,16 @@
         <v>44847</v>
       </c>
       <c r="B425" t="n">
-        <v>13.05206108093262</v>
+        <v>13.0520601272583</v>
       </c>
       <c r="C425" t="n">
-        <v>13.30899135873641</v>
+        <v>13.30899038628898</v>
       </c>
       <c r="D425" t="n">
-        <v>12.57245784072665</v>
+        <v>12.57245692209548</v>
       </c>
       <c r="E425" t="n">
-        <v>12.58958608613578</v>
+        <v>12.58958516625311</v>
       </c>
       <c r="F425" t="n">
         <v>3708082</v>
@@ -8932,16 +8932,16 @@
         <v>44848</v>
       </c>
       <c r="B426" t="n">
-        <v>12.76943683624268</v>
+        <v>12.76943778991699</v>
       </c>
       <c r="C426" t="n">
-        <v>13.12057491625784</v>
+        <v>13.1205758961566</v>
       </c>
       <c r="D426" t="n">
-        <v>12.65809994950008</v>
+        <v>12.65810089485929</v>
       </c>
       <c r="E426" t="n">
-        <v>13.09488172511853</v>
+        <v>13.09488270309842</v>
       </c>
       <c r="F426" t="n">
         <v>2206838</v>
@@ -9012,16 +9012,16 @@
         <v>44854</v>
       </c>
       <c r="B430" t="n">
-        <v>12.78656578063965</v>
+        <v>12.78656482696533</v>
       </c>
       <c r="C430" t="n">
-        <v>13.08631831937005</v>
+        <v>13.08631734333896</v>
       </c>
       <c r="D430" t="n">
-        <v>12.65810064249329</v>
+        <v>12.65809969840043</v>
       </c>
       <c r="E430" t="n">
-        <v>13.08631831937005</v>
+        <v>13.08631734333896</v>
       </c>
       <c r="F430" t="n">
         <v>2107193</v>
@@ -9212,16 +9212,16 @@
         <v>44869</v>
       </c>
       <c r="B440" t="n">
-        <v>14.01126766204834</v>
+        <v>14.01126670837402</v>
       </c>
       <c r="C440" t="n">
-        <v>14.29389195916385</v>
+        <v>14.29389098625276</v>
       </c>
       <c r="D440" t="n">
-        <v>13.80572294357798</v>
+        <v>13.80572200389402</v>
       </c>
       <c r="E440" t="n">
-        <v>14.13973280187356</v>
+        <v>14.13973183945529</v>
       </c>
       <c r="F440" t="n">
         <v>3663661</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.40319633483887</v>
+        <v>13.40319728851318</v>
       </c>
       <c r="C441" t="n">
-        <v>14.0369578109963</v>
+        <v>14.03695880976449</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037572777854</v>
+        <v>13.36037667840605</v>
       </c>
       <c r="E441" t="n">
-        <v>13.93418670488506</v>
+        <v>13.9341876963408</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9252,16 +9252,16 @@
         <v>44873</v>
       </c>
       <c r="B442" t="n">
-        <v>13.36037635803223</v>
+        <v>13.36037731170654</v>
       </c>
       <c r="C442" t="n">
-        <v>13.54879116090197</v>
+        <v>13.54879212802549</v>
       </c>
       <c r="D442" t="n">
-        <v>12.91503047943115</v>
+        <v>12.91503140131632</v>
       </c>
       <c r="E442" t="n">
-        <v>13.33468316800077</v>
+        <v>13.33468411984108</v>
       </c>
       <c r="F442" t="n">
         <v>6245357</v>
@@ -9292,16 +9292,16 @@
         <v>44875</v>
       </c>
       <c r="B444" t="n">
-        <v>12.24701118469238</v>
+        <v>12.2470121383667</v>
       </c>
       <c r="C444" t="n">
-        <v>12.83795040949141</v>
+        <v>12.83795140918214</v>
       </c>
       <c r="D444" t="n">
-        <v>11.6732002028586</v>
+        <v>11.67320111185027</v>
       </c>
       <c r="E444" t="n">
-        <v>12.83795040949141</v>
+        <v>12.83795140918214</v>
       </c>
       <c r="F444" t="n">
         <v>10581398</v>
@@ -9312,16 +9312,16 @@
         <v>44876</v>
       </c>
       <c r="B445" t="n">
-        <v>11.51904106140137</v>
+        <v>11.51904201507568</v>
       </c>
       <c r="C445" t="n">
-        <v>12.25557529843945</v>
+        <v>12.25557631309227</v>
       </c>
       <c r="D445" t="n">
-        <v>11.3477545089409</v>
+        <v>11.34775544843421</v>
       </c>
       <c r="E445" t="n">
-        <v>11.80166449139856</v>
+        <v>11.80166546847159</v>
       </c>
       <c r="F445" t="n">
         <v>9635321</v>
@@ -9332,16 +9332,16 @@
         <v>44879</v>
       </c>
       <c r="B446" t="n">
-        <v>11.90443897247314</v>
+        <v>11.90443801879883</v>
       </c>
       <c r="C446" t="n">
-        <v>12.05859730431752</v>
+        <v>12.05859633829346</v>
       </c>
       <c r="D446" t="n">
-        <v>11.51904273057052</v>
+        <v>11.51904180777061</v>
       </c>
       <c r="E446" t="n">
-        <v>11.69889425515285</v>
+        <v>11.69889331794489</v>
       </c>
       <c r="F446" t="n">
         <v>2658625</v>
@@ -9452,16 +9452,16 @@
         <v>44888</v>
       </c>
       <c r="B452" t="n">
-        <v>11.04800415039062</v>
+        <v>11.04800319671631</v>
       </c>
       <c r="C452" t="n">
-        <v>11.09082641203781</v>
+        <v>11.09082545466704</v>
       </c>
       <c r="D452" t="n">
-        <v>10.78250893176141</v>
+        <v>10.78250800100489</v>
       </c>
       <c r="E452" t="n">
-        <v>10.98805364375123</v>
+        <v>10.9880526952519</v>
       </c>
       <c r="F452" t="n">
         <v>2848931</v>
@@ -9472,16 +9472,16 @@
         <v>44889</v>
       </c>
       <c r="B453" t="n">
-        <v>11.53617095947266</v>
+        <v>11.53617000579834</v>
       </c>
       <c r="C453" t="n">
-        <v>11.81879440981701</v>
+        <v>11.81879343277872</v>
       </c>
       <c r="D453" t="n">
-        <v>11.05656775347163</v>
+        <v>11.05656683944524</v>
       </c>
       <c r="E453" t="n">
-        <v>11.11651825729467</v>
+        <v>11.11651733831228</v>
       </c>
       <c r="F453" t="n">
         <v>3457606</v>
@@ -9492,16 +9492,16 @@
         <v>44890</v>
       </c>
       <c r="B454" t="n">
-        <v>10.95379543304443</v>
+        <v>10.95379447937012</v>
       </c>
       <c r="C454" t="n">
-        <v>11.54473550401364</v>
+        <v>11.54473449889009</v>
       </c>
       <c r="D454" t="n">
-        <v>10.89384493130964</v>
+        <v>10.89384398285482</v>
       </c>
       <c r="E454" t="n">
-        <v>11.51047736766524</v>
+        <v>11.51047636552432</v>
       </c>
       <c r="F454" t="n">
         <v>2880833</v>
@@ -9512,16 +9512,16 @@
         <v>44893</v>
       </c>
       <c r="B455" t="n">
-        <v>10.96236038208008</v>
+        <v>10.96235942840576</v>
       </c>
       <c r="C455" t="n">
-        <v>11.18503333764837</v>
+        <v>11.18503236460255</v>
       </c>
       <c r="D455" t="n">
-        <v>10.84245936956254</v>
+        <v>10.84245842631905</v>
       </c>
       <c r="E455" t="n">
-        <v>10.95379625963835</v>
+        <v>10.95379530670907</v>
       </c>
       <c r="F455" t="n">
         <v>2642270</v>
@@ -9592,16 +9592,16 @@
         <v>44897</v>
       </c>
       <c r="B459" t="n">
-        <v>11.32206344604492</v>
+        <v>11.32206249237061</v>
       </c>
       <c r="C459" t="n">
-        <v>11.47622094868901</v>
+        <v>11.47621998202977</v>
       </c>
       <c r="D459" t="n">
-        <v>11.07369647340539</v>
+        <v>11.07369554065139</v>
       </c>
       <c r="E459" t="n">
-        <v>11.19359748620264</v>
+        <v>11.1935965433492</v>
       </c>
       <c r="F459" t="n">
         <v>2110020</v>
@@ -9612,16 +9612,16 @@
         <v>44900</v>
       </c>
       <c r="B460" t="n">
-        <v>10.65404415130615</v>
+        <v>10.65404319763184</v>
       </c>
       <c r="C460" t="n">
-        <v>11.26211248883013</v>
+        <v>11.26211148072586</v>
       </c>
       <c r="D460" t="n">
-        <v>10.56839963178404</v>
+        <v>10.56839868577602</v>
       </c>
       <c r="E460" t="n">
-        <v>11.26211248883013</v>
+        <v>11.26211148072586</v>
       </c>
       <c r="F460" t="n">
         <v>2438739</v>
@@ -9672,16 +9672,16 @@
         <v>44903</v>
       </c>
       <c r="B463" t="n">
-        <v>9.763352394104004</v>
+        <v>9.763351440429688</v>
       </c>
       <c r="C463" t="n">
-        <v>10.37998573239832</v>
+        <v>10.37998471849188</v>
       </c>
       <c r="D463" t="n">
-        <v>9.686273639108899</v>
+        <v>9.686272692963557</v>
       </c>
       <c r="E463" t="n">
-        <v>10.27721295962702</v>
+        <v>10.27721195575933</v>
       </c>
       <c r="F463" t="n">
         <v>6542779</v>
@@ -9692,16 +9692,16 @@
         <v>44904</v>
       </c>
       <c r="B464" t="n">
-        <v>9.694835662841797</v>
+        <v>9.694836616516113</v>
       </c>
       <c r="C464" t="n">
-        <v>10.02884545286159</v>
+        <v>10.02884643939223</v>
       </c>
       <c r="D464" t="n">
-        <v>9.463598623340824</v>
+        <v>9.463599554268511</v>
       </c>
       <c r="E464" t="n">
-        <v>9.848993964036843</v>
+        <v>9.848994932875605</v>
       </c>
       <c r="F464" t="n">
         <v>4631040</v>
@@ -9792,16 +9792,16 @@
         <v>44911</v>
       </c>
       <c r="B469" t="n">
-        <v>9.84043025970459</v>
+        <v>9.840431213378906</v>
       </c>
       <c r="C469" t="n">
-        <v>10.22582647359747</v>
+        <v>10.22582746462203</v>
       </c>
       <c r="D469" t="n">
-        <v>9.754787389580212</v>
+        <v>9.754788334954545</v>
       </c>
       <c r="E469" t="n">
-        <v>9.797609649225695</v>
+        <v>9.797610598750099</v>
       </c>
       <c r="F469" t="n">
         <v>14258386</v>
@@ -9812,16 +9812,16 @@
         <v>44914</v>
       </c>
       <c r="B470" t="n">
-        <v>9.951767921447754</v>
+        <v>9.951766967773438</v>
       </c>
       <c r="C470" t="n">
-        <v>10.03741162283501</v>
+        <v>10.03741066095349</v>
       </c>
       <c r="D470" t="n">
-        <v>9.686273519105638</v>
+        <v>9.686272590873555</v>
       </c>
       <c r="E470" t="n">
-        <v>9.840431027185991</v>
+        <v>9.840430084181047</v>
       </c>
       <c r="F470" t="n">
         <v>3753211</v>
@@ -9892,16 +9892,16 @@
         <v>44918</v>
       </c>
       <c r="B474" t="n">
-        <v>10.83389568328857</v>
+        <v>10.83389472961426</v>
       </c>
       <c r="C474" t="n">
-        <v>11.26211336678155</v>
+        <v>11.26211237541256</v>
       </c>
       <c r="D474" t="n">
-        <v>10.55983633286973</v>
+        <v>10.55983540332002</v>
       </c>
       <c r="E474" t="n">
-        <v>10.57696457844277</v>
+        <v>10.57696364738531</v>
       </c>
       <c r="F474" t="n">
         <v>4288288</v>
@@ -9912,16 +9912,16 @@
         <v>44921</v>
       </c>
       <c r="B475" t="n">
-        <v>10.66260814666748</v>
+        <v>10.66260719299316</v>
       </c>
       <c r="C475" t="n">
-        <v>10.87671696917752</v>
+        <v>10.8767159963531</v>
       </c>
       <c r="D475" t="n">
-        <v>10.57696362816352</v>
+        <v>10.57696268214933</v>
       </c>
       <c r="E475" t="n">
-        <v>10.82533058790846</v>
+        <v>10.82532961968009</v>
       </c>
       <c r="F475" t="n">
         <v>1667319</v>
@@ -9932,16 +9932,16 @@
         <v>44922</v>
       </c>
       <c r="B476" t="n">
-        <v>10.52296161651611</v>
+        <v>10.5229606628418</v>
       </c>
       <c r="C476" t="n">
-        <v>10.75039054378364</v>
+        <v>10.75038956949791</v>
       </c>
       <c r="D476" t="n">
-        <v>10.37425773083552</v>
+        <v>10.37425679063793</v>
       </c>
       <c r="E476" t="n">
-        <v>10.73289562221141</v>
+        <v>10.73289464951121</v>
       </c>
       <c r="F476" t="n">
         <v>2935250</v>
@@ -9952,16 +9952,16 @@
         <v>44923</v>
       </c>
       <c r="B477" t="n">
-        <v>10.96907138824463</v>
+        <v>10.96907234191895</v>
       </c>
       <c r="C477" t="n">
-        <v>11.03030234933299</v>
+        <v>11.03030330833085</v>
       </c>
       <c r="D477" t="n">
-        <v>10.4354885018964</v>
+        <v>10.43548940917989</v>
       </c>
       <c r="E477" t="n">
-        <v>10.56669662140617</v>
+        <v>10.56669754009717</v>
       </c>
       <c r="F477" t="n">
         <v>2605824</v>
@@ -9992,16 +9992,16 @@
         <v>44928</v>
       </c>
       <c r="B479" t="n">
-        <v>10.1555757522583</v>
+        <v>10.15557479858398</v>
       </c>
       <c r="C479" t="n">
-        <v>10.91658756882882</v>
+        <v>10.91658654369057</v>
       </c>
       <c r="D479" t="n">
-        <v>9.963135827664333</v>
+        <v>9.963134892061372</v>
       </c>
       <c r="E479" t="n">
-        <v>10.91658756882882</v>
+        <v>10.91658654369057</v>
       </c>
       <c r="F479" t="n">
         <v>2948980</v>
@@ -10092,16 +10092,16 @@
         <v>44935</v>
       </c>
       <c r="B484" t="n">
-        <v>10.59293937683105</v>
+        <v>10.59294033050537</v>
       </c>
       <c r="C484" t="n">
-        <v>10.64542245596033</v>
+        <v>10.64542341435966</v>
       </c>
       <c r="D484" t="n">
-        <v>10.09434465083405</v>
+        <v>10.09434555962026</v>
       </c>
       <c r="E484" t="n">
-        <v>10.2517955726123</v>
+        <v>10.2517964955737</v>
       </c>
       <c r="F484" t="n">
         <v>3368460</v>
@@ -10112,16 +10112,16 @@
         <v>44936</v>
       </c>
       <c r="B485" t="n">
-        <v>11.11777591705322</v>
+        <v>11.11777496337891</v>
       </c>
       <c r="C485" t="n">
-        <v>11.29272092875768</v>
+        <v>11.29271996007671</v>
       </c>
       <c r="D485" t="n">
-        <v>10.48797219052666</v>
+        <v>10.48797129087642</v>
       </c>
       <c r="E485" t="n">
-        <v>10.55795019520844</v>
+        <v>10.55794928955554</v>
       </c>
       <c r="F485" t="n">
         <v>3522522</v>
@@ -10232,16 +10232,16 @@
         <v>44944</v>
       </c>
       <c r="B491" t="n">
-        <v>11.61636924743652</v>
+        <v>11.61636829376221</v>
       </c>
       <c r="C491" t="n">
-        <v>11.81755621132026</v>
+        <v>11.81755524112901</v>
       </c>
       <c r="D491" t="n">
-        <v>11.08278551475007</v>
+        <v>11.08278460488162</v>
       </c>
       <c r="E491" t="n">
-        <v>11.12652239712147</v>
+        <v>11.12652148366233</v>
       </c>
       <c r="F491" t="n">
         <v>4176830</v>
@@ -10272,16 +10272,16 @@
         <v>44946</v>
       </c>
       <c r="B493" t="n">
-        <v>11.86129283905029</v>
+        <v>11.86129379272461</v>
       </c>
       <c r="C493" t="n">
-        <v>12.01874291718245</v>
+        <v>12.0187438835161</v>
       </c>
       <c r="D493" t="n">
-        <v>11.51140199856674</v>
+        <v>11.51140292410906</v>
       </c>
       <c r="E493" t="n">
-        <v>11.92252379929955</v>
+        <v>11.92252475789698</v>
       </c>
       <c r="F493" t="n">
         <v>2495174</v>
@@ -10292,16 +10292,16 @@
         <v>44949</v>
       </c>
       <c r="B494" t="n">
-        <v>11.66885280609131</v>
+        <v>11.66885185241699</v>
       </c>
       <c r="C494" t="n">
-        <v>12.07122759256721</v>
+        <v>12.07122660600753</v>
       </c>
       <c r="D494" t="n">
-        <v>11.65135872618098</v>
+        <v>11.65135777393643</v>
       </c>
       <c r="E494" t="n">
-        <v>11.86129358047173</v>
+        <v>11.86129261106957</v>
       </c>
       <c r="F494" t="n">
         <v>1283174</v>
@@ -10332,16 +10332,16 @@
         <v>44951</v>
       </c>
       <c r="B496" t="n">
-        <v>12.24617290496826</v>
+        <v>12.24617195129395</v>
       </c>
       <c r="C496" t="n">
-        <v>12.44736072427057</v>
+        <v>12.44735975492869</v>
       </c>
       <c r="D496" t="n">
-        <v>11.96626088193075</v>
+        <v>11.96625995005467</v>
       </c>
       <c r="E496" t="n">
-        <v>12.10621689344951</v>
+        <v>12.10621595067431</v>
       </c>
       <c r="F496" t="n">
         <v>2519909</v>
@@ -10352,16 +10352,16 @@
         <v>44952</v>
       </c>
       <c r="B497" t="n">
-        <v>12.42986488342285</v>
+        <v>12.42986392974854</v>
       </c>
       <c r="C497" t="n">
-        <v>12.56982088460175</v>
+        <v>12.56981992018939</v>
       </c>
       <c r="D497" t="n">
-        <v>12.18494103916456</v>
+        <v>12.18494010428189</v>
       </c>
       <c r="E497" t="n">
-        <v>12.27241396099898</v>
+        <v>12.272413019405</v>
       </c>
       <c r="F497" t="n">
         <v>2815211</v>
@@ -10372,16 +10372,16 @@
         <v>44953</v>
       </c>
       <c r="B498" t="n">
-        <v>12.43861198425293</v>
+        <v>12.43861293792725</v>
       </c>
       <c r="C498" t="n">
-        <v>12.67478793196411</v>
+        <v>12.67478890374615</v>
       </c>
       <c r="D498" t="n">
-        <v>12.25491911259136</v>
+        <v>12.25492005218186</v>
       </c>
       <c r="E498" t="n">
-        <v>12.41236918293538</v>
+        <v>12.41237013459764</v>
       </c>
       <c r="F498" t="n">
         <v>1981500</v>
@@ -10392,16 +10392,16 @@
         <v>44956</v>
       </c>
       <c r="B499" t="n">
-        <v>12.48234844207764</v>
+        <v>12.48234748840332</v>
       </c>
       <c r="C499" t="n">
-        <v>12.81474522093406</v>
+        <v>12.81474424186402</v>
       </c>
       <c r="D499" t="n">
-        <v>12.39487635907959</v>
+        <v>12.3948754120883</v>
       </c>
       <c r="E499" t="n">
-        <v>12.46485436235613</v>
+        <v>12.46485341001839</v>
       </c>
       <c r="F499" t="n">
         <v>2566955</v>
@@ -10432,16 +10432,16 @@
         <v>44958</v>
       </c>
       <c r="B501" t="n">
-        <v>12.88472270965576</v>
+        <v>12.88472175598145</v>
       </c>
       <c r="C501" t="n">
-        <v>13.46204163472943</v>
+        <v>13.46204063832434</v>
       </c>
       <c r="D501" t="n">
-        <v>12.79724978795572</v>
+        <v>12.79724884075579</v>
       </c>
       <c r="E501" t="n">
-        <v>12.96344859184436</v>
+        <v>12.96344763234308</v>
       </c>
       <c r="F501" t="n">
         <v>8623319</v>
@@ -10452,16 +10452,16 @@
         <v>44959</v>
       </c>
       <c r="B502" t="n">
-        <v>12.91096591949463</v>
+        <v>12.91096496582031</v>
       </c>
       <c r="C502" t="n">
-        <v>13.36582380882906</v>
+        <v>13.36582282155647</v>
       </c>
       <c r="D502" t="n">
-        <v>12.77100906279498</v>
+        <v>12.77100811945864</v>
       </c>
       <c r="E502" t="n">
-        <v>12.77100906279498</v>
+        <v>12.77100811945864</v>
       </c>
       <c r="F502" t="n">
         <v>4085160</v>
@@ -10592,16 +10592,16 @@
         <v>44970</v>
       </c>
       <c r="B509" t="n">
-        <v>12.52608394622803</v>
+        <v>12.52608489990234</v>
       </c>
       <c r="C509" t="n">
-        <v>12.77100693072163</v>
+        <v>12.77100790304318</v>
       </c>
       <c r="D509" t="n">
-        <v>12.35113811510887</v>
+        <v>12.35113905546367</v>
       </c>
       <c r="E509" t="n">
-        <v>12.38612795508882</v>
+        <v>12.38612889810758</v>
       </c>
       <c r="F509" t="n">
         <v>2916169</v>
@@ -10612,16 +10612,16 @@
         <v>44971</v>
       </c>
       <c r="B510" t="n">
-        <v>12.21993064880371</v>
+        <v>12.21992969512939</v>
       </c>
       <c r="C510" t="n">
-        <v>13.11215140261074</v>
+        <v>13.11215037930526</v>
       </c>
       <c r="D510" t="n">
-        <v>12.1674467282641</v>
+        <v>12.16744577868576</v>
       </c>
       <c r="E510" t="n">
-        <v>12.94595260163369</v>
+        <v>12.94595159129879</v>
       </c>
       <c r="F510" t="n">
         <v>6896737</v>
@@ -10772,16 +10772,16 @@
         <v>44985</v>
       </c>
       <c r="B518" t="n">
-        <v>11.61636924743652</v>
+        <v>11.61636829376221</v>
       </c>
       <c r="C518" t="n">
-        <v>11.86129309369166</v>
+        <v>11.86129211990972</v>
       </c>
       <c r="D518" t="n">
-        <v>11.4064352439566</v>
+        <v>11.40643430751733</v>
       </c>
       <c r="E518" t="n">
-        <v>11.7125892095803</v>
+        <v>11.71258824800656</v>
       </c>
       <c r="F518" t="n">
         <v>5639205</v>
@@ -10832,16 +10832,16 @@
         <v>44988</v>
       </c>
       <c r="B521" t="n">
-        <v>11.6776008605957</v>
+        <v>11.67759990692139</v>
       </c>
       <c r="C521" t="n">
-        <v>11.98375484330241</v>
+        <v>11.98375386462542</v>
       </c>
       <c r="D521" t="n">
-        <v>11.60762201333577</v>
+        <v>11.60762106537642</v>
       </c>
       <c r="E521" t="n">
-        <v>11.80006279055649</v>
+        <v>11.80006182688108</v>
       </c>
       <c r="F521" t="n">
         <v>1946973</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.26366710662842</v>
+        <v>12.2636661529541</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738199094953</v>
+        <v>12.37738102843226</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87004021572346</v>
+        <v>11.87003929265923</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12371026114126</v>
+        <v>12.12370931835058</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10892,16 +10892,16 @@
         <v>44993</v>
       </c>
       <c r="B524" t="n">
-        <v>12.6835355758667</v>
+        <v>12.68353652954102</v>
       </c>
       <c r="C524" t="n">
-        <v>12.75351357540048</v>
+        <v>12.75351453433644</v>
       </c>
       <c r="D524" t="n">
-        <v>12.17619381595395</v>
+        <v>12.17619473148127</v>
       </c>
       <c r="E524" t="n">
-        <v>12.28990869684275</v>
+        <v>12.28990962092029</v>
       </c>
       <c r="F524" t="n">
         <v>2396134</v>
@@ -10912,16 +10912,16 @@
         <v>44994</v>
       </c>
       <c r="B525" t="n">
-        <v>12.70977687835693</v>
+        <v>12.70977783203125</v>
       </c>
       <c r="C525" t="n">
-        <v>12.88472272192359</v>
+        <v>12.88472368872491</v>
       </c>
       <c r="D525" t="n">
-        <v>12.55232679822025</v>
+        <v>12.55232774008035</v>
       </c>
       <c r="E525" t="n">
-        <v>12.71852476007192</v>
+        <v>12.71852571440263</v>
       </c>
       <c r="F525" t="n">
         <v>3354932</v>
@@ -10972,16 +10972,16 @@
         <v>44999</v>
       </c>
       <c r="B528" t="n">
-        <v>12.17619514465332</v>
+        <v>12.176194190979</v>
       </c>
       <c r="C528" t="n">
-        <v>12.80599889357369</v>
+        <v>12.80599789057135</v>
       </c>
       <c r="D528" t="n">
-        <v>12.10621713748334</v>
+        <v>12.10621618928991</v>
       </c>
       <c r="E528" t="n">
-        <v>12.58731698952104</v>
+        <v>12.58731600364649</v>
       </c>
       <c r="F528" t="n">
         <v>1444505</v>
@@ -11052,16 +11052,16 @@
         <v>45005</v>
       </c>
       <c r="B532" t="n">
-        <v>11.36269950866699</v>
+        <v>11.36269760131836</v>
       </c>
       <c r="C532" t="n">
-        <v>11.90502949350345</v>
+        <v>11.90502749511903</v>
       </c>
       <c r="D532" t="n">
-        <v>11.17025956495234</v>
+        <v>11.17025768990678</v>
       </c>
       <c r="E532" t="n">
-        <v>11.73008447294255</v>
+        <v>11.73008250392448</v>
       </c>
       <c r="F532" t="n">
         <v>5506849</v>
@@ -11152,16 +11152,16 @@
         <v>45012</v>
       </c>
       <c r="B537" t="n">
-        <v>11.36269950866699</v>
+        <v>11.36269760131836</v>
       </c>
       <c r="C537" t="n">
-        <v>11.52889748874868</v>
+        <v>11.52889555350197</v>
       </c>
       <c r="D537" t="n">
-        <v>11.12652352036094</v>
+        <v>11.12652165265694</v>
       </c>
       <c r="E537" t="n">
-        <v>11.18775448810609</v>
+        <v>11.18775261012382</v>
       </c>
       <c r="F537" t="n">
         <v>2536971</v>
@@ -11172,16 +11172,16 @@
         <v>45013</v>
       </c>
       <c r="B538" t="n">
-        <v>11.56388568878174</v>
+        <v>11.56388664245605</v>
       </c>
       <c r="C538" t="n">
-        <v>11.7738196835679</v>
+        <v>11.77382065455549</v>
       </c>
       <c r="D538" t="n">
-        <v>11.31021397124021</v>
+        <v>11.31021490399421</v>
       </c>
       <c r="E538" t="n">
-        <v>11.31021397124021</v>
+        <v>11.31021490399421</v>
       </c>
       <c r="F538" t="n">
         <v>2291643</v>
@@ -11232,16 +11232,16 @@
         <v>45016</v>
       </c>
       <c r="B541" t="n">
-        <v>11.6776008605957</v>
+        <v>11.67759990692139</v>
       </c>
       <c r="C541" t="n">
-        <v>12.14995365807506</v>
+        <v>12.14995266582512</v>
       </c>
       <c r="D541" t="n">
-        <v>11.6601059382319</v>
+        <v>11.66010498598634</v>
       </c>
       <c r="E541" t="n">
-        <v>12.00999680575047</v>
+        <v>12.00999582493039</v>
       </c>
       <c r="F541" t="n">
         <v>2337175</v>
@@ -11412,16 +11412,16 @@
         <v>45030</v>
       </c>
       <c r="B550" t="n">
-        <v>12.52608394622803</v>
+        <v>12.52608489990234</v>
       </c>
       <c r="C550" t="n">
-        <v>12.72727089403942</v>
+        <v>12.72727186303112</v>
       </c>
       <c r="D550" t="n">
-        <v>12.22867704395964</v>
+        <v>12.22867797499086</v>
       </c>
       <c r="E550" t="n">
-        <v>12.42111611067847</v>
+        <v>12.42111705636105</v>
       </c>
       <c r="F550" t="n">
         <v>2806225</v>
@@ -11492,16 +11492,16 @@
         <v>45036</v>
       </c>
       <c r="B554" t="n">
-        <v>11.47641277313232</v>
+        <v>11.47641372680664</v>
       </c>
       <c r="C554" t="n">
-        <v>11.60762088826473</v>
+        <v>11.60762185284227</v>
       </c>
       <c r="D554" t="n">
-        <v>11.24023597618649</v>
+        <v>11.24023691023484</v>
       </c>
       <c r="E554" t="n">
-        <v>11.34520381580472</v>
+        <v>11.34520475857576</v>
       </c>
       <c r="F554" t="n">
         <v>2067718</v>
@@ -11552,16 +11552,16 @@
         <v>45042</v>
       </c>
       <c r="B557" t="n">
-        <v>11.25773143768311</v>
+        <v>11.25773239135742</v>
       </c>
       <c r="C557" t="n">
-        <v>11.49390740377979</v>
+        <v>11.49390837746124</v>
       </c>
       <c r="D557" t="n">
-        <v>11.21399539720453</v>
+        <v>11.21399634717384</v>
       </c>
       <c r="E557" t="n">
-        <v>11.24898355583121</v>
+        <v>11.24898450876447</v>
       </c>
       <c r="F557" t="n">
         <v>2213905</v>
@@ -11612,16 +11612,16 @@
         <v>45048</v>
       </c>
       <c r="B560" t="n">
-        <v>10.1555757522583</v>
+        <v>10.15557479858398</v>
       </c>
       <c r="C560" t="n">
-        <v>10.65416964296346</v>
+        <v>10.65416864246794</v>
       </c>
       <c r="D560" t="n">
-        <v>10.02436678932562</v>
+        <v>10.02436584797267</v>
       </c>
       <c r="E560" t="n">
-        <v>10.5929395234974</v>
+        <v>10.59293852875179</v>
       </c>
       <c r="F560" t="n">
         <v>7078259</v>
@@ -11672,16 +11672,16 @@
         <v>45051</v>
       </c>
       <c r="B563" t="n">
-        <v>9.971882820129395</v>
+        <v>9.971883773803711</v>
       </c>
       <c r="C563" t="n">
-        <v>10.03311378150119</v>
+        <v>10.03311474103141</v>
       </c>
       <c r="D563" t="n">
-        <v>9.490783853114243</v>
+        <v>9.490784760778016</v>
       </c>
       <c r="E563" t="n">
-        <v>9.490783853114243</v>
+        <v>9.490784760778016</v>
       </c>
       <c r="F563" t="n">
         <v>9369095</v>
@@ -27832,19 +27832,39 @@
         <v>46233</v>
       </c>
       <c r="B1371" t="n">
-        <v>3.42</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="C1371" t="n">
-        <v>3.43</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="D1371" t="n">
-        <v>3.32</v>
+        <v>3.319999933242798</v>
       </c>
       <c r="E1371" t="n">
-        <v>3.33</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="F1371" t="n">
         <v>6351000</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1372" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="C1372" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>9078100</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1372"/>
+  <dimension ref="A1:F1373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,16 +492,16 @@
         <v>44231</v>
       </c>
       <c r="B4" t="n">
-        <v>6.886315822601318</v>
+        <v>6.88631534576416</v>
       </c>
       <c r="C4" t="n">
-        <v>7.012284415532206</v>
+        <v>7.012283929972458</v>
       </c>
       <c r="D4" t="n">
-        <v>6.806535091369281</v>
+        <v>6.806534620056473</v>
       </c>
       <c r="E4" t="n">
-        <v>6.91990706854544</v>
+        <v>6.919906589382284</v>
       </c>
       <c r="F4" t="n">
         <v>3650229</v>
@@ -532,16 +532,16 @@
         <v>44235</v>
       </c>
       <c r="B6" t="n">
-        <v>7.211735725402832</v>
+        <v>7.211735248565674</v>
       </c>
       <c r="C6" t="n">
-        <v>7.619035766065515</v>
+        <v>7.619035262297836</v>
       </c>
       <c r="D6" t="n">
-        <v>6.827529615229921</v>
+        <v>6.827529163796321</v>
       </c>
       <c r="E6" t="n">
-        <v>6.85482295876889</v>
+        <v>6.854822505530665</v>
       </c>
       <c r="F6" t="n">
         <v>3162478</v>
@@ -572,16 +572,16 @@
         <v>44237</v>
       </c>
       <c r="B8" t="n">
-        <v>6.928305149078369</v>
+        <v>6.928304672241211</v>
       </c>
       <c r="C8" t="n">
-        <v>7.180243149138246</v>
+        <v>7.18024265496158</v>
       </c>
       <c r="D8" t="n">
-        <v>6.74984876127967</v>
+        <v>6.749848296724684</v>
       </c>
       <c r="E8" t="n">
-        <v>7.180243149138246</v>
+        <v>7.18024265496158</v>
       </c>
       <c r="F8" t="n">
         <v>3511567</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029080867767334</v>
+        <v>7.029080390930176</v>
       </c>
       <c r="C10" t="n">
-        <v>7.194940242201317</v>
+        <v>7.194939754112628</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913608771181656</v>
+        <v>6.913608302177867</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949300131730055</v>
+        <v>6.949299660305043</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.22223424911499</v>
+        <v>7.222233772277832</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379695623026483</v>
+        <v>7.379695135793175</v>
       </c>
       <c r="D12" t="n">
-        <v>7.13825490381517</v>
+        <v>7.138254432522623</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287318262017216</v>
+        <v>7.287317780882985</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.306214332580566</v>
+        <v>7.30621337890625</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724011753890583</v>
+        <v>7.724010745681502</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050076073715654</v>
+        <v>7.050075153474859</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054275487425385</v>
+        <v>7.054274566636445</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.306214332580566</v>
+        <v>7.30621337890625</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480471736154864</v>
+        <v>7.480470759734867</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243228809497124</v>
+        <v>7.243227864044258</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308312821743462</v>
+        <v>7.308311867795231</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -732,16 +732,16 @@
         <v>44251</v>
       </c>
       <c r="B16" t="n">
-        <v>7.327207088470459</v>
+        <v>7.327207565307617</v>
       </c>
       <c r="C16" t="n">
-        <v>7.556051129077507</v>
+        <v>7.556051620807289</v>
       </c>
       <c r="D16" t="n">
-        <v>7.108860361756294</v>
+        <v>7.108860824383968</v>
       </c>
       <c r="E16" t="n">
-        <v>7.451077178354241</v>
+        <v>7.451077663252569</v>
       </c>
       <c r="F16" t="n">
         <v>1445414</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253211975098</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400690302893193</v>
+        <v>7.400689314157277</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945101447895325</v>
+        <v>6.945100520026308</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360800341244324</v>
+        <v>7.360799357837727</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -772,16 +772,16 @@
         <v>44253</v>
       </c>
       <c r="B18" t="n">
-        <v>7.243227958679199</v>
+        <v>7.243227481842041</v>
       </c>
       <c r="C18" t="n">
-        <v>7.480470857469459</v>
+        <v>7.480470365014094</v>
       </c>
       <c r="D18" t="n">
-        <v>6.833828601083652</v>
+        <v>6.833828151198126</v>
       </c>
       <c r="E18" t="n">
-        <v>7.157149323379279</v>
+        <v>7.157148852208861</v>
       </c>
       <c r="F18" t="n">
         <v>1865862</v>
@@ -792,16 +792,16 @@
         <v>44256</v>
       </c>
       <c r="B19" t="n">
-        <v>7.001787185668945</v>
+        <v>7.001787662506104</v>
       </c>
       <c r="C19" t="n">
-        <v>7.390191907873347</v>
+        <v>7.390192411161723</v>
       </c>
       <c r="D19" t="n">
-        <v>7.001787185668945</v>
+        <v>7.001787662506104</v>
       </c>
       <c r="E19" t="n">
-        <v>7.249526585020872</v>
+        <v>7.24952707872963</v>
       </c>
       <c r="F19" t="n">
         <v>1349729</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253211975098</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233502264944</v>
+        <v>7.222232537370945</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966096890895136</v>
+        <v>6.966095960221117</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117259534444174</v>
+        <v>7.117258583574751</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -872,16 +872,16 @@
         <v>44260</v>
       </c>
       <c r="B23" t="n">
-        <v>7.016484260559082</v>
+        <v>7.016483783721924</v>
       </c>
       <c r="C23" t="n">
-        <v>7.176045732845249</v>
+        <v>7.176045245164364</v>
       </c>
       <c r="D23" t="n">
-        <v>7.014384147975241</v>
+        <v>7.014383671280806</v>
       </c>
       <c r="E23" t="n">
-        <v>7.11725962818392</v>
+        <v>7.117259144498113</v>
       </c>
       <c r="F23" t="n">
         <v>1309995</v>
@@ -912,16 +912,16 @@
         <v>44264</v>
       </c>
       <c r="B25" t="n">
-        <v>6.42442798614502</v>
+        <v>6.424428462982178</v>
       </c>
       <c r="C25" t="n">
-        <v>6.819131399595795</v>
+        <v>6.819131905728831</v>
       </c>
       <c r="D25" t="n">
-        <v>6.367742000113356</v>
+        <v>6.36774247274314</v>
       </c>
       <c r="E25" t="n">
-        <v>6.754047399508202</v>
+        <v>6.75404790081054</v>
       </c>
       <c r="F25" t="n">
         <v>2514170</v>
@@ -932,16 +932,16 @@
         <v>44265</v>
       </c>
       <c r="B26" t="n">
-        <v>6.252270698547363</v>
+        <v>6.252270221710205</v>
       </c>
       <c r="C26" t="n">
-        <v>6.592387447038047</v>
+        <v>6.592386944261464</v>
       </c>
       <c r="D26" t="n">
-        <v>6.124201991216056</v>
+        <v>6.124201524146216</v>
       </c>
       <c r="E26" t="n">
-        <v>6.58608954496226</v>
+        <v>6.586089042665994</v>
       </c>
       <c r="F26" t="n">
         <v>1291345</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033279895782471</v>
+        <v>7.033280372619629</v>
       </c>
       <c r="C29" t="n">
-        <v>7.127756543943293</v>
+        <v>7.12775702718571</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1012,16 +1012,16 @@
         <v>44271</v>
       </c>
       <c r="B30" t="n">
-        <v>7.390192031860352</v>
+        <v>7.390191555023193</v>
       </c>
       <c r="C30" t="n">
-        <v>7.42588420308686</v>
+        <v>7.425883723946737</v>
       </c>
       <c r="D30" t="n">
-        <v>6.970294545149255</v>
+        <v>6.970294095405131</v>
       </c>
       <c r="E30" t="n">
-        <v>6.970294545149255</v>
+        <v>6.970294095405131</v>
       </c>
       <c r="F30" t="n">
         <v>4282725</v>
@@ -1032,16 +1032,16 @@
         <v>44272</v>
       </c>
       <c r="B31" t="n">
-        <v>7.558151245117188</v>
+        <v>7.558150768280029</v>
       </c>
       <c r="C31" t="n">
-        <v>7.642130577117119</v>
+        <v>7.642130094981778</v>
       </c>
       <c r="D31" t="n">
-        <v>7.285217807271516</v>
+        <v>7.285217347653489</v>
       </c>
       <c r="E31" t="n">
-        <v>7.390191769322798</v>
+        <v>7.390191303082056</v>
       </c>
       <c r="F31" t="n">
         <v>5070506</v>
@@ -1052,16 +1052,16 @@
         <v>44273</v>
       </c>
       <c r="B32" t="n">
-        <v>7.589643478393555</v>
+        <v>7.589643001556396</v>
       </c>
       <c r="C32" t="n">
-        <v>7.89826828612256</v>
+        <v>7.898267789895324</v>
       </c>
       <c r="D32" t="n">
-        <v>7.459475468261102</v>
+        <v>7.459474999602055</v>
       </c>
       <c r="E32" t="n">
-        <v>7.600140793817841</v>
+        <v>7.600140316321165</v>
       </c>
       <c r="F32" t="n">
         <v>3661176</v>
@@ -1092,16 +1092,16 @@
         <v>44277</v>
       </c>
       <c r="B34" t="n">
-        <v>7.558151245117188</v>
+        <v>7.558150768280029</v>
       </c>
       <c r="C34" t="n">
-        <v>7.807989940470752</v>
+        <v>7.807989447871488</v>
       </c>
       <c r="D34" t="n">
-        <v>7.201238475271585</v>
+        <v>7.201238020951741</v>
       </c>
       <c r="E34" t="n">
-        <v>7.514061872573729</v>
+        <v>7.51406139851813</v>
       </c>
       <c r="F34" t="n">
         <v>5377429</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159248352050781</v>
+        <v>7.159247875213623</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656827250339138</v>
+        <v>7.656826740361056</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159248352050781</v>
+        <v>7.159247875213623</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392291828769327</v>
+        <v>7.392291336410457</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.705114364624023</v>
+        <v>7.70511531829834</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789094507299701</v>
+        <v>7.789095471368375</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033279717574721</v>
+        <v>7.033280588094989</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159248307999206</v>
+        <v>7.159249194110809</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.51826000213623</v>
+        <v>7.518260955810547</v>
       </c>
       <c r="C38" t="n">
-        <v>7.789094122342303</v>
+        <v>7.789095110371317</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455275304139598</v>
+        <v>7.455276249824448</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721910823316651</v>
+        <v>7.721911802823614</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253211975098</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379694859893382</v>
+        <v>7.379693873962468</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138254165649414</v>
+        <v>7.138253211975098</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257924862390593</v>
+        <v>7.257923892728211</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1272,16 +1272,16 @@
         <v>44291</v>
       </c>
       <c r="B43" t="n">
-        <v>7.327207088470459</v>
+        <v>7.327207565307617</v>
       </c>
       <c r="C43" t="n">
-        <v>7.400689097515077</v>
+        <v>7.400689579134269</v>
       </c>
       <c r="D43" t="n">
-        <v>7.260022980684908</v>
+        <v>7.260023453149884</v>
       </c>
       <c r="E43" t="n">
-        <v>7.400689097515077</v>
+        <v>7.400689579134269</v>
       </c>
       <c r="F43" t="n">
         <v>1080107</v>
@@ -1292,16 +1292,16 @@
         <v>44292</v>
       </c>
       <c r="B44" t="n">
-        <v>7.211735725402832</v>
+        <v>7.211735248565674</v>
       </c>
       <c r="C44" t="n">
-        <v>7.379694387891328</v>
+        <v>7.379693899948808</v>
       </c>
       <c r="D44" t="n">
-        <v>7.190741095540401</v>
+        <v>7.190740620091399</v>
       </c>
       <c r="E44" t="n">
-        <v>7.369197072960112</v>
+        <v>7.36919658571167</v>
       </c>
       <c r="F44" t="n">
         <v>1319726</v>
@@ -1312,16 +1312,16 @@
         <v>44293</v>
       </c>
       <c r="B45" t="n">
-        <v>7.243227958679199</v>
+        <v>7.243227481842041</v>
       </c>
       <c r="C45" t="n">
-        <v>7.388092696447584</v>
+        <v>7.388092210073672</v>
       </c>
       <c r="D45" t="n">
-        <v>7.146652008029977</v>
+        <v>7.146651537550619</v>
       </c>
       <c r="E45" t="n">
-        <v>7.213835313342242</v>
+        <v>7.213834838440065</v>
       </c>
       <c r="F45" t="n">
         <v>1401221</v>
@@ -1332,16 +1332,16 @@
         <v>44294</v>
       </c>
       <c r="B46" t="n">
-        <v>7.589643478393555</v>
+        <v>7.589643001556396</v>
       </c>
       <c r="C46" t="n">
-        <v>7.789094906838682</v>
+        <v>7.78909441747052</v>
       </c>
       <c r="D46" t="n">
-        <v>7.215935477392881</v>
+        <v>7.215935024034804</v>
       </c>
       <c r="E46" t="n">
-        <v>7.243228010419292</v>
+        <v>7.2432275553465</v>
       </c>
       <c r="F46" t="n">
         <v>2111967</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652628898620605</v>
+        <v>7.652627944946289</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873074978536558</v>
+        <v>7.873073997390144</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474172084329807</v>
+        <v>7.474171152894864</v>
       </c>
       <c r="E47" t="n">
-        <v>7.59594290294987</v>
+        <v>7.595941956339789</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1392,16 +1392,16 @@
         <v>44299</v>
       </c>
       <c r="B49" t="n">
-        <v>7.726109504699707</v>
+        <v>7.726110458374023</v>
       </c>
       <c r="C49" t="n">
-        <v>7.898267572775072</v>
+        <v>7.898268547699764</v>
       </c>
       <c r="D49" t="n">
-        <v>7.64213017709561</v>
+        <v>7.642131120403916</v>
       </c>
       <c r="E49" t="n">
-        <v>7.786994902815057</v>
+        <v>7.786995864004779</v>
       </c>
       <c r="F49" t="n">
         <v>1044023</v>
@@ -1412,16 +1412,16 @@
         <v>44300</v>
       </c>
       <c r="B50" t="n">
-        <v>7.877273082733154</v>
+        <v>7.877274036407471</v>
       </c>
       <c r="C50" t="n">
-        <v>7.877273082733154</v>
+        <v>7.877274036407471</v>
       </c>
       <c r="D50" t="n">
-        <v>7.518260212908098</v>
+        <v>7.518261123117962</v>
       </c>
       <c r="E50" t="n">
-        <v>7.78699504013355</v>
+        <v>7.786995982878214</v>
       </c>
       <c r="F50" t="n">
         <v>2026013</v>
@@ -1452,16 +1452,16 @@
         <v>44302</v>
       </c>
       <c r="B52" t="n">
-        <v>8.187996864318848</v>
+        <v>8.187995910644531</v>
       </c>
       <c r="C52" t="n">
-        <v>8.25098237977971</v>
+        <v>8.25098141876933</v>
       </c>
       <c r="D52" t="n">
-        <v>8.09142091401317</v>
+        <v>8.091419971587269</v>
       </c>
       <c r="E52" t="n">
-        <v>8.112415544637091</v>
+        <v>8.1124145997659</v>
       </c>
       <c r="F52" t="n">
         <v>1067133</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208992004394531</v>
+        <v>8.208991050720215</v>
       </c>
       <c r="C53" t="n">
-        <v>8.24468336574694</v>
+        <v>8.244682407926204</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059929468278197</v>
+        <v>8.059928531921125</v>
       </c>
       <c r="E53" t="n">
-        <v>8.187997372467679</v>
+        <v>8.1879964212324</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1492,16 +1492,16 @@
         <v>44306</v>
       </c>
       <c r="B54" t="n">
-        <v>8.196395874023438</v>
+        <v>8.196394920349121</v>
       </c>
       <c r="C54" t="n">
-        <v>8.244683038461606</v>
+        <v>8.244682079168939</v>
       </c>
       <c r="D54" t="n">
-        <v>8.078823666875394</v>
+        <v>8.078822726880942</v>
       </c>
       <c r="E54" t="n">
-        <v>8.206893189570158</v>
+        <v>8.206892234674447</v>
       </c>
       <c r="F54" t="n">
         <v>282595</v>
@@ -1512,16 +1512,16 @@
         <v>44308</v>
       </c>
       <c r="B55" t="n">
-        <v>8.183797836303711</v>
+        <v>8.183796882629395</v>
       </c>
       <c r="C55" t="n">
-        <v>8.370652636858729</v>
+        <v>8.37065166140985</v>
       </c>
       <c r="D55" t="n">
-        <v>8.06412714911432</v>
+        <v>8.064126209385469</v>
       </c>
       <c r="E55" t="n">
-        <v>8.259379152045536</v>
+        <v>8.259378189563577</v>
       </c>
       <c r="F55" t="n">
         <v>608979</v>
@@ -1532,16 +1532,16 @@
         <v>44309</v>
       </c>
       <c r="B56" t="n">
-        <v>8.187996864318848</v>
+        <v>8.187995910644531</v>
       </c>
       <c r="C56" t="n">
-        <v>8.219489622049279</v>
+        <v>8.21948866470693</v>
       </c>
       <c r="D56" t="n">
-        <v>7.923461433638152</v>
+        <v>7.923460510774868</v>
       </c>
       <c r="E56" t="n">
-        <v>8.215291020642315</v>
+        <v>8.215290063788986</v>
       </c>
       <c r="F56" t="n">
         <v>1129166</v>
@@ -1572,16 +1572,16 @@
         <v>44313</v>
       </c>
       <c r="B58" t="n">
-        <v>8.11661434173584</v>
+        <v>8.116615295410156</v>
       </c>
       <c r="C58" t="n">
-        <v>8.183797641709477</v>
+        <v>8.1837986032776</v>
       </c>
       <c r="D58" t="n">
-        <v>7.940257671933487</v>
+        <v>7.9402586048865</v>
       </c>
       <c r="E58" t="n">
-        <v>7.999042957936108</v>
+        <v>7.999043897796192</v>
       </c>
       <c r="F58" t="n">
         <v>2786224</v>
@@ -1612,16 +1612,16 @@
         <v>44315</v>
       </c>
       <c r="B60" t="n">
-        <v>8.607894897460938</v>
+        <v>8.607893943786621</v>
       </c>
       <c r="C60" t="n">
-        <v>8.815744351658321</v>
+        <v>8.815743374956226</v>
       </c>
       <c r="D60" t="n">
-        <v>8.167002755425871</v>
+        <v>8.167001850598284</v>
       </c>
       <c r="E60" t="n">
-        <v>8.469328865260882</v>
+        <v>8.469327926938387</v>
       </c>
       <c r="F60" t="n">
         <v>3250459</v>
@@ -1672,16 +1672,16 @@
         <v>44320</v>
       </c>
       <c r="B63" t="n">
-        <v>9.298624038696289</v>
+        <v>9.298624992370605</v>
       </c>
       <c r="C63" t="n">
-        <v>9.54426492153458</v>
+        <v>9.544265900402022</v>
       </c>
       <c r="D63" t="n">
-        <v>8.71916597157877</v>
+        <v>8.719166865823404</v>
       </c>
       <c r="E63" t="n">
-        <v>8.849333964571231</v>
+        <v>8.849334872165999</v>
       </c>
       <c r="F63" t="n">
         <v>2875017</v>
@@ -1712,16 +1712,16 @@
         <v>44322</v>
       </c>
       <c r="B65" t="n">
-        <v>9.764713287353516</v>
+        <v>9.764711380004883</v>
       </c>
       <c r="C65" t="n">
-        <v>9.78360780771288</v>
+        <v>9.783605896673567</v>
       </c>
       <c r="D65" t="n">
-        <v>9.537967677916114</v>
+        <v>9.537965814857868</v>
       </c>
       <c r="E65" t="n">
-        <v>9.78360780771288</v>
+        <v>9.783605896673567</v>
       </c>
       <c r="F65" t="n">
         <v>8042425</v>
@@ -1792,16 +1792,16 @@
         <v>44328</v>
       </c>
       <c r="B69" t="n">
-        <v>9.531668663024902</v>
+        <v>9.531667709350586</v>
       </c>
       <c r="C69" t="n">
-        <v>9.743716705677796</v>
+        <v>9.743715730787388</v>
       </c>
       <c r="D69" t="n">
-        <v>9.321719921078722</v>
+        <v>9.321718988410458</v>
       </c>
       <c r="E69" t="n">
-        <v>9.563160609009282</v>
+        <v>9.563159652184094</v>
       </c>
       <c r="F69" t="n">
         <v>1563804</v>
@@ -1812,16 +1812,16 @@
         <v>44329</v>
       </c>
       <c r="B70" t="n">
-        <v>9.655539512634277</v>
+        <v>9.655538558959961</v>
       </c>
       <c r="C70" t="n">
-        <v>9.699628889839794</v>
+        <v>9.699627931810785</v>
       </c>
       <c r="D70" t="n">
-        <v>9.489680131742498</v>
+        <v>9.489679194450057</v>
       </c>
       <c r="E70" t="n">
-        <v>9.556863442087572</v>
+        <v>9.556862498159457</v>
       </c>
       <c r="F70" t="n">
         <v>2493897</v>
@@ -1852,16 +1852,16 @@
         <v>44333</v>
       </c>
       <c r="B72" t="n">
-        <v>9.657638549804688</v>
+        <v>9.657637596130371</v>
       </c>
       <c r="C72" t="n">
-        <v>9.773109835938806</v>
+        <v>9.773108870861909</v>
       </c>
       <c r="D72" t="n">
-        <v>9.36161115804209</v>
+        <v>9.361610233599944</v>
       </c>
       <c r="E72" t="n">
-        <v>9.613549173803014</v>
+        <v>9.613548224482443</v>
       </c>
       <c r="F72" t="n">
         <v>1884107</v>
@@ -1872,16 +1872,16 @@
         <v>44334</v>
       </c>
       <c r="B73" t="n">
-        <v>9.657638549804688</v>
+        <v>9.657637596130371</v>
       </c>
       <c r="C73" t="n">
-        <v>9.666036564842845</v>
+        <v>9.66603561033924</v>
       </c>
       <c r="D73" t="n">
-        <v>9.458187113289004</v>
+        <v>9.458186179310156</v>
       </c>
       <c r="E73" t="n">
-        <v>9.655539248993795</v>
+        <v>9.655538295526782</v>
       </c>
       <c r="F73" t="n">
         <v>1385003</v>
@@ -1952,16 +1952,16 @@
         <v>44340</v>
       </c>
       <c r="B77" t="n">
-        <v>10.18250942230225</v>
+        <v>10.18250846862793</v>
       </c>
       <c r="C77" t="n">
-        <v>10.39035886155727</v>
+        <v>10.39035788841617</v>
       </c>
       <c r="D77" t="n">
-        <v>9.951566051904743</v>
+        <v>9.951565119860142</v>
       </c>
       <c r="E77" t="n">
-        <v>10.15731537867855</v>
+        <v>10.15731442736386</v>
       </c>
       <c r="F77" t="n">
         <v>3407772</v>
@@ -2012,16 +2012,16 @@
         <v>44343</v>
       </c>
       <c r="B80" t="n">
-        <v>10.65489387512207</v>
+        <v>10.65489482879639</v>
       </c>
       <c r="C80" t="n">
-        <v>10.74937052028797</v>
+        <v>10.74937148241849</v>
       </c>
       <c r="D80" t="n">
-        <v>10.44284503095825</v>
+        <v>10.44284596565298</v>
       </c>
       <c r="E80" t="n">
-        <v>10.49743171745289</v>
+        <v>10.49743265703344</v>
       </c>
       <c r="F80" t="n">
         <v>6818384</v>
@@ -2032,16 +2032,16 @@
         <v>44344</v>
       </c>
       <c r="B81" t="n">
-        <v>10.72837734222412</v>
+        <v>10.72837543487549</v>
       </c>
       <c r="C81" t="n">
-        <v>10.82915271463439</v>
+        <v>10.82915078936937</v>
       </c>
       <c r="D81" t="n">
-        <v>10.46804048995072</v>
+        <v>10.46803862888618</v>
       </c>
       <c r="E81" t="n">
-        <v>10.65489531675402</v>
+        <v>10.65489342246942</v>
       </c>
       <c r="F81" t="n">
         <v>2512953</v>
@@ -2092,16 +2092,16 @@
         <v>44349</v>
       </c>
       <c r="B84" t="n">
-        <v>10.91522979736328</v>
+        <v>10.9152307510376</v>
       </c>
       <c r="C84" t="n">
-        <v>11.25114711619596</v>
+        <v>11.25114809921971</v>
       </c>
       <c r="D84" t="n">
-        <v>10.79765841105404</v>
+        <v>10.79765935445603</v>
       </c>
       <c r="E84" t="n">
-        <v>11.25114711619596</v>
+        <v>11.25114809921971</v>
       </c>
       <c r="F84" t="n">
         <v>2442811</v>
@@ -2152,16 +2152,16 @@
         <v>44355</v>
       </c>
       <c r="B87" t="n">
-        <v>11.0202054977417</v>
+        <v>11.02020454406738</v>
       </c>
       <c r="C87" t="n">
-        <v>11.16926884083993</v>
+        <v>11.16926787426587</v>
       </c>
       <c r="D87" t="n">
-        <v>10.93412604839051</v>
+        <v>10.9341251021654</v>
       </c>
       <c r="E87" t="n">
-        <v>11.1209800524548</v>
+        <v>11.12097909005958</v>
       </c>
       <c r="F87" t="n">
         <v>1135248</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462299346924</v>
+        <v>10.94462203979492</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192304724218</v>
+        <v>11.35192205807723</v>
       </c>
       <c r="D92" t="n">
-        <v>10.81445498526105</v>
+        <v>10.8144540429291</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152825044157</v>
+        <v>10.92152729877964</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2292,16 +2292,16 @@
         <v>44364</v>
       </c>
       <c r="B94" t="n">
-        <v>11.30573463439941</v>
+        <v>11.3057336807251</v>
       </c>
       <c r="C94" t="n">
-        <v>11.52408220658267</v>
+        <v>11.52408123449005</v>
       </c>
       <c r="D94" t="n">
-        <v>11.07689055849889</v>
+        <v>11.0768896241283</v>
       </c>
       <c r="E94" t="n">
-        <v>11.21125798299837</v>
+        <v>11.21125703729346</v>
       </c>
       <c r="F94" t="n">
         <v>2709189</v>
@@ -2352,16 +2352,16 @@
         <v>44369</v>
       </c>
       <c r="B97" t="n">
-        <v>11.28473949432373</v>
+        <v>11.28473854064941</v>
       </c>
       <c r="C97" t="n">
-        <v>11.42330632585396</v>
+        <v>11.42330536046935</v>
       </c>
       <c r="D97" t="n">
-        <v>11.16297031516165</v>
+        <v>11.16296937177805</v>
       </c>
       <c r="E97" t="n">
-        <v>11.23855163287302</v>
+        <v>11.23855068310205</v>
       </c>
       <c r="F97" t="n">
         <v>1033076</v>
@@ -2372,16 +2372,16 @@
         <v>44370</v>
       </c>
       <c r="B98" t="n">
-        <v>11.50308799743652</v>
+        <v>11.50308704376221</v>
       </c>
       <c r="C98" t="n">
-        <v>11.7487273000881</v>
+        <v>11.74872632604882</v>
       </c>
       <c r="D98" t="n">
-        <v>11.30573504903898</v>
+        <v>11.3057341117264</v>
       </c>
       <c r="E98" t="n">
-        <v>11.42120714749321</v>
+        <v>11.4212062006073</v>
       </c>
       <c r="F98" t="n">
         <v>4341920</v>
@@ -2432,16 +2432,16 @@
         <v>44375</v>
       </c>
       <c r="B101" t="n">
-        <v>11.86209869384766</v>
+        <v>11.86209774017334</v>
       </c>
       <c r="C101" t="n">
-        <v>12.00066471799965</v>
+        <v>12.00066375318507</v>
       </c>
       <c r="D101" t="n">
-        <v>11.40441135990023</v>
+        <v>11.40441044302249</v>
       </c>
       <c r="E101" t="n">
-        <v>11.58916605876955</v>
+        <v>11.58916512703814</v>
       </c>
       <c r="F101" t="n">
         <v>1601511</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.0174617767334</v>
+        <v>12.01746082305908</v>
       </c>
       <c r="C102" t="n">
-        <v>12.0174617767334</v>
+        <v>12.01746082305908</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916626863832</v>
+        <v>11.58916534895242</v>
       </c>
       <c r="E102" t="n">
-        <v>11.8599996079053</v>
+        <v>11.85999866672677</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2512,16 +2512,16 @@
         <v>44379</v>
       </c>
       <c r="B105" t="n">
-        <v>12.95803165435791</v>
+        <v>12.95803070068359</v>
       </c>
       <c r="C105" t="n">
-        <v>13.12809044392446</v>
+        <v>13.1280894777343</v>
       </c>
       <c r="D105" t="n">
-        <v>12.50034348842697</v>
+        <v>12.5003425684372</v>
       </c>
       <c r="E105" t="n">
-        <v>12.52133812009879</v>
+        <v>12.52133719856387</v>
       </c>
       <c r="F105" t="n">
         <v>2908669</v>
@@ -2552,16 +2552,16 @@
         <v>44383</v>
       </c>
       <c r="B107" t="n">
-        <v>13.04830932617188</v>
+        <v>13.04830837249756</v>
       </c>
       <c r="C107" t="n">
-        <v>13.36113192669314</v>
+        <v>13.36113095015526</v>
       </c>
       <c r="D107" t="n">
-        <v>13.00002053822385</v>
+        <v>13.00001958807886</v>
       </c>
       <c r="E107" t="n">
-        <v>13.14908469176732</v>
+        <v>13.14908373072754</v>
       </c>
       <c r="F107" t="n">
         <v>1738957</v>
@@ -2612,16 +2612,16 @@
         <v>44389</v>
       </c>
       <c r="B110" t="n">
-        <v>13.33173942565918</v>
+        <v>13.3317403793335</v>
       </c>
       <c r="C110" t="n">
-        <v>13.79572545725768</v>
+        <v>13.79572644412283</v>
       </c>
       <c r="D110" t="n">
-        <v>13.07140260401543</v>
+        <v>13.07140353906678</v>
       </c>
       <c r="E110" t="n">
-        <v>13.19107329393574</v>
+        <v>13.19107423754762</v>
       </c>
       <c r="F110" t="n">
         <v>8663568</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103643972576</v>
+        <v>14.16103739980534</v>
       </c>
       <c r="D116" t="n">
-        <v>13.77473102080758</v>
+        <v>13.7747319546967</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059038615415</v>
+        <v>13.94059133128809</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2752,16 +2752,16 @@
         <v>44398</v>
       </c>
       <c r="B117" t="n">
-        <v>14.3184986114502</v>
+        <v>14.31849765777588</v>
       </c>
       <c r="C117" t="n">
-        <v>14.34789044445824</v>
+        <v>14.3478894888263</v>
       </c>
       <c r="D117" t="n">
-        <v>14.01617171355511</v>
+        <v>14.01617078001709</v>
       </c>
       <c r="E117" t="n">
-        <v>14.06865910114192</v>
+        <v>14.06865816410801</v>
       </c>
       <c r="F117" t="n">
         <v>2316312</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.99873352050781</v>
+        <v>14.99873447418213</v>
       </c>
       <c r="C118" t="n">
-        <v>15.0113309493248</v>
+        <v>15.01133190380011</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36048923001167</v>
+        <v>14.36049014310408</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36048923001167</v>
+        <v>14.36049014310408</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801414489746</v>
+        <v>15.06801605224609</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127770885214</v>
+        <v>15.22127963560127</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92944893307399</v>
+        <v>14.92945082288267</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127770885214</v>
+        <v>15.22127963560127</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2812,16 +2812,16 @@
         <v>44403</v>
       </c>
       <c r="B120" t="n">
-        <v>14.87486267089844</v>
+        <v>14.87486171722412</v>
       </c>
       <c r="C120" t="n">
-        <v>15.17089005658931</v>
+        <v>15.17088908393575</v>
       </c>
       <c r="D120" t="n">
-        <v>14.64601940413482</v>
+        <v>14.64601846513237</v>
       </c>
       <c r="E120" t="n">
-        <v>15.07431410332324</v>
+        <v>15.07431313686146</v>
       </c>
       <c r="F120" t="n">
         <v>4655330</v>
@@ -2872,16 +2872,16 @@
         <v>44406</v>
       </c>
       <c r="B123" t="n">
-        <v>15.28426170349121</v>
+        <v>15.28425884246826</v>
       </c>
       <c r="C123" t="n">
-        <v>15.32415166438117</v>
+        <v>15.32414879589132</v>
       </c>
       <c r="D123" t="n">
-        <v>14.85386771299919</v>
+        <v>14.85386493254062</v>
       </c>
       <c r="E123" t="n">
-        <v>15.09950700409309</v>
+        <v>15.09950417765391</v>
       </c>
       <c r="F123" t="n">
         <v>6067903</v>
@@ -2952,16 +2952,16 @@
         <v>44412</v>
       </c>
       <c r="B127" t="n">
-        <v>14.73839473724365</v>
+        <v>14.73839569091797</v>
       </c>
       <c r="C127" t="n">
-        <v>15.32205228991032</v>
+        <v>15.32205328135125</v>
       </c>
       <c r="D127" t="n">
-        <v>14.73839473724365</v>
+        <v>14.73839569091797</v>
       </c>
       <c r="E127" t="n">
-        <v>15.18768567924637</v>
+        <v>15.18768666199287</v>
       </c>
       <c r="F127" t="n">
         <v>2159810</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.93639183044434</v>
+        <v>13.93639087677002</v>
       </c>
       <c r="C129" t="n">
-        <v>14.41927319977593</v>
+        <v>14.4192722130578</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373643553897</v>
+        <v>13.75373549436386</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153461307515</v>
+        <v>14.17153364330989</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893713905431</v>
+        <v>14.15893809899156</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462098074336</v>
+        <v>13.81462191733692</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351631037553</v>
+        <v>13.83351724825013</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3072,16 +3072,16 @@
         <v>44420</v>
       </c>
       <c r="B133" t="n">
-        <v>13.68025398254395</v>
+        <v>13.68025493621826</v>
       </c>
       <c r="C133" t="n">
-        <v>14.21142412135836</v>
+        <v>14.21142511206147</v>
       </c>
       <c r="D133" t="n">
-        <v>13.64666192558043</v>
+        <v>13.64666287691298</v>
       </c>
       <c r="E133" t="n">
-        <v>13.82511871345597</v>
+        <v>13.82511967722906</v>
       </c>
       <c r="F133" t="n">
         <v>1819641</v>
@@ -3172,16 +3172,16 @@
         <v>44427</v>
       </c>
       <c r="B138" t="n">
-        <v>13.08400058746338</v>
+        <v>13.08399963378906</v>
       </c>
       <c r="C138" t="n">
-        <v>13.26875528769718</v>
+        <v>13.26875432055636</v>
       </c>
       <c r="D138" t="n">
-        <v>11.91668547123142</v>
+        <v>11.91668460264106</v>
       </c>
       <c r="E138" t="n">
-        <v>12.41216428069283</v>
+        <v>12.41216337598772</v>
       </c>
       <c r="F138" t="n">
         <v>2072031</v>
@@ -3192,16 +3192,16 @@
         <v>44428</v>
       </c>
       <c r="B139" t="n">
-        <v>13.52069187164307</v>
+        <v>13.52069282531738</v>
       </c>
       <c r="C139" t="n">
-        <v>13.70544655244245</v>
+        <v>13.70544751914833</v>
       </c>
       <c r="D139" t="n">
-        <v>12.64730573886667</v>
+        <v>12.6473066309372</v>
       </c>
       <c r="E139" t="n">
-        <v>12.80686637815856</v>
+        <v>12.8068672814836</v>
       </c>
       <c r="F139" t="n">
         <v>3576438</v>
@@ -3272,16 +3272,16 @@
         <v>44434</v>
       </c>
       <c r="B143" t="n">
-        <v>13.12599086761475</v>
+        <v>13.12598991394043</v>
       </c>
       <c r="C143" t="n">
-        <v>13.76423435323049</v>
+        <v>13.76423335318433</v>
       </c>
       <c r="D143" t="n">
-        <v>12.82366474965109</v>
+        <v>12.82366381794241</v>
       </c>
       <c r="E143" t="n">
-        <v>13.47870507780299</v>
+        <v>13.47870409850207</v>
       </c>
       <c r="F143" t="n">
         <v>2624147</v>
@@ -3312,16 +3312,16 @@
         <v>44438</v>
       </c>
       <c r="B145" t="n">
-        <v>13.34433555603027</v>
+        <v>13.34433650970459</v>
       </c>
       <c r="C145" t="n">
-        <v>14.09175231274281</v>
+        <v>14.09175331983246</v>
       </c>
       <c r="D145" t="n">
-        <v>13.24356019914138</v>
+        <v>13.24356114561362</v>
       </c>
       <c r="E145" t="n">
-        <v>13.68865088518722</v>
+        <v>13.68865186346858</v>
       </c>
       <c r="F145" t="n">
         <v>1186841</v>
@@ -3432,16 +3432,16 @@
         <v>44447</v>
       </c>
       <c r="B151" t="n">
-        <v>13.23516273498535</v>
+        <v>13.23516178131104</v>
       </c>
       <c r="C151" t="n">
-        <v>14.67960903587777</v>
+        <v>14.67960797812228</v>
       </c>
       <c r="D151" t="n">
-        <v>13.10079531628589</v>
+        <v>13.10079437229357</v>
       </c>
       <c r="E151" t="n">
-        <v>13.80622203202309</v>
+        <v>13.80622103720047</v>
       </c>
       <c r="F151" t="n">
         <v>4568970</v>
@@ -3452,16 +3452,16 @@
         <v>44448</v>
       </c>
       <c r="B152" t="n">
-        <v>13.12599086761475</v>
+        <v>13.12598991394043</v>
       </c>
       <c r="C152" t="n">
-        <v>13.37792970514844</v>
+        <v>13.3779287331694</v>
       </c>
       <c r="D152" t="n">
-        <v>12.5297366470582</v>
+        <v>12.52973573670498</v>
       </c>
       <c r="E152" t="n">
-        <v>13.21836822489853</v>
+        <v>13.2183672645125</v>
       </c>
       <c r="F152" t="n">
         <v>3739731</v>
@@ -3472,16 +3472,16 @@
         <v>44449</v>
       </c>
       <c r="B153" t="n">
-        <v>13.08400058746338</v>
+        <v>13.08399963378906</v>
       </c>
       <c r="C153" t="n">
-        <v>13.77263211187781</v>
+        <v>13.77263110801012</v>
       </c>
       <c r="D153" t="n">
-        <v>13.00841845499036</v>
+        <v>13.00841750682512</v>
       </c>
       <c r="E153" t="n">
-        <v>13.77263211187781</v>
+        <v>13.77263110801012</v>
       </c>
       <c r="F153" t="n">
         <v>2018917</v>
@@ -3512,16 +3512,16 @@
         <v>44453</v>
       </c>
       <c r="B155" t="n">
-        <v>13.55428600311279</v>
+        <v>13.55428504943848</v>
       </c>
       <c r="C155" t="n">
-        <v>14.04976483634768</v>
+        <v>14.04976384781166</v>
       </c>
       <c r="D155" t="n">
-        <v>13.27715393946506</v>
+        <v>13.27715300528965</v>
       </c>
       <c r="E155" t="n">
-        <v>13.43671460319705</v>
+        <v>13.43671365779501</v>
       </c>
       <c r="F155" t="n">
         <v>1943200</v>
@@ -3552,16 +3552,16 @@
         <v>44455</v>
       </c>
       <c r="B157" t="n">
-        <v>13.56268215179443</v>
+        <v>13.56268310546875</v>
       </c>
       <c r="C157" t="n">
-        <v>13.78942690530008</v>
+        <v>13.78942787491819</v>
       </c>
       <c r="D157" t="n">
-        <v>13.33593739828879</v>
+        <v>13.33593833601931</v>
       </c>
       <c r="E157" t="n">
-        <v>13.47870282392425</v>
+        <v>13.47870377169347</v>
       </c>
       <c r="F157" t="n">
         <v>1227183</v>
@@ -3612,16 +3612,16 @@
         <v>44460</v>
       </c>
       <c r="B160" t="n">
-        <v>13.52069187164307</v>
+        <v>13.52069282531738</v>
       </c>
       <c r="C160" t="n">
-        <v>13.64666126738609</v>
+        <v>13.64666222994559</v>
       </c>
       <c r="D160" t="n">
-        <v>12.80686637815856</v>
+        <v>12.8068672814836</v>
       </c>
       <c r="E160" t="n">
-        <v>12.98322385691658</v>
+        <v>12.9832247726809</v>
       </c>
       <c r="F160" t="n">
         <v>1911981</v>
@@ -3632,16 +3632,16 @@
         <v>44461</v>
       </c>
       <c r="B161" t="n">
-        <v>14.10015106201172</v>
+        <v>14.10015201568604</v>
       </c>
       <c r="C161" t="n">
-        <v>14.46126322911574</v>
+        <v>14.46126420721415</v>
       </c>
       <c r="D161" t="n">
-        <v>13.58787626629261</v>
+        <v>13.58787718531884</v>
       </c>
       <c r="E161" t="n">
-        <v>13.71384566466818</v>
+        <v>13.71384659221444</v>
       </c>
       <c r="F161" t="n">
         <v>3751489</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.61242866516113</v>
+        <v>14.6124267578125</v>
       </c>
       <c r="C162" t="n">
-        <v>15.1163047318822</v>
+        <v>15.11630275876303</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893906859966</v>
+        <v>14.15893722044467</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19253113109893</v>
+        <v>14.19252927855919</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3692,16 +3692,16 @@
         <v>44466</v>
       </c>
       <c r="B164" t="n">
-        <v>13.77263164520264</v>
+        <v>13.77263069152832</v>
       </c>
       <c r="C164" t="n">
-        <v>13.99097677332576</v>
+        <v>13.99097580453232</v>
       </c>
       <c r="D164" t="n">
-        <v>13.51229563311167</v>
+        <v>13.5122946974641</v>
       </c>
       <c r="E164" t="n">
-        <v>13.8650089921894</v>
+        <v>13.86500803211849</v>
       </c>
       <c r="F164" t="n">
         <v>2647359</v>
@@ -3752,16 +3752,16 @@
         <v>44469</v>
       </c>
       <c r="B167" t="n">
-        <v>12.55492782592773</v>
+        <v>12.55492877960205</v>
       </c>
       <c r="C167" t="n">
-        <v>13.05880457412719</v>
+        <v>13.05880556607607</v>
       </c>
       <c r="D167" t="n">
-        <v>12.37017315355367</v>
+        <v>12.370174093194</v>
       </c>
       <c r="E167" t="n">
-        <v>13.05880457412719</v>
+        <v>13.05880556607607</v>
       </c>
       <c r="F167" t="n">
         <v>6213762</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498023986816</v>
+        <v>12.34498119354248</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366299139635</v>
+        <v>12.82366398204986</v>
       </c>
       <c r="D169" t="n">
-        <v>12.1350315079744</v>
+        <v>12.13503244542976</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288763255913</v>
+        <v>12.72288861542754</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14343070983887</v>
+        <v>12.14342975616455</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55493019965232</v>
+        <v>12.55492921366123</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027798749311</v>
+        <v>11.95027704898789</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337946226592</v>
+        <v>12.35337849210345</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3852,16 +3852,16 @@
         <v>44476</v>
       </c>
       <c r="B172" t="n">
-        <v>13.00002098083496</v>
+        <v>13.00002002716064</v>
       </c>
       <c r="C172" t="n">
-        <v>13.02521502604024</v>
+        <v>13.02521407051771</v>
       </c>
       <c r="D172" t="n">
-        <v>12.36177670640198</v>
+        <v>12.36177579954892</v>
       </c>
       <c r="E172" t="n">
-        <v>12.56332825624967</v>
+        <v>12.56332733461089</v>
       </c>
       <c r="F172" t="n">
         <v>3555051</v>
@@ -3912,16 +3912,16 @@
         <v>44482</v>
       </c>
       <c r="B175" t="n">
-        <v>13.12599086761475</v>
+        <v>13.12598991394043</v>
       </c>
       <c r="C175" t="n">
-        <v>13.34433764366538</v>
+        <v>13.34433667412699</v>
       </c>
       <c r="D175" t="n">
-        <v>12.83206357681648</v>
+        <v>12.83206264449757</v>
       </c>
       <c r="E175" t="n">
-        <v>12.83206357681648</v>
+        <v>12.83206264449757</v>
       </c>
       <c r="F175" t="n">
         <v>2244954</v>
@@ -3952,16 +3952,16 @@
         <v>44484</v>
       </c>
       <c r="B177" t="n">
-        <v>13.41991710662842</v>
+        <v>13.4199161529541</v>
       </c>
       <c r="C177" t="n">
-        <v>13.4871012202649</v>
+        <v>13.4871002618162</v>
       </c>
       <c r="D177" t="n">
-        <v>13.08399978562405</v>
+        <v>13.08399885582139</v>
       </c>
       <c r="E177" t="n">
-        <v>13.24356043192167</v>
+        <v>13.24355949077998</v>
       </c>
       <c r="F177" t="n">
         <v>1650266</v>
@@ -3972,16 +3972,16 @@
         <v>44487</v>
       </c>
       <c r="B178" t="n">
-        <v>13.20156955718994</v>
+        <v>13.20157051086426</v>
       </c>
       <c r="C178" t="n">
-        <v>13.3695290192613</v>
+        <v>13.36952998506892</v>
       </c>
       <c r="D178" t="n">
-        <v>13.04200892060634</v>
+        <v>13.04200986275408</v>
       </c>
       <c r="E178" t="n">
-        <v>13.30234572150943</v>
+        <v>13.30234668246376</v>
       </c>
       <c r="F178" t="n">
         <v>1423013</v>
@@ -4052,16 +4052,16 @@
         <v>44491</v>
       </c>
       <c r="B182" t="n">
-        <v>10.53102397918701</v>
+        <v>10.5310230255127</v>
       </c>
       <c r="C182" t="n">
-        <v>10.84174807577158</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="D182" t="n">
-        <v>9.624046544360398</v>
+        <v>9.624045672820648</v>
       </c>
       <c r="E182" t="n">
-        <v>10.84174807577158</v>
+        <v>10.84174709395853</v>
       </c>
       <c r="F182" t="n">
         <v>15708900</v>
@@ -4112,16 +4112,16 @@
         <v>44496</v>
       </c>
       <c r="B185" t="n">
-        <v>10.3294734954834</v>
+        <v>10.32947444915771</v>
       </c>
       <c r="C185" t="n">
-        <v>10.57301348265372</v>
+        <v>10.573014458813</v>
       </c>
       <c r="D185" t="n">
-        <v>9.976760130686884</v>
+        <v>9.976761051796744</v>
       </c>
       <c r="E185" t="n">
-        <v>10.07753468194771</v>
+        <v>10.07753561236163</v>
       </c>
       <c r="F185" t="n">
         <v>4005501</v>
@@ -4132,16 +4132,16 @@
         <v>44497</v>
       </c>
       <c r="B186" t="n">
-        <v>9.909577369689941</v>
+        <v>9.909576416015625</v>
       </c>
       <c r="C186" t="n">
-        <v>10.43864744591674</v>
+        <v>10.43864644132597</v>
       </c>
       <c r="D186" t="n">
-        <v>9.825597219373378</v>
+        <v>9.825596273781114</v>
       </c>
       <c r="E186" t="n">
-        <v>10.25389273880949</v>
+        <v>10.25389175199907</v>
       </c>
       <c r="F186" t="n">
         <v>4167680</v>
@@ -4152,16 +4152,16 @@
         <v>44498</v>
       </c>
       <c r="B187" t="n">
-        <v>9.514872550964355</v>
+        <v>9.514873504638672</v>
       </c>
       <c r="C187" t="n">
-        <v>10.06913659309689</v>
+        <v>10.06913760232501</v>
       </c>
       <c r="D187" t="n">
-        <v>9.069781065056384</v>
+        <v>9.069781974119245</v>
       </c>
       <c r="E187" t="n">
-        <v>10.06913659309689</v>
+        <v>10.06913760232501</v>
       </c>
       <c r="F187" t="n">
         <v>8163450</v>
@@ -4172,16 +4172,16 @@
         <v>44501</v>
       </c>
       <c r="B188" t="n">
-        <v>9.464486122131348</v>
+        <v>9.464485168457031</v>
       </c>
       <c r="C188" t="n">
-        <v>9.817199517534991</v>
+        <v>9.817198528320054</v>
       </c>
       <c r="D188" t="n">
-        <v>9.002598527833245</v>
+        <v>9.002597620700316</v>
       </c>
       <c r="E188" t="n">
-        <v>9.220945302032934</v>
+        <v>9.220944372898632</v>
       </c>
       <c r="F188" t="n">
         <v>8542036</v>
@@ -4212,16 +4212,16 @@
         <v>44504</v>
       </c>
       <c r="B190" t="n">
-        <v>10.3546667098999</v>
+        <v>10.35466766357422</v>
       </c>
       <c r="C190" t="n">
-        <v>11.22805366096068</v>
+        <v>11.22805469507473</v>
       </c>
       <c r="D190" t="n">
-        <v>10.02714660325211</v>
+        <v>10.02714752676152</v>
       </c>
       <c r="E190" t="n">
-        <v>10.08593270053977</v>
+        <v>10.08593362946343</v>
       </c>
       <c r="F190" t="n">
         <v>7850142</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.74937057495117</v>
+        <v>10.74936962127686</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324737138916</v>
+        <v>11.25324637301136</v>
       </c>
       <c r="D193" t="n">
-        <v>10.40505523759868</v>
+        <v>10.4050543144717</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660514437936</v>
+        <v>10.60660420337106</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4332,16 +4332,16 @@
         <v>44512</v>
       </c>
       <c r="B196" t="n">
-        <v>10.75776863098145</v>
+        <v>10.75776767730713</v>
       </c>
       <c r="C196" t="n">
-        <v>11.5051862765822</v>
+        <v>11.50518525664944</v>
       </c>
       <c r="D196" t="n">
-        <v>10.70738135323696</v>
+        <v>10.70738040402947</v>
       </c>
       <c r="E196" t="n">
-        <v>11.19446297160295</v>
+        <v>11.19446197921575</v>
       </c>
       <c r="F196" t="n">
         <v>1618134</v>
@@ -4372,16 +4372,16 @@
         <v>44517</v>
       </c>
       <c r="B198" t="n">
-        <v>10.10272884368896</v>
+        <v>10.10272789001465</v>
       </c>
       <c r="C198" t="n">
-        <v>10.35466766016802</v>
+        <v>10.35466668271126</v>
       </c>
       <c r="D198" t="n">
-        <v>9.800403562785382</v>
+        <v>9.800402637649874</v>
       </c>
       <c r="E198" t="n">
-        <v>10.29588155748545</v>
+        <v>10.29588058557796</v>
       </c>
       <c r="F198" t="n">
         <v>3557179</v>
@@ -4412,16 +4412,16 @@
         <v>44519</v>
       </c>
       <c r="B200" t="n">
-        <v>10.80815505981445</v>
+        <v>10.80815601348877</v>
       </c>
       <c r="C200" t="n">
-        <v>10.95092047977755</v>
+        <v>10.950921446049</v>
       </c>
       <c r="D200" t="n">
-        <v>10.33787035535008</v>
+        <v>10.3378712675281</v>
       </c>
       <c r="E200" t="n">
-        <v>10.33787035535008</v>
+        <v>10.3378712675281</v>
       </c>
       <c r="F200" t="n">
         <v>2187279</v>
@@ -4472,16 +4472,16 @@
         <v>44524</v>
       </c>
       <c r="B203" t="n">
-        <v>9.699627876281738</v>
+        <v>9.699628829956055</v>
       </c>
       <c r="C203" t="n">
-        <v>10.11952534859934</v>
+        <v>10.11952634355827</v>
       </c>
       <c r="D203" t="n">
-        <v>9.38050576484858</v>
+        <v>9.380506687146584</v>
       </c>
       <c r="E203" t="n">
-        <v>9.842392497321224</v>
+        <v>9.842393465032259</v>
       </c>
       <c r="F203" t="n">
         <v>3236370</v>
@@ -4492,16 +4492,16 @@
         <v>44525</v>
       </c>
       <c r="B204" t="n">
-        <v>9.825597763061523</v>
+        <v>9.825596809387207</v>
       </c>
       <c r="C204" t="n">
-        <v>10.15311712024066</v>
+        <v>10.15311613477726</v>
       </c>
       <c r="D204" t="n">
-        <v>9.657639076723777</v>
+        <v>9.657638139351562</v>
       </c>
       <c r="E204" t="n">
-        <v>9.901179090734045</v>
+        <v>9.901178129723791</v>
       </c>
       <c r="F204" t="n">
         <v>1557621</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884383201599121</v>
+        <v>9.884382247924805</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709658136135</v>
+        <v>10.23709559365621</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573658272883511</v>
+        <v>9.573657349188849</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867586359950231</v>
+        <v>9.867585407896522</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4672,16 +4672,16 @@
         <v>44538</v>
       </c>
       <c r="B213" t="n">
-        <v>10.57301330566406</v>
+        <v>10.57301425933838</v>
       </c>
       <c r="C213" t="n">
-        <v>10.66539146439676</v>
+        <v>10.66539242640349</v>
       </c>
       <c r="D213" t="n">
-        <v>9.792004458007494</v>
+        <v>9.792005341235662</v>
       </c>
       <c r="E213" t="n">
-        <v>9.985157978108607</v>
+        <v>9.985158878759011</v>
       </c>
       <c r="F213" t="n">
         <v>3040540</v>
@@ -4752,16 +4752,16 @@
         <v>44544</v>
       </c>
       <c r="B217" t="n">
-        <v>11.11490821838379</v>
+        <v>11.11490726470947</v>
       </c>
       <c r="C217" t="n">
-        <v>11.43905767023386</v>
+        <v>11.43905668874708</v>
       </c>
       <c r="D217" t="n">
-        <v>10.91871264942408</v>
+        <v>10.91871171258361</v>
       </c>
       <c r="E217" t="n">
-        <v>11.25992272893731</v>
+        <v>11.25992176282055</v>
       </c>
       <c r="F217" t="n">
         <v>1511299</v>
@@ -4772,16 +4772,16 @@
         <v>44545</v>
       </c>
       <c r="B218" t="n">
-        <v>11.26845455169678</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C218" t="n">
-        <v>11.37934699719004</v>
+        <v>11.37934603413065</v>
       </c>
       <c r="D218" t="n">
-        <v>10.81635115641641</v>
+        <v>10.8163502410046</v>
       </c>
       <c r="E218" t="n">
-        <v>10.9016534815715</v>
+        <v>10.90165255894037</v>
       </c>
       <c r="F218" t="n">
         <v>3122034</v>
@@ -4812,16 +4812,16 @@
         <v>44547</v>
       </c>
       <c r="B220" t="n">
-        <v>11.17461967468262</v>
+        <v>11.17462062835693</v>
       </c>
       <c r="C220" t="n">
-        <v>11.21727124416134</v>
+        <v>11.21727220147566</v>
       </c>
       <c r="D220" t="n">
-        <v>10.91871273156008</v>
+        <v>10.91871366339456</v>
       </c>
       <c r="E220" t="n">
-        <v>11.19168112705737</v>
+        <v>11.19168208218776</v>
       </c>
       <c r="F220" t="n">
         <v>2659218</v>
@@ -4832,16 +4832,16 @@
         <v>44550</v>
       </c>
       <c r="B221" t="n">
-        <v>10.92724323272705</v>
+        <v>10.92724227905273</v>
       </c>
       <c r="C221" t="n">
-        <v>11.08931838717097</v>
+        <v>11.08931741935155</v>
       </c>
       <c r="D221" t="n">
-        <v>10.64574614643413</v>
+        <v>10.64574521732745</v>
       </c>
       <c r="E221" t="n">
-        <v>10.83341142035164</v>
+        <v>10.83341047486649</v>
       </c>
       <c r="F221" t="n">
         <v>2144606</v>
@@ -4952,16 +4952,16 @@
         <v>44559</v>
       </c>
       <c r="B227" t="n">
-        <v>9.715949058532715</v>
+        <v>9.715948104858398</v>
       </c>
       <c r="C227" t="n">
-        <v>10.21923349127314</v>
+        <v>10.21923248819867</v>
       </c>
       <c r="D227" t="n">
-        <v>9.596525480078773</v>
+        <v>9.596524538126543</v>
       </c>
       <c r="E227" t="n">
-        <v>10.21923349127314</v>
+        <v>10.21923248819867</v>
       </c>
       <c r="F227" t="n">
         <v>1535423</v>
@@ -4972,16 +4972,16 @@
         <v>44560</v>
       </c>
       <c r="B228" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="C228" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="D228" t="n">
-        <v>9.647705662569827</v>
+        <v>9.647706562908386</v>
       </c>
       <c r="E228" t="n">
-        <v>9.792720171305367</v>
+        <v>9.7927210851769</v>
       </c>
       <c r="F228" t="n">
         <v>3325771</v>
@@ -4992,16 +4992,16 @@
         <v>44564</v>
       </c>
       <c r="B229" t="n">
-        <v>9.664767265319824</v>
+        <v>9.664768218994141</v>
       </c>
       <c r="C229" t="n">
-        <v>10.21923271856821</v>
+        <v>10.2192337269546</v>
       </c>
       <c r="D229" t="n">
-        <v>9.349147301752897</v>
+        <v>9.349148224283301</v>
       </c>
       <c r="E229" t="n">
-        <v>10.21923271856821</v>
+        <v>10.2192337269546</v>
       </c>
       <c r="F229" t="n">
         <v>4324384</v>
@@ -5052,16 +5052,16 @@
         <v>44567</v>
       </c>
       <c r="B232" t="n">
-        <v>8.948226928710938</v>
+        <v>8.948225021362305</v>
       </c>
       <c r="C232" t="n">
-        <v>8.948226928710938</v>
+        <v>8.948225021362305</v>
       </c>
       <c r="D232" t="n">
-        <v>8.393761408545751</v>
+        <v>8.393759619383555</v>
       </c>
       <c r="E232" t="n">
-        <v>8.547306251931259</v>
+        <v>8.547304430040395</v>
       </c>
       <c r="F232" t="n">
         <v>4969753</v>
@@ -5092,16 +5092,16 @@
         <v>44571</v>
       </c>
       <c r="B234" t="n">
-        <v>8.581424713134766</v>
+        <v>8.581425666809082</v>
       </c>
       <c r="C234" t="n">
-        <v>8.828802138797872</v>
+        <v>8.828803119963837</v>
       </c>
       <c r="D234" t="n">
-        <v>8.316986661621351</v>
+        <v>8.316987585908032</v>
       </c>
       <c r="E234" t="n">
-        <v>8.828802138797872</v>
+        <v>8.828803119963837</v>
       </c>
       <c r="F234" t="n">
         <v>3048446</v>
@@ -5212,16 +5212,16 @@
         <v>44579</v>
       </c>
       <c r="B240" t="n">
-        <v>8.308456420898438</v>
+        <v>8.308457374572754</v>
       </c>
       <c r="C240" t="n">
-        <v>8.760560536110937</v>
+        <v>8.76056154167938</v>
       </c>
       <c r="D240" t="n">
-        <v>8.206093489490213</v>
+        <v>8.206094431414945</v>
       </c>
       <c r="E240" t="n">
-        <v>8.530242909713456</v>
+        <v>8.530243888845217</v>
       </c>
       <c r="F240" t="n">
         <v>2291580</v>
@@ -5352,16 +5352,16 @@
         <v>44588</v>
       </c>
       <c r="B247" t="n">
-        <v>10.15952014923096</v>
+        <v>10.15952110290527</v>
       </c>
       <c r="C247" t="n">
-        <v>10.50073021728269</v>
+        <v>10.5007312029864</v>
       </c>
       <c r="D247" t="n">
-        <v>9.988916352079942</v>
+        <v>9.988917289739678</v>
       </c>
       <c r="E247" t="n">
-        <v>10.28747402782326</v>
+        <v>10.28747499350861</v>
       </c>
       <c r="F247" t="n">
         <v>2570932</v>
@@ -5372,16 +5372,16 @@
         <v>44589</v>
       </c>
       <c r="B248" t="n">
-        <v>10.2192325592041</v>
+        <v>10.21923351287842</v>
       </c>
       <c r="C248" t="n">
-        <v>10.26188330324402</v>
+        <v>10.26188426089857</v>
       </c>
       <c r="D248" t="n">
-        <v>9.681826917468367</v>
+        <v>9.681827820991172</v>
       </c>
       <c r="E248" t="n">
-        <v>10.1936416180302</v>
+        <v>10.19364256931633</v>
       </c>
       <c r="F248" t="n">
         <v>1431224</v>
@@ -5572,16 +5572,16 @@
         <v>44603</v>
       </c>
       <c r="B258" t="n">
-        <v>9.929204940795898</v>
+        <v>9.929203987121582</v>
       </c>
       <c r="C258" t="n">
-        <v>10.31306495769742</v>
+        <v>10.31306396715434</v>
       </c>
       <c r="D258" t="n">
-        <v>9.647706220762624</v>
+        <v>9.647705294125526</v>
       </c>
       <c r="E258" t="n">
-        <v>9.997446629958024</v>
+        <v>9.99744566972927</v>
       </c>
       <c r="F258" t="n">
         <v>2967053</v>
@@ -5612,16 +5612,16 @@
         <v>44607</v>
       </c>
       <c r="B260" t="n">
-        <v>10.65427684783936</v>
+        <v>10.65427589416504</v>
       </c>
       <c r="C260" t="n">
-        <v>10.86753307355439</v>
+        <v>10.8675321007913</v>
       </c>
       <c r="D260" t="n">
-        <v>10.42395999213378</v>
+        <v>10.42395905907534</v>
       </c>
       <c r="E260" t="n">
-        <v>10.64574653284408</v>
+        <v>10.64574557993332</v>
       </c>
       <c r="F260" t="n">
         <v>2656887</v>
@@ -5672,16 +5672,16 @@
         <v>44610</v>
       </c>
       <c r="B263" t="n">
-        <v>9.95479679107666</v>
+        <v>9.954795837402344</v>
       </c>
       <c r="C263" t="n">
-        <v>10.38983955753546</v>
+        <v>10.38983856218384</v>
       </c>
       <c r="D263" t="n">
-        <v>9.519754024617859</v>
+        <v>9.519753112620847</v>
       </c>
       <c r="E263" t="n">
-        <v>10.38983955753546</v>
+        <v>10.38983856218384</v>
       </c>
       <c r="F263" t="n">
         <v>12813814</v>
@@ -5732,16 +5732,16 @@
         <v>44615</v>
       </c>
       <c r="B266" t="n">
-        <v>9.767128944396973</v>
+        <v>9.767129898071289</v>
       </c>
       <c r="C266" t="n">
-        <v>10.11686932312569</v>
+        <v>10.11687031094908</v>
       </c>
       <c r="D266" t="n">
-        <v>9.68182663422937</v>
+        <v>9.681827579574664</v>
       </c>
       <c r="E266" t="n">
-        <v>9.775660082455282</v>
+        <v>9.775661036962589</v>
       </c>
       <c r="F266" t="n">
         <v>2319860</v>
@@ -5792,16 +5792,16 @@
         <v>44622</v>
       </c>
       <c r="B269" t="n">
-        <v>9.57093334197998</v>
+        <v>9.570934295654297</v>
       </c>
       <c r="C269" t="n">
-        <v>9.656235651776313</v>
+        <v>9.656236613950387</v>
       </c>
       <c r="D269" t="n">
-        <v>9.272374845401204</v>
+        <v>9.272375769326324</v>
       </c>
       <c r="E269" t="n">
-        <v>9.34914684175958</v>
+        <v>9.349147773334476</v>
       </c>
       <c r="F269" t="n">
         <v>1474809</v>
@@ -5832,16 +5832,16 @@
         <v>44624</v>
       </c>
       <c r="B271" t="n">
-        <v>9.323556900024414</v>
+        <v>9.323555946350098</v>
       </c>
       <c r="C271" t="n">
-        <v>9.613585938811369</v>
+        <v>9.613584955470987</v>
       </c>
       <c r="D271" t="n">
-        <v>8.931165738185172</v>
+        <v>8.931164824647187</v>
       </c>
       <c r="E271" t="n">
-        <v>9.511222166592459</v>
+        <v>9.511221193722513</v>
       </c>
       <c r="F271" t="n">
         <v>3245493</v>
@@ -5892,16 +5892,16 @@
         <v>44629</v>
       </c>
       <c r="B274" t="n">
-        <v>9.255313873291016</v>
+        <v>9.255314826965332</v>
       </c>
       <c r="C274" t="n">
-        <v>9.391798058624058</v>
+        <v>9.391799026361806</v>
       </c>
       <c r="D274" t="n">
-        <v>8.845862141875079</v>
+        <v>8.845863053359189</v>
       </c>
       <c r="E274" t="n">
-        <v>8.93969558619249</v>
+        <v>8.939696507345268</v>
       </c>
       <c r="F274" t="n">
         <v>2821903</v>
@@ -5932,16 +5932,16 @@
         <v>44631</v>
       </c>
       <c r="B276" t="n">
-        <v>8.615548133850098</v>
+        <v>8.615547180175781</v>
       </c>
       <c r="C276" t="n">
-        <v>9.195604611294117</v>
+        <v>9.19560359341205</v>
       </c>
       <c r="D276" t="n">
-        <v>8.470533602197403</v>
+        <v>8.470532664575069</v>
       </c>
       <c r="E276" t="n">
-        <v>9.195604611294117</v>
+        <v>9.19560359341205</v>
       </c>
       <c r="F276" t="n">
         <v>3220051</v>
@@ -5972,16 +5972,16 @@
         <v>44635</v>
       </c>
       <c r="B278" t="n">
-        <v>8.905576705932617</v>
+        <v>8.905575752258301</v>
       </c>
       <c r="C278" t="n">
-        <v>8.948227458309324</v>
+        <v>8.948226500067653</v>
       </c>
       <c r="D278" t="n">
-        <v>8.581427194785949</v>
+        <v>8.581426275823933</v>
       </c>
       <c r="E278" t="n">
-        <v>8.666729524122774</v>
+        <v>8.666728596025962</v>
       </c>
       <c r="F278" t="n">
         <v>2087539</v>
@@ -5992,16 +5992,16 @@
         <v>44636</v>
       </c>
       <c r="B279" t="n">
-        <v>8.948226928710938</v>
+        <v>8.948225021362305</v>
       </c>
       <c r="C279" t="n">
-        <v>9.229725670820471</v>
+        <v>9.229723703469311</v>
       </c>
       <c r="D279" t="n">
-        <v>8.589957001783693</v>
+        <v>8.589955170801659</v>
       </c>
       <c r="E279" t="n">
-        <v>8.956757243598096</v>
+        <v>8.956755334431195</v>
       </c>
       <c r="F279" t="n">
         <v>2215964</v>
@@ -6052,16 +6052,16 @@
         <v>44641</v>
       </c>
       <c r="B282" t="n">
-        <v>9.61358642578125</v>
+        <v>9.613585472106934</v>
       </c>
       <c r="C282" t="n">
-        <v>9.741540322952996</v>
+        <v>9.741539356585566</v>
       </c>
       <c r="D282" t="n">
-        <v>9.39179989057245</v>
+        <v>9.391798958899509</v>
       </c>
       <c r="E282" t="n">
-        <v>9.451512094058163</v>
+        <v>9.451511156461731</v>
       </c>
       <c r="F282" t="n">
         <v>1800179</v>
@@ -6112,16 +6112,16 @@
         <v>44644</v>
       </c>
       <c r="B285" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485107421875</v>
       </c>
       <c r="C285" t="n">
-        <v>10.66280508866036</v>
+        <v>10.66280412340302</v>
       </c>
       <c r="D285" t="n">
-        <v>10.11686994044226</v>
+        <v>10.11686902460604</v>
       </c>
       <c r="E285" t="n">
-        <v>10.27894508177519</v>
+        <v>10.27894415126702</v>
       </c>
       <c r="F285" t="n">
         <v>1712400</v>
@@ -6132,16 +6132,16 @@
         <v>44645</v>
       </c>
       <c r="B286" t="n">
-        <v>10.75663948059082</v>
+        <v>10.7566385269165</v>
       </c>
       <c r="C286" t="n">
-        <v>10.83341148866237</v>
+        <v>10.83341052818152</v>
       </c>
       <c r="D286" t="n">
-        <v>10.37277779106635</v>
+        <v>10.37277687142488</v>
       </c>
       <c r="E286" t="n">
-        <v>10.60309463986436</v>
+        <v>10.6030936998032</v>
       </c>
       <c r="F286" t="n">
         <v>2057131</v>
@@ -6272,16 +6272,16 @@
         <v>44656</v>
       </c>
       <c r="B293" t="n">
-        <v>10.76516819000244</v>
+        <v>10.76516914367676</v>
       </c>
       <c r="C293" t="n">
-        <v>11.22580185419098</v>
+        <v>11.22580284867232</v>
       </c>
       <c r="D293" t="n">
-        <v>10.66280524513646</v>
+        <v>10.66280618974256</v>
       </c>
       <c r="E293" t="n">
-        <v>11.18315028358712</v>
+        <v>11.18315127429</v>
       </c>
       <c r="F293" t="n">
         <v>1686452</v>
@@ -6312,16 +6312,16 @@
         <v>44658</v>
       </c>
       <c r="B295" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485107421875</v>
       </c>
       <c r="C295" t="n">
-        <v>10.67133540265596</v>
+        <v>10.67133443662639</v>
       </c>
       <c r="D295" t="n">
-        <v>10.38130720055572</v>
+        <v>10.38130626078115</v>
       </c>
       <c r="E295" t="n">
-        <v>10.50073077191071</v>
+        <v>10.50072982132524</v>
       </c>
       <c r="F295" t="n">
         <v>1517584</v>
@@ -6352,16 +6352,16 @@
         <v>44662</v>
       </c>
       <c r="B297" t="n">
-        <v>10.53485202789307</v>
+        <v>10.53485107421875</v>
       </c>
       <c r="C297" t="n">
-        <v>10.6116240292701</v>
+        <v>10.61162306864595</v>
       </c>
       <c r="D297" t="n">
-        <v>10.17658213841139</v>
+        <v>10.17658121716968</v>
       </c>
       <c r="E297" t="n">
-        <v>10.28747457118751</v>
+        <v>10.28747363990719</v>
       </c>
       <c r="F297" t="n">
         <v>2558465</v>
@@ -6412,16 +6412,16 @@
         <v>44665</v>
       </c>
       <c r="B300" t="n">
-        <v>10.80781936645508</v>
+        <v>10.80782032012939</v>
       </c>
       <c r="C300" t="n">
-        <v>10.85047011092021</v>
+        <v>10.850471068358</v>
       </c>
       <c r="D300" t="n">
-        <v>10.48366991543704</v>
+        <v>10.48367084050864</v>
       </c>
       <c r="E300" t="n">
-        <v>10.54338211210479</v>
+        <v>10.54338304244535</v>
       </c>
       <c r="F300" t="n">
         <v>1300569</v>
@@ -6432,16 +6432,16 @@
         <v>44669</v>
       </c>
       <c r="B301" t="n">
-        <v>10.75663948059082</v>
+        <v>10.7566385269165</v>
       </c>
       <c r="C301" t="n">
-        <v>10.97842519006605</v>
+        <v>10.9784242167284</v>
       </c>
       <c r="D301" t="n">
-        <v>10.66280601845705</v>
+        <v>10.66280507310193</v>
       </c>
       <c r="E301" t="n">
-        <v>10.81635085918351</v>
+        <v>10.81634990021523</v>
       </c>
       <c r="F301" t="n">
         <v>2677159</v>
@@ -6452,16 +6452,16 @@
         <v>44670</v>
       </c>
       <c r="B302" t="n">
-        <v>10.94430351257324</v>
+        <v>10.94430446624756</v>
       </c>
       <c r="C302" t="n">
-        <v>11.07225656996439</v>
+        <v>11.07225753478839</v>
       </c>
       <c r="D302" t="n">
-        <v>10.4836698672987</v>
+        <v>10.48367078083392</v>
       </c>
       <c r="E302" t="n">
-        <v>10.68839574862444</v>
+        <v>10.68839667999924</v>
       </c>
       <c r="F302" t="n">
         <v>3002225</v>
@@ -6472,16 +6472,16 @@
         <v>44671</v>
       </c>
       <c r="B303" t="n">
-        <v>10.90165328979492</v>
+        <v>10.90165233612061</v>
       </c>
       <c r="C303" t="n">
-        <v>11.13197014087041</v>
+        <v>11.13196916704802</v>
       </c>
       <c r="D303" t="n">
-        <v>10.65427663365522</v>
+        <v>10.65427570162136</v>
       </c>
       <c r="E303" t="n">
-        <v>10.92724340968292</v>
+        <v>10.92724245376998</v>
       </c>
       <c r="F303" t="n">
         <v>2911811</v>
@@ -6492,16 +6492,16 @@
         <v>44673</v>
       </c>
       <c r="B304" t="n">
-        <v>10.37277603149414</v>
+        <v>10.37277698516846</v>
       </c>
       <c r="C304" t="n">
-        <v>10.83340965095118</v>
+        <v>10.83341064697621</v>
       </c>
       <c r="D304" t="n">
-        <v>10.30453434973811</v>
+        <v>10.30453529713828</v>
       </c>
       <c r="E304" t="n">
-        <v>10.72251640273312</v>
+        <v>10.72251738856261</v>
       </c>
       <c r="F304" t="n">
         <v>1699122</v>
@@ -6512,16 +6512,16 @@
         <v>44676</v>
       </c>
       <c r="B305" t="n">
-        <v>10.37277603149414</v>
+        <v>10.37277698516846</v>
       </c>
       <c r="C305" t="n">
-        <v>10.43248822454098</v>
+        <v>10.43248918370524</v>
       </c>
       <c r="D305" t="n">
-        <v>10.15098953505802</v>
+        <v>10.15099046834126</v>
       </c>
       <c r="E305" t="n">
-        <v>10.18511078822764</v>
+        <v>10.185111724648</v>
       </c>
       <c r="F305" t="n">
         <v>3255528</v>
@@ -6612,16 +6612,16 @@
         <v>44683</v>
       </c>
       <c r="B310" t="n">
-        <v>11.43905925750732</v>
+        <v>11.43905830383301</v>
       </c>
       <c r="C310" t="n">
-        <v>11.75467761473748</v>
+        <v>11.75467663475006</v>
       </c>
       <c r="D310" t="n">
-        <v>11.32816516230928</v>
+        <v>11.32816421788021</v>
       </c>
       <c r="E310" t="n">
-        <v>11.47317969298488</v>
+        <v>11.47317873646595</v>
       </c>
       <c r="F310" t="n">
         <v>3385270</v>
@@ -6652,16 +6652,16 @@
         <v>44685</v>
       </c>
       <c r="B312" t="n">
-        <v>11.83144855499268</v>
+        <v>11.83144950866699</v>
       </c>
       <c r="C312" t="n">
-        <v>11.95087212149613</v>
+        <v>11.95087308479659</v>
       </c>
       <c r="D312" t="n">
-        <v>10.95283284580649</v>
+        <v>10.95283372865995</v>
       </c>
       <c r="E312" t="n">
-        <v>11.09784735325709</v>
+        <v>11.09784824779946</v>
       </c>
       <c r="F312" t="n">
         <v>3044087</v>
@@ -6692,16 +6692,16 @@
         <v>44687</v>
       </c>
       <c r="B314" t="n">
-        <v>11.52436065673828</v>
+        <v>11.52435970306396</v>
       </c>
       <c r="C314" t="n">
-        <v>11.61819328978013</v>
+        <v>11.61819232834089</v>
       </c>
       <c r="D314" t="n">
-        <v>11.20874150029449</v>
+        <v>11.20874057273858</v>
       </c>
       <c r="E314" t="n">
-        <v>11.60966297545057</v>
+        <v>11.60966201471724</v>
       </c>
       <c r="F314" t="n">
         <v>3256744</v>
@@ -6752,16 +6752,16 @@
         <v>44692</v>
       </c>
       <c r="B317" t="n">
-        <v>11.25992298126221</v>
+        <v>11.25992393493652</v>
       </c>
       <c r="C317" t="n">
-        <v>11.45611855461848</v>
+        <v>11.45611952490985</v>
       </c>
       <c r="D317" t="n">
-        <v>11.00401603433009</v>
+        <v>11.00401696633002</v>
       </c>
       <c r="E317" t="n">
-        <v>11.22580172517128</v>
+        <v>11.22580267595565</v>
       </c>
       <c r="F317" t="n">
         <v>2884545</v>
@@ -6792,16 +6792,16 @@
         <v>44694</v>
       </c>
       <c r="B319" t="n">
-        <v>11.82291984558105</v>
+        <v>11.82291889190674</v>
       </c>
       <c r="C319" t="n">
-        <v>12.07882681602652</v>
+        <v>12.07882584170994</v>
       </c>
       <c r="D319" t="n">
-        <v>11.45611960723421</v>
+        <v>11.45611868314717</v>
       </c>
       <c r="E319" t="n">
-        <v>11.53289161590952</v>
+        <v>11.5328906856298</v>
       </c>
       <c r="F319" t="n">
         <v>2912723</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381214141846</v>
+        <v>11.93381309509277</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470540028707</v>
+        <v>12.04470636282327</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908542732132</v>
+        <v>11.72908636463518</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81438856843816</v>
+        <v>11.81438951256891</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6832,16 +6832,16 @@
         <v>44698</v>
       </c>
       <c r="B321" t="n">
-        <v>12.15559768676758</v>
+        <v>12.15559864044189</v>
       </c>
       <c r="C321" t="n">
-        <v>12.29208188631167</v>
+        <v>12.29208285069394</v>
       </c>
       <c r="D321" t="n">
-        <v>11.95087262432635</v>
+        <v>11.95087356193885</v>
       </c>
       <c r="E321" t="n">
-        <v>12.02764462581472</v>
+        <v>12.02764556945041</v>
       </c>
       <c r="F321" t="n">
         <v>4223023</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415782928467</v>
+        <v>12.45415687561035</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505109394068</v>
+        <v>12.56505013177474</v>
       </c>
       <c r="D323" t="n">
-        <v>11.95087339334582</v>
+        <v>11.9508724782104</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559846896078</v>
+        <v>12.15559753814858</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6892,16 +6892,16 @@
         <v>44701</v>
       </c>
       <c r="B324" t="n">
-        <v>12.50533866882324</v>
+        <v>12.50533771514893</v>
       </c>
       <c r="C324" t="n">
-        <v>12.65888350352286</v>
+        <v>12.658882538139</v>
       </c>
       <c r="D324" t="n">
-        <v>12.30914391126722</v>
+        <v>12.30914297255499</v>
       </c>
       <c r="E324" t="n">
-        <v>12.47974772560942</v>
+        <v>12.4797467738867</v>
       </c>
       <c r="F324" t="n">
         <v>4482610</v>
@@ -6932,16 +6932,16 @@
         <v>44705</v>
       </c>
       <c r="B326" t="n">
-        <v>12.2664909362793</v>
+        <v>12.26649188995361</v>
       </c>
       <c r="C326" t="n">
-        <v>12.62476165062991</v>
+        <v>12.62476263215845</v>
       </c>
       <c r="D326" t="n">
-        <v>12.02764461796216</v>
+        <v>12.02764555306706</v>
       </c>
       <c r="E326" t="n">
-        <v>12.53092902118688</v>
+        <v>12.53092999542028</v>
       </c>
       <c r="F326" t="n">
         <v>3539137</v>
@@ -6952,16 +6952,16 @@
         <v>44706</v>
       </c>
       <c r="B327" t="n">
-        <v>12.36885356903076</v>
+        <v>12.36885452270508</v>
       </c>
       <c r="C327" t="n">
-        <v>12.51386807884551</v>
+        <v>12.51386904370087</v>
       </c>
       <c r="D327" t="n">
-        <v>12.08735568777263</v>
+        <v>12.08735661974265</v>
       </c>
       <c r="E327" t="n">
-        <v>12.21530957001115</v>
+        <v>12.21531051184678</v>
       </c>
       <c r="F327" t="n">
         <v>1655537</v>
@@ -6992,16 +6992,16 @@
         <v>44708</v>
       </c>
       <c r="B329" t="n">
-        <v>13.06833457946777</v>
+        <v>13.06833267211914</v>
       </c>
       <c r="C329" t="n">
-        <v>13.35836279785892</v>
+        <v>13.35836084818011</v>
       </c>
       <c r="D329" t="n">
-        <v>12.76124655671047</v>
+        <v>12.76124469418193</v>
       </c>
       <c r="E329" t="n">
-        <v>12.78683750013469</v>
+        <v>12.78683563387109</v>
       </c>
       <c r="F329" t="n">
         <v>4177410</v>
@@ -7052,16 +7052,16 @@
         <v>44713</v>
       </c>
       <c r="B332" t="n">
-        <v>12.6930046081543</v>
+        <v>12.69300365447998</v>
       </c>
       <c r="C332" t="n">
-        <v>12.71006606244956</v>
+        <v>12.71006510749335</v>
       </c>
       <c r="D332" t="n">
-        <v>12.23237172884965</v>
+        <v>12.23237080978446</v>
       </c>
       <c r="E332" t="n">
-        <v>12.52239996020196</v>
+        <v>12.52239901934583</v>
       </c>
       <c r="F332" t="n">
         <v>4014218</v>
@@ -7072,16 +7072,16 @@
         <v>44714</v>
       </c>
       <c r="B333" t="n">
-        <v>12.57358169555664</v>
+        <v>12.57358074188232</v>
       </c>
       <c r="C333" t="n">
-        <v>13.05980551348239</v>
+        <v>13.05980452292923</v>
       </c>
       <c r="D333" t="n">
-        <v>12.43709748411402</v>
+        <v>12.43709654079169</v>
       </c>
       <c r="E333" t="n">
-        <v>12.69300445291266</v>
+        <v>12.69300349018043</v>
       </c>
       <c r="F333" t="n">
         <v>2071017</v>
@@ -7112,16 +7112,16 @@
         <v>44718</v>
       </c>
       <c r="B335" t="n">
-        <v>12.36885356903076</v>
+        <v>12.36885452270508</v>
       </c>
       <c r="C335" t="n">
-        <v>12.65888258866027</v>
+        <v>12.65888356469666</v>
       </c>
       <c r="D335" t="n">
-        <v>12.19824894243491</v>
+        <v>12.19824988295512</v>
       </c>
       <c r="E335" t="n">
-        <v>12.65888258866027</v>
+        <v>12.65888356469666</v>
       </c>
       <c r="F335" t="n">
         <v>1740275</v>
@@ -7132,16 +7132,16 @@
         <v>44719</v>
       </c>
       <c r="B336" t="n">
-        <v>12.02764415740967</v>
+        <v>12.02764511108398</v>
       </c>
       <c r="C336" t="n">
-        <v>12.37738371978268</v>
+        <v>12.37738470118792</v>
       </c>
       <c r="D336" t="n">
-        <v>11.87410016041255</v>
+        <v>11.87410110191233</v>
       </c>
       <c r="E336" t="n">
-        <v>12.36885340610692</v>
+        <v>12.36885438683579</v>
       </c>
       <c r="F336" t="n">
         <v>3370370</v>
@@ -7152,16 +7152,16 @@
         <v>44720</v>
       </c>
       <c r="B337" t="n">
-        <v>12.02764415740967</v>
+        <v>12.02764511108398</v>
       </c>
       <c r="C337" t="n">
-        <v>12.14706772428701</v>
+        <v>12.14706868743044</v>
       </c>
       <c r="D337" t="n">
-        <v>11.80585847558975</v>
+        <v>11.80585941167863</v>
       </c>
       <c r="E337" t="n">
-        <v>11.96793196167938</v>
+        <v>11.9679329106191</v>
       </c>
       <c r="F337" t="n">
         <v>2224783</v>
@@ -7172,16 +7172,16 @@
         <v>44721</v>
       </c>
       <c r="B338" t="n">
-        <v>12.15559768676758</v>
+        <v>12.15559864044189</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20678039539862</v>
+        <v>12.20678135308851</v>
       </c>
       <c r="D338" t="n">
-        <v>11.83997936680614</v>
+        <v>11.83998029571844</v>
       </c>
       <c r="E338" t="n">
-        <v>12.07029619585453</v>
+        <v>12.07029714283646</v>
       </c>
       <c r="F338" t="n">
         <v>1444097</v>
@@ -7212,16 +7212,16 @@
         <v>44725</v>
       </c>
       <c r="B340" t="n">
-        <v>10.72251796722412</v>
+        <v>10.7225170135498</v>
       </c>
       <c r="C340" t="n">
-        <v>11.507300307965</v>
+        <v>11.50729928449115</v>
       </c>
       <c r="D340" t="n">
-        <v>10.57750426926113</v>
+        <v>10.57750332848451</v>
       </c>
       <c r="E340" t="n">
-        <v>11.23433271652977</v>
+        <v>11.234331717334</v>
       </c>
       <c r="F340" t="n">
         <v>3958469</v>
@@ -7312,16 +7312,16 @@
         <v>44733</v>
       </c>
       <c r="B345" t="n">
-        <v>10.4666109085083</v>
+        <v>10.46660995483398</v>
       </c>
       <c r="C345" t="n">
-        <v>10.65427617742885</v>
+        <v>10.65427520665525</v>
       </c>
       <c r="D345" t="n">
-        <v>10.33012670175548</v>
+        <v>10.33012576051704</v>
       </c>
       <c r="E345" t="n">
-        <v>10.43248965067427</v>
+        <v>10.43248870010894</v>
       </c>
       <c r="F345" t="n">
         <v>1967020</v>
@@ -7352,16 +7352,16 @@
         <v>44735</v>
       </c>
       <c r="B347" t="n">
-        <v>10.80781936645508</v>
+        <v>10.80782032012939</v>
       </c>
       <c r="C347" t="n">
-        <v>10.91018230758797</v>
+        <v>10.91018327029472</v>
       </c>
       <c r="D347" t="n">
-        <v>10.48366991543704</v>
+        <v>10.48367084050864</v>
       </c>
       <c r="E347" t="n">
-        <v>10.49220022924672</v>
+        <v>10.49220115507102</v>
       </c>
       <c r="F347" t="n">
         <v>2364459</v>
@@ -7412,16 +7412,16 @@
         <v>44740</v>
       </c>
       <c r="B350" t="n">
-        <v>10.23629283905029</v>
+        <v>10.23629379272461</v>
       </c>
       <c r="C350" t="n">
-        <v>10.81635007643811</v>
+        <v>10.81635108415403</v>
       </c>
       <c r="D350" t="n">
-        <v>10.18511177890085</v>
+        <v>10.18511272780684</v>
       </c>
       <c r="E350" t="n">
-        <v>10.70545681743382</v>
+        <v>10.70545781481826</v>
       </c>
       <c r="F350" t="n">
         <v>2763519</v>
@@ -7472,16 +7472,16 @@
         <v>44743</v>
       </c>
       <c r="B353" t="n">
-        <v>9.95479679107666</v>
+        <v>9.954795837402344</v>
       </c>
       <c r="C353" t="n">
-        <v>10.01450817146478</v>
+        <v>10.01450721207008</v>
       </c>
       <c r="D353" t="n">
-        <v>9.698888165782213</v>
+        <v>9.698887236624065</v>
       </c>
       <c r="E353" t="n">
-        <v>9.801251945733341</v>
+        <v>9.801251006768695</v>
       </c>
       <c r="F353" t="n">
         <v>1955465</v>
@@ -7532,16 +7532,16 @@
         <v>44748</v>
       </c>
       <c r="B356" t="n">
-        <v>9.647706031799316</v>
+        <v>9.647706985473633</v>
       </c>
       <c r="C356" t="n">
-        <v>9.869492547961359</v>
+        <v>9.869493523559241</v>
       </c>
       <c r="D356" t="n">
-        <v>9.400329398067255</v>
+        <v>9.400330327288428</v>
       </c>
       <c r="E356" t="n">
-        <v>9.681827288003719</v>
+        <v>9.681828245050916</v>
       </c>
       <c r="F356" t="n">
         <v>2475348</v>
@@ -7592,16 +7592,16 @@
         <v>44753</v>
       </c>
       <c r="B359" t="n">
-        <v>9.110300064086914</v>
+        <v>9.11030101776123</v>
       </c>
       <c r="C359" t="n">
-        <v>9.707417904730018</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="D359" t="n">
-        <v>9.076179633609632</v>
+        <v>9.076180583712192</v>
       </c>
       <c r="E359" t="n">
-        <v>9.707417904730018</v>
+        <v>9.707418920911163</v>
       </c>
       <c r="F359" t="n">
         <v>1811329</v>
@@ -7632,16 +7632,16 @@
         <v>44755</v>
       </c>
       <c r="B361" t="n">
-        <v>9.255313873291016</v>
+        <v>9.255314826965332</v>
       </c>
       <c r="C361" t="n">
-        <v>9.383267745504293</v>
+        <v>9.383268712363071</v>
       </c>
       <c r="D361" t="n">
-        <v>9.050588832166239</v>
+        <v>9.050589764745537</v>
       </c>
       <c r="E361" t="n">
-        <v>9.204132819155619</v>
+        <v>9.204133767556202</v>
       </c>
       <c r="F361" t="n">
         <v>1870727</v>
@@ -7672,16 +7672,16 @@
         <v>44757</v>
       </c>
       <c r="B363" t="n">
-        <v>9.297966003417969</v>
+        <v>9.297965049743652</v>
       </c>
       <c r="C363" t="n">
-        <v>9.451511662513374</v>
+        <v>9.451510693090178</v>
       </c>
       <c r="D363" t="n">
-        <v>9.263846395007841</v>
+        <v>9.263845444833107</v>
       </c>
       <c r="E363" t="n">
-        <v>9.374739657548986</v>
+        <v>9.374738696000145</v>
       </c>
       <c r="F363" t="n">
         <v>1899514</v>
@@ -7692,16 +7692,16 @@
         <v>44760</v>
       </c>
       <c r="B364" t="n">
-        <v>9.511221885681152</v>
+        <v>9.511220932006836</v>
       </c>
       <c r="C364" t="n">
-        <v>9.698887146706557</v>
+        <v>9.698886174215358</v>
       </c>
       <c r="D364" t="n">
-        <v>9.212664190527063</v>
+        <v>9.212663266788628</v>
       </c>
       <c r="E364" t="n">
-        <v>9.212664190527063</v>
+        <v>9.212663266788628</v>
       </c>
       <c r="F364" t="n">
         <v>1476836</v>
@@ -7712,16 +7712,16 @@
         <v>44761</v>
       </c>
       <c r="B365" t="n">
-        <v>9.767128944396973</v>
+        <v>9.767129898071289</v>
       </c>
       <c r="C365" t="n">
-        <v>9.929204075840321</v>
+        <v>9.929205045339851</v>
       </c>
       <c r="D365" t="n">
-        <v>9.562403894744662</v>
+        <v>9.562404828429376</v>
       </c>
       <c r="E365" t="n">
-        <v>9.562403894744662</v>
+        <v>9.562404828429376</v>
       </c>
       <c r="F365" t="n">
         <v>2310433</v>
@@ -7752,16 +7752,16 @@
         <v>44763</v>
       </c>
       <c r="B367" t="n">
-        <v>9.963324546813965</v>
+        <v>9.963325500488281</v>
       </c>
       <c r="C367" t="n">
-        <v>10.1936413624377</v>
+        <v>10.19364233815759</v>
       </c>
       <c r="D367" t="n">
-        <v>9.94626391979247</v>
+        <v>9.946264871833769</v>
       </c>
       <c r="E367" t="n">
-        <v>10.02303591680597</v>
+        <v>10.02303687619577</v>
       </c>
       <c r="F367" t="n">
         <v>1242590</v>
@@ -7792,16 +7792,16 @@
         <v>44767</v>
       </c>
       <c r="B369" t="n">
-        <v>10.17658138275146</v>
+        <v>10.17658233642578</v>
       </c>
       <c r="C369" t="n">
-        <v>10.41542768314268</v>
+        <v>10.41542865919991</v>
       </c>
       <c r="D369" t="n">
-        <v>10.11686918921625</v>
+        <v>10.11687013729478</v>
       </c>
       <c r="E369" t="n">
-        <v>10.27041318056894</v>
+        <v>10.27041414303648</v>
       </c>
       <c r="F369" t="n">
         <v>1372535</v>
@@ -7852,16 +7852,16 @@
         <v>44770</v>
       </c>
       <c r="B372" t="n">
-        <v>10.74810695648193</v>
+        <v>10.74810791015625</v>
       </c>
       <c r="C372" t="n">
-        <v>10.8419404065262</v>
+        <v>10.84194136852631</v>
       </c>
       <c r="D372" t="n">
-        <v>10.21923245827733</v>
+        <v>10.21923336502487</v>
       </c>
       <c r="E372" t="n">
-        <v>10.21923245827733</v>
+        <v>10.21923336502487</v>
       </c>
       <c r="F372" t="n">
         <v>1467207</v>
@@ -7892,16 +7892,16 @@
         <v>44774</v>
       </c>
       <c r="B374" t="n">
-        <v>11.26845455169678</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C374" t="n">
-        <v>11.77173901223685</v>
+        <v>11.77173801596846</v>
       </c>
       <c r="D374" t="n">
-        <v>11.09784907680322</v>
+        <v>11.09784813756763</v>
       </c>
       <c r="E374" t="n">
-        <v>11.64378511221253</v>
+        <v>11.64378412677316</v>
       </c>
       <c r="F374" t="n">
         <v>4838693</v>
@@ -7912,16 +7912,16 @@
         <v>44775</v>
       </c>
       <c r="B375" t="n">
-        <v>11.26845455169678</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C375" t="n">
-        <v>11.49877058224051</v>
+        <v>11.49876960907404</v>
       </c>
       <c r="D375" t="n">
-        <v>11.24286360677524</v>
+        <v>11.24286265526674</v>
       </c>
       <c r="E375" t="n">
-        <v>11.39640762713773</v>
+        <v>11.39640666263446</v>
       </c>
       <c r="F375" t="n">
         <v>2088249</v>
@@ -7932,16 +7932,16 @@
         <v>44776</v>
       </c>
       <c r="B376" t="n">
-        <v>11.59260177612305</v>
+        <v>11.59260272979736</v>
       </c>
       <c r="C376" t="n">
-        <v>11.59260177612305</v>
+        <v>11.59260272979736</v>
       </c>
       <c r="D376" t="n">
-        <v>11.16608937897419</v>
+        <v>11.16609029756113</v>
       </c>
       <c r="E376" t="n">
-        <v>11.37934557754862</v>
+        <v>11.37934651367925</v>
       </c>
       <c r="F376" t="n">
         <v>1856232</v>
@@ -7972,16 +7972,16 @@
         <v>44778</v>
       </c>
       <c r="B378" t="n">
-        <v>12.79536628723145</v>
+        <v>12.79536724090576</v>
       </c>
       <c r="C378" t="n">
-        <v>12.93185048674745</v>
+        <v>12.93185145059431</v>
       </c>
       <c r="D378" t="n">
-        <v>12.24090082432778</v>
+        <v>12.24090173667624</v>
       </c>
       <c r="E378" t="n">
-        <v>12.32620313980655</v>
+        <v>12.32620405851283</v>
       </c>
       <c r="F378" t="n">
         <v>4419056</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.16216850280762</v>
+        <v>13.1621675491333</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718220482493</v>
+        <v>13.30718124064354</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271669191557</v>
+        <v>12.75271576790837</v>
       </c>
       <c r="E379" t="n">
-        <v>12.79536744120987</v>
+        <v>12.79536651411238</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8012,16 +8012,16 @@
         <v>44782</v>
       </c>
       <c r="B380" t="n">
-        <v>13.09392356872559</v>
+        <v>13.0939245223999</v>
       </c>
       <c r="C380" t="n">
-        <v>13.34983131560886</v>
+        <v>13.34983228792179</v>
       </c>
       <c r="D380" t="n">
-        <v>12.92331895385887</v>
+        <v>12.92331989510748</v>
       </c>
       <c r="E380" t="n">
-        <v>13.3413010024072</v>
+        <v>13.34130197409885</v>
       </c>
       <c r="F380" t="n">
         <v>4116999</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248371124268</v>
+        <v>13.39248466491699</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634537898129</v>
+        <v>13.77634635999027</v>
       </c>
       <c r="D381" t="n">
-        <v>13.17922832861007</v>
+        <v>13.17922926709854</v>
       </c>
       <c r="E381" t="n">
-        <v>13.30718139327297</v>
+        <v>13.30718234087294</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8052,16 +8052,16 @@
         <v>44784</v>
       </c>
       <c r="B382" t="n">
-        <v>13.36689281463623</v>
+        <v>13.36689376831055</v>
       </c>
       <c r="C382" t="n">
-        <v>13.63986038115962</v>
+        <v>13.63986135430908</v>
       </c>
       <c r="D382" t="n">
-        <v>13.1195153648052</v>
+        <v>13.11951630083012</v>
       </c>
       <c r="E382" t="n">
-        <v>13.52043681312337</v>
+        <v>13.52043777775243</v>
       </c>
       <c r="F382" t="n">
         <v>2014153</v>
@@ -8072,16 +8072,16 @@
         <v>44785</v>
       </c>
       <c r="B383" t="n">
-        <v>13.75928497314453</v>
+        <v>13.75928592681885</v>
       </c>
       <c r="C383" t="n">
-        <v>13.84458729249473</v>
+        <v>13.84458825208146</v>
       </c>
       <c r="D383" t="n">
-        <v>13.47778707191389</v>
+        <v>13.47778800607721</v>
       </c>
       <c r="E383" t="n">
-        <v>13.47778707191389</v>
+        <v>13.47778800607721</v>
       </c>
       <c r="F383" t="n">
         <v>2291478</v>
@@ -8092,16 +8092,16 @@
         <v>44788</v>
       </c>
       <c r="B384" t="n">
-        <v>13.55455875396729</v>
+        <v>13.5545597076416</v>
       </c>
       <c r="C384" t="n">
-        <v>13.70810276022317</v>
+        <v>13.70810372470057</v>
       </c>
       <c r="D384" t="n">
-        <v>13.44366549407879</v>
+        <v>13.44366643995086</v>
       </c>
       <c r="E384" t="n">
-        <v>13.6483913854755</v>
+        <v>13.64839234575172</v>
       </c>
       <c r="F384" t="n">
         <v>3349490</v>
@@ -8132,16 +8132,16 @@
         <v>44790</v>
       </c>
       <c r="B386" t="n">
-        <v>13.56308746337891</v>
+        <v>13.56308841705322</v>
       </c>
       <c r="C386" t="n">
-        <v>13.64838977060406</v>
+        <v>13.64839073027631</v>
       </c>
       <c r="D386" t="n">
-        <v>13.23893803625678</v>
+        <v>13.23893896713886</v>
       </c>
       <c r="E386" t="n">
-        <v>13.64838977060406</v>
+        <v>13.64839073027631</v>
       </c>
       <c r="F386" t="n">
         <v>4054357</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066864013672</v>
+        <v>12.88066959381104</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59720924665701</v>
+        <v>13.59721025338341</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801789456504</v>
+        <v>12.83801884508153</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59720924665701</v>
+        <v>13.59721025338341</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8212,16 +8212,16 @@
         <v>44796</v>
       </c>
       <c r="B390" t="n">
-        <v>12.29208278656006</v>
+        <v>12.29208183288574</v>
       </c>
       <c r="C390" t="n">
-        <v>12.64182321275093</v>
+        <v>12.6418222319422</v>
       </c>
       <c r="D390" t="n">
-        <v>12.25796235261258</v>
+        <v>12.25796140158548</v>
       </c>
       <c r="E390" t="n">
-        <v>12.64182321275093</v>
+        <v>12.6418222319422</v>
       </c>
       <c r="F390" t="n">
         <v>5845922</v>
@@ -8252,16 +8252,16 @@
         <v>44798</v>
       </c>
       <c r="B392" t="n">
-        <v>12.37738513946533</v>
+        <v>12.37738418579102</v>
       </c>
       <c r="C392" t="n">
-        <v>12.61623230061571</v>
+        <v>12.61623132853828</v>
       </c>
       <c r="D392" t="n">
-        <v>12.25796238347348</v>
+        <v>12.25796143900066</v>
       </c>
       <c r="E392" t="n">
-        <v>12.47974809073216</v>
+        <v>12.47974712917081</v>
       </c>
       <c r="F392" t="n">
         <v>1475823</v>
@@ -8292,16 +8292,16 @@
         <v>44802</v>
       </c>
       <c r="B394" t="n">
-        <v>12.25796222686768</v>
+        <v>12.25796127319336</v>
       </c>
       <c r="C394" t="n">
-        <v>12.40297592496939</v>
+        <v>12.40297496001295</v>
       </c>
       <c r="D394" t="n">
-        <v>12.04470601240437</v>
+        <v>12.04470507532147</v>
       </c>
       <c r="E394" t="n">
-        <v>12.18118939596089</v>
+        <v>12.18118844825953</v>
       </c>
       <c r="F394" t="n">
         <v>4196061</v>
@@ -8372,16 +8372,16 @@
         <v>44806</v>
       </c>
       <c r="B398" t="n">
-        <v>12.42003631591797</v>
+        <v>12.42003726959229</v>
       </c>
       <c r="C398" t="n">
-        <v>12.7015333734898</v>
+        <v>12.70153434877891</v>
       </c>
       <c r="D398" t="n">
-        <v>12.36885360844292</v>
+        <v>12.36885455818716</v>
       </c>
       <c r="E398" t="n">
-        <v>12.52239843253504</v>
+        <v>12.52239939406925</v>
       </c>
       <c r="F398" t="n">
         <v>3090207</v>
@@ -8392,16 +8392,16 @@
         <v>44809</v>
       </c>
       <c r="B399" t="n">
-        <v>13.3071813583374</v>
+        <v>13.30718231201172</v>
       </c>
       <c r="C399" t="n">
-        <v>13.40954430454897</v>
+        <v>13.40954526555925</v>
       </c>
       <c r="D399" t="n">
-        <v>12.38591566701658</v>
+        <v>12.38591655466734</v>
       </c>
       <c r="E399" t="n">
-        <v>12.48827778864485</v>
+        <v>12.48827868363151</v>
       </c>
       <c r="F399" t="n">
         <v>2134165</v>
@@ -8432,16 +8432,16 @@
         <v>44812</v>
       </c>
       <c r="B401" t="n">
-        <v>12.15559768676758</v>
+        <v>12.15559864044189</v>
       </c>
       <c r="C401" t="n">
-        <v>12.53945934337598</v>
+        <v>12.53946032716638</v>
       </c>
       <c r="D401" t="n">
-        <v>11.79732779676633</v>
+        <v>11.79732872233238</v>
       </c>
       <c r="E401" t="n">
-        <v>12.53945934337598</v>
+        <v>12.53946032716638</v>
       </c>
       <c r="F401" t="n">
         <v>2311852</v>
@@ -8492,16 +8492,16 @@
         <v>44817</v>
       </c>
       <c r="B404" t="n">
-        <v>11.82735919952393</v>
+        <v>11.82736015319824</v>
       </c>
       <c r="C404" t="n">
-        <v>12.11854676809748</v>
+        <v>12.11854774525109</v>
       </c>
       <c r="D404" t="n">
-        <v>11.7417155059729</v>
+        <v>11.74171645274152</v>
       </c>
       <c r="E404" t="n">
-        <v>12.11854676809748</v>
+        <v>12.11854774525109</v>
       </c>
       <c r="F404" t="n">
         <v>3904244</v>
@@ -8532,16 +8532,16 @@
         <v>44819</v>
       </c>
       <c r="B406" t="n">
-        <v>12.76943778991699</v>
+        <v>12.76943683624268</v>
       </c>
       <c r="C406" t="n">
-        <v>12.9321602465077</v>
+        <v>12.9321592806806</v>
       </c>
       <c r="D406" t="n">
-        <v>12.33265598167787</v>
+        <v>12.33265506062422</v>
       </c>
       <c r="E406" t="n">
-        <v>12.54676482438496</v>
+        <v>12.54676388734078</v>
       </c>
       <c r="F406" t="n">
         <v>3409247</v>
@@ -8572,16 +8572,16 @@
         <v>44823</v>
       </c>
       <c r="B408" t="n">
-        <v>12.39260768890381</v>
+        <v>12.39260673522949</v>
       </c>
       <c r="C408" t="n">
-        <v>12.60671488890061</v>
+        <v>12.60671391874965</v>
       </c>
       <c r="D408" t="n">
-        <v>12.19562708590662</v>
+        <v>12.19562614739096</v>
       </c>
       <c r="E408" t="n">
-        <v>12.34122130123787</v>
+        <v>12.34122035151799</v>
       </c>
       <c r="F408" t="n">
         <v>1221893</v>
@@ -8592,16 +8592,16 @@
         <v>44824</v>
       </c>
       <c r="B409" t="n">
-        <v>11.88730907440186</v>
+        <v>11.88731002807617</v>
       </c>
       <c r="C409" t="n">
-        <v>12.52106973452375</v>
+        <v>12.52107073904231</v>
       </c>
       <c r="D409" t="n">
-        <v>11.87017918218023</v>
+        <v>11.87018013448028</v>
       </c>
       <c r="E409" t="n">
-        <v>12.44399016702588</v>
+        <v>12.44399116536064</v>
       </c>
       <c r="F409" t="n">
         <v>1700434</v>
@@ -8632,16 +8632,16 @@
         <v>44826</v>
       </c>
       <c r="B411" t="n">
-        <v>12.18706130981445</v>
+        <v>12.18706226348877</v>
       </c>
       <c r="C411" t="n">
-        <v>12.24701181243212</v>
+        <v>12.24701277079775</v>
       </c>
       <c r="D411" t="n">
-        <v>11.07369577501007</v>
+        <v>11.07369664156018</v>
       </c>
       <c r="E411" t="n">
-        <v>11.26211222936794</v>
+        <v>11.2621131106622</v>
       </c>
       <c r="F411" t="n">
         <v>10292961</v>
@@ -8672,16 +8672,16 @@
         <v>44830</v>
       </c>
       <c r="B413" t="n">
-        <v>11.45909214019775</v>
+        <v>11.45909118652344</v>
       </c>
       <c r="C413" t="n">
-        <v>11.84448752702055</v>
+        <v>11.844486541272</v>
       </c>
       <c r="D413" t="n">
-        <v>11.34775525533786</v>
+        <v>11.34775431092947</v>
       </c>
       <c r="E413" t="n">
-        <v>11.81879433631571</v>
+        <v>11.81879335270545</v>
       </c>
       <c r="F413" t="n">
         <v>3443068</v>
@@ -8732,16 +8732,16 @@
         <v>44833</v>
       </c>
       <c r="B416" t="n">
-        <v>11.61324977874756</v>
+        <v>11.61325073242188</v>
       </c>
       <c r="C416" t="n">
-        <v>11.66463533256029</v>
+        <v>11.66463629045436</v>
       </c>
       <c r="D416" t="n">
-        <v>11.29636821141672</v>
+        <v>11.29636913906888</v>
       </c>
       <c r="E416" t="n">
-        <v>11.45052734660464</v>
+        <v>11.45052828691627</v>
       </c>
       <c r="F416" t="n">
         <v>3327572</v>
@@ -8872,16 +8872,16 @@
         <v>44844</v>
       </c>
       <c r="B423" t="n">
-        <v>12.76087188720703</v>
+        <v>12.76087284088135</v>
       </c>
       <c r="C423" t="n">
-        <v>12.84651557726097</v>
+        <v>12.8465165373358</v>
       </c>
       <c r="D423" t="n">
-        <v>12.4953766954148</v>
+        <v>12.49537762924753</v>
       </c>
       <c r="E423" t="n">
-        <v>12.66666325093943</v>
+        <v>12.66666419757313</v>
       </c>
       <c r="F423" t="n">
         <v>2045508</v>
@@ -8892,16 +8892,16 @@
         <v>44845</v>
       </c>
       <c r="B424" t="n">
-        <v>12.75230693817139</v>
+        <v>12.7523078918457</v>
       </c>
       <c r="C424" t="n">
-        <v>12.80369331710903</v>
+        <v>12.80369427462625</v>
       </c>
       <c r="D424" t="n">
-        <v>12.5381989499588</v>
+        <v>12.53819988762117</v>
       </c>
       <c r="E424" t="n">
-        <v>12.72661374870257</v>
+        <v>12.72661470045543</v>
       </c>
       <c r="F424" t="n">
         <v>1848640</v>
@@ -8932,16 +8932,16 @@
         <v>44848</v>
       </c>
       <c r="B426" t="n">
-        <v>12.76943778991699</v>
+        <v>12.76943683624268</v>
       </c>
       <c r="C426" t="n">
-        <v>13.1205758961566</v>
+        <v>13.12057491625784</v>
       </c>
       <c r="D426" t="n">
-        <v>12.65810089485929</v>
+        <v>12.65809994950008</v>
       </c>
       <c r="E426" t="n">
-        <v>13.09488270309842</v>
+        <v>13.09488172511853</v>
       </c>
       <c r="F426" t="n">
         <v>2206838</v>
@@ -8952,16 +8952,16 @@
         <v>44851</v>
       </c>
       <c r="B427" t="n">
-        <v>12.6495361328125</v>
+        <v>12.64953708648682</v>
       </c>
       <c r="C427" t="n">
-        <v>13.19765480841111</v>
+        <v>13.19765580340922</v>
       </c>
       <c r="D427" t="n">
-        <v>12.5810215045085</v>
+        <v>12.58102245301736</v>
       </c>
       <c r="E427" t="n">
-        <v>12.87220908709215</v>
+        <v>12.87221005755423</v>
       </c>
       <c r="F427" t="n">
         <v>1088124</v>
@@ -8992,16 +8992,16 @@
         <v>44853</v>
       </c>
       <c r="B429" t="n">
-        <v>12.95785045623779</v>
+        <v>12.95785140991211</v>
       </c>
       <c r="C429" t="n">
-        <v>13.02636590117292</v>
+        <v>13.02636685988985</v>
       </c>
       <c r="D429" t="n">
-        <v>12.71804928500614</v>
+        <v>12.71805022103153</v>
       </c>
       <c r="E429" t="n">
-        <v>12.80369297273763</v>
+        <v>12.80369391506624</v>
       </c>
       <c r="F429" t="n">
         <v>1282165</v>
@@ -9032,16 +9032,16 @@
         <v>44855</v>
       </c>
       <c r="B431" t="n">
-        <v>13.08631706237793</v>
+        <v>13.08631801605225</v>
       </c>
       <c r="C431" t="n">
-        <v>13.26616856834072</v>
+        <v>13.26616953512184</v>
       </c>
       <c r="D431" t="n">
-        <v>12.58958480281398</v>
+        <v>12.58958572028859</v>
       </c>
       <c r="E431" t="n">
-        <v>12.74374311869877</v>
+        <v>12.74374404740777</v>
       </c>
       <c r="F431" t="n">
         <v>1434409</v>
@@ -9052,16 +9052,16 @@
         <v>44858</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94928646087646</v>
+        <v>12.94928741455078</v>
       </c>
       <c r="C432" t="n">
-        <v>13.31755357958135</v>
+        <v>13.31755456037738</v>
       </c>
       <c r="D432" t="n">
-        <v>12.82082134032048</v>
+        <v>12.82082228453374</v>
       </c>
       <c r="E432" t="n">
-        <v>13.00923696041369</v>
+        <v>13.00923791850317</v>
       </c>
       <c r="F432" t="n">
         <v>2377861</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805095672607</v>
+        <v>12.71805000305176</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775399772944</v>
+        <v>13.07775301708247</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235858915441</v>
+        <v>12.69235763740665</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87220928507275</v>
+        <v>12.87220831983874</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9092,16 +9092,16 @@
         <v>44860</v>
       </c>
       <c r="B434" t="n">
-        <v>12.2983980178833</v>
+        <v>12.29839706420898</v>
       </c>
       <c r="C434" t="n">
-        <v>13.00923831573856</v>
+        <v>13.00923730694242</v>
       </c>
       <c r="D434" t="n">
-        <v>12.17849783090068</v>
+        <v>12.17849688652397</v>
       </c>
       <c r="E434" t="n">
-        <v>12.61527879154568</v>
+        <v>12.61527781329898</v>
       </c>
       <c r="F434" t="n">
         <v>4556230</v>
@@ -9132,16 +9132,16 @@
         <v>44862</v>
       </c>
       <c r="B436" t="n">
-        <v>13.06918907165527</v>
+        <v>13.06918811798096</v>
       </c>
       <c r="C436" t="n">
-        <v>13.48027849763024</v>
+        <v>13.48027751395823</v>
       </c>
       <c r="D436" t="n">
-        <v>12.4525565818595</v>
+        <v>12.45255567318159</v>
       </c>
       <c r="E436" t="n">
-        <v>13.154832770782</v>
+        <v>13.15483181085816</v>
       </c>
       <c r="F436" t="n">
         <v>6048388</v>
@@ -9172,16 +9172,16 @@
         <v>44866</v>
       </c>
       <c r="B438" t="n">
-        <v>13.61730670928955</v>
+        <v>13.61730575561523</v>
       </c>
       <c r="C438" t="n">
-        <v>14.01126705916312</v>
+        <v>14.01126607789819</v>
       </c>
       <c r="D438" t="n">
-        <v>13.53166383614674</v>
+        <v>13.53166288847033</v>
       </c>
       <c r="E438" t="n">
-        <v>13.70295123159901</v>
+        <v>13.70295027192667</v>
       </c>
       <c r="F438" t="n">
         <v>3366744</v>
@@ -9292,16 +9292,16 @@
         <v>44875</v>
       </c>
       <c r="B444" t="n">
-        <v>12.2470121383667</v>
+        <v>12.24701118469238</v>
       </c>
       <c r="C444" t="n">
-        <v>12.83795140918214</v>
+        <v>12.83795040949141</v>
       </c>
       <c r="D444" t="n">
-        <v>11.67320111185027</v>
+        <v>11.6732002028586</v>
       </c>
       <c r="E444" t="n">
-        <v>12.83795140918214</v>
+        <v>12.83795040949141</v>
       </c>
       <c r="F444" t="n">
         <v>10581398</v>
@@ -9372,16 +9372,16 @@
         <v>44882</v>
       </c>
       <c r="B448" t="n">
-        <v>10.94523143768311</v>
+        <v>10.94523239135742</v>
       </c>
       <c r="C448" t="n">
-        <v>10.94523143768311</v>
+        <v>10.94523239135742</v>
       </c>
       <c r="D448" t="n">
-        <v>9.900381355318869</v>
+        <v>9.900382217953842</v>
       </c>
       <c r="E448" t="n">
-        <v>10.79963724256202</v>
+        <v>10.7996381835505</v>
       </c>
       <c r="F448" t="n">
         <v>12061945</v>
@@ -9392,16 +9392,16 @@
         <v>44883</v>
       </c>
       <c r="B449" t="n">
-        <v>10.92810249328613</v>
+        <v>10.92810344696045</v>
       </c>
       <c r="C449" t="n">
-        <v>11.38201332758762</v>
+        <v>11.38201432087386</v>
       </c>
       <c r="D449" t="n">
-        <v>10.91953837129458</v>
+        <v>10.91953932422152</v>
       </c>
       <c r="E449" t="n">
-        <v>11.13364636858307</v>
+        <v>11.1336473401948</v>
       </c>
       <c r="F449" t="n">
         <v>5719164</v>
@@ -9472,16 +9472,16 @@
         <v>44889</v>
       </c>
       <c r="B453" t="n">
-        <v>11.53617000579834</v>
+        <v>11.53617095947266</v>
       </c>
       <c r="C453" t="n">
-        <v>11.81879343277872</v>
+        <v>11.81879440981701</v>
       </c>
       <c r="D453" t="n">
-        <v>11.05656683944524</v>
+        <v>11.05656775347163</v>
       </c>
       <c r="E453" t="n">
-        <v>11.11651733831228</v>
+        <v>11.11651825729467</v>
       </c>
       <c r="F453" t="n">
         <v>3457606</v>
@@ -9492,16 +9492,16 @@
         <v>44890</v>
       </c>
       <c r="B454" t="n">
-        <v>10.95379447937012</v>
+        <v>10.95379543304443</v>
       </c>
       <c r="C454" t="n">
-        <v>11.54473449889009</v>
+        <v>11.54473550401364</v>
       </c>
       <c r="D454" t="n">
-        <v>10.89384398285482</v>
+        <v>10.89384493130964</v>
       </c>
       <c r="E454" t="n">
-        <v>11.51047636552432</v>
+        <v>11.51047736766524</v>
       </c>
       <c r="F454" t="n">
         <v>2880833</v>
@@ -9572,16 +9572,16 @@
         <v>44896</v>
       </c>
       <c r="B458" t="n">
-        <v>11.15077495574951</v>
+        <v>11.15077590942383</v>
       </c>
       <c r="C458" t="n">
-        <v>11.33919057892909</v>
+        <v>11.33919154871773</v>
       </c>
       <c r="D458" t="n">
-        <v>10.97092345419175</v>
+        <v>10.9709243924842</v>
       </c>
       <c r="E458" t="n">
-        <v>11.32206233568545</v>
+        <v>11.32206330400918</v>
       </c>
       <c r="F458" t="n">
         <v>2224001</v>
@@ -9612,16 +9612,16 @@
         <v>44900</v>
       </c>
       <c r="B460" t="n">
-        <v>10.65404319763184</v>
+        <v>10.65404510498047</v>
       </c>
       <c r="C460" t="n">
-        <v>11.26211148072586</v>
+        <v>11.2621134969344</v>
       </c>
       <c r="D460" t="n">
-        <v>10.56839868577602</v>
+        <v>10.56840057779207</v>
       </c>
       <c r="E460" t="n">
-        <v>11.26211148072586</v>
+        <v>11.2621134969344</v>
       </c>
       <c r="F460" t="n">
         <v>2438739</v>
@@ -9672,16 +9672,16 @@
         <v>44903</v>
       </c>
       <c r="B463" t="n">
-        <v>9.763351440429688</v>
+        <v>9.763352394104004</v>
       </c>
       <c r="C463" t="n">
-        <v>10.37998471849188</v>
+        <v>10.37998573239832</v>
       </c>
       <c r="D463" t="n">
-        <v>9.686272692963557</v>
+        <v>9.686273639108899</v>
       </c>
       <c r="E463" t="n">
-        <v>10.27721195575933</v>
+        <v>10.27721295962702</v>
       </c>
       <c r="F463" t="n">
         <v>6542779</v>
@@ -9712,16 +9712,16 @@
         <v>44907</v>
       </c>
       <c r="B465" t="n">
-        <v>9.50642204284668</v>
+        <v>9.506422996520996</v>
       </c>
       <c r="C465" t="n">
-        <v>10.02884668216042</v>
+        <v>10.02884768824383</v>
       </c>
       <c r="D465" t="n">
-        <v>9.42077834844417</v>
+        <v>9.420779293526801</v>
       </c>
       <c r="E465" t="n">
-        <v>9.57493666853537</v>
+        <v>9.574937629083003</v>
       </c>
       <c r="F465" t="n">
         <v>6343387</v>
@@ -9732,16 +9732,16 @@
         <v>44908</v>
       </c>
       <c r="B466" t="n">
-        <v>9.377956390380859</v>
+        <v>9.377955436706543</v>
       </c>
       <c r="C466" t="n">
-        <v>9.9517674296964</v>
+        <v>9.951766417669408</v>
       </c>
       <c r="D466" t="n">
-        <v>9.352264023359256</v>
+        <v>9.352263072297678</v>
       </c>
       <c r="E466" t="n">
-        <v>9.532114715427072</v>
+        <v>9.532113746075902</v>
       </c>
       <c r="F466" t="n">
         <v>6881089</v>
@@ -9772,16 +9772,16 @@
         <v>44910</v>
       </c>
       <c r="B468" t="n">
-        <v>9.831865310668945</v>
+        <v>9.831866264343262</v>
       </c>
       <c r="C468" t="n">
-        <v>9.90894487679782</v>
+        <v>9.908945837948723</v>
       </c>
       <c r="D468" t="n">
-        <v>9.352262969477668</v>
+        <v>9.352263876631365</v>
       </c>
       <c r="E468" t="n">
-        <v>9.429341711023316</v>
+        <v>9.429342625653522</v>
       </c>
       <c r="F468" t="n">
         <v>3938569</v>
@@ -9792,16 +9792,16 @@
         <v>44911</v>
       </c>
       <c r="B469" t="n">
-        <v>9.840431213378906</v>
+        <v>9.84043025970459</v>
       </c>
       <c r="C469" t="n">
-        <v>10.22582746462203</v>
+        <v>10.22582647359747</v>
       </c>
       <c r="D469" t="n">
-        <v>9.754788334954545</v>
+        <v>9.754787389580212</v>
       </c>
       <c r="E469" t="n">
-        <v>9.797610598750099</v>
+        <v>9.797609649225695</v>
       </c>
       <c r="F469" t="n">
         <v>14258386</v>
@@ -9812,16 +9812,16 @@
         <v>44914</v>
       </c>
       <c r="B470" t="n">
-        <v>9.951766967773438</v>
+        <v>9.951766014099121</v>
       </c>
       <c r="C470" t="n">
-        <v>10.03741066095349</v>
+        <v>10.03740969907196</v>
       </c>
       <c r="D470" t="n">
-        <v>9.686272590873555</v>
+        <v>9.68627166264147</v>
       </c>
       <c r="E470" t="n">
-        <v>9.840430084181047</v>
+        <v>9.840429141176106</v>
       </c>
       <c r="F470" t="n">
         <v>3753211</v>
@@ -9872,16 +9872,16 @@
         <v>44917</v>
       </c>
       <c r="B473" t="n">
-        <v>10.53414344787598</v>
+        <v>10.53414249420166</v>
       </c>
       <c r="C473" t="n">
-        <v>10.60265807597463</v>
+        <v>10.60265711609756</v>
       </c>
       <c r="D473" t="n">
-        <v>10.29434224953069</v>
+        <v>10.29434131756599</v>
       </c>
       <c r="E473" t="n">
-        <v>10.4399356280945</v>
+        <v>10.43993468294898</v>
       </c>
       <c r="F473" t="n">
         <v>2407341</v>
@@ -9892,16 +9892,16 @@
         <v>44918</v>
       </c>
       <c r="B474" t="n">
-        <v>10.83389472961426</v>
+        <v>10.83389377593994</v>
       </c>
       <c r="C474" t="n">
-        <v>11.26211237541256</v>
+        <v>11.26211138404356</v>
       </c>
       <c r="D474" t="n">
-        <v>10.55983540332002</v>
+        <v>10.55983447377029</v>
       </c>
       <c r="E474" t="n">
-        <v>10.57696364738531</v>
+        <v>10.57696271632784</v>
       </c>
       <c r="F474" t="n">
         <v>4288288</v>
@@ -27852,19 +27852,39 @@
         <v>46234</v>
       </c>
       <c r="B1372" t="n">
-        <v>3.34</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="C1372" t="n">
-        <v>3.45</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="D1372" t="n">
-        <v>3.33</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="E1372" t="n">
-        <v>3.44</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="F1372" t="n">
-        <v>9078100</v>
+        <v>9078300</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1373" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="C1373" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E1373" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>10648100</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -532,16 +532,16 @@
         <v>44235</v>
       </c>
       <c r="B6" t="n">
-        <v>7.211735248565674</v>
+        <v>7.211735725402832</v>
       </c>
       <c r="C6" t="n">
-        <v>7.619035262297836</v>
+        <v>7.619035766065515</v>
       </c>
       <c r="D6" t="n">
-        <v>6.827529163796321</v>
+        <v>6.827529615229921</v>
       </c>
       <c r="E6" t="n">
-        <v>6.854822505530665</v>
+        <v>6.85482295876889</v>
       </c>
       <c r="F6" t="n">
         <v>3162478</v>
@@ -572,16 +572,16 @@
         <v>44237</v>
       </c>
       <c r="B8" t="n">
-        <v>6.928304672241211</v>
+        <v>6.928305149078369</v>
       </c>
       <c r="C8" t="n">
-        <v>7.18024265496158</v>
+        <v>7.180243149138246</v>
       </c>
       <c r="D8" t="n">
-        <v>6.749848296724684</v>
+        <v>6.74984876127967</v>
       </c>
       <c r="E8" t="n">
-        <v>7.18024265496158</v>
+        <v>7.180243149138246</v>
       </c>
       <c r="F8" t="n">
         <v>3511567</v>
@@ -592,16 +592,16 @@
         <v>44238</v>
       </c>
       <c r="B9" t="n">
-        <v>6.963996410369873</v>
+        <v>6.963996887207031</v>
       </c>
       <c r="C9" t="n">
-        <v>7.058473057595991</v>
+        <v>7.058473540902132</v>
       </c>
       <c r="D9" t="n">
-        <v>6.850623621904003</v>
+        <v>6.850624090978325</v>
       </c>
       <c r="E9" t="n">
-        <v>6.928305052130111</v>
+        <v>6.928305526523419</v>
       </c>
       <c r="F9" t="n">
         <v>1655030</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029080390930176</v>
+        <v>7.029080867767334</v>
       </c>
       <c r="C10" t="n">
-        <v>7.194939754112628</v>
+        <v>7.194940242201317</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913608302177867</v>
+        <v>6.913608771181656</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949299660305043</v>
+        <v>6.949300131730055</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -632,16 +632,16 @@
         <v>44244</v>
       </c>
       <c r="B11" t="n">
-        <v>7.274719715118408</v>
+        <v>7.274720191955566</v>
       </c>
       <c r="C11" t="n">
-        <v>7.38809167943809</v>
+        <v>7.388092163706458</v>
       </c>
       <c r="D11" t="n">
-        <v>7.113058970326766</v>
+        <v>7.113059436567523</v>
       </c>
       <c r="E11" t="n">
-        <v>7.117258382965146</v>
+        <v>7.117258849481164</v>
       </c>
       <c r="F11" t="n">
         <v>2613098</v>
@@ -672,16 +672,16 @@
         <v>44246</v>
       </c>
       <c r="B13" t="n">
-        <v>7.453176975250244</v>
+        <v>7.453176021575928</v>
       </c>
       <c r="C13" t="n">
-        <v>7.595942417560001</v>
+        <v>7.595941445618074</v>
       </c>
       <c r="D13" t="n">
-        <v>7.142453669377954</v>
+        <v>7.142452755462365</v>
       </c>
       <c r="E13" t="n">
-        <v>7.159248887478</v>
+        <v>7.159247971413373</v>
       </c>
       <c r="F13" t="n">
         <v>1995604</v>
@@ -732,16 +732,16 @@
         <v>44251</v>
       </c>
       <c r="B16" t="n">
-        <v>7.327207565307617</v>
+        <v>7.327208042144775</v>
       </c>
       <c r="C16" t="n">
-        <v>7.556051620807289</v>
+        <v>7.556052112537071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.108860824383968</v>
+        <v>7.108861287011643</v>
       </c>
       <c r="E16" t="n">
-        <v>7.451077663252569</v>
+        <v>7.451078148150898</v>
       </c>
       <c r="F16" t="n">
         <v>1445414</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138253211975098</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400689314157277</v>
+        <v>7.400689808525235</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945100520026308</v>
+        <v>6.945100983960817</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360799357837727</v>
+        <v>7.360799849541025</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -772,16 +772,16 @@
         <v>44253</v>
       </c>
       <c r="B18" t="n">
-        <v>7.243227481842041</v>
+        <v>7.243227958679199</v>
       </c>
       <c r="C18" t="n">
-        <v>7.480470365014094</v>
+        <v>7.480470857469459</v>
       </c>
       <c r="D18" t="n">
-        <v>6.833828151198126</v>
+        <v>6.833828601083652</v>
       </c>
       <c r="E18" t="n">
-        <v>7.157148852208861</v>
+        <v>7.157149323379279</v>
       </c>
       <c r="F18" t="n">
         <v>1865862</v>
@@ -792,16 +792,16 @@
         <v>44256</v>
       </c>
       <c r="B19" t="n">
-        <v>7.001787662506104</v>
+        <v>7.001786708831787</v>
       </c>
       <c r="C19" t="n">
-        <v>7.390192411161723</v>
+        <v>7.390191404584969</v>
       </c>
       <c r="D19" t="n">
-        <v>7.001787662506104</v>
+        <v>7.001786708831787</v>
       </c>
       <c r="E19" t="n">
-        <v>7.24952707872963</v>
+        <v>7.249526091312114</v>
       </c>
       <c r="F19" t="n">
         <v>1349729</v>
@@ -832,16 +832,16 @@
         <v>44258</v>
       </c>
       <c r="B21" t="n">
-        <v>7.085766792297363</v>
+        <v>7.085767269134521</v>
       </c>
       <c r="C21" t="n">
-        <v>7.108860721672044</v>
+        <v>7.10886120006331</v>
       </c>
       <c r="D21" t="n">
-        <v>6.896812697275568</v>
+        <v>6.896813161397048</v>
       </c>
       <c r="E21" t="n">
-        <v>7.108860721672044</v>
+        <v>7.10886120006331</v>
       </c>
       <c r="F21" t="n">
         <v>1419466</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138253211975098</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222232537370945</v>
+        <v>7.222233019817944</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966095960221117</v>
+        <v>6.966096425558127</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117258583574751</v>
+        <v>7.117259059009463</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -872,16 +872,16 @@
         <v>44260</v>
       </c>
       <c r="B23" t="n">
-        <v>7.016483783721924</v>
+        <v>7.016484260559082</v>
       </c>
       <c r="C23" t="n">
-        <v>7.176045245164364</v>
+        <v>7.176045732845249</v>
       </c>
       <c r="D23" t="n">
-        <v>7.014383671280806</v>
+        <v>7.014384147975241</v>
       </c>
       <c r="E23" t="n">
-        <v>7.117259144498113</v>
+        <v>7.11725962818392</v>
       </c>
       <c r="F23" t="n">
         <v>1309995</v>
@@ -952,16 +952,16 @@
         <v>44266</v>
       </c>
       <c r="B27" t="n">
-        <v>6.67006778717041</v>
+        <v>6.670068264007568</v>
       </c>
       <c r="C27" t="n">
-        <v>6.67006778717041</v>
+        <v>6.670068264007568</v>
       </c>
       <c r="D27" t="n">
-        <v>6.21447937230484</v>
+        <v>6.214479816572392</v>
       </c>
       <c r="E27" t="n">
-        <v>6.287961793693228</v>
+        <v>6.287962243213972</v>
       </c>
       <c r="F27" t="n">
         <v>2230763</v>
@@ -972,16 +972,16 @@
         <v>44267</v>
       </c>
       <c r="B28" t="n">
-        <v>6.695262432098389</v>
+        <v>6.69526195526123</v>
       </c>
       <c r="C28" t="n">
-        <v>6.896813573576604</v>
+        <v>6.896813082384956</v>
       </c>
       <c r="D28" t="n">
-        <v>6.455920629173074</v>
+        <v>6.45592016938186</v>
       </c>
       <c r="E28" t="n">
-        <v>6.646974454893159</v>
+        <v>6.646973981495075</v>
       </c>
       <c r="F28" t="n">
         <v>3263434</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033280372619629</v>
+        <v>7.033279895782471</v>
       </c>
       <c r="C29" t="n">
-        <v>7.12775702718571</v>
+        <v>7.127756543943293</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969559237991</v>
+        <v>6.667969107167907</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969559237991</v>
+        <v>6.667969107167907</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1032,16 +1032,16 @@
         <v>44272</v>
       </c>
       <c r="B31" t="n">
-        <v>7.558150768280029</v>
+        <v>7.558151721954346</v>
       </c>
       <c r="C31" t="n">
-        <v>7.642130094981778</v>
+        <v>7.642131059252459</v>
       </c>
       <c r="D31" t="n">
-        <v>7.285217347653489</v>
+        <v>7.285218266889542</v>
       </c>
       <c r="E31" t="n">
-        <v>7.390191303082056</v>
+        <v>7.390192235563539</v>
       </c>
       <c r="F31" t="n">
         <v>5070506</v>
@@ -1052,16 +1052,16 @@
         <v>44273</v>
       </c>
       <c r="B32" t="n">
-        <v>7.589643001556396</v>
+        <v>7.589643478393555</v>
       </c>
       <c r="C32" t="n">
-        <v>7.898267789895324</v>
+        <v>7.89826828612256</v>
       </c>
       <c r="D32" t="n">
-        <v>7.459474999602055</v>
+        <v>7.459475468261102</v>
       </c>
       <c r="E32" t="n">
-        <v>7.600140316321165</v>
+        <v>7.600140793817841</v>
       </c>
       <c r="F32" t="n">
         <v>3661176</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.516162395477295</v>
+        <v>7.516161918640137</v>
       </c>
       <c r="C33" t="n">
-        <v>7.778597720834538</v>
+        <v>7.77859722734807</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430082134541178</v>
+        <v>7.430081663165087</v>
       </c>
       <c r="E33" t="n">
-        <v>7.600140920268824</v>
+        <v>7.600140438103936</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1092,16 +1092,16 @@
         <v>44277</v>
       </c>
       <c r="B34" t="n">
-        <v>7.558150768280029</v>
+        <v>7.558151721954346</v>
       </c>
       <c r="C34" t="n">
-        <v>7.807989447871488</v>
+        <v>7.807990433070015</v>
       </c>
       <c r="D34" t="n">
-        <v>7.201238020951741</v>
+        <v>7.201238929591428</v>
       </c>
       <c r="E34" t="n">
-        <v>7.51406139851813</v>
+        <v>7.514062346629327</v>
       </c>
       <c r="F34" t="n">
         <v>5377429</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.516162395477295</v>
+        <v>7.516161918640137</v>
       </c>
       <c r="C35" t="n">
-        <v>7.55815165787306</v>
+        <v>7.558151178372036</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436381660412942</v>
+        <v>7.436381188637199</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511962982160976</v>
+        <v>7.511962505590234</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.70511531829834</v>
+        <v>7.705114364624023</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789095471368375</v>
+        <v>7.789094507299701</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033280588094989</v>
+        <v>7.033279717574721</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159249194110809</v>
+        <v>7.159248307999206</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1172,16 +1172,16 @@
         <v>44281</v>
       </c>
       <c r="B38" t="n">
-        <v>7.518260955810547</v>
+        <v>7.518261432647705</v>
       </c>
       <c r="C38" t="n">
-        <v>7.789095110371317</v>
+        <v>7.789095604385824</v>
       </c>
       <c r="D38" t="n">
-        <v>7.455276249824448</v>
+        <v>7.455276722666873</v>
       </c>
       <c r="E38" t="n">
-        <v>7.721911802823614</v>
+        <v>7.721912292577096</v>
       </c>
       <c r="F38" t="n">
         <v>2604179</v>
@@ -1192,16 +1192,16 @@
         <v>44284</v>
       </c>
       <c r="B39" t="n">
-        <v>7.232730865478516</v>
+        <v>7.232730388641357</v>
       </c>
       <c r="C39" t="n">
-        <v>7.663125678786516</v>
+        <v>7.663125173574427</v>
       </c>
       <c r="D39" t="n">
-        <v>7.232730865478516</v>
+        <v>7.232730388641357</v>
       </c>
       <c r="E39" t="n">
-        <v>7.568649025946455</v>
+        <v>7.568648526962992</v>
       </c>
       <c r="F39" t="n">
         <v>3953908</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138253211975098</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379693873962468</v>
+        <v>7.379694366927925</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138253211975098</v>
+        <v>7.138253688812256</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257923892728211</v>
+        <v>7.257924377559402</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1232,16 +1232,16 @@
         <v>44286</v>
       </c>
       <c r="B41" t="n">
-        <v>7.348202705383301</v>
+        <v>7.348202228546143</v>
       </c>
       <c r="C41" t="n">
-        <v>7.379694651301018</v>
+        <v>7.379694172420294</v>
       </c>
       <c r="D41" t="n">
-        <v>6.997588639911132</v>
+        <v>6.997588185825906</v>
       </c>
       <c r="E41" t="n">
-        <v>7.226432711322428</v>
+        <v>7.226432242387128</v>
       </c>
       <c r="F41" t="n">
         <v>2544984</v>
@@ -1252,16 +1252,16 @@
         <v>44287</v>
       </c>
       <c r="B42" t="n">
-        <v>7.348202705383301</v>
+        <v>7.348202228546143</v>
       </c>
       <c r="C42" t="n">
-        <v>7.524559388470522</v>
+        <v>7.524558900189283</v>
       </c>
       <c r="D42" t="n">
-        <v>7.171846022296081</v>
+        <v>7.171845556903002</v>
       </c>
       <c r="E42" t="n">
-        <v>7.358700020689207</v>
+        <v>7.35869954317086</v>
       </c>
       <c r="F42" t="n">
         <v>877384</v>
@@ -1272,16 +1272,16 @@
         <v>44291</v>
       </c>
       <c r="B43" t="n">
-        <v>7.327207565307617</v>
+        <v>7.327208042144775</v>
       </c>
       <c r="C43" t="n">
-        <v>7.400689579134269</v>
+        <v>7.400690060753461</v>
       </c>
       <c r="D43" t="n">
-        <v>7.260023453149884</v>
+        <v>7.260023925614861</v>
       </c>
       <c r="E43" t="n">
-        <v>7.400689579134269</v>
+        <v>7.400690060753461</v>
       </c>
       <c r="F43" t="n">
         <v>1080107</v>
@@ -1292,16 +1292,16 @@
         <v>44292</v>
       </c>
       <c r="B44" t="n">
-        <v>7.211735248565674</v>
+        <v>7.211735725402832</v>
       </c>
       <c r="C44" t="n">
-        <v>7.379693899948808</v>
+        <v>7.379694387891328</v>
       </c>
       <c r="D44" t="n">
-        <v>7.190740620091399</v>
+        <v>7.190741095540401</v>
       </c>
       <c r="E44" t="n">
-        <v>7.36919658571167</v>
+        <v>7.369197072960112</v>
       </c>
       <c r="F44" t="n">
         <v>1319726</v>
@@ -1312,16 +1312,16 @@
         <v>44293</v>
       </c>
       <c r="B45" t="n">
-        <v>7.243227481842041</v>
+        <v>7.243227958679199</v>
       </c>
       <c r="C45" t="n">
-        <v>7.388092210073672</v>
+        <v>7.388092696447584</v>
       </c>
       <c r="D45" t="n">
-        <v>7.146651537550619</v>
+        <v>7.146652008029977</v>
       </c>
       <c r="E45" t="n">
-        <v>7.213834838440065</v>
+        <v>7.213835313342242</v>
       </c>
       <c r="F45" t="n">
         <v>1401221</v>
@@ -1332,16 +1332,16 @@
         <v>44294</v>
       </c>
       <c r="B46" t="n">
-        <v>7.589643001556396</v>
+        <v>7.589643478393555</v>
       </c>
       <c r="C46" t="n">
-        <v>7.78909441747052</v>
+        <v>7.789094906838682</v>
       </c>
       <c r="D46" t="n">
-        <v>7.215935024034804</v>
+        <v>7.215935477392881</v>
       </c>
       <c r="E46" t="n">
-        <v>7.2432275553465</v>
+        <v>7.243228010419292</v>
       </c>
       <c r="F46" t="n">
         <v>2111967</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652627944946289</v>
+        <v>7.652626991271973</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873073997390144</v>
+        <v>7.873073016243731</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474171152894864</v>
+        <v>7.474170221459922</v>
       </c>
       <c r="E47" t="n">
-        <v>7.595941956339789</v>
+        <v>7.595941009729709</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1412,16 +1412,16 @@
         <v>44300</v>
       </c>
       <c r="B50" t="n">
-        <v>7.877274036407471</v>
+        <v>7.877272129058838</v>
       </c>
       <c r="C50" t="n">
-        <v>7.877274036407471</v>
+        <v>7.877272129058838</v>
       </c>
       <c r="D50" t="n">
-        <v>7.518261123117962</v>
+        <v>7.518259302698232</v>
       </c>
       <c r="E50" t="n">
-        <v>7.786995982878214</v>
+        <v>7.786994097388884</v>
       </c>
       <c r="F50" t="n">
         <v>2026013</v>
@@ -1432,16 +1432,16 @@
         <v>44301</v>
       </c>
       <c r="B51" t="n">
-        <v>8.112414360046387</v>
+        <v>8.112415313720703</v>
       </c>
       <c r="C51" t="n">
-        <v>8.185897180089103</v>
+        <v>8.185898142401868</v>
       </c>
       <c r="D51" t="n">
-        <v>7.891968335301526</v>
+        <v>7.891969263060783</v>
       </c>
       <c r="E51" t="n">
-        <v>7.894067635698465</v>
+        <v>7.894068563704509</v>
       </c>
       <c r="F51" t="n">
         <v>2034122</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208991050720215</v>
+        <v>8.208992958068848</v>
       </c>
       <c r="C53" t="n">
-        <v>8.244682407926204</v>
+        <v>8.244684323567677</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059928531921125</v>
+        <v>8.059930404635271</v>
       </c>
       <c r="E53" t="n">
-        <v>8.1879964212324</v>
+        <v>8.187998323702958</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1492,16 +1492,16 @@
         <v>44306</v>
       </c>
       <c r="B54" t="n">
-        <v>8.196394920349121</v>
+        <v>8.196395874023438</v>
       </c>
       <c r="C54" t="n">
-        <v>8.244682079168939</v>
+        <v>8.244683038461606</v>
       </c>
       <c r="D54" t="n">
-        <v>8.078822726880942</v>
+        <v>8.078823666875394</v>
       </c>
       <c r="E54" t="n">
-        <v>8.206892234674447</v>
+        <v>8.206893189570158</v>
       </c>
       <c r="F54" t="n">
         <v>282595</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397944450378418</v>
+        <v>8.397945404052734</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469327158830897</v>
+        <v>8.469328120611465</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116613840986611</v>
+        <v>8.116614762712898</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116613840986611</v>
+        <v>8.116614762712898</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1652,16 +1652,16 @@
         <v>44319</v>
       </c>
       <c r="B62" t="n">
-        <v>8.849335670471191</v>
+        <v>8.849334716796875</v>
       </c>
       <c r="C62" t="n">
-        <v>9.122269135355927</v>
+        <v>9.122268152268145</v>
       </c>
       <c r="D62" t="n">
-        <v>8.641487026423638</v>
+        <v>8.641486095148732</v>
       </c>
       <c r="E62" t="n">
-        <v>8.733864381954685</v>
+        <v>8.733863440724466</v>
       </c>
       <c r="F62" t="n">
         <v>2468354</v>
@@ -1672,16 +1672,16 @@
         <v>44320</v>
       </c>
       <c r="B63" t="n">
-        <v>9.298624992370605</v>
+        <v>9.298625946044922</v>
       </c>
       <c r="C63" t="n">
-        <v>9.544265900402022</v>
+        <v>9.544266879269465</v>
       </c>
       <c r="D63" t="n">
-        <v>8.719166865823404</v>
+        <v>8.719167760068038</v>
       </c>
       <c r="E63" t="n">
-        <v>8.849334872165999</v>
+        <v>8.849335779760766</v>
       </c>
       <c r="F63" t="n">
         <v>2875017</v>
@@ -1692,16 +1692,16 @@
         <v>44321</v>
       </c>
       <c r="B64" t="n">
-        <v>9.783605575561523</v>
+        <v>9.78360652923584</v>
       </c>
       <c r="C64" t="n">
-        <v>9.993554294101639</v>
+        <v>9.99355526824108</v>
       </c>
       <c r="D64" t="n">
-        <v>9.273430912006111</v>
+        <v>9.273431815950246</v>
       </c>
       <c r="E64" t="n">
-        <v>9.298624141267135</v>
+        <v>9.298625047667027</v>
       </c>
       <c r="F64" t="n">
         <v>3818084</v>
@@ -1752,16 +1752,16 @@
         <v>44326</v>
       </c>
       <c r="B67" t="n">
-        <v>9.38050651550293</v>
+        <v>9.380505561828613</v>
       </c>
       <c r="C67" t="n">
-        <v>9.886482661063617</v>
+        <v>9.886481655948959</v>
       </c>
       <c r="D67" t="n">
-        <v>9.254537101368319</v>
+        <v>9.254536160500752</v>
       </c>
       <c r="E67" t="n">
-        <v>9.867586518328292</v>
+        <v>9.867585515134721</v>
       </c>
       <c r="F67" t="n">
         <v>3466157</v>
@@ -1772,16 +1772,16 @@
         <v>44327</v>
       </c>
       <c r="B68" t="n">
-        <v>9.61774730682373</v>
+        <v>9.617746353149414</v>
       </c>
       <c r="C68" t="n">
-        <v>9.645041463213841</v>
+        <v>9.645040506833098</v>
       </c>
       <c r="D68" t="n">
-        <v>8.964807960828002</v>
+        <v>8.964807071897692</v>
       </c>
       <c r="E68" t="n">
-        <v>9.294427396683329</v>
+        <v>9.294426475068693</v>
       </c>
       <c r="F68" t="n">
         <v>2188597</v>
@@ -1792,16 +1792,16 @@
         <v>44328</v>
       </c>
       <c r="B69" t="n">
-        <v>9.531667709350586</v>
+        <v>9.531669616699219</v>
       </c>
       <c r="C69" t="n">
-        <v>9.743715730787388</v>
+        <v>9.743717680568206</v>
       </c>
       <c r="D69" t="n">
-        <v>9.321718988410458</v>
+        <v>9.321720853746987</v>
       </c>
       <c r="E69" t="n">
-        <v>9.563159652184094</v>
+        <v>9.563161565834468</v>
       </c>
       <c r="F69" t="n">
         <v>1563804</v>
@@ -1832,16 +1832,16 @@
         <v>44330</v>
       </c>
       <c r="B71" t="n">
-        <v>9.626144409179688</v>
+        <v>9.626145362854004</v>
       </c>
       <c r="C71" t="n">
-        <v>9.657637164002436</v>
+        <v>9.657638120796779</v>
       </c>
       <c r="D71" t="n">
-        <v>9.273431075367332</v>
+        <v>9.273431994097892</v>
       </c>
       <c r="E71" t="n">
-        <v>9.655537863492778</v>
+        <v>9.655538820079142</v>
       </c>
       <c r="F71" t="n">
         <v>1271072</v>
@@ -1852,16 +1852,16 @@
         <v>44333</v>
       </c>
       <c r="B72" t="n">
-        <v>9.657637596130371</v>
+        <v>9.657638549804688</v>
       </c>
       <c r="C72" t="n">
-        <v>9.773108870861909</v>
+        <v>9.773109835938806</v>
       </c>
       <c r="D72" t="n">
-        <v>9.361610233599944</v>
+        <v>9.36161115804209</v>
       </c>
       <c r="E72" t="n">
-        <v>9.613548224482443</v>
+        <v>9.613549173803014</v>
       </c>
       <c r="F72" t="n">
         <v>1884107</v>
@@ -1872,16 +1872,16 @@
         <v>44334</v>
       </c>
       <c r="B73" t="n">
-        <v>9.657637596130371</v>
+        <v>9.657638549804688</v>
       </c>
       <c r="C73" t="n">
-        <v>9.66603561033924</v>
+        <v>9.666036564842845</v>
       </c>
       <c r="D73" t="n">
-        <v>9.458186179310156</v>
+        <v>9.458187113289004</v>
       </c>
       <c r="E73" t="n">
-        <v>9.655538295526782</v>
+        <v>9.655539248993795</v>
       </c>
       <c r="F73" t="n">
         <v>1385003</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.823495864868164</v>
+        <v>9.82349681854248</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272800283195</v>
+        <v>10.10272898361439</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334316624833162</v>
+        <v>9.334317531017494</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678631950423839</v>
+        <v>9.678632890034629</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1912,16 +1912,16 @@
         <v>44336</v>
       </c>
       <c r="B75" t="n">
-        <v>10.1300220489502</v>
+        <v>10.13002300262451</v>
       </c>
       <c r="C75" t="n">
-        <v>10.22869810319815</v>
+        <v>10.22869906616216</v>
       </c>
       <c r="D75" t="n">
-        <v>9.504375291530147</v>
+        <v>9.504376186303976</v>
       </c>
       <c r="E75" t="n">
-        <v>9.873884655086501</v>
+        <v>9.873885584647184</v>
       </c>
       <c r="F75" t="n">
         <v>2816227</v>
@@ -1952,16 +1952,16 @@
         <v>44340</v>
       </c>
       <c r="B77" t="n">
-        <v>10.18250846862793</v>
+        <v>10.18250942230225</v>
       </c>
       <c r="C77" t="n">
-        <v>10.39035788841617</v>
+        <v>10.39035886155727</v>
       </c>
       <c r="D77" t="n">
-        <v>9.951565119860142</v>
+        <v>9.951566051904743</v>
       </c>
       <c r="E77" t="n">
-        <v>10.15731442736386</v>
+        <v>10.15731537867855</v>
       </c>
       <c r="F77" t="n">
         <v>3407772</v>
@@ -1972,16 +1972,16 @@
         <v>44341</v>
       </c>
       <c r="B78" t="n">
-        <v>10.4344482421875</v>
+        <v>10.43444728851318</v>
       </c>
       <c r="C78" t="n">
-        <v>10.49323272042781</v>
+        <v>10.49323176138078</v>
       </c>
       <c r="D78" t="n">
-        <v>10.18880814322383</v>
+        <v>10.18880721200021</v>
       </c>
       <c r="E78" t="n">
-        <v>10.23499681733537</v>
+        <v>10.23499588189026</v>
       </c>
       <c r="F78" t="n">
         <v>2528360</v>
@@ -1992,16 +1992,16 @@
         <v>44342</v>
       </c>
       <c r="B79" t="n">
-        <v>10.4974308013916</v>
+        <v>10.49743175506592</v>
       </c>
       <c r="C79" t="n">
-        <v>10.51842624099203</v>
+        <v>10.51842719657374</v>
       </c>
       <c r="D79" t="n">
-        <v>10.31897484145185</v>
+        <v>10.31897577891374</v>
       </c>
       <c r="E79" t="n">
-        <v>10.42394960407066</v>
+        <v>10.42395055106932</v>
       </c>
       <c r="F79" t="n">
         <v>2052367</v>
@@ -2092,16 +2092,16 @@
         <v>44349</v>
       </c>
       <c r="B84" t="n">
-        <v>10.9152307510376</v>
+        <v>10.91522979736328</v>
       </c>
       <c r="C84" t="n">
-        <v>11.25114809921971</v>
+        <v>11.25114711619596</v>
       </c>
       <c r="D84" t="n">
-        <v>10.79765935445603</v>
+        <v>10.79765841105404</v>
       </c>
       <c r="E84" t="n">
-        <v>11.25114809921971</v>
+        <v>11.25114711619596</v>
       </c>
       <c r="F84" t="n">
         <v>2442811</v>
@@ -2152,16 +2152,16 @@
         <v>44355</v>
       </c>
       <c r="B87" t="n">
-        <v>11.02020454406738</v>
+        <v>11.0202054977417</v>
       </c>
       <c r="C87" t="n">
-        <v>11.16926787426587</v>
+        <v>11.16926884083993</v>
       </c>
       <c r="D87" t="n">
-        <v>10.9341251021654</v>
+        <v>10.93412604839051</v>
       </c>
       <c r="E87" t="n">
-        <v>11.12097909005958</v>
+        <v>11.1209800524548</v>
       </c>
       <c r="F87" t="n">
         <v>1135248</v>
@@ -2192,16 +2192,16 @@
         <v>44357</v>
       </c>
       <c r="B89" t="n">
-        <v>10.79135990142822</v>
+        <v>10.79136085510254</v>
       </c>
       <c r="C89" t="n">
-        <v>10.99081132062593</v>
+        <v>10.99081229192654</v>
       </c>
       <c r="D89" t="n">
-        <v>10.70108266824717</v>
+        <v>10.70108361394333</v>
       </c>
       <c r="E89" t="n">
-        <v>10.94042404656661</v>
+        <v>10.9404250134143</v>
       </c>
       <c r="F89" t="n">
         <v>1040779</v>
@@ -2232,16 +2232,16 @@
         <v>44361</v>
       </c>
       <c r="B91" t="n">
-        <v>10.9425220489502</v>
+        <v>10.94252300262451</v>
       </c>
       <c r="C91" t="n">
-        <v>11.24904750537457</v>
+        <v>11.24904848576352</v>
       </c>
       <c r="D91" t="n">
-        <v>10.64649471801241</v>
+        <v>10.64649564588704</v>
       </c>
       <c r="E91" t="n">
-        <v>10.72837473896458</v>
+        <v>10.72837567397531</v>
       </c>
       <c r="F91" t="n">
         <v>2250630</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462203979492</v>
+        <v>10.94462299346924</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192205807723</v>
+        <v>11.35192304724218</v>
       </c>
       <c r="D92" t="n">
-        <v>10.8144540429291</v>
+        <v>10.81445498526105</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152729877964</v>
+        <v>10.92152825044157</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2292,16 +2292,16 @@
         <v>44364</v>
       </c>
       <c r="B94" t="n">
-        <v>11.3057336807251</v>
+        <v>11.30573463439941</v>
       </c>
       <c r="C94" t="n">
-        <v>11.52408123449005</v>
+        <v>11.52408220658267</v>
       </c>
       <c r="D94" t="n">
-        <v>11.0768896241283</v>
+        <v>11.07689055849889</v>
       </c>
       <c r="E94" t="n">
-        <v>11.21125703729346</v>
+        <v>11.21125798299837</v>
       </c>
       <c r="F94" t="n">
         <v>2709189</v>
@@ -2352,16 +2352,16 @@
         <v>44369</v>
       </c>
       <c r="B97" t="n">
-        <v>11.28473854064941</v>
+        <v>11.28474044799805</v>
       </c>
       <c r="C97" t="n">
-        <v>11.42330536046935</v>
+        <v>11.42330729123857</v>
       </c>
       <c r="D97" t="n">
-        <v>11.16296937177805</v>
+        <v>11.16297125854524</v>
       </c>
       <c r="E97" t="n">
-        <v>11.23855068310205</v>
+        <v>11.238552582644</v>
       </c>
       <c r="F97" t="n">
         <v>1033076</v>
@@ -2392,16 +2392,16 @@
         <v>44371</v>
       </c>
       <c r="B99" t="n">
-        <v>11.71093654632568</v>
+        <v>11.71093559265137</v>
       </c>
       <c r="C99" t="n">
-        <v>12.02165985453709</v>
+        <v>12.02165887555918</v>
       </c>
       <c r="D99" t="n">
-        <v>11.35612305046303</v>
+        <v>11.35612212568278</v>
       </c>
       <c r="E99" t="n">
-        <v>11.54717565951756</v>
+        <v>11.54717471917903</v>
       </c>
       <c r="F99" t="n">
         <v>3545624</v>
@@ -2532,16 +2532,16 @@
         <v>44382</v>
       </c>
       <c r="B106" t="n">
-        <v>13.12179088592529</v>
+        <v>13.12179183959961</v>
       </c>
       <c r="C106" t="n">
-        <v>13.50179840315787</v>
+        <v>13.50179938445063</v>
       </c>
       <c r="D106" t="n">
-        <v>12.96432872312831</v>
+        <v>12.96432966535849</v>
       </c>
       <c r="E106" t="n">
-        <v>12.96432872312831</v>
+        <v>12.96432966535849</v>
       </c>
       <c r="F106" t="n">
         <v>1748688</v>
@@ -2552,16 +2552,16 @@
         <v>44383</v>
       </c>
       <c r="B107" t="n">
-        <v>13.04830837249756</v>
+        <v>13.04830932617188</v>
       </c>
       <c r="C107" t="n">
-        <v>13.36113095015526</v>
+        <v>13.36113192669314</v>
       </c>
       <c r="D107" t="n">
-        <v>13.00001958807886</v>
+        <v>13.00002053822385</v>
       </c>
       <c r="E107" t="n">
-        <v>13.14908373072754</v>
+        <v>13.14908469176732</v>
       </c>
       <c r="F107" t="n">
         <v>1738957</v>
@@ -2572,16 +2572,16 @@
         <v>44384</v>
       </c>
       <c r="B108" t="n">
-        <v>13.22676563262939</v>
+        <v>13.22676658630371</v>
       </c>
       <c r="C108" t="n">
-        <v>13.31074415373561</v>
+        <v>13.31074511346494</v>
       </c>
       <c r="D108" t="n">
-        <v>13.05040814056382</v>
+        <v>13.05040908152244</v>
       </c>
       <c r="E108" t="n">
-        <v>13.05880615503335</v>
+        <v>13.05880709659748</v>
       </c>
       <c r="F108" t="n">
         <v>2057638</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C114" t="n">
-        <v>13.9384904687512</v>
+        <v>13.93849142806081</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969768169454</v>
+        <v>13.49969861080446</v>
       </c>
       <c r="E114" t="n">
-        <v>13.64246310974914</v>
+        <v>13.64246404868482</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501433064608</v>
+        <v>14.24501531105205</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969768169454</v>
+        <v>13.49969861080446</v>
       </c>
       <c r="E115" t="n">
-        <v>13.7495355572011</v>
+        <v>13.74953650350598</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06656074523926</v>
+        <v>14.06655979156494</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103739980534</v>
+        <v>14.16103643972576</v>
       </c>
       <c r="D116" t="n">
-        <v>13.7747319546967</v>
+        <v>13.77473102080758</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059133128809</v>
+        <v>13.94059038615415</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.99873447418213</v>
+        <v>14.9987325668335</v>
       </c>
       <c r="C118" t="n">
-        <v>15.01133190380011</v>
+        <v>15.01132999484949</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36049014310408</v>
+        <v>14.36048831691926</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36049014310408</v>
+        <v>14.36048831691926</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801605224609</v>
+        <v>15.06801414489746</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127963560127</v>
+        <v>15.22127770885214</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92945082288267</v>
+        <v>14.92944893307399</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127963560127</v>
+        <v>15.22127770885214</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2832,16 +2832,16 @@
         <v>44404</v>
       </c>
       <c r="B121" t="n">
-        <v>14.54943943023682</v>
+        <v>14.54944038391113</v>
       </c>
       <c r="C121" t="n">
-        <v>15.05961489326427</v>
+        <v>15.05961588037913</v>
       </c>
       <c r="D121" t="n">
-        <v>14.45076419245981</v>
+        <v>14.45076513966624</v>
       </c>
       <c r="E121" t="n">
-        <v>14.87486022024207</v>
+        <v>14.87486119524679</v>
       </c>
       <c r="F121" t="n">
         <v>2070206</v>
@@ -2852,16 +2852,16 @@
         <v>44405</v>
       </c>
       <c r="B122" t="n">
-        <v>15.08691120147705</v>
+        <v>15.08691024780273</v>
       </c>
       <c r="C122" t="n">
-        <v>15.36824185204953</v>
+        <v>15.36824088059173</v>
       </c>
       <c r="D122" t="n">
-        <v>14.03716667235407</v>
+        <v>14.03716578503624</v>
       </c>
       <c r="E122" t="n">
-        <v>15.13519836525918</v>
+        <v>15.13519740853254</v>
       </c>
       <c r="F122" t="n">
         <v>6581198</v>
@@ -2872,16 +2872,16 @@
         <v>44406</v>
       </c>
       <c r="B123" t="n">
-        <v>15.28425884246826</v>
+        <v>15.28426361083984</v>
       </c>
       <c r="C123" t="n">
-        <v>15.32414879589132</v>
+        <v>15.32415357670774</v>
       </c>
       <c r="D123" t="n">
-        <v>14.85386493254062</v>
+        <v>14.85386956663824</v>
       </c>
       <c r="E123" t="n">
-        <v>15.09950417765391</v>
+        <v>15.09950888838588</v>
       </c>
       <c r="F123" t="n">
         <v>6067903</v>
@@ -2912,16 +2912,16 @@
         <v>44410</v>
       </c>
       <c r="B125" t="n">
-        <v>15.31785297393799</v>
+        <v>15.31785106658936</v>
       </c>
       <c r="C125" t="n">
-        <v>15.85742193931368</v>
+        <v>15.85741996477899</v>
       </c>
       <c r="D125" t="n">
-        <v>15.1687896416575</v>
+        <v>15.16878775286993</v>
       </c>
       <c r="E125" t="n">
-        <v>15.64327379365431</v>
+        <v>15.64327184578493</v>
       </c>
       <c r="F125" t="n">
         <v>3314925</v>
@@ -2932,16 +2932,16 @@
         <v>44411</v>
       </c>
       <c r="B126" t="n">
-        <v>15.20448207855225</v>
+        <v>15.20448112487793</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39343538308269</v>
+        <v>15.39343441755661</v>
       </c>
       <c r="D126" t="n">
-        <v>14.76149065149246</v>
+        <v>14.761489725604</v>
       </c>
       <c r="E126" t="n">
-        <v>15.39343538308269</v>
+        <v>15.39343441755661</v>
       </c>
       <c r="F126" t="n">
         <v>3496971</v>
@@ -2972,16 +2972,16 @@
         <v>44413</v>
       </c>
       <c r="B128" t="n">
-        <v>14.17153358459473</v>
+        <v>14.17153453826904</v>
       </c>
       <c r="C128" t="n">
-        <v>14.82237357326046</v>
+        <v>14.82237457073309</v>
       </c>
       <c r="D128" t="n">
-        <v>14.17153358459473</v>
+        <v>14.17153453826904</v>
       </c>
       <c r="E128" t="n">
-        <v>14.61662426223638</v>
+        <v>14.61662524586311</v>
       </c>
       <c r="F128" t="n">
         <v>2928535</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.93639087677002</v>
+        <v>13.93639183044434</v>
       </c>
       <c r="C129" t="n">
-        <v>14.4192722130578</v>
+        <v>14.41927319977593</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373549436386</v>
+        <v>13.75373643553897</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153364330989</v>
+        <v>14.17153461307515</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06656074523926</v>
+        <v>14.06655979156494</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893809899156</v>
+        <v>14.15893713905431</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462191733692</v>
+        <v>13.81462098074336</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351724825013</v>
+        <v>13.83351631037553</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3052,16 +3052,16 @@
         <v>44419</v>
       </c>
       <c r="B132" t="n">
-        <v>13.82511901855469</v>
+        <v>13.82511806488037</v>
       </c>
       <c r="C132" t="n">
-        <v>13.86710827889121</v>
+        <v>13.86710732232042</v>
       </c>
       <c r="D132" t="n">
-        <v>13.6340647992043</v>
+        <v>13.63406385870915</v>
       </c>
       <c r="E132" t="n">
-        <v>13.64666222674088</v>
+        <v>13.64666128537674</v>
       </c>
       <c r="F132" t="n">
         <v>1882485</v>
@@ -3092,16 +3092,16 @@
         <v>44421</v>
       </c>
       <c r="B134" t="n">
-        <v>12.95593070983887</v>
+        <v>12.95593166351318</v>
       </c>
       <c r="C134" t="n">
-        <v>13.76423290704215</v>
+        <v>13.76423392021486</v>
       </c>
       <c r="D134" t="n">
-        <v>12.78797285545454</v>
+        <v>12.78797379676563</v>
       </c>
       <c r="E134" t="n">
-        <v>13.5710801973981</v>
+        <v>13.57108119635301</v>
       </c>
       <c r="F134" t="n">
         <v>3730102</v>
@@ -3112,16 +3112,16 @@
         <v>44424</v>
       </c>
       <c r="B135" t="n">
-        <v>11.84110355377197</v>
+        <v>11.84110260009766</v>
       </c>
       <c r="C135" t="n">
-        <v>12.94963251110049</v>
+        <v>12.94963146814602</v>
       </c>
       <c r="D135" t="n">
-        <v>11.76552223690275</v>
+        <v>11.7655212893157</v>
       </c>
       <c r="E135" t="n">
-        <v>12.94963251110049</v>
+        <v>12.94963146814602</v>
       </c>
       <c r="F135" t="n">
         <v>7844263</v>
@@ -3132,16 +3132,16 @@
         <v>44425</v>
       </c>
       <c r="B136" t="n">
-        <v>12.27779674530029</v>
+        <v>12.27779769897461</v>
       </c>
       <c r="C136" t="n">
-        <v>12.78167271978735</v>
+        <v>12.78167371260009</v>
       </c>
       <c r="D136" t="n">
-        <v>11.42960381681197</v>
+        <v>11.42960470460314</v>
       </c>
       <c r="E136" t="n">
-        <v>11.66474658767486</v>
+        <v>11.66474749373068</v>
       </c>
       <c r="F136" t="n">
         <v>5635292</v>
@@ -3192,16 +3192,16 @@
         <v>44428</v>
       </c>
       <c r="B139" t="n">
-        <v>13.52069282531738</v>
+        <v>13.5206937789917</v>
       </c>
       <c r="C139" t="n">
-        <v>13.70544751914833</v>
+        <v>13.70544848585422</v>
       </c>
       <c r="D139" t="n">
-        <v>12.6473066309372</v>
+        <v>12.64730752300772</v>
       </c>
       <c r="E139" t="n">
-        <v>12.8068672814836</v>
+        <v>12.80686818480864</v>
       </c>
       <c r="F139" t="n">
         <v>3576438</v>
@@ -3232,16 +3232,16 @@
         <v>44432</v>
       </c>
       <c r="B141" t="n">
-        <v>13.63826465606689</v>
+        <v>13.63826560974121</v>
       </c>
       <c r="C141" t="n">
-        <v>13.92379389167463</v>
+        <v>13.92379486531496</v>
       </c>
       <c r="D141" t="n">
-        <v>13.37792783946889</v>
+        <v>13.3779287749388</v>
       </c>
       <c r="E141" t="n">
-        <v>13.63826465606689</v>
+        <v>13.63826560974121</v>
       </c>
       <c r="F141" t="n">
         <v>2525015</v>
@@ -3252,16 +3252,16 @@
         <v>44433</v>
       </c>
       <c r="B142" t="n">
-        <v>13.47870349884033</v>
+        <v>13.47870254516602</v>
       </c>
       <c r="C142" t="n">
-        <v>13.57947804789503</v>
+        <v>13.57947708709049</v>
       </c>
       <c r="D142" t="n">
-        <v>13.05040801228251</v>
+        <v>13.05040708891188</v>
       </c>
       <c r="E142" t="n">
-        <v>13.44511144129242</v>
+        <v>13.44511048999488</v>
       </c>
       <c r="F142" t="n">
         <v>2709595</v>
@@ -3272,16 +3272,16 @@
         <v>44434</v>
       </c>
       <c r="B143" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C143" t="n">
-        <v>13.76423335318433</v>
+        <v>13.76423235313817</v>
       </c>
       <c r="D143" t="n">
-        <v>12.82366381794241</v>
+        <v>12.82366288623372</v>
       </c>
       <c r="E143" t="n">
-        <v>13.47870409850207</v>
+        <v>13.47870311920116</v>
       </c>
       <c r="F143" t="n">
         <v>2624147</v>
@@ -3312,16 +3312,16 @@
         <v>44438</v>
       </c>
       <c r="B145" t="n">
-        <v>13.34433650970459</v>
+        <v>13.34433555603027</v>
       </c>
       <c r="C145" t="n">
-        <v>14.09175331983246</v>
+        <v>14.09175231274281</v>
       </c>
       <c r="D145" t="n">
-        <v>13.24356114561362</v>
+        <v>13.24356019914138</v>
       </c>
       <c r="E145" t="n">
-        <v>13.68865186346858</v>
+        <v>13.68865088518722</v>
       </c>
       <c r="F145" t="n">
         <v>1186841</v>
@@ -3372,16 +3372,16 @@
         <v>44441</v>
       </c>
       <c r="B148" t="n">
-        <v>12.80686664581299</v>
+        <v>12.80686855316162</v>
       </c>
       <c r="C148" t="n">
-        <v>13.18477402914559</v>
+        <v>13.18477599277661</v>
       </c>
       <c r="D148" t="n">
-        <v>12.69769408725448</v>
+        <v>12.69769597834385</v>
       </c>
       <c r="E148" t="n">
-        <v>13.06720345657573</v>
+        <v>13.06720540269677</v>
       </c>
       <c r="F148" t="n">
         <v>2514879</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00001949529792</v>
+        <v>13.00002039001773</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113085479707</v>
+        <v>13.36113177437019</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3432,16 +3432,16 @@
         <v>44447</v>
       </c>
       <c r="B151" t="n">
-        <v>13.23516178131104</v>
+        <v>13.23516273498535</v>
       </c>
       <c r="C151" t="n">
-        <v>14.67960797812228</v>
+        <v>14.67960903587777</v>
       </c>
       <c r="D151" t="n">
-        <v>13.10079437229357</v>
+        <v>13.10079531628589</v>
       </c>
       <c r="E151" t="n">
-        <v>13.80622103720047</v>
+        <v>13.80622203202309</v>
       </c>
       <c r="F151" t="n">
         <v>4568970</v>
@@ -3452,16 +3452,16 @@
         <v>44448</v>
       </c>
       <c r="B152" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C152" t="n">
-        <v>13.3779287331694</v>
+        <v>13.37792776119036</v>
       </c>
       <c r="D152" t="n">
-        <v>12.52973573670498</v>
+        <v>12.52973482635177</v>
       </c>
       <c r="E152" t="n">
-        <v>13.2183672645125</v>
+        <v>13.21836630412647</v>
       </c>
       <c r="F152" t="n">
         <v>3739731</v>
@@ -3512,16 +3512,16 @@
         <v>44453</v>
       </c>
       <c r="B155" t="n">
-        <v>13.55428504943848</v>
+        <v>13.55428600311279</v>
       </c>
       <c r="C155" t="n">
-        <v>14.04976384781166</v>
+        <v>14.04976483634768</v>
       </c>
       <c r="D155" t="n">
-        <v>13.27715300528965</v>
+        <v>13.27715393946506</v>
       </c>
       <c r="E155" t="n">
-        <v>13.43671365779501</v>
+        <v>13.43671460319705</v>
       </c>
       <c r="F155" t="n">
         <v>1943200</v>
@@ -3552,16 +3552,16 @@
         <v>44455</v>
       </c>
       <c r="B157" t="n">
-        <v>13.56268310546875</v>
+        <v>13.56268215179443</v>
       </c>
       <c r="C157" t="n">
-        <v>13.78942787491819</v>
+        <v>13.78942690530008</v>
       </c>
       <c r="D157" t="n">
-        <v>13.33593833601931</v>
+        <v>13.33593739828879</v>
       </c>
       <c r="E157" t="n">
-        <v>13.47870377169347</v>
+        <v>13.47870282392425</v>
       </c>
       <c r="F157" t="n">
         <v>1227183</v>
@@ -3592,16 +3592,16 @@
         <v>44459</v>
       </c>
       <c r="B159" t="n">
-        <v>12.84885692596436</v>
+        <v>12.84885787963867</v>
       </c>
       <c r="C159" t="n">
-        <v>13.10919292918942</v>
+        <v>13.10919390218652</v>
       </c>
       <c r="D159" t="n">
-        <v>12.63051018168811</v>
+        <v>12.63051111915618</v>
       </c>
       <c r="E159" t="n">
-        <v>13.10919292918942</v>
+        <v>13.10919390218652</v>
       </c>
       <c r="F159" t="n">
         <v>1643373</v>
@@ -3612,16 +3612,16 @@
         <v>44460</v>
       </c>
       <c r="B160" t="n">
-        <v>13.52069282531738</v>
+        <v>13.5206937789917</v>
       </c>
       <c r="C160" t="n">
-        <v>13.64666222994559</v>
+        <v>13.64666319250508</v>
       </c>
       <c r="D160" t="n">
-        <v>12.8068672814836</v>
+        <v>12.80686818480864</v>
       </c>
       <c r="E160" t="n">
-        <v>12.9832247726809</v>
+        <v>12.98322568844521</v>
       </c>
       <c r="F160" t="n">
         <v>1911981</v>
@@ -3632,16 +3632,16 @@
         <v>44461</v>
       </c>
       <c r="B161" t="n">
-        <v>14.10015201568604</v>
+        <v>14.10015106201172</v>
       </c>
       <c r="C161" t="n">
-        <v>14.46126420721415</v>
+        <v>14.46126322911574</v>
       </c>
       <c r="D161" t="n">
-        <v>13.58787718531884</v>
+        <v>13.58787626629261</v>
       </c>
       <c r="E161" t="n">
-        <v>13.71384659221444</v>
+        <v>13.71384566466818</v>
       </c>
       <c r="F161" t="n">
         <v>3751489</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661125183105</v>
+        <v>13.85661220550537</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26810988418833</v>
+        <v>14.26811086618383</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141639771024</v>
+        <v>13.83141734965053</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733371488308</v>
+        <v>14.16733468994271</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3712,16 +3712,16 @@
         <v>44467</v>
       </c>
       <c r="B165" t="n">
-        <v>13.1679801940918</v>
+        <v>13.16797828674316</v>
       </c>
       <c r="C165" t="n">
-        <v>13.89020298046473</v>
+        <v>13.89020096850395</v>
       </c>
       <c r="D165" t="n">
-        <v>13.15118335251281</v>
+        <v>13.15118144759716</v>
       </c>
       <c r="E165" t="n">
-        <v>13.64666298397454</v>
+        <v>13.64666100728992</v>
       </c>
       <c r="F165" t="n">
         <v>3700200</v>
@@ -3772,16 +3772,16 @@
         <v>44470</v>
       </c>
       <c r="B168" t="n">
-        <v>12.78167343139648</v>
+        <v>12.78167247772217</v>
       </c>
       <c r="C168" t="n">
-        <v>13.1175923900122</v>
+        <v>13.11759141127408</v>
       </c>
       <c r="D168" t="n">
-        <v>12.00066457212668</v>
+        <v>12.00066367672549</v>
       </c>
       <c r="E168" t="n">
-        <v>12.65570483665877</v>
+        <v>12.6557038923833</v>
       </c>
       <c r="F168" t="n">
         <v>6332153</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498119354248</v>
+        <v>12.34498023986816</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366398204986</v>
+        <v>12.82366299139635</v>
       </c>
       <c r="D169" t="n">
-        <v>12.13503244542976</v>
+        <v>12.1350315079744</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288861542754</v>
+        <v>12.72288763255913</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14342975616455</v>
+        <v>12.14342880249023</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55492921366123</v>
+        <v>12.55492822767014</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027704898789</v>
+        <v>11.95027611048266</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337849210345</v>
+        <v>12.35337752194098</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3832,16 +3832,16 @@
         <v>44475</v>
       </c>
       <c r="B171" t="n">
-        <v>12.51294040679932</v>
+        <v>12.51294136047363</v>
       </c>
       <c r="C171" t="n">
-        <v>12.61371495943398</v>
+        <v>12.61371592078883</v>
       </c>
       <c r="D171" t="n">
-        <v>11.68154263551506</v>
+        <v>11.68154352582436</v>
       </c>
       <c r="E171" t="n">
-        <v>11.9418794671707</v>
+        <v>11.94188037732158</v>
       </c>
       <c r="F171" t="n">
         <v>5058241</v>
@@ -3912,16 +3912,16 @@
         <v>44482</v>
       </c>
       <c r="B175" t="n">
-        <v>13.12598991394043</v>
+        <v>13.12598896026611</v>
       </c>
       <c r="C175" t="n">
-        <v>13.34433667412699</v>
+        <v>13.34433570458859</v>
       </c>
       <c r="D175" t="n">
-        <v>12.83206264449757</v>
+        <v>12.83206171217867</v>
       </c>
       <c r="E175" t="n">
-        <v>12.83206264449757</v>
+        <v>12.83206171217867</v>
       </c>
       <c r="F175" t="n">
         <v>2244954</v>
@@ -3932,16 +3932,16 @@
         <v>44483</v>
       </c>
       <c r="B176" t="n">
-        <v>13.1679801940918</v>
+        <v>13.16797828674316</v>
       </c>
       <c r="C176" t="n">
-        <v>13.2939487938857</v>
+        <v>13.29394686829084</v>
       </c>
       <c r="D176" t="n">
-        <v>12.85725607846398</v>
+        <v>12.85725421612295</v>
       </c>
       <c r="E176" t="n">
-        <v>13.12599011963078</v>
+        <v>13.1259882183643</v>
       </c>
       <c r="F176" t="n">
         <v>1588233</v>
@@ -3952,16 +3952,16 @@
         <v>44484</v>
       </c>
       <c r="B177" t="n">
-        <v>13.4199161529541</v>
+        <v>13.41991806030273</v>
       </c>
       <c r="C177" t="n">
-        <v>13.4871002618162</v>
+        <v>13.48710217871359</v>
       </c>
       <c r="D177" t="n">
-        <v>13.08399885582139</v>
+        <v>13.0840007154267</v>
       </c>
       <c r="E177" t="n">
-        <v>13.24355949077998</v>
+        <v>13.24356137306336</v>
       </c>
       <c r="F177" t="n">
         <v>1650266</v>
@@ -3972,16 +3972,16 @@
         <v>44487</v>
       </c>
       <c r="B178" t="n">
-        <v>13.20157051086426</v>
+        <v>13.20157146453857</v>
       </c>
       <c r="C178" t="n">
-        <v>13.36952998506892</v>
+        <v>13.36953095087653</v>
       </c>
       <c r="D178" t="n">
-        <v>13.04200986275408</v>
+        <v>13.04201080490182</v>
       </c>
       <c r="E178" t="n">
-        <v>13.30234668246376</v>
+        <v>13.3023476434181</v>
       </c>
       <c r="F178" t="n">
         <v>1423013</v>
@@ -4012,16 +4012,16 @@
         <v>44489</v>
       </c>
       <c r="B180" t="n">
-        <v>11.98386859893799</v>
+        <v>11.9838695526123</v>
       </c>
       <c r="C180" t="n">
-        <v>12.58852073800141</v>
+        <v>12.58852173979385</v>
       </c>
       <c r="D180" t="n">
-        <v>11.874695228402</v>
+        <v>11.87469617338831</v>
       </c>
       <c r="E180" t="n">
-        <v>12.45415332538915</v>
+        <v>12.45415431648865</v>
       </c>
       <c r="F180" t="n">
         <v>2144403</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55621814727783</v>
+        <v>10.55621910095215</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650289901313</v>
+        <v>11.02650389517411</v>
       </c>
       <c r="D183" t="n">
-        <v>10.35466742342063</v>
+        <v>10.35466835888637</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699350920643</v>
+        <v>10.65699447198504</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4112,16 +4112,16 @@
         <v>44496</v>
       </c>
       <c r="B185" t="n">
-        <v>10.32947444915771</v>
+        <v>10.32947254180908</v>
       </c>
       <c r="C185" t="n">
-        <v>10.573014458813</v>
+        <v>10.57301250649444</v>
       </c>
       <c r="D185" t="n">
-        <v>9.976761051796744</v>
+        <v>9.976759209577022</v>
       </c>
       <c r="E185" t="n">
-        <v>10.07753561236163</v>
+        <v>10.07753375153378</v>
       </c>
       <c r="F185" t="n">
         <v>4005501</v>
@@ -4132,16 +4132,16 @@
         <v>44497</v>
       </c>
       <c r="B186" t="n">
-        <v>9.909576416015625</v>
+        <v>9.909575462341309</v>
       </c>
       <c r="C186" t="n">
-        <v>10.43864644132597</v>
+        <v>10.4386454367352</v>
       </c>
       <c r="D186" t="n">
-        <v>9.825596273781114</v>
+        <v>9.82559532818885</v>
       </c>
       <c r="E186" t="n">
-        <v>10.25389175199907</v>
+        <v>10.25389076518866</v>
       </c>
       <c r="F186" t="n">
         <v>4167680</v>
@@ -4152,16 +4152,16 @@
         <v>44498</v>
       </c>
       <c r="B187" t="n">
-        <v>9.514873504638672</v>
+        <v>9.514872550964355</v>
       </c>
       <c r="C187" t="n">
-        <v>10.06913760232501</v>
+        <v>10.06913659309689</v>
       </c>
       <c r="D187" t="n">
-        <v>9.069781974119245</v>
+        <v>9.069781065056384</v>
       </c>
       <c r="E187" t="n">
-        <v>10.06913760232501</v>
+        <v>10.06913659309689</v>
       </c>
       <c r="F187" t="n">
         <v>8163450</v>
@@ -4172,16 +4172,16 @@
         <v>44501</v>
       </c>
       <c r="B188" t="n">
-        <v>9.464485168457031</v>
+        <v>9.464484214782715</v>
       </c>
       <c r="C188" t="n">
-        <v>9.817198528320054</v>
+        <v>9.817197539105118</v>
       </c>
       <c r="D188" t="n">
-        <v>9.002597620700316</v>
+        <v>9.002596713567389</v>
       </c>
       <c r="E188" t="n">
-        <v>9.220944372898632</v>
+        <v>9.22094344376433</v>
       </c>
       <c r="F188" t="n">
         <v>8542036</v>
@@ -4192,16 +4192,16 @@
         <v>44503</v>
       </c>
       <c r="B189" t="n">
-        <v>10.14471817016602</v>
+        <v>10.14471912384033</v>
       </c>
       <c r="C189" t="n">
-        <v>10.29588079948901</v>
+        <v>10.29588176737367</v>
       </c>
       <c r="D189" t="n">
-        <v>9.548463231541206</v>
+        <v>9.548464129163397</v>
       </c>
       <c r="E189" t="n">
-        <v>9.657637414199865</v>
+        <v>9.657638322085189</v>
       </c>
       <c r="F189" t="n">
         <v>6020061</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55621814727783</v>
+        <v>10.55621910095215</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771679767463</v>
+        <v>10.96771778852473</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588132208213</v>
+        <v>10.29588225223699</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64019748025258</v>
+        <v>10.64019844151379</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.74936962127686</v>
+        <v>10.74937057495117</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324637301136</v>
+        <v>11.25324737138916</v>
       </c>
       <c r="D193" t="n">
-        <v>10.4050543144717</v>
+        <v>10.40505523759868</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660420337106</v>
+        <v>10.60660514437936</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4292,16 +4292,16 @@
         <v>44510</v>
       </c>
       <c r="B194" t="n">
-        <v>10.66539096832275</v>
+        <v>10.66539287567139</v>
       </c>
       <c r="C194" t="n">
-        <v>11.16926775172825</v>
+        <v>11.16926974918785</v>
       </c>
       <c r="D194" t="n">
-        <v>10.44704422688129</v>
+        <v>10.44704609518181</v>
       </c>
       <c r="E194" t="n">
-        <v>10.74937029692459</v>
+        <v>10.74937221929169</v>
       </c>
       <c r="F194" t="n">
         <v>2771222</v>
@@ -4312,16 +4312,16 @@
         <v>44511</v>
       </c>
       <c r="B195" t="n">
-        <v>11.21965503692627</v>
+        <v>11.21965599060059</v>
       </c>
       <c r="C195" t="n">
-        <v>11.53037912136244</v>
+        <v>11.5303801014484</v>
       </c>
       <c r="D195" t="n">
-        <v>10.69058502259491</v>
+        <v>10.69058593129811</v>
       </c>
       <c r="E195" t="n">
-        <v>10.7829615535469</v>
+        <v>10.78296247010213</v>
       </c>
       <c r="F195" t="n">
         <v>2903296</v>
@@ -4332,16 +4332,16 @@
         <v>44512</v>
       </c>
       <c r="B196" t="n">
-        <v>10.75776767730713</v>
+        <v>10.75776863098145</v>
       </c>
       <c r="C196" t="n">
-        <v>11.50518525664944</v>
+        <v>11.5051862765822</v>
       </c>
       <c r="D196" t="n">
-        <v>10.70738040402947</v>
+        <v>10.70738135323696</v>
       </c>
       <c r="E196" t="n">
-        <v>11.19446197921575</v>
+        <v>11.19446297160295</v>
       </c>
       <c r="F196" t="n">
         <v>1618134</v>
@@ -4352,16 +4352,16 @@
         <v>44516</v>
       </c>
       <c r="B197" t="n">
-        <v>10.16991233825684</v>
+        <v>10.16991329193115</v>
       </c>
       <c r="C197" t="n">
-        <v>10.85854381637763</v>
+        <v>10.85854483462774</v>
       </c>
       <c r="D197" t="n">
-        <v>10.10272822501953</v>
+        <v>10.10272917239372</v>
       </c>
       <c r="E197" t="n">
-        <v>10.85854381637763</v>
+        <v>10.85854483462774</v>
       </c>
       <c r="F197" t="n">
         <v>2296952</v>
@@ -4372,16 +4372,16 @@
         <v>44517</v>
       </c>
       <c r="B198" t="n">
-        <v>10.10272789001465</v>
+        <v>10.10272884368896</v>
       </c>
       <c r="C198" t="n">
-        <v>10.35466668271126</v>
+        <v>10.35466766016802</v>
       </c>
       <c r="D198" t="n">
-        <v>9.800402637649874</v>
+        <v>9.800403562785382</v>
       </c>
       <c r="E198" t="n">
-        <v>10.29588058557796</v>
+        <v>10.29588155748545</v>
       </c>
       <c r="F198" t="n">
         <v>3557179</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674433708190918</v>
+        <v>9.674434661865234</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34626916814729</v>
+        <v>10.34627018804897</v>
       </c>
       <c r="D202" t="n">
-        <v>9.48128100330603</v>
+        <v>9.481281937939977</v>
       </c>
       <c r="E202" t="n">
-        <v>10.28748306817697</v>
+        <v>10.2874840822837</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4472,16 +4472,16 @@
         <v>44524</v>
       </c>
       <c r="B203" t="n">
-        <v>9.699628829956055</v>
+        <v>9.699627876281738</v>
       </c>
       <c r="C203" t="n">
-        <v>10.11952634355827</v>
+        <v>10.11952534859934</v>
       </c>
       <c r="D203" t="n">
-        <v>9.380506687146584</v>
+        <v>9.38050576484858</v>
       </c>
       <c r="E203" t="n">
-        <v>9.842393465032259</v>
+        <v>9.842392497321224</v>
       </c>
       <c r="F203" t="n">
         <v>3236370</v>
@@ -4512,16 +4512,16 @@
         <v>44526</v>
       </c>
       <c r="B205" t="n">
-        <v>9.472881317138672</v>
+        <v>9.472882270812988</v>
       </c>
       <c r="C205" t="n">
-        <v>9.682830031524192</v>
+        <v>9.682831006334919</v>
       </c>
       <c r="D205" t="n">
-        <v>9.178953279357833</v>
+        <v>9.178954203441192</v>
       </c>
       <c r="E205" t="n">
-        <v>9.657636802761706</v>
+        <v>9.657637775036125</v>
       </c>
       <c r="F205" t="n">
         <v>2092506</v>
@@ -4612,16 +4612,16 @@
         <v>44533</v>
       </c>
       <c r="B210" t="n">
-        <v>9.901178359985352</v>
+        <v>9.901177406311035</v>
       </c>
       <c r="C210" t="n">
-        <v>10.0859338754747</v>
+        <v>10.08593290400486</v>
       </c>
       <c r="D210" t="n">
-        <v>9.615648289566654</v>
+        <v>9.615647363394388</v>
       </c>
       <c r="E210" t="n">
-        <v>9.649240349072821</v>
+        <v>9.649239419664992</v>
       </c>
       <c r="F210" t="n">
         <v>1913704</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884382247924805</v>
+        <v>9.884383201599121</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709559365621</v>
+        <v>10.23709658136135</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573657349188849</v>
+        <v>9.573658272883511</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867585407896522</v>
+        <v>9.867586359950231</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4692,16 +4692,16 @@
         <v>44539</v>
       </c>
       <c r="B214" t="n">
-        <v>10.78222942352295</v>
+        <v>10.78222846984863</v>
       </c>
       <c r="C214" t="n">
-        <v>11.00401677853015</v>
+        <v>11.00401580523902</v>
       </c>
       <c r="D214" t="n">
-        <v>10.23629341206293</v>
+        <v>10.23629250667595</v>
       </c>
       <c r="E214" t="n">
-        <v>10.46661108166976</v>
+        <v>10.46661015591148</v>
       </c>
       <c r="F214" t="n">
         <v>2489235</v>
@@ -4732,16 +4732,16 @@
         <v>44543</v>
       </c>
       <c r="B216" t="n">
-        <v>11.19168281555176</v>
+        <v>11.19168186187744</v>
       </c>
       <c r="C216" t="n">
-        <v>11.55848307007503</v>
+        <v>11.55848208514464</v>
       </c>
       <c r="D216" t="n">
-        <v>11.13197060927274</v>
+        <v>11.13196966068666</v>
       </c>
       <c r="E216" t="n">
-        <v>11.2599245124301</v>
+        <v>11.25992355294072</v>
       </c>
       <c r="F216" t="n">
         <v>3334589</v>
@@ -4752,16 +4752,16 @@
         <v>44544</v>
       </c>
       <c r="B217" t="n">
-        <v>11.11490726470947</v>
+        <v>11.11490917205811</v>
       </c>
       <c r="C217" t="n">
-        <v>11.43905668874708</v>
+        <v>11.43905865172065</v>
       </c>
       <c r="D217" t="n">
-        <v>10.91871171258361</v>
+        <v>10.91871358626455</v>
       </c>
       <c r="E217" t="n">
-        <v>11.25992176282055</v>
+        <v>11.25992369505407</v>
       </c>
       <c r="F217" t="n">
         <v>1511299</v>
@@ -4772,16 +4772,16 @@
         <v>44545</v>
       </c>
       <c r="B218" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845264434814</v>
       </c>
       <c r="C218" t="n">
-        <v>11.37934603413065</v>
+        <v>11.37934507107126</v>
       </c>
       <c r="D218" t="n">
-        <v>10.8163502410046</v>
+        <v>10.8163493255928</v>
       </c>
       <c r="E218" t="n">
-        <v>10.90165255894037</v>
+        <v>10.90165163630924</v>
       </c>
       <c r="F218" t="n">
         <v>3122034</v>
@@ -4792,16 +4792,16 @@
         <v>44546</v>
       </c>
       <c r="B219" t="n">
-        <v>11.14049911499023</v>
+        <v>11.14049816131592</v>
       </c>
       <c r="C219" t="n">
-        <v>11.49023953281247</v>
+        <v>11.49023854919888</v>
       </c>
       <c r="D219" t="n">
-        <v>10.85900203718004</v>
+        <v>10.85900110760307</v>
       </c>
       <c r="E219" t="n">
-        <v>11.3964068986813</v>
+        <v>11.39640592310018</v>
       </c>
       <c r="F219" t="n">
         <v>2253468</v>
@@ -4832,16 +4832,16 @@
         <v>44550</v>
       </c>
       <c r="B221" t="n">
-        <v>10.92724227905273</v>
+        <v>10.92724323272705</v>
       </c>
       <c r="C221" t="n">
-        <v>11.08931741935155</v>
+        <v>11.08931838717097</v>
       </c>
       <c r="D221" t="n">
-        <v>10.64574521732745</v>
+        <v>10.64574614643413</v>
       </c>
       <c r="E221" t="n">
-        <v>10.83341047486649</v>
+        <v>10.83341142035164</v>
       </c>
       <c r="F221" t="n">
         <v>2144606</v>
@@ -4952,16 +4952,16 @@
         <v>44559</v>
       </c>
       <c r="B227" t="n">
-        <v>9.715948104858398</v>
+        <v>9.715949058532715</v>
       </c>
       <c r="C227" t="n">
-        <v>10.21923248819867</v>
+        <v>10.21923349127314</v>
       </c>
       <c r="D227" t="n">
-        <v>9.596524538126543</v>
+        <v>9.596525480078773</v>
       </c>
       <c r="E227" t="n">
-        <v>10.21923248819867</v>
+        <v>10.21923349127314</v>
       </c>
       <c r="F227" t="n">
         <v>1535423</v>
@@ -5012,16 +5012,16 @@
         <v>44565</v>
       </c>
       <c r="B230" t="n">
-        <v>9.238255500793457</v>
+        <v>9.238256454467773</v>
       </c>
       <c r="C230" t="n">
-        <v>9.826842249612479</v>
+        <v>9.826843264047191</v>
       </c>
       <c r="D230" t="n">
-        <v>9.170012985278218</v>
+        <v>9.170013931907791</v>
       </c>
       <c r="E230" t="n">
-        <v>9.75859973409724</v>
+        <v>9.758600741487211</v>
       </c>
       <c r="F230" t="n">
         <v>4143150</v>
@@ -5032,16 +5032,16 @@
         <v>44566</v>
       </c>
       <c r="B231" t="n">
-        <v>8.530243873596191</v>
+        <v>8.530244827270508</v>
       </c>
       <c r="C231" t="n">
-        <v>9.255314788383105</v>
+        <v>9.255315823119759</v>
       </c>
       <c r="D231" t="n">
-        <v>8.479062814400418</v>
+        <v>8.479063762352734</v>
       </c>
       <c r="E231" t="n">
-        <v>9.255314788383105</v>
+        <v>9.255315823119759</v>
       </c>
       <c r="F231" t="n">
         <v>5451524</v>
@@ -5052,16 +5052,16 @@
         <v>44567</v>
       </c>
       <c r="B232" t="n">
-        <v>8.948225021362305</v>
+        <v>8.948225975036621</v>
       </c>
       <c r="C232" t="n">
-        <v>8.948225021362305</v>
+        <v>8.948225975036621</v>
       </c>
       <c r="D232" t="n">
-        <v>8.393759619383555</v>
+        <v>8.393760513964654</v>
       </c>
       <c r="E232" t="n">
-        <v>8.547304430040395</v>
+        <v>8.547305340985826</v>
       </c>
       <c r="F232" t="n">
         <v>4969753</v>
@@ -5132,16 +5132,16 @@
         <v>44573</v>
       </c>
       <c r="B236" t="n">
-        <v>9.221194267272949</v>
+        <v>9.221193313598633</v>
       </c>
       <c r="C236" t="n">
-        <v>9.408860364832703</v>
+        <v>9.408859391749584</v>
       </c>
       <c r="D236" t="n">
-        <v>8.64113781905797</v>
+        <v>8.64113692537425</v>
       </c>
       <c r="E236" t="n">
-        <v>8.914106238463063</v>
+        <v>8.914105316548403</v>
       </c>
       <c r="F236" t="n">
         <v>2757539</v>
@@ -5212,16 +5212,16 @@
         <v>44579</v>
       </c>
       <c r="B240" t="n">
-        <v>8.308457374572754</v>
+        <v>8.30845832824707</v>
       </c>
       <c r="C240" t="n">
-        <v>8.76056154167938</v>
+        <v>8.760562547247821</v>
       </c>
       <c r="D240" t="n">
-        <v>8.206094431414945</v>
+        <v>8.206095373339679</v>
       </c>
       <c r="E240" t="n">
-        <v>8.530243888845217</v>
+        <v>8.530244867976979</v>
       </c>
       <c r="F240" t="n">
         <v>2291580</v>
@@ -5252,16 +5252,16 @@
         <v>44581</v>
       </c>
       <c r="B242" t="n">
-        <v>9.383269309997559</v>
+        <v>9.383268356323242</v>
       </c>
       <c r="C242" t="n">
-        <v>9.656236901592942</v>
+        <v>9.6562359201754</v>
       </c>
       <c r="D242" t="n">
-        <v>8.530244452459904</v>
+        <v>8.530243585483291</v>
       </c>
       <c r="E242" t="n">
-        <v>8.581426339712161</v>
+        <v>8.581425467533645</v>
       </c>
       <c r="F242" t="n">
         <v>5361414</v>
@@ -5552,16 +5552,16 @@
         <v>44602</v>
       </c>
       <c r="B257" t="n">
-        <v>9.997446060180664</v>
+        <v>9.99744701385498</v>
       </c>
       <c r="C257" t="n">
-        <v>10.38130687978837</v>
+        <v>10.38130787007986</v>
       </c>
       <c r="D257" t="n">
-        <v>9.920674061175772</v>
+        <v>9.92067500752667</v>
       </c>
       <c r="E257" t="n">
-        <v>10.36424625232434</v>
+        <v>10.36424724098838</v>
       </c>
       <c r="F257" t="n">
         <v>2000064</v>
@@ -5572,16 +5572,16 @@
         <v>44603</v>
       </c>
       <c r="B258" t="n">
-        <v>9.929203987121582</v>
+        <v>9.929204940795898</v>
       </c>
       <c r="C258" t="n">
-        <v>10.31306396715434</v>
+        <v>10.31306495769742</v>
       </c>
       <c r="D258" t="n">
-        <v>9.647705294125526</v>
+        <v>9.647706220762624</v>
       </c>
       <c r="E258" t="n">
-        <v>9.99744566972927</v>
+        <v>9.997446629958024</v>
       </c>
       <c r="F258" t="n">
         <v>2967053</v>
@@ -5632,16 +5632,16 @@
         <v>44608</v>
       </c>
       <c r="B261" t="n">
-        <v>10.56897354125977</v>
+        <v>10.56897258758545</v>
       </c>
       <c r="C261" t="n">
-        <v>10.69692660514308</v>
+        <v>10.69692563992313</v>
       </c>
       <c r="D261" t="n">
-        <v>10.38983859215648</v>
+        <v>10.38983765464612</v>
       </c>
       <c r="E261" t="n">
-        <v>10.66280534832977</v>
+        <v>10.66280438618869</v>
       </c>
       <c r="F261" t="n">
         <v>4241775</v>
@@ -5692,16 +5692,16 @@
         <v>44613</v>
       </c>
       <c r="B264" t="n">
-        <v>9.383269309997559</v>
+        <v>9.383268356323242</v>
       </c>
       <c r="C264" t="n">
-        <v>10.193642594825</v>
+        <v>10.1936415587879</v>
       </c>
       <c r="D264" t="n">
-        <v>9.263846555575617</v>
+        <v>9.263845614038905</v>
       </c>
       <c r="E264" t="n">
-        <v>10.06568952586101</v>
+        <v>10.0656885028285</v>
       </c>
       <c r="F264" t="n">
         <v>2949517</v>
@@ -5712,16 +5712,16 @@
         <v>44614</v>
       </c>
       <c r="B265" t="n">
-        <v>9.73300838470459</v>
+        <v>9.733009338378906</v>
       </c>
       <c r="C265" t="n">
-        <v>9.843902467790201</v>
+        <v>9.843903432330309</v>
       </c>
       <c r="D265" t="n">
-        <v>9.391799119697389</v>
+        <v>9.391800039938824</v>
       </c>
       <c r="E265" t="n">
-        <v>9.545343124033971</v>
+        <v>9.545344059320188</v>
       </c>
       <c r="F265" t="n">
         <v>6936571</v>
@@ -5732,16 +5732,16 @@
         <v>44615</v>
       </c>
       <c r="B266" t="n">
-        <v>9.767129898071289</v>
+        <v>9.767128944396973</v>
       </c>
       <c r="C266" t="n">
-        <v>10.11687031094908</v>
+        <v>10.11686932312569</v>
       </c>
       <c r="D266" t="n">
-        <v>9.681827579574664</v>
+        <v>9.68182663422937</v>
       </c>
       <c r="E266" t="n">
-        <v>9.775661036962589</v>
+        <v>9.775660082455282</v>
       </c>
       <c r="F266" t="n">
         <v>2319860</v>
@@ -5752,16 +5752,16 @@
         <v>44616</v>
       </c>
       <c r="B267" t="n">
-        <v>9.784191131591797</v>
+        <v>9.78419017791748</v>
       </c>
       <c r="C267" t="n">
-        <v>9.886554085032964</v>
+        <v>9.886553121381233</v>
       </c>
       <c r="D267" t="n">
-        <v>9.15295278127404</v>
+        <v>9.15295188912712</v>
       </c>
       <c r="E267" t="n">
-        <v>9.15295278127404</v>
+        <v>9.15295188912712</v>
       </c>
       <c r="F267" t="n">
         <v>2513764</v>
@@ -5772,16 +5772,16 @@
         <v>44617</v>
       </c>
       <c r="B268" t="n">
-        <v>9.425919532775879</v>
+        <v>9.425921440124512</v>
       </c>
       <c r="C268" t="n">
-        <v>9.86949170251933</v>
+        <v>9.869493699625441</v>
       </c>
       <c r="D268" t="n">
-        <v>9.383267966174003</v>
+        <v>9.383269864892029</v>
       </c>
       <c r="E268" t="n">
-        <v>9.579463523376209</v>
+        <v>9.579465461794694</v>
       </c>
       <c r="F268" t="n">
         <v>3597927</v>
@@ -5792,16 +5792,16 @@
         <v>44622</v>
       </c>
       <c r="B269" t="n">
-        <v>9.570934295654297</v>
+        <v>9.57093334197998</v>
       </c>
       <c r="C269" t="n">
-        <v>9.656236613950387</v>
+        <v>9.656235651776313</v>
       </c>
       <c r="D269" t="n">
-        <v>9.272375769326324</v>
+        <v>9.272374845401204</v>
       </c>
       <c r="E269" t="n">
-        <v>9.349147773334476</v>
+        <v>9.34914684175958</v>
       </c>
       <c r="F269" t="n">
         <v>1474809</v>
@@ -5812,16 +5812,16 @@
         <v>44623</v>
       </c>
       <c r="B270" t="n">
-        <v>9.639177322387695</v>
+        <v>9.639176368713379</v>
       </c>
       <c r="C270" t="n">
-        <v>10.15952157411429</v>
+        <v>10.15952056895851</v>
       </c>
       <c r="D270" t="n">
-        <v>9.562405314298255</v>
+        <v>9.562404368219553</v>
       </c>
       <c r="E270" t="n">
-        <v>9.860963031914597</v>
+        <v>9.860962056297398</v>
       </c>
       <c r="F270" t="n">
         <v>3265562</v>
@@ -5852,16 +5852,16 @@
         <v>44627</v>
       </c>
       <c r="B272" t="n">
-        <v>8.666728019714355</v>
+        <v>8.666728973388672</v>
       </c>
       <c r="C272" t="n">
-        <v>9.417389871825412</v>
+        <v>9.417390908101481</v>
       </c>
       <c r="D272" t="n">
-        <v>8.658197705803062</v>
+        <v>8.658198658538714</v>
       </c>
       <c r="E272" t="n">
-        <v>9.32355641880117</v>
+        <v>9.323557444751941</v>
       </c>
       <c r="F272" t="n">
         <v>2527651</v>
@@ -5872,16 +5872,16 @@
         <v>44628</v>
       </c>
       <c r="B273" t="n">
-        <v>8.897043228149414</v>
+        <v>8.89704418182373</v>
       </c>
       <c r="C273" t="n">
-        <v>8.922634167601151</v>
+        <v>8.92263512401856</v>
       </c>
       <c r="D273" t="n">
-        <v>8.521712747856723</v>
+        <v>8.521713661299355</v>
       </c>
       <c r="E273" t="n">
-        <v>8.726439438887422</v>
+        <v>8.726440374274713</v>
       </c>
       <c r="F273" t="n">
         <v>2260563</v>
@@ -5992,16 +5992,16 @@
         <v>44636</v>
       </c>
       <c r="B279" t="n">
-        <v>8.948225021362305</v>
+        <v>8.948225975036621</v>
       </c>
       <c r="C279" t="n">
-        <v>9.229723703469311</v>
+        <v>9.229724687144891</v>
       </c>
       <c r="D279" t="n">
-        <v>8.589955170801659</v>
+        <v>8.589956086292677</v>
       </c>
       <c r="E279" t="n">
-        <v>8.956755334431195</v>
+        <v>8.956756289014645</v>
       </c>
       <c r="F279" t="n">
         <v>2215964</v>
@@ -6012,16 +6012,16 @@
         <v>44637</v>
       </c>
       <c r="B280" t="n">
-        <v>9.238255500793457</v>
+        <v>9.238256454467773</v>
       </c>
       <c r="C280" t="n">
-        <v>9.297966052702654</v>
+        <v>9.297967012540948</v>
       </c>
       <c r="D280" t="n">
-        <v>8.632607298512305</v>
+        <v>8.632608189664953</v>
       </c>
       <c r="E280" t="n">
-        <v>8.999408345656759</v>
+        <v>8.999409274674644</v>
       </c>
       <c r="F280" t="n">
         <v>2645230</v>
@@ -6072,16 +6072,16 @@
         <v>44642</v>
       </c>
       <c r="B283" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C283" t="n">
-        <v>10.12539894068065</v>
+        <v>10.1253999073854</v>
       </c>
       <c r="D283" t="n">
-        <v>9.570933505254049</v>
+        <v>9.57093441902218</v>
       </c>
       <c r="E283" t="n">
-        <v>9.570933505254049</v>
+        <v>9.57093441902218</v>
       </c>
       <c r="F283" t="n">
         <v>2594043</v>
@@ -6112,16 +6112,16 @@
         <v>44644</v>
       </c>
       <c r="B285" t="n">
-        <v>10.53485107421875</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C285" t="n">
-        <v>10.66280412340302</v>
+        <v>10.66280605391772</v>
       </c>
       <c r="D285" t="n">
-        <v>10.11686902460604</v>
+        <v>10.11687085627847</v>
       </c>
       <c r="E285" t="n">
-        <v>10.27894415126702</v>
+        <v>10.27894601228337</v>
       </c>
       <c r="F285" t="n">
         <v>1712400</v>
@@ -6152,16 +6152,16 @@
         <v>44648</v>
       </c>
       <c r="B287" t="n">
-        <v>10.88459205627441</v>
+        <v>10.8845911026001</v>
       </c>
       <c r="C287" t="n">
-        <v>11.12343920892254</v>
+        <v>11.12343823432117</v>
       </c>
       <c r="D287" t="n">
-        <v>10.71398659384719</v>
+        <v>10.7139856551208</v>
       </c>
       <c r="E287" t="n">
-        <v>10.73957753689877</v>
+        <v>10.73957659593018</v>
       </c>
       <c r="F287" t="n">
         <v>1829574</v>
@@ -6232,16 +6232,16 @@
         <v>44652</v>
       </c>
       <c r="B291" t="n">
-        <v>11.24286270141602</v>
+        <v>11.24286365509033</v>
       </c>
       <c r="C291" t="n">
-        <v>11.25139219111963</v>
+        <v>11.25139314551746</v>
       </c>
       <c r="D291" t="n">
-        <v>10.77369871396854</v>
+        <v>10.77369962784609</v>
       </c>
       <c r="E291" t="n">
-        <v>10.96136397911421</v>
+        <v>10.96136490891043</v>
       </c>
       <c r="F291" t="n">
         <v>2500385</v>
@@ -6252,16 +6252,16 @@
         <v>44655</v>
       </c>
       <c r="B292" t="n">
-        <v>11.24286270141602</v>
+        <v>11.24286365509033</v>
       </c>
       <c r="C292" t="n">
-        <v>11.32816419511862</v>
+        <v>11.32816515602863</v>
       </c>
       <c r="D292" t="n">
-        <v>10.84194122826391</v>
+        <v>10.84194214793012</v>
       </c>
       <c r="E292" t="n">
-        <v>11.14903006884318</v>
+        <v>11.14903101455816</v>
       </c>
       <c r="F292" t="n">
         <v>2094330</v>
@@ -6272,16 +6272,16 @@
         <v>44656</v>
       </c>
       <c r="B293" t="n">
-        <v>10.76516914367676</v>
+        <v>10.76516819000244</v>
       </c>
       <c r="C293" t="n">
-        <v>11.22580284867232</v>
+        <v>11.22580185419098</v>
       </c>
       <c r="D293" t="n">
-        <v>10.66280618974256</v>
+        <v>10.66280524513646</v>
       </c>
       <c r="E293" t="n">
-        <v>11.18315127429</v>
+        <v>11.18315028358712</v>
       </c>
       <c r="F293" t="n">
         <v>1686452</v>
@@ -6312,16 +6312,16 @@
         <v>44658</v>
       </c>
       <c r="B295" t="n">
-        <v>10.53485107421875</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C295" t="n">
-        <v>10.67133443662639</v>
+        <v>10.67133636868552</v>
       </c>
       <c r="D295" t="n">
-        <v>10.38130626078115</v>
+        <v>10.38130814033029</v>
       </c>
       <c r="E295" t="n">
-        <v>10.50072982132524</v>
+        <v>10.50073172249617</v>
       </c>
       <c r="F295" t="n">
         <v>1517584</v>
@@ -6352,16 +6352,16 @@
         <v>44662</v>
       </c>
       <c r="B297" t="n">
-        <v>10.53485107421875</v>
+        <v>10.53485298156738</v>
       </c>
       <c r="C297" t="n">
-        <v>10.61162306864595</v>
+        <v>10.61162498989425</v>
       </c>
       <c r="D297" t="n">
-        <v>10.17658121716968</v>
+        <v>10.17658305965309</v>
       </c>
       <c r="E297" t="n">
-        <v>10.28747363990719</v>
+        <v>10.28747550246782</v>
       </c>
       <c r="F297" t="n">
         <v>2558465</v>
@@ -6372,16 +6372,16 @@
         <v>44663</v>
       </c>
       <c r="B298" t="n">
-        <v>10.55191135406494</v>
+        <v>10.55191230773926</v>
       </c>
       <c r="C298" t="n">
-        <v>10.90165173831644</v>
+        <v>10.90165272360005</v>
       </c>
       <c r="D298" t="n">
-        <v>10.40689767186506</v>
+        <v>10.40689861243314</v>
       </c>
       <c r="E298" t="n">
-        <v>10.44954841533075</v>
+        <v>10.44954935975358</v>
       </c>
       <c r="F298" t="n">
         <v>1608302</v>
@@ -6392,16 +6392,16 @@
         <v>44664</v>
       </c>
       <c r="B299" t="n">
-        <v>10.60309410095215</v>
+        <v>10.60309314727783</v>
       </c>
       <c r="C299" t="n">
-        <v>10.73104799095693</v>
+        <v>10.73104702577405</v>
       </c>
       <c r="D299" t="n">
-        <v>10.38130757816608</v>
+        <v>10.38130664443992</v>
       </c>
       <c r="E299" t="n">
-        <v>10.62015472956389</v>
+        <v>10.62015377435509</v>
       </c>
       <c r="F299" t="n">
         <v>1276242</v>
@@ -6552,16 +6552,16 @@
         <v>44678</v>
       </c>
       <c r="B307" t="n">
-        <v>10.60309410095215</v>
+        <v>10.60309314727783</v>
       </c>
       <c r="C307" t="n">
-        <v>10.79076019109803</v>
+        <v>10.79075922054446</v>
       </c>
       <c r="D307" t="n">
-        <v>10.4068985210837</v>
+        <v>10.40689758505581</v>
       </c>
       <c r="E307" t="n">
-        <v>10.4068985210837</v>
+        <v>10.40689758505581</v>
       </c>
       <c r="F307" t="n">
         <v>2204206</v>
@@ -6652,16 +6652,16 @@
         <v>44685</v>
       </c>
       <c r="B312" t="n">
-        <v>11.83144950866699</v>
+        <v>11.83144855499268</v>
       </c>
       <c r="C312" t="n">
-        <v>11.95087308479659</v>
+        <v>11.95087212149613</v>
       </c>
       <c r="D312" t="n">
-        <v>10.95283372865995</v>
+        <v>10.95283284580649</v>
       </c>
       <c r="E312" t="n">
-        <v>11.09784824779946</v>
+        <v>11.09784735325709</v>
       </c>
       <c r="F312" t="n">
         <v>3044087</v>
@@ -6692,16 +6692,16 @@
         <v>44687</v>
       </c>
       <c r="B314" t="n">
-        <v>11.52435970306396</v>
+        <v>11.52436065673828</v>
       </c>
       <c r="C314" t="n">
-        <v>11.61819232834089</v>
+        <v>11.61819328978013</v>
       </c>
       <c r="D314" t="n">
-        <v>11.20874057273858</v>
+        <v>11.20874150029449</v>
       </c>
       <c r="E314" t="n">
-        <v>11.60966201471724</v>
+        <v>11.60966297545057</v>
       </c>
       <c r="F314" t="n">
         <v>3256744</v>
@@ -6712,16 +6712,16 @@
         <v>44690</v>
       </c>
       <c r="B315" t="n">
-        <v>10.99548625946045</v>
+        <v>10.99548530578613</v>
       </c>
       <c r="C315" t="n">
-        <v>11.41346840008224</v>
+        <v>11.41346741015497</v>
       </c>
       <c r="D315" t="n">
-        <v>10.85900286733568</v>
+        <v>10.85900192549901</v>
       </c>
       <c r="E315" t="n">
-        <v>11.4049389095849</v>
+        <v>11.40493792039742</v>
       </c>
       <c r="F315" t="n">
         <v>3635836</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381309509277</v>
+        <v>11.93381404876709</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470636282327</v>
+        <v>12.04470732535947</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908636463518</v>
+        <v>11.72908730194904</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81438951256891</v>
+        <v>11.81439045669965</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415687561035</v>
+        <v>12.45415782928467</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505013177474</v>
+        <v>12.56505109394068</v>
       </c>
       <c r="D323" t="n">
-        <v>11.9508724782104</v>
+        <v>11.95087339334582</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559753814858</v>
+        <v>12.15559846896078</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6892,16 +6892,16 @@
         <v>44701</v>
       </c>
       <c r="B324" t="n">
-        <v>12.50533771514893</v>
+        <v>12.50533866882324</v>
       </c>
       <c r="C324" t="n">
-        <v>12.658882538139</v>
+        <v>12.65888350352286</v>
       </c>
       <c r="D324" t="n">
-        <v>12.30914297255499</v>
+        <v>12.30914391126722</v>
       </c>
       <c r="E324" t="n">
-        <v>12.4797467738867</v>
+        <v>12.47974772560942</v>
       </c>
       <c r="F324" t="n">
         <v>4482610</v>
@@ -6972,16 +6972,16 @@
         <v>44707</v>
       </c>
       <c r="B328" t="n">
-        <v>12.70153427124023</v>
+        <v>12.70153331756592</v>
       </c>
       <c r="C328" t="n">
-        <v>12.92332079694747</v>
+        <v>12.92331982662067</v>
       </c>
       <c r="D328" t="n">
-        <v>12.38591593609915</v>
+        <v>12.38591500612253</v>
       </c>
       <c r="E328" t="n">
-        <v>12.42003719377205</v>
+        <v>12.42003626123349</v>
       </c>
       <c r="F328" t="n">
         <v>2007160</v>
@@ -6992,16 +6992,16 @@
         <v>44708</v>
       </c>
       <c r="B329" t="n">
-        <v>13.06833267211914</v>
+        <v>13.06833362579346</v>
       </c>
       <c r="C329" t="n">
-        <v>13.35836084818011</v>
+        <v>13.35836182301952</v>
       </c>
       <c r="D329" t="n">
-        <v>12.76124469418193</v>
+        <v>12.7612456254462</v>
       </c>
       <c r="E329" t="n">
-        <v>12.78683563387109</v>
+        <v>12.78683656700289</v>
       </c>
       <c r="F329" t="n">
         <v>4177410</v>
@@ -7012,16 +7012,16 @@
         <v>44711</v>
       </c>
       <c r="B330" t="n">
-        <v>12.73565483093262</v>
+        <v>12.73565578460693</v>
       </c>
       <c r="C330" t="n">
-        <v>13.33277185998338</v>
+        <v>13.33277285837116</v>
       </c>
       <c r="D330" t="n">
-        <v>12.73565483093262</v>
+        <v>12.73565578460693</v>
       </c>
       <c r="E330" t="n">
-        <v>13.26453017296089</v>
+        <v>13.26453116623858</v>
       </c>
       <c r="F330" t="n">
         <v>1851063</v>
@@ -7052,16 +7052,16 @@
         <v>44713</v>
       </c>
       <c r="B332" t="n">
-        <v>12.69300365447998</v>
+        <v>12.6930046081543</v>
       </c>
       <c r="C332" t="n">
-        <v>12.71006510749335</v>
+        <v>12.71006606244956</v>
       </c>
       <c r="D332" t="n">
-        <v>12.23237080978446</v>
+        <v>12.23237172884965</v>
       </c>
       <c r="E332" t="n">
-        <v>12.52239901934583</v>
+        <v>12.52239996020196</v>
       </c>
       <c r="F332" t="n">
         <v>4014218</v>
@@ -7072,16 +7072,16 @@
         <v>44714</v>
       </c>
       <c r="B333" t="n">
-        <v>12.57358074188232</v>
+        <v>12.57357978820801</v>
       </c>
       <c r="C333" t="n">
-        <v>13.05980452292923</v>
+        <v>13.05980353237607</v>
       </c>
       <c r="D333" t="n">
-        <v>12.43709654079169</v>
+        <v>12.43709559746936</v>
       </c>
       <c r="E333" t="n">
-        <v>12.69300349018043</v>
+        <v>12.6930025274482</v>
       </c>
       <c r="F333" t="n">
         <v>2071017</v>
@@ -7092,16 +7092,16 @@
         <v>44715</v>
       </c>
       <c r="B334" t="n">
-        <v>12.44562721252441</v>
+        <v>12.4456262588501</v>
       </c>
       <c r="C334" t="n">
-        <v>12.51386890273903</v>
+        <v>12.51386794383554</v>
       </c>
       <c r="D334" t="n">
-        <v>12.34326344032753</v>
+        <v>12.34326249449706</v>
       </c>
       <c r="E334" t="n">
-        <v>12.44562721252441</v>
+        <v>12.4456262588501</v>
       </c>
       <c r="F334" t="n">
         <v>1748789</v>
@@ -7192,16 +7192,16 @@
         <v>44722</v>
       </c>
       <c r="B339" t="n">
-        <v>11.64378452301025</v>
+        <v>11.64378356933594</v>
       </c>
       <c r="C339" t="n">
-        <v>12.07882644174544</v>
+        <v>12.07882545243938</v>
       </c>
       <c r="D339" t="n">
-        <v>11.4219979940799</v>
+        <v>11.42199705857082</v>
       </c>
       <c r="E339" t="n">
-        <v>12.06176663724438</v>
+        <v>12.06176564933559</v>
       </c>
       <c r="F339" t="n">
         <v>2898634</v>
@@ -7212,16 +7212,16 @@
         <v>44725</v>
       </c>
       <c r="B340" t="n">
-        <v>10.7225170135498</v>
+        <v>10.72251892089844</v>
       </c>
       <c r="C340" t="n">
-        <v>11.50729928449115</v>
+        <v>11.50730133143885</v>
       </c>
       <c r="D340" t="n">
-        <v>10.57750332848451</v>
+        <v>10.57750521003774</v>
       </c>
       <c r="E340" t="n">
-        <v>11.234331717334</v>
+        <v>11.23433371572554</v>
       </c>
       <c r="F340" t="n">
         <v>3958469</v>
@@ -7232,16 +7232,16 @@
         <v>44726</v>
       </c>
       <c r="B341" t="n">
-        <v>10.69692707061768</v>
+        <v>10.69692611694336</v>
       </c>
       <c r="C341" t="n">
-        <v>10.94430454411216</v>
+        <v>10.94430356838314</v>
       </c>
       <c r="D341" t="n">
-        <v>10.57750431574103</v>
+        <v>10.57750337271373</v>
       </c>
       <c r="E341" t="n">
-        <v>10.79076053093742</v>
+        <v>10.79075956889747</v>
       </c>
       <c r="F341" t="n">
         <v>2253062</v>
@@ -7252,16 +7252,16 @@
         <v>44727</v>
       </c>
       <c r="B342" t="n">
-        <v>10.83341026306152</v>
+        <v>10.83341121673584</v>
       </c>
       <c r="C342" t="n">
-        <v>11.07225657499456</v>
+        <v>11.07225754969472</v>
       </c>
       <c r="D342" t="n">
-        <v>10.67133512593145</v>
+        <v>10.67133606533815</v>
       </c>
       <c r="E342" t="n">
-        <v>10.88459132112458</v>
+        <v>10.88459227930441</v>
       </c>
       <c r="F342" t="n">
         <v>3158221</v>
@@ -7272,16 +7272,16 @@
         <v>44729</v>
       </c>
       <c r="B343" t="n">
-        <v>10.66280460357666</v>
+        <v>10.66280555725098</v>
       </c>
       <c r="C343" t="n">
-        <v>10.69692585800674</v>
+        <v>10.69692681473284</v>
       </c>
       <c r="D343" t="n">
-        <v>10.29600441678626</v>
+        <v>10.2960053376542</v>
       </c>
       <c r="E343" t="n">
-        <v>10.69692585800674</v>
+        <v>10.69692681473284</v>
       </c>
       <c r="F343" t="n">
         <v>2862346</v>
@@ -7292,16 +7292,16 @@
         <v>44732</v>
       </c>
       <c r="B344" t="n">
-        <v>10.38130760192871</v>
+        <v>10.38130664825439</v>
       </c>
       <c r="C344" t="n">
-        <v>10.93577391016304</v>
+        <v>10.93577290555292</v>
       </c>
       <c r="D344" t="n">
-        <v>10.33012654055963</v>
+        <v>10.33012559158704</v>
       </c>
       <c r="E344" t="n">
-        <v>10.93577391016304</v>
+        <v>10.93577290555292</v>
       </c>
       <c r="F344" t="n">
         <v>1404768</v>
@@ -7412,16 +7412,16 @@
         <v>44740</v>
       </c>
       <c r="B350" t="n">
-        <v>10.23629379272461</v>
+        <v>10.23629283905029</v>
       </c>
       <c r="C350" t="n">
-        <v>10.81635108415403</v>
+        <v>10.81635007643811</v>
       </c>
       <c r="D350" t="n">
-        <v>10.18511272780684</v>
+        <v>10.18511177890085</v>
       </c>
       <c r="E350" t="n">
-        <v>10.70545781481826</v>
+        <v>10.70545681743382</v>
       </c>
       <c r="F350" t="n">
         <v>2763519</v>
@@ -7452,16 +7452,16 @@
         <v>44742</v>
       </c>
       <c r="B352" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C352" t="n">
-        <v>10.12539894068065</v>
+        <v>10.1253999073854</v>
       </c>
       <c r="D352" t="n">
-        <v>9.724477500590167</v>
+        <v>9.724478429017642</v>
       </c>
       <c r="E352" t="n">
-        <v>9.971854945344536</v>
+        <v>9.97185589738994</v>
       </c>
       <c r="F352" t="n">
         <v>3400779</v>
@@ -7492,16 +7492,16 @@
         <v>44746</v>
       </c>
       <c r="B354" t="n">
-        <v>9.65623664855957</v>
+        <v>9.656235694885254</v>
       </c>
       <c r="C354" t="n">
-        <v>10.02303686592241</v>
+        <v>10.02303587602198</v>
       </c>
       <c r="D354" t="n">
-        <v>9.65623664855957</v>
+        <v>9.656235694885254</v>
       </c>
       <c r="E354" t="n">
-        <v>9.920674743266868</v>
+        <v>9.920673763475978</v>
       </c>
       <c r="F354" t="n">
         <v>1779400</v>
@@ -7512,16 +7512,16 @@
         <v>44747</v>
       </c>
       <c r="B355" t="n">
-        <v>9.622115135192871</v>
+        <v>9.622116088867188</v>
       </c>
       <c r="C355" t="n">
-        <v>9.681827333833224</v>
+        <v>9.681828293425781</v>
       </c>
       <c r="D355" t="n">
-        <v>9.178542925352392</v>
+        <v>9.178543835063046</v>
       </c>
       <c r="E355" t="n">
-        <v>9.681827333833224</v>
+        <v>9.681828293425781</v>
       </c>
       <c r="F355" t="n">
         <v>3899578</v>
@@ -7572,16 +7572,16 @@
         <v>44750</v>
       </c>
       <c r="B358" t="n">
-        <v>9.784191131591797</v>
+        <v>9.78419017791748</v>
       </c>
       <c r="C358" t="n">
-        <v>10.19364294535647</v>
+        <v>10.19364195177249</v>
       </c>
       <c r="D358" t="n">
-        <v>9.724478927744158</v>
+        <v>9.724477979890045</v>
       </c>
       <c r="E358" t="n">
-        <v>9.86949345536221</v>
+        <v>9.869492493373395</v>
       </c>
       <c r="F358" t="n">
         <v>1378414</v>
@@ -7612,16 +7612,16 @@
         <v>44754</v>
       </c>
       <c r="B360" t="n">
-        <v>9.229723930358887</v>
+        <v>9.229724884033203</v>
       </c>
       <c r="C360" t="n">
-        <v>9.289435298725786</v>
+        <v>9.289436258569864</v>
       </c>
       <c r="D360" t="n">
-        <v>8.879983559686456</v>
+        <v>8.879984477223353</v>
       </c>
       <c r="E360" t="n">
-        <v>9.229723930358887</v>
+        <v>9.229724884033203</v>
       </c>
       <c r="F360" t="n">
         <v>1719496</v>
@@ -7652,16 +7652,16 @@
         <v>44756</v>
       </c>
       <c r="B362" t="n">
-        <v>9.383269309997559</v>
+        <v>9.383268356323242</v>
       </c>
       <c r="C362" t="n">
-        <v>9.485632259918743</v>
+        <v>9.485631295840706</v>
       </c>
       <c r="D362" t="n">
-        <v>9.067650145691958</v>
+        <v>9.06764922409579</v>
       </c>
       <c r="E362" t="n">
-        <v>9.204134353781315</v>
+        <v>9.204133418313491</v>
       </c>
       <c r="F362" t="n">
         <v>823562</v>
@@ -7692,16 +7692,16 @@
         <v>44760</v>
       </c>
       <c r="B364" t="n">
-        <v>9.511220932006836</v>
+        <v>9.511222839355469</v>
       </c>
       <c r="C364" t="n">
-        <v>9.698886174215358</v>
+        <v>9.698888119197754</v>
       </c>
       <c r="D364" t="n">
-        <v>9.212663266788628</v>
+        <v>9.212665114265498</v>
       </c>
       <c r="E364" t="n">
-        <v>9.212663266788628</v>
+        <v>9.212665114265498</v>
       </c>
       <c r="F364" t="n">
         <v>1476836</v>
@@ -7712,16 +7712,16 @@
         <v>44761</v>
       </c>
       <c r="B365" t="n">
-        <v>9.767129898071289</v>
+        <v>9.767128944396973</v>
       </c>
       <c r="C365" t="n">
-        <v>9.929205045339851</v>
+        <v>9.929204075840321</v>
       </c>
       <c r="D365" t="n">
-        <v>9.562404828429376</v>
+        <v>9.562403894744662</v>
       </c>
       <c r="E365" t="n">
-        <v>9.562404828429376</v>
+        <v>9.562403894744662</v>
       </c>
       <c r="F365" t="n">
         <v>2310433</v>
@@ -7772,16 +7772,16 @@
         <v>44764</v>
       </c>
       <c r="B368" t="n">
-        <v>10.35571670532227</v>
+        <v>10.35571765899658</v>
       </c>
       <c r="C368" t="n">
-        <v>10.38983796005971</v>
+        <v>10.3898389168763</v>
       </c>
       <c r="D368" t="n">
-        <v>9.954795260490318</v>
+        <v>9.954796177243145</v>
       </c>
       <c r="E368" t="n">
-        <v>10.07421800290487</v>
+        <v>10.07421893065553</v>
       </c>
       <c r="F368" t="n">
         <v>1969757</v>
@@ -7812,16 +7812,16 @@
         <v>44768</v>
       </c>
       <c r="B370" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="C370" t="n">
-        <v>10.40689763976893</v>
+        <v>10.40689863334928</v>
       </c>
       <c r="D370" t="n">
-        <v>9.988916397094727</v>
+        <v>9.988917350769043</v>
       </c>
       <c r="E370" t="n">
-        <v>10.22776270368238</v>
+        <v>10.22776368016013</v>
       </c>
       <c r="F370" t="n">
         <v>1502988</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.50926113128662</v>
+        <v>10.5092601776123</v>
       </c>
       <c r="C371" t="n">
-        <v>10.61162407509244</v>
+        <v>10.61162311212909</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421841396606</v>
+        <v>10.07421749977017</v>
       </c>
       <c r="E371" t="n">
-        <v>10.12539947357733</v>
+        <v>10.12539855473696</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7892,16 +7892,16 @@
         <v>44774</v>
       </c>
       <c r="B374" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845264434814</v>
       </c>
       <c r="C374" t="n">
-        <v>11.77173801596846</v>
+        <v>11.77173701970006</v>
       </c>
       <c r="D374" t="n">
-        <v>11.09784813756763</v>
+        <v>11.09784719833203</v>
       </c>
       <c r="E374" t="n">
-        <v>11.64378412677316</v>
+        <v>11.64378314133378</v>
       </c>
       <c r="F374" t="n">
         <v>4838693</v>
@@ -7912,16 +7912,16 @@
         <v>44775</v>
       </c>
       <c r="B375" t="n">
-        <v>11.26845359802246</v>
+        <v>11.26845264434814</v>
       </c>
       <c r="C375" t="n">
-        <v>11.49876960907404</v>
+        <v>11.49876863590757</v>
       </c>
       <c r="D375" t="n">
-        <v>11.24286265526674</v>
+        <v>11.24286170375824</v>
       </c>
       <c r="E375" t="n">
-        <v>11.39640666263446</v>
+        <v>11.39640569813119</v>
       </c>
       <c r="F375" t="n">
         <v>2088249</v>
@@ -7972,16 +7972,16 @@
         <v>44778</v>
       </c>
       <c r="B378" t="n">
-        <v>12.79536724090576</v>
+        <v>12.79536628723145</v>
       </c>
       <c r="C378" t="n">
-        <v>12.93185145059431</v>
+        <v>12.93185048674745</v>
       </c>
       <c r="D378" t="n">
-        <v>12.24090173667624</v>
+        <v>12.24090082432778</v>
       </c>
       <c r="E378" t="n">
-        <v>12.32620405851283</v>
+        <v>12.32620313980655</v>
       </c>
       <c r="F378" t="n">
         <v>4419056</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248466491699</v>
+        <v>13.39248371124268</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634635999027</v>
+        <v>13.77634537898129</v>
       </c>
       <c r="D381" t="n">
-        <v>13.17922926709854</v>
+        <v>13.17922832861007</v>
       </c>
       <c r="E381" t="n">
-        <v>13.30718234087294</v>
+        <v>13.30718139327297</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8052,16 +8052,16 @@
         <v>44784</v>
       </c>
       <c r="B382" t="n">
-        <v>13.36689376831055</v>
+        <v>13.36689472198486</v>
       </c>
       <c r="C382" t="n">
-        <v>13.63986135430908</v>
+        <v>13.63986232745854</v>
       </c>
       <c r="D382" t="n">
-        <v>13.11951630083012</v>
+        <v>13.11951723685505</v>
       </c>
       <c r="E382" t="n">
-        <v>13.52043777775243</v>
+        <v>13.5204387423815</v>
       </c>
       <c r="F382" t="n">
         <v>2014153</v>
@@ -8072,16 +8072,16 @@
         <v>44785</v>
       </c>
       <c r="B383" t="n">
-        <v>13.75928592681885</v>
+        <v>13.75928497314453</v>
       </c>
       <c r="C383" t="n">
-        <v>13.84458825208146</v>
+        <v>13.84458729249473</v>
       </c>
       <c r="D383" t="n">
-        <v>13.47778800607721</v>
+        <v>13.47778707191389</v>
       </c>
       <c r="E383" t="n">
-        <v>13.47778800607721</v>
+        <v>13.47778707191389</v>
       </c>
       <c r="F383" t="n">
         <v>2291478</v>
@@ -8092,16 +8092,16 @@
         <v>44788</v>
       </c>
       <c r="B384" t="n">
-        <v>13.5545597076416</v>
+        <v>13.55455875396729</v>
       </c>
       <c r="C384" t="n">
-        <v>13.70810372470057</v>
+        <v>13.70810276022317</v>
       </c>
       <c r="D384" t="n">
-        <v>13.44366643995086</v>
+        <v>13.44366549407879</v>
       </c>
       <c r="E384" t="n">
-        <v>13.64839234575172</v>
+        <v>13.6483913854755</v>
       </c>
       <c r="F384" t="n">
         <v>3349490</v>
@@ -8132,16 +8132,16 @@
         <v>44790</v>
       </c>
       <c r="B386" t="n">
-        <v>13.56308841705322</v>
+        <v>13.56308746337891</v>
       </c>
       <c r="C386" t="n">
-        <v>13.64839073027631</v>
+        <v>13.64838977060406</v>
       </c>
       <c r="D386" t="n">
-        <v>13.23893896713886</v>
+        <v>13.23893803625678</v>
       </c>
       <c r="E386" t="n">
-        <v>13.64839073027631</v>
+        <v>13.64838977060406</v>
       </c>
       <c r="F386" t="n">
         <v>4054357</v>
@@ -8172,16 +8172,16 @@
         <v>44792</v>
       </c>
       <c r="B388" t="n">
-        <v>12.88066959381104</v>
+        <v>12.88066864013672</v>
       </c>
       <c r="C388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="D388" t="n">
-        <v>12.83801884508153</v>
+        <v>12.83801789456504</v>
       </c>
       <c r="E388" t="n">
-        <v>13.59721025338341</v>
+        <v>13.59720924665701</v>
       </c>
       <c r="F388" t="n">
         <v>3352328</v>
@@ -8212,16 +8212,16 @@
         <v>44796</v>
       </c>
       <c r="B390" t="n">
-        <v>12.29208183288574</v>
+        <v>12.29208278656006</v>
       </c>
       <c r="C390" t="n">
-        <v>12.6418222319422</v>
+        <v>12.64182321275093</v>
       </c>
       <c r="D390" t="n">
-        <v>12.25796140158548</v>
+        <v>12.25796235261258</v>
       </c>
       <c r="E390" t="n">
-        <v>12.6418222319422</v>
+        <v>12.64182321275093</v>
       </c>
       <c r="F390" t="n">
         <v>5845922</v>
@@ -8292,16 +8292,16 @@
         <v>44802</v>
       </c>
       <c r="B394" t="n">
-        <v>12.25796127319336</v>
+        <v>12.25796031951904</v>
       </c>
       <c r="C394" t="n">
-        <v>12.40297496001295</v>
+        <v>12.40297399505652</v>
       </c>
       <c r="D394" t="n">
-        <v>12.04470507532147</v>
+        <v>12.04470413823857</v>
       </c>
       <c r="E394" t="n">
-        <v>12.18118844825953</v>
+        <v>12.18118750055817</v>
       </c>
       <c r="F394" t="n">
         <v>4196061</v>
@@ -8332,16 +8332,16 @@
         <v>44804</v>
       </c>
       <c r="B396" t="n">
-        <v>12.03617572784424</v>
+        <v>12.03617477416992</v>
       </c>
       <c r="C396" t="n">
-        <v>12.33473426391999</v>
+        <v>12.33473328658969</v>
       </c>
       <c r="D396" t="n">
-        <v>11.92528246306372</v>
+        <v>11.92528151817592</v>
       </c>
       <c r="E396" t="n">
-        <v>12.1044174197925</v>
+        <v>12.10441646071113</v>
       </c>
       <c r="F396" t="n">
         <v>1958303</v>
@@ -8392,16 +8392,16 @@
         <v>44809</v>
       </c>
       <c r="B399" t="n">
-        <v>13.30718231201172</v>
+        <v>13.3071813583374</v>
       </c>
       <c r="C399" t="n">
-        <v>13.40954526555925</v>
+        <v>13.40954430454897</v>
       </c>
       <c r="D399" t="n">
-        <v>12.38591655466734</v>
+        <v>12.38591566701658</v>
       </c>
       <c r="E399" t="n">
-        <v>12.48827868363151</v>
+        <v>12.48827778864485</v>
       </c>
       <c r="F399" t="n">
         <v>2134165</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.33473491668701</v>
+        <v>12.3347339630127</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121913238976</v>
+        <v>12.47121816816301</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646415968605</v>
+        <v>11.97646323371185</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22384164603791</v>
+        <v>12.22384070093743</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8472,16 +8472,16 @@
         <v>44816</v>
       </c>
       <c r="B403" t="n">
-        <v>12.30696105957031</v>
+        <v>12.30696201324463</v>
       </c>
       <c r="C403" t="n">
-        <v>12.58102037271514</v>
+        <v>12.58102134762649</v>
       </c>
       <c r="D403" t="n">
-        <v>12.05859576045719</v>
+        <v>12.05859669488552</v>
       </c>
       <c r="E403" t="n">
-        <v>12.05859576045719</v>
+        <v>12.05859669488552</v>
       </c>
       <c r="F403" t="n">
         <v>4043263</v>
@@ -8492,16 +8492,16 @@
         <v>44817</v>
       </c>
       <c r="B404" t="n">
-        <v>11.82736015319824</v>
+        <v>11.82735824584961</v>
       </c>
       <c r="C404" t="n">
-        <v>12.11854774525109</v>
+        <v>12.11854579094386</v>
       </c>
       <c r="D404" t="n">
-        <v>11.74171645274152</v>
+        <v>11.74171455920428</v>
       </c>
       <c r="E404" t="n">
-        <v>12.11854774525109</v>
+        <v>12.11854579094386</v>
       </c>
       <c r="F404" t="n">
         <v>3904244</v>
@@ -8512,16 +8512,16 @@
         <v>44818</v>
       </c>
       <c r="B405" t="n">
-        <v>12.58102035522461</v>
+        <v>12.58102130889893</v>
       </c>
       <c r="C405" t="n">
-        <v>12.6067127200541</v>
+        <v>12.60671367567597</v>
       </c>
       <c r="D405" t="n">
-        <v>11.73315005210365</v>
+        <v>11.73315094150718</v>
       </c>
       <c r="E405" t="n">
-        <v>11.86161517458411</v>
+        <v>11.86161607372562</v>
       </c>
       <c r="F405" t="n">
         <v>3060135</v>
@@ -8552,16 +8552,16 @@
         <v>44820</v>
       </c>
       <c r="B407" t="n">
-        <v>12.40117168426514</v>
+        <v>12.40117073059082</v>
       </c>
       <c r="C407" t="n">
-        <v>12.57245826708186</v>
+        <v>12.57245730023527</v>
       </c>
       <c r="D407" t="n">
-        <v>12.09285418602828</v>
+        <v>12.09285325606418</v>
       </c>
       <c r="E407" t="n">
-        <v>12.57245826708186</v>
+        <v>12.57245730023527</v>
       </c>
       <c r="F407" t="n">
         <v>2796130</v>
@@ -8572,16 +8572,16 @@
         <v>44823</v>
       </c>
       <c r="B408" t="n">
-        <v>12.39260673522949</v>
+        <v>12.39260578155518</v>
       </c>
       <c r="C408" t="n">
-        <v>12.60671391874965</v>
+        <v>12.6067129485987</v>
       </c>
       <c r="D408" t="n">
-        <v>12.19562614739096</v>
+        <v>12.19562520887531</v>
       </c>
       <c r="E408" t="n">
-        <v>12.34122035151799</v>
+        <v>12.34121940179812</v>
       </c>
       <c r="F408" t="n">
         <v>1221893</v>
@@ -8672,16 +8672,16 @@
         <v>44830</v>
       </c>
       <c r="B413" t="n">
-        <v>11.45909118652344</v>
+        <v>11.45909214019775</v>
       </c>
       <c r="C413" t="n">
-        <v>11.844486541272</v>
+        <v>11.84448752702055</v>
       </c>
       <c r="D413" t="n">
-        <v>11.34775431092947</v>
+        <v>11.34775525533786</v>
       </c>
       <c r="E413" t="n">
-        <v>11.81879335270545</v>
+        <v>11.81879433631571</v>
       </c>
       <c r="F413" t="n">
         <v>3443068</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186389923096</v>
+        <v>11.56186485290527</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889314808853</v>
+        <v>11.69889411306563</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072583059598</v>
+        <v>11.21072675530685</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775507945355</v>
+        <v>11.34775601546721</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8772,16 +8772,16 @@
         <v>44837</v>
       </c>
       <c r="B418" t="n">
-        <v>12.41829872131348</v>
+        <v>12.41829967498779</v>
       </c>
       <c r="C418" t="n">
-        <v>12.62384342526681</v>
+        <v>12.62384439472611</v>
       </c>
       <c r="D418" t="n">
-        <v>12.01577426015137</v>
+        <v>12.01577518291347</v>
       </c>
       <c r="E418" t="n">
-        <v>12.06716064228553</v>
+        <v>12.06716156899389</v>
       </c>
       <c r="F418" t="n">
         <v>3117277</v>
@@ -8952,16 +8952,16 @@
         <v>44851</v>
       </c>
       <c r="B427" t="n">
-        <v>12.64953708648682</v>
+        <v>12.6495361328125</v>
       </c>
       <c r="C427" t="n">
-        <v>13.19765580340922</v>
+        <v>13.19765480841111</v>
       </c>
       <c r="D427" t="n">
-        <v>12.58102245301736</v>
+        <v>12.5810215045085</v>
       </c>
       <c r="E427" t="n">
-        <v>12.87221005755423</v>
+        <v>12.87220908709215</v>
       </c>
       <c r="F427" t="n">
         <v>1088124</v>
@@ -8992,16 +8992,16 @@
         <v>44853</v>
       </c>
       <c r="B429" t="n">
-        <v>12.95785140991211</v>
+        <v>12.95785045623779</v>
       </c>
       <c r="C429" t="n">
-        <v>13.02636685988985</v>
+        <v>13.02636590117292</v>
       </c>
       <c r="D429" t="n">
-        <v>12.71805022103153</v>
+        <v>12.71804928500614</v>
       </c>
       <c r="E429" t="n">
-        <v>12.80369391506624</v>
+        <v>12.80369297273763</v>
       </c>
       <c r="F429" t="n">
         <v>1282165</v>
@@ -9012,16 +9012,16 @@
         <v>44854</v>
       </c>
       <c r="B430" t="n">
-        <v>12.78656482696533</v>
+        <v>12.78656387329102</v>
       </c>
       <c r="C430" t="n">
-        <v>13.08631734333896</v>
+        <v>13.08631636730787</v>
       </c>
       <c r="D430" t="n">
-        <v>12.65809969840043</v>
+        <v>12.65809875430757</v>
       </c>
       <c r="E430" t="n">
-        <v>13.08631734333896</v>
+        <v>13.08631636730787</v>
       </c>
       <c r="F430" t="n">
         <v>2107193</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805000305176</v>
+        <v>12.71805095672607</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775301708247</v>
+        <v>13.07775399772944</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235763740665</v>
+        <v>12.69235858915441</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87220831983874</v>
+        <v>12.87220928507275</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9132,16 +9132,16 @@
         <v>44862</v>
       </c>
       <c r="B436" t="n">
-        <v>13.06918811798096</v>
+        <v>13.06918907165527</v>
       </c>
       <c r="C436" t="n">
-        <v>13.48027751395823</v>
+        <v>13.48027849763024</v>
       </c>
       <c r="D436" t="n">
-        <v>12.45255567318159</v>
+        <v>12.4525565818595</v>
       </c>
       <c r="E436" t="n">
-        <v>13.15483181085816</v>
+        <v>13.154832770782</v>
       </c>
       <c r="F436" t="n">
         <v>6048388</v>
@@ -9172,16 +9172,16 @@
         <v>44866</v>
       </c>
       <c r="B438" t="n">
-        <v>13.61730575561523</v>
+        <v>13.61730670928955</v>
       </c>
       <c r="C438" t="n">
-        <v>14.01126607789819</v>
+        <v>14.01126705916312</v>
       </c>
       <c r="D438" t="n">
-        <v>13.53166288847033</v>
+        <v>13.53166383614674</v>
       </c>
       <c r="E438" t="n">
-        <v>13.70295027192667</v>
+        <v>13.70295123159901</v>
       </c>
       <c r="F438" t="n">
         <v>3366744</v>
@@ -9212,16 +9212,16 @@
         <v>44869</v>
       </c>
       <c r="B440" t="n">
-        <v>14.01126670837402</v>
+        <v>14.01126766204834</v>
       </c>
       <c r="C440" t="n">
-        <v>14.29389098625276</v>
+        <v>14.29389195916385</v>
       </c>
       <c r="D440" t="n">
-        <v>13.80572200389402</v>
+        <v>13.80572294357798</v>
       </c>
       <c r="E440" t="n">
-        <v>14.13973183945529</v>
+        <v>14.13973280187356</v>
       </c>
       <c r="F440" t="n">
         <v>3663661</v>
@@ -9292,16 +9292,16 @@
         <v>44875</v>
       </c>
       <c r="B444" t="n">
-        <v>12.24701118469238</v>
+        <v>12.2470121383667</v>
       </c>
       <c r="C444" t="n">
-        <v>12.83795040949141</v>
+        <v>12.83795140918214</v>
       </c>
       <c r="D444" t="n">
-        <v>11.6732002028586</v>
+        <v>11.67320111185027</v>
       </c>
       <c r="E444" t="n">
-        <v>12.83795040949141</v>
+        <v>12.83795140918214</v>
       </c>
       <c r="F444" t="n">
         <v>10581398</v>
@@ -9352,16 +9352,16 @@
         <v>44881</v>
       </c>
       <c r="B447" t="n">
-        <v>11.26211261749268</v>
+        <v>11.26211357116699</v>
       </c>
       <c r="C447" t="n">
-        <v>12.15280359178205</v>
+        <v>12.15280462087997</v>
       </c>
       <c r="D447" t="n">
-        <v>11.15934067714197</v>
+        <v>11.15934162211358</v>
       </c>
       <c r="E447" t="n">
-        <v>12.06716072044812</v>
+        <v>12.06716174229381</v>
       </c>
       <c r="F447" t="n">
         <v>3929079</v>
@@ -9372,16 +9372,16 @@
         <v>44882</v>
       </c>
       <c r="B448" t="n">
-        <v>10.94523239135742</v>
+        <v>10.94523143768311</v>
       </c>
       <c r="C448" t="n">
-        <v>10.94523239135742</v>
+        <v>10.94523143768311</v>
       </c>
       <c r="D448" t="n">
-        <v>9.900382217953842</v>
+        <v>9.900381355318869</v>
       </c>
       <c r="E448" t="n">
-        <v>10.7996381835505</v>
+        <v>10.79963724256202</v>
       </c>
       <c r="F448" t="n">
         <v>12061945</v>
@@ -9392,16 +9392,16 @@
         <v>44883</v>
       </c>
       <c r="B449" t="n">
-        <v>10.92810344696045</v>
+        <v>10.92810249328613</v>
       </c>
       <c r="C449" t="n">
-        <v>11.38201432087386</v>
+        <v>11.38201332758762</v>
       </c>
       <c r="D449" t="n">
-        <v>10.91953932422152</v>
+        <v>10.91953837129458</v>
       </c>
       <c r="E449" t="n">
-        <v>11.1336473401948</v>
+        <v>11.13364636858307</v>
       </c>
       <c r="F449" t="n">
         <v>5719164</v>
@@ -9412,16 +9412,16 @@
         <v>44886</v>
       </c>
       <c r="B450" t="n">
-        <v>11.25354766845703</v>
+        <v>11.25354671478271</v>
       </c>
       <c r="C450" t="n">
-        <v>11.33062724214222</v>
+        <v>11.33062628193585</v>
       </c>
       <c r="D450" t="n">
-        <v>10.80820259369247</v>
+        <v>10.80820167775862</v>
       </c>
       <c r="E450" t="n">
-        <v>10.98805328312464</v>
+        <v>10.98805235194947</v>
       </c>
       <c r="F450" t="n">
         <v>4991964</v>
@@ -9432,16 +9432,16 @@
         <v>44887</v>
       </c>
       <c r="B451" t="n">
-        <v>10.98805236816406</v>
+        <v>10.98805332183838</v>
       </c>
       <c r="C451" t="n">
-        <v>11.33919042015788</v>
+        <v>11.33919140430814</v>
       </c>
       <c r="D451" t="n">
-        <v>10.89384455789337</v>
+        <v>10.89384550339121</v>
       </c>
       <c r="E451" t="n">
-        <v>11.27923992047805</v>
+        <v>11.2792408994251</v>
       </c>
       <c r="F451" t="n">
         <v>2547672</v>
@@ -9452,16 +9452,16 @@
         <v>44888</v>
       </c>
       <c r="B452" t="n">
-        <v>11.04800319671631</v>
+        <v>11.04800415039062</v>
       </c>
       <c r="C452" t="n">
-        <v>11.09082545466704</v>
+        <v>11.09082641203781</v>
       </c>
       <c r="D452" t="n">
-        <v>10.78250800100489</v>
+        <v>10.78250893176141</v>
       </c>
       <c r="E452" t="n">
-        <v>10.9880526952519</v>
+        <v>10.98805364375123</v>
       </c>
       <c r="F452" t="n">
         <v>2848931</v>
@@ -9512,16 +9512,16 @@
         <v>44893</v>
       </c>
       <c r="B455" t="n">
-        <v>10.96235942840576</v>
+        <v>10.96235847473145</v>
       </c>
       <c r="C455" t="n">
-        <v>11.18503236460255</v>
+        <v>11.18503139155672</v>
       </c>
       <c r="D455" t="n">
-        <v>10.84245842631905</v>
+        <v>10.84245748307556</v>
       </c>
       <c r="E455" t="n">
-        <v>10.95379530670907</v>
+        <v>10.95379435377979</v>
       </c>
       <c r="F455" t="n">
         <v>2642270</v>
@@ -9552,16 +9552,16 @@
         <v>44895</v>
       </c>
       <c r="B457" t="n">
-        <v>11.35631942749023</v>
+        <v>11.35632038116455</v>
       </c>
       <c r="C457" t="n">
-        <v>11.57042825153101</v>
+        <v>11.57042922318563</v>
       </c>
       <c r="D457" t="n">
-        <v>11.04800361142147</v>
+        <v>11.04800453920422</v>
       </c>
       <c r="E457" t="n">
-        <v>11.34775530541193</v>
+        <v>11.34775625836705</v>
       </c>
       <c r="F457" t="n">
         <v>6904107</v>
@@ -9612,16 +9612,16 @@
         <v>44900</v>
       </c>
       <c r="B460" t="n">
-        <v>10.65404510498047</v>
+        <v>10.65404415130615</v>
       </c>
       <c r="C460" t="n">
-        <v>11.2621134969344</v>
+        <v>11.26211248883013</v>
       </c>
       <c r="D460" t="n">
-        <v>10.56840057779207</v>
+        <v>10.56839963178404</v>
       </c>
       <c r="E460" t="n">
-        <v>11.2621134969344</v>
+        <v>11.26211248883013</v>
       </c>
       <c r="F460" t="n">
         <v>2438739</v>
@@ -9712,16 +9712,16 @@
         <v>44907</v>
       </c>
       <c r="B465" t="n">
-        <v>9.506422996520996</v>
+        <v>9.50642204284668</v>
       </c>
       <c r="C465" t="n">
-        <v>10.02884768824383</v>
+        <v>10.02884668216042</v>
       </c>
       <c r="D465" t="n">
-        <v>9.420779293526801</v>
+        <v>9.42077834844417</v>
       </c>
       <c r="E465" t="n">
-        <v>9.574937629083003</v>
+        <v>9.57493666853537</v>
       </c>
       <c r="F465" t="n">
         <v>6343387</v>
@@ -9752,16 +9752,16 @@
         <v>44909</v>
       </c>
       <c r="B467" t="n">
-        <v>9.489291191101074</v>
+        <v>9.489292144775391</v>
       </c>
       <c r="C467" t="n">
-        <v>9.652014441405267</v>
+        <v>9.652015411433279</v>
       </c>
       <c r="D467" t="n">
-        <v>9.138153976058327</v>
+        <v>9.138154894443332</v>
       </c>
       <c r="E467" t="n">
-        <v>9.318004644179831</v>
+        <v>9.31800558063984</v>
       </c>
       <c r="F467" t="n">
         <v>7822016</v>
@@ -9812,16 +9812,16 @@
         <v>44914</v>
       </c>
       <c r="B470" t="n">
-        <v>9.951766014099121</v>
+        <v>9.951766967773438</v>
       </c>
       <c r="C470" t="n">
-        <v>10.03740969907196</v>
+        <v>10.03741066095349</v>
       </c>
       <c r="D470" t="n">
-        <v>9.68627166264147</v>
+        <v>9.686272590873555</v>
       </c>
       <c r="E470" t="n">
-        <v>9.840429141176106</v>
+        <v>9.840430084181047</v>
       </c>
       <c r="F470" t="n">
         <v>3753211</v>
@@ -9832,16 +9832,16 @@
         <v>44915</v>
       </c>
       <c r="B471" t="n">
-        <v>10.33716297149658</v>
+        <v>10.33716201782227</v>
       </c>
       <c r="C471" t="n">
-        <v>10.65404457284976</v>
+        <v>10.65404358994094</v>
       </c>
       <c r="D471" t="n">
-        <v>9.857560569696266</v>
+        <v>9.857559660268567</v>
       </c>
       <c r="E471" t="n">
-        <v>9.926074373941555</v>
+        <v>9.926073458192986</v>
       </c>
       <c r="F471" t="n">
         <v>4483944</v>
@@ -9852,16 +9852,16 @@
         <v>44916</v>
       </c>
       <c r="B472" t="n">
-        <v>10.42280578613281</v>
+        <v>10.42280673980713</v>
       </c>
       <c r="C472" t="n">
-        <v>10.58552904653355</v>
+        <v>10.58553001509685</v>
       </c>
       <c r="D472" t="n">
-        <v>10.08879679276622</v>
+        <v>10.08879771587911</v>
       </c>
       <c r="E472" t="n">
-        <v>10.36285610942807</v>
+        <v>10.36285705761706</v>
       </c>
       <c r="F472" t="n">
         <v>3195923</v>
@@ -9892,16 +9892,16 @@
         <v>44918</v>
       </c>
       <c r="B474" t="n">
-        <v>10.83389377593994</v>
+        <v>10.83389472961426</v>
       </c>
       <c r="C474" t="n">
-        <v>11.26211138404356</v>
+        <v>11.26211237541256</v>
       </c>
       <c r="D474" t="n">
-        <v>10.55983447377029</v>
+        <v>10.55983540332002</v>
       </c>
       <c r="E474" t="n">
-        <v>10.57696271632784</v>
+        <v>10.57696364738531</v>
       </c>
       <c r="F474" t="n">
         <v>4288288</v>
@@ -9912,16 +9912,16 @@
         <v>44921</v>
       </c>
       <c r="B475" t="n">
-        <v>10.66260719299316</v>
+        <v>10.66260814666748</v>
       </c>
       <c r="C475" t="n">
-        <v>10.8767159963531</v>
+        <v>10.87671696917752</v>
       </c>
       <c r="D475" t="n">
-        <v>10.57696268214933</v>
+        <v>10.57696362816352</v>
       </c>
       <c r="E475" t="n">
-        <v>10.82532961968009</v>
+        <v>10.82533058790846</v>
       </c>
       <c r="F475" t="n">
         <v>1667319</v>
@@ -9932,16 +9932,16 @@
         <v>44922</v>
       </c>
       <c r="B476" t="n">
-        <v>10.5229606628418</v>
+        <v>10.52296161651611</v>
       </c>
       <c r="C476" t="n">
-        <v>10.75038956949791</v>
+        <v>10.75039054378364</v>
       </c>
       <c r="D476" t="n">
-        <v>10.37425679063793</v>
+        <v>10.37425773083552</v>
       </c>
       <c r="E476" t="n">
-        <v>10.73289464951121</v>
+        <v>10.73289562221141</v>
       </c>
       <c r="F476" t="n">
         <v>2935250</v>
@@ -9952,16 +9952,16 @@
         <v>44923</v>
       </c>
       <c r="B477" t="n">
-        <v>10.96907234191895</v>
+        <v>10.96907043457031</v>
       </c>
       <c r="C477" t="n">
-        <v>11.03030330833085</v>
+        <v>11.03030139033512</v>
       </c>
       <c r="D477" t="n">
-        <v>10.43548940917989</v>
+        <v>10.43548759461291</v>
       </c>
       <c r="E477" t="n">
-        <v>10.56669754009717</v>
+        <v>10.56669570271517</v>
       </c>
       <c r="F477" t="n">
         <v>2605824</v>
@@ -9972,16 +9972,16 @@
         <v>44924</v>
       </c>
       <c r="B478" t="n">
-        <v>11.05654335021973</v>
+        <v>11.05654430389404</v>
       </c>
       <c r="C478" t="n">
-        <v>11.29271929234563</v>
+        <v>11.29272026639114</v>
       </c>
       <c r="D478" t="n">
-        <v>10.75038941355245</v>
+        <v>10.75039034081968</v>
       </c>
       <c r="E478" t="n">
-        <v>11.00405943321613</v>
+        <v>11.00406038236348</v>
       </c>
       <c r="F478" t="n">
         <v>3691424</v>
@@ -9992,16 +9992,16 @@
         <v>44928</v>
       </c>
       <c r="B479" t="n">
-        <v>10.15557479858398</v>
+        <v>10.15557670593262</v>
       </c>
       <c r="C479" t="n">
-        <v>10.91658654369057</v>
+        <v>10.91658859396708</v>
       </c>
       <c r="D479" t="n">
-        <v>9.963134892061372</v>
+        <v>9.963136763267295</v>
       </c>
       <c r="E479" t="n">
-        <v>10.91658654369057</v>
+        <v>10.91658859396708</v>
       </c>
       <c r="F479" t="n">
         <v>2948980</v>
@@ -10032,16 +10032,16 @@
         <v>44930</v>
       </c>
       <c r="B481" t="n">
-        <v>9.814431190490723</v>
+        <v>9.814432144165039</v>
       </c>
       <c r="C481" t="n">
-        <v>9.83192611056422</v>
+        <v>9.83192706593853</v>
       </c>
       <c r="D481" t="n">
-        <v>9.482036131045863</v>
+        <v>9.482037052421148</v>
       </c>
       <c r="E481" t="n">
-        <v>9.648234081865873</v>
+        <v>9.648235019390714</v>
       </c>
       <c r="F481" t="n">
         <v>3712928</v>
@@ -10052,16 +10052,16 @@
         <v>44931</v>
       </c>
       <c r="B482" t="n">
-        <v>10.05935668945312</v>
+        <v>10.05935573577881</v>
       </c>
       <c r="C482" t="n">
-        <v>10.33926871956802</v>
+        <v>10.33926773935673</v>
       </c>
       <c r="D482" t="n">
-        <v>9.779444659338226</v>
+        <v>9.779443732200887</v>
       </c>
       <c r="E482" t="n">
-        <v>9.796938740122757</v>
+        <v>9.796937811326897</v>
       </c>
       <c r="F482" t="n">
         <v>3524036</v>
@@ -10072,16 +10072,16 @@
         <v>44932</v>
       </c>
       <c r="B483" t="n">
-        <v>10.43548774719238</v>
+        <v>10.4354887008667</v>
       </c>
       <c r="C483" t="n">
-        <v>10.4967178616573</v>
+        <v>10.49671882092729</v>
       </c>
       <c r="D483" t="n">
-        <v>10.03311300945403</v>
+        <v>10.03311392635628</v>
       </c>
       <c r="E483" t="n">
-        <v>10.05935496833623</v>
+        <v>10.05935588763667</v>
       </c>
       <c r="F483" t="n">
         <v>2102448</v>
@@ -10112,16 +10112,16 @@
         <v>44936</v>
       </c>
       <c r="B485" t="n">
-        <v>11.11777496337891</v>
+        <v>11.11777591705322</v>
       </c>
       <c r="C485" t="n">
-        <v>11.29271996007671</v>
+        <v>11.29272092875768</v>
       </c>
       <c r="D485" t="n">
-        <v>10.48797129087642</v>
+        <v>10.48797219052666</v>
       </c>
       <c r="E485" t="n">
-        <v>10.55794928955554</v>
+        <v>10.55795019520844</v>
       </c>
       <c r="F485" t="n">
         <v>3522522</v>
@@ -10172,16 +10172,16 @@
         <v>44939</v>
       </c>
       <c r="B488" t="n">
-        <v>11.24898338317871</v>
+        <v>11.24898242950439</v>
       </c>
       <c r="C488" t="n">
-        <v>11.33645714718375</v>
+        <v>11.33645618609352</v>
       </c>
       <c r="D488" t="n">
-        <v>10.94282942013715</v>
+        <v>10.94282849241817</v>
       </c>
       <c r="E488" t="n">
-        <v>11.12652230327921</v>
+        <v>11.12652135998699</v>
       </c>
       <c r="F488" t="n">
         <v>2088011</v>
@@ -10192,16 +10192,16 @@
         <v>44942</v>
       </c>
       <c r="B489" t="n">
-        <v>10.80287265777588</v>
+        <v>10.8028736114502</v>
       </c>
       <c r="C489" t="n">
-        <v>11.30146738941439</v>
+        <v>11.3014683871045</v>
       </c>
       <c r="D489" t="n">
-        <v>10.69790649832965</v>
+        <v>10.69790744273759</v>
       </c>
       <c r="E489" t="n">
-        <v>11.25773134927926</v>
+        <v>11.25773234310836</v>
       </c>
       <c r="F489" t="n">
         <v>2251058</v>
@@ -10212,16 +10212,16 @@
         <v>44943</v>
       </c>
       <c r="B490" t="n">
-        <v>11.00406074523926</v>
+        <v>11.00405979156494</v>
       </c>
       <c r="C490" t="n">
-        <v>11.10902859176186</v>
+        <v>11.10902762899043</v>
       </c>
       <c r="D490" t="n">
-        <v>10.7503906953303</v>
+        <v>10.75038976364046</v>
       </c>
       <c r="E490" t="n">
-        <v>10.8466098176506</v>
+        <v>10.84660887762188</v>
       </c>
       <c r="F490" t="n">
         <v>2581089</v>
@@ -10232,16 +10232,16 @@
         <v>44944</v>
       </c>
       <c r="B491" t="n">
-        <v>11.61636829376221</v>
+        <v>11.61636924743652</v>
       </c>
       <c r="C491" t="n">
-        <v>11.81755524112901</v>
+        <v>11.81755621132026</v>
       </c>
       <c r="D491" t="n">
-        <v>11.08278460488162</v>
+        <v>11.08278551475007</v>
       </c>
       <c r="E491" t="n">
-        <v>11.12652148366233</v>
+        <v>11.12652239712147</v>
       </c>
       <c r="F491" t="n">
         <v>4176830</v>
@@ -10252,16 +10252,16 @@
         <v>44945</v>
       </c>
       <c r="B492" t="n">
-        <v>11.93127059936523</v>
+        <v>11.93127155303955</v>
       </c>
       <c r="C492" t="n">
-        <v>12.30740255052876</v>
+        <v>12.30740353426755</v>
       </c>
       <c r="D492" t="n">
-        <v>11.33645677201188</v>
+        <v>11.33645767814233</v>
       </c>
       <c r="E492" t="n">
-        <v>11.49390684698556</v>
+        <v>11.49390776570111</v>
       </c>
       <c r="F492" t="n">
         <v>5394988</v>
@@ -10312,16 +10312,16 @@
         <v>44950</v>
       </c>
       <c r="B495" t="n">
-        <v>12.12371063232422</v>
+        <v>12.1237096786499</v>
       </c>
       <c r="C495" t="n">
-        <v>12.25492044217159</v>
+        <v>12.25491947817606</v>
       </c>
       <c r="D495" t="n">
-        <v>11.5551387198968</v>
+        <v>11.55513781094744</v>
       </c>
       <c r="E495" t="n">
-        <v>11.67760064762417</v>
+        <v>11.67759972904172</v>
       </c>
       <c r="F495" t="n">
         <v>5075153</v>
@@ -10372,16 +10372,16 @@
         <v>44953</v>
       </c>
       <c r="B498" t="n">
-        <v>12.43861293792725</v>
+        <v>12.43861389160156</v>
       </c>
       <c r="C498" t="n">
-        <v>12.67478890374615</v>
+        <v>12.67478987552819</v>
       </c>
       <c r="D498" t="n">
-        <v>12.25492005218186</v>
+        <v>12.25492099177236</v>
       </c>
       <c r="E498" t="n">
-        <v>12.41237013459764</v>
+        <v>12.41237108625991</v>
       </c>
       <c r="F498" t="n">
         <v>1981500</v>
@@ -10432,16 +10432,16 @@
         <v>44958</v>
       </c>
       <c r="B501" t="n">
-        <v>12.88472175598145</v>
+        <v>12.88472270965576</v>
       </c>
       <c r="C501" t="n">
-        <v>13.46204063832434</v>
+        <v>13.46204163472943</v>
       </c>
       <c r="D501" t="n">
-        <v>12.79724884075579</v>
+        <v>12.79724978795572</v>
       </c>
       <c r="E501" t="n">
-        <v>12.96344763234308</v>
+        <v>12.96344859184436</v>
       </c>
       <c r="F501" t="n">
         <v>8623319</v>
@@ -10512,16 +10512,16 @@
         <v>44964</v>
       </c>
       <c r="B505" t="n">
-        <v>12.76226043701172</v>
+        <v>12.76226139068604</v>
       </c>
       <c r="C505" t="n">
-        <v>12.93720543340915</v>
+        <v>12.93720640015643</v>
       </c>
       <c r="D505" t="n">
-        <v>12.52608448132639</v>
+        <v>12.52608541735219</v>
       </c>
       <c r="E505" t="n">
-        <v>12.8584803955791</v>
+        <v>12.85848135644357</v>
       </c>
       <c r="F505" t="n">
         <v>2203204</v>
@@ -10532,16 +10532,16 @@
         <v>44965</v>
       </c>
       <c r="B506" t="n">
-        <v>12.77100849151611</v>
+        <v>12.7710075378418</v>
       </c>
       <c r="C506" t="n">
-        <v>12.98094334607703</v>
+        <v>12.98094237672584</v>
       </c>
       <c r="D506" t="n">
-        <v>12.56982151911688</v>
+        <v>12.56982058046619</v>
       </c>
       <c r="E506" t="n">
-        <v>12.8584814177661</v>
+        <v>12.85848045755975</v>
       </c>
       <c r="F506" t="n">
         <v>1737889</v>
@@ -10552,16 +10552,16 @@
         <v>44966</v>
       </c>
       <c r="B507" t="n">
-        <v>12.1324577331543</v>
+        <v>12.13245677947998</v>
       </c>
       <c r="C507" t="n">
-        <v>12.77975637693486</v>
+        <v>12.7797553723795</v>
       </c>
       <c r="D507" t="n">
-        <v>12.06247972901458</v>
+        <v>12.06247878084089</v>
       </c>
       <c r="E507" t="n">
-        <v>12.7622614548023</v>
+        <v>12.76226045162213</v>
       </c>
       <c r="F507" t="n">
         <v>2590377</v>
@@ -10592,16 +10592,16 @@
         <v>44970</v>
       </c>
       <c r="B509" t="n">
-        <v>12.52608489990234</v>
+        <v>12.52608585357666</v>
       </c>
       <c r="C509" t="n">
-        <v>12.77100790304318</v>
+        <v>12.77100887536473</v>
       </c>
       <c r="D509" t="n">
-        <v>12.35113905546367</v>
+        <v>12.35113999581847</v>
       </c>
       <c r="E509" t="n">
-        <v>12.38612889810758</v>
+        <v>12.38612984112634</v>
       </c>
       <c r="F509" t="n">
         <v>2916169</v>
@@ -10612,16 +10612,16 @@
         <v>44971</v>
       </c>
       <c r="B510" t="n">
-        <v>12.21992969512939</v>
+        <v>12.21993064880371</v>
       </c>
       <c r="C510" t="n">
-        <v>13.11215037930526</v>
+        <v>13.11215140261074</v>
       </c>
       <c r="D510" t="n">
-        <v>12.16744577868576</v>
+        <v>12.1674467282641</v>
       </c>
       <c r="E510" t="n">
-        <v>12.94595159129879</v>
+        <v>12.94595260163369</v>
       </c>
       <c r="F510" t="n">
         <v>6896737</v>
@@ -10652,16 +10652,16 @@
         <v>44973</v>
       </c>
       <c r="B512" t="n">
-        <v>12.86722755432129</v>
+        <v>12.86722850799561</v>
       </c>
       <c r="C512" t="n">
-        <v>12.98968947403414</v>
+        <v>12.98969043678491</v>
       </c>
       <c r="D512" t="n">
-        <v>12.6135575177385</v>
+        <v>12.61355845261168</v>
       </c>
       <c r="E512" t="n">
-        <v>12.64854567514766</v>
+        <v>12.64854661261404</v>
       </c>
       <c r="F512" t="n">
         <v>1907195</v>
@@ -10732,16 +10732,16 @@
         <v>44981</v>
       </c>
       <c r="B516" t="n">
-        <v>11.80880928039551</v>
+        <v>11.80881023406982</v>
       </c>
       <c r="C516" t="n">
-        <v>12.48234817940498</v>
+        <v>12.48234918747401</v>
       </c>
       <c r="D516" t="n">
-        <v>11.69509523801289</v>
+        <v>11.69509618250371</v>
       </c>
       <c r="E516" t="n">
-        <v>12.33364513612039</v>
+        <v>12.33364613218022</v>
       </c>
       <c r="F516" t="n">
         <v>3419242</v>
@@ -10772,16 +10772,16 @@
         <v>44985</v>
       </c>
       <c r="B518" t="n">
-        <v>11.61636829376221</v>
+        <v>11.61636924743652</v>
       </c>
       <c r="C518" t="n">
-        <v>11.86129211990972</v>
+        <v>11.86129309369166</v>
       </c>
       <c r="D518" t="n">
-        <v>11.40643430751733</v>
+        <v>11.4064352439566</v>
       </c>
       <c r="E518" t="n">
-        <v>11.71258824800656</v>
+        <v>11.7125892095803</v>
       </c>
       <c r="F518" t="n">
         <v>5639205</v>
@@ -10812,16 +10812,16 @@
         <v>44987</v>
       </c>
       <c r="B520" t="n">
-        <v>11.80880928039551</v>
+        <v>11.80881023406982</v>
       </c>
       <c r="C520" t="n">
-        <v>11.9750072452287</v>
+        <v>11.9750082123251</v>
       </c>
       <c r="D520" t="n">
-        <v>11.67760031646429</v>
+        <v>11.67760125954223</v>
       </c>
       <c r="E520" t="n">
-        <v>11.76507239762161</v>
+        <v>11.76507334776376</v>
       </c>
       <c r="F520" t="n">
         <v>2331118</v>
@@ -10852,16 +10852,16 @@
         <v>44991</v>
       </c>
       <c r="B522" t="n">
-        <v>12.1324577331543</v>
+        <v>12.13245677947998</v>
       </c>
       <c r="C522" t="n">
-        <v>12.23742558155914</v>
+        <v>12.2374246196338</v>
       </c>
       <c r="D522" t="n">
-        <v>11.68634774621477</v>
+        <v>11.68634682760701</v>
       </c>
       <c r="E522" t="n">
-        <v>11.68634774621477</v>
+        <v>11.68634682760701</v>
       </c>
       <c r="F522" t="n">
         <v>3047313</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.2636661529541</v>
+        <v>12.26366806030273</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738102843226</v>
+        <v>12.37738295346679</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87003929265923</v>
+        <v>11.87004113878769</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12370931835058</v>
+        <v>12.12371120393195</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10992,16 +10992,16 @@
         <v>45000</v>
       </c>
       <c r="B529" t="n">
-        <v>12.34239292144775</v>
+        <v>12.34239196777344</v>
       </c>
       <c r="C529" t="n">
-        <v>12.44736077269042</v>
+        <v>12.44735981090543</v>
       </c>
       <c r="D529" t="n">
-        <v>11.63386497873145</v>
+        <v>11.6338640798038</v>
       </c>
       <c r="E529" t="n">
-        <v>11.94001896566847</v>
+        <v>11.94001804308486</v>
       </c>
       <c r="F529" t="n">
         <v>3332216</v>
@@ -11032,16 +11032,16 @@
         <v>45002</v>
       </c>
       <c r="B531" t="n">
-        <v>11.73008346557617</v>
+        <v>11.73008251190186</v>
       </c>
       <c r="C531" t="n">
-        <v>12.42986517211394</v>
+        <v>12.42986416154627</v>
       </c>
       <c r="D531" t="n">
-        <v>11.52889649866001</v>
+        <v>11.52889556134252</v>
       </c>
       <c r="E531" t="n">
-        <v>12.26366720630515</v>
+        <v>12.26366620924963</v>
       </c>
       <c r="F531" t="n">
         <v>9035530</v>
@@ -11052,16 +11052,16 @@
         <v>45005</v>
       </c>
       <c r="B532" t="n">
-        <v>11.36269760131836</v>
+        <v>11.36269855499268</v>
       </c>
       <c r="C532" t="n">
-        <v>11.90502749511903</v>
+        <v>11.90502849431124</v>
       </c>
       <c r="D532" t="n">
-        <v>11.17025768990678</v>
+        <v>11.17025862742956</v>
       </c>
       <c r="E532" t="n">
-        <v>11.73008250392448</v>
+        <v>11.73008348843351</v>
       </c>
       <c r="F532" t="n">
         <v>5506849</v>
@@ -11152,16 +11152,16 @@
         <v>45012</v>
       </c>
       <c r="B537" t="n">
-        <v>11.36269760131836</v>
+        <v>11.36269855499268</v>
       </c>
       <c r="C537" t="n">
-        <v>11.52889555350197</v>
+        <v>11.52889652112532</v>
       </c>
       <c r="D537" t="n">
-        <v>11.12652165265694</v>
+        <v>11.12652258650894</v>
       </c>
       <c r="E537" t="n">
-        <v>11.18775261012382</v>
+        <v>11.18775354911495</v>
       </c>
       <c r="F537" t="n">
         <v>2536971</v>
@@ -11172,16 +11172,16 @@
         <v>45013</v>
       </c>
       <c r="B538" t="n">
-        <v>11.56388664245605</v>
+        <v>11.56388759613037</v>
       </c>
       <c r="C538" t="n">
-        <v>11.77382065455549</v>
+        <v>11.77382162554307</v>
       </c>
       <c r="D538" t="n">
-        <v>11.31021490399421</v>
+        <v>11.3102158367482</v>
       </c>
       <c r="E538" t="n">
-        <v>11.31021490399421</v>
+        <v>11.3102158367482</v>
       </c>
       <c r="F538" t="n">
         <v>2291643</v>
@@ -11192,16 +11192,16 @@
         <v>45014</v>
       </c>
       <c r="B539" t="n">
-        <v>11.72133541107178</v>
+        <v>11.72133636474609</v>
       </c>
       <c r="C539" t="n">
-        <v>11.76507144812072</v>
+        <v>11.7650724053535</v>
       </c>
       <c r="D539" t="n">
-        <v>11.36269754912399</v>
+        <v>11.36269847361872</v>
       </c>
       <c r="E539" t="n">
-        <v>11.6076205356713</v>
+        <v>11.60762148009351</v>
       </c>
       <c r="F539" t="n">
         <v>3319697</v>
@@ -11212,16 +11212,16 @@
         <v>45015</v>
       </c>
       <c r="B540" t="n">
-        <v>12.11496353149414</v>
+        <v>12.11496257781982</v>
       </c>
       <c r="C540" t="n">
-        <v>12.28116150020495</v>
+        <v>12.28116053344774</v>
       </c>
       <c r="D540" t="n">
-        <v>11.7125895906359</v>
+        <v>11.71258866863594</v>
       </c>
       <c r="E540" t="n">
-        <v>11.72133663051666</v>
+        <v>11.72133570782815</v>
       </c>
       <c r="F540" t="n">
         <v>2232381</v>
@@ -11272,16 +11272,16 @@
         <v>45020</v>
       </c>
       <c r="B543" t="n">
-        <v>11.27522563934326</v>
+        <v>11.27522659301758</v>
       </c>
       <c r="C543" t="n">
-        <v>11.66010462381228</v>
+        <v>11.66010561004019</v>
       </c>
       <c r="D543" t="n">
-        <v>11.25773071895163</v>
+        <v>11.2577316711462</v>
       </c>
       <c r="E543" t="n">
-        <v>11.29271971753972</v>
+        <v>11.29272067269371</v>
       </c>
       <c r="F543" t="n">
         <v>2416225</v>
@@ -11312,16 +11312,16 @@
         <v>45022</v>
       </c>
       <c r="B545" t="n">
-        <v>10.80287265777588</v>
+        <v>10.8028736114502</v>
       </c>
       <c r="C545" t="n">
-        <v>11.10902830750268</v>
+        <v>11.10902928820433</v>
       </c>
       <c r="D545" t="n">
-        <v>10.4617305340876</v>
+        <v>10.46173145764599</v>
       </c>
       <c r="E545" t="n">
-        <v>10.71540057750562</v>
+        <v>10.71540152345793</v>
       </c>
       <c r="F545" t="n">
         <v>8557394</v>
@@ -11372,16 +11372,16 @@
         <v>45028</v>
       </c>
       <c r="B548" t="n">
-        <v>12.11496353149414</v>
+        <v>12.11496257781982</v>
       </c>
       <c r="C548" t="n">
-        <v>12.33364542388005</v>
+        <v>12.33364445299137</v>
       </c>
       <c r="D548" t="n">
-        <v>11.80880955591008</v>
+        <v>11.80880862633581</v>
       </c>
       <c r="E548" t="n">
-        <v>11.96626048474012</v>
+        <v>11.96625954277151</v>
       </c>
       <c r="F548" t="n">
         <v>6602445</v>
@@ -11412,16 +11412,16 @@
         <v>45030</v>
       </c>
       <c r="B550" t="n">
-        <v>12.52608489990234</v>
+        <v>12.52608585357666</v>
       </c>
       <c r="C550" t="n">
-        <v>12.72727186303112</v>
+        <v>12.72727283202282</v>
       </c>
       <c r="D550" t="n">
-        <v>12.22867797499086</v>
+        <v>12.22867890602208</v>
       </c>
       <c r="E550" t="n">
-        <v>12.42111705636105</v>
+        <v>12.42111800204363</v>
       </c>
       <c r="F550" t="n">
         <v>2806225</v>
@@ -11432,16 +11432,16 @@
         <v>45033</v>
       </c>
       <c r="B551" t="n">
-        <v>12.34239292144775</v>
+        <v>12.34239196777344</v>
       </c>
       <c r="C551" t="n">
-        <v>12.56982186214806</v>
+        <v>12.56982089090072</v>
       </c>
       <c r="D551" t="n">
-        <v>12.22867887219524</v>
+        <v>12.2286779273074</v>
       </c>
       <c r="E551" t="n">
-        <v>12.50859173851688</v>
+        <v>12.50859077200068</v>
       </c>
       <c r="F551" t="n">
         <v>3419242</v>
@@ -11512,16 +11512,16 @@
         <v>45040</v>
       </c>
       <c r="B555" t="n">
-        <v>11.52889633178711</v>
+        <v>11.52889728546143</v>
       </c>
       <c r="C555" t="n">
-        <v>11.6688523341908</v>
+        <v>11.66885329944233</v>
       </c>
       <c r="D555" t="n">
-        <v>11.41518229038292</v>
+        <v>11.41518323465077</v>
       </c>
       <c r="E555" t="n">
-        <v>11.53764337138853</v>
+        <v>11.53764432578641</v>
       </c>
       <c r="F555" t="n">
         <v>1779282</v>
@@ -11552,16 +11552,16 @@
         <v>45042</v>
       </c>
       <c r="B557" t="n">
-        <v>11.25773239135742</v>
+        <v>11.25773143768311</v>
       </c>
       <c r="C557" t="n">
-        <v>11.49390837746124</v>
+        <v>11.49390740377979</v>
       </c>
       <c r="D557" t="n">
-        <v>11.21399634717384</v>
+        <v>11.21399539720453</v>
       </c>
       <c r="E557" t="n">
-        <v>11.24898450876447</v>
+        <v>11.24898355583121</v>
       </c>
       <c r="F557" t="n">
         <v>2213905</v>
@@ -11612,16 +11612,16 @@
         <v>45048</v>
       </c>
       <c r="B560" t="n">
-        <v>10.15557479858398</v>
+        <v>10.15557670593262</v>
       </c>
       <c r="C560" t="n">
-        <v>10.65416864246794</v>
+        <v>10.65417064345897</v>
       </c>
       <c r="D560" t="n">
-        <v>10.02436584797267</v>
+        <v>10.02436773067856</v>
       </c>
       <c r="E560" t="n">
-        <v>10.59293852875179</v>
+        <v>10.592940518243</v>
       </c>
       <c r="F560" t="n">
         <v>7078259</v>
@@ -11672,16 +11672,16 @@
         <v>45051</v>
       </c>
       <c r="B563" t="n">
-        <v>9.971883773803711</v>
+        <v>9.971882820129395</v>
       </c>
       <c r="C563" t="n">
-        <v>10.03311474103141</v>
+        <v>10.03311378150119</v>
       </c>
       <c r="D563" t="n">
-        <v>9.490784760778016</v>
+        <v>9.490783853114243</v>
       </c>
       <c r="E563" t="n">
-        <v>9.490784760778016</v>
+        <v>9.490783853114243</v>
       </c>
       <c r="F563" t="n">
         <v>9369095</v>
@@ -11692,16 +11692,16 @@
         <v>45054</v>
       </c>
       <c r="B564" t="n">
-        <v>9.960692405700684</v>
+        <v>9.960693359375</v>
       </c>
       <c r="C564" t="n">
-        <v>10.13590215170305</v>
+        <v>10.13590312215261</v>
       </c>
       <c r="D564" t="n">
-        <v>9.759200143460824</v>
+        <v>9.75920107784351</v>
       </c>
       <c r="E564" t="n">
-        <v>10.10962047893527</v>
+        <v>10.10962144686852</v>
       </c>
       <c r="F564" t="n">
         <v>5548545</v>
@@ -11732,16 +11732,16 @@
         <v>45056</v>
       </c>
       <c r="B566" t="n">
-        <v>10.00449466705322</v>
+        <v>10.00449562072754</v>
       </c>
       <c r="C566" t="n">
-        <v>10.33739447891732</v>
+        <v>10.33739546432518</v>
       </c>
       <c r="D566" t="n">
-        <v>9.969453558243071</v>
+        <v>9.969454508577106</v>
       </c>
       <c r="E566" t="n">
-        <v>10.24979001995237</v>
+        <v>10.24979099700936</v>
       </c>
       <c r="F566" t="n">
         <v>5572472</v>
@@ -11792,16 +11792,16 @@
         <v>45061</v>
       </c>
       <c r="B569" t="n">
-        <v>10.15342426300049</v>
+        <v>10.15342330932617</v>
       </c>
       <c r="C569" t="n">
-        <v>10.2147478943812</v>
+        <v>10.21474693494698</v>
       </c>
       <c r="D569" t="n">
-        <v>9.98697476788276</v>
+        <v>9.986973829842441</v>
       </c>
       <c r="E569" t="n">
-        <v>10.16218538424762</v>
+        <v>10.1621844297504</v>
       </c>
       <c r="F569" t="n">
         <v>4041445</v>
@@ -11812,16 +11812,16 @@
         <v>45062</v>
       </c>
       <c r="B570" t="n">
-        <v>9.951932907104492</v>
+        <v>9.951933860778809</v>
       </c>
       <c r="C570" t="n">
-        <v>10.35491493267188</v>
+        <v>10.35491592496318</v>
       </c>
       <c r="D570" t="n">
-        <v>9.864327605521281</v>
+        <v>9.864328550800552</v>
       </c>
       <c r="E570" t="n">
-        <v>10.17970517297524</v>
+        <v>10.17970614847653</v>
       </c>
       <c r="F570" t="n">
         <v>2372207</v>
@@ -11832,16 +11832,16 @@
         <v>45063</v>
       </c>
       <c r="B571" t="n">
-        <v>10.07458019256592</v>
+        <v>10.0745792388916</v>
       </c>
       <c r="C571" t="n">
-        <v>10.14466410253436</v>
+        <v>10.1446631422258</v>
       </c>
       <c r="D571" t="n">
-        <v>9.934412372629026</v>
+        <v>9.934411432223198</v>
       </c>
       <c r="E571" t="n">
-        <v>9.986974883370435</v>
+        <v>9.986973937988964</v>
       </c>
       <c r="F571" t="n">
         <v>5003473</v>
@@ -11872,16 +11872,16 @@
         <v>45065</v>
       </c>
       <c r="B573" t="n">
-        <v>11.44121837615967</v>
+        <v>11.44121742248535</v>
       </c>
       <c r="C573" t="n">
-        <v>12.00189047040555</v>
+        <v>12.00188946999683</v>
       </c>
       <c r="D573" t="n">
-        <v>10.51260450838727</v>
+        <v>10.51260363211687</v>
       </c>
       <c r="E573" t="n">
-        <v>10.60897093395166</v>
+        <v>10.60897004964872</v>
       </c>
       <c r="F573" t="n">
         <v>14298668</v>
@@ -11932,16 +11932,16 @@
         <v>45070</v>
       </c>
       <c r="B576" t="n">
-        <v>10.93310832977295</v>
+        <v>10.93310928344727</v>
       </c>
       <c r="C576" t="n">
-        <v>11.28352953369865</v>
+        <v>11.28353051793955</v>
       </c>
       <c r="D576" t="n">
-        <v>10.92434805271574</v>
+        <v>10.92434900562591</v>
       </c>
       <c r="E576" t="n">
-        <v>11.0820372570944</v>
+        <v>11.0820382237595</v>
       </c>
       <c r="F576" t="n">
         <v>2685985</v>
@@ -11972,16 +11972,16 @@
         <v>45072</v>
       </c>
       <c r="B578" t="n">
-        <v>11.6777515411377</v>
+        <v>11.67775058746338</v>
       </c>
       <c r="C578" t="n">
-        <v>11.90552465401795</v>
+        <v>11.90552368174234</v>
       </c>
       <c r="D578" t="n">
-        <v>11.47626010348781</v>
+        <v>11.47625916626848</v>
       </c>
       <c r="E578" t="n">
-        <v>11.54634400845561</v>
+        <v>11.54634306551281</v>
       </c>
       <c r="F578" t="n">
         <v>3617321</v>
@@ -12012,16 +12012,16 @@
         <v>45076</v>
       </c>
       <c r="B580" t="n">
-        <v>11.21344566345215</v>
+        <v>11.21344470977783</v>
       </c>
       <c r="C580" t="n">
-        <v>11.82668113132278</v>
+        <v>11.82668012549439</v>
       </c>
       <c r="D580" t="n">
-        <v>11.12584119909194</v>
+        <v>11.12584025286816</v>
       </c>
       <c r="E580" t="n">
-        <v>11.66899191461664</v>
+        <v>11.6689909221993</v>
       </c>
       <c r="F580" t="n">
         <v>4905847</v>
@@ -12032,16 +12032,16 @@
         <v>45077</v>
       </c>
       <c r="B581" t="n">
-        <v>11.2747688293457</v>
+        <v>11.27476787567139</v>
       </c>
       <c r="C581" t="n">
-        <v>11.46749999253707</v>
+        <v>11.46749902256062</v>
       </c>
       <c r="D581" t="n">
-        <v>11.07327738877377</v>
+        <v>11.07327645214257</v>
       </c>
       <c r="E581" t="n">
-        <v>11.20468492336154</v>
+        <v>11.20468397561525</v>
       </c>
       <c r="F581" t="n">
         <v>3703640</v>
@@ -12112,16 +12112,16 @@
         <v>45083</v>
       </c>
       <c r="B585" t="n">
-        <v>12.53628063201904</v>
+        <v>12.53628158569336</v>
       </c>
       <c r="C585" t="n">
-        <v>12.73777205594852</v>
+        <v>12.73777302495092</v>
       </c>
       <c r="D585" t="n">
-        <v>11.88800329000613</v>
+        <v>11.88800419436395</v>
       </c>
       <c r="E585" t="n">
-        <v>11.91428411997714</v>
+        <v>11.91428502633423</v>
       </c>
       <c r="F585" t="n">
         <v>8194955</v>
@@ -12152,16 +12152,16 @@
         <v>45086</v>
       </c>
       <c r="B587" t="n">
-        <v>12.7903356552124</v>
+        <v>12.79033470153809</v>
       </c>
       <c r="C587" t="n">
-        <v>13.0181087720978</v>
+        <v>13.01810780144024</v>
       </c>
       <c r="D587" t="n">
-        <v>12.60636561230446</v>
+        <v>12.60636467234733</v>
       </c>
       <c r="E587" t="n">
-        <v>12.69397091678955</v>
+        <v>12.69396997030039</v>
       </c>
       <c r="F587" t="n">
         <v>3362705</v>
@@ -12192,16 +12192,16 @@
         <v>45090</v>
       </c>
       <c r="B589" t="n">
-        <v>12.52752113342285</v>
+        <v>12.52752208709717</v>
       </c>
       <c r="C589" t="n">
-        <v>13.04439014033381</v>
+        <v>13.04439113335547</v>
       </c>
       <c r="D589" t="n">
-        <v>12.29974717843629</v>
+        <v>12.29974811477101</v>
       </c>
       <c r="E589" t="n">
-        <v>12.86042010176204</v>
+        <v>12.86042108077874</v>
       </c>
       <c r="F589" t="n">
         <v>6116837</v>
@@ -12252,16 +12252,16 @@
         <v>45093</v>
       </c>
       <c r="B592" t="n">
-        <v>11.92304515838623</v>
+        <v>11.92304420471191</v>
       </c>
       <c r="C592" t="n">
-        <v>12.76405454487264</v>
+        <v>12.76405352392952</v>
       </c>
       <c r="D592" t="n">
-        <v>11.66023093759705</v>
+        <v>11.66023000494414</v>
       </c>
       <c r="E592" t="n">
-        <v>12.76405454487264</v>
+        <v>12.76405352392952</v>
       </c>
       <c r="F592" t="n">
         <v>19648730</v>
@@ -12392,16 +12392,16 @@
         <v>45104</v>
       </c>
       <c r="B599" t="n">
-        <v>10.52486228942871</v>
+        <v>10.52486133575439</v>
       </c>
       <c r="C599" t="n">
-        <v>10.94055037724765</v>
+        <v>10.94054938590718</v>
       </c>
       <c r="D599" t="n">
-        <v>10.41872932213938</v>
+        <v>10.41872837808194</v>
       </c>
       <c r="E599" t="n">
-        <v>10.58677381961654</v>
+        <v>10.58677286033232</v>
       </c>
       <c r="F599" t="n">
         <v>17154900</v>
@@ -12452,16 +12452,16 @@
         <v>45107</v>
       </c>
       <c r="B602" t="n">
-        <v>10.71059513092041</v>
+        <v>10.71059417724609</v>
       </c>
       <c r="C602" t="n">
-        <v>11.12628321632794</v>
+        <v>11.12628222564065</v>
       </c>
       <c r="D602" t="n">
-        <v>10.56023988393194</v>
+        <v>10.56023894364529</v>
       </c>
       <c r="E602" t="n">
-        <v>10.83441734710793</v>
+        <v>10.83441638240845</v>
       </c>
       <c r="F602" t="n">
         <v>11622700</v>
@@ -12472,16 +12472,16 @@
         <v>45110</v>
       </c>
       <c r="B603" t="n">
-        <v>10.79019355773926</v>
+        <v>10.79019451141357</v>
       </c>
       <c r="C603" t="n">
-        <v>11.00245946140029</v>
+        <v>11.0024604338354</v>
       </c>
       <c r="D603" t="n">
-        <v>10.66637220233851</v>
+        <v>10.66637314506908</v>
       </c>
       <c r="E603" t="n">
-        <v>10.8344158318694</v>
+        <v>10.83441678945224</v>
       </c>
       <c r="F603" t="n">
         <v>4753300</v>
@@ -12552,16 +12552,16 @@
         <v>45114</v>
       </c>
       <c r="B607" t="n">
-        <v>10.52486228942871</v>
+        <v>10.52486133575439</v>
       </c>
       <c r="C607" t="n">
-        <v>10.71943981786074</v>
+        <v>10.71943884655545</v>
       </c>
       <c r="D607" t="n">
-        <v>10.40104091599275</v>
+        <v>10.40103997353808</v>
       </c>
       <c r="E607" t="n">
-        <v>10.52486228942871</v>
+        <v>10.52486133575439</v>
       </c>
       <c r="F607" t="n">
         <v>9448200</v>
@@ -12612,16 +12612,16 @@
         <v>45119</v>
       </c>
       <c r="B610" t="n">
-        <v>10.40988540649414</v>
+        <v>10.40988445281982</v>
       </c>
       <c r="C610" t="n">
-        <v>10.772506584255</v>
+        <v>10.7725055973601</v>
       </c>
       <c r="D610" t="n">
-        <v>10.39219615710589</v>
+        <v>10.39219520505212</v>
       </c>
       <c r="E610" t="n">
-        <v>10.61330671364005</v>
+        <v>10.61330574132983</v>
       </c>
       <c r="F610" t="n">
         <v>7787100</v>
@@ -12712,16 +12712,16 @@
         <v>45126</v>
       </c>
       <c r="B615" t="n">
-        <v>9.905753135681152</v>
+        <v>9.905752182006836</v>
       </c>
       <c r="C615" t="n">
-        <v>10.24184129543884</v>
+        <v>10.2418403094077</v>
       </c>
       <c r="D615" t="n">
-        <v>9.720020227485323</v>
+        <v>9.720019291692406</v>
       </c>
       <c r="E615" t="n">
-        <v>10.24184129543884</v>
+        <v>10.2418403094077</v>
       </c>
       <c r="F615" t="n">
         <v>11108100</v>
@@ -12772,16 +12772,16 @@
         <v>45131</v>
       </c>
       <c r="B618" t="n">
-        <v>10.52486228942871</v>
+        <v>10.52486133575439</v>
       </c>
       <c r="C618" t="n">
-        <v>10.64868450633452</v>
+        <v>10.64868354144048</v>
       </c>
       <c r="D618" t="n">
-        <v>10.40988554080099</v>
+        <v>10.40988459754489</v>
       </c>
       <c r="E618" t="n">
-        <v>10.62215147537965</v>
+        <v>10.62215051288981</v>
       </c>
       <c r="F618" t="n">
         <v>4297000</v>
@@ -12852,16 +12852,16 @@
         <v>45135</v>
       </c>
       <c r="B622" t="n">
-        <v>10.35681819915771</v>
+        <v>10.3568172454834</v>
       </c>
       <c r="C622" t="n">
-        <v>10.3921958534306</v>
+        <v>10.39219489649865</v>
       </c>
       <c r="D622" t="n">
-        <v>10.18877455222896</v>
+        <v>10.1887736140284</v>
       </c>
       <c r="E622" t="n">
-        <v>10.34797357472204</v>
+        <v>10.34797262186215</v>
       </c>
       <c r="F622" t="n">
         <v>4029200</v>
@@ -12912,16 +12912,16 @@
         <v>45140</v>
       </c>
       <c r="B625" t="n">
-        <v>10.40988540649414</v>
+        <v>10.40988445281982</v>
       </c>
       <c r="C625" t="n">
-        <v>10.83441727017422</v>
+        <v>10.83441627760753</v>
       </c>
       <c r="D625" t="n">
-        <v>10.25068553587919</v>
+        <v>10.25068459678955</v>
       </c>
       <c r="E625" t="n">
-        <v>10.66637361833498</v>
+        <v>10.66637264116317</v>
       </c>
       <c r="F625" t="n">
         <v>9104400</v>
@@ -12952,16 +12952,16 @@
         <v>45142</v>
       </c>
       <c r="B627" t="n">
-        <v>10.71943950653076</v>
+        <v>10.71943855285645</v>
       </c>
       <c r="C627" t="n">
-        <v>11.21472751629927</v>
+        <v>11.21472651856076</v>
       </c>
       <c r="D627" t="n">
-        <v>10.59561729322118</v>
+        <v>10.59561635056293</v>
       </c>
       <c r="E627" t="n">
-        <v>10.70175110089786</v>
+        <v>10.70175014879723</v>
       </c>
       <c r="F627" t="n">
         <v>16706200</v>
@@ -13032,16 +13032,16 @@
         <v>45148</v>
       </c>
       <c r="B631" t="n">
-        <v>10.63099575042725</v>
+        <v>10.63099479675293</v>
       </c>
       <c r="C631" t="n">
-        <v>10.86095008358703</v>
+        <v>10.86094910928421</v>
       </c>
       <c r="D631" t="n">
-        <v>10.52486194315988</v>
+        <v>10.5248609990065</v>
       </c>
       <c r="E631" t="n">
-        <v>10.66637340502643</v>
+        <v>10.66637244817849</v>
       </c>
       <c r="F631" t="n">
         <v>4975000</v>
@@ -13052,16 +13052,16 @@
         <v>45149</v>
       </c>
       <c r="B632" t="n">
-        <v>10.44526290893555</v>
+        <v>10.44526195526123</v>
       </c>
       <c r="C632" t="n">
-        <v>10.78135020769543</v>
+        <v>10.78134922333564</v>
       </c>
       <c r="D632" t="n">
-        <v>10.39219600501725</v>
+        <v>10.39219505618805</v>
       </c>
       <c r="E632" t="n">
-        <v>10.56908427896187</v>
+        <v>10.56908331398241</v>
       </c>
       <c r="F632" t="n">
         <v>4348800</v>
@@ -13072,16 +13072,16 @@
         <v>45152</v>
       </c>
       <c r="B633" t="n">
-        <v>10.44526290893555</v>
+        <v>10.44526195526123</v>
       </c>
       <c r="C633" t="n">
-        <v>10.6044619337508</v>
+        <v>10.60446096554128</v>
       </c>
       <c r="D633" t="n">
-        <v>10.27721841608578</v>
+        <v>10.27721747775428</v>
       </c>
       <c r="E633" t="n">
-        <v>10.42757365980617</v>
+        <v>10.42757270774692</v>
       </c>
       <c r="F633" t="n">
         <v>3064200</v>
@@ -13132,16 +13132,16 @@
         <v>45155</v>
       </c>
       <c r="B636" t="n">
-        <v>10.13570785522461</v>
+        <v>10.13570690155029</v>
       </c>
       <c r="C636" t="n">
-        <v>10.51601827899524</v>
+        <v>10.51601728953731</v>
       </c>
       <c r="D636" t="n">
-        <v>10.10917482484777</v>
+        <v>10.10917387366996</v>
       </c>
       <c r="E636" t="n">
-        <v>10.43641834439489</v>
+        <v>10.43641736242656</v>
       </c>
       <c r="F636" t="n">
         <v>6587600</v>
@@ -13192,16 +13192,16 @@
         <v>45160</v>
       </c>
       <c r="B639" t="n">
-        <v>10.63099575042725</v>
+        <v>10.63099479675293</v>
       </c>
       <c r="C639" t="n">
-        <v>10.70175105962561</v>
+        <v>10.70175009960405</v>
       </c>
       <c r="D639" t="n">
-        <v>10.18877464620255</v>
+        <v>10.18877373219854</v>
       </c>
       <c r="E639" t="n">
-        <v>10.24184070636641</v>
+        <v>10.24183978760201</v>
       </c>
       <c r="F639" t="n">
         <v>5680500</v>
@@ -13332,16 +13332,16 @@
         <v>45169</v>
       </c>
       <c r="B646" t="n">
-        <v>10.35681819915771</v>
+        <v>10.3568172454834</v>
       </c>
       <c r="C646" t="n">
-        <v>10.71059474188658</v>
+        <v>10.71059375563589</v>
       </c>
       <c r="D646" t="n">
-        <v>10.27721826617627</v>
+        <v>10.27721731983166</v>
       </c>
       <c r="E646" t="n">
-        <v>10.59561715463224</v>
+        <v>10.59561617896889</v>
       </c>
       <c r="F646" t="n">
         <v>8716900</v>
@@ -13392,16 +13392,16 @@
         <v>45174</v>
       </c>
       <c r="B649" t="n">
-        <v>10.21530818939209</v>
+        <v>10.21530723571777</v>
       </c>
       <c r="C649" t="n">
-        <v>10.7371292535431</v>
+        <v>10.73712825115294</v>
       </c>
       <c r="D649" t="n">
-        <v>10.21530818939209</v>
+        <v>10.21530723571777</v>
       </c>
       <c r="E649" t="n">
-        <v>10.7371292535431</v>
+        <v>10.73712825115294</v>
       </c>
       <c r="F649" t="n">
         <v>8659200</v>
@@ -13532,16 +13532,16 @@
         <v>45184</v>
       </c>
       <c r="B656" t="n">
-        <v>9.375087738037109</v>
+        <v>9.375086784362793</v>
       </c>
       <c r="C656" t="n">
-        <v>10.00304173917788</v>
+        <v>10.00304072162537</v>
       </c>
       <c r="D656" t="n">
-        <v>9.375087738037109</v>
+        <v>9.375086784362793</v>
       </c>
       <c r="E656" t="n">
-        <v>9.923441805537948</v>
+        <v>9.923440796082692</v>
       </c>
       <c r="F656" t="n">
         <v>14904000</v>
@@ -13552,16 +13552,16 @@
         <v>45187</v>
       </c>
       <c r="B657" t="n">
-        <v>8.844422340393066</v>
+        <v>8.84442138671875</v>
       </c>
       <c r="C657" t="n">
-        <v>9.322021113035499</v>
+        <v>9.322020107862773</v>
       </c>
       <c r="D657" t="n">
-        <v>8.773667029147509</v>
+        <v>8.773666083102581</v>
       </c>
       <c r="E657" t="n">
-        <v>9.322021113035499</v>
+        <v>9.322020107862773</v>
       </c>
       <c r="F657" t="n">
         <v>19156300</v>
@@ -13572,16 +13572,16 @@
         <v>45188</v>
       </c>
       <c r="B658" t="n">
-        <v>8.800199508666992</v>
+        <v>8.800198554992676</v>
       </c>
       <c r="C658" t="n">
-        <v>8.950554746511546</v>
+        <v>8.950553776543289</v>
       </c>
       <c r="D658" t="n">
-        <v>8.667533519260521</v>
+        <v>8.667532579963169</v>
       </c>
       <c r="E658" t="n">
-        <v>8.844421786292413</v>
+        <v>8.844420827825743</v>
       </c>
       <c r="F658" t="n">
         <v>8872800</v>
@@ -13612,16 +13612,16 @@
         <v>45190</v>
       </c>
       <c r="B660" t="n">
-        <v>8.932867050170898</v>
+        <v>8.932866096496582</v>
       </c>
       <c r="C660" t="n">
-        <v>8.985933112755202</v>
+        <v>8.985932153415543</v>
       </c>
       <c r="D660" t="n">
-        <v>8.738289519265452</v>
+        <v>8.738288586364265</v>
       </c>
       <c r="E660" t="n">
-        <v>8.853267112824586</v>
+        <v>8.853266167648371</v>
       </c>
       <c r="F660" t="n">
         <v>7093000</v>
@@ -13632,16 +13632,16 @@
         <v>45191</v>
       </c>
       <c r="B661" t="n">
-        <v>8.579089164733887</v>
+        <v>8.57908821105957</v>
       </c>
       <c r="C661" t="n">
-        <v>9.003621859012968</v>
+        <v>9.003620858146471</v>
       </c>
       <c r="D661" t="n">
-        <v>8.428733923371484</v>
+        <v>8.428732986411056</v>
       </c>
       <c r="E661" t="n">
-        <v>8.994777234586989</v>
+        <v>8.994776234703684</v>
       </c>
       <c r="F661" t="n">
         <v>16137800</v>
@@ -13732,16 +13732,16 @@
         <v>45198</v>
       </c>
       <c r="B666" t="n">
-        <v>8.623311996459961</v>
+        <v>8.623311042785645</v>
       </c>
       <c r="C666" t="n">
-        <v>8.755977997479093</v>
+        <v>8.7559770291329</v>
       </c>
       <c r="D666" t="n">
-        <v>8.587934339956869</v>
+        <v>8.587933390195058</v>
       </c>
       <c r="E666" t="n">
-        <v>8.702911934459385</v>
+        <v>8.702910971981906</v>
       </c>
       <c r="F666" t="n">
         <v>6662100</v>
@@ -13772,16 +13772,16 @@
         <v>45202</v>
       </c>
       <c r="B668" t="n">
-        <v>7.659268856048584</v>
+        <v>7.659268379211426</v>
       </c>
       <c r="C668" t="n">
-        <v>7.933446292673103</v>
+        <v>7.933445798766693</v>
       </c>
       <c r="D668" t="n">
-        <v>7.570825147453722</v>
+        <v>7.570824676122735</v>
       </c>
       <c r="E668" t="n">
-        <v>7.880379392740378</v>
+        <v>7.880378902137712</v>
       </c>
       <c r="F668" t="n">
         <v>18608300</v>
@@ -13792,16 +13792,16 @@
         <v>45203</v>
       </c>
       <c r="B669" t="n">
-        <v>7.738869190216064</v>
+        <v>7.738868236541748</v>
       </c>
       <c r="C669" t="n">
-        <v>7.853846776544223</v>
+        <v>7.853845808701018</v>
       </c>
       <c r="D669" t="n">
-        <v>7.632736228252335</v>
+        <v>7.632735287656968</v>
       </c>
       <c r="E669" t="n">
-        <v>7.756558438944921</v>
+        <v>7.756557483090727</v>
       </c>
       <c r="F669" t="n">
         <v>14186500</v>
@@ -13812,16 +13812,16 @@
         <v>45204</v>
       </c>
       <c r="B670" t="n">
-        <v>7.685802459716797</v>
+        <v>7.68580150604248</v>
       </c>
       <c r="C670" t="n">
-        <v>7.800780048621283</v>
+        <v>7.800779080680249</v>
       </c>
       <c r="D670" t="n">
-        <v>7.579669495374922</v>
+        <v>7.579668554869859</v>
       </c>
       <c r="E670" t="n">
-        <v>7.738869363622646</v>
+        <v>7.73886840336365</v>
       </c>
       <c r="F670" t="n">
         <v>5277500</v>
@@ -13832,16 +13832,16 @@
         <v>45205</v>
       </c>
       <c r="B671" t="n">
-        <v>7.473536491394043</v>
+        <v>7.473536014556885</v>
       </c>
       <c r="C671" t="n">
-        <v>7.6062033287201</v>
+        <v>7.606202843418344</v>
       </c>
       <c r="D671" t="n">
-        <v>7.38509277664649</v>
+        <v>7.385092305452343</v>
       </c>
       <c r="E671" t="n">
-        <v>7.561981049611414</v>
+        <v>7.561980567131191</v>
       </c>
       <c r="F671" t="n">
         <v>8202400</v>
@@ -13872,16 +13872,16 @@
         <v>45209</v>
       </c>
       <c r="B673" t="n">
-        <v>8.101490020751953</v>
+        <v>8.101489067077637</v>
       </c>
       <c r="C673" t="n">
-        <v>8.18993457381352</v>
+        <v>8.189933609727872</v>
       </c>
       <c r="D673" t="n">
-        <v>7.906912510098369</v>
+        <v>7.906911579328923</v>
       </c>
       <c r="E673" t="n">
-        <v>7.951134786629153</v>
+        <v>7.95113385065404</v>
       </c>
       <c r="F673" t="n">
         <v>9907700</v>
@@ -13912,16 +13912,16 @@
         <v>45212</v>
       </c>
       <c r="B675" t="n">
-        <v>7.561980724334717</v>
+        <v>7.561980247497559</v>
       </c>
       <c r="C675" t="n">
-        <v>7.933446503317459</v>
+        <v>7.933446003056718</v>
       </c>
       <c r="D675" t="n">
-        <v>7.500069198857738</v>
+        <v>7.500068725924546</v>
       </c>
       <c r="E675" t="n">
-        <v>7.898068850246236</v>
+        <v>7.898068352216309</v>
       </c>
       <c r="F675" t="n">
         <v>6681200</v>
@@ -13932,16 +13932,16 @@
         <v>45215</v>
       </c>
       <c r="B676" t="n">
-        <v>7.561980724334717</v>
+        <v>7.561980247497559</v>
       </c>
       <c r="C676" t="n">
-        <v>7.721179741420333</v>
+        <v>7.721179254544534</v>
       </c>
       <c r="D676" t="n">
-        <v>7.473536169921766</v>
+        <v>7.473535698661672</v>
       </c>
       <c r="E676" t="n">
-        <v>7.623891406341913</v>
+        <v>7.623890925600842</v>
       </c>
       <c r="F676" t="n">
         <v>6364500</v>
@@ -13952,16 +13952,16 @@
         <v>45216</v>
       </c>
       <c r="B677" t="n">
-        <v>7.641581058502197</v>
+        <v>7.641580104827881</v>
       </c>
       <c r="C677" t="n">
-        <v>7.668114088840552</v>
+        <v>7.668113131854896</v>
       </c>
       <c r="D677" t="n">
-        <v>7.447003534591332</v>
+        <v>7.447002605200417</v>
       </c>
       <c r="E677" t="n">
-        <v>7.544291874811851</v>
+        <v>7.544290933279289</v>
       </c>
       <c r="F677" t="n">
         <v>6592700</v>
@@ -14232,16 +14232,16 @@
         <v>45237</v>
       </c>
       <c r="B691" t="n">
-        <v>8.357978820800781</v>
+        <v>8.357977867126465</v>
       </c>
       <c r="C691" t="n">
-        <v>8.37566807008851</v>
+        <v>8.375667114395791</v>
       </c>
       <c r="D691" t="n">
-        <v>7.845002400034246</v>
+        <v>7.845001504892315</v>
       </c>
       <c r="E691" t="n">
-        <v>7.871535430496009</v>
+        <v>7.871534532326568</v>
       </c>
       <c r="F691" t="n">
         <v>8029000</v>
@@ -14252,16 +14252,16 @@
         <v>45238</v>
       </c>
       <c r="B692" t="n">
-        <v>8.101490020751953</v>
+        <v>8.101489067077637</v>
       </c>
       <c r="C692" t="n">
-        <v>8.649844056712263</v>
+        <v>8.649843038487949</v>
       </c>
       <c r="D692" t="n">
-        <v>8.013046311160156</v>
+        <v>8.013045367897073</v>
       </c>
       <c r="E692" t="n">
-        <v>8.357978212466772</v>
+        <v>8.357977228599713</v>
       </c>
       <c r="F692" t="n">
         <v>19964500</v>
@@ -14272,16 +14272,16 @@
         <v>45239</v>
       </c>
       <c r="B693" t="n">
-        <v>7.959980010986328</v>
+        <v>7.959979057312012</v>
       </c>
       <c r="C693" t="n">
-        <v>8.189935191514248</v>
+        <v>8.189934210289316</v>
       </c>
       <c r="D693" t="n">
-        <v>7.77424711032452</v>
+        <v>7.774246178902609</v>
       </c>
       <c r="E693" t="n">
-        <v>8.189935191514248</v>
+        <v>8.189934210289316</v>
       </c>
       <c r="F693" t="n">
         <v>11094800</v>
@@ -14392,16 +14392,16 @@
         <v>45250</v>
       </c>
       <c r="B699" t="n">
-        <v>8.932867050170898</v>
+        <v>8.932866096496582</v>
       </c>
       <c r="C699" t="n">
-        <v>8.932867050170898</v>
+        <v>8.932866096496582</v>
       </c>
       <c r="D699" t="n">
-        <v>8.61446730078565</v>
+        <v>8.614466381103741</v>
       </c>
       <c r="E699" t="n">
-        <v>8.676378831760479</v>
+        <v>8.676377905468886</v>
       </c>
       <c r="F699" t="n">
         <v>4921500</v>
@@ -14412,16 +14412,16 @@
         <v>45251</v>
       </c>
       <c r="B700" t="n">
-        <v>8.623311996459961</v>
+        <v>8.623311042785645</v>
       </c>
       <c r="C700" t="n">
-        <v>8.941710904987794</v>
+        <v>8.941709916100921</v>
       </c>
       <c r="D700" t="n">
-        <v>8.614467371466722</v>
+        <v>8.614466418770554</v>
       </c>
       <c r="E700" t="n">
-        <v>8.932867123464419</v>
+        <v>8.932866135555601</v>
       </c>
       <c r="F700" t="n">
         <v>8608600</v>
@@ -14432,16 +14432,16 @@
         <v>45252</v>
       </c>
       <c r="B701" t="n">
-        <v>8.596778869628906</v>
+        <v>8.59677791595459</v>
       </c>
       <c r="C701" t="n">
-        <v>9.03015536785397</v>
+        <v>9.030154366103503</v>
       </c>
       <c r="D701" t="n">
-        <v>8.587934244733736</v>
+        <v>8.587933292040589</v>
       </c>
       <c r="E701" t="n">
-        <v>8.649844932060216</v>
+        <v>8.649843972499074</v>
       </c>
       <c r="F701" t="n">
         <v>12126100</v>
@@ -14492,16 +14492,16 @@
         <v>45257</v>
       </c>
       <c r="B704" t="n">
-        <v>8.092646598815918</v>
+        <v>8.092645645141602</v>
       </c>
       <c r="C704" t="n">
-        <v>8.446424020141739</v>
+        <v>8.446423024776681</v>
       </c>
       <c r="D704" t="n">
-        <v>8.074958191658068</v>
+        <v>8.074957240068235</v>
       </c>
       <c r="E704" t="n">
-        <v>8.411046362356148</v>
+        <v>8.411045371160153</v>
       </c>
       <c r="F704" t="n">
         <v>5901700</v>
@@ -14712,16 +14712,16 @@
         <v>45272</v>
       </c>
       <c r="B715" t="n">
-        <v>8.083802223205566</v>
+        <v>8.08380126953125</v>
       </c>
       <c r="C715" t="n">
-        <v>8.357978840037788</v>
+        <v>8.3579778540179</v>
       </c>
       <c r="D715" t="n">
-        <v>8.066112973877122</v>
+        <v>8.066112022289667</v>
       </c>
       <c r="E715" t="n">
-        <v>8.18109056410251</v>
+        <v>8.181089598950749</v>
       </c>
       <c r="F715" t="n">
         <v>4001400</v>
@@ -14732,16 +14732,16 @@
         <v>45273</v>
       </c>
       <c r="B716" t="n">
-        <v>8.658689498901367</v>
+        <v>8.658688545227051</v>
       </c>
       <c r="C716" t="n">
-        <v>8.711756404446733</v>
+        <v>8.71175544492759</v>
       </c>
       <c r="D716" t="n">
-        <v>8.101490786289347</v>
+        <v>8.101489893985299</v>
       </c>
       <c r="E716" t="n">
-        <v>8.110335411125217</v>
+        <v>8.110334517847015</v>
       </c>
       <c r="F716" t="n">
         <v>4810200</v>
@@ -14752,16 +14752,16 @@
         <v>45274</v>
       </c>
       <c r="B717" t="n">
-        <v>8.623311996459961</v>
+        <v>8.623311042785645</v>
       </c>
       <c r="C717" t="n">
-        <v>8.932867123464419</v>
+        <v>8.932866135555601</v>
       </c>
       <c r="D717" t="n">
-        <v>8.596778964950108</v>
+        <v>8.596778014210148</v>
       </c>
       <c r="E717" t="n">
-        <v>8.685222684472906</v>
+        <v>8.685221723951727</v>
       </c>
       <c r="F717" t="n">
         <v>9075200</v>
@@ -14772,16 +14772,16 @@
         <v>45275</v>
       </c>
       <c r="B718" t="n">
-        <v>8.791356086730957</v>
+        <v>8.791355133056641</v>
       </c>
       <c r="C718" t="n">
-        <v>8.791356086730957</v>
+        <v>8.791355133056641</v>
       </c>
       <c r="D718" t="n">
-        <v>8.534867853590605</v>
+        <v>8.534866927739781</v>
       </c>
       <c r="E718" t="n">
-        <v>8.720600770241887</v>
+        <v>8.720599824243012</v>
       </c>
       <c r="F718" t="n">
         <v>7122400</v>
@@ -14792,16 +14792,16 @@
         <v>45278</v>
       </c>
       <c r="B719" t="n">
-        <v>8.835577011108398</v>
+        <v>8.835576057434082</v>
       </c>
       <c r="C719" t="n">
-        <v>8.977087622316056</v>
+        <v>8.977086653367691</v>
       </c>
       <c r="D719" t="n">
-        <v>8.800199358306484</v>
+        <v>8.800198408450679</v>
       </c>
       <c r="E719" t="n">
-        <v>8.809043982374407</v>
+        <v>8.809043031563952</v>
       </c>
       <c r="F719" t="n">
         <v>3928300</v>
@@ -14812,16 +14812,16 @@
         <v>45279</v>
       </c>
       <c r="B720" t="n">
-        <v>8.879799842834473</v>
+        <v>8.879798889160156</v>
       </c>
       <c r="C720" t="n">
-        <v>8.941710528238881</v>
+        <v>8.941709567915471</v>
       </c>
       <c r="D720" t="n">
-        <v>8.817889157430063</v>
+        <v>8.817888210404842</v>
       </c>
       <c r="E720" t="n">
-        <v>8.932866747088129</v>
+        <v>8.932865787714524</v>
       </c>
       <c r="F720" t="n">
         <v>3267000</v>
@@ -27849,42 +27849,42 @@
     </row>
     <row r="1372">
       <c r="A1372" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1372" t="n">
-        <v>3.339999914169312</v>
+        <v>3.259999990463257</v>
       </c>
       <c r="C1372" t="n">
-        <v>3.450000047683716</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="D1372" t="n">
-        <v>3.329999923706055</v>
+        <v>3.259999990463257</v>
       </c>
       <c r="E1372" t="n">
-        <v>3.440000057220459</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="F1372" t="n">
-        <v>9078300</v>
+        <v>10648100</v>
       </c>
     </row>
     <row r="1373">
       <c r="A1373" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1373" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="C1373" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="D1373" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="E1373" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="F1373" t="n">
-        <v>10648100</v>
+        <v>9699000</v>
       </c>
     </row>
   </sheetData>

--- a/database/VAMO3.xlsx
+++ b/database/VAMO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1373"/>
+  <dimension ref="A1:F1375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44229</v>
       </c>
       <c r="B2" t="n">
-        <v>6.844325542449951</v>
+        <v>6.844325065612793</v>
       </c>
       <c r="C2" t="n">
-        <v>7.276819619617557</v>
+        <v>7.276819112648979</v>
       </c>
       <c r="D2" t="n">
-        <v>6.844325542449951</v>
+        <v>6.844325065612793</v>
       </c>
       <c r="E2" t="n">
-        <v>7.094164231854394</v>
+        <v>7.09416373761123</v>
       </c>
       <c r="F2" t="n">
         <v>4750609</v>
@@ -512,16 +512,16 @@
         <v>44232</v>
       </c>
       <c r="B5" t="n">
-        <v>6.823331356048584</v>
+        <v>6.823330402374268</v>
       </c>
       <c r="C5" t="n">
-        <v>6.909409992235542</v>
+        <v>6.909409026530302</v>
       </c>
       <c r="D5" t="n">
-        <v>6.699461247702325</v>
+        <v>6.699460311340922</v>
       </c>
       <c r="E5" t="n">
-        <v>6.873718632603384</v>
+        <v>6.873717671886607</v>
       </c>
       <c r="F5" t="n">
         <v>4402737</v>
@@ -532,16 +532,16 @@
         <v>44235</v>
       </c>
       <c r="B6" t="n">
-        <v>7.211735725402832</v>
+        <v>7.21173620223999</v>
       </c>
       <c r="C6" t="n">
-        <v>7.619035766065515</v>
+        <v>7.619036269833193</v>
       </c>
       <c r="D6" t="n">
-        <v>6.827529615229921</v>
+        <v>6.82753006666352</v>
       </c>
       <c r="E6" t="n">
-        <v>6.85482295876889</v>
+        <v>6.854823412007115</v>
       </c>
       <c r="F6" t="n">
         <v>3162478</v>
@@ -552,16 +552,16 @@
         <v>44236</v>
       </c>
       <c r="B7" t="n">
-        <v>7.119358539581299</v>
+        <v>7.119358062744141</v>
       </c>
       <c r="C7" t="n">
-        <v>7.367097937617529</v>
+        <v>7.367097444187393</v>
       </c>
       <c r="D7" t="n">
-        <v>6.953499173999</v>
+        <v>6.953498708270694</v>
       </c>
       <c r="E7" t="n">
-        <v>7.266322575504579</v>
+        <v>7.266322088824129</v>
       </c>
       <c r="F7" t="n">
         <v>1374461</v>
@@ -612,16 +612,16 @@
         <v>44239</v>
       </c>
       <c r="B10" t="n">
-        <v>7.029080867767334</v>
+        <v>7.029079914093018</v>
       </c>
       <c r="C10" t="n">
-        <v>7.194940242201317</v>
+        <v>7.19493926602394</v>
       </c>
       <c r="D10" t="n">
-        <v>6.913608771181656</v>
+        <v>6.913607833174078</v>
       </c>
       <c r="E10" t="n">
-        <v>6.949300131730055</v>
+        <v>6.949299188880033</v>
       </c>
       <c r="F10" t="n">
         <v>649929</v>
@@ -632,16 +632,16 @@
         <v>44244</v>
       </c>
       <c r="B11" t="n">
-        <v>7.274720191955566</v>
+        <v>7.274720668792725</v>
       </c>
       <c r="C11" t="n">
-        <v>7.388092163706458</v>
+        <v>7.388092647974826</v>
       </c>
       <c r="D11" t="n">
-        <v>7.113059436567523</v>
+        <v>7.11305990280828</v>
       </c>
       <c r="E11" t="n">
-        <v>7.117258849481164</v>
+        <v>7.11725931599718</v>
       </c>
       <c r="F11" t="n">
         <v>2613098</v>
@@ -652,16 +652,16 @@
         <v>44245</v>
       </c>
       <c r="B12" t="n">
-        <v>7.222233772277832</v>
+        <v>7.222232341766357</v>
       </c>
       <c r="C12" t="n">
-        <v>7.379695135793175</v>
+        <v>7.379693674093248</v>
       </c>
       <c r="D12" t="n">
-        <v>7.138254432522623</v>
+        <v>7.138253018644978</v>
       </c>
       <c r="E12" t="n">
-        <v>7.287317780882985</v>
+        <v>7.287316337480287</v>
       </c>
       <c r="F12" t="n">
         <v>993747</v>
@@ -672,16 +672,16 @@
         <v>44246</v>
       </c>
       <c r="B13" t="n">
-        <v>7.453176021575928</v>
+        <v>7.453176498413086</v>
       </c>
       <c r="C13" t="n">
-        <v>7.595941445618074</v>
+        <v>7.595941931589037</v>
       </c>
       <c r="D13" t="n">
-        <v>7.142452755462365</v>
+        <v>7.142453212420159</v>
       </c>
       <c r="E13" t="n">
-        <v>7.159247971413373</v>
+        <v>7.159248429445686</v>
       </c>
       <c r="F13" t="n">
         <v>1995604</v>
@@ -692,16 +692,16 @@
         <v>44249</v>
       </c>
       <c r="B14" t="n">
-        <v>7.30621337890625</v>
+        <v>7.306212902069092</v>
       </c>
       <c r="C14" t="n">
-        <v>7.724010745681502</v>
+        <v>7.724010241576962</v>
       </c>
       <c r="D14" t="n">
-        <v>7.050075153474859</v>
+        <v>7.050074693354461</v>
       </c>
       <c r="E14" t="n">
-        <v>7.054274566636445</v>
+        <v>7.054274106241974</v>
       </c>
       <c r="F14" t="n">
         <v>1355405</v>
@@ -712,16 +712,16 @@
         <v>44250</v>
       </c>
       <c r="B15" t="n">
-        <v>7.30621337890625</v>
+        <v>7.306212902069092</v>
       </c>
       <c r="C15" t="n">
-        <v>7.480470759734867</v>
+        <v>7.480470271524869</v>
       </c>
       <c r="D15" t="n">
-        <v>7.243227864044258</v>
+        <v>7.243227391317824</v>
       </c>
       <c r="E15" t="n">
-        <v>7.308311867795231</v>
+        <v>7.308311390821116</v>
       </c>
       <c r="F15" t="n">
         <v>1706116</v>
@@ -732,16 +732,16 @@
         <v>44251</v>
       </c>
       <c r="B16" t="n">
-        <v>7.327208042144775</v>
+        <v>7.327207565307617</v>
       </c>
       <c r="C16" t="n">
-        <v>7.556052112537071</v>
+        <v>7.556051620807289</v>
       </c>
       <c r="D16" t="n">
-        <v>7.108861287011643</v>
+        <v>7.108860824383968</v>
       </c>
       <c r="E16" t="n">
-        <v>7.451078148150898</v>
+        <v>7.451077663252569</v>
       </c>
       <c r="F16" t="n">
         <v>1445414</v>
@@ -752,16 +752,16 @@
         <v>44252</v>
       </c>
       <c r="B17" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254642486572</v>
       </c>
       <c r="C17" t="n">
-        <v>7.400689808525235</v>
+        <v>7.40069079726115</v>
       </c>
       <c r="D17" t="n">
-        <v>6.945100983960817</v>
+        <v>6.945101911829834</v>
       </c>
       <c r="E17" t="n">
-        <v>7.360799849541025</v>
+        <v>7.360800832947622</v>
       </c>
       <c r="F17" t="n">
         <v>1264991</v>
@@ -812,16 +812,16 @@
         <v>44257</v>
       </c>
       <c r="B20" t="n">
-        <v>7.178143501281738</v>
+        <v>7.178143978118896</v>
       </c>
       <c r="C20" t="n">
-        <v>7.178143501281738</v>
+        <v>7.178143978118896</v>
       </c>
       <c r="D20" t="n">
-        <v>6.718356084859394</v>
+        <v>6.718356531153318</v>
       </c>
       <c r="E20" t="n">
-        <v>7.003886129168523</v>
+        <v>7.003886594429932</v>
       </c>
       <c r="F20" t="n">
         <v>1173360</v>
@@ -832,16 +832,16 @@
         <v>44258</v>
       </c>
       <c r="B21" t="n">
-        <v>7.085767269134521</v>
+        <v>7.08576774597168</v>
       </c>
       <c r="C21" t="n">
-        <v>7.10886120006331</v>
+        <v>7.108861678454575</v>
       </c>
       <c r="D21" t="n">
-        <v>6.896813161397048</v>
+        <v>6.896813625518528</v>
       </c>
       <c r="E21" t="n">
-        <v>7.10886120006331</v>
+        <v>7.108861678454575</v>
       </c>
       <c r="F21" t="n">
         <v>1419466</v>
@@ -852,16 +852,16 @@
         <v>44259</v>
       </c>
       <c r="B22" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254642486572</v>
       </c>
       <c r="C22" t="n">
-        <v>7.222233019817944</v>
+        <v>7.222233984711942</v>
       </c>
       <c r="D22" t="n">
-        <v>6.966096425558127</v>
+        <v>6.966097356232146</v>
       </c>
       <c r="E22" t="n">
-        <v>7.117259059009463</v>
+        <v>7.117260009878886</v>
       </c>
       <c r="F22" t="n">
         <v>757778</v>
@@ -872,16 +872,16 @@
         <v>44260</v>
       </c>
       <c r="B23" t="n">
-        <v>7.016484260559082</v>
+        <v>7.016482830047607</v>
       </c>
       <c r="C23" t="n">
-        <v>7.176045732845249</v>
+        <v>7.176044269802593</v>
       </c>
       <c r="D23" t="n">
-        <v>7.014384147975241</v>
+        <v>7.014382717891935</v>
       </c>
       <c r="E23" t="n">
-        <v>7.11725962818392</v>
+        <v>7.117258177126498</v>
       </c>
       <c r="F23" t="n">
         <v>1309995</v>
@@ -932,16 +932,16 @@
         <v>44265</v>
       </c>
       <c r="B26" t="n">
-        <v>6.252270221710205</v>
+        <v>6.252270698547363</v>
       </c>
       <c r="C26" t="n">
-        <v>6.592386944261464</v>
+        <v>6.592387447038047</v>
       </c>
       <c r="D26" t="n">
-        <v>6.124201524146216</v>
+        <v>6.124201991216056</v>
       </c>
       <c r="E26" t="n">
-        <v>6.586089042665994</v>
+        <v>6.58608954496226</v>
       </c>
       <c r="F26" t="n">
         <v>1291345</v>
@@ -952,16 +952,16 @@
         <v>44266</v>
       </c>
       <c r="B27" t="n">
-        <v>6.670068264007568</v>
+        <v>6.67006778717041</v>
       </c>
       <c r="C27" t="n">
-        <v>6.670068264007568</v>
+        <v>6.67006778717041</v>
       </c>
       <c r="D27" t="n">
-        <v>6.214479816572392</v>
+        <v>6.21447937230484</v>
       </c>
       <c r="E27" t="n">
-        <v>6.287962243213972</v>
+        <v>6.287961793693228</v>
       </c>
       <c r="F27" t="n">
         <v>2230763</v>
@@ -992,16 +992,16 @@
         <v>44270</v>
       </c>
       <c r="B29" t="n">
-        <v>7.033279895782471</v>
+        <v>7.033280372619629</v>
       </c>
       <c r="C29" t="n">
-        <v>7.127756543943293</v>
+        <v>7.12775702718571</v>
       </c>
       <c r="D29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="E29" t="n">
-        <v>6.667969107167907</v>
+        <v>6.667969559237991</v>
       </c>
       <c r="F29" t="n">
         <v>2428215</v>
@@ -1012,16 +1012,16 @@
         <v>44271</v>
       </c>
       <c r="B30" t="n">
-        <v>7.390191555023193</v>
+        <v>7.390192031860352</v>
       </c>
       <c r="C30" t="n">
-        <v>7.425883723946737</v>
+        <v>7.42588420308686</v>
       </c>
       <c r="D30" t="n">
-        <v>6.970294095405131</v>
+        <v>6.970294545149255</v>
       </c>
       <c r="E30" t="n">
-        <v>6.970294095405131</v>
+        <v>6.970294545149255</v>
       </c>
       <c r="F30" t="n">
         <v>4282725</v>
@@ -1052,16 +1052,16 @@
         <v>44273</v>
       </c>
       <c r="B32" t="n">
-        <v>7.589643478393555</v>
+        <v>7.589643955230713</v>
       </c>
       <c r="C32" t="n">
-        <v>7.89826828612256</v>
+        <v>7.898268782349795</v>
       </c>
       <c r="D32" t="n">
-        <v>7.459475468261102</v>
+        <v>7.45947593692015</v>
       </c>
       <c r="E32" t="n">
-        <v>7.600140793817841</v>
+        <v>7.600141271314518</v>
       </c>
       <c r="F32" t="n">
         <v>3661176</v>
@@ -1072,16 +1072,16 @@
         <v>44274</v>
       </c>
       <c r="B33" t="n">
-        <v>7.516161918640137</v>
+        <v>7.516162872314453</v>
       </c>
       <c r="C33" t="n">
-        <v>7.77859722734807</v>
+        <v>7.778598214321006</v>
       </c>
       <c r="D33" t="n">
-        <v>7.430081663165087</v>
+        <v>7.430082605917269</v>
       </c>
       <c r="E33" t="n">
-        <v>7.600140438103936</v>
+        <v>7.600141402433712</v>
       </c>
       <c r="F33" t="n">
         <v>2872989</v>
@@ -1112,16 +1112,16 @@
         <v>44278</v>
       </c>
       <c r="B35" t="n">
-        <v>7.516161918640137</v>
+        <v>7.516162872314453</v>
       </c>
       <c r="C35" t="n">
-        <v>7.558151178372036</v>
+        <v>7.558152137374083</v>
       </c>
       <c r="D35" t="n">
-        <v>7.436381188637199</v>
+        <v>7.436382132188685</v>
       </c>
       <c r="E35" t="n">
-        <v>7.511962505590234</v>
+        <v>7.511963458731716</v>
       </c>
       <c r="F35" t="n">
         <v>638577</v>
@@ -1132,16 +1132,16 @@
         <v>44279</v>
       </c>
       <c r="B36" t="n">
-        <v>7.159247875213623</v>
+        <v>7.159248352050781</v>
       </c>
       <c r="C36" t="n">
-        <v>7.656826740361056</v>
+        <v>7.656827250339138</v>
       </c>
       <c r="D36" t="n">
-        <v>7.159247875213623</v>
+        <v>7.159248352050781</v>
       </c>
       <c r="E36" t="n">
-        <v>7.392291336410457</v>
+        <v>7.392291828769327</v>
       </c>
       <c r="F36" t="n">
         <v>973070</v>
@@ -1152,16 +1152,16 @@
         <v>44280</v>
       </c>
       <c r="B37" t="n">
-        <v>7.705114364624023</v>
+        <v>7.705113887786865</v>
       </c>
       <c r="C37" t="n">
-        <v>7.789094507299701</v>
+        <v>7.789094025265366</v>
       </c>
       <c r="D37" t="n">
-        <v>7.033279717574721</v>
+        <v>7.033279282314587</v>
       </c>
       <c r="E37" t="n">
-        <v>7.159248307999206</v>
+        <v>7.159247864943406</v>
       </c>
       <c r="F37" t="n">
         <v>2991380</v>
@@ -1192,16 +1192,16 @@
         <v>44284</v>
       </c>
       <c r="B39" t="n">
-        <v>7.232730388641357</v>
+        <v>7.232729911804199</v>
       </c>
       <c r="C39" t="n">
-        <v>7.663125173574427</v>
+        <v>7.663124668362338</v>
       </c>
       <c r="D39" t="n">
-        <v>7.232730388641357</v>
+        <v>7.232729911804199</v>
       </c>
       <c r="E39" t="n">
-        <v>7.568648526962992</v>
+        <v>7.568648027979529</v>
       </c>
       <c r="F39" t="n">
         <v>3953908</v>
@@ -1212,16 +1212,16 @@
         <v>44285</v>
       </c>
       <c r="B40" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254642486572</v>
       </c>
       <c r="C40" t="n">
-        <v>7.379694366927925</v>
+        <v>7.379695352858839</v>
       </c>
       <c r="D40" t="n">
-        <v>7.138253688812256</v>
+        <v>7.138254642486572</v>
       </c>
       <c r="E40" t="n">
-        <v>7.257924377559402</v>
+        <v>7.257925347221784</v>
       </c>
       <c r="F40" t="n">
         <v>1472174</v>
@@ -1232,16 +1232,16 @@
         <v>44286</v>
       </c>
       <c r="B41" t="n">
-        <v>7.348202228546143</v>
+        <v>7.348202705383301</v>
       </c>
       <c r="C41" t="n">
-        <v>7.379694172420294</v>
+        <v>7.379694651301018</v>
       </c>
       <c r="D41" t="n">
-        <v>6.997588185825906</v>
+        <v>6.997588639911132</v>
       </c>
       <c r="E41" t="n">
-        <v>7.226432242387128</v>
+        <v>7.226432711322428</v>
       </c>
       <c r="F41" t="n">
         <v>2544984</v>
@@ -1252,16 +1252,16 @@
         <v>44287</v>
       </c>
       <c r="B42" t="n">
-        <v>7.348202228546143</v>
+        <v>7.348202705383301</v>
       </c>
       <c r="C42" t="n">
-        <v>7.524558900189283</v>
+        <v>7.524559388470522</v>
       </c>
       <c r="D42" t="n">
-        <v>7.171845556903002</v>
+        <v>7.171846022296081</v>
       </c>
       <c r="E42" t="n">
-        <v>7.35869954317086</v>
+        <v>7.358700020689207</v>
       </c>
       <c r="F42" t="n">
         <v>877384</v>
@@ -1272,16 +1272,16 @@
         <v>44291</v>
       </c>
       <c r="B43" t="n">
-        <v>7.327208042144775</v>
+        <v>7.327207565307617</v>
       </c>
       <c r="C43" t="n">
-        <v>7.400690060753461</v>
+        <v>7.400689579134269</v>
       </c>
       <c r="D43" t="n">
-        <v>7.260023925614861</v>
+        <v>7.260023453149884</v>
       </c>
       <c r="E43" t="n">
-        <v>7.400690060753461</v>
+        <v>7.400689579134269</v>
       </c>
       <c r="F43" t="n">
         <v>1080107</v>
@@ -1292,16 +1292,16 @@
         <v>44292</v>
       </c>
       <c r="B44" t="n">
-        <v>7.211735725402832</v>
+        <v>7.21173620223999</v>
       </c>
       <c r="C44" t="n">
-        <v>7.379694387891328</v>
+        <v>7.379694875833847</v>
       </c>
       <c r="D44" t="n">
-        <v>7.190741095540401</v>
+        <v>7.190741570989402</v>
       </c>
       <c r="E44" t="n">
-        <v>7.369197072960112</v>
+        <v>7.369197560208552</v>
       </c>
       <c r="F44" t="n">
         <v>1319726</v>
@@ -1332,16 +1332,16 @@
         <v>44294</v>
       </c>
       <c r="B46" t="n">
-        <v>7.589643478393555</v>
+        <v>7.589643955230713</v>
       </c>
       <c r="C46" t="n">
-        <v>7.789094906838682</v>
+        <v>7.789095396206844</v>
       </c>
       <c r="D46" t="n">
-        <v>7.215935477392881</v>
+        <v>7.215935930750956</v>
       </c>
       <c r="E46" t="n">
-        <v>7.243228010419292</v>
+        <v>7.243228465492086</v>
       </c>
       <c r="F46" t="n">
         <v>2111967</v>
@@ -1352,16 +1352,16 @@
         <v>44295</v>
       </c>
       <c r="B47" t="n">
-        <v>7.652626991271973</v>
+        <v>7.652627468109131</v>
       </c>
       <c r="C47" t="n">
-        <v>7.873073016243731</v>
+        <v>7.873073506816938</v>
       </c>
       <c r="D47" t="n">
-        <v>7.474170221459922</v>
+        <v>7.474170687177393</v>
       </c>
       <c r="E47" t="n">
-        <v>7.595941009729709</v>
+        <v>7.595941483034749</v>
       </c>
       <c r="F47" t="n">
         <v>1442171</v>
@@ -1372,16 +1372,16 @@
         <v>44298</v>
       </c>
       <c r="B48" t="n">
-        <v>7.7890944480896</v>
+        <v>7.789094924926758</v>
       </c>
       <c r="C48" t="n">
-        <v>8.015839208001262</v>
+        <v>8.015839698719409</v>
       </c>
       <c r="D48" t="n">
-        <v>7.644229717818412</v>
+        <v>7.64423018578716</v>
       </c>
       <c r="E48" t="n">
-        <v>7.688319089439362</v>
+        <v>7.688319560107198</v>
       </c>
       <c r="F48" t="n">
         <v>2187380</v>
@@ -1392,16 +1392,16 @@
         <v>44299</v>
       </c>
       <c r="B49" t="n">
-        <v>7.726110458374023</v>
+        <v>7.726109981536865</v>
       </c>
       <c r="C49" t="n">
-        <v>7.898268547699764</v>
+        <v>7.898268060237418</v>
       </c>
       <c r="D49" t="n">
-        <v>7.642131120403916</v>
+        <v>7.642130648749763</v>
       </c>
       <c r="E49" t="n">
-        <v>7.786995864004779</v>
+        <v>7.786995383409918</v>
       </c>
       <c r="F49" t="n">
         <v>1044023</v>
@@ -1412,16 +1412,16 @@
         <v>44300</v>
       </c>
       <c r="B50" t="n">
-        <v>7.877272129058838</v>
+        <v>7.877274036407471</v>
       </c>
       <c r="C50" t="n">
-        <v>7.877272129058838</v>
+        <v>7.877274036407471</v>
       </c>
       <c r="D50" t="n">
-        <v>7.518259302698232</v>
+        <v>7.518261123117962</v>
       </c>
       <c r="E50" t="n">
-        <v>7.786994097388884</v>
+        <v>7.786995982878214</v>
       </c>
       <c r="F50" t="n">
         <v>2026013</v>
@@ -1452,16 +1452,16 @@
         <v>44302</v>
       </c>
       <c r="B52" t="n">
-        <v>8.187995910644531</v>
+        <v>8.187994956970215</v>
       </c>
       <c r="C52" t="n">
-        <v>8.25098141876933</v>
+        <v>8.250980457758949</v>
       </c>
       <c r="D52" t="n">
-        <v>8.091419971587269</v>
+        <v>8.09141902916137</v>
       </c>
       <c r="E52" t="n">
-        <v>8.1124145997659</v>
+        <v>8.112413654894709</v>
       </c>
       <c r="F52" t="n">
         <v>1067133</v>
@@ -1472,16 +1472,16 @@
         <v>44305</v>
       </c>
       <c r="B53" t="n">
-        <v>8.208992958068848</v>
+        <v>8.208991050720215</v>
       </c>
       <c r="C53" t="n">
-        <v>8.244684323567677</v>
+        <v>8.244682407926204</v>
       </c>
       <c r="D53" t="n">
-        <v>8.059930404635271</v>
+        <v>8.059928531921125</v>
       </c>
       <c r="E53" t="n">
-        <v>8.187998323702958</v>
+        <v>8.1879964212324</v>
       </c>
       <c r="F53" t="n">
         <v>546541</v>
@@ -1532,16 +1532,16 @@
         <v>44309</v>
       </c>
       <c r="B56" t="n">
-        <v>8.187995910644531</v>
+        <v>8.187994956970215</v>
       </c>
       <c r="C56" t="n">
-        <v>8.21948866470693</v>
+        <v>8.219487707364582</v>
       </c>
       <c r="D56" t="n">
-        <v>7.923460510774868</v>
+        <v>7.923459587911585</v>
       </c>
       <c r="E56" t="n">
-        <v>8.215290063788986</v>
+        <v>8.215289106935657</v>
       </c>
       <c r="F56" t="n">
         <v>1129166</v>
@@ -1552,16 +1552,16 @@
         <v>44312</v>
       </c>
       <c r="B57" t="n">
-        <v>7.978049278259277</v>
+        <v>7.978048324584961</v>
       </c>
       <c r="C57" t="n">
-        <v>8.187997217134104</v>
+        <v>8.187996238363182</v>
       </c>
       <c r="D57" t="n">
-        <v>7.938158504201501</v>
+        <v>7.93815755529562</v>
       </c>
       <c r="E57" t="n">
-        <v>8.185898728134749</v>
+        <v>8.185897749614673</v>
       </c>
       <c r="F57" t="n">
         <v>1270667</v>
@@ -1592,16 +1592,16 @@
         <v>44314</v>
       </c>
       <c r="B59" t="n">
-        <v>8.397945404052734</v>
+        <v>8.397946357727051</v>
       </c>
       <c r="C59" t="n">
-        <v>8.469328120611465</v>
+        <v>8.469329082392035</v>
       </c>
       <c r="D59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116615684439186</v>
       </c>
       <c r="E59" t="n">
-        <v>8.116614762712898</v>
+        <v>8.116615684439186</v>
       </c>
       <c r="F59" t="n">
         <v>4397466</v>
@@ -1612,16 +1612,16 @@
         <v>44315</v>
       </c>
       <c r="B60" t="n">
-        <v>8.607893943786621</v>
+        <v>8.607894897460938</v>
       </c>
       <c r="C60" t="n">
-        <v>8.815743374956226</v>
+        <v>8.815744351658321</v>
       </c>
       <c r="D60" t="n">
-        <v>8.167001850598284</v>
+        <v>8.167002755425871</v>
       </c>
       <c r="E60" t="n">
-        <v>8.469327926938387</v>
+        <v>8.469328865260882</v>
       </c>
       <c r="F60" t="n">
         <v>3250459</v>
@@ -1632,16 +1632,16 @@
         <v>44316</v>
       </c>
       <c r="B61" t="n">
-        <v>8.733863830566406</v>
+        <v>8.733864784240723</v>
       </c>
       <c r="C61" t="n">
-        <v>8.733863830566406</v>
+        <v>8.733864784240723</v>
       </c>
       <c r="D61" t="n">
-        <v>8.580601889171566</v>
+        <v>8.580602826110796</v>
       </c>
       <c r="E61" t="n">
-        <v>8.580601889171566</v>
+        <v>8.580602826110796</v>
       </c>
       <c r="F61" t="n">
         <v>3200590</v>
@@ -1672,16 +1672,16 @@
         <v>44320</v>
       </c>
       <c r="B63" t="n">
-        <v>9.298625946044922</v>
+        <v>9.298624992370605</v>
       </c>
       <c r="C63" t="n">
-        <v>9.544266879269465</v>
+        <v>9.544265900402022</v>
       </c>
       <c r="D63" t="n">
-        <v>8.719167760068038</v>
+        <v>8.719166865823404</v>
       </c>
       <c r="E63" t="n">
-        <v>8.849335779760766</v>
+        <v>8.849334872165999</v>
       </c>
       <c r="F63" t="n">
         <v>2875017</v>
@@ -1712,16 +1712,16 @@
         <v>44322</v>
       </c>
       <c r="B65" t="n">
-        <v>9.764711380004883</v>
+        <v>9.764712333679199</v>
       </c>
       <c r="C65" t="n">
-        <v>9.783605896673567</v>
+        <v>9.783606852193223</v>
       </c>
       <c r="D65" t="n">
-        <v>9.537965814857868</v>
+        <v>9.537966746386992</v>
       </c>
       <c r="E65" t="n">
-        <v>9.783605896673567</v>
+        <v>9.783606852193223</v>
       </c>
       <c r="F65" t="n">
         <v>8042425</v>
@@ -1732,16 +1732,16 @@
         <v>44323</v>
       </c>
       <c r="B66" t="n">
-        <v>9.867585182189941</v>
+        <v>9.867586135864258</v>
       </c>
       <c r="C66" t="n">
-        <v>10.05234067674103</v>
+        <v>10.05234164827144</v>
       </c>
       <c r="D66" t="n">
-        <v>9.554762613617749</v>
+        <v>9.554763537058646</v>
       </c>
       <c r="E66" t="n">
-        <v>9.827695224893009</v>
+        <v>9.827696174712075</v>
       </c>
       <c r="F66" t="n">
         <v>7085572</v>
@@ -1752,16 +1752,16 @@
         <v>44326</v>
       </c>
       <c r="B67" t="n">
-        <v>9.380505561828613</v>
+        <v>9.38050651550293</v>
       </c>
       <c r="C67" t="n">
-        <v>9.886481655948959</v>
+        <v>9.886482661063617</v>
       </c>
       <c r="D67" t="n">
-        <v>9.254536160500752</v>
+        <v>9.254537101368319</v>
       </c>
       <c r="E67" t="n">
-        <v>9.867585515134721</v>
+        <v>9.867586518328292</v>
       </c>
       <c r="F67" t="n">
         <v>3466157</v>
@@ -1772,16 +1772,16 @@
         <v>44327</v>
       </c>
       <c r="B68" t="n">
-        <v>9.617746353149414</v>
+        <v>9.617748260498047</v>
       </c>
       <c r="C68" t="n">
-        <v>9.645040506833098</v>
+        <v>9.645042419594585</v>
       </c>
       <c r="D68" t="n">
-        <v>8.964807071897692</v>
+        <v>8.964808849758313</v>
       </c>
       <c r="E68" t="n">
-        <v>9.294426475068693</v>
+        <v>9.294428318297966</v>
       </c>
       <c r="F68" t="n">
         <v>2188597</v>
@@ -1812,16 +1812,16 @@
         <v>44329</v>
       </c>
       <c r="B70" t="n">
-        <v>9.655538558959961</v>
+        <v>9.655539512634277</v>
       </c>
       <c r="C70" t="n">
-        <v>9.699627931810785</v>
+        <v>9.699628889839794</v>
       </c>
       <c r="D70" t="n">
-        <v>9.489679194450057</v>
+        <v>9.489680131742498</v>
       </c>
       <c r="E70" t="n">
-        <v>9.556862498159457</v>
+        <v>9.556863442087572</v>
       </c>
       <c r="F70" t="n">
         <v>2493897</v>
@@ -1892,16 +1892,16 @@
         <v>44335</v>
       </c>
       <c r="B74" t="n">
-        <v>9.82349681854248</v>
+        <v>9.823495864868164</v>
       </c>
       <c r="C74" t="n">
-        <v>10.10272898361439</v>
+        <v>10.10272800283195</v>
       </c>
       <c r="D74" t="n">
-        <v>9.334317531017494</v>
+        <v>9.334316624833162</v>
       </c>
       <c r="E74" t="n">
-        <v>9.678632890034629</v>
+        <v>9.678631950423839</v>
       </c>
       <c r="F74" t="n">
         <v>3058684</v>
@@ -1912,16 +1912,16 @@
         <v>44336</v>
       </c>
       <c r="B75" t="n">
-        <v>10.13002300262451</v>
+        <v>10.1300220489502</v>
       </c>
       <c r="C75" t="n">
-        <v>10.22869906616216</v>
+        <v>10.22869810319815</v>
       </c>
       <c r="D75" t="n">
-        <v>9.504376186303976</v>
+        <v>9.504375291530147</v>
       </c>
       <c r="E75" t="n">
-        <v>9.873885584647184</v>
+        <v>9.873884655086501</v>
       </c>
       <c r="F75" t="n">
         <v>2816227</v>
@@ -1972,16 +1972,16 @@
         <v>44341</v>
       </c>
       <c r="B78" t="n">
-        <v>10.43444728851318</v>
+        <v>10.4344482421875</v>
       </c>
       <c r="C78" t="n">
-        <v>10.49323176138078</v>
+        <v>10.49323272042781</v>
       </c>
       <c r="D78" t="n">
-        <v>10.18880721200021</v>
+        <v>10.18880814322383</v>
       </c>
       <c r="E78" t="n">
-        <v>10.23499588189026</v>
+        <v>10.23499681733537</v>
       </c>
       <c r="F78" t="n">
         <v>2528360</v>
@@ -2032,16 +2032,16 @@
         <v>44344</v>
       </c>
       <c r="B81" t="n">
-        <v>10.72837543487549</v>
+        <v>10.7283763885498</v>
       </c>
       <c r="C81" t="n">
-        <v>10.82915078936937</v>
+        <v>10.82915175200188</v>
       </c>
       <c r="D81" t="n">
-        <v>10.46803862888618</v>
+        <v>10.46803955941845</v>
       </c>
       <c r="E81" t="n">
-        <v>10.65489342246942</v>
+        <v>10.65489436961172</v>
       </c>
       <c r="F81" t="n">
         <v>2512953</v>
@@ -2052,16 +2052,16 @@
         <v>44347</v>
       </c>
       <c r="B82" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727928161621</v>
       </c>
       <c r="C82" t="n">
-        <v>11.3960123574381</v>
+        <v>11.39601333414453</v>
       </c>
       <c r="D82" t="n">
-        <v>10.70738084874532</v>
+        <v>10.70738176643192</v>
       </c>
       <c r="E82" t="n">
-        <v>10.7493709213828</v>
+        <v>10.74937184266819</v>
       </c>
       <c r="F82" t="n">
         <v>1849644</v>
@@ -2072,16 +2072,16 @@
         <v>44348</v>
       </c>
       <c r="B83" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727928161621</v>
       </c>
       <c r="C83" t="n">
-        <v>11.25324773405977</v>
+        <v>11.25324869853042</v>
       </c>
       <c r="D83" t="n">
-        <v>11.03280086745621</v>
+        <v>11.03280181303325</v>
       </c>
       <c r="E83" t="n">
-        <v>11.23225229184377</v>
+        <v>11.23225325451498</v>
       </c>
       <c r="F83" t="n">
         <v>1761257</v>
@@ -2112,16 +2112,16 @@
         <v>44351</v>
       </c>
       <c r="B85" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727928161621</v>
       </c>
       <c r="C85" t="n">
-        <v>11.1419742445191</v>
+        <v>11.14197519945295</v>
       </c>
       <c r="D85" t="n">
-        <v>10.6569935733749</v>
+        <v>10.656994486743</v>
       </c>
       <c r="E85" t="n">
-        <v>10.93832503055962</v>
+        <v>10.93832596803951</v>
       </c>
       <c r="F85" t="n">
         <v>2427404</v>
@@ -2132,16 +2132,16 @@
         <v>44354</v>
       </c>
       <c r="B86" t="n">
-        <v>11.10838317871094</v>
+        <v>11.10838222503662</v>
       </c>
       <c r="C86" t="n">
-        <v>11.61225999957573</v>
+        <v>11.6122590026427</v>
       </c>
       <c r="D86" t="n">
-        <v>10.89843524749561</v>
+        <v>10.8984343118457</v>
       </c>
       <c r="E86" t="n">
-        <v>11.14407453808413</v>
+        <v>11.14407358134564</v>
       </c>
       <c r="F86" t="n">
         <v>2940293</v>
@@ -2152,16 +2152,16 @@
         <v>44355</v>
       </c>
       <c r="B87" t="n">
-        <v>11.0202054977417</v>
+        <v>11.02020454406738</v>
       </c>
       <c r="C87" t="n">
-        <v>11.16926884083993</v>
+        <v>11.16926787426587</v>
       </c>
       <c r="D87" t="n">
-        <v>10.93412604839051</v>
+        <v>10.9341251021654</v>
       </c>
       <c r="E87" t="n">
-        <v>11.1209800524548</v>
+        <v>11.12097909005958</v>
       </c>
       <c r="F87" t="n">
         <v>1135248</v>
@@ -2172,16 +2172,16 @@
         <v>44356</v>
       </c>
       <c r="B88" t="n">
-        <v>10.90893268585205</v>
+        <v>10.90893173217773</v>
       </c>
       <c r="C88" t="n">
-        <v>11.1251793334517</v>
+        <v>11.1251783608728</v>
       </c>
       <c r="D88" t="n">
-        <v>10.7325751877154</v>
+        <v>10.7325742494585</v>
       </c>
       <c r="E88" t="n">
-        <v>11.00340933714343</v>
+        <v>11.00340837520983</v>
       </c>
       <c r="F88" t="n">
         <v>1361892</v>
@@ -2192,16 +2192,16 @@
         <v>44357</v>
       </c>
       <c r="B89" t="n">
-        <v>10.79136085510254</v>
+        <v>10.79135990142822</v>
       </c>
       <c r="C89" t="n">
-        <v>10.99081229192654</v>
+        <v>10.99081132062593</v>
       </c>
       <c r="D89" t="n">
-        <v>10.70108361394333</v>
+        <v>10.70108266824717</v>
       </c>
       <c r="E89" t="n">
-        <v>10.9404250134143</v>
+        <v>10.94042404656661</v>
       </c>
       <c r="F89" t="n">
         <v>1040779</v>
@@ -2212,16 +2212,16 @@
         <v>44358</v>
       </c>
       <c r="B90" t="n">
-        <v>10.60240650177002</v>
+        <v>10.60240840911865</v>
       </c>
       <c r="C90" t="n">
-        <v>10.84174787766967</v>
+        <v>10.84174982807527</v>
       </c>
       <c r="D90" t="n">
-        <v>10.51842717132385</v>
+        <v>10.5184290635648</v>
       </c>
       <c r="E90" t="n">
-        <v>10.7598678478309</v>
+        <v>10.75986978350646</v>
       </c>
       <c r="F90" t="n">
         <v>1174982</v>
@@ -2232,16 +2232,16 @@
         <v>44361</v>
       </c>
       <c r="B91" t="n">
-        <v>10.94252300262451</v>
+        <v>10.94252395629883</v>
       </c>
       <c r="C91" t="n">
-        <v>11.24904848576352</v>
+        <v>11.24904946615247</v>
       </c>
       <c r="D91" t="n">
-        <v>10.64649564588704</v>
+        <v>10.64649657376166</v>
       </c>
       <c r="E91" t="n">
-        <v>10.72837567397531</v>
+        <v>10.72837660898603</v>
       </c>
       <c r="F91" t="n">
         <v>2250630</v>
@@ -2252,16 +2252,16 @@
         <v>44362</v>
       </c>
       <c r="B92" t="n">
-        <v>10.94462299346924</v>
+        <v>10.94462203979492</v>
       </c>
       <c r="C92" t="n">
-        <v>11.35192304724218</v>
+        <v>11.35192205807723</v>
       </c>
       <c r="D92" t="n">
-        <v>10.81445498526105</v>
+        <v>10.8144540429291</v>
       </c>
       <c r="E92" t="n">
-        <v>10.92152825044157</v>
+        <v>10.92152729877964</v>
       </c>
       <c r="F92" t="n">
         <v>1573941</v>
@@ -2272,16 +2272,16 @@
         <v>44363</v>
       </c>
       <c r="B93" t="n">
-        <v>11.12727832794189</v>
+        <v>11.12727928161621</v>
       </c>
       <c r="C93" t="n">
-        <v>11.31413313643548</v>
+        <v>11.31413410612437</v>
       </c>
       <c r="D93" t="n">
-        <v>10.89213554476112</v>
+        <v>10.8921364782823</v>
       </c>
       <c r="E93" t="n">
-        <v>10.96141896166432</v>
+        <v>10.9614199011235</v>
       </c>
       <c r="F93" t="n">
         <v>2948808</v>
@@ -2312,16 +2312,16 @@
         <v>44365</v>
       </c>
       <c r="B95" t="n">
-        <v>11.33722591400146</v>
+        <v>11.33722686767578</v>
       </c>
       <c r="C95" t="n">
-        <v>11.33722591400146</v>
+        <v>11.33722686767578</v>
       </c>
       <c r="D95" t="n">
-        <v>10.99290978879124</v>
+        <v>10.99291071350208</v>
       </c>
       <c r="E95" t="n">
-        <v>11.31203187298242</v>
+        <v>11.31203282453744</v>
       </c>
       <c r="F95" t="n">
         <v>1275938</v>
@@ -2412,16 +2412,16 @@
         <v>44372</v>
       </c>
       <c r="B100" t="n">
-        <v>11.61225986480713</v>
+        <v>11.61226081848145</v>
       </c>
       <c r="C100" t="n">
-        <v>11.71933394168402</v>
+        <v>11.71933490415196</v>
       </c>
       <c r="D100" t="n">
-        <v>11.34142572157541</v>
+        <v>11.34142665300706</v>
       </c>
       <c r="E100" t="n">
-        <v>11.71093592711753</v>
+        <v>11.71093688889577</v>
       </c>
       <c r="F100" t="n">
         <v>3580087</v>
@@ -2432,16 +2432,16 @@
         <v>44375</v>
       </c>
       <c r="B101" t="n">
-        <v>11.86209774017334</v>
+        <v>11.86209869384766</v>
       </c>
       <c r="C101" t="n">
-        <v>12.00066375318507</v>
+        <v>12.00066471799965</v>
       </c>
       <c r="D101" t="n">
-        <v>11.40441044302249</v>
+        <v>11.40441135990023</v>
       </c>
       <c r="E101" t="n">
-        <v>11.58916512703814</v>
+        <v>11.58916605876955</v>
       </c>
       <c r="F101" t="n">
         <v>1601511</v>
@@ -2452,16 +2452,16 @@
         <v>44376</v>
       </c>
       <c r="B102" t="n">
-        <v>12.01746082305908</v>
+        <v>12.0174617767334</v>
       </c>
       <c r="C102" t="n">
-        <v>12.01746082305908</v>
+        <v>12.0174617767334</v>
       </c>
       <c r="D102" t="n">
-        <v>11.58916534895242</v>
+        <v>11.58916626863832</v>
       </c>
       <c r="E102" t="n">
-        <v>11.85999866672677</v>
+        <v>11.8599996079053</v>
       </c>
       <c r="F102" t="n">
         <v>1352973</v>
@@ -2492,16 +2492,16 @@
         <v>44378</v>
       </c>
       <c r="B104" t="n">
-        <v>12.47094821929932</v>
+        <v>12.47094917297363</v>
       </c>
       <c r="C104" t="n">
-        <v>12.63470827087047</v>
+        <v>12.6347092370678</v>
       </c>
       <c r="D104" t="n">
-        <v>12.33028290864975</v>
+        <v>12.33028385156715</v>
       </c>
       <c r="E104" t="n">
-        <v>12.38906900530821</v>
+        <v>12.38906995272109</v>
       </c>
       <c r="F104" t="n">
         <v>8890212</v>
@@ -2512,16 +2512,16 @@
         <v>44379</v>
       </c>
       <c r="B105" t="n">
-        <v>12.95803070068359</v>
+        <v>12.95802974700928</v>
       </c>
       <c r="C105" t="n">
-        <v>13.1280894777343</v>
+        <v>13.12808851154414</v>
       </c>
       <c r="D105" t="n">
-        <v>12.5003425684372</v>
+        <v>12.50034164844744</v>
       </c>
       <c r="E105" t="n">
-        <v>12.52133719856387</v>
+        <v>12.52133627702896</v>
       </c>
       <c r="F105" t="n">
         <v>2908669</v>
@@ -2532,16 +2532,16 @@
         <v>44382</v>
       </c>
       <c r="B106" t="n">
-        <v>13.12179183959961</v>
+        <v>13.12179088592529</v>
       </c>
       <c r="C106" t="n">
-        <v>13.50179938445063</v>
+        <v>13.50179840315787</v>
       </c>
       <c r="D106" t="n">
-        <v>12.96432966535849</v>
+        <v>12.96432872312831</v>
       </c>
       <c r="E106" t="n">
-        <v>12.96432966535849</v>
+        <v>12.96432872312831</v>
       </c>
       <c r="F106" t="n">
         <v>1748688</v>
@@ -2552,16 +2552,16 @@
         <v>44383</v>
       </c>
       <c r="B107" t="n">
-        <v>13.04830932617188</v>
+        <v>13.04830837249756</v>
       </c>
       <c r="C107" t="n">
-        <v>13.36113192669314</v>
+        <v>13.36113095015526</v>
       </c>
       <c r="D107" t="n">
-        <v>13.00002053822385</v>
+        <v>13.00001958807886</v>
       </c>
       <c r="E107" t="n">
-        <v>13.14908469176732</v>
+        <v>13.14908373072754</v>
       </c>
       <c r="F107" t="n">
         <v>1738957</v>
@@ -2572,16 +2572,16 @@
         <v>44384</v>
       </c>
       <c r="B108" t="n">
-        <v>13.22676658630371</v>
+        <v>13.22676563262939</v>
       </c>
       <c r="C108" t="n">
-        <v>13.31074511346494</v>
+        <v>13.31074415373561</v>
       </c>
       <c r="D108" t="n">
-        <v>13.05040908152244</v>
+        <v>13.05040814056382</v>
       </c>
       <c r="E108" t="n">
-        <v>13.05880709659748</v>
+        <v>13.05880615503335</v>
       </c>
       <c r="F108" t="n">
         <v>2057638</v>
@@ -2612,16 +2612,16 @@
         <v>44389</v>
       </c>
       <c r="B110" t="n">
-        <v>13.3317403793335</v>
+        <v>13.33173942565918</v>
       </c>
       <c r="C110" t="n">
-        <v>13.79572644412283</v>
+        <v>13.79572545725768</v>
       </c>
       <c r="D110" t="n">
-        <v>13.07140353906678</v>
+        <v>13.07140260401543</v>
       </c>
       <c r="E110" t="n">
-        <v>13.19107423754762</v>
+        <v>13.19107329393574</v>
       </c>
       <c r="F110" t="n">
         <v>8663568</v>
@@ -2632,16 +2632,16 @@
         <v>44390</v>
       </c>
       <c r="B111" t="n">
-        <v>13.27295303344727</v>
+        <v>13.27295398712158</v>
       </c>
       <c r="C111" t="n">
-        <v>13.49759849206305</v>
+        <v>13.49759946187835</v>
       </c>
       <c r="D111" t="n">
-        <v>13.13438701720531</v>
+        <v>13.13438796092353</v>
       </c>
       <c r="E111" t="n">
-        <v>13.33173913269187</v>
+        <v>13.33174009059002</v>
       </c>
       <c r="F111" t="n">
         <v>2696620</v>
@@ -2652,16 +2652,16 @@
         <v>44391</v>
       </c>
       <c r="B112" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196659088135</v>
       </c>
       <c r="C112" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196659088135</v>
       </c>
       <c r="D112" t="n">
-        <v>13.25405823136172</v>
+        <v>13.25405915859814</v>
       </c>
       <c r="E112" t="n">
-        <v>13.27505286174354</v>
+        <v>13.27505379044871</v>
       </c>
       <c r="F112" t="n">
         <v>1800585</v>
@@ -2672,16 +2672,16 @@
         <v>44392</v>
       </c>
       <c r="B113" t="n">
-        <v>13.63196563720703</v>
+        <v>13.63196659088135</v>
       </c>
       <c r="C113" t="n">
-        <v>13.72224368436118</v>
+        <v>13.72224464435123</v>
       </c>
       <c r="D113" t="n">
-        <v>13.39682366626494</v>
+        <v>13.39682460348903</v>
       </c>
       <c r="E113" t="n">
-        <v>13.53958828937361</v>
+        <v>13.53958923658533</v>
       </c>
       <c r="F113" t="n">
         <v>1667599</v>
@@ -2692,16 +2692,16 @@
         <v>44393</v>
       </c>
       <c r="B114" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C114" t="n">
-        <v>13.93849142806081</v>
+        <v>13.9384904687512</v>
       </c>
       <c r="D114" t="n">
-        <v>13.49969861080446</v>
+        <v>13.49969768169454</v>
       </c>
       <c r="E114" t="n">
-        <v>13.64246404868482</v>
+        <v>13.64246310974914</v>
       </c>
       <c r="F114" t="n">
         <v>2056421</v>
@@ -2712,16 +2712,16 @@
         <v>44396</v>
       </c>
       <c r="B115" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C115" t="n">
-        <v>14.24501531105205</v>
+        <v>14.24501433064608</v>
       </c>
       <c r="D115" t="n">
-        <v>13.49969861080446</v>
+        <v>13.49969768169454</v>
       </c>
       <c r="E115" t="n">
-        <v>13.74953650350598</v>
+        <v>13.7495355572011</v>
       </c>
       <c r="F115" t="n">
         <v>4311511</v>
@@ -2732,16 +2732,16 @@
         <v>44397</v>
       </c>
       <c r="B116" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C116" t="n">
-        <v>14.16103643972576</v>
+        <v>14.16103739980534</v>
       </c>
       <c r="D116" t="n">
-        <v>13.77473102080758</v>
+        <v>13.7747319546967</v>
       </c>
       <c r="E116" t="n">
-        <v>13.94059038615415</v>
+        <v>13.94059133128809</v>
       </c>
       <c r="F116" t="n">
         <v>2364155</v>
@@ -2752,16 +2752,16 @@
         <v>44398</v>
       </c>
       <c r="B117" t="n">
-        <v>14.31849765777588</v>
+        <v>14.3184986114502</v>
       </c>
       <c r="C117" t="n">
-        <v>14.3478894888263</v>
+        <v>14.34789044445824</v>
       </c>
       <c r="D117" t="n">
-        <v>14.01617078001709</v>
+        <v>14.01617171355511</v>
       </c>
       <c r="E117" t="n">
-        <v>14.06865816410801</v>
+        <v>14.06865910114192</v>
       </c>
       <c r="F117" t="n">
         <v>2316312</v>
@@ -2772,16 +2772,16 @@
         <v>44399</v>
       </c>
       <c r="B118" t="n">
-        <v>14.9987325668335</v>
+        <v>14.99873065948486</v>
       </c>
       <c r="C118" t="n">
-        <v>15.01132999484949</v>
+        <v>15.01132808589888</v>
       </c>
       <c r="D118" t="n">
-        <v>14.36048831691926</v>
+        <v>14.36048649073444</v>
       </c>
       <c r="E118" t="n">
-        <v>14.36048831691926</v>
+        <v>14.36048649073444</v>
       </c>
       <c r="F118" t="n">
         <v>3546030</v>
@@ -2792,16 +2792,16 @@
         <v>44400</v>
       </c>
       <c r="B119" t="n">
-        <v>15.06801414489746</v>
+        <v>15.06801223754883</v>
       </c>
       <c r="C119" t="n">
-        <v>15.22127770885214</v>
+        <v>15.221275782103</v>
       </c>
       <c r="D119" t="n">
-        <v>14.92944893307399</v>
+        <v>14.9294470432653</v>
       </c>
       <c r="E119" t="n">
-        <v>15.22127770885214</v>
+        <v>15.221275782103</v>
       </c>
       <c r="F119" t="n">
         <v>2488627</v>
@@ -2832,16 +2832,16 @@
         <v>44404</v>
       </c>
       <c r="B121" t="n">
-        <v>14.54944038391113</v>
+        <v>14.54944133758545</v>
       </c>
       <c r="C121" t="n">
-        <v>15.05961588037913</v>
+        <v>15.059616867494</v>
       </c>
       <c r="D121" t="n">
-        <v>14.45076513966624</v>
+        <v>14.45076608687268</v>
       </c>
       <c r="E121" t="n">
-        <v>14.87486119524679</v>
+        <v>14.87486217025152</v>
       </c>
       <c r="F121" t="n">
         <v>2070206</v>
@@ -2892,16 +2892,16 @@
         <v>44407</v>
       </c>
       <c r="B124" t="n">
-        <v>15.45431900024414</v>
+        <v>15.45431709289551</v>
       </c>
       <c r="C124" t="n">
-        <v>15.94140058333477</v>
+        <v>15.94139861587127</v>
       </c>
       <c r="D124" t="n">
-        <v>14.96933834137266</v>
+        <v>14.96933649387961</v>
       </c>
       <c r="E124" t="n">
-        <v>15.28006243564328</v>
+        <v>15.28006054980113</v>
       </c>
       <c r="F124" t="n">
         <v>3070441</v>
@@ -2912,16 +2912,16 @@
         <v>44410</v>
       </c>
       <c r="B125" t="n">
-        <v>15.31785106658936</v>
+        <v>15.3178539276123</v>
       </c>
       <c r="C125" t="n">
-        <v>15.85741996477899</v>
+        <v>15.85742292658102</v>
       </c>
       <c r="D125" t="n">
-        <v>15.16878775286993</v>
+        <v>15.16879058605128</v>
       </c>
       <c r="E125" t="n">
-        <v>15.64327184578493</v>
+        <v>15.64327476758901</v>
       </c>
       <c r="F125" t="n">
         <v>3314925</v>
@@ -2932,16 +2932,16 @@
         <v>44411</v>
       </c>
       <c r="B126" t="n">
-        <v>15.20448112487793</v>
+        <v>15.20448207855225</v>
       </c>
       <c r="C126" t="n">
-        <v>15.39343441755661</v>
+        <v>15.39343538308269</v>
       </c>
       <c r="D126" t="n">
-        <v>14.761489725604</v>
+        <v>14.76149065149246</v>
       </c>
       <c r="E126" t="n">
-        <v>15.39343441755661</v>
+        <v>15.39343538308269</v>
       </c>
       <c r="F126" t="n">
         <v>3496971</v>
@@ -2972,16 +2972,16 @@
         <v>44413</v>
       </c>
       <c r="B128" t="n">
-        <v>14.17153453826904</v>
+        <v>14.17153549194336</v>
       </c>
       <c r="C128" t="n">
-        <v>14.82237457073309</v>
+        <v>14.82237556820573</v>
       </c>
       <c r="D128" t="n">
-        <v>14.17153453826904</v>
+        <v>14.17153549194336</v>
       </c>
       <c r="E128" t="n">
-        <v>14.61662524586311</v>
+        <v>14.61662622948983</v>
       </c>
       <c r="F128" t="n">
         <v>2928535</v>
@@ -2992,16 +2992,16 @@
         <v>44414</v>
       </c>
       <c r="B129" t="n">
-        <v>13.93639183044434</v>
+        <v>13.9363899230957</v>
       </c>
       <c r="C129" t="n">
-        <v>14.41927319977593</v>
+        <v>14.41927122633967</v>
       </c>
       <c r="D129" t="n">
-        <v>13.75373643553897</v>
+        <v>13.75373455318874</v>
       </c>
       <c r="E129" t="n">
-        <v>14.17153461307515</v>
+        <v>14.17153267354464</v>
       </c>
       <c r="F129" t="n">
         <v>4270967</v>
@@ -3012,16 +3012,16 @@
         <v>44417</v>
       </c>
       <c r="B130" t="n">
-        <v>14.06655979156494</v>
+        <v>14.06656074523926</v>
       </c>
       <c r="C130" t="n">
-        <v>14.15893713905431</v>
+        <v>14.15893809899156</v>
       </c>
       <c r="D130" t="n">
-        <v>13.81462098074336</v>
+        <v>13.81462191733692</v>
       </c>
       <c r="E130" t="n">
-        <v>13.83351631037553</v>
+        <v>13.83351724825013</v>
       </c>
       <c r="F130" t="n">
         <v>2523089</v>
@@ -3032,16 +3032,16 @@
         <v>44418</v>
       </c>
       <c r="B131" t="n">
-        <v>13.64666271209717</v>
+        <v>13.64666080474854</v>
       </c>
       <c r="C131" t="n">
-        <v>14.43816890261326</v>
+        <v>14.43816688463844</v>
       </c>
       <c r="D131" t="n">
-        <v>13.56688278990252</v>
+        <v>13.56688089370446</v>
       </c>
       <c r="E131" t="n">
-        <v>14.05396277317898</v>
+        <v>14.05396080890337</v>
       </c>
       <c r="F131" t="n">
         <v>2933806</v>
@@ -3052,16 +3052,16 @@
         <v>44419</v>
       </c>
       <c r="B132" t="n">
-        <v>13.82511806488037</v>
+        <v>13.82511901855469</v>
       </c>
       <c r="C132" t="n">
-        <v>13.86710732232042</v>
+        <v>13.86710827889121</v>
       </c>
       <c r="D132" t="n">
-        <v>13.63406385870915</v>
+        <v>13.6340647992043</v>
       </c>
       <c r="E132" t="n">
-        <v>13.64666128537674</v>
+        <v>13.64666222674088</v>
       </c>
       <c r="F132" t="n">
         <v>1882485</v>
@@ -3092,16 +3092,16 @@
         <v>44421</v>
       </c>
       <c r="B134" t="n">
-        <v>12.95593166351318</v>
+        <v>12.95593070983887</v>
       </c>
       <c r="C134" t="n">
-        <v>13.76423392021486</v>
+        <v>13.76423290704215</v>
       </c>
       <c r="D134" t="n">
-        <v>12.78797379676563</v>
+        <v>12.78797285545454</v>
       </c>
       <c r="E134" t="n">
-        <v>13.57108119635301</v>
+        <v>13.5710801973981</v>
       </c>
       <c r="F134" t="n">
         <v>3730102</v>
@@ -3112,16 +3112,16 @@
         <v>44424</v>
       </c>
       <c r="B135" t="n">
-        <v>11.84110260009766</v>
+        <v>11.84110450744629</v>
       </c>
       <c r="C135" t="n">
-        <v>12.94963146814602</v>
+        <v>12.94963355405497</v>
       </c>
       <c r="D135" t="n">
-        <v>11.7655212893157</v>
+        <v>11.7655231844898</v>
       </c>
       <c r="E135" t="n">
-        <v>12.94963146814602</v>
+        <v>12.94963355405497</v>
       </c>
       <c r="F135" t="n">
         <v>7844263</v>
@@ -3132,16 +3132,16 @@
         <v>44425</v>
       </c>
       <c r="B136" t="n">
-        <v>12.27779769897461</v>
+        <v>12.27779674530029</v>
       </c>
       <c r="C136" t="n">
-        <v>12.78167371260009</v>
+        <v>12.78167271978735</v>
       </c>
       <c r="D136" t="n">
-        <v>11.42960470460314</v>
+        <v>11.42960381681197</v>
       </c>
       <c r="E136" t="n">
-        <v>11.66474749373068</v>
+        <v>11.66474658767486</v>
       </c>
       <c r="F136" t="n">
         <v>5635292</v>
@@ -3152,16 +3152,16 @@
         <v>44426</v>
       </c>
       <c r="B137" t="n">
-        <v>12.59691905975342</v>
+        <v>12.5969181060791</v>
       </c>
       <c r="C137" t="n">
-        <v>13.13438794617422</v>
+        <v>13.13438695180978</v>
       </c>
       <c r="D137" t="n">
-        <v>12.21901164220178</v>
+        <v>12.21901071713769</v>
       </c>
       <c r="E137" t="n">
-        <v>12.38697031404816</v>
+        <v>12.38696937626842</v>
       </c>
       <c r="F137" t="n">
         <v>3796291</v>
@@ -3192,16 +3192,16 @@
         <v>44428</v>
       </c>
       <c r="B139" t="n">
-        <v>13.5206937789917</v>
+        <v>13.52069282531738</v>
       </c>
       <c r="C139" t="n">
-        <v>13.70544848585422</v>
+        <v>13.70544751914833</v>
       </c>
       <c r="D139" t="n">
-        <v>12.64730752300772</v>
+        <v>12.6473066309372</v>
       </c>
       <c r="E139" t="n">
-        <v>12.80686818480864</v>
+        <v>12.8068672814836</v>
       </c>
       <c r="F139" t="n">
         <v>3576438</v>
@@ -3212,16 +3212,16 @@
         <v>44431</v>
       </c>
       <c r="B140" t="n">
-        <v>13.49549865722656</v>
+        <v>13.49549770355225</v>
       </c>
       <c r="C140" t="n">
-        <v>14.19252897755238</v>
+        <v>14.19252797462165</v>
       </c>
       <c r="D140" t="n">
-        <v>13.26035669079564</v>
+        <v>13.26035575373789</v>
       </c>
       <c r="E140" t="n">
-        <v>13.72224342110149</v>
+        <v>13.72224245140401</v>
       </c>
       <c r="F140" t="n">
         <v>2675233</v>
@@ -3252,16 +3252,16 @@
         <v>44433</v>
       </c>
       <c r="B142" t="n">
-        <v>13.47870254516602</v>
+        <v>13.47870349884033</v>
       </c>
       <c r="C142" t="n">
-        <v>13.57947708709049</v>
+        <v>13.57947804789503</v>
       </c>
       <c r="D142" t="n">
-        <v>13.05040708891188</v>
+        <v>13.05040801228251</v>
       </c>
       <c r="E142" t="n">
-        <v>13.44511048999488</v>
+        <v>13.44511144129242</v>
       </c>
       <c r="F142" t="n">
         <v>2709595</v>
@@ -3292,16 +3292,16 @@
         <v>44435</v>
       </c>
       <c r="B144" t="n">
-        <v>13.6886510848999</v>
+        <v>13.68865013122559</v>
       </c>
       <c r="C144" t="n">
-        <v>13.6886510848999</v>
+        <v>13.68865013122559</v>
       </c>
       <c r="D144" t="n">
-        <v>12.95803034564176</v>
+        <v>12.95802944286904</v>
       </c>
       <c r="E144" t="n">
-        <v>13.32753972236057</v>
+        <v>13.32753879384451</v>
       </c>
       <c r="F144" t="n">
         <v>2006349</v>
@@ -3332,16 +3332,16 @@
         <v>44439</v>
       </c>
       <c r="B146" t="n">
-        <v>12.77327537536621</v>
+        <v>12.77327728271484</v>
       </c>
       <c r="C146" t="n">
-        <v>13.40312155415849</v>
+        <v>13.40312355555788</v>
       </c>
       <c r="D146" t="n">
-        <v>12.49614253714914</v>
+        <v>12.49614440311536</v>
       </c>
       <c r="E146" t="n">
-        <v>13.28554935824077</v>
+        <v>13.28555134208388</v>
       </c>
       <c r="F146" t="n">
         <v>2117441</v>
@@ -3352,16 +3352,16 @@
         <v>44440</v>
       </c>
       <c r="B147" t="n">
-        <v>13.06720447540283</v>
+        <v>13.06720352172852</v>
       </c>
       <c r="C147" t="n">
-        <v>13.2855504213384</v>
+        <v>13.2855494517287</v>
       </c>
       <c r="D147" t="n">
-        <v>12.56332765440814</v>
+        <v>12.56332673750791</v>
       </c>
       <c r="E147" t="n">
-        <v>13.0923985194012</v>
+        <v>13.09239756388817</v>
       </c>
       <c r="F147" t="n">
         <v>3411726</v>
@@ -3372,16 +3372,16 @@
         <v>44441</v>
       </c>
       <c r="B148" t="n">
-        <v>12.80686855316162</v>
+        <v>12.80686664581299</v>
       </c>
       <c r="C148" t="n">
-        <v>13.18477599277661</v>
+        <v>13.18477402914559</v>
       </c>
       <c r="D148" t="n">
-        <v>12.69769597834385</v>
+        <v>12.69769408725448</v>
       </c>
       <c r="E148" t="n">
-        <v>13.06720540269677</v>
+        <v>13.06720345657573</v>
       </c>
       <c r="F148" t="n">
         <v>2514879</v>
@@ -3392,16 +3392,16 @@
         <v>44442</v>
       </c>
       <c r="B149" t="n">
-        <v>13.10079574584961</v>
+        <v>13.10079669952393</v>
       </c>
       <c r="C149" t="n">
-        <v>13.21836713959238</v>
+        <v>13.21836810182533</v>
       </c>
       <c r="D149" t="n">
-        <v>12.74808237641584</v>
+        <v>12.74808330441434</v>
       </c>
       <c r="E149" t="n">
-        <v>12.94963310517644</v>
+        <v>12.94963404784685</v>
       </c>
       <c r="F149" t="n">
         <v>3315331</v>
@@ -3412,16 +3412,16 @@
         <v>44445</v>
       </c>
       <c r="B150" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C150" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="D150" t="n">
-        <v>13.00002039001773</v>
+        <v>13.00001949529792</v>
       </c>
       <c r="E150" t="n">
-        <v>13.36113177437019</v>
+        <v>13.36113085479707</v>
       </c>
       <c r="F150" t="n">
         <v>1953438</v>
@@ -3432,16 +3432,16 @@
         <v>44447</v>
       </c>
       <c r="B151" t="n">
-        <v>13.23516273498535</v>
+        <v>13.23516368865967</v>
       </c>
       <c r="C151" t="n">
-        <v>14.67960903587777</v>
+        <v>14.67961009363327</v>
       </c>
       <c r="D151" t="n">
-        <v>13.10079531628589</v>
+        <v>13.10079626027822</v>
       </c>
       <c r="E151" t="n">
-        <v>13.80622203202309</v>
+        <v>13.80622302684572</v>
       </c>
       <c r="F151" t="n">
         <v>4568970</v>
@@ -3492,16 +3492,16 @@
         <v>44452</v>
       </c>
       <c r="B154" t="n">
-        <v>13.3947229385376</v>
+        <v>13.39472389221191</v>
       </c>
       <c r="C154" t="n">
-        <v>13.53748836688323</v>
+        <v>13.53748933072213</v>
       </c>
       <c r="D154" t="n">
-        <v>12.97482629121558</v>
+        <v>12.9748272149942</v>
       </c>
       <c r="E154" t="n">
-        <v>13.24356030786057</v>
+        <v>13.24356125077245</v>
       </c>
       <c r="F154" t="n">
         <v>1856739</v>
@@ -3512,16 +3512,16 @@
         <v>44453</v>
       </c>
       <c r="B155" t="n">
-        <v>13.55428600311279</v>
+        <v>13.55428504943848</v>
       </c>
       <c r="C155" t="n">
-        <v>14.04976483634768</v>
+        <v>14.04976384781166</v>
       </c>
       <c r="D155" t="n">
-        <v>13.27715393946506</v>
+        <v>13.27715300528965</v>
       </c>
       <c r="E155" t="n">
-        <v>13.43671460319705</v>
+        <v>13.43671365779501</v>
       </c>
       <c r="F155" t="n">
         <v>1943200</v>
@@ -3532,16 +3532,16 @@
         <v>44454</v>
       </c>
       <c r="B156" t="n">
-        <v>13.44511222839355</v>
+        <v>13.44511127471924</v>
       </c>
       <c r="C156" t="n">
-        <v>14.07495766172759</v>
+        <v>14.07495666337775</v>
       </c>
       <c r="D156" t="n">
-        <v>13.23516348001735</v>
+        <v>13.2351625412349</v>
       </c>
       <c r="E156" t="n">
-        <v>13.47030546123482</v>
+        <v>13.47030450577353</v>
       </c>
       <c r="F156" t="n">
         <v>2602050</v>
@@ -3552,16 +3552,16 @@
         <v>44455</v>
       </c>
       <c r="B157" t="n">
-        <v>13.56268215179443</v>
+        <v>13.56268405914307</v>
       </c>
       <c r="C157" t="n">
-        <v>13.78942690530008</v>
+        <v>13.7894288445363</v>
       </c>
       <c r="D157" t="n">
-        <v>13.33593739828879</v>
+        <v>13.33593927374983</v>
       </c>
       <c r="E157" t="n">
-        <v>13.47870282392425</v>
+        <v>13.47870471946269</v>
       </c>
       <c r="F157" t="n">
         <v>1227183</v>
@@ -3572,16 +3572,16 @@
         <v>44456</v>
       </c>
       <c r="B158" t="n">
-        <v>13.44511222839355</v>
+        <v>13.44511127471924</v>
       </c>
       <c r="C158" t="n">
-        <v>13.74743914043451</v>
+        <v>13.74743816531587</v>
       </c>
       <c r="D158" t="n">
-        <v>13.29394877237308</v>
+        <v>13.29394782942092</v>
       </c>
       <c r="E158" t="n">
-        <v>13.40312296579506</v>
+        <v>13.40312201509908</v>
       </c>
       <c r="F158" t="n">
         <v>5378949</v>
@@ -3612,16 +3612,16 @@
         <v>44460</v>
       </c>
       <c r="B160" t="n">
-        <v>13.5206937789917</v>
+        <v>13.52069282531738</v>
       </c>
       <c r="C160" t="n">
-        <v>13.64666319250508</v>
+        <v>13.64666222994559</v>
       </c>
       <c r="D160" t="n">
-        <v>12.80686818480864</v>
+        <v>12.8068672814836</v>
       </c>
       <c r="E160" t="n">
-        <v>12.98322568844521</v>
+        <v>12.9832247726809</v>
       </c>
       <c r="F160" t="n">
         <v>1911981</v>
@@ -3652,16 +3652,16 @@
         <v>44462</v>
       </c>
       <c r="B162" t="n">
-        <v>14.6124267578125</v>
+        <v>14.61242580413818</v>
       </c>
       <c r="C162" t="n">
-        <v>15.11630275876303</v>
+        <v>15.11630177220344</v>
       </c>
       <c r="D162" t="n">
-        <v>14.15893722044467</v>
+        <v>14.15893629636717</v>
       </c>
       <c r="E162" t="n">
-        <v>14.19252927855919</v>
+        <v>14.19252835228931</v>
       </c>
       <c r="F162" t="n">
         <v>3399055</v>
@@ -3672,16 +3672,16 @@
         <v>44463</v>
       </c>
       <c r="B163" t="n">
-        <v>13.85661220550537</v>
+        <v>13.85661125183105</v>
       </c>
       <c r="C163" t="n">
-        <v>14.26811086618383</v>
+        <v>14.26810988418833</v>
       </c>
       <c r="D163" t="n">
-        <v>13.83141734965053</v>
+        <v>13.83141639771024</v>
       </c>
       <c r="E163" t="n">
-        <v>14.16733468994271</v>
+        <v>14.16733371488308</v>
       </c>
       <c r="F163" t="n">
         <v>7509973</v>
@@ -3792,16 +3792,16 @@
         <v>44473</v>
       </c>
       <c r="B169" t="n">
-        <v>12.34498023986816</v>
+        <v>12.34498119354248</v>
       </c>
       <c r="C169" t="n">
-        <v>12.82366299139635</v>
+        <v>12.82366398204986</v>
       </c>
       <c r="D169" t="n">
-        <v>12.1350315079744</v>
+        <v>12.13503244542976</v>
       </c>
       <c r="E169" t="n">
-        <v>12.72288763255913</v>
+        <v>12.72288861542754</v>
       </c>
       <c r="F169" t="n">
         <v>1681992</v>
@@ -3812,16 +3812,16 @@
         <v>44474</v>
       </c>
       <c r="B170" t="n">
-        <v>12.14342880249023</v>
+        <v>12.14343070983887</v>
       </c>
       <c r="C170" t="n">
-        <v>12.55492822767014</v>
+        <v>12.55493019965232</v>
       </c>
       <c r="D170" t="n">
-        <v>11.95027611048266</v>
+        <v>11.95027798749311</v>
       </c>
       <c r="E170" t="n">
-        <v>12.35337752194098</v>
+        <v>12.35337946226592</v>
       </c>
       <c r="F170" t="n">
         <v>4189574</v>
@@ -3832,16 +3832,16 @@
         <v>44475</v>
       </c>
       <c r="B171" t="n">
-        <v>12.51294136047363</v>
+        <v>12.512939453125</v>
       </c>
       <c r="C171" t="n">
-        <v>12.61371592078883</v>
+        <v>12.61371399807913</v>
       </c>
       <c r="D171" t="n">
-        <v>11.68154352582436</v>
+        <v>11.68154174520576</v>
       </c>
       <c r="E171" t="n">
-        <v>11.94188037732158</v>
+        <v>11.94187855701982</v>
       </c>
       <c r="F171" t="n">
         <v>5058241</v>
@@ -3852,16 +3852,16 @@
         <v>44476</v>
       </c>
       <c r="B172" t="n">
-        <v>13.00002002716064</v>
+        <v>13.00001907348633</v>
       </c>
       <c r="C172" t="n">
-        <v>13.02521407051771</v>
+        <v>13.02521311499517</v>
       </c>
       <c r="D172" t="n">
-        <v>12.36177579954892</v>
+        <v>12.36177489269584</v>
       </c>
       <c r="E172" t="n">
-        <v>12.56332733461089</v>
+        <v>12.5633264129721</v>
       </c>
       <c r="F172" t="n">
         <v>3555051</v>
@@ -3952,16 +3952,16 @@
         <v>44484</v>
       </c>
       <c r="B177" t="n">
-        <v>13.41991806030273</v>
+        <v>13.41991710662842</v>
       </c>
       <c r="C177" t="n">
-        <v>13.48710217871359</v>
+        <v>13.4871012202649</v>
       </c>
       <c r="D177" t="n">
-        <v>13.0840007154267</v>
+        <v>13.08399978562405</v>
       </c>
       <c r="E177" t="n">
-        <v>13.24356137306336</v>
+        <v>13.24356043192167</v>
       </c>
       <c r="F177" t="n">
         <v>1650266</v>
@@ -3972,16 +3972,16 @@
         <v>44487</v>
       </c>
       <c r="B178" t="n">
-        <v>13.20157146453857</v>
+        <v>13.20156955718994</v>
       </c>
       <c r="C178" t="n">
-        <v>13.36953095087653</v>
+        <v>13.3695290192613</v>
       </c>
       <c r="D178" t="n">
-        <v>13.04201080490182</v>
+        <v>13.04200892060634</v>
       </c>
       <c r="E178" t="n">
-        <v>13.3023476434181</v>
+        <v>13.30234572150943</v>
       </c>
       <c r="F178" t="n">
         <v>1423013</v>
@@ -3992,16 +3992,16 @@
         <v>44488</v>
       </c>
       <c r="B179" t="n">
-        <v>12.39536762237549</v>
+        <v>12.39536666870117</v>
       </c>
       <c r="C179" t="n">
-        <v>13.10919315473166</v>
+        <v>13.10919214613706</v>
       </c>
       <c r="D179" t="n">
-        <v>12.17702087434261</v>
+        <v>12.17701993746745</v>
       </c>
       <c r="E179" t="n">
-        <v>13.05880588076728</v>
+        <v>13.05880487604937</v>
       </c>
       <c r="F179" t="n">
         <v>2260766</v>
@@ -4032,16 +4032,16 @@
         <v>44490</v>
       </c>
       <c r="B181" t="n">
-        <v>11.24484920501709</v>
+        <v>11.24485015869141</v>
       </c>
       <c r="C181" t="n">
-        <v>11.95867472463081</v>
+        <v>11.95867573884459</v>
       </c>
       <c r="D181" t="n">
-        <v>10.83335057097093</v>
+        <v>10.8333514897461</v>
       </c>
       <c r="E181" t="n">
-        <v>11.84950135256322</v>
+        <v>11.84950235751801</v>
       </c>
       <c r="F181" t="n">
         <v>4870723</v>
@@ -4072,16 +4072,16 @@
         <v>44494</v>
       </c>
       <c r="B183" t="n">
-        <v>10.55621910095215</v>
+        <v>10.55621814727783</v>
       </c>
       <c r="C183" t="n">
-        <v>11.02650389517411</v>
+        <v>11.02650289901313</v>
       </c>
       <c r="D183" t="n">
-        <v>10.35466835888637</v>
+        <v>10.35466742342063</v>
       </c>
       <c r="E183" t="n">
-        <v>10.65699447198504</v>
+        <v>10.65699350920643</v>
       </c>
       <c r="F183" t="n">
         <v>10777158</v>
@@ -4132,16 +4132,16 @@
         <v>44497</v>
       </c>
       <c r="B186" t="n">
-        <v>9.909575462341309</v>
+        <v>9.909576416015625</v>
       </c>
       <c r="C186" t="n">
-        <v>10.4386454367352</v>
+        <v>10.43864644132597</v>
       </c>
       <c r="D186" t="n">
-        <v>9.82559532818885</v>
+        <v>9.825596273781114</v>
       </c>
       <c r="E186" t="n">
-        <v>10.25389076518866</v>
+        <v>10.25389175199907</v>
       </c>
       <c r="F186" t="n">
         <v>4167680</v>
@@ -4152,16 +4152,16 @@
         <v>44498</v>
       </c>
       <c r="B187" t="n">
-        <v>9.514872550964355</v>
+        <v>9.514873504638672</v>
       </c>
       <c r="C187" t="n">
-        <v>10.06913659309689</v>
+        <v>10.06913760232501</v>
       </c>
       <c r="D187" t="n">
-        <v>9.069781065056384</v>
+        <v>9.069781974119245</v>
       </c>
       <c r="E187" t="n">
-        <v>10.06913659309689</v>
+        <v>10.06913760232501</v>
       </c>
       <c r="F187" t="n">
         <v>8163450</v>
@@ -4172,16 +4172,16 @@
         <v>44501</v>
       </c>
       <c r="B188" t="n">
-        <v>9.464484214782715</v>
+        <v>9.464485168457031</v>
       </c>
       <c r="C188" t="n">
-        <v>9.817197539105118</v>
+        <v>9.817198528320054</v>
       </c>
       <c r="D188" t="n">
-        <v>9.002596713567389</v>
+        <v>9.002597620700316</v>
       </c>
       <c r="E188" t="n">
-        <v>9.22094344376433</v>
+        <v>9.220944372898632</v>
       </c>
       <c r="F188" t="n">
         <v>8542036</v>
@@ -4232,16 +4232,16 @@
         <v>44505</v>
       </c>
       <c r="B191" t="n">
-        <v>10.55621910095215</v>
+        <v>10.55621814727783</v>
       </c>
       <c r="C191" t="n">
-        <v>10.96771778852473</v>
+        <v>10.96771679767463</v>
       </c>
       <c r="D191" t="n">
-        <v>10.29588225223699</v>
+        <v>10.29588132208213</v>
       </c>
       <c r="E191" t="n">
-        <v>10.64019844151379</v>
+        <v>10.64019748025258</v>
       </c>
       <c r="F191" t="n">
         <v>3221166</v>
@@ -4272,16 +4272,16 @@
         <v>44509</v>
       </c>
       <c r="B193" t="n">
-        <v>10.74937057495117</v>
+        <v>10.74937152862549</v>
       </c>
       <c r="C193" t="n">
-        <v>11.25324737138916</v>
+        <v>11.25324836976697</v>
       </c>
       <c r="D193" t="n">
-        <v>10.40505523759868</v>
+        <v>10.40505616072565</v>
       </c>
       <c r="E193" t="n">
-        <v>10.60660514437936</v>
+        <v>10.60660608538766</v>
       </c>
       <c r="F193" t="n">
         <v>3973268</v>
@@ -4292,16 +4292,16 @@
         <v>44510</v>
       </c>
       <c r="B194" t="n">
-        <v>10.66539287567139</v>
+        <v>10.66539096832275</v>
       </c>
       <c r="C194" t="n">
-        <v>11.16926974918785</v>
+        <v>11.16926775172825</v>
       </c>
       <c r="D194" t="n">
-        <v>10.44704609518181</v>
+        <v>10.44704422688129</v>
       </c>
       <c r="E194" t="n">
-        <v>10.74937221929169</v>
+        <v>10.74937029692459</v>
       </c>
       <c r="F194" t="n">
         <v>2771222</v>
@@ -4312,16 +4312,16 @@
         <v>44511</v>
       </c>
       <c r="B195" t="n">
-        <v>11.21965599060059</v>
+        <v>11.21965503692627</v>
       </c>
       <c r="C195" t="n">
-        <v>11.5303801014484</v>
+        <v>11.53037912136244</v>
       </c>
       <c r="D195" t="n">
-        <v>10.69058593129811</v>
+        <v>10.69058502259491</v>
       </c>
       <c r="E195" t="n">
-        <v>10.78296247010213</v>
+        <v>10.7829615535469</v>
       </c>
       <c r="F195" t="n">
         <v>2903296</v>
@@ -4452,16 +4452,16 @@
         <v>44523</v>
       </c>
       <c r="B202" t="n">
-        <v>9.674434661865234</v>
+        <v>9.674432754516602</v>
       </c>
       <c r="C202" t="n">
-        <v>10.34627018804897</v>
+        <v>10.34626814824561</v>
       </c>
       <c r="D202" t="n">
-        <v>9.481281937939977</v>
+        <v>9.481280068672081</v>
       </c>
       <c r="E202" t="n">
-        <v>10.2874840822837</v>
+        <v>10.28748205407023</v>
       </c>
       <c r="F202" t="n">
         <v>4258094</v>
@@ -4632,16 +4632,16 @@
         <v>44536</v>
       </c>
       <c r="B211" t="n">
-        <v>9.884383201599121</v>
+        <v>9.884382247924805</v>
       </c>
       <c r="C211" t="n">
-        <v>10.23709658136135</v>
+        <v>10.23709559365621</v>
       </c>
       <c r="D211" t="n">
-        <v>9.573658272883511</v>
+        <v>9.573657349188849</v>
       </c>
       <c r="E211" t="n">
-        <v>9.867586359950231</v>
+        <v>9.867585407896522</v>
       </c>
       <c r="F211" t="n">
         <v>2021553</v>
@@ -4732,16 +4732,16 @@
         <v>44543</v>
       </c>
       <c r="B216" t="n">
-        <v>11.19168186187744</v>
+        <v>11.19168090820312</v>
       </c>
       <c r="C216" t="n">
-        <v>11.55848208514464</v>
+        <v>11.55848110021426</v>
       </c>
       <c r="D216" t="n">
-        <v>11.13196966068666</v>
+        <v>11.13196871210059</v>
       </c>
       <c r="E216" t="n">
-        <v>11.25992355294072</v>
+        <v>11.25992259345134</v>
       </c>
       <c r="F216" t="n">
         <v>3334589</v>
@@ -4752,16 +4752,16 @@
         <v>44544</v>
       </c>
       <c r="B217" t="n">
-        <v>11.11490917205811</v>
+        <v>11.11490821838379</v>
       </c>
       <c r="C217" t="n">
-        <v>11.43905865172065</v>
+        <v>11.43905767023386</v>
       </c>
       <c r="D217" t="n">
-        <v>10.91871358626455</v>
+        <v>10.91871264942408</v>
       </c>
       <c r="E217" t="n">
-        <v>11.25992369505407</v>
+        <v>11.25992272893731</v>
       </c>
       <c r="F217" t="n">
         <v>1511299</v>
@@ -4772,16 +4772,16 @@
         <v>44545</v>
       </c>
       <c r="B218" t="n">
-        <v>11.26845264434814</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C218" t="n">
-        <v>11.37934507107126</v>
+        <v>11.37934603413065</v>
       </c>
       <c r="D218" t="n">
-        <v>10.8163493255928</v>
+        <v>10.8163502410046</v>
       </c>
       <c r="E218" t="n">
-        <v>10.90165163630924</v>
+        <v>10.90165255894037</v>
       </c>
       <c r="F218" t="n">
         <v>3122034</v>
@@ -4792,16 +4792,16 @@
         <v>44546</v>
       </c>
       <c r="B219" t="n">
-        <v>11.14049816131592</v>
+        <v>11.14049911499023</v>
       </c>
       <c r="C219" t="n">
-        <v>11.49023854919888</v>
+        <v>11.49023953281247</v>
       </c>
       <c r="D219" t="n">
-        <v>10.85900110760307</v>
+        <v>10.85900203718004</v>
       </c>
       <c r="E219" t="n">
-        <v>11.39640592310018</v>
+        <v>11.3964068986813</v>
       </c>
       <c r="F219" t="n">
         <v>2253468</v>
@@ -4852,16 +4852,16 @@
         <v>44551</v>
       </c>
       <c r="B222" t="n">
-        <v>10.73957824707031</v>
+        <v>10.739577293396</v>
       </c>
       <c r="C222" t="n">
-        <v>11.05519824974405</v>
+        <v>11.05519726804268</v>
       </c>
       <c r="D222" t="n">
-        <v>10.51779253304062</v>
+        <v>10.51779159906087</v>
       </c>
       <c r="E222" t="n">
-        <v>10.8419420260456</v>
+        <v>10.84194106328138</v>
       </c>
       <c r="F222" t="n">
         <v>1915833</v>
@@ -4952,16 +4952,16 @@
         <v>44559</v>
       </c>
       <c r="B227" t="n">
-        <v>9.715949058532715</v>
+        <v>9.715948104858398</v>
       </c>
       <c r="C227" t="n">
-        <v>10.21923349127314</v>
+        <v>10.21923248819867</v>
       </c>
       <c r="D227" t="n">
-        <v>9.596525480078773</v>
+        <v>9.596524538126543</v>
       </c>
       <c r="E227" t="n">
-        <v>10.21923349127314</v>
+        <v>10.21923248819867</v>
       </c>
       <c r="F227" t="n">
         <v>1535423</v>
@@ -4972,16 +4972,16 @@
         <v>44560</v>
       </c>
       <c r="B228" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="C228" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="D228" t="n">
-        <v>9.647706562908386</v>
+        <v>9.647705662569827</v>
       </c>
       <c r="E228" t="n">
-        <v>9.7927210851769</v>
+        <v>9.792720171305367</v>
       </c>
       <c r="F228" t="n">
         <v>3325771</v>
@@ -4992,16 +4992,16 @@
         <v>44564</v>
       </c>
       <c r="B229" t="n">
-        <v>9.664768218994141</v>
+        <v>9.664767265319824</v>
       </c>
       <c r="C229" t="n">
-        <v>10.2192337269546</v>
+        <v>10.21923271856821</v>
       </c>
       <c r="D229" t="n">
-        <v>9.349148224283301</v>
+        <v>9.349147301752897</v>
       </c>
       <c r="E229" t="n">
-        <v>10.2192337269546</v>
+        <v>10.21923271856821</v>
       </c>
       <c r="F229" t="n">
         <v>4324384</v>
@@ -5012,16 +5012,16 @@
         <v>44565</v>
       </c>
       <c r="B230" t="n">
-        <v>9.238256454467773</v>
+        <v>9.238255500793457</v>
       </c>
       <c r="C230" t="n">
-        <v>9.826843264047191</v>
+        <v>9.826842249612479</v>
       </c>
       <c r="D230" t="n">
-        <v>9.170013931907791</v>
+        <v>9.170012985278218</v>
       </c>
       <c r="E230" t="n">
-        <v>9.758600741487211</v>
+        <v>9.75859973409724</v>
       </c>
       <c r="F230" t="n">
         <v>4143150</v>
@@ -5032,16 +5032,16 @@
         <v>44566</v>
       </c>
       <c r="B231" t="n">
-        <v>8.530244827270508</v>
+        <v>8.530243873596191</v>
       </c>
       <c r="C231" t="n">
-        <v>9.255315823119759</v>
+        <v>9.255314788383105</v>
       </c>
       <c r="D231" t="n">
-        <v>8.479063762352734</v>
+        <v>8.479062814400418</v>
       </c>
       <c r="E231" t="n">
-        <v>9.255315823119759</v>
+        <v>9.255314788383105</v>
       </c>
       <c r="F231" t="n">
         <v>5451524</v>
@@ -5052,16 +5052,16 @@
         <v>44567</v>
       </c>
       <c r="B232" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="C232" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="D232" t="n">
-        <v>8.393760513964654</v>
+        <v>8.393761408545751</v>
       </c>
       <c r="E232" t="n">
-        <v>8.547305340985826</v>
+        <v>8.547306251931259</v>
       </c>
       <c r="F232" t="n">
         <v>4969753</v>
@@ -5112,16 +5112,16 @@
         <v>44572</v>
       </c>
       <c r="B235" t="n">
-        <v>8.71790885925293</v>
+        <v>8.717909812927246</v>
       </c>
       <c r="C235" t="n">
-        <v>8.914105249693064</v>
+        <v>8.914106224829805</v>
       </c>
       <c r="D235" t="n">
-        <v>8.530243607092713</v>
+        <v>8.530244540237847</v>
       </c>
       <c r="E235" t="n">
-        <v>8.530243607092713</v>
+        <v>8.530244540237847</v>
       </c>
       <c r="F235" t="n">
         <v>1168089</v>
@@ -5212,16 +5212,16 @@
         <v>44579</v>
       </c>
       <c r="B240" t="n">
-        <v>8.30845832824707</v>
+        <v>8.308457374572754</v>
       </c>
       <c r="C240" t="n">
-        <v>8.760562547247821</v>
+        <v>8.76056154167938</v>
       </c>
       <c r="D240" t="n">
-        <v>8.206095373339679</v>
+        <v>8.206094431414945</v>
       </c>
       <c r="E240" t="n">
-        <v>8.530244867976979</v>
+        <v>8.530243888845217</v>
       </c>
       <c r="F240" t="n">
         <v>2291580</v>
@@ -5252,16 +5252,16 @@
         <v>44581</v>
       </c>
       <c r="B242" t="n">
-        <v>9.383268356323242</v>
+        <v>9.383269309997559</v>
       </c>
       <c r="C242" t="n">
-        <v>9.6562359201754</v>
+        <v>9.656236901592942</v>
       </c>
       <c r="D242" t="n">
-        <v>8.530243585483291</v>
+        <v>8.530244452459904</v>
       </c>
       <c r="E242" t="n">
-        <v>8.581425467533645</v>
+        <v>8.581426339712161</v>
       </c>
       <c r="F242" t="n">
         <v>5361414</v>
@@ -5352,16 +5352,16 @@
         <v>44588</v>
       </c>
       <c r="B247" t="n">
-        <v>10.15952110290527</v>
+        <v>10.15952014923096</v>
       </c>
       <c r="C247" t="n">
-        <v>10.5007312029864</v>
+        <v>10.50073021728269</v>
       </c>
       <c r="D247" t="n">
-        <v>9.988917289739678</v>
+        <v>9.988916352079942</v>
       </c>
       <c r="E247" t="n">
-        <v>10.28747499350861</v>
+        <v>10.28747402782326</v>
       </c>
       <c r="F247" t="n">
         <v>2570932</v>
@@ -5372,16 +5372,16 @@
         <v>44589</v>
       </c>
       <c r="B248" t="n">
-        <v>10.21923351287842</v>
+        <v>10.2192325592041</v>
       </c>
       <c r="C248" t="n">
-        <v>10.26188426089857</v>
+        <v>10.26188330324402</v>
       </c>
       <c r="D248" t="n">
-        <v>9.681827820991172</v>
+        <v>9.681826917468367</v>
       </c>
       <c r="E248" t="n">
-        <v>10.19364256931633</v>
+        <v>10.1936416180302</v>
       </c>
       <c r="F248" t="n">
         <v>1431224</v>
@@ -5392,16 +5392,16 @@
         <v>44592</v>
       </c>
       <c r="B249" t="n">
-        <v>10.47513961791992</v>
+        <v>10.47514057159424</v>
       </c>
       <c r="C249" t="n">
-        <v>10.56044193156613</v>
+        <v>10.56044289300652</v>
       </c>
       <c r="D249" t="n">
-        <v>10.1851114216895</v>
+        <v>10.18511234895917</v>
       </c>
       <c r="E249" t="n">
-        <v>10.22776299080424</v>
+        <v>10.22776392195697</v>
       </c>
       <c r="F249" t="n">
         <v>3321007</v>
@@ -5472,16 +5472,16 @@
         <v>44596</v>
       </c>
       <c r="B253" t="n">
-        <v>10.2533540725708</v>
+        <v>10.25335502624512</v>
       </c>
       <c r="C253" t="n">
-        <v>10.56044207606577</v>
+        <v>10.56044305830264</v>
       </c>
       <c r="D253" t="n">
-        <v>9.835371163276871</v>
+        <v>9.835372078074196</v>
       </c>
       <c r="E253" t="n">
-        <v>10.56044207606577</v>
+        <v>10.56044305830264</v>
       </c>
       <c r="F253" t="n">
         <v>2130212</v>
@@ -5492,16 +5492,16 @@
         <v>44599</v>
       </c>
       <c r="B254" t="n">
-        <v>10.13393115997314</v>
+        <v>10.13393020629883</v>
       </c>
       <c r="C254" t="n">
-        <v>10.34718654856125</v>
+        <v>10.3471855748181</v>
       </c>
       <c r="D254" t="n">
-        <v>9.937734751205435</v>
+        <v>9.937733815994584</v>
       </c>
       <c r="E254" t="n">
-        <v>10.04862801503791</v>
+        <v>10.04862706939122</v>
       </c>
       <c r="F254" t="n">
         <v>1517482</v>
@@ -5552,16 +5552,16 @@
         <v>44602</v>
       </c>
       <c r="B257" t="n">
-        <v>9.99744701385498</v>
+        <v>9.997446060180664</v>
       </c>
       <c r="C257" t="n">
-        <v>10.38130787007986</v>
+        <v>10.38130687978837</v>
       </c>
       <c r="D257" t="n">
-        <v>9.92067500752667</v>
+        <v>9.920674061175772</v>
       </c>
       <c r="E257" t="n">
-        <v>10.36424724098838</v>
+        <v>10.36424625232434</v>
       </c>
       <c r="F257" t="n">
         <v>2000064</v>
@@ -5692,16 +5692,16 @@
         <v>44613</v>
       </c>
       <c r="B264" t="n">
-        <v>9.383268356323242</v>
+        <v>9.383269309997559</v>
       </c>
       <c r="C264" t="n">
-        <v>10.1936415587879</v>
+        <v>10.193642594825</v>
       </c>
       <c r="D264" t="n">
-        <v>9.263845614038905</v>
+        <v>9.263846555575617</v>
       </c>
       <c r="E264" t="n">
-        <v>10.0656885028285</v>
+        <v>10.06568952586101</v>
       </c>
       <c r="F264" t="n">
         <v>2949517</v>
@@ -5732,16 +5732,16 @@
         <v>44615</v>
       </c>
       <c r="B266" t="n">
-        <v>9.767128944396973</v>
+        <v>9.767129898071289</v>
       </c>
       <c r="C266" t="n">
-        <v>10.11686932312569</v>
+        <v>10.11687031094908</v>
       </c>
       <c r="D266" t="n">
-        <v>9.68182663422937</v>
+        <v>9.681827579574664</v>
       </c>
       <c r="E266" t="n">
-        <v>9.775660082455282</v>
+        <v>9.775661036962589</v>
       </c>
       <c r="F266" t="n">
         <v>2319860</v>
@@ -5772,16 +5772,16 @@
         <v>44617</v>
       </c>
       <c r="B268" t="n">
-        <v>9.425921440124512</v>
+        <v>9.425920486450195</v>
       </c>
       <c r="C268" t="n">
-        <v>9.869493699625441</v>
+        <v>9.869492701072385</v>
       </c>
       <c r="D268" t="n">
-        <v>9.383269864892029</v>
+        <v>9.383268915533016</v>
       </c>
       <c r="E268" t="n">
-        <v>9.579465461794694</v>
+        <v>9.579464492585451</v>
       </c>
       <c r="F268" t="n">
         <v>3597927</v>
@@ -5812,16 +5812,16 @@
         <v>44623</v>
       </c>
       <c r="B270" t="n">
-        <v>9.639176368713379</v>
+        <v>9.639177322387695</v>
       </c>
       <c r="C270" t="n">
-        <v>10.15952056895851</v>
+        <v>10.15952157411429</v>
       </c>
       <c r="D270" t="n">
-        <v>9.562404368219553</v>
+        <v>9.562405314298255</v>
       </c>
       <c r="E270" t="n">
-        <v>9.860962056297398</v>
+        <v>9.860963031914597</v>
       </c>
       <c r="F270" t="n">
         <v>3265562</v>
@@ -5872,16 +5872,16 @@
         <v>44628</v>
       </c>
       <c r="B273" t="n">
-        <v>8.89704418182373</v>
+        <v>8.897045135498047</v>
       </c>
       <c r="C273" t="n">
-        <v>8.92263512401856</v>
+        <v>8.92263608043597</v>
       </c>
       <c r="D273" t="n">
-        <v>8.521713661299355</v>
+        <v>8.521714574741987</v>
       </c>
       <c r="E273" t="n">
-        <v>8.726440374274713</v>
+        <v>8.726441309662004</v>
       </c>
       <c r="F273" t="n">
         <v>2260563</v>
@@ -5892,16 +5892,16 @@
         <v>44629</v>
       </c>
       <c r="B274" t="n">
-        <v>9.255314826965332</v>
+        <v>9.255315780639648</v>
       </c>
       <c r="C274" t="n">
-        <v>9.391799026361806</v>
+        <v>9.391799994099552</v>
       </c>
       <c r="D274" t="n">
-        <v>8.845863053359189</v>
+        <v>8.845863964843298</v>
       </c>
       <c r="E274" t="n">
-        <v>8.939696507345268</v>
+        <v>8.939697428498043</v>
       </c>
       <c r="F274" t="n">
         <v>2821903</v>
@@ -5932,16 +5932,16 @@
         <v>44631</v>
       </c>
       <c r="B276" t="n">
-        <v>8.615547180175781</v>
+        <v>8.615548133850098</v>
       </c>
       <c r="C276" t="n">
-        <v>9.19560359341205</v>
+        <v>9.195604611294117</v>
       </c>
       <c r="D276" t="n">
-        <v>8.470532664575069</v>
+        <v>8.470533602197403</v>
       </c>
       <c r="E276" t="n">
-        <v>9.19560359341205</v>
+        <v>9.195604611294117</v>
       </c>
       <c r="F276" t="n">
         <v>3220051</v>
@@ -5992,16 +5992,16 @@
         <v>44636</v>
       </c>
       <c r="B279" t="n">
-        <v>8.948225975036621</v>
+        <v>8.948226928710938</v>
       </c>
       <c r="C279" t="n">
-        <v>9.229724687144891</v>
+        <v>9.229725670820471</v>
       </c>
       <c r="D279" t="n">
-        <v>8.589956086292677</v>
+        <v>8.589957001783693</v>
       </c>
       <c r="E279" t="n">
-        <v>8.956756289014645</v>
+        <v>8.956757243598096</v>
       </c>
       <c r="F279" t="n">
         <v>2215964</v>
@@ -6012,16 +6012,16 @@
         <v>44637</v>
       </c>
       <c r="B280" t="n">
-        <v>9.238256454467773</v>
+        <v>9.238255500793457</v>
       </c>
       <c r="C280" t="n">
-        <v>9.297967012540948</v>
+        <v>9.297966052702654</v>
       </c>
       <c r="D280" t="n">
-        <v>8.632608189664953</v>
+        <v>8.632607298512305</v>
       </c>
       <c r="E280" t="n">
-        <v>8.999409274674644</v>
+        <v>8.999408345656759</v>
       </c>
       <c r="F280" t="n">
         <v>2645230</v>
@@ -6032,16 +6032,16 @@
         <v>44638</v>
       </c>
       <c r="B281" t="n">
-        <v>9.47710132598877</v>
+        <v>9.477102279663086</v>
       </c>
       <c r="C281" t="n">
-        <v>9.724477957790413</v>
+        <v>9.724478936358073</v>
       </c>
       <c r="D281" t="n">
-        <v>9.101770809002399</v>
+        <v>9.10177172490746</v>
       </c>
       <c r="E281" t="n">
-        <v>9.238255008171659</v>
+        <v>9.238255937811031</v>
       </c>
       <c r="F281" t="n">
         <v>3558801</v>
@@ -6052,16 +6052,16 @@
         <v>44641</v>
       </c>
       <c r="B282" t="n">
-        <v>9.613585472106934</v>
+        <v>9.61358642578125</v>
       </c>
       <c r="C282" t="n">
-        <v>9.741539356585566</v>
+        <v>9.741540322952996</v>
       </c>
       <c r="D282" t="n">
-        <v>9.391798958899509</v>
+        <v>9.39179989057245</v>
       </c>
       <c r="E282" t="n">
-        <v>9.451511156461731</v>
+        <v>9.451512094058163</v>
       </c>
       <c r="F282" t="n">
         <v>1800179</v>
@@ -6092,16 +6092,16 @@
         <v>44643</v>
       </c>
       <c r="B284" t="n">
-        <v>10.31306552886963</v>
+        <v>10.31306457519531</v>
       </c>
       <c r="C284" t="n">
-        <v>10.31306552886963</v>
+        <v>10.31306457519531</v>
       </c>
       <c r="D284" t="n">
-        <v>9.809781909623382</v>
+        <v>9.809781002488929</v>
       </c>
       <c r="E284" t="n">
-        <v>9.988917693542961</v>
+        <v>9.988916769843387</v>
       </c>
       <c r="F284" t="n">
         <v>2504946</v>
@@ -6112,16 +6112,16 @@
         <v>44644</v>
       </c>
       <c r="B285" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C285" t="n">
-        <v>10.66280605391772</v>
+        <v>10.66280508866036</v>
       </c>
       <c r="D285" t="n">
-        <v>10.11687085627847</v>
+        <v>10.11686994044226</v>
       </c>
       <c r="E285" t="n">
-        <v>10.27894601228337</v>
+        <v>10.27894508177519</v>
       </c>
       <c r="F285" t="n">
         <v>1712400</v>
@@ -6172,16 +6172,16 @@
         <v>44649</v>
       </c>
       <c r="B288" t="n">
-        <v>11.34522533416748</v>
+        <v>11.3452262878418</v>
       </c>
       <c r="C288" t="n">
-        <v>11.52436028006663</v>
+        <v>11.52436124879894</v>
       </c>
       <c r="D288" t="n">
-        <v>10.85047041755722</v>
+        <v>10.85047132964267</v>
       </c>
       <c r="E288" t="n">
-        <v>10.97842430373515</v>
+        <v>10.97842522657635</v>
       </c>
       <c r="F288" t="n">
         <v>4333811</v>
@@ -6232,16 +6232,16 @@
         <v>44652</v>
       </c>
       <c r="B291" t="n">
-        <v>11.24286365509033</v>
+        <v>11.24286270141602</v>
       </c>
       <c r="C291" t="n">
-        <v>11.25139314551746</v>
+        <v>11.25139219111963</v>
       </c>
       <c r="D291" t="n">
-        <v>10.77369962784609</v>
+        <v>10.77369871396854</v>
       </c>
       <c r="E291" t="n">
-        <v>10.96136490891043</v>
+        <v>10.96136397911421</v>
       </c>
       <c r="F291" t="n">
         <v>2500385</v>
@@ -6252,16 +6252,16 @@
         <v>44655</v>
       </c>
       <c r="B292" t="n">
-        <v>11.24286365509033</v>
+        <v>11.24286270141602</v>
       </c>
       <c r="C292" t="n">
-        <v>11.32816515602863</v>
+        <v>11.32816419511862</v>
       </c>
       <c r="D292" t="n">
-        <v>10.84194214793012</v>
+        <v>10.84194122826391</v>
       </c>
       <c r="E292" t="n">
-        <v>11.14903101455816</v>
+        <v>11.14903006884318</v>
       </c>
       <c r="F292" t="n">
         <v>2094330</v>
@@ -6312,16 +6312,16 @@
         <v>44658</v>
       </c>
       <c r="B295" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C295" t="n">
-        <v>10.67133636868552</v>
+        <v>10.67133540265596</v>
       </c>
       <c r="D295" t="n">
-        <v>10.38130814033029</v>
+        <v>10.38130720055572</v>
       </c>
       <c r="E295" t="n">
-        <v>10.50073172249617</v>
+        <v>10.50073077191071</v>
       </c>
       <c r="F295" t="n">
         <v>1517584</v>
@@ -6332,16 +6332,16 @@
         <v>44659</v>
       </c>
       <c r="B296" t="n">
-        <v>10.36424732208252</v>
+        <v>10.36424541473389</v>
       </c>
       <c r="C296" t="n">
-        <v>10.53485278974883</v>
+        <v>10.53485085100341</v>
       </c>
       <c r="D296" t="n">
-        <v>10.17658287435791</v>
+        <v>10.17658100154546</v>
       </c>
       <c r="E296" t="n">
-        <v>10.53485278974883</v>
+        <v>10.53485085100341</v>
       </c>
       <c r="F296" t="n">
         <v>1523665</v>
@@ -6352,16 +6352,16 @@
         <v>44662</v>
       </c>
       <c r="B297" t="n">
-        <v>10.53485298156738</v>
+        <v>10.53485202789307</v>
       </c>
       <c r="C297" t="n">
-        <v>10.61162498989425</v>
+        <v>10.6116240292701</v>
       </c>
       <c r="D297" t="n">
-        <v>10.17658305965309</v>
+        <v>10.17658213841139</v>
       </c>
       <c r="E297" t="n">
-        <v>10.28747550246782</v>
+        <v>10.28747457118751</v>
       </c>
       <c r="F297" t="n">
         <v>2558465</v>
@@ -6392,16 +6392,16 @@
         <v>44664</v>
       </c>
       <c r="B299" t="n">
-        <v>10.60309314727783</v>
+        <v>10.60309505462646</v>
       </c>
       <c r="C299" t="n">
-        <v>10.73104702577405</v>
+        <v>10.7310489561398</v>
       </c>
       <c r="D299" t="n">
-        <v>10.38130664443992</v>
+        <v>10.38130851189225</v>
       </c>
       <c r="E299" t="n">
-        <v>10.62015377435509</v>
+        <v>10.62015568477269</v>
       </c>
       <c r="F299" t="n">
         <v>1276242</v>
@@ -6412,16 +6412,16 @@
         <v>44665</v>
       </c>
       <c r="B300" t="n">
-        <v>10.80782032012939</v>
+        <v>10.80781936645508</v>
       </c>
       <c r="C300" t="n">
-        <v>10.850471068358</v>
+        <v>10.85047011092021</v>
       </c>
       <c r="D300" t="n">
-        <v>10.48367084050864</v>
+        <v>10.48366991543704</v>
       </c>
       <c r="E300" t="n">
-        <v>10.54338304244535</v>
+        <v>10.54338211210479</v>
       </c>
       <c r="F300" t="n">
         <v>1300569</v>
@@ -6492,16 +6492,16 @@
         <v>44673</v>
       </c>
       <c r="B304" t="n">
-        <v>10.37277698516846</v>
+        <v>10.37277793884277</v>
       </c>
       <c r="C304" t="n">
-        <v>10.83341064697621</v>
+        <v>10.83341164300124</v>
       </c>
       <c r="D304" t="n">
-        <v>10.30453529713828</v>
+        <v>10.30453624453844</v>
       </c>
       <c r="E304" t="n">
-        <v>10.72251738856261</v>
+        <v>10.7225183743921</v>
       </c>
       <c r="F304" t="n">
         <v>1699122</v>
@@ -6512,16 +6512,16 @@
         <v>44676</v>
       </c>
       <c r="B305" t="n">
-        <v>10.37277698516846</v>
+        <v>10.37277793884277</v>
       </c>
       <c r="C305" t="n">
-        <v>10.43248918370524</v>
+        <v>10.4324901428695</v>
       </c>
       <c r="D305" t="n">
-        <v>10.15099046834126</v>
+        <v>10.1509914016245</v>
       </c>
       <c r="E305" t="n">
-        <v>10.185111724648</v>
+        <v>10.18511266106835</v>
       </c>
       <c r="F305" t="n">
         <v>3255528</v>
@@ -6552,16 +6552,16 @@
         <v>44678</v>
       </c>
       <c r="B307" t="n">
-        <v>10.60309314727783</v>
+        <v>10.60309505462646</v>
       </c>
       <c r="C307" t="n">
-        <v>10.79075922054446</v>
+        <v>10.79076116165161</v>
       </c>
       <c r="D307" t="n">
-        <v>10.40689758505581</v>
+        <v>10.40689945711159</v>
       </c>
       <c r="E307" t="n">
-        <v>10.40689758505581</v>
+        <v>10.40689945711159</v>
       </c>
       <c r="F307" t="n">
         <v>2204206</v>
@@ -6632,16 +6632,16 @@
         <v>44684</v>
       </c>
       <c r="B311" t="n">
-        <v>11.31963348388672</v>
+        <v>11.31963443756104</v>
       </c>
       <c r="C311" t="n">
-        <v>11.52435935551378</v>
+        <v>11.52436032643616</v>
       </c>
       <c r="D311" t="n">
-        <v>11.25992211490517</v>
+        <v>11.25992306354883</v>
       </c>
       <c r="E311" t="n">
-        <v>11.38787516623467</v>
+        <v>11.38787612565832</v>
       </c>
       <c r="F311" t="n">
         <v>2034324</v>
@@ -6652,16 +6652,16 @@
         <v>44685</v>
       </c>
       <c r="B312" t="n">
-        <v>11.83144855499268</v>
+        <v>11.83144950866699</v>
       </c>
       <c r="C312" t="n">
-        <v>11.95087212149613</v>
+        <v>11.95087308479659</v>
       </c>
       <c r="D312" t="n">
-        <v>10.95283284580649</v>
+        <v>10.95283372865995</v>
       </c>
       <c r="E312" t="n">
-        <v>11.09784735325709</v>
+        <v>11.09784824779946</v>
       </c>
       <c r="F312" t="n">
         <v>3044087</v>
@@ -6712,16 +6712,16 @@
         <v>44690</v>
       </c>
       <c r="B315" t="n">
-        <v>10.99548530578613</v>
+        <v>10.99548625946045</v>
       </c>
       <c r="C315" t="n">
-        <v>11.41346741015497</v>
+        <v>11.41346840008224</v>
       </c>
       <c r="D315" t="n">
-        <v>10.85900192549901</v>
+        <v>10.85900286733568</v>
       </c>
       <c r="E315" t="n">
-        <v>11.40493792039742</v>
+        <v>11.4049389095849</v>
       </c>
       <c r="F315" t="n">
         <v>3635836</v>
@@ -6792,16 +6792,16 @@
         <v>44694</v>
       </c>
       <c r="B319" t="n">
-        <v>11.82291889190674</v>
+        <v>11.82291984558105</v>
       </c>
       <c r="C319" t="n">
-        <v>12.07882584170994</v>
+        <v>12.07882681602652</v>
       </c>
       <c r="D319" t="n">
-        <v>11.45611868314717</v>
+        <v>11.45611960723421</v>
       </c>
       <c r="E319" t="n">
-        <v>11.5328906856298</v>
+        <v>11.53289161590952</v>
       </c>
       <c r="F319" t="n">
         <v>2912723</v>
@@ -6812,16 +6812,16 @@
         <v>44697</v>
       </c>
       <c r="B320" t="n">
-        <v>11.93381404876709</v>
+        <v>11.93381118774414</v>
       </c>
       <c r="C320" t="n">
-        <v>12.04470732535947</v>
+        <v>12.04470443775087</v>
       </c>
       <c r="D320" t="n">
-        <v>11.72908730194904</v>
+        <v>11.72908449000746</v>
       </c>
       <c r="E320" t="n">
-        <v>11.81439045669965</v>
+        <v>11.81438762430742</v>
       </c>
       <c r="F320" t="n">
         <v>3054528</v>
@@ -6832,16 +6832,16 @@
         <v>44698</v>
       </c>
       <c r="B321" t="n">
-        <v>12.15559864044189</v>
+        <v>12.15559768676758</v>
       </c>
       <c r="C321" t="n">
-        <v>12.29208285069394</v>
+        <v>12.29208188631167</v>
       </c>
       <c r="D321" t="n">
-        <v>11.95087356193885</v>
+        <v>11.95087262432635</v>
       </c>
       <c r="E321" t="n">
-        <v>12.02764556945041</v>
+        <v>12.02764462581472</v>
       </c>
       <c r="F321" t="n">
         <v>4223023</v>
@@ -6872,16 +6872,16 @@
         <v>44700</v>
       </c>
       <c r="B323" t="n">
-        <v>12.45415782928467</v>
+        <v>12.45415687561035</v>
       </c>
       <c r="C323" t="n">
-        <v>12.56505109394068</v>
+        <v>12.56505013177474</v>
       </c>
       <c r="D323" t="n">
-        <v>11.95087339334582</v>
+        <v>11.9508724782104</v>
       </c>
       <c r="E323" t="n">
-        <v>12.15559846896078</v>
+        <v>12.15559753814858</v>
       </c>
       <c r="F323" t="n">
         <v>1912285</v>
@@ -6892,16 +6892,16 @@
         <v>44701</v>
       </c>
       <c r="B324" t="n">
-        <v>12.50533866882324</v>
+        <v>12.50533771514893</v>
       </c>
       <c r="C324" t="n">
-        <v>12.65888350352286</v>
+        <v>12.658882538139</v>
       </c>
       <c r="D324" t="n">
-        <v>12.30914391126722</v>
+        <v>12.30914297255499</v>
       </c>
       <c r="E324" t="n">
-        <v>12.47974772560942</v>
+        <v>12.4797467738867</v>
       </c>
       <c r="F324" t="n">
         <v>4482610</v>
@@ -6912,16 +6912,16 @@
         <v>44704</v>
       </c>
       <c r="B325" t="n">
-        <v>12.55651950836182</v>
+        <v>12.55652046203613</v>
       </c>
       <c r="C325" t="n">
-        <v>12.7185946545966</v>
+        <v>12.71859562058061</v>
       </c>
       <c r="D325" t="n">
-        <v>12.45415738648542</v>
+        <v>12.45415833238528</v>
       </c>
       <c r="E325" t="n">
-        <v>12.52239907593079</v>
+        <v>12.52240002701364</v>
       </c>
       <c r="F325" t="n">
         <v>3535792</v>
@@ -6932,16 +6932,16 @@
         <v>44705</v>
       </c>
       <c r="B326" t="n">
-        <v>12.26649188995361</v>
+        <v>12.2664909362793</v>
       </c>
       <c r="C326" t="n">
-        <v>12.62476263215845</v>
+        <v>12.62476165062991</v>
       </c>
       <c r="D326" t="n">
-        <v>12.02764555306706</v>
+        <v>12.02764461796216</v>
       </c>
       <c r="E326" t="n">
-        <v>12.53092999542028</v>
+        <v>12.53092902118688</v>
       </c>
       <c r="F326" t="n">
         <v>3539137</v>
@@ -6952,16 +6952,16 @@
         <v>44706</v>
       </c>
       <c r="B327" t="n">
-        <v>12.36885452270508</v>
+        <v>12.36885356903076</v>
       </c>
       <c r="C327" t="n">
-        <v>12.51386904370087</v>
+        <v>12.51386807884551</v>
       </c>
       <c r="D327" t="n">
-        <v>12.08735661974265</v>
+        <v>12.08735568777263</v>
       </c>
       <c r="E327" t="n">
-        <v>12.21531051184678</v>
+        <v>12.21530957001115</v>
       </c>
       <c r="F327" t="n">
         <v>1655537</v>
@@ -7072,16 +7072,16 @@
         <v>44714</v>
       </c>
       <c r="B333" t="n">
-        <v>12.57357978820801</v>
+        <v>12.57358074188232</v>
       </c>
       <c r="C333" t="n">
-        <v>13.05980353237607</v>
+        <v>13.05980452292923</v>
       </c>
       <c r="D333" t="n">
-        <v>12.43709559746936</v>
+        <v>12.43709654079169</v>
       </c>
       <c r="E333" t="n">
-        <v>12.6930025274482</v>
+        <v>12.69300349018043</v>
       </c>
       <c r="F333" t="n">
         <v>2071017</v>
@@ -7092,16 +7092,16 @@
         <v>44715</v>
       </c>
       <c r="B334" t="n">
-        <v>12.4456262588501</v>
+        <v>12.44562721252441</v>
       </c>
       <c r="C334" t="n">
-        <v>12.51386794383554</v>
+        <v>12.51386890273903</v>
       </c>
       <c r="D334" t="n">
-        <v>12.34326249449706</v>
+        <v>12.34326344032753</v>
       </c>
       <c r="E334" t="n">
-        <v>12.4456262588501</v>
+        <v>12.44562721252441</v>
       </c>
       <c r="F334" t="n">
         <v>1748789</v>
@@ -7112,16 +7112,16 @@
         <v>44718</v>
       </c>
       <c r="B335" t="n">
-        <v>12.36885452270508</v>
+        <v>12.36885356903076</v>
       </c>
       <c r="C335" t="n">
-        <v>12.65888356469666</v>
+        <v>12.65888258866027</v>
       </c>
       <c r="D335" t="n">
-        <v>12.19824988295512</v>
+        <v>12.19824894243491</v>
       </c>
       <c r="E335" t="n">
-        <v>12.65888356469666</v>
+        <v>12.65888258866027</v>
       </c>
       <c r="F335" t="n">
         <v>1740275</v>
@@ -7172,16 +7172,16 @@
         <v>44721</v>
       </c>
       <c r="B338" t="n">
-        <v>12.15559864044189</v>
+        <v>12.15559768676758</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20678135308851</v>
+        <v>12.20678039539862</v>
       </c>
       <c r="D338" t="n">
-        <v>11.83998029571844</v>
+        <v>11.83997936680614</v>
       </c>
       <c r="E338" t="n">
-        <v>12.07029714283646</v>
+        <v>12.07029619585453</v>
       </c>
       <c r="F338" t="n">
         <v>1444097</v>
@@ -7192,16 +7192,16 @@
         <v>44722</v>
       </c>
       <c r="B339" t="n">
-        <v>11.64378356933594</v>
+        <v>11.64378452301025</v>
       </c>
       <c r="C339" t="n">
-        <v>12.07882545243938</v>
+        <v>12.07882644174544</v>
       </c>
       <c r="D339" t="n">
-        <v>11.42199705857082</v>
+        <v>11.4219979940799</v>
       </c>
       <c r="E339" t="n">
-        <v>12.06176564933559</v>
+        <v>12.06176663724438</v>
       </c>
       <c r="F339" t="n">
         <v>2898634</v>
@@ -7212,16 +7212,16 @@
         <v>44725</v>
       </c>
       <c r="B340" t="n">
-        <v>10.72251892089844</v>
+        <v>10.72251796722412</v>
       </c>
       <c r="C340" t="n">
-        <v>11.50730133143885</v>
+        <v>11.507300307965</v>
       </c>
       <c r="D340" t="n">
-        <v>10.57750521003774</v>
+        <v>10.57750426926113</v>
       </c>
       <c r="E340" t="n">
-        <v>11.23433371572554</v>
+        <v>11.23433271652977</v>
       </c>
       <c r="F340" t="n">
         <v>3958469</v>
@@ -7252,16 +7252,16 @@
         <v>44727</v>
       </c>
       <c r="B342" t="n">
-        <v>10.83341121673584</v>
+        <v>10.83341026306152</v>
       </c>
       <c r="C342" t="n">
-        <v>11.07225754969472</v>
+        <v>11.07225657499456</v>
       </c>
       <c r="D342" t="n">
-        <v>10.67133606533815</v>
+        <v>10.67133512593145</v>
       </c>
       <c r="E342" t="n">
-        <v>10.88459227930441</v>
+        <v>10.88459132112458</v>
       </c>
       <c r="F342" t="n">
         <v>3158221</v>
@@ -7272,16 +7272,16 @@
         <v>44729</v>
       </c>
       <c r="B343" t="n">
-        <v>10.66280555725098</v>
+        <v>10.66280460357666</v>
       </c>
       <c r="C343" t="n">
-        <v>10.69692681473284</v>
+        <v>10.69692585800674</v>
       </c>
       <c r="D343" t="n">
-        <v>10.2960053376542</v>
+        <v>10.29600441678626</v>
       </c>
       <c r="E343" t="n">
-        <v>10.69692681473284</v>
+        <v>10.69692585800674</v>
       </c>
       <c r="F343" t="n">
         <v>2862346</v>
@@ -7292,16 +7292,16 @@
         <v>44732</v>
       </c>
       <c r="B344" t="n">
-        <v>10.38130664825439</v>
+        <v>10.38130760192871</v>
       </c>
       <c r="C344" t="n">
-        <v>10.93577290555292</v>
+        <v>10.93577391016304</v>
       </c>
       <c r="D344" t="n">
-        <v>10.33012559158704</v>
+        <v>10.33012654055963</v>
       </c>
       <c r="E344" t="n">
-        <v>10.93577290555292</v>
+        <v>10.93577391016304</v>
       </c>
       <c r="F344" t="n">
         <v>1404768</v>
@@ -7352,16 +7352,16 @@
         <v>44735</v>
       </c>
       <c r="B347" t="n">
-        <v>10.80782032012939</v>
+        <v>10.80781936645508</v>
       </c>
       <c r="C347" t="n">
-        <v>10.91018327029472</v>
+        <v>10.91018230758797</v>
       </c>
       <c r="D347" t="n">
-        <v>10.48367084050864</v>
+        <v>10.48366991543704</v>
       </c>
       <c r="E347" t="n">
-        <v>10.49220115507102</v>
+        <v>10.49220022924672</v>
       </c>
       <c r="F347" t="n">
         <v>2364459</v>
@@ -7392,16 +7392,16 @@
         <v>44739</v>
       </c>
       <c r="B349" t="n">
-        <v>10.73957824707031</v>
+        <v>10.739577293396</v>
       </c>
       <c r="C349" t="n">
-        <v>10.85047151637684</v>
+        <v>10.8504705528552</v>
       </c>
       <c r="D349" t="n">
-        <v>10.45808032863837</v>
+        <v>10.45807939996106</v>
       </c>
       <c r="E349" t="n">
-        <v>10.79929045147256</v>
+        <v>10.7992894924958</v>
       </c>
       <c r="F349" t="n">
         <v>1685945</v>
@@ -7432,16 +7432,16 @@
         <v>44741</v>
       </c>
       <c r="B351" t="n">
-        <v>10.16805171966553</v>
+        <v>10.16805076599121</v>
       </c>
       <c r="C351" t="n">
-        <v>10.33865636248849</v>
+        <v>10.33865539281295</v>
       </c>
       <c r="D351" t="n">
-        <v>10.03156833524049</v>
+        <v>10.03156739436712</v>
       </c>
       <c r="E351" t="n">
-        <v>10.32159655787287</v>
+        <v>10.32159558979739</v>
       </c>
       <c r="F351" t="n">
         <v>1480384</v>
@@ -7492,16 +7492,16 @@
         <v>44746</v>
       </c>
       <c r="B354" t="n">
-        <v>9.656235694885254</v>
+        <v>9.65623664855957</v>
       </c>
       <c r="C354" t="n">
-        <v>10.02303587602198</v>
+        <v>10.02303686592241</v>
       </c>
       <c r="D354" t="n">
-        <v>9.656235694885254</v>
+        <v>9.65623664855957</v>
       </c>
       <c r="E354" t="n">
-        <v>9.920673763475978</v>
+        <v>9.920674743266868</v>
       </c>
       <c r="F354" t="n">
         <v>1779400</v>
@@ -7512,16 +7512,16 @@
         <v>44747</v>
       </c>
       <c r="B355" t="n">
-        <v>9.622116088867188</v>
+        <v>9.622114181518555</v>
       </c>
       <c r="C355" t="n">
-        <v>9.681828293425781</v>
+        <v>9.681826374240668</v>
       </c>
       <c r="D355" t="n">
-        <v>9.178543835063046</v>
+        <v>9.178542015641739</v>
       </c>
       <c r="E355" t="n">
-        <v>9.681828293425781</v>
+        <v>9.681826374240668</v>
       </c>
       <c r="F355" t="n">
         <v>3899578</v>
@@ -7532,16 +7532,16 @@
         <v>44748</v>
       </c>
       <c r="B356" t="n">
-        <v>9.647706985473633</v>
+        <v>9.647706031799316</v>
       </c>
       <c r="C356" t="n">
-        <v>9.869493523559241</v>
+        <v>9.869492547961359</v>
       </c>
       <c r="D356" t="n">
-        <v>9.400330327288428</v>
+        <v>9.400329398067255</v>
       </c>
       <c r="E356" t="n">
-        <v>9.681828245050916</v>
+        <v>9.681827288003719</v>
       </c>
       <c r="F356" t="n">
         <v>2475348</v>
@@ -7552,16 +7552,16 @@
         <v>44749</v>
       </c>
       <c r="B357" t="n">
-        <v>9.912143707275391</v>
+        <v>9.912142753601074</v>
       </c>
       <c r="C357" t="n">
-        <v>10.11687042846193</v>
+        <v>10.1168694550903</v>
       </c>
       <c r="D357" t="n">
-        <v>9.630646630175109</v>
+        <v>9.630645703584392</v>
       </c>
       <c r="E357" t="n">
-        <v>9.647706434405947</v>
+        <v>9.647705506173859</v>
       </c>
       <c r="F357" t="n">
         <v>2588468</v>
@@ -7612,16 +7612,16 @@
         <v>44754</v>
       </c>
       <c r="B360" t="n">
-        <v>9.229724884033203</v>
+        <v>9.22972583770752</v>
       </c>
       <c r="C360" t="n">
-        <v>9.289436258569864</v>
+        <v>9.289437218413942</v>
       </c>
       <c r="D360" t="n">
-        <v>8.879984477223353</v>
+        <v>8.879985394760249</v>
       </c>
       <c r="E360" t="n">
-        <v>9.229724884033203</v>
+        <v>9.22972583770752</v>
       </c>
       <c r="F360" t="n">
         <v>1719496</v>
@@ -7632,16 +7632,16 @@
         <v>44755</v>
       </c>
       <c r="B361" t="n">
-        <v>9.255314826965332</v>
+        <v>9.255315780639648</v>
       </c>
       <c r="C361" t="n">
-        <v>9.383268712363071</v>
+        <v>9.383269679221847</v>
       </c>
       <c r="D361" t="n">
-        <v>9.050589764745537</v>
+        <v>9.050590697324836</v>
       </c>
       <c r="E361" t="n">
-        <v>9.204133767556202</v>
+        <v>9.204134715956785</v>
       </c>
       <c r="F361" t="n">
         <v>1870727</v>
@@ -7652,16 +7652,16 @@
         <v>44756</v>
       </c>
       <c r="B362" t="n">
-        <v>9.383268356323242</v>
+        <v>9.383269309997559</v>
       </c>
       <c r="C362" t="n">
-        <v>9.485631295840706</v>
+        <v>9.485632259918743</v>
       </c>
       <c r="D362" t="n">
-        <v>9.06764922409579</v>
+        <v>9.067650145691958</v>
       </c>
       <c r="E362" t="n">
-        <v>9.204133418313491</v>
+        <v>9.204134353781315</v>
       </c>
       <c r="F362" t="n">
         <v>823562</v>
@@ -7712,16 +7712,16 @@
         <v>44761</v>
       </c>
       <c r="B365" t="n">
-        <v>9.767128944396973</v>
+        <v>9.767129898071289</v>
       </c>
       <c r="C365" t="n">
-        <v>9.929204075840321</v>
+        <v>9.929205045339851</v>
       </c>
       <c r="D365" t="n">
-        <v>9.562403894744662</v>
+        <v>9.562404828429376</v>
       </c>
       <c r="E365" t="n">
-        <v>9.562403894744662</v>
+        <v>9.562404828429376</v>
       </c>
       <c r="F365" t="n">
         <v>2310433</v>
@@ -7752,16 +7752,16 @@
         <v>44763</v>
       </c>
       <c r="B367" t="n">
-        <v>9.963325500488281</v>
+        <v>9.963324546813965</v>
       </c>
       <c r="C367" t="n">
-        <v>10.19364233815759</v>
+        <v>10.1936413624377</v>
       </c>
       <c r="D367" t="n">
-        <v>9.946264871833769</v>
+        <v>9.94626391979247</v>
       </c>
       <c r="E367" t="n">
-        <v>10.02303687619577</v>
+        <v>10.02303591680597</v>
       </c>
       <c r="F367" t="n">
         <v>1242590</v>
@@ -7792,16 +7792,16 @@
         <v>44767</v>
       </c>
       <c r="B369" t="n">
-        <v>10.17658233642578</v>
+        <v>10.1765832901001</v>
       </c>
       <c r="C369" t="n">
-        <v>10.41542865919991</v>
+        <v>10.41542963525714</v>
       </c>
       <c r="D369" t="n">
-        <v>10.11687013729478</v>
+        <v>10.11687108537331</v>
       </c>
       <c r="E369" t="n">
-        <v>10.27041414303648</v>
+        <v>10.27041510550403</v>
       </c>
       <c r="F369" t="n">
         <v>1372535</v>
@@ -7832,16 +7832,16 @@
         <v>44769</v>
       </c>
       <c r="B371" t="n">
-        <v>10.5092601776123</v>
+        <v>10.50926208496094</v>
       </c>
       <c r="C371" t="n">
-        <v>10.61162311212909</v>
+        <v>10.6116250380558</v>
       </c>
       <c r="D371" t="n">
-        <v>10.07421749977017</v>
+        <v>10.07421932816195</v>
       </c>
       <c r="E371" t="n">
-        <v>10.12539855473696</v>
+        <v>10.1254003924177</v>
       </c>
       <c r="F371" t="n">
         <v>2091898</v>
@@ -7852,16 +7852,16 @@
         <v>44770</v>
       </c>
       <c r="B372" t="n">
-        <v>10.74810791015625</v>
+        <v>10.74810695648193</v>
       </c>
       <c r="C372" t="n">
-        <v>10.84194136852631</v>
+        <v>10.8419404065262</v>
       </c>
       <c r="D372" t="n">
-        <v>10.21923336502487</v>
+        <v>10.21923245827733</v>
       </c>
       <c r="E372" t="n">
-        <v>10.21923336502487</v>
+        <v>10.21923245827733</v>
       </c>
       <c r="F372" t="n">
         <v>1467207</v>
@@ -7892,16 +7892,16 @@
         <v>44774</v>
       </c>
       <c r="B374" t="n">
-        <v>11.26845264434814</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C374" t="n">
-        <v>11.77173701970006</v>
+        <v>11.77173801596846</v>
       </c>
       <c r="D374" t="n">
-        <v>11.09784719833203</v>
+        <v>11.09784813756763</v>
       </c>
       <c r="E374" t="n">
-        <v>11.64378314133378</v>
+        <v>11.64378412677316</v>
       </c>
       <c r="F374" t="n">
         <v>4838693</v>
@@ -7912,16 +7912,16 @@
         <v>44775</v>
       </c>
       <c r="B375" t="n">
-        <v>11.26845264434814</v>
+        <v>11.26845359802246</v>
       </c>
       <c r="C375" t="n">
-        <v>11.49876863590757</v>
+        <v>11.49876960907404</v>
       </c>
       <c r="D375" t="n">
-        <v>11.24286170375824</v>
+        <v>11.24286265526674</v>
       </c>
       <c r="E375" t="n">
-        <v>11.39640569813119</v>
+        <v>11.39640666263446</v>
       </c>
       <c r="F375" t="n">
         <v>2088249</v>
@@ -7992,16 +7992,16 @@
         <v>44781</v>
       </c>
       <c r="B379" t="n">
-        <v>13.1621675491333</v>
+        <v>13.16216659545898</v>
       </c>
       <c r="C379" t="n">
-        <v>13.30718124064354</v>
+        <v>13.30718027646215</v>
       </c>
       <c r="D379" t="n">
-        <v>12.75271576790837</v>
+        <v>12.75271484390118</v>
       </c>
       <c r="E379" t="n">
-        <v>12.79536651411238</v>
+        <v>12.7953655870149</v>
       </c>
       <c r="F379" t="n">
         <v>3550084</v>
@@ -8032,16 +8032,16 @@
         <v>44783</v>
       </c>
       <c r="B381" t="n">
-        <v>13.39248371124268</v>
+        <v>13.39248466491699</v>
       </c>
       <c r="C381" t="n">
-        <v>13.77634537898129</v>
+        <v>13.77634635999027</v>
       </c>
       <c r="D381" t="n">
-        <v>13.17922832861007</v>
+        <v>13.17922926709854</v>
       </c>
       <c r="E381" t="n">
-        <v>13.30718139327297</v>
+        <v>13.30718234087294</v>
       </c>
       <c r="F381" t="n">
         <v>6344215</v>
@@ -8052,16 +8052,16 @@
         <v>44784</v>
       </c>
       <c r="B382" t="n">
-        <v>13.36689472198486</v>
+        <v>13.36689281463623</v>
       </c>
       <c r="C382" t="n">
-        <v>13.63986232745854</v>
+        <v>13.63986038115962</v>
       </c>
       <c r="D382" t="n">
-        <v>13.11951723685505</v>
+        <v>13.1195153648052</v>
       </c>
       <c r="E382" t="n">
-        <v>13.5204387423815</v>
+        <v>13.52043681312337</v>
       </c>
       <c r="F382" t="n">
         <v>2014153</v>
@@ -8132,16 +8132,16 @@
         <v>44790</v>
       </c>
       <c r="B386" t="n">
-        <v>13.56308746337891</v>
+        <v>13.56308937072754</v>
       </c>
       <c r="C386" t="n">
-        <v>13.64838977060406</v>
+        <v>13.64839168994857</v>
       </c>
       <c r="D386" t="n">
-        <v>13.23893803625678</v>
+        <v>13.23893989802095</v>
       </c>
       <c r="E386" t="n">
-        <v>13.64838977060406</v>
+        <v>13.64839168994857</v>
       </c>
       <c r="F386" t="n">
         <v>4054357</v>
@@ -8212,16 +8212,16 @@
         <v>44796</v>
       </c>
       <c r="B390" t="n">
-        <v>12.29208278656006</v>
+        <v>12.29208183288574</v>
       </c>
       <c r="C390" t="n">
-        <v>12.64182321275093</v>
+        <v>12.6418222319422</v>
       </c>
       <c r="D390" t="n">
-        <v>12.25796235261258</v>
+        <v>12.25796140158548</v>
       </c>
       <c r="E390" t="n">
-        <v>12.64182321275093</v>
+        <v>12.6418222319422</v>
       </c>
       <c r="F390" t="n">
         <v>5845922</v>
@@ -8232,16 +8232,16 @@
         <v>44797</v>
       </c>
       <c r="B391" t="n">
-        <v>12.42856693267822</v>
+        <v>12.42856597900391</v>
       </c>
       <c r="C391" t="n">
-        <v>12.57358145611087</v>
+        <v>12.57358049130923</v>
       </c>
       <c r="D391" t="n">
-        <v>12.13000839580709</v>
+        <v>12.1300074650419</v>
       </c>
       <c r="E391" t="n">
-        <v>12.29208272383475</v>
+        <v>12.2920817806332</v>
       </c>
       <c r="F391" t="n">
         <v>4991546</v>
@@ -8272,16 +8272,16 @@
         <v>44799</v>
       </c>
       <c r="B393" t="n">
-        <v>12.18118953704834</v>
+        <v>12.18118858337402</v>
       </c>
       <c r="C393" t="n">
-        <v>12.49680952970967</v>
+        <v>12.49680855132523</v>
       </c>
       <c r="D393" t="n">
-        <v>12.03617583726701</v>
+        <v>12.03617489494593</v>
       </c>
       <c r="E393" t="n">
-        <v>12.45415795648967</v>
+        <v>12.45415698144445</v>
       </c>
       <c r="F393" t="n">
         <v>1257591</v>
@@ -8292,16 +8292,16 @@
         <v>44802</v>
       </c>
       <c r="B394" t="n">
-        <v>12.25796031951904</v>
+        <v>12.25796127319336</v>
       </c>
       <c r="C394" t="n">
-        <v>12.40297399505652</v>
+        <v>12.40297496001295</v>
       </c>
       <c r="D394" t="n">
-        <v>12.04470413823857</v>
+        <v>12.04470507532147</v>
       </c>
       <c r="E394" t="n">
-        <v>12.18118750055817</v>
+        <v>12.18118844825953</v>
       </c>
       <c r="F394" t="n">
         <v>4196061</v>
@@ -8332,16 +8332,16 @@
         <v>44804</v>
       </c>
       <c r="B396" t="n">
-        <v>12.03617477416992</v>
+        <v>12.03617572784424</v>
       </c>
       <c r="C396" t="n">
-        <v>12.33473328658969</v>
+        <v>12.33473426391999</v>
       </c>
       <c r="D396" t="n">
-        <v>11.92528151817592</v>
+        <v>11.92528246306372</v>
       </c>
       <c r="E396" t="n">
-        <v>12.10441646071113</v>
+        <v>12.1044174197925</v>
       </c>
       <c r="F396" t="n">
         <v>1958303</v>
@@ -8372,16 +8372,16 @@
         <v>44806</v>
       </c>
       <c r="B398" t="n">
-        <v>12.42003726959229</v>
+        <v>12.42003631591797</v>
       </c>
       <c r="C398" t="n">
-        <v>12.70153434877891</v>
+        <v>12.7015333734898</v>
       </c>
       <c r="D398" t="n">
-        <v>12.36885455818716</v>
+        <v>12.36885360844292</v>
       </c>
       <c r="E398" t="n">
-        <v>12.52239939406925</v>
+        <v>12.52239843253504</v>
       </c>
       <c r="F398" t="n">
         <v>3090207</v>
@@ -8392,16 +8392,16 @@
         <v>44809</v>
       </c>
       <c r="B399" t="n">
-        <v>13.3071813583374</v>
+        <v>13.30718231201172</v>
       </c>
       <c r="C399" t="n">
-        <v>13.40954430454897</v>
+        <v>13.40954526555925</v>
       </c>
       <c r="D399" t="n">
-        <v>12.38591566701658</v>
+        <v>12.38591655466734</v>
       </c>
       <c r="E399" t="n">
-        <v>12.48827778864485</v>
+        <v>12.48827868363151</v>
       </c>
       <c r="F399" t="n">
         <v>2134165</v>
@@ -8412,16 +8412,16 @@
         <v>44810</v>
       </c>
       <c r="B400" t="n">
-        <v>12.19824981689453</v>
+        <v>12.19824886322021</v>
       </c>
       <c r="C400" t="n">
-        <v>13.29012181421445</v>
+        <v>13.29012077517622</v>
       </c>
       <c r="D400" t="n">
-        <v>12.19824981689453</v>
+        <v>12.19824886322021</v>
       </c>
       <c r="E400" t="n">
-        <v>13.29012181421445</v>
+        <v>13.29012077517622</v>
       </c>
       <c r="F400" t="n">
         <v>5053579</v>
@@ -8432,16 +8432,16 @@
         <v>44812</v>
       </c>
       <c r="B401" t="n">
-        <v>12.15559864044189</v>
+        <v>12.15559768676758</v>
       </c>
       <c r="C401" t="n">
-        <v>12.53946032716638</v>
+        <v>12.53945934337598</v>
       </c>
       <c r="D401" t="n">
-        <v>11.79732872233238</v>
+        <v>11.79732779676633</v>
       </c>
       <c r="E401" t="n">
-        <v>12.53946032716638</v>
+        <v>12.53945934337598</v>
       </c>
       <c r="F401" t="n">
         <v>2311852</v>
@@ -8452,16 +8452,16 @@
         <v>44813</v>
       </c>
       <c r="B402" t="n">
-        <v>12.3347339630127</v>
+        <v>12.33473491668701</v>
       </c>
       <c r="C402" t="n">
-        <v>12.47121816816301</v>
+        <v>12.47121913238976</v>
       </c>
       <c r="D402" t="n">
-        <v>11.97646323371185</v>
+        <v>11.97646415968605</v>
       </c>
       <c r="E402" t="n">
-        <v>12.22384070093743</v>
+        <v>12.22384164603791</v>
       </c>
       <c r="F402" t="n">
         <v>2499270</v>
@@ -8472,16 +8472,16 @@
         <v>44816</v>
       </c>
       <c r="B403" t="n">
-        <v>12.30696201324463</v>
+        <v>12.30696105957031</v>
       </c>
       <c r="C403" t="n">
-        <v>12.58102134762649</v>
+        <v>12.58102037271514</v>
       </c>
       <c r="D403" t="n">
-        <v>12.05859669488552</v>
+        <v>12.05859576045719</v>
       </c>
       <c r="E403" t="n">
-        <v>12.05859669488552</v>
+        <v>12.05859576045719</v>
       </c>
       <c r="F403" t="n">
         <v>4043263</v>
@@ -8492,16 +8492,16 @@
         <v>44817</v>
       </c>
       <c r="B404" t="n">
-        <v>11.82735824584961</v>
+        <v>11.82735919952393</v>
       </c>
       <c r="C404" t="n">
-        <v>12.11854579094386</v>
+        <v>12.11854676809748</v>
       </c>
       <c r="D404" t="n">
-        <v>11.74171455920428</v>
+        <v>11.7417155059729</v>
       </c>
       <c r="E404" t="n">
-        <v>12.11854579094386</v>
+        <v>12.11854676809748</v>
       </c>
       <c r="F404" t="n">
         <v>3904244</v>
@@ -8612,16 +8612,16 @@
         <v>44825</v>
       </c>
       <c r="B410" t="n">
-        <v>11.65607070922852</v>
+        <v>11.65607166290283</v>
       </c>
       <c r="C410" t="n">
-        <v>12.10998235665763</v>
+        <v>12.10998334747001</v>
       </c>
       <c r="D410" t="n">
-        <v>11.50191321893803</v>
+        <v>11.50191415999951</v>
       </c>
       <c r="E410" t="n">
-        <v>11.9472590954252</v>
+        <v>11.94726007292391</v>
       </c>
       <c r="F410" t="n">
         <v>3396829</v>
@@ -8672,16 +8672,16 @@
         <v>44830</v>
       </c>
       <c r="B413" t="n">
-        <v>11.45909214019775</v>
+        <v>11.45909118652344</v>
       </c>
       <c r="C413" t="n">
-        <v>11.84448752702055</v>
+        <v>11.844486541272</v>
       </c>
       <c r="D413" t="n">
-        <v>11.34775525533786</v>
+        <v>11.34775431092947</v>
       </c>
       <c r="E413" t="n">
-        <v>11.81879433631571</v>
+        <v>11.81879335270545</v>
       </c>
       <c r="F413" t="n">
         <v>3443068</v>
@@ -8692,16 +8692,16 @@
         <v>44831</v>
       </c>
       <c r="B414" t="n">
-        <v>11.30493450164795</v>
+        <v>11.30493354797363</v>
       </c>
       <c r="C414" t="n">
-        <v>11.63894352718433</v>
+        <v>11.6389425453333</v>
       </c>
       <c r="D414" t="n">
-        <v>11.26211306428218</v>
+        <v>11.26211211422024</v>
       </c>
       <c r="E414" t="n">
-        <v>11.53617158275647</v>
+        <v>11.53617060957519</v>
       </c>
       <c r="F414" t="n">
         <v>2656202</v>
@@ -8712,16 +8712,16 @@
         <v>44832</v>
       </c>
       <c r="B415" t="n">
-        <v>11.56186485290527</v>
+        <v>11.56186389923096</v>
       </c>
       <c r="C415" t="n">
-        <v>11.69889411306563</v>
+        <v>11.69889314808853</v>
       </c>
       <c r="D415" t="n">
-        <v>11.21072675530685</v>
+        <v>11.21072583059598</v>
       </c>
       <c r="E415" t="n">
-        <v>11.34775601546721</v>
+        <v>11.34775507945355</v>
       </c>
       <c r="F415" t="n">
         <v>2669428</v>
@@ -8732,16 +8732,16 @@
         <v>44833</v>
       </c>
       <c r="B416" t="n">
-        <v>11.61325073242188</v>
+        <v>11.61324977874756</v>
       </c>
       <c r="C416" t="n">
-        <v>11.66463629045436</v>
+        <v>11.66463533256029</v>
       </c>
       <c r="D416" t="n">
-        <v>11.29636913906888</v>
+        <v>11.29636821141672</v>
       </c>
       <c r="E416" t="n">
-        <v>11.45052828691627</v>
+        <v>11.45052734660464</v>
       </c>
       <c r="F416" t="n">
         <v>3327572</v>
@@ -8772,16 +8772,16 @@
         <v>44837</v>
       </c>
       <c r="B418" t="n">
-        <v>12.41829967498779</v>
+        <v>12.41829872131348</v>
       </c>
       <c r="C418" t="n">
-        <v>12.62384439472611</v>
+        <v>12.62384342526681</v>
       </c>
       <c r="D418" t="n">
-        <v>12.01577518291347</v>
+        <v>12.01577426015137</v>
       </c>
       <c r="E418" t="n">
-        <v>12.06716156899389</v>
+        <v>12.06716064228553</v>
       </c>
       <c r="F418" t="n">
         <v>3117277</v>
@@ -8852,16 +8852,16 @@
         <v>44841</v>
       </c>
       <c r="B422" t="n">
-        <v>12.6238431930542</v>
+        <v>12.62384414672852</v>
       </c>
       <c r="C422" t="n">
-        <v>12.92359488443413</v>
+        <v>12.92359586075333</v>
       </c>
       <c r="D422" t="n">
-        <v>12.54676362127082</v>
+        <v>12.54676456912213</v>
       </c>
       <c r="E422" t="n">
-        <v>12.92359488443413</v>
+        <v>12.92359586075333</v>
       </c>
       <c r="F422" t="n">
         <v>1382517</v>
@@ -8912,16 +8912,16 @@
         <v>44847</v>
       </c>
       <c r="B425" t="n">
-        <v>13.0520601272583</v>
+        <v>13.05206108093262</v>
       </c>
       <c r="C425" t="n">
-        <v>13.30899038628898</v>
+        <v>13.30899135873641</v>
       </c>
       <c r="D425" t="n">
-        <v>12.57245692209548</v>
+        <v>12.57245784072665</v>
       </c>
       <c r="E425" t="n">
-        <v>12.58958516625311</v>
+        <v>12.58958608613578</v>
       </c>
       <c r="F425" t="n">
         <v>3708082</v>
@@ -8992,16 +8992,16 @@
         <v>44853</v>
       </c>
       <c r="B429" t="n">
-        <v>12.95785045623779</v>
+        <v>12.95785236358643</v>
       </c>
       <c r="C429" t="n">
-        <v>13.02636590117292</v>
+        <v>13.02636781860678</v>
       </c>
       <c r="D429" t="n">
-        <v>12.71804928500614</v>
+        <v>12.71805115705691</v>
       </c>
       <c r="E429" t="n">
-        <v>12.80369297273763</v>
+        <v>12.80369485739484</v>
       </c>
       <c r="F429" t="n">
         <v>1282165</v>
@@ -9012,16 +9012,16 @@
         <v>44854</v>
       </c>
       <c r="B430" t="n">
-        <v>12.78656387329102</v>
+        <v>12.78656578063965</v>
       </c>
       <c r="C430" t="n">
-        <v>13.08631636730787</v>
+        <v>13.08631831937005</v>
       </c>
       <c r="D430" t="n">
-        <v>12.65809875430757</v>
+        <v>12.65810064249329</v>
       </c>
       <c r="E430" t="n">
-        <v>13.08631636730787</v>
+        <v>13.08631831937005</v>
       </c>
       <c r="F430" t="n">
         <v>2107193</v>
@@ -9072,16 +9072,16 @@
         <v>44859</v>
       </c>
       <c r="B433" t="n">
-        <v>12.71805095672607</v>
+        <v>12.71805191040039</v>
       </c>
       <c r="C433" t="n">
-        <v>13.07775399772944</v>
+        <v>13.07775497837641</v>
       </c>
       <c r="D433" t="n">
-        <v>12.69235858915441</v>
+        <v>12.69235954090216</v>
       </c>
       <c r="E433" t="n">
-        <v>12.87220928507275</v>
+        <v>12.87221025030677</v>
       </c>
       <c r="F433" t="n">
         <v>1601293</v>
@@ -9092,16 +9092,16 @@
         <v>44860</v>
       </c>
       <c r="B434" t="n">
-        <v>12.29839706420898</v>
+        <v>12.29839897155762</v>
       </c>
       <c r="C434" t="n">
-        <v>13.00923730694242</v>
+        <v>13.0092393245347</v>
       </c>
       <c r="D434" t="n">
-        <v>12.17849688652397</v>
+        <v>12.17849877527738</v>
       </c>
       <c r="E434" t="n">
-        <v>12.61527781329898</v>
+        <v>12.61527976979239</v>
       </c>
       <c r="F434" t="n">
         <v>4556230</v>
@@ -9112,16 +9112,16 @@
         <v>44861</v>
       </c>
       <c r="B435" t="n">
-        <v>13.13770389556885</v>
+        <v>13.13770484924316</v>
       </c>
       <c r="C435" t="n">
-        <v>13.30042633889646</v>
+        <v>13.30042730438291</v>
       </c>
       <c r="D435" t="n">
-        <v>12.22131809049146</v>
+        <v>12.22131897764474</v>
       </c>
       <c r="E435" t="n">
-        <v>12.35834816743837</v>
+        <v>12.35834906453876</v>
       </c>
       <c r="F435" t="n">
         <v>3242667</v>
@@ -9212,16 +9212,16 @@
         <v>44869</v>
       </c>
       <c r="B440" t="n">
-        <v>14.01126766204834</v>
+        <v>14.01126575469971</v>
       </c>
       <c r="C440" t="n">
-        <v>14.29389195916385</v>
+        <v>14.29389001334168</v>
       </c>
       <c r="D440" t="n">
-        <v>13.80572294357798</v>
+        <v>13.80572106421007</v>
       </c>
       <c r="E440" t="n">
-        <v>14.13973280187356</v>
+        <v>14.13973087703701</v>
       </c>
       <c r="F440" t="n">
         <v>3663661</v>
@@ -9232,16 +9232,16 @@
         <v>44872</v>
       </c>
       <c r="B441" t="n">
-        <v>13.40319728851318</v>
+        <v>13.4031982421875</v>
       </c>
       <c r="C441" t="n">
-        <v>14.03695880976449</v>
+        <v>14.03695980853268</v>
       </c>
       <c r="D441" t="n">
-        <v>13.36037667840605</v>
+        <v>13.36037762903356</v>
       </c>
       <c r="E441" t="n">
-        <v>13.9341876963408</v>
+        <v>13.93418868779654</v>
       </c>
       <c r="F441" t="n">
         <v>2151917</v>
@@ -9272,16 +9272,16 @@
         <v>44874</v>
       </c>
       <c r="B443" t="n">
-        <v>13.13770389556885</v>
+        <v>13.13770484924316</v>
       </c>
       <c r="C443" t="n">
-        <v>13.55735659936989</v>
+        <v>13.55735758350707</v>
       </c>
       <c r="D443" t="n">
-        <v>12.98354557436813</v>
+        <v>12.983546516852</v>
       </c>
       <c r="E443" t="n">
-        <v>13.29186139218626</v>
+        <v>13.29186235705097</v>
       </c>
       <c r="F443" t="n">
         <v>3144132</v>
@@ -9292,16 +9292,16 @@
         <v>44875</v>
       </c>
       <c r="B444" t="n">
-        <v>12.2470121383667</v>
+        <v>12.24701118469238</v>
       </c>
       <c r="C444" t="n">
-        <v>12.83795140918214</v>
+        <v>12.83795040949141</v>
       </c>
       <c r="D444" t="n">
-        <v>11.67320111185027</v>
+        <v>11.6732002028586</v>
       </c>
       <c r="E444" t="n">
-        <v>12.83795140918214</v>
+        <v>12.83795040949141</v>
       </c>
       <c r="F444" t="n">
         <v>10581398</v>
@@ -9352,16 +9352,16 @@
         <v>44881</v>
       </c>
       <c r="B447" t="n">
-        <v>11.26211357116699</v>
+        <v>11.26211166381836</v>
       </c>
       <c r="C447" t="n">
-        <v>12.15280462087997</v>
+        <v>12.15280256268413</v>
       </c>
       <c r="D447" t="n">
-        <v>11.15934162211358</v>
+        <v>11.15933973217037</v>
       </c>
       <c r="E447" t="n">
-        <v>12.06716174229381</v>
+        <v>12.06715969860243</v>
       </c>
       <c r="F447" t="n">
         <v>3929079</v>
@@ -9392,16 +9392,16 @@
         <v>44883</v>
       </c>
       <c r="B449" t="n">
-        <v>10.92810249328613</v>
+        <v>10.92810153961182</v>
       </c>
       <c r="C449" t="n">
-        <v>11.38201332758762</v>
+        <v>11.38201233430139</v>
       </c>
       <c r="D449" t="n">
-        <v>10.91953837129458</v>
+        <v>10.91953741836764</v>
       </c>
       <c r="E449" t="n">
-        <v>11.13364636858307</v>
+        <v>11.13364539697134</v>
       </c>
       <c r="F449" t="n">
         <v>5719164</v>
@@ -9412,16 +9412,16 @@
         <v>44886</v>
       </c>
       <c r="B450" t="n">
-        <v>11.25354671478271</v>
+        <v>11.25354766845703</v>
       </c>
       <c r="C450" t="n">
-        <v>11.33062628193585</v>
+        <v>11.33062724214222</v>
       </c>
       <c r="D450" t="n">
-        <v>10.80820167775862</v>
+        <v>10.80820259369247</v>
       </c>
       <c r="E450" t="n">
-        <v>10.98805235194947</v>
+        <v>10.98805328312464</v>
       </c>
       <c r="F450" t="n">
         <v>4991964</v>
@@ -9512,16 +9512,16 @@
         <v>44893</v>
       </c>
       <c r="B455" t="n">
-        <v>10.96235847473145</v>
+        <v>10.96236038208008</v>
       </c>
       <c r="C455" t="n">
-        <v>11.18503139155672</v>
+        <v>11.18503333764837</v>
       </c>
       <c r="D455" t="n">
-        <v>10.84245748307556</v>
+        <v>10.84245936956254</v>
       </c>
       <c r="E455" t="n">
-        <v>10.95379435377979</v>
+        <v>10.95379625963835</v>
       </c>
       <c r="F455" t="n">
         <v>2642270</v>
@@ -9552,16 +9552,16 @@
         <v>44895</v>
       </c>
       <c r="B457" t="n">
-        <v>11.35632038116455</v>
+        <v>11.35631942749023</v>
       </c>
       <c r="C457" t="n">
-        <v>11.57042922318563</v>
+        <v>11.57042825153101</v>
       </c>
       <c r="D457" t="n">
-        <v>11.04800453920422</v>
+        <v>11.04800361142147</v>
       </c>
       <c r="E457" t="n">
-        <v>11.34775625836705</v>
+        <v>11.34775530541193</v>
       </c>
       <c r="F457" t="n">
         <v>6904107</v>
@@ -9592,16 +9592,16 @@
         <v>44897</v>
       </c>
       <c r="B459" t="n">
-        <v>11.32206249237061</v>
+        <v>11.32206344604492</v>
       </c>
       <c r="C459" t="n">
-        <v>11.47621998202977</v>
+        <v>11.47622094868901</v>
       </c>
       <c r="D459" t="n">
-        <v>11.07369554065139</v>
+        <v>11.07369647340539</v>
       </c>
       <c r="E459" t="n">
-        <v>11.1935965433492</v>
+        <v>11.19359748620264</v>
       </c>
       <c r="F459" t="n">
         <v>2110020</v>
@@ -9632,16 +9632,16 @@
         <v>44901</v>
       </c>
       <c r="B461" t="n">
-        <v>10.64548015594482</v>
+        <v>10.64547920227051</v>
       </c>
       <c r="C461" t="n">
-        <v>10.88528219337026</v>
+        <v>10.8852812182133</v>
       </c>
       <c r="D461" t="n">
-        <v>10.44850038210729</v>
+        <v>10.44849944607939</v>
       </c>
       <c r="E461" t="n">
-        <v>10.62835108559299</v>
+        <v>10.62835013345318</v>
       </c>
       <c r="F461" t="n">
         <v>3634787</v>
@@ -9652,16 +9652,16 @@
         <v>44902</v>
       </c>
       <c r="B462" t="n">
-        <v>10.36285591125488</v>
+        <v>10.36285781860352</v>
       </c>
       <c r="C462" t="n">
-        <v>10.91097288493018</v>
+        <v>10.91097489316318</v>
       </c>
       <c r="D462" t="n">
-        <v>10.24295491097179</v>
+        <v>10.24295679625189</v>
       </c>
       <c r="E462" t="n">
-        <v>10.59409296566996</v>
+        <v>10.59409491557922</v>
       </c>
       <c r="F462" t="n">
         <v>7006882</v>
@@ -9672,16 +9672,16 @@
         <v>44903</v>
       </c>
       <c r="B463" t="n">
-        <v>9.763352394104004</v>
+        <v>9.763351440429688</v>
       </c>
       <c r="C463" t="n">
-        <v>10.37998573239832</v>
+        <v>10.37998471849188</v>
       </c>
       <c r="D463" t="n">
-        <v>9.686273639108899</v>
+        <v>9.686272692963557</v>
       </c>
       <c r="E463" t="n">
-        <v>10.27721295962702</v>
+        <v>10.27721195575933</v>
       </c>
       <c r="F463" t="n">
         <v>6542779</v>
@@ -9692,16 +9692,16 @@
         <v>44904</v>
       </c>
       <c r="B464" t="n">
-        <v>9.694836616516113</v>
+        <v>9.69483757019043</v>
       </c>
       <c r="C464" t="n">
-        <v>10.02884643939223</v>
+        <v>10.02884742592286</v>
       </c>
       <c r="D464" t="n">
-        <v>9.463599554268511</v>
+        <v>9.463600485196199</v>
       </c>
       <c r="E464" t="n">
-        <v>9.848994932875605</v>
+        <v>9.848995901714368</v>
       </c>
       <c r="F464" t="n">
         <v>4631040</v>
@@ -9712,16 +9712,16 @@
         <v>44907</v>
       </c>
       <c r="B465" t="n">
-        <v>9.50642204284668</v>
+        <v>9.506421089172363</v>
       </c>
       <c r="C465" t="n">
-        <v>10.02884668216042</v>
+        <v>10.02884567607701</v>
       </c>
       <c r="D465" t="n">
-        <v>9.42077834844417</v>
+        <v>9.420777403361539</v>
       </c>
       <c r="E465" t="n">
-        <v>9.57493666853537</v>
+        <v>9.57493570798774</v>
       </c>
       <c r="F465" t="n">
         <v>6343387</v>
@@ -9732,16 +9732,16 @@
         <v>44908</v>
       </c>
       <c r="B466" t="n">
-        <v>9.377955436706543</v>
+        <v>9.377956390380859</v>
       </c>
       <c r="C466" t="n">
-        <v>9.951766417669408</v>
+        <v>9.9517674296964</v>
       </c>
       <c r="D466" t="n">
-        <v>9.352263072297678</v>
+        <v>9.352264023359256</v>
       </c>
       <c r="E466" t="n">
-        <v>9.532113746075902</v>
+        <v>9.532114715427072</v>
       </c>
       <c r="F466" t="n">
         <v>6881089</v>
@@ -9832,16 +9832,16 @@
         <v>44915</v>
       </c>
       <c r="B471" t="n">
-        <v>10.33716201782227</v>
+        <v>10.33716297149658</v>
       </c>
       <c r="C471" t="n">
-        <v>10.65404358994094</v>
+        <v>10.65404457284976</v>
       </c>
       <c r="D471" t="n">
-        <v>9.857559660268567</v>
+        <v>9.857560569696266</v>
       </c>
       <c r="E471" t="n">
-        <v>9.926073458192986</v>
+        <v>9.926074373941555</v>
       </c>
       <c r="F471" t="n">
         <v>4483944</v>
@@ -9852,16 +9852,16 @@
         <v>44916</v>
       </c>
       <c r="B472" t="n">
-        <v>10.42280673980713</v>
+        <v>10.42280578613281</v>
       </c>
       <c r="C472" t="n">
-        <v>10.58553001509685</v>
+        <v>10.58552904653355</v>
       </c>
       <c r="D472" t="n">
-        <v>10.08879771587911</v>
+        <v>10.08879679276622</v>
       </c>
       <c r="E472" t="n">
-        <v>10.36285705761706</v>
+        <v>10.36285610942807</v>
       </c>
       <c r="F472" t="n">
         <v>3195923</v>
@@ -9872,16 +9872,16 @@
         <v>44917</v>
       </c>
       <c r="B473" t="n">
-        <v>10.53414249420166</v>
+        <v>10.53414344787598</v>
       </c>
       <c r="C473" t="n">
-        <v>10.60265711609756</v>
+        <v>10.60265807597463</v>
       </c>
       <c r="D473" t="n">
-        <v>10.29434131756599</v>
+        <v>10.29434224953069</v>
       </c>
       <c r="E473" t="n">
-        <v>10.43993468294898</v>
+        <v>10.4399356280945</v>
       </c>
       <c r="F473" t="n">
         <v>2407341</v>
@@ -9912,16 +9912,16 @@
         <v>44921</v>
       </c>
       <c r="B475" t="n">
-        <v>10.66260814666748</v>
+        <v>10.6626091003418</v>
       </c>
       <c r="C475" t="n">
-        <v>10.87671696917752</v>
+        <v>10.87671794200195</v>
       </c>
       <c r="D475" t="n">
-        <v>10.57696362816352</v>
+        <v>10.5769645741777</v>
       </c>
       <c r="E475" t="n">
-        <v>10.82533058790846</v>
+        <v>10.82533155613684</v>
       </c>
       <c r="F475" t="n">
         <v>1667319</v>
@@ -9952,16 +9952,16 @@
         <v>44923</v>
       </c>
       <c r="B477" t="n">
-        <v>10.96907043457031</v>
+        <v>10.96907138824463</v>
       </c>
       <c r="C477" t="n">
-        <v>11.03030139033512</v>
+        <v>11.03030234933299</v>
       </c>
       <c r="D477" t="n">
-        <v>10.43548759461291</v>
+        <v>10.4354885018964</v>
       </c>
       <c r="E477" t="n">
-        <v>10.56669570271517</v>
+        <v>10.56669662140617</v>
       </c>
       <c r="F477" t="n">
         <v>2605824</v>
@@ -9992,16 +9992,16 @@
         <v>44928</v>
       </c>
       <c r="B479" t="n">
-        <v>10.15557670593262</v>
+        <v>10.1555757522583</v>
       </c>
       <c r="C479" t="n">
-        <v>10.91658859396708</v>
+        <v>10.91658756882882</v>
       </c>
       <c r="D479" t="n">
-        <v>9.963136763267295</v>
+        <v>9.963135827664333</v>
       </c>
       <c r="E479" t="n">
-        <v>10.91658859396708</v>
+        <v>10.91658756882882</v>
       </c>
       <c r="F479" t="n">
         <v>2948980</v>
@@ -10052,16 +10052,16 @@
         <v>44931</v>
       </c>
       <c r="B482" t="n">
-        <v>10.05935573577881</v>
+        <v>10.05935478210449</v>
       </c>
       <c r="C482" t="n">
-        <v>10.33926773935673</v>
+        <v>10.33926675914544</v>
       </c>
       <c r="D482" t="n">
-        <v>9.779443732200887</v>
+        <v>9.779442805063548</v>
       </c>
       <c r="E482" t="n">
-        <v>9.796937811326897</v>
+        <v>9.796936882531035</v>
       </c>
       <c r="F482" t="n">
         <v>3524036</v>
@@ -10132,16 +10132,16 @@
         <v>44937</v>
       </c>
       <c r="B486" t="n">
-        <v>11.55513763427734</v>
+        <v>11.55513858795166</v>
       </c>
       <c r="C486" t="n">
-        <v>11.63386351278937</v>
+        <v>11.63386447296113</v>
       </c>
       <c r="D486" t="n">
-        <v>11.09153192889364</v>
+        <v>11.09153284430542</v>
       </c>
       <c r="E486" t="n">
-        <v>11.10902769148988</v>
+        <v>11.10902860834563</v>
       </c>
       <c r="F486" t="n">
         <v>4034277</v>
@@ -10172,16 +10172,16 @@
         <v>44939</v>
       </c>
       <c r="B488" t="n">
-        <v>11.24898242950439</v>
+        <v>11.24898338317871</v>
       </c>
       <c r="C488" t="n">
-        <v>11.33645618609352</v>
+        <v>11.33645714718375</v>
       </c>
       <c r="D488" t="n">
-        <v>10.94282849241817</v>
+        <v>10.94282942013715</v>
       </c>
       <c r="E488" t="n">
-        <v>11.12652135998699</v>
+        <v>11.12652230327921</v>
       </c>
       <c r="F488" t="n">
         <v>2088011</v>
@@ -10192,16 +10192,16 @@
         <v>44942</v>
       </c>
       <c r="B489" t="n">
-        <v>10.8028736114502</v>
+        <v>10.80287265777588</v>
       </c>
       <c r="C489" t="n">
-        <v>11.3014683871045</v>
+        <v>11.30146738941439</v>
       </c>
       <c r="D489" t="n">
-        <v>10.69790744273759</v>
+        <v>10.69790649832965</v>
       </c>
       <c r="E489" t="n">
-        <v>11.25773234310836</v>
+        <v>11.25773134927926</v>
       </c>
       <c r="F489" t="n">
         <v>2251058</v>
@@ -10212,16 +10212,16 @@
         <v>44943</v>
       </c>
       <c r="B490" t="n">
-        <v>11.00405979156494</v>
+        <v>11.00406074523926</v>
       </c>
       <c r="C490" t="n">
-        <v>11.10902762899043</v>
+        <v>11.10902859176186</v>
       </c>
       <c r="D490" t="n">
-        <v>10.75038976364046</v>
+        <v>10.7503906953303</v>
       </c>
       <c r="E490" t="n">
-        <v>10.84660887762188</v>
+        <v>10.8466098176506</v>
       </c>
       <c r="F490" t="n">
         <v>2581089</v>
@@ -10232,16 +10232,16 @@
         <v>44944</v>
       </c>
       <c r="B491" t="n">
-        <v>11.61636924743652</v>
+        <v>11.61636829376221</v>
       </c>
       <c r="C491" t="n">
-        <v>11.81755621132026</v>
+        <v>11.81755524112901</v>
       </c>
       <c r="D491" t="n">
-        <v>11.08278551475007</v>
+        <v>11.08278460488162</v>
       </c>
       <c r="E491" t="n">
-        <v>11.12652239712147</v>
+        <v>11.12652148366233</v>
       </c>
       <c r="F491" t="n">
         <v>4176830</v>
@@ -10252,16 +10252,16 @@
         <v>44945</v>
       </c>
       <c r="B492" t="n">
-        <v>11.93127155303955</v>
+        <v>11.93127059936523</v>
       </c>
       <c r="C492" t="n">
-        <v>12.30740353426755</v>
+        <v>12.30740255052876</v>
       </c>
       <c r="D492" t="n">
-        <v>11.33645767814233</v>
+        <v>11.33645677201188</v>
       </c>
       <c r="E492" t="n">
-        <v>11.49390776570111</v>
+        <v>11.49390684698556</v>
       </c>
       <c r="F492" t="n">
         <v>5394988</v>
@@ -10272,16 +10272,16 @@
         <v>44946</v>
       </c>
       <c r="B493" t="n">
-        <v>11.86129379272461</v>
+        <v>11.86129283905029</v>
       </c>
       <c r="C493" t="n">
-        <v>12.0187438835161</v>
+        <v>12.01874291718245</v>
       </c>
       <c r="D493" t="n">
-        <v>11.51140292410906</v>
+        <v>11.51140199856674</v>
       </c>
       <c r="E493" t="n">
-        <v>11.92252475789698</v>
+        <v>11.92252379929955</v>
       </c>
       <c r="F493" t="n">
         <v>2495174</v>
@@ -10312,16 +10312,16 @@
         <v>44950</v>
       </c>
       <c r="B495" t="n">
-        <v>12.1237096786499</v>
+        <v>12.12371063232422</v>
       </c>
       <c r="C495" t="n">
-        <v>12.25491947817606</v>
+        <v>12.25492044217159</v>
       </c>
       <c r="D495" t="n">
-        <v>11.55513781094744</v>
+        <v>11.5551387198968</v>
       </c>
       <c r="E495" t="n">
-        <v>11.67759972904172</v>
+        <v>11.67760064762417</v>
       </c>
       <c r="F495" t="n">
         <v>5075153</v>
@@ -10332,16 +10332,16 @@
         <v>44951</v>
       </c>
       <c r="B496" t="n">
-        <v>12.24617195129395</v>
+        <v>12.24617099761963</v>
       </c>
       <c r="C496" t="n">
-        <v>12.44735975492869</v>
+        <v>12.44735878558682</v>
       </c>
       <c r="D496" t="n">
-        <v>11.96625995005467</v>
+        <v>11.96625901817858</v>
       </c>
       <c r="E496" t="n">
-        <v>12.10621595067431</v>
+        <v>12.10621500789911</v>
       </c>
       <c r="F496" t="n">
         <v>2519909</v>
@@ -10352,16 +10352,16 @@
         <v>44952</v>
       </c>
       <c r="B497" t="n">
-        <v>12.42986392974854</v>
+        <v>12.42986488342285</v>
       </c>
       <c r="C497" t="n">
-        <v>12.56981992018939</v>
+        <v>12.56982088460175</v>
       </c>
       <c r="D497" t="n">
-        <v>12.18494010428189</v>
+        <v>12.18494103916456</v>
       </c>
       <c r="E497" t="n">
-        <v>12.272413019405</v>
+        <v>12.27241396099898</v>
       </c>
       <c r="F497" t="n">
         <v>2815211</v>
@@ -10372,16 +10372,16 @@
         <v>44953</v>
       </c>
       <c r="B498" t="n">
-        <v>12.43861389160156</v>
+        <v>12.43861293792725</v>
       </c>
       <c r="C498" t="n">
-        <v>12.67478987552819</v>
+        <v>12.67478890374615</v>
       </c>
       <c r="D498" t="n">
-        <v>12.25492099177236</v>
+        <v>12.25492005218186</v>
       </c>
       <c r="E498" t="n">
-        <v>12.41237108625991</v>
+        <v>12.41237013459764</v>
       </c>
       <c r="F498" t="n">
         <v>1981500</v>
@@ -10392,16 +10392,16 @@
         <v>44956</v>
       </c>
       <c r="B499" t="n">
-        <v>12.48234748840332</v>
+        <v>12.48234844207764</v>
       </c>
       <c r="C499" t="n">
-        <v>12.81474424186402</v>
+        <v>12.81474522093406</v>
       </c>
       <c r="D499" t="n">
-        <v>12.3948754120883</v>
+        <v>12.39487635907959</v>
       </c>
       <c r="E499" t="n">
-        <v>12.46485341001839</v>
+        <v>12.46485436235613</v>
       </c>
       <c r="F499" t="n">
         <v>2566955</v>
@@ -10472,16 +10472,16 @@
         <v>44960</v>
       </c>
       <c r="B503" t="n">
-        <v>12.57856750488281</v>
+        <v>12.57856845855713</v>
       </c>
       <c r="C503" t="n">
-        <v>12.90221722066339</v>
+        <v>12.90221819887599</v>
       </c>
       <c r="D503" t="n">
-        <v>12.42986446913531</v>
+        <v>12.42986541153535</v>
       </c>
       <c r="E503" t="n">
-        <v>12.81474430174445</v>
+        <v>12.81474527332507</v>
       </c>
       <c r="F503" t="n">
         <v>2892746</v>
@@ -10492,16 +10492,16 @@
         <v>44963</v>
       </c>
       <c r="B504" t="n">
-        <v>12.75351428985596</v>
+        <v>12.75351333618164</v>
       </c>
       <c r="C504" t="n">
-        <v>12.83224017538812</v>
+        <v>12.83223921582688</v>
       </c>
       <c r="D504" t="n">
-        <v>12.33364542693687</v>
+        <v>12.33364450465924</v>
       </c>
       <c r="E504" t="n">
-        <v>12.53483239741585</v>
+        <v>12.53483146009399</v>
       </c>
       <c r="F504" t="n">
         <v>1342942</v>
@@ -10512,16 +10512,16 @@
         <v>44964</v>
       </c>
       <c r="B505" t="n">
-        <v>12.76226139068604</v>
+        <v>12.76226043701172</v>
       </c>
       <c r="C505" t="n">
-        <v>12.93720640015643</v>
+        <v>12.93720543340915</v>
       </c>
       <c r="D505" t="n">
-        <v>12.52608541735219</v>
+        <v>12.52608448132639</v>
       </c>
       <c r="E505" t="n">
-        <v>12.85848135644357</v>
+        <v>12.8584803955791</v>
       </c>
       <c r="F505" t="n">
         <v>2203204</v>
@@ -10532,16 +10532,16 @@
         <v>44965</v>
       </c>
       <c r="B506" t="n">
-        <v>12.7710075378418</v>
+        <v>12.77100849151611</v>
       </c>
       <c r="C506" t="n">
-        <v>12.98094237672584</v>
+        <v>12.98094334607703</v>
       </c>
       <c r="D506" t="n">
-        <v>12.56982058046619</v>
+        <v>12.56982151911688</v>
       </c>
       <c r="E506" t="n">
-        <v>12.85848045755975</v>
+        <v>12.8584814177661</v>
       </c>
       <c r="F506" t="n">
         <v>1737889</v>
@@ -10552,16 +10552,16 @@
         <v>44966</v>
       </c>
       <c r="B507" t="n">
-        <v>12.13245677947998</v>
+        <v>12.1324577331543</v>
       </c>
       <c r="C507" t="n">
-        <v>12.7797553723795</v>
+        <v>12.77975637693486</v>
       </c>
       <c r="D507" t="n">
-        <v>12.06247878084089</v>
+        <v>12.06247972901458</v>
       </c>
       <c r="E507" t="n">
-        <v>12.76226045162213</v>
+        <v>12.7622614548023</v>
       </c>
       <c r="F507" t="n">
         <v>2590377</v>
@@ -10572,16 +10572,16 @@
         <v>44967</v>
       </c>
       <c r="B508" t="n">
-        <v>12.40362358093262</v>
+        <v>12.4036226272583</v>
       </c>
       <c r="C508" t="n">
-        <v>12.47360158523591</v>
+        <v>12.47360062618121</v>
       </c>
       <c r="D508" t="n">
-        <v>11.97500767292852</v>
+        <v>11.97500675220909</v>
       </c>
       <c r="E508" t="n">
-        <v>12.03623863724271</v>
+        <v>12.03623771181543</v>
       </c>
       <c r="F508" t="n">
         <v>3559170</v>
@@ -10592,16 +10592,16 @@
         <v>44970</v>
       </c>
       <c r="B509" t="n">
-        <v>12.52608585357666</v>
+        <v>12.52608489990234</v>
       </c>
       <c r="C509" t="n">
-        <v>12.77100887536473</v>
+        <v>12.77100790304318</v>
       </c>
       <c r="D509" t="n">
-        <v>12.35113999581847</v>
+        <v>12.35113905546367</v>
       </c>
       <c r="E509" t="n">
-        <v>12.38612984112634</v>
+        <v>12.38612889810758</v>
       </c>
       <c r="F509" t="n">
         <v>2916169</v>
@@ -10632,16 +10632,16 @@
         <v>44972</v>
       </c>
       <c r="B511" t="n">
-        <v>12.75351428985596</v>
+        <v>12.75351333618164</v>
       </c>
       <c r="C511" t="n">
-        <v>12.94595337825676</v>
+        <v>12.94595241019235</v>
       </c>
       <c r="D511" t="n">
-        <v>11.91377656401778</v>
+        <v>11.91377567313685</v>
       </c>
       <c r="E511" t="n">
-        <v>12.24617250152178</v>
+        <v>12.24617158578515</v>
       </c>
       <c r="F511" t="n">
         <v>3838217</v>
@@ -10652,16 +10652,16 @@
         <v>44973</v>
       </c>
       <c r="B512" t="n">
-        <v>12.86722850799561</v>
+        <v>12.86722755432129</v>
       </c>
       <c r="C512" t="n">
-        <v>12.98969043678491</v>
+        <v>12.98968947403414</v>
       </c>
       <c r="D512" t="n">
-        <v>12.61355845261168</v>
+        <v>12.6135575177385</v>
       </c>
       <c r="E512" t="n">
-        <v>12.64854661261404</v>
+        <v>12.64854567514766</v>
       </c>
       <c r="F512" t="n">
         <v>1907195</v>
@@ -10712,16 +10712,16 @@
         <v>44980</v>
       </c>
       <c r="B515" t="n">
-        <v>12.28990936279297</v>
+        <v>12.28990840911865</v>
       </c>
       <c r="C515" t="n">
-        <v>12.77100834620573</v>
+        <v>12.77100735519902</v>
       </c>
       <c r="D515" t="n">
-        <v>12.24617247906799</v>
+        <v>12.24617152878757</v>
       </c>
       <c r="E515" t="n">
-        <v>12.57856841596253</v>
+        <v>12.5785674398888</v>
       </c>
       <c r="F515" t="n">
         <v>1820271</v>
@@ -10732,16 +10732,16 @@
         <v>44981</v>
       </c>
       <c r="B516" t="n">
-        <v>11.80881023406982</v>
+        <v>11.80880928039551</v>
       </c>
       <c r="C516" t="n">
-        <v>12.48234918747401</v>
+        <v>12.48234817940498</v>
       </c>
       <c r="D516" t="n">
-        <v>11.69509618250371</v>
+        <v>11.69509523801289</v>
       </c>
       <c r="E516" t="n">
-        <v>12.33364613218022</v>
+        <v>12.33364513612039</v>
       </c>
       <c r="F516" t="n">
         <v>3419242</v>
@@ -10772,16 +10772,16 @@
         <v>44985</v>
       </c>
       <c r="B518" t="n">
-        <v>11.61636924743652</v>
+        <v>11.61636829376221</v>
       </c>
       <c r="C518" t="n">
-        <v>11.86129309369166</v>
+        <v>11.86129211990972</v>
       </c>
       <c r="D518" t="n">
-        <v>11.4064352439566</v>
+        <v>11.40643430751733</v>
       </c>
       <c r="E518" t="n">
-        <v>11.7125892095803</v>
+        <v>11.71258824800656</v>
       </c>
       <c r="F518" t="n">
         <v>5639205</v>
@@ -10792,16 +10792,16 @@
         <v>44986</v>
       </c>
       <c r="B519" t="n">
-        <v>11.74757862091064</v>
+        <v>11.74757766723633</v>
       </c>
       <c r="C519" t="n">
-        <v>11.78256762271401</v>
+        <v>11.78256666619927</v>
       </c>
       <c r="D519" t="n">
-        <v>11.39768860287697</v>
+        <v>11.3976876776069</v>
       </c>
       <c r="E519" t="n">
-        <v>11.61636965359921</v>
+        <v>11.6163687105765</v>
       </c>
       <c r="F519" t="n">
         <v>4662539</v>
@@ -10812,16 +10812,16 @@
         <v>44987</v>
       </c>
       <c r="B520" t="n">
-        <v>11.80881023406982</v>
+        <v>11.80880928039551</v>
       </c>
       <c r="C520" t="n">
-        <v>11.9750082123251</v>
+        <v>11.9750072452287</v>
       </c>
       <c r="D520" t="n">
-        <v>11.67760125954223</v>
+        <v>11.67760031646429</v>
       </c>
       <c r="E520" t="n">
-        <v>11.76507334776376</v>
+        <v>11.76507239762161</v>
       </c>
       <c r="F520" t="n">
         <v>2331118</v>
@@ -10832,16 +10832,16 @@
         <v>44988</v>
       </c>
       <c r="B521" t="n">
-        <v>11.67759990692139</v>
+        <v>11.6776008605957</v>
       </c>
       <c r="C521" t="n">
-        <v>11.98375386462542</v>
+        <v>11.98375484330241</v>
       </c>
       <c r="D521" t="n">
-        <v>11.60762106537642</v>
+        <v>11.60762201333577</v>
       </c>
       <c r="E521" t="n">
-        <v>11.80006182688108</v>
+        <v>11.80006279055649</v>
       </c>
       <c r="F521" t="n">
         <v>1946973</v>
@@ -10852,16 +10852,16 @@
         <v>44991</v>
       </c>
       <c r="B522" t="n">
-        <v>12.13245677947998</v>
+        <v>12.1324577331543</v>
       </c>
       <c r="C522" t="n">
-        <v>12.2374246196338</v>
+        <v>12.23742558155914</v>
       </c>
       <c r="D522" t="n">
-        <v>11.68634682760701</v>
+        <v>11.68634774621477</v>
       </c>
       <c r="E522" t="n">
-        <v>11.68634682760701</v>
+        <v>11.68634774621477</v>
       </c>
       <c r="F522" t="n">
         <v>3047313</v>
@@ -10872,16 +10872,16 @@
         <v>44992</v>
       </c>
       <c r="B523" t="n">
-        <v>12.26366806030273</v>
+        <v>12.26366710662842</v>
       </c>
       <c r="C523" t="n">
-        <v>12.37738295346679</v>
+        <v>12.37738199094953</v>
       </c>
       <c r="D523" t="n">
-        <v>11.87004113878769</v>
+        <v>11.87004021572346</v>
       </c>
       <c r="E523" t="n">
-        <v>12.12371120393195</v>
+        <v>12.12371026114126</v>
       </c>
       <c r="F523" t="n">
         <v>2615617</v>
@@ -10892,16 +10892,16 @@
         <v>44993</v>
       </c>
       <c r="B524" t="n">
-        <v>12.68353652954102</v>
+        <v>12.6835355758667</v>
       </c>
       <c r="C524" t="n">
-        <v>12.75351453433644</v>
+        <v>12.75351357540048</v>
       </c>
       <c r="D524" t="n">
-        <v>12.17619473148127</v>
+        <v>12.17619381595395</v>
       </c>
       <c r="E524" t="n">
-        <v>12.28990962092029</v>
+        <v>12.28990869684275</v>
       </c>
       <c r="F524" t="n">
         <v>2396134</v>
@@ -10912,16 +10912,16 @@
         <v>44994</v>
       </c>
       <c r="B525" t="n">
-        <v>12.70977783203125</v>
+        <v>12.70977687835693</v>
       </c>
       <c r="C525" t="n">
-        <v>12.88472368872491</v>
+        <v>12.88472272192359</v>
       </c>
       <c r="D525" t="n">
-        <v>12.55232774008035</v>
+        <v>12.55232679822025</v>
       </c>
       <c r="E525" t="n">
-        <v>12.71852571440263</v>
+        <v>12.71852476007192</v>
       </c>
       <c r="F525" t="n">
         <v>3354932</v>
@@ -10932,16 +10932,16 @@
         <v>44995</v>
       </c>
       <c r="B526" t="n">
-        <v>12.59606266021729</v>
+        <v>12.5960636138916</v>
       </c>
       <c r="C526" t="n">
-        <v>12.78850258010713</v>
+        <v>12.78850354835147</v>
       </c>
       <c r="D526" t="n">
-        <v>12.31615066197402</v>
+        <v>12.31615159445562</v>
       </c>
       <c r="E526" t="n">
-        <v>12.6485457387903</v>
+        <v>12.64854669643821</v>
       </c>
       <c r="F526" t="n">
         <v>1798565</v>
@@ -11012,16 +11012,16 @@
         <v>45001</v>
       </c>
       <c r="B530" t="n">
-        <v>12.44736003875732</v>
+        <v>12.44735908508301</v>
       </c>
       <c r="C530" t="n">
-        <v>12.6310520832104</v>
+        <v>12.63105111546223</v>
       </c>
       <c r="D530" t="n">
-        <v>12.28990911337238</v>
+        <v>12.28990817176142</v>
       </c>
       <c r="E530" t="n">
-        <v>12.35113923339325</v>
+        <v>12.35113828709104</v>
       </c>
       <c r="F530" t="n">
         <v>3275478</v>
@@ -11032,16 +11032,16 @@
         <v>45002</v>
       </c>
       <c r="B531" t="n">
-        <v>11.73008251190186</v>
+        <v>11.73008346557617</v>
       </c>
       <c r="C531" t="n">
-        <v>12.42986416154627</v>
+        <v>12.42986517211394</v>
       </c>
       <c r="D531" t="n">
-        <v>11.52889556134252</v>
+        <v>11.52889649866001</v>
       </c>
       <c r="E531" t="n">
-        <v>12.26366620924963</v>
+        <v>12.26366720630515</v>
       </c>
       <c r="F531" t="n">
         <v>9035530</v>
@@ -11132,16 +11132,16 @@
         <v>45009</v>
       </c>
       <c r="B536" t="n">
-        <v>11.12652206420898</v>
+        <v>11.12652111053467</v>
       </c>
       <c r="C536" t="n">
-        <v>11.23148906280827</v>
+        <v>11.23148810013704</v>
       </c>
       <c r="D536" t="n">
-        <v>10.68041126741802</v>
+        <v>10.68041035198067</v>
       </c>
       <c r="E536" t="n">
-        <v>10.6891591489477</v>
+        <v>10.68915823276055</v>
       </c>
       <c r="F536" t="n">
         <v>2554134</v>
@@ -11172,16 +11172,16 @@
         <v>45013</v>
       </c>
       <c r="B538" t="n">
-        <v>11.56388759613037</v>
+        <v>11.56388664245605</v>
       </c>
       <c r="C538" t="n">
-        <v>11.77382162554307</v>
+        <v>11.77382065455549</v>
       </c>
       <c r="D538" t="n">
-        <v>11.3102158367482</v>
+        <v>11.31021490399421</v>
       </c>
       <c r="E538" t="n">
-        <v>11.3102158367482</v>
+        <v>11.31021490399421</v>
       </c>
       <c r="F538" t="n">
         <v>2291643</v>
@@ -11192,16 +11192,16 @@
         <v>45014</v>
       </c>
       <c r="B539" t="n">
-        <v>11.72133636474609</v>
+        <v>11.72133541107178</v>
       </c>
       <c r="C539" t="n">
-        <v>11.7650724053535</v>
+        <v>11.76507144812072</v>
       </c>
       <c r="D539" t="n">
-        <v>11.36269847361872</v>
+        <v>11.36269754912399</v>
       </c>
       <c r="E539" t="n">
-        <v>11.60762148009351</v>
+        <v>11.6076205356713</v>
       </c>
       <c r="F539" t="n">
         <v>3319697</v>
@@ -11232,16 +11232,16 @@
         <v>45016</v>
       </c>
       <c r="B541" t="n">
-        <v>11.67759990692139</v>
+        <v>11.6776008605957</v>
       </c>
       <c r="C541" t="n">
-        <v>12.14995266582512</v>
+        <v>12.14995365807506</v>
       </c>
       <c r="D541" t="n">
-        <v>11.66010498598634</v>
+        <v>11.6601059382319</v>
       </c>
       <c r="E541" t="n">
-        <v>12.00999582493039</v>
+        <v>12.00999680575047</v>
       </c>
       <c r="F541" t="n">
         <v>2337175</v>
@@ -11292,16 +11292,16 @@
         <v>45021</v>
       </c>
       <c r="B544" t="n">
-        <v>10.67166423797607</v>
+        <v>10.67166519165039</v>
       </c>
       <c r="C544" t="n">
-        <v>11.3539509927967</v>
+        <v>11.35395200744364</v>
       </c>
       <c r="D544" t="n">
-        <v>10.58419216015985</v>
+        <v>10.58419310601722</v>
       </c>
       <c r="E544" t="n">
-        <v>11.17900599496905</v>
+        <v>11.17900699398201</v>
       </c>
       <c r="F544" t="n">
         <v>4730079</v>
@@ -11312,16 +11312,16 @@
         <v>45022</v>
       </c>
       <c r="B545" t="n">
-        <v>10.8028736114502</v>
+        <v>10.80287265777588</v>
       </c>
       <c r="C545" t="n">
-        <v>11.10902928820433</v>
+        <v>11.10902830750268</v>
       </c>
       <c r="D545" t="n">
-        <v>10.46173145764599</v>
+        <v>10.4617305340876</v>
       </c>
       <c r="E545" t="n">
-        <v>10.71540152345793</v>
+        <v>10.71540057750562</v>
       </c>
       <c r="F545" t="n">
         <v>8557394</v>
@@ -11332,16 +11332,16 @@
         <v>45026</v>
       </c>
       <c r="B546" t="n">
-        <v>10.89909362792969</v>
+        <v>10.89909267425537</v>
       </c>
       <c r="C546" t="n">
-        <v>11.14401663548793</v>
+        <v>11.14401566038277</v>
       </c>
       <c r="D546" t="n">
-        <v>10.64542273845509</v>
+        <v>10.64542180697705</v>
       </c>
       <c r="E546" t="n">
-        <v>10.71540074061458</v>
+        <v>10.71539980301345</v>
       </c>
       <c r="F546" t="n">
         <v>4871319</v>
@@ -11352,16 +11352,16 @@
         <v>45027</v>
       </c>
       <c r="B547" t="n">
-        <v>11.85254573822021</v>
+        <v>11.85254669189453</v>
       </c>
       <c r="C547" t="n">
-        <v>11.87878685630945</v>
+        <v>11.87878781209517</v>
       </c>
       <c r="D547" t="n">
-        <v>10.96907118108362</v>
+        <v>10.9690720636722</v>
       </c>
       <c r="E547" t="n">
-        <v>10.96907118108362</v>
+        <v>10.9690720636722</v>
       </c>
       <c r="F547" t="n">
         <v>9432295</v>
@@ -11392,16 +11392,16 @@
         <v>45029</v>
       </c>
       <c r="B549" t="n">
-        <v>12.4561071395874</v>
+        <v>12.45610618591309</v>
       </c>
       <c r="C549" t="n">
-        <v>12.64854622467444</v>
+        <v>12.64854525626645</v>
       </c>
       <c r="D549" t="n">
-        <v>11.97500732138171</v>
+        <v>11.97500640454174</v>
       </c>
       <c r="E549" t="n">
-        <v>12.09746924641502</v>
+        <v>12.09746832019902</v>
       </c>
       <c r="F549" t="n">
         <v>4483641</v>
@@ -11412,16 +11412,16 @@
         <v>45030</v>
       </c>
       <c r="B550" t="n">
-        <v>12.52608585357666</v>
+        <v>12.52608489990234</v>
       </c>
       <c r="C550" t="n">
-        <v>12.72727283202282</v>
+        <v>12.72727186303112</v>
       </c>
       <c r="D550" t="n">
-        <v>12.22867890602208</v>
+        <v>12.22867797499086</v>
       </c>
       <c r="E550" t="n">
-        <v>12.42111800204363</v>
+        <v>12.42111705636105</v>
       </c>
       <c r="F550" t="n">
         <v>2806225</v>
@@ -11512,16 +11512,16 @@
         <v>45040</v>
       </c>
       <c r="B555" t="n">
-        <v>11.52889728546143</v>
+        <v>11.52889633178711</v>
       </c>
       <c r="C555" t="n">
-        <v>11.66885329944233</v>
+        <v>11.6688523341908</v>
       </c>
       <c r="D555" t="n">
-        <v>11.41518323465077</v>
+        <v>11.41518229038292</v>
       </c>
       <c r="E555" t="n">
-        <v>11.53764432578641</v>
+        <v>11.53764337138853</v>
       </c>
       <c r="F555" t="n">
         <v>1779282</v>
@@ -11572,16 +11572,16 @@
         <v>45043</v>
       </c>
       <c r="B558" t="n">
-        <v>10.78537845611572</v>
+        <v>10.78537750244141</v>
       </c>
       <c r="C558" t="n">
-        <v>11.51140210416322</v>
+        <v>11.5114010862918</v>
       </c>
       <c r="D558" t="n">
-        <v>10.56669657353309</v>
+        <v>10.56669563919525</v>
       </c>
       <c r="E558" t="n">
-        <v>11.37144526136882</v>
+        <v>11.37144425587279</v>
       </c>
       <c r="F558" t="n">
         <v>8945577</v>
@@ -11592,16 +11592,16 @@
         <v>45044</v>
       </c>
       <c r="B559" t="n">
-        <v>10.68915939331055</v>
+        <v>10.68916034698486</v>
       </c>
       <c r="C559" t="n">
-        <v>10.86410439497541</v>
+        <v>10.86410536425811</v>
       </c>
       <c r="D559" t="n">
-        <v>10.36551050858414</v>
+        <v>10.36551143338288</v>
       </c>
       <c r="E559" t="n">
-        <v>10.83786243417687</v>
+        <v>10.8378634011183</v>
       </c>
       <c r="F559" t="n">
         <v>8236247</v>
@@ -11612,16 +11612,16 @@
         <v>45048</v>
       </c>
       <c r="B560" t="n">
-        <v>10.15557670593262</v>
+        <v>10.1555757522583</v>
       </c>
       <c r="C560" t="n">
-        <v>10.65417064345897</v>
+        <v>10.65416964296346</v>
       </c>
       <c r="D560" t="n">
-        <v>10.02436773067856</v>
+        <v>10.02436678932562</v>
       </c>
       <c r="E560" t="n">
-        <v>10.592940518243</v>
+        <v>10.5929395234974</v>
       </c>
       <c r="F560" t="n">
         <v>7078259</v>
@@ -11632,16 +11632,16 @@
         <v>45049</v>
       </c>
       <c r="B561" t="n">
-        <v>10.12933349609375</v>
+        <v>10.12933444976807</v>
       </c>
       <c r="C561" t="n">
-        <v>10.29553229701482</v>
+        <v>10.29553326633671</v>
       </c>
       <c r="D561" t="n">
-        <v>9.875662617229723</v>
+        <v>9.875663547020988</v>
       </c>
       <c r="E561" t="n">
-        <v>10.12058645673849</v>
+        <v>10.12058740958928</v>
       </c>
       <c r="F561" t="n">
         <v>7064832</v>
@@ -11732,16 +11732,16 @@
         <v>45056</v>
       </c>
       <c r="B566" t="n">
-        <v>10.00449562072754</v>
+        <v>10.00449466705322</v>
       </c>
       <c r="C566" t="n">
-        <v>10.33739546432518</v>
+        <v>10.33739447891732</v>
       </c>
       <c r="D566" t="n">
-        <v>9.969454508577106</v>
+        <v>9.969453558243071</v>
       </c>
       <c r="E566" t="n">
-        <v>10.24979099700936</v>
+        <v>10.24979001995237</v>
       </c>
       <c r="F566" t="n">
         <v>5572472</v>
@@ -11812,16 +11812,16 @@
         <v>45062</v>
       </c>
       <c r="B570" t="n">
-        <v>9.951933860778809</v>
+        <v>9.951932907104492</v>
       </c>
       <c r="C570" t="n">
-        <v>10.35491592496318</v>
+        <v>10.35491493267188</v>
       </c>
       <c r="D570" t="n">
-        <v>9.864328550800552</v>
+        <v>9.864327605521281</v>
       </c>
       <c r="E570" t="n">
-        <v>10.17970614847653</v>
+        <v>10.17970517297524</v>
       </c>
       <c r="F570" t="n">
         <v>2372207</v>
@@ -11872,16 +11872,16 @@
         <v>45065</v>
       </c>
       <c r="B573" t="n">
-        <v>11.44121742248535</v>
+        <v>11.44121837615967</v>
       </c>
       <c r="C573" t="n">
-        <v>12.00188946999683</v>
+        <v>12.00189047040555</v>
       </c>
       <c r="D573" t="n">
-        <v>10.51260363211687</v>
+        <v>10.51260450838727</v>
       </c>
       <c r="E573" t="n">
-        <v>10.60897004964872</v>
+        <v>10.60897093395166</v>
       </c>
       <c r="F573" t="n">
         <v>14298668</v>
@@ -11932,16 +11932,16 @@
         <v>45070</v>
       </c>
       <c r="B576" t="n">
-        <v>10.93310928344727</v>
+        <v>10.93310832977295</v>
       </c>
       <c r="C576" t="n">
-        <v>11.28353051793955</v>
+        <v>11.28352953369865</v>
       </c>
       <c r="D576" t="n">
-        <v>10.92434900562591</v>
+        <v>10.92434805271574</v>
       </c>
       <c r="E576" t="n">
-        <v>11.0820382237595</v>
+        <v>11.0820372570944</v>
       </c>
       <c r="F576" t="n">
         <v>2685985</v>
@@ -11972,16 +11972,16 @@
         <v>45072</v>
       </c>
       <c r="B578" t="n">
-        <v>11.67775058746338</v>
+        <v>11.6777515411377</v>
       </c>
       <c r="C578" t="n">
-        <v>11.90552368174234</v>
+        <v>11.90552465401795</v>
       </c>
       <c r="D578" t="n">
-        <v>11.47625916626848</v>
+        <v>11.47626010348781</v>
       </c>
       <c r="E578" t="n">
-        <v>11.54634306551281</v>
+        <v>11.54634400845561</v>
       </c>
       <c r="F578" t="n">
         <v>3617321</v>
@@ -12172,16 +12172,16 @@
         <v>45089</v>
       </c>
       <c r="B588" t="n">
-        <v>12.80785655975342</v>
+        <v>12.80785751342773</v>
       </c>
       <c r="C588" t="n">
-        <v>12.97430688489936</v>
+        <v>12.97430785096759</v>
       </c>
       <c r="D588" t="n">
-        <v>12.72025125864552</v>
+        <v>12.72025220579673</v>
       </c>
       <c r="E588" t="n">
-        <v>12.79909628268356</v>
+        <v>12.79909723570558</v>
       </c>
       <c r="F588" t="n">
         <v>2677201</v>
@@ -12192,16 +12192,16 @@
         <v>45090</v>
       </c>
       <c r="B589" t="n">
-        <v>12.52752208709717</v>
+        <v>12.52752113342285</v>
       </c>
       <c r="C589" t="n">
-        <v>13.04439113335547</v>
+        <v>13.04439014033381</v>
       </c>
       <c r="D589" t="n">
-        <v>12.29974811477101</v>
+        <v>12.29974717843629</v>
       </c>
       <c r="E589" t="n">
-        <v>12.86042108077874</v>
+        <v>12.86042010176204</v>
       </c>
       <c r="F589" t="n">
         <v>6116837</v>
@@ -12212,16 +12212,16 @@
         <v>45091</v>
       </c>
       <c r="B590" t="n">
-        <v>12.88670063018799</v>
+        <v>12.8867015838623</v>
       </c>
       <c r="C590" t="n">
-        <v>12.93926397909746</v>
+        <v>12.9392649366617</v>
       </c>
       <c r="D590" t="n">
-        <v>12.46619721279127</v>
+        <v>12.46619813534643</v>
       </c>
       <c r="E590" t="n">
-        <v>12.58884362113043</v>
+        <v>12.58884455276198</v>
       </c>
       <c r="F590" t="n">
         <v>4237809</v>
@@ -12232,16 +12232,16 @@
         <v>45092</v>
       </c>
       <c r="B591" t="n">
-        <v>12.83413791656494</v>
+        <v>12.83413887023926</v>
       </c>
       <c r="C591" t="n">
-        <v>13.0794315727341</v>
+        <v>13.07943254463561</v>
       </c>
       <c r="D591" t="n">
-        <v>12.77281429165521</v>
+        <v>12.77281524077272</v>
       </c>
       <c r="E591" t="n">
-        <v>12.86917986744625</v>
+        <v>12.86918082372445</v>
       </c>
       <c r="F591" t="n">
         <v>4574806</v>
@@ -12252,16 +12252,16 @@
         <v>45093</v>
       </c>
       <c r="B592" t="n">
-        <v>11.92304420471191</v>
+        <v>11.92304515838623</v>
       </c>
       <c r="C592" t="n">
-        <v>12.76405352392952</v>
+        <v>12.76405454487264</v>
       </c>
       <c r="D592" t="n">
-        <v>11.66023000494414</v>
+        <v>11.66023093759705</v>
       </c>
       <c r="E592" t="n">
-        <v>12.76405352392952</v>
+        <v>12.76405454487264</v>
       </c>
       <c r="F592" t="n">
         <v>19648730</v>
@@ -12312,16 +12312,16 @@
         <v>45098</v>
       </c>
       <c r="B595" t="n">
-        <v>10.94939422607422</v>
+        <v>10.9493932723999</v>
       </c>
       <c r="C595" t="n">
-        <v>10.99361650351154</v>
+        <v>10.99361554598554</v>
       </c>
       <c r="D595" t="n">
-        <v>10.5248615435336</v>
+        <v>10.52486062683539</v>
       </c>
       <c r="E595" t="n">
-        <v>10.93170497771137</v>
+        <v>10.93170402557776</v>
       </c>
       <c r="F595" t="n">
         <v>15399400</v>
@@ -12532,16 +12532,16 @@
         <v>45113</v>
       </c>
       <c r="B606" t="n">
-        <v>10.34797286987305</v>
+        <v>10.34797382354736</v>
       </c>
       <c r="C606" t="n">
-        <v>10.56908340488516</v>
+        <v>10.56908437893714</v>
       </c>
       <c r="D606" t="n">
-        <v>10.19761763858723</v>
+        <v>10.19761857840473</v>
       </c>
       <c r="E606" t="n">
-        <v>10.51601734882532</v>
+        <v>10.5160183179867</v>
       </c>
       <c r="F606" t="n">
         <v>6243800</v>
@@ -12732,16 +12732,16 @@
         <v>45127</v>
       </c>
       <c r="B616" t="n">
-        <v>10.19761753082275</v>
+        <v>10.19761848449707</v>
       </c>
       <c r="C616" t="n">
-        <v>10.22415140204203</v>
+        <v>10.22415235819778</v>
       </c>
       <c r="D616" t="n">
-        <v>9.914596318908426</v>
+        <v>9.91459724611479</v>
       </c>
       <c r="E616" t="n">
-        <v>10.07379617234511</v>
+        <v>10.07379711443973</v>
       </c>
       <c r="F616" t="n">
         <v>5709500</v>
@@ -12792,16 +12792,16 @@
         <v>45132</v>
       </c>
       <c r="B619" t="n">
-        <v>10.53370666503906</v>
+        <v>10.53370571136475</v>
       </c>
       <c r="C619" t="n">
-        <v>10.82557252904746</v>
+        <v>10.82557154894893</v>
       </c>
       <c r="D619" t="n">
-        <v>10.46295135518671</v>
+        <v>10.46295040791826</v>
       </c>
       <c r="E619" t="n">
-        <v>10.61330659949041</v>
+        <v>10.61330563860948</v>
       </c>
       <c r="F619" t="n">
         <v>5058400</v>
@@ -12932,16 +12932,16 @@
         <v>45141</v>
       </c>
       <c r="B626" t="n">
-        <v>10.64868354797363</v>
+        <v>10.64868450164795</v>
       </c>
       <c r="C626" t="n">
-        <v>10.84326105889407</v>
+        <v>10.84326202999435</v>
       </c>
       <c r="D626" t="n">
-        <v>10.50717293765687</v>
+        <v>10.50717387865778</v>
       </c>
       <c r="E626" t="n">
-        <v>10.63099514341892</v>
+        <v>10.6309960955091</v>
       </c>
       <c r="F626" t="n">
         <v>7397700</v>
@@ -12952,16 +12952,16 @@
         <v>45142</v>
       </c>
       <c r="B627" t="n">
-        <v>10.71943855285645</v>
+        <v>10.71943950653076</v>
       </c>
       <c r="C627" t="n">
-        <v>11.21472651856076</v>
+        <v>11.21472751629927</v>
       </c>
       <c r="D627" t="n">
-        <v>10.59561635056293</v>
+        <v>10.59561729322118</v>
       </c>
       <c r="E627" t="n">
-        <v>10.70175014879723</v>
+        <v>10.70175110089786</v>
       </c>
       <c r="F627" t="n">
         <v>16706200</v>
@@ -12992,16 +12992,16 @@
         <v>45146</v>
       </c>
       <c r="B629" t="n">
-        <v>10.53370666503906</v>
+        <v>10.53370571136475</v>
       </c>
       <c r="C629" t="n">
-        <v>10.59561735029241</v>
+        <v>10.59561639101298</v>
       </c>
       <c r="D629" t="n">
-        <v>10.00304184114644</v>
+        <v>10.00304093551612</v>
       </c>
       <c r="E629" t="n">
-        <v>10.24184080103066</v>
+        <v>10.24183987378056</v>
       </c>
       <c r="F629" t="n">
         <v>6465200</v>
@@ -13012,16 +13012,16 @@
         <v>45147</v>
       </c>
       <c r="B630" t="n">
-        <v>10.5425500869751</v>
+        <v>10.54255104064941</v>
       </c>
       <c r="C630" t="n">
-        <v>10.68406069053669</v>
+        <v>10.68406165701199</v>
       </c>
       <c r="D630" t="n">
-        <v>10.36566183252311</v>
+        <v>10.3656627701962</v>
       </c>
       <c r="E630" t="n">
-        <v>10.53370546338507</v>
+        <v>10.5337064162593</v>
       </c>
       <c r="F630" t="n">
         <v>5435200</v>
@@ -13032,16 +13032,16 @@
         <v>45148</v>
       </c>
       <c r="B631" t="n">
-        <v>10.63099479675293</v>
+        <v>10.63099575042725</v>
       </c>
       <c r="C631" t="n">
-        <v>10.86094910928421</v>
+        <v>10.86095008358703</v>
       </c>
       <c r="D631" t="n">
-        <v>10.5248609990065</v>
+        <v>10.52486194315988</v>
       </c>
       <c r="E631" t="n">
-        <v>10.66637244817849</v>
+        <v>10.66637340502643</v>
       </c>
       <c r="F631" t="n">
         <v>4975000</v>
@@ -13112,16 +13112,16 @@
         <v>45154</v>
       </c>
       <c r="B635" t="n">
-        <v>10.38335132598877</v>
+        <v>10.38335037231445</v>
       </c>
       <c r="C635" t="n">
-        <v>10.48064050875037</v>
+        <v>10.48063954614038</v>
       </c>
       <c r="D635" t="n">
-        <v>10.25952995661192</v>
+        <v>10.25952901431016</v>
       </c>
       <c r="E635" t="n">
-        <v>10.46295125971378</v>
+        <v>10.46295029872849</v>
       </c>
       <c r="F635" t="n">
         <v>5623400</v>
@@ -13172,16 +13172,16 @@
         <v>45159</v>
       </c>
       <c r="B638" t="n">
-        <v>10.14455223083496</v>
+        <v>10.14455127716064</v>
       </c>
       <c r="C638" t="n">
-        <v>10.34797353118066</v>
+        <v>10.34797255838301</v>
       </c>
       <c r="D638" t="n">
-        <v>10.09148532791402</v>
+        <v>10.09148437922844</v>
       </c>
       <c r="E638" t="n">
-        <v>10.2595298176055</v>
+        <v>10.25952885312231</v>
       </c>
       <c r="F638" t="n">
         <v>3931700</v>
@@ -13192,16 +13192,16 @@
         <v>45160</v>
       </c>
       <c r="B639" t="n">
-        <v>10.63099479675293</v>
+        <v>10.63099575042725</v>
       </c>
       <c r="C639" t="n">
-        <v>10.70175009960405</v>
+        <v>10.70175105962561</v>
       </c>
       <c r="D639" t="n">
-        <v>10.18877373219854</v>
+        <v>10.18877464620255</v>
       </c>
       <c r="E639" t="n">
-        <v>10.24183978760201</v>
+        <v>10.24184070636641</v>
       </c>
       <c r="F639" t="n">
         <v>5680500</v>
@@ -13232,16 +13232,16 @@
         <v>45162</v>
       </c>
       <c r="B641" t="n">
-        <v>10.73712730407715</v>
+        <v>10.73712825775146</v>
       </c>
       <c r="C641" t="n">
-        <v>10.99361547710312</v>
+        <v>10.99361645355878</v>
       </c>
       <c r="D641" t="n">
-        <v>10.64868275746004</v>
+        <v>10.64868370327869</v>
       </c>
       <c r="E641" t="n">
-        <v>10.85210487729151</v>
+        <v>10.85210584117816</v>
       </c>
       <c r="F641" t="n">
         <v>5730800</v>
@@ -13252,16 +13252,16 @@
         <v>45163</v>
       </c>
       <c r="B642" t="n">
-        <v>10.29490756988525</v>
+        <v>10.29490661621094</v>
       </c>
       <c r="C642" t="n">
-        <v>10.82557238680523</v>
+        <v>10.82557138397249</v>
       </c>
       <c r="D642" t="n">
-        <v>10.25068529094114</v>
+        <v>10.25068434136337</v>
       </c>
       <c r="E642" t="n">
-        <v>10.72828404790402</v>
+        <v>10.72828305408364</v>
       </c>
       <c r="F642" t="n">
         <v>6496000</v>
@@ -13312,16 +13312,16 @@
         <v>45168</v>
       </c>
       <c r="B645" t="n">
-        <v>10.53370666503906</v>
+        <v>10.53370571136475</v>
       </c>
       <c r="C645" t="n">
-        <v>10.59561735029241</v>
+        <v>10.59561639101298</v>
       </c>
       <c r="D645" t="n">
-        <v>10.40104066993336</v>
+        <v>10.40103972827003</v>
       </c>
       <c r="E645" t="n">
-        <v>10.52486204044006</v>
+        <v>10.5248610875665</v>
       </c>
       <c r="F645" t="n">
         <v>3749300</v>
@@ -13352,16 +13352,16 @@
         <v>45170</v>
       </c>
       <c r="B647" t="n">
-        <v>10.57792854309082</v>
+        <v>10.5779275894165</v>
       </c>
       <c r="C647" t="n">
-        <v>10.64868385025773</v>
+        <v>10.64868289020433</v>
       </c>
       <c r="D647" t="n">
-        <v>10.436417928757</v>
+        <v>10.43641698784085</v>
       </c>
       <c r="E647" t="n">
-        <v>10.436417928757</v>
+        <v>10.43641698784085</v>
       </c>
       <c r="F647" t="n">
         <v>11645200</v>
@@ -13372,16 +13372,16 @@
         <v>45173</v>
       </c>
       <c r="B648" t="n">
-        <v>10.78134918212891</v>
+        <v>10.78135013580322</v>
       </c>
       <c r="C648" t="n">
-        <v>10.90517138384658</v>
+        <v>10.9051723484737</v>
       </c>
       <c r="D648" t="n">
-        <v>10.56908327358697</v>
+        <v>10.5690842084851</v>
       </c>
       <c r="E648" t="n">
-        <v>10.57792789731032</v>
+        <v>10.57792883299081</v>
       </c>
       <c r="F648" t="n">
         <v>4629200</v>
@@ -13412,16 +13412,16 @@
         <v>45175</v>
       </c>
       <c r="B650" t="n">
-        <v>9.49006462097168</v>
+        <v>9.490063667297363</v>
       </c>
       <c r="C650" t="n">
-        <v>10.02073029065247</v>
+        <v>10.02072928365057</v>
       </c>
       <c r="D650" t="n">
-        <v>9.419309310810219</v>
+        <v>9.419308364246236</v>
       </c>
       <c r="E650" t="n">
-        <v>10.01188566601482</v>
+        <v>10.01188465990174</v>
       </c>
       <c r="F650" t="n">
         <v>30094100</v>
@@ -13532,16 +13532,16 @@
         <v>45184</v>
       </c>
       <c r="B656" t="n">
-        <v>9.375086784362793</v>
+        <v>9.375087738037109</v>
       </c>
       <c r="C656" t="n">
-        <v>10.00304072162537</v>
+        <v>10.00304173917788</v>
       </c>
       <c r="D656" t="n">
-        <v>9.375086784362793</v>
+        <v>9.375087738037109</v>
       </c>
       <c r="E656" t="n">
-        <v>9.923440796082692</v>
+        <v>9.923441805537948</v>
       </c>
       <c r="F656" t="n">
         <v>14904000</v>
@@ -13672,16 +13672,16 @@
         <v>45195</v>
       </c>
       <c r="B663" t="n">
-        <v>8.499488830566406</v>
+        <v>8.49948787689209</v>
       </c>
       <c r="C663" t="n">
-        <v>8.623311036274854</v>
+        <v>8.623310068707225</v>
       </c>
       <c r="D663" t="n">
-        <v>8.499488830566406</v>
+        <v>8.49948787689209</v>
       </c>
       <c r="E663" t="n">
-        <v>8.561400355155516</v>
+        <v>8.561399394534495</v>
       </c>
       <c r="F663" t="n">
         <v>4158300</v>
@@ -13712,16 +13712,16 @@
         <v>45197</v>
       </c>
       <c r="B665" t="n">
-        <v>8.561399459838867</v>
+        <v>8.561400413513184</v>
       </c>
       <c r="C665" t="n">
-        <v>8.676377029515013</v>
+        <v>8.676377995996951</v>
       </c>
       <c r="D665" t="n">
-        <v>8.331444320486574</v>
+        <v>8.33144524854565</v>
       </c>
       <c r="E665" t="n">
-        <v>8.375666592434273</v>
+        <v>8.375667525419372</v>
       </c>
       <c r="F665" t="n">
         <v>5776700</v>
@@ -13772,16 +13772,16 @@
         <v>45202</v>
       </c>
       <c r="B668" t="n">
-        <v>7.659268379211426</v>
+        <v>7.659268856048584</v>
       </c>
       <c r="C668" t="n">
-        <v>7.933445798766693</v>
+        <v>7.933446292673103</v>
       </c>
       <c r="D668" t="n">
-        <v>7.570824676122735</v>
+        <v>7.570825147453722</v>
       </c>
       <c r="E668" t="n">
-        <v>7.880378902137712</v>
+        <v>7.880379392740378</v>
       </c>
       <c r="F668" t="n">
         <v>18608300</v>
@@ -13792,16 +13792,16 @@
         <v>45203</v>
       </c>
       <c r="B669" t="n">
-        <v>7.738868236541748</v>
+        <v>7.738868713378906</v>
       </c>
       <c r="C669" t="n">
-        <v>7.853845808701018</v>
+        <v>7.85384629262262</v>
       </c>
       <c r="D669" t="n">
-        <v>7.632735287656968</v>
+        <v>7.632735757954652</v>
       </c>
       <c r="E669" t="n">
-        <v>7.756557483090727</v>
+        <v>7.756557961017825</v>
       </c>
       <c r="F669" t="n">
         <v>14186500</v>
@@ -13852,16 +13852,16 @@
         <v>45208</v>
       </c>
       <c r="B672" t="n">
-        <v>7.71233606338501</v>
+        <v>7.712335586547852</v>
       </c>
       <c r="C672" t="n">
-        <v>7.809624399758072</v>
+        <v>7.809623916905786</v>
       </c>
       <c r="D672" t="n">
-        <v>7.385092557254024</v>
+        <v>7.385092100649629</v>
       </c>
       <c r="E672" t="n">
-        <v>7.393936338037181</v>
+        <v>7.393935880885993</v>
       </c>
       <c r="F672" t="n">
         <v>4734000</v>
@@ -13872,16 +13872,16 @@
         <v>45209</v>
       </c>
       <c r="B673" t="n">
-        <v>8.101489067077637</v>
+        <v>8.101490020751953</v>
       </c>
       <c r="C673" t="n">
-        <v>8.189933609727872</v>
+        <v>8.18993457381352</v>
       </c>
       <c r="D673" t="n">
-        <v>7.906911579328923</v>
+        <v>7.906912510098369</v>
       </c>
       <c r="E673" t="n">
-        <v>7.95113385065404</v>
+        <v>7.951134786629153</v>
       </c>
       <c r="F673" t="n">
         <v>9907700</v>
@@ -13892,16 +13892,16 @@
         <v>45210</v>
       </c>
       <c r="B674" t="n">
-        <v>7.933446407318115</v>
+        <v>7.933445930480957</v>
       </c>
       <c r="C674" t="n">
-        <v>8.22531225249141</v>
+        <v>8.225311758111753</v>
       </c>
       <c r="D674" t="n">
-        <v>7.818468825360488</v>
+        <v>7.818468355434018</v>
       </c>
       <c r="E674" t="n">
-        <v>8.207623004434957</v>
+        <v>8.207622511118506</v>
       </c>
       <c r="F674" t="n">
         <v>7415900</v>
@@ -14012,16 +14012,16 @@
         <v>45219</v>
       </c>
       <c r="B680" t="n">
-        <v>7.102070331573486</v>
+        <v>7.102070808410645</v>
       </c>
       <c r="C680" t="n">
-        <v>7.163981856532952</v>
+        <v>7.163982337526886</v>
       </c>
       <c r="D680" t="n">
-        <v>6.916337865369526</v>
+        <v>6.916338329736497</v>
       </c>
       <c r="E680" t="n">
-        <v>7.013626199634722</v>
+        <v>7.013626670533689</v>
       </c>
       <c r="F680" t="n">
         <v>6704900</v>
@@ -14092,16 +14092,16 @@
         <v>45225</v>
       </c>
       <c r="B684" t="n">
-        <v>7.102070331573486</v>
+        <v>7.102070808410645</v>
       </c>
       <c r="C684" t="n">
-        <v>7.137447984348992</v>
+        <v>7.137448463561426</v>
       </c>
       <c r="D684" t="n">
-        <v>6.783671456593937</v>
+        <v>6.783671912053608</v>
       </c>
       <c r="E684" t="n">
-        <v>6.854426762144948</v>
+        <v>6.854427222355172</v>
       </c>
       <c r="F684" t="n">
         <v>6790200</v>
@@ -14172,16 +14172,16 @@
         <v>45231</v>
       </c>
       <c r="B688" t="n">
-        <v>7.013626575469971</v>
+        <v>7.013626098632812</v>
       </c>
       <c r="C688" t="n">
-        <v>7.402781198588827</v>
+        <v>7.402780695294118</v>
       </c>
       <c r="D688" t="n">
-        <v>6.916338235991438</v>
+        <v>6.916337765768647</v>
       </c>
       <c r="E688" t="n">
-        <v>6.969404717998341</v>
+        <v>6.969404244167705</v>
       </c>
       <c r="F688" t="n">
         <v>11133300</v>
@@ -14192,16 +14192,16 @@
         <v>45233</v>
       </c>
       <c r="B689" t="n">
-        <v>8.030734062194824</v>
+        <v>8.030735015869141</v>
       </c>
       <c r="C689" t="n">
-        <v>8.030734062194824</v>
+        <v>8.030735015869141</v>
       </c>
       <c r="D689" t="n">
-        <v>7.23473652329359</v>
+        <v>7.234737382440756</v>
       </c>
       <c r="E689" t="n">
-        <v>7.305491822597268</v>
+        <v>7.305492690146844</v>
       </c>
       <c r="F689" t="n">
         <v>15995000</v>
@@ -14212,16 +14212,16 @@
         <v>45236</v>
       </c>
       <c r="B690" t="n">
-        <v>7.915757179260254</v>
+        <v>7.915756702423096</v>
       </c>
       <c r="C690" t="n">
-        <v>8.119179315074533</v>
+        <v>8.119178825983433</v>
       </c>
       <c r="D690" t="n">
-        <v>7.791935816431346</v>
+        <v>7.791935347053061</v>
       </c>
       <c r="E690" t="n">
-        <v>